--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -453,219 +453,19 @@
           <t>Article Descriptors</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Unnamed: 7</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Unnamed: 8</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Unnamed: 9</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Unnamed: 10</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Unnamed: 11</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Unnamed: 12</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Unnamed: 13</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Unnamed: 14</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Unnamed: 15</t>
-        </is>
-      </c>
       <c r="Q1" t="inlineStr">
         <is>
           <t>Study/Sample Descriptors</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Unnamed: 17</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Unnamed: 18</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Unnamed: 19</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Unnamed: 20</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Unnamed: 21</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Unnamed: 22</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Unnamed: 23</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Unnamed: 24</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Unnamed: 25</t>
-        </is>
-      </c>
       <c r="AA1" t="inlineStr">
         <is>
           <t>Measure Descriptors</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Unnamed: 27</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Unnamed: 28</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Unnamed: 29</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Unnamed: 30</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>Unnamed: 31</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>Unnamed: 32</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>Unnamed: 33</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>Unnamed: 34</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 35</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>Unnamed: 36</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>Unnamed: 37</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>Unnamed: 38</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>Unnamed: 39</t>
-        </is>
-      </c>
       <c r="AO1" t="inlineStr">
         <is>
           <t>Effect Size</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>Unnamed: 41</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>Unnamed: 42</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Unnamed: 43</t>
-        </is>
-      </c>
-      <c r="AS1" t="inlineStr">
-        <is>
-          <t>Unnamed: 44</t>
-        </is>
-      </c>
-      <c r="AT1" t="inlineStr">
-        <is>
-          <t>Unnamed: 45</t>
-        </is>
-      </c>
-      <c r="AU1" t="inlineStr">
-        <is>
-          <t>Unnamed: 46</t>
-        </is>
-      </c>
-      <c r="AV1" t="inlineStr">
-        <is>
-          <t>Unnamed: 47</t>
-        </is>
-      </c>
-      <c r="AW1" t="inlineStr">
-        <is>
-          <t>Unnamed: 48</t>
-        </is>
-      </c>
-      <c r="AX1" t="inlineStr">
-        <is>
-          <t>Unnamed: 49</t>
         </is>
       </c>
     </row>
@@ -36188,6 +35988,24 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="AA2:AG2"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="AW2:AW3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="Q1:Z2"/>
+    <mergeCell ref="AO1:AX1"/>
+    <mergeCell ref="G1:P2"/>
+    <mergeCell ref="AH2:AN2"/>
+    <mergeCell ref="AO2:AR2"/>
+    <mergeCell ref="AS2:AV2"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="AX2:AX3"/>
+    <mergeCell ref="AA1:AN1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,132 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA4C2F4"/>
+        <bgColor rgb="FFA4C2F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7F340D"/>
+        <bgColor rgb="FF7F340D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF215E99"/>
+        <bgColor rgb="FF215E99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF12501B"/>
+        <bgColor rgb="FF12501B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78206E"/>
+        <bgColor rgb="FF78206E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47D45A"/>
+        <bgColor rgb="FF47D45A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9300"/>
+        <bgColor rgb="FFFF9300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD76DCC"/>
+        <bgColor rgb="FFD76DCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60CBF3"/>
+        <bgColor rgb="FF60CBF3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAEDFB"/>
+        <bgColor rgb="FFCAEDFB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBFBFBF"/>
+        <bgColor rgb="FFBFBFBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1A983"/>
+        <bgColor rgb="FFF1A983"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6C9EB"/>
+        <bgColor rgb="FFA6C9EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1F0C8"/>
+        <bgColor rgb="FFC1F0C8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE6BB"/>
+        <bgColor rgb="FFFFE6BB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1CEEE"/>
+        <bgColor rgb="FFF1CEEE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +165,49 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,303 +575,447 @@
   </sheetPr>
   <dimension ref="A1:AX704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8.6875" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="8.6875" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="11.6875" customWidth="1" min="20" max="20"/>
+    <col width="14.875" customWidth="1" min="21" max="21"/>
+    <col width="8.6875" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="11.125" customWidth="1" min="27" max="27"/>
+    <col width="7.125" customWidth="1" min="28" max="28"/>
+    <col width="7.3125" customWidth="1" min="29" max="29"/>
+    <col width="11.4375" customWidth="1" min="30" max="30"/>
+    <col width="20.75" customWidth="1" min="31" max="31"/>
+    <col width="15.125" customWidth="1" min="32" max="32"/>
+    <col width="8.6875" customWidth="1" min="33" max="33"/>
+    <col width="11.125" customWidth="1" min="34" max="34"/>
+    <col width="7.125" customWidth="1" min="35" max="35"/>
+    <col width="7.3125" customWidth="1" min="36" max="36"/>
+    <col width="10.25" customWidth="1" min="37" max="37"/>
+    <col width="20.75" customWidth="1" min="38" max="38"/>
+    <col width="21.3125" customWidth="1" min="39" max="39"/>
+    <col width="8.6875" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="13" customWidth="1" min="45" max="45"/>
+    <col width="13" customWidth="1" min="46" max="46"/>
+    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="13" customWidth="1" min="48" max="48"/>
+    <col width="9.4375" customWidth="1" min="49" max="49"/>
+    <col width="8.6875" customWidth="1" min="50" max="50"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Coder Initials</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Article ID</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Sample ID</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Effect size ID</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Inclusion-
 Exclusion Judgment</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Reason for Exclusion</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Article Descriptors</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+      <c r="M1" s="4" t="n"/>
+      <c r="N1" s="4" t="n"/>
+      <c r="O1" s="4" t="n"/>
+      <c r="P1" s="4" t="n"/>
+      <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>Study/Sample Descriptors</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="R1" s="4" t="n"/>
+      <c r="S1" s="4" t="n"/>
+      <c r="T1" s="4" t="n"/>
+      <c r="U1" s="4" t="n"/>
+      <c r="V1" s="4" t="n"/>
+      <c r="W1" s="4" t="n"/>
+      <c r="X1" s="4" t="n"/>
+      <c r="Y1" s="4" t="n"/>
+      <c r="Z1" s="4" t="n"/>
+      <c r="AA1" s="6" t="inlineStr">
         <is>
           <t>Measure Descriptors</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AB1" s="4" t="n"/>
+      <c r="AC1" s="4" t="n"/>
+      <c r="AD1" s="4" t="n"/>
+      <c r="AE1" s="4" t="n"/>
+      <c r="AF1" s="4" t="n"/>
+      <c r="AG1" s="4" t="n"/>
+      <c r="AH1" s="4" t="n"/>
+      <c r="AI1" s="4" t="n"/>
+      <c r="AJ1" s="4" t="n"/>
+      <c r="AK1" s="4" t="n"/>
+      <c r="AL1" s="4" t="n"/>
+      <c r="AM1" s="4" t="n"/>
+      <c r="AN1" s="4" t="n"/>
+      <c r="AO1" s="7" t="inlineStr">
         <is>
           <t>Effect Size</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="AA2" t="inlineStr">
+      <c r="AP1" s="4" t="n"/>
+      <c r="AQ1" s="4" t="n"/>
+      <c r="AR1" s="4" t="n"/>
+      <c r="AS1" s="4" t="n"/>
+      <c r="AT1" s="4" t="n"/>
+      <c r="AU1" s="4" t="n"/>
+      <c r="AV1" s="4" t="n"/>
+      <c r="AW1" s="4" t="n"/>
+      <c r="AX1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="4" t="n"/>
+      <c r="R2" s="4" t="n"/>
+      <c r="S2" s="4" t="n"/>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
+      <c r="W2" s="4" t="n"/>
+      <c r="X2" s="4" t="n"/>
+      <c r="Y2" s="4" t="n"/>
+      <c r="Z2" s="4" t="n"/>
+      <c r="AA2" s="8" t="inlineStr">
         <is>
           <t>Boundary spanning</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AB2" s="4" t="n"/>
+      <c r="AC2" s="4" t="n"/>
+      <c r="AD2" s="4" t="n"/>
+      <c r="AE2" s="4" t="n"/>
+      <c r="AF2" s="4" t="n"/>
+      <c r="AG2" s="4" t="n"/>
+      <c r="AH2" s="9" t="inlineStr">
         <is>
           <t>Non-boundary-spanning variable</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AI2" s="4" t="n"/>
+      <c r="AJ2" s="4" t="n"/>
+      <c r="AK2" s="4" t="n"/>
+      <c r="AL2" s="4" t="n"/>
+      <c r="AM2" s="4" t="n"/>
+      <c r="AN2" s="4" t="n"/>
+      <c r="AO2" s="10" t="inlineStr">
         <is>
           <t>Boundary spanning-related variable</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AP2" s="4" t="n"/>
+      <c r="AQ2" s="4" t="n"/>
+      <c r="AR2" s="4" t="n"/>
+      <c r="AS2" s="11" t="inlineStr">
         <is>
           <t>Non-boundary-spanning variable</t>
         </is>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="AT2" s="4" t="n"/>
+      <c r="AU2" s="4" t="n"/>
+      <c r="AV2" s="4" t="n"/>
+      <c r="AW2" s="12" t="inlineStr">
         <is>
           <t>Correlation r</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX2" s="12" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="G3" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Abstract</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Publication Name</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Authors</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>Publication Type</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t>Other (specify)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>Full Citation (APA Style)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>Secondary Data? (If yes, provide reference to the original paper)</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="15" t="inlineStr">
         <is>
           <t>Study Design</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="15" t="inlineStr">
         <is>
           <t>Other (specify)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="15" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="15" t="inlineStr">
         <is>
           <t>Country (specify)</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="15" t="inlineStr">
         <is>
           <t>International Context</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="15" t="inlineStr">
         <is>
           <t>Sample size (N)</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="15" t="inlineStr">
         <is>
           <t>Mean Age</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="15" t="inlineStr">
         <is>
           <t>% Female</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" s="15" t="inlineStr">
         <is>
           <t>Org Tenure</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z3" s="15" t="inlineStr">
         <is>
           <t>Occupation Type</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" s="16" t="inlineStr">
         <is>
           <t>Number of Items</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB3" s="16" t="inlineStr">
         <is>
           <t>Min Score</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC3" s="16" t="inlineStr">
         <is>
           <t>Max Score</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" s="16" t="inlineStr">
         <is>
           <t>Report Type</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE3" s="16" t="inlineStr">
         <is>
           <t>Report Type Note (if necessary)</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF3" s="16" t="inlineStr">
         <is>
           <t>Specific Measure Used</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG3" s="16" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AH3" s="17" t="inlineStr">
         <is>
           <t>Number of Items</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AI3" s="17" t="inlineStr">
         <is>
           <t>Min Score</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AJ3" s="17" t="inlineStr">
         <is>
           <t>Max Score</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AK3" s="17" t="inlineStr">
         <is>
           <t>Report Type</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AL3" s="17" t="inlineStr">
         <is>
           <t>Report Type Note (if necessary)</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AM3" s="17" t="inlineStr">
         <is>
           <t>Specific Measure Used</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AN3" s="17" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AO3" s="18" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AP3" s="18" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="AQ3" s="18" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AR3" s="18" t="inlineStr">
         <is>
           <t>Reliability (Alpha)</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AS3" s="19" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AT3" s="19" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
       </c>
-      <c r="AU3" t="inlineStr">
+      <c r="AU3" s="19" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="AV3" t="inlineStr">
+      <c r="AV3" s="19" t="inlineStr">
         <is>
           <t>Reliability (Alpha)</t>
         </is>
       </c>
+      <c r="AW3" s="4" t="n"/>
+      <c r="AX3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -665,127 +665,43 @@
           <t>Article Descriptors</t>
         </is>
       </c>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-      <c r="M1" s="4" t="n"/>
-      <c r="N1" s="4" t="n"/>
-      <c r="O1" s="4" t="n"/>
-      <c r="P1" s="4" t="n"/>
       <c r="Q1" s="5" t="inlineStr">
         <is>
           <t>Study/Sample Descriptors</t>
         </is>
       </c>
-      <c r="R1" s="4" t="n"/>
-      <c r="S1" s="4" t="n"/>
-      <c r="T1" s="4" t="n"/>
-      <c r="U1" s="4" t="n"/>
-      <c r="V1" s="4" t="n"/>
-      <c r="W1" s="4" t="n"/>
-      <c r="X1" s="4" t="n"/>
-      <c r="Y1" s="4" t="n"/>
-      <c r="Z1" s="4" t="n"/>
       <c r="AA1" s="6" t="inlineStr">
         <is>
           <t>Measure Descriptors</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="n"/>
-      <c r="AC1" s="4" t="n"/>
-      <c r="AD1" s="4" t="n"/>
-      <c r="AE1" s="4" t="n"/>
-      <c r="AF1" s="4" t="n"/>
-      <c r="AG1" s="4" t="n"/>
-      <c r="AH1" s="4" t="n"/>
-      <c r="AI1" s="4" t="n"/>
-      <c r="AJ1" s="4" t="n"/>
-      <c r="AK1" s="4" t="n"/>
-      <c r="AL1" s="4" t="n"/>
-      <c r="AM1" s="4" t="n"/>
-      <c r="AN1" s="4" t="n"/>
       <c r="AO1" s="7" t="inlineStr">
         <is>
           <t>Effect Size</t>
         </is>
       </c>
-      <c r="AP1" s="4" t="n"/>
-      <c r="AQ1" s="4" t="n"/>
-      <c r="AR1" s="4" t="n"/>
-      <c r="AS1" s="4" t="n"/>
-      <c r="AT1" s="4" t="n"/>
-      <c r="AU1" s="4" t="n"/>
-      <c r="AV1" s="4" t="n"/>
-      <c r="AW1" s="4" t="n"/>
-      <c r="AX1" s="4" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n"/>
-      <c r="W2" s="4" t="n"/>
-      <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="4" t="n"/>
-      <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="8" t="inlineStr">
         <is>
           <t>Boundary spanning</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="n"/>
-      <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="4" t="n"/>
-      <c r="AF2" s="4" t="n"/>
-      <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="9" t="inlineStr">
         <is>
           <t>Non-boundary-spanning variable</t>
         </is>
       </c>
-      <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="4" t="n"/>
-      <c r="AK2" s="4" t="n"/>
-      <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n"/>
       <c r="AO2" s="10" t="inlineStr">
         <is>
           <t>Boundary spanning-related variable</t>
         </is>
       </c>
-      <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n"/>
       <c r="AS2" s="11" t="inlineStr">
         <is>
           <t>Non-boundary-spanning variable</t>
         </is>
       </c>
-      <c r="AT2" s="4" t="n"/>
-      <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="12" t="inlineStr">
         <is>
           <t>Correlation r</t>
@@ -798,12 +714,6 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
       <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Abstract</t>
@@ -1014,8 +924,6 @@
           <t>Reliability (Alpha)</t>
         </is>
       </c>
-      <c r="AW3" s="4" t="n"/>
-      <c r="AX3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -36294,21 +36202,21 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A1:A3"/>
+    <mergeCell ref="AO1:AX1"/>
+    <mergeCell ref="AH2:AN2"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="G1:P2"/>
+    <mergeCell ref="AX2:AX3"/>
     <mergeCell ref="AA2:AG2"/>
+    <mergeCell ref="AA1:AN1"/>
     <mergeCell ref="D1:D3"/>
+    <mergeCell ref="B1:B3"/>
     <mergeCell ref="AW2:AW3"/>
-    <mergeCell ref="B1:B3"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="F1:F3"/>
     <mergeCell ref="Q1:Z2"/>
-    <mergeCell ref="AO1:AX1"/>
-    <mergeCell ref="G1:P2"/>
-    <mergeCell ref="AH2:AN2"/>
     <mergeCell ref="AO2:AR2"/>
     <mergeCell ref="AS2:AV2"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="AX2:AX3"/>
-    <mergeCell ref="AA1:AN1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX1000"/>
+  <dimension ref="A1:P1000"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="8.6875" customWidth="1" style="10" min="1" max="16"/>
@@ -564,54 +564,8 @@
           <t>Article Descriptors</t>
         </is>
       </c>
-      <c r="Q1" s="13" t="inlineStr">
-        <is>
-          <t>Study/Sample Descriptors</t>
-        </is>
-      </c>
-      <c r="AA1" s="20" t="inlineStr">
-        <is>
-          <t>Measure Descriptors</t>
-        </is>
-      </c>
-      <c r="AO1" s="14" t="inlineStr">
-        <is>
-          <t>Effect Size</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" s="10">
-      <c r="AA2" s="19" t="inlineStr">
-        <is>
-          <t>Boundary spanning</t>
-        </is>
-      </c>
-      <c r="AH2" s="16" t="inlineStr">
-        <is>
-          <t>Non-boundary-spanning variable</t>
-        </is>
-      </c>
-      <c r="AO2" s="17" t="inlineStr">
-        <is>
-          <t>Boundary spanning-related variable</t>
-        </is>
-      </c>
-      <c r="AS2" s="18" t="inlineStr">
-        <is>
-          <t>Non-boundary-spanning variable</t>
-        </is>
-      </c>
-      <c r="AW2" s="11" t="inlineStr">
-        <is>
-          <t>Correlation r</t>
-        </is>
-      </c>
-      <c r="AX2" s="11" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="10"/>
     <row r="3" ht="18" customHeight="1" s="10">
       <c r="G3" s="1" t="inlineStr">
         <is>
@@ -661,166 +615,6 @@
       <c r="P3" s="2" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>Study Design</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>Other (specify)</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>Country (specify)</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>International Context</t>
-        </is>
-      </c>
-      <c r="V3" s="3" t="inlineStr">
-        <is>
-          <t>Sample size (N)</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="inlineStr">
-        <is>
-          <t>Mean Age</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>% Female</t>
-        </is>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>Org Tenure</t>
-        </is>
-      </c>
-      <c r="Z3" s="3" t="inlineStr">
-        <is>
-          <t>Occupation Type</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>Number of Items</t>
-        </is>
-      </c>
-      <c r="AB3" s="4" t="inlineStr">
-        <is>
-          <t>Min Score</t>
-        </is>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>Max Score</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>Report Type</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr">
-        <is>
-          <t>Report Type Note (if necessary)</t>
-        </is>
-      </c>
-      <c r="AF3" s="4" t="inlineStr">
-        <is>
-          <t>Specific Measure Used</t>
-        </is>
-      </c>
-      <c r="AG3" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="AH3" s="5" t="inlineStr">
-        <is>
-          <t>Number of Items</t>
-        </is>
-      </c>
-      <c r="AI3" s="5" t="inlineStr">
-        <is>
-          <t>Min Score</t>
-        </is>
-      </c>
-      <c r="AJ3" s="5" t="inlineStr">
-        <is>
-          <t>Max Score</t>
-        </is>
-      </c>
-      <c r="AK3" s="5" t="inlineStr">
-        <is>
-          <t>Report Type</t>
-        </is>
-      </c>
-      <c r="AL3" s="5" t="inlineStr">
-        <is>
-          <t>Report Type Note (if necessary)</t>
-        </is>
-      </c>
-      <c r="AM3" s="5" t="inlineStr">
-        <is>
-          <t>Specific Measure Used</t>
-        </is>
-      </c>
-      <c r="AN3" s="5" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="AO3" s="6" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="AP3" s="6" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="AQ3" s="6" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="AR3" s="6" t="inlineStr">
-        <is>
-          <t>Reliability (Alpha)</t>
-        </is>
-      </c>
-      <c r="AS3" s="7" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="AT3" s="7" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="AU3" s="7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="AV3" s="7" t="inlineStr">
-        <is>
-          <t>Reliability (Alpha)</t>
         </is>
       </c>
     </row>
@@ -36987,23 +36781,14 @@
       <c r="P1000" s="8" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="7">
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="D1:D3"/>
-    <mergeCell ref="AW2:AW3"/>
     <mergeCell ref="B1:B3"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="F1:F3"/>
-    <mergeCell ref="Q1:Z2"/>
-    <mergeCell ref="AO1:AX1"/>
-    <mergeCell ref="AX2:AX3"/>
     <mergeCell ref="G1:P2"/>
-    <mergeCell ref="AH2:AN2"/>
-    <mergeCell ref="AO2:AR2"/>
-    <mergeCell ref="AS2:AV2"/>
     <mergeCell ref="E1:E3"/>
-    <mergeCell ref="AA2:AG2"/>
-    <mergeCell ref="AA1:AN1"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation sqref="F4:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="g:\My Drive\UCL\BSMA\BSMA ANTIGRAVITY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ED9DF42-288F-4468-9654-FD5C189157AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530354F1-1D02-476A-B8E8-CD406977BD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5415" uniqueCount="3572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5530" uniqueCount="3611">
   <si>
     <t>Coder Initials</t>
   </si>
@@ -6648,6 +6648,9 @@
     <t>Mazzoni, Leonardo; Sedita, Silvia Rita</t>
   </si>
   <si>
+    <t>Non-individual level (firm-level start-ups) and non-employee (entrepreneurs/founders). [Code 2 &amp; Code 3]. Verbatim Evidence: "[Abstract] "Poisson family estimations (negative binomial and zero-inflated negative binomial) of 172 innovative ICT start-ups based in Italy reveal different driving factors of their socio-environmental sustainability." [Methodology] "We collected survey data from the administration of a questionnaire through telephone interviews conducted by a Computer-Assisted Telephone Interview (CATI) service supply company... The questionnaire is composed of 24 items divided into three parts and was addressed to one of the founders, reporting data and information on behalf of the other founders (when multiple founders existed)." [Introduction] "Boundary spanning refers to the extent to which a start-up leverages a network of information sources and collaborations to enhance its market and technology knowledge""</t>
+  </si>
+  <si>
     <t>BSMA0406</t>
   </si>
   <si>
@@ -6660,6 +6663,9 @@
     <t>McAmis, Gregory; Evans, Kenneth R.; Arnold, Todd J.</t>
   </si>
   <si>
+    <t>The study focuses on developing a scale for 'salesperson directive modification intention' (the intention to alter or ignore an organizational directive) rather than measuring interpersonal boundary spanning behavior (such as information scanning, representation, or coordination). Furthermore, it is a scale development paper that does not report a correlation matrix of substantive variables.. Verbatim Evidence: "[Abstract] Given frequently high autonomy levels and varied job roles, boundary spanning agents have ample opportunity and motivation to modify/ignore organizational directives. Based on a multi-theoretical perspective, this research sets forth a three-dimensional conceptualization of directive modification intentions and develops and empirically tests a scale designed to better explain this phenomenon while empirically validating its occurrence."</t>
+  </si>
+  <si>
     <t>BSMA0407</t>
   </si>
   <si>
@@ -6675,6 +6681,9 @@
     <t>McBeath, Bowen; Chuang, Emmeline; Carnochan, Sarah; Austin, Michael J.; Stuart, Marla</t>
   </si>
   <si>
+    <t>No correlation matrix or zero-order effect sizes provided. Verbatim Evidence: "[No effect size of interest] The study does not provide a full correlation matrix or extractable zero-order correlations between boundary spanning and substantive variables, only reporting multivariate ordinal logistic regression results and collinearity bounds. Verbatim Evidence: "[Analyses] Bivariate Pearson, Spearman, and phi correlation tests did not indicate any problematic collinearity among independent variables (e.g., &gt;0.33). Nor were the dependent variables highly correlated with any of the independent or control variables (i.e., all &gt;0.21)." "[Multivariate Results] Table 4 presents the results of three multivariate ordinal logistic regressions concerning county managerial perspectives of the difficulty of coordinating services with contracted agency staff.""</t>
+  </si>
+  <si>
     <t>BSMA0408</t>
   </si>
   <si>
@@ -6690,6 +6699,11 @@
     <t>McDermott, Imelda; Astbury, Jayne; Jacobs, Sally; Willis, Sarah; Hindi, Ali; Seston, Elizabeth; Schafheutle, Ellen</t>
   </si>
   <si>
+    <t>Qualitative study without quantitative effect sizes. Verbatim Evidence: "[Methods] The data for 
+this article came from a qualitative study involving in-depth interviews with learners (pharma-
+cists) (January–November 2020)."</t>
+  </si>
+  <si>
     <t>BSMA0409</t>
   </si>
   <si>
@@ -6702,6 +6716,9 @@
     <t>McEvoy, Phil; Escott, Diane; Bee, Penny</t>
   </si>
   <si>
+    <t>Qualitative evaluation study lacking extractable quantitative effect sizes (Code 1). Verbatim Evidence: "[Methods] "The quality of the organisational infrastructure supporting the case management service was measured using the Assessment of Chronic Illness Care (ACIC) Survey... Ten questionnaires were completed and returned... Semi-structured qualitative interviews were conducted... The interview data were analysed using a combination of elements from framework analysis..." [Discussion] "This formative evaluation has considerable limitations. It is essentially a single case study... The quality of the ACIC survey was impaired by the relatively low response rate and the incompleteness of the dataset. The interview data were also abstracted from long conversations with front line practitioners""</t>
+  </si>
+  <si>
     <t>BSMA0410</t>
   </si>
   <si>
@@ -6717,6 +6734,9 @@
     <t>McMillan, Janice</t>
   </si>
   <si>
+    <t>Qualitative study without quantitative effect sizes. Verbatim Evidence: "[The research study] "By the nature of the questions and issues that guided my thinking, I was drawn to undertaking a qualitative study. Such ‘interpretive’ studies are designed to ‘investigate human experience and to do so in ways that both reveal its complexity and reflect its historical and situational contexts’ (Maclean 1987, 132).""</t>
+  </si>
+  <si>
     <t>BSMA0411</t>
   </si>
   <si>
@@ -6747,6 +6767,9 @@
     <t>Meisandi Arya; Charles Mercelie; Netania Emilisa</t>
   </si>
   <si>
+    <t>Code 1 &amp; Code 7: Non-English language and no measure of boundary spanning behavior. Verbatim Evidence: "[Abstract] "The purpose of this research is to determine the description of the employees of the Grand Mercure Hotel Kemayoran Jakarta, to determine and analyze the influence of Emotional Dissonance on Service Sabotage, to determine and analyze the influence of Emotional Intelligence on Service Sabotage, and to determine and analyze the influence of Emotional Exhaustion on Service Sabotage." [1. PENDAHULUAN] "Pasca pandemi Covid-19, sebagian besar sektor di seluruh dunia terkena dampak yang signifikan, termasuk industri pariwisata internasional.""</t>
+  </si>
+  <si>
     <t>BSMA0413</t>
   </si>
   <si>
@@ -6759,6 +6782,9 @@
     <t>Mell, Julija N.; Quintane, Eric; Hirst, Giles; Carnegie, Andrew</t>
   </si>
   <si>
+    <t>Data analyzed at the group-dyad level (N=462 directed dyads between 22 business units) with aggregated individual variables, lacking an individual-level correlation matrix.. Verbatim Evidence: "[Data Collection and Sample] "On the group-dyadic level, this resulted in a sample of Nd = 22*(22−1) = 462 directed dyads. On the individual level, we defined the boundary of the network to be studied as all employees of the selected units in primary functions, i.e., those engaged in project work, project management, and work group management, excluding administrative and support functions. In total, our sample comprised 645 employees nested in 22 interdependent business units, each unit comprising 20 to 50 individuals." [Measures for Main Analyses] "To model boundary spanners’ impact on intergroup knowledge integration, we aggregated boundary spanners’ metaknowledge and proactivity to the inter-unit level""</t>
+  </si>
+  <si>
     <t>BSMA0414</t>
   </si>
   <si>
@@ -6771,6 +6797,9 @@
     <t>Mell, Julija N.; Van Knippenberg, Daan; Van Ginkel, Wendy P.; Heugens, Pursey P. M. A. R.</t>
   </si>
   <si>
+    <t>Individual-level intra-organizational boundary spanning measured via E-I index for advice-seeking ties. Verbatim Evidence: "[Sample] "We recruited 327 full-time employees though the online research platform Prolific for a compensation of £0.70... we retained 302 employees in our final sample" [Advice Seeking] "Participants listed up to 10 contacts from whom they had sought advice on important work matters in the preceding 6 months. Next, participants indicated for each contact whether they were their supervisor, a colleague reporting to the same supervisor, a colleague reporting to a different supervisor, or a person outside the participants’ organization." [Boundary Spanning] "To measure boundary spanning, we used the E–I index (Krackhardt &amp; Stern, 1988) calculated as E–I index =(E−I)/(E+I), where E stands for the number of a person’s connections outside the focal group (here, all advice ties crossing an intraorganizational boundary by going to colleagues within the organization but reporting to another supervisor)""</t>
+  </si>
+  <si>
     <t>BSMA0415</t>
   </si>
   <si>
@@ -6786,6 +6815,9 @@
     <t>Meng, Yu</t>
   </si>
   <si>
+    <t>The study measures purposive boundary-spanning collaboration ties (with industry, government, other universities, and other departments) at the individual ego-network level for academic scientists, and provides a correlation matrix with an innovation outcome (patenting).. Verbatim Evidence: "[Sample] "The data used for this study are drawn from “Women in Science and Engineering Network Access, Participation, and Career Outcomes” (NETWISE), a major national study of academic scientists in the U.S. In NETWISE, a survey was conducted of 3677 individuals randomly drawn from the population of academic scientists and engineers" [Measures] "7876 individuals were named as close collaborators by the survey respondents through a few questions about “closest research collaborators” where “collaboration includes proposal generation, working on a research project, writing/presenting an academic paper/book or book chapter, or developing industrial products or patents.”" "According to these collaborators’ organizational affiliation, four dummy variables were created to indicate whether an academic scientist investigated had one or more collaboration ties with industry (Industrial ties), with government or public agency (Governmental ties), with other universities including foreign universities (Inter-University ties), and with other departments (Interdisciplinary ties)." [Results] "Table 5 Correlation matrix of variables used in the logit regression analyses.""</t>
+  </si>
+  <si>
     <t>BSMA0416</t>
   </si>
   <si>
@@ -6798,6 +6830,9 @@
     <t>Methot, Jessica R.; LePine, Jeffery A.</t>
   </si>
   <si>
+    <t>Work-Family Boundary Management. Verbatim Evidence: "[Abstract] "Purpose We examine the bi-directional nature of role segmentation preferences— preferences to protect the home domain from work intrusions , and to protect the work domain from home intrusions —and hypothesize that the dimensions independently prompt individuals to manage their bound- aries in ways that complement their preferences." [Introduction] "A growing body of literature loosely labeled ‘‘boundary theory’’ (Ashforth et al. 2000 ; Clark 2000 ; Nippert-Eng 1996 ) explores ways people manage boundaries between work and personal domains.""</t>
+  </si>
+  <si>
     <t>BSMA0417</t>
   </si>
   <si>
@@ -6837,6 +6872,9 @@
     <t>MIA At-Twaijri, JR Montanari</t>
   </si>
   <si>
+    <t>Old scanned PDF, unable to extract text. Assumed no extractable effect size.. Verbatim Evidence: "Manual Override"</t>
+  </si>
+  <si>
     <t>BSMA0420</t>
   </si>
   <si>
@@ -6852,6 +6890,9 @@
     <t>Minibas-Poussard, Jale; Tuger, Ahmet Tugrul; Seckin, Tutku; Bingöl, Haluk Baran; Poirot, Matthieu</t>
   </si>
   <si>
+    <t>No BSB construct measured (Code 1). The study samples boundary-spanning bank workers but only measures workplace bullying, turnover intention, negative emotions, and workplace unfairness.. Verbatim Evidence: "[Abstract] "Methods : The research involved collecting data from 269 boundary-spanning bank workers (call center workers, frontline office staff, and customer service representatives) who experienced bullying." [Table 1] "Table 1. Means, Standard Deviations, and Correlation Coefficients. M SD 1 2 3 1. Workplace bullying 88.38 14.60 2. Turnover intention 4.33 0.90 0.24 ** 3. Negative emotions 35.38 6.35 0.63 ** 0.41 ** 4. Workplace unfairness""</t>
+  </si>
+  <si>
     <t>BSMA0421</t>
   </si>
   <si>
@@ -6867,6 +6908,9 @@
     <t>Mishra, Anant A.; Shah, Rachna</t>
   </si>
   <si>
+    <t>Project-level collaborative competence (key informant proxy). Verbatim Evidence: "[Sample] "During administration, each plant coordinator selected a product development manager asthe key respondent for the NPD survey. To get accurate responses, the product development manager was asked to refer to a ‘‘recent major product development project’’ in which he/she participated, thus making a product development project the unit of analysis in this study. Our current study uses responses from the product development manager only. The ﬁnal data set consists of 189 responses from product development managers relating one project to one plant." [Measures] "For instance, the measurement items SUPINV2 ( We partnered with suppliers for the design of this product ), CUSTINV3 ( Customers were an integral part of the design effort for this project ), and CRFINV1 ( New product design teams have frequent interaction with the manufacturing function ) are each a measure of the extent to which the focal ﬁrm collaborates with suppliers, customers, and cross-functional teams in the product development process.""</t>
+  </si>
+  <si>
     <t>BSMA0422</t>
   </si>
   <si>
@@ -6879,6 +6923,9 @@
     <t>Mizrahi-Shtelman, Ravit; Sapir, Adi</t>
   </si>
   <si>
+    <t>Qualitative study without quantitative effect sizes. Verbatim Evidence: "[Qualitative study]. Verbatim Evidence: "[DATA AND METHOD] For the current research, we employed a qualitative methodology that involved in-depth interpretive analysis, in which we used the lens of boundary work to analyze homeroom teachers’ descriptions and perceptions of their professional roles." "[DATA AND METHOD] Within the larger study, we conducted 142 semistructured interviews with homeroom teachers from elementary, middle, and high schools across various regions in Israel.""</t>
+  </si>
+  <si>
     <t>BSMA0423</t>
   </si>
   <si>
@@ -6891,6 +6938,9 @@
     <t>MJ Jayaram</t>
   </si>
   <si>
+    <t>Unit of analysis is the new product development project (macro-level), not individual employees.. Verbatim Evidence: "[Research Methods] The unit of analysis for this research was a new product development project. Firms from a variety of industries were selected in order to test for contingency relationships across different settings. Data collection was conducted using a survey instrument. The ideal respondent for the survey was specified to be the person with overall responsibility for overseeing product development projects."</t>
+  </si>
+  <si>
     <t>BSMA0424</t>
   </si>
   <si>
@@ -6906,6 +6956,9 @@
     <t>ML Tushman</t>
   </si>
   <si>
+    <t>No extractable zero-order correlation matrix for BSB (study only reports comparisons of medians and mean counts).. Verbatim Evidence: "[Methods] "This study focused on the communication activity of all the professionals (N=345) in the R&amp;D facility of a large mid-western U.S. corporation." [Results] "Table 2 compares the median absolute amount of communication, over 15 weeks, of stars and nonstars with the three extra-departmental communication domains." [Results] "Table 4 Mean Number of Boundary Roles per Project for Different Task Areas""</t>
+  </si>
+  <si>
     <t>BSMA0425</t>
   </si>
   <si>
@@ -6921,6 +6974,9 @@
     <t>Moake, Timothy R.; Dougherty, Thomas W.; Dreher, George F.</t>
   </si>
   <si>
+    <t>Does not measure boundary spanning behavior; focuses on mentoring received.. Verbatim Evidence: "[Measures] "Mentoring received. Mentoring received was assessed at Time 1 and Time 2 (test-rest reliability: r = .71) using Dreher and Ash’s (1990) global eighteen-item measure. This scale captures mentoring received as it relates to a broad range of mentoring functions (i.e., career, psychosocial, protection).""</t>
+  </si>
+  <si>
     <t>BSMA0426</t>
   </si>
   <si>
@@ -6933,6 +6989,9 @@
     <t>Moenaert, Rudy K.; Souder, William E.; Meyer, Arnoud De; Deschoolmeester, Dirk</t>
   </si>
   <si>
+    <t>Unit of analysis is the project/team level with project-level pooled correlations.. Verbatim Evidence: "[Research Method] "Within every company, we have selected one commercially successful project and one commercially unsuccessful project. A minimum requirement for the present study was to have one R&amp;D respondent and one marketing respondent per innovation project." [Construct Validity] "The results in Table 1 justify the use of the pooled perceptions by R&amp;D and marketing regarding project centralization and formalization, interfunctional climate, and commercial project success." [Appendix] "4. How often did R&amp;D receive commercial information related to this project from marketing?" [Table 2] "Note: Table entries represent the Pearson product moment correlation coefficients between the determinants of interfunctional communication, the amount of information R&amp;D and marketing have received from each other, and the degree of commercial project success. The number of observations varies between 62 and 69.""</t>
+  </si>
+  <si>
     <t>BSMA0427</t>
   </si>
   <si>
@@ -6948,6 +7007,9 @@
     <t>Moosavi, Sareh; Perrotti, Daniela; Stephan, André</t>
   </si>
   <si>
+    <t>Qualitative/descriptive multi-method study lacking quantitative effect sizes (no correlation matrices or extractable statistics).. Verbatim Evidence: "[Abstract] "Through a multi-method approach and the use of boundary spanning as an analytical lens, we identify different modes of agency of spatial practitioners in enhancing resource efficiency across the life stages of urban landscape projects." [3. Method] "To address the aim of this research, a multi-method approach was used. First, we used an international survey to gather how urban landscape designers/planners understand the UM concept, and perceive the relevance of metabolic thinking in design practice, globally... This quantitative approach was complemented with qualitative data collected via a focus group workshop with invited spatial practitioners, mainly practicing in Belgium... Additionally, for an in-depth understanding of the barriers and facilitators to resource-sensitive design approaches, we conducted 22 interviews with design practitioners in Belgium." [3.1. Survey] "In total 101 individuals responded to the survey (N = 101).""</t>
+  </si>
+  <si>
     <t>BSMA0428</t>
   </si>
   <si>
@@ -6963,6 +7025,12 @@
     <t>Morash, Edward A; Dröge, Cornelia; Vickery, Shawnee</t>
   </si>
   <si>
+    <t>Firm-level analysis (unit of analysis is the firm/business functions, not individual employees). Verbatim Evidence: "[Methodology] "The subjects consisted of the CEOs from 65 furniture manufacturing firms." [Methodology] "The functional performance evaluations for each functionalcapability were made on a seven-point Likert-type scale ranging from 3 = poor
+relative to major competitors, to +3 = excellent relative to major competitors,
+with a midpoint of 0." [Appendix] "Functional area capabilities and their definitions... (B) Marketing 1. Market segmentation The ability to identify promising target markets and to select
+the best ones for marketing""</t>
+  </si>
+  <si>
     <t>BSMA0429</t>
   </si>
   <si>
@@ -6990,6 +7058,13 @@
     <t>Morgan, N. A.; Piercy, N. F.</t>
   </si>
   <si>
+    <t>Non-individual level study (SBU level analysis). The study measures interdepartmental interaction by averaging responses from multiple managers per Strategic Business Unit.. Verbatim Evidence: "[Methodology] "The sampling units 
+were the general manager, the marketing manager, and the 
+quality manager at the SBU level of the organization." [Methodology] "Subsequently, the data from each of the 
+respondents in an SBU were averaged to form a single unit 
+of data for each construct.""</t>
+  </si>
+  <si>
     <t>BSMA0431</t>
   </si>
   <si>
@@ -7002,6 +7077,9 @@
     <t>Munari, Federico; Righi, Hérica Morais; Toschi, Laura</t>
   </si>
   <si>
+    <t>Project-level unit of analysis measuring patent citations. Verbatim Evidence: "[Abstract] "To investigate this issue, we examine 6081 research projects in the Life Sciences, Physical &amp; Engineering, and Social Sciences &amp; Humanities sectors funded by the European Research Council under the 7th Framework Programme and Horizon 2020 Programme in the period 2008 –2016." [Methodology] "Tables 2 and 3 refer to the full sample of 6081 projects, while Tables 4 and 5 focus on the subsample of 2886 research projects cited at least by one patent.""</t>
+  </si>
+  <si>
     <t>BSMA0432</t>
   </si>
   <si>
@@ -7068,6 +7146,9 @@
     <t>Neirotti, Paolo; Raguseo, Elisabetta; Paolucci, Emilio</t>
   </si>
   <si>
+    <t>Firm-level analysis (N = 304 SMEs) examining the firm's ICT-based external orientation rather than individual-level boundary spanning.. Verbatim Evidence: "[Abstract] "A survey was conducted on 304 Italian SMEs, with the aim of identifying the contextual dimensions where flexible work is chosen and the different typologies of flexible work implemented by companies." [Sample and data collection] "The data were collected through a survey sent to SMEs located in the Piedmont region of Italy between February 2010 and June 2010. The firms surveyed had between 10 and 500 employees""</t>
+  </si>
+  <si>
     <t>BSMA0437</t>
   </si>
   <si>
@@ -7083,6 +7164,9 @@
     <t>Newell, Sue; Swan, Jacky; Robertson, Maxine</t>
   </si>
   <si>
+    <t>Firm-level analysis of BPR adoption and lacks a correlation matrix [Code 1 &amp; Code 3]. Verbatim Evidence: "[Method] This methodology provides information about a ﬁrm from the perspective of one organisa-tional employee only. This inevitably produces some bias, as different employees might give somewhat different answers to questions about their ﬁrm. It also provides information on the boundary spanning activity of only one employee. These are limitations of the methodology adopted, but these need to be weighed against the advantages of being able to make comparisons across a large sample of ﬁrms in different industries and different countries. An indicator of diffusion is to look at the spread of adoption of a particular technology. The survey asked respondents to indicate from a list of technologies those that had been adopted in their own organisation (e.g. TQM, MRP2, JIT). For each technology that had been adopted, respondents indicated the length of time since its adoption (on a scale from 1 ¼ not adopted; to 4 ¼ adopted for more than 3 years). Included in this list was BPR (deﬁned simply as ‘‘Business Process Reengineering’’ or its equivalent transla-tion)." "[Results] In the analyses below, independent sample t-tests and chi-squares analyses are used as appro-priate to compare ﬁrms where BPR had been adopted, with ﬁrms where it had not been adopted. In addition, regression analysis was used to consider the relative strength of the different variables in predicting the rate of BPR adoption."</t>
+  </si>
+  <si>
     <t>BSMA0438</t>
   </si>
   <si>
@@ -7098,6 +7182,9 @@
     <t>Ngondo, Prisca S.; Klyueva, Anna</t>
   </si>
   <si>
+    <t>The study explores public relations roles but lacks a formal correlation matrix involving substantive organizational antecedents or outcomes. It only reports correlations between PR roles and agreement with a semantic definition of public relations.. Verbatim Evidence: "[Results] "The relationship between public relations roles (technician, manager, strategist) and view of public relations (agreement with PRSA’s definition) was investigated using Pearson product-moment correlation coefficient (see Table 3)." [Table 3] "Pearson Product-Moment Correlations Between Public Relations Roles and Understanding of PR.""</t>
+  </si>
+  <si>
     <t>BSMA0439</t>
   </si>
   <si>
@@ -7110,6 +7197,9 @@
     <t>NS Floyd</t>
   </si>
   <si>
+    <t>Qualitative/historical study lacking quantitative effect sizes. Verbatim Evidence: "[1. Introduction] "I combine historical methods and a theoretical framework to uncover a new perspective on the development of journalism education. In attempting to unpack the interrelationships and power dynamics that structured the development of journalism education, I deploy traditional historical methods. I rely on primary documents generated by journalism education stakeholders in both the industry and the academy.""</t>
+  </si>
+  <si>
     <t>BSMA0440</t>
   </si>
   <si>
@@ -7135,6 +7225,9 @@
   </si>
   <si>
     <t>Nygaard, Arne; Dahlstrom, Robert</t>
+  </si>
+  <si>
+    <t>The study evaluates role stress (role ambiguity and role conflict) for people in boundary-spanning positions, but does not measure Boundary Spanning Behavior (BSB).. Verbatim Evidence: "[Abstract] "The coalition of disparate corporate cultures yields appreciable levels of rolestress for people in boundary-spanning positions. Dedicated assets and communication modality are factors thatinfluence the level of role ambiguity and conflict. The authors implicate these facets of role stress as antecedentsto four forms of effectiveness drawn from the competing values framework." [APPENDIX] "Role Ambiguity ... Role Conflict""</t>
   </si>
   <si>
     <t>BSMA0442</t>
@@ -7178,6 +7271,9 @@
   </si>
   <si>
     <t>Ojha, Divesh; Dayan, Mumin; Struckell, Beth; Dhir, Amandeep; Pohlen, Terrence</t>
+  </si>
+  <si>
+    <t>Firm-level analysis (Key Informant Proxy) - items ask about 'We/Our business unit' rather than 'I'. Verbatim Evidence: "[Methodology] The respondents were screened to ensure a sampling of only full-time and mid-to-high-level managers and executives in the service industry... The sample included 97 (37%) public and 167 (63%) private firms. [Appendix] Knowledge channels Please respond to Items 14–16 related to knowledge management practices of your business unit. 14. Our employees regularly visit supply chain partners to enable two-way sharing of expertise. 15. We are able to capture best practices via an information source that spans company boundaries. 16. We are able to leverage after-sales service activities as a source of cross-company-learning about customers."</t>
   </si>
   <si>
     <t>BSMA0444</t>
@@ -18708,6 +18804,518 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> avoids close contact with this socio-political actor""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Team level analysis (N=91 teams) and proxy 'we/the team' survey referents.. Verbatim Evidence: "[Abstract] "We do so in a randomized controlled field experiment conducted with 91 teams in a teaching hospital" [Measures] "Because the main structural component of internal coordination was morning rounds (which were conducted by all core teams), for our measure of core </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> internal coordination we focused on emergent coordination. This was captured based on core </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> members' average response to the item 'We tended to run the list after rounds, discussing each patient's tasks/updates'" [Measures] "For the emergent component, we asked the nurse to rate the extent to which 'The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> included me in the decision making' and 'The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> valued my input'" [Results] "Table 2. Descriptive Statistics and Correlations ... Notes. Values in bold are significant at p &lt; 0.05. N = 91.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Boundary spanning is measured as a binary job position (role occupancy) based on HR director classification, not as an individual-level purposive behavior.. Verbatim Evidence: "[Measures] "Boundary spanning. Our operationalization of boundary spanning positions drew on prior research, which has emphasized linking/coordination and information filtration and transfer as key to the concept of boundary spanning (e.g. Miles, 1976). Over the course of two hour-long interviews, we asked the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">’s human resources director to identify 'positions that required a high degree of interaction with and responsiveness to both internal and external constituents'. Of the 116 positions in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, 28 boundary spanning positions were identified by the human resources director.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The study theorizes managers as boundary spanners but operationalizes this via structural variables (span of control) and time metrics (hours in staff contact) rather than purposive boundary-spanning behaviors. Additionally, the paper does not report a zero-order correlation matrix.. Verbatim Evidence: "[Theory] "The framework was based on Open System Theory and the boundary spanning functions of managers." [Rationale, research objectives and study framework] "The first-order predictors reflected boundary spanner functions (i.e. span and time in staff contact) and characteristics (i.e. leadership) as well as operational hours." [Methods] "Span was calculated as the monthly average of the number of direct report employees (by headcount) assigned to the manager." [Methods] "Time in staff contact was the average daily amount of time (in hours) spent by the manager interacting with direct and non-direct report staff, physicians and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>students</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> working in the area(s) assigned to the manager. Contact included verbal, written and email communication and person-to-person interaction.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The study includes a valid individual-level, network-based measure of intra-organizational BSB (Ego Network Functional Diversity) capturing the count of cross-functional information ties for a sample of organizational employees (interns), with a zero-order correlation matrix provided.. Verbatim Evidence: "[Research Setting and Boundary Conditions] The study setting is internships of business </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>students</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (MBA and undergraduate) in the McCombs School of Business. This multi-organizational approach will provide variance on the independent organizational-level or work unit-level variables that influence the nature of work unit integration and social integration of individuals. Interns also operate at the nonmanagerial level, making them an appropriate category of employees. [Ego Network Independent Variables: Social Integration] Informational, reporting, and friendship ties were collected using an open-ended name generator. (See Appendix for the actual presentation of the instrument.) Individuals were first prompted to enter the names (first name &amp; last initial only) of “people who were valuable sources information for you, including individuals to whom you reported and others you interacted with regularly as a part of your job.” [Ego network size] Network diversity was operationalized as a count of alters outside the ego’s functional area. [DESCRIPTIVE STATISTICS] Descriptive statistics (mean and standard deviation) and correlations among all variables are provided in Table 7. Reliabilities for all multi-item measures (reported above in methods section) are all acceptable at levels above .70. Statistics reported in Table 7 are based on only the final observations in the full models reported below."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Non-employee consumer sample; vignette study lacking actual BSB measure [Code 1 &amp; Code 2]. Verbatim Evidence: "[Methodology] "Three dichotomous variables (gender, emotional labor and service quality) were the independent variables in this between-subjects quasi-experimental design. Gender (male, female), emotional labor (surface acting, deep acting), and service quality (low quality, high quality) comprised the cells of the 2x2x2 matrix. The study utilized four scenarios to gauge the impact of these independent variables" [Data collection] "For the full study, a market research </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Qualtrics) was enlisted to recruit, disseminate, and collect the results of the electronic survey. There were only two requirements for participation: prospective samples must have been at least 18 years of age as well as having dined in a full-service restaurant in the previous 1 year.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Multiple reasons [Code 2 &amp; Code 3]. Verbatim Evidence: "[Participants] "Undergraduate psychology and business </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>students</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (N = 384) from a large Southeastern United States university participated in the current study." [Participants] "A total of 64, identically-structured MTSs participated in a laboratory simulation designed to model an MTS situation requiring high levels of interdependence and between-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> coordination." [Results] "Note. LT = Leadership </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">; CT = Component </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>; n varies from 57 to 64.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Firm/alliance level analysis. Unit of analysis is the dyadic strategic alliance, and alliance managers act as key informants.. Verbatim Evidence: "[Abstract] "An empirical examination of data collected from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>alliance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> managers of 144 strategic alliances revealed that social exchanges such as reciprocal commitment, trust, and mutual inﬂuence between partners are pos itively related to learning and knowledge transfer in strategic alliances." [Method] "Si nce the unit of analysis in this study was dyadic strategic </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>alliance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as represe nted by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>alliance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> managers, and to be consistent with the recommendations to make  use of the most knowledgeable respondents (Bagozzi and Phillips 1982), a s elf-report questionnaire survey with reference to the speciﬁc </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>alliance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> par tner was conducted among k""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Non-employee sample (MBA students). Verbatim Evidence: "[Sample and procedures] The sample consisted of 204 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>students</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> enrolled in an MBA program at a large public sector university in Islamabad, Pakistan. The study utilized 51 groups developed by the concerned course instructors on a random basis for group projects."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">[Code 1 &amp; Code 3] Firm-level analysis using demographic proxies instead of behavioral BSB. Verbatim Evidence: "[Code 1 &amp; Code 3] </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">-level analysis (N=228 subsidiaries) and no behavioral BSB measure (uses demographic proxies). Verbatim Evidence: "[Abstract] We tested our hypotheses on a sample of 228 MNE subsidiaries from 11 countries." "[3.1 | Sample and data] With these criteria, we have 228 subsidiaries from 11 countries in our dataset." "[3.3 | Explanatory variables] We measure prior MNE work experience by the percentage of subsidiary top managers with work experience in different MNCs prior to joining the focal </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. The top manager’s industry experience is measured by the number of years the top manager has worked in the same industry as that of the subsidiary.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Firm-level analysis. Verbatim Evidence: "[Sample] "The data set consists of 76 companies. There is considerable variance on control variables: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> size, age, and proportion of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>alliance</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> partners being foreign firms. The companies in the sample have, on average) applied for about 8 nano -tech related patents (mean 7.5) over the observation period""</t>
     </r>
   </si>
 </sst>
@@ -19470,7 +20078,7 @@
         <v>2002</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>3434</v>
+        <v>3463</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -19566,7 +20174,7 @@
         <v>2016</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>3435</v>
+        <v>3464</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -19726,7 +20334,7 @@
         <v>2008</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>3436</v>
+        <v>3465</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -19758,7 +20366,7 @@
         <v>2012</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>3437</v>
+        <v>3466</v>
       </c>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20046,7 +20654,7 @@
         <v>1992</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>3438</v>
+        <v>3467</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20174,7 +20782,7 @@
         <v>2024</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>3439</v>
+        <v>3468</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20206,7 +20814,7 @@
         <v>2017</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>3440</v>
+        <v>3469</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20366,7 +20974,7 @@
         <v>2022</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>3441</v>
+        <v>3470</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20491,7 +21099,7 @@
         <v>2020</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>3442</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20587,7 +21195,7 @@
         <v>1997</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>3443</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20651,7 +21259,7 @@
         <v>2021</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>3444</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21055,7 +21663,7 @@
         <v>2018</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>3445</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21084,7 +21692,7 @@
         <v>2015</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>3446</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21270,7 +21878,7 @@
         <v>2011</v>
       </c>
       <c r="P61" s="8" t="s">
-        <v>3447</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21523,7 +22131,7 @@
         <v>2012</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>3448</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21776,7 +22384,7 @@
         <v>2025</v>
       </c>
       <c r="P77" s="8" t="s">
-        <v>3449</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21808,7 +22416,7 @@
         <v>2023</v>
       </c>
       <c r="P78" s="8" t="s">
-        <v>3450</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21840,7 +22448,7 @@
         <v>2019</v>
       </c>
       <c r="P79" s="8" t="s">
-        <v>3451</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21968,7 +22576,7 @@
         <v>2005</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>3452</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22000,7 +22608,7 @@
         <v>2020</v>
       </c>
       <c r="P84" s="8" t="s">
-        <v>3453</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22029,7 +22637,7 @@
         <v>2021</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>3454</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22221,7 +22829,7 @@
         <v>2010</v>
       </c>
       <c r="P91" s="8" t="s">
-        <v>3455</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22317,7 +22925,7 @@
         <v>2024</v>
       </c>
       <c r="P94" s="8" t="s">
-        <v>3456</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22349,7 +22957,7 @@
         <v>2020</v>
       </c>
       <c r="P95" s="8" t="s">
-        <v>3457</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22410,7 +23018,7 @@
         <v>2021</v>
       </c>
       <c r="P97" s="8" t="s">
-        <v>3458</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22439,7 +23047,7 @@
         <v>2012</v>
       </c>
       <c r="P98" s="8" t="s">
-        <v>3459</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22503,7 +23111,7 @@
         <v>1995</v>
       </c>
       <c r="P100" s="8" t="s">
-        <v>3460</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22535,7 +23143,7 @@
         <v>2008</v>
       </c>
       <c r="P101" s="8" t="s">
-        <v>3461</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22628,7 +23236,7 @@
         <v>2010</v>
       </c>
       <c r="P104" s="8" t="s">
-        <v>3462</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22852,7 +23460,7 @@
         <v>2018</v>
       </c>
       <c r="P111" s="8" t="s">
-        <v>3463</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22948,7 +23556,7 @@
         <v>2018</v>
       </c>
       <c r="P114" s="8" t="s">
-        <v>3464</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23076,7 +23684,7 @@
         <v>2016</v>
       </c>
       <c r="P118" s="8" t="s">
-        <v>3465</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23105,7 +23713,7 @@
         <v>1978</v>
       </c>
       <c r="P119" s="8" t="s">
-        <v>3466</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23169,7 +23777,7 @@
         <v>2012</v>
       </c>
       <c r="P121" s="8" t="s">
-        <v>3467</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23233,7 +23841,7 @@
         <v>2004</v>
       </c>
       <c r="P123" s="8" t="s">
-        <v>3468</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23480,7 +24088,7 @@
         <v>1996</v>
       </c>
       <c r="P131" s="8" t="s">
-        <v>3469</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23512,7 +24120,7 @@
         <v>2004</v>
       </c>
       <c r="P132" s="8" t="s">
-        <v>3470</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23576,7 +24184,7 @@
         <v>1990</v>
       </c>
       <c r="P134" s="8" t="s">
-        <v>3471</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="135" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23704,7 +24312,7 @@
         <v>1984</v>
       </c>
       <c r="P138" s="8" t="s">
-        <v>3472</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23928,7 +24536,7 @@
         <v>2011</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>3473</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23960,7 +24568,7 @@
         <v>2003</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>3474</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24120,7 +24728,7 @@
         <v>2014</v>
       </c>
       <c r="P151" s="8" t="s">
-        <v>3475</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24248,7 +24856,7 @@
         <v>2019</v>
       </c>
       <c r="P155" s="8" t="s">
-        <v>3476</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="156" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24312,7 +24920,7 @@
         <v>2009</v>
       </c>
       <c r="P157" s="8" t="s">
-        <v>3477</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24376,7 +24984,7 @@
         <v>2019</v>
       </c>
       <c r="P159" s="8" t="s">
-        <v>3478</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24725,7 +25333,7 @@
         <v>1998</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>3479</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24946,7 +25554,7 @@
         <v>2022</v>
       </c>
       <c r="P177" s="8" t="s">
-        <v>3480</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="178" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25010,7 +25618,7 @@
         <v>1997</v>
       </c>
       <c r="P179" s="8" t="s">
-        <v>3481</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="180" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25042,7 +25650,7 @@
         <v>2022</v>
       </c>
       <c r="P180" s="8" t="s">
-        <v>3482</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25234,7 +25842,7 @@
         <v>2023</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>3483</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25266,7 +25874,7 @@
         <v>2013</v>
       </c>
       <c r="P187" s="8" t="s">
-        <v>3484</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="188" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25455,7 +26063,7 @@
         <v>2010</v>
       </c>
       <c r="P193" s="8" t="s">
-        <v>3485</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="194" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25551,7 +26159,7 @@
         <v>2012</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>3486</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="197" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25580,7 +26188,7 @@
         <v>2015</v>
       </c>
       <c r="P197" s="8" t="s">
-        <v>3487</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="198" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25644,7 +26252,7 @@
         <v>2015</v>
       </c>
       <c r="P199" s="8" t="s">
-        <v>3488</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="200" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25804,7 +26412,7 @@
         <v>2005</v>
       </c>
       <c r="P204" s="8" t="s">
-        <v>3489</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25897,7 +26505,7 @@
         <v>1998</v>
       </c>
       <c r="P207" s="8" t="s">
-        <v>3490</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25929,7 +26537,7 @@
         <v>1999</v>
       </c>
       <c r="P208" s="8" t="s">
-        <v>3491</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="209" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26019,7 +26627,7 @@
         <v>2024</v>
       </c>
       <c r="P211" s="8" t="s">
-        <v>3492</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="212" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26051,7 +26659,7 @@
         <v>2006</v>
       </c>
       <c r="P212" s="8" t="s">
-        <v>3493</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="213" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26083,7 +26691,7 @@
         <v>2010</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>3494</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="214" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26144,7 +26752,7 @@
         <v>2017</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>3495</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="216" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26272,7 +26880,7 @@
         <v>2014</v>
       </c>
       <c r="P219" s="8" t="s">
-        <v>3496</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26304,7 +26912,7 @@
         <v>2011</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>3497</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="221" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26400,7 +27008,7 @@
         <v>2015</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>3498</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="224" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26464,7 +27072,7 @@
         <v>2023</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>3499</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26493,7 +27101,7 @@
         <v>2004</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>3500</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="227" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26589,7 +27197,7 @@
         <v>2005</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>3501</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="230" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26621,7 +27229,7 @@
         <v>2004</v>
       </c>
       <c r="P230" s="8" t="s">
-        <v>3502</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="231" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26717,7 +27325,7 @@
         <v>1998</v>
       </c>
       <c r="P233" s="8" t="s">
-        <v>3503</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="234" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26813,7 +27421,7 @@
         <v>2014</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>3504</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="237" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27034,7 +27642,7 @@
         <v>2011</v>
       </c>
       <c r="P243" s="8" t="s">
-        <v>3505</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27066,7 +27674,7 @@
         <v>2018</v>
       </c>
       <c r="P244" s="8" t="s">
-        <v>3506</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="245" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27098,7 +27706,7 @@
         <v>2019</v>
       </c>
       <c r="P245" s="8" t="s">
-        <v>3507</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="246" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27130,7 +27738,7 @@
         <v>1998</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>3508</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="247" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27284,7 +27892,7 @@
         <v>2012</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>3509</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="252" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27473,7 +28081,7 @@
         <v>1999</v>
       </c>
       <c r="P257" s="8" t="s">
-        <v>3510</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="258" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27537,7 +28145,7 @@
         <v>2022</v>
       </c>
       <c r="P259" s="8" t="s">
-        <v>3511</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27694,7 +28302,7 @@
         <v>2023</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>3512</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27755,7 +28363,7 @@
         <v>2023</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>3513</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="267" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27787,7 +28395,7 @@
         <v>2018</v>
       </c>
       <c r="P267" s="8" t="s">
-        <v>3514</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="268" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27819,7 +28427,7 @@
         <v>2025</v>
       </c>
       <c r="P268" s="8" t="s">
-        <v>3515</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="269" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27848,7 +28456,7 @@
         <v>2010</v>
       </c>
       <c r="P269" s="8" t="s">
-        <v>3516</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="270" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27938,7 +28546,7 @@
         <v>2002</v>
       </c>
       <c r="P272" s="8" t="s">
-        <v>3517</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28031,7 +28639,7 @@
         <v>2020</v>
       </c>
       <c r="P275" s="8" t="s">
-        <v>3518</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28159,7 +28767,7 @@
         <v>1996</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>3519</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28188,7 +28796,7 @@
         <v>2020</v>
       </c>
       <c r="P280" s="8" t="s">
-        <v>3520</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="281" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28220,7 +28828,7 @@
         <v>2003</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>3521</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28316,7 +28924,7 @@
         <v>2022</v>
       </c>
       <c r="P284" s="8" t="s">
-        <v>3522</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28348,7 +28956,7 @@
         <v>2000</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>3523</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28755,7 +29363,7 @@
         <v>2024</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>3524</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28909,7 +29517,7 @@
         <v>2011</v>
       </c>
       <c r="P303" s="8" t="s">
-        <v>3525</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28970,7 +29578,7 @@
         <v>2022</v>
       </c>
       <c r="P305" s="8" t="s">
-        <v>3526</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29028,7 +29636,7 @@
         <v>2022</v>
       </c>
       <c r="P307" s="8" t="s">
-        <v>3527</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29057,7 +29665,7 @@
         <v>2025</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>3528</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29086,7 +29694,7 @@
         <v>2002</v>
       </c>
       <c r="P309" s="8" t="s">
-        <v>3529</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29435,7 +30043,7 @@
         <v>2008</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>3530</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="321" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29563,7 +30171,7 @@
         <v>2020</v>
       </c>
       <c r="P324" s="8" t="s">
-        <v>3531</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29627,7 +30235,7 @@
         <v>2004</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>3532</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29691,7 +30299,7 @@
         <v>2015</v>
       </c>
       <c r="P328" s="8" t="s">
-        <v>3533</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29880,7 +30488,7 @@
         <v>1991</v>
       </c>
       <c r="P334" s="8" t="s">
-        <v>3534</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29912,7 +30520,7 @@
         <v>2023</v>
       </c>
       <c r="P335" s="8" t="s">
-        <v>3535</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29944,7 +30552,7 @@
         <v>2017</v>
       </c>
       <c r="P336" s="8" t="s">
-        <v>3536</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30066,7 +30674,7 @@
         <v>2011</v>
       </c>
       <c r="P340" s="8" t="s">
-        <v>3537</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="341" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30095,7 +30703,7 @@
         <v>2016</v>
       </c>
       <c r="P341" s="8" t="s">
-        <v>3538</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="342" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30127,7 +30735,7 @@
         <v>2020</v>
       </c>
       <c r="P342" s="8" t="s">
-        <v>3539</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30191,7 +30799,7 @@
         <v>2017</v>
       </c>
       <c r="P344" s="8" t="s">
-        <v>3540</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="345" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30223,7 +30831,7 @@
         <v>2024</v>
       </c>
       <c r="P345" s="8" t="s">
-        <v>3541</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="346" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30255,7 +30863,7 @@
         <v>2016</v>
       </c>
       <c r="P346" s="8" t="s">
-        <v>3542</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="347" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30287,7 +30895,7 @@
         <v>2022</v>
       </c>
       <c r="P347" s="8" t="s">
-        <v>3543</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="348" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30415,7 +31023,7 @@
         <v>2002</v>
       </c>
       <c r="P351" s="8" t="s">
-        <v>3544</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="352" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30444,7 +31052,7 @@
         <v>2022</v>
       </c>
       <c r="P352" s="8" t="s">
-        <v>3545</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="353" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30508,7 +31116,7 @@
         <v>2020</v>
       </c>
       <c r="P354" s="8" t="s">
-        <v>3546</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="355" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30540,7 +31148,7 @@
         <v>2024</v>
       </c>
       <c r="P355" s="8" t="s">
-        <v>3547</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="356" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30572,7 +31180,7 @@
         <v>2000</v>
       </c>
       <c r="P356" s="8" t="s">
-        <v>3548</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="357" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30668,7 +31276,7 @@
         <v>2023</v>
       </c>
       <c r="P359" s="8" t="s">
-        <v>3549</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="360" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30697,7 +31305,7 @@
         <v>2018</v>
       </c>
       <c r="P360" s="8" t="s">
-        <v>3550</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="361" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30726,7 +31334,7 @@
         <v>2014</v>
       </c>
       <c r="P361" s="8" t="s">
-        <v>3551</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="362" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30758,7 +31366,7 @@
         <v>2013</v>
       </c>
       <c r="P362" s="8" t="s">
-        <v>3552</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="363" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30790,7 +31398,7 @@
         <v>2025</v>
       </c>
       <c r="P363" s="8" t="s">
-        <v>3553</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="364" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30982,7 +31590,7 @@
         <v>2023</v>
       </c>
       <c r="P369" s="8" t="s">
-        <v>3554</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="370" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31078,7 +31686,7 @@
         <v>2023</v>
       </c>
       <c r="P372" s="8" t="s">
-        <v>3555</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="373" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31174,7 +31782,7 @@
         <v>1999</v>
       </c>
       <c r="P375" s="8" t="s">
-        <v>3556</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="376" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31238,7 +31846,7 @@
         <v>2023</v>
       </c>
       <c r="P377" s="8" t="s">
-        <v>3557</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="378" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31398,7 +32006,7 @@
         <v>2005</v>
       </c>
       <c r="P382" s="8" t="s">
-        <v>3558</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="383" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31430,7 +32038,7 @@
         <v>2007</v>
       </c>
       <c r="P383" s="8" t="s">
-        <v>3559</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="384" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31462,7 +32070,7 @@
         <v>2008</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>3560</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="385" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31584,7 +32192,7 @@
         <v>2019</v>
       </c>
       <c r="P388" s="8" t="s">
-        <v>3561</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="389" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31616,7 +32224,7 @@
         <v>1994</v>
       </c>
       <c r="P389" s="8" t="s">
-        <v>3562</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="390" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31680,7 +32288,7 @@
         <v>2016</v>
       </c>
       <c r="P391" s="8" t="s">
-        <v>3563</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="392" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31712,7 +32320,7 @@
         <v>2015</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>3564</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="393" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31837,7 +32445,7 @@
         <v>2003</v>
       </c>
       <c r="P396" s="8" t="s">
-        <v>3565</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="397" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31933,7 +32541,7 @@
         <v>2005</v>
       </c>
       <c r="P399" s="8" t="s">
-        <v>3566</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="400" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31965,7 +32573,7 @@
         <v>2010</v>
       </c>
       <c r="P400" s="8" t="s">
-        <v>3567</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="401" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31994,7 +32602,7 @@
         <v>2022</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>3568</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="402" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32026,7 +32634,7 @@
         <v>2007</v>
       </c>
       <c r="P402" s="8" t="s">
-        <v>3569</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="403" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32122,7 +32730,7 @@
         <v>2006</v>
       </c>
       <c r="P405" s="8" t="s">
-        <v>3570</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="406" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32154,7 +32762,7 @@
         <v>2007</v>
       </c>
       <c r="P406" s="8" t="s">
-        <v>3571</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="407" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32164,6 +32772,12 @@
       <c r="B407" t="s">
         <v>2143</v>
       </c>
+      <c r="E407" t="s">
+        <v>85</v>
+      </c>
+      <c r="F407" t="s">
+        <v>61</v>
+      </c>
       <c r="G407" t="s">
         <v>2144</v>
       </c>
@@ -32179,7 +32793,9 @@
       <c r="K407">
         <v>2025</v>
       </c>
-      <c r="P407" s="8"/>
+      <c r="P407" s="8" t="s">
+        <v>3601</v>
+      </c>
     </row>
     <row r="408" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A408" t="s">
@@ -32188,6 +32804,12 @@
       <c r="B408" t="s">
         <v>2147</v>
       </c>
+      <c r="E408" t="s">
+        <v>85</v>
+      </c>
+      <c r="F408" t="s">
+        <v>54</v>
+      </c>
       <c r="G408" t="s">
         <v>2148</v>
       </c>
@@ -32203,938 +32825,1235 @@
       <c r="K408">
         <v>2025</v>
       </c>
-      <c r="P408" s="8"/>
+      <c r="P408" s="8" t="s">
+        <v>2152</v>
+      </c>
     </row>
     <row r="409" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A409" t="s">
         <v>43</v>
       </c>
       <c r="B409" t="s">
-        <v>2152</v>
+        <v>2153</v>
+      </c>
+      <c r="E409" t="s">
+        <v>85</v>
+      </c>
+      <c r="F409" t="s">
+        <v>48</v>
       </c>
       <c r="G409" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="H409" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="I409" t="s">
         <v>745</v>
       </c>
       <c r="J409" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="K409">
         <v>2015</v>
       </c>
-      <c r="P409" s="8"/>
+      <c r="P409" s="8" t="s">
+        <v>2157</v>
+      </c>
     </row>
     <row r="410" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A410" t="s">
         <v>43</v>
       </c>
       <c r="B410" t="s">
-        <v>2156</v>
+        <v>2158</v>
+      </c>
+      <c r="E410" t="s">
+        <v>85</v>
+      </c>
+      <c r="F410" t="s">
+        <v>48</v>
       </c>
       <c r="G410" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="H410" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="I410" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="J410" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="K410">
         <v>2019</v>
       </c>
-      <c r="P410" s="8"/>
+      <c r="P410" s="8" t="s">
+        <v>2163</v>
+      </c>
     </row>
     <row r="411" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A411" t="s">
         <v>43</v>
       </c>
       <c r="B411" t="s">
-        <v>2161</v>
+        <v>2164</v>
+      </c>
+      <c r="E411" t="s">
+        <v>85</v>
+      </c>
+      <c r="F411" t="s">
+        <v>48</v>
       </c>
       <c r="G411" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="H411" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="I411" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="J411" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="K411">
         <v>2023</v>
       </c>
-      <c r="P411" s="8"/>
+      <c r="P411" s="8" t="s">
+        <v>2169</v>
+      </c>
     </row>
     <row r="412" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A412" t="s">
         <v>43</v>
       </c>
       <c r="B412" t="s">
-        <v>2166</v>
+        <v>2170</v>
+      </c>
+      <c r="E412" t="s">
+        <v>85</v>
+      </c>
+      <c r="F412" t="s">
+        <v>48</v>
       </c>
       <c r="G412" t="s">
-        <v>2167</v>
+        <v>2171</v>
       </c>
       <c r="H412" t="s">
-        <v>2168</v>
+        <v>2172</v>
       </c>
       <c r="I412" t="s">
         <v>631</v>
       </c>
       <c r="J412" t="s">
-        <v>2169</v>
+        <v>2173</v>
       </c>
       <c r="K412">
         <v>2011</v>
       </c>
-      <c r="P412" s="8"/>
+      <c r="P412" s="8" t="s">
+        <v>2174</v>
+      </c>
     </row>
     <row r="413" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A413" t="s">
         <v>43</v>
       </c>
       <c r="B413" t="s">
-        <v>2170</v>
+        <v>2175</v>
+      </c>
+      <c r="E413" t="s">
+        <v>85</v>
+      </c>
+      <c r="F413" t="s">
+        <v>48</v>
       </c>
       <c r="G413" t="s">
-        <v>2171</v>
+        <v>2176</v>
       </c>
       <c r="H413" t="s">
-        <v>2172</v>
+        <v>2177</v>
       </c>
       <c r="I413" t="s">
-        <v>2173</v>
+        <v>2178</v>
       </c>
       <c r="J413" t="s">
-        <v>2174</v>
+        <v>2179</v>
       </c>
       <c r="K413">
         <v>2011</v>
       </c>
-      <c r="P413" s="8"/>
+      <c r="P413" s="8" t="s">
+        <v>2180</v>
+      </c>
     </row>
     <row r="414" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A414" t="s">
         <v>43</v>
       </c>
       <c r="B414" t="s">
-        <v>2175</v>
+        <v>2181</v>
+      </c>
+      <c r="E414" t="s">
+        <v>85</v>
+      </c>
+      <c r="F414" t="s">
+        <v>48</v>
       </c>
       <c r="G414" t="s">
-        <v>2176</v>
+        <v>2182</v>
       </c>
       <c r="H414" t="s">
-        <v>2177</v>
+        <v>2183</v>
       </c>
       <c r="I414" t="s">
-        <v>2178</v>
+        <v>2184</v>
       </c>
       <c r="J414" t="s">
-        <v>2179</v>
+        <v>2185</v>
       </c>
       <c r="K414">
         <v>2008</v>
       </c>
-      <c r="P414" s="8"/>
+      <c r="P414" s="8" t="s">
+        <v>3602</v>
+      </c>
     </row>
     <row r="415" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A415" t="s">
         <v>43</v>
       </c>
       <c r="B415" t="s">
-        <v>2180</v>
+        <v>2186</v>
+      </c>
+      <c r="E415" t="s">
+        <v>85</v>
+      </c>
+      <c r="F415" t="s">
+        <v>54</v>
       </c>
       <c r="G415" t="s">
-        <v>2181</v>
+        <v>2187</v>
       </c>
       <c r="H415" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="I415" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="J415" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="K415">
         <v>2023</v>
       </c>
-      <c r="P415" s="8"/>
+      <c r="P415" s="8" t="s">
+        <v>2191</v>
+      </c>
     </row>
     <row r="416" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A416" t="s">
         <v>43</v>
       </c>
       <c r="B416" t="s">
-        <v>2185</v>
+        <v>2192</v>
+      </c>
+      <c r="E416" t="s">
+        <v>85</v>
+      </c>
+      <c r="F416" t="s">
+        <v>61</v>
       </c>
       <c r="G416" t="s">
-        <v>2186</v>
+        <v>2193</v>
       </c>
       <c r="H416" t="s">
-        <v>2187</v>
+        <v>2194</v>
       </c>
       <c r="I416" t="s">
         <v>81</v>
       </c>
       <c r="J416" t="s">
-        <v>2188</v>
+        <v>2195</v>
       </c>
       <c r="K416">
         <v>2022</v>
       </c>
-      <c r="P416" s="8"/>
+      <c r="P416" s="8" t="s">
+        <v>2196</v>
+      </c>
     </row>
     <row r="417" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A417" t="s">
         <v>43</v>
       </c>
       <c r="B417" t="s">
-        <v>2189</v>
+        <v>2197</v>
+      </c>
+      <c r="E417" t="s">
+        <v>48</v>
       </c>
       <c r="G417" t="s">
-        <v>2190</v>
+        <v>2198</v>
       </c>
       <c r="H417" t="s">
-        <v>2191</v>
+        <v>2199</v>
       </c>
       <c r="I417" t="s">
         <v>692</v>
       </c>
       <c r="J417" t="s">
-        <v>2192</v>
+        <v>2200</v>
       </c>
       <c r="K417">
         <v>2022</v>
       </c>
-      <c r="P417" s="8"/>
+      <c r="P417" s="8" t="s">
+        <v>2201</v>
+      </c>
     </row>
     <row r="418" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A418" t="s">
         <v>43</v>
       </c>
       <c r="B418" t="s">
-        <v>2193</v>
+        <v>2202</v>
+      </c>
+      <c r="E418" t="s">
+        <v>48</v>
       </c>
       <c r="G418" t="s">
-        <v>2194</v>
+        <v>2203</v>
       </c>
       <c r="H418" t="s">
-        <v>2195</v>
+        <v>2204</v>
       </c>
       <c r="I418" t="s">
-        <v>2196</v>
+        <v>2205</v>
       </c>
       <c r="J418" t="s">
-        <v>2197</v>
+        <v>2206</v>
       </c>
       <c r="K418">
         <v>2016</v>
       </c>
-      <c r="P418" s="8"/>
+      <c r="P418" s="8" t="s">
+        <v>2207</v>
+      </c>
     </row>
     <row r="419" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A419" t="s">
         <v>43</v>
       </c>
       <c r="B419" t="s">
-        <v>2198</v>
+        <v>2208</v>
+      </c>
+      <c r="E419" t="s">
+        <v>85</v>
+      </c>
+      <c r="F419" t="s">
+        <v>48</v>
       </c>
       <c r="G419" t="s">
-        <v>2199</v>
+        <v>2209</v>
       </c>
       <c r="H419" t="s">
-        <v>2200</v>
+        <v>2210</v>
       </c>
       <c r="I419" t="s">
         <v>1117</v>
       </c>
       <c r="J419" t="s">
-        <v>2201</v>
+        <v>2211</v>
       </c>
       <c r="K419">
         <v>2016</v>
       </c>
-      <c r="P419" s="8"/>
+      <c r="P419" s="8" t="s">
+        <v>2212</v>
+      </c>
     </row>
     <row r="420" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A420" t="s">
         <v>43</v>
       </c>
       <c r="B420" t="s">
-        <v>2202</v>
+        <v>2213</v>
+      </c>
+      <c r="E420" t="s">
+        <v>85</v>
+      </c>
+      <c r="F420" t="s">
+        <v>48</v>
       </c>
       <c r="G420" t="s">
-        <v>2203</v>
+        <v>2214</v>
       </c>
       <c r="H420" t="s">
-        <v>2204</v>
+        <v>2215</v>
       </c>
       <c r="I420" t="s">
-        <v>2205</v>
+        <v>2216</v>
       </c>
       <c r="J420" t="s">
-        <v>2206</v>
+        <v>2217</v>
       </c>
       <c r="K420">
         <v>2011</v>
       </c>
-      <c r="P420" s="8"/>
+      <c r="P420" s="8" t="s">
+        <v>3603</v>
+      </c>
     </row>
     <row r="421" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A421" t="s">
         <v>43</v>
       </c>
       <c r="B421" t="s">
-        <v>2207</v>
+        <v>2218</v>
+      </c>
+      <c r="E421" t="s">
+        <v>48</v>
       </c>
       <c r="G421" t="s">
-        <v>2208</v>
+        <v>2219</v>
       </c>
       <c r="H421" t="s">
-        <v>2209</v>
+        <v>2220</v>
       </c>
       <c r="I421" t="s">
         <v>51</v>
       </c>
       <c r="J421" t="s">
-        <v>2210</v>
+        <v>2221</v>
       </c>
       <c r="K421">
         <v>2008</v>
       </c>
-      <c r="P421" s="8"/>
+      <c r="P421" s="8" t="s">
+        <v>3604</v>
+      </c>
     </row>
     <row r="422" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A422" t="s">
         <v>43</v>
       </c>
       <c r="B422" t="s">
-        <v>2211</v>
+        <v>2222</v>
+      </c>
+      <c r="E422">
+        <v>0</v>
+      </c>
+      <c r="F422" t="s">
+        <v>48</v>
       </c>
       <c r="G422" t="s">
-        <v>2212</v>
+        <v>2223</v>
       </c>
       <c r="H422" t="s">
-        <v>2213</v>
+        <v>2224</v>
       </c>
       <c r="I422" t="s">
         <v>307</v>
       </c>
       <c r="J422" t="s">
-        <v>2214</v>
+        <v>2225</v>
       </c>
       <c r="K422">
         <v>1987</v>
       </c>
-      <c r="P422" s="8"/>
+      <c r="P422" s="8" t="s">
+        <v>2226</v>
+      </c>
     </row>
     <row r="423" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A423" t="s">
         <v>43</v>
       </c>
       <c r="B423" t="s">
-        <v>2215</v>
+        <v>2227</v>
+      </c>
+      <c r="E423" t="s">
+        <v>85</v>
+      </c>
+      <c r="F423" t="s">
+        <v>48</v>
       </c>
       <c r="G423" t="s">
-        <v>2216</v>
+        <v>2228</v>
       </c>
       <c r="H423" t="s">
-        <v>2217</v>
+        <v>2229</v>
       </c>
       <c r="I423" t="s">
-        <v>2218</v>
+        <v>2230</v>
       </c>
       <c r="J423" t="s">
-        <v>2219</v>
+        <v>2231</v>
       </c>
       <c r="K423">
         <v>2025</v>
       </c>
-      <c r="P423" s="8"/>
+      <c r="P423" s="8" t="s">
+        <v>2232</v>
+      </c>
     </row>
     <row r="424" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A424" t="s">
         <v>43</v>
       </c>
       <c r="B424" t="s">
-        <v>2220</v>
+        <v>2233</v>
+      </c>
+      <c r="E424" t="s">
+        <v>85</v>
+      </c>
+      <c r="F424" t="s">
+        <v>61</v>
       </c>
       <c r="G424" t="s">
-        <v>2221</v>
+        <v>2234</v>
       </c>
       <c r="H424" t="s">
-        <v>2222</v>
+        <v>2235</v>
       </c>
       <c r="I424" t="s">
-        <v>2223</v>
+        <v>2236</v>
       </c>
       <c r="J424" t="s">
-        <v>2224</v>
+        <v>2237</v>
       </c>
       <c r="K424">
         <v>2009</v>
       </c>
-      <c r="P424" s="8"/>
+      <c r="P424" s="8" t="s">
+        <v>2238</v>
+      </c>
     </row>
     <row r="425" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A425" t="s">
         <v>43</v>
       </c>
       <c r="B425" t="s">
-        <v>2225</v>
+        <v>2239</v>
+      </c>
+      <c r="E425" t="s">
+        <v>85</v>
+      </c>
+      <c r="F425" t="s">
+        <v>48</v>
       </c>
       <c r="G425" t="s">
-        <v>2226</v>
+        <v>2240</v>
       </c>
       <c r="H425" t="s">
-        <v>2227</v>
+        <v>2241</v>
       </c>
       <c r="I425" t="s">
         <v>643</v>
       </c>
       <c r="J425" t="s">
-        <v>2228</v>
+        <v>2242</v>
       </c>
       <c r="K425">
         <v>2025</v>
       </c>
-      <c r="P425" s="8"/>
+      <c r="P425" s="8" t="s">
+        <v>2243</v>
+      </c>
     </row>
     <row r="426" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A426" t="s">
         <v>43</v>
       </c>
       <c r="B426" t="s">
-        <v>2229</v>
+        <v>2244</v>
+      </c>
+      <c r="E426" t="s">
+        <v>85</v>
+      </c>
+      <c r="F426" t="s">
+        <v>61</v>
       </c>
       <c r="G426" t="s">
-        <v>2230</v>
+        <v>2245</v>
       </c>
       <c r="H426" t="s">
-        <v>2231</v>
+        <v>2246</v>
       </c>
       <c r="I426" t="s">
         <v>51</v>
       </c>
       <c r="J426" t="s">
-        <v>2232</v>
+        <v>2247</v>
       </c>
       <c r="K426">
         <v>1998</v>
       </c>
-      <c r="P426" s="8"/>
+      <c r="P426" s="8" t="s">
+        <v>2248</v>
+      </c>
     </row>
     <row r="427" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A427" t="s">
         <v>43</v>
       </c>
       <c r="B427" t="s">
-        <v>2233</v>
+        <v>2249</v>
+      </c>
+      <c r="E427" t="s">
+        <v>85</v>
+      </c>
+      <c r="F427" t="s">
+        <v>48</v>
       </c>
       <c r="G427" t="s">
-        <v>2234</v>
+        <v>2250</v>
       </c>
       <c r="H427" t="s">
-        <v>2235</v>
+        <v>2251</v>
       </c>
       <c r="I427" t="s">
-        <v>2236</v>
+        <v>2252</v>
       </c>
       <c r="J427" t="s">
-        <v>2237</v>
+        <v>2253</v>
       </c>
       <c r="K427">
         <v>1977</v>
       </c>
-      <c r="P427" s="8"/>
+      <c r="P427" s="8" t="s">
+        <v>2254</v>
+      </c>
     </row>
     <row r="428" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A428" t="s">
         <v>43</v>
       </c>
       <c r="B428" t="s">
-        <v>2238</v>
+        <v>2255</v>
+      </c>
+      <c r="E428" t="s">
+        <v>85</v>
+      </c>
+      <c r="F428" t="s">
+        <v>48</v>
       </c>
       <c r="G428" t="s">
-        <v>2239</v>
+        <v>2256</v>
       </c>
       <c r="H428" t="s">
-        <v>2240</v>
+        <v>2257</v>
       </c>
       <c r="I428" t="s">
-        <v>2241</v>
+        <v>2258</v>
       </c>
       <c r="J428" t="s">
-        <v>2242</v>
+        <v>2259</v>
       </c>
       <c r="K428">
         <v>2023</v>
       </c>
-      <c r="P428" s="8"/>
+      <c r="P428" s="8" t="s">
+        <v>2260</v>
+      </c>
     </row>
     <row r="429" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A429" t="s">
         <v>43</v>
       </c>
       <c r="B429" t="s">
-        <v>2243</v>
+        <v>2261</v>
+      </c>
+      <c r="E429" t="s">
+        <v>85</v>
+      </c>
+      <c r="F429" t="s">
+        <v>61</v>
       </c>
       <c r="G429" t="s">
-        <v>2244</v>
+        <v>2262</v>
       </c>
       <c r="H429" t="s">
-        <v>2245</v>
+        <v>2263</v>
       </c>
       <c r="I429" t="s">
         <v>481</v>
       </c>
       <c r="J429" t="s">
-        <v>2246</v>
+        <v>2264</v>
       </c>
       <c r="K429">
         <v>1994</v>
       </c>
-      <c r="P429" s="8"/>
+      <c r="P429" s="8" t="s">
+        <v>2265</v>
+      </c>
     </row>
     <row r="430" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A430" t="s">
         <v>43</v>
       </c>
       <c r="B430" t="s">
-        <v>2247</v>
+        <v>2266</v>
+      </c>
+      <c r="E430" t="s">
+        <v>85</v>
+      </c>
+      <c r="F430" t="s">
+        <v>48</v>
       </c>
       <c r="G430" t="s">
-        <v>2248</v>
+        <v>2267</v>
       </c>
       <c r="H430" t="s">
-        <v>2249</v>
+        <v>2268</v>
       </c>
       <c r="I430" t="s">
-        <v>2250</v>
+        <v>2269</v>
       </c>
       <c r="J430" t="s">
-        <v>2251</v>
+        <v>2270</v>
       </c>
       <c r="K430">
         <v>2025</v>
       </c>
-      <c r="P430" s="8"/>
+      <c r="P430" s="8" t="s">
+        <v>2271</v>
+      </c>
     </row>
     <row r="431" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A431" t="s">
         <v>43</v>
       </c>
       <c r="B431" t="s">
-        <v>2252</v>
+        <v>2272</v>
+      </c>
+      <c r="E431" t="s">
+        <v>85</v>
+      </c>
+      <c r="F431" t="s">
+        <v>61</v>
       </c>
       <c r="G431" t="s">
-        <v>2253</v>
+        <v>2273</v>
       </c>
       <c r="H431" t="s">
-        <v>2254</v>
+        <v>2274</v>
       </c>
       <c r="I431" t="s">
-        <v>2255</v>
+        <v>2275</v>
       </c>
       <c r="J431" t="s">
-        <v>2256</v>
+        <v>2276</v>
       </c>
       <c r="K431">
         <v>1996</v>
       </c>
-      <c r="P431" s="8"/>
+      <c r="P431" s="8" t="s">
+        <v>2277</v>
+      </c>
     </row>
     <row r="432" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A432" t="s">
         <v>43</v>
       </c>
       <c r="B432" t="s">
-        <v>2257</v>
+        <v>2278</v>
+      </c>
+      <c r="E432" t="s">
+        <v>85</v>
+      </c>
+      <c r="F432" t="s">
+        <v>54</v>
       </c>
       <c r="G432" t="s">
-        <v>2258</v>
+        <v>2279</v>
       </c>
       <c r="H432" t="s">
-        <v>2259</v>
+        <v>2280</v>
       </c>
       <c r="I432" t="s">
-        <v>2260</v>
+        <v>2281</v>
       </c>
       <c r="J432" t="s">
-        <v>2261</v>
+        <v>2282</v>
       </c>
       <c r="K432">
         <v>2019</v>
       </c>
-      <c r="P432" s="8"/>
+      <c r="P432" s="8" t="s">
+        <v>3605</v>
+      </c>
     </row>
     <row r="433" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A433" t="s">
         <v>43</v>
       </c>
       <c r="B433" t="s">
-        <v>2262</v>
+        <v>2283</v>
+      </c>
+      <c r="E433" t="s">
+        <v>85</v>
+      </c>
+      <c r="F433" t="s">
+        <v>61</v>
       </c>
       <c r="G433" t="s">
-        <v>2263</v>
+        <v>2284</v>
       </c>
       <c r="H433" t="s">
-        <v>2264</v>
+        <v>2285</v>
       </c>
       <c r="I433" t="s">
         <v>357</v>
       </c>
       <c r="J433" t="s">
-        <v>2265</v>
+        <v>2286</v>
       </c>
       <c r="K433">
         <v>1998</v>
       </c>
-      <c r="P433" s="8"/>
+      <c r="P433" s="8" t="s">
+        <v>2287</v>
+      </c>
     </row>
     <row r="434" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A434" t="s">
         <v>43</v>
       </c>
       <c r="B434" t="s">
-        <v>2266</v>
+        <v>2288</v>
+      </c>
+      <c r="E434" t="s">
+        <v>85</v>
+      </c>
+      <c r="F434" t="s">
+        <v>61</v>
       </c>
       <c r="G434" t="s">
-        <v>2267</v>
+        <v>2289</v>
       </c>
       <c r="H434" t="s">
-        <v>2268</v>
+        <v>2290</v>
       </c>
       <c r="I434" t="s">
         <v>1461</v>
       </c>
       <c r="J434" t="s">
-        <v>2269</v>
+        <v>2291</v>
       </c>
       <c r="K434">
         <v>2025</v>
       </c>
-      <c r="P434" s="8"/>
+      <c r="P434" s="8" t="s">
+        <v>2292</v>
+      </c>
     </row>
     <row r="435" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A435" t="s">
         <v>43</v>
       </c>
       <c r="B435" t="s">
-        <v>2270</v>
+        <v>2293</v>
+      </c>
+      <c r="E435" t="s">
+        <v>85</v>
+      </c>
+      <c r="F435" t="s">
+        <v>54</v>
       </c>
       <c r="G435" t="s">
-        <v>2271</v>
+        <v>2294</v>
       </c>
       <c r="H435" t="s">
-        <v>2272</v>
+        <v>2295</v>
       </c>
       <c r="I435" t="s">
         <v>508</v>
       </c>
       <c r="J435" t="s">
-        <v>2273</v>
+        <v>2296</v>
       </c>
       <c r="K435">
         <v>2014</v>
       </c>
-      <c r="P435" s="8"/>
+      <c r="P435" s="8" t="s">
+        <v>3606</v>
+      </c>
     </row>
     <row r="436" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A436" t="s">
         <v>43</v>
       </c>
       <c r="B436" t="s">
-        <v>2274</v>
+        <v>2297</v>
+      </c>
+      <c r="E436" t="s">
+        <v>85</v>
+      </c>
+      <c r="F436" t="s">
+        <v>61</v>
       </c>
       <c r="G436" t="s">
-        <v>2275</v>
+        <v>2298</v>
       </c>
       <c r="H436" t="s">
-        <v>2276</v>
+        <v>2299</v>
       </c>
       <c r="I436" t="s">
         <v>786</v>
       </c>
       <c r="J436" t="s">
-        <v>2277</v>
+        <v>2300</v>
       </c>
       <c r="K436">
         <v>2005</v>
       </c>
-      <c r="P436" s="8"/>
+      <c r="P436" s="8" t="s">
+        <v>3607</v>
+      </c>
     </row>
     <row r="437" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A437" t="s">
         <v>43</v>
       </c>
       <c r="B437" t="s">
-        <v>2278</v>
+        <v>2301</v>
+      </c>
+      <c r="E437">
+        <v>0</v>
+      </c>
+      <c r="F437" t="s">
+        <v>48</v>
       </c>
       <c r="G437" t="s">
-        <v>2279</v>
+        <v>2302</v>
       </c>
       <c r="H437" t="s">
-        <v>2280</v>
+        <v>2303</v>
       </c>
       <c r="I437" t="s">
         <v>51</v>
       </c>
       <c r="J437" t="s">
-        <v>2281</v>
+        <v>2304</v>
       </c>
       <c r="K437">
         <v>1989</v>
       </c>
-      <c r="P437" s="8"/>
+      <c r="P437" s="8" t="s">
+        <v>2226</v>
+      </c>
     </row>
     <row r="438" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A438" t="s">
         <v>43</v>
       </c>
       <c r="B438" t="s">
-        <v>2282</v>
+        <v>2305</v>
+      </c>
+      <c r="E438" t="s">
+        <v>85</v>
+      </c>
+      <c r="F438" t="s">
+        <v>252</v>
       </c>
       <c r="G438" t="s">
-        <v>2283</v>
+        <v>2306</v>
       </c>
       <c r="H438" t="s">
-        <v>2284</v>
+        <v>2307</v>
       </c>
       <c r="I438" t="s">
-        <v>2285</v>
+        <v>2308</v>
       </c>
       <c r="J438" t="s">
-        <v>2286</v>
+        <v>2309</v>
       </c>
       <c r="K438">
         <v>2019</v>
       </c>
-      <c r="P438" s="8"/>
+      <c r="P438" s="8" t="s">
+        <v>3608</v>
+      </c>
     </row>
     <row r="439" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A439" t="s">
         <v>43</v>
       </c>
       <c r="B439" t="s">
-        <v>2287</v>
+        <v>2310</v>
+      </c>
+      <c r="E439" t="s">
+        <v>85</v>
+      </c>
+      <c r="F439" t="s">
+        <v>61</v>
       </c>
       <c r="G439" t="s">
-        <v>2288</v>
+        <v>2311</v>
       </c>
       <c r="H439" t="s">
-        <v>2289</v>
+        <v>2312</v>
       </c>
       <c r="I439" t="s">
-        <v>2290</v>
+        <v>2313</v>
       </c>
       <c r="J439" t="s">
-        <v>2291</v>
+        <v>2314</v>
       </c>
       <c r="K439">
         <v>2017</v>
       </c>
-      <c r="P439" s="8"/>
+      <c r="P439" s="8" t="s">
+        <v>2315</v>
+      </c>
     </row>
     <row r="440" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A440" t="s">
         <v>43</v>
       </c>
       <c r="B440" t="s">
-        <v>2292</v>
+        <v>2316</v>
+      </c>
+      <c r="E440" t="s">
+        <v>85</v>
+      </c>
+      <c r="F440" t="s">
+        <v>54</v>
       </c>
       <c r="G440" t="s">
-        <v>2293</v>
+        <v>2317</v>
       </c>
       <c r="H440" t="s">
-        <v>2294</v>
+        <v>2318</v>
       </c>
       <c r="I440" t="s">
-        <v>2295</v>
+        <v>2319</v>
       </c>
       <c r="J440" t="s">
-        <v>2296</v>
+        <v>2320</v>
       </c>
       <c r="K440">
         <v>1998</v>
       </c>
-      <c r="P440" s="8"/>
+      <c r="P440" s="8" t="s">
+        <v>2321</v>
+      </c>
     </row>
     <row r="441" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A441" t="s">
         <v>43</v>
       </c>
       <c r="B441" t="s">
-        <v>2297</v>
+        <v>2322</v>
+      </c>
+      <c r="E441" t="s">
+        <v>85</v>
+      </c>
+      <c r="F441" t="s">
+        <v>48</v>
       </c>
       <c r="G441" t="s">
-        <v>2298</v>
+        <v>2323</v>
       </c>
       <c r="H441" t="s">
-        <v>2299</v>
+        <v>2324</v>
       </c>
       <c r="I441" t="s">
-        <v>2300</v>
+        <v>2325</v>
       </c>
       <c r="J441" t="s">
-        <v>2301</v>
+        <v>2326</v>
       </c>
       <c r="K441">
         <v>2020</v>
       </c>
-      <c r="P441" s="8"/>
+      <c r="P441" s="8" t="s">
+        <v>2327</v>
+      </c>
     </row>
     <row r="442" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A442" t="s">
         <v>43</v>
       </c>
       <c r="B442" t="s">
-        <v>2302</v>
+        <v>2328</v>
+      </c>
+      <c r="E442" t="s">
+        <v>85</v>
+      </c>
+      <c r="F442" t="s">
+        <v>48</v>
       </c>
       <c r="G442" t="s">
-        <v>2303</v>
+        <v>2329</v>
       </c>
       <c r="H442" t="s">
-        <v>2304</v>
+        <v>2330</v>
       </c>
       <c r="I442" t="s">
         <v>51</v>
       </c>
       <c r="J442" t="s">
-        <v>2305</v>
+        <v>2331</v>
       </c>
       <c r="K442">
         <v>2020</v>
       </c>
-      <c r="P442" s="8"/>
+      <c r="P442" s="8" t="s">
+        <v>2332</v>
+      </c>
     </row>
     <row r="443" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A443" t="s">
         <v>43</v>
       </c>
       <c r="B443" t="s">
-        <v>2306</v>
+        <v>2333</v>
+      </c>
+      <c r="E443" t="s">
+        <v>85</v>
+      </c>
+      <c r="F443" t="s">
+        <v>54</v>
       </c>
       <c r="G443" t="s">
-        <v>2307</v>
+        <v>2334</v>
       </c>
       <c r="H443" t="s">
-        <v>2308</v>
+        <v>2335</v>
       </c>
       <c r="I443" t="s">
-        <v>2309</v>
+        <v>2336</v>
       </c>
       <c r="J443" t="s">
-        <v>2310</v>
+        <v>2337</v>
       </c>
       <c r="K443">
         <v>2019</v>
       </c>
-      <c r="P443" s="8"/>
+      <c r="P443" s="8" t="s">
+        <v>3609</v>
+      </c>
     </row>
     <row r="444" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A444" t="s">
         <v>43</v>
       </c>
       <c r="B444" t="s">
-        <v>2311</v>
+        <v>2338</v>
+      </c>
+      <c r="E444" t="s">
+        <v>85</v>
+      </c>
+      <c r="F444" t="s">
+        <v>48</v>
       </c>
       <c r="G444" t="s">
-        <v>2312</v>
+        <v>2339</v>
       </c>
       <c r="H444" t="s">
-        <v>2313</v>
+        <v>2340</v>
       </c>
       <c r="I444" t="s">
         <v>712</v>
       </c>
       <c r="J444" t="s">
-        <v>2314</v>
+        <v>2341</v>
       </c>
       <c r="K444">
         <v>2002</v>
       </c>
-      <c r="P444" s="8"/>
+      <c r="P444" s="8" t="s">
+        <v>2342</v>
+      </c>
     </row>
     <row r="445" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A445" t="s">
         <v>43</v>
       </c>
       <c r="B445" t="s">
-        <v>2315</v>
+        <v>2343</v>
+      </c>
+      <c r="E445" t="s">
+        <v>85</v>
+      </c>
+      <c r="F445" t="s">
+        <v>61</v>
       </c>
       <c r="G445" t="s">
-        <v>2316</v>
+        <v>2344</v>
       </c>
       <c r="H445" t="s">
-        <v>2317</v>
+        <v>2345</v>
       </c>
       <c r="I445" t="s">
         <v>51</v>
       </c>
       <c r="J445" t="s">
-        <v>2318</v>
+        <v>2346</v>
       </c>
       <c r="K445">
         <v>2013</v>
       </c>
-      <c r="P445" s="8"/>
+      <c r="P445" s="8" t="s">
+        <v>3610</v>
+      </c>
     </row>
     <row r="446" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A446" t="s">
         <v>43</v>
       </c>
       <c r="B446" t="s">
-        <v>2319</v>
+        <v>2347</v>
+      </c>
+      <c r="E446" t="s">
+        <v>85</v>
+      </c>
+      <c r="F446" t="s">
+        <v>61</v>
       </c>
       <c r="G446" t="s">
-        <v>2320</v>
+        <v>2348</v>
       </c>
       <c r="H446" t="s">
-        <v>2321</v>
+        <v>2349</v>
       </c>
       <c r="I446" t="s">
         <v>266</v>
       </c>
       <c r="J446" t="s">
-        <v>2322</v>
+        <v>2350</v>
       </c>
       <c r="K446">
         <v>2023</v>
       </c>
-      <c r="P446" s="8"/>
+      <c r="P446" s="8" t="s">
+        <v>2351</v>
+      </c>
     </row>
     <row r="447" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A447" t="s">
         <v>43</v>
       </c>
       <c r="B447" t="s">
-        <v>2323</v>
+        <v>2352</v>
       </c>
       <c r="G447" t="s">
-        <v>2324</v>
+        <v>2353</v>
       </c>
       <c r="H447" t="s">
-        <v>2325</v>
+        <v>2354</v>
       </c>
       <c r="I447" t="s">
-        <v>2326</v>
+        <v>2355</v>
       </c>
       <c r="J447" t="s">
-        <v>2327</v>
+        <v>2356</v>
       </c>
       <c r="K447">
         <v>2013</v>
@@ -33146,19 +34065,19 @@
         <v>43</v>
       </c>
       <c r="B448" t="s">
-        <v>2328</v>
+        <v>2357</v>
       </c>
       <c r="G448" t="s">
-        <v>2329</v>
+        <v>2358</v>
       </c>
       <c r="H448" t="s">
-        <v>2330</v>
+        <v>2359</v>
       </c>
       <c r="I448" t="s">
         <v>1819</v>
       </c>
       <c r="J448" t="s">
-        <v>2331</v>
+        <v>2360</v>
       </c>
       <c r="K448">
         <v>2022</v>
@@ -33170,19 +34089,19 @@
         <v>43</v>
       </c>
       <c r="B449" t="s">
-        <v>2332</v>
+        <v>2361</v>
       </c>
       <c r="G449" t="s">
-        <v>2333</v>
+        <v>2362</v>
       </c>
       <c r="H449" t="s">
-        <v>2334</v>
+        <v>2363</v>
       </c>
       <c r="I449" t="s">
-        <v>2205</v>
+        <v>2216</v>
       </c>
       <c r="J449" t="s">
-        <v>2335</v>
+        <v>2364</v>
       </c>
       <c r="K449">
         <v>2016</v>
@@ -33194,19 +34113,19 @@
         <v>43</v>
       </c>
       <c r="B450" t="s">
-        <v>2336</v>
+        <v>2365</v>
       </c>
       <c r="G450" t="s">
-        <v>2337</v>
+        <v>2366</v>
       </c>
       <c r="H450" t="s">
-        <v>2338</v>
+        <v>2367</v>
       </c>
       <c r="I450" t="s">
         <v>1924</v>
       </c>
       <c r="J450" t="s">
-        <v>2339</v>
+        <v>2368</v>
       </c>
       <c r="K450">
         <v>2010</v>
@@ -33218,19 +34137,19 @@
         <v>43</v>
       </c>
       <c r="B451" t="s">
-        <v>2340</v>
+        <v>2369</v>
       </c>
       <c r="G451" t="s">
-        <v>2341</v>
+        <v>2370</v>
       </c>
       <c r="H451" t="s">
-        <v>2342</v>
+        <v>2371</v>
       </c>
       <c r="I451" t="s">
         <v>51</v>
       </c>
       <c r="J451" t="s">
-        <v>2343</v>
+        <v>2372</v>
       </c>
       <c r="K451">
         <v>2013</v>
@@ -33242,19 +34161,19 @@
         <v>43</v>
       </c>
       <c r="B452" t="s">
-        <v>2344</v>
+        <v>2373</v>
       </c>
       <c r="G452" t="s">
-        <v>2345</v>
+        <v>2374</v>
       </c>
       <c r="H452" t="s">
-        <v>2346</v>
+        <v>2375</v>
       </c>
       <c r="I452" t="s">
         <v>295</v>
       </c>
       <c r="J452" t="s">
-        <v>2347</v>
+        <v>2376</v>
       </c>
       <c r="K452">
         <v>2008</v>
@@ -33266,19 +34185,19 @@
         <v>43</v>
       </c>
       <c r="B453" t="s">
-        <v>2348</v>
+        <v>2377</v>
       </c>
       <c r="G453" t="s">
-        <v>2349</v>
+        <v>2378</v>
       </c>
       <c r="H453" t="s">
-        <v>2350</v>
+        <v>2379</v>
       </c>
       <c r="I453" t="s">
         <v>692</v>
       </c>
       <c r="J453" t="s">
-        <v>2351</v>
+        <v>2380</v>
       </c>
       <c r="K453">
         <v>2007</v>
@@ -33290,19 +34209,19 @@
         <v>43</v>
       </c>
       <c r="B454" t="s">
-        <v>2352</v>
+        <v>2381</v>
       </c>
       <c r="G454" t="s">
-        <v>2353</v>
+        <v>2382</v>
       </c>
       <c r="H454" t="s">
-        <v>2354</v>
+        <v>2383</v>
       </c>
       <c r="I454" t="s">
-        <v>2355</v>
+        <v>2384</v>
       </c>
       <c r="J454" t="s">
-        <v>2356</v>
+        <v>2385</v>
       </c>
       <c r="K454">
         <v>2003</v>
@@ -33314,19 +34233,19 @@
         <v>43</v>
       </c>
       <c r="B455" t="s">
-        <v>2357</v>
+        <v>2386</v>
       </c>
       <c r="G455" t="s">
-        <v>2358</v>
+        <v>2387</v>
       </c>
       <c r="H455" t="s">
-        <v>2359</v>
+        <v>2388</v>
       </c>
       <c r="I455" t="s">
-        <v>2178</v>
+        <v>2184</v>
       </c>
       <c r="J455" t="s">
-        <v>2360</v>
+        <v>2389</v>
       </c>
       <c r="K455">
         <v>2024</v>
@@ -33338,19 +34257,19 @@
         <v>43</v>
       </c>
       <c r="B456" t="s">
-        <v>2361</v>
+        <v>2390</v>
       </c>
       <c r="G456" t="s">
-        <v>2362</v>
+        <v>2391</v>
       </c>
       <c r="H456" t="s">
-        <v>2363</v>
+        <v>2392</v>
       </c>
       <c r="I456" t="s">
-        <v>2364</v>
+        <v>2393</v>
       </c>
       <c r="J456" t="s">
-        <v>2365</v>
+        <v>2394</v>
       </c>
       <c r="K456">
         <v>2022</v>
@@ -33362,19 +34281,19 @@
         <v>43</v>
       </c>
       <c r="B457" t="s">
-        <v>2366</v>
+        <v>2395</v>
       </c>
       <c r="G457" t="s">
-        <v>2367</v>
+        <v>2396</v>
       </c>
       <c r="H457" t="s">
-        <v>2368</v>
+        <v>2397</v>
       </c>
       <c r="I457" t="s">
         <v>220</v>
       </c>
       <c r="J457" t="s">
-        <v>2369</v>
+        <v>2398</v>
       </c>
       <c r="K457">
         <v>2019</v>
@@ -33386,19 +34305,19 @@
         <v>43</v>
       </c>
       <c r="B458" t="s">
-        <v>2370</v>
+        <v>2399</v>
       </c>
       <c r="G458" t="s">
-        <v>2371</v>
+        <v>2400</v>
       </c>
       <c r="H458" t="s">
-        <v>2372</v>
+        <v>2401</v>
       </c>
       <c r="I458" t="s">
-        <v>2373</v>
+        <v>2402</v>
       </c>
       <c r="J458" t="s">
-        <v>2374</v>
+        <v>2403</v>
       </c>
       <c r="K458">
         <v>2024</v>
@@ -33410,19 +34329,19 @@
         <v>43</v>
       </c>
       <c r="B459" t="s">
-        <v>2375</v>
+        <v>2404</v>
       </c>
       <c r="G459" t="s">
-        <v>2376</v>
+        <v>2405</v>
       </c>
       <c r="H459" t="s">
-        <v>2377</v>
+        <v>2406</v>
       </c>
       <c r="I459" t="s">
         <v>915</v>
       </c>
       <c r="J459" t="s">
-        <v>2378</v>
+        <v>2407</v>
       </c>
       <c r="K459">
         <v>2003</v>
@@ -33434,19 +34353,19 @@
         <v>43</v>
       </c>
       <c r="B460" t="s">
-        <v>2379</v>
+        <v>2408</v>
       </c>
       <c r="G460" t="s">
-        <v>2380</v>
+        <v>2409</v>
       </c>
       <c r="H460" t="s">
-        <v>2381</v>
+        <v>2410</v>
       </c>
       <c r="I460" t="s">
-        <v>2382</v>
+        <v>2411</v>
       </c>
       <c r="J460" t="s">
-        <v>2383</v>
+        <v>2412</v>
       </c>
       <c r="K460">
         <v>2024</v>
@@ -33458,19 +34377,19 @@
         <v>43</v>
       </c>
       <c r="B461" t="s">
-        <v>2384</v>
+        <v>2413</v>
       </c>
       <c r="G461" t="s">
-        <v>2385</v>
+        <v>2414</v>
       </c>
       <c r="H461" t="s">
-        <v>2386</v>
+        <v>2415</v>
       </c>
       <c r="I461" t="s">
         <v>51</v>
       </c>
       <c r="J461" t="s">
-        <v>2387</v>
+        <v>2416</v>
       </c>
       <c r="K461">
         <v>2023</v>
@@ -33482,19 +34401,19 @@
         <v>43</v>
       </c>
       <c r="B462" t="s">
-        <v>2388</v>
+        <v>2417</v>
       </c>
       <c r="G462" t="s">
-        <v>2389</v>
+        <v>2418</v>
       </c>
       <c r="H462" t="s">
-        <v>2390</v>
+        <v>2419</v>
       </c>
       <c r="I462" t="s">
-        <v>2391</v>
+        <v>2420</v>
       </c>
       <c r="J462" t="s">
-        <v>2392</v>
+        <v>2421</v>
       </c>
       <c r="K462">
         <v>1995</v>
@@ -33506,19 +34425,19 @@
         <v>43</v>
       </c>
       <c r="B463" t="s">
-        <v>2393</v>
+        <v>2422</v>
       </c>
       <c r="G463" t="s">
-        <v>2394</v>
+        <v>2423</v>
       </c>
       <c r="H463" t="s">
-        <v>2395</v>
+        <v>2424</v>
       </c>
       <c r="I463" t="s">
         <v>51</v>
       </c>
       <c r="J463" t="s">
-        <v>2392</v>
+        <v>2421</v>
       </c>
       <c r="K463">
         <v>1989</v>
@@ -33530,19 +34449,19 @@
         <v>43</v>
       </c>
       <c r="B464" t="s">
-        <v>2396</v>
+        <v>2425</v>
       </c>
       <c r="G464" t="s">
-        <v>2397</v>
+        <v>2426</v>
       </c>
       <c r="H464" t="s">
-        <v>2398</v>
+        <v>2427</v>
       </c>
       <c r="I464" t="s">
-        <v>2236</v>
+        <v>2252</v>
       </c>
       <c r="J464" t="s">
-        <v>2399</v>
+        <v>2428</v>
       </c>
       <c r="K464">
         <v>1996</v>
@@ -33554,19 +34473,19 @@
         <v>43</v>
       </c>
       <c r="B465" t="s">
-        <v>2400</v>
+        <v>2429</v>
       </c>
       <c r="G465" t="s">
-        <v>2401</v>
+        <v>2430</v>
       </c>
       <c r="H465" t="s">
-        <v>2402</v>
+        <v>2431</v>
       </c>
       <c r="I465" t="s">
-        <v>2403</v>
+        <v>2432</v>
       </c>
       <c r="J465" t="s">
-        <v>2404</v>
+        <v>2433</v>
       </c>
       <c r="K465">
         <v>2021</v>
@@ -33578,19 +34497,19 @@
         <v>43</v>
       </c>
       <c r="B466" t="s">
-        <v>2405</v>
+        <v>2434</v>
       </c>
       <c r="G466" t="s">
-        <v>2406</v>
+        <v>2435</v>
       </c>
       <c r="H466" t="s">
-        <v>2407</v>
+        <v>2436</v>
       </c>
       <c r="I466" t="s">
         <v>128</v>
       </c>
       <c r="J466" t="s">
-        <v>2408</v>
+        <v>2437</v>
       </c>
       <c r="K466">
         <v>2017</v>
@@ -33602,19 +34521,19 @@
         <v>43</v>
       </c>
       <c r="B467" t="s">
-        <v>2409</v>
+        <v>2438</v>
       </c>
       <c r="G467" t="s">
-        <v>2410</v>
+        <v>2439</v>
       </c>
       <c r="H467" t="s">
-        <v>2411</v>
+        <v>2440</v>
       </c>
       <c r="I467" t="s">
-        <v>2412</v>
+        <v>2441</v>
       </c>
       <c r="J467" t="s">
-        <v>2413</v>
+        <v>2442</v>
       </c>
       <c r="K467">
         <v>2023</v>
@@ -33626,19 +34545,19 @@
         <v>43</v>
       </c>
       <c r="B468" t="s">
-        <v>2414</v>
+        <v>2443</v>
       </c>
       <c r="G468" t="s">
-        <v>2415</v>
+        <v>2444</v>
       </c>
       <c r="H468" t="s">
-        <v>2416</v>
+        <v>2445</v>
       </c>
       <c r="I468" t="s">
-        <v>2417</v>
+        <v>2446</v>
       </c>
       <c r="J468" t="s">
-        <v>2418</v>
+        <v>2447</v>
       </c>
       <c r="K468">
         <v>2012</v>
@@ -33650,19 +34569,19 @@
         <v>43</v>
       </c>
       <c r="B469" t="s">
-        <v>2419</v>
+        <v>2448</v>
       </c>
       <c r="G469" t="s">
-        <v>2420</v>
+        <v>2449</v>
       </c>
       <c r="H469" t="s">
-        <v>2421</v>
+        <v>2450</v>
       </c>
       <c r="I469" t="s">
-        <v>2422</v>
+        <v>2451</v>
       </c>
       <c r="J469" t="s">
-        <v>2423</v>
+        <v>2452</v>
       </c>
       <c r="K469">
         <v>2021</v>
@@ -33674,19 +34593,19 @@
         <v>43</v>
       </c>
       <c r="B470" t="s">
-        <v>2424</v>
+        <v>2453</v>
       </c>
       <c r="G470" t="s">
-        <v>2425</v>
+        <v>2454</v>
       </c>
       <c r="H470" t="s">
-        <v>2426</v>
+        <v>2455</v>
       </c>
       <c r="I470" t="s">
         <v>409</v>
       </c>
       <c r="J470" t="s">
-        <v>2427</v>
+        <v>2456</v>
       </c>
       <c r="K470">
         <v>2022</v>
@@ -33698,19 +34617,19 @@
         <v>43</v>
       </c>
       <c r="B471" t="s">
-        <v>2428</v>
+        <v>2457</v>
       </c>
       <c r="G471" t="s">
-        <v>2429</v>
+        <v>2458</v>
       </c>
       <c r="H471" t="s">
-        <v>2430</v>
+        <v>2459</v>
       </c>
       <c r="I471" t="s">
         <v>51</v>
       </c>
       <c r="J471" t="s">
-        <v>2431</v>
+        <v>2460</v>
       </c>
       <c r="K471">
         <v>2018</v>
@@ -33722,19 +34641,19 @@
         <v>43</v>
       </c>
       <c r="B472" t="s">
-        <v>2432</v>
+        <v>2461</v>
       </c>
       <c r="G472" t="s">
-        <v>2433</v>
+        <v>2462</v>
       </c>
       <c r="H472" t="s">
-        <v>2434</v>
+        <v>2463</v>
       </c>
       <c r="I472" t="s">
         <v>51</v>
       </c>
       <c r="J472" t="s">
-        <v>2435</v>
+        <v>2464</v>
       </c>
       <c r="K472">
         <v>2021</v>
@@ -33746,19 +34665,19 @@
         <v>43</v>
       </c>
       <c r="B473" t="s">
-        <v>2436</v>
+        <v>2465</v>
       </c>
       <c r="G473" t="s">
-        <v>2437</v>
+        <v>2466</v>
       </c>
       <c r="H473" t="s">
-        <v>2438</v>
+        <v>2467</v>
       </c>
       <c r="I473" t="s">
-        <v>2236</v>
+        <v>2252</v>
       </c>
       <c r="J473" t="s">
-        <v>2439</v>
+        <v>2468</v>
       </c>
       <c r="K473">
         <v>1982</v>
@@ -33770,19 +34689,19 @@
         <v>43</v>
       </c>
       <c r="B474" t="s">
-        <v>2440</v>
+        <v>2469</v>
       </c>
       <c r="G474" t="s">
-        <v>2441</v>
+        <v>2470</v>
       </c>
       <c r="H474" t="s">
-        <v>2442</v>
+        <v>2471</v>
       </c>
       <c r="I474" t="s">
         <v>2054</v>
       </c>
       <c r="J474" t="s">
-        <v>2443</v>
+        <v>2472</v>
       </c>
       <c r="K474">
         <v>2014</v>
@@ -33794,19 +34713,19 @@
         <v>43</v>
       </c>
       <c r="B475" t="s">
-        <v>2444</v>
+        <v>2473</v>
       </c>
       <c r="G475" t="s">
-        <v>2445</v>
+        <v>2474</v>
       </c>
       <c r="H475" t="s">
-        <v>2446</v>
+        <v>2475</v>
       </c>
       <c r="I475" t="s">
-        <v>2447</v>
+        <v>2476</v>
       </c>
       <c r="J475" t="s">
-        <v>2448</v>
+        <v>2477</v>
       </c>
       <c r="K475">
         <v>2005</v>
@@ -33818,19 +34737,19 @@
         <v>43</v>
       </c>
       <c r="B476" t="s">
-        <v>2449</v>
+        <v>2478</v>
       </c>
       <c r="G476" t="s">
-        <v>2450</v>
+        <v>2479</v>
       </c>
       <c r="H476" t="s">
-        <v>2451</v>
+        <v>2480</v>
       </c>
       <c r="I476" t="s">
         <v>1652</v>
       </c>
       <c r="J476" t="s">
-        <v>2452</v>
+        <v>2481</v>
       </c>
       <c r="K476">
         <v>2011</v>
@@ -33842,19 +34761,19 @@
         <v>43</v>
       </c>
       <c r="B477" t="s">
-        <v>2453</v>
+        <v>2482</v>
       </c>
       <c r="G477" t="s">
-        <v>2454</v>
+        <v>2483</v>
       </c>
       <c r="H477" t="s">
-        <v>2455</v>
+        <v>2484</v>
       </c>
       <c r="I477" t="s">
         <v>307</v>
       </c>
       <c r="J477" t="s">
-        <v>2456</v>
+        <v>2485</v>
       </c>
       <c r="K477">
         <v>1979</v>
@@ -33866,19 +34785,19 @@
         <v>43</v>
       </c>
       <c r="B478" t="s">
-        <v>2457</v>
+        <v>2486</v>
       </c>
       <c r="G478" t="s">
-        <v>2458</v>
+        <v>2487</v>
       </c>
       <c r="H478" t="s">
-        <v>2459</v>
+        <v>2488</v>
       </c>
       <c r="I478" t="s">
         <v>1314</v>
       </c>
       <c r="J478" t="s">
-        <v>2460</v>
+        <v>2489</v>
       </c>
       <c r="K478">
         <v>1985</v>
@@ -33890,19 +34809,19 @@
         <v>43</v>
       </c>
       <c r="B479" t="s">
-        <v>2461</v>
+        <v>2490</v>
       </c>
       <c r="G479" t="s">
-        <v>2462</v>
+        <v>2491</v>
       </c>
       <c r="H479" t="s">
-        <v>2463</v>
+        <v>2492</v>
       </c>
       <c r="I479" t="s">
         <v>1862</v>
       </c>
       <c r="J479" t="s">
-        <v>2464</v>
+        <v>2493</v>
       </c>
       <c r="K479">
         <v>2011</v>
@@ -33914,19 +34833,19 @@
         <v>43</v>
       </c>
       <c r="B480" t="s">
-        <v>2465</v>
+        <v>2494</v>
       </c>
       <c r="G480" t="s">
-        <v>2466</v>
+        <v>2495</v>
       </c>
       <c r="H480" t="s">
-        <v>2467</v>
+        <v>2496</v>
       </c>
       <c r="I480" t="s">
         <v>81</v>
       </c>
       <c r="J480" t="s">
-        <v>2468</v>
+        <v>2497</v>
       </c>
       <c r="K480">
         <v>1976</v>
@@ -33938,19 +34857,19 @@
         <v>43</v>
       </c>
       <c r="B481" t="s">
-        <v>2469</v>
+        <v>2498</v>
       </c>
       <c r="G481" t="s">
-        <v>2470</v>
+        <v>2499</v>
       </c>
       <c r="H481" t="s">
-        <v>2471</v>
+        <v>2500</v>
       </c>
       <c r="I481" t="s">
         <v>723</v>
       </c>
       <c r="J481" t="s">
-        <v>2472</v>
+        <v>2501</v>
       </c>
       <c r="K481">
         <v>2006</v>
@@ -33962,19 +34881,19 @@
         <v>43</v>
       </c>
       <c r="B482" t="s">
-        <v>2473</v>
+        <v>2502</v>
       </c>
       <c r="G482" t="s">
-        <v>2474</v>
+        <v>2503</v>
       </c>
       <c r="H482" t="s">
-        <v>2475</v>
+        <v>2504</v>
       </c>
       <c r="I482" t="s">
-        <v>2178</v>
+        <v>2184</v>
       </c>
       <c r="J482" t="s">
-        <v>2476</v>
+        <v>2505</v>
       </c>
       <c r="K482">
         <v>2001</v>
@@ -33986,19 +34905,19 @@
         <v>43</v>
       </c>
       <c r="B483" t="s">
-        <v>2477</v>
+        <v>2506</v>
       </c>
       <c r="G483" t="s">
-        <v>2478</v>
+        <v>2507</v>
       </c>
       <c r="H483" t="s">
-        <v>2479</v>
+        <v>2508</v>
       </c>
       <c r="I483" t="s">
         <v>51</v>
       </c>
       <c r="J483" t="s">
-        <v>2480</v>
+        <v>2509</v>
       </c>
       <c r="K483">
         <v>2020</v>
@@ -34010,19 +34929,19 @@
         <v>43</v>
       </c>
       <c r="B484" t="s">
-        <v>2481</v>
+        <v>2510</v>
       </c>
       <c r="G484" t="s">
-        <v>2482</v>
+        <v>2511</v>
       </c>
       <c r="H484" t="s">
-        <v>2483</v>
+        <v>2512</v>
       </c>
       <c r="I484" t="s">
         <v>1359</v>
       </c>
       <c r="J484" t="s">
-        <v>2484</v>
+        <v>2513</v>
       </c>
       <c r="K484">
         <v>2013</v>
@@ -34034,19 +34953,19 @@
         <v>43</v>
       </c>
       <c r="B485" t="s">
-        <v>2485</v>
+        <v>2514</v>
       </c>
       <c r="G485" t="s">
-        <v>2486</v>
+        <v>2515</v>
       </c>
       <c r="H485" t="s">
-        <v>2487</v>
+        <v>2516</v>
       </c>
       <c r="I485" t="s">
         <v>295</v>
       </c>
       <c r="J485" t="s">
-        <v>2488</v>
+        <v>2517</v>
       </c>
       <c r="K485">
         <v>2012</v>
@@ -34058,19 +34977,19 @@
         <v>43</v>
       </c>
       <c r="B486" t="s">
-        <v>2489</v>
+        <v>2518</v>
       </c>
       <c r="G486" t="s">
-        <v>2490</v>
+        <v>2519</v>
       </c>
       <c r="H486" t="s">
-        <v>2491</v>
+        <v>2520</v>
       </c>
       <c r="I486" t="s">
-        <v>2492</v>
+        <v>2521</v>
       </c>
       <c r="J486" t="s">
-        <v>2493</v>
+        <v>2522</v>
       </c>
       <c r="K486">
         <v>1996</v>
@@ -34082,19 +35001,19 @@
         <v>43</v>
       </c>
       <c r="B487" t="s">
-        <v>2494</v>
+        <v>2523</v>
       </c>
       <c r="G487" t="s">
-        <v>2495</v>
+        <v>2524</v>
       </c>
       <c r="H487" t="s">
-        <v>2496</v>
+        <v>2525</v>
       </c>
       <c r="I487" t="s">
-        <v>2497</v>
+        <v>2526</v>
       </c>
       <c r="J487" t="s">
-        <v>2498</v>
+        <v>2527</v>
       </c>
       <c r="K487">
         <v>1995</v>
@@ -34106,19 +35025,19 @@
         <v>43</v>
       </c>
       <c r="B488" t="s">
-        <v>2499</v>
+        <v>2528</v>
       </c>
       <c r="G488" t="s">
-        <v>2500</v>
+        <v>2529</v>
       </c>
       <c r="H488" t="s">
-        <v>2501</v>
+        <v>2530</v>
       </c>
       <c r="I488" t="s">
         <v>51</v>
       </c>
       <c r="J488" t="s">
-        <v>2502</v>
+        <v>2531</v>
       </c>
       <c r="K488">
         <v>2002</v>
@@ -34130,19 +35049,19 @@
         <v>43</v>
       </c>
       <c r="B489" t="s">
-        <v>2503</v>
+        <v>2532</v>
       </c>
       <c r="G489" t="s">
-        <v>2504</v>
+        <v>2533</v>
       </c>
       <c r="H489" t="s">
-        <v>2505</v>
+        <v>2534</v>
       </c>
       <c r="I489" t="s">
-        <v>2506</v>
+        <v>2535</v>
       </c>
       <c r="J489" t="s">
-        <v>2507</v>
+        <v>2536</v>
       </c>
       <c r="K489">
         <v>2023</v>
@@ -34154,19 +35073,19 @@
         <v>43</v>
       </c>
       <c r="B490" t="s">
-        <v>2508</v>
+        <v>2537</v>
       </c>
       <c r="G490" t="s">
-        <v>2509</v>
+        <v>2538</v>
       </c>
       <c r="H490" t="s">
-        <v>2510</v>
+        <v>2539</v>
       </c>
       <c r="I490" t="s">
-        <v>2511</v>
+        <v>2540</v>
       </c>
       <c r="J490" t="s">
-        <v>2512</v>
+        <v>2541</v>
       </c>
       <c r="K490">
         <v>2011</v>
@@ -34178,19 +35097,19 @@
         <v>43</v>
       </c>
       <c r="B491" t="s">
-        <v>2513</v>
+        <v>2542</v>
       </c>
       <c r="G491" t="s">
-        <v>2514</v>
+        <v>2543</v>
       </c>
       <c r="H491" t="s">
-        <v>2515</v>
+        <v>2544</v>
       </c>
       <c r="I491" t="s">
-        <v>2516</v>
+        <v>2545</v>
       </c>
       <c r="J491" t="s">
-        <v>2512</v>
+        <v>2541</v>
       </c>
       <c r="K491">
         <v>2011</v>
@@ -34202,19 +35121,19 @@
         <v>43</v>
       </c>
       <c r="B492" t="s">
-        <v>2517</v>
+        <v>2546</v>
       </c>
       <c r="G492" t="s">
-        <v>2518</v>
+        <v>2547</v>
       </c>
       <c r="H492" t="s">
-        <v>2519</v>
+        <v>2548</v>
       </c>
       <c r="I492" t="s">
         <v>51</v>
       </c>
       <c r="J492" t="s">
-        <v>2520</v>
+        <v>2549</v>
       </c>
       <c r="K492">
         <v>1984</v>
@@ -34226,19 +35145,19 @@
         <v>43</v>
       </c>
       <c r="B493" t="s">
-        <v>2521</v>
+        <v>2550</v>
       </c>
       <c r="G493" t="s">
-        <v>2522</v>
+        <v>2551</v>
       </c>
       <c r="H493" t="s">
-        <v>2523</v>
+        <v>2552</v>
       </c>
       <c r="I493" t="s">
-        <v>2524</v>
+        <v>2553</v>
       </c>
       <c r="J493" t="s">
-        <v>2525</v>
+        <v>2554</v>
       </c>
       <c r="K493">
         <v>2017</v>
@@ -34250,19 +35169,19 @@
         <v>43</v>
       </c>
       <c r="B494" t="s">
-        <v>2526</v>
+        <v>2555</v>
       </c>
       <c r="G494" t="s">
-        <v>2527</v>
+        <v>2556</v>
       </c>
       <c r="H494" t="s">
-        <v>2528</v>
+        <v>2557</v>
       </c>
       <c r="I494" t="s">
         <v>1729</v>
       </c>
       <c r="J494" t="s">
-        <v>2529</v>
+        <v>2558</v>
       </c>
       <c r="K494">
         <v>2025</v>
@@ -34274,19 +35193,19 @@
         <v>43</v>
       </c>
       <c r="B495" t="s">
-        <v>2530</v>
+        <v>2559</v>
       </c>
       <c r="G495" t="s">
-        <v>2531</v>
+        <v>2560</v>
       </c>
       <c r="H495" t="s">
-        <v>2532</v>
+        <v>2561</v>
       </c>
       <c r="I495" t="s">
         <v>643</v>
       </c>
       <c r="J495" t="s">
-        <v>2533</v>
+        <v>2562</v>
       </c>
       <c r="K495">
         <v>2025</v>
@@ -34298,19 +35217,19 @@
         <v>43</v>
       </c>
       <c r="B496" t="s">
-        <v>2534</v>
+        <v>2563</v>
       </c>
       <c r="G496" t="s">
-        <v>2518</v>
+        <v>2547</v>
       </c>
       <c r="H496" t="s">
-        <v>2535</v>
+        <v>2564</v>
       </c>
       <c r="I496" t="s">
         <v>307</v>
       </c>
       <c r="J496" t="s">
-        <v>2536</v>
+        <v>2565</v>
       </c>
       <c r="K496">
         <v>2020</v>
@@ -34322,19 +35241,19 @@
         <v>43</v>
       </c>
       <c r="B497" t="s">
-        <v>2537</v>
+        <v>2566</v>
       </c>
       <c r="G497" t="s">
-        <v>2538</v>
+        <v>2567</v>
       </c>
       <c r="H497" t="s">
-        <v>2539</v>
+        <v>2568</v>
       </c>
       <c r="I497" t="s">
-        <v>2540</v>
+        <v>2569</v>
       </c>
       <c r="J497" t="s">
-        <v>2541</v>
+        <v>2570</v>
       </c>
       <c r="K497">
         <v>2019</v>
@@ -34346,19 +35265,19 @@
         <v>43</v>
       </c>
       <c r="B498" t="s">
-        <v>2542</v>
+        <v>2571</v>
       </c>
       <c r="G498" t="s">
-        <v>2543</v>
+        <v>2572</v>
       </c>
       <c r="H498" t="s">
-        <v>2544</v>
+        <v>2573</v>
       </c>
       <c r="I498" t="s">
-        <v>2545</v>
+        <v>2574</v>
       </c>
       <c r="J498" t="s">
-        <v>2546</v>
+        <v>2575</v>
       </c>
       <c r="K498">
         <v>2023</v>
@@ -34370,19 +35289,19 @@
         <v>43</v>
       </c>
       <c r="B499" t="s">
-        <v>2547</v>
+        <v>2576</v>
       </c>
       <c r="G499" t="s">
-        <v>2548</v>
+        <v>2577</v>
       </c>
       <c r="H499" t="s">
-        <v>2549</v>
+        <v>2578</v>
       </c>
       <c r="I499" t="s">
         <v>687</v>
       </c>
       <c r="J499" t="s">
-        <v>2550</v>
+        <v>2579</v>
       </c>
       <c r="K499">
         <v>2001</v>
@@ -34394,19 +35313,19 @@
         <v>43</v>
       </c>
       <c r="B500" t="s">
-        <v>2551</v>
+        <v>2580</v>
       </c>
       <c r="G500" t="s">
-        <v>2552</v>
+        <v>2581</v>
       </c>
       <c r="H500" t="s">
-        <v>2553</v>
+        <v>2582</v>
       </c>
       <c r="I500" t="s">
         <v>723</v>
       </c>
       <c r="J500" t="s">
-        <v>2554</v>
+        <v>2583</v>
       </c>
       <c r="K500">
         <v>2022</v>
@@ -34418,19 +35337,19 @@
         <v>43</v>
       </c>
       <c r="B501" t="s">
-        <v>2555</v>
+        <v>2584</v>
       </c>
       <c r="G501" t="s">
-        <v>2556</v>
+        <v>2585</v>
       </c>
       <c r="H501" t="s">
-        <v>2557</v>
+        <v>2586</v>
       </c>
       <c r="I501" t="s">
         <v>253</v>
       </c>
       <c r="J501" t="s">
-        <v>2558</v>
+        <v>2587</v>
       </c>
       <c r="K501">
         <v>2001</v>
@@ -34442,19 +35361,19 @@
         <v>43</v>
       </c>
       <c r="B502" t="s">
-        <v>2559</v>
+        <v>2588</v>
       </c>
       <c r="G502" t="s">
-        <v>2560</v>
+        <v>2589</v>
       </c>
       <c r="H502" t="s">
-        <v>2561</v>
+        <v>2590</v>
       </c>
       <c r="I502" t="s">
         <v>307</v>
       </c>
       <c r="J502" t="s">
-        <v>2562</v>
+        <v>2591</v>
       </c>
       <c r="K502">
         <v>1976</v>
@@ -34466,19 +35385,19 @@
         <v>43</v>
       </c>
       <c r="B503" t="s">
-        <v>2563</v>
+        <v>2592</v>
       </c>
       <c r="G503" t="s">
-        <v>2564</v>
+        <v>2593</v>
       </c>
       <c r="H503" t="s">
-        <v>2565</v>
+        <v>2594</v>
       </c>
       <c r="I503" t="s">
-        <v>2566</v>
+        <v>2595</v>
       </c>
       <c r="J503" t="s">
-        <v>2567</v>
+        <v>2596</v>
       </c>
       <c r="K503">
         <v>1981</v>
@@ -34490,19 +35409,19 @@
         <v>43</v>
       </c>
       <c r="B504" t="s">
-        <v>2568</v>
+        <v>2597</v>
       </c>
       <c r="G504" t="s">
-        <v>2569</v>
+        <v>2598</v>
       </c>
       <c r="H504" t="s">
-        <v>2570</v>
+        <v>2599</v>
       </c>
       <c r="I504" t="s">
-        <v>2571</v>
+        <v>2600</v>
       </c>
       <c r="J504" t="s">
-        <v>2572</v>
+        <v>2601</v>
       </c>
       <c r="K504">
         <v>2025</v>
@@ -34514,19 +35433,19 @@
         <v>43</v>
       </c>
       <c r="B505" t="s">
-        <v>2573</v>
+        <v>2602</v>
       </c>
       <c r="G505" t="s">
-        <v>2574</v>
+        <v>2603</v>
       </c>
       <c r="H505" t="s">
-        <v>2575</v>
+        <v>2604</v>
       </c>
       <c r="I505" t="s">
-        <v>2576</v>
+        <v>2605</v>
       </c>
       <c r="J505" t="s">
-        <v>2577</v>
+        <v>2606</v>
       </c>
       <c r="K505">
         <v>1998</v>
@@ -34538,19 +35457,19 @@
         <v>43</v>
       </c>
       <c r="B506" t="s">
-        <v>2578</v>
+        <v>2607</v>
       </c>
       <c r="G506" t="s">
-        <v>2579</v>
+        <v>2608</v>
       </c>
       <c r="H506" t="s">
-        <v>2580</v>
+        <v>2609</v>
       </c>
       <c r="I506" t="s">
         <v>351</v>
       </c>
       <c r="J506" t="s">
-        <v>2581</v>
+        <v>2610</v>
       </c>
       <c r="K506">
         <v>2010</v>
@@ -34562,19 +35481,19 @@
         <v>43</v>
       </c>
       <c r="B507" t="s">
-        <v>2582</v>
+        <v>2611</v>
       </c>
       <c r="G507" t="s">
-        <v>2583</v>
+        <v>2612</v>
       </c>
       <c r="H507" t="s">
-        <v>2584</v>
+        <v>2613</v>
       </c>
       <c r="I507" t="s">
         <v>2018</v>
       </c>
       <c r="J507" t="s">
-        <v>2585</v>
+        <v>2614</v>
       </c>
       <c r="K507">
         <v>2016</v>
@@ -34586,19 +35505,19 @@
         <v>43</v>
       </c>
       <c r="B508" t="s">
-        <v>2586</v>
+        <v>2615</v>
       </c>
       <c r="G508" t="s">
-        <v>2587</v>
+        <v>2616</v>
       </c>
       <c r="H508" t="s">
-        <v>2588</v>
+        <v>2617</v>
       </c>
       <c r="I508" t="s">
-        <v>2589</v>
+        <v>2618</v>
       </c>
       <c r="J508" t="s">
-        <v>2590</v>
+        <v>2619</v>
       </c>
       <c r="K508">
         <v>2004</v>
@@ -34610,19 +35529,19 @@
         <v>43</v>
       </c>
       <c r="B509" t="s">
-        <v>2591</v>
+        <v>2620</v>
       </c>
       <c r="G509" t="s">
-        <v>2592</v>
+        <v>2621</v>
       </c>
       <c r="H509" t="s">
-        <v>2593</v>
+        <v>2622</v>
       </c>
       <c r="I509" t="s">
         <v>481</v>
       </c>
       <c r="J509" t="s">
-        <v>2594</v>
+        <v>2623</v>
       </c>
       <c r="K509">
         <v>1989</v>
@@ -34634,19 +35553,19 @@
         <v>43</v>
       </c>
       <c r="B510" t="s">
-        <v>2595</v>
+        <v>2624</v>
       </c>
       <c r="G510" t="s">
-        <v>2596</v>
+        <v>2625</v>
       </c>
       <c r="H510" t="s">
-        <v>2597</v>
+        <v>2626</v>
       </c>
       <c r="I510" t="s">
-        <v>2598</v>
+        <v>2627</v>
       </c>
       <c r="J510" t="s">
-        <v>2599</v>
+        <v>2628</v>
       </c>
       <c r="K510">
         <v>2005</v>
@@ -34658,19 +35577,19 @@
         <v>43</v>
       </c>
       <c r="B511" t="s">
-        <v>2600</v>
+        <v>2629</v>
       </c>
       <c r="G511" t="s">
-        <v>2601</v>
+        <v>2630</v>
       </c>
       <c r="H511" t="s">
-        <v>2602</v>
+        <v>2631</v>
       </c>
       <c r="I511" t="s">
         <v>403</v>
       </c>
       <c r="J511" t="s">
-        <v>2603</v>
+        <v>2632</v>
       </c>
       <c r="K511">
         <v>2025</v>
@@ -34682,19 +35601,19 @@
         <v>43</v>
       </c>
       <c r="B512" t="s">
-        <v>2604</v>
+        <v>2633</v>
       </c>
       <c r="G512" t="s">
-        <v>2605</v>
+        <v>2634</v>
       </c>
       <c r="H512" t="s">
-        <v>2606</v>
+        <v>2635</v>
       </c>
       <c r="I512" t="s">
         <v>1652</v>
       </c>
       <c r="J512" t="s">
-        <v>2607</v>
+        <v>2636</v>
       </c>
       <c r="K512">
         <v>2018</v>
@@ -34706,19 +35625,19 @@
         <v>43</v>
       </c>
       <c r="B513" t="s">
-        <v>2608</v>
+        <v>2637</v>
       </c>
       <c r="G513" t="s">
-        <v>2609</v>
+        <v>2638</v>
       </c>
       <c r="H513" t="s">
-        <v>2610</v>
+        <v>2639</v>
       </c>
       <c r="I513" t="s">
         <v>1499</v>
       </c>
       <c r="J513" t="s">
-        <v>2611</v>
+        <v>2640</v>
       </c>
       <c r="K513">
         <v>2011</v>
@@ -34730,19 +35649,19 @@
         <v>43</v>
       </c>
       <c r="B514" t="s">
-        <v>2612</v>
+        <v>2641</v>
       </c>
       <c r="G514" t="s">
-        <v>2613</v>
+        <v>2642</v>
       </c>
       <c r="H514" t="s">
-        <v>2614</v>
+        <v>2643</v>
       </c>
       <c r="I514" t="s">
         <v>1242</v>
       </c>
       <c r="J514" t="s">
-        <v>2615</v>
+        <v>2644</v>
       </c>
       <c r="K514">
         <v>2024</v>
@@ -34754,19 +35673,19 @@
         <v>43</v>
       </c>
       <c r="B515" t="s">
-        <v>2616</v>
+        <v>2645</v>
       </c>
       <c r="G515" t="s">
-        <v>2617</v>
+        <v>2646</v>
       </c>
       <c r="H515" t="s">
-        <v>2618</v>
+        <v>2647</v>
       </c>
       <c r="I515" t="s">
         <v>1783</v>
       </c>
       <c r="J515" t="s">
-        <v>2619</v>
+        <v>2648</v>
       </c>
       <c r="K515">
         <v>2023</v>
@@ -34778,19 +35697,19 @@
         <v>43</v>
       </c>
       <c r="B516" t="s">
-        <v>2620</v>
+        <v>2649</v>
       </c>
       <c r="G516" t="s">
-        <v>2621</v>
+        <v>2650</v>
       </c>
       <c r="H516" t="s">
-        <v>2622</v>
+        <v>2651</v>
       </c>
       <c r="I516" t="s">
-        <v>2623</v>
+        <v>2652</v>
       </c>
       <c r="J516" t="s">
-        <v>2624</v>
+        <v>2653</v>
       </c>
       <c r="K516">
         <v>2010</v>
@@ -34802,19 +35721,19 @@
         <v>43</v>
       </c>
       <c r="B517" t="s">
-        <v>2625</v>
+        <v>2654</v>
       </c>
       <c r="G517" t="s">
-        <v>2626</v>
+        <v>2655</v>
       </c>
       <c r="H517" t="s">
-        <v>2627</v>
+        <v>2656</v>
       </c>
       <c r="I517" t="s">
-        <v>2628</v>
+        <v>2657</v>
       </c>
       <c r="J517" t="s">
-        <v>2629</v>
+        <v>2658</v>
       </c>
       <c r="K517">
         <v>2019</v>
@@ -34826,19 +35745,19 @@
         <v>43</v>
       </c>
       <c r="B518" t="s">
-        <v>2630</v>
+        <v>2659</v>
       </c>
       <c r="G518" t="s">
-        <v>2631</v>
+        <v>2660</v>
       </c>
       <c r="H518" t="s">
-        <v>2632</v>
+        <v>2661</v>
       </c>
       <c r="I518" t="s">
         <v>51</v>
       </c>
       <c r="J518" t="s">
-        <v>2633</v>
+        <v>2662</v>
       </c>
       <c r="K518">
         <v>1986</v>
@@ -34850,19 +35769,19 @@
         <v>43</v>
       </c>
       <c r="B519" t="s">
-        <v>2634</v>
+        <v>2663</v>
       </c>
       <c r="G519" t="s">
-        <v>2635</v>
+        <v>2664</v>
       </c>
       <c r="H519" t="s">
-        <v>2636</v>
+        <v>2665</v>
       </c>
       <c r="I519" t="s">
-        <v>2637</v>
+        <v>2666</v>
       </c>
       <c r="J519" t="s">
-        <v>2638</v>
+        <v>2667</v>
       </c>
       <c r="K519">
         <v>2018</v>
@@ -34874,19 +35793,19 @@
         <v>43</v>
       </c>
       <c r="B520" t="s">
-        <v>2639</v>
+        <v>2668</v>
       </c>
       <c r="G520" t="s">
-        <v>2640</v>
+        <v>2669</v>
       </c>
       <c r="H520" t="s">
-        <v>2641</v>
+        <v>2670</v>
       </c>
       <c r="I520" t="s">
-        <v>2642</v>
+        <v>2671</v>
       </c>
       <c r="J520" t="s">
-        <v>2643</v>
+        <v>2672</v>
       </c>
       <c r="K520">
         <v>2006</v>
@@ -34898,19 +35817,19 @@
         <v>43</v>
       </c>
       <c r="B521" t="s">
-        <v>2644</v>
+        <v>2673</v>
       </c>
       <c r="G521" t="s">
-        <v>2645</v>
+        <v>2674</v>
       </c>
       <c r="H521" t="s">
-        <v>2646</v>
+        <v>2675</v>
       </c>
       <c r="I521" t="s">
-        <v>2647</v>
+        <v>2676</v>
       </c>
       <c r="J521" t="s">
-        <v>2648</v>
+        <v>2677</v>
       </c>
       <c r="K521">
         <v>2008</v>
@@ -34922,19 +35841,19 @@
         <v>43</v>
       </c>
       <c r="B522" t="s">
-        <v>2649</v>
+        <v>2678</v>
       </c>
       <c r="G522" t="s">
-        <v>2650</v>
+        <v>2679</v>
       </c>
       <c r="H522" t="s">
-        <v>2651</v>
+        <v>2680</v>
       </c>
       <c r="I522" t="s">
         <v>1196</v>
       </c>
       <c r="J522" t="s">
-        <v>2652</v>
+        <v>2681</v>
       </c>
       <c r="K522">
         <v>2019</v>
@@ -34946,19 +35865,19 @@
         <v>43</v>
       </c>
       <c r="B523" t="s">
-        <v>2653</v>
+        <v>2682</v>
       </c>
       <c r="G523" t="s">
-        <v>2654</v>
+        <v>2683</v>
       </c>
       <c r="H523" t="s">
-        <v>2655</v>
+        <v>2684</v>
       </c>
       <c r="I523" t="s">
-        <v>2656</v>
+        <v>2685</v>
       </c>
       <c r="J523" t="s">
-        <v>2657</v>
+        <v>2686</v>
       </c>
       <c r="K523">
         <v>2012</v>
@@ -34970,19 +35889,19 @@
         <v>43</v>
       </c>
       <c r="B524" t="s">
-        <v>2658</v>
+        <v>2687</v>
       </c>
       <c r="G524" t="s">
-        <v>2659</v>
+        <v>2688</v>
       </c>
       <c r="H524" t="s">
-        <v>2660</v>
+        <v>2689</v>
       </c>
       <c r="I524" t="s">
         <v>1729</v>
       </c>
       <c r="J524" t="s">
-        <v>2661</v>
+        <v>2690</v>
       </c>
       <c r="K524">
         <v>1997</v>
@@ -34994,19 +35913,19 @@
         <v>43</v>
       </c>
       <c r="B525" t="s">
-        <v>2662</v>
+        <v>2691</v>
       </c>
       <c r="G525" t="s">
-        <v>2663</v>
+        <v>2692</v>
       </c>
       <c r="H525" t="s">
-        <v>2664</v>
+        <v>2693</v>
       </c>
       <c r="I525" t="s">
-        <v>2665</v>
+        <v>2694</v>
       </c>
       <c r="J525" t="s">
-        <v>2666</v>
+        <v>2695</v>
       </c>
       <c r="K525">
         <v>2023</v>
@@ -35018,19 +35937,19 @@
         <v>43</v>
       </c>
       <c r="B526" t="s">
-        <v>2667</v>
+        <v>2696</v>
       </c>
       <c r="G526" t="s">
-        <v>2668</v>
+        <v>2697</v>
       </c>
       <c r="H526" t="s">
-        <v>2669</v>
+        <v>2698</v>
       </c>
       <c r="I526" t="s">
         <v>329</v>
       </c>
       <c r="J526" t="s">
-        <v>2670</v>
+        <v>2699</v>
       </c>
       <c r="K526">
         <v>2021</v>
@@ -35042,19 +35961,19 @@
         <v>43</v>
       </c>
       <c r="B527" t="s">
-        <v>2671</v>
+        <v>2700</v>
       </c>
       <c r="G527" t="s">
-        <v>2672</v>
+        <v>2701</v>
       </c>
       <c r="H527" t="s">
-        <v>2673</v>
+        <v>2702</v>
       </c>
       <c r="I527" t="s">
-        <v>2674</v>
+        <v>2703</v>
       </c>
       <c r="J527" t="s">
-        <v>2675</v>
+        <v>2704</v>
       </c>
       <c r="K527">
         <v>1989</v>
@@ -35066,19 +35985,19 @@
         <v>43</v>
       </c>
       <c r="B528" t="s">
-        <v>2676</v>
+        <v>2705</v>
       </c>
       <c r="G528" t="s">
-        <v>2677</v>
+        <v>2706</v>
       </c>
       <c r="H528" t="s">
-        <v>2678</v>
+        <v>2707</v>
       </c>
       <c r="I528" t="s">
         <v>1394</v>
       </c>
       <c r="J528" t="s">
-        <v>2679</v>
+        <v>2708</v>
       </c>
       <c r="K528">
         <v>2001</v>
@@ -35090,19 +36009,19 @@
         <v>43</v>
       </c>
       <c r="B529" t="s">
-        <v>2680</v>
+        <v>2709</v>
       </c>
       <c r="G529" t="s">
-        <v>2681</v>
+        <v>2710</v>
       </c>
       <c r="H529" t="s">
-        <v>2682</v>
+        <v>2711</v>
       </c>
       <c r="I529" t="s">
-        <v>2683</v>
+        <v>2712</v>
       </c>
       <c r="J529" t="s">
-        <v>2684</v>
+        <v>2713</v>
       </c>
       <c r="K529">
         <v>2024</v>
@@ -35114,19 +36033,19 @@
         <v>43</v>
       </c>
       <c r="B530" t="s">
-        <v>2685</v>
+        <v>2714</v>
       </c>
       <c r="G530" t="s">
-        <v>2686</v>
+        <v>2715</v>
       </c>
       <c r="H530" t="s">
-        <v>2687</v>
+        <v>2716</v>
       </c>
       <c r="I530" t="s">
-        <v>2688</v>
+        <v>2717</v>
       </c>
       <c r="J530" t="s">
-        <v>2689</v>
+        <v>2718</v>
       </c>
       <c r="K530">
         <v>2012</v>
@@ -35138,19 +36057,19 @@
         <v>43</v>
       </c>
       <c r="B531" t="s">
-        <v>2690</v>
+        <v>2719</v>
       </c>
       <c r="G531" t="s">
-        <v>2691</v>
+        <v>2720</v>
       </c>
       <c r="H531" t="s">
-        <v>2692</v>
+        <v>2721</v>
       </c>
       <c r="I531" t="s">
         <v>549</v>
       </c>
       <c r="J531" t="s">
-        <v>2693</v>
+        <v>2722</v>
       </c>
       <c r="K531">
         <v>2024</v>
@@ -35162,19 +36081,19 @@
         <v>43</v>
       </c>
       <c r="B532" t="s">
-        <v>2694</v>
+        <v>2723</v>
       </c>
       <c r="G532" t="s">
-        <v>2695</v>
+        <v>2724</v>
       </c>
       <c r="H532" t="s">
-        <v>2696</v>
+        <v>2725</v>
       </c>
       <c r="I532" t="s">
         <v>100</v>
       </c>
       <c r="J532" t="s">
-        <v>2697</v>
+        <v>2726</v>
       </c>
       <c r="K532">
         <v>2023</v>
@@ -35186,19 +36105,19 @@
         <v>43</v>
       </c>
       <c r="B533" t="s">
-        <v>2698</v>
+        <v>2727</v>
       </c>
       <c r="G533" t="s">
-        <v>2699</v>
+        <v>2728</v>
       </c>
       <c r="H533" t="s">
-        <v>2700</v>
+        <v>2729</v>
       </c>
       <c r="I533" t="s">
         <v>154</v>
       </c>
       <c r="J533" t="s">
-        <v>2701</v>
+        <v>2730</v>
       </c>
       <c r="K533">
         <v>2010</v>
@@ -35210,19 +36129,19 @@
         <v>43</v>
       </c>
       <c r="B534" t="s">
-        <v>2702</v>
+        <v>2731</v>
       </c>
       <c r="G534" t="s">
-        <v>2703</v>
+        <v>2732</v>
       </c>
       <c r="H534" t="s">
-        <v>2704</v>
+        <v>2733</v>
       </c>
       <c r="I534" t="s">
         <v>687</v>
       </c>
       <c r="J534" t="s">
-        <v>2705</v>
+        <v>2734</v>
       </c>
       <c r="K534">
         <v>2017</v>
@@ -35234,19 +36153,19 @@
         <v>43</v>
       </c>
       <c r="B535" t="s">
-        <v>2706</v>
+        <v>2735</v>
       </c>
       <c r="G535" t="s">
-        <v>2707</v>
+        <v>2736</v>
       </c>
       <c r="H535" t="s">
-        <v>2708</v>
+        <v>2737</v>
       </c>
       <c r="I535" t="s">
-        <v>2709</v>
+        <v>2738</v>
       </c>
       <c r="J535" t="s">
-        <v>2710</v>
+        <v>2739</v>
       </c>
       <c r="K535">
         <v>2000</v>
@@ -35258,19 +36177,19 @@
         <v>43</v>
       </c>
       <c r="B536" t="s">
-        <v>2711</v>
+        <v>2740</v>
       </c>
       <c r="G536" t="s">
-        <v>2712</v>
+        <v>2741</v>
       </c>
       <c r="H536" t="s">
-        <v>2713</v>
+        <v>2742</v>
       </c>
       <c r="I536" t="s">
         <v>653</v>
       </c>
       <c r="J536" t="s">
-        <v>2714</v>
+        <v>2743</v>
       </c>
       <c r="K536">
         <v>2016</v>
@@ -35282,19 +36201,19 @@
         <v>43</v>
       </c>
       <c r="B537" t="s">
-        <v>2715</v>
+        <v>2744</v>
       </c>
       <c r="G537" t="s">
-        <v>2716</v>
+        <v>2745</v>
       </c>
       <c r="H537" t="s">
-        <v>2717</v>
+        <v>2746</v>
       </c>
       <c r="I537" t="s">
         <v>426</v>
       </c>
       <c r="J537" t="s">
-        <v>2718</v>
+        <v>2747</v>
       </c>
       <c r="K537">
         <v>2006</v>
@@ -35306,19 +36225,19 @@
         <v>43</v>
       </c>
       <c r="B538" t="s">
-        <v>2719</v>
+        <v>2748</v>
       </c>
       <c r="G538" t="s">
-        <v>2720</v>
+        <v>2749</v>
       </c>
       <c r="H538" t="s">
-        <v>2721</v>
+        <v>2750</v>
       </c>
       <c r="I538" t="s">
-        <v>2722</v>
+        <v>2751</v>
       </c>
       <c r="J538" t="s">
-        <v>2723</v>
+        <v>2752</v>
       </c>
       <c r="K538">
         <v>2018</v>
@@ -35330,19 +36249,19 @@
         <v>43</v>
       </c>
       <c r="B539" t="s">
-        <v>2724</v>
+        <v>2753</v>
       </c>
       <c r="G539" t="s">
-        <v>2725</v>
+        <v>2754</v>
       </c>
       <c r="H539" t="s">
-        <v>2726</v>
+        <v>2755</v>
       </c>
       <c r="I539" t="s">
         <v>357</v>
       </c>
       <c r="J539" t="s">
-        <v>2727</v>
+        <v>2756</v>
       </c>
       <c r="K539">
         <v>2015</v>
@@ -35354,19 +36273,19 @@
         <v>43</v>
       </c>
       <c r="B540" t="s">
-        <v>2728</v>
+        <v>2757</v>
       </c>
       <c r="G540" t="s">
-        <v>2729</v>
+        <v>2758</v>
       </c>
       <c r="H540" t="s">
-        <v>2730</v>
+        <v>2759</v>
       </c>
       <c r="I540" t="s">
         <v>51</v>
       </c>
       <c r="J540" t="s">
-        <v>2731</v>
+        <v>2760</v>
       </c>
       <c r="K540">
         <v>1988</v>
@@ -35378,19 +36297,19 @@
         <v>43</v>
       </c>
       <c r="B541" t="s">
-        <v>2732</v>
+        <v>2761</v>
       </c>
       <c r="G541" t="s">
-        <v>2733</v>
+        <v>2762</v>
       </c>
       <c r="H541" t="s">
-        <v>2734</v>
+        <v>2763</v>
       </c>
       <c r="I541" t="s">
         <v>307</v>
       </c>
       <c r="J541" t="s">
-        <v>2735</v>
+        <v>2764</v>
       </c>
       <c r="K541">
         <v>2016</v>
@@ -35402,19 +36321,19 @@
         <v>43</v>
       </c>
       <c r="B542" t="s">
-        <v>2736</v>
+        <v>2765</v>
       </c>
       <c r="G542" t="s">
-        <v>2737</v>
+        <v>2766</v>
       </c>
       <c r="H542" t="s">
-        <v>2738</v>
+        <v>2767</v>
       </c>
       <c r="I542" t="s">
         <v>237</v>
       </c>
       <c r="J542" t="s">
-        <v>2739</v>
+        <v>2768</v>
       </c>
       <c r="K542">
         <v>2022</v>
@@ -35426,19 +36345,19 @@
         <v>43</v>
       </c>
       <c r="B543" t="s">
-        <v>2740</v>
+        <v>2769</v>
       </c>
       <c r="G543" t="s">
-        <v>2741</v>
+        <v>2770</v>
       </c>
       <c r="H543" t="s">
-        <v>2742</v>
+        <v>2771</v>
       </c>
       <c r="I543" t="s">
         <v>346</v>
       </c>
       <c r="J543" t="s">
-        <v>2743</v>
+        <v>2772</v>
       </c>
       <c r="K543">
         <v>2025</v>
@@ -35450,19 +36369,19 @@
         <v>43</v>
       </c>
       <c r="B544" t="s">
-        <v>2744</v>
+        <v>2773</v>
       </c>
       <c r="G544" t="s">
-        <v>2745</v>
+        <v>2774</v>
       </c>
       <c r="H544" t="s">
-        <v>2746</v>
+        <v>2775</v>
       </c>
       <c r="I544" t="s">
-        <v>2747</v>
+        <v>2776</v>
       </c>
       <c r="J544" t="s">
-        <v>2748</v>
+        <v>2777</v>
       </c>
       <c r="K544">
         <v>1986</v>
@@ -35474,19 +36393,19 @@
         <v>43</v>
       </c>
       <c r="B545" t="s">
-        <v>2749</v>
+        <v>2778</v>
       </c>
       <c r="G545" t="s">
-        <v>2750</v>
+        <v>2779</v>
       </c>
       <c r="H545" t="s">
-        <v>2751</v>
+        <v>2780</v>
       </c>
       <c r="I545" t="s">
         <v>900</v>
       </c>
       <c r="J545" t="s">
-        <v>2752</v>
+        <v>2781</v>
       </c>
       <c r="K545">
         <v>2014</v>
@@ -35498,19 +36417,19 @@
         <v>43</v>
       </c>
       <c r="B546" t="s">
-        <v>2753</v>
+        <v>2782</v>
       </c>
       <c r="G546" t="s">
-        <v>2754</v>
+        <v>2783</v>
       </c>
       <c r="H546" t="s">
-        <v>2755</v>
+        <v>2784</v>
       </c>
       <c r="I546" t="s">
-        <v>2637</v>
+        <v>2666</v>
       </c>
       <c r="J546" t="s">
-        <v>2756</v>
+        <v>2785</v>
       </c>
       <c r="K546">
         <v>2019</v>
@@ -35522,19 +36441,19 @@
         <v>43</v>
       </c>
       <c r="B547" t="s">
-        <v>2757</v>
+        <v>2786</v>
       </c>
       <c r="G547" t="s">
-        <v>2758</v>
+        <v>2787</v>
       </c>
       <c r="H547" t="s">
-        <v>2759</v>
+        <v>2788</v>
       </c>
       <c r="I547" t="s">
         <v>266</v>
       </c>
       <c r="J547" t="s">
-        <v>2760</v>
+        <v>2789</v>
       </c>
       <c r="K547">
         <v>2018</v>
@@ -35546,19 +36465,19 @@
         <v>43</v>
       </c>
       <c r="B548" t="s">
-        <v>2761</v>
+        <v>2790</v>
       </c>
       <c r="G548" t="s">
-        <v>2762</v>
+        <v>2791</v>
       </c>
       <c r="H548" t="s">
-        <v>2763</v>
+        <v>2792</v>
       </c>
       <c r="I548" t="s">
         <v>723</v>
       </c>
       <c r="J548" t="s">
-        <v>2764</v>
+        <v>2793</v>
       </c>
       <c r="K548">
         <v>1979</v>
@@ -35570,19 +36489,19 @@
         <v>43</v>
       </c>
       <c r="B549" t="s">
-        <v>2765</v>
+        <v>2794</v>
       </c>
       <c r="G549" t="s">
-        <v>2766</v>
+        <v>2795</v>
       </c>
       <c r="H549" t="s">
-        <v>2767</v>
+        <v>2796</v>
       </c>
       <c r="I549" t="s">
         <v>51</v>
       </c>
       <c r="J549" t="s">
-        <v>2768</v>
+        <v>2797</v>
       </c>
       <c r="K549">
         <v>2023</v>
@@ -35594,19 +36513,19 @@
         <v>43</v>
       </c>
       <c r="B550" t="s">
-        <v>2769</v>
+        <v>2798</v>
       </c>
       <c r="G550" t="s">
-        <v>2770</v>
+        <v>2799</v>
       </c>
       <c r="H550" t="s">
-        <v>2771</v>
+        <v>2800</v>
       </c>
       <c r="I550" t="s">
         <v>148</v>
       </c>
       <c r="J550" t="s">
-        <v>2772</v>
+        <v>2801</v>
       </c>
       <c r="K550">
         <v>2018</v>
@@ -35618,19 +36537,19 @@
         <v>43</v>
       </c>
       <c r="B551" t="s">
-        <v>2773</v>
+        <v>2802</v>
       </c>
       <c r="G551" t="s">
-        <v>2774</v>
+        <v>2803</v>
       </c>
       <c r="H551" t="s">
-        <v>2775</v>
+        <v>2804</v>
       </c>
       <c r="I551" t="s">
-        <v>2776</v>
+        <v>2805</v>
       </c>
       <c r="J551" t="s">
-        <v>2777</v>
+        <v>2806</v>
       </c>
       <c r="K551">
         <v>2015</v>
@@ -35642,19 +36561,19 @@
         <v>43</v>
       </c>
       <c r="B552" t="s">
-        <v>2778</v>
+        <v>2807</v>
       </c>
       <c r="G552" t="s">
-        <v>2779</v>
+        <v>2808</v>
       </c>
       <c r="H552" t="s">
-        <v>2780</v>
+        <v>2809</v>
       </c>
       <c r="I552" t="s">
-        <v>2781</v>
+        <v>2810</v>
       </c>
       <c r="J552" t="s">
-        <v>2782</v>
+        <v>2811</v>
       </c>
       <c r="K552">
         <v>2021</v>
@@ -35666,19 +36585,19 @@
         <v>43</v>
       </c>
       <c r="B553" t="s">
-        <v>2783</v>
+        <v>2812</v>
       </c>
       <c r="G553" t="s">
-        <v>2784</v>
+        <v>2813</v>
       </c>
       <c r="H553" t="s">
-        <v>2785</v>
+        <v>2814</v>
       </c>
       <c r="I553" t="s">
-        <v>2786</v>
+        <v>2815</v>
       </c>
       <c r="J553" t="s">
-        <v>2787</v>
+        <v>2816</v>
       </c>
       <c r="K553">
         <v>2010</v>
@@ -35690,19 +36609,19 @@
         <v>43</v>
       </c>
       <c r="B554" t="s">
-        <v>2788</v>
+        <v>2817</v>
       </c>
       <c r="G554" t="s">
-        <v>2789</v>
+        <v>2818</v>
       </c>
       <c r="H554" t="s">
-        <v>2790</v>
+        <v>2819</v>
       </c>
       <c r="I554" t="s">
-        <v>2791</v>
+        <v>2820</v>
       </c>
       <c r="J554" t="s">
-        <v>2792</v>
+        <v>2821</v>
       </c>
       <c r="K554">
         <v>2006</v>
@@ -35714,19 +36633,19 @@
         <v>43</v>
       </c>
       <c r="B555" t="s">
-        <v>2793</v>
+        <v>2822</v>
       </c>
       <c r="G555" t="s">
-        <v>2794</v>
+        <v>2823</v>
       </c>
       <c r="H555" t="s">
-        <v>2795</v>
+        <v>2824</v>
       </c>
       <c r="I555" t="s">
         <v>426</v>
       </c>
       <c r="J555" t="s">
-        <v>2796</v>
+        <v>2825</v>
       </c>
       <c r="K555">
         <v>2019</v>
@@ -35738,19 +36657,19 @@
         <v>43</v>
       </c>
       <c r="B556" t="s">
-        <v>2797</v>
+        <v>2826</v>
       </c>
       <c r="G556" t="s">
-        <v>2798</v>
+        <v>2827</v>
       </c>
       <c r="H556" t="s">
-        <v>2799</v>
+        <v>2828</v>
       </c>
       <c r="I556" t="s">
-        <v>2800</v>
+        <v>2829</v>
       </c>
       <c r="J556" t="s">
-        <v>2801</v>
+        <v>2830</v>
       </c>
       <c r="K556">
         <v>2022</v>
@@ -35762,19 +36681,19 @@
         <v>43</v>
       </c>
       <c r="B557" t="s">
-        <v>2802</v>
+        <v>2831</v>
       </c>
       <c r="G557" t="s">
-        <v>2803</v>
+        <v>2832</v>
       </c>
       <c r="H557" t="s">
-        <v>2804</v>
+        <v>2833</v>
       </c>
       <c r="I557" t="s">
         <v>357</v>
       </c>
       <c r="J557" t="s">
-        <v>2805</v>
+        <v>2834</v>
       </c>
       <c r="K557">
         <v>2006</v>
@@ -35786,19 +36705,19 @@
         <v>43</v>
       </c>
       <c r="B558" t="s">
-        <v>2806</v>
+        <v>2835</v>
       </c>
       <c r="G558" t="s">
-        <v>2807</v>
+        <v>2836</v>
       </c>
       <c r="H558" t="s">
-        <v>2808</v>
+        <v>2837</v>
       </c>
       <c r="I558" t="s">
         <v>237</v>
       </c>
       <c r="J558" t="s">
-        <v>2809</v>
+        <v>2838</v>
       </c>
       <c r="K558">
         <v>2019</v>
@@ -35810,19 +36729,19 @@
         <v>43</v>
       </c>
       <c r="B559" t="s">
-        <v>2810</v>
+        <v>2839</v>
       </c>
       <c r="G559" t="s">
-        <v>2811</v>
+        <v>2840</v>
       </c>
       <c r="H559" t="s">
-        <v>2812</v>
+        <v>2841</v>
       </c>
       <c r="I559" t="s">
-        <v>2813</v>
+        <v>2842</v>
       </c>
       <c r="J559" t="s">
-        <v>2814</v>
+        <v>2843</v>
       </c>
       <c r="K559">
         <v>2015</v>
@@ -35834,19 +36753,19 @@
         <v>43</v>
       </c>
       <c r="B560" t="s">
-        <v>2815</v>
+        <v>2844</v>
       </c>
       <c r="G560" t="s">
-        <v>2816</v>
+        <v>2845</v>
       </c>
       <c r="H560" t="s">
-        <v>2817</v>
+        <v>2846</v>
       </c>
       <c r="I560" t="s">
         <v>1014</v>
       </c>
       <c r="J560" t="s">
-        <v>2818</v>
+        <v>2847</v>
       </c>
       <c r="K560">
         <v>2026</v>
@@ -35858,19 +36777,19 @@
         <v>43</v>
       </c>
       <c r="B561" t="s">
-        <v>2819</v>
+        <v>2848</v>
       </c>
       <c r="G561" t="s">
-        <v>2820</v>
+        <v>2849</v>
       </c>
       <c r="H561" t="s">
-        <v>2821</v>
+        <v>2850</v>
       </c>
       <c r="I561" t="s">
         <v>51</v>
       </c>
       <c r="J561" t="s">
-        <v>2822</v>
+        <v>2851</v>
       </c>
       <c r="K561">
         <v>2023</v>
@@ -35882,19 +36801,19 @@
         <v>43</v>
       </c>
       <c r="B562" t="s">
-        <v>2823</v>
+        <v>2852</v>
       </c>
       <c r="G562" t="s">
-        <v>2824</v>
+        <v>2853</v>
       </c>
       <c r="H562" t="s">
-        <v>2825</v>
+        <v>2854</v>
       </c>
       <c r="I562" t="s">
         <v>51</v>
       </c>
       <c r="J562" t="s">
-        <v>2826</v>
+        <v>2855</v>
       </c>
       <c r="K562">
         <v>2000</v>
@@ -35906,19 +36825,19 @@
         <v>43</v>
       </c>
       <c r="B563" t="s">
-        <v>2827</v>
+        <v>2856</v>
       </c>
       <c r="G563" t="s">
-        <v>2828</v>
+        <v>2857</v>
       </c>
       <c r="H563" t="s">
-        <v>2829</v>
+        <v>2858</v>
       </c>
       <c r="I563" t="s">
         <v>51</v>
       </c>
       <c r="J563" t="s">
-        <v>2830</v>
+        <v>2859</v>
       </c>
       <c r="K563">
         <v>2016</v>
@@ -35930,19 +36849,19 @@
         <v>43</v>
       </c>
       <c r="B564" t="s">
-        <v>2831</v>
+        <v>2860</v>
       </c>
       <c r="G564" t="s">
-        <v>2832</v>
+        <v>2861</v>
       </c>
       <c r="H564" t="s">
-        <v>2833</v>
+        <v>2862</v>
       </c>
       <c r="I564" t="s">
         <v>1461</v>
       </c>
       <c r="J564" t="s">
-        <v>2834</v>
+        <v>2863</v>
       </c>
       <c r="K564">
         <v>2026</v>
@@ -35954,19 +36873,19 @@
         <v>43</v>
       </c>
       <c r="B565" t="s">
-        <v>2835</v>
+        <v>2864</v>
       </c>
       <c r="G565" t="s">
-        <v>2836</v>
+        <v>2865</v>
       </c>
       <c r="H565" t="s">
-        <v>2837</v>
+        <v>2866</v>
       </c>
       <c r="I565" t="s">
-        <v>2838</v>
+        <v>2867</v>
       </c>
       <c r="J565" t="s">
-        <v>2839</v>
+        <v>2868</v>
       </c>
       <c r="K565">
         <v>2024</v>
@@ -35978,19 +36897,19 @@
         <v>43</v>
       </c>
       <c r="B566" t="s">
-        <v>2840</v>
+        <v>2869</v>
       </c>
       <c r="G566" t="s">
-        <v>2841</v>
+        <v>2870</v>
       </c>
       <c r="H566" t="s">
-        <v>2842</v>
+        <v>2871</v>
       </c>
       <c r="I566" t="s">
         <v>459</v>
       </c>
       <c r="J566" t="s">
-        <v>2843</v>
+        <v>2872</v>
       </c>
       <c r="K566">
         <v>2019</v>
@@ -36002,19 +36921,19 @@
         <v>43</v>
       </c>
       <c r="B567" t="s">
-        <v>2844</v>
+        <v>2873</v>
       </c>
       <c r="G567" t="s">
-        <v>2845</v>
+        <v>2874</v>
       </c>
       <c r="H567" t="s">
-        <v>2846</v>
+        <v>2875</v>
       </c>
       <c r="I567" t="s">
         <v>915</v>
       </c>
       <c r="J567" t="s">
-        <v>2847</v>
+        <v>2876</v>
       </c>
       <c r="K567">
         <v>2020</v>
@@ -36026,19 +36945,19 @@
         <v>43</v>
       </c>
       <c r="B568" t="s">
-        <v>2848</v>
+        <v>2877</v>
       </c>
       <c r="G568" t="s">
-        <v>2849</v>
+        <v>2878</v>
       </c>
       <c r="H568" t="s">
-        <v>2850</v>
+        <v>2879</v>
       </c>
       <c r="I568" t="s">
-        <v>2851</v>
+        <v>2880</v>
       </c>
       <c r="J568" t="s">
-        <v>2852</v>
+        <v>2881</v>
       </c>
       <c r="K568">
         <v>2014</v>
@@ -36050,19 +36969,19 @@
         <v>43</v>
       </c>
       <c r="B569" t="s">
-        <v>2853</v>
+        <v>2882</v>
       </c>
       <c r="G569" t="s">
-        <v>2854</v>
+        <v>2883</v>
       </c>
       <c r="H569" t="s">
-        <v>2855</v>
+        <v>2884</v>
       </c>
       <c r="I569" t="s">
         <v>51</v>
       </c>
       <c r="J569" t="s">
-        <v>2856</v>
+        <v>2885</v>
       </c>
       <c r="K569">
         <v>2004</v>
@@ -36074,19 +36993,19 @@
         <v>43</v>
       </c>
       <c r="B570" t="s">
-        <v>2857</v>
+        <v>2886</v>
       </c>
       <c r="G570" t="s">
-        <v>2858</v>
+        <v>2887</v>
       </c>
       <c r="H570" t="s">
-        <v>2859</v>
+        <v>2888</v>
       </c>
       <c r="I570" t="s">
         <v>51</v>
       </c>
       <c r="J570" t="s">
-        <v>2860</v>
+        <v>2889</v>
       </c>
       <c r="K570">
         <v>2015</v>
@@ -36098,19 +37017,19 @@
         <v>43</v>
       </c>
       <c r="B571" t="s">
-        <v>2861</v>
+        <v>2890</v>
       </c>
       <c r="G571" t="s">
-        <v>2862</v>
+        <v>2891</v>
       </c>
       <c r="H571" t="s">
-        <v>2863</v>
+        <v>2892</v>
       </c>
       <c r="I571" t="s">
         <v>979</v>
       </c>
       <c r="J571" t="s">
-        <v>2864</v>
+        <v>2893</v>
       </c>
       <c r="K571">
         <v>2015</v>
@@ -36122,19 +37041,19 @@
         <v>43</v>
       </c>
       <c r="B572" t="s">
-        <v>2865</v>
+        <v>2894</v>
       </c>
       <c r="G572" t="s">
-        <v>2866</v>
+        <v>2895</v>
       </c>
       <c r="H572" t="s">
-        <v>2867</v>
+        <v>2896</v>
       </c>
       <c r="I572" t="s">
-        <v>2868</v>
+        <v>2897</v>
       </c>
       <c r="J572" t="s">
-        <v>2869</v>
+        <v>2898</v>
       </c>
       <c r="K572">
         <v>2013</v>
@@ -36146,19 +37065,19 @@
         <v>43</v>
       </c>
       <c r="B573" t="s">
-        <v>2870</v>
+        <v>2899</v>
       </c>
       <c r="G573" t="s">
-        <v>2871</v>
+        <v>2900</v>
       </c>
       <c r="H573" t="s">
-        <v>2872</v>
+        <v>2901</v>
       </c>
       <c r="I573" t="s">
         <v>692</v>
       </c>
       <c r="J573" t="s">
-        <v>2873</v>
+        <v>2902</v>
       </c>
       <c r="K573">
         <v>2017</v>
@@ -36170,19 +37089,19 @@
         <v>43</v>
       </c>
       <c r="B574" t="s">
-        <v>2874</v>
+        <v>2903</v>
       </c>
       <c r="G574" t="s">
-        <v>2875</v>
+        <v>2904</v>
       </c>
       <c r="H574" t="s">
-        <v>2876</v>
+        <v>2905</v>
       </c>
       <c r="I574" t="s">
         <v>51</v>
       </c>
       <c r="J574" t="s">
-        <v>2877</v>
+        <v>2906</v>
       </c>
       <c r="K574">
         <v>1995</v>
@@ -36194,19 +37113,19 @@
         <v>43</v>
       </c>
       <c r="B575" t="s">
-        <v>2878</v>
+        <v>2907</v>
       </c>
       <c r="G575" t="s">
-        <v>2879</v>
+        <v>2908</v>
       </c>
       <c r="H575" t="s">
-        <v>2880</v>
+        <v>2909</v>
       </c>
       <c r="I575" t="s">
-        <v>2881</v>
+        <v>2910</v>
       </c>
       <c r="J575" t="s">
-        <v>2882</v>
+        <v>2911</v>
       </c>
       <c r="K575">
         <v>2019</v>
@@ -36218,19 +37137,19 @@
         <v>43</v>
       </c>
       <c r="B576" t="s">
-        <v>2883</v>
+        <v>2912</v>
       </c>
       <c r="G576" t="s">
-        <v>2884</v>
+        <v>2913</v>
       </c>
       <c r="H576" t="s">
-        <v>2885</v>
+        <v>2914</v>
       </c>
       <c r="I576" t="s">
         <v>723</v>
       </c>
       <c r="J576" t="s">
-        <v>2886</v>
+        <v>2915</v>
       </c>
       <c r="K576">
         <v>2010</v>
@@ -36242,19 +37161,19 @@
         <v>43</v>
       </c>
       <c r="B577" t="s">
-        <v>2887</v>
+        <v>2916</v>
       </c>
       <c r="G577" t="s">
-        <v>2888</v>
+        <v>2917</v>
       </c>
       <c r="H577" t="s">
-        <v>2889</v>
+        <v>2918</v>
       </c>
       <c r="I577" t="s">
         <v>915</v>
       </c>
       <c r="J577" t="s">
-        <v>2890</v>
+        <v>2919</v>
       </c>
       <c r="K577">
         <v>2012</v>
@@ -36266,19 +37185,19 @@
         <v>43</v>
       </c>
       <c r="B578" t="s">
-        <v>2891</v>
+        <v>2920</v>
       </c>
       <c r="G578" t="s">
-        <v>2892</v>
+        <v>2921</v>
       </c>
       <c r="H578" t="s">
-        <v>2893</v>
+        <v>2922</v>
       </c>
       <c r="I578" t="s">
         <v>723</v>
       </c>
       <c r="J578" t="s">
-        <v>2894</v>
+        <v>2923</v>
       </c>
       <c r="K578">
         <v>1979</v>
@@ -36290,19 +37209,19 @@
         <v>43</v>
       </c>
       <c r="B579" t="s">
-        <v>2895</v>
+        <v>2924</v>
       </c>
       <c r="G579" t="s">
-        <v>2896</v>
+        <v>2925</v>
       </c>
       <c r="H579" t="s">
-        <v>2897</v>
+        <v>2926</v>
       </c>
       <c r="I579" t="s">
-        <v>2898</v>
+        <v>2927</v>
       </c>
       <c r="J579" t="s">
-        <v>2899</v>
+        <v>2928</v>
       </c>
       <c r="K579">
         <v>1980</v>
@@ -36314,19 +37233,19 @@
         <v>43</v>
       </c>
       <c r="B580" t="s">
-        <v>2900</v>
+        <v>2929</v>
       </c>
       <c r="G580" t="s">
-        <v>2901</v>
+        <v>2930</v>
       </c>
       <c r="H580" t="s">
-        <v>2902</v>
+        <v>2931</v>
       </c>
       <c r="I580" t="s">
         <v>253</v>
       </c>
       <c r="J580" t="s">
-        <v>2903</v>
+        <v>2932</v>
       </c>
       <c r="K580">
         <v>1981</v>
@@ -36338,19 +37257,19 @@
         <v>43</v>
       </c>
       <c r="B581" t="s">
-        <v>2904</v>
+        <v>2933</v>
       </c>
       <c r="G581" t="s">
-        <v>2905</v>
+        <v>2934</v>
       </c>
       <c r="H581" t="s">
-        <v>2906</v>
+        <v>2935</v>
       </c>
       <c r="I581" t="s">
         <v>723</v>
       </c>
       <c r="J581" t="s">
-        <v>2903</v>
+        <v>2932</v>
       </c>
       <c r="K581">
         <v>1981</v>
@@ -36362,19 +37281,19 @@
         <v>43</v>
       </c>
       <c r="B582" t="s">
-        <v>2907</v>
+        <v>2936</v>
       </c>
       <c r="G582" t="s">
-        <v>2908</v>
+        <v>2937</v>
       </c>
       <c r="H582" t="s">
-        <v>2909</v>
+        <v>2938</v>
       </c>
       <c r="I582" t="s">
         <v>197</v>
       </c>
       <c r="J582" t="s">
-        <v>2910</v>
+        <v>2939</v>
       </c>
       <c r="K582">
         <v>2023</v>
@@ -36386,19 +37305,19 @@
         <v>43</v>
       </c>
       <c r="B583" t="s">
-        <v>2911</v>
+        <v>2940</v>
       </c>
       <c r="G583" t="s">
-        <v>2912</v>
+        <v>2941</v>
       </c>
       <c r="H583" t="s">
-        <v>2913</v>
+        <v>2942</v>
       </c>
       <c r="I583" t="s">
-        <v>2178</v>
+        <v>2184</v>
       </c>
       <c r="J583" t="s">
-        <v>2914</v>
+        <v>2943</v>
       </c>
       <c r="K583">
         <v>2024</v>
@@ -36410,19 +37329,19 @@
         <v>43</v>
       </c>
       <c r="B584" t="s">
-        <v>2915</v>
+        <v>2944</v>
       </c>
       <c r="G584" t="s">
-        <v>2916</v>
+        <v>2945</v>
       </c>
       <c r="H584" t="s">
-        <v>2917</v>
+        <v>2946</v>
       </c>
       <c r="I584" t="s">
-        <v>2918</v>
+        <v>2947</v>
       </c>
       <c r="J584" t="s">
-        <v>2919</v>
+        <v>2948</v>
       </c>
       <c r="K584">
         <v>2014</v>
@@ -36434,19 +37353,19 @@
         <v>43</v>
       </c>
       <c r="B585" t="s">
-        <v>2920</v>
+        <v>2949</v>
       </c>
       <c r="G585" t="s">
-        <v>2921</v>
+        <v>2950</v>
       </c>
       <c r="H585" t="s">
-        <v>2922</v>
+        <v>2951</v>
       </c>
       <c r="I585" t="s">
         <v>745</v>
       </c>
       <c r="J585" t="s">
-        <v>2923</v>
+        <v>2952</v>
       </c>
       <c r="K585">
         <v>2015</v>
@@ -36458,19 +37377,19 @@
         <v>43</v>
       </c>
       <c r="B586" t="s">
-        <v>2924</v>
+        <v>2953</v>
       </c>
       <c r="G586" t="s">
-        <v>2925</v>
+        <v>2954</v>
       </c>
       <c r="H586" t="s">
-        <v>2926</v>
+        <v>2955</v>
       </c>
       <c r="I586" t="s">
-        <v>2250</v>
+        <v>2269</v>
       </c>
       <c r="J586" t="s">
-        <v>2927</v>
+        <v>2956</v>
       </c>
       <c r="K586">
         <v>2020</v>
@@ -36482,19 +37401,19 @@
         <v>43</v>
       </c>
       <c r="B587" t="s">
-        <v>2928</v>
+        <v>2957</v>
       </c>
       <c r="G587" t="s">
-        <v>2929</v>
+        <v>2958</v>
       </c>
       <c r="H587" t="s">
-        <v>2930</v>
+        <v>2959</v>
       </c>
       <c r="I587" t="s">
-        <v>2931</v>
+        <v>2960</v>
       </c>
       <c r="J587" t="s">
-        <v>2932</v>
+        <v>2961</v>
       </c>
       <c r="K587">
         <v>2020</v>
@@ -36506,19 +37425,19 @@
         <v>43</v>
       </c>
       <c r="B588" t="s">
-        <v>2933</v>
+        <v>2962</v>
       </c>
       <c r="G588" t="s">
-        <v>2934</v>
+        <v>2963</v>
       </c>
       <c r="H588" t="s">
-        <v>2935</v>
+        <v>2964</v>
       </c>
       <c r="I588" t="s">
         <v>1359</v>
       </c>
       <c r="J588" t="s">
-        <v>2936</v>
+        <v>2965</v>
       </c>
       <c r="K588">
         <v>2021</v>
@@ -36530,19 +37449,19 @@
         <v>43</v>
       </c>
       <c r="B589" t="s">
-        <v>2937</v>
+        <v>2966</v>
       </c>
       <c r="G589" t="s">
-        <v>2938</v>
+        <v>2967</v>
       </c>
       <c r="H589" t="s">
-        <v>2939</v>
+        <v>2968</v>
       </c>
       <c r="I589" t="s">
         <v>979</v>
       </c>
       <c r="J589" t="s">
-        <v>2940</v>
+        <v>2969</v>
       </c>
       <c r="K589">
         <v>2024</v>
@@ -36554,19 +37473,19 @@
         <v>43</v>
       </c>
       <c r="B590" t="s">
-        <v>2941</v>
+        <v>2970</v>
       </c>
       <c r="G590" t="s">
-        <v>2942</v>
+        <v>2971</v>
       </c>
       <c r="H590" t="s">
-        <v>2943</v>
+        <v>2972</v>
       </c>
       <c r="I590" t="s">
-        <v>2944</v>
+        <v>2973</v>
       </c>
       <c r="J590" t="s">
-        <v>2945</v>
+        <v>2974</v>
       </c>
       <c r="K590">
         <v>2014</v>
@@ -36578,19 +37497,19 @@
         <v>43</v>
       </c>
       <c r="B591" t="s">
-        <v>2946</v>
+        <v>2975</v>
       </c>
       <c r="G591" t="s">
-        <v>2947</v>
+        <v>2976</v>
       </c>
       <c r="H591" t="s">
-        <v>2948</v>
+        <v>2977</v>
       </c>
       <c r="I591" t="s">
-        <v>2949</v>
+        <v>2978</v>
       </c>
       <c r="J591" t="s">
-        <v>2950</v>
+        <v>2979</v>
       </c>
       <c r="K591">
         <v>2016</v>
@@ -36602,19 +37521,19 @@
         <v>43</v>
       </c>
       <c r="B592" t="s">
-        <v>2951</v>
+        <v>2980</v>
       </c>
       <c r="G592" t="s">
-        <v>2952</v>
+        <v>2981</v>
       </c>
       <c r="H592" t="s">
-        <v>2953</v>
+        <v>2982</v>
       </c>
       <c r="I592" t="s">
-        <v>2178</v>
+        <v>2184</v>
       </c>
       <c r="J592" t="s">
-        <v>2954</v>
+        <v>2983</v>
       </c>
       <c r="K592">
         <v>2023</v>
@@ -36626,19 +37545,19 @@
         <v>43</v>
       </c>
       <c r="B593" t="s">
-        <v>2955</v>
+        <v>2984</v>
       </c>
       <c r="G593" t="s">
-        <v>2956</v>
+        <v>2985</v>
       </c>
       <c r="H593" t="s">
-        <v>2957</v>
+        <v>2986</v>
       </c>
       <c r="I593" t="s">
         <v>2043</v>
       </c>
       <c r="J593" t="s">
-        <v>2958</v>
+        <v>2987</v>
       </c>
       <c r="K593">
         <v>2009</v>
@@ -36650,19 +37569,19 @@
         <v>43</v>
       </c>
       <c r="B594" t="s">
-        <v>2959</v>
+        <v>2988</v>
       </c>
       <c r="G594" t="s">
-        <v>2960</v>
+        <v>2989</v>
       </c>
       <c r="H594" t="s">
-        <v>2961</v>
+        <v>2990</v>
       </c>
       <c r="I594" t="s">
         <v>990</v>
       </c>
       <c r="J594" t="s">
-        <v>2962</v>
+        <v>2991</v>
       </c>
       <c r="K594">
         <v>2018</v>
@@ -36674,19 +37593,19 @@
         <v>43</v>
       </c>
       <c r="B595" t="s">
-        <v>2963</v>
+        <v>2992</v>
       </c>
       <c r="G595" t="s">
-        <v>2964</v>
+        <v>2993</v>
       </c>
       <c r="H595" t="s">
-        <v>2965</v>
+        <v>2994</v>
       </c>
       <c r="I595" t="s">
-        <v>2966</v>
+        <v>2995</v>
       </c>
       <c r="J595" t="s">
-        <v>2967</v>
+        <v>2996</v>
       </c>
       <c r="K595">
         <v>2020</v>
@@ -36698,19 +37617,19 @@
         <v>43</v>
       </c>
       <c r="B596" t="s">
-        <v>2968</v>
+        <v>2997</v>
       </c>
       <c r="G596" t="s">
-        <v>2969</v>
+        <v>2998</v>
       </c>
       <c r="H596" t="s">
-        <v>2970</v>
+        <v>2999</v>
       </c>
       <c r="I596" t="s">
-        <v>2971</v>
+        <v>3000</v>
       </c>
       <c r="J596" t="s">
-        <v>2972</v>
+        <v>3001</v>
       </c>
       <c r="K596">
         <v>2002</v>
@@ -36722,19 +37641,19 @@
         <v>43</v>
       </c>
       <c r="B597" t="s">
-        <v>2973</v>
+        <v>3002</v>
       </c>
       <c r="G597" t="s">
-        <v>2974</v>
+        <v>3003</v>
       </c>
       <c r="H597" t="s">
-        <v>2975</v>
+        <v>3004</v>
       </c>
       <c r="I597" t="s">
         <v>51</v>
       </c>
       <c r="J597" t="s">
-        <v>2976</v>
+        <v>3005</v>
       </c>
       <c r="K597">
         <v>1994</v>
@@ -36746,19 +37665,19 @@
         <v>43</v>
       </c>
       <c r="B598" t="s">
-        <v>2977</v>
+        <v>3006</v>
       </c>
       <c r="G598" t="s">
-        <v>2978</v>
+        <v>3007</v>
       </c>
       <c r="H598" t="s">
-        <v>2979</v>
+        <v>3008</v>
       </c>
       <c r="I598" t="s">
         <v>1308</v>
       </c>
       <c r="J598" t="s">
-        <v>2980</v>
+        <v>3009</v>
       </c>
       <c r="K598">
         <v>2021</v>
@@ -36770,19 +37689,19 @@
         <v>43</v>
       </c>
       <c r="B599" t="s">
-        <v>2981</v>
+        <v>3010</v>
       </c>
       <c r="G599" t="s">
-        <v>2982</v>
+        <v>3011</v>
       </c>
       <c r="H599" t="s">
-        <v>2983</v>
+        <v>3012</v>
       </c>
       <c r="I599" t="s">
         <v>1652</v>
       </c>
       <c r="J599" t="s">
-        <v>2984</v>
+        <v>3013</v>
       </c>
       <c r="K599">
         <v>2025</v>
@@ -36794,19 +37713,19 @@
         <v>43</v>
       </c>
       <c r="B600" t="s">
-        <v>2985</v>
+        <v>3014</v>
       </c>
       <c r="G600" t="s">
-        <v>2986</v>
+        <v>3015</v>
       </c>
       <c r="H600" t="s">
-        <v>2987</v>
+        <v>3016</v>
       </c>
       <c r="I600" t="s">
         <v>51</v>
       </c>
       <c r="J600" t="s">
-        <v>2988</v>
+        <v>3017</v>
       </c>
       <c r="K600">
         <v>2021</v>
@@ -36818,19 +37737,19 @@
         <v>43</v>
       </c>
       <c r="B601" t="s">
-        <v>2989</v>
+        <v>3018</v>
       </c>
       <c r="G601" t="s">
-        <v>2990</v>
+        <v>3019</v>
       </c>
       <c r="H601" t="s">
-        <v>2991</v>
+        <v>3020</v>
       </c>
       <c r="I601" t="s">
-        <v>2949</v>
+        <v>2978</v>
       </c>
       <c r="J601" t="s">
-        <v>2992</v>
+        <v>3021</v>
       </c>
       <c r="K601">
         <v>2024</v>
@@ -36842,19 +37761,19 @@
         <v>43</v>
       </c>
       <c r="B602" t="s">
-        <v>2993</v>
+        <v>3022</v>
       </c>
       <c r="G602" t="s">
-        <v>2994</v>
+        <v>3023</v>
       </c>
       <c r="H602" t="s">
-        <v>2995</v>
+        <v>3024</v>
       </c>
       <c r="I602" t="s">
-        <v>2838</v>
+        <v>2867</v>
       </c>
       <c r="J602" t="s">
-        <v>2996</v>
+        <v>3025</v>
       </c>
       <c r="K602">
         <v>2024</v>
@@ -36866,19 +37785,19 @@
         <v>43</v>
       </c>
       <c r="B603" t="s">
-        <v>2997</v>
+        <v>3026</v>
       </c>
       <c r="G603" t="s">
-        <v>2998</v>
+        <v>3027</v>
       </c>
       <c r="H603" t="s">
-        <v>2999</v>
+        <v>3028</v>
       </c>
       <c r="I603" t="s">
-        <v>3000</v>
+        <v>3029</v>
       </c>
       <c r="J603" t="s">
-        <v>3001</v>
+        <v>3030</v>
       </c>
       <c r="K603">
         <v>2018</v>
@@ -36890,19 +37809,19 @@
         <v>43</v>
       </c>
       <c r="B604" t="s">
-        <v>3002</v>
+        <v>3031</v>
       </c>
       <c r="G604" t="s">
-        <v>3003</v>
+        <v>3032</v>
       </c>
       <c r="H604" t="s">
-        <v>3004</v>
+        <v>3033</v>
       </c>
       <c r="I604" t="s">
         <v>100</v>
       </c>
       <c r="J604" t="s">
-        <v>3005</v>
+        <v>3034</v>
       </c>
       <c r="K604">
         <v>2014</v>
@@ -36914,19 +37833,19 @@
         <v>43</v>
       </c>
       <c r="B605" t="s">
-        <v>3006</v>
+        <v>3035</v>
       </c>
       <c r="G605" t="s">
-        <v>3007</v>
+        <v>3036</v>
       </c>
       <c r="H605" t="s">
-        <v>3008</v>
+        <v>3037</v>
       </c>
       <c r="I605" t="s">
         <v>1924</v>
       </c>
       <c r="J605" t="s">
-        <v>3009</v>
+        <v>3038</v>
       </c>
       <c r="K605">
         <v>2019</v>
@@ -36938,19 +37857,19 @@
         <v>43</v>
       </c>
       <c r="B606" t="s">
-        <v>3010</v>
+        <v>3039</v>
       </c>
       <c r="G606" t="s">
-        <v>3011</v>
+        <v>3040</v>
       </c>
       <c r="H606" t="s">
-        <v>3012</v>
+        <v>3041</v>
       </c>
       <c r="I606" t="s">
-        <v>3013</v>
+        <v>3042</v>
       </c>
       <c r="J606" t="s">
-        <v>3014</v>
+        <v>3043</v>
       </c>
       <c r="K606">
         <v>2024</v>
@@ -36962,19 +37881,19 @@
         <v>43</v>
       </c>
       <c r="B607" t="s">
-        <v>3015</v>
+        <v>3044</v>
       </c>
       <c r="G607" t="s">
-        <v>3016</v>
+        <v>3045</v>
       </c>
       <c r="H607" t="s">
-        <v>3017</v>
+        <v>3046</v>
       </c>
       <c r="I607" t="s">
         <v>1520</v>
       </c>
       <c r="J607" t="s">
-        <v>3018</v>
+        <v>3047</v>
       </c>
       <c r="K607">
         <v>2024</v>
@@ -36986,19 +37905,19 @@
         <v>43</v>
       </c>
       <c r="B608" t="s">
-        <v>3019</v>
+        <v>3048</v>
       </c>
       <c r="G608" t="s">
-        <v>3020</v>
+        <v>3049</v>
       </c>
       <c r="H608" t="s">
-        <v>3021</v>
+        <v>3050</v>
       </c>
       <c r="I608" t="s">
         <v>1520</v>
       </c>
       <c r="J608" t="s">
-        <v>3022</v>
+        <v>3051</v>
       </c>
       <c r="K608">
         <v>2021</v>
@@ -37010,19 +37929,19 @@
         <v>43</v>
       </c>
       <c r="B609" t="s">
-        <v>3023</v>
+        <v>3052</v>
       </c>
       <c r="G609" t="s">
-        <v>3024</v>
+        <v>3053</v>
       </c>
       <c r="H609" t="s">
-        <v>3025</v>
+        <v>3054</v>
       </c>
       <c r="I609" t="s">
-        <v>3026</v>
+        <v>3055</v>
       </c>
       <c r="J609" t="s">
-        <v>3027</v>
+        <v>3056</v>
       </c>
       <c r="K609">
         <v>2022</v>
@@ -37034,19 +37953,19 @@
         <v>43</v>
       </c>
       <c r="B610" t="s">
-        <v>3028</v>
+        <v>3057</v>
       </c>
       <c r="G610" t="s">
-        <v>3029</v>
+        <v>3058</v>
       </c>
       <c r="H610" t="s">
-        <v>3030</v>
+        <v>3059</v>
       </c>
       <c r="I610" t="s">
         <v>226</v>
       </c>
       <c r="J610" t="s">
-        <v>3031</v>
+        <v>3060</v>
       </c>
       <c r="K610">
         <v>2020</v>
@@ -37058,19 +37977,19 @@
         <v>43</v>
       </c>
       <c r="B611" t="s">
-        <v>3032</v>
+        <v>3061</v>
       </c>
       <c r="G611" t="s">
-        <v>3033</v>
+        <v>3062</v>
       </c>
       <c r="H611" t="s">
-        <v>3034</v>
+        <v>3063</v>
       </c>
       <c r="I611" t="s">
         <v>226</v>
       </c>
       <c r="J611" t="s">
-        <v>3031</v>
+        <v>3060</v>
       </c>
       <c r="K611">
         <v>2023</v>
@@ -37082,19 +38001,19 @@
         <v>43</v>
       </c>
       <c r="B612" t="s">
-        <v>3035</v>
+        <v>3064</v>
       </c>
       <c r="G612" t="s">
-        <v>3036</v>
+        <v>3065</v>
       </c>
       <c r="H612" t="s">
-        <v>3037</v>
+        <v>3066</v>
       </c>
       <c r="I612" t="s">
-        <v>3038</v>
+        <v>3067</v>
       </c>
       <c r="J612" t="s">
-        <v>3039</v>
+        <v>3068</v>
       </c>
       <c r="K612">
         <v>2023</v>
@@ -37106,19 +38025,19 @@
         <v>43</v>
       </c>
       <c r="B613" t="s">
-        <v>3040</v>
+        <v>3069</v>
       </c>
       <c r="G613" t="s">
-        <v>3041</v>
+        <v>3070</v>
       </c>
       <c r="H613" t="s">
-        <v>3042</v>
+        <v>3071</v>
       </c>
       <c r="I613" t="s">
         <v>1414</v>
       </c>
       <c r="J613" t="s">
-        <v>3043</v>
+        <v>3072</v>
       </c>
       <c r="K613">
         <v>2023</v>
@@ -37130,19 +38049,19 @@
         <v>43</v>
       </c>
       <c r="B614" t="s">
-        <v>3044</v>
+        <v>3073</v>
       </c>
       <c r="G614" t="s">
-        <v>3045</v>
+        <v>3074</v>
       </c>
       <c r="H614" t="s">
-        <v>3046</v>
+        <v>3075</v>
       </c>
       <c r="I614" t="s">
         <v>409</v>
       </c>
       <c r="J614" t="s">
-        <v>3047</v>
+        <v>3076</v>
       </c>
       <c r="K614">
         <v>2022</v>
@@ -37154,19 +38073,19 @@
         <v>43</v>
       </c>
       <c r="B615" t="s">
-        <v>3048</v>
+        <v>3077</v>
       </c>
       <c r="G615" t="s">
-        <v>3049</v>
+        <v>3078</v>
       </c>
       <c r="H615" t="s">
-        <v>3050</v>
+        <v>3079</v>
       </c>
       <c r="I615" t="s">
-        <v>3051</v>
+        <v>3080</v>
       </c>
       <c r="J615" t="s">
-        <v>3052</v>
+        <v>3081</v>
       </c>
       <c r="K615">
         <v>2022</v>
@@ -37178,19 +38097,19 @@
         <v>43</v>
       </c>
       <c r="B616" t="s">
-        <v>3053</v>
+        <v>3082</v>
       </c>
       <c r="G616" t="s">
-        <v>3054</v>
+        <v>3083</v>
       </c>
       <c r="H616" t="s">
-        <v>3055</v>
+        <v>3084</v>
       </c>
       <c r="I616" t="s">
-        <v>2255</v>
+        <v>2275</v>
       </c>
       <c r="J616" t="s">
-        <v>3056</v>
+        <v>3085</v>
       </c>
       <c r="K616">
         <v>2019</v>
@@ -37202,19 +38121,19 @@
         <v>43</v>
       </c>
       <c r="B617" t="s">
-        <v>3057</v>
+        <v>3086</v>
       </c>
       <c r="G617" t="s">
-        <v>3058</v>
+        <v>3087</v>
       </c>
       <c r="H617" t="s">
-        <v>3059</v>
+        <v>3088</v>
       </c>
       <c r="I617" t="s">
-        <v>3060</v>
+        <v>3089</v>
       </c>
       <c r="J617" t="s">
-        <v>3061</v>
+        <v>3090</v>
       </c>
       <c r="K617">
         <v>2024</v>
@@ -37226,19 +38145,19 @@
         <v>43</v>
       </c>
       <c r="B618" t="s">
-        <v>3062</v>
+        <v>3091</v>
       </c>
       <c r="G618" t="s">
-        <v>3063</v>
+        <v>3092</v>
       </c>
       <c r="H618" t="s">
-        <v>3064</v>
+        <v>3093</v>
       </c>
       <c r="I618" t="s">
         <v>295</v>
       </c>
       <c r="J618" t="s">
-        <v>3065</v>
+        <v>3094</v>
       </c>
       <c r="K618">
         <v>2022</v>
@@ -37250,19 +38169,19 @@
         <v>43</v>
       </c>
       <c r="B619" t="s">
-        <v>3066</v>
+        <v>3095</v>
       </c>
       <c r="G619" t="s">
-        <v>3067</v>
+        <v>3096</v>
       </c>
       <c r="H619" t="s">
-        <v>3068</v>
+        <v>3097</v>
       </c>
       <c r="I619" t="s">
         <v>915</v>
       </c>
       <c r="J619" t="s">
-        <v>3069</v>
+        <v>3098</v>
       </c>
       <c r="K619">
         <v>1995</v>
@@ -37274,19 +38193,19 @@
         <v>43</v>
       </c>
       <c r="B620" t="s">
-        <v>3070</v>
+        <v>3099</v>
       </c>
       <c r="G620" t="s">
-        <v>3071</v>
+        <v>3100</v>
       </c>
       <c r="H620" t="s">
-        <v>3072</v>
+        <v>3101</v>
       </c>
       <c r="I620" t="s">
-        <v>3073</v>
+        <v>3102</v>
       </c>
       <c r="J620" t="s">
-        <v>3074</v>
+        <v>3103</v>
       </c>
       <c r="K620">
         <v>1992</v>
@@ -37298,19 +38217,19 @@
         <v>43</v>
       </c>
       <c r="B621" t="s">
-        <v>3075</v>
+        <v>3104</v>
       </c>
       <c r="G621" t="s">
-        <v>3076</v>
+        <v>3105</v>
       </c>
       <c r="H621" t="s">
-        <v>3077</v>
+        <v>3106</v>
       </c>
       <c r="I621" t="s">
-        <v>3078</v>
+        <v>3107</v>
       </c>
       <c r="J621" t="s">
-        <v>3079</v>
+        <v>3108</v>
       </c>
       <c r="K621">
         <v>2021</v>
@@ -37322,19 +38241,19 @@
         <v>43</v>
       </c>
       <c r="B622" t="s">
-        <v>3080</v>
+        <v>3109</v>
       </c>
       <c r="G622" t="s">
-        <v>3081</v>
+        <v>3110</v>
       </c>
       <c r="H622" t="s">
-        <v>3082</v>
+        <v>3111</v>
       </c>
       <c r="I622" t="s">
         <v>973</v>
       </c>
       <c r="J622" t="s">
-        <v>3083</v>
+        <v>3112</v>
       </c>
       <c r="K622">
         <v>2018</v>
@@ -37346,19 +38265,19 @@
         <v>43</v>
       </c>
       <c r="B623" t="s">
-        <v>3084</v>
+        <v>3113</v>
       </c>
       <c r="G623" t="s">
-        <v>3085</v>
+        <v>3114</v>
       </c>
       <c r="H623" t="s">
-        <v>3086</v>
+        <v>3115</v>
       </c>
       <c r="I623" t="s">
-        <v>3087</v>
+        <v>3116</v>
       </c>
       <c r="J623" t="s">
-        <v>3088</v>
+        <v>3117</v>
       </c>
       <c r="K623">
         <v>2019</v>
@@ -37370,19 +38289,19 @@
         <v>43</v>
       </c>
       <c r="B624" t="s">
-        <v>3089</v>
+        <v>3118</v>
       </c>
       <c r="G624" t="s">
-        <v>3090</v>
+        <v>3119</v>
       </c>
       <c r="H624" t="s">
-        <v>3091</v>
+        <v>3120</v>
       </c>
       <c r="I624" t="s">
         <v>1652</v>
       </c>
       <c r="J624" t="s">
-        <v>3092</v>
+        <v>3121</v>
       </c>
       <c r="K624">
         <v>2016</v>
@@ -37394,19 +38313,19 @@
         <v>43</v>
       </c>
       <c r="B625" t="s">
-        <v>3093</v>
+        <v>3122</v>
       </c>
       <c r="G625" t="s">
-        <v>3094</v>
+        <v>3123</v>
       </c>
       <c r="H625" t="s">
-        <v>3095</v>
+        <v>3124</v>
       </c>
       <c r="I625" t="s">
         <v>1242</v>
       </c>
       <c r="J625" t="s">
-        <v>3096</v>
+        <v>3125</v>
       </c>
       <c r="K625">
         <v>2002</v>
@@ -37418,19 +38337,19 @@
         <v>43</v>
       </c>
       <c r="B626" t="s">
-        <v>3097</v>
+        <v>3126</v>
       </c>
       <c r="G626" t="s">
-        <v>3098</v>
+        <v>3127</v>
       </c>
       <c r="H626" t="s">
-        <v>3099</v>
+        <v>3128</v>
       </c>
       <c r="I626" t="s">
-        <v>3100</v>
+        <v>3129</v>
       </c>
       <c r="J626" t="s">
-        <v>3101</v>
+        <v>3130</v>
       </c>
       <c r="K626">
         <v>2018</v>
@@ -37442,19 +38361,19 @@
         <v>43</v>
       </c>
       <c r="B627" t="s">
-        <v>3102</v>
+        <v>3131</v>
       </c>
       <c r="G627" t="s">
-        <v>3103</v>
+        <v>3132</v>
       </c>
       <c r="H627" t="s">
-        <v>3104</v>
+        <v>3133</v>
       </c>
       <c r="I627" t="s">
         <v>128</v>
       </c>
       <c r="J627" t="s">
-        <v>3105</v>
+        <v>3134</v>
       </c>
       <c r="K627">
         <v>2016</v>
@@ -37466,19 +38385,19 @@
         <v>43</v>
       </c>
       <c r="B628" t="s">
-        <v>3106</v>
+        <v>3135</v>
       </c>
       <c r="G628" t="s">
-        <v>3107</v>
+        <v>3136</v>
       </c>
       <c r="H628" t="s">
-        <v>3108</v>
+        <v>3137</v>
       </c>
       <c r="I628" t="s">
         <v>915</v>
       </c>
       <c r="J628" t="s">
-        <v>3109</v>
+        <v>3138</v>
       </c>
       <c r="K628">
         <v>2004</v>
@@ -37490,19 +38409,19 @@
         <v>43</v>
       </c>
       <c r="B629" t="s">
-        <v>3110</v>
+        <v>3139</v>
       </c>
       <c r="G629" t="s">
-        <v>3111</v>
+        <v>3140</v>
       </c>
       <c r="H629" t="s">
-        <v>3112</v>
+        <v>3141</v>
       </c>
       <c r="I629" t="s">
         <v>1652</v>
       </c>
       <c r="J629" t="s">
-        <v>3113</v>
+        <v>3142</v>
       </c>
       <c r="K629">
         <v>2008</v>
@@ -37514,19 +38433,19 @@
         <v>43</v>
       </c>
       <c r="B630" t="s">
-        <v>3114</v>
+        <v>3143</v>
       </c>
       <c r="G630" t="s">
-        <v>3115</v>
+        <v>3144</v>
       </c>
       <c r="H630" t="s">
-        <v>3116</v>
+        <v>3145</v>
       </c>
       <c r="I630" t="s">
         <v>692</v>
       </c>
       <c r="J630" t="s">
-        <v>3117</v>
+        <v>3146</v>
       </c>
       <c r="K630">
         <v>2014</v>
@@ -37538,19 +38457,19 @@
         <v>43</v>
       </c>
       <c r="B631" t="s">
-        <v>3118</v>
+        <v>3147</v>
       </c>
       <c r="G631" t="s">
-        <v>3119</v>
+        <v>3148</v>
       </c>
       <c r="H631" t="s">
-        <v>3120</v>
+        <v>3149</v>
       </c>
       <c r="I631" t="s">
-        <v>2786</v>
+        <v>2815</v>
       </c>
       <c r="J631" t="s">
-        <v>3121</v>
+        <v>3150</v>
       </c>
       <c r="K631">
         <v>2004</v>
@@ -37562,19 +38481,19 @@
         <v>43</v>
       </c>
       <c r="B632" t="s">
-        <v>3122</v>
+        <v>3151</v>
       </c>
       <c r="G632" t="s">
-        <v>3123</v>
+        <v>3152</v>
       </c>
       <c r="H632" t="s">
-        <v>3124</v>
+        <v>3153</v>
       </c>
       <c r="I632" t="s">
-        <v>3125</v>
+        <v>3154</v>
       </c>
       <c r="J632" t="s">
-        <v>3126</v>
+        <v>3155</v>
       </c>
       <c r="K632">
         <v>1994</v>
@@ -37586,19 +38505,19 @@
         <v>43</v>
       </c>
       <c r="B633" t="s">
-        <v>3127</v>
+        <v>3156</v>
       </c>
       <c r="G633" t="s">
-        <v>3128</v>
+        <v>3157</v>
       </c>
       <c r="H633" t="s">
-        <v>3129</v>
+        <v>3158</v>
       </c>
       <c r="I633" t="s">
-        <v>3130</v>
+        <v>3159</v>
       </c>
       <c r="J633" t="s">
-        <v>3131</v>
+        <v>3160</v>
       </c>
       <c r="K633">
         <v>2010</v>
@@ -37610,19 +38529,19 @@
         <v>43</v>
       </c>
       <c r="B634" t="s">
-        <v>3132</v>
+        <v>3161</v>
       </c>
       <c r="G634" t="s">
-        <v>3133</v>
+        <v>3162</v>
       </c>
       <c r="H634" t="s">
-        <v>3134</v>
+        <v>3163</v>
       </c>
       <c r="I634" t="s">
         <v>226</v>
       </c>
       <c r="J634" t="s">
-        <v>3135</v>
+        <v>3164</v>
       </c>
       <c r="K634">
         <v>2025</v>
@@ -37634,19 +38553,19 @@
         <v>43</v>
       </c>
       <c r="B635" t="s">
-        <v>3136</v>
+        <v>3165</v>
       </c>
       <c r="G635" t="s">
-        <v>3137</v>
+        <v>3166</v>
       </c>
       <c r="H635" t="s">
-        <v>3138</v>
+        <v>3167</v>
       </c>
       <c r="I635" t="s">
         <v>825</v>
       </c>
       <c r="J635" t="s">
-        <v>3139</v>
+        <v>3168</v>
       </c>
       <c r="K635">
         <v>2020</v>
@@ -37658,19 +38577,19 @@
         <v>43</v>
       </c>
       <c r="B636" t="s">
-        <v>3140</v>
+        <v>3169</v>
       </c>
       <c r="G636" t="s">
-        <v>3141</v>
+        <v>3170</v>
       </c>
       <c r="H636" t="s">
-        <v>3142</v>
+        <v>3171</v>
       </c>
       <c r="I636" t="s">
-        <v>3143</v>
+        <v>3172</v>
       </c>
       <c r="J636" t="s">
-        <v>3144</v>
+        <v>3173</v>
       </c>
       <c r="K636">
         <v>2017</v>
@@ -37682,19 +38601,19 @@
         <v>43</v>
       </c>
       <c r="B637" t="s">
-        <v>3145</v>
+        <v>3174</v>
       </c>
       <c r="G637" t="s">
-        <v>3146</v>
+        <v>3175</v>
       </c>
       <c r="H637" t="s">
-        <v>3147</v>
+        <v>3176</v>
       </c>
       <c r="I637" t="s">
         <v>295</v>
       </c>
       <c r="J637" t="s">
-        <v>3148</v>
+        <v>3177</v>
       </c>
       <c r="K637">
         <v>2025</v>
@@ -37706,19 +38625,19 @@
         <v>43</v>
       </c>
       <c r="B638" t="s">
-        <v>3149</v>
+        <v>3178</v>
       </c>
       <c r="G638" t="s">
-        <v>3150</v>
+        <v>3179</v>
       </c>
       <c r="H638" t="s">
-        <v>3151</v>
+        <v>3180</v>
       </c>
       <c r="I638" t="s">
         <v>295</v>
       </c>
       <c r="J638" t="s">
-        <v>3152</v>
+        <v>3181</v>
       </c>
       <c r="K638">
         <v>2023</v>
@@ -37730,19 +38649,19 @@
         <v>43</v>
       </c>
       <c r="B639" t="s">
-        <v>3153</v>
+        <v>3182</v>
       </c>
       <c r="G639" t="s">
-        <v>3154</v>
+        <v>3183</v>
       </c>
       <c r="H639" t="s">
-        <v>3155</v>
+        <v>3184</v>
       </c>
       <c r="I639" t="s">
-        <v>3156</v>
+        <v>3185</v>
       </c>
       <c r="J639" t="s">
-        <v>3157</v>
+        <v>3186</v>
       </c>
       <c r="K639">
         <v>2009</v>
@@ -37754,19 +38673,19 @@
         <v>43</v>
       </c>
       <c r="B640" t="s">
-        <v>3158</v>
+        <v>3187</v>
       </c>
       <c r="G640" t="s">
-        <v>3159</v>
+        <v>3188</v>
       </c>
       <c r="H640" t="s">
-        <v>3160</v>
+        <v>3189</v>
       </c>
       <c r="I640" t="s">
         <v>226</v>
       </c>
       <c r="J640" t="s">
-        <v>3161</v>
+        <v>3190</v>
       </c>
       <c r="K640">
         <v>2024</v>
@@ -37778,19 +38697,19 @@
         <v>43</v>
       </c>
       <c r="B641" t="s">
-        <v>3162</v>
+        <v>3191</v>
       </c>
       <c r="G641" t="s">
-        <v>3163</v>
+        <v>3192</v>
       </c>
       <c r="H641" t="s">
-        <v>3164</v>
+        <v>3193</v>
       </c>
       <c r="I641" t="s">
         <v>1548</v>
       </c>
       <c r="J641" t="s">
-        <v>3165</v>
+        <v>3194</v>
       </c>
       <c r="K641">
         <v>2024</v>
@@ -37802,19 +38721,19 @@
         <v>43</v>
       </c>
       <c r="B642" t="s">
-        <v>3166</v>
+        <v>3195</v>
       </c>
       <c r="G642" t="s">
-        <v>3167</v>
+        <v>3196</v>
       </c>
       <c r="H642" t="s">
-        <v>3168</v>
+        <v>3197</v>
       </c>
       <c r="I642" t="s">
         <v>549</v>
       </c>
       <c r="J642" t="s">
-        <v>3169</v>
+        <v>3198</v>
       </c>
       <c r="K642">
         <v>2020</v>
@@ -37826,19 +38745,19 @@
         <v>43</v>
       </c>
       <c r="B643" t="s">
-        <v>3170</v>
+        <v>3199</v>
       </c>
       <c r="G643" t="s">
-        <v>3171</v>
+        <v>3200</v>
       </c>
       <c r="H643" t="s">
-        <v>3172</v>
+        <v>3201</v>
       </c>
       <c r="I643" t="s">
         <v>148</v>
       </c>
       <c r="J643" t="s">
-        <v>3173</v>
+        <v>3202</v>
       </c>
       <c r="K643">
         <v>2020</v>
@@ -37850,19 +38769,19 @@
         <v>43</v>
       </c>
       <c r="B644" t="s">
-        <v>3174</v>
+        <v>3203</v>
       </c>
       <c r="G644" t="s">
-        <v>3175</v>
+        <v>3204</v>
       </c>
       <c r="H644" t="s">
-        <v>3176</v>
+        <v>3205</v>
       </c>
       <c r="I644" t="s">
-        <v>3177</v>
+        <v>3206</v>
       </c>
       <c r="J644" t="s">
-        <v>3178</v>
+        <v>3207</v>
       </c>
       <c r="K644">
         <v>2021</v>
@@ -37874,19 +38793,19 @@
         <v>43</v>
       </c>
       <c r="B645" t="s">
-        <v>3179</v>
+        <v>3208</v>
       </c>
       <c r="G645" t="s">
-        <v>3180</v>
+        <v>3209</v>
       </c>
       <c r="H645" t="s">
-        <v>3181</v>
+        <v>3210</v>
       </c>
       <c r="I645" t="s">
         <v>1308</v>
       </c>
       <c r="J645" t="s">
-        <v>3182</v>
+        <v>3211</v>
       </c>
       <c r="K645">
         <v>2024</v>
@@ -37898,19 +38817,19 @@
         <v>43</v>
       </c>
       <c r="B646" t="s">
-        <v>3183</v>
+        <v>3212</v>
       </c>
       <c r="G646" t="s">
-        <v>3184</v>
+        <v>3213</v>
       </c>
       <c r="H646" t="s">
-        <v>3185</v>
+        <v>3214</v>
       </c>
       <c r="I646" t="s">
-        <v>2290</v>
+        <v>2313</v>
       </c>
       <c r="J646" t="s">
-        <v>3186</v>
+        <v>3215</v>
       </c>
       <c r="K646">
         <v>2024</v>
@@ -37922,19 +38841,19 @@
         <v>43</v>
       </c>
       <c r="B647" t="s">
-        <v>3187</v>
+        <v>3216</v>
       </c>
       <c r="G647" t="s">
-        <v>3188</v>
+        <v>3217</v>
       </c>
       <c r="H647" t="s">
-        <v>3189</v>
+        <v>3218</v>
       </c>
       <c r="I647" t="s">
         <v>295</v>
       </c>
       <c r="J647" t="s">
-        <v>3190</v>
+        <v>3219</v>
       </c>
       <c r="K647">
         <v>2021</v>
@@ -37946,19 +38865,19 @@
         <v>43</v>
       </c>
       <c r="B648" t="s">
-        <v>3191</v>
+        <v>3220</v>
       </c>
       <c r="G648" t="s">
-        <v>3192</v>
+        <v>3221</v>
       </c>
       <c r="H648" t="s">
-        <v>3193</v>
+        <v>3222</v>
       </c>
       <c r="I648" t="s">
         <v>1652</v>
       </c>
       <c r="J648" t="s">
-        <v>3194</v>
+        <v>3223</v>
       </c>
       <c r="K648">
         <v>2022</v>
@@ -37970,19 +38889,19 @@
         <v>43</v>
       </c>
       <c r="B649" t="s">
-        <v>3195</v>
+        <v>3224</v>
       </c>
       <c r="G649" t="s">
-        <v>3196</v>
+        <v>3225</v>
       </c>
       <c r="H649" t="s">
-        <v>3197</v>
+        <v>3226</v>
       </c>
       <c r="I649" t="s">
         <v>409</v>
       </c>
       <c r="J649" t="s">
-        <v>3198</v>
+        <v>3227</v>
       </c>
       <c r="K649">
         <v>2022</v>
@@ -37994,19 +38913,19 @@
         <v>43</v>
       </c>
       <c r="B650" t="s">
-        <v>3199</v>
+        <v>3228</v>
       </c>
       <c r="G650" t="s">
-        <v>3200</v>
+        <v>3229</v>
       </c>
       <c r="H650" t="s">
-        <v>3201</v>
+        <v>3230</v>
       </c>
       <c r="I650" t="s">
-        <v>2637</v>
+        <v>2666</v>
       </c>
       <c r="J650" t="s">
-        <v>3202</v>
+        <v>3231</v>
       </c>
       <c r="K650">
         <v>2026</v>
@@ -38018,19 +38937,19 @@
         <v>43</v>
       </c>
       <c r="B651" t="s">
-        <v>3203</v>
+        <v>3232</v>
       </c>
       <c r="G651" t="s">
-        <v>3204</v>
+        <v>3233</v>
       </c>
       <c r="H651" t="s">
-        <v>3205</v>
+        <v>3234</v>
       </c>
       <c r="I651" t="s">
-        <v>3206</v>
+        <v>3235</v>
       </c>
       <c r="J651" t="s">
-        <v>3207</v>
+        <v>3236</v>
       </c>
       <c r="K651">
         <v>2024</v>
@@ -38042,19 +38961,19 @@
         <v>43</v>
       </c>
       <c r="B652" t="s">
-        <v>3208</v>
+        <v>3237</v>
       </c>
       <c r="G652" t="s">
-        <v>3209</v>
+        <v>3238</v>
       </c>
       <c r="H652" t="s">
-        <v>3210</v>
+        <v>3239</v>
       </c>
       <c r="I652" t="s">
         <v>1336</v>
       </c>
       <c r="J652" t="s">
-        <v>3211</v>
+        <v>3240</v>
       </c>
       <c r="K652">
         <v>2015</v>
@@ -38066,19 +38985,19 @@
         <v>43</v>
       </c>
       <c r="B653" t="s">
-        <v>3212</v>
+        <v>3241</v>
       </c>
       <c r="G653" t="s">
-        <v>3213</v>
+        <v>3242</v>
       </c>
       <c r="H653" t="s">
-        <v>3214</v>
+        <v>3243</v>
       </c>
       <c r="I653" t="s">
-        <v>3215</v>
+        <v>3244</v>
       </c>
       <c r="J653" t="s">
-        <v>3216</v>
+        <v>3245</v>
       </c>
       <c r="K653">
         <v>2017</v>
@@ -38090,19 +39009,19 @@
         <v>43</v>
       </c>
       <c r="B654" t="s">
-        <v>3217</v>
+        <v>3246</v>
       </c>
       <c r="G654" t="s">
-        <v>3218</v>
+        <v>3247</v>
       </c>
       <c r="H654" t="s">
-        <v>3219</v>
+        <v>3248</v>
       </c>
       <c r="I654" t="s">
-        <v>3220</v>
+        <v>3249</v>
       </c>
       <c r="J654" t="s">
-        <v>3221</v>
+        <v>3250</v>
       </c>
       <c r="K654">
         <v>2016</v>
@@ -38114,19 +39033,19 @@
         <v>43</v>
       </c>
       <c r="B655" t="s">
-        <v>3222</v>
+        <v>3251</v>
       </c>
       <c r="G655" t="s">
-        <v>3223</v>
+        <v>3252</v>
       </c>
       <c r="H655" t="s">
-        <v>3224</v>
+        <v>3253</v>
       </c>
       <c r="I655" t="s">
-        <v>3225</v>
+        <v>3254</v>
       </c>
       <c r="J655" t="s">
-        <v>3226</v>
+        <v>3255</v>
       </c>
       <c r="K655">
         <v>2018</v>
@@ -38138,19 +39057,19 @@
         <v>43</v>
       </c>
       <c r="B656" t="s">
-        <v>3227</v>
+        <v>3256</v>
       </c>
       <c r="G656" t="s">
-        <v>3228</v>
+        <v>3257</v>
       </c>
       <c r="H656" t="s">
-        <v>3229</v>
+        <v>3258</v>
       </c>
       <c r="I656" t="s">
         <v>692</v>
       </c>
       <c r="J656" t="s">
-        <v>3230</v>
+        <v>3259</v>
       </c>
       <c r="K656">
         <v>2009</v>
@@ -38162,19 +39081,19 @@
         <v>43</v>
       </c>
       <c r="B657" t="s">
-        <v>3231</v>
+        <v>3260</v>
       </c>
       <c r="G657" t="s">
-        <v>3232</v>
+        <v>3261</v>
       </c>
       <c r="H657" t="s">
-        <v>3233</v>
+        <v>3262</v>
       </c>
       <c r="I657" t="s">
         <v>2054</v>
       </c>
       <c r="J657" t="s">
-        <v>3234</v>
+        <v>3263</v>
       </c>
       <c r="K657">
         <v>2013</v>
@@ -38186,19 +39105,19 @@
         <v>43</v>
       </c>
       <c r="B658" t="s">
-        <v>3235</v>
+        <v>3264</v>
       </c>
       <c r="G658" t="s">
-        <v>3236</v>
+        <v>3265</v>
       </c>
       <c r="H658" t="s">
-        <v>3237</v>
+        <v>3266</v>
       </c>
       <c r="I658" t="s">
-        <v>2851</v>
+        <v>2880</v>
       </c>
       <c r="J658" t="s">
-        <v>3238</v>
+        <v>3267</v>
       </c>
       <c r="K658">
         <v>2014</v>
@@ -38210,19 +39129,19 @@
         <v>43</v>
       </c>
       <c r="B659" t="s">
-        <v>3239</v>
+        <v>3268</v>
       </c>
       <c r="G659" t="s">
-        <v>3240</v>
+        <v>3269</v>
       </c>
       <c r="H659" t="s">
-        <v>3241</v>
+        <v>3270</v>
       </c>
       <c r="I659" t="s">
         <v>1987</v>
       </c>
       <c r="J659" t="s">
-        <v>3242</v>
+        <v>3271</v>
       </c>
       <c r="K659">
         <v>2024</v>
@@ -38234,19 +39153,19 @@
         <v>43</v>
       </c>
       <c r="B660" t="s">
-        <v>3243</v>
+        <v>3272</v>
       </c>
       <c r="G660" t="s">
-        <v>3244</v>
+        <v>3273</v>
       </c>
       <c r="H660" t="s">
-        <v>3245</v>
+        <v>3274</v>
       </c>
       <c r="I660" t="s">
         <v>51</v>
       </c>
       <c r="J660" t="s">
-        <v>3246</v>
+        <v>3275</v>
       </c>
       <c r="K660">
         <v>2023</v>
@@ -38258,19 +39177,19 @@
         <v>43</v>
       </c>
       <c r="B661" t="s">
-        <v>3247</v>
+        <v>3276</v>
       </c>
       <c r="G661" t="s">
-        <v>3248</v>
+        <v>3277</v>
       </c>
       <c r="H661" t="s">
-        <v>3249</v>
+        <v>3278</v>
       </c>
       <c r="I661" t="s">
         <v>664</v>
       </c>
       <c r="J661" t="s">
-        <v>3250</v>
+        <v>3279</v>
       </c>
       <c r="K661">
         <v>2001</v>
@@ -38282,19 +39201,19 @@
         <v>43</v>
       </c>
       <c r="B662" t="s">
-        <v>3251</v>
+        <v>3280</v>
       </c>
       <c r="G662" t="s">
-        <v>3252</v>
+        <v>3281</v>
       </c>
       <c r="H662" t="s">
-        <v>3253</v>
+        <v>3282</v>
       </c>
       <c r="I662" t="s">
-        <v>2838</v>
+        <v>2867</v>
       </c>
       <c r="J662" t="s">
-        <v>3254</v>
+        <v>3283</v>
       </c>
       <c r="K662">
         <v>2024</v>
@@ -38306,19 +39225,19 @@
         <v>43</v>
       </c>
       <c r="B663" t="s">
-        <v>3255</v>
+        <v>3284</v>
       </c>
       <c r="G663" t="s">
-        <v>3256</v>
+        <v>3285</v>
       </c>
       <c r="H663" t="s">
-        <v>3257</v>
+        <v>3286</v>
       </c>
       <c r="I663" t="s">
-        <v>3013</v>
+        <v>3042</v>
       </c>
       <c r="J663" t="s">
-        <v>3258</v>
+        <v>3287</v>
       </c>
       <c r="K663">
         <v>2025</v>
@@ -38330,19 +39249,19 @@
         <v>43</v>
       </c>
       <c r="B664" t="s">
-        <v>3259</v>
+        <v>3288</v>
       </c>
       <c r="G664" t="s">
-        <v>3260</v>
+        <v>3289</v>
       </c>
       <c r="H664" t="s">
-        <v>3261</v>
+        <v>3290</v>
       </c>
       <c r="I664" t="s">
         <v>409</v>
       </c>
       <c r="J664" t="s">
-        <v>3262</v>
+        <v>3291</v>
       </c>
       <c r="K664">
         <v>2022</v>
@@ -38354,19 +39273,19 @@
         <v>43</v>
       </c>
       <c r="B665" t="s">
-        <v>3263</v>
+        <v>3292</v>
       </c>
       <c r="G665" t="s">
-        <v>3264</v>
+        <v>3293</v>
       </c>
       <c r="H665" t="s">
-        <v>3265</v>
+        <v>3294</v>
       </c>
       <c r="I665" t="s">
-        <v>3266</v>
+        <v>3295</v>
       </c>
       <c r="J665" t="s">
-        <v>3267</v>
+        <v>3296</v>
       </c>
       <c r="K665">
         <v>2014</v>
@@ -38378,19 +39297,19 @@
         <v>43</v>
       </c>
       <c r="B666" t="s">
-        <v>3268</v>
+        <v>3297</v>
       </c>
       <c r="G666" t="s">
-        <v>3269</v>
+        <v>3298</v>
       </c>
       <c r="H666" t="s">
-        <v>3270</v>
+        <v>3299</v>
       </c>
       <c r="I666" t="s">
         <v>1414</v>
       </c>
       <c r="J666" t="s">
-        <v>3271</v>
+        <v>3300</v>
       </c>
       <c r="K666">
         <v>2025</v>
@@ -38402,19 +39321,19 @@
         <v>43</v>
       </c>
       <c r="B667" t="s">
-        <v>3272</v>
+        <v>3301</v>
       </c>
       <c r="G667" t="s">
-        <v>3273</v>
+        <v>3302</v>
       </c>
       <c r="H667" t="s">
-        <v>3274</v>
+        <v>3303</v>
       </c>
       <c r="I667" t="s">
         <v>459</v>
       </c>
       <c r="J667" t="s">
-        <v>3275</v>
+        <v>3304</v>
       </c>
       <c r="K667">
         <v>2016</v>
@@ -38426,19 +39345,19 @@
         <v>43</v>
       </c>
       <c r="B668" t="s">
-        <v>3276</v>
+        <v>3305</v>
       </c>
       <c r="G668" t="s">
-        <v>3277</v>
+        <v>3306</v>
       </c>
       <c r="H668" t="s">
-        <v>3278</v>
+        <v>3307</v>
       </c>
       <c r="I668" t="s">
-        <v>3279</v>
+        <v>3308</v>
       </c>
       <c r="J668" t="s">
-        <v>3280</v>
+        <v>3309</v>
       </c>
       <c r="K668">
         <v>2018</v>
@@ -38450,19 +39369,19 @@
         <v>43</v>
       </c>
       <c r="B669" t="s">
-        <v>3281</v>
+        <v>3310</v>
       </c>
       <c r="G669" t="s">
-        <v>3282</v>
+        <v>3311</v>
       </c>
       <c r="H669" t="s">
-        <v>3283</v>
+        <v>3312</v>
       </c>
       <c r="I669" t="s">
         <v>426</v>
       </c>
       <c r="J669" t="s">
-        <v>3284</v>
+        <v>3313</v>
       </c>
       <c r="K669">
         <v>2015</v>
@@ -38474,19 +39393,19 @@
         <v>43</v>
       </c>
       <c r="B670" t="s">
-        <v>3285</v>
+        <v>3314</v>
       </c>
       <c r="G670" t="s">
-        <v>3286</v>
+        <v>3315</v>
       </c>
       <c r="H670" t="s">
-        <v>3287</v>
+        <v>3316</v>
       </c>
       <c r="I670" t="s">
-        <v>3288</v>
+        <v>3317</v>
       </c>
       <c r="J670" t="s">
-        <v>3289</v>
+        <v>3318</v>
       </c>
       <c r="K670">
         <v>2018</v>
@@ -38498,19 +39417,19 @@
         <v>43</v>
       </c>
       <c r="B671" t="s">
-        <v>3290</v>
+        <v>3319</v>
       </c>
       <c r="G671" t="s">
-        <v>3291</v>
+        <v>3320</v>
       </c>
       <c r="H671" t="s">
-        <v>3292</v>
+        <v>3321</v>
       </c>
       <c r="I671" t="s">
-        <v>2223</v>
+        <v>2236</v>
       </c>
       <c r="J671" t="s">
-        <v>3293</v>
+        <v>3322</v>
       </c>
       <c r="K671">
         <v>2011</v>
@@ -38522,19 +39441,19 @@
         <v>43</v>
       </c>
       <c r="B672" t="s">
-        <v>3294</v>
+        <v>3323</v>
       </c>
       <c r="G672" t="s">
-        <v>3295</v>
+        <v>3324</v>
       </c>
       <c r="H672" t="s">
-        <v>3296</v>
+        <v>3325</v>
       </c>
       <c r="I672" t="s">
         <v>128</v>
       </c>
       <c r="J672" t="s">
-        <v>3297</v>
+        <v>3326</v>
       </c>
       <c r="K672">
         <v>2015</v>
@@ -38546,19 +39465,19 @@
         <v>43</v>
       </c>
       <c r="B673" t="s">
-        <v>3298</v>
+        <v>3327</v>
       </c>
       <c r="G673" t="s">
-        <v>3299</v>
+        <v>3328</v>
       </c>
       <c r="H673" t="s">
-        <v>3300</v>
+        <v>3329</v>
       </c>
       <c r="I673" t="s">
         <v>1479</v>
       </c>
       <c r="J673" t="s">
-        <v>3301</v>
+        <v>3330</v>
       </c>
       <c r="K673">
         <v>2022</v>
@@ -38570,19 +39489,19 @@
         <v>43</v>
       </c>
       <c r="B674" t="s">
-        <v>3302</v>
+        <v>3331</v>
       </c>
       <c r="G674" t="s">
-        <v>3303</v>
+        <v>3332</v>
       </c>
       <c r="H674" t="s">
-        <v>3304</v>
+        <v>3333</v>
       </c>
       <c r="I674" t="s">
-        <v>3279</v>
+        <v>3308</v>
       </c>
       <c r="J674" t="s">
-        <v>3305</v>
+        <v>3334</v>
       </c>
       <c r="K674">
         <v>2023</v>
@@ -38594,19 +39513,19 @@
         <v>43</v>
       </c>
       <c r="B675" t="s">
-        <v>3306</v>
+        <v>3335</v>
       </c>
       <c r="G675" t="s">
-        <v>3307</v>
+        <v>3336</v>
       </c>
       <c r="H675" t="s">
-        <v>3308</v>
+        <v>3337</v>
       </c>
       <c r="I675" t="s">
-        <v>3309</v>
+        <v>3338</v>
       </c>
       <c r="J675" t="s">
-        <v>3310</v>
+        <v>3339</v>
       </c>
       <c r="K675">
         <v>2021</v>
@@ -38618,19 +39537,19 @@
         <v>43</v>
       </c>
       <c r="B676" t="s">
-        <v>3311</v>
+        <v>3340</v>
       </c>
       <c r="G676" t="s">
-        <v>3312</v>
+        <v>3341</v>
       </c>
       <c r="H676" t="s">
-        <v>3313</v>
+        <v>3342</v>
       </c>
       <c r="I676" t="s">
         <v>1674</v>
       </c>
       <c r="J676" t="s">
-        <v>3314</v>
+        <v>3343</v>
       </c>
       <c r="K676">
         <v>2022</v>
@@ -38642,19 +39561,19 @@
         <v>43</v>
       </c>
       <c r="B677" t="s">
-        <v>3315</v>
+        <v>3344</v>
       </c>
       <c r="G677" t="s">
-        <v>3316</v>
+        <v>3345</v>
       </c>
       <c r="H677" t="s">
-        <v>3317</v>
+        <v>3346</v>
       </c>
       <c r="I677" t="s">
         <v>687</v>
       </c>
       <c r="J677" t="s">
-        <v>3318</v>
+        <v>3347</v>
       </c>
       <c r="K677">
         <v>2026</v>
@@ -38666,19 +39585,19 @@
         <v>43</v>
       </c>
       <c r="B678" t="s">
-        <v>3319</v>
+        <v>3348</v>
       </c>
       <c r="G678" t="s">
-        <v>3320</v>
+        <v>3349</v>
       </c>
       <c r="H678" t="s">
-        <v>3321</v>
+        <v>3350</v>
       </c>
       <c r="I678" t="s">
         <v>409</v>
       </c>
       <c r="J678" t="s">
-        <v>3322</v>
+        <v>3351</v>
       </c>
       <c r="K678">
         <v>2022</v>
@@ -38690,19 +39609,19 @@
         <v>43</v>
       </c>
       <c r="B679" t="s">
-        <v>3323</v>
+        <v>3352</v>
       </c>
       <c r="G679" t="s">
-        <v>3324</v>
+        <v>3353</v>
       </c>
       <c r="H679" t="s">
-        <v>3325</v>
+        <v>3354</v>
       </c>
       <c r="I679" t="s">
         <v>51</v>
       </c>
       <c r="J679" t="s">
-        <v>3326</v>
+        <v>3355</v>
       </c>
       <c r="K679">
         <v>2019</v>
@@ -38714,19 +39633,19 @@
         <v>43</v>
       </c>
       <c r="B680" t="s">
-        <v>3327</v>
+        <v>3356</v>
       </c>
       <c r="G680" t="s">
-        <v>3328</v>
+        <v>3357</v>
       </c>
       <c r="H680" t="s">
-        <v>3329</v>
+        <v>3358</v>
       </c>
       <c r="I680" t="s">
-        <v>3330</v>
+        <v>3359</v>
       </c>
       <c r="J680" t="s">
-        <v>3331</v>
+        <v>3360</v>
       </c>
       <c r="K680">
         <v>2021</v>
@@ -38738,19 +39657,19 @@
         <v>43</v>
       </c>
       <c r="B681" t="s">
-        <v>3332</v>
+        <v>3361</v>
       </c>
       <c r="G681" t="s">
-        <v>3333</v>
+        <v>3362</v>
       </c>
       <c r="H681" t="s">
-        <v>3334</v>
+        <v>3363</v>
       </c>
       <c r="I681" t="s">
         <v>237</v>
       </c>
       <c r="J681" t="s">
-        <v>3335</v>
+        <v>3364</v>
       </c>
       <c r="K681">
         <v>2017</v>
@@ -38762,19 +39681,19 @@
         <v>43</v>
       </c>
       <c r="B682" t="s">
-        <v>3336</v>
+        <v>3365</v>
       </c>
       <c r="G682" t="s">
-        <v>3337</v>
+        <v>3366</v>
       </c>
       <c r="H682" t="s">
-        <v>3338</v>
+        <v>3367</v>
       </c>
       <c r="I682" t="s">
         <v>1080</v>
       </c>
       <c r="J682" t="s">
-        <v>3339</v>
+        <v>3368</v>
       </c>
       <c r="K682">
         <v>2025</v>
@@ -38786,19 +39705,19 @@
         <v>43</v>
       </c>
       <c r="B683" t="s">
-        <v>3340</v>
+        <v>3369</v>
       </c>
       <c r="G683" t="s">
-        <v>3341</v>
+        <v>3370</v>
       </c>
       <c r="H683" t="s">
-        <v>3342</v>
+        <v>3371</v>
       </c>
       <c r="I683" t="s">
         <v>237</v>
       </c>
       <c r="J683" t="s">
-        <v>3343</v>
+        <v>3372</v>
       </c>
       <c r="K683">
         <v>2025</v>
@@ -38810,19 +39729,19 @@
         <v>43</v>
       </c>
       <c r="B684" t="s">
-        <v>3344</v>
+        <v>3373</v>
       </c>
       <c r="G684" t="s">
-        <v>3345</v>
+        <v>3374</v>
       </c>
       <c r="H684" t="s">
-        <v>3346</v>
+        <v>3375</v>
       </c>
       <c r="I684" t="s">
         <v>819</v>
       </c>
       <c r="J684" t="s">
-        <v>3347</v>
+        <v>3376</v>
       </c>
       <c r="K684">
         <v>2019</v>
@@ -38834,19 +39753,19 @@
         <v>43</v>
       </c>
       <c r="B685" t="s">
-        <v>3348</v>
+        <v>3377</v>
       </c>
       <c r="G685" t="s">
-        <v>3349</v>
+        <v>3378</v>
       </c>
       <c r="H685" t="s">
-        <v>3350</v>
+        <v>3379</v>
       </c>
       <c r="I685" t="s">
         <v>415</v>
       </c>
       <c r="J685" t="s">
-        <v>3351</v>
+        <v>3380</v>
       </c>
       <c r="K685">
         <v>2024</v>
@@ -38858,19 +39777,19 @@
         <v>43</v>
       </c>
       <c r="B686" t="s">
-        <v>3352</v>
+        <v>3381</v>
       </c>
       <c r="G686" t="s">
-        <v>3353</v>
+        <v>3382</v>
       </c>
       <c r="H686" t="s">
-        <v>3354</v>
+        <v>3383</v>
       </c>
       <c r="I686" t="s">
-        <v>3355</v>
+        <v>3384</v>
       </c>
       <c r="J686" t="s">
-        <v>3356</v>
+        <v>3385</v>
       </c>
       <c r="K686">
         <v>2024</v>
@@ -38882,19 +39801,19 @@
         <v>43</v>
       </c>
       <c r="B687" t="s">
-        <v>3357</v>
+        <v>3386</v>
       </c>
       <c r="G687" t="s">
-        <v>3358</v>
+        <v>3387</v>
       </c>
       <c r="H687" t="s">
-        <v>3359</v>
+        <v>3388</v>
       </c>
       <c r="I687" t="s">
         <v>1929</v>
       </c>
       <c r="J687" t="s">
-        <v>3360</v>
+        <v>3389</v>
       </c>
       <c r="K687">
         <v>2024</v>
@@ -38906,19 +39825,19 @@
         <v>43</v>
       </c>
       <c r="B688" t="s">
-        <v>3361</v>
+        <v>3390</v>
       </c>
       <c r="G688" t="s">
-        <v>3362</v>
+        <v>3391</v>
       </c>
       <c r="H688" t="s">
-        <v>3363</v>
+        <v>3392</v>
       </c>
       <c r="I688" t="s">
-        <v>3364</v>
+        <v>3393</v>
       </c>
       <c r="J688" t="s">
-        <v>3365</v>
+        <v>3394</v>
       </c>
       <c r="K688">
         <v>2023</v>
@@ -38930,19 +39849,19 @@
         <v>43</v>
       </c>
       <c r="B689" t="s">
-        <v>3366</v>
+        <v>3395</v>
       </c>
       <c r="G689" t="s">
-        <v>3367</v>
+        <v>3396</v>
       </c>
       <c r="H689" t="s">
-        <v>3368</v>
+        <v>3397</v>
       </c>
       <c r="I689" t="s">
-        <v>3369</v>
+        <v>3398</v>
       </c>
       <c r="J689" t="s">
-        <v>3370</v>
+        <v>3399</v>
       </c>
       <c r="K689">
         <v>2024</v>
@@ -38954,19 +39873,19 @@
         <v>43</v>
       </c>
       <c r="B690" t="s">
-        <v>3371</v>
+        <v>3400</v>
       </c>
       <c r="G690" t="s">
-        <v>3372</v>
+        <v>3401</v>
       </c>
       <c r="H690" t="s">
-        <v>3373</v>
+        <v>3402</v>
       </c>
       <c r="I690" t="s">
         <v>403</v>
       </c>
       <c r="J690" t="s">
-        <v>3374</v>
+        <v>3403</v>
       </c>
       <c r="K690">
         <v>2014</v>
@@ -38978,19 +39897,19 @@
         <v>43</v>
       </c>
       <c r="B691" t="s">
-        <v>3375</v>
+        <v>3404</v>
       </c>
       <c r="G691" t="s">
-        <v>3376</v>
+        <v>3405</v>
       </c>
       <c r="H691" t="s">
-        <v>3377</v>
+        <v>3406</v>
       </c>
       <c r="I691" t="s">
         <v>2043</v>
       </c>
       <c r="J691" t="s">
-        <v>3378</v>
+        <v>3407</v>
       </c>
       <c r="K691">
         <v>2024</v>
@@ -39002,19 +39921,19 @@
         <v>43</v>
       </c>
       <c r="B692" t="s">
-        <v>3379</v>
+        <v>3408</v>
       </c>
       <c r="G692" t="s">
-        <v>3380</v>
+        <v>3409</v>
       </c>
       <c r="H692" t="s">
-        <v>3381</v>
+        <v>3410</v>
       </c>
       <c r="I692" t="s">
-        <v>3382</v>
+        <v>3411</v>
       </c>
       <c r="J692" t="s">
-        <v>3383</v>
+        <v>3412</v>
       </c>
       <c r="K692">
         <v>2023</v>
@@ -39026,19 +39945,19 @@
         <v>43</v>
       </c>
       <c r="B693" t="s">
-        <v>3384</v>
+        <v>3413</v>
       </c>
       <c r="G693" t="s">
-        <v>3385</v>
+        <v>3414</v>
       </c>
       <c r="H693" t="s">
-        <v>3386</v>
+        <v>3415</v>
       </c>
       <c r="I693" t="s">
         <v>237</v>
       </c>
       <c r="J693" t="s">
-        <v>3387</v>
+        <v>3416</v>
       </c>
       <c r="K693">
         <v>2026</v>
@@ -39050,19 +39969,19 @@
         <v>43</v>
       </c>
       <c r="B694" t="s">
-        <v>3388</v>
+        <v>3417</v>
       </c>
       <c r="G694" t="s">
-        <v>3389</v>
+        <v>3418</v>
       </c>
       <c r="H694" t="s">
-        <v>3390</v>
+        <v>3419</v>
       </c>
       <c r="I694" t="s">
         <v>973</v>
       </c>
       <c r="J694" t="s">
-        <v>3391</v>
+        <v>3420</v>
       </c>
       <c r="K694">
         <v>2025</v>
@@ -39074,19 +39993,19 @@
         <v>43</v>
       </c>
       <c r="B695" t="s">
-        <v>3392</v>
+        <v>3421</v>
       </c>
       <c r="G695" t="s">
-        <v>3393</v>
+        <v>3422</v>
       </c>
       <c r="H695" t="s">
-        <v>3394</v>
+        <v>3423</v>
       </c>
       <c r="I695" t="s">
         <v>1929</v>
       </c>
       <c r="J695" t="s">
-        <v>3395</v>
+        <v>3424</v>
       </c>
       <c r="K695">
         <v>2020</v>
@@ -39098,19 +40017,19 @@
         <v>43</v>
       </c>
       <c r="B696" t="s">
-        <v>3396</v>
+        <v>3425</v>
       </c>
       <c r="G696" t="s">
-        <v>3397</v>
+        <v>3426</v>
       </c>
       <c r="H696" t="s">
-        <v>3398</v>
+        <v>3427</v>
       </c>
       <c r="I696" t="s">
         <v>973</v>
       </c>
       <c r="J696" t="s">
-        <v>3399</v>
+        <v>3428</v>
       </c>
       <c r="K696">
         <v>2024</v>
@@ -39122,19 +40041,19 @@
         <v>43</v>
       </c>
       <c r="B697" t="s">
-        <v>3400</v>
+        <v>3429</v>
       </c>
       <c r="G697" t="s">
-        <v>3401</v>
+        <v>3430</v>
       </c>
       <c r="H697" t="s">
-        <v>3402</v>
+        <v>3431</v>
       </c>
       <c r="I697" t="s">
         <v>1461</v>
       </c>
       <c r="J697" t="s">
-        <v>3403</v>
+        <v>3432</v>
       </c>
       <c r="K697">
         <v>2023</v>
@@ -39146,19 +40065,19 @@
         <v>43</v>
       </c>
       <c r="B698" t="s">
-        <v>3404</v>
+        <v>3433</v>
       </c>
       <c r="G698" t="s">
-        <v>3405</v>
+        <v>3434</v>
       </c>
       <c r="H698" t="s">
-        <v>3406</v>
+        <v>3435</v>
       </c>
       <c r="I698" t="s">
         <v>723</v>
       </c>
       <c r="J698" t="s">
-        <v>3407</v>
+        <v>3436</v>
       </c>
       <c r="K698">
         <v>2022</v>
@@ -39170,19 +40089,19 @@
         <v>43</v>
       </c>
       <c r="B699" t="s">
-        <v>3408</v>
+        <v>3437</v>
       </c>
       <c r="G699" t="s">
-        <v>3409</v>
+        <v>3438</v>
       </c>
       <c r="H699" t="s">
-        <v>3410</v>
+        <v>3439</v>
       </c>
       <c r="I699" t="s">
-        <v>3288</v>
+        <v>3317</v>
       </c>
       <c r="J699" t="s">
-        <v>3411</v>
+        <v>3440</v>
       </c>
       <c r="K699">
         <v>2017</v>
@@ -39194,19 +40113,19 @@
         <v>43</v>
       </c>
       <c r="B700" t="s">
-        <v>3412</v>
+        <v>3441</v>
       </c>
       <c r="G700" t="s">
-        <v>3413</v>
+        <v>3442</v>
       </c>
       <c r="H700" t="s">
-        <v>3414</v>
+        <v>3443</v>
       </c>
       <c r="I700" t="s">
         <v>915</v>
       </c>
       <c r="J700" t="s">
-        <v>3415</v>
+        <v>3444</v>
       </c>
       <c r="K700">
         <v>2024</v>
@@ -39218,19 +40137,19 @@
         <v>43</v>
       </c>
       <c r="B701" t="s">
-        <v>3416</v>
+        <v>3445</v>
       </c>
       <c r="G701" t="s">
-        <v>3417</v>
+        <v>3446</v>
       </c>
       <c r="H701" t="s">
-        <v>3418</v>
+        <v>3447</v>
       </c>
       <c r="I701" t="s">
-        <v>3419</v>
+        <v>3448</v>
       </c>
       <c r="J701" t="s">
-        <v>3420</v>
+        <v>3449</v>
       </c>
       <c r="K701">
         <v>2026</v>
@@ -39242,19 +40161,19 @@
         <v>43</v>
       </c>
       <c r="B702" t="s">
-        <v>3421</v>
+        <v>3450</v>
       </c>
       <c r="G702" t="s">
-        <v>3422</v>
+        <v>3451</v>
       </c>
       <c r="H702" t="s">
-        <v>3423</v>
+        <v>3452</v>
       </c>
       <c r="I702" t="s">
         <v>915</v>
       </c>
       <c r="J702" t="s">
-        <v>3424</v>
+        <v>3453</v>
       </c>
       <c r="K702">
         <v>2007</v>
@@ -39266,19 +40185,19 @@
         <v>43</v>
       </c>
       <c r="B703" t="s">
-        <v>3425</v>
+        <v>3454</v>
       </c>
       <c r="G703" t="s">
-        <v>3426</v>
+        <v>3455</v>
       </c>
       <c r="H703" t="s">
-        <v>3427</v>
+        <v>3456</v>
       </c>
       <c r="I703" t="s">
-        <v>3428</v>
+        <v>3457</v>
       </c>
       <c r="J703" t="s">
-        <v>3429</v>
+        <v>3458</v>
       </c>
       <c r="K703">
         <v>2013</v>
@@ -39290,19 +40209,19 @@
         <v>43</v>
       </c>
       <c r="B704" t="s">
-        <v>3430</v>
+        <v>3459</v>
       </c>
       <c r="G704" t="s">
-        <v>3431</v>
+        <v>3460</v>
       </c>
       <c r="H704" t="s">
-        <v>3432</v>
+        <v>3461</v>
       </c>
       <c r="I704" t="s">
         <v>51</v>
       </c>
       <c r="J704" t="s">
-        <v>3433</v>
+        <v>3462</v>
       </c>
       <c r="K704">
         <v>2001</v>

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="g:\My Drive\UCL\BSMA\BSMA ANTIGRAVITY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530354F1-1D02-476A-B8E8-CD406977BD33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F2AE90-5D7B-4F01-AE7E-66F723FD9362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5530" uniqueCount="3611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="3647">
   <si>
     <t>Coder Initials</t>
   </si>
@@ -6872,7 +6872,7 @@
     <t>MIA At-Twaijri, JR Montanari</t>
   </si>
   <si>
-    <t>Old scanned PDF, unable to extract text. Assumed no extractable effect size.. Verbatim Evidence: "Manual Override"</t>
+    <t>Individual employee sample (purchasing agents) measuring boundary-spanning activities using Jemison's 25-item scale with extractable zero-order correlations.. Verbatim Evidence: "[Participants] "The sample consisted of 133 (41% usable response rate) purchasing agents from electronics firms in the southwest United States." [Measures] "Finally, boundary-spanning activities were assessed using Jemison's 25-item scale based on his formulation.""</t>
   </si>
   <si>
     <t>BSMA0420</t>
@@ -7114,6 +7114,9 @@
   </si>
   <si>
     <t>N Bennett</t>
+  </si>
+  <si>
+    <t>Unit of analysis is the organization/HR department, not individual employee BSB.. Verbatim Evidence: "[Sample] "data for this analysis were collected from &amp; sample of Atlanta area worksites with at least 250 employees" [Sample] "Once the sample had been selected and confirmed, companies were contacted and interviews scheduled with the highest level human resource person at that site." [Chapter I] "The important difference between a focus on boundary spanning units and jobs is a level of analysis and has bcaring on thc choice of dependent variables:""</t>
   </si>
   <si>
     <t>BSMA0435</t>
@@ -7303,6 +7306,9 @@
     <t>Olorunsola, Victor Oluwafemi; Saydam, Mehmet Bahri; Ogunmokun, Oluwatobi A.; Ozturen, Ali</t>
   </si>
   <si>
+    <t>Study measures individual-level customer-oriented boundary-spanning behavior (COBSB) using Bettencourt's scale in a sample of 355 frontline bank employees, and provides quantitative effect sizes.. Verbatim Evidence: "[Methodology and analysis] "Data were obtained from FBE of private banks in Nigeria in the summer of 2020." [Methodology and analysis] "A total of 355 completed surveys were obtained from the data collection process." [Methodology and analysis] "COBSB was measured using nine items in our study (Time 2). These components have been adopted from Bettencourt et al. (2005).""</t>
+  </si>
+  <si>
     <t>BSMA0446</t>
   </si>
   <si>
@@ -7315,6 +7321,9 @@
     <t>Onishi, Mami</t>
   </si>
   <si>
+    <t>Included based on Rule 16 (Leader BSB rated by subordinates) with zero-order correlation provided.. Verbatim Evidence: "[Methodology] "We designed the NMBS to assess staff perceptions of their nurse managers’ behaviour because it has the advantage of greater objectivity than self-assessment." [NMBS reliability and validity] "In addition, to examine whether the NMBS is a useful indicator of nursing management, we recruited 166 nurses at an acute-care hospital as another sample. They were asked to respond to the NMBS and an additional item evaluating their nurse manager as a unit leader: ‘The nurse manager is a good leader for nurses in this unit’." [Results] "Table 3 Correlation between Nurse Managers Boundary Spanning Scale (NMBS) score and nurses’ evaluations of their nurse manager""</t>
+  </si>
+  <si>
     <t>BSMA0447</t>
   </si>
   <si>
@@ -7325,6 +7334,9 @@
   </si>
   <si>
     <t>Onyemah, Vincent; Rouziès, Dominique; Panagopoulos, Nikolaos G.</t>
+  </si>
+  <si>
+    <t>The study measures boundary spanning (focus on the customer/supervisor) simply by the percentage of time devoted, violating the requirement for purposive boundary-spanning action (Rule 18).. Verbatim Evidence: "[Dependent variables: salesperson behavioural strategies and satisfaction] "The three facets of behavioural strategies (i.e., focus on the supervisor, the customer and the administrative aspects of the job) were each measured by the percentage of time the salesperson devotes to supervisors, customers and administrative tasks respectively.""</t>
   </si>
   <si>
     <t>BSMA0448</t>
@@ -7373,6 +7385,9 @@
     <t>Packell, Kathryn M</t>
   </si>
   <si>
+    <t>Examines work-nonwork (work-life) boundary management rather than inter- or intra-organizational boundary spanning.. Verbatim Evidence: "[ABSTRACT] In an effort to balance competing work and personal demands, recent research suggests that individuals put forth effort to control the implicit or explicit boundaries around their work and nonwork domains by either segmenting domains from one another or integrating them. [CHAPTER 3] More specifically, I seek to understand through my study how individuals prevent their work domain from encroaching upon the personal domain that encapsulates all their other nonwork (personal) roles."</t>
+  </si>
+  <si>
     <t>BSMA0449</t>
   </si>
   <si>
@@ -7385,6 +7400,9 @@
     <t>Pappas, James M.; Flaherty, Karen E.</t>
   </si>
   <si>
+    <t>Measures strategic activities instead of boundary spanning behavior. Verbatim Evidence: "[Measures] "Supervisors also reported on salesperson performance using the Sujan et al. (1994) six-item measure and salesperson participation in strategic activities using the Floyd and Wooldridge (1992) twenty-item measure. We adopt Floyd and Wooldridge's (1992, 2000 ) conceptualization that middle managers engage in four primary activities: championing newideas, synthesizing information, facilitating adaptability, andimplementing. We conceptualize strategic activity as a higherorder construct including the four first order constructsdescribed by Floyd and Wooldridge (2000)""</t>
+  </si>
+  <si>
     <t>BSMA0450</t>
   </si>
   <si>
@@ -7397,6 +7415,9 @@
     <t>Pappas, James M.; Wooldridge, Bill</t>
   </si>
   <si>
+    <t>The study does not measure Boundary Spanning Behavior (BSB). The 'boundary-spanning' variable is a binary dummy based on formal departmental roles rather than interpersonal behavior. Additionally, the network centrality measures assess pure communication frequency without purposive boundary-spanning action, violating Rule 18.. Verbatim Evidence: "[Measures] "Thus, our measure of boundary-spanning was based on functional descriptions of sub-units and formal organizational roles." [Measures] "To classify respondents as having positions with boundary-spanning or non-boundary-spanning responsibilities, we closely followed procedures utilized by Floyd and Wooldridge (1997). First, consistent with Thompson (1967), the following functions were classified as boundary-spanning: direct patient care, marketing, human resource management, purchasing. Non-boundary-spanning positions included MIS, accounting, finance, and utilization review." [Measures] "In total, 34 mid-level managers were classified as boundary-spanners and 55 were coded non-boundary-spanners." [Measures] "To measure network centrality respondents were asked to review an alphabetical roster of fellow employees and place checks next to the names of those individuals to whom they frequently (i.e. many times daily) communicate.""</t>
+  </si>
+  <si>
     <t>BSMA0451</t>
   </si>
   <si>
@@ -7424,6 +7445,9 @@
     <t>Pattinson, Steven; Dawson, Patrick</t>
   </si>
   <si>
+    <t>Qualitative study without effect sizes. Verbatim Evidence: "[Research design] "Thisstudydrawsondatafromqualitativefieldwork,al-lowing an in-depth exploration of the phenomenon of interest. Semi-structured interviews provided the flexi-bility to gather rich data essential to answering our re-search question." [Data collection and sample] "We conducted 23 in-depth interviews with a range of individuals in the seven companies""</t>
+  </si>
+  <si>
     <t>BSMA0453</t>
   </si>
   <si>
@@ -7439,6 +7463,9 @@
     <t>Pavez, Ignacio; Feyerherm, Ann; Valenzuela, Francisco; Zandee, Danielle</t>
   </si>
   <si>
+    <t>Editorial for a special issue (non-primary study). Verbatim Evidence: "[Introduction] "To place the papers included in this special issue in context, we first describe the basic concepts and approaches that constitute IOC as a field of study. Then, we examine how the papers that comprise this edition contribute to the IOC knowledge base. We conclude the editorial by discussing how current debates in the field have given precedence to a more normative framing of collaborative action.""</t>
+  </si>
+  <si>
     <t>BSMA0454</t>
   </si>
   <si>
@@ -7451,6 +7478,9 @@
     <t>Pedersen, Torben; Soda, Giuseppe; Stea, Diego</t>
   </si>
   <si>
+    <t>Included. The study measures individual-level intra-organizational boundary spanning behavior (advice-seeking ties across geographical, hierarchical, and intra-functional boundaries) among 275 employees in a global company, and provides a zero-order correlation matrix.. Verbatim Evidence: "[Methods] "We tested our theory in the Supply Chain function of a global company, which we will label “BigEye” for anonymity reasons." [Methods] "After the data cleaning procedure and imputation of a few missing values (where we had holes in an otherwise complete data string) we were able to use data on 275 employees in all our analyses, representing 58 percent of all employees in Supply Chain at the time of the survey." [Methods] "Boundary spanning network. We asked each respondent to identify those colleagues “to whom you turn to seek advice on work-related issues”... based on the adjacency matrix, we constructed three additional matrices depicting whether each possible dyad was spanning across geographical, hierarchical, and intra-functional boundaries." [Analysis and results] "The correlation matrix for all variables including mean values, standard deviation, minimum and maximum values are shown in Table 1.""</t>
+  </si>
+  <si>
     <t>BSMA0455</t>
   </si>
   <si>
@@ -7478,6 +7508,9 @@
     <t>Perrone, Vincenzo; Zaheer, Akbar; McEvily, Bill</t>
   </si>
   <si>
+    <t>The study does not measure boundary spanning behavior. It focuses on role autonomy, clan culture, and trust in boundary spanners. It also includes communication frequency which violates Rule 18.. Verbatim Evidence: "[Abstract] We present a view of trust in boundary spanners as explained by the extent of role autonomy, a multidimensional concept that reflects the discretion that agents have in interpreting and enacting their roles. We argue that, in a buyer-supplier context, purchasing managers will be trusted to a greater extent by supplier representatives when they are free from constraints that limit their ability to interpret their boundary-spanning roles. We conceptualize and measure three key components of role autonomy: Functional influence, tenure, and clan culture. [Table 1] Frequency of communication. On average, about how often did you use the following to communicate with your contact person during the past year? 1. Telephone 2. Fax 3. Scheduled meetings 4. Unscheduled meetings 5. E-mail"</t>
+  </si>
+  <si>
     <t>BSMA0457</t>
   </si>
   <si>
@@ -7520,6 +7553,9 @@
     <t>PJ Robertson</t>
   </si>
   <si>
+    <t>Boundary spanning is used solely as a sample-splitting moderator (Spanners vs. Nonspanners) and correlations are calculated only against regression residuals ('relationship strength index'), lacking substantive zero-order correlations.. Verbatim Evidence: "[Analyses] Two types of multiple regression analyses were used to assess hypothesis 1, that the relationship between work setting and behavior would be weaker among boundary spanners. In the first, work behavior was regressed on managerial behavior, job design, and goal effectiveness, with separate regressions for boundary spanners and for nonspanners. [Relationship strength] To assess the strength of the relationship between work setting and behavior, work behavior was regressed on managerial behavior, job design, and goal effectiveness. For each respondent, the absolute value of the residual from this regression is a measure of how well behavior is predicted by the three work-setting variables, and thus provides an index for relationship strength. ... Since a larger regression residual indicates a weaker relationship between work setting and behavior, positive correlations between the boundary activity measures and the relationship strength index would support the hypotheses regarding a negative association between boundary-spanning activity and the strength of the relationship. [Results] First, there is a significant correlation between relationship strength and the total amount of boundary activity in which an individual engages (r = .27, p &lt; .01), indicating that the work-setting variables predict behavior less accurately as the total amount of boundary activity increases."</t>
+  </si>
+  <si>
     <t>BSMA0460</t>
   </si>
   <si>
@@ -7529,6 +7565,9 @@
     <t>The relationship between work setting and behavior and the moderating effects of boundary spanning activity</t>
   </si>
   <si>
+    <t>Boundary spanning used solely as a moderator to split sample and continuous BSB measures are only correlated with regression residuals.. Verbatim Evidence: "[Results] "To explore the effect of involvement in boundary activity, two general types of analyses were performed. The first type examined the relationships between the variables for two subsets of the sample. Specifically, non-spanners were compared to spanners, with the two groups defined in terms of whether or not the respondent reported any involvement in boundary activity. The second type of analysis incorporated boundary activity as a continuous variable, rather than as a dichotomous variable, utilizing measures of the amount of boundary activity." [Results] "First, for each individual, the absolute value of the residual from the regression of the Workstyle behaviors on the work setting variables m ust be determined. The size of these residuals reflects the accuracy with which behavior can be predicted from characteristics of the work setting. The second step, therefore, is to correlate the absolute value of the residuals19 with the am ount of boundary activity.""</t>
+  </si>
+  <si>
     <t>BSMA0461</t>
   </si>
   <si>
@@ -7541,6 +7580,9 @@
     <t>Powell, Walter W; Koput, Kenneth W; Smith-Doerr, Laurel</t>
   </si>
   <si>
+    <t>Firm-level analysis of interorganizational alliances and networks. Verbatim Evidence: "[Method] "We built a relational database that contains separate files for (1) DBFs in human therapeutics and diagnostics, (2} the formal contractual, interorganizational agreements involving DBFs, and (3) the partners to these agreements. The information gathered for each DBF includes founding date, employment levels, sources of financing, and collaborative agreements, which we treated as ties.""</t>
+  </si>
+  <si>
     <t>BSMA0462</t>
   </si>
   <si>
@@ -7556,6 +7598,9 @@
     <t>Pramanik, Roshni</t>
   </si>
   <si>
+    <t>No extractable zero-order correlation matrix or quantitative effect size (r). Experimental study using non-parametric Wilcoxon tests.. Verbatim Evidence: "[Abstract] "Through design of experiments, using tabletop exercises and online surveys, this study investigates the drivers of collaboration during a crisis scenario." [3.5 Results from Doe] "Table 2 presents the p values, the signed ranks or W values from the Wilcoxon signed rank tests and the measures of A12 values from the paired tests." [4.2 The effect of ECFI on EOC] "Spearman analyses between EOC and willingness to contribute were carried out in the study, which revealed an absence of a perfect correlation between the two.""</t>
+  </si>
+  <si>
     <t>BSMA0463</t>
   </si>
   <si>
@@ -7583,6 +7628,9 @@
     <t>Purcell, Jennifer W.; Smith, Deborah N.</t>
   </si>
   <si>
+    <t>Conceptual paper discussing disciplinary expertise and faculty credentialing.. Verbatim Evidence: "[Abstract] The current article presents a conceptualization of how disciplinary expertise and faculty credentialing may shape the future of leadership studies."</t>
+  </si>
+  <si>
     <t>BSMA0465</t>
   </si>
   <si>
@@ -7661,6 +7709,9 @@
     <t>R Katz</t>
   </si>
   <si>
+    <t>Old scanned PDF, unable to extract text. Assumed no extractable effect size.. Verbatim Evidence: "Manual Override"</t>
+  </si>
+  <si>
     <t>BSMA0471</t>
   </si>
   <si>
@@ -7673,6 +7724,9 @@
     <t>R. Morgan, Tyler; Rapp, Adam; Glenn Richey, Jr., R.; E. Ellinger, Alexander</t>
   </si>
   <si>
+    <t>Measures flexibility/adaptive selling (ADAPTS scale) rather than Boundary Spanning Behavior.. Verbatim Evidence: "[Measures] "Boundary-spanning employee ﬂexibility was assessed using four items based on Spiro and Weitz’s (1990) ADAPTS scale. Spiro and Weitz’s study emphasized the importance of boundary-spanning employee ﬂexibility on their performance, and the items used from the scale measure employee ﬂexibility.""</t>
+  </si>
+  <si>
     <t>BSMA0472</t>
   </si>
   <si>
@@ -7688,6 +7742,9 @@
     <t>Rajeswari, K. S.; Anantharaman, R. N.</t>
   </si>
   <si>
+    <t>No effect size of interest. The study mentions boundary-spanning as a job characteristic in the introduction but does not measure Boundary Spanning Behavior (BSB). It only correlates occupational stress, work exhaustion, and human-computer interaction variables.. Verbatim Evidence: "[Abstract] "Software professionals perform boundary-spanning activities, and thus need strong in- terpersonal, technical, and organizational knowledge to be professionally competent." [4. HYPOTHESES] "The following hypotheses were framed to examine the moderating role of HCI variables in the relationship between occupational stress and work exhaustion: H1a. Stress is negatively associated with all HCI variables." [8.2. Descriptives and Correlation Analysis] "Table 3: Relationship Between Occupational Stress, Work Exhaustion, and Human-Computer Interaction Variables""</t>
+  </si>
+  <si>
     <t>BSMA0473</t>
   </si>
   <si>
@@ -7700,6 +7757,9 @@
     <t>Ramarajan, Lakshmi; Bezrukova, Katerina; Jehn, Karen A.; Euwema, Martin</t>
   </si>
   <si>
+    <t>Excluded because the independent variable measures mere frequency of contact with external organizations without specifying any purposive boundary-spanning action.. Verbatim Evidence: "[Measures] "Participants responded to the question, 'What parties did you have contact with? Please indicate the frequency of these contacts for your job.' Three choices of parties were listed under this question, 'Contact with NGOs (for example The Red Cross); Contact with local (or regional) authorities; Contact with Governmental Organizations (e.g., UNHCR).' Frequency of contact was measured on a five-point Likert scale (1 = hardly ever; 5 = daily) for each item""</t>
+  </si>
+  <si>
     <t>BSMA0474</t>
   </si>
   <si>
@@ -7736,6 +7796,9 @@
     <t>Reiche, B. Sebastian</t>
   </si>
   <si>
+    <t>Valid individual-level boundary spanning behavior by implanted boundary spanners (inpatriates) with zero-order effect sizes available.. Verbatim Evidence: "[Sample and Procedure] "To test the hypothesized relationships, an online survey was sent to a sample of 643 inpatriates at the HQs of 10 German MNCs." [Measures] "Inpatriates' Boundary Spanning. No measure of inpatriates' boundary spanning existed that appropriately reflected the brokering of social ties between the home unit and the HQ, so I developed a new scale." [APPENDIX] "Items of Inpatriates' Boundary Spanning Scale: (1) I am willing to share my personal contacts at my home unit with HQ staff. (2) It is important for me to establish close working relationships with as many local employees at the HQ as possible." [TABLE II] "Note: N = 269.""</t>
+  </si>
+  <si>
     <t>BSMA0477</t>
   </si>
   <si>
@@ -7748,6 +7811,9 @@
     <t>RH Miles</t>
   </si>
   <si>
+    <t>Study provides zero-order correlations between intra/inter-organizational boundary-spanning activities and role stress among individual R&amp;D professionals.. Verbatim Evidence: "[Research Site and Sample] "Of the 210 professionals asked to volunteer for participation in this study, 96% completed usable questionnaires. These participants represented five major organizational roles: integrator (w = 2S), division manager (= 43), technical group leader (n  38), nonsupervisory basic scientists and engineers (n = 30), and nonsupervisory applied scientists and engineers (--63). The job classification of \"inte-grator\" in this study includes both boundary role persons (Adams, in press) and intraorganizational integrators (Lawrence &amp; Lorsch, 1969)." [Development and Validation oj Role Requirement Measiires] "Factor II: Integration and boundary-spanning activities 1. Represent your directorate/laboratory to outsiders. 2. Review plans with agencies outside the laboratory. 3. Travel at least 30 days per year as a representative of your organization 4. Inspect or review projects under contract. 5. Integrate or coordinate interdependent activities of others." [Role Requirements and Role Conflict] "A correlational analysis of relationships between the role stress and role requirement variables provides support for the hypotheses (see Table 4). Both general role conflict and intersender conflict were directly related to the role requirement measure of integration and boundary-spanning activities.""</t>
+  </si>
+  <si>
     <t>BSMA0478</t>
   </si>
   <si>
@@ -7760,6 +7826,9 @@
     <t>Richter, Andreas W.; West, Michael A.; Van Dick, Rolf; Dawson, Jeremy F.</t>
   </si>
   <si>
+    <t>The study does not measure boundary spanning behavior (BSB). It measures boundary spanners' group/organizational identification and intergroup contact frequency. Intergroup contact is measured purely as interaction frequency, which is excluded under Rule 18.. Verbatim Evidence: "[Abstract] "We examined the relationship between group boundary spanners' work group identification and effective (i.e., harmonious and productive) intergroup relations in 53 workgroups in five health care organizations." [Measures] "The amount of such contact was determined from responses to a question adapted from van de Ven and Ferry (1980): 'How frequently do you interact on work-related matters with members of [out-group's name]?' (1, 'not at all'; 7, 'daily')." [Measures] "Group and organizational identification were measured using Doosje and colleagues' four-item scale (Doosje, Ellemers, &amp; Spears, 1995)... A sample item is, 'I see myself as a member of [group X/organization X]' (1, 'strongly disagree'; 5, 'strongly agree').""</t>
+  </si>
+  <si>
     <t>BSMA0479</t>
   </si>
   <si>
@@ -7794,6 +7863,9 @@
   </si>
   <si>
     <t>Rigg, Clare; O'Mahony, Noreen</t>
+  </si>
+  <si>
+    <t>Qualitative action research study lacking quantitative effect sizes.. Verbatim Evidence: "[Abstract] "Qualitative evidence from an action research study is used to address the research question ‘how can institutional context help explain frustrations within local collaborations?’" [THE STUDY] "The action research study on which this article is based was conducted by one of the authors as a participant within the economic strategy panel of one of the CDB organizations... An ethnographic approach dominated (Gray, 2009), in which much of the research material collected consisted of extensive observational notes and quotes recorded verbatim in the course of regular ESP and sub-group meetings""</t>
   </si>
   <si>
     <t>BSMA0482</t>
@@ -19316,6 +19388,780 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> partners being foreign firms. The companies in the sample have, on average) applied for about 8 nano -tech related patents (mean 7.5) over the observation period""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Firm-level analysis of outsourcing and subcontracting in small high-tech firms, not individual-level boundary spanning behavior.. Verbatim Evidence: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-level analysis of outsourcing and subcontracting in small high-tech firms. Verbatim Evidence: "[4.1 Data set and measures] A total of 579 cases with a combined response rate of 13.3 per cent were collected aspart of the study. Although the response rate is relatively low, it is consistent withsimilar studies in the operations management literature (Song and Benedetto, 2008;Rosenzweig et al. , 2003; Swink et al. , 2006). Median age of the ﬁrms in the sample was 24 and median size of the ﬁrm was 41 employees." "[4.1 Data set and measures] We measured radical innovativeness using the count data of the number of patent applications with respect to radical products, services and processes developed by thebusiness" "[4.1 Data set and measures] The extent of subcontracting-in was measured as work carried out on a subcontract basis for other ﬁrms as percent of total sales. Similarly, the extent of outsourcing was measured as work undertaken by the other ﬁrms for the business on a subcontract basis as a percent of total sales.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Qualitative case study lacking quantitative effect sizes. Verbatim Evidence: "[Study approach] "In this case study, data was collected by the following steps, First, to understand the entire corporate information system environment, we referred to the enterprise information system planning reports that include overall specifications of hardware, software, human resources, and business processes, and gathered information on how the case </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> started and managed their customer relationship management activities. Then we conducted several in-depth interviews with senior managers of the marketing, customer service, and information system divisions." [Relationship value analysis and positioning] "We can analyze the relationship value of the two different customer relationships only qualitatively since Maeil Corp. lacks transactional data about customers and there are no formal channels for monitoring their customer value (see Table III).""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Qualitative interview study without quantitative effect sizes.. Verbatim Evidence: "[Abstract] Through the lens of boundary work, this study explores how (n=33) self-identifying rural journalists navigated this gray area and walked the line between creating authentic journalistic content and publishing public relations content. [Method] Each participant was interviewed individually (n=33) by a member of the research </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. ... Researchers transcribed the interviews and used textual analysis on the transcripts."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Measures Boundary Spanning Capabilities (traits/knowledge/skills) rather than purposive Boundary Spanning Behavior.. Verbatim Evidence: "[Measures] "Buyer agents’ BSC measures were adapted from Zhang et al. (2011). Professional purchasing knowl­ edge was measured with four items indicating the extent to which a buyer agent has knowledge about products, suppliers’ capability, competitors, and the market. Compromise ability was measured with three items indicating buyer agents’ ability to reach equita­ ble solutions for both sides, considering suppliers’ interests. The three items of strategic communication capability measured a buyer agent’s effectiveness in conveying their </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">’s purchasing plans and strategies to the supplier </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and explaining the buyer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">’s suggestions regarding the programme/contract or agreements to the supplier </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sample items were ‘I have knowledge about the supplier </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">’s capabilities (e.g. quality, timely delivery, safety standards)’, ‘I gen­ erally strive to reach solutions that are equitable to both the supplier </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when differences arise’, and ‘I am effective at explaining my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">’s pur­ chasing strategy to the supplier </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>’.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Qualitative participatory action research study without quantitative effect sizes. Verbatim Evidence: "[Abstract] "This participatory action research study brought together a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of employees within a remote-work, start-up organization to define and design a process for implementing wellness at work for their organization.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Student sample. Verbatim Evidence: "[5.1. Sample] "The sample consisted of 148 undergraduate, 30 graduate and 42 MBA </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>students</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> at universities in the Netherlands, United States and France, respectively (17 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>students</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> were excluded earlier due to missing values, 2 because they reported different negotiation outcomes). All </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>students</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> enrolled in supply management courses.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The study measures interdepartmental connectedness (ease of communication) and role capability locus rather than purposive interpersonal boundary-spanning behaviors.. Verbatim Evidence: "[Measures] The internal boundary-spanning activities capture marketing managers’ efforts of sharing market intelligence and interacting with organisational members from different functional departments. We adapted Jaworski and Kohli (1993)’s scale on interdepartmental connectedness to measure cross-functional market intelligence exchange. The following is a sample item: ‘I find communication between the marketing department and other departments easy’. The external boundary-spanning activities capture marketing managers’ effort of accommodating customers’ needs. ... We derived a three-item scale to measure customer accommodation from Moorman and Rust (1999)’s study. The following is a sample item: ‘The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>’s ability to translate customer needs into technical specifications for new products /services resides in me’."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Study measures Leader Boundary-Spanning Behavior at the individual level (self-rated by team leaders; 1 leader per team, N=83). It contains a valid quantitative correlation matrix for employee participants.. Verbatim Evidence: "[Sample] We collected data from new product development (NPD) teams in 10 high-tech companies in Shaanxi and Henan provinces in China. ... we obtained a sample set consisting of 83 teams (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> leaders) and 305 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> members. [Measures] Leader comprehensive boundary-spanning strategy Following Ancona and Caldwell (1992), we used the self-evaluation method to ask </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> leaders to evaluate their level of boundary-spanning behaviors. Typical items concerning ambassadorial activities were: “To what extent did you persuade outsiders to support </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> decisions?” and “To what extent did you keep other groups in the company informed of your </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>’s activities?”"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Firm-level analysis with managers as key informants for the firm. Verbatim Evidence: "[Abstract] "Data was collected through a convenient sampling technique from 353 middle and senior managers of entrepreneurial enterprises in China through online and offline modes." [Appendix 1] "Organizational forgetting OF1. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> develops practical training and learning plans according to its own development needs" [Appendix 1] "Cross-boundary innovation CBI1. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>firm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> often introduces elements from different fields to improve the operating conditions of related businesses""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Work-life boundary management (Code 1) and MBA student sample (Code 2). Verbatim Evidence: "[Abstract] "WORK-LIFE BOUNDARY MANAGEMENT STRATEGY AND ITS RELATIONSHIP TO JOB ATTRACTION" [Abstract] "The purpose of this research study was to determine whether there was a statistically significant difference in applicant attraction to a job that offers a telecommuting work arrangement (TelWA) or a standard work arrangement (StdWA), depending on whether participants prefer an integration or segmentation boundary management strategy." [Abstract] "The data were collected from 144 part-time MBA </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>students</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from across the U.S., interested in pursuing professional job opportunities in business, through a Qualtrics, LLC. online survey panel.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Non-individual level. The unit of analysis is the cross-functional group/team. Individual responses were aggregated to the team level, and survey items measure team-level boundary spanning (e.g., 'does the group encourage its members').. Verbatim Evidence: "[Unit of Analysis] "My unit of analysis is the entrepreneurial group pursuing radical innovation initiatives , as previously discussed ." [INTERCLASS CORRELATIONS (ICC)] "Because our model focuses on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">/group level, we took a number of steps before aggregating individual responses to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> level." [Measures] "four boundary spanning items are (1) To what extent does the group encourage its members to try to influence important actors elsewhere in and/or beyond the group on behalf of the group and its work? and (2) To what extent does the group value group members for making use of their relationships with others on behalf of the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Team-level referent for boundary spanning behavior (respondents act as key informants rating their team). Verbatim Evidence: "[Sample] "Forty-four opportunities for data collection were taken and a total of 1103 useable inventories collected from participants across European, Asian and African locations. Teams reported on were predominantly work-related. ... Respondents supplied information from teams within their experience" [Survey Referent / Macro Construct] "Network activators </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> members are good at networking with key individuals outside formal organizational" "TF16 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> members had contacts outside the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> that were helpful" "TF17 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> members were good at mobilizing help from outside the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" "TF18 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> members were good networkers""</t>
     </r>
   </si>
 </sst>
@@ -20078,7 +20924,7 @@
         <v>2002</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>3463</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20174,7 +21020,7 @@
         <v>2016</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>3464</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20334,7 +21180,7 @@
         <v>2008</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>3465</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20366,7 +21212,7 @@
         <v>2012</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>3466</v>
+        <v>3490</v>
       </c>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20654,7 +21500,7 @@
         <v>1992</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>3467</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20782,7 +21628,7 @@
         <v>2024</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>3468</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20814,7 +21660,7 @@
         <v>2017</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>3469</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -20974,7 +21820,7 @@
         <v>2022</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>3470</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21099,7 +21945,7 @@
         <v>2020</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>3471</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21195,7 +22041,7 @@
         <v>1997</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>3472</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21259,7 +22105,7 @@
         <v>2021</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>3473</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21663,7 +22509,7 @@
         <v>2018</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>3474</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21692,7 +22538,7 @@
         <v>2015</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>3475</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21878,7 +22724,7 @@
         <v>2011</v>
       </c>
       <c r="P61" s="8" t="s">
-        <v>3476</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22131,7 +22977,7 @@
         <v>2012</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>3477</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22384,7 +23230,7 @@
         <v>2025</v>
       </c>
       <c r="P77" s="8" t="s">
-        <v>3478</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22416,7 +23262,7 @@
         <v>2023</v>
       </c>
       <c r="P78" s="8" t="s">
-        <v>3479</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22448,7 +23294,7 @@
         <v>2019</v>
       </c>
       <c r="P79" s="8" t="s">
-        <v>3480</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22576,7 +23422,7 @@
         <v>2005</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>3481</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22608,7 +23454,7 @@
         <v>2020</v>
       </c>
       <c r="P84" s="8" t="s">
-        <v>3482</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22637,7 +23483,7 @@
         <v>2021</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>3483</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22829,7 +23675,7 @@
         <v>2010</v>
       </c>
       <c r="P91" s="8" t="s">
-        <v>3484</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22925,7 +23771,7 @@
         <v>2024</v>
       </c>
       <c r="P94" s="8" t="s">
-        <v>3485</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22957,7 +23803,7 @@
         <v>2020</v>
       </c>
       <c r="P95" s="8" t="s">
-        <v>3486</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23018,7 +23864,7 @@
         <v>2021</v>
       </c>
       <c r="P97" s="8" t="s">
-        <v>3487</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23047,7 +23893,7 @@
         <v>2012</v>
       </c>
       <c r="P98" s="8" t="s">
-        <v>3488</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23111,7 +23957,7 @@
         <v>1995</v>
       </c>
       <c r="P100" s="8" t="s">
-        <v>3489</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23143,7 +23989,7 @@
         <v>2008</v>
       </c>
       <c r="P101" s="8" t="s">
-        <v>3490</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23236,7 +24082,7 @@
         <v>2010</v>
       </c>
       <c r="P104" s="8" t="s">
-        <v>3491</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23460,7 +24306,7 @@
         <v>2018</v>
       </c>
       <c r="P111" s="8" t="s">
-        <v>3492</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23556,7 +24402,7 @@
         <v>2018</v>
       </c>
       <c r="P114" s="8" t="s">
-        <v>3493</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23684,7 +24530,7 @@
         <v>2016</v>
       </c>
       <c r="P118" s="8" t="s">
-        <v>3494</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23713,7 +24559,7 @@
         <v>1978</v>
       </c>
       <c r="P119" s="8" t="s">
-        <v>3495</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23777,7 +24623,7 @@
         <v>2012</v>
       </c>
       <c r="P121" s="8" t="s">
-        <v>3496</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23841,7 +24687,7 @@
         <v>2004</v>
       </c>
       <c r="P123" s="8" t="s">
-        <v>3497</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24088,7 +24934,7 @@
         <v>1996</v>
       </c>
       <c r="P131" s="8" t="s">
-        <v>3498</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24120,7 +24966,7 @@
         <v>2004</v>
       </c>
       <c r="P132" s="8" t="s">
-        <v>3499</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24184,7 +25030,7 @@
         <v>1990</v>
       </c>
       <c r="P134" s="8" t="s">
-        <v>3500</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="135" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24312,7 +25158,7 @@
         <v>1984</v>
       </c>
       <c r="P138" s="8" t="s">
-        <v>3501</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24536,7 +25382,7 @@
         <v>2011</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>3502</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24568,7 +25414,7 @@
         <v>2003</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>3503</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24728,7 +25574,7 @@
         <v>2014</v>
       </c>
       <c r="P151" s="8" t="s">
-        <v>3504</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24856,7 +25702,7 @@
         <v>2019</v>
       </c>
       <c r="P155" s="8" t="s">
-        <v>3505</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="156" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24920,7 +25766,7 @@
         <v>2009</v>
       </c>
       <c r="P157" s="8" t="s">
-        <v>3506</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24984,7 +25830,7 @@
         <v>2019</v>
       </c>
       <c r="P159" s="8" t="s">
-        <v>3507</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25333,7 +26179,7 @@
         <v>1998</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>3508</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25554,7 +26400,7 @@
         <v>2022</v>
       </c>
       <c r="P177" s="8" t="s">
-        <v>3509</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="178" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25618,7 +26464,7 @@
         <v>1997</v>
       </c>
       <c r="P179" s="8" t="s">
-        <v>3510</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="180" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25650,7 +26496,7 @@
         <v>2022</v>
       </c>
       <c r="P180" s="8" t="s">
-        <v>3511</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25842,7 +26688,7 @@
         <v>2023</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>3512</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25874,7 +26720,7 @@
         <v>2013</v>
       </c>
       <c r="P187" s="8" t="s">
-        <v>3513</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="188" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26063,7 +26909,7 @@
         <v>2010</v>
       </c>
       <c r="P193" s="8" t="s">
-        <v>3514</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="194" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26159,7 +27005,7 @@
         <v>2012</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>3515</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="197" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26188,7 +27034,7 @@
         <v>2015</v>
       </c>
       <c r="P197" s="8" t="s">
-        <v>3516</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="198" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26252,7 +27098,7 @@
         <v>2015</v>
       </c>
       <c r="P199" s="8" t="s">
-        <v>3517</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="200" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26412,7 +27258,7 @@
         <v>2005</v>
       </c>
       <c r="P204" s="8" t="s">
-        <v>3518</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26505,7 +27351,7 @@
         <v>1998</v>
       </c>
       <c r="P207" s="8" t="s">
-        <v>3519</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26537,7 +27383,7 @@
         <v>1999</v>
       </c>
       <c r="P208" s="8" t="s">
-        <v>3520</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="209" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26627,7 +27473,7 @@
         <v>2024</v>
       </c>
       <c r="P211" s="8" t="s">
-        <v>3521</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="212" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26659,7 +27505,7 @@
         <v>2006</v>
       </c>
       <c r="P212" s="8" t="s">
-        <v>3522</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="213" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26691,7 +27537,7 @@
         <v>2010</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>3523</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="214" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26752,7 +27598,7 @@
         <v>2017</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>3524</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="216" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26880,7 +27726,7 @@
         <v>2014</v>
       </c>
       <c r="P219" s="8" t="s">
-        <v>3525</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26912,7 +27758,7 @@
         <v>2011</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>3526</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="221" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27008,7 +27854,7 @@
         <v>2015</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>3527</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="224" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27072,7 +27918,7 @@
         <v>2023</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>3528</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27101,7 +27947,7 @@
         <v>2004</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>3529</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="227" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27197,7 +28043,7 @@
         <v>2005</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>3530</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="230" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27229,7 +28075,7 @@
         <v>2004</v>
       </c>
       <c r="P230" s="8" t="s">
-        <v>3531</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="231" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27325,7 +28171,7 @@
         <v>1998</v>
       </c>
       <c r="P233" s="8" t="s">
-        <v>3532</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="234" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27421,7 +28267,7 @@
         <v>2014</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>3533</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="237" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27642,7 +28488,7 @@
         <v>2011</v>
       </c>
       <c r="P243" s="8" t="s">
-        <v>3534</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27674,7 +28520,7 @@
         <v>2018</v>
       </c>
       <c r="P244" s="8" t="s">
-        <v>3535</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="245" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27706,7 +28552,7 @@
         <v>2019</v>
       </c>
       <c r="P245" s="8" t="s">
-        <v>3536</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="246" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27738,7 +28584,7 @@
         <v>1998</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>3537</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="247" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27892,7 +28738,7 @@
         <v>2012</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>3538</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="252" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28081,7 +28927,7 @@
         <v>1999</v>
       </c>
       <c r="P257" s="8" t="s">
-        <v>3539</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="258" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28145,7 +28991,7 @@
         <v>2022</v>
       </c>
       <c r="P259" s="8" t="s">
-        <v>3540</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28302,7 +29148,7 @@
         <v>2023</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>3541</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28363,7 +29209,7 @@
         <v>2023</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>3542</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="267" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28395,7 +29241,7 @@
         <v>2018</v>
       </c>
       <c r="P267" s="8" t="s">
-        <v>3543</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="268" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28427,7 +29273,7 @@
         <v>2025</v>
       </c>
       <c r="P268" s="8" t="s">
-        <v>3544</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="269" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28456,7 +29302,7 @@
         <v>2010</v>
       </c>
       <c r="P269" s="8" t="s">
-        <v>3545</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="270" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28546,7 +29392,7 @@
         <v>2002</v>
       </c>
       <c r="P272" s="8" t="s">
-        <v>3546</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28639,7 +29485,7 @@
         <v>2020</v>
       </c>
       <c r="P275" s="8" t="s">
-        <v>3547</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28767,7 +29613,7 @@
         <v>1996</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>3548</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28796,7 +29642,7 @@
         <v>2020</v>
       </c>
       <c r="P280" s="8" t="s">
-        <v>3549</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="281" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28828,7 +29674,7 @@
         <v>2003</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>3550</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28924,7 +29770,7 @@
         <v>2022</v>
       </c>
       <c r="P284" s="8" t="s">
-        <v>3551</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28956,7 +29802,7 @@
         <v>2000</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>3552</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29363,7 +30209,7 @@
         <v>2024</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>3553</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29517,7 +30363,7 @@
         <v>2011</v>
       </c>
       <c r="P303" s="8" t="s">
-        <v>3554</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29578,7 +30424,7 @@
         <v>2022</v>
       </c>
       <c r="P305" s="8" t="s">
-        <v>3555</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29636,7 +30482,7 @@
         <v>2022</v>
       </c>
       <c r="P307" s="8" t="s">
-        <v>3556</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29665,7 +30511,7 @@
         <v>2025</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>3557</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29694,7 +30540,7 @@
         <v>2002</v>
       </c>
       <c r="P309" s="8" t="s">
-        <v>3558</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30043,7 +30889,7 @@
         <v>2008</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>3559</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="321" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30171,7 +31017,7 @@
         <v>2020</v>
       </c>
       <c r="P324" s="8" t="s">
-        <v>3560</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30235,7 +31081,7 @@
         <v>2004</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>3561</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30299,7 +31145,7 @@
         <v>2015</v>
       </c>
       <c r="P328" s="8" t="s">
-        <v>3562</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30488,7 +31334,7 @@
         <v>1991</v>
       </c>
       <c r="P334" s="8" t="s">
-        <v>3563</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30520,7 +31366,7 @@
         <v>2023</v>
       </c>
       <c r="P335" s="8" t="s">
-        <v>3564</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30552,7 +31398,7 @@
         <v>2017</v>
       </c>
       <c r="P336" s="8" t="s">
-        <v>3565</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30674,7 +31520,7 @@
         <v>2011</v>
       </c>
       <c r="P340" s="8" t="s">
-        <v>3566</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="341" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30703,7 +31549,7 @@
         <v>2016</v>
       </c>
       <c r="P341" s="8" t="s">
-        <v>3567</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="342" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30735,7 +31581,7 @@
         <v>2020</v>
       </c>
       <c r="P342" s="8" t="s">
-        <v>3568</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30799,7 +31645,7 @@
         <v>2017</v>
       </c>
       <c r="P344" s="8" t="s">
-        <v>3569</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="345" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30831,7 +31677,7 @@
         <v>2024</v>
       </c>
       <c r="P345" s="8" t="s">
-        <v>3570</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="346" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30863,7 +31709,7 @@
         <v>2016</v>
       </c>
       <c r="P346" s="8" t="s">
-        <v>3571</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="347" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30895,7 +31741,7 @@
         <v>2022</v>
       </c>
       <c r="P347" s="8" t="s">
-        <v>3572</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="348" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31023,7 +31869,7 @@
         <v>2002</v>
       </c>
       <c r="P351" s="8" t="s">
-        <v>3573</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="352" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31052,7 +31898,7 @@
         <v>2022</v>
       </c>
       <c r="P352" s="8" t="s">
-        <v>3574</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="353" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31116,7 +31962,7 @@
         <v>2020</v>
       </c>
       <c r="P354" s="8" t="s">
-        <v>3575</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="355" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31148,7 +31994,7 @@
         <v>2024</v>
       </c>
       <c r="P355" s="8" t="s">
-        <v>3576</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="356" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31180,7 +32026,7 @@
         <v>2000</v>
       </c>
       <c r="P356" s="8" t="s">
-        <v>3577</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="357" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31276,7 +32122,7 @@
         <v>2023</v>
       </c>
       <c r="P359" s="8" t="s">
-        <v>3578</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="360" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31305,7 +32151,7 @@
         <v>2018</v>
       </c>
       <c r="P360" s="8" t="s">
-        <v>3579</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="361" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31334,7 +32180,7 @@
         <v>2014</v>
       </c>
       <c r="P361" s="8" t="s">
-        <v>3580</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="362" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31366,7 +32212,7 @@
         <v>2013</v>
       </c>
       <c r="P362" s="8" t="s">
-        <v>3581</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="363" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31398,7 +32244,7 @@
         <v>2025</v>
       </c>
       <c r="P363" s="8" t="s">
-        <v>3582</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="364" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31590,7 +32436,7 @@
         <v>2023</v>
       </c>
       <c r="P369" s="8" t="s">
-        <v>3583</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="370" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31686,7 +32532,7 @@
         <v>2023</v>
       </c>
       <c r="P372" s="8" t="s">
-        <v>3584</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="373" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31782,7 +32628,7 @@
         <v>1999</v>
       </c>
       <c r="P375" s="8" t="s">
-        <v>3585</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="376" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31846,7 +32692,7 @@
         <v>2023</v>
       </c>
       <c r="P377" s="8" t="s">
-        <v>3586</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="378" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32006,7 +32852,7 @@
         <v>2005</v>
       </c>
       <c r="P382" s="8" t="s">
-        <v>3587</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="383" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32038,7 +32884,7 @@
         <v>2007</v>
       </c>
       <c r="P383" s="8" t="s">
-        <v>3588</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="384" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32070,7 +32916,7 @@
         <v>2008</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>3589</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="385" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32192,7 +33038,7 @@
         <v>2019</v>
       </c>
       <c r="P388" s="8" t="s">
-        <v>3590</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="389" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32224,7 +33070,7 @@
         <v>1994</v>
       </c>
       <c r="P389" s="8" t="s">
-        <v>3591</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="390" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32288,7 +33134,7 @@
         <v>2016</v>
       </c>
       <c r="P391" s="8" t="s">
-        <v>3592</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="392" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32320,7 +33166,7 @@
         <v>2015</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>3593</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="393" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32445,7 +33291,7 @@
         <v>2003</v>
       </c>
       <c r="P396" s="8" t="s">
-        <v>3594</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="397" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32541,7 +33387,7 @@
         <v>2005</v>
       </c>
       <c r="P399" s="8" t="s">
-        <v>3595</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="400" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32573,7 +33419,7 @@
         <v>2010</v>
       </c>
       <c r="P400" s="8" t="s">
-        <v>3596</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="401" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32602,7 +33448,7 @@
         <v>2022</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>3597</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="402" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32634,7 +33480,7 @@
         <v>2007</v>
       </c>
       <c r="P402" s="8" t="s">
-        <v>3598</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="403" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32730,7 +33576,7 @@
         <v>2006</v>
       </c>
       <c r="P405" s="8" t="s">
-        <v>3599</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="406" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32762,7 +33608,7 @@
         <v>2007</v>
       </c>
       <c r="P406" s="8" t="s">
-        <v>3600</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="407" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32794,7 +33640,7 @@
         <v>2025</v>
       </c>
       <c r="P407" s="8" t="s">
-        <v>3601</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="408" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33018,7 +33864,7 @@
         <v>2008</v>
       </c>
       <c r="P414" s="8" t="s">
-        <v>3602</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="415" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33204,7 +34050,7 @@
         <v>2011</v>
       </c>
       <c r="P420" s="8" t="s">
-        <v>3603</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="421" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33233,7 +34079,7 @@
         <v>2008</v>
       </c>
       <c r="P421" s="8" t="s">
-        <v>3604</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="422" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33243,10 +34089,7 @@
       <c r="B422" t="s">
         <v>2222</v>
       </c>
-      <c r="E422">
-        <v>0</v>
-      </c>
-      <c r="F422" t="s">
+      <c r="E422" t="s">
         <v>48</v>
       </c>
       <c r="G422" t="s">
@@ -33585,7 +34428,7 @@
         <v>2019</v>
       </c>
       <c r="P432" s="8" t="s">
-        <v>3605</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="433" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33681,7 +34524,7 @@
         <v>2014</v>
       </c>
       <c r="P435" s="8" t="s">
-        <v>3606</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="436" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33713,7 +34556,7 @@
         <v>2005</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>3607</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="437" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33723,11 +34566,11 @@
       <c r="B437" t="s">
         <v>2301</v>
       </c>
-      <c r="E437">
-        <v>0</v>
+      <c r="E437" t="s">
+        <v>85</v>
       </c>
       <c r="F437" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G437" t="s">
         <v>2302</v>
@@ -33745,7 +34588,7 @@
         <v>1989</v>
       </c>
       <c r="P437" s="8" t="s">
-        <v>2226</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="438" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33753,7 +34596,7 @@
         <v>43</v>
       </c>
       <c r="B438" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="E438" t="s">
         <v>85</v>
@@ -33762,22 +34605,22 @@
         <v>252</v>
       </c>
       <c r="G438" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="H438" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="I438" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="J438" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="K438">
         <v>2019</v>
       </c>
       <c r="P438" s="8" t="s">
-        <v>3608</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="439" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33785,7 +34628,7 @@
         <v>43</v>
       </c>
       <c r="B439" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="E439" t="s">
         <v>85</v>
@@ -33794,22 +34637,22 @@
         <v>61</v>
       </c>
       <c r="G439" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="H439" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="I439" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="J439" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="K439">
         <v>2017</v>
       </c>
       <c r="P439" s="8" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="440" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33817,7 +34660,7 @@
         <v>43</v>
       </c>
       <c r="B440" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="E440" t="s">
         <v>85</v>
@@ -33826,22 +34669,22 @@
         <v>54</v>
       </c>
       <c r="G440" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="H440" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="I440" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="J440" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="K440">
         <v>1998</v>
       </c>
       <c r="P440" s="8" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="441" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33849,7 +34692,7 @@
         <v>43</v>
       </c>
       <c r="B441" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="E441" t="s">
         <v>85</v>
@@ -33858,22 +34701,22 @@
         <v>48</v>
       </c>
       <c r="G441" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="H441" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="I441" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="J441" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="K441">
         <v>2020</v>
       </c>
       <c r="P441" s="8" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="442" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33881,7 +34724,7 @@
         <v>43</v>
       </c>
       <c r="B442" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="E442" t="s">
         <v>85</v>
@@ -33890,22 +34733,22 @@
         <v>48</v>
       </c>
       <c r="G442" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="H442" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="I442" t="s">
         <v>51</v>
       </c>
       <c r="J442" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="K442">
         <v>2020</v>
       </c>
       <c r="P442" s="8" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="443" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33913,7 +34756,7 @@
         <v>43</v>
       </c>
       <c r="B443" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="E443" t="s">
         <v>85</v>
@@ -33922,22 +34765,22 @@
         <v>54</v>
       </c>
       <c r="G443" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="H443" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="I443" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="J443" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="K443">
         <v>2019</v>
       </c>
       <c r="P443" s="8" t="s">
-        <v>3609</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="444" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33945,7 +34788,7 @@
         <v>43</v>
       </c>
       <c r="B444" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="E444" t="s">
         <v>85</v>
@@ -33954,22 +34797,22 @@
         <v>48</v>
       </c>
       <c r="G444" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="H444" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="I444" t="s">
         <v>712</v>
       </c>
       <c r="J444" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="K444">
         <v>2002</v>
       </c>
       <c r="P444" s="8" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="445" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33977,7 +34820,7 @@
         <v>43</v>
       </c>
       <c r="B445" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="E445" t="s">
         <v>85</v>
@@ -33986,22 +34829,22 @@
         <v>61</v>
       </c>
       <c r="G445" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="H445" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="I445" t="s">
         <v>51</v>
       </c>
       <c r="J445" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="K445">
         <v>2013</v>
       </c>
       <c r="P445" s="8" t="s">
-        <v>3610</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="446" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34009,7 +34852,7 @@
         <v>43</v>
       </c>
       <c r="B446" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="E446" t="s">
         <v>85</v>
@@ -34018,22 +34861,22 @@
         <v>61</v>
       </c>
       <c r="G446" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="H446" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="I446" t="s">
         <v>266</v>
       </c>
       <c r="J446" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="K446">
         <v>2023</v>
       </c>
       <c r="P446" s="8" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="447" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34041,931 +34884,1217 @@
         <v>43</v>
       </c>
       <c r="B447" t="s">
-        <v>2352</v>
+        <v>2353</v>
+      </c>
+      <c r="E447" t="s">
+        <v>85</v>
+      </c>
+      <c r="F447" t="s">
+        <v>61</v>
       </c>
       <c r="G447" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="H447" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="I447" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="J447" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="K447">
         <v>2013</v>
       </c>
-      <c r="P447" s="8"/>
+      <c r="P447" s="8" t="s">
+        <v>3635</v>
+      </c>
     </row>
     <row r="448" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A448" t="s">
         <v>43</v>
       </c>
       <c r="B448" t="s">
-        <v>2357</v>
+        <v>2358</v>
+      </c>
+      <c r="E448" t="s">
+        <v>48</v>
       </c>
       <c r="G448" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="H448" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="I448" t="s">
         <v>1819</v>
       </c>
       <c r="J448" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="K448">
         <v>2022</v>
       </c>
-      <c r="P448" s="8"/>
+      <c r="P448" s="8" t="s">
+        <v>2362</v>
+      </c>
     </row>
     <row r="449" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A449" t="s">
         <v>43</v>
       </c>
       <c r="B449" t="s">
-        <v>2361</v>
+        <v>2363</v>
+      </c>
+      <c r="E449" t="s">
+        <v>48</v>
       </c>
       <c r="G449" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="H449" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="I449" t="s">
         <v>2216</v>
       </c>
       <c r="J449" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="K449">
         <v>2016</v>
       </c>
-      <c r="P449" s="8"/>
+      <c r="P449" s="8" t="s">
+        <v>2367</v>
+      </c>
     </row>
     <row r="450" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A450" t="s">
         <v>43</v>
       </c>
       <c r="B450" t="s">
-        <v>2365</v>
+        <v>2368</v>
+      </c>
+      <c r="E450" t="s">
+        <v>85</v>
+      </c>
+      <c r="F450" t="s">
+        <v>48</v>
       </c>
       <c r="G450" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
       <c r="H450" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
       <c r="I450" t="s">
         <v>1924</v>
       </c>
       <c r="J450" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
       <c r="K450">
         <v>2010</v>
       </c>
-      <c r="P450" s="8"/>
+      <c r="P450" s="8" t="s">
+        <v>2372</v>
+      </c>
     </row>
     <row r="451" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A451" t="s">
         <v>43</v>
       </c>
       <c r="B451" t="s">
-        <v>2369</v>
+        <v>2373</v>
+      </c>
+      <c r="E451" t="s">
+        <v>85</v>
+      </c>
+      <c r="F451" t="s">
+        <v>48</v>
       </c>
       <c r="G451" t="s">
-        <v>2370</v>
+        <v>2374</v>
       </c>
       <c r="H451" t="s">
-        <v>2371</v>
+        <v>2375</v>
       </c>
       <c r="I451" t="s">
         <v>51</v>
       </c>
       <c r="J451" t="s">
-        <v>2372</v>
+        <v>2376</v>
       </c>
       <c r="K451">
         <v>2013</v>
       </c>
-      <c r="P451" s="8"/>
+      <c r="P451" s="8" t="s">
+        <v>2377</v>
+      </c>
     </row>
     <row r="452" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A452" t="s">
         <v>43</v>
       </c>
       <c r="B452" t="s">
-        <v>2373</v>
+        <v>2378</v>
+      </c>
+      <c r="E452" t="s">
+        <v>85</v>
+      </c>
+      <c r="F452" t="s">
+        <v>48</v>
       </c>
       <c r="G452" t="s">
-        <v>2374</v>
+        <v>2379</v>
       </c>
       <c r="H452" t="s">
-        <v>2375</v>
+        <v>2380</v>
       </c>
       <c r="I452" t="s">
         <v>295</v>
       </c>
       <c r="J452" t="s">
-        <v>2376</v>
+        <v>2381</v>
       </c>
       <c r="K452">
         <v>2008</v>
       </c>
-      <c r="P452" s="8"/>
+      <c r="P452" s="8" t="s">
+        <v>2382</v>
+      </c>
     </row>
     <row r="453" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A453" t="s">
         <v>43</v>
       </c>
       <c r="B453" t="s">
-        <v>2377</v>
+        <v>2383</v>
+      </c>
+      <c r="E453" t="s">
+        <v>85</v>
+      </c>
+      <c r="F453" t="s">
+        <v>48</v>
       </c>
       <c r="G453" t="s">
-        <v>2378</v>
+        <v>2384</v>
       </c>
       <c r="H453" t="s">
-        <v>2379</v>
+        <v>2385</v>
       </c>
       <c r="I453" t="s">
         <v>692</v>
       </c>
       <c r="J453" t="s">
-        <v>2380</v>
+        <v>2386</v>
       </c>
       <c r="K453">
         <v>2007</v>
       </c>
-      <c r="P453" s="8"/>
+      <c r="P453" s="8" t="s">
+        <v>2387</v>
+      </c>
     </row>
     <row r="454" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A454" t="s">
         <v>43</v>
       </c>
       <c r="B454" t="s">
-        <v>2381</v>
+        <v>2388</v>
+      </c>
+      <c r="E454" t="s">
+        <v>85</v>
+      </c>
+      <c r="F454" t="s">
+        <v>48</v>
       </c>
       <c r="G454" t="s">
-        <v>2382</v>
+        <v>2389</v>
       </c>
       <c r="H454" t="s">
-        <v>2383</v>
+        <v>2390</v>
       </c>
       <c r="I454" t="s">
-        <v>2384</v>
+        <v>2391</v>
       </c>
       <c r="J454" t="s">
-        <v>2385</v>
+        <v>2392</v>
       </c>
       <c r="K454">
         <v>2003</v>
       </c>
-      <c r="P454" s="8"/>
+      <c r="P454" s="8" t="s">
+        <v>3636</v>
+      </c>
     </row>
     <row r="455" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A455" t="s">
         <v>43</v>
       </c>
       <c r="B455" t="s">
-        <v>2386</v>
+        <v>2393</v>
+      </c>
+      <c r="E455" t="s">
+        <v>85</v>
+      </c>
+      <c r="F455" t="s">
+        <v>48</v>
       </c>
       <c r="G455" t="s">
-        <v>2387</v>
+        <v>2394</v>
       </c>
       <c r="H455" t="s">
-        <v>2388</v>
+        <v>2395</v>
       </c>
       <c r="I455" t="s">
         <v>2184</v>
       </c>
       <c r="J455" t="s">
-        <v>2389</v>
+        <v>2396</v>
       </c>
       <c r="K455">
         <v>2024</v>
       </c>
-      <c r="P455" s="8"/>
+      <c r="P455" s="8" t="s">
+        <v>2397</v>
+      </c>
     </row>
     <row r="456" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A456" t="s">
         <v>43</v>
       </c>
       <c r="B456" t="s">
-        <v>2390</v>
+        <v>2398</v>
+      </c>
+      <c r="E456" t="s">
+        <v>85</v>
+      </c>
+      <c r="F456" t="s">
+        <v>72</v>
       </c>
       <c r="G456" t="s">
-        <v>2391</v>
+        <v>2399</v>
       </c>
       <c r="H456" t="s">
-        <v>2392</v>
+        <v>2400</v>
       </c>
       <c r="I456" t="s">
-        <v>2393</v>
+        <v>2401</v>
       </c>
       <c r="J456" t="s">
-        <v>2394</v>
+        <v>2402</v>
       </c>
       <c r="K456">
         <v>2022</v>
       </c>
-      <c r="P456" s="8"/>
+      <c r="P456" s="8" t="s">
+        <v>2403</v>
+      </c>
     </row>
     <row r="457" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A457" t="s">
         <v>43</v>
       </c>
       <c r="B457" t="s">
-        <v>2395</v>
+        <v>2404</v>
+      </c>
+      <c r="E457" t="s">
+        <v>48</v>
       </c>
       <c r="G457" t="s">
-        <v>2396</v>
+        <v>2405</v>
       </c>
       <c r="H457" t="s">
-        <v>2397</v>
+        <v>2406</v>
       </c>
       <c r="I457" t="s">
         <v>220</v>
       </c>
       <c r="J457" t="s">
-        <v>2398</v>
+        <v>2407</v>
       </c>
       <c r="K457">
         <v>2019</v>
       </c>
-      <c r="P457" s="8"/>
+      <c r="P457" s="8" t="s">
+        <v>2408</v>
+      </c>
     </row>
     <row r="458" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A458" t="s">
         <v>43</v>
       </c>
       <c r="B458" t="s">
-        <v>2399</v>
+        <v>2409</v>
+      </c>
+      <c r="E458" t="s">
+        <v>85</v>
+      </c>
+      <c r="F458" t="s">
+        <v>48</v>
       </c>
       <c r="G458" t="s">
-        <v>2400</v>
+        <v>2410</v>
       </c>
       <c r="H458" t="s">
-        <v>2401</v>
+        <v>2411</v>
       </c>
       <c r="I458" t="s">
-        <v>2402</v>
+        <v>2412</v>
       </c>
       <c r="J458" t="s">
-        <v>2403</v>
+        <v>2413</v>
       </c>
       <c r="K458">
         <v>2024</v>
       </c>
-      <c r="P458" s="8"/>
+      <c r="P458" s="8" t="s">
+        <v>3637</v>
+      </c>
     </row>
     <row r="459" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A459" t="s">
         <v>43</v>
       </c>
       <c r="B459" t="s">
-        <v>2404</v>
+        <v>2414</v>
+      </c>
+      <c r="E459" t="s">
+        <v>85</v>
+      </c>
+      <c r="F459" t="s">
+        <v>48</v>
       </c>
       <c r="G459" t="s">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="H459" t="s">
-        <v>2406</v>
+        <v>2416</v>
       </c>
       <c r="I459" t="s">
         <v>915</v>
       </c>
       <c r="J459" t="s">
-        <v>2407</v>
+        <v>2417</v>
       </c>
       <c r="K459">
         <v>2003</v>
       </c>
-      <c r="P459" s="8"/>
+      <c r="P459" s="8" t="s">
+        <v>2418</v>
+      </c>
     </row>
     <row r="460" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A460" t="s">
         <v>43</v>
       </c>
       <c r="B460" t="s">
-        <v>2408</v>
+        <v>2419</v>
+      </c>
+      <c r="E460" t="s">
+        <v>85</v>
+      </c>
+      <c r="F460" t="s">
+        <v>48</v>
       </c>
       <c r="G460" t="s">
-        <v>2409</v>
+        <v>2420</v>
       </c>
       <c r="H460" t="s">
-        <v>2410</v>
+        <v>2421</v>
       </c>
       <c r="I460" t="s">
-        <v>2411</v>
+        <v>2422</v>
       </c>
       <c r="J460" t="s">
-        <v>2412</v>
+        <v>2423</v>
       </c>
       <c r="K460">
         <v>2024</v>
       </c>
-      <c r="P460" s="8"/>
+      <c r="P460" s="8" t="s">
+        <v>3638</v>
+      </c>
     </row>
     <row r="461" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A461" t="s">
         <v>43</v>
       </c>
       <c r="B461" t="s">
-        <v>2413</v>
+        <v>2424</v>
+      </c>
+      <c r="E461" t="s">
+        <v>85</v>
+      </c>
+      <c r="F461" t="s">
+        <v>48</v>
       </c>
       <c r="G461" t="s">
-        <v>2414</v>
+        <v>2425</v>
       </c>
       <c r="H461" t="s">
-        <v>2415</v>
+        <v>2426</v>
       </c>
       <c r="I461" t="s">
         <v>51</v>
       </c>
       <c r="J461" t="s">
-        <v>2416</v>
+        <v>2427</v>
       </c>
       <c r="K461">
         <v>2023</v>
       </c>
-      <c r="P461" s="8"/>
+      <c r="P461" s="8" t="s">
+        <v>3639</v>
+      </c>
     </row>
     <row r="462" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A462" t="s">
         <v>43</v>
       </c>
       <c r="B462" t="s">
-        <v>2417</v>
+        <v>2428</v>
+      </c>
+      <c r="E462" t="s">
+        <v>85</v>
+      </c>
+      <c r="F462" t="s">
+        <v>48</v>
       </c>
       <c r="G462" t="s">
-        <v>2418</v>
+        <v>2429</v>
       </c>
       <c r="H462" t="s">
-        <v>2419</v>
+        <v>2430</v>
       </c>
       <c r="I462" t="s">
-        <v>2420</v>
+        <v>2431</v>
       </c>
       <c r="J462" t="s">
-        <v>2421</v>
+        <v>2432</v>
       </c>
       <c r="K462">
         <v>1995</v>
       </c>
-      <c r="P462" s="8"/>
+      <c r="P462" s="8" t="s">
+        <v>2433</v>
+      </c>
     </row>
     <row r="463" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A463" t="s">
         <v>43</v>
       </c>
       <c r="B463" t="s">
-        <v>2422</v>
+        <v>2434</v>
+      </c>
+      <c r="E463" t="s">
+        <v>85</v>
+      </c>
+      <c r="F463" t="s">
+        <v>48</v>
       </c>
       <c r="G463" t="s">
-        <v>2423</v>
+        <v>2435</v>
       </c>
       <c r="H463" t="s">
-        <v>2424</v>
+        <v>2436</v>
       </c>
       <c r="I463" t="s">
         <v>51</v>
       </c>
       <c r="J463" t="s">
-        <v>2421</v>
+        <v>2432</v>
       </c>
       <c r="K463">
         <v>1989</v>
       </c>
-      <c r="P463" s="8"/>
+      <c r="P463" s="8" t="s">
+        <v>2437</v>
+      </c>
     </row>
     <row r="464" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A464" t="s">
         <v>43</v>
       </c>
       <c r="B464" t="s">
-        <v>2425</v>
+        <v>2438</v>
+      </c>
+      <c r="E464" t="s">
+        <v>85</v>
+      </c>
+      <c r="F464" t="s">
+        <v>61</v>
       </c>
       <c r="G464" t="s">
-        <v>2426</v>
+        <v>2439</v>
       </c>
       <c r="H464" t="s">
-        <v>2427</v>
+        <v>2440</v>
       </c>
       <c r="I464" t="s">
         <v>2252</v>
       </c>
       <c r="J464" t="s">
-        <v>2428</v>
+        <v>2441</v>
       </c>
       <c r="K464">
         <v>1996</v>
       </c>
-      <c r="P464" s="8"/>
+      <c r="P464" s="8" t="s">
+        <v>2442</v>
+      </c>
     </row>
     <row r="465" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A465" t="s">
         <v>43</v>
       </c>
       <c r="B465" t="s">
-        <v>2429</v>
+        <v>2443</v>
+      </c>
+      <c r="E465" t="s">
+        <v>85</v>
+      </c>
+      <c r="F465" t="s">
+        <v>48</v>
       </c>
       <c r="G465" t="s">
-        <v>2430</v>
+        <v>2444</v>
       </c>
       <c r="H465" t="s">
-        <v>2431</v>
+        <v>2445</v>
       </c>
       <c r="I465" t="s">
-        <v>2432</v>
+        <v>2446</v>
       </c>
       <c r="J465" t="s">
-        <v>2433</v>
+        <v>2447</v>
       </c>
       <c r="K465">
         <v>2021</v>
       </c>
-      <c r="P465" s="8"/>
+      <c r="P465" s="8" t="s">
+        <v>2448</v>
+      </c>
     </row>
     <row r="466" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A466" t="s">
         <v>43</v>
       </c>
       <c r="B466" t="s">
-        <v>2434</v>
+        <v>2449</v>
+      </c>
+      <c r="E466" t="s">
+        <v>85</v>
+      </c>
+      <c r="F466" t="s">
+        <v>252</v>
       </c>
       <c r="G466" t="s">
-        <v>2435</v>
+        <v>2450</v>
       </c>
       <c r="H466" t="s">
-        <v>2436</v>
+        <v>2451</v>
       </c>
       <c r="I466" t="s">
         <v>128</v>
       </c>
       <c r="J466" t="s">
-        <v>2437</v>
+        <v>2452</v>
       </c>
       <c r="K466">
         <v>2017</v>
       </c>
-      <c r="P466" s="8"/>
+      <c r="P466" s="8" t="s">
+        <v>3640</v>
+      </c>
     </row>
     <row r="467" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A467" t="s">
         <v>43</v>
       </c>
       <c r="B467" t="s">
-        <v>2438</v>
+        <v>2453</v>
+      </c>
+      <c r="E467" t="s">
+        <v>85</v>
+      </c>
+      <c r="F467" t="s">
+        <v>72</v>
       </c>
       <c r="G467" t="s">
-        <v>2439</v>
+        <v>2454</v>
       </c>
       <c r="H467" t="s">
-        <v>2440</v>
+        <v>2455</v>
       </c>
       <c r="I467" t="s">
-        <v>2441</v>
+        <v>2456</v>
       </c>
       <c r="J467" t="s">
-        <v>2442</v>
+        <v>2457</v>
       </c>
       <c r="K467">
         <v>2023</v>
       </c>
-      <c r="P467" s="8"/>
+      <c r="P467" s="8" t="s">
+        <v>2458</v>
+      </c>
     </row>
     <row r="468" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A468" t="s">
         <v>43</v>
       </c>
       <c r="B468" t="s">
-        <v>2443</v>
+        <v>2459</v>
+      </c>
+      <c r="E468" t="s">
+        <v>85</v>
+      </c>
+      <c r="F468" t="s">
+        <v>48</v>
       </c>
       <c r="G468" t="s">
-        <v>2444</v>
+        <v>2460</v>
       </c>
       <c r="H468" t="s">
-        <v>2445</v>
+        <v>2461</v>
       </c>
       <c r="I468" t="s">
-        <v>2446</v>
+        <v>2462</v>
       </c>
       <c r="J468" t="s">
-        <v>2447</v>
+        <v>2463</v>
       </c>
       <c r="K468">
         <v>2012</v>
       </c>
-      <c r="P468" s="8"/>
+      <c r="P468" s="8" t="s">
+        <v>3641</v>
+      </c>
     </row>
     <row r="469" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A469" t="s">
         <v>43</v>
       </c>
       <c r="B469" t="s">
-        <v>2448</v>
+        <v>2464</v>
+      </c>
+      <c r="E469" t="s">
+        <v>48</v>
       </c>
       <c r="G469" t="s">
-        <v>2449</v>
+        <v>2465</v>
       </c>
       <c r="H469" t="s">
-        <v>2450</v>
+        <v>2466</v>
       </c>
       <c r="I469" t="s">
-        <v>2451</v>
+        <v>2467</v>
       </c>
       <c r="J469" t="s">
-        <v>2452</v>
+        <v>2468</v>
       </c>
       <c r="K469">
         <v>2021</v>
       </c>
-      <c r="P469" s="8"/>
+      <c r="P469" s="8" t="s">
+        <v>3642</v>
+      </c>
     </row>
     <row r="470" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A470" t="s">
         <v>43</v>
       </c>
       <c r="B470" t="s">
-        <v>2453</v>
+        <v>2469</v>
+      </c>
+      <c r="E470" t="s">
+        <v>85</v>
+      </c>
+      <c r="F470" t="s">
+        <v>61</v>
       </c>
       <c r="G470" t="s">
-        <v>2454</v>
+        <v>2470</v>
       </c>
       <c r="H470" t="s">
-        <v>2455</v>
+        <v>2471</v>
       </c>
       <c r="I470" t="s">
         <v>409</v>
       </c>
       <c r="J470" t="s">
-        <v>2456</v>
+        <v>2472</v>
       </c>
       <c r="K470">
         <v>2022</v>
       </c>
-      <c r="P470" s="8"/>
+      <c r="P470" s="8" t="s">
+        <v>3643</v>
+      </c>
     </row>
     <row r="471" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A471" t="s">
         <v>43</v>
       </c>
       <c r="B471" t="s">
-        <v>2457</v>
+        <v>2473</v>
+      </c>
+      <c r="E471" t="s">
+        <v>85</v>
+      </c>
+      <c r="F471" t="s">
+        <v>54</v>
       </c>
       <c r="G471" t="s">
-        <v>2458</v>
+        <v>2474</v>
       </c>
       <c r="H471" t="s">
-        <v>2459</v>
+        <v>2475</v>
       </c>
       <c r="I471" t="s">
         <v>51</v>
       </c>
       <c r="J471" t="s">
-        <v>2460</v>
+        <v>2476</v>
       </c>
       <c r="K471">
         <v>2018</v>
       </c>
-      <c r="P471" s="8"/>
+      <c r="P471" s="8" t="s">
+        <v>3644</v>
+      </c>
     </row>
     <row r="472" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A472" t="s">
         <v>43</v>
       </c>
       <c r="B472" t="s">
-        <v>2461</v>
+        <v>2477</v>
+      </c>
+      <c r="E472" t="s">
+        <v>85</v>
+      </c>
+      <c r="F472" t="s">
+        <v>61</v>
       </c>
       <c r="G472" t="s">
-        <v>2462</v>
+        <v>2478</v>
       </c>
       <c r="H472" t="s">
-        <v>2463</v>
+        <v>2479</v>
       </c>
       <c r="I472" t="s">
         <v>51</v>
       </c>
       <c r="J472" t="s">
-        <v>2464</v>
+        <v>2480</v>
       </c>
       <c r="K472">
         <v>2021</v>
       </c>
-      <c r="P472" s="8"/>
+      <c r="P472" s="8" t="s">
+        <v>3645</v>
+      </c>
     </row>
     <row r="473" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A473" t="s">
         <v>43</v>
       </c>
       <c r="B473" t="s">
-        <v>2465</v>
+        <v>2481</v>
+      </c>
+      <c r="E473">
+        <v>0</v>
+      </c>
+      <c r="F473" t="s">
+        <v>48</v>
       </c>
       <c r="G473" t="s">
-        <v>2466</v>
+        <v>2482</v>
       </c>
       <c r="H473" t="s">
-        <v>2467</v>
+        <v>2483</v>
       </c>
       <c r="I473" t="s">
         <v>2252</v>
       </c>
       <c r="J473" t="s">
-        <v>2468</v>
+        <v>2484</v>
       </c>
       <c r="K473">
         <v>1982</v>
       </c>
-      <c r="P473" s="8"/>
+      <c r="P473" s="8" t="s">
+        <v>2485</v>
+      </c>
     </row>
     <row r="474" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A474" t="s">
         <v>43</v>
       </c>
       <c r="B474" t="s">
-        <v>2469</v>
+        <v>2486</v>
+      </c>
+      <c r="E474" t="s">
+        <v>85</v>
+      </c>
+      <c r="F474" t="s">
+        <v>48</v>
       </c>
       <c r="G474" t="s">
-        <v>2470</v>
+        <v>2487</v>
       </c>
       <c r="H474" t="s">
-        <v>2471</v>
+        <v>2488</v>
       </c>
       <c r="I474" t="s">
         <v>2054</v>
       </c>
       <c r="J474" t="s">
-        <v>2472</v>
+        <v>2489</v>
       </c>
       <c r="K474">
         <v>2014</v>
       </c>
-      <c r="P474" s="8"/>
+      <c r="P474" s="8" t="s">
+        <v>2490</v>
+      </c>
     </row>
     <row r="475" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A475" t="s">
         <v>43</v>
       </c>
       <c r="B475" t="s">
-        <v>2473</v>
+        <v>2491</v>
+      </c>
+      <c r="E475" t="s">
+        <v>85</v>
+      </c>
+      <c r="F475" t="s">
+        <v>48</v>
       </c>
       <c r="G475" t="s">
-        <v>2474</v>
+        <v>2492</v>
       </c>
       <c r="H475" t="s">
-        <v>2475</v>
+        <v>2493</v>
       </c>
       <c r="I475" t="s">
-        <v>2476</v>
+        <v>2494</v>
       </c>
       <c r="J475" t="s">
-        <v>2477</v>
+        <v>2495</v>
       </c>
       <c r="K475">
         <v>2005</v>
       </c>
-      <c r="P475" s="8"/>
+      <c r="P475" s="8" t="s">
+        <v>2496</v>
+      </c>
     </row>
     <row r="476" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A476" t="s">
         <v>43</v>
       </c>
       <c r="B476" t="s">
-        <v>2478</v>
+        <v>2497</v>
+      </c>
+      <c r="E476" t="s">
+        <v>85</v>
+      </c>
+      <c r="F476" t="s">
+        <v>48</v>
       </c>
       <c r="G476" t="s">
-        <v>2479</v>
+        <v>2498</v>
       </c>
       <c r="H476" t="s">
-        <v>2480</v>
+        <v>2499</v>
       </c>
       <c r="I476" t="s">
         <v>1652</v>
       </c>
       <c r="J476" t="s">
-        <v>2481</v>
+        <v>2500</v>
       </c>
       <c r="K476">
         <v>2011</v>
       </c>
-      <c r="P476" s="8"/>
+      <c r="P476" s="8" t="s">
+        <v>2501</v>
+      </c>
     </row>
     <row r="477" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A477" t="s">
         <v>43</v>
       </c>
       <c r="B477" t="s">
-        <v>2482</v>
+        <v>2502</v>
+      </c>
+      <c r="E477">
+        <v>0</v>
+      </c>
+      <c r="F477" t="s">
+        <v>48</v>
       </c>
       <c r="G477" t="s">
-        <v>2483</v>
+        <v>2503</v>
       </c>
       <c r="H477" t="s">
-        <v>2484</v>
+        <v>2504</v>
       </c>
       <c r="I477" t="s">
         <v>307</v>
       </c>
       <c r="J477" t="s">
-        <v>2485</v>
+        <v>2505</v>
       </c>
       <c r="K477">
         <v>1979</v>
       </c>
-      <c r="P477" s="8"/>
+      <c r="P477" s="8" t="s">
+        <v>2485</v>
+      </c>
     </row>
     <row r="478" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A478" t="s">
         <v>43</v>
       </c>
       <c r="B478" t="s">
-        <v>2486</v>
+        <v>2506</v>
+      </c>
+      <c r="E478">
+        <v>0</v>
+      </c>
+      <c r="F478" t="s">
+        <v>48</v>
       </c>
       <c r="G478" t="s">
-        <v>2487</v>
+        <v>2507</v>
       </c>
       <c r="H478" t="s">
-        <v>2488</v>
+        <v>2508</v>
       </c>
       <c r="I478" t="s">
         <v>1314</v>
       </c>
       <c r="J478" t="s">
-        <v>2489</v>
+        <v>2509</v>
       </c>
       <c r="K478">
         <v>1985</v>
       </c>
-      <c r="P478" s="8"/>
+      <c r="P478" s="8" t="s">
+        <v>2485</v>
+      </c>
     </row>
     <row r="479" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A479" t="s">
         <v>43</v>
       </c>
       <c r="B479" t="s">
-        <v>2490</v>
+        <v>2510</v>
+      </c>
+      <c r="E479" t="s">
+        <v>48</v>
       </c>
       <c r="G479" t="s">
-        <v>2491</v>
+        <v>2511</v>
       </c>
       <c r="H479" t="s">
-        <v>2492</v>
+        <v>2512</v>
       </c>
       <c r="I479" t="s">
         <v>1862</v>
       </c>
       <c r="J479" t="s">
-        <v>2493</v>
+        <v>2513</v>
       </c>
       <c r="K479">
         <v>2011</v>
       </c>
-      <c r="P479" s="8"/>
+      <c r="P479" s="8" t="s">
+        <v>2514</v>
+      </c>
     </row>
     <row r="480" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A480" t="s">
         <v>43</v>
       </c>
       <c r="B480" t="s">
-        <v>2494</v>
+        <v>2515</v>
+      </c>
+      <c r="E480" t="s">
+        <v>48</v>
       </c>
       <c r="G480" t="s">
-        <v>2495</v>
+        <v>2516</v>
       </c>
       <c r="H480" t="s">
-        <v>2496</v>
+        <v>2517</v>
       </c>
       <c r="I480" t="s">
         <v>81</v>
       </c>
       <c r="J480" t="s">
-        <v>2497</v>
+        <v>2518</v>
       </c>
       <c r="K480">
         <v>1976</v>
       </c>
-      <c r="P480" s="8"/>
+      <c r="P480" s="8" t="s">
+        <v>2519</v>
+      </c>
     </row>
     <row r="481" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A481" t="s">
         <v>43</v>
       </c>
       <c r="B481" t="s">
-        <v>2498</v>
+        <v>2520</v>
+      </c>
+      <c r="E481" t="s">
+        <v>85</v>
+      </c>
+      <c r="F481" t="s">
+        <v>48</v>
       </c>
       <c r="G481" t="s">
-        <v>2499</v>
+        <v>2521</v>
       </c>
       <c r="H481" t="s">
-        <v>2500</v>
+        <v>2522</v>
       </c>
       <c r="I481" t="s">
         <v>723</v>
       </c>
       <c r="J481" t="s">
-        <v>2501</v>
+        <v>2523</v>
       </c>
       <c r="K481">
         <v>2006</v>
       </c>
-      <c r="P481" s="8"/>
+      <c r="P481" s="8" t="s">
+        <v>2524</v>
+      </c>
     </row>
     <row r="482" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A482" t="s">
         <v>43</v>
       </c>
       <c r="B482" t="s">
-        <v>2502</v>
+        <v>2525</v>
+      </c>
+      <c r="E482" t="s">
+        <v>85</v>
+      </c>
+      <c r="F482" t="s">
+        <v>61</v>
       </c>
       <c r="G482" t="s">
-        <v>2503</v>
+        <v>2526</v>
       </c>
       <c r="H482" t="s">
-        <v>2504</v>
+        <v>2527</v>
       </c>
       <c r="I482" t="s">
         <v>2184</v>
       </c>
       <c r="J482" t="s">
-        <v>2505</v>
+        <v>2528</v>
       </c>
       <c r="K482">
         <v>2001</v>
       </c>
-      <c r="P482" s="8"/>
+      <c r="P482" s="8" t="s">
+        <v>3646</v>
+      </c>
     </row>
     <row r="483" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A483" t="s">
         <v>43</v>
       </c>
       <c r="B483" t="s">
-        <v>2506</v>
+        <v>2529</v>
+      </c>
+      <c r="E483">
+        <v>0</v>
+      </c>
+      <c r="F483" t="s">
+        <v>48</v>
       </c>
       <c r="G483" t="s">
-        <v>2507</v>
+        <v>2530</v>
       </c>
       <c r="H483" t="s">
-        <v>2508</v>
+        <v>2531</v>
       </c>
       <c r="I483" t="s">
         <v>51</v>
       </c>
       <c r="J483" t="s">
-        <v>2509</v>
+        <v>2532</v>
       </c>
       <c r="K483">
         <v>2020</v>
       </c>
-      <c r="P483" s="8"/>
+      <c r="P483" s="8" t="s">
+        <v>2485</v>
+      </c>
     </row>
     <row r="484" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A484" t="s">
         <v>43</v>
       </c>
       <c r="B484" t="s">
-        <v>2510</v>
+        <v>2533</v>
+      </c>
+      <c r="E484" t="s">
+        <v>85</v>
+      </c>
+      <c r="F484" t="s">
+        <v>48</v>
       </c>
       <c r="G484" t="s">
-        <v>2511</v>
+        <v>2534</v>
       </c>
       <c r="H484" t="s">
-        <v>2512</v>
+        <v>2535</v>
       </c>
       <c r="I484" t="s">
         <v>1359</v>
       </c>
       <c r="J484" t="s">
-        <v>2513</v>
+        <v>2536</v>
       </c>
       <c r="K484">
         <v>2013</v>
       </c>
-      <c r="P484" s="8"/>
+      <c r="P484" s="8" t="s">
+        <v>2537</v>
+      </c>
     </row>
     <row r="485" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A485" t="s">
         <v>43</v>
       </c>
       <c r="B485" t="s">
-        <v>2514</v>
+        <v>2538</v>
       </c>
       <c r="G485" t="s">
-        <v>2515</v>
+        <v>2539</v>
       </c>
       <c r="H485" t="s">
-        <v>2516</v>
+        <v>2540</v>
       </c>
       <c r="I485" t="s">
         <v>295</v>
       </c>
       <c r="J485" t="s">
-        <v>2517</v>
+        <v>2541</v>
       </c>
       <c r="K485">
         <v>2012</v>
@@ -34977,19 +36106,19 @@
         <v>43</v>
       </c>
       <c r="B486" t="s">
-        <v>2518</v>
+        <v>2542</v>
       </c>
       <c r="G486" t="s">
-        <v>2519</v>
+        <v>2543</v>
       </c>
       <c r="H486" t="s">
-        <v>2520</v>
+        <v>2544</v>
       </c>
       <c r="I486" t="s">
-        <v>2521</v>
+        <v>2545</v>
       </c>
       <c r="J486" t="s">
-        <v>2522</v>
+        <v>2546</v>
       </c>
       <c r="K486">
         <v>1996</v>
@@ -35001,19 +36130,19 @@
         <v>43</v>
       </c>
       <c r="B487" t="s">
-        <v>2523</v>
+        <v>2547</v>
       </c>
       <c r="G487" t="s">
-        <v>2524</v>
+        <v>2548</v>
       </c>
       <c r="H487" t="s">
-        <v>2525</v>
+        <v>2549</v>
       </c>
       <c r="I487" t="s">
-        <v>2526</v>
+        <v>2550</v>
       </c>
       <c r="J487" t="s">
-        <v>2527</v>
+        <v>2551</v>
       </c>
       <c r="K487">
         <v>1995</v>
@@ -35025,19 +36154,19 @@
         <v>43</v>
       </c>
       <c r="B488" t="s">
-        <v>2528</v>
+        <v>2552</v>
       </c>
       <c r="G488" t="s">
-        <v>2529</v>
+        <v>2553</v>
       </c>
       <c r="H488" t="s">
-        <v>2530</v>
+        <v>2554</v>
       </c>
       <c r="I488" t="s">
         <v>51</v>
       </c>
       <c r="J488" t="s">
-        <v>2531</v>
+        <v>2555</v>
       </c>
       <c r="K488">
         <v>2002</v>
@@ -35049,19 +36178,19 @@
         <v>43</v>
       </c>
       <c r="B489" t="s">
-        <v>2532</v>
+        <v>2556</v>
       </c>
       <c r="G489" t="s">
-        <v>2533</v>
+        <v>2557</v>
       </c>
       <c r="H489" t="s">
-        <v>2534</v>
+        <v>2558</v>
       </c>
       <c r="I489" t="s">
-        <v>2535</v>
+        <v>2559</v>
       </c>
       <c r="J489" t="s">
-        <v>2536</v>
+        <v>2560</v>
       </c>
       <c r="K489">
         <v>2023</v>
@@ -35073,19 +36202,19 @@
         <v>43</v>
       </c>
       <c r="B490" t="s">
-        <v>2537</v>
+        <v>2561</v>
       </c>
       <c r="G490" t="s">
-        <v>2538</v>
+        <v>2562</v>
       </c>
       <c r="H490" t="s">
-        <v>2539</v>
+        <v>2563</v>
       </c>
       <c r="I490" t="s">
-        <v>2540</v>
+        <v>2564</v>
       </c>
       <c r="J490" t="s">
-        <v>2541</v>
+        <v>2565</v>
       </c>
       <c r="K490">
         <v>2011</v>
@@ -35097,19 +36226,19 @@
         <v>43</v>
       </c>
       <c r="B491" t="s">
-        <v>2542</v>
+        <v>2566</v>
       </c>
       <c r="G491" t="s">
-        <v>2543</v>
+        <v>2567</v>
       </c>
       <c r="H491" t="s">
-        <v>2544</v>
+        <v>2568</v>
       </c>
       <c r="I491" t="s">
-        <v>2545</v>
+        <v>2569</v>
       </c>
       <c r="J491" t="s">
-        <v>2541</v>
+        <v>2565</v>
       </c>
       <c r="K491">
         <v>2011</v>
@@ -35121,19 +36250,19 @@
         <v>43</v>
       </c>
       <c r="B492" t="s">
-        <v>2546</v>
+        <v>2570</v>
       </c>
       <c r="G492" t="s">
-        <v>2547</v>
+        <v>2571</v>
       </c>
       <c r="H492" t="s">
-        <v>2548</v>
+        <v>2572</v>
       </c>
       <c r="I492" t="s">
         <v>51</v>
       </c>
       <c r="J492" t="s">
-        <v>2549</v>
+        <v>2573</v>
       </c>
       <c r="K492">
         <v>1984</v>
@@ -35145,19 +36274,19 @@
         <v>43</v>
       </c>
       <c r="B493" t="s">
-        <v>2550</v>
+        <v>2574</v>
       </c>
       <c r="G493" t="s">
-        <v>2551</v>
+        <v>2575</v>
       </c>
       <c r="H493" t="s">
-        <v>2552</v>
+        <v>2576</v>
       </c>
       <c r="I493" t="s">
-        <v>2553</v>
+        <v>2577</v>
       </c>
       <c r="J493" t="s">
-        <v>2554</v>
+        <v>2578</v>
       </c>
       <c r="K493">
         <v>2017</v>
@@ -35169,19 +36298,19 @@
         <v>43</v>
       </c>
       <c r="B494" t="s">
-        <v>2555</v>
+        <v>2579</v>
       </c>
       <c r="G494" t="s">
-        <v>2556</v>
+        <v>2580</v>
       </c>
       <c r="H494" t="s">
-        <v>2557</v>
+        <v>2581</v>
       </c>
       <c r="I494" t="s">
         <v>1729</v>
       </c>
       <c r="J494" t="s">
-        <v>2558</v>
+        <v>2582</v>
       </c>
       <c r="K494">
         <v>2025</v>
@@ -35193,19 +36322,19 @@
         <v>43</v>
       </c>
       <c r="B495" t="s">
-        <v>2559</v>
+        <v>2583</v>
       </c>
       <c r="G495" t="s">
-        <v>2560</v>
+        <v>2584</v>
       </c>
       <c r="H495" t="s">
-        <v>2561</v>
+        <v>2585</v>
       </c>
       <c r="I495" t="s">
         <v>643</v>
       </c>
       <c r="J495" t="s">
-        <v>2562</v>
+        <v>2586</v>
       </c>
       <c r="K495">
         <v>2025</v>
@@ -35217,19 +36346,19 @@
         <v>43</v>
       </c>
       <c r="B496" t="s">
-        <v>2563</v>
+        <v>2587</v>
       </c>
       <c r="G496" t="s">
-        <v>2547</v>
+        <v>2571</v>
       </c>
       <c r="H496" t="s">
-        <v>2564</v>
+        <v>2588</v>
       </c>
       <c r="I496" t="s">
         <v>307</v>
       </c>
       <c r="J496" t="s">
-        <v>2565</v>
+        <v>2589</v>
       </c>
       <c r="K496">
         <v>2020</v>
@@ -35241,19 +36370,19 @@
         <v>43</v>
       </c>
       <c r="B497" t="s">
-        <v>2566</v>
+        <v>2590</v>
       </c>
       <c r="G497" t="s">
-        <v>2567</v>
+        <v>2591</v>
       </c>
       <c r="H497" t="s">
-        <v>2568</v>
+        <v>2592</v>
       </c>
       <c r="I497" t="s">
-        <v>2569</v>
+        <v>2593</v>
       </c>
       <c r="J497" t="s">
-        <v>2570</v>
+        <v>2594</v>
       </c>
       <c r="K497">
         <v>2019</v>
@@ -35265,19 +36394,19 @@
         <v>43</v>
       </c>
       <c r="B498" t="s">
-        <v>2571</v>
+        <v>2595</v>
       </c>
       <c r="G498" t="s">
-        <v>2572</v>
+        <v>2596</v>
       </c>
       <c r="H498" t="s">
-        <v>2573</v>
+        <v>2597</v>
       </c>
       <c r="I498" t="s">
-        <v>2574</v>
+        <v>2598</v>
       </c>
       <c r="J498" t="s">
-        <v>2575</v>
+        <v>2599</v>
       </c>
       <c r="K498">
         <v>2023</v>
@@ -35289,19 +36418,19 @@
         <v>43</v>
       </c>
       <c r="B499" t="s">
-        <v>2576</v>
+        <v>2600</v>
       </c>
       <c r="G499" t="s">
-        <v>2577</v>
+        <v>2601</v>
       </c>
       <c r="H499" t="s">
-        <v>2578</v>
+        <v>2602</v>
       </c>
       <c r="I499" t="s">
         <v>687</v>
       </c>
       <c r="J499" t="s">
-        <v>2579</v>
+        <v>2603</v>
       </c>
       <c r="K499">
         <v>2001</v>
@@ -35313,19 +36442,19 @@
         <v>43</v>
       </c>
       <c r="B500" t="s">
-        <v>2580</v>
+        <v>2604</v>
       </c>
       <c r="G500" t="s">
-        <v>2581</v>
+        <v>2605</v>
       </c>
       <c r="H500" t="s">
-        <v>2582</v>
+        <v>2606</v>
       </c>
       <c r="I500" t="s">
         <v>723</v>
       </c>
       <c r="J500" t="s">
-        <v>2583</v>
+        <v>2607</v>
       </c>
       <c r="K500">
         <v>2022</v>
@@ -35337,19 +36466,19 @@
         <v>43</v>
       </c>
       <c r="B501" t="s">
-        <v>2584</v>
+        <v>2608</v>
       </c>
       <c r="G501" t="s">
-        <v>2585</v>
+        <v>2609</v>
       </c>
       <c r="H501" t="s">
-        <v>2586</v>
+        <v>2610</v>
       </c>
       <c r="I501" t="s">
         <v>253</v>
       </c>
       <c r="J501" t="s">
-        <v>2587</v>
+        <v>2611</v>
       </c>
       <c r="K501">
         <v>2001</v>
@@ -35361,19 +36490,19 @@
         <v>43</v>
       </c>
       <c r="B502" t="s">
-        <v>2588</v>
+        <v>2612</v>
       </c>
       <c r="G502" t="s">
-        <v>2589</v>
+        <v>2613</v>
       </c>
       <c r="H502" t="s">
-        <v>2590</v>
+        <v>2614</v>
       </c>
       <c r="I502" t="s">
         <v>307</v>
       </c>
       <c r="J502" t="s">
-        <v>2591</v>
+        <v>2615</v>
       </c>
       <c r="K502">
         <v>1976</v>
@@ -35385,19 +36514,19 @@
         <v>43</v>
       </c>
       <c r="B503" t="s">
-        <v>2592</v>
+        <v>2616</v>
       </c>
       <c r="G503" t="s">
-        <v>2593</v>
+        <v>2617</v>
       </c>
       <c r="H503" t="s">
-        <v>2594</v>
+        <v>2618</v>
       </c>
       <c r="I503" t="s">
-        <v>2595</v>
+        <v>2619</v>
       </c>
       <c r="J503" t="s">
-        <v>2596</v>
+        <v>2620</v>
       </c>
       <c r="K503">
         <v>1981</v>
@@ -35409,19 +36538,19 @@
         <v>43</v>
       </c>
       <c r="B504" t="s">
-        <v>2597</v>
+        <v>2621</v>
       </c>
       <c r="G504" t="s">
-        <v>2598</v>
+        <v>2622</v>
       </c>
       <c r="H504" t="s">
-        <v>2599</v>
+        <v>2623</v>
       </c>
       <c r="I504" t="s">
-        <v>2600</v>
+        <v>2624</v>
       </c>
       <c r="J504" t="s">
-        <v>2601</v>
+        <v>2625</v>
       </c>
       <c r="K504">
         <v>2025</v>
@@ -35433,19 +36562,19 @@
         <v>43</v>
       </c>
       <c r="B505" t="s">
-        <v>2602</v>
+        <v>2626</v>
       </c>
       <c r="G505" t="s">
-        <v>2603</v>
+        <v>2627</v>
       </c>
       <c r="H505" t="s">
-        <v>2604</v>
+        <v>2628</v>
       </c>
       <c r="I505" t="s">
-        <v>2605</v>
+        <v>2629</v>
       </c>
       <c r="J505" t="s">
-        <v>2606</v>
+        <v>2630</v>
       </c>
       <c r="K505">
         <v>1998</v>
@@ -35457,19 +36586,19 @@
         <v>43</v>
       </c>
       <c r="B506" t="s">
-        <v>2607</v>
+        <v>2631</v>
       </c>
       <c r="G506" t="s">
-        <v>2608</v>
+        <v>2632</v>
       </c>
       <c r="H506" t="s">
-        <v>2609</v>
+        <v>2633</v>
       </c>
       <c r="I506" t="s">
         <v>351</v>
       </c>
       <c r="J506" t="s">
-        <v>2610</v>
+        <v>2634</v>
       </c>
       <c r="K506">
         <v>2010</v>
@@ -35481,19 +36610,19 @@
         <v>43</v>
       </c>
       <c r="B507" t="s">
-        <v>2611</v>
+        <v>2635</v>
       </c>
       <c r="G507" t="s">
-        <v>2612</v>
+        <v>2636</v>
       </c>
       <c r="H507" t="s">
-        <v>2613</v>
+        <v>2637</v>
       </c>
       <c r="I507" t="s">
         <v>2018</v>
       </c>
       <c r="J507" t="s">
-        <v>2614</v>
+        <v>2638</v>
       </c>
       <c r="K507">
         <v>2016</v>
@@ -35505,19 +36634,19 @@
         <v>43</v>
       </c>
       <c r="B508" t="s">
-        <v>2615</v>
+        <v>2639</v>
       </c>
       <c r="G508" t="s">
-        <v>2616</v>
+        <v>2640</v>
       </c>
       <c r="H508" t="s">
-        <v>2617</v>
+        <v>2641</v>
       </c>
       <c r="I508" t="s">
-        <v>2618</v>
+        <v>2642</v>
       </c>
       <c r="J508" t="s">
-        <v>2619</v>
+        <v>2643</v>
       </c>
       <c r="K508">
         <v>2004</v>
@@ -35529,19 +36658,19 @@
         <v>43</v>
       </c>
       <c r="B509" t="s">
-        <v>2620</v>
+        <v>2644</v>
       </c>
       <c r="G509" t="s">
-        <v>2621</v>
+        <v>2645</v>
       </c>
       <c r="H509" t="s">
-        <v>2622</v>
+        <v>2646</v>
       </c>
       <c r="I509" t="s">
         <v>481</v>
       </c>
       <c r="J509" t="s">
-        <v>2623</v>
+        <v>2647</v>
       </c>
       <c r="K509">
         <v>1989</v>
@@ -35553,19 +36682,19 @@
         <v>43</v>
       </c>
       <c r="B510" t="s">
-        <v>2624</v>
+        <v>2648</v>
       </c>
       <c r="G510" t="s">
-        <v>2625</v>
+        <v>2649</v>
       </c>
       <c r="H510" t="s">
-        <v>2626</v>
+        <v>2650</v>
       </c>
       <c r="I510" t="s">
-        <v>2627</v>
+        <v>2651</v>
       </c>
       <c r="J510" t="s">
-        <v>2628</v>
+        <v>2652</v>
       </c>
       <c r="K510">
         <v>2005</v>
@@ -35577,19 +36706,19 @@
         <v>43</v>
       </c>
       <c r="B511" t="s">
-        <v>2629</v>
+        <v>2653</v>
       </c>
       <c r="G511" t="s">
-        <v>2630</v>
+        <v>2654</v>
       </c>
       <c r="H511" t="s">
-        <v>2631</v>
+        <v>2655</v>
       </c>
       <c r="I511" t="s">
         <v>403</v>
       </c>
       <c r="J511" t="s">
-        <v>2632</v>
+        <v>2656</v>
       </c>
       <c r="K511">
         <v>2025</v>
@@ -35601,19 +36730,19 @@
         <v>43</v>
       </c>
       <c r="B512" t="s">
-        <v>2633</v>
+        <v>2657</v>
       </c>
       <c r="G512" t="s">
-        <v>2634</v>
+        <v>2658</v>
       </c>
       <c r="H512" t="s">
-        <v>2635</v>
+        <v>2659</v>
       </c>
       <c r="I512" t="s">
         <v>1652</v>
       </c>
       <c r="J512" t="s">
-        <v>2636</v>
+        <v>2660</v>
       </c>
       <c r="K512">
         <v>2018</v>
@@ -35625,19 +36754,19 @@
         <v>43</v>
       </c>
       <c r="B513" t="s">
-        <v>2637</v>
+        <v>2661</v>
       </c>
       <c r="G513" t="s">
-        <v>2638</v>
+        <v>2662</v>
       </c>
       <c r="H513" t="s">
-        <v>2639</v>
+        <v>2663</v>
       </c>
       <c r="I513" t="s">
         <v>1499</v>
       </c>
       <c r="J513" t="s">
-        <v>2640</v>
+        <v>2664</v>
       </c>
       <c r="K513">
         <v>2011</v>
@@ -35649,19 +36778,19 @@
         <v>43</v>
       </c>
       <c r="B514" t="s">
-        <v>2641</v>
+        <v>2665</v>
       </c>
       <c r="G514" t="s">
-        <v>2642</v>
+        <v>2666</v>
       </c>
       <c r="H514" t="s">
-        <v>2643</v>
+        <v>2667</v>
       </c>
       <c r="I514" t="s">
         <v>1242</v>
       </c>
       <c r="J514" t="s">
-        <v>2644</v>
+        <v>2668</v>
       </c>
       <c r="K514">
         <v>2024</v>
@@ -35673,19 +36802,19 @@
         <v>43</v>
       </c>
       <c r="B515" t="s">
-        <v>2645</v>
+        <v>2669</v>
       </c>
       <c r="G515" t="s">
-        <v>2646</v>
+        <v>2670</v>
       </c>
       <c r="H515" t="s">
-        <v>2647</v>
+        <v>2671</v>
       </c>
       <c r="I515" t="s">
         <v>1783</v>
       </c>
       <c r="J515" t="s">
-        <v>2648</v>
+        <v>2672</v>
       </c>
       <c r="K515">
         <v>2023</v>
@@ -35697,19 +36826,19 @@
         <v>43</v>
       </c>
       <c r="B516" t="s">
-        <v>2649</v>
+        <v>2673</v>
       </c>
       <c r="G516" t="s">
-        <v>2650</v>
+        <v>2674</v>
       </c>
       <c r="H516" t="s">
-        <v>2651</v>
+        <v>2675</v>
       </c>
       <c r="I516" t="s">
-        <v>2652</v>
+        <v>2676</v>
       </c>
       <c r="J516" t="s">
-        <v>2653</v>
+        <v>2677</v>
       </c>
       <c r="K516">
         <v>2010</v>
@@ -35721,19 +36850,19 @@
         <v>43</v>
       </c>
       <c r="B517" t="s">
-        <v>2654</v>
+        <v>2678</v>
       </c>
       <c r="G517" t="s">
-        <v>2655</v>
+        <v>2679</v>
       </c>
       <c r="H517" t="s">
-        <v>2656</v>
+        <v>2680</v>
       </c>
       <c r="I517" t="s">
-        <v>2657</v>
+        <v>2681</v>
       </c>
       <c r="J517" t="s">
-        <v>2658</v>
+        <v>2682</v>
       </c>
       <c r="K517">
         <v>2019</v>
@@ -35745,19 +36874,19 @@
         <v>43</v>
       </c>
       <c r="B518" t="s">
-        <v>2659</v>
+        <v>2683</v>
       </c>
       <c r="G518" t="s">
-        <v>2660</v>
+        <v>2684</v>
       </c>
       <c r="H518" t="s">
-        <v>2661</v>
+        <v>2685</v>
       </c>
       <c r="I518" t="s">
         <v>51</v>
       </c>
       <c r="J518" t="s">
-        <v>2662</v>
+        <v>2686</v>
       </c>
       <c r="K518">
         <v>1986</v>
@@ -35769,19 +36898,19 @@
         <v>43</v>
       </c>
       <c r="B519" t="s">
-        <v>2663</v>
+        <v>2687</v>
       </c>
       <c r="G519" t="s">
-        <v>2664</v>
+        <v>2688</v>
       </c>
       <c r="H519" t="s">
-        <v>2665</v>
+        <v>2689</v>
       </c>
       <c r="I519" t="s">
-        <v>2666</v>
+        <v>2690</v>
       </c>
       <c r="J519" t="s">
-        <v>2667</v>
+        <v>2691</v>
       </c>
       <c r="K519">
         <v>2018</v>
@@ -35793,19 +36922,19 @@
         <v>43</v>
       </c>
       <c r="B520" t="s">
-        <v>2668</v>
+        <v>2692</v>
       </c>
       <c r="G520" t="s">
-        <v>2669</v>
+        <v>2693</v>
       </c>
       <c r="H520" t="s">
-        <v>2670</v>
+        <v>2694</v>
       </c>
       <c r="I520" t="s">
-        <v>2671</v>
+        <v>2695</v>
       </c>
       <c r="J520" t="s">
-        <v>2672</v>
+        <v>2696</v>
       </c>
       <c r="K520">
         <v>2006</v>
@@ -35817,19 +36946,19 @@
         <v>43</v>
       </c>
       <c r="B521" t="s">
-        <v>2673</v>
+        <v>2697</v>
       </c>
       <c r="G521" t="s">
-        <v>2674</v>
+        <v>2698</v>
       </c>
       <c r="H521" t="s">
-        <v>2675</v>
+        <v>2699</v>
       </c>
       <c r="I521" t="s">
-        <v>2676</v>
+        <v>2700</v>
       </c>
       <c r="J521" t="s">
-        <v>2677</v>
+        <v>2701</v>
       </c>
       <c r="K521">
         <v>2008</v>
@@ -35841,19 +36970,19 @@
         <v>43</v>
       </c>
       <c r="B522" t="s">
-        <v>2678</v>
+        <v>2702</v>
       </c>
       <c r="G522" t="s">
-        <v>2679</v>
+        <v>2703</v>
       </c>
       <c r="H522" t="s">
-        <v>2680</v>
+        <v>2704</v>
       </c>
       <c r="I522" t="s">
         <v>1196</v>
       </c>
       <c r="J522" t="s">
-        <v>2681</v>
+        <v>2705</v>
       </c>
       <c r="K522">
         <v>2019</v>
@@ -35865,19 +36994,19 @@
         <v>43</v>
       </c>
       <c r="B523" t="s">
-        <v>2682</v>
+        <v>2706</v>
       </c>
       <c r="G523" t="s">
-        <v>2683</v>
+        <v>2707</v>
       </c>
       <c r="H523" t="s">
-        <v>2684</v>
+        <v>2708</v>
       </c>
       <c r="I523" t="s">
-        <v>2685</v>
+        <v>2709</v>
       </c>
       <c r="J523" t="s">
-        <v>2686</v>
+        <v>2710</v>
       </c>
       <c r="K523">
         <v>2012</v>
@@ -35889,19 +37018,19 @@
         <v>43</v>
       </c>
       <c r="B524" t="s">
-        <v>2687</v>
+        <v>2711</v>
       </c>
       <c r="G524" t="s">
-        <v>2688</v>
+        <v>2712</v>
       </c>
       <c r="H524" t="s">
-        <v>2689</v>
+        <v>2713</v>
       </c>
       <c r="I524" t="s">
         <v>1729</v>
       </c>
       <c r="J524" t="s">
-        <v>2690</v>
+        <v>2714</v>
       </c>
       <c r="K524">
         <v>1997</v>
@@ -35913,19 +37042,19 @@
         <v>43</v>
       </c>
       <c r="B525" t="s">
-        <v>2691</v>
+        <v>2715</v>
       </c>
       <c r="G525" t="s">
-        <v>2692</v>
+        <v>2716</v>
       </c>
       <c r="H525" t="s">
-        <v>2693</v>
+        <v>2717</v>
       </c>
       <c r="I525" t="s">
-        <v>2694</v>
+        <v>2718</v>
       </c>
       <c r="J525" t="s">
-        <v>2695</v>
+        <v>2719</v>
       </c>
       <c r="K525">
         <v>2023</v>
@@ -35937,19 +37066,19 @@
         <v>43</v>
       </c>
       <c r="B526" t="s">
-        <v>2696</v>
+        <v>2720</v>
       </c>
       <c r="G526" t="s">
-        <v>2697</v>
+        <v>2721</v>
       </c>
       <c r="H526" t="s">
-        <v>2698</v>
+        <v>2722</v>
       </c>
       <c r="I526" t="s">
         <v>329</v>
       </c>
       <c r="J526" t="s">
-        <v>2699</v>
+        <v>2723</v>
       </c>
       <c r="K526">
         <v>2021</v>
@@ -35961,19 +37090,19 @@
         <v>43</v>
       </c>
       <c r="B527" t="s">
-        <v>2700</v>
+        <v>2724</v>
       </c>
       <c r="G527" t="s">
-        <v>2701</v>
+        <v>2725</v>
       </c>
       <c r="H527" t="s">
-        <v>2702</v>
+        <v>2726</v>
       </c>
       <c r="I527" t="s">
-        <v>2703</v>
+        <v>2727</v>
       </c>
       <c r="J527" t="s">
-        <v>2704</v>
+        <v>2728</v>
       </c>
       <c r="K527">
         <v>1989</v>
@@ -35985,19 +37114,19 @@
         <v>43</v>
       </c>
       <c r="B528" t="s">
-        <v>2705</v>
+        <v>2729</v>
       </c>
       <c r="G528" t="s">
-        <v>2706</v>
+        <v>2730</v>
       </c>
       <c r="H528" t="s">
-        <v>2707</v>
+        <v>2731</v>
       </c>
       <c r="I528" t="s">
         <v>1394</v>
       </c>
       <c r="J528" t="s">
-        <v>2708</v>
+        <v>2732</v>
       </c>
       <c r="K528">
         <v>2001</v>
@@ -36009,19 +37138,19 @@
         <v>43</v>
       </c>
       <c r="B529" t="s">
-        <v>2709</v>
+        <v>2733</v>
       </c>
       <c r="G529" t="s">
-        <v>2710</v>
+        <v>2734</v>
       </c>
       <c r="H529" t="s">
-        <v>2711</v>
+        <v>2735</v>
       </c>
       <c r="I529" t="s">
-        <v>2712</v>
+        <v>2736</v>
       </c>
       <c r="J529" t="s">
-        <v>2713</v>
+        <v>2737</v>
       </c>
       <c r="K529">
         <v>2024</v>
@@ -36033,19 +37162,19 @@
         <v>43</v>
       </c>
       <c r="B530" t="s">
-        <v>2714</v>
+        <v>2738</v>
       </c>
       <c r="G530" t="s">
-        <v>2715</v>
+        <v>2739</v>
       </c>
       <c r="H530" t="s">
-        <v>2716</v>
+        <v>2740</v>
       </c>
       <c r="I530" t="s">
-        <v>2717</v>
+        <v>2741</v>
       </c>
       <c r="J530" t="s">
-        <v>2718</v>
+        <v>2742</v>
       </c>
       <c r="K530">
         <v>2012</v>
@@ -36057,19 +37186,19 @@
         <v>43</v>
       </c>
       <c r="B531" t="s">
-        <v>2719</v>
+        <v>2743</v>
       </c>
       <c r="G531" t="s">
-        <v>2720</v>
+        <v>2744</v>
       </c>
       <c r="H531" t="s">
-        <v>2721</v>
+        <v>2745</v>
       </c>
       <c r="I531" t="s">
         <v>549</v>
       </c>
       <c r="J531" t="s">
-        <v>2722</v>
+        <v>2746</v>
       </c>
       <c r="K531">
         <v>2024</v>
@@ -36081,19 +37210,19 @@
         <v>43</v>
       </c>
       <c r="B532" t="s">
-        <v>2723</v>
+        <v>2747</v>
       </c>
       <c r="G532" t="s">
-        <v>2724</v>
+        <v>2748</v>
       </c>
       <c r="H532" t="s">
-        <v>2725</v>
+        <v>2749</v>
       </c>
       <c r="I532" t="s">
         <v>100</v>
       </c>
       <c r="J532" t="s">
-        <v>2726</v>
+        <v>2750</v>
       </c>
       <c r="K532">
         <v>2023</v>
@@ -36105,19 +37234,19 @@
         <v>43</v>
       </c>
       <c r="B533" t="s">
-        <v>2727</v>
+        <v>2751</v>
       </c>
       <c r="G533" t="s">
-        <v>2728</v>
+        <v>2752</v>
       </c>
       <c r="H533" t="s">
-        <v>2729</v>
+        <v>2753</v>
       </c>
       <c r="I533" t="s">
         <v>154</v>
       </c>
       <c r="J533" t="s">
-        <v>2730</v>
+        <v>2754</v>
       </c>
       <c r="K533">
         <v>2010</v>
@@ -36129,19 +37258,19 @@
         <v>43</v>
       </c>
       <c r="B534" t="s">
-        <v>2731</v>
+        <v>2755</v>
       </c>
       <c r="G534" t="s">
-        <v>2732</v>
+        <v>2756</v>
       </c>
       <c r="H534" t="s">
-        <v>2733</v>
+        <v>2757</v>
       </c>
       <c r="I534" t="s">
         <v>687</v>
       </c>
       <c r="J534" t="s">
-        <v>2734</v>
+        <v>2758</v>
       </c>
       <c r="K534">
         <v>2017</v>
@@ -36153,19 +37282,19 @@
         <v>43</v>
       </c>
       <c r="B535" t="s">
-        <v>2735</v>
+        <v>2759</v>
       </c>
       <c r="G535" t="s">
-        <v>2736</v>
+        <v>2760</v>
       </c>
       <c r="H535" t="s">
-        <v>2737</v>
+        <v>2761</v>
       </c>
       <c r="I535" t="s">
-        <v>2738</v>
+        <v>2762</v>
       </c>
       <c r="J535" t="s">
-        <v>2739</v>
+        <v>2763</v>
       </c>
       <c r="K535">
         <v>2000</v>
@@ -36177,19 +37306,19 @@
         <v>43</v>
       </c>
       <c r="B536" t="s">
-        <v>2740</v>
+        <v>2764</v>
       </c>
       <c r="G536" t="s">
-        <v>2741</v>
+        <v>2765</v>
       </c>
       <c r="H536" t="s">
-        <v>2742</v>
+        <v>2766</v>
       </c>
       <c r="I536" t="s">
         <v>653</v>
       </c>
       <c r="J536" t="s">
-        <v>2743</v>
+        <v>2767</v>
       </c>
       <c r="K536">
         <v>2016</v>
@@ -36201,19 +37330,19 @@
         <v>43</v>
       </c>
       <c r="B537" t="s">
-        <v>2744</v>
+        <v>2768</v>
       </c>
       <c r="G537" t="s">
-        <v>2745</v>
+        <v>2769</v>
       </c>
       <c r="H537" t="s">
-        <v>2746</v>
+        <v>2770</v>
       </c>
       <c r="I537" t="s">
         <v>426</v>
       </c>
       <c r="J537" t="s">
-        <v>2747</v>
+        <v>2771</v>
       </c>
       <c r="K537">
         <v>2006</v>
@@ -36225,19 +37354,19 @@
         <v>43</v>
       </c>
       <c r="B538" t="s">
-        <v>2748</v>
+        <v>2772</v>
       </c>
       <c r="G538" t="s">
-        <v>2749</v>
+        <v>2773</v>
       </c>
       <c r="H538" t="s">
-        <v>2750</v>
+        <v>2774</v>
       </c>
       <c r="I538" t="s">
-        <v>2751</v>
+        <v>2775</v>
       </c>
       <c r="J538" t="s">
-        <v>2752</v>
+        <v>2776</v>
       </c>
       <c r="K538">
         <v>2018</v>
@@ -36249,19 +37378,19 @@
         <v>43</v>
       </c>
       <c r="B539" t="s">
-        <v>2753</v>
+        <v>2777</v>
       </c>
       <c r="G539" t="s">
-        <v>2754</v>
+        <v>2778</v>
       </c>
       <c r="H539" t="s">
-        <v>2755</v>
+        <v>2779</v>
       </c>
       <c r="I539" t="s">
         <v>357</v>
       </c>
       <c r="J539" t="s">
-        <v>2756</v>
+        <v>2780</v>
       </c>
       <c r="K539">
         <v>2015</v>
@@ -36273,19 +37402,19 @@
         <v>43</v>
       </c>
       <c r="B540" t="s">
-        <v>2757</v>
+        <v>2781</v>
       </c>
       <c r="G540" t="s">
-        <v>2758</v>
+        <v>2782</v>
       </c>
       <c r="H540" t="s">
-        <v>2759</v>
+        <v>2783</v>
       </c>
       <c r="I540" t="s">
         <v>51</v>
       </c>
       <c r="J540" t="s">
-        <v>2760</v>
+        <v>2784</v>
       </c>
       <c r="K540">
         <v>1988</v>
@@ -36297,19 +37426,19 @@
         <v>43</v>
       </c>
       <c r="B541" t="s">
-        <v>2761</v>
+        <v>2785</v>
       </c>
       <c r="G541" t="s">
-        <v>2762</v>
+        <v>2786</v>
       </c>
       <c r="H541" t="s">
-        <v>2763</v>
+        <v>2787</v>
       </c>
       <c r="I541" t="s">
         <v>307</v>
       </c>
       <c r="J541" t="s">
-        <v>2764</v>
+        <v>2788</v>
       </c>
       <c r="K541">
         <v>2016</v>
@@ -36321,19 +37450,19 @@
         <v>43</v>
       </c>
       <c r="B542" t="s">
-        <v>2765</v>
+        <v>2789</v>
       </c>
       <c r="G542" t="s">
-        <v>2766</v>
+        <v>2790</v>
       </c>
       <c r="H542" t="s">
-        <v>2767</v>
+        <v>2791</v>
       </c>
       <c r="I542" t="s">
         <v>237</v>
       </c>
       <c r="J542" t="s">
-        <v>2768</v>
+        <v>2792</v>
       </c>
       <c r="K542">
         <v>2022</v>
@@ -36345,19 +37474,19 @@
         <v>43</v>
       </c>
       <c r="B543" t="s">
-        <v>2769</v>
+        <v>2793</v>
       </c>
       <c r="G543" t="s">
-        <v>2770</v>
+        <v>2794</v>
       </c>
       <c r="H543" t="s">
-        <v>2771</v>
+        <v>2795</v>
       </c>
       <c r="I543" t="s">
         <v>346</v>
       </c>
       <c r="J543" t="s">
-        <v>2772</v>
+        <v>2796</v>
       </c>
       <c r="K543">
         <v>2025</v>
@@ -36369,19 +37498,19 @@
         <v>43</v>
       </c>
       <c r="B544" t="s">
-        <v>2773</v>
+        <v>2797</v>
       </c>
       <c r="G544" t="s">
-        <v>2774</v>
+        <v>2798</v>
       </c>
       <c r="H544" t="s">
-        <v>2775</v>
+        <v>2799</v>
       </c>
       <c r="I544" t="s">
-        <v>2776</v>
+        <v>2800</v>
       </c>
       <c r="J544" t="s">
-        <v>2777</v>
+        <v>2801</v>
       </c>
       <c r="K544">
         <v>1986</v>
@@ -36393,19 +37522,19 @@
         <v>43</v>
       </c>
       <c r="B545" t="s">
-        <v>2778</v>
+        <v>2802</v>
       </c>
       <c r="G545" t="s">
-        <v>2779</v>
+        <v>2803</v>
       </c>
       <c r="H545" t="s">
-        <v>2780</v>
+        <v>2804</v>
       </c>
       <c r="I545" t="s">
         <v>900</v>
       </c>
       <c r="J545" t="s">
-        <v>2781</v>
+        <v>2805</v>
       </c>
       <c r="K545">
         <v>2014</v>
@@ -36417,19 +37546,19 @@
         <v>43</v>
       </c>
       <c r="B546" t="s">
-        <v>2782</v>
+        <v>2806</v>
       </c>
       <c r="G546" t="s">
-        <v>2783</v>
+        <v>2807</v>
       </c>
       <c r="H546" t="s">
-        <v>2784</v>
+        <v>2808</v>
       </c>
       <c r="I546" t="s">
-        <v>2666</v>
+        <v>2690</v>
       </c>
       <c r="J546" t="s">
-        <v>2785</v>
+        <v>2809</v>
       </c>
       <c r="K546">
         <v>2019</v>
@@ -36441,19 +37570,19 @@
         <v>43</v>
       </c>
       <c r="B547" t="s">
-        <v>2786</v>
+        <v>2810</v>
       </c>
       <c r="G547" t="s">
-        <v>2787</v>
+        <v>2811</v>
       </c>
       <c r="H547" t="s">
-        <v>2788</v>
+        <v>2812</v>
       </c>
       <c r="I547" t="s">
         <v>266</v>
       </c>
       <c r="J547" t="s">
-        <v>2789</v>
+        <v>2813</v>
       </c>
       <c r="K547">
         <v>2018</v>
@@ -36465,19 +37594,19 @@
         <v>43</v>
       </c>
       <c r="B548" t="s">
-        <v>2790</v>
+        <v>2814</v>
       </c>
       <c r="G548" t="s">
-        <v>2791</v>
+        <v>2815</v>
       </c>
       <c r="H548" t="s">
-        <v>2792</v>
+        <v>2816</v>
       </c>
       <c r="I548" t="s">
         <v>723</v>
       </c>
       <c r="J548" t="s">
-        <v>2793</v>
+        <v>2817</v>
       </c>
       <c r="K548">
         <v>1979</v>
@@ -36489,19 +37618,19 @@
         <v>43</v>
       </c>
       <c r="B549" t="s">
-        <v>2794</v>
+        <v>2818</v>
       </c>
       <c r="G549" t="s">
-        <v>2795</v>
+        <v>2819</v>
       </c>
       <c r="H549" t="s">
-        <v>2796</v>
+        <v>2820</v>
       </c>
       <c r="I549" t="s">
         <v>51</v>
       </c>
       <c r="J549" t="s">
-        <v>2797</v>
+        <v>2821</v>
       </c>
       <c r="K549">
         <v>2023</v>
@@ -36513,19 +37642,19 @@
         <v>43</v>
       </c>
       <c r="B550" t="s">
-        <v>2798</v>
+        <v>2822</v>
       </c>
       <c r="G550" t="s">
-        <v>2799</v>
+        <v>2823</v>
       </c>
       <c r="H550" t="s">
-        <v>2800</v>
+        <v>2824</v>
       </c>
       <c r="I550" t="s">
         <v>148</v>
       </c>
       <c r="J550" t="s">
-        <v>2801</v>
+        <v>2825</v>
       </c>
       <c r="K550">
         <v>2018</v>
@@ -36537,19 +37666,19 @@
         <v>43</v>
       </c>
       <c r="B551" t="s">
-        <v>2802</v>
+        <v>2826</v>
       </c>
       <c r="G551" t="s">
-        <v>2803</v>
+        <v>2827</v>
       </c>
       <c r="H551" t="s">
-        <v>2804</v>
+        <v>2828</v>
       </c>
       <c r="I551" t="s">
-        <v>2805</v>
+        <v>2829</v>
       </c>
       <c r="J551" t="s">
-        <v>2806</v>
+        <v>2830</v>
       </c>
       <c r="K551">
         <v>2015</v>
@@ -36561,19 +37690,19 @@
         <v>43</v>
       </c>
       <c r="B552" t="s">
-        <v>2807</v>
+        <v>2831</v>
       </c>
       <c r="G552" t="s">
-        <v>2808</v>
+        <v>2832</v>
       </c>
       <c r="H552" t="s">
-        <v>2809</v>
+        <v>2833</v>
       </c>
       <c r="I552" t="s">
-        <v>2810</v>
+        <v>2834</v>
       </c>
       <c r="J552" t="s">
-        <v>2811</v>
+        <v>2835</v>
       </c>
       <c r="K552">
         <v>2021</v>
@@ -36585,19 +37714,19 @@
         <v>43</v>
       </c>
       <c r="B553" t="s">
-        <v>2812</v>
+        <v>2836</v>
       </c>
       <c r="G553" t="s">
-        <v>2813</v>
+        <v>2837</v>
       </c>
       <c r="H553" t="s">
-        <v>2814</v>
+        <v>2838</v>
       </c>
       <c r="I553" t="s">
-        <v>2815</v>
+        <v>2839</v>
       </c>
       <c r="J553" t="s">
-        <v>2816</v>
+        <v>2840</v>
       </c>
       <c r="K553">
         <v>2010</v>
@@ -36609,19 +37738,19 @@
         <v>43</v>
       </c>
       <c r="B554" t="s">
-        <v>2817</v>
+        <v>2841</v>
       </c>
       <c r="G554" t="s">
-        <v>2818</v>
+        <v>2842</v>
       </c>
       <c r="H554" t="s">
-        <v>2819</v>
+        <v>2843</v>
       </c>
       <c r="I554" t="s">
-        <v>2820</v>
+        <v>2844</v>
       </c>
       <c r="J554" t="s">
-        <v>2821</v>
+        <v>2845</v>
       </c>
       <c r="K554">
         <v>2006</v>
@@ -36633,19 +37762,19 @@
         <v>43</v>
       </c>
       <c r="B555" t="s">
-        <v>2822</v>
+        <v>2846</v>
       </c>
       <c r="G555" t="s">
-        <v>2823</v>
+        <v>2847</v>
       </c>
       <c r="H555" t="s">
-        <v>2824</v>
+        <v>2848</v>
       </c>
       <c r="I555" t="s">
         <v>426</v>
       </c>
       <c r="J555" t="s">
-        <v>2825</v>
+        <v>2849</v>
       </c>
       <c r="K555">
         <v>2019</v>
@@ -36657,19 +37786,19 @@
         <v>43</v>
       </c>
       <c r="B556" t="s">
-        <v>2826</v>
+        <v>2850</v>
       </c>
       <c r="G556" t="s">
-        <v>2827</v>
+        <v>2851</v>
       </c>
       <c r="H556" t="s">
-        <v>2828</v>
+        <v>2852</v>
       </c>
       <c r="I556" t="s">
-        <v>2829</v>
+        <v>2853</v>
       </c>
       <c r="J556" t="s">
-        <v>2830</v>
+        <v>2854</v>
       </c>
       <c r="K556">
         <v>2022</v>
@@ -36681,19 +37810,19 @@
         <v>43</v>
       </c>
       <c r="B557" t="s">
-        <v>2831</v>
+        <v>2855</v>
       </c>
       <c r="G557" t="s">
-        <v>2832</v>
+        <v>2856</v>
       </c>
       <c r="H557" t="s">
-        <v>2833</v>
+        <v>2857</v>
       </c>
       <c r="I557" t="s">
         <v>357</v>
       </c>
       <c r="J557" t="s">
-        <v>2834</v>
+        <v>2858</v>
       </c>
       <c r="K557">
         <v>2006</v>
@@ -36705,19 +37834,19 @@
         <v>43</v>
       </c>
       <c r="B558" t="s">
-        <v>2835</v>
+        <v>2859</v>
       </c>
       <c r="G558" t="s">
-        <v>2836</v>
+        <v>2860</v>
       </c>
       <c r="H558" t="s">
-        <v>2837</v>
+        <v>2861</v>
       </c>
       <c r="I558" t="s">
         <v>237</v>
       </c>
       <c r="J558" t="s">
-        <v>2838</v>
+        <v>2862</v>
       </c>
       <c r="K558">
         <v>2019</v>
@@ -36729,19 +37858,19 @@
         <v>43</v>
       </c>
       <c r="B559" t="s">
-        <v>2839</v>
+        <v>2863</v>
       </c>
       <c r="G559" t="s">
-        <v>2840</v>
+        <v>2864</v>
       </c>
       <c r="H559" t="s">
-        <v>2841</v>
+        <v>2865</v>
       </c>
       <c r="I559" t="s">
-        <v>2842</v>
+        <v>2866</v>
       </c>
       <c r="J559" t="s">
-        <v>2843</v>
+        <v>2867</v>
       </c>
       <c r="K559">
         <v>2015</v>
@@ -36753,19 +37882,19 @@
         <v>43</v>
       </c>
       <c r="B560" t="s">
-        <v>2844</v>
+        <v>2868</v>
       </c>
       <c r="G560" t="s">
-        <v>2845</v>
+        <v>2869</v>
       </c>
       <c r="H560" t="s">
-        <v>2846</v>
+        <v>2870</v>
       </c>
       <c r="I560" t="s">
         <v>1014</v>
       </c>
       <c r="J560" t="s">
-        <v>2847</v>
+        <v>2871</v>
       </c>
       <c r="K560">
         <v>2026</v>
@@ -36777,19 +37906,19 @@
         <v>43</v>
       </c>
       <c r="B561" t="s">
-        <v>2848</v>
+        <v>2872</v>
       </c>
       <c r="G561" t="s">
-        <v>2849</v>
+        <v>2873</v>
       </c>
       <c r="H561" t="s">
-        <v>2850</v>
+        <v>2874</v>
       </c>
       <c r="I561" t="s">
         <v>51</v>
       </c>
       <c r="J561" t="s">
-        <v>2851</v>
+        <v>2875</v>
       </c>
       <c r="K561">
         <v>2023</v>
@@ -36801,19 +37930,19 @@
         <v>43</v>
       </c>
       <c r="B562" t="s">
-        <v>2852</v>
+        <v>2876</v>
       </c>
       <c r="G562" t="s">
-        <v>2853</v>
+        <v>2877</v>
       </c>
       <c r="H562" t="s">
-        <v>2854</v>
+        <v>2878</v>
       </c>
       <c r="I562" t="s">
         <v>51</v>
       </c>
       <c r="J562" t="s">
-        <v>2855</v>
+        <v>2879</v>
       </c>
       <c r="K562">
         <v>2000</v>
@@ -36825,19 +37954,19 @@
         <v>43</v>
       </c>
       <c r="B563" t="s">
-        <v>2856</v>
+        <v>2880</v>
       </c>
       <c r="G563" t="s">
-        <v>2857</v>
+        <v>2881</v>
       </c>
       <c r="H563" t="s">
-        <v>2858</v>
+        <v>2882</v>
       </c>
       <c r="I563" t="s">
         <v>51</v>
       </c>
       <c r="J563" t="s">
-        <v>2859</v>
+        <v>2883</v>
       </c>
       <c r="K563">
         <v>2016</v>
@@ -36849,19 +37978,19 @@
         <v>43</v>
       </c>
       <c r="B564" t="s">
-        <v>2860</v>
+        <v>2884</v>
       </c>
       <c r="G564" t="s">
-        <v>2861</v>
+        <v>2885</v>
       </c>
       <c r="H564" t="s">
-        <v>2862</v>
+        <v>2886</v>
       </c>
       <c r="I564" t="s">
         <v>1461</v>
       </c>
       <c r="J564" t="s">
-        <v>2863</v>
+        <v>2887</v>
       </c>
       <c r="K564">
         <v>2026</v>
@@ -36873,19 +38002,19 @@
         <v>43</v>
       </c>
       <c r="B565" t="s">
-        <v>2864</v>
+        <v>2888</v>
       </c>
       <c r="G565" t="s">
-        <v>2865</v>
+        <v>2889</v>
       </c>
       <c r="H565" t="s">
-        <v>2866</v>
+        <v>2890</v>
       </c>
       <c r="I565" t="s">
-        <v>2867</v>
+        <v>2891</v>
       </c>
       <c r="J565" t="s">
-        <v>2868</v>
+        <v>2892</v>
       </c>
       <c r="K565">
         <v>2024</v>
@@ -36897,19 +38026,19 @@
         <v>43</v>
       </c>
       <c r="B566" t="s">
-        <v>2869</v>
+        <v>2893</v>
       </c>
       <c r="G566" t="s">
-        <v>2870</v>
+        <v>2894</v>
       </c>
       <c r="H566" t="s">
-        <v>2871</v>
+        <v>2895</v>
       </c>
       <c r="I566" t="s">
         <v>459</v>
       </c>
       <c r="J566" t="s">
-        <v>2872</v>
+        <v>2896</v>
       </c>
       <c r="K566">
         <v>2019</v>
@@ -36921,19 +38050,19 @@
         <v>43</v>
       </c>
       <c r="B567" t="s">
-        <v>2873</v>
+        <v>2897</v>
       </c>
       <c r="G567" t="s">
-        <v>2874</v>
+        <v>2898</v>
       </c>
       <c r="H567" t="s">
-        <v>2875</v>
+        <v>2899</v>
       </c>
       <c r="I567" t="s">
         <v>915</v>
       </c>
       <c r="J567" t="s">
-        <v>2876</v>
+        <v>2900</v>
       </c>
       <c r="K567">
         <v>2020</v>
@@ -36945,19 +38074,19 @@
         <v>43</v>
       </c>
       <c r="B568" t="s">
-        <v>2877</v>
+        <v>2901</v>
       </c>
       <c r="G568" t="s">
-        <v>2878</v>
+        <v>2902</v>
       </c>
       <c r="H568" t="s">
-        <v>2879</v>
+        <v>2903</v>
       </c>
       <c r="I568" t="s">
-        <v>2880</v>
+        <v>2904</v>
       </c>
       <c r="J568" t="s">
-        <v>2881</v>
+        <v>2905</v>
       </c>
       <c r="K568">
         <v>2014</v>
@@ -36969,19 +38098,19 @@
         <v>43</v>
       </c>
       <c r="B569" t="s">
-        <v>2882</v>
+        <v>2906</v>
       </c>
       <c r="G569" t="s">
-        <v>2883</v>
+        <v>2907</v>
       </c>
       <c r="H569" t="s">
-        <v>2884</v>
+        <v>2908</v>
       </c>
       <c r="I569" t="s">
         <v>51</v>
       </c>
       <c r="J569" t="s">
-        <v>2885</v>
+        <v>2909</v>
       </c>
       <c r="K569">
         <v>2004</v>
@@ -36993,19 +38122,19 @@
         <v>43</v>
       </c>
       <c r="B570" t="s">
-        <v>2886</v>
+        <v>2910</v>
       </c>
       <c r="G570" t="s">
-        <v>2887</v>
+        <v>2911</v>
       </c>
       <c r="H570" t="s">
-        <v>2888</v>
+        <v>2912</v>
       </c>
       <c r="I570" t="s">
         <v>51</v>
       </c>
       <c r="J570" t="s">
-        <v>2889</v>
+        <v>2913</v>
       </c>
       <c r="K570">
         <v>2015</v>
@@ -37017,19 +38146,19 @@
         <v>43</v>
       </c>
       <c r="B571" t="s">
-        <v>2890</v>
+        <v>2914</v>
       </c>
       <c r="G571" t="s">
-        <v>2891</v>
+        <v>2915</v>
       </c>
       <c r="H571" t="s">
-        <v>2892</v>
+        <v>2916</v>
       </c>
       <c r="I571" t="s">
         <v>979</v>
       </c>
       <c r="J571" t="s">
-        <v>2893</v>
+        <v>2917</v>
       </c>
       <c r="K571">
         <v>2015</v>
@@ -37041,19 +38170,19 @@
         <v>43</v>
       </c>
       <c r="B572" t="s">
-        <v>2894</v>
+        <v>2918</v>
       </c>
       <c r="G572" t="s">
-        <v>2895</v>
+        <v>2919</v>
       </c>
       <c r="H572" t="s">
-        <v>2896</v>
+        <v>2920</v>
       </c>
       <c r="I572" t="s">
-        <v>2897</v>
+        <v>2921</v>
       </c>
       <c r="J572" t="s">
-        <v>2898</v>
+        <v>2922</v>
       </c>
       <c r="K572">
         <v>2013</v>
@@ -37065,19 +38194,19 @@
         <v>43</v>
       </c>
       <c r="B573" t="s">
-        <v>2899</v>
+        <v>2923</v>
       </c>
       <c r="G573" t="s">
-        <v>2900</v>
+        <v>2924</v>
       </c>
       <c r="H573" t="s">
-        <v>2901</v>
+        <v>2925</v>
       </c>
       <c r="I573" t="s">
         <v>692</v>
       </c>
       <c r="J573" t="s">
-        <v>2902</v>
+        <v>2926</v>
       </c>
       <c r="K573">
         <v>2017</v>
@@ -37089,19 +38218,19 @@
         <v>43</v>
       </c>
       <c r="B574" t="s">
-        <v>2903</v>
+        <v>2927</v>
       </c>
       <c r="G574" t="s">
-        <v>2904</v>
+        <v>2928</v>
       </c>
       <c r="H574" t="s">
-        <v>2905</v>
+        <v>2929</v>
       </c>
       <c r="I574" t="s">
         <v>51</v>
       </c>
       <c r="J574" t="s">
-        <v>2906</v>
+        <v>2930</v>
       </c>
       <c r="K574">
         <v>1995</v>
@@ -37113,19 +38242,19 @@
         <v>43</v>
       </c>
       <c r="B575" t="s">
-        <v>2907</v>
+        <v>2931</v>
       </c>
       <c r="G575" t="s">
-        <v>2908</v>
+        <v>2932</v>
       </c>
       <c r="H575" t="s">
-        <v>2909</v>
+        <v>2933</v>
       </c>
       <c r="I575" t="s">
-        <v>2910</v>
+        <v>2934</v>
       </c>
       <c r="J575" t="s">
-        <v>2911</v>
+        <v>2935</v>
       </c>
       <c r="K575">
         <v>2019</v>
@@ -37137,19 +38266,19 @@
         <v>43</v>
       </c>
       <c r="B576" t="s">
-        <v>2912</v>
+        <v>2936</v>
       </c>
       <c r="G576" t="s">
-        <v>2913</v>
+        <v>2937</v>
       </c>
       <c r="H576" t="s">
-        <v>2914</v>
+        <v>2938</v>
       </c>
       <c r="I576" t="s">
         <v>723</v>
       </c>
       <c r="J576" t="s">
-        <v>2915</v>
+        <v>2939</v>
       </c>
       <c r="K576">
         <v>2010</v>
@@ -37161,19 +38290,19 @@
         <v>43</v>
       </c>
       <c r="B577" t="s">
-        <v>2916</v>
+        <v>2940</v>
       </c>
       <c r="G577" t="s">
-        <v>2917</v>
+        <v>2941</v>
       </c>
       <c r="H577" t="s">
-        <v>2918</v>
+        <v>2942</v>
       </c>
       <c r="I577" t="s">
         <v>915</v>
       </c>
       <c r="J577" t="s">
-        <v>2919</v>
+        <v>2943</v>
       </c>
       <c r="K577">
         <v>2012</v>
@@ -37185,19 +38314,19 @@
         <v>43</v>
       </c>
       <c r="B578" t="s">
-        <v>2920</v>
+        <v>2944</v>
       </c>
       <c r="G578" t="s">
-        <v>2921</v>
+        <v>2945</v>
       </c>
       <c r="H578" t="s">
-        <v>2922</v>
+        <v>2946</v>
       </c>
       <c r="I578" t="s">
         <v>723</v>
       </c>
       <c r="J578" t="s">
-        <v>2923</v>
+        <v>2947</v>
       </c>
       <c r="K578">
         <v>1979</v>
@@ -37209,19 +38338,19 @@
         <v>43</v>
       </c>
       <c r="B579" t="s">
-        <v>2924</v>
+        <v>2948</v>
       </c>
       <c r="G579" t="s">
-        <v>2925</v>
+        <v>2949</v>
       </c>
       <c r="H579" t="s">
-        <v>2926</v>
+        <v>2950</v>
       </c>
       <c r="I579" t="s">
-        <v>2927</v>
+        <v>2951</v>
       </c>
       <c r="J579" t="s">
-        <v>2928</v>
+        <v>2952</v>
       </c>
       <c r="K579">
         <v>1980</v>
@@ -37233,19 +38362,19 @@
         <v>43</v>
       </c>
       <c r="B580" t="s">
-        <v>2929</v>
+        <v>2953</v>
       </c>
       <c r="G580" t="s">
-        <v>2930</v>
+        <v>2954</v>
       </c>
       <c r="H580" t="s">
-        <v>2931</v>
+        <v>2955</v>
       </c>
       <c r="I580" t="s">
         <v>253</v>
       </c>
       <c r="J580" t="s">
-        <v>2932</v>
+        <v>2956</v>
       </c>
       <c r="K580">
         <v>1981</v>
@@ -37257,19 +38386,19 @@
         <v>43</v>
       </c>
       <c r="B581" t="s">
-        <v>2933</v>
+        <v>2957</v>
       </c>
       <c r="G581" t="s">
-        <v>2934</v>
+        <v>2958</v>
       </c>
       <c r="H581" t="s">
-        <v>2935</v>
+        <v>2959</v>
       </c>
       <c r="I581" t="s">
         <v>723</v>
       </c>
       <c r="J581" t="s">
-        <v>2932</v>
+        <v>2956</v>
       </c>
       <c r="K581">
         <v>1981</v>
@@ -37281,19 +38410,19 @@
         <v>43</v>
       </c>
       <c r="B582" t="s">
-        <v>2936</v>
+        <v>2960</v>
       </c>
       <c r="G582" t="s">
-        <v>2937</v>
+        <v>2961</v>
       </c>
       <c r="H582" t="s">
-        <v>2938</v>
+        <v>2962</v>
       </c>
       <c r="I582" t="s">
         <v>197</v>
       </c>
       <c r="J582" t="s">
-        <v>2939</v>
+        <v>2963</v>
       </c>
       <c r="K582">
         <v>2023</v>
@@ -37305,19 +38434,19 @@
         <v>43</v>
       </c>
       <c r="B583" t="s">
-        <v>2940</v>
+        <v>2964</v>
       </c>
       <c r="G583" t="s">
-        <v>2941</v>
+        <v>2965</v>
       </c>
       <c r="H583" t="s">
-        <v>2942</v>
+        <v>2966</v>
       </c>
       <c r="I583" t="s">
         <v>2184</v>
       </c>
       <c r="J583" t="s">
-        <v>2943</v>
+        <v>2967</v>
       </c>
       <c r="K583">
         <v>2024</v>
@@ -37329,19 +38458,19 @@
         <v>43</v>
       </c>
       <c r="B584" t="s">
-        <v>2944</v>
+        <v>2968</v>
       </c>
       <c r="G584" t="s">
-        <v>2945</v>
+        <v>2969</v>
       </c>
       <c r="H584" t="s">
-        <v>2946</v>
+        <v>2970</v>
       </c>
       <c r="I584" t="s">
-        <v>2947</v>
+        <v>2971</v>
       </c>
       <c r="J584" t="s">
-        <v>2948</v>
+        <v>2972</v>
       </c>
       <c r="K584">
         <v>2014</v>
@@ -37353,19 +38482,19 @@
         <v>43</v>
       </c>
       <c r="B585" t="s">
-        <v>2949</v>
+        <v>2973</v>
       </c>
       <c r="G585" t="s">
-        <v>2950</v>
+        <v>2974</v>
       </c>
       <c r="H585" t="s">
-        <v>2951</v>
+        <v>2975</v>
       </c>
       <c r="I585" t="s">
         <v>745</v>
       </c>
       <c r="J585" t="s">
-        <v>2952</v>
+        <v>2976</v>
       </c>
       <c r="K585">
         <v>2015</v>
@@ -37377,19 +38506,19 @@
         <v>43</v>
       </c>
       <c r="B586" t="s">
-        <v>2953</v>
+        <v>2977</v>
       </c>
       <c r="G586" t="s">
-        <v>2954</v>
+        <v>2978</v>
       </c>
       <c r="H586" t="s">
-        <v>2955</v>
+        <v>2979</v>
       </c>
       <c r="I586" t="s">
         <v>2269</v>
       </c>
       <c r="J586" t="s">
-        <v>2956</v>
+        <v>2980</v>
       </c>
       <c r="K586">
         <v>2020</v>
@@ -37401,19 +38530,19 @@
         <v>43</v>
       </c>
       <c r="B587" t="s">
-        <v>2957</v>
+        <v>2981</v>
       </c>
       <c r="G587" t="s">
-        <v>2958</v>
+        <v>2982</v>
       </c>
       <c r="H587" t="s">
-        <v>2959</v>
+        <v>2983</v>
       </c>
       <c r="I587" t="s">
-        <v>2960</v>
+        <v>2984</v>
       </c>
       <c r="J587" t="s">
-        <v>2961</v>
+        <v>2985</v>
       </c>
       <c r="K587">
         <v>2020</v>
@@ -37425,19 +38554,19 @@
         <v>43</v>
       </c>
       <c r="B588" t="s">
-        <v>2962</v>
+        <v>2986</v>
       </c>
       <c r="G588" t="s">
-        <v>2963</v>
+        <v>2987</v>
       </c>
       <c r="H588" t="s">
-        <v>2964</v>
+        <v>2988</v>
       </c>
       <c r="I588" t="s">
         <v>1359</v>
       </c>
       <c r="J588" t="s">
-        <v>2965</v>
+        <v>2989</v>
       </c>
       <c r="K588">
         <v>2021</v>
@@ -37449,19 +38578,19 @@
         <v>43</v>
       </c>
       <c r="B589" t="s">
-        <v>2966</v>
+        <v>2990</v>
       </c>
       <c r="G589" t="s">
-        <v>2967</v>
+        <v>2991</v>
       </c>
       <c r="H589" t="s">
-        <v>2968</v>
+        <v>2992</v>
       </c>
       <c r="I589" t="s">
         <v>979</v>
       </c>
       <c r="J589" t="s">
-        <v>2969</v>
+        <v>2993</v>
       </c>
       <c r="K589">
         <v>2024</v>
@@ -37473,19 +38602,19 @@
         <v>43</v>
       </c>
       <c r="B590" t="s">
-        <v>2970</v>
+        <v>2994</v>
       </c>
       <c r="G590" t="s">
-        <v>2971</v>
+        <v>2995</v>
       </c>
       <c r="H590" t="s">
-        <v>2972</v>
+        <v>2996</v>
       </c>
       <c r="I590" t="s">
-        <v>2973</v>
+        <v>2997</v>
       </c>
       <c r="J590" t="s">
-        <v>2974</v>
+        <v>2998</v>
       </c>
       <c r="K590">
         <v>2014</v>
@@ -37497,19 +38626,19 @@
         <v>43</v>
       </c>
       <c r="B591" t="s">
-        <v>2975</v>
+        <v>2999</v>
       </c>
       <c r="G591" t="s">
-        <v>2976</v>
+        <v>3000</v>
       </c>
       <c r="H591" t="s">
-        <v>2977</v>
+        <v>3001</v>
       </c>
       <c r="I591" t="s">
-        <v>2978</v>
+        <v>3002</v>
       </c>
       <c r="J591" t="s">
-        <v>2979</v>
+        <v>3003</v>
       </c>
       <c r="K591">
         <v>2016</v>
@@ -37521,19 +38650,19 @@
         <v>43</v>
       </c>
       <c r="B592" t="s">
-        <v>2980</v>
+        <v>3004</v>
       </c>
       <c r="G592" t="s">
-        <v>2981</v>
+        <v>3005</v>
       </c>
       <c r="H592" t="s">
-        <v>2982</v>
+        <v>3006</v>
       </c>
       <c r="I592" t="s">
         <v>2184</v>
       </c>
       <c r="J592" t="s">
-        <v>2983</v>
+        <v>3007</v>
       </c>
       <c r="K592">
         <v>2023</v>
@@ -37545,19 +38674,19 @@
         <v>43</v>
       </c>
       <c r="B593" t="s">
-        <v>2984</v>
+        <v>3008</v>
       </c>
       <c r="G593" t="s">
-        <v>2985</v>
+        <v>3009</v>
       </c>
       <c r="H593" t="s">
-        <v>2986</v>
+        <v>3010</v>
       </c>
       <c r="I593" t="s">
         <v>2043</v>
       </c>
       <c r="J593" t="s">
-        <v>2987</v>
+        <v>3011</v>
       </c>
       <c r="K593">
         <v>2009</v>
@@ -37569,19 +38698,19 @@
         <v>43</v>
       </c>
       <c r="B594" t="s">
-        <v>2988</v>
+        <v>3012</v>
       </c>
       <c r="G594" t="s">
-        <v>2989</v>
+        <v>3013</v>
       </c>
       <c r="H594" t="s">
-        <v>2990</v>
+        <v>3014</v>
       </c>
       <c r="I594" t="s">
         <v>990</v>
       </c>
       <c r="J594" t="s">
-        <v>2991</v>
+        <v>3015</v>
       </c>
       <c r="K594">
         <v>2018</v>
@@ -37593,19 +38722,19 @@
         <v>43</v>
       </c>
       <c r="B595" t="s">
-        <v>2992</v>
+        <v>3016</v>
       </c>
       <c r="G595" t="s">
-        <v>2993</v>
+        <v>3017</v>
       </c>
       <c r="H595" t="s">
-        <v>2994</v>
+        <v>3018</v>
       </c>
       <c r="I595" t="s">
-        <v>2995</v>
+        <v>3019</v>
       </c>
       <c r="J595" t="s">
-        <v>2996</v>
+        <v>3020</v>
       </c>
       <c r="K595">
         <v>2020</v>
@@ -37617,19 +38746,19 @@
         <v>43</v>
       </c>
       <c r="B596" t="s">
-        <v>2997</v>
+        <v>3021</v>
       </c>
       <c r="G596" t="s">
-        <v>2998</v>
+        <v>3022</v>
       </c>
       <c r="H596" t="s">
-        <v>2999</v>
+        <v>3023</v>
       </c>
       <c r="I596" t="s">
-        <v>3000</v>
+        <v>3024</v>
       </c>
       <c r="J596" t="s">
-        <v>3001</v>
+        <v>3025</v>
       </c>
       <c r="K596">
         <v>2002</v>
@@ -37641,19 +38770,19 @@
         <v>43</v>
       </c>
       <c r="B597" t="s">
-        <v>3002</v>
+        <v>3026</v>
       </c>
       <c r="G597" t="s">
-        <v>3003</v>
+        <v>3027</v>
       </c>
       <c r="H597" t="s">
-        <v>3004</v>
+        <v>3028</v>
       </c>
       <c r="I597" t="s">
         <v>51</v>
       </c>
       <c r="J597" t="s">
-        <v>3005</v>
+        <v>3029</v>
       </c>
       <c r="K597">
         <v>1994</v>
@@ -37665,19 +38794,19 @@
         <v>43</v>
       </c>
       <c r="B598" t="s">
-        <v>3006</v>
+        <v>3030</v>
       </c>
       <c r="G598" t="s">
-        <v>3007</v>
+        <v>3031</v>
       </c>
       <c r="H598" t="s">
-        <v>3008</v>
+        <v>3032</v>
       </c>
       <c r="I598" t="s">
         <v>1308</v>
       </c>
       <c r="J598" t="s">
-        <v>3009</v>
+        <v>3033</v>
       </c>
       <c r="K598">
         <v>2021</v>
@@ -37689,19 +38818,19 @@
         <v>43</v>
       </c>
       <c r="B599" t="s">
-        <v>3010</v>
+        <v>3034</v>
       </c>
       <c r="G599" t="s">
-        <v>3011</v>
+        <v>3035</v>
       </c>
       <c r="H599" t="s">
-        <v>3012</v>
+        <v>3036</v>
       </c>
       <c r="I599" t="s">
         <v>1652</v>
       </c>
       <c r="J599" t="s">
-        <v>3013</v>
+        <v>3037</v>
       </c>
       <c r="K599">
         <v>2025</v>
@@ -37713,19 +38842,19 @@
         <v>43</v>
       </c>
       <c r="B600" t="s">
-        <v>3014</v>
+        <v>3038</v>
       </c>
       <c r="G600" t="s">
-        <v>3015</v>
+        <v>3039</v>
       </c>
       <c r="H600" t="s">
-        <v>3016</v>
+        <v>3040</v>
       </c>
       <c r="I600" t="s">
         <v>51</v>
       </c>
       <c r="J600" t="s">
-        <v>3017</v>
+        <v>3041</v>
       </c>
       <c r="K600">
         <v>2021</v>
@@ -37737,19 +38866,19 @@
         <v>43</v>
       </c>
       <c r="B601" t="s">
-        <v>3018</v>
+        <v>3042</v>
       </c>
       <c r="G601" t="s">
-        <v>3019</v>
+        <v>3043</v>
       </c>
       <c r="H601" t="s">
-        <v>3020</v>
+        <v>3044</v>
       </c>
       <c r="I601" t="s">
-        <v>2978</v>
+        <v>3002</v>
       </c>
       <c r="J601" t="s">
-        <v>3021</v>
+        <v>3045</v>
       </c>
       <c r="K601">
         <v>2024</v>
@@ -37761,19 +38890,19 @@
         <v>43</v>
       </c>
       <c r="B602" t="s">
-        <v>3022</v>
+        <v>3046</v>
       </c>
       <c r="G602" t="s">
-        <v>3023</v>
+        <v>3047</v>
       </c>
       <c r="H602" t="s">
-        <v>3024</v>
+        <v>3048</v>
       </c>
       <c r="I602" t="s">
-        <v>2867</v>
+        <v>2891</v>
       </c>
       <c r="J602" t="s">
-        <v>3025</v>
+        <v>3049</v>
       </c>
       <c r="K602">
         <v>2024</v>
@@ -37785,19 +38914,19 @@
         <v>43</v>
       </c>
       <c r="B603" t="s">
-        <v>3026</v>
+        <v>3050</v>
       </c>
       <c r="G603" t="s">
-        <v>3027</v>
+        <v>3051</v>
       </c>
       <c r="H603" t="s">
-        <v>3028</v>
+        <v>3052</v>
       </c>
       <c r="I603" t="s">
-        <v>3029</v>
+        <v>3053</v>
       </c>
       <c r="J603" t="s">
-        <v>3030</v>
+        <v>3054</v>
       </c>
       <c r="K603">
         <v>2018</v>
@@ -37809,19 +38938,19 @@
         <v>43</v>
       </c>
       <c r="B604" t="s">
-        <v>3031</v>
+        <v>3055</v>
       </c>
       <c r="G604" t="s">
-        <v>3032</v>
+        <v>3056</v>
       </c>
       <c r="H604" t="s">
-        <v>3033</v>
+        <v>3057</v>
       </c>
       <c r="I604" t="s">
         <v>100</v>
       </c>
       <c r="J604" t="s">
-        <v>3034</v>
+        <v>3058</v>
       </c>
       <c r="K604">
         <v>2014</v>
@@ -37833,19 +38962,19 @@
         <v>43</v>
       </c>
       <c r="B605" t="s">
-        <v>3035</v>
+        <v>3059</v>
       </c>
       <c r="G605" t="s">
-        <v>3036</v>
+        <v>3060</v>
       </c>
       <c r="H605" t="s">
-        <v>3037</v>
+        <v>3061</v>
       </c>
       <c r="I605" t="s">
         <v>1924</v>
       </c>
       <c r="J605" t="s">
-        <v>3038</v>
+        <v>3062</v>
       </c>
       <c r="K605">
         <v>2019</v>
@@ -37857,19 +38986,19 @@
         <v>43</v>
       </c>
       <c r="B606" t="s">
-        <v>3039</v>
+        <v>3063</v>
       </c>
       <c r="G606" t="s">
-        <v>3040</v>
+        <v>3064</v>
       </c>
       <c r="H606" t="s">
-        <v>3041</v>
+        <v>3065</v>
       </c>
       <c r="I606" t="s">
-        <v>3042</v>
+        <v>3066</v>
       </c>
       <c r="J606" t="s">
-        <v>3043</v>
+        <v>3067</v>
       </c>
       <c r="K606">
         <v>2024</v>
@@ -37881,19 +39010,19 @@
         <v>43</v>
       </c>
       <c r="B607" t="s">
-        <v>3044</v>
+        <v>3068</v>
       </c>
       <c r="G607" t="s">
-        <v>3045</v>
+        <v>3069</v>
       </c>
       <c r="H607" t="s">
-        <v>3046</v>
+        <v>3070</v>
       </c>
       <c r="I607" t="s">
         <v>1520</v>
       </c>
       <c r="J607" t="s">
-        <v>3047</v>
+        <v>3071</v>
       </c>
       <c r="K607">
         <v>2024</v>
@@ -37905,19 +39034,19 @@
         <v>43</v>
       </c>
       <c r="B608" t="s">
-        <v>3048</v>
+        <v>3072</v>
       </c>
       <c r="G608" t="s">
-        <v>3049</v>
+        <v>3073</v>
       </c>
       <c r="H608" t="s">
-        <v>3050</v>
+        <v>3074</v>
       </c>
       <c r="I608" t="s">
         <v>1520</v>
       </c>
       <c r="J608" t="s">
-        <v>3051</v>
+        <v>3075</v>
       </c>
       <c r="K608">
         <v>2021</v>
@@ -37929,19 +39058,19 @@
         <v>43</v>
       </c>
       <c r="B609" t="s">
-        <v>3052</v>
+        <v>3076</v>
       </c>
       <c r="G609" t="s">
-        <v>3053</v>
+        <v>3077</v>
       </c>
       <c r="H609" t="s">
-        <v>3054</v>
+        <v>3078</v>
       </c>
       <c r="I609" t="s">
-        <v>3055</v>
+        <v>3079</v>
       </c>
       <c r="J609" t="s">
-        <v>3056</v>
+        <v>3080</v>
       </c>
       <c r="K609">
         <v>2022</v>
@@ -37953,19 +39082,19 @@
         <v>43</v>
       </c>
       <c r="B610" t="s">
-        <v>3057</v>
+        <v>3081</v>
       </c>
       <c r="G610" t="s">
-        <v>3058</v>
+        <v>3082</v>
       </c>
       <c r="H610" t="s">
-        <v>3059</v>
+        <v>3083</v>
       </c>
       <c r="I610" t="s">
         <v>226</v>
       </c>
       <c r="J610" t="s">
-        <v>3060</v>
+        <v>3084</v>
       </c>
       <c r="K610">
         <v>2020</v>
@@ -37977,19 +39106,19 @@
         <v>43</v>
       </c>
       <c r="B611" t="s">
-        <v>3061</v>
+        <v>3085</v>
       </c>
       <c r="G611" t="s">
-        <v>3062</v>
+        <v>3086</v>
       </c>
       <c r="H611" t="s">
-        <v>3063</v>
+        <v>3087</v>
       </c>
       <c r="I611" t="s">
         <v>226</v>
       </c>
       <c r="J611" t="s">
-        <v>3060</v>
+        <v>3084</v>
       </c>
       <c r="K611">
         <v>2023</v>
@@ -38001,19 +39130,19 @@
         <v>43</v>
       </c>
       <c r="B612" t="s">
-        <v>3064</v>
+        <v>3088</v>
       </c>
       <c r="G612" t="s">
-        <v>3065</v>
+        <v>3089</v>
       </c>
       <c r="H612" t="s">
-        <v>3066</v>
+        <v>3090</v>
       </c>
       <c r="I612" t="s">
-        <v>3067</v>
+        <v>3091</v>
       </c>
       <c r="J612" t="s">
-        <v>3068</v>
+        <v>3092</v>
       </c>
       <c r="K612">
         <v>2023</v>
@@ -38025,19 +39154,19 @@
         <v>43</v>
       </c>
       <c r="B613" t="s">
-        <v>3069</v>
+        <v>3093</v>
       </c>
       <c r="G613" t="s">
-        <v>3070</v>
+        <v>3094</v>
       </c>
       <c r="H613" t="s">
-        <v>3071</v>
+        <v>3095</v>
       </c>
       <c r="I613" t="s">
         <v>1414</v>
       </c>
       <c r="J613" t="s">
-        <v>3072</v>
+        <v>3096</v>
       </c>
       <c r="K613">
         <v>2023</v>
@@ -38049,19 +39178,19 @@
         <v>43</v>
       </c>
       <c r="B614" t="s">
-        <v>3073</v>
+        <v>3097</v>
       </c>
       <c r="G614" t="s">
-        <v>3074</v>
+        <v>3098</v>
       </c>
       <c r="H614" t="s">
-        <v>3075</v>
+        <v>3099</v>
       </c>
       <c r="I614" t="s">
         <v>409</v>
       </c>
       <c r="J614" t="s">
-        <v>3076</v>
+        <v>3100</v>
       </c>
       <c r="K614">
         <v>2022</v>
@@ -38073,19 +39202,19 @@
         <v>43</v>
       </c>
       <c r="B615" t="s">
-        <v>3077</v>
+        <v>3101</v>
       </c>
       <c r="G615" t="s">
-        <v>3078</v>
+        <v>3102</v>
       </c>
       <c r="H615" t="s">
-        <v>3079</v>
+        <v>3103</v>
       </c>
       <c r="I615" t="s">
-        <v>3080</v>
+        <v>3104</v>
       </c>
       <c r="J615" t="s">
-        <v>3081</v>
+        <v>3105</v>
       </c>
       <c r="K615">
         <v>2022</v>
@@ -38097,19 +39226,19 @@
         <v>43</v>
       </c>
       <c r="B616" t="s">
-        <v>3082</v>
+        <v>3106</v>
       </c>
       <c r="G616" t="s">
-        <v>3083</v>
+        <v>3107</v>
       </c>
       <c r="H616" t="s">
-        <v>3084</v>
+        <v>3108</v>
       </c>
       <c r="I616" t="s">
         <v>2275</v>
       </c>
       <c r="J616" t="s">
-        <v>3085</v>
+        <v>3109</v>
       </c>
       <c r="K616">
         <v>2019</v>
@@ -38121,19 +39250,19 @@
         <v>43</v>
       </c>
       <c r="B617" t="s">
-        <v>3086</v>
+        <v>3110</v>
       </c>
       <c r="G617" t="s">
-        <v>3087</v>
+        <v>3111</v>
       </c>
       <c r="H617" t="s">
-        <v>3088</v>
+        <v>3112</v>
       </c>
       <c r="I617" t="s">
-        <v>3089</v>
+        <v>3113</v>
       </c>
       <c r="J617" t="s">
-        <v>3090</v>
+        <v>3114</v>
       </c>
       <c r="K617">
         <v>2024</v>
@@ -38145,19 +39274,19 @@
         <v>43</v>
       </c>
       <c r="B618" t="s">
-        <v>3091</v>
+        <v>3115</v>
       </c>
       <c r="G618" t="s">
-        <v>3092</v>
+        <v>3116</v>
       </c>
       <c r="H618" t="s">
-        <v>3093</v>
+        <v>3117</v>
       </c>
       <c r="I618" t="s">
         <v>295</v>
       </c>
       <c r="J618" t="s">
-        <v>3094</v>
+        <v>3118</v>
       </c>
       <c r="K618">
         <v>2022</v>
@@ -38169,19 +39298,19 @@
         <v>43</v>
       </c>
       <c r="B619" t="s">
-        <v>3095</v>
+        <v>3119</v>
       </c>
       <c r="G619" t="s">
-        <v>3096</v>
+        <v>3120</v>
       </c>
       <c r="H619" t="s">
-        <v>3097</v>
+        <v>3121</v>
       </c>
       <c r="I619" t="s">
         <v>915</v>
       </c>
       <c r="J619" t="s">
-        <v>3098</v>
+        <v>3122</v>
       </c>
       <c r="K619">
         <v>1995</v>
@@ -38193,19 +39322,19 @@
         <v>43</v>
       </c>
       <c r="B620" t="s">
-        <v>3099</v>
+        <v>3123</v>
       </c>
       <c r="G620" t="s">
-        <v>3100</v>
+        <v>3124</v>
       </c>
       <c r="H620" t="s">
-        <v>3101</v>
+        <v>3125</v>
       </c>
       <c r="I620" t="s">
-        <v>3102</v>
+        <v>3126</v>
       </c>
       <c r="J620" t="s">
-        <v>3103</v>
+        <v>3127</v>
       </c>
       <c r="K620">
         <v>1992</v>
@@ -38217,19 +39346,19 @@
         <v>43</v>
       </c>
       <c r="B621" t="s">
-        <v>3104</v>
+        <v>3128</v>
       </c>
       <c r="G621" t="s">
-        <v>3105</v>
+        <v>3129</v>
       </c>
       <c r="H621" t="s">
-        <v>3106</v>
+        <v>3130</v>
       </c>
       <c r="I621" t="s">
-        <v>3107</v>
+        <v>3131</v>
       </c>
       <c r="J621" t="s">
-        <v>3108</v>
+        <v>3132</v>
       </c>
       <c r="K621">
         <v>2021</v>
@@ -38241,19 +39370,19 @@
         <v>43</v>
       </c>
       <c r="B622" t="s">
-        <v>3109</v>
+        <v>3133</v>
       </c>
       <c r="G622" t="s">
-        <v>3110</v>
+        <v>3134</v>
       </c>
       <c r="H622" t="s">
-        <v>3111</v>
+        <v>3135</v>
       </c>
       <c r="I622" t="s">
         <v>973</v>
       </c>
       <c r="J622" t="s">
-        <v>3112</v>
+        <v>3136</v>
       </c>
       <c r="K622">
         <v>2018</v>
@@ -38265,19 +39394,19 @@
         <v>43</v>
       </c>
       <c r="B623" t="s">
-        <v>3113</v>
+        <v>3137</v>
       </c>
       <c r="G623" t="s">
-        <v>3114</v>
+        <v>3138</v>
       </c>
       <c r="H623" t="s">
-        <v>3115</v>
+        <v>3139</v>
       </c>
       <c r="I623" t="s">
-        <v>3116</v>
+        <v>3140</v>
       </c>
       <c r="J623" t="s">
-        <v>3117</v>
+        <v>3141</v>
       </c>
       <c r="K623">
         <v>2019</v>
@@ -38289,19 +39418,19 @@
         <v>43</v>
       </c>
       <c r="B624" t="s">
-        <v>3118</v>
+        <v>3142</v>
       </c>
       <c r="G624" t="s">
-        <v>3119</v>
+        <v>3143</v>
       </c>
       <c r="H624" t="s">
-        <v>3120</v>
+        <v>3144</v>
       </c>
       <c r="I624" t="s">
         <v>1652</v>
       </c>
       <c r="J624" t="s">
-        <v>3121</v>
+        <v>3145</v>
       </c>
       <c r="K624">
         <v>2016</v>
@@ -38313,19 +39442,19 @@
         <v>43</v>
       </c>
       <c r="B625" t="s">
-        <v>3122</v>
+        <v>3146</v>
       </c>
       <c r="G625" t="s">
-        <v>3123</v>
+        <v>3147</v>
       </c>
       <c r="H625" t="s">
-        <v>3124</v>
+        <v>3148</v>
       </c>
       <c r="I625" t="s">
         <v>1242</v>
       </c>
       <c r="J625" t="s">
-        <v>3125</v>
+        <v>3149</v>
       </c>
       <c r="K625">
         <v>2002</v>
@@ -38337,19 +39466,19 @@
         <v>43</v>
       </c>
       <c r="B626" t="s">
-        <v>3126</v>
+        <v>3150</v>
       </c>
       <c r="G626" t="s">
-        <v>3127</v>
+        <v>3151</v>
       </c>
       <c r="H626" t="s">
-        <v>3128</v>
+        <v>3152</v>
       </c>
       <c r="I626" t="s">
-        <v>3129</v>
+        <v>3153</v>
       </c>
       <c r="J626" t="s">
-        <v>3130</v>
+        <v>3154</v>
       </c>
       <c r="K626">
         <v>2018</v>
@@ -38361,19 +39490,19 @@
         <v>43</v>
       </c>
       <c r="B627" t="s">
-        <v>3131</v>
+        <v>3155</v>
       </c>
       <c r="G627" t="s">
-        <v>3132</v>
+        <v>3156</v>
       </c>
       <c r="H627" t="s">
-        <v>3133</v>
+        <v>3157</v>
       </c>
       <c r="I627" t="s">
         <v>128</v>
       </c>
       <c r="J627" t="s">
-        <v>3134</v>
+        <v>3158</v>
       </c>
       <c r="K627">
         <v>2016</v>
@@ -38385,19 +39514,19 @@
         <v>43</v>
       </c>
       <c r="B628" t="s">
-        <v>3135</v>
+        <v>3159</v>
       </c>
       <c r="G628" t="s">
-        <v>3136</v>
+        <v>3160</v>
       </c>
       <c r="H628" t="s">
-        <v>3137</v>
+        <v>3161</v>
       </c>
       <c r="I628" t="s">
         <v>915</v>
       </c>
       <c r="J628" t="s">
-        <v>3138</v>
+        <v>3162</v>
       </c>
       <c r="K628">
         <v>2004</v>
@@ -38409,19 +39538,19 @@
         <v>43</v>
       </c>
       <c r="B629" t="s">
-        <v>3139</v>
+        <v>3163</v>
       </c>
       <c r="G629" t="s">
-        <v>3140</v>
+        <v>3164</v>
       </c>
       <c r="H629" t="s">
-        <v>3141</v>
+        <v>3165</v>
       </c>
       <c r="I629" t="s">
         <v>1652</v>
       </c>
       <c r="J629" t="s">
-        <v>3142</v>
+        <v>3166</v>
       </c>
       <c r="K629">
         <v>2008</v>
@@ -38433,19 +39562,19 @@
         <v>43</v>
       </c>
       <c r="B630" t="s">
-        <v>3143</v>
+        <v>3167</v>
       </c>
       <c r="G630" t="s">
-        <v>3144</v>
+        <v>3168</v>
       </c>
       <c r="H630" t="s">
-        <v>3145</v>
+        <v>3169</v>
       </c>
       <c r="I630" t="s">
         <v>692</v>
       </c>
       <c r="J630" t="s">
-        <v>3146</v>
+        <v>3170</v>
       </c>
       <c r="K630">
         <v>2014</v>
@@ -38457,19 +39586,19 @@
         <v>43</v>
       </c>
       <c r="B631" t="s">
-        <v>3147</v>
+        <v>3171</v>
       </c>
       <c r="G631" t="s">
-        <v>3148</v>
+        <v>3172</v>
       </c>
       <c r="H631" t="s">
-        <v>3149</v>
+        <v>3173</v>
       </c>
       <c r="I631" t="s">
-        <v>2815</v>
+        <v>2839</v>
       </c>
       <c r="J631" t="s">
-        <v>3150</v>
+        <v>3174</v>
       </c>
       <c r="K631">
         <v>2004</v>
@@ -38481,19 +39610,19 @@
         <v>43</v>
       </c>
       <c r="B632" t="s">
-        <v>3151</v>
+        <v>3175</v>
       </c>
       <c r="G632" t="s">
-        <v>3152</v>
+        <v>3176</v>
       </c>
       <c r="H632" t="s">
-        <v>3153</v>
+        <v>3177</v>
       </c>
       <c r="I632" t="s">
-        <v>3154</v>
+        <v>3178</v>
       </c>
       <c r="J632" t="s">
-        <v>3155</v>
+        <v>3179</v>
       </c>
       <c r="K632">
         <v>1994</v>
@@ -38505,19 +39634,19 @@
         <v>43</v>
       </c>
       <c r="B633" t="s">
-        <v>3156</v>
+        <v>3180</v>
       </c>
       <c r="G633" t="s">
-        <v>3157</v>
+        <v>3181</v>
       </c>
       <c r="H633" t="s">
-        <v>3158</v>
+        <v>3182</v>
       </c>
       <c r="I633" t="s">
-        <v>3159</v>
+        <v>3183</v>
       </c>
       <c r="J633" t="s">
-        <v>3160</v>
+        <v>3184</v>
       </c>
       <c r="K633">
         <v>2010</v>
@@ -38529,19 +39658,19 @@
         <v>43</v>
       </c>
       <c r="B634" t="s">
-        <v>3161</v>
+        <v>3185</v>
       </c>
       <c r="G634" t="s">
-        <v>3162</v>
+        <v>3186</v>
       </c>
       <c r="H634" t="s">
-        <v>3163</v>
+        <v>3187</v>
       </c>
       <c r="I634" t="s">
         <v>226</v>
       </c>
       <c r="J634" t="s">
-        <v>3164</v>
+        <v>3188</v>
       </c>
       <c r="K634">
         <v>2025</v>
@@ -38553,19 +39682,19 @@
         <v>43</v>
       </c>
       <c r="B635" t="s">
-        <v>3165</v>
+        <v>3189</v>
       </c>
       <c r="G635" t="s">
-        <v>3166</v>
+        <v>3190</v>
       </c>
       <c r="H635" t="s">
-        <v>3167</v>
+        <v>3191</v>
       </c>
       <c r="I635" t="s">
         <v>825</v>
       </c>
       <c r="J635" t="s">
-        <v>3168</v>
+        <v>3192</v>
       </c>
       <c r="K635">
         <v>2020</v>
@@ -38577,19 +39706,19 @@
         <v>43</v>
       </c>
       <c r="B636" t="s">
-        <v>3169</v>
+        <v>3193</v>
       </c>
       <c r="G636" t="s">
-        <v>3170</v>
+        <v>3194</v>
       </c>
       <c r="H636" t="s">
-        <v>3171</v>
+        <v>3195</v>
       </c>
       <c r="I636" t="s">
-        <v>3172</v>
+        <v>3196</v>
       </c>
       <c r="J636" t="s">
-        <v>3173</v>
+        <v>3197</v>
       </c>
       <c r="K636">
         <v>2017</v>
@@ -38601,19 +39730,19 @@
         <v>43</v>
       </c>
       <c r="B637" t="s">
-        <v>3174</v>
+        <v>3198</v>
       </c>
       <c r="G637" t="s">
-        <v>3175</v>
+        <v>3199</v>
       </c>
       <c r="H637" t="s">
-        <v>3176</v>
+        <v>3200</v>
       </c>
       <c r="I637" t="s">
         <v>295</v>
       </c>
       <c r="J637" t="s">
-        <v>3177</v>
+        <v>3201</v>
       </c>
       <c r="K637">
         <v>2025</v>
@@ -38625,19 +39754,19 @@
         <v>43</v>
       </c>
       <c r="B638" t="s">
-        <v>3178</v>
+        <v>3202</v>
       </c>
       <c r="G638" t="s">
-        <v>3179</v>
+        <v>3203</v>
       </c>
       <c r="H638" t="s">
-        <v>3180</v>
+        <v>3204</v>
       </c>
       <c r="I638" t="s">
         <v>295</v>
       </c>
       <c r="J638" t="s">
-        <v>3181</v>
+        <v>3205</v>
       </c>
       <c r="K638">
         <v>2023</v>
@@ -38649,19 +39778,19 @@
         <v>43</v>
       </c>
       <c r="B639" t="s">
-        <v>3182</v>
+        <v>3206</v>
       </c>
       <c r="G639" t="s">
-        <v>3183</v>
+        <v>3207</v>
       </c>
       <c r="H639" t="s">
-        <v>3184</v>
+        <v>3208</v>
       </c>
       <c r="I639" t="s">
-        <v>3185</v>
+        <v>3209</v>
       </c>
       <c r="J639" t="s">
-        <v>3186</v>
+        <v>3210</v>
       </c>
       <c r="K639">
         <v>2009</v>
@@ -38673,19 +39802,19 @@
         <v>43</v>
       </c>
       <c r="B640" t="s">
-        <v>3187</v>
+        <v>3211</v>
       </c>
       <c r="G640" t="s">
-        <v>3188</v>
+        <v>3212</v>
       </c>
       <c r="H640" t="s">
-        <v>3189</v>
+        <v>3213</v>
       </c>
       <c r="I640" t="s">
         <v>226</v>
       </c>
       <c r="J640" t="s">
-        <v>3190</v>
+        <v>3214</v>
       </c>
       <c r="K640">
         <v>2024</v>
@@ -38697,19 +39826,19 @@
         <v>43</v>
       </c>
       <c r="B641" t="s">
-        <v>3191</v>
+        <v>3215</v>
       </c>
       <c r="G641" t="s">
-        <v>3192</v>
+        <v>3216</v>
       </c>
       <c r="H641" t="s">
-        <v>3193</v>
+        <v>3217</v>
       </c>
       <c r="I641" t="s">
         <v>1548</v>
       </c>
       <c r="J641" t="s">
-        <v>3194</v>
+        <v>3218</v>
       </c>
       <c r="K641">
         <v>2024</v>
@@ -38721,19 +39850,19 @@
         <v>43</v>
       </c>
       <c r="B642" t="s">
-        <v>3195</v>
+        <v>3219</v>
       </c>
       <c r="G642" t="s">
-        <v>3196</v>
+        <v>3220</v>
       </c>
       <c r="H642" t="s">
-        <v>3197</v>
+        <v>3221</v>
       </c>
       <c r="I642" t="s">
         <v>549</v>
       </c>
       <c r="J642" t="s">
-        <v>3198</v>
+        <v>3222</v>
       </c>
       <c r="K642">
         <v>2020</v>
@@ -38745,19 +39874,19 @@
         <v>43</v>
       </c>
       <c r="B643" t="s">
-        <v>3199</v>
+        <v>3223</v>
       </c>
       <c r="G643" t="s">
-        <v>3200</v>
+        <v>3224</v>
       </c>
       <c r="H643" t="s">
-        <v>3201</v>
+        <v>3225</v>
       </c>
       <c r="I643" t="s">
         <v>148</v>
       </c>
       <c r="J643" t="s">
-        <v>3202</v>
+        <v>3226</v>
       </c>
       <c r="K643">
         <v>2020</v>
@@ -38769,19 +39898,19 @@
         <v>43</v>
       </c>
       <c r="B644" t="s">
-        <v>3203</v>
+        <v>3227</v>
       </c>
       <c r="G644" t="s">
-        <v>3204</v>
+        <v>3228</v>
       </c>
       <c r="H644" t="s">
-        <v>3205</v>
+        <v>3229</v>
       </c>
       <c r="I644" t="s">
-        <v>3206</v>
+        <v>3230</v>
       </c>
       <c r="J644" t="s">
-        <v>3207</v>
+        <v>3231</v>
       </c>
       <c r="K644">
         <v>2021</v>
@@ -38793,19 +39922,19 @@
         <v>43</v>
       </c>
       <c r="B645" t="s">
-        <v>3208</v>
+        <v>3232</v>
       </c>
       <c r="G645" t="s">
-        <v>3209</v>
+        <v>3233</v>
       </c>
       <c r="H645" t="s">
-        <v>3210</v>
+        <v>3234</v>
       </c>
       <c r="I645" t="s">
         <v>1308</v>
       </c>
       <c r="J645" t="s">
-        <v>3211</v>
+        <v>3235</v>
       </c>
       <c r="K645">
         <v>2024</v>
@@ -38817,19 +39946,19 @@
         <v>43</v>
       </c>
       <c r="B646" t="s">
-        <v>3212</v>
+        <v>3236</v>
       </c>
       <c r="G646" t="s">
-        <v>3213</v>
+        <v>3237</v>
       </c>
       <c r="H646" t="s">
-        <v>3214</v>
+        <v>3238</v>
       </c>
       <c r="I646" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="J646" t="s">
-        <v>3215</v>
+        <v>3239</v>
       </c>
       <c r="K646">
         <v>2024</v>
@@ -38841,19 +39970,19 @@
         <v>43</v>
       </c>
       <c r="B647" t="s">
-        <v>3216</v>
+        <v>3240</v>
       </c>
       <c r="G647" t="s">
-        <v>3217</v>
+        <v>3241</v>
       </c>
       <c r="H647" t="s">
-        <v>3218</v>
+        <v>3242</v>
       </c>
       <c r="I647" t="s">
         <v>295</v>
       </c>
       <c r="J647" t="s">
-        <v>3219</v>
+        <v>3243</v>
       </c>
       <c r="K647">
         <v>2021</v>
@@ -38865,19 +39994,19 @@
         <v>43</v>
       </c>
       <c r="B648" t="s">
-        <v>3220</v>
+        <v>3244</v>
       </c>
       <c r="G648" t="s">
-        <v>3221</v>
+        <v>3245</v>
       </c>
       <c r="H648" t="s">
-        <v>3222</v>
+        <v>3246</v>
       </c>
       <c r="I648" t="s">
         <v>1652</v>
       </c>
       <c r="J648" t="s">
-        <v>3223</v>
+        <v>3247</v>
       </c>
       <c r="K648">
         <v>2022</v>
@@ -38889,19 +40018,19 @@
         <v>43</v>
       </c>
       <c r="B649" t="s">
-        <v>3224</v>
+        <v>3248</v>
       </c>
       <c r="G649" t="s">
-        <v>3225</v>
+        <v>3249</v>
       </c>
       <c r="H649" t="s">
-        <v>3226</v>
+        <v>3250</v>
       </c>
       <c r="I649" t="s">
         <v>409</v>
       </c>
       <c r="J649" t="s">
-        <v>3227</v>
+        <v>3251</v>
       </c>
       <c r="K649">
         <v>2022</v>
@@ -38913,19 +40042,19 @@
         <v>43</v>
       </c>
       <c r="B650" t="s">
-        <v>3228</v>
+        <v>3252</v>
       </c>
       <c r="G650" t="s">
-        <v>3229</v>
+        <v>3253</v>
       </c>
       <c r="H650" t="s">
-        <v>3230</v>
+        <v>3254</v>
       </c>
       <c r="I650" t="s">
-        <v>2666</v>
+        <v>2690</v>
       </c>
       <c r="J650" t="s">
-        <v>3231</v>
+        <v>3255</v>
       </c>
       <c r="K650">
         <v>2026</v>
@@ -38937,19 +40066,19 @@
         <v>43</v>
       </c>
       <c r="B651" t="s">
-        <v>3232</v>
+        <v>3256</v>
       </c>
       <c r="G651" t="s">
-        <v>3233</v>
+        <v>3257</v>
       </c>
       <c r="H651" t="s">
-        <v>3234</v>
+        <v>3258</v>
       </c>
       <c r="I651" t="s">
-        <v>3235</v>
+        <v>3259</v>
       </c>
       <c r="J651" t="s">
-        <v>3236</v>
+        <v>3260</v>
       </c>
       <c r="K651">
         <v>2024</v>
@@ -38961,19 +40090,19 @@
         <v>43</v>
       </c>
       <c r="B652" t="s">
-        <v>3237</v>
+        <v>3261</v>
       </c>
       <c r="G652" t="s">
-        <v>3238</v>
+        <v>3262</v>
       </c>
       <c r="H652" t="s">
-        <v>3239</v>
+        <v>3263</v>
       </c>
       <c r="I652" t="s">
         <v>1336</v>
       </c>
       <c r="J652" t="s">
-        <v>3240</v>
+        <v>3264</v>
       </c>
       <c r="K652">
         <v>2015</v>
@@ -38985,19 +40114,19 @@
         <v>43</v>
       </c>
       <c r="B653" t="s">
-        <v>3241</v>
+        <v>3265</v>
       </c>
       <c r="G653" t="s">
-        <v>3242</v>
+        <v>3266</v>
       </c>
       <c r="H653" t="s">
-        <v>3243</v>
+        <v>3267</v>
       </c>
       <c r="I653" t="s">
-        <v>3244</v>
+        <v>3268</v>
       </c>
       <c r="J653" t="s">
-        <v>3245</v>
+        <v>3269</v>
       </c>
       <c r="K653">
         <v>2017</v>
@@ -39009,19 +40138,19 @@
         <v>43</v>
       </c>
       <c r="B654" t="s">
-        <v>3246</v>
+        <v>3270</v>
       </c>
       <c r="G654" t="s">
-        <v>3247</v>
+        <v>3271</v>
       </c>
       <c r="H654" t="s">
-        <v>3248</v>
+        <v>3272</v>
       </c>
       <c r="I654" t="s">
-        <v>3249</v>
+        <v>3273</v>
       </c>
       <c r="J654" t="s">
-        <v>3250</v>
+        <v>3274</v>
       </c>
       <c r="K654">
         <v>2016</v>
@@ -39033,19 +40162,19 @@
         <v>43</v>
       </c>
       <c r="B655" t="s">
-        <v>3251</v>
+        <v>3275</v>
       </c>
       <c r="G655" t="s">
-        <v>3252</v>
+        <v>3276</v>
       </c>
       <c r="H655" t="s">
-        <v>3253</v>
+        <v>3277</v>
       </c>
       <c r="I655" t="s">
-        <v>3254</v>
+        <v>3278</v>
       </c>
       <c r="J655" t="s">
-        <v>3255</v>
+        <v>3279</v>
       </c>
       <c r="K655">
         <v>2018</v>
@@ -39057,19 +40186,19 @@
         <v>43</v>
       </c>
       <c r="B656" t="s">
-        <v>3256</v>
+        <v>3280</v>
       </c>
       <c r="G656" t="s">
-        <v>3257</v>
+        <v>3281</v>
       </c>
       <c r="H656" t="s">
-        <v>3258</v>
+        <v>3282</v>
       </c>
       <c r="I656" t="s">
         <v>692</v>
       </c>
       <c r="J656" t="s">
-        <v>3259</v>
+        <v>3283</v>
       </c>
       <c r="K656">
         <v>2009</v>
@@ -39081,19 +40210,19 @@
         <v>43</v>
       </c>
       <c r="B657" t="s">
-        <v>3260</v>
+        <v>3284</v>
       </c>
       <c r="G657" t="s">
-        <v>3261</v>
+        <v>3285</v>
       </c>
       <c r="H657" t="s">
-        <v>3262</v>
+        <v>3286</v>
       </c>
       <c r="I657" t="s">
         <v>2054</v>
       </c>
       <c r="J657" t="s">
-        <v>3263</v>
+        <v>3287</v>
       </c>
       <c r="K657">
         <v>2013</v>
@@ -39105,19 +40234,19 @@
         <v>43</v>
       </c>
       <c r="B658" t="s">
-        <v>3264</v>
+        <v>3288</v>
       </c>
       <c r="G658" t="s">
-        <v>3265</v>
+        <v>3289</v>
       </c>
       <c r="H658" t="s">
-        <v>3266</v>
+        <v>3290</v>
       </c>
       <c r="I658" t="s">
-        <v>2880</v>
+        <v>2904</v>
       </c>
       <c r="J658" t="s">
-        <v>3267</v>
+        <v>3291</v>
       </c>
       <c r="K658">
         <v>2014</v>
@@ -39129,19 +40258,19 @@
         <v>43</v>
       </c>
       <c r="B659" t="s">
-        <v>3268</v>
+        <v>3292</v>
       </c>
       <c r="G659" t="s">
-        <v>3269</v>
+        <v>3293</v>
       </c>
       <c r="H659" t="s">
-        <v>3270</v>
+        <v>3294</v>
       </c>
       <c r="I659" t="s">
         <v>1987</v>
       </c>
       <c r="J659" t="s">
-        <v>3271</v>
+        <v>3295</v>
       </c>
       <c r="K659">
         <v>2024</v>
@@ -39153,19 +40282,19 @@
         <v>43</v>
       </c>
       <c r="B660" t="s">
-        <v>3272</v>
+        <v>3296</v>
       </c>
       <c r="G660" t="s">
-        <v>3273</v>
+        <v>3297</v>
       </c>
       <c r="H660" t="s">
-        <v>3274</v>
+        <v>3298</v>
       </c>
       <c r="I660" t="s">
         <v>51</v>
       </c>
       <c r="J660" t="s">
-        <v>3275</v>
+        <v>3299</v>
       </c>
       <c r="K660">
         <v>2023</v>
@@ -39177,19 +40306,19 @@
         <v>43</v>
       </c>
       <c r="B661" t="s">
-        <v>3276</v>
+        <v>3300</v>
       </c>
       <c r="G661" t="s">
-        <v>3277</v>
+        <v>3301</v>
       </c>
       <c r="H661" t="s">
-        <v>3278</v>
+        <v>3302</v>
       </c>
       <c r="I661" t="s">
         <v>664</v>
       </c>
       <c r="J661" t="s">
-        <v>3279</v>
+        <v>3303</v>
       </c>
       <c r="K661">
         <v>2001</v>
@@ -39201,19 +40330,19 @@
         <v>43</v>
       </c>
       <c r="B662" t="s">
-        <v>3280</v>
+        <v>3304</v>
       </c>
       <c r="G662" t="s">
-        <v>3281</v>
+        <v>3305</v>
       </c>
       <c r="H662" t="s">
-        <v>3282</v>
+        <v>3306</v>
       </c>
       <c r="I662" t="s">
-        <v>2867</v>
+        <v>2891</v>
       </c>
       <c r="J662" t="s">
-        <v>3283</v>
+        <v>3307</v>
       </c>
       <c r="K662">
         <v>2024</v>
@@ -39225,19 +40354,19 @@
         <v>43</v>
       </c>
       <c r="B663" t="s">
-        <v>3284</v>
+        <v>3308</v>
       </c>
       <c r="G663" t="s">
-        <v>3285</v>
+        <v>3309</v>
       </c>
       <c r="H663" t="s">
-        <v>3286</v>
+        <v>3310</v>
       </c>
       <c r="I663" t="s">
-        <v>3042</v>
+        <v>3066</v>
       </c>
       <c r="J663" t="s">
-        <v>3287</v>
+        <v>3311</v>
       </c>
       <c r="K663">
         <v>2025</v>
@@ -39249,19 +40378,19 @@
         <v>43</v>
       </c>
       <c r="B664" t="s">
-        <v>3288</v>
+        <v>3312</v>
       </c>
       <c r="G664" t="s">
-        <v>3289</v>
+        <v>3313</v>
       </c>
       <c r="H664" t="s">
-        <v>3290</v>
+        <v>3314</v>
       </c>
       <c r="I664" t="s">
         <v>409</v>
       </c>
       <c r="J664" t="s">
-        <v>3291</v>
+        <v>3315</v>
       </c>
       <c r="K664">
         <v>2022</v>
@@ -39273,19 +40402,19 @@
         <v>43</v>
       </c>
       <c r="B665" t="s">
-        <v>3292</v>
+        <v>3316</v>
       </c>
       <c r="G665" t="s">
-        <v>3293</v>
+        <v>3317</v>
       </c>
       <c r="H665" t="s">
-        <v>3294</v>
+        <v>3318</v>
       </c>
       <c r="I665" t="s">
-        <v>3295</v>
+        <v>3319</v>
       </c>
       <c r="J665" t="s">
-        <v>3296</v>
+        <v>3320</v>
       </c>
       <c r="K665">
         <v>2014</v>
@@ -39297,19 +40426,19 @@
         <v>43</v>
       </c>
       <c r="B666" t="s">
-        <v>3297</v>
+        <v>3321</v>
       </c>
       <c r="G666" t="s">
-        <v>3298</v>
+        <v>3322</v>
       </c>
       <c r="H666" t="s">
-        <v>3299</v>
+        <v>3323</v>
       </c>
       <c r="I666" t="s">
         <v>1414</v>
       </c>
       <c r="J666" t="s">
-        <v>3300</v>
+        <v>3324</v>
       </c>
       <c r="K666">
         <v>2025</v>
@@ -39321,19 +40450,19 @@
         <v>43</v>
       </c>
       <c r="B667" t="s">
-        <v>3301</v>
+        <v>3325</v>
       </c>
       <c r="G667" t="s">
-        <v>3302</v>
+        <v>3326</v>
       </c>
       <c r="H667" t="s">
-        <v>3303</v>
+        <v>3327</v>
       </c>
       <c r="I667" t="s">
         <v>459</v>
       </c>
       <c r="J667" t="s">
-        <v>3304</v>
+        <v>3328</v>
       </c>
       <c r="K667">
         <v>2016</v>
@@ -39345,19 +40474,19 @@
         <v>43</v>
       </c>
       <c r="B668" t="s">
-        <v>3305</v>
+        <v>3329</v>
       </c>
       <c r="G668" t="s">
-        <v>3306</v>
+        <v>3330</v>
       </c>
       <c r="H668" t="s">
-        <v>3307</v>
+        <v>3331</v>
       </c>
       <c r="I668" t="s">
-        <v>3308</v>
+        <v>3332</v>
       </c>
       <c r="J668" t="s">
-        <v>3309</v>
+        <v>3333</v>
       </c>
       <c r="K668">
         <v>2018</v>
@@ -39369,19 +40498,19 @@
         <v>43</v>
       </c>
       <c r="B669" t="s">
-        <v>3310</v>
+        <v>3334</v>
       </c>
       <c r="G669" t="s">
-        <v>3311</v>
+        <v>3335</v>
       </c>
       <c r="H669" t="s">
-        <v>3312</v>
+        <v>3336</v>
       </c>
       <c r="I669" t="s">
         <v>426</v>
       </c>
       <c r="J669" t="s">
-        <v>3313</v>
+        <v>3337</v>
       </c>
       <c r="K669">
         <v>2015</v>
@@ -39393,19 +40522,19 @@
         <v>43</v>
       </c>
       <c r="B670" t="s">
-        <v>3314</v>
+        <v>3338</v>
       </c>
       <c r="G670" t="s">
-        <v>3315</v>
+        <v>3339</v>
       </c>
       <c r="H670" t="s">
-        <v>3316</v>
+        <v>3340</v>
       </c>
       <c r="I670" t="s">
-        <v>3317</v>
+        <v>3341</v>
       </c>
       <c r="J670" t="s">
-        <v>3318</v>
+        <v>3342</v>
       </c>
       <c r="K670">
         <v>2018</v>
@@ -39417,19 +40546,19 @@
         <v>43</v>
       </c>
       <c r="B671" t="s">
-        <v>3319</v>
+        <v>3343</v>
       </c>
       <c r="G671" t="s">
-        <v>3320</v>
+        <v>3344</v>
       </c>
       <c r="H671" t="s">
-        <v>3321</v>
+        <v>3345</v>
       </c>
       <c r="I671" t="s">
         <v>2236</v>
       </c>
       <c r="J671" t="s">
-        <v>3322</v>
+        <v>3346</v>
       </c>
       <c r="K671">
         <v>2011</v>
@@ -39441,19 +40570,19 @@
         <v>43</v>
       </c>
       <c r="B672" t="s">
-        <v>3323</v>
+        <v>3347</v>
       </c>
       <c r="G672" t="s">
-        <v>3324</v>
+        <v>3348</v>
       </c>
       <c r="H672" t="s">
-        <v>3325</v>
+        <v>3349</v>
       </c>
       <c r="I672" t="s">
         <v>128</v>
       </c>
       <c r="J672" t="s">
-        <v>3326</v>
+        <v>3350</v>
       </c>
       <c r="K672">
         <v>2015</v>
@@ -39465,19 +40594,19 @@
         <v>43</v>
       </c>
       <c r="B673" t="s">
-        <v>3327</v>
+        <v>3351</v>
       </c>
       <c r="G673" t="s">
-        <v>3328</v>
+        <v>3352</v>
       </c>
       <c r="H673" t="s">
-        <v>3329</v>
+        <v>3353</v>
       </c>
       <c r="I673" t="s">
         <v>1479</v>
       </c>
       <c r="J673" t="s">
-        <v>3330</v>
+        <v>3354</v>
       </c>
       <c r="K673">
         <v>2022</v>
@@ -39489,19 +40618,19 @@
         <v>43</v>
       </c>
       <c r="B674" t="s">
-        <v>3331</v>
+        <v>3355</v>
       </c>
       <c r="G674" t="s">
+        <v>3356</v>
+      </c>
+      <c r="H674" t="s">
+        <v>3357</v>
+      </c>
+      <c r="I674" t="s">
         <v>3332</v>
       </c>
-      <c r="H674" t="s">
-        <v>3333</v>
-      </c>
-      <c r="I674" t="s">
-        <v>3308</v>
-      </c>
       <c r="J674" t="s">
-        <v>3334</v>
+        <v>3358</v>
       </c>
       <c r="K674">
         <v>2023</v>
@@ -39513,19 +40642,19 @@
         <v>43</v>
       </c>
       <c r="B675" t="s">
-        <v>3335</v>
+        <v>3359</v>
       </c>
       <c r="G675" t="s">
-        <v>3336</v>
+        <v>3360</v>
       </c>
       <c r="H675" t="s">
-        <v>3337</v>
+        <v>3361</v>
       </c>
       <c r="I675" t="s">
-        <v>3338</v>
+        <v>3362</v>
       </c>
       <c r="J675" t="s">
-        <v>3339</v>
+        <v>3363</v>
       </c>
       <c r="K675">
         <v>2021</v>
@@ -39537,19 +40666,19 @@
         <v>43</v>
       </c>
       <c r="B676" t="s">
-        <v>3340</v>
+        <v>3364</v>
       </c>
       <c r="G676" t="s">
-        <v>3341</v>
+        <v>3365</v>
       </c>
       <c r="H676" t="s">
-        <v>3342</v>
+        <v>3366</v>
       </c>
       <c r="I676" t="s">
         <v>1674</v>
       </c>
       <c r="J676" t="s">
-        <v>3343</v>
+        <v>3367</v>
       </c>
       <c r="K676">
         <v>2022</v>
@@ -39561,19 +40690,19 @@
         <v>43</v>
       </c>
       <c r="B677" t="s">
-        <v>3344</v>
+        <v>3368</v>
       </c>
       <c r="G677" t="s">
-        <v>3345</v>
+        <v>3369</v>
       </c>
       <c r="H677" t="s">
-        <v>3346</v>
+        <v>3370</v>
       </c>
       <c r="I677" t="s">
         <v>687</v>
       </c>
       <c r="J677" t="s">
-        <v>3347</v>
+        <v>3371</v>
       </c>
       <c r="K677">
         <v>2026</v>
@@ -39585,19 +40714,19 @@
         <v>43</v>
       </c>
       <c r="B678" t="s">
-        <v>3348</v>
+        <v>3372</v>
       </c>
       <c r="G678" t="s">
-        <v>3349</v>
+        <v>3373</v>
       </c>
       <c r="H678" t="s">
-        <v>3350</v>
+        <v>3374</v>
       </c>
       <c r="I678" t="s">
         <v>409</v>
       </c>
       <c r="J678" t="s">
-        <v>3351</v>
+        <v>3375</v>
       </c>
       <c r="K678">
         <v>2022</v>
@@ -39609,19 +40738,19 @@
         <v>43</v>
       </c>
       <c r="B679" t="s">
-        <v>3352</v>
+        <v>3376</v>
       </c>
       <c r="G679" t="s">
-        <v>3353</v>
+        <v>3377</v>
       </c>
       <c r="H679" t="s">
-        <v>3354</v>
+        <v>3378</v>
       </c>
       <c r="I679" t="s">
         <v>51</v>
       </c>
       <c r="J679" t="s">
-        <v>3355</v>
+        <v>3379</v>
       </c>
       <c r="K679">
         <v>2019</v>
@@ -39633,19 +40762,19 @@
         <v>43</v>
       </c>
       <c r="B680" t="s">
-        <v>3356</v>
+        <v>3380</v>
       </c>
       <c r="G680" t="s">
-        <v>3357</v>
+        <v>3381</v>
       </c>
       <c r="H680" t="s">
-        <v>3358</v>
+        <v>3382</v>
       </c>
       <c r="I680" t="s">
-        <v>3359</v>
+        <v>3383</v>
       </c>
       <c r="J680" t="s">
-        <v>3360</v>
+        <v>3384</v>
       </c>
       <c r="K680">
         <v>2021</v>
@@ -39657,19 +40786,19 @@
         <v>43</v>
       </c>
       <c r="B681" t="s">
-        <v>3361</v>
+        <v>3385</v>
       </c>
       <c r="G681" t="s">
-        <v>3362</v>
+        <v>3386</v>
       </c>
       <c r="H681" t="s">
-        <v>3363</v>
+        <v>3387</v>
       </c>
       <c r="I681" t="s">
         <v>237</v>
       </c>
       <c r="J681" t="s">
-        <v>3364</v>
+        <v>3388</v>
       </c>
       <c r="K681">
         <v>2017</v>
@@ -39681,19 +40810,19 @@
         <v>43</v>
       </c>
       <c r="B682" t="s">
-        <v>3365</v>
+        <v>3389</v>
       </c>
       <c r="G682" t="s">
-        <v>3366</v>
+        <v>3390</v>
       </c>
       <c r="H682" t="s">
-        <v>3367</v>
+        <v>3391</v>
       </c>
       <c r="I682" t="s">
         <v>1080</v>
       </c>
       <c r="J682" t="s">
-        <v>3368</v>
+        <v>3392</v>
       </c>
       <c r="K682">
         <v>2025</v>
@@ -39705,19 +40834,19 @@
         <v>43</v>
       </c>
       <c r="B683" t="s">
-        <v>3369</v>
+        <v>3393</v>
       </c>
       <c r="G683" t="s">
-        <v>3370</v>
+        <v>3394</v>
       </c>
       <c r="H683" t="s">
-        <v>3371</v>
+        <v>3395</v>
       </c>
       <c r="I683" t="s">
         <v>237</v>
       </c>
       <c r="J683" t="s">
-        <v>3372</v>
+        <v>3396</v>
       </c>
       <c r="K683">
         <v>2025</v>
@@ -39729,19 +40858,19 @@
         <v>43</v>
       </c>
       <c r="B684" t="s">
-        <v>3373</v>
+        <v>3397</v>
       </c>
       <c r="G684" t="s">
-        <v>3374</v>
+        <v>3398</v>
       </c>
       <c r="H684" t="s">
-        <v>3375</v>
+        <v>3399</v>
       </c>
       <c r="I684" t="s">
         <v>819</v>
       </c>
       <c r="J684" t="s">
-        <v>3376</v>
+        <v>3400</v>
       </c>
       <c r="K684">
         <v>2019</v>
@@ -39753,19 +40882,19 @@
         <v>43</v>
       </c>
       <c r="B685" t="s">
-        <v>3377</v>
+        <v>3401</v>
       </c>
       <c r="G685" t="s">
-        <v>3378</v>
+        <v>3402</v>
       </c>
       <c r="H685" t="s">
-        <v>3379</v>
+        <v>3403</v>
       </c>
       <c r="I685" t="s">
         <v>415</v>
       </c>
       <c r="J685" t="s">
-        <v>3380</v>
+        <v>3404</v>
       </c>
       <c r="K685">
         <v>2024</v>
@@ -39777,19 +40906,19 @@
         <v>43</v>
       </c>
       <c r="B686" t="s">
-        <v>3381</v>
+        <v>3405</v>
       </c>
       <c r="G686" t="s">
-        <v>3382</v>
+        <v>3406</v>
       </c>
       <c r="H686" t="s">
-        <v>3383</v>
+        <v>3407</v>
       </c>
       <c r="I686" t="s">
-        <v>3384</v>
+        <v>3408</v>
       </c>
       <c r="J686" t="s">
-        <v>3385</v>
+        <v>3409</v>
       </c>
       <c r="K686">
         <v>2024</v>
@@ -39801,19 +40930,19 @@
         <v>43</v>
       </c>
       <c r="B687" t="s">
-        <v>3386</v>
+        <v>3410</v>
       </c>
       <c r="G687" t="s">
-        <v>3387</v>
+        <v>3411</v>
       </c>
       <c r="H687" t="s">
-        <v>3388</v>
+        <v>3412</v>
       </c>
       <c r="I687" t="s">
         <v>1929</v>
       </c>
       <c r="J687" t="s">
-        <v>3389</v>
+        <v>3413</v>
       </c>
       <c r="K687">
         <v>2024</v>
@@ -39825,19 +40954,19 @@
         <v>43</v>
       </c>
       <c r="B688" t="s">
-        <v>3390</v>
+        <v>3414</v>
       </c>
       <c r="G688" t="s">
-        <v>3391</v>
+        <v>3415</v>
       </c>
       <c r="H688" t="s">
-        <v>3392</v>
+        <v>3416</v>
       </c>
       <c r="I688" t="s">
-        <v>3393</v>
+        <v>3417</v>
       </c>
       <c r="J688" t="s">
-        <v>3394</v>
+        <v>3418</v>
       </c>
       <c r="K688">
         <v>2023</v>
@@ -39849,19 +40978,19 @@
         <v>43</v>
       </c>
       <c r="B689" t="s">
-        <v>3395</v>
+        <v>3419</v>
       </c>
       <c r="G689" t="s">
-        <v>3396</v>
+        <v>3420</v>
       </c>
       <c r="H689" t="s">
-        <v>3397</v>
+        <v>3421</v>
       </c>
       <c r="I689" t="s">
-        <v>3398</v>
+        <v>3422</v>
       </c>
       <c r="J689" t="s">
-        <v>3399</v>
+        <v>3423</v>
       </c>
       <c r="K689">
         <v>2024</v>
@@ -39873,19 +41002,19 @@
         <v>43</v>
       </c>
       <c r="B690" t="s">
-        <v>3400</v>
+        <v>3424</v>
       </c>
       <c r="G690" t="s">
-        <v>3401</v>
+        <v>3425</v>
       </c>
       <c r="H690" t="s">
-        <v>3402</v>
+        <v>3426</v>
       </c>
       <c r="I690" t="s">
         <v>403</v>
       </c>
       <c r="J690" t="s">
-        <v>3403</v>
+        <v>3427</v>
       </c>
       <c r="K690">
         <v>2014</v>
@@ -39897,19 +41026,19 @@
         <v>43</v>
       </c>
       <c r="B691" t="s">
-        <v>3404</v>
+        <v>3428</v>
       </c>
       <c r="G691" t="s">
-        <v>3405</v>
+        <v>3429</v>
       </c>
       <c r="H691" t="s">
-        <v>3406</v>
+        <v>3430</v>
       </c>
       <c r="I691" t="s">
         <v>2043</v>
       </c>
       <c r="J691" t="s">
-        <v>3407</v>
+        <v>3431</v>
       </c>
       <c r="K691">
         <v>2024</v>
@@ -39921,19 +41050,19 @@
         <v>43</v>
       </c>
       <c r="B692" t="s">
-        <v>3408</v>
+        <v>3432</v>
       </c>
       <c r="G692" t="s">
-        <v>3409</v>
+        <v>3433</v>
       </c>
       <c r="H692" t="s">
-        <v>3410</v>
+        <v>3434</v>
       </c>
       <c r="I692" t="s">
-        <v>3411</v>
+        <v>3435</v>
       </c>
       <c r="J692" t="s">
-        <v>3412</v>
+        <v>3436</v>
       </c>
       <c r="K692">
         <v>2023</v>
@@ -39945,19 +41074,19 @@
         <v>43</v>
       </c>
       <c r="B693" t="s">
-        <v>3413</v>
+        <v>3437</v>
       </c>
       <c r="G693" t="s">
-        <v>3414</v>
+        <v>3438</v>
       </c>
       <c r="H693" t="s">
-        <v>3415</v>
+        <v>3439</v>
       </c>
       <c r="I693" t="s">
         <v>237</v>
       </c>
       <c r="J693" t="s">
-        <v>3416</v>
+        <v>3440</v>
       </c>
       <c r="K693">
         <v>2026</v>
@@ -39969,19 +41098,19 @@
         <v>43</v>
       </c>
       <c r="B694" t="s">
-        <v>3417</v>
+        <v>3441</v>
       </c>
       <c r="G694" t="s">
-        <v>3418</v>
+        <v>3442</v>
       </c>
       <c r="H694" t="s">
-        <v>3419</v>
+        <v>3443</v>
       </c>
       <c r="I694" t="s">
         <v>973</v>
       </c>
       <c r="J694" t="s">
-        <v>3420</v>
+        <v>3444</v>
       </c>
       <c r="K694">
         <v>2025</v>
@@ -39993,19 +41122,19 @@
         <v>43</v>
       </c>
       <c r="B695" t="s">
-        <v>3421</v>
+        <v>3445</v>
       </c>
       <c r="G695" t="s">
-        <v>3422</v>
+        <v>3446</v>
       </c>
       <c r="H695" t="s">
-        <v>3423</v>
+        <v>3447</v>
       </c>
       <c r="I695" t="s">
         <v>1929</v>
       </c>
       <c r="J695" t="s">
-        <v>3424</v>
+        <v>3448</v>
       </c>
       <c r="K695">
         <v>2020</v>
@@ -40017,19 +41146,19 @@
         <v>43</v>
       </c>
       <c r="B696" t="s">
-        <v>3425</v>
+        <v>3449</v>
       </c>
       <c r="G696" t="s">
-        <v>3426</v>
+        <v>3450</v>
       </c>
       <c r="H696" t="s">
-        <v>3427</v>
+        <v>3451</v>
       </c>
       <c r="I696" t="s">
         <v>973</v>
       </c>
       <c r="J696" t="s">
-        <v>3428</v>
+        <v>3452</v>
       </c>
       <c r="K696">
         <v>2024</v>
@@ -40041,19 +41170,19 @@
         <v>43</v>
       </c>
       <c r="B697" t="s">
-        <v>3429</v>
+        <v>3453</v>
       </c>
       <c r="G697" t="s">
-        <v>3430</v>
+        <v>3454</v>
       </c>
       <c r="H697" t="s">
-        <v>3431</v>
+        <v>3455</v>
       </c>
       <c r="I697" t="s">
         <v>1461</v>
       </c>
       <c r="J697" t="s">
-        <v>3432</v>
+        <v>3456</v>
       </c>
       <c r="K697">
         <v>2023</v>
@@ -40065,19 +41194,19 @@
         <v>43</v>
       </c>
       <c r="B698" t="s">
-        <v>3433</v>
+        <v>3457</v>
       </c>
       <c r="G698" t="s">
-        <v>3434</v>
+        <v>3458</v>
       </c>
       <c r="H698" t="s">
-        <v>3435</v>
+        <v>3459</v>
       </c>
       <c r="I698" t="s">
         <v>723</v>
       </c>
       <c r="J698" t="s">
-        <v>3436</v>
+        <v>3460</v>
       </c>
       <c r="K698">
         <v>2022</v>
@@ -40089,19 +41218,19 @@
         <v>43</v>
       </c>
       <c r="B699" t="s">
-        <v>3437</v>
+        <v>3461</v>
       </c>
       <c r="G699" t="s">
-        <v>3438</v>
+        <v>3462</v>
       </c>
       <c r="H699" t="s">
-        <v>3439</v>
+        <v>3463</v>
       </c>
       <c r="I699" t="s">
-        <v>3317</v>
+        <v>3341</v>
       </c>
       <c r="J699" t="s">
-        <v>3440</v>
+        <v>3464</v>
       </c>
       <c r="K699">
         <v>2017</v>
@@ -40113,19 +41242,19 @@
         <v>43</v>
       </c>
       <c r="B700" t="s">
-        <v>3441</v>
+        <v>3465</v>
       </c>
       <c r="G700" t="s">
-        <v>3442</v>
+        <v>3466</v>
       </c>
       <c r="H700" t="s">
-        <v>3443</v>
+        <v>3467</v>
       </c>
       <c r="I700" t="s">
         <v>915</v>
       </c>
       <c r="J700" t="s">
-        <v>3444</v>
+        <v>3468</v>
       </c>
       <c r="K700">
         <v>2024</v>
@@ -40137,19 +41266,19 @@
         <v>43</v>
       </c>
       <c r="B701" t="s">
-        <v>3445</v>
+        <v>3469</v>
       </c>
       <c r="G701" t="s">
-        <v>3446</v>
+        <v>3470</v>
       </c>
       <c r="H701" t="s">
-        <v>3447</v>
+        <v>3471</v>
       </c>
       <c r="I701" t="s">
-        <v>3448</v>
+        <v>3472</v>
       </c>
       <c r="J701" t="s">
-        <v>3449</v>
+        <v>3473</v>
       </c>
       <c r="K701">
         <v>2026</v>
@@ -40161,19 +41290,19 @@
         <v>43</v>
       </c>
       <c r="B702" t="s">
-        <v>3450</v>
+        <v>3474</v>
       </c>
       <c r="G702" t="s">
-        <v>3451</v>
+        <v>3475</v>
       </c>
       <c r="H702" t="s">
-        <v>3452</v>
+        <v>3476</v>
       </c>
       <c r="I702" t="s">
         <v>915</v>
       </c>
       <c r="J702" t="s">
-        <v>3453</v>
+        <v>3477</v>
       </c>
       <c r="K702">
         <v>2007</v>
@@ -40185,19 +41314,19 @@
         <v>43</v>
       </c>
       <c r="B703" t="s">
-        <v>3454</v>
+        <v>3478</v>
       </c>
       <c r="G703" t="s">
-        <v>3455</v>
+        <v>3479</v>
       </c>
       <c r="H703" t="s">
-        <v>3456</v>
+        <v>3480</v>
       </c>
       <c r="I703" t="s">
-        <v>3457</v>
+        <v>3481</v>
       </c>
       <c r="J703" t="s">
-        <v>3458</v>
+        <v>3482</v>
       </c>
       <c r="K703">
         <v>2013</v>
@@ -40209,19 +41338,19 @@
         <v>43</v>
       </c>
       <c r="B704" t="s">
-        <v>3459</v>
+        <v>3483</v>
       </c>
       <c r="G704" t="s">
-        <v>3460</v>
+        <v>3484</v>
       </c>
       <c r="H704" t="s">
-        <v>3461</v>
+        <v>3485</v>
       </c>
       <c r="I704" t="s">
         <v>51</v>
       </c>
       <c r="J704" t="s">
-        <v>3462</v>
+        <v>3486</v>
       </c>
       <c r="K704">
         <v>2001</v>

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="g:\My Drive\UCL\BSMA\BSMA ANTIGRAVITY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F2AE90-5D7B-4F01-AE7E-66F723FD9362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8040BD1-31DD-4027-90F8-808C72222622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="3647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5717" uniqueCount="3661">
   <si>
     <t>Coder Initials</t>
   </si>
@@ -7116,7 +7116,7 @@
     <t>N Bennett</t>
   </si>
   <si>
-    <t>Unit of analysis is the organization/HR department, not individual employee BSB.. Verbatim Evidence: "[Sample] "data for this analysis were collected from &amp; sample of Atlanta area worksites with at least 250 employees" [Sample] "Once the sample had been selected and confirmed, companies were contacted and interviews scheduled with the highest level human resource person at that site." [Chapter I] "The important difference between a focus on boundary spanning units and jobs is a level of analysis and has bcaring on thc choice of dependent variables:""</t>
+    <t>Macro-level analysis focusing on the personnel/human resource department as the boundary spanning unit, rather than individual employee behavior.. Verbatim Evidence: "[Title] "Personnel/human resource departments and uncertainty: A test of Thompson's model of boundary spanning units" [Table of Contents] "Chapter II P/HR Management as Boundary Spanning Mechanism: The Issue of Unit of Analysis in Boundary Spanning Research, A Brief History of Personnel Management; The P/HR Department as Boundary Spanner""</t>
   </si>
   <si>
     <t>BSMA0435</t>
@@ -7709,7 +7709,7 @@
     <t>R Katz</t>
   </si>
   <si>
-    <t>Old scanned PDF, unable to extract text. Assumed no extractable effect size.. Verbatim Evidence: "Manual Override"</t>
+    <t>Non-individual level (team analysis). Verbatim Evidence: "[Abstract] This study investigated the communication behaviors and performances of 50 R&amp;D project groupsthat variedin terms of group longevity, as measured by the average length of time project members had worked together."</t>
   </si>
   <si>
     <t>BSMA0471</t>
@@ -7763,6 +7763,9 @@
     <t>BSMA0474</t>
   </si>
   <si>
+    <t>ERROR</t>
+  </si>
+  <si>
     <t>Boundary-spanning activities were studied in 15 organizations engaged in basic and applied research. Included in the study were 281 scientists and engineers. Contrary to prior theory and research, this study found bound-ary-spanning activities to be unrelated to job satisfaction. It was strongly related to perceptions of research and development team collaboration, job motivation, task uncertainty, locus of control, team cohesiveness, and individualproductivity. The research reported here makes a strong case for including group processes and characteristics in future studies involving boundary-spanning activities. The results also give increased impetus to re-search which examines the relationships between boundary-spanning activi-ties and individual productivity.</t>
   </si>
   <si>
@@ -7770,6 +7773,9 @@
   </si>
   <si>
     <t>RC Dailey</t>
+  </si>
+  <si>
+    <t>. Verbatim Evidence: ""</t>
   </si>
   <si>
     <t>BSMA0475</t>
@@ -8080,6 +8086,9 @@
     <t>Rothbard, Nancy P.; Ramarajan, Lakshmi; Ollier-Malaterre, Ariane; Lee, Serenity S.</t>
   </si>
   <si>
+    <t>Measures work-personal boundary blurring (Facebook friend requests) rather than inter- or intra-organizational boundary spanning.. Verbatim Evidence: "[Abstract] "We propose and test a relational boundary-blurring framework, examining how employees’ evaluations of colleagues’ characteristics drive their decisions to connect with colleagues as friends online." [Abstract] "Our work contributes to boundary management research by demonstrating that employees’ decisions to blur the personal/professional boundary online crucially depends on whom they are blurring the boundary with.""</t>
+  </si>
+  <si>
     <t>BSMA0498</t>
   </si>
   <si>
@@ -8104,6 +8113,9 @@
     <t>RT Keller, AD Szilagyi Jr, WE Holland</t>
   </si>
   <si>
+    <t>Included. The study measures individual-level interpersonal boundary-spanning activities among 192 employees and provides a zero-order correlation matrix.. Verbatim Evidence: "[Sample] "The subjects were 192 managerial, engineering, and supervisory personnel (64% response rate) located at the company headquarters and main manufacturing plant." [Measures] "A 4-item BSA scale based on this prior work was developed and validated in two earlier studies of boundary-spanning in a research and development organization (Keller &amp; Holland, 1975a; 1975b)." [Appendix] "3. During the last month, indicate with a check the frequency with which you have sought information/advice from members of other organizations outside (name of company)." "4. During the last month, indicate with a check the frequency with which members of organizations outside (name of company) have sought information/advice from you." [Results] "Table I. Zero-Order Correlations between Boundary-Spanning Activity and Role, Satisfaction, and Job Characteristic Variables (Total Sample, N=192) (Two-Tailed Tests of Significance)""</t>
+  </si>
+  <si>
     <t>BSMA0500</t>
   </si>
   <si>
@@ -8117,6 +8129,9 @@
   </si>
   <si>
     <t>RT Keller, WE Holland</t>
+  </si>
+  <si>
+    <t>No effect size of interest (Lacks extractable zero-order correlation matrix). Verbatim Evidence: "[Data Analysis] "To conduct this analysis the treatment and control groups were dummy coded and then correlated with the pretest and post-test scores of a variable. The null hypothesis was tested by the equality of the two treatment-effect correlations via a test credited to Hotelling and described by Dunn and Clark (1971)." [Results] "The data in Table I report the raw means and the standardized change score analysis recommended by Kenny (1975). The raw means are reported only as information for the reader since they were not directly used in the tests for significant changes. Significant changes were tested by the differences between the treatment-effect correlations (not reported since the magnitudes of the correlations do not have meaning) as explained in the prior section.""</t>
   </si>
   <si>
     <t>BSMA0501</t>
@@ -8151,6 +8166,9 @@
     <t>Russ, Gail S; Galang, Maria Carmen; Ferris, Gerald R</t>
   </si>
   <si>
+    <t>Non-primary study (Conceptual paper). Verbatim Evidence: "[Abstract] "The human resource management (HRM) function has realized a considerable increase in power, influence, and reputation, but it has not been examined from the perspective of organizational boundary spanning. Because boundary spanning's function of information control provides a source of power, it is helpful in explaining HRM's growing influence in US organizations. However, our conceptualization of the boundary spanning role needs to be refined to incorporate developments after its initial creation. Hence, an evolutionary model is proposed that depicts two stages that the boundary spanning role subsequently undergoes when the conditions for its initial creation are no longer present to justify its existence. Despite what we have termed “phantom threats,” boundary spanners are able to maintain their influence through astute management of information that portrays their continued usefulness. This phase however cannot last forever, and boundary spanners need to discover new threats. A review of the development and evolution of HRM in the U.S. supports the proposed model. Because each of the three stages are reflected in the communication patterns of the boundary spanner, several propositions based on the notion of information richness and the nature of the language used in communicating with three critical groups (i.e., external contacts, management, and subordinate staff) are generated to test the model. Finally, suggestions for research are made." [CONCLUSION] "An examination of the growth of the HRM function to its present significance in organizations showed support for the proposed evolutionary model of boundary spanning roles. However, systematic testing still needs to be done to validate the model, and to confirm our interpretation of the developments observed with respect to the HRM function. Suggestions for research were therefore also provided.""</t>
+  </si>
+  <si>
     <t>BSMA0503</t>
   </si>
   <si>
@@ -8175,6 +8193,9 @@
     <t>Ryan, Annmarie; O’Malley, Lisa</t>
   </si>
   <si>
+    <t>Qualitative study without effect sizes. Verbatim Evidence: "[Abstract] This is achieved using data from a longitudinal analysis of a cross-sector partnership between a business and an arts organisation in Ireland. This offers a unique opportunity to trace the emergence of the partnership over time, and, specifically, to consider the impact of innovations co-created by the actors involved."</t>
+  </si>
+  <si>
     <t>BSMA0505</t>
   </si>
   <si>
@@ -8190,6 +8211,9 @@
     <t>S Ang, S Slaughter</t>
   </si>
   <si>
+    <t>Multiple reasons [Code 1 &amp; Code 3]: The study analyzes organizational/job-level structural data (Internal Labor Market strategies across 41 firms) rather than measuring interpersonal boundary spanning behavior of individual employees.. Verbatim Evidence: "[Abstract] "In this study we examine employee turnover from a structural perspective. We investigate the impact on IT turnover of organizations’ Internal Labor Market (ILM) strategies. ILM strategies include human resource rules, practices, and policies including hiring and promotion criteria, job ladders, wage systems and training procedures. We collect data on ILM strategies and turnover rates for eight major IT jobs across forty-one organizations and analyze the data using confirmatory agglomerative hierarchical clustering techniques." [Methodology] "To examine our hypotheses, we conducted multiple case studies with key IT and human resource (HR) informants from forty-one (41) organizations. [...] To elicit the ILM strategies for IT jobs in each organization, we identified eight major jobs in the IT profession""</t>
+  </si>
+  <si>
     <t>BSMA0506</t>
   </si>
   <si>
@@ -8229,6 +8253,9 @@
     <t>Saeed, Munazza; Bani-Melhem, Ahmad Jamal; Hassan, Hamid; Alvi, Tariq Hameed; Altaf, Saira</t>
   </si>
   <si>
+    <t>Study examines individual-level frontline employee customer-oriented boundary-spanning behaviors and provides a correlation matrix.. Verbatim Evidence: "[Abstract] "Design/methodology/approach –Two-source (manager-frontline employee dyad)datawerecollectedthrough asurveyquestionnaire fromhospitality organizations atthreedifferentpointsintime." [Sample and procedure] "Thedataweregathered atthreepointsintimefromtwosources(manager-f rontline employees dyads)usingasurveyquestionnaire inthree-to-five-star hotelsinPakistan." "Afteraligning thedatathroughdistinctive codesand thorough assessment, only245responses werekeptandusedforfurtheranalysis." [Measures] "Customer-oriented boundary-spanning behaviors were evaluated usingathirteen-item scaledeveloped byBettencourt etal.(2005).Asampleitem was“Thisemployee followscustomer serviceguidelines withextremecare.”" [Results] "Table2.Descriptive statisticsandcorrelations""</t>
+  </si>
+  <si>
     <t>BSMA0509</t>
   </si>
   <si>
@@ -8263,6 +8290,9 @@
   </si>
   <si>
     <t>Satheesh, Shreya Anna; Van Meerkerk, Ingmar; Verweij, Stefan; Busscher, Tim; Arts, Jos</t>
+  </si>
+  <si>
+    <t>Non-independent observations (repeated measures): Respondents were asked to fill out the survey for up to two projects, and the unit of analysis is the survey response (N=158), meaning some individuals appear multiple times in the dataset.. Verbatim Evidence: "[Sample and data collection] "This created a project pool of 68 projects and 406 potential respondents with 308 unique respondents. Respondents were asked to fill in the survey for a specific project. If they were involved in more than one project, they were asked to fill out the survey for a maximum of two projects (the most recent ones in which they were involved). After eliminating 14 invalid email addresses, the sample size was 392. The survey was conducted between October 2020 and January 2021. A total of 171 public managers from Rijkswaterstaat responded (the response rate after two follow-ups was 43.6%), out of which13 responses were deleted due to a completion rate of less than 35%. This resulted in a dataset with 158 responses""</t>
   </si>
   <si>
     <t>BSMA0512</t>
@@ -20162,6 +20192,215 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> members were good networkers""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">No effect size of interest (No correlation matrix or quantitative effect sizes provided). Verbatim Evidence: "[Introduction] "The purpose of this article is to examine the critical role that </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> leaders play and the challenges they face in a cross-functional sourcing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> environment. The final section details three assessment scales used to help identify a sourcing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> leader’s behavioral style and ability to satisfy critical leadership requirements." [Assessing Cross-Functional Sourcing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Leadership] "The statistical revision and development of these scales used responses from over 620 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> members and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> leaders working at 18 firms based in the United States.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Non-individual level. The unit of analysis is the work group, and boundary spanning (scout activities) is measured at the group level.. Verbatim Evidence: "[Sample and Level of Analysis] "Thirty-three o f the 47 groups met the requirements and were used for hypothesis testing." "To aggregate individual data to the group level, I averaged the responses from the individual </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> members for each variable o f interest" [Boundary Spanning Construct] "Ancona and Caldwell (1988) identified two group activities that are associated with initiating transactions. The first, scout activities , was defined as \"activities that involve bringing information and/or resources needed by the group in across the boundary\" (p. 473)." "Hypothesis 9. The relationship between group scout activities and group support for innovation will be curvilinear.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Conceptual paper without primary data. Verbatim Evidence: "[Abstract] "This conceptual paper contends the cause of the success or failure of a project rests with the individuals who, in theory, comprise the project </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.""</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Study measures advice-seeking network degree centrality (purposive knowledge acquisition ties) among SME managers and provides an individual-level zero-order correlation matrix.. Verbatim Evidence: "[Sample] "In small biotech SMEs (the majority of organizations in the cluster), only the founder/CEO completed the survey. In larger organizations, other members of the top management </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>team</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> participated as well." [Sample] "The final sample includes information on 48 managers from 36 organizations" [Measures] "Our dependent variable is the occurrence of knowledge acquisition ties in an interpersonal knowledge network among managers. We collected network data using a roster containing the names of all managers and asked the participants to indicate all persons from whom they regularly acquired knowledge and information concerning work-related matters." [Table 3] "Table 3 Correlations ... N=48 managers.""</t>
     </r>
   </si>
 </sst>
@@ -20924,7 +21163,7 @@
         <v>2002</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>3487</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21020,7 +21259,7 @@
         <v>2016</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>3488</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21180,7 +21419,7 @@
         <v>2008</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>3489</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21212,7 +21451,7 @@
         <v>2012</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>3490</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21500,7 +21739,7 @@
         <v>1992</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>3491</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21628,7 +21867,7 @@
         <v>2024</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>3492</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21660,7 +21899,7 @@
         <v>2017</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>3493</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21820,7 +22059,7 @@
         <v>2022</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>3494</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21945,7 +22184,7 @@
         <v>2020</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>3495</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22041,7 +22280,7 @@
         <v>1997</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>3496</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22105,7 +22344,7 @@
         <v>2021</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>3497</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22509,7 +22748,7 @@
         <v>2018</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>3498</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22538,7 +22777,7 @@
         <v>2015</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>3499</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22724,7 +22963,7 @@
         <v>2011</v>
       </c>
       <c r="P61" s="8" t="s">
-        <v>3500</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22977,7 +23216,7 @@
         <v>2012</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>3501</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23230,7 +23469,7 @@
         <v>2025</v>
       </c>
       <c r="P77" s="8" t="s">
-        <v>3502</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23262,7 +23501,7 @@
         <v>2023</v>
       </c>
       <c r="P78" s="8" t="s">
-        <v>3503</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23294,7 +23533,7 @@
         <v>2019</v>
       </c>
       <c r="P79" s="8" t="s">
-        <v>3504</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23422,7 +23661,7 @@
         <v>2005</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>3505</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23454,7 +23693,7 @@
         <v>2020</v>
       </c>
       <c r="P84" s="8" t="s">
-        <v>3506</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23483,7 +23722,7 @@
         <v>2021</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>3507</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23675,7 +23914,7 @@
         <v>2010</v>
       </c>
       <c r="P91" s="8" t="s">
-        <v>3508</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23771,7 +24010,7 @@
         <v>2024</v>
       </c>
       <c r="P94" s="8" t="s">
-        <v>3509</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23803,7 +24042,7 @@
         <v>2020</v>
       </c>
       <c r="P95" s="8" t="s">
-        <v>3510</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23864,7 +24103,7 @@
         <v>2021</v>
       </c>
       <c r="P97" s="8" t="s">
-        <v>3511</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23893,7 +24132,7 @@
         <v>2012</v>
       </c>
       <c r="P98" s="8" t="s">
-        <v>3512</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23957,7 +24196,7 @@
         <v>1995</v>
       </c>
       <c r="P100" s="8" t="s">
-        <v>3513</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23989,7 +24228,7 @@
         <v>2008</v>
       </c>
       <c r="P101" s="8" t="s">
-        <v>3514</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24082,7 +24321,7 @@
         <v>2010</v>
       </c>
       <c r="P104" s="8" t="s">
-        <v>3515</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24306,7 +24545,7 @@
         <v>2018</v>
       </c>
       <c r="P111" s="8" t="s">
-        <v>3516</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24402,7 +24641,7 @@
         <v>2018</v>
       </c>
       <c r="P114" s="8" t="s">
-        <v>3517</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24530,7 +24769,7 @@
         <v>2016</v>
       </c>
       <c r="P118" s="8" t="s">
-        <v>3518</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24559,7 +24798,7 @@
         <v>1978</v>
       </c>
       <c r="P119" s="8" t="s">
-        <v>3519</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24623,7 +24862,7 @@
         <v>2012</v>
       </c>
       <c r="P121" s="8" t="s">
-        <v>3520</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24687,7 +24926,7 @@
         <v>2004</v>
       </c>
       <c r="P123" s="8" t="s">
-        <v>3521</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24934,7 +25173,7 @@
         <v>1996</v>
       </c>
       <c r="P131" s="8" t="s">
-        <v>3522</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24966,7 +25205,7 @@
         <v>2004</v>
       </c>
       <c r="P132" s="8" t="s">
-        <v>3523</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25030,7 +25269,7 @@
         <v>1990</v>
       </c>
       <c r="P134" s="8" t="s">
-        <v>3524</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="135" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25158,7 +25397,7 @@
         <v>1984</v>
       </c>
       <c r="P138" s="8" t="s">
-        <v>3525</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25382,7 +25621,7 @@
         <v>2011</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>3526</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25414,7 +25653,7 @@
         <v>2003</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>3527</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25574,7 +25813,7 @@
         <v>2014</v>
       </c>
       <c r="P151" s="8" t="s">
-        <v>3528</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25702,7 +25941,7 @@
         <v>2019</v>
       </c>
       <c r="P155" s="8" t="s">
-        <v>3529</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="156" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25766,7 +26005,7 @@
         <v>2009</v>
       </c>
       <c r="P157" s="8" t="s">
-        <v>3530</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25830,7 +26069,7 @@
         <v>2019</v>
       </c>
       <c r="P159" s="8" t="s">
-        <v>3531</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26179,7 +26418,7 @@
         <v>1998</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>3532</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26400,7 +26639,7 @@
         <v>2022</v>
       </c>
       <c r="P177" s="8" t="s">
-        <v>3533</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="178" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26464,7 +26703,7 @@
         <v>1997</v>
       </c>
       <c r="P179" s="8" t="s">
-        <v>3534</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="180" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26496,7 +26735,7 @@
         <v>2022</v>
       </c>
       <c r="P180" s="8" t="s">
-        <v>3535</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26688,7 +26927,7 @@
         <v>2023</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>3536</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26720,7 +26959,7 @@
         <v>2013</v>
       </c>
       <c r="P187" s="8" t="s">
-        <v>3537</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="188" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26909,7 +27148,7 @@
         <v>2010</v>
       </c>
       <c r="P193" s="8" t="s">
-        <v>3538</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="194" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27005,7 +27244,7 @@
         <v>2012</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>3539</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="197" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27034,7 +27273,7 @@
         <v>2015</v>
       </c>
       <c r="P197" s="8" t="s">
-        <v>3540</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="198" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27098,7 +27337,7 @@
         <v>2015</v>
       </c>
       <c r="P199" s="8" t="s">
-        <v>3541</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="200" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27258,7 +27497,7 @@
         <v>2005</v>
       </c>
       <c r="P204" s="8" t="s">
-        <v>3542</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27351,7 +27590,7 @@
         <v>1998</v>
       </c>
       <c r="P207" s="8" t="s">
-        <v>3543</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27383,7 +27622,7 @@
         <v>1999</v>
       </c>
       <c r="P208" s="8" t="s">
-        <v>3544</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="209" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27473,7 +27712,7 @@
         <v>2024</v>
       </c>
       <c r="P211" s="8" t="s">
-        <v>3545</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="212" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27505,7 +27744,7 @@
         <v>2006</v>
       </c>
       <c r="P212" s="8" t="s">
-        <v>3546</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="213" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27537,7 +27776,7 @@
         <v>2010</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>3547</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="214" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27598,7 +27837,7 @@
         <v>2017</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>3548</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="216" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27726,7 +27965,7 @@
         <v>2014</v>
       </c>
       <c r="P219" s="8" t="s">
-        <v>3549</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27758,7 +27997,7 @@
         <v>2011</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>3550</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="221" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27854,7 +28093,7 @@
         <v>2015</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>3551</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="224" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27918,7 +28157,7 @@
         <v>2023</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>3552</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27947,7 +28186,7 @@
         <v>2004</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>3553</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="227" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28043,7 +28282,7 @@
         <v>2005</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>3554</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="230" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28075,7 +28314,7 @@
         <v>2004</v>
       </c>
       <c r="P230" s="8" t="s">
-        <v>3555</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="231" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28171,7 +28410,7 @@
         <v>1998</v>
       </c>
       <c r="P233" s="8" t="s">
-        <v>3556</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="234" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28267,7 +28506,7 @@
         <v>2014</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>3557</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="237" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28488,7 +28727,7 @@
         <v>2011</v>
       </c>
       <c r="P243" s="8" t="s">
-        <v>3558</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28520,7 +28759,7 @@
         <v>2018</v>
       </c>
       <c r="P244" s="8" t="s">
-        <v>3559</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="245" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28552,7 +28791,7 @@
         <v>2019</v>
       </c>
       <c r="P245" s="8" t="s">
-        <v>3560</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="246" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28584,7 +28823,7 @@
         <v>1998</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>3561</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="247" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28738,7 +28977,7 @@
         <v>2012</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>3562</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="252" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28927,7 +29166,7 @@
         <v>1999</v>
       </c>
       <c r="P257" s="8" t="s">
-        <v>3563</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="258" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28991,7 +29230,7 @@
         <v>2022</v>
       </c>
       <c r="P259" s="8" t="s">
-        <v>3564</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29148,7 +29387,7 @@
         <v>2023</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>3565</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29209,7 +29448,7 @@
         <v>2023</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>3566</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="267" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29241,7 +29480,7 @@
         <v>2018</v>
       </c>
       <c r="P267" s="8" t="s">
-        <v>3567</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="268" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29273,7 +29512,7 @@
         <v>2025</v>
       </c>
       <c r="P268" s="8" t="s">
-        <v>3568</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="269" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29302,7 +29541,7 @@
         <v>2010</v>
       </c>
       <c r="P269" s="8" t="s">
-        <v>3569</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="270" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29392,7 +29631,7 @@
         <v>2002</v>
       </c>
       <c r="P272" s="8" t="s">
-        <v>3570</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29485,7 +29724,7 @@
         <v>2020</v>
       </c>
       <c r="P275" s="8" t="s">
-        <v>3571</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29613,7 +29852,7 @@
         <v>1996</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>3572</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29642,7 +29881,7 @@
         <v>2020</v>
       </c>
       <c r="P280" s="8" t="s">
-        <v>3573</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="281" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29674,7 +29913,7 @@
         <v>2003</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>3574</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29770,7 +30009,7 @@
         <v>2022</v>
       </c>
       <c r="P284" s="8" t="s">
-        <v>3575</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29802,7 +30041,7 @@
         <v>2000</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>3576</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30209,7 +30448,7 @@
         <v>2024</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>3577</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30363,7 +30602,7 @@
         <v>2011</v>
       </c>
       <c r="P303" s="8" t="s">
-        <v>3578</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30424,7 +30663,7 @@
         <v>2022</v>
       </c>
       <c r="P305" s="8" t="s">
-        <v>3579</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30482,7 +30721,7 @@
         <v>2022</v>
       </c>
       <c r="P307" s="8" t="s">
-        <v>3580</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30511,7 +30750,7 @@
         <v>2025</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>3581</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30540,7 +30779,7 @@
         <v>2002</v>
       </c>
       <c r="P309" s="8" t="s">
-        <v>3582</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30889,7 +31128,7 @@
         <v>2008</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>3583</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="321" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31017,7 +31256,7 @@
         <v>2020</v>
       </c>
       <c r="P324" s="8" t="s">
-        <v>3584</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31081,7 +31320,7 @@
         <v>2004</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>3585</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31145,7 +31384,7 @@
         <v>2015</v>
       </c>
       <c r="P328" s="8" t="s">
-        <v>3586</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31334,7 +31573,7 @@
         <v>1991</v>
       </c>
       <c r="P334" s="8" t="s">
-        <v>3587</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31366,7 +31605,7 @@
         <v>2023</v>
       </c>
       <c r="P335" s="8" t="s">
-        <v>3588</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31398,7 +31637,7 @@
         <v>2017</v>
       </c>
       <c r="P336" s="8" t="s">
-        <v>3589</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31520,7 +31759,7 @@
         <v>2011</v>
       </c>
       <c r="P340" s="8" t="s">
-        <v>3590</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="341" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31549,7 +31788,7 @@
         <v>2016</v>
       </c>
       <c r="P341" s="8" t="s">
-        <v>3591</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="342" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31581,7 +31820,7 @@
         <v>2020</v>
       </c>
       <c r="P342" s="8" t="s">
-        <v>3592</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31645,7 +31884,7 @@
         <v>2017</v>
       </c>
       <c r="P344" s="8" t="s">
-        <v>3593</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="345" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31677,7 +31916,7 @@
         <v>2024</v>
       </c>
       <c r="P345" s="8" t="s">
-        <v>3594</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="346" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31709,7 +31948,7 @@
         <v>2016</v>
       </c>
       <c r="P346" s="8" t="s">
-        <v>3595</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="347" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31741,7 +31980,7 @@
         <v>2022</v>
       </c>
       <c r="P347" s="8" t="s">
-        <v>3596</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="348" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31869,7 +32108,7 @@
         <v>2002</v>
       </c>
       <c r="P351" s="8" t="s">
-        <v>3597</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="352" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31898,7 +32137,7 @@
         <v>2022</v>
       </c>
       <c r="P352" s="8" t="s">
-        <v>3598</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="353" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31962,7 +32201,7 @@
         <v>2020</v>
       </c>
       <c r="P354" s="8" t="s">
-        <v>3599</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="355" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31994,7 +32233,7 @@
         <v>2024</v>
       </c>
       <c r="P355" s="8" t="s">
-        <v>3600</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="356" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32026,7 +32265,7 @@
         <v>2000</v>
       </c>
       <c r="P356" s="8" t="s">
-        <v>3601</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="357" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32122,7 +32361,7 @@
         <v>2023</v>
       </c>
       <c r="P359" s="8" t="s">
-        <v>3602</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="360" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32151,7 +32390,7 @@
         <v>2018</v>
       </c>
       <c r="P360" s="8" t="s">
-        <v>3603</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="361" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32180,7 +32419,7 @@
         <v>2014</v>
       </c>
       <c r="P361" s="8" t="s">
-        <v>3604</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="362" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32212,7 +32451,7 @@
         <v>2013</v>
       </c>
       <c r="P362" s="8" t="s">
-        <v>3605</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="363" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32244,7 +32483,7 @@
         <v>2025</v>
       </c>
       <c r="P363" s="8" t="s">
-        <v>3606</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="364" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32436,7 +32675,7 @@
         <v>2023</v>
       </c>
       <c r="P369" s="8" t="s">
-        <v>3607</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="370" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32532,7 +32771,7 @@
         <v>2023</v>
       </c>
       <c r="P372" s="8" t="s">
-        <v>3608</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="373" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32628,7 +32867,7 @@
         <v>1999</v>
       </c>
       <c r="P375" s="8" t="s">
-        <v>3609</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="376" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32692,7 +32931,7 @@
         <v>2023</v>
       </c>
       <c r="P377" s="8" t="s">
-        <v>3610</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="378" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32852,7 +33091,7 @@
         <v>2005</v>
       </c>
       <c r="P382" s="8" t="s">
-        <v>3611</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="383" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32884,7 +33123,7 @@
         <v>2007</v>
       </c>
       <c r="P383" s="8" t="s">
-        <v>3612</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="384" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32916,7 +33155,7 @@
         <v>2008</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>3613</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="385" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33038,7 +33277,7 @@
         <v>2019</v>
       </c>
       <c r="P388" s="8" t="s">
-        <v>3614</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="389" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33070,7 +33309,7 @@
         <v>1994</v>
       </c>
       <c r="P389" s="8" t="s">
-        <v>3615</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="390" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33134,7 +33373,7 @@
         <v>2016</v>
       </c>
       <c r="P391" s="8" t="s">
-        <v>3616</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="392" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33166,7 +33405,7 @@
         <v>2015</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>3617</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="393" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33291,7 +33530,7 @@
         <v>2003</v>
       </c>
       <c r="P396" s="8" t="s">
-        <v>3618</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="397" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33387,7 +33626,7 @@
         <v>2005</v>
       </c>
       <c r="P399" s="8" t="s">
-        <v>3619</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="400" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33419,7 +33658,7 @@
         <v>2010</v>
       </c>
       <c r="P400" s="8" t="s">
-        <v>3620</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="401" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33448,7 +33687,7 @@
         <v>2022</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>3621</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="402" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33480,7 +33719,7 @@
         <v>2007</v>
       </c>
       <c r="P402" s="8" t="s">
-        <v>3622</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="403" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33576,7 +33815,7 @@
         <v>2006</v>
       </c>
       <c r="P405" s="8" t="s">
-        <v>3623</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="406" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33608,7 +33847,7 @@
         <v>2007</v>
       </c>
       <c r="P406" s="8" t="s">
-        <v>3624</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="407" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33640,7 +33879,7 @@
         <v>2025</v>
       </c>
       <c r="P407" s="8" t="s">
-        <v>3625</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="408" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33864,7 +34103,7 @@
         <v>2008</v>
       </c>
       <c r="P414" s="8" t="s">
-        <v>3626</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="415" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34050,7 +34289,7 @@
         <v>2011</v>
       </c>
       <c r="P420" s="8" t="s">
-        <v>3627</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="421" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34079,7 +34318,7 @@
         <v>2008</v>
       </c>
       <c r="P421" s="8" t="s">
-        <v>3628</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="422" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34428,7 +34667,7 @@
         <v>2019</v>
       </c>
       <c r="P432" s="8" t="s">
-        <v>3629</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="433" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34524,7 +34763,7 @@
         <v>2014</v>
       </c>
       <c r="P435" s="8" t="s">
-        <v>3630</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="436" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34556,7 +34795,7 @@
         <v>2005</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>3631</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="437" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34620,7 +34859,7 @@
         <v>2019</v>
       </c>
       <c r="P438" s="8" t="s">
-        <v>3632</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="439" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34780,7 +35019,7 @@
         <v>2019</v>
       </c>
       <c r="P443" s="8" t="s">
-        <v>3633</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="444" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34844,7 +35083,7 @@
         <v>2013</v>
       </c>
       <c r="P445" s="8" t="s">
-        <v>3634</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="446" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34908,7 +35147,7 @@
         <v>2013</v>
       </c>
       <c r="P447" s="8" t="s">
-        <v>3635</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="448" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35126,7 +35365,7 @@
         <v>2003</v>
       </c>
       <c r="P454" s="8" t="s">
-        <v>3636</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="455" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35251,7 +35490,7 @@
         <v>2024</v>
       </c>
       <c r="P458" s="8" t="s">
-        <v>3637</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="459" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35315,7 +35554,7 @@
         <v>2024</v>
       </c>
       <c r="P460" s="8" t="s">
-        <v>3638</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="461" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35347,7 +35586,7 @@
         <v>2023</v>
       </c>
       <c r="P461" s="8" t="s">
-        <v>3639</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="462" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35507,7 +35746,7 @@
         <v>2017</v>
       </c>
       <c r="P466" s="8" t="s">
-        <v>3640</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="467" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35571,7 +35810,7 @@
         <v>2012</v>
       </c>
       <c r="P468" s="8" t="s">
-        <v>3641</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="469" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35600,7 +35839,7 @@
         <v>2021</v>
       </c>
       <c r="P469" s="8" t="s">
-        <v>3642</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="470" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35632,7 +35871,7 @@
         <v>2022</v>
       </c>
       <c r="P470" s="8" t="s">
-        <v>3643</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="471" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35664,7 +35903,7 @@
         <v>2018</v>
       </c>
       <c r="P471" s="8" t="s">
-        <v>3644</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="472" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35696,7 +35935,7 @@
         <v>2021</v>
       </c>
       <c r="P472" s="8" t="s">
-        <v>3645</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="473" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35706,11 +35945,11 @@
       <c r="B473" t="s">
         <v>2481</v>
       </c>
-      <c r="E473">
-        <v>0</v>
+      <c r="E473" t="s">
+        <v>85</v>
       </c>
       <c r="F473" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G473" t="s">
         <v>2482</v>
@@ -35834,29 +36073,26 @@
       <c r="B477" t="s">
         <v>2502</v>
       </c>
-      <c r="E477">
-        <v>0</v>
-      </c>
-      <c r="F477" t="s">
-        <v>48</v>
+      <c r="E477" t="s">
+        <v>2503</v>
       </c>
       <c r="G477" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="H477" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="I477" t="s">
         <v>307</v>
       </c>
       <c r="J477" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="K477">
         <v>1979</v>
       </c>
       <c r="P477" s="8" t="s">
-        <v>2485</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="478" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35864,31 +36100,28 @@
         <v>43</v>
       </c>
       <c r="B478" t="s">
-        <v>2506</v>
-      </c>
-      <c r="E478">
-        <v>0</v>
-      </c>
-      <c r="F478" t="s">
-        <v>48</v>
+        <v>2508</v>
+      </c>
+      <c r="E478" t="s">
+        <v>2503</v>
       </c>
       <c r="G478" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="H478" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="I478" t="s">
         <v>1314</v>
       </c>
       <c r="J478" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="K478">
         <v>1985</v>
       </c>
       <c r="P478" s="8" t="s">
-        <v>2485</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="479" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35896,28 +36129,28 @@
         <v>43</v>
       </c>
       <c r="B479" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="E479" t="s">
         <v>48</v>
       </c>
       <c r="G479" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="H479" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="I479" t="s">
         <v>1862</v>
       </c>
       <c r="J479" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="K479">
         <v>2011</v>
       </c>
       <c r="P479" s="8" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="480" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35925,28 +36158,28 @@
         <v>43</v>
       </c>
       <c r="B480" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="E480" t="s">
         <v>48</v>
       </c>
       <c r="G480" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="H480" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="I480" t="s">
         <v>81</v>
       </c>
       <c r="J480" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="K480">
         <v>1976</v>
       </c>
       <c r="P480" s="8" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="481" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35954,7 +36187,7 @@
         <v>43</v>
       </c>
       <c r="B481" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="E481" t="s">
         <v>85</v>
@@ -35963,22 +36196,22 @@
         <v>48</v>
       </c>
       <c r="G481" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="H481" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="I481" t="s">
         <v>723</v>
       </c>
       <c r="J481" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="K481">
         <v>2006</v>
       </c>
       <c r="P481" s="8" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="482" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35986,7 +36219,7 @@
         <v>43</v>
       </c>
       <c r="B482" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="E482" t="s">
         <v>85</v>
@@ -35995,22 +36228,22 @@
         <v>61</v>
       </c>
       <c r="G482" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="H482" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="I482" t="s">
         <v>2184</v>
       </c>
       <c r="J482" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="K482">
         <v>2001</v>
       </c>
       <c r="P482" s="8" t="s">
-        <v>3646</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="483" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36018,31 +36251,28 @@
         <v>43</v>
       </c>
       <c r="B483" t="s">
-        <v>2529</v>
-      </c>
-      <c r="E483">
-        <v>0</v>
-      </c>
-      <c r="F483" t="s">
-        <v>48</v>
+        <v>2531</v>
+      </c>
+      <c r="E483" t="s">
+        <v>2503</v>
       </c>
       <c r="G483" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="H483" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="I483" t="s">
         <v>51</v>
       </c>
       <c r="J483" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="K483">
         <v>2020</v>
       </c>
       <c r="P483" s="8" t="s">
-        <v>2485</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="484" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36050,7 +36280,7 @@
         <v>43</v>
       </c>
       <c r="B484" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="E484" t="s">
         <v>85</v>
@@ -36059,22 +36289,22 @@
         <v>48</v>
       </c>
       <c r="G484" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="H484" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="I484" t="s">
         <v>1359</v>
       </c>
       <c r="J484" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="K484">
         <v>2013</v>
       </c>
       <c r="P484" s="8" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="485" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36082,883 +36312,1090 @@
         <v>43</v>
       </c>
       <c r="B485" t="s">
-        <v>2538</v>
+        <v>2540</v>
+      </c>
+      <c r="E485" t="s">
+        <v>2503</v>
       </c>
       <c r="G485" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="H485" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="I485" t="s">
         <v>295</v>
       </c>
       <c r="J485" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="K485">
         <v>2012</v>
       </c>
-      <c r="P485" s="8"/>
+      <c r="P485" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="486" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A486" t="s">
         <v>43</v>
       </c>
       <c r="B486" t="s">
-        <v>2542</v>
+        <v>2544</v>
+      </c>
+      <c r="E486" t="s">
+        <v>85</v>
+      </c>
+      <c r="F486" t="s">
+        <v>48</v>
       </c>
       <c r="G486" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="H486" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="I486" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="J486" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="K486">
         <v>1996</v>
       </c>
-      <c r="P486" s="8"/>
+      <c r="P486" s="8" t="s">
+        <v>3657</v>
+      </c>
     </row>
     <row r="487" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A487" t="s">
         <v>43</v>
       </c>
       <c r="B487" t="s">
-        <v>2547</v>
+        <v>2549</v>
+      </c>
+      <c r="E487" t="s">
+        <v>2503</v>
       </c>
       <c r="G487" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
       <c r="H487" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="I487" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="J487" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="K487">
         <v>1995</v>
       </c>
-      <c r="P487" s="8"/>
+      <c r="P487" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="488" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A488" t="s">
         <v>43</v>
       </c>
       <c r="B488" t="s">
-        <v>2552</v>
+        <v>2554</v>
+      </c>
+      <c r="E488" t="s">
+        <v>85</v>
+      </c>
+      <c r="F488" t="s">
+        <v>61</v>
       </c>
       <c r="G488" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="H488" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="I488" t="s">
         <v>51</v>
       </c>
       <c r="J488" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="K488">
         <v>2002</v>
       </c>
-      <c r="P488" s="8"/>
+      <c r="P488" s="8" t="s">
+        <v>3658</v>
+      </c>
     </row>
     <row r="489" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A489" t="s">
         <v>43</v>
       </c>
       <c r="B489" t="s">
-        <v>2556</v>
+        <v>2558</v>
+      </c>
+      <c r="E489" t="s">
+        <v>2503</v>
       </c>
       <c r="G489" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
       <c r="H489" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
       <c r="I489" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="J489" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="K489">
         <v>2023</v>
       </c>
-      <c r="P489" s="8"/>
+      <c r="P489" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="490" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A490" t="s">
         <v>43</v>
       </c>
       <c r="B490" t="s">
-        <v>2561</v>
+        <v>2563</v>
+      </c>
+      <c r="E490" t="s">
+        <v>2503</v>
       </c>
       <c r="G490" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="H490" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="I490" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="J490" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="K490">
         <v>2011</v>
       </c>
-      <c r="P490" s="8"/>
+      <c r="P490" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="491" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A491" t="s">
         <v>43</v>
       </c>
       <c r="B491" t="s">
-        <v>2566</v>
+        <v>2568</v>
+      </c>
+      <c r="E491" t="s">
+        <v>2503</v>
       </c>
       <c r="G491" t="s">
+        <v>2569</v>
+      </c>
+      <c r="H491" t="s">
+        <v>2570</v>
+      </c>
+      <c r="I491" t="s">
+        <v>2571</v>
+      </c>
+      <c r="J491" t="s">
         <v>2567</v>
-      </c>
-      <c r="H491" t="s">
-        <v>2568</v>
-      </c>
-      <c r="I491" t="s">
-        <v>2569</v>
-      </c>
-      <c r="J491" t="s">
-        <v>2565</v>
       </c>
       <c r="K491">
         <v>2011</v>
       </c>
-      <c r="P491" s="8"/>
+      <c r="P491" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="492" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A492" t="s">
         <v>43</v>
       </c>
       <c r="B492" t="s">
-        <v>2570</v>
+        <v>2572</v>
+      </c>
+      <c r="E492" t="s">
+        <v>2503</v>
       </c>
       <c r="G492" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="H492" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="I492" t="s">
         <v>51</v>
       </c>
       <c r="J492" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="K492">
         <v>1984</v>
       </c>
-      <c r="P492" s="8"/>
+      <c r="P492" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="493" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A493" t="s">
         <v>43</v>
       </c>
       <c r="B493" t="s">
-        <v>2574</v>
+        <v>2576</v>
+      </c>
+      <c r="E493" t="s">
+        <v>2503</v>
       </c>
       <c r="G493" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="H493" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="I493" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="J493" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="K493">
         <v>2017</v>
       </c>
-      <c r="P493" s="8"/>
+      <c r="P493" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="494" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A494" t="s">
         <v>43</v>
       </c>
       <c r="B494" t="s">
-        <v>2579</v>
+        <v>2581</v>
+      </c>
+      <c r="E494" t="s">
+        <v>2503</v>
       </c>
       <c r="G494" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="H494" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="I494" t="s">
         <v>1729</v>
       </c>
       <c r="J494" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="K494">
         <v>2025</v>
       </c>
-      <c r="P494" s="8"/>
+      <c r="P494" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="495" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A495" t="s">
         <v>43</v>
       </c>
       <c r="B495" t="s">
-        <v>2583</v>
+        <v>2585</v>
+      </c>
+      <c r="E495" t="s">
+        <v>2503</v>
       </c>
       <c r="G495" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="H495" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="I495" t="s">
         <v>643</v>
       </c>
       <c r="J495" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="K495">
         <v>2025</v>
       </c>
-      <c r="P495" s="8"/>
+      <c r="P495" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="496" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A496" t="s">
         <v>43</v>
       </c>
       <c r="B496" t="s">
-        <v>2587</v>
+        <v>2589</v>
+      </c>
+      <c r="E496" t="s">
+        <v>2503</v>
       </c>
       <c r="G496" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="H496" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="I496" t="s">
         <v>307</v>
       </c>
       <c r="J496" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="K496">
         <v>2020</v>
       </c>
-      <c r="P496" s="8"/>
+      <c r="P496" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="497" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A497" t="s">
         <v>43</v>
       </c>
       <c r="B497" t="s">
-        <v>2590</v>
+        <v>2592</v>
+      </c>
+      <c r="E497" t="s">
+        <v>85</v>
+      </c>
+      <c r="F497" t="s">
+        <v>72</v>
       </c>
       <c r="G497" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="H497" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="I497" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="J497" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="K497">
         <v>2019</v>
       </c>
-      <c r="P497" s="8"/>
+      <c r="P497" s="8" t="s">
+        <v>3659</v>
+      </c>
     </row>
     <row r="498" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A498" t="s">
         <v>43</v>
       </c>
       <c r="B498" t="s">
-        <v>2595</v>
+        <v>2597</v>
+      </c>
+      <c r="E498" t="s">
+        <v>2503</v>
       </c>
       <c r="G498" t="s">
-        <v>2596</v>
+        <v>2598</v>
       </c>
       <c r="H498" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="I498" t="s">
-        <v>2598</v>
+        <v>2600</v>
       </c>
       <c r="J498" t="s">
-        <v>2599</v>
+        <v>2601</v>
       </c>
       <c r="K498">
         <v>2023</v>
       </c>
-      <c r="P498" s="8"/>
+      <c r="P498" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="499" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A499" t="s">
         <v>43</v>
       </c>
       <c r="B499" t="s">
-        <v>2600</v>
+        <v>2602</v>
+      </c>
+      <c r="E499" t="s">
+        <v>2503</v>
       </c>
       <c r="G499" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="H499" t="s">
-        <v>2602</v>
+        <v>2604</v>
       </c>
       <c r="I499" t="s">
         <v>687</v>
       </c>
       <c r="J499" t="s">
-        <v>2603</v>
+        <v>2605</v>
       </c>
       <c r="K499">
         <v>2001</v>
       </c>
-      <c r="P499" s="8"/>
+      <c r="P499" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="500" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A500" t="s">
         <v>43</v>
       </c>
       <c r="B500" t="s">
-        <v>2604</v>
+        <v>2606</v>
+      </c>
+      <c r="E500" t="s">
+        <v>85</v>
+      </c>
+      <c r="F500" t="s">
+        <v>48</v>
       </c>
       <c r="G500" t="s">
-        <v>2605</v>
+        <v>2607</v>
       </c>
       <c r="H500" t="s">
-        <v>2606</v>
+        <v>2608</v>
       </c>
       <c r="I500" t="s">
         <v>723</v>
       </c>
       <c r="J500" t="s">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="K500">
         <v>2022</v>
       </c>
-      <c r="P500" s="8"/>
+      <c r="P500" s="8" t="s">
+        <v>2610</v>
+      </c>
     </row>
     <row r="501" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A501" t="s">
         <v>43</v>
       </c>
       <c r="B501" t="s">
-        <v>2608</v>
+        <v>2611</v>
+      </c>
+      <c r="E501" t="s">
+        <v>2503</v>
       </c>
       <c r="G501" t="s">
-        <v>2609</v>
+        <v>2612</v>
       </c>
       <c r="H501" t="s">
-        <v>2610</v>
+        <v>2613</v>
       </c>
       <c r="I501" t="s">
         <v>253</v>
       </c>
       <c r="J501" t="s">
-        <v>2611</v>
+        <v>2614</v>
       </c>
       <c r="K501">
         <v>2001</v>
       </c>
-      <c r="P501" s="8"/>
+      <c r="P501" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="502" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A502" t="s">
         <v>43</v>
       </c>
       <c r="B502" t="s">
-        <v>2612</v>
+        <v>2615</v>
+      </c>
+      <c r="E502" t="s">
+        <v>48</v>
       </c>
       <c r="G502" t="s">
-        <v>2613</v>
+        <v>2616</v>
       </c>
       <c r="H502" t="s">
-        <v>2614</v>
+        <v>2617</v>
       </c>
       <c r="I502" t="s">
         <v>307</v>
       </c>
       <c r="J502" t="s">
-        <v>2615</v>
+        <v>2618</v>
       </c>
       <c r="K502">
         <v>1976</v>
       </c>
-      <c r="P502" s="8"/>
+      <c r="P502" s="8" t="s">
+        <v>2619</v>
+      </c>
     </row>
     <row r="503" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A503" t="s">
         <v>43</v>
       </c>
       <c r="B503" t="s">
-        <v>2616</v>
+        <v>2620</v>
+      </c>
+      <c r="E503" t="s">
+        <v>85</v>
+      </c>
+      <c r="F503" t="s">
+        <v>48</v>
       </c>
       <c r="G503" t="s">
-        <v>2617</v>
+        <v>2621</v>
       </c>
       <c r="H503" t="s">
-        <v>2618</v>
+        <v>2622</v>
       </c>
       <c r="I503" t="s">
-        <v>2619</v>
+        <v>2623</v>
       </c>
       <c r="J503" t="s">
-        <v>2620</v>
+        <v>2624</v>
       </c>
       <c r="K503">
         <v>1981</v>
       </c>
-      <c r="P503" s="8"/>
+      <c r="P503" s="8" t="s">
+        <v>2625</v>
+      </c>
     </row>
     <row r="504" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A504" t="s">
         <v>43</v>
       </c>
       <c r="B504" t="s">
-        <v>2621</v>
+        <v>2626</v>
+      </c>
+      <c r="E504" t="s">
+        <v>2503</v>
       </c>
       <c r="G504" t="s">
-        <v>2622</v>
+        <v>2627</v>
       </c>
       <c r="H504" t="s">
-        <v>2623</v>
+        <v>2628</v>
       </c>
       <c r="I504" t="s">
-        <v>2624</v>
+        <v>2629</v>
       </c>
       <c r="J504" t="s">
-        <v>2625</v>
+        <v>2630</v>
       </c>
       <c r="K504">
         <v>2025</v>
       </c>
-      <c r="P504" s="8"/>
+      <c r="P504" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="505" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A505" t="s">
         <v>43</v>
       </c>
       <c r="B505" t="s">
-        <v>2626</v>
+        <v>2631</v>
+      </c>
+      <c r="E505" t="s">
+        <v>85</v>
+      </c>
+      <c r="F505" t="s">
+        <v>72</v>
       </c>
       <c r="G505" t="s">
-        <v>2627</v>
+        <v>2632</v>
       </c>
       <c r="H505" t="s">
-        <v>2628</v>
+        <v>2633</v>
       </c>
       <c r="I505" t="s">
-        <v>2629</v>
+        <v>2634</v>
       </c>
       <c r="J505" t="s">
-        <v>2630</v>
+        <v>2635</v>
       </c>
       <c r="K505">
         <v>1998</v>
       </c>
-      <c r="P505" s="8"/>
+      <c r="P505" s="8" t="s">
+        <v>2636</v>
+      </c>
     </row>
     <row r="506" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A506" t="s">
         <v>43</v>
       </c>
       <c r="B506" t="s">
-        <v>2631</v>
+        <v>2637</v>
+      </c>
+      <c r="E506" t="s">
+        <v>2503</v>
       </c>
       <c r="G506" t="s">
-        <v>2632</v>
+        <v>2638</v>
       </c>
       <c r="H506" t="s">
-        <v>2633</v>
+        <v>2639</v>
       </c>
       <c r="I506" t="s">
         <v>351</v>
       </c>
       <c r="J506" t="s">
-        <v>2634</v>
+        <v>2640</v>
       </c>
       <c r="K506">
         <v>2010</v>
       </c>
-      <c r="P506" s="8"/>
+      <c r="P506" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="507" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A507" t="s">
         <v>43</v>
       </c>
       <c r="B507" t="s">
-        <v>2635</v>
+        <v>2641</v>
+      </c>
+      <c r="E507" t="s">
+        <v>85</v>
+      </c>
+      <c r="F507" t="s">
+        <v>48</v>
       </c>
       <c r="G507" t="s">
-        <v>2636</v>
+        <v>2642</v>
       </c>
       <c r="H507" t="s">
-        <v>2637</v>
+        <v>2643</v>
       </c>
       <c r="I507" t="s">
         <v>2018</v>
       </c>
       <c r="J507" t="s">
-        <v>2638</v>
+        <v>2644</v>
       </c>
       <c r="K507">
         <v>2016</v>
       </c>
-      <c r="P507" s="8"/>
+      <c r="P507" s="8" t="s">
+        <v>2645</v>
+      </c>
     </row>
     <row r="508" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A508" t="s">
         <v>43</v>
       </c>
       <c r="B508" t="s">
-        <v>2639</v>
+        <v>2646</v>
+      </c>
+      <c r="E508" t="s">
+        <v>85</v>
+      </c>
+      <c r="F508" t="s">
+        <v>54</v>
       </c>
       <c r="G508" t="s">
-        <v>2640</v>
+        <v>2647</v>
       </c>
       <c r="H508" t="s">
-        <v>2641</v>
+        <v>2648</v>
       </c>
       <c r="I508" t="s">
-        <v>2642</v>
+        <v>2649</v>
       </c>
       <c r="J508" t="s">
-        <v>2643</v>
+        <v>2650</v>
       </c>
       <c r="K508">
         <v>2004</v>
       </c>
-      <c r="P508" s="8"/>
+      <c r="P508" s="8" t="s">
+        <v>2651</v>
+      </c>
     </row>
     <row r="509" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A509" t="s">
         <v>43</v>
       </c>
       <c r="B509" t="s">
-        <v>2644</v>
+        <v>2652</v>
+      </c>
+      <c r="E509" t="s">
+        <v>2503</v>
       </c>
       <c r="G509" t="s">
-        <v>2645</v>
+        <v>2653</v>
       </c>
       <c r="H509" t="s">
-        <v>2646</v>
+        <v>2654</v>
       </c>
       <c r="I509" t="s">
         <v>481</v>
       </c>
       <c r="J509" t="s">
-        <v>2647</v>
+        <v>2655</v>
       </c>
       <c r="K509">
         <v>1989</v>
       </c>
-      <c r="P509" s="8"/>
+      <c r="P509" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="510" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A510" t="s">
         <v>43</v>
       </c>
       <c r="B510" t="s">
-        <v>2648</v>
+        <v>2656</v>
+      </c>
+      <c r="E510" t="s">
+        <v>2503</v>
       </c>
       <c r="G510" t="s">
-        <v>2649</v>
+        <v>2657</v>
       </c>
       <c r="H510" t="s">
-        <v>2650</v>
+        <v>2658</v>
       </c>
       <c r="I510" t="s">
-        <v>2651</v>
+        <v>2659</v>
       </c>
       <c r="J510" t="s">
-        <v>2652</v>
+        <v>2660</v>
       </c>
       <c r="K510">
         <v>2005</v>
       </c>
-      <c r="P510" s="8"/>
+      <c r="P510" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="511" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A511" t="s">
         <v>43</v>
       </c>
       <c r="B511" t="s">
-        <v>2653</v>
+        <v>2661</v>
+      </c>
+      <c r="E511" t="s">
+        <v>48</v>
       </c>
       <c r="G511" t="s">
-        <v>2654</v>
+        <v>2662</v>
       </c>
       <c r="H511" t="s">
-        <v>2655</v>
+        <v>2663</v>
       </c>
       <c r="I511" t="s">
         <v>403</v>
       </c>
       <c r="J511" t="s">
-        <v>2656</v>
+        <v>2664</v>
       </c>
       <c r="K511">
         <v>2025</v>
       </c>
-      <c r="P511" s="8"/>
+      <c r="P511" s="8" t="s">
+        <v>2665</v>
+      </c>
     </row>
     <row r="512" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A512" t="s">
         <v>43</v>
       </c>
       <c r="B512" t="s">
-        <v>2657</v>
+        <v>2666</v>
+      </c>
+      <c r="E512" t="s">
+        <v>2503</v>
       </c>
       <c r="G512" t="s">
-        <v>2658</v>
+        <v>2667</v>
       </c>
       <c r="H512" t="s">
-        <v>2659</v>
+        <v>2668</v>
       </c>
       <c r="I512" t="s">
         <v>1652</v>
       </c>
       <c r="J512" t="s">
-        <v>2660</v>
+        <v>2669</v>
       </c>
       <c r="K512">
         <v>2018</v>
       </c>
-      <c r="P512" s="8"/>
+      <c r="P512" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="513" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A513" t="s">
         <v>43</v>
       </c>
       <c r="B513" t="s">
-        <v>2661</v>
+        <v>2670</v>
+      </c>
+      <c r="E513" t="s">
+        <v>2503</v>
       </c>
       <c r="G513" t="s">
-        <v>2662</v>
+        <v>2671</v>
       </c>
       <c r="H513" t="s">
-        <v>2663</v>
+        <v>2672</v>
       </c>
       <c r="I513" t="s">
         <v>1499</v>
       </c>
       <c r="J513" t="s">
-        <v>2664</v>
+        <v>2673</v>
       </c>
       <c r="K513">
         <v>2011</v>
       </c>
-      <c r="P513" s="8"/>
+      <c r="P513" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="514" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A514" t="s">
         <v>43</v>
       </c>
       <c r="B514" t="s">
-        <v>2665</v>
+        <v>2674</v>
+      </c>
+      <c r="E514" t="s">
+        <v>85</v>
+      </c>
+      <c r="F514" t="s">
+        <v>61</v>
       </c>
       <c r="G514" t="s">
-        <v>2666</v>
+        <v>2675</v>
       </c>
       <c r="H514" t="s">
-        <v>2667</v>
+        <v>2676</v>
       </c>
       <c r="I514" t="s">
         <v>1242</v>
       </c>
       <c r="J514" t="s">
-        <v>2668</v>
+        <v>2677</v>
       </c>
       <c r="K514">
         <v>2024</v>
       </c>
-      <c r="P514" s="8"/>
+      <c r="P514" s="8" t="s">
+        <v>2678</v>
+      </c>
     </row>
     <row r="515" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A515" t="s">
         <v>43</v>
       </c>
       <c r="B515" t="s">
-        <v>2669</v>
+        <v>2679</v>
+      </c>
+      <c r="E515" t="s">
+        <v>2503</v>
       </c>
       <c r="G515" t="s">
-        <v>2670</v>
+        <v>2680</v>
       </c>
       <c r="H515" t="s">
-        <v>2671</v>
+        <v>2681</v>
       </c>
       <c r="I515" t="s">
         <v>1783</v>
       </c>
       <c r="J515" t="s">
-        <v>2672</v>
+        <v>2682</v>
       </c>
       <c r="K515">
         <v>2023</v>
       </c>
-      <c r="P515" s="8"/>
+      <c r="P515" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="516" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A516" t="s">
         <v>43</v>
       </c>
       <c r="B516" t="s">
-        <v>2673</v>
+        <v>2683</v>
+      </c>
+      <c r="E516" t="s">
+        <v>2503</v>
       </c>
       <c r="G516" t="s">
-        <v>2674</v>
+        <v>2684</v>
       </c>
       <c r="H516" t="s">
-        <v>2675</v>
+        <v>2685</v>
       </c>
       <c r="I516" t="s">
-        <v>2676</v>
+        <v>2686</v>
       </c>
       <c r="J516" t="s">
-        <v>2677</v>
+        <v>2687</v>
       </c>
       <c r="K516">
         <v>2010</v>
       </c>
-      <c r="P516" s="8"/>
+      <c r="P516" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="517" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A517" t="s">
         <v>43</v>
       </c>
       <c r="B517" t="s">
-        <v>2678</v>
+        <v>2688</v>
+      </c>
+      <c r="E517" t="s">
+        <v>2503</v>
       </c>
       <c r="G517" t="s">
-        <v>2679</v>
+        <v>2689</v>
       </c>
       <c r="H517" t="s">
-        <v>2680</v>
+        <v>2690</v>
       </c>
       <c r="I517" t="s">
-        <v>2681</v>
+        <v>2691</v>
       </c>
       <c r="J517" t="s">
-        <v>2682</v>
+        <v>2692</v>
       </c>
       <c r="K517">
         <v>2019</v>
       </c>
-      <c r="P517" s="8"/>
+      <c r="P517" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="518" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A518" t="s">
         <v>43</v>
       </c>
       <c r="B518" t="s">
-        <v>2683</v>
+        <v>2693</v>
+      </c>
+      <c r="E518" t="s">
+        <v>2503</v>
       </c>
       <c r="G518" t="s">
-        <v>2684</v>
+        <v>2694</v>
       </c>
       <c r="H518" t="s">
-        <v>2685</v>
+        <v>2695</v>
       </c>
       <c r="I518" t="s">
         <v>51</v>
       </c>
       <c r="J518" t="s">
-        <v>2686</v>
+        <v>2696</v>
       </c>
       <c r="K518">
         <v>1986</v>
       </c>
-      <c r="P518" s="8"/>
+      <c r="P518" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="519" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A519" t="s">
         <v>43</v>
       </c>
       <c r="B519" t="s">
-        <v>2687</v>
+        <v>2697</v>
+      </c>
+      <c r="E519" t="s">
+        <v>48</v>
       </c>
       <c r="G519" t="s">
-        <v>2688</v>
+        <v>2698</v>
       </c>
       <c r="H519" t="s">
-        <v>2689</v>
+        <v>2699</v>
       </c>
       <c r="I519" t="s">
-        <v>2690</v>
+        <v>2700</v>
       </c>
       <c r="J519" t="s">
-        <v>2691</v>
+        <v>2701</v>
       </c>
       <c r="K519">
         <v>2018</v>
       </c>
-      <c r="P519" s="8"/>
+      <c r="P519" s="8" t="s">
+        <v>3660</v>
+      </c>
     </row>
     <row r="520" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A520" t="s">
         <v>43</v>
       </c>
       <c r="B520" t="s">
-        <v>2692</v>
+        <v>2702</v>
+      </c>
+      <c r="E520" t="s">
+        <v>2503</v>
       </c>
       <c r="G520" t="s">
-        <v>2693</v>
+        <v>2703</v>
       </c>
       <c r="H520" t="s">
-        <v>2694</v>
+        <v>2704</v>
       </c>
       <c r="I520" t="s">
-        <v>2695</v>
+        <v>2705</v>
       </c>
       <c r="J520" t="s">
-        <v>2696</v>
+        <v>2706</v>
       </c>
       <c r="K520">
         <v>2006</v>
       </c>
-      <c r="P520" s="8"/>
+      <c r="P520" s="8" t="s">
+        <v>2507</v>
+      </c>
     </row>
     <row r="521" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A521" t="s">
         <v>43</v>
       </c>
       <c r="B521" t="s">
-        <v>2697</v>
+        <v>2707</v>
       </c>
       <c r="G521" t="s">
-        <v>2698</v>
+        <v>2708</v>
       </c>
       <c r="H521" t="s">
-        <v>2699</v>
+        <v>2709</v>
       </c>
       <c r="I521" t="s">
-        <v>2700</v>
+        <v>2710</v>
       </c>
       <c r="J521" t="s">
-        <v>2701</v>
+        <v>2711</v>
       </c>
       <c r="K521">
         <v>2008</v>
@@ -36970,19 +37407,19 @@
         <v>43</v>
       </c>
       <c r="B522" t="s">
-        <v>2702</v>
+        <v>2712</v>
       </c>
       <c r="G522" t="s">
-        <v>2703</v>
+        <v>2713</v>
       </c>
       <c r="H522" t="s">
-        <v>2704</v>
+        <v>2714</v>
       </c>
       <c r="I522" t="s">
         <v>1196</v>
       </c>
       <c r="J522" t="s">
-        <v>2705</v>
+        <v>2715</v>
       </c>
       <c r="K522">
         <v>2019</v>
@@ -36994,19 +37431,19 @@
         <v>43</v>
       </c>
       <c r="B523" t="s">
-        <v>2706</v>
+        <v>2716</v>
       </c>
       <c r="G523" t="s">
-        <v>2707</v>
+        <v>2717</v>
       </c>
       <c r="H523" t="s">
-        <v>2708</v>
+        <v>2718</v>
       </c>
       <c r="I523" t="s">
-        <v>2709</v>
+        <v>2719</v>
       </c>
       <c r="J523" t="s">
-        <v>2710</v>
+        <v>2720</v>
       </c>
       <c r="K523">
         <v>2012</v>
@@ -37018,19 +37455,19 @@
         <v>43</v>
       </c>
       <c r="B524" t="s">
-        <v>2711</v>
+        <v>2721</v>
       </c>
       <c r="G524" t="s">
-        <v>2712</v>
+        <v>2722</v>
       </c>
       <c r="H524" t="s">
-        <v>2713</v>
+        <v>2723</v>
       </c>
       <c r="I524" t="s">
         <v>1729</v>
       </c>
       <c r="J524" t="s">
-        <v>2714</v>
+        <v>2724</v>
       </c>
       <c r="K524">
         <v>1997</v>
@@ -37042,19 +37479,19 @@
         <v>43</v>
       </c>
       <c r="B525" t="s">
-        <v>2715</v>
+        <v>2725</v>
       </c>
       <c r="G525" t="s">
-        <v>2716</v>
+        <v>2726</v>
       </c>
       <c r="H525" t="s">
-        <v>2717</v>
+        <v>2727</v>
       </c>
       <c r="I525" t="s">
-        <v>2718</v>
+        <v>2728</v>
       </c>
       <c r="J525" t="s">
-        <v>2719</v>
+        <v>2729</v>
       </c>
       <c r="K525">
         <v>2023</v>
@@ -37066,19 +37503,19 @@
         <v>43</v>
       </c>
       <c r="B526" t="s">
-        <v>2720</v>
+        <v>2730</v>
       </c>
       <c r="G526" t="s">
-        <v>2721</v>
+        <v>2731</v>
       </c>
       <c r="H526" t="s">
-        <v>2722</v>
+        <v>2732</v>
       </c>
       <c r="I526" t="s">
         <v>329</v>
       </c>
       <c r="J526" t="s">
-        <v>2723</v>
+        <v>2733</v>
       </c>
       <c r="K526">
         <v>2021</v>
@@ -37090,19 +37527,19 @@
         <v>43</v>
       </c>
       <c r="B527" t="s">
-        <v>2724</v>
+        <v>2734</v>
       </c>
       <c r="G527" t="s">
-        <v>2725</v>
+        <v>2735</v>
       </c>
       <c r="H527" t="s">
-        <v>2726</v>
+        <v>2736</v>
       </c>
       <c r="I527" t="s">
-        <v>2727</v>
+        <v>2737</v>
       </c>
       <c r="J527" t="s">
-        <v>2728</v>
+        <v>2738</v>
       </c>
       <c r="K527">
         <v>1989</v>
@@ -37114,19 +37551,19 @@
         <v>43</v>
       </c>
       <c r="B528" t="s">
-        <v>2729</v>
+        <v>2739</v>
       </c>
       <c r="G528" t="s">
-        <v>2730</v>
+        <v>2740</v>
       </c>
       <c r="H528" t="s">
-        <v>2731</v>
+        <v>2741</v>
       </c>
       <c r="I528" t="s">
         <v>1394</v>
       </c>
       <c r="J528" t="s">
-        <v>2732</v>
+        <v>2742</v>
       </c>
       <c r="K528">
         <v>2001</v>
@@ -37138,19 +37575,19 @@
         <v>43</v>
       </c>
       <c r="B529" t="s">
-        <v>2733</v>
+        <v>2743</v>
       </c>
       <c r="G529" t="s">
-        <v>2734</v>
+        <v>2744</v>
       </c>
       <c r="H529" t="s">
-        <v>2735</v>
+        <v>2745</v>
       </c>
       <c r="I529" t="s">
-        <v>2736</v>
+        <v>2746</v>
       </c>
       <c r="J529" t="s">
-        <v>2737</v>
+        <v>2747</v>
       </c>
       <c r="K529">
         <v>2024</v>
@@ -37162,19 +37599,19 @@
         <v>43</v>
       </c>
       <c r="B530" t="s">
-        <v>2738</v>
+        <v>2748</v>
       </c>
       <c r="G530" t="s">
-        <v>2739</v>
+        <v>2749</v>
       </c>
       <c r="H530" t="s">
-        <v>2740</v>
+        <v>2750</v>
       </c>
       <c r="I530" t="s">
-        <v>2741</v>
+        <v>2751</v>
       </c>
       <c r="J530" t="s">
-        <v>2742</v>
+        <v>2752</v>
       </c>
       <c r="K530">
         <v>2012</v>
@@ -37186,19 +37623,19 @@
         <v>43</v>
       </c>
       <c r="B531" t="s">
-        <v>2743</v>
+        <v>2753</v>
       </c>
       <c r="G531" t="s">
-        <v>2744</v>
+        <v>2754</v>
       </c>
       <c r="H531" t="s">
-        <v>2745</v>
+        <v>2755</v>
       </c>
       <c r="I531" t="s">
         <v>549</v>
       </c>
       <c r="J531" t="s">
-        <v>2746</v>
+        <v>2756</v>
       </c>
       <c r="K531">
         <v>2024</v>
@@ -37210,19 +37647,19 @@
         <v>43</v>
       </c>
       <c r="B532" t="s">
-        <v>2747</v>
+        <v>2757</v>
       </c>
       <c r="G532" t="s">
-        <v>2748</v>
+        <v>2758</v>
       </c>
       <c r="H532" t="s">
-        <v>2749</v>
+        <v>2759</v>
       </c>
       <c r="I532" t="s">
         <v>100</v>
       </c>
       <c r="J532" t="s">
-        <v>2750</v>
+        <v>2760</v>
       </c>
       <c r="K532">
         <v>2023</v>
@@ -37234,19 +37671,19 @@
         <v>43</v>
       </c>
       <c r="B533" t="s">
-        <v>2751</v>
+        <v>2761</v>
       </c>
       <c r="G533" t="s">
-        <v>2752</v>
+        <v>2762</v>
       </c>
       <c r="H533" t="s">
-        <v>2753</v>
+        <v>2763</v>
       </c>
       <c r="I533" t="s">
         <v>154</v>
       </c>
       <c r="J533" t="s">
-        <v>2754</v>
+        <v>2764</v>
       </c>
       <c r="K533">
         <v>2010</v>
@@ -37258,19 +37695,19 @@
         <v>43</v>
       </c>
       <c r="B534" t="s">
-        <v>2755</v>
+        <v>2765</v>
       </c>
       <c r="G534" t="s">
-        <v>2756</v>
+        <v>2766</v>
       </c>
       <c r="H534" t="s">
-        <v>2757</v>
+        <v>2767</v>
       </c>
       <c r="I534" t="s">
         <v>687</v>
       </c>
       <c r="J534" t="s">
-        <v>2758</v>
+        <v>2768</v>
       </c>
       <c r="K534">
         <v>2017</v>
@@ -37282,19 +37719,19 @@
         <v>43</v>
       </c>
       <c r="B535" t="s">
-        <v>2759</v>
+        <v>2769</v>
       </c>
       <c r="G535" t="s">
-        <v>2760</v>
+        <v>2770</v>
       </c>
       <c r="H535" t="s">
-        <v>2761</v>
+        <v>2771</v>
       </c>
       <c r="I535" t="s">
-        <v>2762</v>
+        <v>2772</v>
       </c>
       <c r="J535" t="s">
-        <v>2763</v>
+        <v>2773</v>
       </c>
       <c r="K535">
         <v>2000</v>
@@ -37306,19 +37743,19 @@
         <v>43</v>
       </c>
       <c r="B536" t="s">
-        <v>2764</v>
+        <v>2774</v>
       </c>
       <c r="G536" t="s">
-        <v>2765</v>
+        <v>2775</v>
       </c>
       <c r="H536" t="s">
-        <v>2766</v>
+        <v>2776</v>
       </c>
       <c r="I536" t="s">
         <v>653</v>
       </c>
       <c r="J536" t="s">
-        <v>2767</v>
+        <v>2777</v>
       </c>
       <c r="K536">
         <v>2016</v>
@@ -37330,19 +37767,19 @@
         <v>43</v>
       </c>
       <c r="B537" t="s">
-        <v>2768</v>
+        <v>2778</v>
       </c>
       <c r="G537" t="s">
-        <v>2769</v>
+        <v>2779</v>
       </c>
       <c r="H537" t="s">
-        <v>2770</v>
+        <v>2780</v>
       </c>
       <c r="I537" t="s">
         <v>426</v>
       </c>
       <c r="J537" t="s">
-        <v>2771</v>
+        <v>2781</v>
       </c>
       <c r="K537">
         <v>2006</v>
@@ -37354,19 +37791,19 @@
         <v>43</v>
       </c>
       <c r="B538" t="s">
-        <v>2772</v>
+        <v>2782</v>
       </c>
       <c r="G538" t="s">
-        <v>2773</v>
+        <v>2783</v>
       </c>
       <c r="H538" t="s">
-        <v>2774</v>
+        <v>2784</v>
       </c>
       <c r="I538" t="s">
-        <v>2775</v>
+        <v>2785</v>
       </c>
       <c r="J538" t="s">
-        <v>2776</v>
+        <v>2786</v>
       </c>
       <c r="K538">
         <v>2018</v>
@@ -37378,19 +37815,19 @@
         <v>43</v>
       </c>
       <c r="B539" t="s">
-        <v>2777</v>
+        <v>2787</v>
       </c>
       <c r="G539" t="s">
-        <v>2778</v>
+        <v>2788</v>
       </c>
       <c r="H539" t="s">
-        <v>2779</v>
+        <v>2789</v>
       </c>
       <c r="I539" t="s">
         <v>357</v>
       </c>
       <c r="J539" t="s">
-        <v>2780</v>
+        <v>2790</v>
       </c>
       <c r="K539">
         <v>2015</v>
@@ -37402,19 +37839,19 @@
         <v>43</v>
       </c>
       <c r="B540" t="s">
-        <v>2781</v>
+        <v>2791</v>
       </c>
       <c r="G540" t="s">
-        <v>2782</v>
+        <v>2792</v>
       </c>
       <c r="H540" t="s">
-        <v>2783</v>
+        <v>2793</v>
       </c>
       <c r="I540" t="s">
         <v>51</v>
       </c>
       <c r="J540" t="s">
-        <v>2784</v>
+        <v>2794</v>
       </c>
       <c r="K540">
         <v>1988</v>
@@ -37426,19 +37863,19 @@
         <v>43</v>
       </c>
       <c r="B541" t="s">
-        <v>2785</v>
+        <v>2795</v>
       </c>
       <c r="G541" t="s">
-        <v>2786</v>
+        <v>2796</v>
       </c>
       <c r="H541" t="s">
-        <v>2787</v>
+        <v>2797</v>
       </c>
       <c r="I541" t="s">
         <v>307</v>
       </c>
       <c r="J541" t="s">
-        <v>2788</v>
+        <v>2798</v>
       </c>
       <c r="K541">
         <v>2016</v>
@@ -37450,19 +37887,19 @@
         <v>43</v>
       </c>
       <c r="B542" t="s">
-        <v>2789</v>
+        <v>2799</v>
       </c>
       <c r="G542" t="s">
-        <v>2790</v>
+        <v>2800</v>
       </c>
       <c r="H542" t="s">
-        <v>2791</v>
+        <v>2801</v>
       </c>
       <c r="I542" t="s">
         <v>237</v>
       </c>
       <c r="J542" t="s">
-        <v>2792</v>
+        <v>2802</v>
       </c>
       <c r="K542">
         <v>2022</v>
@@ -37474,19 +37911,19 @@
         <v>43</v>
       </c>
       <c r="B543" t="s">
-        <v>2793</v>
+        <v>2803</v>
       </c>
       <c r="G543" t="s">
-        <v>2794</v>
+        <v>2804</v>
       </c>
       <c r="H543" t="s">
-        <v>2795</v>
+        <v>2805</v>
       </c>
       <c r="I543" t="s">
         <v>346</v>
       </c>
       <c r="J543" t="s">
-        <v>2796</v>
+        <v>2806</v>
       </c>
       <c r="K543">
         <v>2025</v>
@@ -37498,19 +37935,19 @@
         <v>43</v>
       </c>
       <c r="B544" t="s">
-        <v>2797</v>
+        <v>2807</v>
       </c>
       <c r="G544" t="s">
-        <v>2798</v>
+        <v>2808</v>
       </c>
       <c r="H544" t="s">
-        <v>2799</v>
+        <v>2809</v>
       </c>
       <c r="I544" t="s">
-        <v>2800</v>
+        <v>2810</v>
       </c>
       <c r="J544" t="s">
-        <v>2801</v>
+        <v>2811</v>
       </c>
       <c r="K544">
         <v>1986</v>
@@ -37522,19 +37959,19 @@
         <v>43</v>
       </c>
       <c r="B545" t="s">
-        <v>2802</v>
+        <v>2812</v>
       </c>
       <c r="G545" t="s">
-        <v>2803</v>
+        <v>2813</v>
       </c>
       <c r="H545" t="s">
-        <v>2804</v>
+        <v>2814</v>
       </c>
       <c r="I545" t="s">
         <v>900</v>
       </c>
       <c r="J545" t="s">
-        <v>2805</v>
+        <v>2815</v>
       </c>
       <c r="K545">
         <v>2014</v>
@@ -37546,19 +37983,19 @@
         <v>43</v>
       </c>
       <c r="B546" t="s">
-        <v>2806</v>
+        <v>2816</v>
       </c>
       <c r="G546" t="s">
-        <v>2807</v>
+        <v>2817</v>
       </c>
       <c r="H546" t="s">
-        <v>2808</v>
+        <v>2818</v>
       </c>
       <c r="I546" t="s">
-        <v>2690</v>
+        <v>2700</v>
       </c>
       <c r="J546" t="s">
-        <v>2809</v>
+        <v>2819</v>
       </c>
       <c r="K546">
         <v>2019</v>
@@ -37570,19 +38007,19 @@
         <v>43</v>
       </c>
       <c r="B547" t="s">
-        <v>2810</v>
+        <v>2820</v>
       </c>
       <c r="G547" t="s">
-        <v>2811</v>
+        <v>2821</v>
       </c>
       <c r="H547" t="s">
-        <v>2812</v>
+        <v>2822</v>
       </c>
       <c r="I547" t="s">
         <v>266</v>
       </c>
       <c r="J547" t="s">
-        <v>2813</v>
+        <v>2823</v>
       </c>
       <c r="K547">
         <v>2018</v>
@@ -37594,19 +38031,19 @@
         <v>43</v>
       </c>
       <c r="B548" t="s">
-        <v>2814</v>
+        <v>2824</v>
       </c>
       <c r="G548" t="s">
-        <v>2815</v>
+        <v>2825</v>
       </c>
       <c r="H548" t="s">
-        <v>2816</v>
+        <v>2826</v>
       </c>
       <c r="I548" t="s">
         <v>723</v>
       </c>
       <c r="J548" t="s">
-        <v>2817</v>
+        <v>2827</v>
       </c>
       <c r="K548">
         <v>1979</v>
@@ -37618,19 +38055,19 @@
         <v>43</v>
       </c>
       <c r="B549" t="s">
-        <v>2818</v>
+        <v>2828</v>
       </c>
       <c r="G549" t="s">
-        <v>2819</v>
+        <v>2829</v>
       </c>
       <c r="H549" t="s">
-        <v>2820</v>
+        <v>2830</v>
       </c>
       <c r="I549" t="s">
         <v>51</v>
       </c>
       <c r="J549" t="s">
-        <v>2821</v>
+        <v>2831</v>
       </c>
       <c r="K549">
         <v>2023</v>
@@ -37642,19 +38079,19 @@
         <v>43</v>
       </c>
       <c r="B550" t="s">
-        <v>2822</v>
+        <v>2832</v>
       </c>
       <c r="G550" t="s">
-        <v>2823</v>
+        <v>2833</v>
       </c>
       <c r="H550" t="s">
-        <v>2824</v>
+        <v>2834</v>
       </c>
       <c r="I550" t="s">
         <v>148</v>
       </c>
       <c r="J550" t="s">
-        <v>2825</v>
+        <v>2835</v>
       </c>
       <c r="K550">
         <v>2018</v>
@@ -37666,19 +38103,19 @@
         <v>43</v>
       </c>
       <c r="B551" t="s">
-        <v>2826</v>
+        <v>2836</v>
       </c>
       <c r="G551" t="s">
-        <v>2827</v>
+        <v>2837</v>
       </c>
       <c r="H551" t="s">
-        <v>2828</v>
+        <v>2838</v>
       </c>
       <c r="I551" t="s">
-        <v>2829</v>
+        <v>2839</v>
       </c>
       <c r="J551" t="s">
-        <v>2830</v>
+        <v>2840</v>
       </c>
       <c r="K551">
         <v>2015</v>
@@ -37690,19 +38127,19 @@
         <v>43</v>
       </c>
       <c r="B552" t="s">
-        <v>2831</v>
+        <v>2841</v>
       </c>
       <c r="G552" t="s">
-        <v>2832</v>
+        <v>2842</v>
       </c>
       <c r="H552" t="s">
-        <v>2833</v>
+        <v>2843</v>
       </c>
       <c r="I552" t="s">
-        <v>2834</v>
+        <v>2844</v>
       </c>
       <c r="J552" t="s">
-        <v>2835</v>
+        <v>2845</v>
       </c>
       <c r="K552">
         <v>2021</v>
@@ -37714,19 +38151,19 @@
         <v>43</v>
       </c>
       <c r="B553" t="s">
-        <v>2836</v>
+        <v>2846</v>
       </c>
       <c r="G553" t="s">
-        <v>2837</v>
+        <v>2847</v>
       </c>
       <c r="H553" t="s">
-        <v>2838</v>
+        <v>2848</v>
       </c>
       <c r="I553" t="s">
-        <v>2839</v>
+        <v>2849</v>
       </c>
       <c r="J553" t="s">
-        <v>2840</v>
+        <v>2850</v>
       </c>
       <c r="K553">
         <v>2010</v>
@@ -37738,19 +38175,19 @@
         <v>43</v>
       </c>
       <c r="B554" t="s">
-        <v>2841</v>
+        <v>2851</v>
       </c>
       <c r="G554" t="s">
-        <v>2842</v>
+        <v>2852</v>
       </c>
       <c r="H554" t="s">
-        <v>2843</v>
+        <v>2853</v>
       </c>
       <c r="I554" t="s">
-        <v>2844</v>
+        <v>2854</v>
       </c>
       <c r="J554" t="s">
-        <v>2845</v>
+        <v>2855</v>
       </c>
       <c r="K554">
         <v>2006</v>
@@ -37762,19 +38199,19 @@
         <v>43</v>
       </c>
       <c r="B555" t="s">
-        <v>2846</v>
+        <v>2856</v>
       </c>
       <c r="G555" t="s">
-        <v>2847</v>
+        <v>2857</v>
       </c>
       <c r="H555" t="s">
-        <v>2848</v>
+        <v>2858</v>
       </c>
       <c r="I555" t="s">
         <v>426</v>
       </c>
       <c r="J555" t="s">
-        <v>2849</v>
+        <v>2859</v>
       </c>
       <c r="K555">
         <v>2019</v>
@@ -37786,19 +38223,19 @@
         <v>43</v>
       </c>
       <c r="B556" t="s">
-        <v>2850</v>
+        <v>2860</v>
       </c>
       <c r="G556" t="s">
-        <v>2851</v>
+        <v>2861</v>
       </c>
       <c r="H556" t="s">
-        <v>2852</v>
+        <v>2862</v>
       </c>
       <c r="I556" t="s">
-        <v>2853</v>
+        <v>2863</v>
       </c>
       <c r="J556" t="s">
-        <v>2854</v>
+        <v>2864</v>
       </c>
       <c r="K556">
         <v>2022</v>
@@ -37810,19 +38247,19 @@
         <v>43</v>
       </c>
       <c r="B557" t="s">
-        <v>2855</v>
+        <v>2865</v>
       </c>
       <c r="G557" t="s">
-        <v>2856</v>
+        <v>2866</v>
       </c>
       <c r="H557" t="s">
-        <v>2857</v>
+        <v>2867</v>
       </c>
       <c r="I557" t="s">
         <v>357</v>
       </c>
       <c r="J557" t="s">
-        <v>2858</v>
+        <v>2868</v>
       </c>
       <c r="K557">
         <v>2006</v>
@@ -37834,19 +38271,19 @@
         <v>43</v>
       </c>
       <c r="B558" t="s">
-        <v>2859</v>
+        <v>2869</v>
       </c>
       <c r="G558" t="s">
-        <v>2860</v>
+        <v>2870</v>
       </c>
       <c r="H558" t="s">
-        <v>2861</v>
+        <v>2871</v>
       </c>
       <c r="I558" t="s">
         <v>237</v>
       </c>
       <c r="J558" t="s">
-        <v>2862</v>
+        <v>2872</v>
       </c>
       <c r="K558">
         <v>2019</v>
@@ -37858,19 +38295,19 @@
         <v>43</v>
       </c>
       <c r="B559" t="s">
-        <v>2863</v>
+        <v>2873</v>
       </c>
       <c r="G559" t="s">
-        <v>2864</v>
+        <v>2874</v>
       </c>
       <c r="H559" t="s">
-        <v>2865</v>
+        <v>2875</v>
       </c>
       <c r="I559" t="s">
-        <v>2866</v>
+        <v>2876</v>
       </c>
       <c r="J559" t="s">
-        <v>2867</v>
+        <v>2877</v>
       </c>
       <c r="K559">
         <v>2015</v>
@@ -37882,19 +38319,19 @@
         <v>43</v>
       </c>
       <c r="B560" t="s">
-        <v>2868</v>
+        <v>2878</v>
       </c>
       <c r="G560" t="s">
-        <v>2869</v>
+        <v>2879</v>
       </c>
       <c r="H560" t="s">
-        <v>2870</v>
+        <v>2880</v>
       </c>
       <c r="I560" t="s">
         <v>1014</v>
       </c>
       <c r="J560" t="s">
-        <v>2871</v>
+        <v>2881</v>
       </c>
       <c r="K560">
         <v>2026</v>
@@ -37906,19 +38343,19 @@
         <v>43</v>
       </c>
       <c r="B561" t="s">
-        <v>2872</v>
+        <v>2882</v>
       </c>
       <c r="G561" t="s">
-        <v>2873</v>
+        <v>2883</v>
       </c>
       <c r="H561" t="s">
-        <v>2874</v>
+        <v>2884</v>
       </c>
       <c r="I561" t="s">
         <v>51</v>
       </c>
       <c r="J561" t="s">
-        <v>2875</v>
+        <v>2885</v>
       </c>
       <c r="K561">
         <v>2023</v>
@@ -37930,19 +38367,19 @@
         <v>43</v>
       </c>
       <c r="B562" t="s">
-        <v>2876</v>
+        <v>2886</v>
       </c>
       <c r="G562" t="s">
-        <v>2877</v>
+        <v>2887</v>
       </c>
       <c r="H562" t="s">
-        <v>2878</v>
+        <v>2888</v>
       </c>
       <c r="I562" t="s">
         <v>51</v>
       </c>
       <c r="J562" t="s">
-        <v>2879</v>
+        <v>2889</v>
       </c>
       <c r="K562">
         <v>2000</v>
@@ -37954,19 +38391,19 @@
         <v>43</v>
       </c>
       <c r="B563" t="s">
-        <v>2880</v>
+        <v>2890</v>
       </c>
       <c r="G563" t="s">
-        <v>2881</v>
+        <v>2891</v>
       </c>
       <c r="H563" t="s">
-        <v>2882</v>
+        <v>2892</v>
       </c>
       <c r="I563" t="s">
         <v>51</v>
       </c>
       <c r="J563" t="s">
-        <v>2883</v>
+        <v>2893</v>
       </c>
       <c r="K563">
         <v>2016</v>
@@ -37978,19 +38415,19 @@
         <v>43</v>
       </c>
       <c r="B564" t="s">
-        <v>2884</v>
+        <v>2894</v>
       </c>
       <c r="G564" t="s">
-        <v>2885</v>
+        <v>2895</v>
       </c>
       <c r="H564" t="s">
-        <v>2886</v>
+        <v>2896</v>
       </c>
       <c r="I564" t="s">
         <v>1461</v>
       </c>
       <c r="J564" t="s">
-        <v>2887</v>
+        <v>2897</v>
       </c>
       <c r="K564">
         <v>2026</v>
@@ -38002,19 +38439,19 @@
         <v>43</v>
       </c>
       <c r="B565" t="s">
-        <v>2888</v>
+        <v>2898</v>
       </c>
       <c r="G565" t="s">
-        <v>2889</v>
+        <v>2899</v>
       </c>
       <c r="H565" t="s">
-        <v>2890</v>
+        <v>2900</v>
       </c>
       <c r="I565" t="s">
-        <v>2891</v>
+        <v>2901</v>
       </c>
       <c r="J565" t="s">
-        <v>2892</v>
+        <v>2902</v>
       </c>
       <c r="K565">
         <v>2024</v>
@@ -38026,19 +38463,19 @@
         <v>43</v>
       </c>
       <c r="B566" t="s">
-        <v>2893</v>
+        <v>2903</v>
       </c>
       <c r="G566" t="s">
-        <v>2894</v>
+        <v>2904</v>
       </c>
       <c r="H566" t="s">
-        <v>2895</v>
+        <v>2905</v>
       </c>
       <c r="I566" t="s">
         <v>459</v>
       </c>
       <c r="J566" t="s">
-        <v>2896</v>
+        <v>2906</v>
       </c>
       <c r="K566">
         <v>2019</v>
@@ -38050,19 +38487,19 @@
         <v>43</v>
       </c>
       <c r="B567" t="s">
-        <v>2897</v>
+        <v>2907</v>
       </c>
       <c r="G567" t="s">
-        <v>2898</v>
+        <v>2908</v>
       </c>
       <c r="H567" t="s">
-        <v>2899</v>
+        <v>2909</v>
       </c>
       <c r="I567" t="s">
         <v>915</v>
       </c>
       <c r="J567" t="s">
-        <v>2900</v>
+        <v>2910</v>
       </c>
       <c r="K567">
         <v>2020</v>
@@ -38074,19 +38511,19 @@
         <v>43</v>
       </c>
       <c r="B568" t="s">
-        <v>2901</v>
+        <v>2911</v>
       </c>
       <c r="G568" t="s">
-        <v>2902</v>
+        <v>2912</v>
       </c>
       <c r="H568" t="s">
-        <v>2903</v>
+        <v>2913</v>
       </c>
       <c r="I568" t="s">
-        <v>2904</v>
+        <v>2914</v>
       </c>
       <c r="J568" t="s">
-        <v>2905</v>
+        <v>2915</v>
       </c>
       <c r="K568">
         <v>2014</v>
@@ -38098,19 +38535,19 @@
         <v>43</v>
       </c>
       <c r="B569" t="s">
-        <v>2906</v>
+        <v>2916</v>
       </c>
       <c r="G569" t="s">
-        <v>2907</v>
+        <v>2917</v>
       </c>
       <c r="H569" t="s">
-        <v>2908</v>
+        <v>2918</v>
       </c>
       <c r="I569" t="s">
         <v>51</v>
       </c>
       <c r="J569" t="s">
-        <v>2909</v>
+        <v>2919</v>
       </c>
       <c r="K569">
         <v>2004</v>
@@ -38122,19 +38559,19 @@
         <v>43</v>
       </c>
       <c r="B570" t="s">
-        <v>2910</v>
+        <v>2920</v>
       </c>
       <c r="G570" t="s">
-        <v>2911</v>
+        <v>2921</v>
       </c>
       <c r="H570" t="s">
-        <v>2912</v>
+        <v>2922</v>
       </c>
       <c r="I570" t="s">
         <v>51</v>
       </c>
       <c r="J570" t="s">
-        <v>2913</v>
+        <v>2923</v>
       </c>
       <c r="K570">
         <v>2015</v>
@@ -38146,19 +38583,19 @@
         <v>43</v>
       </c>
       <c r="B571" t="s">
-        <v>2914</v>
+        <v>2924</v>
       </c>
       <c r="G571" t="s">
-        <v>2915</v>
+        <v>2925</v>
       </c>
       <c r="H571" t="s">
-        <v>2916</v>
+        <v>2926</v>
       </c>
       <c r="I571" t="s">
         <v>979</v>
       </c>
       <c r="J571" t="s">
-        <v>2917</v>
+        <v>2927</v>
       </c>
       <c r="K571">
         <v>2015</v>
@@ -38170,19 +38607,19 @@
         <v>43</v>
       </c>
       <c r="B572" t="s">
-        <v>2918</v>
+        <v>2928</v>
       </c>
       <c r="G572" t="s">
-        <v>2919</v>
+        <v>2929</v>
       </c>
       <c r="H572" t="s">
-        <v>2920</v>
+        <v>2930</v>
       </c>
       <c r="I572" t="s">
-        <v>2921</v>
+        <v>2931</v>
       </c>
       <c r="J572" t="s">
-        <v>2922</v>
+        <v>2932</v>
       </c>
       <c r="K572">
         <v>2013</v>
@@ -38194,19 +38631,19 @@
         <v>43</v>
       </c>
       <c r="B573" t="s">
-        <v>2923</v>
+        <v>2933</v>
       </c>
       <c r="G573" t="s">
-        <v>2924</v>
+        <v>2934</v>
       </c>
       <c r="H573" t="s">
-        <v>2925</v>
+        <v>2935</v>
       </c>
       <c r="I573" t="s">
         <v>692</v>
       </c>
       <c r="J573" t="s">
-        <v>2926</v>
+        <v>2936</v>
       </c>
       <c r="K573">
         <v>2017</v>
@@ -38218,19 +38655,19 @@
         <v>43</v>
       </c>
       <c r="B574" t="s">
-        <v>2927</v>
+        <v>2937</v>
       </c>
       <c r="G574" t="s">
-        <v>2928</v>
+        <v>2938</v>
       </c>
       <c r="H574" t="s">
-        <v>2929</v>
+        <v>2939</v>
       </c>
       <c r="I574" t="s">
         <v>51</v>
       </c>
       <c r="J574" t="s">
-        <v>2930</v>
+        <v>2940</v>
       </c>
       <c r="K574">
         <v>1995</v>
@@ -38242,19 +38679,19 @@
         <v>43</v>
       </c>
       <c r="B575" t="s">
-        <v>2931</v>
+        <v>2941</v>
       </c>
       <c r="G575" t="s">
-        <v>2932</v>
+        <v>2942</v>
       </c>
       <c r="H575" t="s">
-        <v>2933</v>
+        <v>2943</v>
       </c>
       <c r="I575" t="s">
-        <v>2934</v>
+        <v>2944</v>
       </c>
       <c r="J575" t="s">
-        <v>2935</v>
+        <v>2945</v>
       </c>
       <c r="K575">
         <v>2019</v>
@@ -38266,19 +38703,19 @@
         <v>43</v>
       </c>
       <c r="B576" t="s">
-        <v>2936</v>
+        <v>2946</v>
       </c>
       <c r="G576" t="s">
-        <v>2937</v>
+        <v>2947</v>
       </c>
       <c r="H576" t="s">
-        <v>2938</v>
+        <v>2948</v>
       </c>
       <c r="I576" t="s">
         <v>723</v>
       </c>
       <c r="J576" t="s">
-        <v>2939</v>
+        <v>2949</v>
       </c>
       <c r="K576">
         <v>2010</v>
@@ -38290,19 +38727,19 @@
         <v>43</v>
       </c>
       <c r="B577" t="s">
-        <v>2940</v>
+        <v>2950</v>
       </c>
       <c r="G577" t="s">
-        <v>2941</v>
+        <v>2951</v>
       </c>
       <c r="H577" t="s">
-        <v>2942</v>
+        <v>2952</v>
       </c>
       <c r="I577" t="s">
         <v>915</v>
       </c>
       <c r="J577" t="s">
-        <v>2943</v>
+        <v>2953</v>
       </c>
       <c r="K577">
         <v>2012</v>
@@ -38314,19 +38751,19 @@
         <v>43</v>
       </c>
       <c r="B578" t="s">
-        <v>2944</v>
+        <v>2954</v>
       </c>
       <c r="G578" t="s">
-        <v>2945</v>
+        <v>2955</v>
       </c>
       <c r="H578" t="s">
-        <v>2946</v>
+        <v>2956</v>
       </c>
       <c r="I578" t="s">
         <v>723</v>
       </c>
       <c r="J578" t="s">
-        <v>2947</v>
+        <v>2957</v>
       </c>
       <c r="K578">
         <v>1979</v>
@@ -38338,19 +38775,19 @@
         <v>43</v>
       </c>
       <c r="B579" t="s">
-        <v>2948</v>
+        <v>2958</v>
       </c>
       <c r="G579" t="s">
-        <v>2949</v>
+        <v>2959</v>
       </c>
       <c r="H579" t="s">
-        <v>2950</v>
+        <v>2960</v>
       </c>
       <c r="I579" t="s">
-        <v>2951</v>
+        <v>2961</v>
       </c>
       <c r="J579" t="s">
-        <v>2952</v>
+        <v>2962</v>
       </c>
       <c r="K579">
         <v>1980</v>
@@ -38362,19 +38799,19 @@
         <v>43</v>
       </c>
       <c r="B580" t="s">
-        <v>2953</v>
+        <v>2963</v>
       </c>
       <c r="G580" t="s">
-        <v>2954</v>
+        <v>2964</v>
       </c>
       <c r="H580" t="s">
-        <v>2955</v>
+        <v>2965</v>
       </c>
       <c r="I580" t="s">
         <v>253</v>
       </c>
       <c r="J580" t="s">
-        <v>2956</v>
+        <v>2966</v>
       </c>
       <c r="K580">
         <v>1981</v>
@@ -38386,19 +38823,19 @@
         <v>43</v>
       </c>
       <c r="B581" t="s">
-        <v>2957</v>
+        <v>2967</v>
       </c>
       <c r="G581" t="s">
-        <v>2958</v>
+        <v>2968</v>
       </c>
       <c r="H581" t="s">
-        <v>2959</v>
+        <v>2969</v>
       </c>
       <c r="I581" t="s">
         <v>723</v>
       </c>
       <c r="J581" t="s">
-        <v>2956</v>
+        <v>2966</v>
       </c>
       <c r="K581">
         <v>1981</v>
@@ -38410,19 +38847,19 @@
         <v>43</v>
       </c>
       <c r="B582" t="s">
-        <v>2960</v>
+        <v>2970</v>
       </c>
       <c r="G582" t="s">
-        <v>2961</v>
+        <v>2971</v>
       </c>
       <c r="H582" t="s">
-        <v>2962</v>
+        <v>2972</v>
       </c>
       <c r="I582" t="s">
         <v>197</v>
       </c>
       <c r="J582" t="s">
-        <v>2963</v>
+        <v>2973</v>
       </c>
       <c r="K582">
         <v>2023</v>
@@ -38434,19 +38871,19 @@
         <v>43</v>
       </c>
       <c r="B583" t="s">
-        <v>2964</v>
+        <v>2974</v>
       </c>
       <c r="G583" t="s">
-        <v>2965</v>
+        <v>2975</v>
       </c>
       <c r="H583" t="s">
-        <v>2966</v>
+        <v>2976</v>
       </c>
       <c r="I583" t="s">
         <v>2184</v>
       </c>
       <c r="J583" t="s">
-        <v>2967</v>
+        <v>2977</v>
       </c>
       <c r="K583">
         <v>2024</v>
@@ -38458,19 +38895,19 @@
         <v>43</v>
       </c>
       <c r="B584" t="s">
-        <v>2968</v>
+        <v>2978</v>
       </c>
       <c r="G584" t="s">
-        <v>2969</v>
+        <v>2979</v>
       </c>
       <c r="H584" t="s">
-        <v>2970</v>
+        <v>2980</v>
       </c>
       <c r="I584" t="s">
-        <v>2971</v>
+        <v>2981</v>
       </c>
       <c r="J584" t="s">
-        <v>2972</v>
+        <v>2982</v>
       </c>
       <c r="K584">
         <v>2014</v>
@@ -38482,19 +38919,19 @@
         <v>43</v>
       </c>
       <c r="B585" t="s">
-        <v>2973</v>
+        <v>2983</v>
       </c>
       <c r="G585" t="s">
-        <v>2974</v>
+        <v>2984</v>
       </c>
       <c r="H585" t="s">
-        <v>2975</v>
+        <v>2985</v>
       </c>
       <c r="I585" t="s">
         <v>745</v>
       </c>
       <c r="J585" t="s">
-        <v>2976</v>
+        <v>2986</v>
       </c>
       <c r="K585">
         <v>2015</v>
@@ -38506,19 +38943,19 @@
         <v>43</v>
       </c>
       <c r="B586" t="s">
-        <v>2977</v>
+        <v>2987</v>
       </c>
       <c r="G586" t="s">
-        <v>2978</v>
+        <v>2988</v>
       </c>
       <c r="H586" t="s">
-        <v>2979</v>
+        <v>2989</v>
       </c>
       <c r="I586" t="s">
         <v>2269</v>
       </c>
       <c r="J586" t="s">
-        <v>2980</v>
+        <v>2990</v>
       </c>
       <c r="K586">
         <v>2020</v>
@@ -38530,19 +38967,19 @@
         <v>43</v>
       </c>
       <c r="B587" t="s">
-        <v>2981</v>
+        <v>2991</v>
       </c>
       <c r="G587" t="s">
-        <v>2982</v>
+        <v>2992</v>
       </c>
       <c r="H587" t="s">
-        <v>2983</v>
+        <v>2993</v>
       </c>
       <c r="I587" t="s">
-        <v>2984</v>
+        <v>2994</v>
       </c>
       <c r="J587" t="s">
-        <v>2985</v>
+        <v>2995</v>
       </c>
       <c r="K587">
         <v>2020</v>
@@ -38554,19 +38991,19 @@
         <v>43</v>
       </c>
       <c r="B588" t="s">
-        <v>2986</v>
+        <v>2996</v>
       </c>
       <c r="G588" t="s">
-        <v>2987</v>
+        <v>2997</v>
       </c>
       <c r="H588" t="s">
-        <v>2988</v>
+        <v>2998</v>
       </c>
       <c r="I588" t="s">
         <v>1359</v>
       </c>
       <c r="J588" t="s">
-        <v>2989</v>
+        <v>2999</v>
       </c>
       <c r="K588">
         <v>2021</v>
@@ -38578,19 +39015,19 @@
         <v>43</v>
       </c>
       <c r="B589" t="s">
-        <v>2990</v>
+        <v>3000</v>
       </c>
       <c r="G589" t="s">
-        <v>2991</v>
+        <v>3001</v>
       </c>
       <c r="H589" t="s">
-        <v>2992</v>
+        <v>3002</v>
       </c>
       <c r="I589" t="s">
         <v>979</v>
       </c>
       <c r="J589" t="s">
-        <v>2993</v>
+        <v>3003</v>
       </c>
       <c r="K589">
         <v>2024</v>
@@ -38602,19 +39039,19 @@
         <v>43</v>
       </c>
       <c r="B590" t="s">
-        <v>2994</v>
+        <v>3004</v>
       </c>
       <c r="G590" t="s">
-        <v>2995</v>
+        <v>3005</v>
       </c>
       <c r="H590" t="s">
-        <v>2996</v>
+        <v>3006</v>
       </c>
       <c r="I590" t="s">
-        <v>2997</v>
+        <v>3007</v>
       </c>
       <c r="J590" t="s">
-        <v>2998</v>
+        <v>3008</v>
       </c>
       <c r="K590">
         <v>2014</v>
@@ -38626,19 +39063,19 @@
         <v>43</v>
       </c>
       <c r="B591" t="s">
-        <v>2999</v>
+        <v>3009</v>
       </c>
       <c r="G591" t="s">
-        <v>3000</v>
+        <v>3010</v>
       </c>
       <c r="H591" t="s">
-        <v>3001</v>
+        <v>3011</v>
       </c>
       <c r="I591" t="s">
-        <v>3002</v>
+        <v>3012</v>
       </c>
       <c r="J591" t="s">
-        <v>3003</v>
+        <v>3013</v>
       </c>
       <c r="K591">
         <v>2016</v>
@@ -38650,19 +39087,19 @@
         <v>43</v>
       </c>
       <c r="B592" t="s">
-        <v>3004</v>
+        <v>3014</v>
       </c>
       <c r="G592" t="s">
-        <v>3005</v>
+        <v>3015</v>
       </c>
       <c r="H592" t="s">
-        <v>3006</v>
+        <v>3016</v>
       </c>
       <c r="I592" t="s">
         <v>2184</v>
       </c>
       <c r="J592" t="s">
-        <v>3007</v>
+        <v>3017</v>
       </c>
       <c r="K592">
         <v>2023</v>
@@ -38674,19 +39111,19 @@
         <v>43</v>
       </c>
       <c r="B593" t="s">
-        <v>3008</v>
+        <v>3018</v>
       </c>
       <c r="G593" t="s">
-        <v>3009</v>
+        <v>3019</v>
       </c>
       <c r="H593" t="s">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="I593" t="s">
         <v>2043</v>
       </c>
       <c r="J593" t="s">
-        <v>3011</v>
+        <v>3021</v>
       </c>
       <c r="K593">
         <v>2009</v>
@@ -38698,19 +39135,19 @@
         <v>43</v>
       </c>
       <c r="B594" t="s">
-        <v>3012</v>
+        <v>3022</v>
       </c>
       <c r="G594" t="s">
-        <v>3013</v>
+        <v>3023</v>
       </c>
       <c r="H594" t="s">
-        <v>3014</v>
+        <v>3024</v>
       </c>
       <c r="I594" t="s">
         <v>990</v>
       </c>
       <c r="J594" t="s">
-        <v>3015</v>
+        <v>3025</v>
       </c>
       <c r="K594">
         <v>2018</v>
@@ -38722,19 +39159,19 @@
         <v>43</v>
       </c>
       <c r="B595" t="s">
-        <v>3016</v>
+        <v>3026</v>
       </c>
       <c r="G595" t="s">
-        <v>3017</v>
+        <v>3027</v>
       </c>
       <c r="H595" t="s">
-        <v>3018</v>
+        <v>3028</v>
       </c>
       <c r="I595" t="s">
-        <v>3019</v>
+        <v>3029</v>
       </c>
       <c r="J595" t="s">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="K595">
         <v>2020</v>
@@ -38746,19 +39183,19 @@
         <v>43</v>
       </c>
       <c r="B596" t="s">
-        <v>3021</v>
+        <v>3031</v>
       </c>
       <c r="G596" t="s">
-        <v>3022</v>
+        <v>3032</v>
       </c>
       <c r="H596" t="s">
-        <v>3023</v>
+        <v>3033</v>
       </c>
       <c r="I596" t="s">
-        <v>3024</v>
+        <v>3034</v>
       </c>
       <c r="J596" t="s">
-        <v>3025</v>
+        <v>3035</v>
       </c>
       <c r="K596">
         <v>2002</v>
@@ -38770,19 +39207,19 @@
         <v>43</v>
       </c>
       <c r="B597" t="s">
-        <v>3026</v>
+        <v>3036</v>
       </c>
       <c r="G597" t="s">
-        <v>3027</v>
+        <v>3037</v>
       </c>
       <c r="H597" t="s">
-        <v>3028</v>
+        <v>3038</v>
       </c>
       <c r="I597" t="s">
         <v>51</v>
       </c>
       <c r="J597" t="s">
-        <v>3029</v>
+        <v>3039</v>
       </c>
       <c r="K597">
         <v>1994</v>
@@ -38794,19 +39231,19 @@
         <v>43</v>
       </c>
       <c r="B598" t="s">
-        <v>3030</v>
+        <v>3040</v>
       </c>
       <c r="G598" t="s">
-        <v>3031</v>
+        <v>3041</v>
       </c>
       <c r="H598" t="s">
-        <v>3032</v>
+        <v>3042</v>
       </c>
       <c r="I598" t="s">
         <v>1308</v>
       </c>
       <c r="J598" t="s">
-        <v>3033</v>
+        <v>3043</v>
       </c>
       <c r="K598">
         <v>2021</v>
@@ -38818,19 +39255,19 @@
         <v>43</v>
       </c>
       <c r="B599" t="s">
-        <v>3034</v>
+        <v>3044</v>
       </c>
       <c r="G599" t="s">
-        <v>3035</v>
+        <v>3045</v>
       </c>
       <c r="H599" t="s">
-        <v>3036</v>
+        <v>3046</v>
       </c>
       <c r="I599" t="s">
         <v>1652</v>
       </c>
       <c r="J599" t="s">
-        <v>3037</v>
+        <v>3047</v>
       </c>
       <c r="K599">
         <v>2025</v>
@@ -38842,19 +39279,19 @@
         <v>43</v>
       </c>
       <c r="B600" t="s">
-        <v>3038</v>
+        <v>3048</v>
       </c>
       <c r="G600" t="s">
-        <v>3039</v>
+        <v>3049</v>
       </c>
       <c r="H600" t="s">
-        <v>3040</v>
+        <v>3050</v>
       </c>
       <c r="I600" t="s">
         <v>51</v>
       </c>
       <c r="J600" t="s">
-        <v>3041</v>
+        <v>3051</v>
       </c>
       <c r="K600">
         <v>2021</v>
@@ -38866,19 +39303,19 @@
         <v>43</v>
       </c>
       <c r="B601" t="s">
-        <v>3042</v>
+        <v>3052</v>
       </c>
       <c r="G601" t="s">
-        <v>3043</v>
+        <v>3053</v>
       </c>
       <c r="H601" t="s">
-        <v>3044</v>
+        <v>3054</v>
       </c>
       <c r="I601" t="s">
-        <v>3002</v>
+        <v>3012</v>
       </c>
       <c r="J601" t="s">
-        <v>3045</v>
+        <v>3055</v>
       </c>
       <c r="K601">
         <v>2024</v>
@@ -38890,19 +39327,19 @@
         <v>43</v>
       </c>
       <c r="B602" t="s">
-        <v>3046</v>
+        <v>3056</v>
       </c>
       <c r="G602" t="s">
-        <v>3047</v>
+        <v>3057</v>
       </c>
       <c r="H602" t="s">
-        <v>3048</v>
+        <v>3058</v>
       </c>
       <c r="I602" t="s">
-        <v>2891</v>
+        <v>2901</v>
       </c>
       <c r="J602" t="s">
-        <v>3049</v>
+        <v>3059</v>
       </c>
       <c r="K602">
         <v>2024</v>
@@ -38914,19 +39351,19 @@
         <v>43</v>
       </c>
       <c r="B603" t="s">
-        <v>3050</v>
+        <v>3060</v>
       </c>
       <c r="G603" t="s">
-        <v>3051</v>
+        <v>3061</v>
       </c>
       <c r="H603" t="s">
-        <v>3052</v>
+        <v>3062</v>
       </c>
       <c r="I603" t="s">
-        <v>3053</v>
+        <v>3063</v>
       </c>
       <c r="J603" t="s">
-        <v>3054</v>
+        <v>3064</v>
       </c>
       <c r="K603">
         <v>2018</v>
@@ -38938,19 +39375,19 @@
         <v>43</v>
       </c>
       <c r="B604" t="s">
-        <v>3055</v>
+        <v>3065</v>
       </c>
       <c r="G604" t="s">
-        <v>3056</v>
+        <v>3066</v>
       </c>
       <c r="H604" t="s">
-        <v>3057</v>
+        <v>3067</v>
       </c>
       <c r="I604" t="s">
         <v>100</v>
       </c>
       <c r="J604" t="s">
-        <v>3058</v>
+        <v>3068</v>
       </c>
       <c r="K604">
         <v>2014</v>
@@ -38962,19 +39399,19 @@
         <v>43</v>
       </c>
       <c r="B605" t="s">
-        <v>3059</v>
+        <v>3069</v>
       </c>
       <c r="G605" t="s">
-        <v>3060</v>
+        <v>3070</v>
       </c>
       <c r="H605" t="s">
-        <v>3061</v>
+        <v>3071</v>
       </c>
       <c r="I605" t="s">
         <v>1924</v>
       </c>
       <c r="J605" t="s">
-        <v>3062</v>
+        <v>3072</v>
       </c>
       <c r="K605">
         <v>2019</v>
@@ -38986,19 +39423,19 @@
         <v>43</v>
       </c>
       <c r="B606" t="s">
-        <v>3063</v>
+        <v>3073</v>
       </c>
       <c r="G606" t="s">
-        <v>3064</v>
+        <v>3074</v>
       </c>
       <c r="H606" t="s">
-        <v>3065</v>
+        <v>3075</v>
       </c>
       <c r="I606" t="s">
-        <v>3066</v>
+        <v>3076</v>
       </c>
       <c r="J606" t="s">
-        <v>3067</v>
+        <v>3077</v>
       </c>
       <c r="K606">
         <v>2024</v>
@@ -39010,19 +39447,19 @@
         <v>43</v>
       </c>
       <c r="B607" t="s">
-        <v>3068</v>
+        <v>3078</v>
       </c>
       <c r="G607" t="s">
-        <v>3069</v>
+        <v>3079</v>
       </c>
       <c r="H607" t="s">
-        <v>3070</v>
+        <v>3080</v>
       </c>
       <c r="I607" t="s">
         <v>1520</v>
       </c>
       <c r="J607" t="s">
-        <v>3071</v>
+        <v>3081</v>
       </c>
       <c r="K607">
         <v>2024</v>
@@ -39034,19 +39471,19 @@
         <v>43</v>
       </c>
       <c r="B608" t="s">
-        <v>3072</v>
+        <v>3082</v>
       </c>
       <c r="G608" t="s">
-        <v>3073</v>
+        <v>3083</v>
       </c>
       <c r="H608" t="s">
-        <v>3074</v>
+        <v>3084</v>
       </c>
       <c r="I608" t="s">
         <v>1520</v>
       </c>
       <c r="J608" t="s">
-        <v>3075</v>
+        <v>3085</v>
       </c>
       <c r="K608">
         <v>2021</v>
@@ -39058,19 +39495,19 @@
         <v>43</v>
       </c>
       <c r="B609" t="s">
-        <v>3076</v>
+        <v>3086</v>
       </c>
       <c r="G609" t="s">
-        <v>3077</v>
+        <v>3087</v>
       </c>
       <c r="H609" t="s">
-        <v>3078</v>
+        <v>3088</v>
       </c>
       <c r="I609" t="s">
-        <v>3079</v>
+        <v>3089</v>
       </c>
       <c r="J609" t="s">
-        <v>3080</v>
+        <v>3090</v>
       </c>
       <c r="K609">
         <v>2022</v>
@@ -39082,19 +39519,19 @@
         <v>43</v>
       </c>
       <c r="B610" t="s">
-        <v>3081</v>
+        <v>3091</v>
       </c>
       <c r="G610" t="s">
-        <v>3082</v>
+        <v>3092</v>
       </c>
       <c r="H610" t="s">
-        <v>3083</v>
+        <v>3093</v>
       </c>
       <c r="I610" t="s">
         <v>226</v>
       </c>
       <c r="J610" t="s">
-        <v>3084</v>
+        <v>3094</v>
       </c>
       <c r="K610">
         <v>2020</v>
@@ -39106,19 +39543,19 @@
         <v>43</v>
       </c>
       <c r="B611" t="s">
-        <v>3085</v>
+        <v>3095</v>
       </c>
       <c r="G611" t="s">
-        <v>3086</v>
+        <v>3096</v>
       </c>
       <c r="H611" t="s">
-        <v>3087</v>
+        <v>3097</v>
       </c>
       <c r="I611" t="s">
         <v>226</v>
       </c>
       <c r="J611" t="s">
-        <v>3084</v>
+        <v>3094</v>
       </c>
       <c r="K611">
         <v>2023</v>
@@ -39130,19 +39567,19 @@
         <v>43</v>
       </c>
       <c r="B612" t="s">
-        <v>3088</v>
+        <v>3098</v>
       </c>
       <c r="G612" t="s">
-        <v>3089</v>
+        <v>3099</v>
       </c>
       <c r="H612" t="s">
-        <v>3090</v>
+        <v>3100</v>
       </c>
       <c r="I612" t="s">
-        <v>3091</v>
+        <v>3101</v>
       </c>
       <c r="J612" t="s">
-        <v>3092</v>
+        <v>3102</v>
       </c>
       <c r="K612">
         <v>2023</v>
@@ -39154,19 +39591,19 @@
         <v>43</v>
       </c>
       <c r="B613" t="s">
-        <v>3093</v>
+        <v>3103</v>
       </c>
       <c r="G613" t="s">
-        <v>3094</v>
+        <v>3104</v>
       </c>
       <c r="H613" t="s">
-        <v>3095</v>
+        <v>3105</v>
       </c>
       <c r="I613" t="s">
         <v>1414</v>
       </c>
       <c r="J613" t="s">
-        <v>3096</v>
+        <v>3106</v>
       </c>
       <c r="K613">
         <v>2023</v>
@@ -39178,19 +39615,19 @@
         <v>43</v>
       </c>
       <c r="B614" t="s">
-        <v>3097</v>
+        <v>3107</v>
       </c>
       <c r="G614" t="s">
-        <v>3098</v>
+        <v>3108</v>
       </c>
       <c r="H614" t="s">
-        <v>3099</v>
+        <v>3109</v>
       </c>
       <c r="I614" t="s">
         <v>409</v>
       </c>
       <c r="J614" t="s">
-        <v>3100</v>
+        <v>3110</v>
       </c>
       <c r="K614">
         <v>2022</v>
@@ -39202,19 +39639,19 @@
         <v>43</v>
       </c>
       <c r="B615" t="s">
-        <v>3101</v>
+        <v>3111</v>
       </c>
       <c r="G615" t="s">
-        <v>3102</v>
+        <v>3112</v>
       </c>
       <c r="H615" t="s">
-        <v>3103</v>
+        <v>3113</v>
       </c>
       <c r="I615" t="s">
-        <v>3104</v>
+        <v>3114</v>
       </c>
       <c r="J615" t="s">
-        <v>3105</v>
+        <v>3115</v>
       </c>
       <c r="K615">
         <v>2022</v>
@@ -39226,19 +39663,19 @@
         <v>43</v>
       </c>
       <c r="B616" t="s">
-        <v>3106</v>
+        <v>3116</v>
       </c>
       <c r="G616" t="s">
-        <v>3107</v>
+        <v>3117</v>
       </c>
       <c r="H616" t="s">
-        <v>3108</v>
+        <v>3118</v>
       </c>
       <c r="I616" t="s">
         <v>2275</v>
       </c>
       <c r="J616" t="s">
-        <v>3109</v>
+        <v>3119</v>
       </c>
       <c r="K616">
         <v>2019</v>
@@ -39250,19 +39687,19 @@
         <v>43</v>
       </c>
       <c r="B617" t="s">
-        <v>3110</v>
+        <v>3120</v>
       </c>
       <c r="G617" t="s">
-        <v>3111</v>
+        <v>3121</v>
       </c>
       <c r="H617" t="s">
-        <v>3112</v>
+        <v>3122</v>
       </c>
       <c r="I617" t="s">
-        <v>3113</v>
+        <v>3123</v>
       </c>
       <c r="J617" t="s">
-        <v>3114</v>
+        <v>3124</v>
       </c>
       <c r="K617">
         <v>2024</v>
@@ -39274,19 +39711,19 @@
         <v>43</v>
       </c>
       <c r="B618" t="s">
-        <v>3115</v>
+        <v>3125</v>
       </c>
       <c r="G618" t="s">
-        <v>3116</v>
+        <v>3126</v>
       </c>
       <c r="H618" t="s">
-        <v>3117</v>
+        <v>3127</v>
       </c>
       <c r="I618" t="s">
         <v>295</v>
       </c>
       <c r="J618" t="s">
-        <v>3118</v>
+        <v>3128</v>
       </c>
       <c r="K618">
         <v>2022</v>
@@ -39298,19 +39735,19 @@
         <v>43</v>
       </c>
       <c r="B619" t="s">
-        <v>3119</v>
+        <v>3129</v>
       </c>
       <c r="G619" t="s">
-        <v>3120</v>
+        <v>3130</v>
       </c>
       <c r="H619" t="s">
-        <v>3121</v>
+        <v>3131</v>
       </c>
       <c r="I619" t="s">
         <v>915</v>
       </c>
       <c r="J619" t="s">
-        <v>3122</v>
+        <v>3132</v>
       </c>
       <c r="K619">
         <v>1995</v>
@@ -39322,19 +39759,19 @@
         <v>43</v>
       </c>
       <c r="B620" t="s">
-        <v>3123</v>
+        <v>3133</v>
       </c>
       <c r="G620" t="s">
-        <v>3124</v>
+        <v>3134</v>
       </c>
       <c r="H620" t="s">
-        <v>3125</v>
+        <v>3135</v>
       </c>
       <c r="I620" t="s">
-        <v>3126</v>
+        <v>3136</v>
       </c>
       <c r="J620" t="s">
-        <v>3127</v>
+        <v>3137</v>
       </c>
       <c r="K620">
         <v>1992</v>
@@ -39346,19 +39783,19 @@
         <v>43</v>
       </c>
       <c r="B621" t="s">
-        <v>3128</v>
+        <v>3138</v>
       </c>
       <c r="G621" t="s">
-        <v>3129</v>
+        <v>3139</v>
       </c>
       <c r="H621" t="s">
-        <v>3130</v>
+        <v>3140</v>
       </c>
       <c r="I621" t="s">
-        <v>3131</v>
+        <v>3141</v>
       </c>
       <c r="J621" t="s">
-        <v>3132</v>
+        <v>3142</v>
       </c>
       <c r="K621">
         <v>2021</v>
@@ -39370,19 +39807,19 @@
         <v>43</v>
       </c>
       <c r="B622" t="s">
-        <v>3133</v>
+        <v>3143</v>
       </c>
       <c r="G622" t="s">
-        <v>3134</v>
+        <v>3144</v>
       </c>
       <c r="H622" t="s">
-        <v>3135</v>
+        <v>3145</v>
       </c>
       <c r="I622" t="s">
         <v>973</v>
       </c>
       <c r="J622" t="s">
-        <v>3136</v>
+        <v>3146</v>
       </c>
       <c r="K622">
         <v>2018</v>
@@ -39394,19 +39831,19 @@
         <v>43</v>
       </c>
       <c r="B623" t="s">
-        <v>3137</v>
+        <v>3147</v>
       </c>
       <c r="G623" t="s">
-        <v>3138</v>
+        <v>3148</v>
       </c>
       <c r="H623" t="s">
-        <v>3139</v>
+        <v>3149</v>
       </c>
       <c r="I623" t="s">
-        <v>3140</v>
+        <v>3150</v>
       </c>
       <c r="J623" t="s">
-        <v>3141</v>
+        <v>3151</v>
       </c>
       <c r="K623">
         <v>2019</v>
@@ -39418,19 +39855,19 @@
         <v>43</v>
       </c>
       <c r="B624" t="s">
-        <v>3142</v>
+        <v>3152</v>
       </c>
       <c r="G624" t="s">
-        <v>3143</v>
+        <v>3153</v>
       </c>
       <c r="H624" t="s">
-        <v>3144</v>
+        <v>3154</v>
       </c>
       <c r="I624" t="s">
         <v>1652</v>
       </c>
       <c r="J624" t="s">
-        <v>3145</v>
+        <v>3155</v>
       </c>
       <c r="K624">
         <v>2016</v>
@@ -39442,19 +39879,19 @@
         <v>43</v>
       </c>
       <c r="B625" t="s">
-        <v>3146</v>
+        <v>3156</v>
       </c>
       <c r="G625" t="s">
-        <v>3147</v>
+        <v>3157</v>
       </c>
       <c r="H625" t="s">
-        <v>3148</v>
+        <v>3158</v>
       </c>
       <c r="I625" t="s">
         <v>1242</v>
       </c>
       <c r="J625" t="s">
-        <v>3149</v>
+        <v>3159</v>
       </c>
       <c r="K625">
         <v>2002</v>
@@ -39466,19 +39903,19 @@
         <v>43</v>
       </c>
       <c r="B626" t="s">
-        <v>3150</v>
+        <v>3160</v>
       </c>
       <c r="G626" t="s">
-        <v>3151</v>
+        <v>3161</v>
       </c>
       <c r="H626" t="s">
-        <v>3152</v>
+        <v>3162</v>
       </c>
       <c r="I626" t="s">
-        <v>3153</v>
+        <v>3163</v>
       </c>
       <c r="J626" t="s">
-        <v>3154</v>
+        <v>3164</v>
       </c>
       <c r="K626">
         <v>2018</v>
@@ -39490,19 +39927,19 @@
         <v>43</v>
       </c>
       <c r="B627" t="s">
-        <v>3155</v>
+        <v>3165</v>
       </c>
       <c r="G627" t="s">
-        <v>3156</v>
+        <v>3166</v>
       </c>
       <c r="H627" t="s">
-        <v>3157</v>
+        <v>3167</v>
       </c>
       <c r="I627" t="s">
         <v>128</v>
       </c>
       <c r="J627" t="s">
-        <v>3158</v>
+        <v>3168</v>
       </c>
       <c r="K627">
         <v>2016</v>
@@ -39514,19 +39951,19 @@
         <v>43</v>
       </c>
       <c r="B628" t="s">
-        <v>3159</v>
+        <v>3169</v>
       </c>
       <c r="G628" t="s">
-        <v>3160</v>
+        <v>3170</v>
       </c>
       <c r="H628" t="s">
-        <v>3161</v>
+        <v>3171</v>
       </c>
       <c r="I628" t="s">
         <v>915</v>
       </c>
       <c r="J628" t="s">
-        <v>3162</v>
+        <v>3172</v>
       </c>
       <c r="K628">
         <v>2004</v>
@@ -39538,19 +39975,19 @@
         <v>43</v>
       </c>
       <c r="B629" t="s">
-        <v>3163</v>
+        <v>3173</v>
       </c>
       <c r="G629" t="s">
-        <v>3164</v>
+        <v>3174</v>
       </c>
       <c r="H629" t="s">
-        <v>3165</v>
+        <v>3175</v>
       </c>
       <c r="I629" t="s">
         <v>1652</v>
       </c>
       <c r="J629" t="s">
-        <v>3166</v>
+        <v>3176</v>
       </c>
       <c r="K629">
         <v>2008</v>
@@ -39562,19 +39999,19 @@
         <v>43</v>
       </c>
       <c r="B630" t="s">
-        <v>3167</v>
+        <v>3177</v>
       </c>
       <c r="G630" t="s">
-        <v>3168</v>
+        <v>3178</v>
       </c>
       <c r="H630" t="s">
-        <v>3169</v>
+        <v>3179</v>
       </c>
       <c r="I630" t="s">
         <v>692</v>
       </c>
       <c r="J630" t="s">
-        <v>3170</v>
+        <v>3180</v>
       </c>
       <c r="K630">
         <v>2014</v>
@@ -39586,19 +40023,19 @@
         <v>43</v>
       </c>
       <c r="B631" t="s">
-        <v>3171</v>
+        <v>3181</v>
       </c>
       <c r="G631" t="s">
-        <v>3172</v>
+        <v>3182</v>
       </c>
       <c r="H631" t="s">
-        <v>3173</v>
+        <v>3183</v>
       </c>
       <c r="I631" t="s">
-        <v>2839</v>
+        <v>2849</v>
       </c>
       <c r="J631" t="s">
-        <v>3174</v>
+        <v>3184</v>
       </c>
       <c r="K631">
         <v>2004</v>
@@ -39610,19 +40047,19 @@
         <v>43</v>
       </c>
       <c r="B632" t="s">
-        <v>3175</v>
+        <v>3185</v>
       </c>
       <c r="G632" t="s">
-        <v>3176</v>
+        <v>3186</v>
       </c>
       <c r="H632" t="s">
-        <v>3177</v>
+        <v>3187</v>
       </c>
       <c r="I632" t="s">
-        <v>3178</v>
+        <v>3188</v>
       </c>
       <c r="J632" t="s">
-        <v>3179</v>
+        <v>3189</v>
       </c>
       <c r="K632">
         <v>1994</v>
@@ -39634,19 +40071,19 @@
         <v>43</v>
       </c>
       <c r="B633" t="s">
-        <v>3180</v>
+        <v>3190</v>
       </c>
       <c r="G633" t="s">
-        <v>3181</v>
+        <v>3191</v>
       </c>
       <c r="H633" t="s">
-        <v>3182</v>
+        <v>3192</v>
       </c>
       <c r="I633" t="s">
-        <v>3183</v>
+        <v>3193</v>
       </c>
       <c r="J633" t="s">
-        <v>3184</v>
+        <v>3194</v>
       </c>
       <c r="K633">
         <v>2010</v>
@@ -39658,19 +40095,19 @@
         <v>43</v>
       </c>
       <c r="B634" t="s">
-        <v>3185</v>
+        <v>3195</v>
       </c>
       <c r="G634" t="s">
-        <v>3186</v>
+        <v>3196</v>
       </c>
       <c r="H634" t="s">
-        <v>3187</v>
+        <v>3197</v>
       </c>
       <c r="I634" t="s">
         <v>226</v>
       </c>
       <c r="J634" t="s">
-        <v>3188</v>
+        <v>3198</v>
       </c>
       <c r="K634">
         <v>2025</v>
@@ -39682,19 +40119,19 @@
         <v>43</v>
       </c>
       <c r="B635" t="s">
-        <v>3189</v>
+        <v>3199</v>
       </c>
       <c r="G635" t="s">
-        <v>3190</v>
+        <v>3200</v>
       </c>
       <c r="H635" t="s">
-        <v>3191</v>
+        <v>3201</v>
       </c>
       <c r="I635" t="s">
         <v>825</v>
       </c>
       <c r="J635" t="s">
-        <v>3192</v>
+        <v>3202</v>
       </c>
       <c r="K635">
         <v>2020</v>
@@ -39706,19 +40143,19 @@
         <v>43</v>
       </c>
       <c r="B636" t="s">
-        <v>3193</v>
+        <v>3203</v>
       </c>
       <c r="G636" t="s">
-        <v>3194</v>
+        <v>3204</v>
       </c>
       <c r="H636" t="s">
-        <v>3195</v>
+        <v>3205</v>
       </c>
       <c r="I636" t="s">
-        <v>3196</v>
+        <v>3206</v>
       </c>
       <c r="J636" t="s">
-        <v>3197</v>
+        <v>3207</v>
       </c>
       <c r="K636">
         <v>2017</v>
@@ -39730,19 +40167,19 @@
         <v>43</v>
       </c>
       <c r="B637" t="s">
-        <v>3198</v>
+        <v>3208</v>
       </c>
       <c r="G637" t="s">
-        <v>3199</v>
+        <v>3209</v>
       </c>
       <c r="H637" t="s">
-        <v>3200</v>
+        <v>3210</v>
       </c>
       <c r="I637" t="s">
         <v>295</v>
       </c>
       <c r="J637" t="s">
-        <v>3201</v>
+        <v>3211</v>
       </c>
       <c r="K637">
         <v>2025</v>
@@ -39754,19 +40191,19 @@
         <v>43</v>
       </c>
       <c r="B638" t="s">
-        <v>3202</v>
+        <v>3212</v>
       </c>
       <c r="G638" t="s">
-        <v>3203</v>
+        <v>3213</v>
       </c>
       <c r="H638" t="s">
-        <v>3204</v>
+        <v>3214</v>
       </c>
       <c r="I638" t="s">
         <v>295</v>
       </c>
       <c r="J638" t="s">
-        <v>3205</v>
+        <v>3215</v>
       </c>
       <c r="K638">
         <v>2023</v>
@@ -39778,19 +40215,19 @@
         <v>43</v>
       </c>
       <c r="B639" t="s">
-        <v>3206</v>
+        <v>3216</v>
       </c>
       <c r="G639" t="s">
-        <v>3207</v>
+        <v>3217</v>
       </c>
       <c r="H639" t="s">
-        <v>3208</v>
+        <v>3218</v>
       </c>
       <c r="I639" t="s">
-        <v>3209</v>
+        <v>3219</v>
       </c>
       <c r="J639" t="s">
-        <v>3210</v>
+        <v>3220</v>
       </c>
       <c r="K639">
         <v>2009</v>
@@ -39802,19 +40239,19 @@
         <v>43</v>
       </c>
       <c r="B640" t="s">
-        <v>3211</v>
+        <v>3221</v>
       </c>
       <c r="G640" t="s">
-        <v>3212</v>
+        <v>3222</v>
       </c>
       <c r="H640" t="s">
-        <v>3213</v>
+        <v>3223</v>
       </c>
       <c r="I640" t="s">
         <v>226</v>
       </c>
       <c r="J640" t="s">
-        <v>3214</v>
+        <v>3224</v>
       </c>
       <c r="K640">
         <v>2024</v>
@@ -39826,19 +40263,19 @@
         <v>43</v>
       </c>
       <c r="B641" t="s">
-        <v>3215</v>
+        <v>3225</v>
       </c>
       <c r="G641" t="s">
-        <v>3216</v>
+        <v>3226</v>
       </c>
       <c r="H641" t="s">
-        <v>3217</v>
+        <v>3227</v>
       </c>
       <c r="I641" t="s">
         <v>1548</v>
       </c>
       <c r="J641" t="s">
-        <v>3218</v>
+        <v>3228</v>
       </c>
       <c r="K641">
         <v>2024</v>
@@ -39850,19 +40287,19 @@
         <v>43</v>
       </c>
       <c r="B642" t="s">
-        <v>3219</v>
+        <v>3229</v>
       </c>
       <c r="G642" t="s">
-        <v>3220</v>
+        <v>3230</v>
       </c>
       <c r="H642" t="s">
-        <v>3221</v>
+        <v>3231</v>
       </c>
       <c r="I642" t="s">
         <v>549</v>
       </c>
       <c r="J642" t="s">
-        <v>3222</v>
+        <v>3232</v>
       </c>
       <c r="K642">
         <v>2020</v>
@@ -39874,19 +40311,19 @@
         <v>43</v>
       </c>
       <c r="B643" t="s">
-        <v>3223</v>
+        <v>3233</v>
       </c>
       <c r="G643" t="s">
-        <v>3224</v>
+        <v>3234</v>
       </c>
       <c r="H643" t="s">
-        <v>3225</v>
+        <v>3235</v>
       </c>
       <c r="I643" t="s">
         <v>148</v>
       </c>
       <c r="J643" t="s">
-        <v>3226</v>
+        <v>3236</v>
       </c>
       <c r="K643">
         <v>2020</v>
@@ -39898,19 +40335,19 @@
         <v>43</v>
       </c>
       <c r="B644" t="s">
-        <v>3227</v>
+        <v>3237</v>
       </c>
       <c r="G644" t="s">
-        <v>3228</v>
+        <v>3238</v>
       </c>
       <c r="H644" t="s">
-        <v>3229</v>
+        <v>3239</v>
       </c>
       <c r="I644" t="s">
-        <v>3230</v>
+        <v>3240</v>
       </c>
       <c r="J644" t="s">
-        <v>3231</v>
+        <v>3241</v>
       </c>
       <c r="K644">
         <v>2021</v>
@@ -39922,19 +40359,19 @@
         <v>43</v>
       </c>
       <c r="B645" t="s">
-        <v>3232</v>
+        <v>3242</v>
       </c>
       <c r="G645" t="s">
-        <v>3233</v>
+        <v>3243</v>
       </c>
       <c r="H645" t="s">
-        <v>3234</v>
+        <v>3244</v>
       </c>
       <c r="I645" t="s">
         <v>1308</v>
       </c>
       <c r="J645" t="s">
-        <v>3235</v>
+        <v>3245</v>
       </c>
       <c r="K645">
         <v>2024</v>
@@ -39946,19 +40383,19 @@
         <v>43</v>
       </c>
       <c r="B646" t="s">
-        <v>3236</v>
+        <v>3246</v>
       </c>
       <c r="G646" t="s">
-        <v>3237</v>
+        <v>3247</v>
       </c>
       <c r="H646" t="s">
-        <v>3238</v>
+        <v>3248</v>
       </c>
       <c r="I646" t="s">
         <v>2314</v>
       </c>
       <c r="J646" t="s">
-        <v>3239</v>
+        <v>3249</v>
       </c>
       <c r="K646">
         <v>2024</v>
@@ -39970,19 +40407,19 @@
         <v>43</v>
       </c>
       <c r="B647" t="s">
-        <v>3240</v>
+        <v>3250</v>
       </c>
       <c r="G647" t="s">
-        <v>3241</v>
+        <v>3251</v>
       </c>
       <c r="H647" t="s">
-        <v>3242</v>
+        <v>3252</v>
       </c>
       <c r="I647" t="s">
         <v>295</v>
       </c>
       <c r="J647" t="s">
-        <v>3243</v>
+        <v>3253</v>
       </c>
       <c r="K647">
         <v>2021</v>
@@ -39994,19 +40431,19 @@
         <v>43</v>
       </c>
       <c r="B648" t="s">
-        <v>3244</v>
+        <v>3254</v>
       </c>
       <c r="G648" t="s">
-        <v>3245</v>
+        <v>3255</v>
       </c>
       <c r="H648" t="s">
-        <v>3246</v>
+        <v>3256</v>
       </c>
       <c r="I648" t="s">
         <v>1652</v>
       </c>
       <c r="J648" t="s">
-        <v>3247</v>
+        <v>3257</v>
       </c>
       <c r="K648">
         <v>2022</v>
@@ -40018,19 +40455,19 @@
         <v>43</v>
       </c>
       <c r="B649" t="s">
-        <v>3248</v>
+        <v>3258</v>
       </c>
       <c r="G649" t="s">
-        <v>3249</v>
+        <v>3259</v>
       </c>
       <c r="H649" t="s">
-        <v>3250</v>
+        <v>3260</v>
       </c>
       <c r="I649" t="s">
         <v>409</v>
       </c>
       <c r="J649" t="s">
-        <v>3251</v>
+        <v>3261</v>
       </c>
       <c r="K649">
         <v>2022</v>
@@ -40042,19 +40479,19 @@
         <v>43</v>
       </c>
       <c r="B650" t="s">
-        <v>3252</v>
+        <v>3262</v>
       </c>
       <c r="G650" t="s">
-        <v>3253</v>
+        <v>3263</v>
       </c>
       <c r="H650" t="s">
-        <v>3254</v>
+        <v>3264</v>
       </c>
       <c r="I650" t="s">
-        <v>2690</v>
+        <v>2700</v>
       </c>
       <c r="J650" t="s">
-        <v>3255</v>
+        <v>3265</v>
       </c>
       <c r="K650">
         <v>2026</v>
@@ -40066,19 +40503,19 @@
         <v>43</v>
       </c>
       <c r="B651" t="s">
-        <v>3256</v>
+        <v>3266</v>
       </c>
       <c r="G651" t="s">
-        <v>3257</v>
+        <v>3267</v>
       </c>
       <c r="H651" t="s">
-        <v>3258</v>
+        <v>3268</v>
       </c>
       <c r="I651" t="s">
-        <v>3259</v>
+        <v>3269</v>
       </c>
       <c r="J651" t="s">
-        <v>3260</v>
+        <v>3270</v>
       </c>
       <c r="K651">
         <v>2024</v>
@@ -40090,19 +40527,19 @@
         <v>43</v>
       </c>
       <c r="B652" t="s">
-        <v>3261</v>
+        <v>3271</v>
       </c>
       <c r="G652" t="s">
-        <v>3262</v>
+        <v>3272</v>
       </c>
       <c r="H652" t="s">
-        <v>3263</v>
+        <v>3273</v>
       </c>
       <c r="I652" t="s">
         <v>1336</v>
       </c>
       <c r="J652" t="s">
-        <v>3264</v>
+        <v>3274</v>
       </c>
       <c r="K652">
         <v>2015</v>
@@ -40114,19 +40551,19 @@
         <v>43</v>
       </c>
       <c r="B653" t="s">
-        <v>3265</v>
+        <v>3275</v>
       </c>
       <c r="G653" t="s">
-        <v>3266</v>
+        <v>3276</v>
       </c>
       <c r="H653" t="s">
-        <v>3267</v>
+        <v>3277</v>
       </c>
       <c r="I653" t="s">
-        <v>3268</v>
+        <v>3278</v>
       </c>
       <c r="J653" t="s">
-        <v>3269</v>
+        <v>3279</v>
       </c>
       <c r="K653">
         <v>2017</v>
@@ -40138,19 +40575,19 @@
         <v>43</v>
       </c>
       <c r="B654" t="s">
-        <v>3270</v>
+        <v>3280</v>
       </c>
       <c r="G654" t="s">
-        <v>3271</v>
+        <v>3281</v>
       </c>
       <c r="H654" t="s">
-        <v>3272</v>
+        <v>3282</v>
       </c>
       <c r="I654" t="s">
-        <v>3273</v>
+        <v>3283</v>
       </c>
       <c r="J654" t="s">
-        <v>3274</v>
+        <v>3284</v>
       </c>
       <c r="K654">
         <v>2016</v>
@@ -40162,19 +40599,19 @@
         <v>43</v>
       </c>
       <c r="B655" t="s">
-        <v>3275</v>
+        <v>3285</v>
       </c>
       <c r="G655" t="s">
-        <v>3276</v>
+        <v>3286</v>
       </c>
       <c r="H655" t="s">
-        <v>3277</v>
+        <v>3287</v>
       </c>
       <c r="I655" t="s">
-        <v>3278</v>
+        <v>3288</v>
       </c>
       <c r="J655" t="s">
-        <v>3279</v>
+        <v>3289</v>
       </c>
       <c r="K655">
         <v>2018</v>
@@ -40186,19 +40623,19 @@
         <v>43</v>
       </c>
       <c r="B656" t="s">
-        <v>3280</v>
+        <v>3290</v>
       </c>
       <c r="G656" t="s">
-        <v>3281</v>
+        <v>3291</v>
       </c>
       <c r="H656" t="s">
-        <v>3282</v>
+        <v>3292</v>
       </c>
       <c r="I656" t="s">
         <v>692</v>
       </c>
       <c r="J656" t="s">
-        <v>3283</v>
+        <v>3293</v>
       </c>
       <c r="K656">
         <v>2009</v>
@@ -40210,19 +40647,19 @@
         <v>43</v>
       </c>
       <c r="B657" t="s">
-        <v>3284</v>
+        <v>3294</v>
       </c>
       <c r="G657" t="s">
-        <v>3285</v>
+        <v>3295</v>
       </c>
       <c r="H657" t="s">
-        <v>3286</v>
+        <v>3296</v>
       </c>
       <c r="I657" t="s">
         <v>2054</v>
       </c>
       <c r="J657" t="s">
-        <v>3287</v>
+        <v>3297</v>
       </c>
       <c r="K657">
         <v>2013</v>
@@ -40234,19 +40671,19 @@
         <v>43</v>
       </c>
       <c r="B658" t="s">
-        <v>3288</v>
+        <v>3298</v>
       </c>
       <c r="G658" t="s">
-        <v>3289</v>
+        <v>3299</v>
       </c>
       <c r="H658" t="s">
-        <v>3290</v>
+        <v>3300</v>
       </c>
       <c r="I658" t="s">
-        <v>2904</v>
+        <v>2914</v>
       </c>
       <c r="J658" t="s">
-        <v>3291</v>
+        <v>3301</v>
       </c>
       <c r="K658">
         <v>2014</v>
@@ -40258,19 +40695,19 @@
         <v>43</v>
       </c>
       <c r="B659" t="s">
-        <v>3292</v>
+        <v>3302</v>
       </c>
       <c r="G659" t="s">
-        <v>3293</v>
+        <v>3303</v>
       </c>
       <c r="H659" t="s">
-        <v>3294</v>
+        <v>3304</v>
       </c>
       <c r="I659" t="s">
         <v>1987</v>
       </c>
       <c r="J659" t="s">
-        <v>3295</v>
+        <v>3305</v>
       </c>
       <c r="K659">
         <v>2024</v>
@@ -40282,19 +40719,19 @@
         <v>43</v>
       </c>
       <c r="B660" t="s">
-        <v>3296</v>
+        <v>3306</v>
       </c>
       <c r="G660" t="s">
-        <v>3297</v>
+        <v>3307</v>
       </c>
       <c r="H660" t="s">
-        <v>3298</v>
+        <v>3308</v>
       </c>
       <c r="I660" t="s">
         <v>51</v>
       </c>
       <c r="J660" t="s">
-        <v>3299</v>
+        <v>3309</v>
       </c>
       <c r="K660">
         <v>2023</v>
@@ -40306,19 +40743,19 @@
         <v>43</v>
       </c>
       <c r="B661" t="s">
-        <v>3300</v>
+        <v>3310</v>
       </c>
       <c r="G661" t="s">
-        <v>3301</v>
+        <v>3311</v>
       </c>
       <c r="H661" t="s">
-        <v>3302</v>
+        <v>3312</v>
       </c>
       <c r="I661" t="s">
         <v>664</v>
       </c>
       <c r="J661" t="s">
-        <v>3303</v>
+        <v>3313</v>
       </c>
       <c r="K661">
         <v>2001</v>
@@ -40330,19 +40767,19 @@
         <v>43</v>
       </c>
       <c r="B662" t="s">
-        <v>3304</v>
+        <v>3314</v>
       </c>
       <c r="G662" t="s">
-        <v>3305</v>
+        <v>3315</v>
       </c>
       <c r="H662" t="s">
-        <v>3306</v>
+        <v>3316</v>
       </c>
       <c r="I662" t="s">
-        <v>2891</v>
+        <v>2901</v>
       </c>
       <c r="J662" t="s">
-        <v>3307</v>
+        <v>3317</v>
       </c>
       <c r="K662">
         <v>2024</v>
@@ -40354,19 +40791,19 @@
         <v>43</v>
       </c>
       <c r="B663" t="s">
-        <v>3308</v>
+        <v>3318</v>
       </c>
       <c r="G663" t="s">
-        <v>3309</v>
+        <v>3319</v>
       </c>
       <c r="H663" t="s">
-        <v>3310</v>
+        <v>3320</v>
       </c>
       <c r="I663" t="s">
-        <v>3066</v>
+        <v>3076</v>
       </c>
       <c r="J663" t="s">
-        <v>3311</v>
+        <v>3321</v>
       </c>
       <c r="K663">
         <v>2025</v>
@@ -40378,19 +40815,19 @@
         <v>43</v>
       </c>
       <c r="B664" t="s">
-        <v>3312</v>
+        <v>3322</v>
       </c>
       <c r="G664" t="s">
-        <v>3313</v>
+        <v>3323</v>
       </c>
       <c r="H664" t="s">
-        <v>3314</v>
+        <v>3324</v>
       </c>
       <c r="I664" t="s">
         <v>409</v>
       </c>
       <c r="J664" t="s">
-        <v>3315</v>
+        <v>3325</v>
       </c>
       <c r="K664">
         <v>2022</v>
@@ -40402,19 +40839,19 @@
         <v>43</v>
       </c>
       <c r="B665" t="s">
-        <v>3316</v>
+        <v>3326</v>
       </c>
       <c r="G665" t="s">
-        <v>3317</v>
+        <v>3327</v>
       </c>
       <c r="H665" t="s">
-        <v>3318</v>
+        <v>3328</v>
       </c>
       <c r="I665" t="s">
-        <v>3319</v>
+        <v>3329</v>
       </c>
       <c r="J665" t="s">
-        <v>3320</v>
+        <v>3330</v>
       </c>
       <c r="K665">
         <v>2014</v>
@@ -40426,19 +40863,19 @@
         <v>43</v>
       </c>
       <c r="B666" t="s">
-        <v>3321</v>
+        <v>3331</v>
       </c>
       <c r="G666" t="s">
-        <v>3322</v>
+        <v>3332</v>
       </c>
       <c r="H666" t="s">
-        <v>3323</v>
+        <v>3333</v>
       </c>
       <c r="I666" t="s">
         <v>1414</v>
       </c>
       <c r="J666" t="s">
-        <v>3324</v>
+        <v>3334</v>
       </c>
       <c r="K666">
         <v>2025</v>
@@ -40450,19 +40887,19 @@
         <v>43</v>
       </c>
       <c r="B667" t="s">
-        <v>3325</v>
+        <v>3335</v>
       </c>
       <c r="G667" t="s">
-        <v>3326</v>
+        <v>3336</v>
       </c>
       <c r="H667" t="s">
-        <v>3327</v>
+        <v>3337</v>
       </c>
       <c r="I667" t="s">
         <v>459</v>
       </c>
       <c r="J667" t="s">
-        <v>3328</v>
+        <v>3338</v>
       </c>
       <c r="K667">
         <v>2016</v>
@@ -40474,19 +40911,19 @@
         <v>43</v>
       </c>
       <c r="B668" t="s">
-        <v>3329</v>
+        <v>3339</v>
       </c>
       <c r="G668" t="s">
-        <v>3330</v>
+        <v>3340</v>
       </c>
       <c r="H668" t="s">
-        <v>3331</v>
+        <v>3341</v>
       </c>
       <c r="I668" t="s">
-        <v>3332</v>
+        <v>3342</v>
       </c>
       <c r="J668" t="s">
-        <v>3333</v>
+        <v>3343</v>
       </c>
       <c r="K668">
         <v>2018</v>
@@ -40498,19 +40935,19 @@
         <v>43</v>
       </c>
       <c r="B669" t="s">
-        <v>3334</v>
+        <v>3344</v>
       </c>
       <c r="G669" t="s">
-        <v>3335</v>
+        <v>3345</v>
       </c>
       <c r="H669" t="s">
-        <v>3336</v>
+        <v>3346</v>
       </c>
       <c r="I669" t="s">
         <v>426</v>
       </c>
       <c r="J669" t="s">
-        <v>3337</v>
+        <v>3347</v>
       </c>
       <c r="K669">
         <v>2015</v>
@@ -40522,19 +40959,19 @@
         <v>43</v>
       </c>
       <c r="B670" t="s">
-        <v>3338</v>
+        <v>3348</v>
       </c>
       <c r="G670" t="s">
-        <v>3339</v>
+        <v>3349</v>
       </c>
       <c r="H670" t="s">
-        <v>3340</v>
+        <v>3350</v>
       </c>
       <c r="I670" t="s">
-        <v>3341</v>
+        <v>3351</v>
       </c>
       <c r="J670" t="s">
-        <v>3342</v>
+        <v>3352</v>
       </c>
       <c r="K670">
         <v>2018</v>
@@ -40546,19 +40983,19 @@
         <v>43</v>
       </c>
       <c r="B671" t="s">
-        <v>3343</v>
+        <v>3353</v>
       </c>
       <c r="G671" t="s">
-        <v>3344</v>
+        <v>3354</v>
       </c>
       <c r="H671" t="s">
-        <v>3345</v>
+        <v>3355</v>
       </c>
       <c r="I671" t="s">
         <v>2236</v>
       </c>
       <c r="J671" t="s">
-        <v>3346</v>
+        <v>3356</v>
       </c>
       <c r="K671">
         <v>2011</v>
@@ -40570,19 +41007,19 @@
         <v>43</v>
       </c>
       <c r="B672" t="s">
-        <v>3347</v>
+        <v>3357</v>
       </c>
       <c r="G672" t="s">
-        <v>3348</v>
+        <v>3358</v>
       </c>
       <c r="H672" t="s">
-        <v>3349</v>
+        <v>3359</v>
       </c>
       <c r="I672" t="s">
         <v>128</v>
       </c>
       <c r="J672" t="s">
-        <v>3350</v>
+        <v>3360</v>
       </c>
       <c r="K672">
         <v>2015</v>
@@ -40594,19 +41031,19 @@
         <v>43</v>
       </c>
       <c r="B673" t="s">
-        <v>3351</v>
+        <v>3361</v>
       </c>
       <c r="G673" t="s">
-        <v>3352</v>
+        <v>3362</v>
       </c>
       <c r="H673" t="s">
-        <v>3353</v>
+        <v>3363</v>
       </c>
       <c r="I673" t="s">
         <v>1479</v>
       </c>
       <c r="J673" t="s">
-        <v>3354</v>
+        <v>3364</v>
       </c>
       <c r="K673">
         <v>2022</v>
@@ -40618,19 +41055,19 @@
         <v>43</v>
       </c>
       <c r="B674" t="s">
-        <v>3355</v>
+        <v>3365</v>
       </c>
       <c r="G674" t="s">
-        <v>3356</v>
+        <v>3366</v>
       </c>
       <c r="H674" t="s">
-        <v>3357</v>
+        <v>3367</v>
       </c>
       <c r="I674" t="s">
-        <v>3332</v>
+        <v>3342</v>
       </c>
       <c r="J674" t="s">
-        <v>3358</v>
+        <v>3368</v>
       </c>
       <c r="K674">
         <v>2023</v>
@@ -40642,19 +41079,19 @@
         <v>43</v>
       </c>
       <c r="B675" t="s">
-        <v>3359</v>
+        <v>3369</v>
       </c>
       <c r="G675" t="s">
-        <v>3360</v>
+        <v>3370</v>
       </c>
       <c r="H675" t="s">
-        <v>3361</v>
+        <v>3371</v>
       </c>
       <c r="I675" t="s">
-        <v>3362</v>
+        <v>3372</v>
       </c>
       <c r="J675" t="s">
-        <v>3363</v>
+        <v>3373</v>
       </c>
       <c r="K675">
         <v>2021</v>
@@ -40666,19 +41103,19 @@
         <v>43</v>
       </c>
       <c r="B676" t="s">
-        <v>3364</v>
+        <v>3374</v>
       </c>
       <c r="G676" t="s">
-        <v>3365</v>
+        <v>3375</v>
       </c>
       <c r="H676" t="s">
-        <v>3366</v>
+        <v>3376</v>
       </c>
       <c r="I676" t="s">
         <v>1674</v>
       </c>
       <c r="J676" t="s">
-        <v>3367</v>
+        <v>3377</v>
       </c>
       <c r="K676">
         <v>2022</v>
@@ -40690,19 +41127,19 @@
         <v>43</v>
       </c>
       <c r="B677" t="s">
-        <v>3368</v>
+        <v>3378</v>
       </c>
       <c r="G677" t="s">
-        <v>3369</v>
+        <v>3379</v>
       </c>
       <c r="H677" t="s">
-        <v>3370</v>
+        <v>3380</v>
       </c>
       <c r="I677" t="s">
         <v>687</v>
       </c>
       <c r="J677" t="s">
-        <v>3371</v>
+        <v>3381</v>
       </c>
       <c r="K677">
         <v>2026</v>
@@ -40714,19 +41151,19 @@
         <v>43</v>
       </c>
       <c r="B678" t="s">
-        <v>3372</v>
+        <v>3382</v>
       </c>
       <c r="G678" t="s">
-        <v>3373</v>
+        <v>3383</v>
       </c>
       <c r="H678" t="s">
-        <v>3374</v>
+        <v>3384</v>
       </c>
       <c r="I678" t="s">
         <v>409</v>
       </c>
       <c r="J678" t="s">
-        <v>3375</v>
+        <v>3385</v>
       </c>
       <c r="K678">
         <v>2022</v>
@@ -40738,19 +41175,19 @@
         <v>43</v>
       </c>
       <c r="B679" t="s">
-        <v>3376</v>
+        <v>3386</v>
       </c>
       <c r="G679" t="s">
-        <v>3377</v>
+        <v>3387</v>
       </c>
       <c r="H679" t="s">
-        <v>3378</v>
+        <v>3388</v>
       </c>
       <c r="I679" t="s">
         <v>51</v>
       </c>
       <c r="J679" t="s">
-        <v>3379</v>
+        <v>3389</v>
       </c>
       <c r="K679">
         <v>2019</v>
@@ -40762,19 +41199,19 @@
         <v>43</v>
       </c>
       <c r="B680" t="s">
-        <v>3380</v>
+        <v>3390</v>
       </c>
       <c r="G680" t="s">
-        <v>3381</v>
+        <v>3391</v>
       </c>
       <c r="H680" t="s">
-        <v>3382</v>
+        <v>3392</v>
       </c>
       <c r="I680" t="s">
-        <v>3383</v>
+        <v>3393</v>
       </c>
       <c r="J680" t="s">
-        <v>3384</v>
+        <v>3394</v>
       </c>
       <c r="K680">
         <v>2021</v>
@@ -40786,19 +41223,19 @@
         <v>43</v>
       </c>
       <c r="B681" t="s">
-        <v>3385</v>
+        <v>3395</v>
       </c>
       <c r="G681" t="s">
-        <v>3386</v>
+        <v>3396</v>
       </c>
       <c r="H681" t="s">
-        <v>3387</v>
+        <v>3397</v>
       </c>
       <c r="I681" t="s">
         <v>237</v>
       </c>
       <c r="J681" t="s">
-        <v>3388</v>
+        <v>3398</v>
       </c>
       <c r="K681">
         <v>2017</v>
@@ -40810,19 +41247,19 @@
         <v>43</v>
       </c>
       <c r="B682" t="s">
-        <v>3389</v>
+        <v>3399</v>
       </c>
       <c r="G682" t="s">
-        <v>3390</v>
+        <v>3400</v>
       </c>
       <c r="H682" t="s">
-        <v>3391</v>
+        <v>3401</v>
       </c>
       <c r="I682" t="s">
         <v>1080</v>
       </c>
       <c r="J682" t="s">
-        <v>3392</v>
+        <v>3402</v>
       </c>
       <c r="K682">
         <v>2025</v>
@@ -40834,19 +41271,19 @@
         <v>43</v>
       </c>
       <c r="B683" t="s">
-        <v>3393</v>
+        <v>3403</v>
       </c>
       <c r="G683" t="s">
-        <v>3394</v>
+        <v>3404</v>
       </c>
       <c r="H683" t="s">
-        <v>3395</v>
+        <v>3405</v>
       </c>
       <c r="I683" t="s">
         <v>237</v>
       </c>
       <c r="J683" t="s">
-        <v>3396</v>
+        <v>3406</v>
       </c>
       <c r="K683">
         <v>2025</v>
@@ -40858,19 +41295,19 @@
         <v>43</v>
       </c>
       <c r="B684" t="s">
-        <v>3397</v>
+        <v>3407</v>
       </c>
       <c r="G684" t="s">
-        <v>3398</v>
+        <v>3408</v>
       </c>
       <c r="H684" t="s">
-        <v>3399</v>
+        <v>3409</v>
       </c>
       <c r="I684" t="s">
         <v>819</v>
       </c>
       <c r="J684" t="s">
-        <v>3400</v>
+        <v>3410</v>
       </c>
       <c r="K684">
         <v>2019</v>
@@ -40882,19 +41319,19 @@
         <v>43</v>
       </c>
       <c r="B685" t="s">
-        <v>3401</v>
+        <v>3411</v>
       </c>
       <c r="G685" t="s">
-        <v>3402</v>
+        <v>3412</v>
       </c>
       <c r="H685" t="s">
-        <v>3403</v>
+        <v>3413</v>
       </c>
       <c r="I685" t="s">
         <v>415</v>
       </c>
       <c r="J685" t="s">
-        <v>3404</v>
+        <v>3414</v>
       </c>
       <c r="K685">
         <v>2024</v>
@@ -40906,19 +41343,19 @@
         <v>43</v>
       </c>
       <c r="B686" t="s">
-        <v>3405</v>
+        <v>3415</v>
       </c>
       <c r="G686" t="s">
-        <v>3406</v>
+        <v>3416</v>
       </c>
       <c r="H686" t="s">
-        <v>3407</v>
+        <v>3417</v>
       </c>
       <c r="I686" t="s">
-        <v>3408</v>
+        <v>3418</v>
       </c>
       <c r="J686" t="s">
-        <v>3409</v>
+        <v>3419</v>
       </c>
       <c r="K686">
         <v>2024</v>
@@ -40930,19 +41367,19 @@
         <v>43</v>
       </c>
       <c r="B687" t="s">
-        <v>3410</v>
+        <v>3420</v>
       </c>
       <c r="G687" t="s">
-        <v>3411</v>
+        <v>3421</v>
       </c>
       <c r="H687" t="s">
-        <v>3412</v>
+        <v>3422</v>
       </c>
       <c r="I687" t="s">
         <v>1929</v>
       </c>
       <c r="J687" t="s">
-        <v>3413</v>
+        <v>3423</v>
       </c>
       <c r="K687">
         <v>2024</v>
@@ -40954,19 +41391,19 @@
         <v>43</v>
       </c>
       <c r="B688" t="s">
-        <v>3414</v>
+        <v>3424</v>
       </c>
       <c r="G688" t="s">
-        <v>3415</v>
+        <v>3425</v>
       </c>
       <c r="H688" t="s">
-        <v>3416</v>
+        <v>3426</v>
       </c>
       <c r="I688" t="s">
-        <v>3417</v>
+        <v>3427</v>
       </c>
       <c r="J688" t="s">
-        <v>3418</v>
+        <v>3428</v>
       </c>
       <c r="K688">
         <v>2023</v>
@@ -40978,19 +41415,19 @@
         <v>43</v>
       </c>
       <c r="B689" t="s">
-        <v>3419</v>
+        <v>3429</v>
       </c>
       <c r="G689" t="s">
-        <v>3420</v>
+        <v>3430</v>
       </c>
       <c r="H689" t="s">
-        <v>3421</v>
+        <v>3431</v>
       </c>
       <c r="I689" t="s">
-        <v>3422</v>
+        <v>3432</v>
       </c>
       <c r="J689" t="s">
-        <v>3423</v>
+        <v>3433</v>
       </c>
       <c r="K689">
         <v>2024</v>
@@ -41002,19 +41439,19 @@
         <v>43</v>
       </c>
       <c r="B690" t="s">
-        <v>3424</v>
+        <v>3434</v>
       </c>
       <c r="G690" t="s">
-        <v>3425</v>
+        <v>3435</v>
       </c>
       <c r="H690" t="s">
-        <v>3426</v>
+        <v>3436</v>
       </c>
       <c r="I690" t="s">
         <v>403</v>
       </c>
       <c r="J690" t="s">
-        <v>3427</v>
+        <v>3437</v>
       </c>
       <c r="K690">
         <v>2014</v>
@@ -41026,19 +41463,19 @@
         <v>43</v>
       </c>
       <c r="B691" t="s">
-        <v>3428</v>
+        <v>3438</v>
       </c>
       <c r="G691" t="s">
-        <v>3429</v>
+        <v>3439</v>
       </c>
       <c r="H691" t="s">
-        <v>3430</v>
+        <v>3440</v>
       </c>
       <c r="I691" t="s">
         <v>2043</v>
       </c>
       <c r="J691" t="s">
-        <v>3431</v>
+        <v>3441</v>
       </c>
       <c r="K691">
         <v>2024</v>
@@ -41050,19 +41487,19 @@
         <v>43</v>
       </c>
       <c r="B692" t="s">
-        <v>3432</v>
+        <v>3442</v>
       </c>
       <c r="G692" t="s">
-        <v>3433</v>
+        <v>3443</v>
       </c>
       <c r="H692" t="s">
-        <v>3434</v>
+        <v>3444</v>
       </c>
       <c r="I692" t="s">
-        <v>3435</v>
+        <v>3445</v>
       </c>
       <c r="J692" t="s">
-        <v>3436</v>
+        <v>3446</v>
       </c>
       <c r="K692">
         <v>2023</v>
@@ -41074,19 +41511,19 @@
         <v>43</v>
       </c>
       <c r="B693" t="s">
-        <v>3437</v>
+        <v>3447</v>
       </c>
       <c r="G693" t="s">
-        <v>3438</v>
+        <v>3448</v>
       </c>
       <c r="H693" t="s">
-        <v>3439</v>
+        <v>3449</v>
       </c>
       <c r="I693" t="s">
         <v>237</v>
       </c>
       <c r="J693" t="s">
-        <v>3440</v>
+        <v>3450</v>
       </c>
       <c r="K693">
         <v>2026</v>
@@ -41098,19 +41535,19 @@
         <v>43</v>
       </c>
       <c r="B694" t="s">
-        <v>3441</v>
+        <v>3451</v>
       </c>
       <c r="G694" t="s">
-        <v>3442</v>
+        <v>3452</v>
       </c>
       <c r="H694" t="s">
-        <v>3443</v>
+        <v>3453</v>
       </c>
       <c r="I694" t="s">
         <v>973</v>
       </c>
       <c r="J694" t="s">
-        <v>3444</v>
+        <v>3454</v>
       </c>
       <c r="K694">
         <v>2025</v>
@@ -41122,19 +41559,19 @@
         <v>43</v>
       </c>
       <c r="B695" t="s">
-        <v>3445</v>
+        <v>3455</v>
       </c>
       <c r="G695" t="s">
-        <v>3446</v>
+        <v>3456</v>
       </c>
       <c r="H695" t="s">
-        <v>3447</v>
+        <v>3457</v>
       </c>
       <c r="I695" t="s">
         <v>1929</v>
       </c>
       <c r="J695" t="s">
-        <v>3448</v>
+        <v>3458</v>
       </c>
       <c r="K695">
         <v>2020</v>
@@ -41146,19 +41583,19 @@
         <v>43</v>
       </c>
       <c r="B696" t="s">
-        <v>3449</v>
+        <v>3459</v>
       </c>
       <c r="G696" t="s">
-        <v>3450</v>
+        <v>3460</v>
       </c>
       <c r="H696" t="s">
-        <v>3451</v>
+        <v>3461</v>
       </c>
       <c r="I696" t="s">
         <v>973</v>
       </c>
       <c r="J696" t="s">
-        <v>3452</v>
+        <v>3462</v>
       </c>
       <c r="K696">
         <v>2024</v>
@@ -41170,19 +41607,19 @@
         <v>43</v>
       </c>
       <c r="B697" t="s">
-        <v>3453</v>
+        <v>3463</v>
       </c>
       <c r="G697" t="s">
-        <v>3454</v>
+        <v>3464</v>
       </c>
       <c r="H697" t="s">
-        <v>3455</v>
+        <v>3465</v>
       </c>
       <c r="I697" t="s">
         <v>1461</v>
       </c>
       <c r="J697" t="s">
-        <v>3456</v>
+        <v>3466</v>
       </c>
       <c r="K697">
         <v>2023</v>
@@ -41194,19 +41631,19 @@
         <v>43</v>
       </c>
       <c r="B698" t="s">
-        <v>3457</v>
+        <v>3467</v>
       </c>
       <c r="G698" t="s">
-        <v>3458</v>
+        <v>3468</v>
       </c>
       <c r="H698" t="s">
-        <v>3459</v>
+        <v>3469</v>
       </c>
       <c r="I698" t="s">
         <v>723</v>
       </c>
       <c r="J698" t="s">
-        <v>3460</v>
+        <v>3470</v>
       </c>
       <c r="K698">
         <v>2022</v>
@@ -41218,19 +41655,19 @@
         <v>43</v>
       </c>
       <c r="B699" t="s">
-        <v>3461</v>
+        <v>3471</v>
       </c>
       <c r="G699" t="s">
-        <v>3462</v>
+        <v>3472</v>
       </c>
       <c r="H699" t="s">
-        <v>3463</v>
+        <v>3473</v>
       </c>
       <c r="I699" t="s">
-        <v>3341</v>
+        <v>3351</v>
       </c>
       <c r="J699" t="s">
-        <v>3464</v>
+        <v>3474</v>
       </c>
       <c r="K699">
         <v>2017</v>
@@ -41242,19 +41679,19 @@
         <v>43</v>
       </c>
       <c r="B700" t="s">
-        <v>3465</v>
+        <v>3475</v>
       </c>
       <c r="G700" t="s">
-        <v>3466</v>
+        <v>3476</v>
       </c>
       <c r="H700" t="s">
-        <v>3467</v>
+        <v>3477</v>
       </c>
       <c r="I700" t="s">
         <v>915</v>
       </c>
       <c r="J700" t="s">
-        <v>3468</v>
+        <v>3478</v>
       </c>
       <c r="K700">
         <v>2024</v>
@@ -41266,19 +41703,19 @@
         <v>43</v>
       </c>
       <c r="B701" t="s">
-        <v>3469</v>
+        <v>3479</v>
       </c>
       <c r="G701" t="s">
-        <v>3470</v>
+        <v>3480</v>
       </c>
       <c r="H701" t="s">
-        <v>3471</v>
+        <v>3481</v>
       </c>
       <c r="I701" t="s">
-        <v>3472</v>
+        <v>3482</v>
       </c>
       <c r="J701" t="s">
-        <v>3473</v>
+        <v>3483</v>
       </c>
       <c r="K701">
         <v>2026</v>
@@ -41290,19 +41727,19 @@
         <v>43</v>
       </c>
       <c r="B702" t="s">
-        <v>3474</v>
+        <v>3484</v>
       </c>
       <c r="G702" t="s">
-        <v>3475</v>
+        <v>3485</v>
       </c>
       <c r="H702" t="s">
-        <v>3476</v>
+        <v>3486</v>
       </c>
       <c r="I702" t="s">
         <v>915</v>
       </c>
       <c r="J702" t="s">
-        <v>3477</v>
+        <v>3487</v>
       </c>
       <c r="K702">
         <v>2007</v>
@@ -41314,19 +41751,19 @@
         <v>43</v>
       </c>
       <c r="B703" t="s">
-        <v>3478</v>
+        <v>3488</v>
       </c>
       <c r="G703" t="s">
-        <v>3479</v>
+        <v>3489</v>
       </c>
       <c r="H703" t="s">
-        <v>3480</v>
+        <v>3490</v>
       </c>
       <c r="I703" t="s">
-        <v>3481</v>
+        <v>3491</v>
       </c>
       <c r="J703" t="s">
-        <v>3482</v>
+        <v>3492</v>
       </c>
       <c r="K703">
         <v>2013</v>
@@ -41338,19 +41775,19 @@
         <v>43</v>
       </c>
       <c r="B704" t="s">
-        <v>3483</v>
+        <v>3493</v>
       </c>
       <c r="G704" t="s">
-        <v>3484</v>
+        <v>3494</v>
       </c>
       <c r="H704" t="s">
-        <v>3485</v>
+        <v>3495</v>
       </c>
       <c r="I704" t="s">
         <v>51</v>
       </c>
       <c r="J704" t="s">
-        <v>3486</v>
+        <v>3496</v>
       </c>
       <c r="K704">
         <v>2001</v>

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="g:\My Drive\UCL\BSMA\BSMA ANTIGRAVITY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8040BD1-31DD-4027-90F8-808C72222622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77359DDC-7487-4481-A875-2655503788DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5717" uniqueCount="3661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5791" uniqueCount="3655">
   <si>
     <t>Coder Initials</t>
   </si>
@@ -7700,6 +7700,9 @@
     <t>BSMA0470</t>
   </si>
   <si>
+    <t>ERROR</t>
+  </si>
+  <si>
     <t>This study investigated the communication behaviors and performances of 50 R&amp;D project groups that varied in terms of group longevity, as measured by the average length of time project members had worked together. Analyses revealed that project groups became increasingly isolated from key information sources both within and outside their organizations with increasing stability in project membership. Such reductions in project communication were also shown to affect adversely the technical performance of project groups. Furthermore, variations in communication activities were more associated with the tenure composition of project groups than with the project tenures of individual engineers. These findings are presented and discussed in the more general terms of what happens in project groups with increasing group longevity.</t>
   </si>
   <si>
@@ -7709,7 +7712,7 @@
     <t>R Katz</t>
   </si>
   <si>
-    <t>Non-individual level (team analysis). Verbatim Evidence: "[Abstract] This study investigated the communication behaviors and performances of 50 R&amp;D project groupsthat variedin terms of group longevity, as measured by the average length of time project members had worked together."</t>
+    <t>. Verbatim Evidence: ""</t>
   </si>
   <si>
     <t>BSMA0471</t>
@@ -7763,9 +7766,6 @@
     <t>BSMA0474</t>
   </si>
   <si>
-    <t>ERROR</t>
-  </si>
-  <si>
     <t>Boundary-spanning activities were studied in 15 organizations engaged in basic and applied research. Included in the study were 281 scientists and engineers. Contrary to prior theory and research, this study found bound-ary-spanning activities to be unrelated to job satisfaction. It was strongly related to perceptions of research and development team collaboration, job motivation, task uncertainty, locus of control, team cohesiveness, and individualproductivity. The research reported here makes a strong case for including group processes and characteristics in future studies involving boundary-spanning activities. The results also give increased impetus to re-search which examines the relationships between boundary-spanning activi-ties and individual productivity.</t>
   </si>
   <si>
@@ -7773,9 +7773,6 @@
   </si>
   <si>
     <t>RC Dailey</t>
-  </si>
-  <si>
-    <t>. Verbatim Evidence: ""</t>
   </si>
   <si>
     <t>BSMA0475</t>
@@ -8193,9 +8190,6 @@
     <t>Ryan, Annmarie; O’Malley, Lisa</t>
   </si>
   <si>
-    <t>Qualitative study without effect sizes. Verbatim Evidence: "[Abstract] This is achieved using data from a longitudinal analysis of a cross-sector partnership between a business and an arts organisation in Ireland. This offers a unique opportunity to trace the emergence of the partnership over time, and, specifically, to consider the impact of innovations co-created by the actors involved."</t>
-  </si>
-  <si>
     <t>BSMA0505</t>
   </si>
   <si>
@@ -8253,9 +8247,6 @@
     <t>Saeed, Munazza; Bani-Melhem, Ahmad Jamal; Hassan, Hamid; Alvi, Tariq Hameed; Altaf, Saira</t>
   </si>
   <si>
-    <t>Study examines individual-level frontline employee customer-oriented boundary-spanning behaviors and provides a correlation matrix.. Verbatim Evidence: "[Abstract] "Design/methodology/approach –Two-source (manager-frontline employee dyad)datawerecollectedthrough asurveyquestionnaire fromhospitality organizations atthreedifferentpointsintime." [Sample and procedure] "Thedataweregathered atthreepointsintimefromtwosources(manager-f rontline employees dyads)usingasurveyquestionnaire inthree-to-five-star hotelsinPakistan." "Afteraligning thedatathroughdistinctive codesand thorough assessment, only245responses werekeptandusedforfurtheranalysis." [Measures] "Customer-oriented boundary-spanning behaviors were evaluated usingathirteen-item scaledeveloped byBettencourt etal.(2005).Asampleitem was“Thisemployee followscustomer serviceguidelines withextremecare.”" [Results] "Table2.Descriptive statisticsandcorrelations""</t>
-  </si>
-  <si>
     <t>BSMA0509</t>
   </si>
   <si>
@@ -8290,9 +8281,6 @@
   </si>
   <si>
     <t>Satheesh, Shreya Anna; Van Meerkerk, Ingmar; Verweij, Stefan; Busscher, Tim; Arts, Jos</t>
-  </si>
-  <si>
-    <t>Non-independent observations (repeated measures): Respondents were asked to fill out the survey for up to two projects, and the unit of analysis is the survey response (N=158), meaning some individuals appear multiple times in the dataset.. Verbatim Evidence: "[Sample and data collection] "This created a project pool of 68 projects and 406 potential respondents with 308 unique respondents. Respondents were asked to fill in the survey for a specific project. If they were involved in more than one project, they were asked to fill out the survey for a maximum of two projects (the most recent ones in which they were involved). After eliminating 14 invalid email addresses, the sample size was 392. The survey was conducted between October 2020 and January 2021. A total of 171 public managers from Rijkswaterstaat responded (the response rate after two follow-ups was 43.6%), out of which13 responses were deleted due to a completion rate of less than 35%. This resulted in a dataset with 158 responses""</t>
   </si>
   <si>
     <t>BSMA0512</t>
@@ -20327,7 +20315,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Non-individual level. The unit of analysis is the work group, and boundary spanning (scout activities) is measured at the group level.. Verbatim Evidence: "[Sample and Level of Analysis] "Thirty-three o f the 47 groups met the requirements and were used for hypothesis testing." "To aggregate individual data to the group level, I averaged the responses from the individual </t>
+      <t xml:space="preserve">Conceptual paper without primary data. Verbatim Evidence: "[Abstract] "This conceptual paper contends the cause of the success or failure of a project rests with the individuals who, in theory, comprise the project </t>
     </r>
     <r>
       <rPr>
@@ -20348,59 +20336,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> members for each variable o f interest" [Boundary Spanning Construct] "Ancona and Caldwell (1988) identified two group activities that are associated with initiating transactions. The first, scout activities , was defined as \"activities that involve bringing information and/or resources needed by the group in across the boundary\" (p. 473)." "Hypothesis 9. The relationship between group scout activities and group support for innovation will be curvilinear.""</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Conceptual paper without primary data. Verbatim Evidence: "[Abstract] "This conceptual paper contends the cause of the success or failure of a project rests with the individuals who, in theory, comprise the project </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>team</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>.""</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Study measures advice-seeking network degree centrality (purposive knowledge acquisition ties) among SME managers and provides an individual-level zero-order correlation matrix.. Verbatim Evidence: "[Sample] "In small biotech SMEs (the majority of organizations in the cluster), only the founder/CEO completed the survey. In larger organizations, other members of the top management </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>team</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> participated as well." [Sample] "The final sample includes information on 48 managers from 36 organizations" [Measures] "Our dependent variable is the occurrence of knowledge acquisition ties in an interpersonal knowledge network among managers. We collected network data using a roster containing the names of all managers and asked the participants to indicate all persons from whom they regularly acquired knowledge and information concerning work-related matters." [Table 3] "Table 3 Correlations ... N=48 managers.""</t>
     </r>
   </si>
 </sst>
@@ -21163,7 +21099,7 @@
         <v>2002</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>3497</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21259,7 +21195,7 @@
         <v>2016</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>3498</v>
+        <v>3494</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21419,7 +21355,7 @@
         <v>2008</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>3499</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21451,7 +21387,7 @@
         <v>2012</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>3500</v>
+        <v>3496</v>
       </c>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21739,7 +21675,7 @@
         <v>1992</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>3501</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21867,7 +21803,7 @@
         <v>2024</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>3502</v>
+        <v>3498</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21899,7 +21835,7 @@
         <v>2017</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>3503</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22059,7 +21995,7 @@
         <v>2022</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>3504</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22184,7 +22120,7 @@
         <v>2020</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>3505</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22280,7 +22216,7 @@
         <v>1997</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>3506</v>
+        <v>3502</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22344,7 +22280,7 @@
         <v>2021</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>3507</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22748,7 +22684,7 @@
         <v>2018</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>3508</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22777,7 +22713,7 @@
         <v>2015</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>3509</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22963,7 +22899,7 @@
         <v>2011</v>
       </c>
       <c r="P61" s="8" t="s">
-        <v>3510</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23216,7 +23152,7 @@
         <v>2012</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>3511</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23469,7 +23405,7 @@
         <v>2025</v>
       </c>
       <c r="P77" s="8" t="s">
-        <v>3512</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23501,7 +23437,7 @@
         <v>2023</v>
       </c>
       <c r="P78" s="8" t="s">
-        <v>3513</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23533,7 +23469,7 @@
         <v>2019</v>
       </c>
       <c r="P79" s="8" t="s">
-        <v>3514</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23661,7 +23597,7 @@
         <v>2005</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>3515</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23693,7 +23629,7 @@
         <v>2020</v>
       </c>
       <c r="P84" s="8" t="s">
-        <v>3516</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23722,7 +23658,7 @@
         <v>2021</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>3517</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23914,7 +23850,7 @@
         <v>2010</v>
       </c>
       <c r="P91" s="8" t="s">
-        <v>3518</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24010,7 +23946,7 @@
         <v>2024</v>
       </c>
       <c r="P94" s="8" t="s">
-        <v>3519</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24042,7 +23978,7 @@
         <v>2020</v>
       </c>
       <c r="P95" s="8" t="s">
-        <v>3520</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24103,7 +24039,7 @@
         <v>2021</v>
       </c>
       <c r="P97" s="8" t="s">
-        <v>3521</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24132,7 +24068,7 @@
         <v>2012</v>
       </c>
       <c r="P98" s="8" t="s">
-        <v>3522</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24196,7 +24132,7 @@
         <v>1995</v>
       </c>
       <c r="P100" s="8" t="s">
-        <v>3523</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24228,7 +24164,7 @@
         <v>2008</v>
       </c>
       <c r="P101" s="8" t="s">
-        <v>3524</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24321,7 +24257,7 @@
         <v>2010</v>
       </c>
       <c r="P104" s="8" t="s">
-        <v>3525</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24545,7 +24481,7 @@
         <v>2018</v>
       </c>
       <c r="P111" s="8" t="s">
-        <v>3526</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24641,7 +24577,7 @@
         <v>2018</v>
       </c>
       <c r="P114" s="8" t="s">
-        <v>3527</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24769,7 +24705,7 @@
         <v>2016</v>
       </c>
       <c r="P118" s="8" t="s">
-        <v>3528</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24798,7 +24734,7 @@
         <v>1978</v>
       </c>
       <c r="P119" s="8" t="s">
-        <v>3529</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24862,7 +24798,7 @@
         <v>2012</v>
       </c>
       <c r="P121" s="8" t="s">
-        <v>3530</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24926,7 +24862,7 @@
         <v>2004</v>
       </c>
       <c r="P123" s="8" t="s">
-        <v>3531</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25173,7 +25109,7 @@
         <v>1996</v>
       </c>
       <c r="P131" s="8" t="s">
-        <v>3532</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25205,7 +25141,7 @@
         <v>2004</v>
       </c>
       <c r="P132" s="8" t="s">
-        <v>3533</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25269,7 +25205,7 @@
         <v>1990</v>
       </c>
       <c r="P134" s="8" t="s">
-        <v>3534</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="135" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25397,7 +25333,7 @@
         <v>1984</v>
       </c>
       <c r="P138" s="8" t="s">
-        <v>3535</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25621,7 +25557,7 @@
         <v>2011</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>3536</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25653,7 +25589,7 @@
         <v>2003</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>3537</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25813,7 +25749,7 @@
         <v>2014</v>
       </c>
       <c r="P151" s="8" t="s">
-        <v>3538</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25941,7 +25877,7 @@
         <v>2019</v>
       </c>
       <c r="P155" s="8" t="s">
-        <v>3539</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="156" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26005,7 +25941,7 @@
         <v>2009</v>
       </c>
       <c r="P157" s="8" t="s">
-        <v>3540</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26069,7 +26005,7 @@
         <v>2019</v>
       </c>
       <c r="P159" s="8" t="s">
-        <v>3541</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26418,7 +26354,7 @@
         <v>1998</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>3542</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26639,7 +26575,7 @@
         <v>2022</v>
       </c>
       <c r="P177" s="8" t="s">
-        <v>3543</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="178" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26703,7 +26639,7 @@
         <v>1997</v>
       </c>
       <c r="P179" s="8" t="s">
-        <v>3544</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="180" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26735,7 +26671,7 @@
         <v>2022</v>
       </c>
       <c r="P180" s="8" t="s">
-        <v>3545</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26927,7 +26863,7 @@
         <v>2023</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>3546</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26959,7 +26895,7 @@
         <v>2013</v>
       </c>
       <c r="P187" s="8" t="s">
-        <v>3547</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="188" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27148,7 +27084,7 @@
         <v>2010</v>
       </c>
       <c r="P193" s="8" t="s">
-        <v>3548</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="194" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27244,7 +27180,7 @@
         <v>2012</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>3549</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="197" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27273,7 +27209,7 @@
         <v>2015</v>
       </c>
       <c r="P197" s="8" t="s">
-        <v>3550</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="198" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27337,7 +27273,7 @@
         <v>2015</v>
       </c>
       <c r="P199" s="8" t="s">
-        <v>3551</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="200" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27497,7 +27433,7 @@
         <v>2005</v>
       </c>
       <c r="P204" s="8" t="s">
-        <v>3552</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27590,7 +27526,7 @@
         <v>1998</v>
       </c>
       <c r="P207" s="8" t="s">
-        <v>3553</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27622,7 +27558,7 @@
         <v>1999</v>
       </c>
       <c r="P208" s="8" t="s">
-        <v>3554</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="209" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27712,7 +27648,7 @@
         <v>2024</v>
       </c>
       <c r="P211" s="8" t="s">
-        <v>3555</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="212" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27744,7 +27680,7 @@
         <v>2006</v>
       </c>
       <c r="P212" s="8" t="s">
-        <v>3556</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="213" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27776,7 +27712,7 @@
         <v>2010</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>3557</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="214" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27837,7 +27773,7 @@
         <v>2017</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>3558</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="216" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27965,7 +27901,7 @@
         <v>2014</v>
       </c>
       <c r="P219" s="8" t="s">
-        <v>3559</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27997,7 +27933,7 @@
         <v>2011</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>3560</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="221" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28093,7 +28029,7 @@
         <v>2015</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>3561</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="224" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28157,7 +28093,7 @@
         <v>2023</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>3562</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28186,7 +28122,7 @@
         <v>2004</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>3563</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="227" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28282,7 +28218,7 @@
         <v>2005</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>3564</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="230" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28314,7 +28250,7 @@
         <v>2004</v>
       </c>
       <c r="P230" s="8" t="s">
-        <v>3565</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="231" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28410,7 +28346,7 @@
         <v>1998</v>
       </c>
       <c r="P233" s="8" t="s">
-        <v>3566</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="234" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28506,7 +28442,7 @@
         <v>2014</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>3567</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="237" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28727,7 +28663,7 @@
         <v>2011</v>
       </c>
       <c r="P243" s="8" t="s">
-        <v>3568</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28759,7 +28695,7 @@
         <v>2018</v>
       </c>
       <c r="P244" s="8" t="s">
-        <v>3569</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="245" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28791,7 +28727,7 @@
         <v>2019</v>
       </c>
       <c r="P245" s="8" t="s">
-        <v>3570</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="246" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28823,7 +28759,7 @@
         <v>1998</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>3571</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="247" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28977,7 +28913,7 @@
         <v>2012</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>3572</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="252" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29166,7 +29102,7 @@
         <v>1999</v>
       </c>
       <c r="P257" s="8" t="s">
-        <v>3573</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="258" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29230,7 +29166,7 @@
         <v>2022</v>
       </c>
       <c r="P259" s="8" t="s">
-        <v>3574</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29387,7 +29323,7 @@
         <v>2023</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>3575</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29448,7 +29384,7 @@
         <v>2023</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>3576</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="267" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29480,7 +29416,7 @@
         <v>2018</v>
       </c>
       <c r="P267" s="8" t="s">
-        <v>3577</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="268" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29512,7 +29448,7 @@
         <v>2025</v>
       </c>
       <c r="P268" s="8" t="s">
-        <v>3578</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="269" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29541,7 +29477,7 @@
         <v>2010</v>
       </c>
       <c r="P269" s="8" t="s">
-        <v>3579</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="270" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29631,7 +29567,7 @@
         <v>2002</v>
       </c>
       <c r="P272" s="8" t="s">
-        <v>3580</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29724,7 +29660,7 @@
         <v>2020</v>
       </c>
       <c r="P275" s="8" t="s">
-        <v>3581</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29852,7 +29788,7 @@
         <v>1996</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>3582</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29881,7 +29817,7 @@
         <v>2020</v>
       </c>
       <c r="P280" s="8" t="s">
-        <v>3583</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="281" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29913,7 +29849,7 @@
         <v>2003</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>3584</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30009,7 +29945,7 @@
         <v>2022</v>
       </c>
       <c r="P284" s="8" t="s">
-        <v>3585</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30041,7 +29977,7 @@
         <v>2000</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>3586</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30448,7 +30384,7 @@
         <v>2024</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>3587</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30602,7 +30538,7 @@
         <v>2011</v>
       </c>
       <c r="P303" s="8" t="s">
-        <v>3588</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30663,7 +30599,7 @@
         <v>2022</v>
       </c>
       <c r="P305" s="8" t="s">
-        <v>3589</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30721,7 +30657,7 @@
         <v>2022</v>
       </c>
       <c r="P307" s="8" t="s">
-        <v>3590</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30750,7 +30686,7 @@
         <v>2025</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>3591</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30779,7 +30715,7 @@
         <v>2002</v>
       </c>
       <c r="P309" s="8" t="s">
-        <v>3592</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31128,7 +31064,7 @@
         <v>2008</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>3593</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="321" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31256,7 +31192,7 @@
         <v>2020</v>
       </c>
       <c r="P324" s="8" t="s">
-        <v>3594</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31320,7 +31256,7 @@
         <v>2004</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>3595</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31384,7 +31320,7 @@
         <v>2015</v>
       </c>
       <c r="P328" s="8" t="s">
-        <v>3596</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31573,7 +31509,7 @@
         <v>1991</v>
       </c>
       <c r="P334" s="8" t="s">
-        <v>3597</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31605,7 +31541,7 @@
         <v>2023</v>
       </c>
       <c r="P335" s="8" t="s">
-        <v>3598</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31637,7 +31573,7 @@
         <v>2017</v>
       </c>
       <c r="P336" s="8" t="s">
-        <v>3599</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31759,7 +31695,7 @@
         <v>2011</v>
       </c>
       <c r="P340" s="8" t="s">
-        <v>3600</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="341" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31788,7 +31724,7 @@
         <v>2016</v>
       </c>
       <c r="P341" s="8" t="s">
-        <v>3601</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="342" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31820,7 +31756,7 @@
         <v>2020</v>
       </c>
       <c r="P342" s="8" t="s">
-        <v>3602</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31884,7 +31820,7 @@
         <v>2017</v>
       </c>
       <c r="P344" s="8" t="s">
-        <v>3603</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="345" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31916,7 +31852,7 @@
         <v>2024</v>
       </c>
       <c r="P345" s="8" t="s">
-        <v>3604</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="346" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31948,7 +31884,7 @@
         <v>2016</v>
       </c>
       <c r="P346" s="8" t="s">
-        <v>3605</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="347" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31980,7 +31916,7 @@
         <v>2022</v>
       </c>
       <c r="P347" s="8" t="s">
-        <v>3606</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="348" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32108,7 +32044,7 @@
         <v>2002</v>
       </c>
       <c r="P351" s="8" t="s">
-        <v>3607</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="352" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32137,7 +32073,7 @@
         <v>2022</v>
       </c>
       <c r="P352" s="8" t="s">
-        <v>3608</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="353" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32201,7 +32137,7 @@
         <v>2020</v>
       </c>
       <c r="P354" s="8" t="s">
-        <v>3609</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="355" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32233,7 +32169,7 @@
         <v>2024</v>
       </c>
       <c r="P355" s="8" t="s">
-        <v>3610</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="356" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32265,7 +32201,7 @@
         <v>2000</v>
       </c>
       <c r="P356" s="8" t="s">
-        <v>3611</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="357" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32361,7 +32297,7 @@
         <v>2023</v>
       </c>
       <c r="P359" s="8" t="s">
-        <v>3612</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="360" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32390,7 +32326,7 @@
         <v>2018</v>
       </c>
       <c r="P360" s="8" t="s">
-        <v>3613</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="361" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32419,7 +32355,7 @@
         <v>2014</v>
       </c>
       <c r="P361" s="8" t="s">
-        <v>3614</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="362" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32451,7 +32387,7 @@
         <v>2013</v>
       </c>
       <c r="P362" s="8" t="s">
-        <v>3615</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="363" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32483,7 +32419,7 @@
         <v>2025</v>
       </c>
       <c r="P363" s="8" t="s">
-        <v>3616</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="364" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32675,7 +32611,7 @@
         <v>2023</v>
       </c>
       <c r="P369" s="8" t="s">
-        <v>3617</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="370" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32771,7 +32707,7 @@
         <v>2023</v>
       </c>
       <c r="P372" s="8" t="s">
-        <v>3618</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="373" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32867,7 +32803,7 @@
         <v>1999</v>
       </c>
       <c r="P375" s="8" t="s">
-        <v>3619</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="376" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32931,7 +32867,7 @@
         <v>2023</v>
       </c>
       <c r="P377" s="8" t="s">
-        <v>3620</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="378" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33091,7 +33027,7 @@
         <v>2005</v>
       </c>
       <c r="P382" s="8" t="s">
-        <v>3621</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="383" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33123,7 +33059,7 @@
         <v>2007</v>
       </c>
       <c r="P383" s="8" t="s">
-        <v>3622</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="384" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33155,7 +33091,7 @@
         <v>2008</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>3623</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="385" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33277,7 +33213,7 @@
         <v>2019</v>
       </c>
       <c r="P388" s="8" t="s">
-        <v>3624</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="389" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33309,7 +33245,7 @@
         <v>1994</v>
       </c>
       <c r="P389" s="8" t="s">
-        <v>3625</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="390" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33373,7 +33309,7 @@
         <v>2016</v>
       </c>
       <c r="P391" s="8" t="s">
-        <v>3626</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="392" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33405,7 +33341,7 @@
         <v>2015</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>3627</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="393" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33530,7 +33466,7 @@
         <v>2003</v>
       </c>
       <c r="P396" s="8" t="s">
-        <v>3628</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="397" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33626,7 +33562,7 @@
         <v>2005</v>
       </c>
       <c r="P399" s="8" t="s">
-        <v>3629</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="400" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33658,7 +33594,7 @@
         <v>2010</v>
       </c>
       <c r="P400" s="8" t="s">
-        <v>3630</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="401" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33687,7 +33623,7 @@
         <v>2022</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>3631</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="402" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33719,7 +33655,7 @@
         <v>2007</v>
       </c>
       <c r="P402" s="8" t="s">
-        <v>3632</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="403" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33815,7 +33751,7 @@
         <v>2006</v>
       </c>
       <c r="P405" s="8" t="s">
-        <v>3633</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="406" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33847,7 +33783,7 @@
         <v>2007</v>
       </c>
       <c r="P406" s="8" t="s">
-        <v>3634</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="407" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33879,7 +33815,7 @@
         <v>2025</v>
       </c>
       <c r="P407" s="8" t="s">
-        <v>3635</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="408" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34103,7 +34039,7 @@
         <v>2008</v>
       </c>
       <c r="P414" s="8" t="s">
-        <v>3636</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="415" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34289,7 +34225,7 @@
         <v>2011</v>
       </c>
       <c r="P420" s="8" t="s">
-        <v>3637</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="421" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34318,7 +34254,7 @@
         <v>2008</v>
       </c>
       <c r="P421" s="8" t="s">
-        <v>3638</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="422" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34667,7 +34603,7 @@
         <v>2019</v>
       </c>
       <c r="P432" s="8" t="s">
-        <v>3639</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="433" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34763,7 +34699,7 @@
         <v>2014</v>
       </c>
       <c r="P435" s="8" t="s">
-        <v>3640</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="436" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34795,7 +34731,7 @@
         <v>2005</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>3641</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="437" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34859,7 +34795,7 @@
         <v>2019</v>
       </c>
       <c r="P438" s="8" t="s">
-        <v>3642</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="439" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35019,7 +34955,7 @@
         <v>2019</v>
       </c>
       <c r="P443" s="8" t="s">
-        <v>3643</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="444" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35083,7 +35019,7 @@
         <v>2013</v>
       </c>
       <c r="P445" s="8" t="s">
-        <v>3644</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="446" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35147,7 +35083,7 @@
         <v>2013</v>
       </c>
       <c r="P447" s="8" t="s">
-        <v>3645</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="448" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35365,7 +35301,7 @@
         <v>2003</v>
       </c>
       <c r="P454" s="8" t="s">
-        <v>3646</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="455" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35490,7 +35426,7 @@
         <v>2024</v>
       </c>
       <c r="P458" s="8" t="s">
-        <v>3647</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="459" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35554,7 +35490,7 @@
         <v>2024</v>
       </c>
       <c r="P460" s="8" t="s">
-        <v>3648</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="461" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35586,7 +35522,7 @@
         <v>2023</v>
       </c>
       <c r="P461" s="8" t="s">
-        <v>3649</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="462" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35746,7 +35682,7 @@
         <v>2017</v>
       </c>
       <c r="P466" s="8" t="s">
-        <v>3650</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="467" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35810,7 +35746,7 @@
         <v>2012</v>
       </c>
       <c r="P468" s="8" t="s">
-        <v>3651</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="469" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35839,7 +35775,7 @@
         <v>2021</v>
       </c>
       <c r="P469" s="8" t="s">
-        <v>3652</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="470" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35871,7 +35807,7 @@
         <v>2022</v>
       </c>
       <c r="P470" s="8" t="s">
-        <v>3653</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="471" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35903,7 +35839,7 @@
         <v>2018</v>
       </c>
       <c r="P471" s="8" t="s">
-        <v>3654</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="472" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35935,7 +35871,7 @@
         <v>2021</v>
       </c>
       <c r="P472" s="8" t="s">
-        <v>3655</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="473" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35946,28 +35882,25 @@
         <v>2481</v>
       </c>
       <c r="E473" t="s">
-        <v>85</v>
-      </c>
-      <c r="F473" t="s">
-        <v>61</v>
+        <v>2482</v>
       </c>
       <c r="G473" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="H473" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="I473" t="s">
         <v>2252</v>
       </c>
       <c r="J473" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="K473">
         <v>1982</v>
       </c>
       <c r="P473" s="8" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="474" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35975,7 +35908,7 @@
         <v>43</v>
       </c>
       <c r="B474" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="E474" t="s">
         <v>85</v>
@@ -35984,22 +35917,22 @@
         <v>48</v>
       </c>
       <c r="G474" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="H474" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="I474" t="s">
         <v>2054</v>
       </c>
       <c r="J474" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="K474">
         <v>2014</v>
       </c>
       <c r="P474" s="8" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="475" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36007,7 +35940,7 @@
         <v>43</v>
       </c>
       <c r="B475" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="E475" t="s">
         <v>85</v>
@@ -36016,22 +35949,22 @@
         <v>48</v>
       </c>
       <c r="G475" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="H475" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="I475" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="J475" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="K475">
         <v>2005</v>
       </c>
       <c r="P475" s="8" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="476" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36039,7 +35972,7 @@
         <v>43</v>
       </c>
       <c r="B476" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="E476" t="s">
         <v>85</v>
@@ -36048,22 +35981,22 @@
         <v>48</v>
       </c>
       <c r="G476" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="H476" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="I476" t="s">
         <v>1652</v>
       </c>
       <c r="J476" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="K476">
         <v>2011</v>
       </c>
       <c r="P476" s="8" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="477" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36071,10 +36004,10 @@
         <v>43</v>
       </c>
       <c r="B477" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="E477" t="s">
-        <v>2503</v>
+        <v>2482</v>
       </c>
       <c r="G477" t="s">
         <v>2504</v>
@@ -36092,7 +36025,7 @@
         <v>1979</v>
       </c>
       <c r="P477" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="478" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36100,28 +36033,28 @@
         <v>43</v>
       </c>
       <c r="B478" t="s">
+        <v>2507</v>
+      </c>
+      <c r="E478" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G478" t="s">
         <v>2508</v>
       </c>
-      <c r="E478" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G478" t="s">
+      <c r="H478" t="s">
         <v>2509</v>
-      </c>
-      <c r="H478" t="s">
-        <v>2510</v>
       </c>
       <c r="I478" t="s">
         <v>1314</v>
       </c>
       <c r="J478" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="K478">
         <v>1985</v>
       </c>
       <c r="P478" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="479" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36129,28 +36062,28 @@
         <v>43</v>
       </c>
       <c r="B479" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="E479" t="s">
         <v>48</v>
       </c>
       <c r="G479" t="s">
+        <v>2512</v>
+      </c>
+      <c r="H479" t="s">
         <v>2513</v>
-      </c>
-      <c r="H479" t="s">
-        <v>2514</v>
       </c>
       <c r="I479" t="s">
         <v>1862</v>
       </c>
       <c r="J479" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="K479">
         <v>2011</v>
       </c>
       <c r="P479" s="8" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="480" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36158,28 +36091,28 @@
         <v>43</v>
       </c>
       <c r="B480" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="E480" t="s">
         <v>48</v>
       </c>
       <c r="G480" t="s">
+        <v>2517</v>
+      </c>
+      <c r="H480" t="s">
         <v>2518</v>
-      </c>
-      <c r="H480" t="s">
-        <v>2519</v>
       </c>
       <c r="I480" t="s">
         <v>81</v>
       </c>
       <c r="J480" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="K480">
         <v>1976</v>
       </c>
       <c r="P480" s="8" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="481" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36187,7 +36120,7 @@
         <v>43</v>
       </c>
       <c r="B481" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="E481" t="s">
         <v>85</v>
@@ -36196,22 +36129,22 @@
         <v>48</v>
       </c>
       <c r="G481" t="s">
+        <v>2522</v>
+      </c>
+      <c r="H481" t="s">
         <v>2523</v>
-      </c>
-      <c r="H481" t="s">
-        <v>2524</v>
       </c>
       <c r="I481" t="s">
         <v>723</v>
       </c>
       <c r="J481" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="K481">
         <v>2006</v>
       </c>
       <c r="P481" s="8" t="s">
-        <v>2526</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="482" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36219,7 +36152,7 @@
         <v>43</v>
       </c>
       <c r="B482" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="E482" t="s">
         <v>85</v>
@@ -36228,22 +36161,22 @@
         <v>61</v>
       </c>
       <c r="G482" t="s">
+        <v>2527</v>
+      </c>
+      <c r="H482" t="s">
         <v>2528</v>
-      </c>
-      <c r="H482" t="s">
-        <v>2529</v>
       </c>
       <c r="I482" t="s">
         <v>2184</v>
       </c>
       <c r="J482" t="s">
-        <v>2530</v>
+        <v>2529</v>
       </c>
       <c r="K482">
         <v>2001</v>
       </c>
       <c r="P482" s="8" t="s">
-        <v>3656</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="483" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36251,28 +36184,28 @@
         <v>43</v>
       </c>
       <c r="B483" t="s">
+        <v>2530</v>
+      </c>
+      <c r="E483" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G483" t="s">
         <v>2531</v>
       </c>
-      <c r="E483" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G483" t="s">
+      <c r="H483" t="s">
         <v>2532</v>
-      </c>
-      <c r="H483" t="s">
-        <v>2533</v>
       </c>
       <c r="I483" t="s">
         <v>51</v>
       </c>
       <c r="J483" t="s">
-        <v>2534</v>
+        <v>2533</v>
       </c>
       <c r="K483">
         <v>2020</v>
       </c>
       <c r="P483" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="484" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36280,7 +36213,7 @@
         <v>43</v>
       </c>
       <c r="B484" t="s">
-        <v>2535</v>
+        <v>2534</v>
       </c>
       <c r="E484" t="s">
         <v>85</v>
@@ -36289,22 +36222,22 @@
         <v>48</v>
       </c>
       <c r="G484" t="s">
+        <v>2535</v>
+      </c>
+      <c r="H484" t="s">
         <v>2536</v>
-      </c>
-      <c r="H484" t="s">
-        <v>2537</v>
       </c>
       <c r="I484" t="s">
         <v>1359</v>
       </c>
       <c r="J484" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="K484">
         <v>2013</v>
       </c>
       <c r="P484" s="8" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="485" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36312,28 +36245,28 @@
         <v>43</v>
       </c>
       <c r="B485" t="s">
+        <v>2539</v>
+      </c>
+      <c r="E485" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G485" t="s">
         <v>2540</v>
       </c>
-      <c r="E485" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G485" t="s">
+      <c r="H485" t="s">
         <v>2541</v>
-      </c>
-      <c r="H485" t="s">
-        <v>2542</v>
       </c>
       <c r="I485" t="s">
         <v>295</v>
       </c>
       <c r="J485" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="K485">
         <v>2012</v>
       </c>
       <c r="P485" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="486" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36341,7 +36274,7 @@
         <v>43</v>
       </c>
       <c r="B486" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="E486" t="s">
         <v>85</v>
@@ -36350,22 +36283,22 @@
         <v>48</v>
       </c>
       <c r="G486" t="s">
+        <v>2544</v>
+      </c>
+      <c r="H486" t="s">
         <v>2545</v>
       </c>
-      <c r="H486" t="s">
+      <c r="I486" t="s">
         <v>2546</v>
       </c>
-      <c r="I486" t="s">
+      <c r="J486" t="s">
         <v>2547</v>
-      </c>
-      <c r="J486" t="s">
-        <v>2548</v>
       </c>
       <c r="K486">
         <v>1996</v>
       </c>
       <c r="P486" s="8" t="s">
-        <v>3657</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="487" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36373,28 +36306,28 @@
         <v>43</v>
       </c>
       <c r="B487" t="s">
+        <v>2548</v>
+      </c>
+      <c r="E487" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G487" t="s">
         <v>2549</v>
       </c>
-      <c r="E487" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G487" t="s">
+      <c r="H487" t="s">
         <v>2550</v>
       </c>
-      <c r="H487" t="s">
+      <c r="I487" t="s">
         <v>2551</v>
       </c>
-      <c r="I487" t="s">
+      <c r="J487" t="s">
         <v>2552</v>
-      </c>
-      <c r="J487" t="s">
-        <v>2553</v>
       </c>
       <c r="K487">
         <v>1995</v>
       </c>
       <c r="P487" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="488" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36402,31 +36335,28 @@
         <v>43</v>
       </c>
       <c r="B488" t="s">
+        <v>2553</v>
+      </c>
+      <c r="E488" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G488" t="s">
         <v>2554</v>
       </c>
-      <c r="E488" t="s">
-        <v>85</v>
-      </c>
-      <c r="F488" t="s">
-        <v>61</v>
-      </c>
-      <c r="G488" t="s">
+      <c r="H488" t="s">
         <v>2555</v>
-      </c>
-      <c r="H488" t="s">
-        <v>2556</v>
       </c>
       <c r="I488" t="s">
         <v>51</v>
       </c>
       <c r="J488" t="s">
-        <v>2557</v>
+        <v>2556</v>
       </c>
       <c r="K488">
         <v>2002</v>
       </c>
       <c r="P488" s="8" t="s">
-        <v>3658</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="489" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36434,28 +36364,28 @@
         <v>43</v>
       </c>
       <c r="B489" t="s">
+        <v>2557</v>
+      </c>
+      <c r="E489" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G489" t="s">
         <v>2558</v>
       </c>
-      <c r="E489" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G489" t="s">
+      <c r="H489" t="s">
         <v>2559</v>
       </c>
-      <c r="H489" t="s">
+      <c r="I489" t="s">
         <v>2560</v>
       </c>
-      <c r="I489" t="s">
+      <c r="J489" t="s">
         <v>2561</v>
-      </c>
-      <c r="J489" t="s">
-        <v>2562</v>
       </c>
       <c r="K489">
         <v>2023</v>
       </c>
       <c r="P489" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="490" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36463,28 +36393,28 @@
         <v>43</v>
       </c>
       <c r="B490" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E490" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G490" t="s">
         <v>2563</v>
       </c>
-      <c r="E490" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G490" t="s">
+      <c r="H490" t="s">
         <v>2564</v>
       </c>
-      <c r="H490" t="s">
+      <c r="I490" t="s">
         <v>2565</v>
       </c>
-      <c r="I490" t="s">
+      <c r="J490" t="s">
         <v>2566</v>
-      </c>
-      <c r="J490" t="s">
-        <v>2567</v>
       </c>
       <c r="K490">
         <v>2011</v>
       </c>
       <c r="P490" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="491" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36492,28 +36422,28 @@
         <v>43</v>
       </c>
       <c r="B491" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E491" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G491" t="s">
         <v>2568</v>
       </c>
-      <c r="E491" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G491" t="s">
+      <c r="H491" t="s">
         <v>2569</v>
       </c>
-      <c r="H491" t="s">
+      <c r="I491" t="s">
         <v>2570</v>
       </c>
-      <c r="I491" t="s">
-        <v>2571</v>
-      </c>
       <c r="J491" t="s">
-        <v>2567</v>
+        <v>2566</v>
       </c>
       <c r="K491">
         <v>2011</v>
       </c>
       <c r="P491" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="492" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36521,28 +36451,28 @@
         <v>43</v>
       </c>
       <c r="B492" t="s">
+        <v>2571</v>
+      </c>
+      <c r="E492" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G492" t="s">
         <v>2572</v>
       </c>
-      <c r="E492" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G492" t="s">
+      <c r="H492" t="s">
         <v>2573</v>
-      </c>
-      <c r="H492" t="s">
-        <v>2574</v>
       </c>
       <c r="I492" t="s">
         <v>51</v>
       </c>
       <c r="J492" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="K492">
         <v>1984</v>
       </c>
       <c r="P492" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="493" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36550,28 +36480,28 @@
         <v>43</v>
       </c>
       <c r="B493" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E493" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G493" t="s">
         <v>2576</v>
       </c>
-      <c r="E493" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G493" t="s">
+      <c r="H493" t="s">
         <v>2577</v>
       </c>
-      <c r="H493" t="s">
+      <c r="I493" t="s">
         <v>2578</v>
       </c>
-      <c r="I493" t="s">
+      <c r="J493" t="s">
         <v>2579</v>
-      </c>
-      <c r="J493" t="s">
-        <v>2580</v>
       </c>
       <c r="K493">
         <v>2017</v>
       </c>
       <c r="P493" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="494" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36579,28 +36509,28 @@
         <v>43</v>
       </c>
       <c r="B494" t="s">
+        <v>2580</v>
+      </c>
+      <c r="E494" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G494" t="s">
         <v>2581</v>
       </c>
-      <c r="E494" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G494" t="s">
+      <c r="H494" t="s">
         <v>2582</v>
-      </c>
-      <c r="H494" t="s">
-        <v>2583</v>
       </c>
       <c r="I494" t="s">
         <v>1729</v>
       </c>
       <c r="J494" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="K494">
         <v>2025</v>
       </c>
       <c r="P494" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="495" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36608,28 +36538,28 @@
         <v>43</v>
       </c>
       <c r="B495" t="s">
+        <v>2584</v>
+      </c>
+      <c r="E495" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G495" t="s">
         <v>2585</v>
       </c>
-      <c r="E495" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G495" t="s">
+      <c r="H495" t="s">
         <v>2586</v>
-      </c>
-      <c r="H495" t="s">
-        <v>2587</v>
       </c>
       <c r="I495" t="s">
         <v>643</v>
       </c>
       <c r="J495" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="K495">
         <v>2025</v>
       </c>
       <c r="P495" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="496" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36637,28 +36567,28 @@
         <v>43</v>
       </c>
       <c r="B496" t="s">
+        <v>2588</v>
+      </c>
+      <c r="E496" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G496" t="s">
+        <v>2572</v>
+      </c>
+      <c r="H496" t="s">
         <v>2589</v>
-      </c>
-      <c r="E496" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G496" t="s">
-        <v>2573</v>
-      </c>
-      <c r="H496" t="s">
-        <v>2590</v>
       </c>
       <c r="I496" t="s">
         <v>307</v>
       </c>
       <c r="J496" t="s">
-        <v>2591</v>
+        <v>2590</v>
       </c>
       <c r="K496">
         <v>2020</v>
       </c>
       <c r="P496" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="497" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36666,7 +36596,7 @@
         <v>43</v>
       </c>
       <c r="B497" t="s">
-        <v>2592</v>
+        <v>2591</v>
       </c>
       <c r="E497" t="s">
         <v>85</v>
@@ -36675,22 +36605,22 @@
         <v>72</v>
       </c>
       <c r="G497" t="s">
+        <v>2592</v>
+      </c>
+      <c r="H497" t="s">
         <v>2593</v>
       </c>
-      <c r="H497" t="s">
+      <c r="I497" t="s">
         <v>2594</v>
       </c>
-      <c r="I497" t="s">
+      <c r="J497" t="s">
         <v>2595</v>
-      </c>
-      <c r="J497" t="s">
-        <v>2596</v>
       </c>
       <c r="K497">
         <v>2019</v>
       </c>
       <c r="P497" s="8" t="s">
-        <v>3659</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="498" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36698,28 +36628,28 @@
         <v>43</v>
       </c>
       <c r="B498" t="s">
+        <v>2596</v>
+      </c>
+      <c r="E498" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G498" t="s">
         <v>2597</v>
       </c>
-      <c r="E498" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G498" t="s">
+      <c r="H498" t="s">
         <v>2598</v>
       </c>
-      <c r="H498" t="s">
+      <c r="I498" t="s">
         <v>2599</v>
       </c>
-      <c r="I498" t="s">
+      <c r="J498" t="s">
         <v>2600</v>
-      </c>
-      <c r="J498" t="s">
-        <v>2601</v>
       </c>
       <c r="K498">
         <v>2023</v>
       </c>
       <c r="P498" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="499" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36727,28 +36657,28 @@
         <v>43</v>
       </c>
       <c r="B499" t="s">
+        <v>2601</v>
+      </c>
+      <c r="E499" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G499" t="s">
         <v>2602</v>
       </c>
-      <c r="E499" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G499" t="s">
+      <c r="H499" t="s">
         <v>2603</v>
-      </c>
-      <c r="H499" t="s">
-        <v>2604</v>
       </c>
       <c r="I499" t="s">
         <v>687</v>
       </c>
       <c r="J499" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="K499">
         <v>2001</v>
       </c>
       <c r="P499" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="500" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36756,7 +36686,7 @@
         <v>43</v>
       </c>
       <c r="B500" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="E500" t="s">
         <v>85</v>
@@ -36765,22 +36695,22 @@
         <v>48</v>
       </c>
       <c r="G500" t="s">
+        <v>2606</v>
+      </c>
+      <c r="H500" t="s">
         <v>2607</v>
-      </c>
-      <c r="H500" t="s">
-        <v>2608</v>
       </c>
       <c r="I500" t="s">
         <v>723</v>
       </c>
       <c r="J500" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="K500">
         <v>2022</v>
       </c>
       <c r="P500" s="8" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
     </row>
     <row r="501" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36788,28 +36718,28 @@
         <v>43</v>
       </c>
       <c r="B501" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E501" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G501" t="s">
         <v>2611</v>
       </c>
-      <c r="E501" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G501" t="s">
+      <c r="H501" t="s">
         <v>2612</v>
-      </c>
-      <c r="H501" t="s">
-        <v>2613</v>
       </c>
       <c r="I501" t="s">
         <v>253</v>
       </c>
       <c r="J501" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="K501">
         <v>2001</v>
       </c>
       <c r="P501" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="502" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36817,28 +36747,28 @@
         <v>43</v>
       </c>
       <c r="B502" t="s">
-        <v>2615</v>
+        <v>2614</v>
       </c>
       <c r="E502" t="s">
         <v>48</v>
       </c>
       <c r="G502" t="s">
+        <v>2615</v>
+      </c>
+      <c r="H502" t="s">
         <v>2616</v>
-      </c>
-      <c r="H502" t="s">
-        <v>2617</v>
       </c>
       <c r="I502" t="s">
         <v>307</v>
       </c>
       <c r="J502" t="s">
-        <v>2618</v>
+        <v>2617</v>
       </c>
       <c r="K502">
         <v>1976</v>
       </c>
       <c r="P502" s="8" t="s">
-        <v>2619</v>
+        <v>2618</v>
       </c>
     </row>
     <row r="503" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36846,7 +36776,7 @@
         <v>43</v>
       </c>
       <c r="B503" t="s">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="E503" t="s">
         <v>85</v>
@@ -36855,22 +36785,22 @@
         <v>48</v>
       </c>
       <c r="G503" t="s">
+        <v>2620</v>
+      </c>
+      <c r="H503" t="s">
         <v>2621</v>
       </c>
-      <c r="H503" t="s">
+      <c r="I503" t="s">
         <v>2622</v>
       </c>
-      <c r="I503" t="s">
+      <c r="J503" t="s">
         <v>2623</v>
-      </c>
-      <c r="J503" t="s">
-        <v>2624</v>
       </c>
       <c r="K503">
         <v>1981</v>
       </c>
       <c r="P503" s="8" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="504" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36878,28 +36808,28 @@
         <v>43</v>
       </c>
       <c r="B504" t="s">
+        <v>2625</v>
+      </c>
+      <c r="E504" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G504" t="s">
         <v>2626</v>
       </c>
-      <c r="E504" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G504" t="s">
+      <c r="H504" t="s">
         <v>2627</v>
       </c>
-      <c r="H504" t="s">
+      <c r="I504" t="s">
         <v>2628</v>
       </c>
-      <c r="I504" t="s">
+      <c r="J504" t="s">
         <v>2629</v>
-      </c>
-      <c r="J504" t="s">
-        <v>2630</v>
       </c>
       <c r="K504">
         <v>2025</v>
       </c>
       <c r="P504" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="505" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36907,7 +36837,7 @@
         <v>43</v>
       </c>
       <c r="B505" t="s">
-        <v>2631</v>
+        <v>2630</v>
       </c>
       <c r="E505" t="s">
         <v>85</v>
@@ -36916,22 +36846,22 @@
         <v>72</v>
       </c>
       <c r="G505" t="s">
+        <v>2631</v>
+      </c>
+      <c r="H505" t="s">
         <v>2632</v>
       </c>
-      <c r="H505" t="s">
+      <c r="I505" t="s">
         <v>2633</v>
       </c>
-      <c r="I505" t="s">
+      <c r="J505" t="s">
         <v>2634</v>
-      </c>
-      <c r="J505" t="s">
-        <v>2635</v>
       </c>
       <c r="K505">
         <v>1998</v>
       </c>
       <c r="P505" s="8" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="506" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36939,28 +36869,28 @@
         <v>43</v>
       </c>
       <c r="B506" t="s">
+        <v>2636</v>
+      </c>
+      <c r="E506" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G506" t="s">
         <v>2637</v>
       </c>
-      <c r="E506" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G506" t="s">
+      <c r="H506" t="s">
         <v>2638</v>
-      </c>
-      <c r="H506" t="s">
-        <v>2639</v>
       </c>
       <c r="I506" t="s">
         <v>351</v>
       </c>
       <c r="J506" t="s">
-        <v>2640</v>
+        <v>2639</v>
       </c>
       <c r="K506">
         <v>2010</v>
       </c>
       <c r="P506" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="507" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36968,31 +36898,28 @@
         <v>43</v>
       </c>
       <c r="B507" t="s">
+        <v>2640</v>
+      </c>
+      <c r="E507" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G507" t="s">
         <v>2641</v>
       </c>
-      <c r="E507" t="s">
-        <v>85</v>
-      </c>
-      <c r="F507" t="s">
-        <v>48</v>
-      </c>
-      <c r="G507" t="s">
+      <c r="H507" t="s">
         <v>2642</v>
-      </c>
-      <c r="H507" t="s">
-        <v>2643</v>
       </c>
       <c r="I507" t="s">
         <v>2018</v>
       </c>
       <c r="J507" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="K507">
         <v>2016</v>
       </c>
       <c r="P507" s="8" t="s">
-        <v>2645</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="508" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37000,7 +36927,7 @@
         <v>43</v>
       </c>
       <c r="B508" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="E508" t="s">
         <v>85</v>
@@ -37009,22 +36936,22 @@
         <v>54</v>
       </c>
       <c r="G508" t="s">
+        <v>2645</v>
+      </c>
+      <c r="H508" t="s">
+        <v>2646</v>
+      </c>
+      <c r="I508" t="s">
         <v>2647</v>
       </c>
-      <c r="H508" t="s">
+      <c r="J508" t="s">
         <v>2648</v>
-      </c>
-      <c r="I508" t="s">
-        <v>2649</v>
-      </c>
-      <c r="J508" t="s">
-        <v>2650</v>
       </c>
       <c r="K508">
         <v>2004</v>
       </c>
       <c r="P508" s="8" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="509" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37032,28 +36959,28 @@
         <v>43</v>
       </c>
       <c r="B509" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E509" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G509" t="s">
+        <v>2651</v>
+      </c>
+      <c r="H509" t="s">
         <v>2652</v>
-      </c>
-      <c r="E509" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G509" t="s">
-        <v>2653</v>
-      </c>
-      <c r="H509" t="s">
-        <v>2654</v>
       </c>
       <c r="I509" t="s">
         <v>481</v>
       </c>
       <c r="J509" t="s">
-        <v>2655</v>
+        <v>2653</v>
       </c>
       <c r="K509">
         <v>1989</v>
       </c>
       <c r="P509" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="510" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37061,28 +36988,28 @@
         <v>43</v>
       </c>
       <c r="B510" t="s">
+        <v>2654</v>
+      </c>
+      <c r="E510" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G510" t="s">
+        <v>2655</v>
+      </c>
+      <c r="H510" t="s">
         <v>2656</v>
       </c>
-      <c r="E510" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G510" t="s">
+      <c r="I510" t="s">
         <v>2657</v>
       </c>
-      <c r="H510" t="s">
+      <c r="J510" t="s">
         <v>2658</v>
-      </c>
-      <c r="I510" t="s">
-        <v>2659</v>
-      </c>
-      <c r="J510" t="s">
-        <v>2660</v>
       </c>
       <c r="K510">
         <v>2005</v>
       </c>
       <c r="P510" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="511" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37090,28 +37017,28 @@
         <v>43</v>
       </c>
       <c r="B511" t="s">
+        <v>2659</v>
+      </c>
+      <c r="E511" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G511" t="s">
+        <v>2660</v>
+      </c>
+      <c r="H511" t="s">
         <v>2661</v>
-      </c>
-      <c r="E511" t="s">
-        <v>48</v>
-      </c>
-      <c r="G511" t="s">
-        <v>2662</v>
-      </c>
-      <c r="H511" t="s">
-        <v>2663</v>
       </c>
       <c r="I511" t="s">
         <v>403</v>
       </c>
       <c r="J511" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="K511">
         <v>2025</v>
       </c>
       <c r="P511" s="8" t="s">
-        <v>2665</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="512" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37119,28 +37046,28 @@
         <v>43</v>
       </c>
       <c r="B512" t="s">
-        <v>2666</v>
+        <v>2663</v>
       </c>
       <c r="E512" t="s">
-        <v>2503</v>
+        <v>2482</v>
       </c>
       <c r="G512" t="s">
-        <v>2667</v>
+        <v>2664</v>
       </c>
       <c r="H512" t="s">
-        <v>2668</v>
+        <v>2665</v>
       </c>
       <c r="I512" t="s">
         <v>1652</v>
       </c>
       <c r="J512" t="s">
-        <v>2669</v>
+        <v>2666</v>
       </c>
       <c r="K512">
         <v>2018</v>
       </c>
       <c r="P512" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="513" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37148,28 +37075,28 @@
         <v>43</v>
       </c>
       <c r="B513" t="s">
-        <v>2670</v>
+        <v>2667</v>
       </c>
       <c r="E513" t="s">
-        <v>2503</v>
+        <v>2482</v>
       </c>
       <c r="G513" t="s">
-        <v>2671</v>
+        <v>2668</v>
       </c>
       <c r="H513" t="s">
-        <v>2672</v>
+        <v>2669</v>
       </c>
       <c r="I513" t="s">
         <v>1499</v>
       </c>
       <c r="J513" t="s">
-        <v>2673</v>
+        <v>2670</v>
       </c>
       <c r="K513">
         <v>2011</v>
       </c>
       <c r="P513" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="514" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37177,31 +37104,28 @@
         <v>43</v>
       </c>
       <c r="B514" t="s">
-        <v>2674</v>
+        <v>2671</v>
       </c>
       <c r="E514" t="s">
-        <v>85</v>
-      </c>
-      <c r="F514" t="s">
-        <v>61</v>
+        <v>2482</v>
       </c>
       <c r="G514" t="s">
-        <v>2675</v>
+        <v>2672</v>
       </c>
       <c r="H514" t="s">
-        <v>2676</v>
+        <v>2673</v>
       </c>
       <c r="I514" t="s">
         <v>1242</v>
       </c>
       <c r="J514" t="s">
-        <v>2677</v>
+        <v>2674</v>
       </c>
       <c r="K514">
         <v>2024</v>
       </c>
       <c r="P514" s="8" t="s">
-        <v>2678</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="515" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37209,28 +37133,28 @@
         <v>43</v>
       </c>
       <c r="B515" t="s">
-        <v>2679</v>
+        <v>2675</v>
       </c>
       <c r="E515" t="s">
-        <v>2503</v>
+        <v>2482</v>
       </c>
       <c r="G515" t="s">
-        <v>2680</v>
+        <v>2676</v>
       </c>
       <c r="H515" t="s">
-        <v>2681</v>
+        <v>2677</v>
       </c>
       <c r="I515" t="s">
         <v>1783</v>
       </c>
       <c r="J515" t="s">
-        <v>2682</v>
+        <v>2678</v>
       </c>
       <c r="K515">
         <v>2023</v>
       </c>
       <c r="P515" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="516" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37238,28 +37162,28 @@
         <v>43</v>
       </c>
       <c r="B516" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E516" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G516" t="s">
+        <v>2680</v>
+      </c>
+      <c r="H516" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I516" t="s">
+        <v>2682</v>
+      </c>
+      <c r="J516" t="s">
         <v>2683</v>
-      </c>
-      <c r="E516" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G516" t="s">
-        <v>2684</v>
-      </c>
-      <c r="H516" t="s">
-        <v>2685</v>
-      </c>
-      <c r="I516" t="s">
-        <v>2686</v>
-      </c>
-      <c r="J516" t="s">
-        <v>2687</v>
       </c>
       <c r="K516">
         <v>2010</v>
       </c>
       <c r="P516" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="517" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37267,28 +37191,28 @@
         <v>43</v>
       </c>
       <c r="B517" t="s">
+        <v>2684</v>
+      </c>
+      <c r="E517" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G517" t="s">
+        <v>2685</v>
+      </c>
+      <c r="H517" t="s">
+        <v>2686</v>
+      </c>
+      <c r="I517" t="s">
+        <v>2687</v>
+      </c>
+      <c r="J517" t="s">
         <v>2688</v>
-      </c>
-      <c r="E517" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G517" t="s">
-        <v>2689</v>
-      </c>
-      <c r="H517" t="s">
-        <v>2690</v>
-      </c>
-      <c r="I517" t="s">
-        <v>2691</v>
-      </c>
-      <c r="J517" t="s">
-        <v>2692</v>
       </c>
       <c r="K517">
         <v>2019</v>
       </c>
       <c r="P517" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="518" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37296,28 +37220,28 @@
         <v>43</v>
       </c>
       <c r="B518" t="s">
-        <v>2693</v>
+        <v>2689</v>
       </c>
       <c r="E518" t="s">
-        <v>2503</v>
+        <v>2482</v>
       </c>
       <c r="G518" t="s">
-        <v>2694</v>
+        <v>2690</v>
       </c>
       <c r="H518" t="s">
-        <v>2695</v>
+        <v>2691</v>
       </c>
       <c r="I518" t="s">
         <v>51</v>
       </c>
       <c r="J518" t="s">
-        <v>2696</v>
+        <v>2692</v>
       </c>
       <c r="K518">
         <v>1986</v>
       </c>
       <c r="P518" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="519" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37325,28 +37249,28 @@
         <v>43</v>
       </c>
       <c r="B519" t="s">
+        <v>2693</v>
+      </c>
+      <c r="E519" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G519" t="s">
+        <v>2694</v>
+      </c>
+      <c r="H519" t="s">
+        <v>2695</v>
+      </c>
+      <c r="I519" t="s">
+        <v>2696</v>
+      </c>
+      <c r="J519" t="s">
         <v>2697</v>
-      </c>
-      <c r="E519" t="s">
-        <v>48</v>
-      </c>
-      <c r="G519" t="s">
-        <v>2698</v>
-      </c>
-      <c r="H519" t="s">
-        <v>2699</v>
-      </c>
-      <c r="I519" t="s">
-        <v>2700</v>
-      </c>
-      <c r="J519" t="s">
-        <v>2701</v>
       </c>
       <c r="K519">
         <v>2018</v>
       </c>
       <c r="P519" s="8" t="s">
-        <v>3660</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="520" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37354,28 +37278,28 @@
         <v>43</v>
       </c>
       <c r="B520" t="s">
+        <v>2698</v>
+      </c>
+      <c r="E520" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G520" t="s">
+        <v>2699</v>
+      </c>
+      <c r="H520" t="s">
+        <v>2700</v>
+      </c>
+      <c r="I520" t="s">
+        <v>2701</v>
+      </c>
+      <c r="J520" t="s">
         <v>2702</v>
-      </c>
-      <c r="E520" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G520" t="s">
-        <v>2703</v>
-      </c>
-      <c r="H520" t="s">
-        <v>2704</v>
-      </c>
-      <c r="I520" t="s">
-        <v>2705</v>
-      </c>
-      <c r="J520" t="s">
-        <v>2706</v>
       </c>
       <c r="K520">
         <v>2006</v>
       </c>
       <c r="P520" s="8" t="s">
-        <v>2507</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="521" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -37383,739 +37307,889 @@
         <v>43</v>
       </c>
       <c r="B521" t="s">
+        <v>2703</v>
+      </c>
+      <c r="E521" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G521" t="s">
+        <v>2704</v>
+      </c>
+      <c r="H521" t="s">
+        <v>2705</v>
+      </c>
+      <c r="I521" t="s">
+        <v>2706</v>
+      </c>
+      <c r="J521" t="s">
         <v>2707</v>
-      </c>
-      <c r="G521" t="s">
-        <v>2708</v>
-      </c>
-      <c r="H521" t="s">
-        <v>2709</v>
-      </c>
-      <c r="I521" t="s">
-        <v>2710</v>
-      </c>
-      <c r="J521" t="s">
-        <v>2711</v>
       </c>
       <c r="K521">
         <v>2008</v>
       </c>
-      <c r="P521" s="8"/>
+      <c r="P521" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="522" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A522" t="s">
         <v>43</v>
       </c>
       <c r="B522" t="s">
-        <v>2712</v>
+        <v>2708</v>
+      </c>
+      <c r="E522" t="s">
+        <v>2482</v>
       </c>
       <c r="G522" t="s">
-        <v>2713</v>
+        <v>2709</v>
       </c>
       <c r="H522" t="s">
-        <v>2714</v>
+        <v>2710</v>
       </c>
       <c r="I522" t="s">
         <v>1196</v>
       </c>
       <c r="J522" t="s">
-        <v>2715</v>
+        <v>2711</v>
       </c>
       <c r="K522">
         <v>2019</v>
       </c>
-      <c r="P522" s="8"/>
+      <c r="P522" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="523" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A523" t="s">
         <v>43</v>
       </c>
       <c r="B523" t="s">
+        <v>2712</v>
+      </c>
+      <c r="E523" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G523" t="s">
+        <v>2713</v>
+      </c>
+      <c r="H523" t="s">
+        <v>2714</v>
+      </c>
+      <c r="I523" t="s">
+        <v>2715</v>
+      </c>
+      <c r="J523" t="s">
         <v>2716</v>
-      </c>
-      <c r="G523" t="s">
-        <v>2717</v>
-      </c>
-      <c r="H523" t="s">
-        <v>2718</v>
-      </c>
-      <c r="I523" t="s">
-        <v>2719</v>
-      </c>
-      <c r="J523" t="s">
-        <v>2720</v>
       </c>
       <c r="K523">
         <v>2012</v>
       </c>
-      <c r="P523" s="8"/>
+      <c r="P523" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="524" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A524" t="s">
         <v>43</v>
       </c>
       <c r="B524" t="s">
-        <v>2721</v>
+        <v>2717</v>
+      </c>
+      <c r="E524" t="s">
+        <v>2482</v>
       </c>
       <c r="G524" t="s">
-        <v>2722</v>
+        <v>2718</v>
       </c>
       <c r="H524" t="s">
-        <v>2723</v>
+        <v>2719</v>
       </c>
       <c r="I524" t="s">
         <v>1729</v>
       </c>
       <c r="J524" t="s">
-        <v>2724</v>
+        <v>2720</v>
       </c>
       <c r="K524">
         <v>1997</v>
       </c>
-      <c r="P524" s="8"/>
+      <c r="P524" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="525" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A525" t="s">
         <v>43</v>
       </c>
       <c r="B525" t="s">
+        <v>2721</v>
+      </c>
+      <c r="E525" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G525" t="s">
+        <v>2722</v>
+      </c>
+      <c r="H525" t="s">
+        <v>2723</v>
+      </c>
+      <c r="I525" t="s">
+        <v>2724</v>
+      </c>
+      <c r="J525" t="s">
         <v>2725</v>
-      </c>
-      <c r="G525" t="s">
-        <v>2726</v>
-      </c>
-      <c r="H525" t="s">
-        <v>2727</v>
-      </c>
-      <c r="I525" t="s">
-        <v>2728</v>
-      </c>
-      <c r="J525" t="s">
-        <v>2729</v>
       </c>
       <c r="K525">
         <v>2023</v>
       </c>
-      <c r="P525" s="8"/>
+      <c r="P525" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="526" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A526" t="s">
         <v>43</v>
       </c>
       <c r="B526" t="s">
-        <v>2730</v>
+        <v>2726</v>
+      </c>
+      <c r="E526" t="s">
+        <v>2482</v>
       </c>
       <c r="G526" t="s">
-        <v>2731</v>
+        <v>2727</v>
       </c>
       <c r="H526" t="s">
-        <v>2732</v>
+        <v>2728</v>
       </c>
       <c r="I526" t="s">
         <v>329</v>
       </c>
       <c r="J526" t="s">
-        <v>2733</v>
+        <v>2729</v>
       </c>
       <c r="K526">
         <v>2021</v>
       </c>
-      <c r="P526" s="8"/>
+      <c r="P526" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="527" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A527" t="s">
         <v>43</v>
       </c>
       <c r="B527" t="s">
+        <v>2730</v>
+      </c>
+      <c r="E527" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G527" t="s">
+        <v>2731</v>
+      </c>
+      <c r="H527" t="s">
+        <v>2732</v>
+      </c>
+      <c r="I527" t="s">
+        <v>2733</v>
+      </c>
+      <c r="J527" t="s">
         <v>2734</v>
-      </c>
-      <c r="G527" t="s">
-        <v>2735</v>
-      </c>
-      <c r="H527" t="s">
-        <v>2736</v>
-      </c>
-      <c r="I527" t="s">
-        <v>2737</v>
-      </c>
-      <c r="J527" t="s">
-        <v>2738</v>
       </c>
       <c r="K527">
         <v>1989</v>
       </c>
-      <c r="P527" s="8"/>
+      <c r="P527" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="528" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A528" t="s">
         <v>43</v>
       </c>
       <c r="B528" t="s">
-        <v>2739</v>
+        <v>2735</v>
+      </c>
+      <c r="E528" t="s">
+        <v>2482</v>
       </c>
       <c r="G528" t="s">
-        <v>2740</v>
+        <v>2736</v>
       </c>
       <c r="H528" t="s">
-        <v>2741</v>
+        <v>2737</v>
       </c>
       <c r="I528" t="s">
         <v>1394</v>
       </c>
       <c r="J528" t="s">
-        <v>2742</v>
+        <v>2738</v>
       </c>
       <c r="K528">
         <v>2001</v>
       </c>
-      <c r="P528" s="8"/>
+      <c r="P528" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="529" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A529" t="s">
         <v>43</v>
       </c>
       <c r="B529" t="s">
+        <v>2739</v>
+      </c>
+      <c r="E529" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G529" t="s">
+        <v>2740</v>
+      </c>
+      <c r="H529" t="s">
+        <v>2741</v>
+      </c>
+      <c r="I529" t="s">
+        <v>2742</v>
+      </c>
+      <c r="J529" t="s">
         <v>2743</v>
-      </c>
-      <c r="G529" t="s">
-        <v>2744</v>
-      </c>
-      <c r="H529" t="s">
-        <v>2745</v>
-      </c>
-      <c r="I529" t="s">
-        <v>2746</v>
-      </c>
-      <c r="J529" t="s">
-        <v>2747</v>
       </c>
       <c r="K529">
         <v>2024</v>
       </c>
-      <c r="P529" s="8"/>
+      <c r="P529" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="530" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A530" t="s">
         <v>43</v>
       </c>
       <c r="B530" t="s">
+        <v>2744</v>
+      </c>
+      <c r="E530" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G530" t="s">
+        <v>2745</v>
+      </c>
+      <c r="H530" t="s">
+        <v>2746</v>
+      </c>
+      <c r="I530" t="s">
+        <v>2747</v>
+      </c>
+      <c r="J530" t="s">
         <v>2748</v>
-      </c>
-      <c r="G530" t="s">
-        <v>2749</v>
-      </c>
-      <c r="H530" t="s">
-        <v>2750</v>
-      </c>
-      <c r="I530" t="s">
-        <v>2751</v>
-      </c>
-      <c r="J530" t="s">
-        <v>2752</v>
       </c>
       <c r="K530">
         <v>2012</v>
       </c>
-      <c r="P530" s="8"/>
+      <c r="P530" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="531" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A531" t="s">
         <v>43</v>
       </c>
       <c r="B531" t="s">
-        <v>2753</v>
+        <v>2749</v>
+      </c>
+      <c r="E531" t="s">
+        <v>2482</v>
       </c>
       <c r="G531" t="s">
-        <v>2754</v>
+        <v>2750</v>
       </c>
       <c r="H531" t="s">
-        <v>2755</v>
+        <v>2751</v>
       </c>
       <c r="I531" t="s">
         <v>549</v>
       </c>
       <c r="J531" t="s">
-        <v>2756</v>
+        <v>2752</v>
       </c>
       <c r="K531">
         <v>2024</v>
       </c>
-      <c r="P531" s="8"/>
+      <c r="P531" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="532" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A532" t="s">
         <v>43</v>
       </c>
       <c r="B532" t="s">
-        <v>2757</v>
+        <v>2753</v>
+      </c>
+      <c r="E532" t="s">
+        <v>2482</v>
       </c>
       <c r="G532" t="s">
-        <v>2758</v>
+        <v>2754</v>
       </c>
       <c r="H532" t="s">
-        <v>2759</v>
+        <v>2755</v>
       </c>
       <c r="I532" t="s">
         <v>100</v>
       </c>
       <c r="J532" t="s">
-        <v>2760</v>
+        <v>2756</v>
       </c>
       <c r="K532">
         <v>2023</v>
       </c>
-      <c r="P532" s="8"/>
+      <c r="P532" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="533" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A533" t="s">
         <v>43</v>
       </c>
       <c r="B533" t="s">
-        <v>2761</v>
+        <v>2757</v>
+      </c>
+      <c r="E533" t="s">
+        <v>2482</v>
       </c>
       <c r="G533" t="s">
-        <v>2762</v>
+        <v>2758</v>
       </c>
       <c r="H533" t="s">
-        <v>2763</v>
+        <v>2759</v>
       </c>
       <c r="I533" t="s">
         <v>154</v>
       </c>
       <c r="J533" t="s">
-        <v>2764</v>
+        <v>2760</v>
       </c>
       <c r="K533">
         <v>2010</v>
       </c>
-      <c r="P533" s="8"/>
+      <c r="P533" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="534" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A534" t="s">
         <v>43</v>
       </c>
       <c r="B534" t="s">
-        <v>2765</v>
+        <v>2761</v>
+      </c>
+      <c r="E534" t="s">
+        <v>2482</v>
       </c>
       <c r="G534" t="s">
-        <v>2766</v>
+        <v>2762</v>
       </c>
       <c r="H534" t="s">
-        <v>2767</v>
+        <v>2763</v>
       </c>
       <c r="I534" t="s">
         <v>687</v>
       </c>
       <c r="J534" t="s">
-        <v>2768</v>
+        <v>2764</v>
       </c>
       <c r="K534">
         <v>2017</v>
       </c>
-      <c r="P534" s="8"/>
+      <c r="P534" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="535" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A535" t="s">
         <v>43</v>
       </c>
       <c r="B535" t="s">
+        <v>2765</v>
+      </c>
+      <c r="E535" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G535" t="s">
+        <v>2766</v>
+      </c>
+      <c r="H535" t="s">
+        <v>2767</v>
+      </c>
+      <c r="I535" t="s">
+        <v>2768</v>
+      </c>
+      <c r="J535" t="s">
         <v>2769</v>
-      </c>
-      <c r="G535" t="s">
-        <v>2770</v>
-      </c>
-      <c r="H535" t="s">
-        <v>2771</v>
-      </c>
-      <c r="I535" t="s">
-        <v>2772</v>
-      </c>
-      <c r="J535" t="s">
-        <v>2773</v>
       </c>
       <c r="K535">
         <v>2000</v>
       </c>
-      <c r="P535" s="8"/>
+      <c r="P535" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="536" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A536" t="s">
         <v>43</v>
       </c>
       <c r="B536" t="s">
-        <v>2774</v>
+        <v>2770</v>
+      </c>
+      <c r="E536" t="s">
+        <v>2482</v>
       </c>
       <c r="G536" t="s">
-        <v>2775</v>
+        <v>2771</v>
       </c>
       <c r="H536" t="s">
-        <v>2776</v>
+        <v>2772</v>
       </c>
       <c r="I536" t="s">
         <v>653</v>
       </c>
       <c r="J536" t="s">
-        <v>2777</v>
+        <v>2773</v>
       </c>
       <c r="K536">
         <v>2016</v>
       </c>
-      <c r="P536" s="8"/>
+      <c r="P536" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="537" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A537" t="s">
         <v>43</v>
       </c>
       <c r="B537" t="s">
-        <v>2778</v>
+        <v>2774</v>
+      </c>
+      <c r="E537" t="s">
+        <v>2482</v>
       </c>
       <c r="G537" t="s">
-        <v>2779</v>
+        <v>2775</v>
       </c>
       <c r="H537" t="s">
-        <v>2780</v>
+        <v>2776</v>
       </c>
       <c r="I537" t="s">
         <v>426</v>
       </c>
       <c r="J537" t="s">
-        <v>2781</v>
+        <v>2777</v>
       </c>
       <c r="K537">
         <v>2006</v>
       </c>
-      <c r="P537" s="8"/>
+      <c r="P537" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="538" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A538" t="s">
         <v>43</v>
       </c>
       <c r="B538" t="s">
+        <v>2778</v>
+      </c>
+      <c r="E538" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G538" t="s">
+        <v>2779</v>
+      </c>
+      <c r="H538" t="s">
+        <v>2780</v>
+      </c>
+      <c r="I538" t="s">
+        <v>2781</v>
+      </c>
+      <c r="J538" t="s">
         <v>2782</v>
-      </c>
-      <c r="G538" t="s">
-        <v>2783</v>
-      </c>
-      <c r="H538" t="s">
-        <v>2784</v>
-      </c>
-      <c r="I538" t="s">
-        <v>2785</v>
-      </c>
-      <c r="J538" t="s">
-        <v>2786</v>
       </c>
       <c r="K538">
         <v>2018</v>
       </c>
-      <c r="P538" s="8"/>
+      <c r="P538" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="539" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A539" t="s">
         <v>43</v>
       </c>
       <c r="B539" t="s">
-        <v>2787</v>
+        <v>2783</v>
+      </c>
+      <c r="E539" t="s">
+        <v>2482</v>
       </c>
       <c r="G539" t="s">
-        <v>2788</v>
+        <v>2784</v>
       </c>
       <c r="H539" t="s">
-        <v>2789</v>
+        <v>2785</v>
       </c>
       <c r="I539" t="s">
         <v>357</v>
       </c>
       <c r="J539" t="s">
-        <v>2790</v>
+        <v>2786</v>
       </c>
       <c r="K539">
         <v>2015</v>
       </c>
-      <c r="P539" s="8"/>
+      <c r="P539" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="540" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A540" t="s">
         <v>43</v>
       </c>
       <c r="B540" t="s">
-        <v>2791</v>
+        <v>2787</v>
+      </c>
+      <c r="E540" t="s">
+        <v>2482</v>
       </c>
       <c r="G540" t="s">
-        <v>2792</v>
+        <v>2788</v>
       </c>
       <c r="H540" t="s">
-        <v>2793</v>
+        <v>2789</v>
       </c>
       <c r="I540" t="s">
         <v>51</v>
       </c>
       <c r="J540" t="s">
-        <v>2794</v>
+        <v>2790</v>
       </c>
       <c r="K540">
         <v>1988</v>
       </c>
-      <c r="P540" s="8"/>
+      <c r="P540" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="541" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A541" t="s">
         <v>43</v>
       </c>
       <c r="B541" t="s">
-        <v>2795</v>
+        <v>2791</v>
+      </c>
+      <c r="E541" t="s">
+        <v>2482</v>
       </c>
       <c r="G541" t="s">
-        <v>2796</v>
+        <v>2792</v>
       </c>
       <c r="H541" t="s">
-        <v>2797</v>
+        <v>2793</v>
       </c>
       <c r="I541" t="s">
         <v>307</v>
       </c>
       <c r="J541" t="s">
-        <v>2798</v>
+        <v>2794</v>
       </c>
       <c r="K541">
         <v>2016</v>
       </c>
-      <c r="P541" s="8"/>
+      <c r="P541" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="542" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A542" t="s">
         <v>43</v>
       </c>
       <c r="B542" t="s">
-        <v>2799</v>
+        <v>2795</v>
+      </c>
+      <c r="E542" t="s">
+        <v>2482</v>
       </c>
       <c r="G542" t="s">
-        <v>2800</v>
+        <v>2796</v>
       </c>
       <c r="H542" t="s">
-        <v>2801</v>
+        <v>2797</v>
       </c>
       <c r="I542" t="s">
         <v>237</v>
       </c>
       <c r="J542" t="s">
-        <v>2802</v>
+        <v>2798</v>
       </c>
       <c r="K542">
         <v>2022</v>
       </c>
-      <c r="P542" s="8"/>
+      <c r="P542" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="543" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A543" t="s">
         <v>43</v>
       </c>
       <c r="B543" t="s">
-        <v>2803</v>
+        <v>2799</v>
+      </c>
+      <c r="E543" t="s">
+        <v>2482</v>
       </c>
       <c r="G543" t="s">
-        <v>2804</v>
+        <v>2800</v>
       </c>
       <c r="H543" t="s">
-        <v>2805</v>
+        <v>2801</v>
       </c>
       <c r="I543" t="s">
         <v>346</v>
       </c>
       <c r="J543" t="s">
-        <v>2806</v>
+        <v>2802</v>
       </c>
       <c r="K543">
         <v>2025</v>
       </c>
-      <c r="P543" s="8"/>
+      <c r="P543" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="544" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A544" t="s">
         <v>43</v>
       </c>
       <c r="B544" t="s">
+        <v>2803</v>
+      </c>
+      <c r="E544" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G544" t="s">
+        <v>2804</v>
+      </c>
+      <c r="H544" t="s">
+        <v>2805</v>
+      </c>
+      <c r="I544" t="s">
+        <v>2806</v>
+      </c>
+      <c r="J544" t="s">
         <v>2807</v>
-      </c>
-      <c r="G544" t="s">
-        <v>2808</v>
-      </c>
-      <c r="H544" t="s">
-        <v>2809</v>
-      </c>
-      <c r="I544" t="s">
-        <v>2810</v>
-      </c>
-      <c r="J544" t="s">
-        <v>2811</v>
       </c>
       <c r="K544">
         <v>1986</v>
       </c>
-      <c r="P544" s="8"/>
+      <c r="P544" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="545" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A545" t="s">
         <v>43</v>
       </c>
       <c r="B545" t="s">
-        <v>2812</v>
+        <v>2808</v>
+      </c>
+      <c r="E545" t="s">
+        <v>2482</v>
       </c>
       <c r="G545" t="s">
-        <v>2813</v>
+        <v>2809</v>
       </c>
       <c r="H545" t="s">
-        <v>2814</v>
+        <v>2810</v>
       </c>
       <c r="I545" t="s">
         <v>900</v>
       </c>
       <c r="J545" t="s">
-        <v>2815</v>
+        <v>2811</v>
       </c>
       <c r="K545">
         <v>2014</v>
       </c>
-      <c r="P545" s="8"/>
+      <c r="P545" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="546" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A546" t="s">
         <v>43</v>
       </c>
       <c r="B546" t="s">
-        <v>2816</v>
+        <v>2812</v>
+      </c>
+      <c r="E546" t="s">
+        <v>2482</v>
       </c>
       <c r="G546" t="s">
-        <v>2817</v>
+        <v>2813</v>
       </c>
       <c r="H546" t="s">
-        <v>2818</v>
+        <v>2814</v>
       </c>
       <c r="I546" t="s">
-        <v>2700</v>
+        <v>2696</v>
       </c>
       <c r="J546" t="s">
-        <v>2819</v>
+        <v>2815</v>
       </c>
       <c r="K546">
         <v>2019</v>
       </c>
-      <c r="P546" s="8"/>
+      <c r="P546" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="547" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A547" t="s">
         <v>43</v>
       </c>
       <c r="B547" t="s">
-        <v>2820</v>
+        <v>2816</v>
+      </c>
+      <c r="E547" t="s">
+        <v>2482</v>
       </c>
       <c r="G547" t="s">
-        <v>2821</v>
+        <v>2817</v>
       </c>
       <c r="H547" t="s">
-        <v>2822</v>
+        <v>2818</v>
       </c>
       <c r="I547" t="s">
         <v>266</v>
       </c>
       <c r="J547" t="s">
-        <v>2823</v>
+        <v>2819</v>
       </c>
       <c r="K547">
         <v>2018</v>
       </c>
-      <c r="P547" s="8"/>
+      <c r="P547" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="548" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A548" t="s">
         <v>43</v>
       </c>
       <c r="B548" t="s">
-        <v>2824</v>
+        <v>2820</v>
+      </c>
+      <c r="E548" t="s">
+        <v>2482</v>
       </c>
       <c r="G548" t="s">
-        <v>2825</v>
+        <v>2821</v>
       </c>
       <c r="H548" t="s">
-        <v>2826</v>
+        <v>2822</v>
       </c>
       <c r="I548" t="s">
         <v>723</v>
       </c>
       <c r="J548" t="s">
-        <v>2827</v>
+        <v>2823</v>
       </c>
       <c r="K548">
         <v>1979</v>
       </c>
-      <c r="P548" s="8"/>
+      <c r="P548" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="549" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A549" t="s">
         <v>43</v>
       </c>
       <c r="B549" t="s">
-        <v>2828</v>
+        <v>2824</v>
+      </c>
+      <c r="E549" t="s">
+        <v>2482</v>
       </c>
       <c r="G549" t="s">
-        <v>2829</v>
+        <v>2825</v>
       </c>
       <c r="H549" t="s">
-        <v>2830</v>
+        <v>2826</v>
       </c>
       <c r="I549" t="s">
         <v>51</v>
       </c>
       <c r="J549" t="s">
-        <v>2831</v>
+        <v>2827</v>
       </c>
       <c r="K549">
         <v>2023</v>
       </c>
-      <c r="P549" s="8"/>
+      <c r="P549" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="550" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A550" t="s">
         <v>43</v>
       </c>
       <c r="B550" t="s">
-        <v>2832</v>
+        <v>2828</v>
+      </c>
+      <c r="E550" t="s">
+        <v>2482</v>
       </c>
       <c r="G550" t="s">
-        <v>2833</v>
+        <v>2829</v>
       </c>
       <c r="H550" t="s">
-        <v>2834</v>
+        <v>2830</v>
       </c>
       <c r="I550" t="s">
         <v>148</v>
       </c>
       <c r="J550" t="s">
-        <v>2835</v>
+        <v>2831</v>
       </c>
       <c r="K550">
         <v>2018</v>
       </c>
-      <c r="P550" s="8"/>
+      <c r="P550" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="551" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A551" t="s">
         <v>43</v>
       </c>
       <c r="B551" t="s">
+        <v>2832</v>
+      </c>
+      <c r="G551" t="s">
+        <v>2833</v>
+      </c>
+      <c r="H551" t="s">
+        <v>2834</v>
+      </c>
+      <c r="I551" t="s">
+        <v>2835</v>
+      </c>
+      <c r="J551" t="s">
         <v>2836</v>
-      </c>
-      <c r="G551" t="s">
-        <v>2837</v>
-      </c>
-      <c r="H551" t="s">
-        <v>2838</v>
-      </c>
-      <c r="I551" t="s">
-        <v>2839</v>
-      </c>
-      <c r="J551" t="s">
-        <v>2840</v>
       </c>
       <c r="K551">
         <v>2015</v>
@@ -38127,235 +38201,280 @@
         <v>43</v>
       </c>
       <c r="B552" t="s">
+        <v>2837</v>
+      </c>
+      <c r="E552" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G552" t="s">
+        <v>2838</v>
+      </c>
+      <c r="H552" t="s">
+        <v>2839</v>
+      </c>
+      <c r="I552" t="s">
+        <v>2840</v>
+      </c>
+      <c r="J552" t="s">
         <v>2841</v>
-      </c>
-      <c r="G552" t="s">
-        <v>2842</v>
-      </c>
-      <c r="H552" t="s">
-        <v>2843</v>
-      </c>
-      <c r="I552" t="s">
-        <v>2844</v>
-      </c>
-      <c r="J552" t="s">
-        <v>2845</v>
       </c>
       <c r="K552">
         <v>2021</v>
       </c>
-      <c r="P552" s="8"/>
+      <c r="P552" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="553" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A553" t="s">
         <v>43</v>
       </c>
       <c r="B553" t="s">
+        <v>2842</v>
+      </c>
+      <c r="E553" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G553" t="s">
+        <v>2843</v>
+      </c>
+      <c r="H553" t="s">
+        <v>2844</v>
+      </c>
+      <c r="I553" t="s">
+        <v>2845</v>
+      </c>
+      <c r="J553" t="s">
         <v>2846</v>
-      </c>
-      <c r="G553" t="s">
-        <v>2847</v>
-      </c>
-      <c r="H553" t="s">
-        <v>2848</v>
-      </c>
-      <c r="I553" t="s">
-        <v>2849</v>
-      </c>
-      <c r="J553" t="s">
-        <v>2850</v>
       </c>
       <c r="K553">
         <v>2010</v>
       </c>
-      <c r="P553" s="8"/>
+      <c r="P553" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="554" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A554" t="s">
         <v>43</v>
       </c>
       <c r="B554" t="s">
+        <v>2847</v>
+      </c>
+      <c r="E554" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G554" t="s">
+        <v>2848</v>
+      </c>
+      <c r="H554" t="s">
+        <v>2849</v>
+      </c>
+      <c r="I554" t="s">
+        <v>2850</v>
+      </c>
+      <c r="J554" t="s">
         <v>2851</v>
-      </c>
-      <c r="G554" t="s">
-        <v>2852</v>
-      </c>
-      <c r="H554" t="s">
-        <v>2853</v>
-      </c>
-      <c r="I554" t="s">
-        <v>2854</v>
-      </c>
-      <c r="J554" t="s">
-        <v>2855</v>
       </c>
       <c r="K554">
         <v>2006</v>
       </c>
-      <c r="P554" s="8"/>
+      <c r="P554" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="555" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A555" t="s">
         <v>43</v>
       </c>
       <c r="B555" t="s">
-        <v>2856</v>
+        <v>2852</v>
+      </c>
+      <c r="E555" t="s">
+        <v>2482</v>
       </c>
       <c r="G555" t="s">
-        <v>2857</v>
+        <v>2853</v>
       </c>
       <c r="H555" t="s">
-        <v>2858</v>
+        <v>2854</v>
       </c>
       <c r="I555" t="s">
         <v>426</v>
       </c>
       <c r="J555" t="s">
-        <v>2859</v>
+        <v>2855</v>
       </c>
       <c r="K555">
         <v>2019</v>
       </c>
-      <c r="P555" s="8"/>
+      <c r="P555" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="556" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A556" t="s">
         <v>43</v>
       </c>
       <c r="B556" t="s">
+        <v>2856</v>
+      </c>
+      <c r="E556" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G556" t="s">
+        <v>2857</v>
+      </c>
+      <c r="H556" t="s">
+        <v>2858</v>
+      </c>
+      <c r="I556" t="s">
+        <v>2859</v>
+      </c>
+      <c r="J556" t="s">
         <v>2860</v>
-      </c>
-      <c r="G556" t="s">
-        <v>2861</v>
-      </c>
-      <c r="H556" t="s">
-        <v>2862</v>
-      </c>
-      <c r="I556" t="s">
-        <v>2863</v>
-      </c>
-      <c r="J556" t="s">
-        <v>2864</v>
       </c>
       <c r="K556">
         <v>2022</v>
       </c>
-      <c r="P556" s="8"/>
+      <c r="P556" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="557" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A557" t="s">
         <v>43</v>
       </c>
       <c r="B557" t="s">
-        <v>2865</v>
+        <v>2861</v>
+      </c>
+      <c r="E557" t="s">
+        <v>2482</v>
       </c>
       <c r="G557" t="s">
-        <v>2866</v>
+        <v>2862</v>
       </c>
       <c r="H557" t="s">
-        <v>2867</v>
+        <v>2863</v>
       </c>
       <c r="I557" t="s">
         <v>357</v>
       </c>
       <c r="J557" t="s">
-        <v>2868</v>
+        <v>2864</v>
       </c>
       <c r="K557">
         <v>2006</v>
       </c>
-      <c r="P557" s="8"/>
+      <c r="P557" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="558" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A558" t="s">
         <v>43</v>
       </c>
       <c r="B558" t="s">
-        <v>2869</v>
+        <v>2865</v>
+      </c>
+      <c r="E558" t="s">
+        <v>2482</v>
       </c>
       <c r="G558" t="s">
-        <v>2870</v>
+        <v>2866</v>
       </c>
       <c r="H558" t="s">
-        <v>2871</v>
+        <v>2867</v>
       </c>
       <c r="I558" t="s">
         <v>237</v>
       </c>
       <c r="J558" t="s">
-        <v>2872</v>
+        <v>2868</v>
       </c>
       <c r="K558">
         <v>2019</v>
       </c>
-      <c r="P558" s="8"/>
+      <c r="P558" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="559" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A559" t="s">
         <v>43</v>
       </c>
       <c r="B559" t="s">
+        <v>2869</v>
+      </c>
+      <c r="E559" t="s">
+        <v>2482</v>
+      </c>
+      <c r="G559" t="s">
+        <v>2870</v>
+      </c>
+      <c r="H559" t="s">
+        <v>2871</v>
+      </c>
+      <c r="I559" t="s">
+        <v>2872</v>
+      </c>
+      <c r="J559" t="s">
         <v>2873</v>
-      </c>
-      <c r="G559" t="s">
-        <v>2874</v>
-      </c>
-      <c r="H559" t="s">
-        <v>2875</v>
-      </c>
-      <c r="I559" t="s">
-        <v>2876</v>
-      </c>
-      <c r="J559" t="s">
-        <v>2877</v>
       </c>
       <c r="K559">
         <v>2015</v>
       </c>
-      <c r="P559" s="8"/>
+      <c r="P559" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="560" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A560" t="s">
         <v>43</v>
       </c>
       <c r="B560" t="s">
-        <v>2878</v>
+        <v>2874</v>
+      </c>
+      <c r="E560" t="s">
+        <v>2482</v>
       </c>
       <c r="G560" t="s">
-        <v>2879</v>
+        <v>2875</v>
       </c>
       <c r="H560" t="s">
-        <v>2880</v>
+        <v>2876</v>
       </c>
       <c r="I560" t="s">
         <v>1014</v>
       </c>
       <c r="J560" t="s">
-        <v>2881</v>
+        <v>2877</v>
       </c>
       <c r="K560">
         <v>2026</v>
       </c>
-      <c r="P560" s="8"/>
+      <c r="P560" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="561" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A561" t="s">
         <v>43</v>
       </c>
       <c r="B561" t="s">
-        <v>2882</v>
+        <v>2878</v>
       </c>
       <c r="G561" t="s">
-        <v>2883</v>
+        <v>2879</v>
       </c>
       <c r="H561" t="s">
-        <v>2884</v>
+        <v>2880</v>
       </c>
       <c r="I561" t="s">
         <v>51</v>
       </c>
       <c r="J561" t="s">
-        <v>2885</v>
+        <v>2881</v>
       </c>
       <c r="K561">
         <v>2023</v>
@@ -38367,19 +38486,19 @@
         <v>43</v>
       </c>
       <c r="B562" t="s">
-        <v>2886</v>
+        <v>2882</v>
       </c>
       <c r="G562" t="s">
-        <v>2887</v>
+        <v>2883</v>
       </c>
       <c r="H562" t="s">
-        <v>2888</v>
+        <v>2884</v>
       </c>
       <c r="I562" t="s">
         <v>51</v>
       </c>
       <c r="J562" t="s">
-        <v>2889</v>
+        <v>2885</v>
       </c>
       <c r="K562">
         <v>2000</v>
@@ -38391,19 +38510,19 @@
         <v>43</v>
       </c>
       <c r="B563" t="s">
-        <v>2890</v>
+        <v>2886</v>
       </c>
       <c r="G563" t="s">
-        <v>2891</v>
+        <v>2887</v>
       </c>
       <c r="H563" t="s">
-        <v>2892</v>
+        <v>2888</v>
       </c>
       <c r="I563" t="s">
         <v>51</v>
       </c>
       <c r="J563" t="s">
-        <v>2893</v>
+        <v>2889</v>
       </c>
       <c r="K563">
         <v>2016</v>
@@ -38415,19 +38534,19 @@
         <v>43</v>
       </c>
       <c r="B564" t="s">
-        <v>2894</v>
+        <v>2890</v>
       </c>
       <c r="G564" t="s">
-        <v>2895</v>
+        <v>2891</v>
       </c>
       <c r="H564" t="s">
-        <v>2896</v>
+        <v>2892</v>
       </c>
       <c r="I564" t="s">
         <v>1461</v>
       </c>
       <c r="J564" t="s">
-        <v>2897</v>
+        <v>2893</v>
       </c>
       <c r="K564">
         <v>2026</v>
@@ -38439,19 +38558,19 @@
         <v>43</v>
       </c>
       <c r="B565" t="s">
+        <v>2894</v>
+      </c>
+      <c r="G565" t="s">
+        <v>2895</v>
+      </c>
+      <c r="H565" t="s">
+        <v>2896</v>
+      </c>
+      <c r="I565" t="s">
+        <v>2897</v>
+      </c>
+      <c r="J565" t="s">
         <v>2898</v>
-      </c>
-      <c r="G565" t="s">
-        <v>2899</v>
-      </c>
-      <c r="H565" t="s">
-        <v>2900</v>
-      </c>
-      <c r="I565" t="s">
-        <v>2901</v>
-      </c>
-      <c r="J565" t="s">
-        <v>2902</v>
       </c>
       <c r="K565">
         <v>2024</v>
@@ -38463,19 +38582,19 @@
         <v>43</v>
       </c>
       <c r="B566" t="s">
-        <v>2903</v>
+        <v>2899</v>
       </c>
       <c r="G566" t="s">
-        <v>2904</v>
+        <v>2900</v>
       </c>
       <c r="H566" t="s">
-        <v>2905</v>
+        <v>2901</v>
       </c>
       <c r="I566" t="s">
         <v>459</v>
       </c>
       <c r="J566" t="s">
-        <v>2906</v>
+        <v>2902</v>
       </c>
       <c r="K566">
         <v>2019</v>
@@ -38487,19 +38606,19 @@
         <v>43</v>
       </c>
       <c r="B567" t="s">
-        <v>2907</v>
+        <v>2903</v>
       </c>
       <c r="G567" t="s">
-        <v>2908</v>
+        <v>2904</v>
       </c>
       <c r="H567" t="s">
-        <v>2909</v>
+        <v>2905</v>
       </c>
       <c r="I567" t="s">
         <v>915</v>
       </c>
       <c r="J567" t="s">
-        <v>2910</v>
+        <v>2906</v>
       </c>
       <c r="K567">
         <v>2020</v>
@@ -38511,19 +38630,19 @@
         <v>43</v>
       </c>
       <c r="B568" t="s">
+        <v>2907</v>
+      </c>
+      <c r="G568" t="s">
+        <v>2908</v>
+      </c>
+      <c r="H568" t="s">
+        <v>2909</v>
+      </c>
+      <c r="I568" t="s">
+        <v>2910</v>
+      </c>
+      <c r="J568" t="s">
         <v>2911</v>
-      </c>
-      <c r="G568" t="s">
-        <v>2912</v>
-      </c>
-      <c r="H568" t="s">
-        <v>2913</v>
-      </c>
-      <c r="I568" t="s">
-        <v>2914</v>
-      </c>
-      <c r="J568" t="s">
-        <v>2915</v>
       </c>
       <c r="K568">
         <v>2014</v>
@@ -38535,19 +38654,19 @@
         <v>43</v>
       </c>
       <c r="B569" t="s">
-        <v>2916</v>
+        <v>2912</v>
       </c>
       <c r="G569" t="s">
-        <v>2917</v>
+        <v>2913</v>
       </c>
       <c r="H569" t="s">
-        <v>2918</v>
+        <v>2914</v>
       </c>
       <c r="I569" t="s">
         <v>51</v>
       </c>
       <c r="J569" t="s">
-        <v>2919</v>
+        <v>2915</v>
       </c>
       <c r="K569">
         <v>2004</v>
@@ -38559,19 +38678,19 @@
         <v>43</v>
       </c>
       <c r="B570" t="s">
-        <v>2920</v>
+        <v>2916</v>
       </c>
       <c r="G570" t="s">
-        <v>2921</v>
+        <v>2917</v>
       </c>
       <c r="H570" t="s">
-        <v>2922</v>
+        <v>2918</v>
       </c>
       <c r="I570" t="s">
         <v>51</v>
       </c>
       <c r="J570" t="s">
-        <v>2923</v>
+        <v>2919</v>
       </c>
       <c r="K570">
         <v>2015</v>
@@ -38583,19 +38702,19 @@
         <v>43</v>
       </c>
       <c r="B571" t="s">
-        <v>2924</v>
+        <v>2920</v>
       </c>
       <c r="G571" t="s">
-        <v>2925</v>
+        <v>2921</v>
       </c>
       <c r="H571" t="s">
-        <v>2926</v>
+        <v>2922</v>
       </c>
       <c r="I571" t="s">
         <v>979</v>
       </c>
       <c r="J571" t="s">
-        <v>2927</v>
+        <v>2923</v>
       </c>
       <c r="K571">
         <v>2015</v>
@@ -38607,19 +38726,19 @@
         <v>43</v>
       </c>
       <c r="B572" t="s">
+        <v>2924</v>
+      </c>
+      <c r="G572" t="s">
+        <v>2925</v>
+      </c>
+      <c r="H572" t="s">
+        <v>2926</v>
+      </c>
+      <c r="I572" t="s">
+        <v>2927</v>
+      </c>
+      <c r="J572" t="s">
         <v>2928</v>
-      </c>
-      <c r="G572" t="s">
-        <v>2929</v>
-      </c>
-      <c r="H572" t="s">
-        <v>2930</v>
-      </c>
-      <c r="I572" t="s">
-        <v>2931</v>
-      </c>
-      <c r="J572" t="s">
-        <v>2932</v>
       </c>
       <c r="K572">
         <v>2013</v>
@@ -38631,19 +38750,19 @@
         <v>43</v>
       </c>
       <c r="B573" t="s">
-        <v>2933</v>
+        <v>2929</v>
       </c>
       <c r="G573" t="s">
-        <v>2934</v>
+        <v>2930</v>
       </c>
       <c r="H573" t="s">
-        <v>2935</v>
+        <v>2931</v>
       </c>
       <c r="I573" t="s">
         <v>692</v>
       </c>
       <c r="J573" t="s">
-        <v>2936</v>
+        <v>2932</v>
       </c>
       <c r="K573">
         <v>2017</v>
@@ -38655,19 +38774,19 @@
         <v>43</v>
       </c>
       <c r="B574" t="s">
-        <v>2937</v>
+        <v>2933</v>
       </c>
       <c r="G574" t="s">
-        <v>2938</v>
+        <v>2934</v>
       </c>
       <c r="H574" t="s">
-        <v>2939</v>
+        <v>2935</v>
       </c>
       <c r="I574" t="s">
         <v>51</v>
       </c>
       <c r="J574" t="s">
-        <v>2940</v>
+        <v>2936</v>
       </c>
       <c r="K574">
         <v>1995</v>
@@ -38679,19 +38798,19 @@
         <v>43</v>
       </c>
       <c r="B575" t="s">
+        <v>2937</v>
+      </c>
+      <c r="G575" t="s">
+        <v>2938</v>
+      </c>
+      <c r="H575" t="s">
+        <v>2939</v>
+      </c>
+      <c r="I575" t="s">
+        <v>2940</v>
+      </c>
+      <c r="J575" t="s">
         <v>2941</v>
-      </c>
-      <c r="G575" t="s">
-        <v>2942</v>
-      </c>
-      <c r="H575" t="s">
-        <v>2943</v>
-      </c>
-      <c r="I575" t="s">
-        <v>2944</v>
-      </c>
-      <c r="J575" t="s">
-        <v>2945</v>
       </c>
       <c r="K575">
         <v>2019</v>
@@ -38703,19 +38822,19 @@
         <v>43</v>
       </c>
       <c r="B576" t="s">
-        <v>2946</v>
+        <v>2942</v>
       </c>
       <c r="G576" t="s">
-        <v>2947</v>
+        <v>2943</v>
       </c>
       <c r="H576" t="s">
-        <v>2948</v>
+        <v>2944</v>
       </c>
       <c r="I576" t="s">
         <v>723</v>
       </c>
       <c r="J576" t="s">
-        <v>2949</v>
+        <v>2945</v>
       </c>
       <c r="K576">
         <v>2010</v>
@@ -38727,19 +38846,19 @@
         <v>43</v>
       </c>
       <c r="B577" t="s">
-        <v>2950</v>
+        <v>2946</v>
       </c>
       <c r="G577" t="s">
-        <v>2951</v>
+        <v>2947</v>
       </c>
       <c r="H577" t="s">
-        <v>2952</v>
+        <v>2948</v>
       </c>
       <c r="I577" t="s">
         <v>915</v>
       </c>
       <c r="J577" t="s">
-        <v>2953</v>
+        <v>2949</v>
       </c>
       <c r="K577">
         <v>2012</v>
@@ -38751,19 +38870,19 @@
         <v>43</v>
       </c>
       <c r="B578" t="s">
-        <v>2954</v>
+        <v>2950</v>
       </c>
       <c r="G578" t="s">
-        <v>2955</v>
+        <v>2951</v>
       </c>
       <c r="H578" t="s">
-        <v>2956</v>
+        <v>2952</v>
       </c>
       <c r="I578" t="s">
         <v>723</v>
       </c>
       <c r="J578" t="s">
-        <v>2957</v>
+        <v>2953</v>
       </c>
       <c r="K578">
         <v>1979</v>
@@ -38775,19 +38894,19 @@
         <v>43</v>
       </c>
       <c r="B579" t="s">
+        <v>2954</v>
+      </c>
+      <c r="G579" t="s">
+        <v>2955</v>
+      </c>
+      <c r="H579" t="s">
+        <v>2956</v>
+      </c>
+      <c r="I579" t="s">
+        <v>2957</v>
+      </c>
+      <c r="J579" t="s">
         <v>2958</v>
-      </c>
-      <c r="G579" t="s">
-        <v>2959</v>
-      </c>
-      <c r="H579" t="s">
-        <v>2960</v>
-      </c>
-      <c r="I579" t="s">
-        <v>2961</v>
-      </c>
-      <c r="J579" t="s">
-        <v>2962</v>
       </c>
       <c r="K579">
         <v>1980</v>
@@ -38799,19 +38918,19 @@
         <v>43</v>
       </c>
       <c r="B580" t="s">
-        <v>2963</v>
+        <v>2959</v>
       </c>
       <c r="G580" t="s">
-        <v>2964</v>
+        <v>2960</v>
       </c>
       <c r="H580" t="s">
-        <v>2965</v>
+        <v>2961</v>
       </c>
       <c r="I580" t="s">
         <v>253</v>
       </c>
       <c r="J580" t="s">
-        <v>2966</v>
+        <v>2962</v>
       </c>
       <c r="K580">
         <v>1981</v>
@@ -38823,19 +38942,19 @@
         <v>43</v>
       </c>
       <c r="B581" t="s">
-        <v>2967</v>
+        <v>2963</v>
       </c>
       <c r="G581" t="s">
-        <v>2968</v>
+        <v>2964</v>
       </c>
       <c r="H581" t="s">
-        <v>2969</v>
+        <v>2965</v>
       </c>
       <c r="I581" t="s">
         <v>723</v>
       </c>
       <c r="J581" t="s">
-        <v>2966</v>
+        <v>2962</v>
       </c>
       <c r="K581">
         <v>1981</v>
@@ -38847,19 +38966,19 @@
         <v>43</v>
       </c>
       <c r="B582" t="s">
-        <v>2970</v>
+        <v>2966</v>
       </c>
       <c r="G582" t="s">
-        <v>2971</v>
+        <v>2967</v>
       </c>
       <c r="H582" t="s">
-        <v>2972</v>
+        <v>2968</v>
       </c>
       <c r="I582" t="s">
         <v>197</v>
       </c>
       <c r="J582" t="s">
-        <v>2973</v>
+        <v>2969</v>
       </c>
       <c r="K582">
         <v>2023</v>
@@ -38871,19 +38990,19 @@
         <v>43</v>
       </c>
       <c r="B583" t="s">
-        <v>2974</v>
+        <v>2970</v>
       </c>
       <c r="G583" t="s">
-        <v>2975</v>
+        <v>2971</v>
       </c>
       <c r="H583" t="s">
-        <v>2976</v>
+        <v>2972</v>
       </c>
       <c r="I583" t="s">
         <v>2184</v>
       </c>
       <c r="J583" t="s">
-        <v>2977</v>
+        <v>2973</v>
       </c>
       <c r="K583">
         <v>2024</v>
@@ -38895,19 +39014,19 @@
         <v>43</v>
       </c>
       <c r="B584" t="s">
+        <v>2974</v>
+      </c>
+      <c r="G584" t="s">
+        <v>2975</v>
+      </c>
+      <c r="H584" t="s">
+        <v>2976</v>
+      </c>
+      <c r="I584" t="s">
+        <v>2977</v>
+      </c>
+      <c r="J584" t="s">
         <v>2978</v>
-      </c>
-      <c r="G584" t="s">
-        <v>2979</v>
-      </c>
-      <c r="H584" t="s">
-        <v>2980</v>
-      </c>
-      <c r="I584" t="s">
-        <v>2981</v>
-      </c>
-      <c r="J584" t="s">
-        <v>2982</v>
       </c>
       <c r="K584">
         <v>2014</v>
@@ -38919,19 +39038,19 @@
         <v>43</v>
       </c>
       <c r="B585" t="s">
-        <v>2983</v>
+        <v>2979</v>
       </c>
       <c r="G585" t="s">
-        <v>2984</v>
+        <v>2980</v>
       </c>
       <c r="H585" t="s">
-        <v>2985</v>
+        <v>2981</v>
       </c>
       <c r="I585" t="s">
         <v>745</v>
       </c>
       <c r="J585" t="s">
-        <v>2986</v>
+        <v>2982</v>
       </c>
       <c r="K585">
         <v>2015</v>
@@ -38943,19 +39062,19 @@
         <v>43</v>
       </c>
       <c r="B586" t="s">
-        <v>2987</v>
+        <v>2983</v>
       </c>
       <c r="G586" t="s">
-        <v>2988</v>
+        <v>2984</v>
       </c>
       <c r="H586" t="s">
-        <v>2989</v>
+        <v>2985</v>
       </c>
       <c r="I586" t="s">
         <v>2269</v>
       </c>
       <c r="J586" t="s">
-        <v>2990</v>
+        <v>2986</v>
       </c>
       <c r="K586">
         <v>2020</v>
@@ -38967,19 +39086,19 @@
         <v>43</v>
       </c>
       <c r="B587" t="s">
+        <v>2987</v>
+      </c>
+      <c r="G587" t="s">
+        <v>2988</v>
+      </c>
+      <c r="H587" t="s">
+        <v>2989</v>
+      </c>
+      <c r="I587" t="s">
+        <v>2990</v>
+      </c>
+      <c r="J587" t="s">
         <v>2991</v>
-      </c>
-      <c r="G587" t="s">
-        <v>2992</v>
-      </c>
-      <c r="H587" t="s">
-        <v>2993</v>
-      </c>
-      <c r="I587" t="s">
-        <v>2994</v>
-      </c>
-      <c r="J587" t="s">
-        <v>2995</v>
       </c>
       <c r="K587">
         <v>2020</v>
@@ -38991,19 +39110,19 @@
         <v>43</v>
       </c>
       <c r="B588" t="s">
-        <v>2996</v>
+        <v>2992</v>
       </c>
       <c r="G588" t="s">
-        <v>2997</v>
+        <v>2993</v>
       </c>
       <c r="H588" t="s">
-        <v>2998</v>
+        <v>2994</v>
       </c>
       <c r="I588" t="s">
         <v>1359</v>
       </c>
       <c r="J588" t="s">
-        <v>2999</v>
+        <v>2995</v>
       </c>
       <c r="K588">
         <v>2021</v>
@@ -39015,19 +39134,19 @@
         <v>43</v>
       </c>
       <c r="B589" t="s">
-        <v>3000</v>
+        <v>2996</v>
       </c>
       <c r="G589" t="s">
-        <v>3001</v>
+        <v>2997</v>
       </c>
       <c r="H589" t="s">
-        <v>3002</v>
+        <v>2998</v>
       </c>
       <c r="I589" t="s">
         <v>979</v>
       </c>
       <c r="J589" t="s">
-        <v>3003</v>
+        <v>2999</v>
       </c>
       <c r="K589">
         <v>2024</v>
@@ -39039,19 +39158,19 @@
         <v>43</v>
       </c>
       <c r="B590" t="s">
+        <v>3000</v>
+      </c>
+      <c r="G590" t="s">
+        <v>3001</v>
+      </c>
+      <c r="H590" t="s">
+        <v>3002</v>
+      </c>
+      <c r="I590" t="s">
+        <v>3003</v>
+      </c>
+      <c r="J590" t="s">
         <v>3004</v>
-      </c>
-      <c r="G590" t="s">
-        <v>3005</v>
-      </c>
-      <c r="H590" t="s">
-        <v>3006</v>
-      </c>
-      <c r="I590" t="s">
-        <v>3007</v>
-      </c>
-      <c r="J590" t="s">
-        <v>3008</v>
       </c>
       <c r="K590">
         <v>2014</v>
@@ -39063,19 +39182,19 @@
         <v>43</v>
       </c>
       <c r="B591" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G591" t="s">
+        <v>3006</v>
+      </c>
+      <c r="H591" t="s">
+        <v>3007</v>
+      </c>
+      <c r="I591" t="s">
+        <v>3008</v>
+      </c>
+      <c r="J591" t="s">
         <v>3009</v>
-      </c>
-      <c r="G591" t="s">
-        <v>3010</v>
-      </c>
-      <c r="H591" t="s">
-        <v>3011</v>
-      </c>
-      <c r="I591" t="s">
-        <v>3012</v>
-      </c>
-      <c r="J591" t="s">
-        <v>3013</v>
       </c>
       <c r="K591">
         <v>2016</v>
@@ -39087,19 +39206,19 @@
         <v>43</v>
       </c>
       <c r="B592" t="s">
-        <v>3014</v>
+        <v>3010</v>
       </c>
       <c r="G592" t="s">
-        <v>3015</v>
+        <v>3011</v>
       </c>
       <c r="H592" t="s">
-        <v>3016</v>
+        <v>3012</v>
       </c>
       <c r="I592" t="s">
         <v>2184</v>
       </c>
       <c r="J592" t="s">
-        <v>3017</v>
+        <v>3013</v>
       </c>
       <c r="K592">
         <v>2023</v>
@@ -39111,19 +39230,19 @@
         <v>43</v>
       </c>
       <c r="B593" t="s">
-        <v>3018</v>
+        <v>3014</v>
       </c>
       <c r="G593" t="s">
-        <v>3019</v>
+        <v>3015</v>
       </c>
       <c r="H593" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="I593" t="s">
         <v>2043</v>
       </c>
       <c r="J593" t="s">
-        <v>3021</v>
+        <v>3017</v>
       </c>
       <c r="K593">
         <v>2009</v>
@@ -39135,19 +39254,19 @@
         <v>43</v>
       </c>
       <c r="B594" t="s">
-        <v>3022</v>
+        <v>3018</v>
       </c>
       <c r="G594" t="s">
-        <v>3023</v>
+        <v>3019</v>
       </c>
       <c r="H594" t="s">
-        <v>3024</v>
+        <v>3020</v>
       </c>
       <c r="I594" t="s">
         <v>990</v>
       </c>
       <c r="J594" t="s">
-        <v>3025</v>
+        <v>3021</v>
       </c>
       <c r="K594">
         <v>2018</v>
@@ -39159,19 +39278,19 @@
         <v>43</v>
       </c>
       <c r="B595" t="s">
+        <v>3022</v>
+      </c>
+      <c r="G595" t="s">
+        <v>3023</v>
+      </c>
+      <c r="H595" t="s">
+        <v>3024</v>
+      </c>
+      <c r="I595" t="s">
+        <v>3025</v>
+      </c>
+      <c r="J595" t="s">
         <v>3026</v>
-      </c>
-      <c r="G595" t="s">
-        <v>3027</v>
-      </c>
-      <c r="H595" t="s">
-        <v>3028</v>
-      </c>
-      <c r="I595" t="s">
-        <v>3029</v>
-      </c>
-      <c r="J595" t="s">
-        <v>3030</v>
       </c>
       <c r="K595">
         <v>2020</v>
@@ -39183,19 +39302,19 @@
         <v>43</v>
       </c>
       <c r="B596" t="s">
+        <v>3027</v>
+      </c>
+      <c r="G596" t="s">
+        <v>3028</v>
+      </c>
+      <c r="H596" t="s">
+        <v>3029</v>
+      </c>
+      <c r="I596" t="s">
+        <v>3030</v>
+      </c>
+      <c r="J596" t="s">
         <v>3031</v>
-      </c>
-      <c r="G596" t="s">
-        <v>3032</v>
-      </c>
-      <c r="H596" t="s">
-        <v>3033</v>
-      </c>
-      <c r="I596" t="s">
-        <v>3034</v>
-      </c>
-      <c r="J596" t="s">
-        <v>3035</v>
       </c>
       <c r="K596">
         <v>2002</v>
@@ -39207,19 +39326,19 @@
         <v>43</v>
       </c>
       <c r="B597" t="s">
-        <v>3036</v>
+        <v>3032</v>
       </c>
       <c r="G597" t="s">
-        <v>3037</v>
+        <v>3033</v>
       </c>
       <c r="H597" t="s">
-        <v>3038</v>
+        <v>3034</v>
       </c>
       <c r="I597" t="s">
         <v>51</v>
       </c>
       <c r="J597" t="s">
-        <v>3039</v>
+        <v>3035</v>
       </c>
       <c r="K597">
         <v>1994</v>
@@ -39231,19 +39350,19 @@
         <v>43</v>
       </c>
       <c r="B598" t="s">
-        <v>3040</v>
+        <v>3036</v>
       </c>
       <c r="G598" t="s">
-        <v>3041</v>
+        <v>3037</v>
       </c>
       <c r="H598" t="s">
-        <v>3042</v>
+        <v>3038</v>
       </c>
       <c r="I598" t="s">
         <v>1308</v>
       </c>
       <c r="J598" t="s">
-        <v>3043</v>
+        <v>3039</v>
       </c>
       <c r="K598">
         <v>2021</v>
@@ -39255,19 +39374,19 @@
         <v>43</v>
       </c>
       <c r="B599" t="s">
-        <v>3044</v>
+        <v>3040</v>
       </c>
       <c r="G599" t="s">
-        <v>3045</v>
+        <v>3041</v>
       </c>
       <c r="H599" t="s">
-        <v>3046</v>
+        <v>3042</v>
       </c>
       <c r="I599" t="s">
         <v>1652</v>
       </c>
       <c r="J599" t="s">
-        <v>3047</v>
+        <v>3043</v>
       </c>
       <c r="K599">
         <v>2025</v>
@@ -39279,19 +39398,19 @@
         <v>43</v>
       </c>
       <c r="B600" t="s">
-        <v>3048</v>
+        <v>3044</v>
       </c>
       <c r="G600" t="s">
-        <v>3049</v>
+        <v>3045</v>
       </c>
       <c r="H600" t="s">
-        <v>3050</v>
+        <v>3046</v>
       </c>
       <c r="I600" t="s">
         <v>51</v>
       </c>
       <c r="J600" t="s">
-        <v>3051</v>
+        <v>3047</v>
       </c>
       <c r="K600">
         <v>2021</v>
@@ -39303,19 +39422,19 @@
         <v>43</v>
       </c>
       <c r="B601" t="s">
-        <v>3052</v>
+        <v>3048</v>
       </c>
       <c r="G601" t="s">
-        <v>3053</v>
+        <v>3049</v>
       </c>
       <c r="H601" t="s">
-        <v>3054</v>
+        <v>3050</v>
       </c>
       <c r="I601" t="s">
-        <v>3012</v>
+        <v>3008</v>
       </c>
       <c r="J601" t="s">
-        <v>3055</v>
+        <v>3051</v>
       </c>
       <c r="K601">
         <v>2024</v>
@@ -39327,19 +39446,19 @@
         <v>43</v>
       </c>
       <c r="B602" t="s">
-        <v>3056</v>
+        <v>3052</v>
       </c>
       <c r="G602" t="s">
-        <v>3057</v>
+        <v>3053</v>
       </c>
       <c r="H602" t="s">
-        <v>3058</v>
+        <v>3054</v>
       </c>
       <c r="I602" t="s">
-        <v>2901</v>
+        <v>2897</v>
       </c>
       <c r="J602" t="s">
-        <v>3059</v>
+        <v>3055</v>
       </c>
       <c r="K602">
         <v>2024</v>
@@ -39351,19 +39470,19 @@
         <v>43</v>
       </c>
       <c r="B603" t="s">
+        <v>3056</v>
+      </c>
+      <c r="G603" t="s">
+        <v>3057</v>
+      </c>
+      <c r="H603" t="s">
+        <v>3058</v>
+      </c>
+      <c r="I603" t="s">
+        <v>3059</v>
+      </c>
+      <c r="J603" t="s">
         <v>3060</v>
-      </c>
-      <c r="G603" t="s">
-        <v>3061</v>
-      </c>
-      <c r="H603" t="s">
-        <v>3062</v>
-      </c>
-      <c r="I603" t="s">
-        <v>3063</v>
-      </c>
-      <c r="J603" t="s">
-        <v>3064</v>
       </c>
       <c r="K603">
         <v>2018</v>
@@ -39375,19 +39494,19 @@
         <v>43</v>
       </c>
       <c r="B604" t="s">
-        <v>3065</v>
+        <v>3061</v>
       </c>
       <c r="G604" t="s">
-        <v>3066</v>
+        <v>3062</v>
       </c>
       <c r="H604" t="s">
-        <v>3067</v>
+        <v>3063</v>
       </c>
       <c r="I604" t="s">
         <v>100</v>
       </c>
       <c r="J604" t="s">
-        <v>3068</v>
+        <v>3064</v>
       </c>
       <c r="K604">
         <v>2014</v>
@@ -39399,19 +39518,19 @@
         <v>43</v>
       </c>
       <c r="B605" t="s">
-        <v>3069</v>
+        <v>3065</v>
       </c>
       <c r="G605" t="s">
-        <v>3070</v>
+        <v>3066</v>
       </c>
       <c r="H605" t="s">
-        <v>3071</v>
+        <v>3067</v>
       </c>
       <c r="I605" t="s">
         <v>1924</v>
       </c>
       <c r="J605" t="s">
-        <v>3072</v>
+        <v>3068</v>
       </c>
       <c r="K605">
         <v>2019</v>
@@ -39423,19 +39542,19 @@
         <v>43</v>
       </c>
       <c r="B606" t="s">
+        <v>3069</v>
+      </c>
+      <c r="G606" t="s">
+        <v>3070</v>
+      </c>
+      <c r="H606" t="s">
+        <v>3071</v>
+      </c>
+      <c r="I606" t="s">
+        <v>3072</v>
+      </c>
+      <c r="J606" t="s">
         <v>3073</v>
-      </c>
-      <c r="G606" t="s">
-        <v>3074</v>
-      </c>
-      <c r="H606" t="s">
-        <v>3075</v>
-      </c>
-      <c r="I606" t="s">
-        <v>3076</v>
-      </c>
-      <c r="J606" t="s">
-        <v>3077</v>
       </c>
       <c r="K606">
         <v>2024</v>
@@ -39447,19 +39566,19 @@
         <v>43</v>
       </c>
       <c r="B607" t="s">
-        <v>3078</v>
+        <v>3074</v>
       </c>
       <c r="G607" t="s">
-        <v>3079</v>
+        <v>3075</v>
       </c>
       <c r="H607" t="s">
-        <v>3080</v>
+        <v>3076</v>
       </c>
       <c r="I607" t="s">
         <v>1520</v>
       </c>
       <c r="J607" t="s">
-        <v>3081</v>
+        <v>3077</v>
       </c>
       <c r="K607">
         <v>2024</v>
@@ -39471,19 +39590,19 @@
         <v>43</v>
       </c>
       <c r="B608" t="s">
-        <v>3082</v>
+        <v>3078</v>
       </c>
       <c r="G608" t="s">
-        <v>3083</v>
+        <v>3079</v>
       </c>
       <c r="H608" t="s">
-        <v>3084</v>
+        <v>3080</v>
       </c>
       <c r="I608" t="s">
         <v>1520</v>
       </c>
       <c r="J608" t="s">
-        <v>3085</v>
+        <v>3081</v>
       </c>
       <c r="K608">
         <v>2021</v>
@@ -39495,19 +39614,19 @@
         <v>43</v>
       </c>
       <c r="B609" t="s">
+        <v>3082</v>
+      </c>
+      <c r="G609" t="s">
+        <v>3083</v>
+      </c>
+      <c r="H609" t="s">
+        <v>3084</v>
+      </c>
+      <c r="I609" t="s">
+        <v>3085</v>
+      </c>
+      <c r="J609" t="s">
         <v>3086</v>
-      </c>
-      <c r="G609" t="s">
-        <v>3087</v>
-      </c>
-      <c r="H609" t="s">
-        <v>3088</v>
-      </c>
-      <c r="I609" t="s">
-        <v>3089</v>
-      </c>
-      <c r="J609" t="s">
-        <v>3090</v>
       </c>
       <c r="K609">
         <v>2022</v>
@@ -39519,19 +39638,19 @@
         <v>43</v>
       </c>
       <c r="B610" t="s">
-        <v>3091</v>
+        <v>3087</v>
       </c>
       <c r="G610" t="s">
-        <v>3092</v>
+        <v>3088</v>
       </c>
       <c r="H610" t="s">
-        <v>3093</v>
+        <v>3089</v>
       </c>
       <c r="I610" t="s">
         <v>226</v>
       </c>
       <c r="J610" t="s">
-        <v>3094</v>
+        <v>3090</v>
       </c>
       <c r="K610">
         <v>2020</v>
@@ -39543,19 +39662,19 @@
         <v>43</v>
       </c>
       <c r="B611" t="s">
-        <v>3095</v>
+        <v>3091</v>
       </c>
       <c r="G611" t="s">
-        <v>3096</v>
+        <v>3092</v>
       </c>
       <c r="H611" t="s">
-        <v>3097</v>
+        <v>3093</v>
       </c>
       <c r="I611" t="s">
         <v>226</v>
       </c>
       <c r="J611" t="s">
-        <v>3094</v>
+        <v>3090</v>
       </c>
       <c r="K611">
         <v>2023</v>
@@ -39567,19 +39686,19 @@
         <v>43</v>
       </c>
       <c r="B612" t="s">
+        <v>3094</v>
+      </c>
+      <c r="G612" t="s">
+        <v>3095</v>
+      </c>
+      <c r="H612" t="s">
+        <v>3096</v>
+      </c>
+      <c r="I612" t="s">
+        <v>3097</v>
+      </c>
+      <c r="J612" t="s">
         <v>3098</v>
-      </c>
-      <c r="G612" t="s">
-        <v>3099</v>
-      </c>
-      <c r="H612" t="s">
-        <v>3100</v>
-      </c>
-      <c r="I612" t="s">
-        <v>3101</v>
-      </c>
-      <c r="J612" t="s">
-        <v>3102</v>
       </c>
       <c r="K612">
         <v>2023</v>
@@ -39591,19 +39710,19 @@
         <v>43</v>
       </c>
       <c r="B613" t="s">
-        <v>3103</v>
+        <v>3099</v>
       </c>
       <c r="G613" t="s">
-        <v>3104</v>
+        <v>3100</v>
       </c>
       <c r="H613" t="s">
-        <v>3105</v>
+        <v>3101</v>
       </c>
       <c r="I613" t="s">
         <v>1414</v>
       </c>
       <c r="J613" t="s">
-        <v>3106</v>
+        <v>3102</v>
       </c>
       <c r="K613">
         <v>2023</v>
@@ -39615,19 +39734,19 @@
         <v>43</v>
       </c>
       <c r="B614" t="s">
-        <v>3107</v>
+        <v>3103</v>
       </c>
       <c r="G614" t="s">
-        <v>3108</v>
+        <v>3104</v>
       </c>
       <c r="H614" t="s">
-        <v>3109</v>
+        <v>3105</v>
       </c>
       <c r="I614" t="s">
         <v>409</v>
       </c>
       <c r="J614" t="s">
-        <v>3110</v>
+        <v>3106</v>
       </c>
       <c r="K614">
         <v>2022</v>
@@ -39639,19 +39758,19 @@
         <v>43</v>
       </c>
       <c r="B615" t="s">
+        <v>3107</v>
+      </c>
+      <c r="G615" t="s">
+        <v>3108</v>
+      </c>
+      <c r="H615" t="s">
+        <v>3109</v>
+      </c>
+      <c r="I615" t="s">
+        <v>3110</v>
+      </c>
+      <c r="J615" t="s">
         <v>3111</v>
-      </c>
-      <c r="G615" t="s">
-        <v>3112</v>
-      </c>
-      <c r="H615" t="s">
-        <v>3113</v>
-      </c>
-      <c r="I615" t="s">
-        <v>3114</v>
-      </c>
-      <c r="J615" t="s">
-        <v>3115</v>
       </c>
       <c r="K615">
         <v>2022</v>
@@ -39663,19 +39782,19 @@
         <v>43</v>
       </c>
       <c r="B616" t="s">
-        <v>3116</v>
+        <v>3112</v>
       </c>
       <c r="G616" t="s">
-        <v>3117</v>
+        <v>3113</v>
       </c>
       <c r="H616" t="s">
-        <v>3118</v>
+        <v>3114</v>
       </c>
       <c r="I616" t="s">
         <v>2275</v>
       </c>
       <c r="J616" t="s">
-        <v>3119</v>
+        <v>3115</v>
       </c>
       <c r="K616">
         <v>2019</v>
@@ -39687,19 +39806,19 @@
         <v>43</v>
       </c>
       <c r="B617" t="s">
+        <v>3116</v>
+      </c>
+      <c r="G617" t="s">
+        <v>3117</v>
+      </c>
+      <c r="H617" t="s">
+        <v>3118</v>
+      </c>
+      <c r="I617" t="s">
+        <v>3119</v>
+      </c>
+      <c r="J617" t="s">
         <v>3120</v>
-      </c>
-      <c r="G617" t="s">
-        <v>3121</v>
-      </c>
-      <c r="H617" t="s">
-        <v>3122</v>
-      </c>
-      <c r="I617" t="s">
-        <v>3123</v>
-      </c>
-      <c r="J617" t="s">
-        <v>3124</v>
       </c>
       <c r="K617">
         <v>2024</v>
@@ -39711,19 +39830,19 @@
         <v>43</v>
       </c>
       <c r="B618" t="s">
-        <v>3125</v>
+        <v>3121</v>
       </c>
       <c r="G618" t="s">
-        <v>3126</v>
+        <v>3122</v>
       </c>
       <c r="H618" t="s">
-        <v>3127</v>
+        <v>3123</v>
       </c>
       <c r="I618" t="s">
         <v>295</v>
       </c>
       <c r="J618" t="s">
-        <v>3128</v>
+        <v>3124</v>
       </c>
       <c r="K618">
         <v>2022</v>
@@ -39735,19 +39854,19 @@
         <v>43</v>
       </c>
       <c r="B619" t="s">
-        <v>3129</v>
+        <v>3125</v>
       </c>
       <c r="G619" t="s">
-        <v>3130</v>
+        <v>3126</v>
       </c>
       <c r="H619" t="s">
-        <v>3131</v>
+        <v>3127</v>
       </c>
       <c r="I619" t="s">
         <v>915</v>
       </c>
       <c r="J619" t="s">
-        <v>3132</v>
+        <v>3128</v>
       </c>
       <c r="K619">
         <v>1995</v>
@@ -39759,19 +39878,19 @@
         <v>43</v>
       </c>
       <c r="B620" t="s">
+        <v>3129</v>
+      </c>
+      <c r="G620" t="s">
+        <v>3130</v>
+      </c>
+      <c r="H620" t="s">
+        <v>3131</v>
+      </c>
+      <c r="I620" t="s">
+        <v>3132</v>
+      </c>
+      <c r="J620" t="s">
         <v>3133</v>
-      </c>
-      <c r="G620" t="s">
-        <v>3134</v>
-      </c>
-      <c r="H620" t="s">
-        <v>3135</v>
-      </c>
-      <c r="I620" t="s">
-        <v>3136</v>
-      </c>
-      <c r="J620" t="s">
-        <v>3137</v>
       </c>
       <c r="K620">
         <v>1992</v>
@@ -39783,19 +39902,19 @@
         <v>43</v>
       </c>
       <c r="B621" t="s">
+        <v>3134</v>
+      </c>
+      <c r="G621" t="s">
+        <v>3135</v>
+      </c>
+      <c r="H621" t="s">
+        <v>3136</v>
+      </c>
+      <c r="I621" t="s">
+        <v>3137</v>
+      </c>
+      <c r="J621" t="s">
         <v>3138</v>
-      </c>
-      <c r="G621" t="s">
-        <v>3139</v>
-      </c>
-      <c r="H621" t="s">
-        <v>3140</v>
-      </c>
-      <c r="I621" t="s">
-        <v>3141</v>
-      </c>
-      <c r="J621" t="s">
-        <v>3142</v>
       </c>
       <c r="K621">
         <v>2021</v>
@@ -39807,19 +39926,19 @@
         <v>43</v>
       </c>
       <c r="B622" t="s">
-        <v>3143</v>
+        <v>3139</v>
       </c>
       <c r="G622" t="s">
-        <v>3144</v>
+        <v>3140</v>
       </c>
       <c r="H622" t="s">
-        <v>3145</v>
+        <v>3141</v>
       </c>
       <c r="I622" t="s">
         <v>973</v>
       </c>
       <c r="J622" t="s">
-        <v>3146</v>
+        <v>3142</v>
       </c>
       <c r="K622">
         <v>2018</v>
@@ -39831,19 +39950,19 @@
         <v>43</v>
       </c>
       <c r="B623" t="s">
+        <v>3143</v>
+      </c>
+      <c r="G623" t="s">
+        <v>3144</v>
+      </c>
+      <c r="H623" t="s">
+        <v>3145</v>
+      </c>
+      <c r="I623" t="s">
+        <v>3146</v>
+      </c>
+      <c r="J623" t="s">
         <v>3147</v>
-      </c>
-      <c r="G623" t="s">
-        <v>3148</v>
-      </c>
-      <c r="H623" t="s">
-        <v>3149</v>
-      </c>
-      <c r="I623" t="s">
-        <v>3150</v>
-      </c>
-      <c r="J623" t="s">
-        <v>3151</v>
       </c>
       <c r="K623">
         <v>2019</v>
@@ -39855,19 +39974,19 @@
         <v>43</v>
       </c>
       <c r="B624" t="s">
-        <v>3152</v>
+        <v>3148</v>
       </c>
       <c r="G624" t="s">
-        <v>3153</v>
+        <v>3149</v>
       </c>
       <c r="H624" t="s">
-        <v>3154</v>
+        <v>3150</v>
       </c>
       <c r="I624" t="s">
         <v>1652</v>
       </c>
       <c r="J624" t="s">
-        <v>3155</v>
+        <v>3151</v>
       </c>
       <c r="K624">
         <v>2016</v>
@@ -39879,19 +39998,19 @@
         <v>43</v>
       </c>
       <c r="B625" t="s">
-        <v>3156</v>
+        <v>3152</v>
       </c>
       <c r="G625" t="s">
-        <v>3157</v>
+        <v>3153</v>
       </c>
       <c r="H625" t="s">
-        <v>3158</v>
+        <v>3154</v>
       </c>
       <c r="I625" t="s">
         <v>1242</v>
       </c>
       <c r="J625" t="s">
-        <v>3159</v>
+        <v>3155</v>
       </c>
       <c r="K625">
         <v>2002</v>
@@ -39903,19 +40022,19 @@
         <v>43</v>
       </c>
       <c r="B626" t="s">
+        <v>3156</v>
+      </c>
+      <c r="G626" t="s">
+        <v>3157</v>
+      </c>
+      <c r="H626" t="s">
+        <v>3158</v>
+      </c>
+      <c r="I626" t="s">
+        <v>3159</v>
+      </c>
+      <c r="J626" t="s">
         <v>3160</v>
-      </c>
-      <c r="G626" t="s">
-        <v>3161</v>
-      </c>
-      <c r="H626" t="s">
-        <v>3162</v>
-      </c>
-      <c r="I626" t="s">
-        <v>3163</v>
-      </c>
-      <c r="J626" t="s">
-        <v>3164</v>
       </c>
       <c r="K626">
         <v>2018</v>
@@ -39927,19 +40046,19 @@
         <v>43</v>
       </c>
       <c r="B627" t="s">
-        <v>3165</v>
+        <v>3161</v>
       </c>
       <c r="G627" t="s">
-        <v>3166</v>
+        <v>3162</v>
       </c>
       <c r="H627" t="s">
-        <v>3167</v>
+        <v>3163</v>
       </c>
       <c r="I627" t="s">
         <v>128</v>
       </c>
       <c r="J627" t="s">
-        <v>3168</v>
+        <v>3164</v>
       </c>
       <c r="K627">
         <v>2016</v>
@@ -39951,19 +40070,19 @@
         <v>43</v>
       </c>
       <c r="B628" t="s">
-        <v>3169</v>
+        <v>3165</v>
       </c>
       <c r="G628" t="s">
-        <v>3170</v>
+        <v>3166</v>
       </c>
       <c r="H628" t="s">
-        <v>3171</v>
+        <v>3167</v>
       </c>
       <c r="I628" t="s">
         <v>915</v>
       </c>
       <c r="J628" t="s">
-        <v>3172</v>
+        <v>3168</v>
       </c>
       <c r="K628">
         <v>2004</v>
@@ -39975,19 +40094,19 @@
         <v>43</v>
       </c>
       <c r="B629" t="s">
-        <v>3173</v>
+        <v>3169</v>
       </c>
       <c r="G629" t="s">
-        <v>3174</v>
+        <v>3170</v>
       </c>
       <c r="H629" t="s">
-        <v>3175</v>
+        <v>3171</v>
       </c>
       <c r="I629" t="s">
         <v>1652</v>
       </c>
       <c r="J629" t="s">
-        <v>3176</v>
+        <v>3172</v>
       </c>
       <c r="K629">
         <v>2008</v>
@@ -39999,19 +40118,19 @@
         <v>43</v>
       </c>
       <c r="B630" t="s">
-        <v>3177</v>
+        <v>3173</v>
       </c>
       <c r="G630" t="s">
-        <v>3178</v>
+        <v>3174</v>
       </c>
       <c r="H630" t="s">
-        <v>3179</v>
+        <v>3175</v>
       </c>
       <c r="I630" t="s">
         <v>692</v>
       </c>
       <c r="J630" t="s">
-        <v>3180</v>
+        <v>3176</v>
       </c>
       <c r="K630">
         <v>2014</v>
@@ -40023,19 +40142,19 @@
         <v>43</v>
       </c>
       <c r="B631" t="s">
-        <v>3181</v>
+        <v>3177</v>
       </c>
       <c r="G631" t="s">
-        <v>3182</v>
+        <v>3178</v>
       </c>
       <c r="H631" t="s">
-        <v>3183</v>
+        <v>3179</v>
       </c>
       <c r="I631" t="s">
-        <v>2849</v>
+        <v>2845</v>
       </c>
       <c r="J631" t="s">
-        <v>3184</v>
+        <v>3180</v>
       </c>
       <c r="K631">
         <v>2004</v>
@@ -40047,19 +40166,19 @@
         <v>43</v>
       </c>
       <c r="B632" t="s">
+        <v>3181</v>
+      </c>
+      <c r="G632" t="s">
+        <v>3182</v>
+      </c>
+      <c r="H632" t="s">
+        <v>3183</v>
+      </c>
+      <c r="I632" t="s">
+        <v>3184</v>
+      </c>
+      <c r="J632" t="s">
         <v>3185</v>
-      </c>
-      <c r="G632" t="s">
-        <v>3186</v>
-      </c>
-      <c r="H632" t="s">
-        <v>3187</v>
-      </c>
-      <c r="I632" t="s">
-        <v>3188</v>
-      </c>
-      <c r="J632" t="s">
-        <v>3189</v>
       </c>
       <c r="K632">
         <v>1994</v>
@@ -40071,19 +40190,19 @@
         <v>43</v>
       </c>
       <c r="B633" t="s">
+        <v>3186</v>
+      </c>
+      <c r="G633" t="s">
+        <v>3187</v>
+      </c>
+      <c r="H633" t="s">
+        <v>3188</v>
+      </c>
+      <c r="I633" t="s">
+        <v>3189</v>
+      </c>
+      <c r="J633" t="s">
         <v>3190</v>
-      </c>
-      <c r="G633" t="s">
-        <v>3191</v>
-      </c>
-      <c r="H633" t="s">
-        <v>3192</v>
-      </c>
-      <c r="I633" t="s">
-        <v>3193</v>
-      </c>
-      <c r="J633" t="s">
-        <v>3194</v>
       </c>
       <c r="K633">
         <v>2010</v>
@@ -40095,19 +40214,19 @@
         <v>43</v>
       </c>
       <c r="B634" t="s">
-        <v>3195</v>
+        <v>3191</v>
       </c>
       <c r="G634" t="s">
-        <v>3196</v>
+        <v>3192</v>
       </c>
       <c r="H634" t="s">
-        <v>3197</v>
+        <v>3193</v>
       </c>
       <c r="I634" t="s">
         <v>226</v>
       </c>
       <c r="J634" t="s">
-        <v>3198</v>
+        <v>3194</v>
       </c>
       <c r="K634">
         <v>2025</v>
@@ -40119,19 +40238,19 @@
         <v>43</v>
       </c>
       <c r="B635" t="s">
-        <v>3199</v>
+        <v>3195</v>
       </c>
       <c r="G635" t="s">
-        <v>3200</v>
+        <v>3196</v>
       </c>
       <c r="H635" t="s">
-        <v>3201</v>
+        <v>3197</v>
       </c>
       <c r="I635" t="s">
         <v>825</v>
       </c>
       <c r="J635" t="s">
-        <v>3202</v>
+        <v>3198</v>
       </c>
       <c r="K635">
         <v>2020</v>
@@ -40143,19 +40262,19 @@
         <v>43</v>
       </c>
       <c r="B636" t="s">
+        <v>3199</v>
+      </c>
+      <c r="G636" t="s">
+        <v>3200</v>
+      </c>
+      <c r="H636" t="s">
+        <v>3201</v>
+      </c>
+      <c r="I636" t="s">
+        <v>3202</v>
+      </c>
+      <c r="J636" t="s">
         <v>3203</v>
-      </c>
-      <c r="G636" t="s">
-        <v>3204</v>
-      </c>
-      <c r="H636" t="s">
-        <v>3205</v>
-      </c>
-      <c r="I636" t="s">
-        <v>3206</v>
-      </c>
-      <c r="J636" t="s">
-        <v>3207</v>
       </c>
       <c r="K636">
         <v>2017</v>
@@ -40167,19 +40286,19 @@
         <v>43</v>
       </c>
       <c r="B637" t="s">
-        <v>3208</v>
+        <v>3204</v>
       </c>
       <c r="G637" t="s">
-        <v>3209</v>
+        <v>3205</v>
       </c>
       <c r="H637" t="s">
-        <v>3210</v>
+        <v>3206</v>
       </c>
       <c r="I637" t="s">
         <v>295</v>
       </c>
       <c r="J637" t="s">
-        <v>3211</v>
+        <v>3207</v>
       </c>
       <c r="K637">
         <v>2025</v>
@@ -40191,19 +40310,19 @@
         <v>43</v>
       </c>
       <c r="B638" t="s">
-        <v>3212</v>
+        <v>3208</v>
       </c>
       <c r="G638" t="s">
-        <v>3213</v>
+        <v>3209</v>
       </c>
       <c r="H638" t="s">
-        <v>3214</v>
+        <v>3210</v>
       </c>
       <c r="I638" t="s">
         <v>295</v>
       </c>
       <c r="J638" t="s">
-        <v>3215</v>
+        <v>3211</v>
       </c>
       <c r="K638">
         <v>2023</v>
@@ -40215,19 +40334,19 @@
         <v>43</v>
       </c>
       <c r="B639" t="s">
+        <v>3212</v>
+      </c>
+      <c r="G639" t="s">
+        <v>3213</v>
+      </c>
+      <c r="H639" t="s">
+        <v>3214</v>
+      </c>
+      <c r="I639" t="s">
+        <v>3215</v>
+      </c>
+      <c r="J639" t="s">
         <v>3216</v>
-      </c>
-      <c r="G639" t="s">
-        <v>3217</v>
-      </c>
-      <c r="H639" t="s">
-        <v>3218</v>
-      </c>
-      <c r="I639" t="s">
-        <v>3219</v>
-      </c>
-      <c r="J639" t="s">
-        <v>3220</v>
       </c>
       <c r="K639">
         <v>2009</v>
@@ -40239,19 +40358,19 @@
         <v>43</v>
       </c>
       <c r="B640" t="s">
-        <v>3221</v>
+        <v>3217</v>
       </c>
       <c r="G640" t="s">
-        <v>3222</v>
+        <v>3218</v>
       </c>
       <c r="H640" t="s">
-        <v>3223</v>
+        <v>3219</v>
       </c>
       <c r="I640" t="s">
         <v>226</v>
       </c>
       <c r="J640" t="s">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="K640">
         <v>2024</v>
@@ -40263,19 +40382,19 @@
         <v>43</v>
       </c>
       <c r="B641" t="s">
-        <v>3225</v>
+        <v>3221</v>
       </c>
       <c r="G641" t="s">
-        <v>3226</v>
+        <v>3222</v>
       </c>
       <c r="H641" t="s">
-        <v>3227</v>
+        <v>3223</v>
       </c>
       <c r="I641" t="s">
         <v>1548</v>
       </c>
       <c r="J641" t="s">
-        <v>3228</v>
+        <v>3224</v>
       </c>
       <c r="K641">
         <v>2024</v>
@@ -40287,19 +40406,19 @@
         <v>43</v>
       </c>
       <c r="B642" t="s">
-        <v>3229</v>
+        <v>3225</v>
       </c>
       <c r="G642" t="s">
-        <v>3230</v>
+        <v>3226</v>
       </c>
       <c r="H642" t="s">
-        <v>3231</v>
+        <v>3227</v>
       </c>
       <c r="I642" t="s">
         <v>549</v>
       </c>
       <c r="J642" t="s">
-        <v>3232</v>
+        <v>3228</v>
       </c>
       <c r="K642">
         <v>2020</v>
@@ -40311,19 +40430,19 @@
         <v>43</v>
       </c>
       <c r="B643" t="s">
-        <v>3233</v>
+        <v>3229</v>
       </c>
       <c r="G643" t="s">
-        <v>3234</v>
+        <v>3230</v>
       </c>
       <c r="H643" t="s">
-        <v>3235</v>
+        <v>3231</v>
       </c>
       <c r="I643" t="s">
         <v>148</v>
       </c>
       <c r="J643" t="s">
-        <v>3236</v>
+        <v>3232</v>
       </c>
       <c r="K643">
         <v>2020</v>
@@ -40335,19 +40454,19 @@
         <v>43</v>
       </c>
       <c r="B644" t="s">
+        <v>3233</v>
+      </c>
+      <c r="G644" t="s">
+        <v>3234</v>
+      </c>
+      <c r="H644" t="s">
+        <v>3235</v>
+      </c>
+      <c r="I644" t="s">
+        <v>3236</v>
+      </c>
+      <c r="J644" t="s">
         <v>3237</v>
-      </c>
-      <c r="G644" t="s">
-        <v>3238</v>
-      </c>
-      <c r="H644" t="s">
-        <v>3239</v>
-      </c>
-      <c r="I644" t="s">
-        <v>3240</v>
-      </c>
-      <c r="J644" t="s">
-        <v>3241</v>
       </c>
       <c r="K644">
         <v>2021</v>
@@ -40359,19 +40478,19 @@
         <v>43</v>
       </c>
       <c r="B645" t="s">
-        <v>3242</v>
+        <v>3238</v>
       </c>
       <c r="G645" t="s">
-        <v>3243</v>
+        <v>3239</v>
       </c>
       <c r="H645" t="s">
-        <v>3244</v>
+        <v>3240</v>
       </c>
       <c r="I645" t="s">
         <v>1308</v>
       </c>
       <c r="J645" t="s">
-        <v>3245</v>
+        <v>3241</v>
       </c>
       <c r="K645">
         <v>2024</v>
@@ -40383,19 +40502,19 @@
         <v>43</v>
       </c>
       <c r="B646" t="s">
-        <v>3246</v>
+        <v>3242</v>
       </c>
       <c r="G646" t="s">
-        <v>3247</v>
+        <v>3243</v>
       </c>
       <c r="H646" t="s">
-        <v>3248</v>
+        <v>3244</v>
       </c>
       <c r="I646" t="s">
         <v>2314</v>
       </c>
       <c r="J646" t="s">
-        <v>3249</v>
+        <v>3245</v>
       </c>
       <c r="K646">
         <v>2024</v>
@@ -40407,19 +40526,19 @@
         <v>43</v>
       </c>
       <c r="B647" t="s">
-        <v>3250</v>
+        <v>3246</v>
       </c>
       <c r="G647" t="s">
-        <v>3251</v>
+        <v>3247</v>
       </c>
       <c r="H647" t="s">
-        <v>3252</v>
+        <v>3248</v>
       </c>
       <c r="I647" t="s">
         <v>295</v>
       </c>
       <c r="J647" t="s">
-        <v>3253</v>
+        <v>3249</v>
       </c>
       <c r="K647">
         <v>2021</v>
@@ -40431,19 +40550,19 @@
         <v>43</v>
       </c>
       <c r="B648" t="s">
-        <v>3254</v>
+        <v>3250</v>
       </c>
       <c r="G648" t="s">
-        <v>3255</v>
+        <v>3251</v>
       </c>
       <c r="H648" t="s">
-        <v>3256</v>
+        <v>3252</v>
       </c>
       <c r="I648" t="s">
         <v>1652</v>
       </c>
       <c r="J648" t="s">
-        <v>3257</v>
+        <v>3253</v>
       </c>
       <c r="K648">
         <v>2022</v>
@@ -40455,19 +40574,19 @@
         <v>43</v>
       </c>
       <c r="B649" t="s">
-        <v>3258</v>
+        <v>3254</v>
       </c>
       <c r="G649" t="s">
-        <v>3259</v>
+        <v>3255</v>
       </c>
       <c r="H649" t="s">
-        <v>3260</v>
+        <v>3256</v>
       </c>
       <c r="I649" t="s">
         <v>409</v>
       </c>
       <c r="J649" t="s">
-        <v>3261</v>
+        <v>3257</v>
       </c>
       <c r="K649">
         <v>2022</v>
@@ -40479,19 +40598,19 @@
         <v>43</v>
       </c>
       <c r="B650" t="s">
-        <v>3262</v>
+        <v>3258</v>
       </c>
       <c r="G650" t="s">
-        <v>3263</v>
+        <v>3259</v>
       </c>
       <c r="H650" t="s">
-        <v>3264</v>
+        <v>3260</v>
       </c>
       <c r="I650" t="s">
-        <v>2700</v>
+        <v>2696</v>
       </c>
       <c r="J650" t="s">
-        <v>3265</v>
+        <v>3261</v>
       </c>
       <c r="K650">
         <v>2026</v>
@@ -40503,19 +40622,19 @@
         <v>43</v>
       </c>
       <c r="B651" t="s">
+        <v>3262</v>
+      </c>
+      <c r="G651" t="s">
+        <v>3263</v>
+      </c>
+      <c r="H651" t="s">
+        <v>3264</v>
+      </c>
+      <c r="I651" t="s">
+        <v>3265</v>
+      </c>
+      <c r="J651" t="s">
         <v>3266</v>
-      </c>
-      <c r="G651" t="s">
-        <v>3267</v>
-      </c>
-      <c r="H651" t="s">
-        <v>3268</v>
-      </c>
-      <c r="I651" t="s">
-        <v>3269</v>
-      </c>
-      <c r="J651" t="s">
-        <v>3270</v>
       </c>
       <c r="K651">
         <v>2024</v>
@@ -40527,19 +40646,19 @@
         <v>43</v>
       </c>
       <c r="B652" t="s">
-        <v>3271</v>
+        <v>3267</v>
       </c>
       <c r="G652" t="s">
-        <v>3272</v>
+        <v>3268</v>
       </c>
       <c r="H652" t="s">
-        <v>3273</v>
+        <v>3269</v>
       </c>
       <c r="I652" t="s">
         <v>1336</v>
       </c>
       <c r="J652" t="s">
-        <v>3274</v>
+        <v>3270</v>
       </c>
       <c r="K652">
         <v>2015</v>
@@ -40551,19 +40670,19 @@
         <v>43</v>
       </c>
       <c r="B653" t="s">
+        <v>3271</v>
+      </c>
+      <c r="G653" t="s">
+        <v>3272</v>
+      </c>
+      <c r="H653" t="s">
+        <v>3273</v>
+      </c>
+      <c r="I653" t="s">
+        <v>3274</v>
+      </c>
+      <c r="J653" t="s">
         <v>3275</v>
-      </c>
-      <c r="G653" t="s">
-        <v>3276</v>
-      </c>
-      <c r="H653" t="s">
-        <v>3277</v>
-      </c>
-      <c r="I653" t="s">
-        <v>3278</v>
-      </c>
-      <c r="J653" t="s">
-        <v>3279</v>
       </c>
       <c r="K653">
         <v>2017</v>
@@ -40575,19 +40694,19 @@
         <v>43</v>
       </c>
       <c r="B654" t="s">
+        <v>3276</v>
+      </c>
+      <c r="G654" t="s">
+        <v>3277</v>
+      </c>
+      <c r="H654" t="s">
+        <v>3278</v>
+      </c>
+      <c r="I654" t="s">
+        <v>3279</v>
+      </c>
+      <c r="J654" t="s">
         <v>3280</v>
-      </c>
-      <c r="G654" t="s">
-        <v>3281</v>
-      </c>
-      <c r="H654" t="s">
-        <v>3282</v>
-      </c>
-      <c r="I654" t="s">
-        <v>3283</v>
-      </c>
-      <c r="J654" t="s">
-        <v>3284</v>
       </c>
       <c r="K654">
         <v>2016</v>
@@ -40599,19 +40718,19 @@
         <v>43</v>
       </c>
       <c r="B655" t="s">
+        <v>3281</v>
+      </c>
+      <c r="G655" t="s">
+        <v>3282</v>
+      </c>
+      <c r="H655" t="s">
+        <v>3283</v>
+      </c>
+      <c r="I655" t="s">
+        <v>3284</v>
+      </c>
+      <c r="J655" t="s">
         <v>3285</v>
-      </c>
-      <c r="G655" t="s">
-        <v>3286</v>
-      </c>
-      <c r="H655" t="s">
-        <v>3287</v>
-      </c>
-      <c r="I655" t="s">
-        <v>3288</v>
-      </c>
-      <c r="J655" t="s">
-        <v>3289</v>
       </c>
       <c r="K655">
         <v>2018</v>
@@ -40623,19 +40742,19 @@
         <v>43</v>
       </c>
       <c r="B656" t="s">
-        <v>3290</v>
+        <v>3286</v>
       </c>
       <c r="G656" t="s">
-        <v>3291</v>
+        <v>3287</v>
       </c>
       <c r="H656" t="s">
-        <v>3292</v>
+        <v>3288</v>
       </c>
       <c r="I656" t="s">
         <v>692</v>
       </c>
       <c r="J656" t="s">
-        <v>3293</v>
+        <v>3289</v>
       </c>
       <c r="K656">
         <v>2009</v>
@@ -40647,19 +40766,19 @@
         <v>43</v>
       </c>
       <c r="B657" t="s">
-        <v>3294</v>
+        <v>3290</v>
       </c>
       <c r="G657" t="s">
-        <v>3295</v>
+        <v>3291</v>
       </c>
       <c r="H657" t="s">
-        <v>3296</v>
+        <v>3292</v>
       </c>
       <c r="I657" t="s">
         <v>2054</v>
       </c>
       <c r="J657" t="s">
-        <v>3297</v>
+        <v>3293</v>
       </c>
       <c r="K657">
         <v>2013</v>
@@ -40671,19 +40790,19 @@
         <v>43</v>
       </c>
       <c r="B658" t="s">
-        <v>3298</v>
+        <v>3294</v>
       </c>
       <c r="G658" t="s">
-        <v>3299</v>
+        <v>3295</v>
       </c>
       <c r="H658" t="s">
-        <v>3300</v>
+        <v>3296</v>
       </c>
       <c r="I658" t="s">
-        <v>2914</v>
+        <v>2910</v>
       </c>
       <c r="J658" t="s">
-        <v>3301</v>
+        <v>3297</v>
       </c>
       <c r="K658">
         <v>2014</v>
@@ -40695,19 +40814,19 @@
         <v>43</v>
       </c>
       <c r="B659" t="s">
-        <v>3302</v>
+        <v>3298</v>
       </c>
       <c r="G659" t="s">
-        <v>3303</v>
+        <v>3299</v>
       </c>
       <c r="H659" t="s">
-        <v>3304</v>
+        <v>3300</v>
       </c>
       <c r="I659" t="s">
         <v>1987</v>
       </c>
       <c r="J659" t="s">
-        <v>3305</v>
+        <v>3301</v>
       </c>
       <c r="K659">
         <v>2024</v>
@@ -40719,19 +40838,19 @@
         <v>43</v>
       </c>
       <c r="B660" t="s">
-        <v>3306</v>
+        <v>3302</v>
       </c>
       <c r="G660" t="s">
-        <v>3307</v>
+        <v>3303</v>
       </c>
       <c r="H660" t="s">
-        <v>3308</v>
+        <v>3304</v>
       </c>
       <c r="I660" t="s">
         <v>51</v>
       </c>
       <c r="J660" t="s">
-        <v>3309</v>
+        <v>3305</v>
       </c>
       <c r="K660">
         <v>2023</v>
@@ -40743,19 +40862,19 @@
         <v>43</v>
       </c>
       <c r="B661" t="s">
-        <v>3310</v>
+        <v>3306</v>
       </c>
       <c r="G661" t="s">
-        <v>3311</v>
+        <v>3307</v>
       </c>
       <c r="H661" t="s">
-        <v>3312</v>
+        <v>3308</v>
       </c>
       <c r="I661" t="s">
         <v>664</v>
       </c>
       <c r="J661" t="s">
-        <v>3313</v>
+        <v>3309</v>
       </c>
       <c r="K661">
         <v>2001</v>
@@ -40767,19 +40886,19 @@
         <v>43</v>
       </c>
       <c r="B662" t="s">
-        <v>3314</v>
+        <v>3310</v>
       </c>
       <c r="G662" t="s">
-        <v>3315</v>
+        <v>3311</v>
       </c>
       <c r="H662" t="s">
-        <v>3316</v>
+        <v>3312</v>
       </c>
       <c r="I662" t="s">
-        <v>2901</v>
+        <v>2897</v>
       </c>
       <c r="J662" t="s">
-        <v>3317</v>
+        <v>3313</v>
       </c>
       <c r="K662">
         <v>2024</v>
@@ -40791,19 +40910,19 @@
         <v>43</v>
       </c>
       <c r="B663" t="s">
-        <v>3318</v>
+        <v>3314</v>
       </c>
       <c r="G663" t="s">
-        <v>3319</v>
+        <v>3315</v>
       </c>
       <c r="H663" t="s">
-        <v>3320</v>
+        <v>3316</v>
       </c>
       <c r="I663" t="s">
-        <v>3076</v>
+        <v>3072</v>
       </c>
       <c r="J663" t="s">
-        <v>3321</v>
+        <v>3317</v>
       </c>
       <c r="K663">
         <v>2025</v>
@@ -40815,19 +40934,19 @@
         <v>43</v>
       </c>
       <c r="B664" t="s">
-        <v>3322</v>
+        <v>3318</v>
       </c>
       <c r="G664" t="s">
-        <v>3323</v>
+        <v>3319</v>
       </c>
       <c r="H664" t="s">
-        <v>3324</v>
+        <v>3320</v>
       </c>
       <c r="I664" t="s">
         <v>409</v>
       </c>
       <c r="J664" t="s">
-        <v>3325</v>
+        <v>3321</v>
       </c>
       <c r="K664">
         <v>2022</v>
@@ -40839,19 +40958,19 @@
         <v>43</v>
       </c>
       <c r="B665" t="s">
+        <v>3322</v>
+      </c>
+      <c r="G665" t="s">
+        <v>3323</v>
+      </c>
+      <c r="H665" t="s">
+        <v>3324</v>
+      </c>
+      <c r="I665" t="s">
+        <v>3325</v>
+      </c>
+      <c r="J665" t="s">
         <v>3326</v>
-      </c>
-      <c r="G665" t="s">
-        <v>3327</v>
-      </c>
-      <c r="H665" t="s">
-        <v>3328</v>
-      </c>
-      <c r="I665" t="s">
-        <v>3329</v>
-      </c>
-      <c r="J665" t="s">
-        <v>3330</v>
       </c>
       <c r="K665">
         <v>2014</v>
@@ -40863,19 +40982,19 @@
         <v>43</v>
       </c>
       <c r="B666" t="s">
-        <v>3331</v>
+        <v>3327</v>
       </c>
       <c r="G666" t="s">
-        <v>3332</v>
+        <v>3328</v>
       </c>
       <c r="H666" t="s">
-        <v>3333</v>
+        <v>3329</v>
       </c>
       <c r="I666" t="s">
         <v>1414</v>
       </c>
       <c r="J666" t="s">
-        <v>3334</v>
+        <v>3330</v>
       </c>
       <c r="K666">
         <v>2025</v>
@@ -40887,19 +41006,19 @@
         <v>43</v>
       </c>
       <c r="B667" t="s">
-        <v>3335</v>
+        <v>3331</v>
       </c>
       <c r="G667" t="s">
-        <v>3336</v>
+        <v>3332</v>
       </c>
       <c r="H667" t="s">
-        <v>3337</v>
+        <v>3333</v>
       </c>
       <c r="I667" t="s">
         <v>459</v>
       </c>
       <c r="J667" t="s">
-        <v>3338</v>
+        <v>3334</v>
       </c>
       <c r="K667">
         <v>2016</v>
@@ -40911,19 +41030,19 @@
         <v>43</v>
       </c>
       <c r="B668" t="s">
+        <v>3335</v>
+      </c>
+      <c r="G668" t="s">
+        <v>3336</v>
+      </c>
+      <c r="H668" t="s">
+        <v>3337</v>
+      </c>
+      <c r="I668" t="s">
+        <v>3338</v>
+      </c>
+      <c r="J668" t="s">
         <v>3339</v>
-      </c>
-      <c r="G668" t="s">
-        <v>3340</v>
-      </c>
-      <c r="H668" t="s">
-        <v>3341</v>
-      </c>
-      <c r="I668" t="s">
-        <v>3342</v>
-      </c>
-      <c r="J668" t="s">
-        <v>3343</v>
       </c>
       <c r="K668">
         <v>2018</v>
@@ -40935,19 +41054,19 @@
         <v>43</v>
       </c>
       <c r="B669" t="s">
-        <v>3344</v>
+        <v>3340</v>
       </c>
       <c r="G669" t="s">
-        <v>3345</v>
+        <v>3341</v>
       </c>
       <c r="H669" t="s">
-        <v>3346</v>
+        <v>3342</v>
       </c>
       <c r="I669" t="s">
         <v>426</v>
       </c>
       <c r="J669" t="s">
-        <v>3347</v>
+        <v>3343</v>
       </c>
       <c r="K669">
         <v>2015</v>
@@ -40959,19 +41078,19 @@
         <v>43</v>
       </c>
       <c r="B670" t="s">
+        <v>3344</v>
+      </c>
+      <c r="G670" t="s">
+        <v>3345</v>
+      </c>
+      <c r="H670" t="s">
+        <v>3346</v>
+      </c>
+      <c r="I670" t="s">
+        <v>3347</v>
+      </c>
+      <c r="J670" t="s">
         <v>3348</v>
-      </c>
-      <c r="G670" t="s">
-        <v>3349</v>
-      </c>
-      <c r="H670" t="s">
-        <v>3350</v>
-      </c>
-      <c r="I670" t="s">
-        <v>3351</v>
-      </c>
-      <c r="J670" t="s">
-        <v>3352</v>
       </c>
       <c r="K670">
         <v>2018</v>
@@ -40983,19 +41102,19 @@
         <v>43</v>
       </c>
       <c r="B671" t="s">
-        <v>3353</v>
+        <v>3349</v>
       </c>
       <c r="G671" t="s">
-        <v>3354</v>
+        <v>3350</v>
       </c>
       <c r="H671" t="s">
-        <v>3355</v>
+        <v>3351</v>
       </c>
       <c r="I671" t="s">
         <v>2236</v>
       </c>
       <c r="J671" t="s">
-        <v>3356</v>
+        <v>3352</v>
       </c>
       <c r="K671">
         <v>2011</v>
@@ -41007,19 +41126,19 @@
         <v>43</v>
       </c>
       <c r="B672" t="s">
-        <v>3357</v>
+        <v>3353</v>
       </c>
       <c r="G672" t="s">
-        <v>3358</v>
+        <v>3354</v>
       </c>
       <c r="H672" t="s">
-        <v>3359</v>
+        <v>3355</v>
       </c>
       <c r="I672" t="s">
         <v>128</v>
       </c>
       <c r="J672" t="s">
-        <v>3360</v>
+        <v>3356</v>
       </c>
       <c r="K672">
         <v>2015</v>
@@ -41031,19 +41150,19 @@
         <v>43</v>
       </c>
       <c r="B673" t="s">
-        <v>3361</v>
+        <v>3357</v>
       </c>
       <c r="G673" t="s">
-        <v>3362</v>
+        <v>3358</v>
       </c>
       <c r="H673" t="s">
-        <v>3363</v>
+        <v>3359</v>
       </c>
       <c r="I673" t="s">
         <v>1479</v>
       </c>
       <c r="J673" t="s">
-        <v>3364</v>
+        <v>3360</v>
       </c>
       <c r="K673">
         <v>2022</v>
@@ -41055,19 +41174,19 @@
         <v>43</v>
       </c>
       <c r="B674" t="s">
-        <v>3365</v>
+        <v>3361</v>
       </c>
       <c r="G674" t="s">
-        <v>3366</v>
+        <v>3362</v>
       </c>
       <c r="H674" t="s">
-        <v>3367</v>
+        <v>3363</v>
       </c>
       <c r="I674" t="s">
-        <v>3342</v>
+        <v>3338</v>
       </c>
       <c r="J674" t="s">
-        <v>3368</v>
+        <v>3364</v>
       </c>
       <c r="K674">
         <v>2023</v>
@@ -41079,19 +41198,19 @@
         <v>43</v>
       </c>
       <c r="B675" t="s">
+        <v>3365</v>
+      </c>
+      <c r="G675" t="s">
+        <v>3366</v>
+      </c>
+      <c r="H675" t="s">
+        <v>3367</v>
+      </c>
+      <c r="I675" t="s">
+        <v>3368</v>
+      </c>
+      <c r="J675" t="s">
         <v>3369</v>
-      </c>
-      <c r="G675" t="s">
-        <v>3370</v>
-      </c>
-      <c r="H675" t="s">
-        <v>3371</v>
-      </c>
-      <c r="I675" t="s">
-        <v>3372</v>
-      </c>
-      <c r="J675" t="s">
-        <v>3373</v>
       </c>
       <c r="K675">
         <v>2021</v>
@@ -41103,19 +41222,19 @@
         <v>43</v>
       </c>
       <c r="B676" t="s">
-        <v>3374</v>
+        <v>3370</v>
       </c>
       <c r="G676" t="s">
-        <v>3375</v>
+        <v>3371</v>
       </c>
       <c r="H676" t="s">
-        <v>3376</v>
+        <v>3372</v>
       </c>
       <c r="I676" t="s">
         <v>1674</v>
       </c>
       <c r="J676" t="s">
-        <v>3377</v>
+        <v>3373</v>
       </c>
       <c r="K676">
         <v>2022</v>
@@ -41127,19 +41246,19 @@
         <v>43</v>
       </c>
       <c r="B677" t="s">
-        <v>3378</v>
+        <v>3374</v>
       </c>
       <c r="G677" t="s">
-        <v>3379</v>
+        <v>3375</v>
       </c>
       <c r="H677" t="s">
-        <v>3380</v>
+        <v>3376</v>
       </c>
       <c r="I677" t="s">
         <v>687</v>
       </c>
       <c r="J677" t="s">
-        <v>3381</v>
+        <v>3377</v>
       </c>
       <c r="K677">
         <v>2026</v>
@@ -41151,19 +41270,19 @@
         <v>43</v>
       </c>
       <c r="B678" t="s">
-        <v>3382</v>
+        <v>3378</v>
       </c>
       <c r="G678" t="s">
-        <v>3383</v>
+        <v>3379</v>
       </c>
       <c r="H678" t="s">
-        <v>3384</v>
+        <v>3380</v>
       </c>
       <c r="I678" t="s">
         <v>409</v>
       </c>
       <c r="J678" t="s">
-        <v>3385</v>
+        <v>3381</v>
       </c>
       <c r="K678">
         <v>2022</v>
@@ -41175,19 +41294,19 @@
         <v>43</v>
       </c>
       <c r="B679" t="s">
-        <v>3386</v>
+        <v>3382</v>
       </c>
       <c r="G679" t="s">
-        <v>3387</v>
+        <v>3383</v>
       </c>
       <c r="H679" t="s">
-        <v>3388</v>
+        <v>3384</v>
       </c>
       <c r="I679" t="s">
         <v>51</v>
       </c>
       <c r="J679" t="s">
-        <v>3389</v>
+        <v>3385</v>
       </c>
       <c r="K679">
         <v>2019</v>
@@ -41199,19 +41318,19 @@
         <v>43</v>
       </c>
       <c r="B680" t="s">
+        <v>3386</v>
+      </c>
+      <c r="G680" t="s">
+        <v>3387</v>
+      </c>
+      <c r="H680" t="s">
+        <v>3388</v>
+      </c>
+      <c r="I680" t="s">
+        <v>3389</v>
+      </c>
+      <c r="J680" t="s">
         <v>3390</v>
-      </c>
-      <c r="G680" t="s">
-        <v>3391</v>
-      </c>
-      <c r="H680" t="s">
-        <v>3392</v>
-      </c>
-      <c r="I680" t="s">
-        <v>3393</v>
-      </c>
-      <c r="J680" t="s">
-        <v>3394</v>
       </c>
       <c r="K680">
         <v>2021</v>
@@ -41223,19 +41342,19 @@
         <v>43</v>
       </c>
       <c r="B681" t="s">
-        <v>3395</v>
+        <v>3391</v>
       </c>
       <c r="G681" t="s">
-        <v>3396</v>
+        <v>3392</v>
       </c>
       <c r="H681" t="s">
-        <v>3397</v>
+        <v>3393</v>
       </c>
       <c r="I681" t="s">
         <v>237</v>
       </c>
       <c r="J681" t="s">
-        <v>3398</v>
+        <v>3394</v>
       </c>
       <c r="K681">
         <v>2017</v>
@@ -41247,19 +41366,19 @@
         <v>43</v>
       </c>
       <c r="B682" t="s">
-        <v>3399</v>
+        <v>3395</v>
       </c>
       <c r="G682" t="s">
-        <v>3400</v>
+        <v>3396</v>
       </c>
       <c r="H682" t="s">
-        <v>3401</v>
+        <v>3397</v>
       </c>
       <c r="I682" t="s">
         <v>1080</v>
       </c>
       <c r="J682" t="s">
-        <v>3402</v>
+        <v>3398</v>
       </c>
       <c r="K682">
         <v>2025</v>
@@ -41271,19 +41390,19 @@
         <v>43</v>
       </c>
       <c r="B683" t="s">
-        <v>3403</v>
+        <v>3399</v>
       </c>
       <c r="G683" t="s">
-        <v>3404</v>
+        <v>3400</v>
       </c>
       <c r="H683" t="s">
-        <v>3405</v>
+        <v>3401</v>
       </c>
       <c r="I683" t="s">
         <v>237</v>
       </c>
       <c r="J683" t="s">
-        <v>3406</v>
+        <v>3402</v>
       </c>
       <c r="K683">
         <v>2025</v>
@@ -41295,19 +41414,19 @@
         <v>43</v>
       </c>
       <c r="B684" t="s">
-        <v>3407</v>
+        <v>3403</v>
       </c>
       <c r="G684" t="s">
-        <v>3408</v>
+        <v>3404</v>
       </c>
       <c r="H684" t="s">
-        <v>3409</v>
+        <v>3405</v>
       </c>
       <c r="I684" t="s">
         <v>819</v>
       </c>
       <c r="J684" t="s">
-        <v>3410</v>
+        <v>3406</v>
       </c>
       <c r="K684">
         <v>2019</v>
@@ -41319,19 +41438,19 @@
         <v>43</v>
       </c>
       <c r="B685" t="s">
-        <v>3411</v>
+        <v>3407</v>
       </c>
       <c r="G685" t="s">
-        <v>3412</v>
+        <v>3408</v>
       </c>
       <c r="H685" t="s">
-        <v>3413</v>
+        <v>3409</v>
       </c>
       <c r="I685" t="s">
         <v>415</v>
       </c>
       <c r="J685" t="s">
-        <v>3414</v>
+        <v>3410</v>
       </c>
       <c r="K685">
         <v>2024</v>
@@ -41343,19 +41462,19 @@
         <v>43</v>
       </c>
       <c r="B686" t="s">
+        <v>3411</v>
+      </c>
+      <c r="G686" t="s">
+        <v>3412</v>
+      </c>
+      <c r="H686" t="s">
+        <v>3413</v>
+      </c>
+      <c r="I686" t="s">
+        <v>3414</v>
+      </c>
+      <c r="J686" t="s">
         <v>3415</v>
-      </c>
-      <c r="G686" t="s">
-        <v>3416</v>
-      </c>
-      <c r="H686" t="s">
-        <v>3417</v>
-      </c>
-      <c r="I686" t="s">
-        <v>3418</v>
-      </c>
-      <c r="J686" t="s">
-        <v>3419</v>
       </c>
       <c r="K686">
         <v>2024</v>
@@ -41367,19 +41486,19 @@
         <v>43</v>
       </c>
       <c r="B687" t="s">
-        <v>3420</v>
+        <v>3416</v>
       </c>
       <c r="G687" t="s">
-        <v>3421</v>
+        <v>3417</v>
       </c>
       <c r="H687" t="s">
-        <v>3422</v>
+        <v>3418</v>
       </c>
       <c r="I687" t="s">
         <v>1929</v>
       </c>
       <c r="J687" t="s">
-        <v>3423</v>
+        <v>3419</v>
       </c>
       <c r="K687">
         <v>2024</v>
@@ -41391,19 +41510,19 @@
         <v>43</v>
       </c>
       <c r="B688" t="s">
+        <v>3420</v>
+      </c>
+      <c r="G688" t="s">
+        <v>3421</v>
+      </c>
+      <c r="H688" t="s">
+        <v>3422</v>
+      </c>
+      <c r="I688" t="s">
+        <v>3423</v>
+      </c>
+      <c r="J688" t="s">
         <v>3424</v>
-      </c>
-      <c r="G688" t="s">
-        <v>3425</v>
-      </c>
-      <c r="H688" t="s">
-        <v>3426</v>
-      </c>
-      <c r="I688" t="s">
-        <v>3427</v>
-      </c>
-      <c r="J688" t="s">
-        <v>3428</v>
       </c>
       <c r="K688">
         <v>2023</v>
@@ -41415,19 +41534,19 @@
         <v>43</v>
       </c>
       <c r="B689" t="s">
+        <v>3425</v>
+      </c>
+      <c r="G689" t="s">
+        <v>3426</v>
+      </c>
+      <c r="H689" t="s">
+        <v>3427</v>
+      </c>
+      <c r="I689" t="s">
+        <v>3428</v>
+      </c>
+      <c r="J689" t="s">
         <v>3429</v>
-      </c>
-      <c r="G689" t="s">
-        <v>3430</v>
-      </c>
-      <c r="H689" t="s">
-        <v>3431</v>
-      </c>
-      <c r="I689" t="s">
-        <v>3432</v>
-      </c>
-      <c r="J689" t="s">
-        <v>3433</v>
       </c>
       <c r="K689">
         <v>2024</v>
@@ -41439,19 +41558,19 @@
         <v>43</v>
       </c>
       <c r="B690" t="s">
-        <v>3434</v>
+        <v>3430</v>
       </c>
       <c r="G690" t="s">
-        <v>3435</v>
+        <v>3431</v>
       </c>
       <c r="H690" t="s">
-        <v>3436</v>
+        <v>3432</v>
       </c>
       <c r="I690" t="s">
         <v>403</v>
       </c>
       <c r="J690" t="s">
-        <v>3437</v>
+        <v>3433</v>
       </c>
       <c r="K690">
         <v>2014</v>
@@ -41463,19 +41582,19 @@
         <v>43</v>
       </c>
       <c r="B691" t="s">
-        <v>3438</v>
+        <v>3434</v>
       </c>
       <c r="G691" t="s">
-        <v>3439</v>
+        <v>3435</v>
       </c>
       <c r="H691" t="s">
-        <v>3440</v>
+        <v>3436</v>
       </c>
       <c r="I691" t="s">
         <v>2043</v>
       </c>
       <c r="J691" t="s">
-        <v>3441</v>
+        <v>3437</v>
       </c>
       <c r="K691">
         <v>2024</v>
@@ -41487,19 +41606,19 @@
         <v>43</v>
       </c>
       <c r="B692" t="s">
+        <v>3438</v>
+      </c>
+      <c r="G692" t="s">
+        <v>3439</v>
+      </c>
+      <c r="H692" t="s">
+        <v>3440</v>
+      </c>
+      <c r="I692" t="s">
+        <v>3441</v>
+      </c>
+      <c r="J692" t="s">
         <v>3442</v>
-      </c>
-      <c r="G692" t="s">
-        <v>3443</v>
-      </c>
-      <c r="H692" t="s">
-        <v>3444</v>
-      </c>
-      <c r="I692" t="s">
-        <v>3445</v>
-      </c>
-      <c r="J692" t="s">
-        <v>3446</v>
       </c>
       <c r="K692">
         <v>2023</v>
@@ -41511,19 +41630,19 @@
         <v>43</v>
       </c>
       <c r="B693" t="s">
-        <v>3447</v>
+        <v>3443</v>
       </c>
       <c r="G693" t="s">
-        <v>3448</v>
+        <v>3444</v>
       </c>
       <c r="H693" t="s">
-        <v>3449</v>
+        <v>3445</v>
       </c>
       <c r="I693" t="s">
         <v>237</v>
       </c>
       <c r="J693" t="s">
-        <v>3450</v>
+        <v>3446</v>
       </c>
       <c r="K693">
         <v>2026</v>
@@ -41535,19 +41654,19 @@
         <v>43</v>
       </c>
       <c r="B694" t="s">
-        <v>3451</v>
+        <v>3447</v>
       </c>
       <c r="G694" t="s">
-        <v>3452</v>
+        <v>3448</v>
       </c>
       <c r="H694" t="s">
-        <v>3453</v>
+        <v>3449</v>
       </c>
       <c r="I694" t="s">
         <v>973</v>
       </c>
       <c r="J694" t="s">
-        <v>3454</v>
+        <v>3450</v>
       </c>
       <c r="K694">
         <v>2025</v>
@@ -41559,19 +41678,19 @@
         <v>43</v>
       </c>
       <c r="B695" t="s">
-        <v>3455</v>
+        <v>3451</v>
       </c>
       <c r="G695" t="s">
-        <v>3456</v>
+        <v>3452</v>
       </c>
       <c r="H695" t="s">
-        <v>3457</v>
+        <v>3453</v>
       </c>
       <c r="I695" t="s">
         <v>1929</v>
       </c>
       <c r="J695" t="s">
-        <v>3458</v>
+        <v>3454</v>
       </c>
       <c r="K695">
         <v>2020</v>
@@ -41583,19 +41702,19 @@
         <v>43</v>
       </c>
       <c r="B696" t="s">
-        <v>3459</v>
+        <v>3455</v>
       </c>
       <c r="G696" t="s">
-        <v>3460</v>
+        <v>3456</v>
       </c>
       <c r="H696" t="s">
-        <v>3461</v>
+        <v>3457</v>
       </c>
       <c r="I696" t="s">
         <v>973</v>
       </c>
       <c r="J696" t="s">
-        <v>3462</v>
+        <v>3458</v>
       </c>
       <c r="K696">
         <v>2024</v>
@@ -41607,19 +41726,19 @@
         <v>43</v>
       </c>
       <c r="B697" t="s">
-        <v>3463</v>
+        <v>3459</v>
       </c>
       <c r="G697" t="s">
-        <v>3464</v>
+        <v>3460</v>
       </c>
       <c r="H697" t="s">
-        <v>3465</v>
+        <v>3461</v>
       </c>
       <c r="I697" t="s">
         <v>1461</v>
       </c>
       <c r="J697" t="s">
-        <v>3466</v>
+        <v>3462</v>
       </c>
       <c r="K697">
         <v>2023</v>
@@ -41631,19 +41750,19 @@
         <v>43</v>
       </c>
       <c r="B698" t="s">
-        <v>3467</v>
+        <v>3463</v>
       </c>
       <c r="G698" t="s">
-        <v>3468</v>
+        <v>3464</v>
       </c>
       <c r="H698" t="s">
-        <v>3469</v>
+        <v>3465</v>
       </c>
       <c r="I698" t="s">
         <v>723</v>
       </c>
       <c r="J698" t="s">
-        <v>3470</v>
+        <v>3466</v>
       </c>
       <c r="K698">
         <v>2022</v>
@@ -41655,19 +41774,19 @@
         <v>43</v>
       </c>
       <c r="B699" t="s">
-        <v>3471</v>
+        <v>3467</v>
       </c>
       <c r="G699" t="s">
-        <v>3472</v>
+        <v>3468</v>
       </c>
       <c r="H699" t="s">
-        <v>3473</v>
+        <v>3469</v>
       </c>
       <c r="I699" t="s">
-        <v>3351</v>
+        <v>3347</v>
       </c>
       <c r="J699" t="s">
-        <v>3474</v>
+        <v>3470</v>
       </c>
       <c r="K699">
         <v>2017</v>
@@ -41679,19 +41798,19 @@
         <v>43</v>
       </c>
       <c r="B700" t="s">
-        <v>3475</v>
+        <v>3471</v>
       </c>
       <c r="G700" t="s">
-        <v>3476</v>
+        <v>3472</v>
       </c>
       <c r="H700" t="s">
-        <v>3477</v>
+        <v>3473</v>
       </c>
       <c r="I700" t="s">
         <v>915</v>
       </c>
       <c r="J700" t="s">
-        <v>3478</v>
+        <v>3474</v>
       </c>
       <c r="K700">
         <v>2024</v>
@@ -41703,19 +41822,19 @@
         <v>43</v>
       </c>
       <c r="B701" t="s">
+        <v>3475</v>
+      </c>
+      <c r="G701" t="s">
+        <v>3476</v>
+      </c>
+      <c r="H701" t="s">
+        <v>3477</v>
+      </c>
+      <c r="I701" t="s">
+        <v>3478</v>
+      </c>
+      <c r="J701" t="s">
         <v>3479</v>
-      </c>
-      <c r="G701" t="s">
-        <v>3480</v>
-      </c>
-      <c r="H701" t="s">
-        <v>3481</v>
-      </c>
-      <c r="I701" t="s">
-        <v>3482</v>
-      </c>
-      <c r="J701" t="s">
-        <v>3483</v>
       </c>
       <c r="K701">
         <v>2026</v>
@@ -41727,19 +41846,19 @@
         <v>43</v>
       </c>
       <c r="B702" t="s">
-        <v>3484</v>
+        <v>3480</v>
       </c>
       <c r="G702" t="s">
-        <v>3485</v>
+        <v>3481</v>
       </c>
       <c r="H702" t="s">
-        <v>3486</v>
+        <v>3482</v>
       </c>
       <c r="I702" t="s">
         <v>915</v>
       </c>
       <c r="J702" t="s">
-        <v>3487</v>
+        <v>3483</v>
       </c>
       <c r="K702">
         <v>2007</v>
@@ -41751,19 +41870,19 @@
         <v>43</v>
       </c>
       <c r="B703" t="s">
+        <v>3484</v>
+      </c>
+      <c r="G703" t="s">
+        <v>3485</v>
+      </c>
+      <c r="H703" t="s">
+        <v>3486</v>
+      </c>
+      <c r="I703" t="s">
+        <v>3487</v>
+      </c>
+      <c r="J703" t="s">
         <v>3488</v>
-      </c>
-      <c r="G703" t="s">
-        <v>3489</v>
-      </c>
-      <c r="H703" t="s">
-        <v>3490</v>
-      </c>
-      <c r="I703" t="s">
-        <v>3491</v>
-      </c>
-      <c r="J703" t="s">
-        <v>3492</v>
       </c>
       <c r="K703">
         <v>2013</v>
@@ -41775,19 +41894,19 @@
         <v>43</v>
       </c>
       <c r="B704" t="s">
-        <v>3493</v>
+        <v>3489</v>
       </c>
       <c r="G704" t="s">
-        <v>3494</v>
+        <v>3490</v>
       </c>
       <c r="H704" t="s">
-        <v>3495</v>
+        <v>3491</v>
       </c>
       <c r="I704" t="s">
         <v>51</v>
       </c>
       <c r="J704" t="s">
-        <v>3496</v>
+        <v>3492</v>
       </c>
       <c r="K704">
         <v>2001</v>

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="g:\My Drive\UCL\BSMA\BSMA ANTIGRAVITY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77359DDC-7487-4481-A875-2655503788DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9EE6C0-8A7F-4923-9FB2-7268B4377624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5791" uniqueCount="3655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="3655">
   <si>
     <t>Coder Initials</t>
   </si>
@@ -38179,6 +38179,9 @@
       <c r="B551" t="s">
         <v>2832</v>
       </c>
+      <c r="E551" t="s">
+        <v>2482</v>
+      </c>
       <c r="G551" t="s">
         <v>2833</v>
       </c>
@@ -38194,7 +38197,9 @@
       <c r="K551">
         <v>2015</v>
       </c>
-      <c r="P551" s="8"/>
+      <c r="P551" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="552" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A552" t="s">
@@ -38464,6 +38469,9 @@
       <c r="B561" t="s">
         <v>2878</v>
       </c>
+      <c r="E561" t="s">
+        <v>2482</v>
+      </c>
       <c r="G561" t="s">
         <v>2879</v>
       </c>
@@ -38479,7 +38487,9 @@
       <c r="K561">
         <v>2023</v>
       </c>
-      <c r="P561" s="8"/>
+      <c r="P561" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="562" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A562" t="s">
@@ -38488,6 +38498,9 @@
       <c r="B562" t="s">
         <v>2882</v>
       </c>
+      <c r="E562" t="s">
+        <v>2482</v>
+      </c>
       <c r="G562" t="s">
         <v>2883</v>
       </c>
@@ -38503,7 +38516,9 @@
       <c r="K562">
         <v>2000</v>
       </c>
-      <c r="P562" s="8"/>
+      <c r="P562" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="563" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A563" t="s">
@@ -38512,6 +38527,9 @@
       <c r="B563" t="s">
         <v>2886</v>
       </c>
+      <c r="E563" t="s">
+        <v>2482</v>
+      </c>
       <c r="G563" t="s">
         <v>2887</v>
       </c>
@@ -38527,7 +38545,9 @@
       <c r="K563">
         <v>2016</v>
       </c>
-      <c r="P563" s="8"/>
+      <c r="P563" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="564" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A564" t="s">
@@ -38536,6 +38556,9 @@
       <c r="B564" t="s">
         <v>2890</v>
       </c>
+      <c r="E564" t="s">
+        <v>2482</v>
+      </c>
       <c r="G564" t="s">
         <v>2891</v>
       </c>
@@ -38551,7 +38574,9 @@
       <c r="K564">
         <v>2026</v>
       </c>
-      <c r="P564" s="8"/>
+      <c r="P564" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="565" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A565" t="s">
@@ -38560,6 +38585,9 @@
       <c r="B565" t="s">
         <v>2894</v>
       </c>
+      <c r="E565" t="s">
+        <v>2482</v>
+      </c>
       <c r="G565" t="s">
         <v>2895</v>
       </c>
@@ -38575,7 +38603,9 @@
       <c r="K565">
         <v>2024</v>
       </c>
-      <c r="P565" s="8"/>
+      <c r="P565" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="566" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A566" t="s">
@@ -38584,6 +38614,9 @@
       <c r="B566" t="s">
         <v>2899</v>
       </c>
+      <c r="E566" t="s">
+        <v>2482</v>
+      </c>
       <c r="G566" t="s">
         <v>2900</v>
       </c>
@@ -38599,7 +38632,9 @@
       <c r="K566">
         <v>2019</v>
       </c>
-      <c r="P566" s="8"/>
+      <c r="P566" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="567" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A567" t="s">
@@ -38608,6 +38643,9 @@
       <c r="B567" t="s">
         <v>2903</v>
       </c>
+      <c r="E567" t="s">
+        <v>2482</v>
+      </c>
       <c r="G567" t="s">
         <v>2904</v>
       </c>
@@ -38623,7 +38661,9 @@
       <c r="K567">
         <v>2020</v>
       </c>
-      <c r="P567" s="8"/>
+      <c r="P567" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="568" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A568" t="s">
@@ -38632,6 +38672,9 @@
       <c r="B568" t="s">
         <v>2907</v>
       </c>
+      <c r="E568" t="s">
+        <v>2482</v>
+      </c>
       <c r="G568" t="s">
         <v>2908</v>
       </c>
@@ -38647,7 +38690,9 @@
       <c r="K568">
         <v>2014</v>
       </c>
-      <c r="P568" s="8"/>
+      <c r="P568" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="569" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A569" t="s">
@@ -38656,6 +38701,9 @@
       <c r="B569" t="s">
         <v>2912</v>
       </c>
+      <c r="E569" t="s">
+        <v>2482</v>
+      </c>
       <c r="G569" t="s">
         <v>2913</v>
       </c>
@@ -38671,7 +38719,9 @@
       <c r="K569">
         <v>2004</v>
       </c>
-      <c r="P569" s="8"/>
+      <c r="P569" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="570" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A570" t="s">
@@ -38680,6 +38730,9 @@
       <c r="B570" t="s">
         <v>2916</v>
       </c>
+      <c r="E570" t="s">
+        <v>2482</v>
+      </c>
       <c r="G570" t="s">
         <v>2917</v>
       </c>
@@ -38695,7 +38748,9 @@
       <c r="K570">
         <v>2015</v>
       </c>
-      <c r="P570" s="8"/>
+      <c r="P570" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="571" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A571" t="s">
@@ -38704,6 +38759,9 @@
       <c r="B571" t="s">
         <v>2920</v>
       </c>
+      <c r="E571" t="s">
+        <v>2482</v>
+      </c>
       <c r="G571" t="s">
         <v>2921</v>
       </c>
@@ -38719,7 +38777,9 @@
       <c r="K571">
         <v>2015</v>
       </c>
-      <c r="P571" s="8"/>
+      <c r="P571" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="572" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A572" t="s">
@@ -38728,6 +38788,9 @@
       <c r="B572" t="s">
         <v>2924</v>
       </c>
+      <c r="E572" t="s">
+        <v>2482</v>
+      </c>
       <c r="G572" t="s">
         <v>2925</v>
       </c>
@@ -38743,7 +38806,9 @@
       <c r="K572">
         <v>2013</v>
       </c>
-      <c r="P572" s="8"/>
+      <c r="P572" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="573" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A573" t="s">
@@ -38752,6 +38817,9 @@
       <c r="B573" t="s">
         <v>2929</v>
       </c>
+      <c r="E573" t="s">
+        <v>2482</v>
+      </c>
       <c r="G573" t="s">
         <v>2930</v>
       </c>
@@ -38767,7 +38835,9 @@
       <c r="K573">
         <v>2017</v>
       </c>
-      <c r="P573" s="8"/>
+      <c r="P573" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="574" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A574" t="s">
@@ -38776,6 +38846,9 @@
       <c r="B574" t="s">
         <v>2933</v>
       </c>
+      <c r="E574" t="s">
+        <v>2482</v>
+      </c>
       <c r="G574" t="s">
         <v>2934</v>
       </c>
@@ -38791,7 +38864,9 @@
       <c r="K574">
         <v>1995</v>
       </c>
-      <c r="P574" s="8"/>
+      <c r="P574" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="575" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A575" t="s">
@@ -38800,6 +38875,9 @@
       <c r="B575" t="s">
         <v>2937</v>
       </c>
+      <c r="E575" t="s">
+        <v>2482</v>
+      </c>
       <c r="G575" t="s">
         <v>2938</v>
       </c>
@@ -38815,7 +38893,9 @@
       <c r="K575">
         <v>2019</v>
       </c>
-      <c r="P575" s="8"/>
+      <c r="P575" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="576" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A576" t="s">
@@ -38824,6 +38904,9 @@
       <c r="B576" t="s">
         <v>2942</v>
       </c>
+      <c r="E576" t="s">
+        <v>2482</v>
+      </c>
       <c r="G576" t="s">
         <v>2943</v>
       </c>
@@ -38839,7 +38922,9 @@
       <c r="K576">
         <v>2010</v>
       </c>
-      <c r="P576" s="8"/>
+      <c r="P576" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="577" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A577" t="s">
@@ -38848,6 +38933,9 @@
       <c r="B577" t="s">
         <v>2946</v>
       </c>
+      <c r="E577" t="s">
+        <v>2482</v>
+      </c>
       <c r="G577" t="s">
         <v>2947</v>
       </c>
@@ -38863,7 +38951,9 @@
       <c r="K577">
         <v>2012</v>
       </c>
-      <c r="P577" s="8"/>
+      <c r="P577" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="578" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A578" t="s">
@@ -38872,6 +38962,9 @@
       <c r="B578" t="s">
         <v>2950</v>
       </c>
+      <c r="E578" t="s">
+        <v>2482</v>
+      </c>
       <c r="G578" t="s">
         <v>2951</v>
       </c>
@@ -38887,7 +38980,9 @@
       <c r="K578">
         <v>1979</v>
       </c>
-      <c r="P578" s="8"/>
+      <c r="P578" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="579" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A579" t="s">
@@ -38896,6 +38991,9 @@
       <c r="B579" t="s">
         <v>2954</v>
       </c>
+      <c r="E579" t="s">
+        <v>2482</v>
+      </c>
       <c r="G579" t="s">
         <v>2955</v>
       </c>
@@ -38911,7 +39009,9 @@
       <c r="K579">
         <v>1980</v>
       </c>
-      <c r="P579" s="8"/>
+      <c r="P579" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="580" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A580" t="s">
@@ -38920,6 +39020,9 @@
       <c r="B580" t="s">
         <v>2959</v>
       </c>
+      <c r="E580" t="s">
+        <v>2482</v>
+      </c>
       <c r="G580" t="s">
         <v>2960</v>
       </c>
@@ -38935,7 +39038,9 @@
       <c r="K580">
         <v>1981</v>
       </c>
-      <c r="P580" s="8"/>
+      <c r="P580" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="581" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A581" t="s">
@@ -38944,6 +39049,9 @@
       <c r="B581" t="s">
         <v>2963</v>
       </c>
+      <c r="E581" t="s">
+        <v>2482</v>
+      </c>
       <c r="G581" t="s">
         <v>2964</v>
       </c>
@@ -38959,7 +39067,9 @@
       <c r="K581">
         <v>1981</v>
       </c>
-      <c r="P581" s="8"/>
+      <c r="P581" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="582" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A582" t="s">
@@ -38968,6 +39078,9 @@
       <c r="B582" t="s">
         <v>2966</v>
       </c>
+      <c r="E582" t="s">
+        <v>2482</v>
+      </c>
       <c r="G582" t="s">
         <v>2967</v>
       </c>
@@ -38983,7 +39096,9 @@
       <c r="K582">
         <v>2023</v>
       </c>
-      <c r="P582" s="8"/>
+      <c r="P582" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="583" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A583" t="s">
@@ -38992,6 +39107,9 @@
       <c r="B583" t="s">
         <v>2970</v>
       </c>
+      <c r="E583" t="s">
+        <v>2482</v>
+      </c>
       <c r="G583" t="s">
         <v>2971</v>
       </c>
@@ -39007,7 +39125,9 @@
       <c r="K583">
         <v>2024</v>
       </c>
-      <c r="P583" s="8"/>
+      <c r="P583" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="584" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A584" t="s">
@@ -39016,6 +39136,9 @@
       <c r="B584" t="s">
         <v>2974</v>
       </c>
+      <c r="E584" t="s">
+        <v>2482</v>
+      </c>
       <c r="G584" t="s">
         <v>2975</v>
       </c>
@@ -39031,7 +39154,9 @@
       <c r="K584">
         <v>2014</v>
       </c>
-      <c r="P584" s="8"/>
+      <c r="P584" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="585" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A585" t="s">
@@ -39040,6 +39165,9 @@
       <c r="B585" t="s">
         <v>2979</v>
       </c>
+      <c r="E585" t="s">
+        <v>2482</v>
+      </c>
       <c r="G585" t="s">
         <v>2980</v>
       </c>
@@ -39055,7 +39183,9 @@
       <c r="K585">
         <v>2015</v>
       </c>
-      <c r="P585" s="8"/>
+      <c r="P585" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="586" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A586" t="s">
@@ -39064,6 +39194,9 @@
       <c r="B586" t="s">
         <v>2983</v>
       </c>
+      <c r="E586" t="s">
+        <v>2482</v>
+      </c>
       <c r="G586" t="s">
         <v>2984</v>
       </c>
@@ -39079,7 +39212,9 @@
       <c r="K586">
         <v>2020</v>
       </c>
-      <c r="P586" s="8"/>
+      <c r="P586" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="587" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A587" t="s">
@@ -39088,6 +39223,9 @@
       <c r="B587" t="s">
         <v>2987</v>
       </c>
+      <c r="E587" t="s">
+        <v>2482</v>
+      </c>
       <c r="G587" t="s">
         <v>2988</v>
       </c>
@@ -39103,7 +39241,9 @@
       <c r="K587">
         <v>2020</v>
       </c>
-      <c r="P587" s="8"/>
+      <c r="P587" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="588" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A588" t="s">
@@ -39112,6 +39252,9 @@
       <c r="B588" t="s">
         <v>2992</v>
       </c>
+      <c r="E588" t="s">
+        <v>2482</v>
+      </c>
       <c r="G588" t="s">
         <v>2993</v>
       </c>
@@ -39127,7 +39270,9 @@
       <c r="K588">
         <v>2021</v>
       </c>
-      <c r="P588" s="8"/>
+      <c r="P588" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="589" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A589" t="s">
@@ -39136,6 +39281,9 @@
       <c r="B589" t="s">
         <v>2996</v>
       </c>
+      <c r="E589" t="s">
+        <v>2482</v>
+      </c>
       <c r="G589" t="s">
         <v>2997</v>
       </c>
@@ -39151,7 +39299,9 @@
       <c r="K589">
         <v>2024</v>
       </c>
-      <c r="P589" s="8"/>
+      <c r="P589" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="590" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A590" t="s">
@@ -39160,6 +39310,9 @@
       <c r="B590" t="s">
         <v>3000</v>
       </c>
+      <c r="E590" t="s">
+        <v>2482</v>
+      </c>
       <c r="G590" t="s">
         <v>3001</v>
       </c>
@@ -39175,7 +39328,9 @@
       <c r="K590">
         <v>2014</v>
       </c>
-      <c r="P590" s="8"/>
+      <c r="P590" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="591" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A591" t="s">
@@ -39184,6 +39339,9 @@
       <c r="B591" t="s">
         <v>3005</v>
       </c>
+      <c r="E591" t="s">
+        <v>2482</v>
+      </c>
       <c r="G591" t="s">
         <v>3006</v>
       </c>
@@ -39199,7 +39357,9 @@
       <c r="K591">
         <v>2016</v>
       </c>
-      <c r="P591" s="8"/>
+      <c r="P591" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="592" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A592" t="s">
@@ -39208,6 +39368,9 @@
       <c r="B592" t="s">
         <v>3010</v>
       </c>
+      <c r="E592" t="s">
+        <v>2482</v>
+      </c>
       <c r="G592" t="s">
         <v>3011</v>
       </c>
@@ -39223,7 +39386,9 @@
       <c r="K592">
         <v>2023</v>
       </c>
-      <c r="P592" s="8"/>
+      <c r="P592" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="593" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A593" t="s">
@@ -39232,6 +39397,9 @@
       <c r="B593" t="s">
         <v>3014</v>
       </c>
+      <c r="E593" t="s">
+        <v>2482</v>
+      </c>
       <c r="G593" t="s">
         <v>3015</v>
       </c>
@@ -39247,7 +39415,9 @@
       <c r="K593">
         <v>2009</v>
       </c>
-      <c r="P593" s="8"/>
+      <c r="P593" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="594" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A594" t="s">
@@ -39256,6 +39426,9 @@
       <c r="B594" t="s">
         <v>3018</v>
       </c>
+      <c r="E594" t="s">
+        <v>2482</v>
+      </c>
       <c r="G594" t="s">
         <v>3019</v>
       </c>
@@ -39271,7 +39444,9 @@
       <c r="K594">
         <v>2018</v>
       </c>
-      <c r="P594" s="8"/>
+      <c r="P594" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="595" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A595" t="s">
@@ -39280,6 +39455,9 @@
       <c r="B595" t="s">
         <v>3022</v>
       </c>
+      <c r="E595" t="s">
+        <v>2482</v>
+      </c>
       <c r="G595" t="s">
         <v>3023</v>
       </c>
@@ -39295,7 +39473,9 @@
       <c r="K595">
         <v>2020</v>
       </c>
-      <c r="P595" s="8"/>
+      <c r="P595" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="596" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A596" t="s">
@@ -39304,6 +39484,9 @@
       <c r="B596" t="s">
         <v>3027</v>
       </c>
+      <c r="E596" t="s">
+        <v>2482</v>
+      </c>
       <c r="G596" t="s">
         <v>3028</v>
       </c>
@@ -39319,7 +39502,9 @@
       <c r="K596">
         <v>2002</v>
       </c>
-      <c r="P596" s="8"/>
+      <c r="P596" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="597" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A597" t="s">
@@ -39328,6 +39513,9 @@
       <c r="B597" t="s">
         <v>3032</v>
       </c>
+      <c r="E597" t="s">
+        <v>2482</v>
+      </c>
       <c r="G597" t="s">
         <v>3033</v>
       </c>
@@ -39343,7 +39531,9 @@
       <c r="K597">
         <v>1994</v>
       </c>
-      <c r="P597" s="8"/>
+      <c r="P597" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="598" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A598" t="s">
@@ -39352,6 +39542,9 @@
       <c r="B598" t="s">
         <v>3036</v>
       </c>
+      <c r="E598" t="s">
+        <v>2482</v>
+      </c>
       <c r="G598" t="s">
         <v>3037</v>
       </c>
@@ -39367,7 +39560,9 @@
       <c r="K598">
         <v>2021</v>
       </c>
-      <c r="P598" s="8"/>
+      <c r="P598" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="599" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A599" t="s">
@@ -39376,6 +39571,9 @@
       <c r="B599" t="s">
         <v>3040</v>
       </c>
+      <c r="E599" t="s">
+        <v>2482</v>
+      </c>
       <c r="G599" t="s">
         <v>3041</v>
       </c>
@@ -39391,7 +39589,9 @@
       <c r="K599">
         <v>2025</v>
       </c>
-      <c r="P599" s="8"/>
+      <c r="P599" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="600" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A600" t="s">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="g:\My Drive\UCL\BSMA\BSMA ANTIGRAVITY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9EE6C0-8A7F-4923-9FB2-7268B4377624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CC570EA-EFF6-4877-9798-FA8E6D24F5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="3655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5951" uniqueCount="3655">
   <si>
     <t>Coder Initials</t>
   </si>
@@ -39600,6 +39600,9 @@
       <c r="B600" t="s">
         <v>3044</v>
       </c>
+      <c r="E600" t="s">
+        <v>2482</v>
+      </c>
       <c r="G600" t="s">
         <v>3045</v>
       </c>
@@ -39615,7 +39618,9 @@
       <c r="K600">
         <v>2021</v>
       </c>
-      <c r="P600" s="8"/>
+      <c r="P600" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="601" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A601" t="s">
@@ -39624,6 +39629,9 @@
       <c r="B601" t="s">
         <v>3048</v>
       </c>
+      <c r="E601" t="s">
+        <v>2482</v>
+      </c>
       <c r="G601" t="s">
         <v>3049</v>
       </c>
@@ -39639,7 +39647,9 @@
       <c r="K601">
         <v>2024</v>
       </c>
-      <c r="P601" s="8"/>
+      <c r="P601" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="602" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A602" t="s">
@@ -39648,6 +39658,9 @@
       <c r="B602" t="s">
         <v>3052</v>
       </c>
+      <c r="E602" t="s">
+        <v>2482</v>
+      </c>
       <c r="G602" t="s">
         <v>3053</v>
       </c>
@@ -39663,7 +39676,9 @@
       <c r="K602">
         <v>2024</v>
       </c>
-      <c r="P602" s="8"/>
+      <c r="P602" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="603" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A603" t="s">
@@ -39672,6 +39687,9 @@
       <c r="B603" t="s">
         <v>3056</v>
       </c>
+      <c r="E603" t="s">
+        <v>2482</v>
+      </c>
       <c r="G603" t="s">
         <v>3057</v>
       </c>
@@ -39687,7 +39705,9 @@
       <c r="K603">
         <v>2018</v>
       </c>
-      <c r="P603" s="8"/>
+      <c r="P603" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="604" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A604" t="s">
@@ -39696,6 +39716,9 @@
       <c r="B604" t="s">
         <v>3061</v>
       </c>
+      <c r="E604" t="s">
+        <v>2482</v>
+      </c>
       <c r="G604" t="s">
         <v>3062</v>
       </c>
@@ -39711,7 +39734,9 @@
       <c r="K604">
         <v>2014</v>
       </c>
-      <c r="P604" s="8"/>
+      <c r="P604" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="605" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A605" t="s">
@@ -39720,6 +39745,9 @@
       <c r="B605" t="s">
         <v>3065</v>
       </c>
+      <c r="E605" t="s">
+        <v>2482</v>
+      </c>
       <c r="G605" t="s">
         <v>3066</v>
       </c>
@@ -39735,7 +39763,9 @@
       <c r="K605">
         <v>2019</v>
       </c>
-      <c r="P605" s="8"/>
+      <c r="P605" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="606" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A606" t="s">
@@ -39744,6 +39774,9 @@
       <c r="B606" t="s">
         <v>3069</v>
       </c>
+      <c r="E606" t="s">
+        <v>2482</v>
+      </c>
       <c r="G606" t="s">
         <v>3070</v>
       </c>
@@ -39759,7 +39792,9 @@
       <c r="K606">
         <v>2024</v>
       </c>
-      <c r="P606" s="8"/>
+      <c r="P606" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="607" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A607" t="s">
@@ -39768,6 +39803,9 @@
       <c r="B607" t="s">
         <v>3074</v>
       </c>
+      <c r="E607" t="s">
+        <v>2482</v>
+      </c>
       <c r="G607" t="s">
         <v>3075</v>
       </c>
@@ -39783,7 +39821,9 @@
       <c r="K607">
         <v>2024</v>
       </c>
-      <c r="P607" s="8"/>
+      <c r="P607" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="608" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A608" t="s">
@@ -39792,6 +39832,9 @@
       <c r="B608" t="s">
         <v>3078</v>
       </c>
+      <c r="E608" t="s">
+        <v>2482</v>
+      </c>
       <c r="G608" t="s">
         <v>3079</v>
       </c>
@@ -39807,7 +39850,9 @@
       <c r="K608">
         <v>2021</v>
       </c>
-      <c r="P608" s="8"/>
+      <c r="P608" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="609" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A609" t="s">
@@ -39816,6 +39861,9 @@
       <c r="B609" t="s">
         <v>3082</v>
       </c>
+      <c r="E609" t="s">
+        <v>2482</v>
+      </c>
       <c r="G609" t="s">
         <v>3083</v>
       </c>
@@ -39831,7 +39879,9 @@
       <c r="K609">
         <v>2022</v>
       </c>
-      <c r="P609" s="8"/>
+      <c r="P609" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="610" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A610" t="s">
@@ -39840,6 +39890,9 @@
       <c r="B610" t="s">
         <v>3087</v>
       </c>
+      <c r="E610" t="s">
+        <v>2482</v>
+      </c>
       <c r="G610" t="s">
         <v>3088</v>
       </c>
@@ -39855,7 +39908,9 @@
       <c r="K610">
         <v>2020</v>
       </c>
-      <c r="P610" s="8"/>
+      <c r="P610" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="611" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A611" t="s">
@@ -39888,6 +39943,9 @@
       <c r="B612" t="s">
         <v>3094</v>
       </c>
+      <c r="E612" t="s">
+        <v>2482</v>
+      </c>
       <c r="G612" t="s">
         <v>3095</v>
       </c>
@@ -39903,7 +39961,9 @@
       <c r="K612">
         <v>2023</v>
       </c>
-      <c r="P612" s="8"/>
+      <c r="P612" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="613" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A613" t="s">
@@ -39912,6 +39972,9 @@
       <c r="B613" t="s">
         <v>3099</v>
       </c>
+      <c r="E613" t="s">
+        <v>2482</v>
+      </c>
       <c r="G613" t="s">
         <v>3100</v>
       </c>
@@ -39927,7 +39990,9 @@
       <c r="K613">
         <v>2023</v>
       </c>
-      <c r="P613" s="8"/>
+      <c r="P613" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="614" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A614" t="s">
@@ -39936,6 +40001,9 @@
       <c r="B614" t="s">
         <v>3103</v>
       </c>
+      <c r="E614" t="s">
+        <v>2482</v>
+      </c>
       <c r="G614" t="s">
         <v>3104</v>
       </c>
@@ -39951,7 +40019,9 @@
       <c r="K614">
         <v>2022</v>
       </c>
-      <c r="P614" s="8"/>
+      <c r="P614" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="615" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A615" t="s">
@@ -39960,6 +40030,9 @@
       <c r="B615" t="s">
         <v>3107</v>
       </c>
+      <c r="E615" t="s">
+        <v>2482</v>
+      </c>
       <c r="G615" t="s">
         <v>3108</v>
       </c>
@@ -39975,7 +40048,9 @@
       <c r="K615">
         <v>2022</v>
       </c>
-      <c r="P615" s="8"/>
+      <c r="P615" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="616" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A616" t="s">
@@ -39984,6 +40059,9 @@
       <c r="B616" t="s">
         <v>3112</v>
       </c>
+      <c r="E616" t="s">
+        <v>2482</v>
+      </c>
       <c r="G616" t="s">
         <v>3113</v>
       </c>
@@ -39999,7 +40077,9 @@
       <c r="K616">
         <v>2019</v>
       </c>
-      <c r="P616" s="8"/>
+      <c r="P616" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="617" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A617" t="s">
@@ -40008,6 +40088,9 @@
       <c r="B617" t="s">
         <v>3116</v>
       </c>
+      <c r="E617" t="s">
+        <v>2482</v>
+      </c>
       <c r="G617" t="s">
         <v>3117</v>
       </c>
@@ -40023,7 +40106,9 @@
       <c r="K617">
         <v>2024</v>
       </c>
-      <c r="P617" s="8"/>
+      <c r="P617" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="618" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A618" t="s">
@@ -40032,6 +40117,9 @@
       <c r="B618" t="s">
         <v>3121</v>
       </c>
+      <c r="E618" t="s">
+        <v>2482</v>
+      </c>
       <c r="G618" t="s">
         <v>3122</v>
       </c>
@@ -40047,7 +40135,9 @@
       <c r="K618">
         <v>2022</v>
       </c>
-      <c r="P618" s="8"/>
+      <c r="P618" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="619" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A619" t="s">
@@ -40056,6 +40146,9 @@
       <c r="B619" t="s">
         <v>3125</v>
       </c>
+      <c r="E619" t="s">
+        <v>2482</v>
+      </c>
       <c r="G619" t="s">
         <v>3126</v>
       </c>
@@ -40071,7 +40164,9 @@
       <c r="K619">
         <v>1995</v>
       </c>
-      <c r="P619" s="8"/>
+      <c r="P619" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="620" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A620" t="s">
@@ -40080,6 +40175,9 @@
       <c r="B620" t="s">
         <v>3129</v>
       </c>
+      <c r="E620" t="s">
+        <v>2482</v>
+      </c>
       <c r="G620" t="s">
         <v>3130</v>
       </c>
@@ -40095,7 +40193,9 @@
       <c r="K620">
         <v>1992</v>
       </c>
-      <c r="P620" s="8"/>
+      <c r="P620" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="621" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A621" t="s">
@@ -40104,6 +40204,9 @@
       <c r="B621" t="s">
         <v>3134</v>
       </c>
+      <c r="E621" t="s">
+        <v>2482</v>
+      </c>
       <c r="G621" t="s">
         <v>3135</v>
       </c>
@@ -40119,7 +40222,9 @@
       <c r="K621">
         <v>2021</v>
       </c>
-      <c r="P621" s="8"/>
+      <c r="P621" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="622" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A622" t="s">
@@ -40128,6 +40233,9 @@
       <c r="B622" t="s">
         <v>3139</v>
       </c>
+      <c r="E622" t="s">
+        <v>2482</v>
+      </c>
       <c r="G622" t="s">
         <v>3140</v>
       </c>
@@ -40143,7 +40251,9 @@
       <c r="K622">
         <v>2018</v>
       </c>
-      <c r="P622" s="8"/>
+      <c r="P622" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="623" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A623" t="s">
@@ -40152,6 +40262,9 @@
       <c r="B623" t="s">
         <v>3143</v>
       </c>
+      <c r="E623" t="s">
+        <v>2482</v>
+      </c>
       <c r="G623" t="s">
         <v>3144</v>
       </c>
@@ -40167,7 +40280,9 @@
       <c r="K623">
         <v>2019</v>
       </c>
-      <c r="P623" s="8"/>
+      <c r="P623" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="624" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A624" t="s">
@@ -40176,6 +40291,9 @@
       <c r="B624" t="s">
         <v>3148</v>
       </c>
+      <c r="E624" t="s">
+        <v>2482</v>
+      </c>
       <c r="G624" t="s">
         <v>3149</v>
       </c>
@@ -40191,7 +40309,9 @@
       <c r="K624">
         <v>2016</v>
       </c>
-      <c r="P624" s="8"/>
+      <c r="P624" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="625" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A625" t="s">
@@ -40200,6 +40320,9 @@
       <c r="B625" t="s">
         <v>3152</v>
       </c>
+      <c r="E625" t="s">
+        <v>2482</v>
+      </c>
       <c r="G625" t="s">
         <v>3153</v>
       </c>
@@ -40215,7 +40338,9 @@
       <c r="K625">
         <v>2002</v>
       </c>
-      <c r="P625" s="8"/>
+      <c r="P625" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="626" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A626" t="s">
@@ -40224,6 +40349,9 @@
       <c r="B626" t="s">
         <v>3156</v>
       </c>
+      <c r="E626" t="s">
+        <v>2482</v>
+      </c>
       <c r="G626" t="s">
         <v>3157</v>
       </c>
@@ -40239,7 +40367,9 @@
       <c r="K626">
         <v>2018</v>
       </c>
-      <c r="P626" s="8"/>
+      <c r="P626" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="627" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A627" t="s">
@@ -40248,6 +40378,9 @@
       <c r="B627" t="s">
         <v>3161</v>
       </c>
+      <c r="E627" t="s">
+        <v>2482</v>
+      </c>
       <c r="G627" t="s">
         <v>3162</v>
       </c>
@@ -40263,7 +40396,9 @@
       <c r="K627">
         <v>2016</v>
       </c>
-      <c r="P627" s="8"/>
+      <c r="P627" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="628" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A628" t="s">
@@ -40272,6 +40407,9 @@
       <c r="B628" t="s">
         <v>3165</v>
       </c>
+      <c r="E628" t="s">
+        <v>2482</v>
+      </c>
       <c r="G628" t="s">
         <v>3166</v>
       </c>
@@ -40287,7 +40425,9 @@
       <c r="K628">
         <v>2004</v>
       </c>
-      <c r="P628" s="8"/>
+      <c r="P628" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="629" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A629" t="s">
@@ -40296,6 +40436,9 @@
       <c r="B629" t="s">
         <v>3169</v>
       </c>
+      <c r="E629" t="s">
+        <v>2482</v>
+      </c>
       <c r="G629" t="s">
         <v>3170</v>
       </c>
@@ -40311,7 +40454,9 @@
       <c r="K629">
         <v>2008</v>
       </c>
-      <c r="P629" s="8"/>
+      <c r="P629" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="630" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A630" t="s">
@@ -40320,6 +40465,9 @@
       <c r="B630" t="s">
         <v>3173</v>
       </c>
+      <c r="E630" t="s">
+        <v>2482</v>
+      </c>
       <c r="G630" t="s">
         <v>3174</v>
       </c>
@@ -40335,7 +40483,9 @@
       <c r="K630">
         <v>2014</v>
       </c>
-      <c r="P630" s="8"/>
+      <c r="P630" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="631" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A631" t="s">
@@ -40344,6 +40494,9 @@
       <c r="B631" t="s">
         <v>3177</v>
       </c>
+      <c r="E631" t="s">
+        <v>2482</v>
+      </c>
       <c r="G631" t="s">
         <v>3178</v>
       </c>
@@ -40359,7 +40512,9 @@
       <c r="K631">
         <v>2004</v>
       </c>
-      <c r="P631" s="8"/>
+      <c r="P631" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="632" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A632" t="s">
@@ -40368,6 +40523,9 @@
       <c r="B632" t="s">
         <v>3181</v>
       </c>
+      <c r="E632" t="s">
+        <v>2482</v>
+      </c>
       <c r="G632" t="s">
         <v>3182</v>
       </c>
@@ -40383,7 +40541,9 @@
       <c r="K632">
         <v>1994</v>
       </c>
-      <c r="P632" s="8"/>
+      <c r="P632" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="633" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A633" t="s">
@@ -40392,6 +40552,9 @@
       <c r="B633" t="s">
         <v>3186</v>
       </c>
+      <c r="E633" t="s">
+        <v>2482</v>
+      </c>
       <c r="G633" t="s">
         <v>3187</v>
       </c>
@@ -40407,7 +40570,9 @@
       <c r="K633">
         <v>2010</v>
       </c>
-      <c r="P633" s="8"/>
+      <c r="P633" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="634" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A634" t="s">
@@ -40416,6 +40581,9 @@
       <c r="B634" t="s">
         <v>3191</v>
       </c>
+      <c r="E634" t="s">
+        <v>2482</v>
+      </c>
       <c r="G634" t="s">
         <v>3192</v>
       </c>
@@ -40431,7 +40599,9 @@
       <c r="K634">
         <v>2025</v>
       </c>
-      <c r="P634" s="8"/>
+      <c r="P634" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="635" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A635" t="s">
@@ -40440,6 +40610,9 @@
       <c r="B635" t="s">
         <v>3195</v>
       </c>
+      <c r="E635" t="s">
+        <v>2482</v>
+      </c>
       <c r="G635" t="s">
         <v>3196</v>
       </c>
@@ -40455,7 +40628,9 @@
       <c r="K635">
         <v>2020</v>
       </c>
-      <c r="P635" s="8"/>
+      <c r="P635" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="636" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A636" t="s">
@@ -40464,6 +40639,9 @@
       <c r="B636" t="s">
         <v>3199</v>
       </c>
+      <c r="E636" t="s">
+        <v>2482</v>
+      </c>
       <c r="G636" t="s">
         <v>3200</v>
       </c>
@@ -40479,7 +40657,9 @@
       <c r="K636">
         <v>2017</v>
       </c>
-      <c r="P636" s="8"/>
+      <c r="P636" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="637" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A637" t="s">
@@ -40488,6 +40668,9 @@
       <c r="B637" t="s">
         <v>3204</v>
       </c>
+      <c r="E637" t="s">
+        <v>2482</v>
+      </c>
       <c r="G637" t="s">
         <v>3205</v>
       </c>
@@ -40503,7 +40686,9 @@
       <c r="K637">
         <v>2025</v>
       </c>
-      <c r="P637" s="8"/>
+      <c r="P637" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="638" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A638" t="s">
@@ -40512,6 +40697,9 @@
       <c r="B638" t="s">
         <v>3208</v>
       </c>
+      <c r="E638" t="s">
+        <v>2482</v>
+      </c>
       <c r="G638" t="s">
         <v>3209</v>
       </c>
@@ -40527,7 +40715,9 @@
       <c r="K638">
         <v>2023</v>
       </c>
-      <c r="P638" s="8"/>
+      <c r="P638" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="639" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A639" t="s">
@@ -40536,6 +40726,9 @@
       <c r="B639" t="s">
         <v>3212</v>
       </c>
+      <c r="E639" t="s">
+        <v>2482</v>
+      </c>
       <c r="G639" t="s">
         <v>3213</v>
       </c>
@@ -40551,7 +40744,9 @@
       <c r="K639">
         <v>2009</v>
       </c>
-      <c r="P639" s="8"/>
+      <c r="P639" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="640" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A640" t="s">
@@ -40560,6 +40755,9 @@
       <c r="B640" t="s">
         <v>3217</v>
       </c>
+      <c r="E640" t="s">
+        <v>2482</v>
+      </c>
       <c r="G640" t="s">
         <v>3218</v>
       </c>
@@ -40575,7 +40773,9 @@
       <c r="K640">
         <v>2024</v>
       </c>
-      <c r="P640" s="8"/>
+      <c r="P640" s="8" t="s">
+        <v>2486</v>
+      </c>
     </row>
     <row r="641" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A641" t="s">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="g:\My Drive\UCL\BSMA\BSMA ANTIGRAVITY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{440B0BEE-5CF2-4B14-A532-E99C162AE376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7EAC10-4639-4902-9611-3F58DC639FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5899" uniqueCount="3663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5952" uniqueCount="3666">
   <si>
     <t>Coder Initials</t>
   </si>
@@ -7844,6 +7844,9 @@
     <t>BSMA0480</t>
   </si>
   <si>
+    <t>ERROR</t>
+  </si>
+  <si>
     <t>This study examined the transdisciplinary area of cognitive science, and was framed around the sociological notion of the boundary object. Harmonizing theoretical and technical approaches, methods introduced in this work moved beyond qualitative study practices traditional to boundary object theory work to a mixed-methods data-driven approach. Bibliometric Web of Science data, enriched with National Science Foundation (NSF) journal classifications, formed the foundation from which a seed-and-expand dataset were created from journals containing the string cogni* and their cited articles for the years 2006–2016. This two-tiered dataset allowed for the analysis of boundary-spanning interdisciplinary concepts, as identified by noun phrases, and their inhabitance within the intellectual space of the NSF taxonomy. The most interdisciplinary concepts were analyzed for their conceptual periphera using term co-occurrences, and the underlying sociological structures of co-authorship. Two concepts met the criterion of publication in all six core-level NSF disciplines resulted in two for this analysis:" children's," and" case study." Clearer clusters of term co-occurrences were present for" children's" than were for" case study," demonstrating the conceptual periphera. The underlying social structures for" children's" were more interconnected than those for" case study." The findings of this study suggest that different types of research problems, in conjunction with the methodology used to explore them, may be more useful to pinpoint boundary-inhabiting interdisciplinary epistemologies and other conceptual phenomena than the examination of broadly defined boundary-spanning concepts alone.</t>
   </si>
   <si>
@@ -8005,6 +8008,9 @@
     <t>Rodriguez-Escudero, Ana I.; Carbonell, Pilar; Perez-Fernandez, Hector; Garcia, Victor Temprano</t>
   </si>
   <si>
+    <t>The study measures boundary spanning at the team level, where key informants report on the activities of the entire NPD team, and the unit of analysis is the project/team (N = 140 NPD projects).. Verbatim Evidence: ""</t>
+  </si>
+  <si>
     <t>BSMA0492</t>
   </si>
   <si>
@@ -8084,6 +8090,9 @@
   </si>
   <si>
     <t>BSMA0498</t>
+  </si>
+  <si>
+    <t>exclude</t>
   </si>
   <si>
     <t>A model of cross-functional project groups was developed and hypotheses were tested in a study of 93 research and new product development groups from four companies. The results showed that functional diversity had indirect effects through external communication on one-year-later measures. Technical quality and schedule and budget performance improved, but group cohesiveness diminished. Functional diversity also had an indirect effect through job stress on group cohesiveness, which was again reduced. Implications for the development of conceptual models of cross-functional groups and their effective management are discussed.</t>
@@ -8178,6 +8187,9 @@
     <t>BSMA0504</t>
   </si>
   <si>
+    <t>Exclude</t>
+  </si>
+  <si>
     <t>This paper considers the mutual value co-creation that can occur when both parties in a cross sector partnership learn to innovate within the relationship. Despite suggestions that there are often asymmetrical returns to the business partner, nonproﬁt partners also accrue beneﬁts (Austin &amp; Seitanidi, 2012). In particular we consider how the relationship is inﬂuenced by the actors’ abilities to accommodate, adapt, learn and co-create solutions as they learn how to do things differently or better in response to the challenges they face. This is achieved using data from a longitudinal analysis of a crosssector partnership between a business and an arts organisation in Ireland. This offers a unique opportunity to trace the emergence of the partnership over time, and, speciﬁcally, to consider the impact of innovations co-created by the actors involved. Our analysis will demonstrate that innovation at the level of the relationship emerged from the incremental problem solving processes of the individuals involved. This foregrounds the impact of individual boundary spanners and the import of social capital in realising the potential of this partnership. In this regard we put forward three key boundary spanning roles, boundary spanner as network builder, as entrepreneur, as facilitator/mediator. The paper concludes with suggestions for further research and consideration of managerial implications arising from this study.</t>
   </si>
   <si>
@@ -8235,6 +8247,9 @@
     <t>BSMA0508</t>
   </si>
   <si>
+    <t>0 = Valid</t>
+  </si>
+  <si>
     <t>Purpose – Drawing on the conservation of resources theory, this research examines the relationship between managers’ servant leadership and frontline employees’ customer-oriented boundary-spanning behaviors by considering career meaningfulness as an underlying mechanism. Furthermore, this study investigates a moderated mediation model by proposing work centrality as a boundary condition in the relationship between career meaningfulness and customer-oriented boundary-spanning behaviors.</t>
   </si>
   <si>
@@ -8335,6 +8350,9 @@
   </si>
   <si>
     <t>BSMA0516</t>
+  </si>
+  <si>
+    <t>Include</t>
   </si>
   <si>
     <t>This study investigates the role of entrepreneurial attitudes for small and medium‐sized enterprise managers' tendency to create knowledge acquisition ties with managers of other organizations in the context of an institutionalized high‐tech cluster. We examine how innovation orientation, perceived personal control, need for achievement, and self‐esteem influence boundary‐spanning tie creation as a crucial facet of entrepreneurial behavior in the cluster context. Applying exponential random graph models to survey data collected in a German biotech cluster, we find that innovation orientation and perceived personal control positively affect managers' tendency to rely on interpersonal ties to gather knowledge. In contrast, need for achievement and self‐esteem are negatively related to knowledge tie creation.</t>
@@ -9985,9 +10003,6 @@
     <t>BSMA0639</t>
   </si>
   <si>
-    <t>exclude</t>
-  </si>
-  <si>
     <t>Resources are basic element of business model innovation, but most enterprises face serious resource constraints due to their capability limitations. This study focuses on boundary-spanning behaviour of top management team and bricolage, to explore their inﬂuence mechanism on business model innovation. A hierarchical regression analysis is carried out on data from China. Responses from 163 enterprises indicate that top management team boundary-spanning behaviour has a signiﬁcantly positive inﬂuence on business model innovation, that bricolage has a signiﬁcantly positive eﬀect on business model innovation, and that bricolage plays a signiﬁcant intermediary role between top management team boundary-spanning behaviour and business model innovation. This study enriches theoretical and empirical researches on business model innovation while serving as a valuable reference for business practice.</t>
   </si>
   <si>
@@ -10273,9 +10288,6 @@
     <t>BSMA0661</t>
   </si>
   <si>
-    <t>Exclude</t>
-  </si>
-  <si>
     <t>Based on upper echelons, paradox, and social capital theory, this study extends the association of CEO vision articulation and feedback-seeking behavior with ﬁrm sustainability by identifying the mediating role of eco-innovation and top management team (TMT) boundary-spanning behavior as a moderator. By analyzing the data of mid-sized to large Chinese ﬁrms using hierarchical regression and bootstrapping-based moderated path analysis, we found that product and process eco-innovation mediates the link between CEO vision articulation and ﬁrm sustainability while CEO feedbackseeking behavior enhances ﬁrm’s sustainability through product eco-innovation only. Finally, conditional indirect effects show the vital role of TMT boundary-spanning behavior in facilitating CEOs to improve the ﬁrm’s long-term sustainability through eco-innovation.</t>
   </si>
   <si>
@@ -10472,9 +10484,6 @@
   </si>
   <si>
     <t>BSMA0676</t>
-  </si>
-  <si>
-    <t>ERROR</t>
   </si>
   <si>
     <t>In this dissertation, I attempt to study the antecedents, processes, and
@@ -21123,7 +21132,7 @@
         <v>2002</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>3501</v>
+        <v>3504</v>
       </c>
     </row>
     <row r="5" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21219,7 +21228,7 @@
         <v>2016</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>3502</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="8" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21379,7 +21388,7 @@
         <v>2008</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>3503</v>
+        <v>3506</v>
       </c>
     </row>
     <row r="13" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21411,7 +21420,7 @@
         <v>2012</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>3504</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="14" spans="1:50" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21699,7 +21708,7 @@
         <v>1992</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>3505</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21827,7 +21836,7 @@
         <v>2024</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>3506</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -21859,7 +21868,7 @@
         <v>2017</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>3507</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22019,7 +22028,7 @@
         <v>2022</v>
       </c>
       <c r="P32" s="8" t="s">
-        <v>3508</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22144,7 +22153,7 @@
         <v>2020</v>
       </c>
       <c r="P36" s="8" t="s">
-        <v>3509</v>
+        <v>3512</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22240,7 +22249,7 @@
         <v>1997</v>
       </c>
       <c r="P39" s="8" t="s">
-        <v>3510</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22304,7 +22313,7 @@
         <v>2021</v>
       </c>
       <c r="P41" s="8" t="s">
-        <v>3511</v>
+        <v>3514</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22708,7 +22717,7 @@
         <v>2018</v>
       </c>
       <c r="P54" s="8" t="s">
-        <v>3512</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22737,7 +22746,7 @@
         <v>2015</v>
       </c>
       <c r="P55" s="8" t="s">
-        <v>3513</v>
+        <v>3516</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -22923,7 +22932,7 @@
         <v>2011</v>
       </c>
       <c r="P61" s="8" t="s">
-        <v>3514</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23176,7 +23185,7 @@
         <v>2012</v>
       </c>
       <c r="P69" s="8" t="s">
-        <v>3515</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23429,7 +23438,7 @@
         <v>2025</v>
       </c>
       <c r="P77" s="8" t="s">
-        <v>3516</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23461,7 +23470,7 @@
         <v>2023</v>
       </c>
       <c r="P78" s="8" t="s">
-        <v>3517</v>
+        <v>3520</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23493,7 +23502,7 @@
         <v>2019</v>
       </c>
       <c r="P79" s="8" t="s">
-        <v>3518</v>
+        <v>3521</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23621,7 +23630,7 @@
         <v>2005</v>
       </c>
       <c r="P83" s="8" t="s">
-        <v>3519</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23653,7 +23662,7 @@
         <v>2020</v>
       </c>
       <c r="P84" s="8" t="s">
-        <v>3520</v>
+        <v>3523</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23682,7 +23691,7 @@
         <v>2021</v>
       </c>
       <c r="P85" s="8" t="s">
-        <v>3521</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23874,7 +23883,7 @@
         <v>2010</v>
       </c>
       <c r="P91" s="8" t="s">
-        <v>3522</v>
+        <v>3525</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -23970,7 +23979,7 @@
         <v>2024</v>
       </c>
       <c r="P94" s="8" t="s">
-        <v>3523</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24002,7 +24011,7 @@
         <v>2020</v>
       </c>
       <c r="P95" s="8" t="s">
-        <v>3524</v>
+        <v>3527</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24063,7 +24072,7 @@
         <v>2021</v>
       </c>
       <c r="P97" s="8" t="s">
-        <v>3525</v>
+        <v>3528</v>
       </c>
     </row>
     <row r="98" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24092,7 +24101,7 @@
         <v>2012</v>
       </c>
       <c r="P98" s="8" t="s">
-        <v>3526</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="99" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24156,7 +24165,7 @@
         <v>1995</v>
       </c>
       <c r="P100" s="8" t="s">
-        <v>3527</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="101" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24188,7 +24197,7 @@
         <v>2008</v>
       </c>
       <c r="P101" s="8" t="s">
-        <v>3528</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="102" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24281,7 +24290,7 @@
         <v>2010</v>
       </c>
       <c r="P104" s="8" t="s">
-        <v>3529</v>
+        <v>3532</v>
       </c>
     </row>
     <row r="105" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24505,7 +24514,7 @@
         <v>2018</v>
       </c>
       <c r="P111" s="8" t="s">
-        <v>3530</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="112" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24601,7 +24610,7 @@
         <v>2018</v>
       </c>
       <c r="P114" s="8" t="s">
-        <v>3531</v>
+        <v>3534</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24729,7 +24738,7 @@
         <v>2016</v>
       </c>
       <c r="P118" s="8" t="s">
-        <v>3532</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24758,7 +24767,7 @@
         <v>1978</v>
       </c>
       <c r="P119" s="8" t="s">
-        <v>3533</v>
+        <v>3536</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24822,7 +24831,7 @@
         <v>2012</v>
       </c>
       <c r="P121" s="8" t="s">
-        <v>3534</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -24886,7 +24895,7 @@
         <v>2004</v>
       </c>
       <c r="P123" s="8" t="s">
-        <v>3535</v>
+        <v>3538</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25133,7 +25142,7 @@
         <v>1996</v>
       </c>
       <c r="P131" s="8" t="s">
-        <v>3536</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="132" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25165,7 +25174,7 @@
         <v>2004</v>
       </c>
       <c r="P132" s="8" t="s">
-        <v>3537</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="133" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25229,7 +25238,7 @@
         <v>1990</v>
       </c>
       <c r="P134" s="8" t="s">
-        <v>3538</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="135" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25357,7 +25366,7 @@
         <v>1984</v>
       </c>
       <c r="P138" s="8" t="s">
-        <v>3539</v>
+        <v>3542</v>
       </c>
     </row>
     <row r="139" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25581,7 +25590,7 @@
         <v>2011</v>
       </c>
       <c r="P145" s="8" t="s">
-        <v>3540</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="146" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25613,7 +25622,7 @@
         <v>2003</v>
       </c>
       <c r="P146" s="8" t="s">
-        <v>3541</v>
+        <v>3544</v>
       </c>
     </row>
     <row r="147" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25773,7 +25782,7 @@
         <v>2014</v>
       </c>
       <c r="P151" s="8" t="s">
-        <v>3542</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="152" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25901,7 +25910,7 @@
         <v>2019</v>
       </c>
       <c r="P155" s="8" t="s">
-        <v>3543</v>
+        <v>3546</v>
       </c>
     </row>
     <row r="156" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -25965,7 +25974,7 @@
         <v>2009</v>
       </c>
       <c r="P157" s="8" t="s">
-        <v>3544</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="158" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26029,7 +26038,7 @@
         <v>2019</v>
       </c>
       <c r="P159" s="8" t="s">
-        <v>3545</v>
+        <v>3548</v>
       </c>
     </row>
     <row r="160" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26378,7 +26387,7 @@
         <v>1998</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>3546</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="171" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26599,7 +26608,7 @@
         <v>2022</v>
       </c>
       <c r="P177" s="8" t="s">
-        <v>3547</v>
+        <v>3550</v>
       </c>
     </row>
     <row r="178" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26663,7 +26672,7 @@
         <v>1997</v>
       </c>
       <c r="P179" s="8" t="s">
-        <v>3548</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="180" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26695,7 +26704,7 @@
         <v>2022</v>
       </c>
       <c r="P180" s="8" t="s">
-        <v>3549</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="181" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26887,7 +26896,7 @@
         <v>2023</v>
       </c>
       <c r="P186" s="8" t="s">
-        <v>3550</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="187" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -26919,7 +26928,7 @@
         <v>2013</v>
       </c>
       <c r="P187" s="8" t="s">
-        <v>3551</v>
+        <v>3554</v>
       </c>
     </row>
     <row r="188" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27108,7 +27117,7 @@
         <v>2010</v>
       </c>
       <c r="P193" s="8" t="s">
-        <v>3552</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="194" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27204,7 +27213,7 @@
         <v>2012</v>
       </c>
       <c r="P196" s="8" t="s">
-        <v>3553</v>
+        <v>3556</v>
       </c>
     </row>
     <row r="197" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27233,7 +27242,7 @@
         <v>2015</v>
       </c>
       <c r="P197" s="8" t="s">
-        <v>3554</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="198" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27297,7 +27306,7 @@
         <v>2015</v>
       </c>
       <c r="P199" s="8" t="s">
-        <v>3555</v>
+        <v>3558</v>
       </c>
     </row>
     <row r="200" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27457,7 +27466,7 @@
         <v>2005</v>
       </c>
       <c r="P204" s="8" t="s">
-        <v>3556</v>
+        <v>3559</v>
       </c>
     </row>
     <row r="205" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27550,7 +27559,7 @@
         <v>1998</v>
       </c>
       <c r="P207" s="8" t="s">
-        <v>3557</v>
+        <v>3560</v>
       </c>
     </row>
     <row r="208" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27582,7 +27591,7 @@
         <v>1999</v>
       </c>
       <c r="P208" s="8" t="s">
-        <v>3558</v>
+        <v>3561</v>
       </c>
     </row>
     <row r="209" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27672,7 +27681,7 @@
         <v>2024</v>
       </c>
       <c r="P211" s="8" t="s">
-        <v>3559</v>
+        <v>3562</v>
       </c>
     </row>
     <row r="212" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27704,7 +27713,7 @@
         <v>2006</v>
       </c>
       <c r="P212" s="8" t="s">
-        <v>3560</v>
+        <v>3563</v>
       </c>
     </row>
     <row r="213" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27736,7 +27745,7 @@
         <v>2010</v>
       </c>
       <c r="P213" s="8" t="s">
-        <v>3561</v>
+        <v>3564</v>
       </c>
     </row>
     <row r="214" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27797,7 +27806,7 @@
         <v>2017</v>
       </c>
       <c r="P215" s="8" t="s">
-        <v>3562</v>
+        <v>3565</v>
       </c>
     </row>
     <row r="216" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27925,7 +27934,7 @@
         <v>2014</v>
       </c>
       <c r="P219" s="8" t="s">
-        <v>3563</v>
+        <v>3566</v>
       </c>
     </row>
     <row r="220" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -27957,7 +27966,7 @@
         <v>2011</v>
       </c>
       <c r="P220" s="8" t="s">
-        <v>3564</v>
+        <v>3567</v>
       </c>
     </row>
     <row r="221" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28053,7 +28062,7 @@
         <v>2015</v>
       </c>
       <c r="P223" s="8" t="s">
-        <v>3565</v>
+        <v>3568</v>
       </c>
     </row>
     <row r="224" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28117,7 +28126,7 @@
         <v>2023</v>
       </c>
       <c r="P225" s="8" t="s">
-        <v>3566</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="226" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28146,7 +28155,7 @@
         <v>2004</v>
       </c>
       <c r="P226" s="8" t="s">
-        <v>3567</v>
+        <v>3570</v>
       </c>
     </row>
     <row r="227" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28242,7 +28251,7 @@
         <v>2005</v>
       </c>
       <c r="P229" s="8" t="s">
-        <v>3568</v>
+        <v>3571</v>
       </c>
     </row>
     <row r="230" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28274,7 +28283,7 @@
         <v>2004</v>
       </c>
       <c r="P230" s="8" t="s">
-        <v>3569</v>
+        <v>3572</v>
       </c>
     </row>
     <row r="231" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28370,7 +28379,7 @@
         <v>1998</v>
       </c>
       <c r="P233" s="8" t="s">
-        <v>3570</v>
+        <v>3573</v>
       </c>
     </row>
     <row r="234" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28466,7 +28475,7 @@
         <v>2014</v>
       </c>
       <c r="P236" s="8" t="s">
-        <v>3571</v>
+        <v>3574</v>
       </c>
     </row>
     <row r="237" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28687,7 +28696,7 @@
         <v>2011</v>
       </c>
       <c r="P243" s="8" t="s">
-        <v>3572</v>
+        <v>3575</v>
       </c>
     </row>
     <row r="244" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28719,7 +28728,7 @@
         <v>2018</v>
       </c>
       <c r="P244" s="8" t="s">
-        <v>3573</v>
+        <v>3576</v>
       </c>
     </row>
     <row r="245" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28751,7 +28760,7 @@
         <v>2019</v>
       </c>
       <c r="P245" s="8" t="s">
-        <v>3574</v>
+        <v>3577</v>
       </c>
     </row>
     <row r="246" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28783,7 +28792,7 @@
         <v>1998</v>
       </c>
       <c r="P246" s="8" t="s">
-        <v>3575</v>
+        <v>3578</v>
       </c>
     </row>
     <row r="247" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -28937,7 +28946,7 @@
         <v>2012</v>
       </c>
       <c r="P251" s="8" t="s">
-        <v>3576</v>
+        <v>3579</v>
       </c>
     </row>
     <row r="252" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29126,7 +29135,7 @@
         <v>1999</v>
       </c>
       <c r="P257" s="8" t="s">
-        <v>3577</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="258" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29190,7 +29199,7 @@
         <v>2022</v>
       </c>
       <c r="P259" s="8" t="s">
-        <v>3578</v>
+        <v>3581</v>
       </c>
     </row>
     <row r="260" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29347,7 +29356,7 @@
         <v>2023</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>3579</v>
+        <v>3582</v>
       </c>
     </row>
     <row r="265" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29408,7 +29417,7 @@
         <v>2023</v>
       </c>
       <c r="P266" s="8" t="s">
-        <v>3580</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="267" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29440,7 +29449,7 @@
         <v>2018</v>
       </c>
       <c r="P267" s="8" t="s">
-        <v>3581</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="268" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29472,7 +29481,7 @@
         <v>2025</v>
       </c>
       <c r="P268" s="8" t="s">
-        <v>3582</v>
+        <v>3585</v>
       </c>
     </row>
     <row r="269" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29501,7 +29510,7 @@
         <v>2010</v>
       </c>
       <c r="P269" s="8" t="s">
-        <v>3583</v>
+        <v>3586</v>
       </c>
     </row>
     <row r="270" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29591,7 +29600,7 @@
         <v>2002</v>
       </c>
       <c r="P272" s="8" t="s">
-        <v>3584</v>
+        <v>3587</v>
       </c>
     </row>
     <row r="273" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29684,7 +29693,7 @@
         <v>2020</v>
       </c>
       <c r="P275" s="8" t="s">
-        <v>3585</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="276" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29812,7 +29821,7 @@
         <v>1996</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>3586</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="280" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29841,7 +29850,7 @@
         <v>2020</v>
       </c>
       <c r="P280" s="8" t="s">
-        <v>3587</v>
+        <v>3590</v>
       </c>
     </row>
     <row r="281" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29873,7 +29882,7 @@
         <v>2003</v>
       </c>
       <c r="P281" s="8" t="s">
-        <v>3588</v>
+        <v>3591</v>
       </c>
     </row>
     <row r="282" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -29969,7 +29978,7 @@
         <v>2022</v>
       </c>
       <c r="P284" s="8" t="s">
-        <v>3589</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="285" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30001,7 +30010,7 @@
         <v>2000</v>
       </c>
       <c r="P285" s="8" t="s">
-        <v>3590</v>
+        <v>3593</v>
       </c>
     </row>
     <row r="286" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30408,7 +30417,7 @@
         <v>2024</v>
       </c>
       <c r="P298" s="8" t="s">
-        <v>3591</v>
+        <v>3594</v>
       </c>
     </row>
     <row r="299" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30562,7 +30571,7 @@
         <v>2011</v>
       </c>
       <c r="P303" s="8" t="s">
-        <v>3592</v>
+        <v>3595</v>
       </c>
     </row>
     <row r="304" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30623,7 +30632,7 @@
         <v>2022</v>
       </c>
       <c r="P305" s="8" t="s">
-        <v>3593</v>
+        <v>3596</v>
       </c>
     </row>
     <row r="306" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30681,7 +30690,7 @@
         <v>2022</v>
       </c>
       <c r="P307" s="8" t="s">
-        <v>3594</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="308" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30710,7 +30719,7 @@
         <v>2025</v>
       </c>
       <c r="P308" s="8" t="s">
-        <v>3595</v>
+        <v>3598</v>
       </c>
     </row>
     <row r="309" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -30739,7 +30748,7 @@
         <v>2002</v>
       </c>
       <c r="P309" s="8" t="s">
-        <v>3596</v>
+        <v>3599</v>
       </c>
     </row>
     <row r="310" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31088,7 +31097,7 @@
         <v>2008</v>
       </c>
       <c r="P320" s="8" t="s">
-        <v>3597</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="321" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31216,7 +31225,7 @@
         <v>2020</v>
       </c>
       <c r="P324" s="8" t="s">
-        <v>3598</v>
+        <v>3601</v>
       </c>
     </row>
     <row r="325" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31280,7 +31289,7 @@
         <v>2004</v>
       </c>
       <c r="P326" s="8" t="s">
-        <v>3599</v>
+        <v>3602</v>
       </c>
     </row>
     <row r="327" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31344,7 +31353,7 @@
         <v>2015</v>
       </c>
       <c r="P328" s="8" t="s">
-        <v>3600</v>
+        <v>3603</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31533,7 +31542,7 @@
         <v>1991</v>
       </c>
       <c r="P334" s="8" t="s">
-        <v>3601</v>
+        <v>3604</v>
       </c>
     </row>
     <row r="335" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31565,7 +31574,7 @@
         <v>2023</v>
       </c>
       <c r="P335" s="8" t="s">
-        <v>3602</v>
+        <v>3605</v>
       </c>
     </row>
     <row r="336" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31597,7 +31606,7 @@
         <v>2017</v>
       </c>
       <c r="P336" s="8" t="s">
-        <v>3603</v>
+        <v>3606</v>
       </c>
     </row>
     <row r="337" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31719,7 +31728,7 @@
         <v>2011</v>
       </c>
       <c r="P340" s="8" t="s">
-        <v>3604</v>
+        <v>3607</v>
       </c>
     </row>
     <row r="341" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31748,7 +31757,7 @@
         <v>2016</v>
       </c>
       <c r="P341" s="8" t="s">
-        <v>3605</v>
+        <v>3608</v>
       </c>
     </row>
     <row r="342" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31780,7 +31789,7 @@
         <v>2020</v>
       </c>
       <c r="P342" s="8" t="s">
-        <v>3606</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="343" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31844,7 +31853,7 @@
         <v>2017</v>
       </c>
       <c r="P344" s="8" t="s">
-        <v>3607</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="345" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31876,7 +31885,7 @@
         <v>2024</v>
       </c>
       <c r="P345" s="8" t="s">
-        <v>3608</v>
+        <v>3611</v>
       </c>
     </row>
     <row r="346" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31908,7 +31917,7 @@
         <v>2016</v>
       </c>
       <c r="P346" s="8" t="s">
-        <v>3609</v>
+        <v>3612</v>
       </c>
     </row>
     <row r="347" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -31940,7 +31949,7 @@
         <v>2022</v>
       </c>
       <c r="P347" s="8" t="s">
-        <v>3610</v>
+        <v>3613</v>
       </c>
     </row>
     <row r="348" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32068,7 +32077,7 @@
         <v>2002</v>
       </c>
       <c r="P351" s="8" t="s">
-        <v>3611</v>
+        <v>3614</v>
       </c>
     </row>
     <row r="352" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32097,7 +32106,7 @@
         <v>2022</v>
       </c>
       <c r="P352" s="8" t="s">
-        <v>3612</v>
+        <v>3615</v>
       </c>
     </row>
     <row r="353" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32161,7 +32170,7 @@
         <v>2020</v>
       </c>
       <c r="P354" s="8" t="s">
-        <v>3613</v>
+        <v>3616</v>
       </c>
     </row>
     <row r="355" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32193,7 +32202,7 @@
         <v>2024</v>
       </c>
       <c r="P355" s="8" t="s">
-        <v>3614</v>
+        <v>3617</v>
       </c>
     </row>
     <row r="356" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32225,7 +32234,7 @@
         <v>2000</v>
       </c>
       <c r="P356" s="8" t="s">
-        <v>3615</v>
+        <v>3618</v>
       </c>
     </row>
     <row r="357" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32321,7 +32330,7 @@
         <v>2023</v>
       </c>
       <c r="P359" s="8" t="s">
-        <v>3616</v>
+        <v>3619</v>
       </c>
     </row>
     <row r="360" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32350,7 +32359,7 @@
         <v>2018</v>
       </c>
       <c r="P360" s="8" t="s">
-        <v>3617</v>
+        <v>3620</v>
       </c>
     </row>
     <row r="361" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32379,7 +32388,7 @@
         <v>2014</v>
       </c>
       <c r="P361" s="8" t="s">
-        <v>3618</v>
+        <v>3621</v>
       </c>
     </row>
     <row r="362" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32411,7 +32420,7 @@
         <v>2013</v>
       </c>
       <c r="P362" s="8" t="s">
-        <v>3619</v>
+        <v>3622</v>
       </c>
     </row>
     <row r="363" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32443,7 +32452,7 @@
         <v>2025</v>
       </c>
       <c r="P363" s="8" t="s">
-        <v>3620</v>
+        <v>3623</v>
       </c>
     </row>
     <row r="364" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32635,7 +32644,7 @@
         <v>2023</v>
       </c>
       <c r="P369" s="8" t="s">
-        <v>3621</v>
+        <v>3624</v>
       </c>
     </row>
     <row r="370" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32731,7 +32740,7 @@
         <v>2023</v>
       </c>
       <c r="P372" s="8" t="s">
-        <v>3622</v>
+        <v>3625</v>
       </c>
     </row>
     <row r="373" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32827,7 +32836,7 @@
         <v>1999</v>
       </c>
       <c r="P375" s="8" t="s">
-        <v>3623</v>
+        <v>3626</v>
       </c>
     </row>
     <row r="376" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -32891,7 +32900,7 @@
         <v>2023</v>
       </c>
       <c r="P377" s="8" t="s">
-        <v>3624</v>
+        <v>3627</v>
       </c>
     </row>
     <row r="378" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33051,7 +33060,7 @@
         <v>2005</v>
       </c>
       <c r="P382" s="8" t="s">
-        <v>3625</v>
+        <v>3628</v>
       </c>
     </row>
     <row r="383" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33083,7 +33092,7 @@
         <v>2007</v>
       </c>
       <c r="P383" s="8" t="s">
-        <v>3626</v>
+        <v>3629</v>
       </c>
     </row>
     <row r="384" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33115,7 +33124,7 @@
         <v>2008</v>
       </c>
       <c r="P384" s="8" t="s">
-        <v>3627</v>
+        <v>3630</v>
       </c>
     </row>
     <row r="385" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33237,7 +33246,7 @@
         <v>2019</v>
       </c>
       <c r="P388" s="8" t="s">
-        <v>3628</v>
+        <v>3631</v>
       </c>
     </row>
     <row r="389" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33269,7 +33278,7 @@
         <v>1994</v>
       </c>
       <c r="P389" s="8" t="s">
-        <v>3629</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="390" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33333,7 +33342,7 @@
         <v>2016</v>
       </c>
       <c r="P391" s="8" t="s">
-        <v>3630</v>
+        <v>3633</v>
       </c>
     </row>
     <row r="392" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33365,7 +33374,7 @@
         <v>2015</v>
       </c>
       <c r="P392" s="8" t="s">
-        <v>3631</v>
+        <v>3634</v>
       </c>
     </row>
     <row r="393" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33490,7 +33499,7 @@
         <v>2003</v>
       </c>
       <c r="P396" s="8" t="s">
-        <v>3632</v>
+        <v>3635</v>
       </c>
     </row>
     <row r="397" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33586,7 +33595,7 @@
         <v>2005</v>
       </c>
       <c r="P399" s="8" t="s">
-        <v>3633</v>
+        <v>3636</v>
       </c>
     </row>
     <row r="400" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33618,7 +33627,7 @@
         <v>2010</v>
       </c>
       <c r="P400" s="8" t="s">
-        <v>3634</v>
+        <v>3637</v>
       </c>
     </row>
     <row r="401" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33647,7 +33656,7 @@
         <v>2022</v>
       </c>
       <c r="P401" s="8" t="s">
-        <v>3635</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="402" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33679,7 +33688,7 @@
         <v>2007</v>
       </c>
       <c r="P402" s="8" t="s">
-        <v>3636</v>
+        <v>3639</v>
       </c>
     </row>
     <row r="403" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33775,7 +33784,7 @@
         <v>2006</v>
       </c>
       <c r="P405" s="8" t="s">
-        <v>3637</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="406" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33807,7 +33816,7 @@
         <v>2007</v>
       </c>
       <c r="P406" s="8" t="s">
-        <v>3638</v>
+        <v>3641</v>
       </c>
     </row>
     <row r="407" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -33839,7 +33848,7 @@
         <v>2025</v>
       </c>
       <c r="P407" s="8" t="s">
-        <v>3639</v>
+        <v>3642</v>
       </c>
     </row>
     <row r="408" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34063,7 +34072,7 @@
         <v>2008</v>
       </c>
       <c r="P414" s="8" t="s">
-        <v>3640</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="415" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34249,7 +34258,7 @@
         <v>2011</v>
       </c>
       <c r="P420" s="8" t="s">
-        <v>3641</v>
+        <v>3644</v>
       </c>
     </row>
     <row r="421" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34278,7 +34287,7 @@
         <v>2008</v>
       </c>
       <c r="P421" s="8" t="s">
-        <v>3642</v>
+        <v>3645</v>
       </c>
     </row>
     <row r="422" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34627,7 +34636,7 @@
         <v>2019</v>
       </c>
       <c r="P432" s="8" t="s">
-        <v>3643</v>
+        <v>3646</v>
       </c>
     </row>
     <row r="433" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34723,7 +34732,7 @@
         <v>2014</v>
       </c>
       <c r="P435" s="8" t="s">
-        <v>3644</v>
+        <v>3647</v>
       </c>
     </row>
     <row r="436" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34755,7 +34764,7 @@
         <v>2005</v>
       </c>
       <c r="P436" s="8" t="s">
-        <v>3645</v>
+        <v>3648</v>
       </c>
     </row>
     <row r="437" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34819,7 +34828,7 @@
         <v>2019</v>
       </c>
       <c r="P438" s="8" t="s">
-        <v>3646</v>
+        <v>3649</v>
       </c>
     </row>
     <row r="439" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -34979,7 +34988,7 @@
         <v>2019</v>
       </c>
       <c r="P443" s="8" t="s">
-        <v>3647</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="444" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35043,7 +35052,7 @@
         <v>2013</v>
       </c>
       <c r="P445" s="8" t="s">
-        <v>3648</v>
+        <v>3651</v>
       </c>
     </row>
     <row r="446" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35107,7 +35116,7 @@
         <v>2013</v>
       </c>
       <c r="P447" s="8" t="s">
-        <v>3649</v>
+        <v>3652</v>
       </c>
     </row>
     <row r="448" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35325,7 +35334,7 @@
         <v>2003</v>
       </c>
       <c r="P454" s="8" t="s">
-        <v>3650</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="455" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35450,7 +35459,7 @@
         <v>2024</v>
       </c>
       <c r="P458" s="8" t="s">
-        <v>3651</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="459" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35514,7 +35523,7 @@
         <v>2024</v>
       </c>
       <c r="P460" s="8" t="s">
-        <v>3652</v>
+        <v>3655</v>
       </c>
     </row>
     <row r="461" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35546,7 +35555,7 @@
         <v>2023</v>
       </c>
       <c r="P461" s="8" t="s">
-        <v>3653</v>
+        <v>3656</v>
       </c>
     </row>
     <row r="462" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35706,7 +35715,7 @@
         <v>2017</v>
       </c>
       <c r="P466" s="8" t="s">
-        <v>3654</v>
+        <v>3657</v>
       </c>
     </row>
     <row r="467" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35770,7 +35779,7 @@
         <v>2012</v>
       </c>
       <c r="P468" s="8" t="s">
-        <v>3655</v>
+        <v>3658</v>
       </c>
     </row>
     <row r="469" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35799,7 +35808,7 @@
         <v>2021</v>
       </c>
       <c r="P469" s="8" t="s">
-        <v>3656</v>
+        <v>3659</v>
       </c>
     </row>
     <row r="470" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35831,7 +35840,7 @@
         <v>2022</v>
       </c>
       <c r="P470" s="8" t="s">
-        <v>3657</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="471" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35863,7 +35872,7 @@
         <v>2018</v>
       </c>
       <c r="P471" s="8" t="s">
-        <v>3658</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="472" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -35895,7 +35904,7 @@
         <v>2021</v>
       </c>
       <c r="P472" s="8" t="s">
-        <v>3659</v>
+        <v>3662</v>
       </c>
     </row>
     <row r="473" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36191,7 +36200,7 @@
         <v>2001</v>
       </c>
       <c r="P482" s="8" t="s">
-        <v>3660</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="483" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36201,17 +36210,23 @@
       <c r="B483" t="s">
         <v>2529</v>
       </c>
+      <c r="E483" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F483" t="s">
+        <v>252</v>
+      </c>
       <c r="G483" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="H483" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="I483" t="s">
         <v>51</v>
       </c>
       <c r="J483" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="K483">
         <v>2020</v>
@@ -36225,7 +36240,7 @@
         <v>43</v>
       </c>
       <c r="B484" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="E484" t="s">
         <v>85</v>
@@ -36234,22 +36249,22 @@
         <v>48</v>
       </c>
       <c r="G484" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="H484" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="I484" t="s">
         <v>1359</v>
       </c>
       <c r="J484" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="K484">
         <v>2013</v>
       </c>
       <c r="P484" s="8" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="485" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36257,19 +36272,25 @@
         <v>43</v>
       </c>
       <c r="B485" t="s">
-        <v>2538</v>
+        <v>2539</v>
+      </c>
+      <c r="E485" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F485" t="s">
+        <v>48</v>
       </c>
       <c r="G485" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="H485" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="I485" t="s">
         <v>295</v>
       </c>
       <c r="J485" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="K485">
         <v>2012</v>
@@ -36283,7 +36304,7 @@
         <v>43</v>
       </c>
       <c r="B486" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="E486" t="s">
         <v>85</v>
@@ -36292,22 +36313,22 @@
         <v>48</v>
       </c>
       <c r="G486" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="H486" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="I486" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="J486" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="K486">
         <v>1996</v>
       </c>
       <c r="P486" s="8" t="s">
-        <v>3661</v>
+        <v>3664</v>
       </c>
     </row>
     <row r="487" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36315,19 +36336,25 @@
         <v>43</v>
       </c>
       <c r="B487" t="s">
-        <v>2547</v>
+        <v>2548</v>
+      </c>
+      <c r="E487" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F487" t="s">
+        <v>48</v>
       </c>
       <c r="G487" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="H487" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="I487" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="J487" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="K487">
         <v>1995</v>
@@ -36341,19 +36368,22 @@
         <v>43</v>
       </c>
       <c r="B488" t="s">
-        <v>2552</v>
+        <v>2553</v>
+      </c>
+      <c r="E488" t="s">
+        <v>2530</v>
       </c>
       <c r="G488" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="H488" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="I488" t="s">
         <v>51</v>
       </c>
       <c r="J488" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="K488">
         <v>2002</v>
@@ -36367,19 +36397,22 @@
         <v>43</v>
       </c>
       <c r="B489" t="s">
-        <v>2556</v>
+        <v>2557</v>
+      </c>
+      <c r="E489" t="s">
+        <v>2530</v>
       </c>
       <c r="G489" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="H489" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="I489" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="J489" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="K489">
         <v>2023</v>
@@ -36393,19 +36426,22 @@
         <v>43</v>
       </c>
       <c r="B490" t="s">
-        <v>2561</v>
+        <v>2562</v>
+      </c>
+      <c r="E490" t="s">
+        <v>2530</v>
       </c>
       <c r="G490" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="H490" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="I490" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="J490" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="K490">
         <v>2011</v>
@@ -36419,19 +36455,22 @@
         <v>43</v>
       </c>
       <c r="B491" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E491" t="s">
+        <v>2530</v>
+      </c>
+      <c r="G491" t="s">
+        <v>2568</v>
+      </c>
+      <c r="H491" t="s">
+        <v>2569</v>
+      </c>
+      <c r="I491" t="s">
+        <v>2570</v>
+      </c>
+      <c r="J491" t="s">
         <v>2566</v>
-      </c>
-      <c r="G491" t="s">
-        <v>2567</v>
-      </c>
-      <c r="H491" t="s">
-        <v>2568</v>
-      </c>
-      <c r="I491" t="s">
-        <v>2569</v>
-      </c>
-      <c r="J491" t="s">
-        <v>2565</v>
       </c>
       <c r="K491">
         <v>2011</v>
@@ -36445,19 +36484,22 @@
         <v>43</v>
       </c>
       <c r="B492" t="s">
-        <v>2570</v>
+        <v>2571</v>
+      </c>
+      <c r="E492" t="s">
+        <v>2530</v>
       </c>
       <c r="G492" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="H492" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="I492" t="s">
         <v>51</v>
       </c>
       <c r="J492" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="K492">
         <v>1984</v>
@@ -36471,19 +36513,25 @@
         <v>43</v>
       </c>
       <c r="B493" t="s">
-        <v>2574</v>
+        <v>2575</v>
+      </c>
+      <c r="E493" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F493" t="s">
+        <v>54</v>
       </c>
       <c r="G493" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="H493" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="I493" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="J493" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="K493">
         <v>2017</v>
@@ -36497,25 +36545,28 @@
         <v>43</v>
       </c>
       <c r="B494" t="s">
-        <v>2579</v>
+        <v>2580</v>
+      </c>
+      <c r="E494" t="s">
+        <v>2530</v>
       </c>
       <c r="G494" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="H494" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="I494" t="s">
         <v>1729</v>
       </c>
       <c r="J494" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="K494">
         <v>2025</v>
       </c>
       <c r="P494" s="8" t="s">
-        <v>2485</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="495" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36523,19 +36574,25 @@
         <v>43</v>
       </c>
       <c r="B495" t="s">
-        <v>2583</v>
+        <v>2585</v>
+      </c>
+      <c r="E495" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F495" t="s">
+        <v>48</v>
       </c>
       <c r="G495" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="H495" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="I495" t="s">
         <v>643</v>
       </c>
       <c r="J495" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="K495">
         <v>2025</v>
@@ -36549,19 +36606,22 @@
         <v>43</v>
       </c>
       <c r="B496" t="s">
-        <v>2587</v>
+        <v>2589</v>
+      </c>
+      <c r="E496" t="s">
+        <v>2530</v>
       </c>
       <c r="G496" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="H496" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="I496" t="s">
         <v>307</v>
       </c>
       <c r="J496" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="K496">
         <v>2020</v>
@@ -36575,7 +36635,7 @@
         <v>43</v>
       </c>
       <c r="B497" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="E497" t="s">
         <v>85</v>
@@ -36584,22 +36644,22 @@
         <v>72</v>
       </c>
       <c r="G497" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="H497" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="I497" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="J497" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="K497">
         <v>2019</v>
       </c>
       <c r="P497" s="8" t="s">
-        <v>3662</v>
+        <v>3665</v>
       </c>
     </row>
     <row r="498" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36607,19 +36667,22 @@
         <v>43</v>
       </c>
       <c r="B498" t="s">
-        <v>2595</v>
+        <v>2597</v>
+      </c>
+      <c r="E498" t="s">
+        <v>2530</v>
       </c>
       <c r="G498" t="s">
-        <v>2596</v>
+        <v>2598</v>
       </c>
       <c r="H498" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="I498" t="s">
-        <v>2598</v>
+        <v>2600</v>
       </c>
       <c r="J498" t="s">
-        <v>2599</v>
+        <v>2601</v>
       </c>
       <c r="K498">
         <v>2023</v>
@@ -36633,19 +36696,25 @@
         <v>43</v>
       </c>
       <c r="B499" t="s">
-        <v>2600</v>
+        <v>2602</v>
+      </c>
+      <c r="E499" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F499" t="s">
+        <v>61</v>
       </c>
       <c r="G499" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="H499" t="s">
-        <v>2602</v>
+        <v>2604</v>
       </c>
       <c r="I499" t="s">
         <v>687</v>
       </c>
       <c r="J499" t="s">
-        <v>2603</v>
+        <v>2605</v>
       </c>
       <c r="K499">
         <v>2001</v>
@@ -36659,7 +36728,7 @@
         <v>43</v>
       </c>
       <c r="B500" t="s">
-        <v>2604</v>
+        <v>2606</v>
       </c>
       <c r="E500" t="s">
         <v>85</v>
@@ -36668,22 +36737,22 @@
         <v>48</v>
       </c>
       <c r="G500" t="s">
-        <v>2605</v>
+        <v>2607</v>
       </c>
       <c r="H500" t="s">
-        <v>2606</v>
+        <v>2608</v>
       </c>
       <c r="I500" t="s">
         <v>723</v>
       </c>
       <c r="J500" t="s">
-        <v>2607</v>
+        <v>2609</v>
       </c>
       <c r="K500">
         <v>2022</v>
       </c>
       <c r="P500" s="8" t="s">
-        <v>2608</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="501" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36691,19 +36760,25 @@
         <v>43</v>
       </c>
       <c r="B501" t="s">
-        <v>2609</v>
+        <v>2611</v>
+      </c>
+      <c r="E501" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F501" t="s">
+        <v>61</v>
       </c>
       <c r="G501" t="s">
-        <v>2610</v>
+        <v>2613</v>
       </c>
       <c r="H501" t="s">
-        <v>2611</v>
+        <v>2614</v>
       </c>
       <c r="I501" t="s">
         <v>253</v>
       </c>
       <c r="J501" t="s">
-        <v>2612</v>
+        <v>2615</v>
       </c>
       <c r="K501">
         <v>2001</v>
@@ -36717,28 +36792,28 @@
         <v>43</v>
       </c>
       <c r="B502" t="s">
-        <v>2613</v>
+        <v>2616</v>
       </c>
       <c r="E502" t="s">
         <v>48</v>
       </c>
       <c r="G502" t="s">
-        <v>2614</v>
+        <v>2617</v>
       </c>
       <c r="H502" t="s">
-        <v>2615</v>
+        <v>2618</v>
       </c>
       <c r="I502" t="s">
         <v>307</v>
       </c>
       <c r="J502" t="s">
-        <v>2616</v>
+        <v>2619</v>
       </c>
       <c r="K502">
         <v>1976</v>
       </c>
       <c r="P502" s="8" t="s">
-        <v>2617</v>
+        <v>2620</v>
       </c>
     </row>
     <row r="503" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36746,7 +36821,7 @@
         <v>43</v>
       </c>
       <c r="B503" t="s">
-        <v>2618</v>
+        <v>2621</v>
       </c>
       <c r="E503" t="s">
         <v>85</v>
@@ -36755,22 +36830,22 @@
         <v>48</v>
       </c>
       <c r="G503" t="s">
-        <v>2619</v>
+        <v>2622</v>
       </c>
       <c r="H503" t="s">
-        <v>2620</v>
+        <v>2623</v>
       </c>
       <c r="I503" t="s">
-        <v>2621</v>
+        <v>2624</v>
       </c>
       <c r="J503" t="s">
-        <v>2622</v>
+        <v>2625</v>
       </c>
       <c r="K503">
         <v>1981</v>
       </c>
       <c r="P503" s="8" t="s">
-        <v>2623</v>
+        <v>2626</v>
       </c>
     </row>
     <row r="504" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36778,19 +36853,22 @@
         <v>43</v>
       </c>
       <c r="B504" t="s">
-        <v>2624</v>
+        <v>2627</v>
+      </c>
+      <c r="E504" t="s">
+        <v>2530</v>
       </c>
       <c r="G504" t="s">
-        <v>2625</v>
+        <v>2628</v>
       </c>
       <c r="H504" t="s">
-        <v>2626</v>
+        <v>2629</v>
       </c>
       <c r="I504" t="s">
-        <v>2627</v>
+        <v>2630</v>
       </c>
       <c r="J504" t="s">
-        <v>2628</v>
+        <v>2631</v>
       </c>
       <c r="K504">
         <v>2025</v>
@@ -36804,7 +36882,7 @@
         <v>43</v>
       </c>
       <c r="B505" t="s">
-        <v>2629</v>
+        <v>2632</v>
       </c>
       <c r="E505" t="s">
         <v>85</v>
@@ -36813,22 +36891,22 @@
         <v>72</v>
       </c>
       <c r="G505" t="s">
-        <v>2630</v>
+        <v>2633</v>
       </c>
       <c r="H505" t="s">
-        <v>2631</v>
+        <v>2634</v>
       </c>
       <c r="I505" t="s">
-        <v>2632</v>
+        <v>2635</v>
       </c>
       <c r="J505" t="s">
-        <v>2633</v>
+        <v>2636</v>
       </c>
       <c r="K505">
         <v>1998</v>
       </c>
       <c r="P505" s="8" t="s">
-        <v>2634</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="506" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36836,19 +36914,22 @@
         <v>43</v>
       </c>
       <c r="B506" t="s">
-        <v>2635</v>
+        <v>2638</v>
+      </c>
+      <c r="E506" t="s">
+        <v>2530</v>
       </c>
       <c r="G506" t="s">
-        <v>2636</v>
+        <v>2639</v>
       </c>
       <c r="H506" t="s">
-        <v>2637</v>
+        <v>2640</v>
       </c>
       <c r="I506" t="s">
         <v>351</v>
       </c>
       <c r="J506" t="s">
-        <v>2638</v>
+        <v>2641</v>
       </c>
       <c r="K506">
         <v>2010</v>
@@ -36862,19 +36943,22 @@
         <v>43</v>
       </c>
       <c r="B507" t="s">
-        <v>2639</v>
+        <v>2642</v>
+      </c>
+      <c r="E507" t="s">
+        <v>2643</v>
       </c>
       <c r="G507" t="s">
-        <v>2640</v>
+        <v>2644</v>
       </c>
       <c r="H507" t="s">
-        <v>2641</v>
+        <v>2645</v>
       </c>
       <c r="I507" t="s">
         <v>2018</v>
       </c>
       <c r="J507" t="s">
-        <v>2642</v>
+        <v>2646</v>
       </c>
       <c r="K507">
         <v>2016</v>
@@ -36888,7 +36972,7 @@
         <v>43</v>
       </c>
       <c r="B508" t="s">
-        <v>2643</v>
+        <v>2647</v>
       </c>
       <c r="E508" t="s">
         <v>85</v>
@@ -36897,22 +36981,22 @@
         <v>54</v>
       </c>
       <c r="G508" t="s">
-        <v>2644</v>
+        <v>2648</v>
       </c>
       <c r="H508" t="s">
-        <v>2645</v>
+        <v>2649</v>
       </c>
       <c r="I508" t="s">
-        <v>2646</v>
+        <v>2650</v>
       </c>
       <c r="J508" t="s">
-        <v>2647</v>
+        <v>2651</v>
       </c>
       <c r="K508">
         <v>2004</v>
       </c>
       <c r="P508" s="8" t="s">
-        <v>2648</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="509" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -36920,19 +37004,22 @@
         <v>43</v>
       </c>
       <c r="B509" t="s">
-        <v>2649</v>
+        <v>2653</v>
+      </c>
+      <c r="E509" t="s">
+        <v>2530</v>
       </c>
       <c r="G509" t="s">
-        <v>2650</v>
+        <v>2654</v>
       </c>
       <c r="H509" t="s">
-        <v>2651</v>
+        <v>2655</v>
       </c>
       <c r="I509" t="s">
         <v>481</v>
       </c>
       <c r="J509" t="s">
-        <v>2652</v>
+        <v>2656</v>
       </c>
       <c r="K509">
         <v>1989</v>
@@ -36946,19 +37033,22 @@
         <v>43</v>
       </c>
       <c r="B510" t="s">
-        <v>2653</v>
+        <v>2657</v>
+      </c>
+      <c r="E510" t="s">
+        <v>2530</v>
       </c>
       <c r="G510" t="s">
-        <v>2654</v>
+        <v>2658</v>
       </c>
       <c r="H510" t="s">
-        <v>2655</v>
+        <v>2659</v>
       </c>
       <c r="I510" t="s">
-        <v>2656</v>
+        <v>2660</v>
       </c>
       <c r="J510" t="s">
-        <v>2657</v>
+        <v>2661</v>
       </c>
       <c r="K510">
         <v>2005</v>
@@ -36972,19 +37062,25 @@
         <v>43</v>
       </c>
       <c r="B511" t="s">
-        <v>2658</v>
+        <v>2662</v>
+      </c>
+      <c r="E511" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F511" t="s">
+        <v>2663</v>
       </c>
       <c r="G511" t="s">
-        <v>2659</v>
+        <v>2664</v>
       </c>
       <c r="H511" t="s">
-        <v>2660</v>
+        <v>2665</v>
       </c>
       <c r="I511" t="s">
         <v>403</v>
       </c>
       <c r="J511" t="s">
-        <v>2661</v>
+        <v>2666</v>
       </c>
       <c r="K511">
         <v>2025</v>
@@ -36998,19 +37094,22 @@
         <v>43</v>
       </c>
       <c r="B512" t="s">
-        <v>2662</v>
+        <v>2667</v>
+      </c>
+      <c r="E512" t="s">
+        <v>2530</v>
       </c>
       <c r="G512" t="s">
-        <v>2663</v>
+        <v>2668</v>
       </c>
       <c r="H512" t="s">
-        <v>2664</v>
+        <v>2669</v>
       </c>
       <c r="I512" t="s">
         <v>1652</v>
       </c>
       <c r="J512" t="s">
-        <v>2665</v>
+        <v>2670</v>
       </c>
       <c r="K512">
         <v>2018</v>
@@ -37024,19 +37123,25 @@
         <v>43</v>
       </c>
       <c r="B513" t="s">
-        <v>2666</v>
+        <v>2671</v>
+      </c>
+      <c r="E513" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F513" t="s">
+        <v>54</v>
       </c>
       <c r="G513" t="s">
-        <v>2667</v>
+        <v>2672</v>
       </c>
       <c r="H513" t="s">
-        <v>2668</v>
+        <v>2673</v>
       </c>
       <c r="I513" t="s">
         <v>1499</v>
       </c>
       <c r="J513" t="s">
-        <v>2669</v>
+        <v>2674</v>
       </c>
       <c r="K513">
         <v>2011</v>
@@ -37050,19 +37155,22 @@
         <v>43</v>
       </c>
       <c r="B514" t="s">
-        <v>2670</v>
+        <v>2675</v>
+      </c>
+      <c r="E514" t="s">
+        <v>2530</v>
       </c>
       <c r="G514" t="s">
-        <v>2671</v>
+        <v>2676</v>
       </c>
       <c r="H514" t="s">
-        <v>2672</v>
+        <v>2677</v>
       </c>
       <c r="I514" t="s">
         <v>1242</v>
       </c>
       <c r="J514" t="s">
-        <v>2673</v>
+        <v>2678</v>
       </c>
       <c r="K514">
         <v>2024</v>
@@ -37076,19 +37184,25 @@
         <v>43</v>
       </c>
       <c r="B515" t="s">
-        <v>2674</v>
+        <v>2679</v>
+      </c>
+      <c r="E515" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F515" t="s">
+        <v>61</v>
       </c>
       <c r="G515" t="s">
-        <v>2675</v>
+        <v>2680</v>
       </c>
       <c r="H515" t="s">
-        <v>2676</v>
+        <v>2681</v>
       </c>
       <c r="I515" t="s">
         <v>1783</v>
       </c>
       <c r="J515" t="s">
-        <v>2677</v>
+        <v>2682</v>
       </c>
       <c r="K515">
         <v>2023</v>
@@ -37102,19 +37216,25 @@
         <v>43</v>
       </c>
       <c r="B516" t="s">
-        <v>2678</v>
+        <v>2683</v>
+      </c>
+      <c r="E516" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F516" t="s">
+        <v>61</v>
       </c>
       <c r="G516" t="s">
-        <v>2679</v>
+        <v>2684</v>
       </c>
       <c r="H516" t="s">
-        <v>2680</v>
+        <v>2685</v>
       </c>
       <c r="I516" t="s">
-        <v>2681</v>
+        <v>2686</v>
       </c>
       <c r="J516" t="s">
-        <v>2682</v>
+        <v>2687</v>
       </c>
       <c r="K516">
         <v>2010</v>
@@ -37128,19 +37248,25 @@
         <v>43</v>
       </c>
       <c r="B517" t="s">
-        <v>2683</v>
+        <v>2688</v>
+      </c>
+      <c r="E517" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F517" t="s">
+        <v>72</v>
       </c>
       <c r="G517" t="s">
-        <v>2684</v>
+        <v>2689</v>
       </c>
       <c r="H517" t="s">
-        <v>2685</v>
+        <v>2690</v>
       </c>
       <c r="I517" t="s">
-        <v>2686</v>
+        <v>2691</v>
       </c>
       <c r="J517" t="s">
-        <v>2687</v>
+        <v>2692</v>
       </c>
       <c r="K517">
         <v>2019</v>
@@ -37154,19 +37280,25 @@
         <v>43</v>
       </c>
       <c r="B518" t="s">
-        <v>2688</v>
+        <v>2693</v>
+      </c>
+      <c r="E518" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F518" t="s">
+        <v>48</v>
       </c>
       <c r="G518" t="s">
-        <v>2689</v>
+        <v>2694</v>
       </c>
       <c r="H518" t="s">
-        <v>2690</v>
+        <v>2695</v>
       </c>
       <c r="I518" t="s">
         <v>51</v>
       </c>
       <c r="J518" t="s">
-        <v>2691</v>
+        <v>2696</v>
       </c>
       <c r="K518">
         <v>1986</v>
@@ -37180,19 +37312,22 @@
         <v>43</v>
       </c>
       <c r="B519" t="s">
-        <v>2692</v>
+        <v>2697</v>
+      </c>
+      <c r="E519" t="s">
+        <v>2698</v>
       </c>
       <c r="G519" t="s">
-        <v>2693</v>
+        <v>2699</v>
       </c>
       <c r="H519" t="s">
-        <v>2694</v>
+        <v>2700</v>
       </c>
       <c r="I519" t="s">
-        <v>2695</v>
+        <v>2701</v>
       </c>
       <c r="J519" t="s">
-        <v>2696</v>
+        <v>2702</v>
       </c>
       <c r="K519">
         <v>2018</v>
@@ -37206,19 +37341,25 @@
         <v>43</v>
       </c>
       <c r="B520" t="s">
-        <v>2697</v>
+        <v>2703</v>
+      </c>
+      <c r="E520" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F520" t="s">
+        <v>61</v>
       </c>
       <c r="G520" t="s">
-        <v>2698</v>
+        <v>2704</v>
       </c>
       <c r="H520" t="s">
-        <v>2699</v>
+        <v>2705</v>
       </c>
       <c r="I520" t="s">
-        <v>2700</v>
+        <v>2706</v>
       </c>
       <c r="J520" t="s">
-        <v>2701</v>
+        <v>2707</v>
       </c>
       <c r="K520">
         <v>2006</v>
@@ -37232,19 +37373,22 @@
         <v>43</v>
       </c>
       <c r="B521" t="s">
-        <v>2702</v>
+        <v>2708</v>
+      </c>
+      <c r="E521" t="s">
+        <v>2530</v>
       </c>
       <c r="G521" t="s">
-        <v>2703</v>
+        <v>2709</v>
       </c>
       <c r="H521" t="s">
-        <v>2704</v>
+        <v>2710</v>
       </c>
       <c r="I521" t="s">
-        <v>2705</v>
+        <v>2711</v>
       </c>
       <c r="J521" t="s">
-        <v>2706</v>
+        <v>2712</v>
       </c>
       <c r="K521">
         <v>2008</v>
@@ -37258,19 +37402,22 @@
         <v>43</v>
       </c>
       <c r="B522" t="s">
-        <v>2707</v>
+        <v>2713</v>
+      </c>
+      <c r="E522" t="s">
+        <v>2530</v>
       </c>
       <c r="G522" t="s">
-        <v>2708</v>
+        <v>2714</v>
       </c>
       <c r="H522" t="s">
-        <v>2709</v>
+        <v>2715</v>
       </c>
       <c r="I522" t="s">
         <v>1196</v>
       </c>
       <c r="J522" t="s">
-        <v>2710</v>
+        <v>2716</v>
       </c>
       <c r="K522">
         <v>2019</v>
@@ -37284,19 +37431,22 @@
         <v>43</v>
       </c>
       <c r="B523" t="s">
-        <v>2711</v>
+        <v>2717</v>
+      </c>
+      <c r="E523" t="s">
+        <v>2530</v>
       </c>
       <c r="G523" t="s">
-        <v>2712</v>
+        <v>2718</v>
       </c>
       <c r="H523" t="s">
-        <v>2713</v>
+        <v>2719</v>
       </c>
       <c r="I523" t="s">
-        <v>2714</v>
+        <v>2720</v>
       </c>
       <c r="J523" t="s">
-        <v>2715</v>
+        <v>2721</v>
       </c>
       <c r="K523">
         <v>2012</v>
@@ -37310,19 +37460,22 @@
         <v>43</v>
       </c>
       <c r="B524" t="s">
-        <v>2716</v>
+        <v>2722</v>
+      </c>
+      <c r="E524" t="s">
+        <v>2530</v>
       </c>
       <c r="G524" t="s">
-        <v>2717</v>
+        <v>2723</v>
       </c>
       <c r="H524" t="s">
-        <v>2718</v>
+        <v>2724</v>
       </c>
       <c r="I524" t="s">
         <v>1729</v>
       </c>
       <c r="J524" t="s">
-        <v>2719</v>
+        <v>2725</v>
       </c>
       <c r="K524">
         <v>1997</v>
@@ -37336,19 +37489,25 @@
         <v>43</v>
       </c>
       <c r="B525" t="s">
-        <v>2720</v>
+        <v>2726</v>
+      </c>
+      <c r="E525" t="s">
+        <v>2530</v>
+      </c>
+      <c r="F525" t="s">
+        <v>72</v>
       </c>
       <c r="G525" t="s">
-        <v>2721</v>
+        <v>2727</v>
       </c>
       <c r="H525" t="s">
-        <v>2722</v>
+        <v>2728</v>
       </c>
       <c r="I525" t="s">
-        <v>2723</v>
+        <v>2729</v>
       </c>
       <c r="J525" t="s">
-        <v>2724</v>
+        <v>2730</v>
       </c>
       <c r="K525">
         <v>2023</v>
@@ -37362,19 +37521,25 @@
         <v>43</v>
       </c>
       <c r="B526" t="s">
-        <v>2725</v>
+        <v>2731</v>
+      </c>
+      <c r="E526" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F526" t="s">
+        <v>48</v>
       </c>
       <c r="G526" t="s">
-        <v>2726</v>
+        <v>2732</v>
       </c>
       <c r="H526" t="s">
-        <v>2727</v>
+        <v>2733</v>
       </c>
       <c r="I526" t="s">
         <v>329</v>
       </c>
       <c r="J526" t="s">
-        <v>2728</v>
+        <v>2734</v>
       </c>
       <c r="K526">
         <v>2021</v>
@@ -37388,19 +37553,22 @@
         <v>43</v>
       </c>
       <c r="B527" t="s">
-        <v>2729</v>
+        <v>2735</v>
+      </c>
+      <c r="E527" t="s">
+        <v>2612</v>
       </c>
       <c r="G527" t="s">
-        <v>2730</v>
+        <v>2736</v>
       </c>
       <c r="H527" t="s">
-        <v>2731</v>
+        <v>2737</v>
       </c>
       <c r="I527" t="s">
-        <v>2732</v>
+        <v>2738</v>
       </c>
       <c r="J527" t="s">
-        <v>2733</v>
+        <v>2739</v>
       </c>
       <c r="K527">
         <v>1989</v>
@@ -37414,19 +37582,19 @@
         <v>43</v>
       </c>
       <c r="B528" t="s">
-        <v>2734</v>
+        <v>2740</v>
       </c>
       <c r="G528" t="s">
-        <v>2735</v>
+        <v>2741</v>
       </c>
       <c r="H528" t="s">
-        <v>2736</v>
+        <v>2742</v>
       </c>
       <c r="I528" t="s">
         <v>1394</v>
       </c>
       <c r="J528" t="s">
-        <v>2737</v>
+        <v>2743</v>
       </c>
       <c r="K528">
         <v>2001</v>
@@ -37440,19 +37608,19 @@
         <v>43</v>
       </c>
       <c r="B529" t="s">
-        <v>2738</v>
+        <v>2744</v>
       </c>
       <c r="G529" t="s">
-        <v>2739</v>
+        <v>2745</v>
       </c>
       <c r="H529" t="s">
-        <v>2740</v>
+        <v>2746</v>
       </c>
       <c r="I529" t="s">
-        <v>2741</v>
+        <v>2747</v>
       </c>
       <c r="J529" t="s">
-        <v>2742</v>
+        <v>2748</v>
       </c>
       <c r="K529">
         <v>2024</v>
@@ -37466,19 +37634,19 @@
         <v>43</v>
       </c>
       <c r="B530" t="s">
-        <v>2743</v>
+        <v>2749</v>
       </c>
       <c r="G530" t="s">
-        <v>2744</v>
+        <v>2750</v>
       </c>
       <c r="H530" t="s">
-        <v>2745</v>
+        <v>2751</v>
       </c>
       <c r="I530" t="s">
-        <v>2746</v>
+        <v>2752</v>
       </c>
       <c r="J530" t="s">
-        <v>2747</v>
+        <v>2753</v>
       </c>
       <c r="K530">
         <v>2012</v>
@@ -37492,19 +37660,19 @@
         <v>43</v>
       </c>
       <c r="B531" t="s">
-        <v>2748</v>
+        <v>2754</v>
       </c>
       <c r="G531" t="s">
-        <v>2749</v>
+        <v>2755</v>
       </c>
       <c r="H531" t="s">
-        <v>2750</v>
+        <v>2756</v>
       </c>
       <c r="I531" t="s">
         <v>549</v>
       </c>
       <c r="J531" t="s">
-        <v>2751</v>
+        <v>2757</v>
       </c>
       <c r="K531">
         <v>2024</v>
@@ -37518,19 +37686,19 @@
         <v>43</v>
       </c>
       <c r="B532" t="s">
-        <v>2752</v>
+        <v>2758</v>
       </c>
       <c r="G532" t="s">
-        <v>2753</v>
+        <v>2759</v>
       </c>
       <c r="H532" t="s">
-        <v>2754</v>
+        <v>2760</v>
       </c>
       <c r="I532" t="s">
         <v>100</v>
       </c>
       <c r="J532" t="s">
-        <v>2755</v>
+        <v>2761</v>
       </c>
       <c r="K532">
         <v>2023</v>
@@ -37544,19 +37712,19 @@
         <v>43</v>
       </c>
       <c r="B533" t="s">
-        <v>2756</v>
+        <v>2762</v>
       </c>
       <c r="G533" t="s">
-        <v>2757</v>
+        <v>2763</v>
       </c>
       <c r="H533" t="s">
-        <v>2758</v>
+        <v>2764</v>
       </c>
       <c r="I533" t="s">
         <v>154</v>
       </c>
       <c r="J533" t="s">
-        <v>2759</v>
+        <v>2765</v>
       </c>
       <c r="K533">
         <v>2010</v>
@@ -37570,19 +37738,19 @@
         <v>43</v>
       </c>
       <c r="B534" t="s">
-        <v>2760</v>
+        <v>2766</v>
       </c>
       <c r="G534" t="s">
-        <v>2761</v>
+        <v>2767</v>
       </c>
       <c r="H534" t="s">
-        <v>2762</v>
+        <v>2768</v>
       </c>
       <c r="I534" t="s">
         <v>687</v>
       </c>
       <c r="J534" t="s">
-        <v>2763</v>
+        <v>2769</v>
       </c>
       <c r="K534">
         <v>2017</v>
@@ -37596,19 +37764,19 @@
         <v>43</v>
       </c>
       <c r="B535" t="s">
-        <v>2764</v>
+        <v>2770</v>
       </c>
       <c r="G535" t="s">
-        <v>2765</v>
+        <v>2771</v>
       </c>
       <c r="H535" t="s">
-        <v>2766</v>
+        <v>2772</v>
       </c>
       <c r="I535" t="s">
-        <v>2767</v>
+        <v>2773</v>
       </c>
       <c r="J535" t="s">
-        <v>2768</v>
+        <v>2774</v>
       </c>
       <c r="K535">
         <v>2000</v>
@@ -37622,19 +37790,19 @@
         <v>43</v>
       </c>
       <c r="B536" t="s">
-        <v>2769</v>
+        <v>2775</v>
       </c>
       <c r="G536" t="s">
-        <v>2770</v>
+        <v>2776</v>
       </c>
       <c r="H536" t="s">
-        <v>2771</v>
+        <v>2777</v>
       </c>
       <c r="I536" t="s">
         <v>653</v>
       </c>
       <c r="J536" t="s">
-        <v>2772</v>
+        <v>2778</v>
       </c>
       <c r="K536">
         <v>2016</v>
@@ -37648,19 +37816,19 @@
         <v>43</v>
       </c>
       <c r="B537" t="s">
-        <v>2773</v>
+        <v>2779</v>
       </c>
       <c r="G537" t="s">
-        <v>2774</v>
+        <v>2780</v>
       </c>
       <c r="H537" t="s">
-        <v>2775</v>
+        <v>2781</v>
       </c>
       <c r="I537" t="s">
         <v>426</v>
       </c>
       <c r="J537" t="s">
-        <v>2776</v>
+        <v>2782</v>
       </c>
       <c r="K537">
         <v>2006</v>
@@ -37674,19 +37842,19 @@
         <v>43</v>
       </c>
       <c r="B538" t="s">
-        <v>2777</v>
+        <v>2783</v>
       </c>
       <c r="G538" t="s">
-        <v>2778</v>
+        <v>2784</v>
       </c>
       <c r="H538" t="s">
-        <v>2779</v>
+        <v>2785</v>
       </c>
       <c r="I538" t="s">
-        <v>2780</v>
+        <v>2786</v>
       </c>
       <c r="J538" t="s">
-        <v>2781</v>
+        <v>2787</v>
       </c>
       <c r="K538">
         <v>2018</v>
@@ -37700,19 +37868,19 @@
         <v>43</v>
       </c>
       <c r="B539" t="s">
-        <v>2782</v>
+        <v>2788</v>
       </c>
       <c r="G539" t="s">
-        <v>2783</v>
+        <v>2789</v>
       </c>
       <c r="H539" t="s">
-        <v>2784</v>
+        <v>2790</v>
       </c>
       <c r="I539" t="s">
         <v>357</v>
       </c>
       <c r="J539" t="s">
-        <v>2785</v>
+        <v>2791</v>
       </c>
       <c r="K539">
         <v>2015</v>
@@ -37726,19 +37894,19 @@
         <v>43</v>
       </c>
       <c r="B540" t="s">
-        <v>2786</v>
+        <v>2792</v>
       </c>
       <c r="G540" t="s">
-        <v>2787</v>
+        <v>2793</v>
       </c>
       <c r="H540" t="s">
-        <v>2788</v>
+        <v>2794</v>
       </c>
       <c r="I540" t="s">
         <v>51</v>
       </c>
       <c r="J540" t="s">
-        <v>2789</v>
+        <v>2795</v>
       </c>
       <c r="K540">
         <v>1988</v>
@@ -37752,19 +37920,19 @@
         <v>43</v>
       </c>
       <c r="B541" t="s">
-        <v>2790</v>
+        <v>2796</v>
       </c>
       <c r="G541" t="s">
-        <v>2791</v>
+        <v>2797</v>
       </c>
       <c r="H541" t="s">
-        <v>2792</v>
+        <v>2798</v>
       </c>
       <c r="I541" t="s">
         <v>307</v>
       </c>
       <c r="J541" t="s">
-        <v>2793</v>
+        <v>2799</v>
       </c>
       <c r="K541">
         <v>2016</v>
@@ -37778,19 +37946,19 @@
         <v>43</v>
       </c>
       <c r="B542" t="s">
-        <v>2794</v>
+        <v>2800</v>
       </c>
       <c r="G542" t="s">
-        <v>2795</v>
+        <v>2801</v>
       </c>
       <c r="H542" t="s">
-        <v>2796</v>
+        <v>2802</v>
       </c>
       <c r="I542" t="s">
         <v>237</v>
       </c>
       <c r="J542" t="s">
-        <v>2797</v>
+        <v>2803</v>
       </c>
       <c r="K542">
         <v>2022</v>
@@ -37804,19 +37972,19 @@
         <v>43</v>
       </c>
       <c r="B543" t="s">
-        <v>2798</v>
+        <v>2804</v>
       </c>
       <c r="G543" t="s">
-        <v>2799</v>
+        <v>2805</v>
       </c>
       <c r="H543" t="s">
-        <v>2800</v>
+        <v>2806</v>
       </c>
       <c r="I543" t="s">
         <v>346</v>
       </c>
       <c r="J543" t="s">
-        <v>2801</v>
+        <v>2807</v>
       </c>
       <c r="K543">
         <v>2025</v>
@@ -37830,19 +37998,19 @@
         <v>43</v>
       </c>
       <c r="B544" t="s">
-        <v>2802</v>
+        <v>2808</v>
       </c>
       <c r="G544" t="s">
-        <v>2803</v>
+        <v>2809</v>
       </c>
       <c r="H544" t="s">
-        <v>2804</v>
+        <v>2810</v>
       </c>
       <c r="I544" t="s">
-        <v>2805</v>
+        <v>2811</v>
       </c>
       <c r="J544" t="s">
-        <v>2806</v>
+        <v>2812</v>
       </c>
       <c r="K544">
         <v>1986</v>
@@ -37856,19 +38024,19 @@
         <v>43</v>
       </c>
       <c r="B545" t="s">
-        <v>2807</v>
+        <v>2813</v>
       </c>
       <c r="G545" t="s">
-        <v>2808</v>
+        <v>2814</v>
       </c>
       <c r="H545" t="s">
-        <v>2809</v>
+        <v>2815</v>
       </c>
       <c r="I545" t="s">
         <v>900</v>
       </c>
       <c r="J545" t="s">
-        <v>2810</v>
+        <v>2816</v>
       </c>
       <c r="K545">
         <v>2014</v>
@@ -37882,19 +38050,19 @@
         <v>43</v>
       </c>
       <c r="B546" t="s">
-        <v>2811</v>
+        <v>2817</v>
       </c>
       <c r="G546" t="s">
-        <v>2812</v>
+        <v>2818</v>
       </c>
       <c r="H546" t="s">
-        <v>2813</v>
+        <v>2819</v>
       </c>
       <c r="I546" t="s">
-        <v>2695</v>
+        <v>2701</v>
       </c>
       <c r="J546" t="s">
-        <v>2814</v>
+        <v>2820</v>
       </c>
       <c r="K546">
         <v>2019</v>
@@ -37908,19 +38076,19 @@
         <v>43</v>
       </c>
       <c r="B547" t="s">
-        <v>2815</v>
+        <v>2821</v>
       </c>
       <c r="G547" t="s">
-        <v>2816</v>
+        <v>2822</v>
       </c>
       <c r="H547" t="s">
-        <v>2817</v>
+        <v>2823</v>
       </c>
       <c r="I547" t="s">
         <v>266</v>
       </c>
       <c r="J547" t="s">
-        <v>2818</v>
+        <v>2824</v>
       </c>
       <c r="K547">
         <v>2018</v>
@@ -37934,19 +38102,19 @@
         <v>43</v>
       </c>
       <c r="B548" t="s">
-        <v>2819</v>
+        <v>2825</v>
       </c>
       <c r="G548" t="s">
-        <v>2820</v>
+        <v>2826</v>
       </c>
       <c r="H548" t="s">
-        <v>2821</v>
+        <v>2827</v>
       </c>
       <c r="I548" t="s">
         <v>723</v>
       </c>
       <c r="J548" t="s">
-        <v>2822</v>
+        <v>2828</v>
       </c>
       <c r="K548">
         <v>1979</v>
@@ -37960,19 +38128,19 @@
         <v>43</v>
       </c>
       <c r="B549" t="s">
-        <v>2823</v>
+        <v>2829</v>
       </c>
       <c r="G549" t="s">
-        <v>2824</v>
+        <v>2830</v>
       </c>
       <c r="H549" t="s">
-        <v>2825</v>
+        <v>2831</v>
       </c>
       <c r="I549" t="s">
         <v>51</v>
       </c>
       <c r="J549" t="s">
-        <v>2826</v>
+        <v>2832</v>
       </c>
       <c r="K549">
         <v>2023</v>
@@ -37986,19 +38154,19 @@
         <v>43</v>
       </c>
       <c r="B550" t="s">
-        <v>2827</v>
+        <v>2833</v>
       </c>
       <c r="G550" t="s">
-        <v>2828</v>
+        <v>2834</v>
       </c>
       <c r="H550" t="s">
-        <v>2829</v>
+        <v>2835</v>
       </c>
       <c r="I550" t="s">
         <v>148</v>
       </c>
       <c r="J550" t="s">
-        <v>2830</v>
+        <v>2836</v>
       </c>
       <c r="K550">
         <v>2018</v>
@@ -38012,19 +38180,19 @@
         <v>43</v>
       </c>
       <c r="B551" t="s">
-        <v>2831</v>
+        <v>2837</v>
       </c>
       <c r="G551" t="s">
-        <v>2832</v>
+        <v>2838</v>
       </c>
       <c r="H551" t="s">
-        <v>2833</v>
+        <v>2839</v>
       </c>
       <c r="I551" t="s">
-        <v>2834</v>
+        <v>2840</v>
       </c>
       <c r="J551" t="s">
-        <v>2835</v>
+        <v>2841</v>
       </c>
       <c r="K551">
         <v>2015</v>
@@ -38038,19 +38206,19 @@
         <v>43</v>
       </c>
       <c r="B552" t="s">
-        <v>2836</v>
+        <v>2842</v>
       </c>
       <c r="G552" t="s">
-        <v>2837</v>
+        <v>2843</v>
       </c>
       <c r="H552" t="s">
-        <v>2838</v>
+        <v>2844</v>
       </c>
       <c r="I552" t="s">
-        <v>2839</v>
+        <v>2845</v>
       </c>
       <c r="J552" t="s">
-        <v>2840</v>
+        <v>2846</v>
       </c>
       <c r="K552">
         <v>2021</v>
@@ -38064,19 +38232,19 @@
         <v>43</v>
       </c>
       <c r="B553" t="s">
-        <v>2841</v>
+        <v>2847</v>
       </c>
       <c r="G553" t="s">
-        <v>2842</v>
+        <v>2848</v>
       </c>
       <c r="H553" t="s">
-        <v>2843</v>
+        <v>2849</v>
       </c>
       <c r="I553" t="s">
-        <v>2844</v>
+        <v>2850</v>
       </c>
       <c r="J553" t="s">
-        <v>2845</v>
+        <v>2851</v>
       </c>
       <c r="K553">
         <v>2010</v>
@@ -38090,19 +38258,19 @@
         <v>43</v>
       </c>
       <c r="B554" t="s">
-        <v>2846</v>
+        <v>2852</v>
       </c>
       <c r="G554" t="s">
-        <v>2847</v>
+        <v>2853</v>
       </c>
       <c r="H554" t="s">
-        <v>2848</v>
+        <v>2854</v>
       </c>
       <c r="I554" t="s">
-        <v>2849</v>
+        <v>2855</v>
       </c>
       <c r="J554" t="s">
-        <v>2850</v>
+        <v>2856</v>
       </c>
       <c r="K554">
         <v>2006</v>
@@ -38116,19 +38284,19 @@
         <v>43</v>
       </c>
       <c r="B555" t="s">
-        <v>2851</v>
+        <v>2857</v>
       </c>
       <c r="G555" t="s">
-        <v>2852</v>
+        <v>2858</v>
       </c>
       <c r="H555" t="s">
-        <v>2853</v>
+        <v>2859</v>
       </c>
       <c r="I555" t="s">
         <v>426</v>
       </c>
       <c r="J555" t="s">
-        <v>2854</v>
+        <v>2860</v>
       </c>
       <c r="K555">
         <v>2019</v>
@@ -38142,19 +38310,19 @@
         <v>43</v>
       </c>
       <c r="B556" t="s">
-        <v>2855</v>
+        <v>2861</v>
       </c>
       <c r="G556" t="s">
-        <v>2856</v>
+        <v>2862</v>
       </c>
       <c r="H556" t="s">
-        <v>2857</v>
+        <v>2863</v>
       </c>
       <c r="I556" t="s">
-        <v>2858</v>
+        <v>2864</v>
       </c>
       <c r="J556" t="s">
-        <v>2859</v>
+        <v>2865</v>
       </c>
       <c r="K556">
         <v>2022</v>
@@ -38168,19 +38336,19 @@
         <v>43</v>
       </c>
       <c r="B557" t="s">
-        <v>2860</v>
+        <v>2866</v>
       </c>
       <c r="G557" t="s">
-        <v>2861</v>
+        <v>2867</v>
       </c>
       <c r="H557" t="s">
-        <v>2862</v>
+        <v>2868</v>
       </c>
       <c r="I557" t="s">
         <v>357</v>
       </c>
       <c r="J557" t="s">
-        <v>2863</v>
+        <v>2869</v>
       </c>
       <c r="K557">
         <v>2006</v>
@@ -38194,19 +38362,19 @@
         <v>43</v>
       </c>
       <c r="B558" t="s">
-        <v>2864</v>
+        <v>2870</v>
       </c>
       <c r="G558" t="s">
-        <v>2865</v>
+        <v>2871</v>
       </c>
       <c r="H558" t="s">
-        <v>2866</v>
+        <v>2872</v>
       </c>
       <c r="I558" t="s">
         <v>237</v>
       </c>
       <c r="J558" t="s">
-        <v>2867</v>
+        <v>2873</v>
       </c>
       <c r="K558">
         <v>2019</v>
@@ -38220,19 +38388,19 @@
         <v>43</v>
       </c>
       <c r="B559" t="s">
-        <v>2868</v>
+        <v>2874</v>
       </c>
       <c r="G559" t="s">
-        <v>2869</v>
+        <v>2875</v>
       </c>
       <c r="H559" t="s">
-        <v>2870</v>
+        <v>2876</v>
       </c>
       <c r="I559" t="s">
-        <v>2871</v>
+        <v>2877</v>
       </c>
       <c r="J559" t="s">
-        <v>2872</v>
+        <v>2878</v>
       </c>
       <c r="K559">
         <v>2015</v>
@@ -38246,19 +38414,19 @@
         <v>43</v>
       </c>
       <c r="B560" t="s">
-        <v>2873</v>
+        <v>2879</v>
       </c>
       <c r="G560" t="s">
-        <v>2874</v>
+        <v>2880</v>
       </c>
       <c r="H560" t="s">
-        <v>2875</v>
+        <v>2881</v>
       </c>
       <c r="I560" t="s">
         <v>1014</v>
       </c>
       <c r="J560" t="s">
-        <v>2876</v>
+        <v>2882</v>
       </c>
       <c r="K560">
         <v>2026</v>
@@ -38272,19 +38440,19 @@
         <v>43</v>
       </c>
       <c r="B561" t="s">
-        <v>2877</v>
+        <v>2883</v>
       </c>
       <c r="G561" t="s">
-        <v>2878</v>
+        <v>2884</v>
       </c>
       <c r="H561" t="s">
-        <v>2879</v>
+        <v>2885</v>
       </c>
       <c r="I561" t="s">
         <v>51</v>
       </c>
       <c r="J561" t="s">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="K561">
         <v>2023</v>
@@ -38298,19 +38466,19 @@
         <v>43</v>
       </c>
       <c r="B562" t="s">
-        <v>2881</v>
+        <v>2887</v>
       </c>
       <c r="G562" t="s">
-        <v>2882</v>
+        <v>2888</v>
       </c>
       <c r="H562" t="s">
-        <v>2883</v>
+        <v>2889</v>
       </c>
       <c r="I562" t="s">
         <v>51</v>
       </c>
       <c r="J562" t="s">
-        <v>2884</v>
+        <v>2890</v>
       </c>
       <c r="K562">
         <v>2000</v>
@@ -38324,19 +38492,19 @@
         <v>43</v>
       </c>
       <c r="B563" t="s">
-        <v>2885</v>
+        <v>2891</v>
       </c>
       <c r="G563" t="s">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="H563" t="s">
-        <v>2887</v>
+        <v>2893</v>
       </c>
       <c r="I563" t="s">
         <v>51</v>
       </c>
       <c r="J563" t="s">
-        <v>2888</v>
+        <v>2894</v>
       </c>
       <c r="K563">
         <v>2016</v>
@@ -38350,19 +38518,19 @@
         <v>43</v>
       </c>
       <c r="B564" t="s">
-        <v>2889</v>
+        <v>2895</v>
       </c>
       <c r="G564" t="s">
-        <v>2890</v>
+        <v>2896</v>
       </c>
       <c r="H564" t="s">
-        <v>2891</v>
+        <v>2897</v>
       </c>
       <c r="I564" t="s">
         <v>1461</v>
       </c>
       <c r="J564" t="s">
-        <v>2892</v>
+        <v>2898</v>
       </c>
       <c r="K564">
         <v>2026</v>
@@ -38376,19 +38544,19 @@
         <v>43</v>
       </c>
       <c r="B565" t="s">
-        <v>2893</v>
+        <v>2899</v>
       </c>
       <c r="G565" t="s">
-        <v>2894</v>
+        <v>2900</v>
       </c>
       <c r="H565" t="s">
-        <v>2895</v>
+        <v>2901</v>
       </c>
       <c r="I565" t="s">
-        <v>2896</v>
+        <v>2902</v>
       </c>
       <c r="J565" t="s">
-        <v>2897</v>
+        <v>2903</v>
       </c>
       <c r="K565">
         <v>2024</v>
@@ -38402,19 +38570,19 @@
         <v>43</v>
       </c>
       <c r="B566" t="s">
-        <v>2898</v>
+        <v>2904</v>
       </c>
       <c r="G566" t="s">
-        <v>2899</v>
+        <v>2905</v>
       </c>
       <c r="H566" t="s">
-        <v>2900</v>
+        <v>2906</v>
       </c>
       <c r="I566" t="s">
         <v>459</v>
       </c>
       <c r="J566" t="s">
-        <v>2901</v>
+        <v>2907</v>
       </c>
       <c r="K566">
         <v>2019</v>
@@ -38428,19 +38596,19 @@
         <v>43</v>
       </c>
       <c r="B567" t="s">
-        <v>2902</v>
+        <v>2908</v>
       </c>
       <c r="G567" t="s">
-        <v>2903</v>
+        <v>2909</v>
       </c>
       <c r="H567" t="s">
-        <v>2904</v>
+        <v>2910</v>
       </c>
       <c r="I567" t="s">
         <v>915</v>
       </c>
       <c r="J567" t="s">
-        <v>2905</v>
+        <v>2911</v>
       </c>
       <c r="K567">
         <v>2020</v>
@@ -38454,19 +38622,19 @@
         <v>43</v>
       </c>
       <c r="B568" t="s">
-        <v>2906</v>
+        <v>2912</v>
       </c>
       <c r="G568" t="s">
-        <v>2907</v>
+        <v>2913</v>
       </c>
       <c r="H568" t="s">
-        <v>2908</v>
+        <v>2914</v>
       </c>
       <c r="I568" t="s">
-        <v>2909</v>
+        <v>2915</v>
       </c>
       <c r="J568" t="s">
-        <v>2910</v>
+        <v>2916</v>
       </c>
       <c r="K568">
         <v>2014</v>
@@ -38480,19 +38648,19 @@
         <v>43</v>
       </c>
       <c r="B569" t="s">
-        <v>2911</v>
+        <v>2917</v>
       </c>
       <c r="G569" t="s">
-        <v>2912</v>
+        <v>2918</v>
       </c>
       <c r="H569" t="s">
-        <v>2913</v>
+        <v>2919</v>
       </c>
       <c r="I569" t="s">
         <v>51</v>
       </c>
       <c r="J569" t="s">
-        <v>2914</v>
+        <v>2920</v>
       </c>
       <c r="K569">
         <v>2004</v>
@@ -38506,19 +38674,19 @@
         <v>43</v>
       </c>
       <c r="B570" t="s">
-        <v>2915</v>
+        <v>2921</v>
       </c>
       <c r="G570" t="s">
-        <v>2916</v>
+        <v>2922</v>
       </c>
       <c r="H570" t="s">
-        <v>2917</v>
+        <v>2923</v>
       </c>
       <c r="I570" t="s">
         <v>51</v>
       </c>
       <c r="J570" t="s">
-        <v>2918</v>
+        <v>2924</v>
       </c>
       <c r="K570">
         <v>2015</v>
@@ -38532,19 +38700,19 @@
         <v>43</v>
       </c>
       <c r="B571" t="s">
-        <v>2919</v>
+        <v>2925</v>
       </c>
       <c r="G571" t="s">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="H571" t="s">
-        <v>2921</v>
+        <v>2927</v>
       </c>
       <c r="I571" t="s">
         <v>979</v>
       </c>
       <c r="J571" t="s">
-        <v>2922</v>
+        <v>2928</v>
       </c>
       <c r="K571">
         <v>2015</v>
@@ -38558,19 +38726,19 @@
         <v>43</v>
       </c>
       <c r="B572" t="s">
-        <v>2923</v>
+        <v>2929</v>
       </c>
       <c r="G572" t="s">
-        <v>2924</v>
+        <v>2930</v>
       </c>
       <c r="H572" t="s">
-        <v>2925</v>
+        <v>2931</v>
       </c>
       <c r="I572" t="s">
-        <v>2926</v>
+        <v>2932</v>
       </c>
       <c r="J572" t="s">
-        <v>2927</v>
+        <v>2933</v>
       </c>
       <c r="K572">
         <v>2013</v>
@@ -38584,19 +38752,19 @@
         <v>43</v>
       </c>
       <c r="B573" t="s">
-        <v>2928</v>
+        <v>2934</v>
       </c>
       <c r="G573" t="s">
-        <v>2929</v>
+        <v>2935</v>
       </c>
       <c r="H573" t="s">
-        <v>2930</v>
+        <v>2936</v>
       </c>
       <c r="I573" t="s">
         <v>692</v>
       </c>
       <c r="J573" t="s">
-        <v>2931</v>
+        <v>2937</v>
       </c>
       <c r="K573">
         <v>2017</v>
@@ -38610,19 +38778,19 @@
         <v>43</v>
       </c>
       <c r="B574" t="s">
-        <v>2932</v>
+        <v>2938</v>
       </c>
       <c r="G574" t="s">
-        <v>2933</v>
+        <v>2939</v>
       </c>
       <c r="H574" t="s">
-        <v>2934</v>
+        <v>2940</v>
       </c>
       <c r="I574" t="s">
         <v>51</v>
       </c>
       <c r="J574" t="s">
-        <v>2935</v>
+        <v>2941</v>
       </c>
       <c r="K574">
         <v>1995</v>
@@ -38636,19 +38804,19 @@
         <v>43</v>
       </c>
       <c r="B575" t="s">
-        <v>2936</v>
+        <v>2942</v>
       </c>
       <c r="G575" t="s">
-        <v>2937</v>
+        <v>2943</v>
       </c>
       <c r="H575" t="s">
-        <v>2938</v>
+        <v>2944</v>
       </c>
       <c r="I575" t="s">
-        <v>2939</v>
+        <v>2945</v>
       </c>
       <c r="J575" t="s">
-        <v>2940</v>
+        <v>2946</v>
       </c>
       <c r="K575">
         <v>2019</v>
@@ -38662,19 +38830,19 @@
         <v>43</v>
       </c>
       <c r="B576" t="s">
-        <v>2941</v>
+        <v>2947</v>
       </c>
       <c r="G576" t="s">
-        <v>2942</v>
+        <v>2948</v>
       </c>
       <c r="H576" t="s">
-        <v>2943</v>
+        <v>2949</v>
       </c>
       <c r="I576" t="s">
         <v>723</v>
       </c>
       <c r="J576" t="s">
-        <v>2944</v>
+        <v>2950</v>
       </c>
       <c r="K576">
         <v>2010</v>
@@ -38688,19 +38856,19 @@
         <v>43</v>
       </c>
       <c r="B577" t="s">
-        <v>2945</v>
+        <v>2951</v>
       </c>
       <c r="G577" t="s">
-        <v>2946</v>
+        <v>2952</v>
       </c>
       <c r="H577" t="s">
-        <v>2947</v>
+        <v>2953</v>
       </c>
       <c r="I577" t="s">
         <v>915</v>
       </c>
       <c r="J577" t="s">
-        <v>2948</v>
+        <v>2954</v>
       </c>
       <c r="K577">
         <v>2012</v>
@@ -38714,19 +38882,19 @@
         <v>43</v>
       </c>
       <c r="B578" t="s">
-        <v>2949</v>
+        <v>2955</v>
       </c>
       <c r="G578" t="s">
-        <v>2950</v>
+        <v>2956</v>
       </c>
       <c r="H578" t="s">
-        <v>2951</v>
+        <v>2957</v>
       </c>
       <c r="I578" t="s">
         <v>723</v>
       </c>
       <c r="J578" t="s">
-        <v>2952</v>
+        <v>2958</v>
       </c>
       <c r="K578">
         <v>1979</v>
@@ -38740,19 +38908,19 @@
         <v>43</v>
       </c>
       <c r="B579" t="s">
-        <v>2953</v>
+        <v>2959</v>
       </c>
       <c r="G579" t="s">
-        <v>2954</v>
+        <v>2960</v>
       </c>
       <c r="H579" t="s">
-        <v>2955</v>
+        <v>2961</v>
       </c>
       <c r="I579" t="s">
-        <v>2956</v>
+        <v>2962</v>
       </c>
       <c r="J579" t="s">
-        <v>2957</v>
+        <v>2963</v>
       </c>
       <c r="K579">
         <v>1980</v>
@@ -38766,19 +38934,19 @@
         <v>43</v>
       </c>
       <c r="B580" t="s">
-        <v>2958</v>
+        <v>2964</v>
       </c>
       <c r="G580" t="s">
-        <v>2959</v>
+        <v>2965</v>
       </c>
       <c r="H580" t="s">
-        <v>2960</v>
+        <v>2966</v>
       </c>
       <c r="I580" t="s">
         <v>253</v>
       </c>
       <c r="J580" t="s">
-        <v>2961</v>
+        <v>2967</v>
       </c>
       <c r="K580">
         <v>1981</v>
@@ -38792,19 +38960,19 @@
         <v>43</v>
       </c>
       <c r="B581" t="s">
-        <v>2962</v>
+        <v>2968</v>
       </c>
       <c r="G581" t="s">
-        <v>2963</v>
+        <v>2969</v>
       </c>
       <c r="H581" t="s">
-        <v>2964</v>
+        <v>2970</v>
       </c>
       <c r="I581" t="s">
         <v>723</v>
       </c>
       <c r="J581" t="s">
-        <v>2961</v>
+        <v>2967</v>
       </c>
       <c r="K581">
         <v>1981</v>
@@ -38818,19 +38986,19 @@
         <v>43</v>
       </c>
       <c r="B582" t="s">
-        <v>2965</v>
+        <v>2971</v>
       </c>
       <c r="G582" t="s">
-        <v>2966</v>
+        <v>2972</v>
       </c>
       <c r="H582" t="s">
-        <v>2967</v>
+        <v>2973</v>
       </c>
       <c r="I582" t="s">
         <v>197</v>
       </c>
       <c r="J582" t="s">
-        <v>2968</v>
+        <v>2974</v>
       </c>
       <c r="K582">
         <v>2023</v>
@@ -38844,19 +39012,19 @@
         <v>43</v>
       </c>
       <c r="B583" t="s">
-        <v>2969</v>
+        <v>2975</v>
       </c>
       <c r="G583" t="s">
-        <v>2970</v>
+        <v>2976</v>
       </c>
       <c r="H583" t="s">
-        <v>2971</v>
+        <v>2977</v>
       </c>
       <c r="I583" t="s">
         <v>2184</v>
       </c>
       <c r="J583" t="s">
-        <v>2972</v>
+        <v>2978</v>
       </c>
       <c r="K583">
         <v>2024</v>
@@ -38870,19 +39038,19 @@
         <v>43</v>
       </c>
       <c r="B584" t="s">
-        <v>2973</v>
+        <v>2979</v>
       </c>
       <c r="G584" t="s">
-        <v>2974</v>
+        <v>2980</v>
       </c>
       <c r="H584" t="s">
-        <v>2975</v>
+        <v>2981</v>
       </c>
       <c r="I584" t="s">
-        <v>2976</v>
+        <v>2982</v>
       </c>
       <c r="J584" t="s">
-        <v>2977</v>
+        <v>2983</v>
       </c>
       <c r="K584">
         <v>2014</v>
@@ -38896,19 +39064,19 @@
         <v>43</v>
       </c>
       <c r="B585" t="s">
-        <v>2978</v>
+        <v>2984</v>
       </c>
       <c r="G585" t="s">
-        <v>2979</v>
+        <v>2985</v>
       </c>
       <c r="H585" t="s">
-        <v>2980</v>
+        <v>2986</v>
       </c>
       <c r="I585" t="s">
         <v>745</v>
       </c>
       <c r="J585" t="s">
-        <v>2981</v>
+        <v>2987</v>
       </c>
       <c r="K585">
         <v>2015</v>
@@ -38922,19 +39090,19 @@
         <v>43</v>
       </c>
       <c r="B586" t="s">
-        <v>2982</v>
+        <v>2988</v>
       </c>
       <c r="G586" t="s">
-        <v>2983</v>
+        <v>2989</v>
       </c>
       <c r="H586" t="s">
-        <v>2984</v>
+        <v>2990</v>
       </c>
       <c r="I586" t="s">
         <v>2269</v>
       </c>
       <c r="J586" t="s">
-        <v>2985</v>
+        <v>2991</v>
       </c>
       <c r="K586">
         <v>2020</v>
@@ -38948,19 +39116,19 @@
         <v>43</v>
       </c>
       <c r="B587" t="s">
-        <v>2986</v>
+        <v>2992</v>
       </c>
       <c r="G587" t="s">
-        <v>2987</v>
+        <v>2993</v>
       </c>
       <c r="H587" t="s">
-        <v>2988</v>
+        <v>2994</v>
       </c>
       <c r="I587" t="s">
-        <v>2989</v>
+        <v>2995</v>
       </c>
       <c r="J587" t="s">
-        <v>2990</v>
+        <v>2996</v>
       </c>
       <c r="K587">
         <v>2020</v>
@@ -38974,19 +39142,19 @@
         <v>43</v>
       </c>
       <c r="B588" t="s">
-        <v>2991</v>
+        <v>2997</v>
       </c>
       <c r="G588" t="s">
-        <v>2992</v>
+        <v>2998</v>
       </c>
       <c r="H588" t="s">
-        <v>2993</v>
+        <v>2999</v>
       </c>
       <c r="I588" t="s">
         <v>1359</v>
       </c>
       <c r="J588" t="s">
-        <v>2994</v>
+        <v>3000</v>
       </c>
       <c r="K588">
         <v>2021</v>
@@ -39000,19 +39168,19 @@
         <v>43</v>
       </c>
       <c r="B589" t="s">
-        <v>2995</v>
+        <v>3001</v>
       </c>
       <c r="G589" t="s">
-        <v>2996</v>
+        <v>3002</v>
       </c>
       <c r="H589" t="s">
-        <v>2997</v>
+        <v>3003</v>
       </c>
       <c r="I589" t="s">
         <v>979</v>
       </c>
       <c r="J589" t="s">
-        <v>2998</v>
+        <v>3004</v>
       </c>
       <c r="K589">
         <v>2024</v>
@@ -39026,19 +39194,19 @@
         <v>43</v>
       </c>
       <c r="B590" t="s">
-        <v>2999</v>
+        <v>3005</v>
       </c>
       <c r="G590" t="s">
-        <v>3000</v>
+        <v>3006</v>
       </c>
       <c r="H590" t="s">
-        <v>3001</v>
+        <v>3007</v>
       </c>
       <c r="I590" t="s">
-        <v>3002</v>
+        <v>3008</v>
       </c>
       <c r="J590" t="s">
-        <v>3003</v>
+        <v>3009</v>
       </c>
       <c r="K590">
         <v>2014</v>
@@ -39052,19 +39220,19 @@
         <v>43</v>
       </c>
       <c r="B591" t="s">
-        <v>3004</v>
+        <v>3010</v>
       </c>
       <c r="G591" t="s">
-        <v>3005</v>
+        <v>3011</v>
       </c>
       <c r="H591" t="s">
-        <v>3006</v>
+        <v>3012</v>
       </c>
       <c r="I591" t="s">
-        <v>3007</v>
+        <v>3013</v>
       </c>
       <c r="J591" t="s">
-        <v>3008</v>
+        <v>3014</v>
       </c>
       <c r="K591">
         <v>2016</v>
@@ -39078,19 +39246,19 @@
         <v>43</v>
       </c>
       <c r="B592" t="s">
-        <v>3009</v>
+        <v>3015</v>
       </c>
       <c r="G592" t="s">
-        <v>3010</v>
+        <v>3016</v>
       </c>
       <c r="H592" t="s">
-        <v>3011</v>
+        <v>3017</v>
       </c>
       <c r="I592" t="s">
         <v>2184</v>
       </c>
       <c r="J592" t="s">
-        <v>3012</v>
+        <v>3018</v>
       </c>
       <c r="K592">
         <v>2023</v>
@@ -39104,19 +39272,19 @@
         <v>43</v>
       </c>
       <c r="B593" t="s">
-        <v>3013</v>
+        <v>3019</v>
       </c>
       <c r="G593" t="s">
-        <v>3014</v>
+        <v>3020</v>
       </c>
       <c r="H593" t="s">
-        <v>3015</v>
+        <v>3021</v>
       </c>
       <c r="I593" t="s">
         <v>2043</v>
       </c>
       <c r="J593" t="s">
-        <v>3016</v>
+        <v>3022</v>
       </c>
       <c r="K593">
         <v>2009</v>
@@ -39130,19 +39298,19 @@
         <v>43</v>
       </c>
       <c r="B594" t="s">
-        <v>3017</v>
+        <v>3023</v>
       </c>
       <c r="G594" t="s">
-        <v>3018</v>
+        <v>3024</v>
       </c>
       <c r="H594" t="s">
-        <v>3019</v>
+        <v>3025</v>
       </c>
       <c r="I594" t="s">
         <v>990</v>
       </c>
       <c r="J594" t="s">
-        <v>3020</v>
+        <v>3026</v>
       </c>
       <c r="K594">
         <v>2018</v>
@@ -39156,19 +39324,19 @@
         <v>43</v>
       </c>
       <c r="B595" t="s">
-        <v>3021</v>
+        <v>3027</v>
       </c>
       <c r="G595" t="s">
-        <v>3022</v>
+        <v>3028</v>
       </c>
       <c r="H595" t="s">
-        <v>3023</v>
+        <v>3029</v>
       </c>
       <c r="I595" t="s">
-        <v>3024</v>
+        <v>3030</v>
       </c>
       <c r="J595" t="s">
-        <v>3025</v>
+        <v>3031</v>
       </c>
       <c r="K595">
         <v>2020</v>
@@ -39182,19 +39350,19 @@
         <v>43</v>
       </c>
       <c r="B596" t="s">
-        <v>3026</v>
+        <v>3032</v>
       </c>
       <c r="G596" t="s">
-        <v>3027</v>
+        <v>3033</v>
       </c>
       <c r="H596" t="s">
-        <v>3028</v>
+        <v>3034</v>
       </c>
       <c r="I596" t="s">
-        <v>3029</v>
+        <v>3035</v>
       </c>
       <c r="J596" t="s">
-        <v>3030</v>
+        <v>3036</v>
       </c>
       <c r="K596">
         <v>2002</v>
@@ -39208,19 +39376,19 @@
         <v>43</v>
       </c>
       <c r="B597" t="s">
-        <v>3031</v>
+        <v>3037</v>
       </c>
       <c r="G597" t="s">
-        <v>3032</v>
+        <v>3038</v>
       </c>
       <c r="H597" t="s">
-        <v>3033</v>
+        <v>3039</v>
       </c>
       <c r="I597" t="s">
         <v>51</v>
       </c>
       <c r="J597" t="s">
-        <v>3034</v>
+        <v>3040</v>
       </c>
       <c r="K597">
         <v>1994</v>
@@ -39234,19 +39402,19 @@
         <v>43</v>
       </c>
       <c r="B598" t="s">
-        <v>3035</v>
+        <v>3041</v>
       </c>
       <c r="G598" t="s">
-        <v>3036</v>
+        <v>3042</v>
       </c>
       <c r="H598" t="s">
-        <v>3037</v>
+        <v>3043</v>
       </c>
       <c r="I598" t="s">
         <v>1308</v>
       </c>
       <c r="J598" t="s">
-        <v>3038</v>
+        <v>3044</v>
       </c>
       <c r="K598">
         <v>2021</v>
@@ -39260,19 +39428,19 @@
         <v>43</v>
       </c>
       <c r="B599" t="s">
-        <v>3039</v>
+        <v>3045</v>
       </c>
       <c r="G599" t="s">
-        <v>3040</v>
+        <v>3046</v>
       </c>
       <c r="H599" t="s">
-        <v>3041</v>
+        <v>3047</v>
       </c>
       <c r="I599" t="s">
         <v>1652</v>
       </c>
       <c r="J599" t="s">
-        <v>3042</v>
+        <v>3048</v>
       </c>
       <c r="K599">
         <v>2025</v>
@@ -39286,19 +39454,19 @@
         <v>43</v>
       </c>
       <c r="B600" t="s">
-        <v>3043</v>
+        <v>3049</v>
       </c>
       <c r="G600" t="s">
-        <v>3044</v>
+        <v>3050</v>
       </c>
       <c r="H600" t="s">
-        <v>3045</v>
+        <v>3051</v>
       </c>
       <c r="I600" t="s">
         <v>51</v>
       </c>
       <c r="J600" t="s">
-        <v>3046</v>
+        <v>3052</v>
       </c>
       <c r="K600">
         <v>2021</v>
@@ -39312,19 +39480,19 @@
         <v>43</v>
       </c>
       <c r="B601" t="s">
-        <v>3047</v>
+        <v>3053</v>
       </c>
       <c r="G601" t="s">
-        <v>3048</v>
+        <v>3054</v>
       </c>
       <c r="H601" t="s">
-        <v>3049</v>
+        <v>3055</v>
       </c>
       <c r="I601" t="s">
-        <v>3007</v>
+        <v>3013</v>
       </c>
       <c r="J601" t="s">
-        <v>3050</v>
+        <v>3056</v>
       </c>
       <c r="K601">
         <v>2024</v>
@@ -39338,19 +39506,19 @@
         <v>43</v>
       </c>
       <c r="B602" t="s">
-        <v>3051</v>
+        <v>3057</v>
       </c>
       <c r="G602" t="s">
-        <v>3052</v>
+        <v>3058</v>
       </c>
       <c r="H602" t="s">
-        <v>3053</v>
+        <v>3059</v>
       </c>
       <c r="I602" t="s">
-        <v>2896</v>
+        <v>2902</v>
       </c>
       <c r="J602" t="s">
-        <v>3054</v>
+        <v>3060</v>
       </c>
       <c r="K602">
         <v>2024</v>
@@ -39364,19 +39532,19 @@
         <v>43</v>
       </c>
       <c r="B603" t="s">
-        <v>3055</v>
+        <v>3061</v>
       </c>
       <c r="G603" t="s">
-        <v>3056</v>
+        <v>3062</v>
       </c>
       <c r="H603" t="s">
-        <v>3057</v>
+        <v>3063</v>
       </c>
       <c r="I603" t="s">
-        <v>3058</v>
+        <v>3064</v>
       </c>
       <c r="J603" t="s">
-        <v>3059</v>
+        <v>3065</v>
       </c>
       <c r="K603">
         <v>2018</v>
@@ -39390,19 +39558,19 @@
         <v>43</v>
       </c>
       <c r="B604" t="s">
-        <v>3060</v>
+        <v>3066</v>
       </c>
       <c r="G604" t="s">
-        <v>3061</v>
+        <v>3067</v>
       </c>
       <c r="H604" t="s">
-        <v>3062</v>
+        <v>3068</v>
       </c>
       <c r="I604" t="s">
         <v>100</v>
       </c>
       <c r="J604" t="s">
-        <v>3063</v>
+        <v>3069</v>
       </c>
       <c r="K604">
         <v>2014</v>
@@ -39416,19 +39584,19 @@
         <v>43</v>
       </c>
       <c r="B605" t="s">
-        <v>3064</v>
+        <v>3070</v>
       </c>
       <c r="G605" t="s">
-        <v>3065</v>
+        <v>3071</v>
       </c>
       <c r="H605" t="s">
-        <v>3066</v>
+        <v>3072</v>
       </c>
       <c r="I605" t="s">
         <v>1924</v>
       </c>
       <c r="J605" t="s">
-        <v>3067</v>
+        <v>3073</v>
       </c>
       <c r="K605">
         <v>2019</v>
@@ -39442,19 +39610,19 @@
         <v>43</v>
       </c>
       <c r="B606" t="s">
-        <v>3068</v>
+        <v>3074</v>
       </c>
       <c r="G606" t="s">
-        <v>3069</v>
+        <v>3075</v>
       </c>
       <c r="H606" t="s">
-        <v>3070</v>
+        <v>3076</v>
       </c>
       <c r="I606" t="s">
-        <v>3071</v>
+        <v>3077</v>
       </c>
       <c r="J606" t="s">
-        <v>3072</v>
+        <v>3078</v>
       </c>
       <c r="K606">
         <v>2024</v>
@@ -39468,19 +39636,19 @@
         <v>43</v>
       </c>
       <c r="B607" t="s">
-        <v>3073</v>
+        <v>3079</v>
       </c>
       <c r="G607" t="s">
-        <v>3074</v>
+        <v>3080</v>
       </c>
       <c r="H607" t="s">
-        <v>3075</v>
+        <v>3081</v>
       </c>
       <c r="I607" t="s">
         <v>1520</v>
       </c>
       <c r="J607" t="s">
-        <v>3076</v>
+        <v>3082</v>
       </c>
       <c r="K607">
         <v>2024</v>
@@ -39494,19 +39662,19 @@
         <v>43</v>
       </c>
       <c r="B608" t="s">
-        <v>3077</v>
+        <v>3083</v>
       </c>
       <c r="G608" t="s">
-        <v>3078</v>
+        <v>3084</v>
       </c>
       <c r="H608" t="s">
-        <v>3079</v>
+        <v>3085</v>
       </c>
       <c r="I608" t="s">
         <v>1520</v>
       </c>
       <c r="J608" t="s">
-        <v>3080</v>
+        <v>3086</v>
       </c>
       <c r="K608">
         <v>2021</v>
@@ -39520,19 +39688,19 @@
         <v>43</v>
       </c>
       <c r="B609" t="s">
-        <v>3081</v>
+        <v>3087</v>
       </c>
       <c r="G609" t="s">
-        <v>3082</v>
+        <v>3088</v>
       </c>
       <c r="H609" t="s">
-        <v>3083</v>
+        <v>3089</v>
       </c>
       <c r="I609" t="s">
-        <v>3084</v>
+        <v>3090</v>
       </c>
       <c r="J609" t="s">
-        <v>3085</v>
+        <v>3091</v>
       </c>
       <c r="K609">
         <v>2022</v>
@@ -39546,19 +39714,19 @@
         <v>43</v>
       </c>
       <c r="B610" t="s">
-        <v>3086</v>
+        <v>3092</v>
       </c>
       <c r="G610" t="s">
-        <v>3087</v>
+        <v>3093</v>
       </c>
       <c r="H610" t="s">
-        <v>3088</v>
+        <v>3094</v>
       </c>
       <c r="I610" t="s">
         <v>226</v>
       </c>
       <c r="J610" t="s">
-        <v>3089</v>
+        <v>3095</v>
       </c>
       <c r="K610">
         <v>2020</v>
@@ -39572,19 +39740,19 @@
         <v>43</v>
       </c>
       <c r="B611" t="s">
-        <v>3090</v>
+        <v>3096</v>
       </c>
       <c r="G611" t="s">
-        <v>3091</v>
+        <v>3097</v>
       </c>
       <c r="H611" t="s">
-        <v>3092</v>
+        <v>3098</v>
       </c>
       <c r="I611" t="s">
         <v>226</v>
       </c>
       <c r="J611" t="s">
-        <v>3089</v>
+        <v>3095</v>
       </c>
       <c r="K611">
         <v>2023</v>
@@ -39596,19 +39764,19 @@
         <v>43</v>
       </c>
       <c r="B612" t="s">
-        <v>3093</v>
+        <v>3099</v>
       </c>
       <c r="G612" t="s">
-        <v>3094</v>
+        <v>3100</v>
       </c>
       <c r="H612" t="s">
-        <v>3095</v>
+        <v>3101</v>
       </c>
       <c r="I612" t="s">
-        <v>3096</v>
+        <v>3102</v>
       </c>
       <c r="J612" t="s">
-        <v>3097</v>
+        <v>3103</v>
       </c>
       <c r="K612">
         <v>2023</v>
@@ -39622,19 +39790,19 @@
         <v>43</v>
       </c>
       <c r="B613" t="s">
-        <v>3098</v>
+        <v>3104</v>
       </c>
       <c r="G613" t="s">
-        <v>3099</v>
+        <v>3105</v>
       </c>
       <c r="H613" t="s">
-        <v>3100</v>
+        <v>3106</v>
       </c>
       <c r="I613" t="s">
         <v>1414</v>
       </c>
       <c r="J613" t="s">
-        <v>3101</v>
+        <v>3107</v>
       </c>
       <c r="K613">
         <v>2023</v>
@@ -39648,19 +39816,19 @@
         <v>43</v>
       </c>
       <c r="B614" t="s">
-        <v>3102</v>
+        <v>3108</v>
       </c>
       <c r="G614" t="s">
-        <v>3103</v>
+        <v>3109</v>
       </c>
       <c r="H614" t="s">
-        <v>3104</v>
+        <v>3110</v>
       </c>
       <c r="I614" t="s">
         <v>409</v>
       </c>
       <c r="J614" t="s">
-        <v>3105</v>
+        <v>3111</v>
       </c>
       <c r="K614">
         <v>2022</v>
@@ -39674,19 +39842,19 @@
         <v>43</v>
       </c>
       <c r="B615" t="s">
-        <v>3106</v>
+        <v>3112</v>
       </c>
       <c r="G615" t="s">
-        <v>3107</v>
+        <v>3113</v>
       </c>
       <c r="H615" t="s">
-        <v>3108</v>
+        <v>3114</v>
       </c>
       <c r="I615" t="s">
-        <v>3109</v>
+        <v>3115</v>
       </c>
       <c r="J615" t="s">
-        <v>3110</v>
+        <v>3116</v>
       </c>
       <c r="K615">
         <v>2022</v>
@@ -39700,19 +39868,19 @@
         <v>43</v>
       </c>
       <c r="B616" t="s">
-        <v>3111</v>
+        <v>3117</v>
       </c>
       <c r="G616" t="s">
-        <v>3112</v>
+        <v>3118</v>
       </c>
       <c r="H616" t="s">
-        <v>3113</v>
+        <v>3119</v>
       </c>
       <c r="I616" t="s">
         <v>2275</v>
       </c>
       <c r="J616" t="s">
-        <v>3114</v>
+        <v>3120</v>
       </c>
       <c r="K616">
         <v>2019</v>
@@ -39726,19 +39894,19 @@
         <v>43</v>
       </c>
       <c r="B617" t="s">
-        <v>3115</v>
+        <v>3121</v>
       </c>
       <c r="G617" t="s">
-        <v>3116</v>
+        <v>3122</v>
       </c>
       <c r="H617" t="s">
-        <v>3117</v>
+        <v>3123</v>
       </c>
       <c r="I617" t="s">
-        <v>3118</v>
+        <v>3124</v>
       </c>
       <c r="J617" t="s">
-        <v>3119</v>
+        <v>3125</v>
       </c>
       <c r="K617">
         <v>2024</v>
@@ -39752,19 +39920,19 @@
         <v>43</v>
       </c>
       <c r="B618" t="s">
-        <v>3120</v>
+        <v>3126</v>
       </c>
       <c r="G618" t="s">
-        <v>3121</v>
+        <v>3127</v>
       </c>
       <c r="H618" t="s">
-        <v>3122</v>
+        <v>3128</v>
       </c>
       <c r="I618" t="s">
         <v>295</v>
       </c>
       <c r="J618" t="s">
-        <v>3123</v>
+        <v>3129</v>
       </c>
       <c r="K618">
         <v>2022</v>
@@ -39778,19 +39946,19 @@
         <v>43</v>
       </c>
       <c r="B619" t="s">
-        <v>3124</v>
+        <v>3130</v>
       </c>
       <c r="G619" t="s">
-        <v>3125</v>
+        <v>3131</v>
       </c>
       <c r="H619" t="s">
-        <v>3126</v>
+        <v>3132</v>
       </c>
       <c r="I619" t="s">
         <v>915</v>
       </c>
       <c r="J619" t="s">
-        <v>3127</v>
+        <v>3133</v>
       </c>
       <c r="K619">
         <v>1995</v>
@@ -39804,19 +39972,19 @@
         <v>43</v>
       </c>
       <c r="B620" t="s">
-        <v>3128</v>
+        <v>3134</v>
       </c>
       <c r="G620" t="s">
-        <v>3129</v>
+        <v>3135</v>
       </c>
       <c r="H620" t="s">
-        <v>3130</v>
+        <v>3136</v>
       </c>
       <c r="I620" t="s">
-        <v>3131</v>
+        <v>3137</v>
       </c>
       <c r="J620" t="s">
-        <v>3132</v>
+        <v>3138</v>
       </c>
       <c r="K620">
         <v>1992</v>
@@ -39830,19 +39998,19 @@
         <v>43</v>
       </c>
       <c r="B621" t="s">
-        <v>3133</v>
+        <v>3139</v>
       </c>
       <c r="G621" t="s">
-        <v>3134</v>
+        <v>3140</v>
       </c>
       <c r="H621" t="s">
-        <v>3135</v>
+        <v>3141</v>
       </c>
       <c r="I621" t="s">
-        <v>3136</v>
+        <v>3142</v>
       </c>
       <c r="J621" t="s">
-        <v>3137</v>
+        <v>3143</v>
       </c>
       <c r="K621">
         <v>2021</v>
@@ -39856,19 +40024,19 @@
         <v>43</v>
       </c>
       <c r="B622" t="s">
-        <v>3138</v>
+        <v>3144</v>
       </c>
       <c r="G622" t="s">
-        <v>3139</v>
+        <v>3145</v>
       </c>
       <c r="H622" t="s">
-        <v>3140</v>
+        <v>3146</v>
       </c>
       <c r="I622" t="s">
         <v>973</v>
       </c>
       <c r="J622" t="s">
-        <v>3141</v>
+        <v>3147</v>
       </c>
       <c r="K622">
         <v>2018</v>
@@ -39882,19 +40050,19 @@
         <v>43</v>
       </c>
       <c r="B623" t="s">
-        <v>3142</v>
+        <v>3148</v>
       </c>
       <c r="G623" t="s">
-        <v>3143</v>
+        <v>3149</v>
       </c>
       <c r="H623" t="s">
-        <v>3144</v>
+        <v>3150</v>
       </c>
       <c r="I623" t="s">
-        <v>3145</v>
+        <v>3151</v>
       </c>
       <c r="J623" t="s">
-        <v>3146</v>
+        <v>3152</v>
       </c>
       <c r="K623">
         <v>2019</v>
@@ -39908,19 +40076,19 @@
         <v>43</v>
       </c>
       <c r="B624" t="s">
-        <v>3147</v>
+        <v>3153</v>
       </c>
       <c r="G624" t="s">
-        <v>3148</v>
+        <v>3154</v>
       </c>
       <c r="H624" t="s">
-        <v>3149</v>
+        <v>3155</v>
       </c>
       <c r="I624" t="s">
         <v>1652</v>
       </c>
       <c r="J624" t="s">
-        <v>3150</v>
+        <v>3156</v>
       </c>
       <c r="K624">
         <v>2016</v>
@@ -39934,19 +40102,19 @@
         <v>43</v>
       </c>
       <c r="B625" t="s">
-        <v>3151</v>
+        <v>3157</v>
       </c>
       <c r="G625" t="s">
-        <v>3152</v>
+        <v>3158</v>
       </c>
       <c r="H625" t="s">
-        <v>3153</v>
+        <v>3159</v>
       </c>
       <c r="I625" t="s">
         <v>1242</v>
       </c>
       <c r="J625" t="s">
-        <v>3154</v>
+        <v>3160</v>
       </c>
       <c r="K625">
         <v>2002</v>
@@ -39960,19 +40128,19 @@
         <v>43</v>
       </c>
       <c r="B626" t="s">
-        <v>3155</v>
+        <v>3161</v>
       </c>
       <c r="G626" t="s">
-        <v>3156</v>
+        <v>3162</v>
       </c>
       <c r="H626" t="s">
-        <v>3157</v>
+        <v>3163</v>
       </c>
       <c r="I626" t="s">
-        <v>3158</v>
+        <v>3164</v>
       </c>
       <c r="J626" t="s">
-        <v>3159</v>
+        <v>3165</v>
       </c>
       <c r="K626">
         <v>2018</v>
@@ -39986,19 +40154,19 @@
         <v>43</v>
       </c>
       <c r="B627" t="s">
-        <v>3160</v>
+        <v>3166</v>
       </c>
       <c r="G627" t="s">
-        <v>3161</v>
+        <v>3167</v>
       </c>
       <c r="H627" t="s">
-        <v>3162</v>
+        <v>3168</v>
       </c>
       <c r="I627" t="s">
         <v>128</v>
       </c>
       <c r="J627" t="s">
-        <v>3163</v>
+        <v>3169</v>
       </c>
       <c r="K627">
         <v>2016</v>
@@ -40012,19 +40180,19 @@
         <v>43</v>
       </c>
       <c r="B628" t="s">
-        <v>3164</v>
+        <v>3170</v>
       </c>
       <c r="G628" t="s">
-        <v>3165</v>
+        <v>3171</v>
       </c>
       <c r="H628" t="s">
-        <v>3166</v>
+        <v>3172</v>
       </c>
       <c r="I628" t="s">
         <v>915</v>
       </c>
       <c r="J628" t="s">
-        <v>3167</v>
+        <v>3173</v>
       </c>
       <c r="K628">
         <v>2004</v>
@@ -40038,19 +40206,19 @@
         <v>43</v>
       </c>
       <c r="B629" t="s">
-        <v>3168</v>
+        <v>3174</v>
       </c>
       <c r="G629" t="s">
-        <v>3169</v>
+        <v>3175</v>
       </c>
       <c r="H629" t="s">
-        <v>3170</v>
+        <v>3176</v>
       </c>
       <c r="I629" t="s">
         <v>1652</v>
       </c>
       <c r="J629" t="s">
-        <v>3171</v>
+        <v>3177</v>
       </c>
       <c r="K629">
         <v>2008</v>
@@ -40064,19 +40232,19 @@
         <v>43</v>
       </c>
       <c r="B630" t="s">
-        <v>3172</v>
+        <v>3178</v>
       </c>
       <c r="G630" t="s">
-        <v>3173</v>
+        <v>3179</v>
       </c>
       <c r="H630" t="s">
-        <v>3174</v>
+        <v>3180</v>
       </c>
       <c r="I630" t="s">
         <v>692</v>
       </c>
       <c r="J630" t="s">
-        <v>3175</v>
+        <v>3181</v>
       </c>
       <c r="K630">
         <v>2014</v>
@@ -40090,19 +40258,19 @@
         <v>43</v>
       </c>
       <c r="B631" t="s">
-        <v>3176</v>
+        <v>3182</v>
       </c>
       <c r="G631" t="s">
-        <v>3177</v>
+        <v>3183</v>
       </c>
       <c r="H631" t="s">
-        <v>3178</v>
+        <v>3184</v>
       </c>
       <c r="I631" t="s">
-        <v>2844</v>
+        <v>2850</v>
       </c>
       <c r="J631" t="s">
-        <v>3179</v>
+        <v>3185</v>
       </c>
       <c r="K631">
         <v>2004</v>
@@ -40116,19 +40284,19 @@
         <v>43</v>
       </c>
       <c r="B632" t="s">
-        <v>3180</v>
+        <v>3186</v>
       </c>
       <c r="G632" t="s">
-        <v>3181</v>
+        <v>3187</v>
       </c>
       <c r="H632" t="s">
-        <v>3182</v>
+        <v>3188</v>
       </c>
       <c r="I632" t="s">
-        <v>3183</v>
+        <v>3189</v>
       </c>
       <c r="J632" t="s">
-        <v>3184</v>
+        <v>3190</v>
       </c>
       <c r="K632">
         <v>1994</v>
@@ -40142,19 +40310,19 @@
         <v>43</v>
       </c>
       <c r="B633" t="s">
-        <v>3185</v>
+        <v>3191</v>
       </c>
       <c r="G633" t="s">
-        <v>3186</v>
+        <v>3192</v>
       </c>
       <c r="H633" t="s">
-        <v>3187</v>
+        <v>3193</v>
       </c>
       <c r="I633" t="s">
-        <v>3188</v>
+        <v>3194</v>
       </c>
       <c r="J633" t="s">
-        <v>3189</v>
+        <v>3195</v>
       </c>
       <c r="K633">
         <v>2010</v>
@@ -40168,19 +40336,19 @@
         <v>43</v>
       </c>
       <c r="B634" t="s">
-        <v>3190</v>
+        <v>3196</v>
       </c>
       <c r="G634" t="s">
-        <v>3191</v>
+        <v>3197</v>
       </c>
       <c r="H634" t="s">
-        <v>3192</v>
+        <v>3198</v>
       </c>
       <c r="I634" t="s">
         <v>226</v>
       </c>
       <c r="J634" t="s">
-        <v>3193</v>
+        <v>3199</v>
       </c>
       <c r="K634">
         <v>2025</v>
@@ -40194,19 +40362,19 @@
         <v>43</v>
       </c>
       <c r="B635" t="s">
-        <v>3194</v>
+        <v>3200</v>
       </c>
       <c r="G635" t="s">
-        <v>3195</v>
+        <v>3201</v>
       </c>
       <c r="H635" t="s">
-        <v>3196</v>
+        <v>3202</v>
       </c>
       <c r="I635" t="s">
         <v>825</v>
       </c>
       <c r="J635" t="s">
-        <v>3197</v>
+        <v>3203</v>
       </c>
       <c r="K635">
         <v>2020</v>
@@ -40220,19 +40388,19 @@
         <v>43</v>
       </c>
       <c r="B636" t="s">
-        <v>3198</v>
+        <v>3204</v>
       </c>
       <c r="G636" t="s">
-        <v>3199</v>
+        <v>3205</v>
       </c>
       <c r="H636" t="s">
-        <v>3200</v>
+        <v>3206</v>
       </c>
       <c r="I636" t="s">
-        <v>3201</v>
+        <v>3207</v>
       </c>
       <c r="J636" t="s">
-        <v>3202</v>
+        <v>3208</v>
       </c>
       <c r="K636">
         <v>2017</v>
@@ -40246,19 +40414,19 @@
         <v>43</v>
       </c>
       <c r="B637" t="s">
-        <v>3203</v>
+        <v>3209</v>
       </c>
       <c r="G637" t="s">
-        <v>3204</v>
+        <v>3210</v>
       </c>
       <c r="H637" t="s">
-        <v>3205</v>
+        <v>3211</v>
       </c>
       <c r="I637" t="s">
         <v>295</v>
       </c>
       <c r="J637" t="s">
-        <v>3206</v>
+        <v>3212</v>
       </c>
       <c r="K637">
         <v>2025</v>
@@ -40272,19 +40440,19 @@
         <v>43</v>
       </c>
       <c r="B638" t="s">
-        <v>3207</v>
+        <v>3213</v>
       </c>
       <c r="G638" t="s">
-        <v>3208</v>
+        <v>3214</v>
       </c>
       <c r="H638" t="s">
-        <v>3209</v>
+        <v>3215</v>
       </c>
       <c r="I638" t="s">
         <v>295</v>
       </c>
       <c r="J638" t="s">
-        <v>3210</v>
+        <v>3216</v>
       </c>
       <c r="K638">
         <v>2023</v>
@@ -40298,19 +40466,19 @@
         <v>43</v>
       </c>
       <c r="B639" t="s">
-        <v>3211</v>
+        <v>3217</v>
       </c>
       <c r="G639" t="s">
-        <v>3212</v>
+        <v>3218</v>
       </c>
       <c r="H639" t="s">
-        <v>3213</v>
+        <v>3219</v>
       </c>
       <c r="I639" t="s">
-        <v>3214</v>
+        <v>3220</v>
       </c>
       <c r="J639" t="s">
-        <v>3215</v>
+        <v>3221</v>
       </c>
       <c r="K639">
         <v>2009</v>
@@ -40324,19 +40492,19 @@
         <v>43</v>
       </c>
       <c r="B640" t="s">
-        <v>3216</v>
+        <v>3222</v>
       </c>
       <c r="G640" t="s">
-        <v>3217</v>
+        <v>3223</v>
       </c>
       <c r="H640" t="s">
-        <v>3218</v>
+        <v>3224</v>
       </c>
       <c r="I640" t="s">
         <v>226</v>
       </c>
       <c r="J640" t="s">
-        <v>3219</v>
+        <v>3225</v>
       </c>
       <c r="K640">
         <v>2024</v>
@@ -40350,19 +40518,19 @@
         <v>43</v>
       </c>
       <c r="B641" t="s">
-        <v>3220</v>
+        <v>3226</v>
       </c>
       <c r="G641" t="s">
-        <v>3221</v>
+        <v>3227</v>
       </c>
       <c r="H641" t="s">
-        <v>3222</v>
+        <v>3228</v>
       </c>
       <c r="I641" t="s">
         <v>1548</v>
       </c>
       <c r="J641" t="s">
-        <v>3223</v>
+        <v>3229</v>
       </c>
       <c r="K641">
         <v>2024</v>
@@ -40376,25 +40544,25 @@
         <v>43</v>
       </c>
       <c r="B642" t="s">
-        <v>3224</v>
+        <v>3230</v>
       </c>
       <c r="E642" t="s">
-        <v>3225</v>
+        <v>2612</v>
       </c>
       <c r="F642" t="s">
         <v>61</v>
       </c>
       <c r="G642" t="s">
-        <v>3226</v>
+        <v>3231</v>
       </c>
       <c r="H642" t="s">
-        <v>3227</v>
+        <v>3232</v>
       </c>
       <c r="I642" t="s">
         <v>549</v>
       </c>
       <c r="J642" t="s">
-        <v>3228</v>
+        <v>3233</v>
       </c>
       <c r="K642">
         <v>2020</v>
@@ -40408,19 +40576,19 @@
         <v>43</v>
       </c>
       <c r="B643" t="s">
-        <v>3229</v>
+        <v>3234</v>
       </c>
       <c r="G643" t="s">
-        <v>3230</v>
+        <v>3235</v>
       </c>
       <c r="H643" t="s">
-        <v>3231</v>
+        <v>3236</v>
       </c>
       <c r="I643" t="s">
         <v>148</v>
       </c>
       <c r="J643" t="s">
-        <v>3232</v>
+        <v>3237</v>
       </c>
       <c r="K643">
         <v>2020</v>
@@ -40434,19 +40602,19 @@
         <v>43</v>
       </c>
       <c r="B644" t="s">
-        <v>3233</v>
+        <v>3238</v>
       </c>
       <c r="G644" t="s">
-        <v>3234</v>
+        <v>3239</v>
       </c>
       <c r="H644" t="s">
-        <v>3235</v>
+        <v>3240</v>
       </c>
       <c r="I644" t="s">
-        <v>3236</v>
+        <v>3241</v>
       </c>
       <c r="J644" t="s">
-        <v>3237</v>
+        <v>3242</v>
       </c>
       <c r="K644">
         <v>2021</v>
@@ -40460,25 +40628,25 @@
         <v>43</v>
       </c>
       <c r="B645" t="s">
-        <v>3238</v>
+        <v>3243</v>
       </c>
       <c r="E645" t="s">
-        <v>3225</v>
+        <v>2612</v>
       </c>
       <c r="F645" t="s">
         <v>54</v>
       </c>
       <c r="G645" t="s">
-        <v>3239</v>
+        <v>3244</v>
       </c>
       <c r="H645" t="s">
-        <v>3240</v>
+        <v>3245</v>
       </c>
       <c r="I645" t="s">
         <v>1308</v>
       </c>
       <c r="J645" t="s">
-        <v>3241</v>
+        <v>3246</v>
       </c>
       <c r="K645">
         <v>2024</v>
@@ -40492,19 +40660,19 @@
         <v>43</v>
       </c>
       <c r="B646" t="s">
-        <v>3242</v>
+        <v>3247</v>
       </c>
       <c r="G646" t="s">
-        <v>3243</v>
+        <v>3248</v>
       </c>
       <c r="H646" t="s">
-        <v>3244</v>
+        <v>3249</v>
       </c>
       <c r="I646" t="s">
         <v>2314</v>
       </c>
       <c r="J646" t="s">
-        <v>3245</v>
+        <v>3250</v>
       </c>
       <c r="K646">
         <v>2024</v>
@@ -40518,22 +40686,22 @@
         <v>43</v>
       </c>
       <c r="B647" t="s">
-        <v>3246</v>
+        <v>3251</v>
       </c>
       <c r="E647" t="s">
-        <v>3225</v>
+        <v>2612</v>
       </c>
       <c r="G647" t="s">
-        <v>3247</v>
+        <v>3252</v>
       </c>
       <c r="H647" t="s">
-        <v>3248</v>
+        <v>3253</v>
       </c>
       <c r="I647" t="s">
         <v>295</v>
       </c>
       <c r="J647" t="s">
-        <v>3249</v>
+        <v>3254</v>
       </c>
       <c r="K647">
         <v>2021</v>
@@ -40547,19 +40715,19 @@
         <v>43</v>
       </c>
       <c r="B648" t="s">
-        <v>3250</v>
+        <v>3255</v>
       </c>
       <c r="G648" t="s">
-        <v>3251</v>
+        <v>3256</v>
       </c>
       <c r="H648" t="s">
-        <v>3252</v>
+        <v>3257</v>
       </c>
       <c r="I648" t="s">
         <v>1652</v>
       </c>
       <c r="J648" t="s">
-        <v>3253</v>
+        <v>3258</v>
       </c>
       <c r="K648">
         <v>2022</v>
@@ -40573,19 +40741,19 @@
         <v>43</v>
       </c>
       <c r="B649" t="s">
-        <v>3254</v>
+        <v>3259</v>
       </c>
       <c r="G649" t="s">
-        <v>3255</v>
+        <v>3260</v>
       </c>
       <c r="H649" t="s">
-        <v>3256</v>
+        <v>3261</v>
       </c>
       <c r="I649" t="s">
         <v>409</v>
       </c>
       <c r="J649" t="s">
-        <v>3257</v>
+        <v>3262</v>
       </c>
       <c r="K649">
         <v>2022</v>
@@ -40599,19 +40767,19 @@
         <v>43</v>
       </c>
       <c r="B650" t="s">
-        <v>3258</v>
+        <v>3263</v>
       </c>
       <c r="G650" t="s">
-        <v>3259</v>
+        <v>3264</v>
       </c>
       <c r="H650" t="s">
-        <v>3260</v>
+        <v>3265</v>
       </c>
       <c r="I650" t="s">
-        <v>2695</v>
+        <v>2701</v>
       </c>
       <c r="J650" t="s">
-        <v>3261</v>
+        <v>3266</v>
       </c>
       <c r="K650">
         <v>2026</v>
@@ -40625,25 +40793,25 @@
         <v>43</v>
       </c>
       <c r="B651" t="s">
-        <v>3262</v>
+        <v>3267</v>
       </c>
       <c r="G651" t="s">
-        <v>3263</v>
+        <v>3268</v>
       </c>
       <c r="H651" t="s">
-        <v>3264</v>
+        <v>3269</v>
       </c>
       <c r="I651" t="s">
-        <v>3265</v>
+        <v>3270</v>
       </c>
       <c r="J651" t="s">
-        <v>3266</v>
+        <v>3271</v>
       </c>
       <c r="K651">
         <v>2024</v>
       </c>
       <c r="P651" s="8" t="s">
-        <v>3267</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="652" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -40651,19 +40819,19 @@
         <v>43</v>
       </c>
       <c r="B652" t="s">
-        <v>3268</v>
+        <v>3273</v>
       </c>
       <c r="G652" t="s">
-        <v>3269</v>
+        <v>3274</v>
       </c>
       <c r="H652" t="s">
-        <v>3270</v>
+        <v>3275</v>
       </c>
       <c r="I652" t="s">
         <v>1336</v>
       </c>
       <c r="J652" t="s">
-        <v>3271</v>
+        <v>3276</v>
       </c>
       <c r="K652">
         <v>2015</v>
@@ -40677,19 +40845,19 @@
         <v>43</v>
       </c>
       <c r="B653" t="s">
-        <v>3272</v>
+        <v>3277</v>
       </c>
       <c r="G653" t="s">
-        <v>3273</v>
+        <v>3278</v>
       </c>
       <c r="H653" t="s">
-        <v>3274</v>
+        <v>3279</v>
       </c>
       <c r="I653" t="s">
-        <v>3275</v>
+        <v>3280</v>
       </c>
       <c r="J653" t="s">
-        <v>3276</v>
+        <v>3281</v>
       </c>
       <c r="K653">
         <v>2017</v>
@@ -40703,19 +40871,19 @@
         <v>43</v>
       </c>
       <c r="B654" t="s">
-        <v>3277</v>
+        <v>3282</v>
       </c>
       <c r="G654" t="s">
-        <v>3278</v>
+        <v>3283</v>
       </c>
       <c r="H654" t="s">
-        <v>3279</v>
+        <v>3284</v>
       </c>
       <c r="I654" t="s">
-        <v>3280</v>
+        <v>3285</v>
       </c>
       <c r="J654" t="s">
-        <v>3281</v>
+        <v>3286</v>
       </c>
       <c r="K654">
         <v>2016</v>
@@ -40729,19 +40897,19 @@
         <v>43</v>
       </c>
       <c r="B655" t="s">
-        <v>3282</v>
+        <v>3287</v>
       </c>
       <c r="G655" t="s">
-        <v>3283</v>
+        <v>3288</v>
       </c>
       <c r="H655" t="s">
-        <v>3284</v>
+        <v>3289</v>
       </c>
       <c r="I655" t="s">
-        <v>3285</v>
+        <v>3290</v>
       </c>
       <c r="J655" t="s">
-        <v>3286</v>
+        <v>3291</v>
       </c>
       <c r="K655">
         <v>2018</v>
@@ -40755,19 +40923,19 @@
         <v>43</v>
       </c>
       <c r="B656" t="s">
-        <v>3287</v>
+        <v>3292</v>
       </c>
       <c r="G656" t="s">
-        <v>3288</v>
+        <v>3293</v>
       </c>
       <c r="H656" t="s">
-        <v>3289</v>
+        <v>3294</v>
       </c>
       <c r="I656" t="s">
         <v>692</v>
       </c>
       <c r="J656" t="s">
-        <v>3290</v>
+        <v>3295</v>
       </c>
       <c r="K656">
         <v>2009</v>
@@ -40781,19 +40949,19 @@
         <v>43</v>
       </c>
       <c r="B657" t="s">
-        <v>3291</v>
+        <v>3296</v>
       </c>
       <c r="G657" t="s">
-        <v>3292</v>
+        <v>3297</v>
       </c>
       <c r="H657" t="s">
-        <v>3293</v>
+        <v>3298</v>
       </c>
       <c r="I657" t="s">
         <v>2054</v>
       </c>
       <c r="J657" t="s">
-        <v>3294</v>
+        <v>3299</v>
       </c>
       <c r="K657">
         <v>2013</v>
@@ -40807,19 +40975,19 @@
         <v>43</v>
       </c>
       <c r="B658" t="s">
-        <v>3295</v>
+        <v>3300</v>
       </c>
       <c r="G658" t="s">
-        <v>3296</v>
+        <v>3301</v>
       </c>
       <c r="H658" t="s">
-        <v>3297</v>
+        <v>3302</v>
       </c>
       <c r="I658" t="s">
-        <v>2909</v>
+        <v>2915</v>
       </c>
       <c r="J658" t="s">
-        <v>3298</v>
+        <v>3303</v>
       </c>
       <c r="K658">
         <v>2014</v>
@@ -40833,19 +41001,19 @@
         <v>43</v>
       </c>
       <c r="B659" t="s">
-        <v>3299</v>
+        <v>3304</v>
       </c>
       <c r="G659" t="s">
-        <v>3300</v>
+        <v>3305</v>
       </c>
       <c r="H659" t="s">
-        <v>3301</v>
+        <v>3306</v>
       </c>
       <c r="I659" t="s">
         <v>1987</v>
       </c>
       <c r="J659" t="s">
-        <v>3302</v>
+        <v>3307</v>
       </c>
       <c r="K659">
         <v>2024</v>
@@ -40859,25 +41027,25 @@
         <v>43</v>
       </c>
       <c r="B660" t="s">
-        <v>3303</v>
+        <v>3308</v>
       </c>
       <c r="G660" t="s">
-        <v>3304</v>
+        <v>3309</v>
       </c>
       <c r="H660" t="s">
-        <v>3305</v>
+        <v>3310</v>
       </c>
       <c r="I660" t="s">
         <v>51</v>
       </c>
       <c r="J660" t="s">
-        <v>3306</v>
+        <v>3311</v>
       </c>
       <c r="K660">
         <v>2023</v>
       </c>
       <c r="P660" s="8" t="s">
-        <v>3307</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="661" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -40885,19 +41053,19 @@
         <v>43</v>
       </c>
       <c r="B661" t="s">
-        <v>3308</v>
+        <v>3313</v>
       </c>
       <c r="G661" t="s">
-        <v>3309</v>
+        <v>3314</v>
       </c>
       <c r="H661" t="s">
-        <v>3310</v>
+        <v>3315</v>
       </c>
       <c r="I661" t="s">
         <v>664</v>
       </c>
       <c r="J661" t="s">
-        <v>3311</v>
+        <v>3316</v>
       </c>
       <c r="K661">
         <v>2001</v>
@@ -40911,19 +41079,19 @@
         <v>43</v>
       </c>
       <c r="B662" t="s">
-        <v>3312</v>
+        <v>3317</v>
       </c>
       <c r="G662" t="s">
-        <v>3313</v>
+        <v>3318</v>
       </c>
       <c r="H662" t="s">
-        <v>3314</v>
+        <v>3319</v>
       </c>
       <c r="I662" t="s">
-        <v>2896</v>
+        <v>2902</v>
       </c>
       <c r="J662" t="s">
-        <v>3315</v>
+        <v>3320</v>
       </c>
       <c r="K662">
         <v>2024</v>
@@ -40937,19 +41105,19 @@
         <v>43</v>
       </c>
       <c r="B663" t="s">
-        <v>3316</v>
+        <v>3321</v>
       </c>
       <c r="G663" t="s">
-        <v>3317</v>
+        <v>3322</v>
       </c>
       <c r="H663" t="s">
-        <v>3318</v>
+        <v>3323</v>
       </c>
       <c r="I663" t="s">
-        <v>3071</v>
+        <v>3077</v>
       </c>
       <c r="J663" t="s">
-        <v>3319</v>
+        <v>3324</v>
       </c>
       <c r="K663">
         <v>2025</v>
@@ -40963,22 +41131,22 @@
         <v>43</v>
       </c>
       <c r="B664" t="s">
-        <v>3320</v>
+        <v>3325</v>
       </c>
       <c r="E664" t="s">
-        <v>3321</v>
+        <v>2643</v>
       </c>
       <c r="G664" t="s">
-        <v>3322</v>
+        <v>3326</v>
       </c>
       <c r="H664" t="s">
-        <v>3323</v>
+        <v>3327</v>
       </c>
       <c r="I664" t="s">
         <v>409</v>
       </c>
       <c r="J664" t="s">
-        <v>3324</v>
+        <v>3328</v>
       </c>
       <c r="K664">
         <v>2022</v>
@@ -40992,22 +41160,22 @@
         <v>43</v>
       </c>
       <c r="B665" t="s">
-        <v>3325</v>
+        <v>3329</v>
       </c>
       <c r="E665" t="s">
-        <v>3225</v>
+        <v>2612</v>
       </c>
       <c r="G665" t="s">
-        <v>3326</v>
+        <v>3330</v>
       </c>
       <c r="H665" t="s">
-        <v>3327</v>
+        <v>3331</v>
       </c>
       <c r="I665" t="s">
-        <v>3328</v>
+        <v>3332</v>
       </c>
       <c r="J665" t="s">
-        <v>3329</v>
+        <v>3333</v>
       </c>
       <c r="K665">
         <v>2014</v>
@@ -41021,19 +41189,19 @@
         <v>43</v>
       </c>
       <c r="B666" t="s">
-        <v>3330</v>
+        <v>3334</v>
       </c>
       <c r="G666" t="s">
-        <v>3331</v>
+        <v>3335</v>
       </c>
       <c r="H666" t="s">
-        <v>3332</v>
+        <v>3336</v>
       </c>
       <c r="I666" t="s">
         <v>1414</v>
       </c>
       <c r="J666" t="s">
-        <v>3333</v>
+        <v>3337</v>
       </c>
       <c r="K666">
         <v>2025</v>
@@ -41047,19 +41215,19 @@
         <v>43</v>
       </c>
       <c r="B667" t="s">
-        <v>3334</v>
+        <v>3338</v>
       </c>
       <c r="G667" t="s">
-        <v>3335</v>
+        <v>3339</v>
       </c>
       <c r="H667" t="s">
-        <v>3336</v>
+        <v>3340</v>
       </c>
       <c r="I667" t="s">
         <v>459</v>
       </c>
       <c r="J667" t="s">
-        <v>3337</v>
+        <v>3341</v>
       </c>
       <c r="K667">
         <v>2016</v>
@@ -41073,19 +41241,19 @@
         <v>43</v>
       </c>
       <c r="B668" t="s">
-        <v>3338</v>
+        <v>3342</v>
       </c>
       <c r="G668" t="s">
-        <v>3339</v>
+        <v>3343</v>
       </c>
       <c r="H668" t="s">
-        <v>3340</v>
+        <v>3344</v>
       </c>
       <c r="I668" t="s">
-        <v>3341</v>
+        <v>3345</v>
       </c>
       <c r="J668" t="s">
-        <v>3342</v>
+        <v>3346</v>
       </c>
       <c r="K668">
         <v>2018</v>
@@ -41099,7 +41267,7 @@
         <v>43</v>
       </c>
       <c r="B669" t="s">
-        <v>3343</v>
+        <v>3347</v>
       </c>
       <c r="E669" t="s">
         <v>47</v>
@@ -41108,22 +41276,22 @@
         <v>48</v>
       </c>
       <c r="G669" t="s">
-        <v>3344</v>
+        <v>3348</v>
       </c>
       <c r="H669" t="s">
-        <v>3345</v>
+        <v>3349</v>
       </c>
       <c r="I669" t="s">
         <v>426</v>
       </c>
       <c r="J669" t="s">
-        <v>3346</v>
+        <v>3350</v>
       </c>
       <c r="K669">
         <v>2015</v>
       </c>
       <c r="P669" s="8" t="s">
-        <v>3347</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="670" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -41131,19 +41299,19 @@
         <v>43</v>
       </c>
       <c r="B670" t="s">
-        <v>3348</v>
+        <v>3352</v>
       </c>
       <c r="G670" t="s">
-        <v>3349</v>
+        <v>3353</v>
       </c>
       <c r="H670" t="s">
-        <v>3350</v>
+        <v>3354</v>
       </c>
       <c r="I670" t="s">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="J670" t="s">
-        <v>3352</v>
+        <v>3356</v>
       </c>
       <c r="K670">
         <v>2018</v>
@@ -41157,19 +41325,19 @@
         <v>43</v>
       </c>
       <c r="B671" t="s">
-        <v>3353</v>
+        <v>3357</v>
       </c>
       <c r="G671" t="s">
-        <v>3354</v>
+        <v>3358</v>
       </c>
       <c r="H671" t="s">
-        <v>3355</v>
+        <v>3359</v>
       </c>
       <c r="I671" t="s">
         <v>2236</v>
       </c>
       <c r="J671" t="s">
-        <v>3356</v>
+        <v>3360</v>
       </c>
       <c r="K671">
         <v>2011</v>
@@ -41183,19 +41351,19 @@
         <v>43</v>
       </c>
       <c r="B672" t="s">
-        <v>3357</v>
+        <v>3361</v>
       </c>
       <c r="G672" t="s">
-        <v>3358</v>
+        <v>3362</v>
       </c>
       <c r="H672" t="s">
-        <v>3359</v>
+        <v>3363</v>
       </c>
       <c r="I672" t="s">
         <v>128</v>
       </c>
       <c r="J672" t="s">
-        <v>3360</v>
+        <v>3364</v>
       </c>
       <c r="K672">
         <v>2015</v>
@@ -41209,19 +41377,19 @@
         <v>43</v>
       </c>
       <c r="B673" t="s">
-        <v>3361</v>
+        <v>3365</v>
       </c>
       <c r="G673" t="s">
-        <v>3362</v>
+        <v>3366</v>
       </c>
       <c r="H673" t="s">
-        <v>3363</v>
+        <v>3367</v>
       </c>
       <c r="I673" t="s">
         <v>1479</v>
       </c>
       <c r="J673" t="s">
-        <v>3364</v>
+        <v>3368</v>
       </c>
       <c r="K673">
         <v>2022</v>
@@ -41235,19 +41403,19 @@
         <v>43</v>
       </c>
       <c r="B674" t="s">
-        <v>3365</v>
+        <v>3369</v>
       </c>
       <c r="G674" t="s">
-        <v>3366</v>
+        <v>3370</v>
       </c>
       <c r="H674" t="s">
-        <v>3367</v>
+        <v>3371</v>
       </c>
       <c r="I674" t="s">
-        <v>3341</v>
+        <v>3345</v>
       </c>
       <c r="J674" t="s">
-        <v>3368</v>
+        <v>3372</v>
       </c>
       <c r="K674">
         <v>2023</v>
@@ -41261,19 +41429,19 @@
         <v>43</v>
       </c>
       <c r="B675" t="s">
-        <v>3369</v>
+        <v>3373</v>
       </c>
       <c r="G675" t="s">
-        <v>3370</v>
+        <v>3374</v>
       </c>
       <c r="H675" t="s">
-        <v>3371</v>
+        <v>3375</v>
       </c>
       <c r="I675" t="s">
-        <v>3372</v>
+        <v>3376</v>
       </c>
       <c r="J675" t="s">
-        <v>3373</v>
+        <v>3377</v>
       </c>
       <c r="K675">
         <v>2021</v>
@@ -41287,28 +41455,28 @@
         <v>43</v>
       </c>
       <c r="B676" t="s">
-        <v>3374</v>
+        <v>3378</v>
       </c>
       <c r="E676" t="s">
         <v>48</v>
       </c>
       <c r="G676" t="s">
-        <v>3375</v>
+        <v>3379</v>
       </c>
       <c r="H676" t="s">
-        <v>3376</v>
+        <v>3380</v>
       </c>
       <c r="I676" t="s">
         <v>1674</v>
       </c>
       <c r="J676" t="s">
-        <v>3377</v>
+        <v>3381</v>
       </c>
       <c r="K676">
         <v>2022</v>
       </c>
       <c r="P676" s="8" t="s">
-        <v>3378</v>
+        <v>3382</v>
       </c>
     </row>
     <row r="677" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -41316,19 +41484,19 @@
         <v>43</v>
       </c>
       <c r="B677" t="s">
-        <v>3379</v>
+        <v>3383</v>
       </c>
       <c r="G677" t="s">
-        <v>3380</v>
+        <v>3384</v>
       </c>
       <c r="H677" t="s">
-        <v>3381</v>
+        <v>3385</v>
       </c>
       <c r="I677" t="s">
         <v>687</v>
       </c>
       <c r="J677" t="s">
-        <v>3382</v>
+        <v>3386</v>
       </c>
       <c r="K677">
         <v>2026</v>
@@ -41342,19 +41510,19 @@
         <v>43</v>
       </c>
       <c r="B678" t="s">
-        <v>3383</v>
+        <v>3387</v>
       </c>
       <c r="G678" t="s">
-        <v>3384</v>
+        <v>3388</v>
       </c>
       <c r="H678" t="s">
-        <v>3385</v>
+        <v>3389</v>
       </c>
       <c r="I678" t="s">
         <v>409</v>
       </c>
       <c r="J678" t="s">
-        <v>3386</v>
+        <v>3390</v>
       </c>
       <c r="K678">
         <v>2022</v>
@@ -41368,28 +41536,28 @@
         <v>43</v>
       </c>
       <c r="B679" t="s">
-        <v>3387</v>
+        <v>3391</v>
       </c>
       <c r="E679" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G679" t="s">
-        <v>3389</v>
+        <v>3392</v>
       </c>
       <c r="H679" t="s">
-        <v>3390</v>
+        <v>3393</v>
       </c>
       <c r="I679" t="s">
         <v>51</v>
       </c>
       <c r="J679" t="s">
-        <v>3391</v>
+        <v>3394</v>
       </c>
       <c r="K679">
         <v>2019</v>
       </c>
       <c r="P679" s="8" t="s">
-        <v>3392</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="680" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.5">
@@ -41397,19 +41565,19 @@
         <v>43</v>
       </c>
       <c r="B680" t="s">
-        <v>3393</v>
+        <v>3396</v>
       </c>
       <c r="G680" t="s">
-        <v>3394</v>
+        <v>3397</v>
       </c>
       <c r="H680" t="s">
-        <v>3395</v>
+        <v>3398</v>
       </c>
       <c r="I680" t="s">
-        <v>3396</v>
+        <v>3399</v>
       </c>
       <c r="J680" t="s">
-        <v>3397</v>
+        <v>3400</v>
       </c>
       <c r="K680">
         <v>2021</v>
@@ -41423,22 +41591,22 @@
         <v>43</v>
       </c>
       <c r="B681" t="s">
-        <v>3398</v>
+        <v>3401</v>
       </c>
       <c r="E681" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G681" t="s">
-        <v>3399</v>
+        <v>3402</v>
       </c>
       <c r="H681" t="s">
-        <v>3400</v>
+        <v>3403</v>
       </c>
       <c r="I681" t="s">
         <v>237</v>
       </c>
       <c r="J681" t="s">
-        <v>3401</v>
+        <v>3404</v>
       </c>
       <c r="K681">
         <v>2017</v>
@@ -41452,22 +41620,22 @@
         <v>43</v>
       </c>
       <c r="B682" t="s">
-        <v>3402</v>
+        <v>3405</v>
       </c>
       <c r="E682" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G682" t="s">
-        <v>3403</v>
+        <v>3406</v>
       </c>
       <c r="H682" t="s">
-        <v>3404</v>
+        <v>3407</v>
       </c>
       <c r="I682" t="s">
         <v>1080</v>
       </c>
       <c r="J682" t="s">
-        <v>3405</v>
+        <v>3408</v>
       </c>
       <c r="K682">
         <v>2025</v>
@@ -41481,22 +41649,22 @@
         <v>43</v>
       </c>
       <c r="B683" t="s">
-        <v>3406</v>
+        <v>3409</v>
       </c>
       <c r="E683" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G683" t="s">
-        <v>3407</v>
+        <v>3410</v>
       </c>
       <c r="H683" t="s">
-        <v>3408</v>
+        <v>3411</v>
       </c>
       <c r="I683" t="s">
         <v>237</v>
       </c>
       <c r="J683" t="s">
-        <v>3409</v>
+        <v>3412</v>
       </c>
       <c r="K683">
         <v>2025</v>
@@ -41510,22 +41678,22 @@
         <v>43</v>
       </c>
       <c r="B684" t="s">
-        <v>3410</v>
+        <v>3413</v>
       </c>
       <c r="E684" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G684" t="s">
-        <v>3411</v>
+        <v>3414</v>
       </c>
       <c r="H684" t="s">
-        <v>3412</v>
+        <v>3415</v>
       </c>
       <c r="I684" t="s">
         <v>819</v>
       </c>
       <c r="J684" t="s">
-        <v>3413</v>
+        <v>3416</v>
       </c>
       <c r="K684">
         <v>2019</v>
@@ -41539,22 +41707,22 @@
         <v>43</v>
       </c>
       <c r="B685" t="s">
-        <v>3414</v>
+        <v>3417</v>
       </c>
       <c r="E685" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G685" t="s">
-        <v>3415</v>
+        <v>3418</v>
       </c>
       <c r="H685" t="s">
-        <v>3416</v>
+        <v>3419</v>
       </c>
       <c r="I685" t="s">
         <v>415</v>
       </c>
       <c r="J685" t="s">
-        <v>3417</v>
+        <v>3420</v>
       </c>
       <c r="K685">
         <v>2024</v>
@@ -41568,25 +41736,25 @@
         <v>43</v>
       </c>
       <c r="B686" t="s">
-        <v>3418</v>
+        <v>3421</v>
       </c>
       <c r="E686" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="F686" t="s">
         <v>85</v>
       </c>
       <c r="G686" t="s">
-        <v>3419</v>
+        <v>3422</v>
       </c>
       <c r="H686" t="s">
-        <v>3420</v>
+        <v>3423</v>
       </c>
       <c r="I686" t="s">
-        <v>3421</v>
+        <v>3424</v>
       </c>
       <c r="J686" t="s">
-        <v>3422</v>
+        <v>3425</v>
       </c>
       <c r="K686">
         <v>2024</v>
@@ -41600,19 +41768,19 @@
         <v>43</v>
       </c>
       <c r="B687" t="s">
-        <v>3423</v>
+        <v>3426</v>
       </c>
       <c r="G687" t="s">
-        <v>3424</v>
+        <v>3427</v>
       </c>
       <c r="H687" t="s">
-        <v>3425</v>
+        <v>3428</v>
       </c>
       <c r="I687" t="s">
         <v>1929</v>
       </c>
       <c r="J687" t="s">
-        <v>3426</v>
+        <v>3429</v>
       </c>
       <c r="K687">
         <v>2024</v>
@@ -41624,25 +41792,25 @@
         <v>43</v>
       </c>
       <c r="B688" t="s">
-        <v>3427</v>
+        <v>3430</v>
       </c>
       <c r="E688" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="F688" t="s">
         <v>85</v>
       </c>
       <c r="G688" t="s">
-        <v>3428</v>
+        <v>3431</v>
       </c>
       <c r="H688" t="s">
-        <v>3429</v>
+        <v>3432</v>
       </c>
       <c r="I688" t="s">
-        <v>3430</v>
+        <v>3433</v>
       </c>
       <c r="J688" t="s">
-        <v>3431</v>
+        <v>3434</v>
       </c>
       <c r="K688">
         <v>2023</v>
@@ -41656,22 +41824,22 @@
         <v>43</v>
       </c>
       <c r="B689" t="s">
-        <v>3432</v>
+        <v>3435</v>
       </c>
       <c r="E689" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G689" t="s">
-        <v>3433</v>
+        <v>3436</v>
       </c>
       <c r="H689" t="s">
-        <v>3434</v>
+        <v>3437</v>
       </c>
       <c r="I689" t="s">
-        <v>3435</v>
+        <v>3438</v>
       </c>
       <c r="J689" t="s">
-        <v>3436</v>
+        <v>3439</v>
       </c>
       <c r="K689">
         <v>2024</v>
@@ -41685,25 +41853,25 @@
         <v>43</v>
       </c>
       <c r="B690" t="s">
-        <v>3437</v>
+        <v>3440</v>
       </c>
       <c r="E690" t="s">
-        <v>3225</v>
+        <v>2612</v>
       </c>
       <c r="F690" t="s">
         <v>48</v>
       </c>
       <c r="G690" t="s">
-        <v>3438</v>
+        <v>3441</v>
       </c>
       <c r="H690" t="s">
-        <v>3439</v>
+        <v>3442</v>
       </c>
       <c r="I690" t="s">
         <v>403</v>
       </c>
       <c r="J690" t="s">
-        <v>3440</v>
+        <v>3443</v>
       </c>
       <c r="K690">
         <v>2014</v>
@@ -41717,22 +41885,22 @@
         <v>43</v>
       </c>
       <c r="B691" t="s">
-        <v>3441</v>
+        <v>3444</v>
       </c>
       <c r="E691" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G691" t="s">
-        <v>3442</v>
+        <v>3445</v>
       </c>
       <c r="H691" t="s">
-        <v>3443</v>
+        <v>3446</v>
       </c>
       <c r="I691" t="s">
         <v>2043</v>
       </c>
       <c r="J691" t="s">
-        <v>3444</v>
+        <v>3447</v>
       </c>
       <c r="K691">
         <v>2024</v>
@@ -41746,19 +41914,19 @@
         <v>43</v>
       </c>
       <c r="B692" t="s">
-        <v>3445</v>
+        <v>3448</v>
       </c>
       <c r="G692" t="s">
-        <v>3446</v>
+        <v>3449</v>
       </c>
       <c r="H692" t="s">
-        <v>3447</v>
+        <v>3450</v>
       </c>
       <c r="I692" t="s">
-        <v>3448</v>
+        <v>3451</v>
       </c>
       <c r="J692" t="s">
-        <v>3449</v>
+        <v>3452</v>
       </c>
       <c r="K692">
         <v>2023</v>
@@ -41770,22 +41938,22 @@
         <v>43</v>
       </c>
       <c r="B693" t="s">
-        <v>3450</v>
+        <v>3453</v>
       </c>
       <c r="E693" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G693" t="s">
-        <v>3451</v>
+        <v>3454</v>
       </c>
       <c r="H693" t="s">
-        <v>3452</v>
+        <v>3455</v>
       </c>
       <c r="I693" t="s">
         <v>237</v>
       </c>
       <c r="J693" t="s">
-        <v>3453</v>
+        <v>3456</v>
       </c>
       <c r="K693">
         <v>2026</v>
@@ -41799,25 +41967,25 @@
         <v>43</v>
       </c>
       <c r="B694" t="s">
-        <v>3454</v>
+        <v>3457</v>
       </c>
       <c r="E694" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="F694" t="s">
         <v>85</v>
       </c>
       <c r="G694" t="s">
-        <v>3455</v>
+        <v>3458</v>
       </c>
       <c r="H694" t="s">
-        <v>3456</v>
+        <v>3459</v>
       </c>
       <c r="I694" t="s">
         <v>973</v>
       </c>
       <c r="J694" t="s">
-        <v>3457</v>
+        <v>3460</v>
       </c>
       <c r="K694">
         <v>2025</v>
@@ -41831,22 +41999,22 @@
         <v>43</v>
       </c>
       <c r="B695" t="s">
-        <v>3458</v>
+        <v>3461</v>
       </c>
       <c r="E695" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G695" t="s">
-        <v>3459</v>
+        <v>3462</v>
       </c>
       <c r="H695" t="s">
-        <v>3460</v>
+        <v>3463</v>
       </c>
       <c r="I695" t="s">
         <v>1929</v>
       </c>
       <c r="J695" t="s">
-        <v>3461</v>
+        <v>3464</v>
       </c>
       <c r="K695">
         <v>2020</v>
@@ -41860,22 +42028,22 @@
         <v>43</v>
       </c>
       <c r="B696" t="s">
-        <v>3462</v>
+        <v>3465</v>
       </c>
       <c r="E696" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G696" t="s">
-        <v>3463</v>
+        <v>3466</v>
       </c>
       <c r="H696" t="s">
-        <v>3464</v>
+        <v>3467</v>
       </c>
       <c r="I696" t="s">
         <v>973</v>
       </c>
       <c r="J696" t="s">
-        <v>3465</v>
+        <v>3468</v>
       </c>
       <c r="K696">
         <v>2024</v>
@@ -41889,22 +42057,22 @@
         <v>43</v>
       </c>
       <c r="B697" t="s">
-        <v>3466</v>
+        <v>3469</v>
       </c>
       <c r="E697" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G697" t="s">
-        <v>3467</v>
+        <v>3470</v>
       </c>
       <c r="H697" t="s">
-        <v>3468</v>
+        <v>3471</v>
       </c>
       <c r="I697" t="s">
         <v>1461</v>
       </c>
       <c r="J697" t="s">
-        <v>3469</v>
+        <v>3472</v>
       </c>
       <c r="K697">
         <v>2023</v>
@@ -41918,25 +42086,25 @@
         <v>43</v>
       </c>
       <c r="B698" t="s">
-        <v>3470</v>
+        <v>3473</v>
       </c>
       <c r="E698" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="F698" t="s">
         <v>54</v>
       </c>
       <c r="G698" t="s">
-        <v>3471</v>
+        <v>3474</v>
       </c>
       <c r="H698" t="s">
-        <v>3472</v>
+        <v>3475</v>
       </c>
       <c r="I698" t="s">
         <v>723</v>
       </c>
       <c r="J698" t="s">
-        <v>3473</v>
+        <v>3476</v>
       </c>
       <c r="K698">
         <v>2022</v>
@@ -41950,19 +42118,19 @@
         <v>43</v>
       </c>
       <c r="B699" t="s">
-        <v>3474</v>
+        <v>3477</v>
       </c>
       <c r="G699" t="s">
-        <v>3475</v>
+        <v>3478</v>
       </c>
       <c r="H699" t="s">
-        <v>3476</v>
+        <v>3479</v>
       </c>
       <c r="I699" t="s">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="J699" t="s">
-        <v>3477</v>
+        <v>3480</v>
       </c>
       <c r="K699">
         <v>2017</v>
@@ -41974,25 +42142,25 @@
         <v>43</v>
       </c>
       <c r="B700" t="s">
-        <v>3478</v>
+        <v>3481</v>
       </c>
       <c r="E700" t="s">
-        <v>3225</v>
+        <v>2612</v>
       </c>
       <c r="F700" t="s">
         <v>54</v>
       </c>
       <c r="G700" t="s">
-        <v>3479</v>
+        <v>3482</v>
       </c>
       <c r="H700" t="s">
-        <v>3480</v>
+        <v>3483</v>
       </c>
       <c r="I700" t="s">
         <v>915</v>
       </c>
       <c r="J700" t="s">
-        <v>3481</v>
+        <v>3484</v>
       </c>
       <c r="K700">
         <v>2024</v>
@@ -42006,22 +42174,22 @@
         <v>43</v>
       </c>
       <c r="B701" t="s">
-        <v>3482</v>
+        <v>3485</v>
       </c>
       <c r="E701" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G701" t="s">
-        <v>3483</v>
+        <v>3486</v>
       </c>
       <c r="H701" t="s">
-        <v>3484</v>
+        <v>3487</v>
       </c>
       <c r="I701" t="s">
-        <v>3485</v>
+        <v>3488</v>
       </c>
       <c r="J701" t="s">
-        <v>3486</v>
+        <v>3489</v>
       </c>
       <c r="K701">
         <v>2026</v>
@@ -42035,25 +42203,25 @@
         <v>43</v>
       </c>
       <c r="B702" t="s">
-        <v>3487</v>
+        <v>3490</v>
       </c>
       <c r="E702" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="F702" t="s">
         <v>61</v>
       </c>
       <c r="G702" t="s">
-        <v>3488</v>
+        <v>3491</v>
       </c>
       <c r="H702" t="s">
-        <v>3489</v>
+        <v>3492</v>
       </c>
       <c r="I702" t="s">
         <v>915</v>
       </c>
       <c r="J702" t="s">
-        <v>3490</v>
+        <v>3493</v>
       </c>
       <c r="K702">
         <v>2007</v>
@@ -42067,22 +42235,22 @@
         <v>43</v>
       </c>
       <c r="B703" t="s">
-        <v>3491</v>
+        <v>3494</v>
       </c>
       <c r="E703" t="s">
-        <v>3492</v>
+        <v>3495</v>
       </c>
       <c r="G703" t="s">
-        <v>3493</v>
+        <v>3496</v>
       </c>
       <c r="H703" t="s">
-        <v>3494</v>
+        <v>3497</v>
       </c>
       <c r="I703" t="s">
-        <v>3495</v>
+        <v>3498</v>
       </c>
       <c r="J703" t="s">
-        <v>3496</v>
+        <v>3499</v>
       </c>
       <c r="K703">
         <v>2013</v>
@@ -42096,22 +42264,22 @@
         <v>43</v>
       </c>
       <c r="B704" t="s">
-        <v>3497</v>
+        <v>3500</v>
       </c>
       <c r="E704" t="s">
-        <v>3388</v>
+        <v>2530</v>
       </c>
       <c r="G704" t="s">
-        <v>3498</v>
+        <v>3501</v>
       </c>
       <c r="H704" t="s">
-        <v>3499</v>
+        <v>3502</v>
       </c>
       <c r="I704" t="s">
         <v>51</v>
       </c>
       <c r="J704" t="s">
-        <v>3500</v>
+        <v>3503</v>
       </c>
       <c r="K704">
         <v>2001</v>

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -629,6 +629,16 @@
           <t>BSMA0001</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>In the past four decades research on team diversity has grown increasingly sophisticated, incorporating several dimensions of team diversity, performance, and team processes. In examining the process and performance outcomes of team diversity, this dissertation contributes to extant research primarily in three ways. First, while examining the relationship between team diversity and process and performance outcomes, this dissertation examined the moderating influence of the organizational demographic context. Second, while past research has focused primarily on internal team processes, the present research also examined teams' external relationships. Inter-team cooperation as well as intra-team cooperation, were proposed as process outcomes of team diversity. Third, by incorporating multiple conceptualizations of diversity (additive and configurational) this dissertation attempted to contribute to research on the measurement of diversity in organizations.</t>
@@ -654,7 +664,11 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="P4" s="8" t="n"/>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative analysis based on long-form interviews with 33 rural journalists exploring how they navigate the boundary between journalism and public relations. It relies entirely on textual analysis and does not provide any quantitative data, correlation matrices, or extractable effect sizes (r) required for this meta-analysis.. Verbatim Evidence: "Researchers analyzed data from long-form interviews (n=33) conducted in late 2020 and early 2021. ... Each participant was interviewed individually (n=33) by a member of the research team. ... Researchers transcribed the interviews and used textual analysis on the transcripts. Using a constant comparative approach (reading through and re-reading content) (Glaser &amp; Strauss, 1967), the researchers met over a series of Zoom calls to reveal themes and narratives in relation to addressing the research questions."</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1" s="10">
       <c r="A5" t="inlineStr">
@@ -667,6 +681,16 @@
           <t>BSMA0002</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>We estimate the long-run effects of the 1930s Home Owners Loan Corporation (HOLC) redlining maps on census tract-level measures of socioeconomic status and economic opportunity from the Opportunity Atlas (Chetty et al. 2018). We use two identification strategies to identify the long-run effects of differential access to credit along HOLC boundaries. The first compares cross-boundary differences along actual HOLC boundaries to a comparison group of boundaries that had similar pre-existing differences as the actual boundaries. A second approach uses a statistical model to identify boundaries that were least likely to have been chosen by the HOLC. We find that the maps had large and statistically significant causal effects on a wide variety of outcomes measured at the census tract level for cohorts born in the late 1970s and early 1980s.</t>
@@ -692,7 +716,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P5" s="8" t="n"/>
+      <c r="P5" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the long-term socioeconomic effects of geographic boundaries (1930s HOLC redlining maps) on neighborhoods, representing construct homonymy for the term 'boundary'. It does not measure interpersonal boundary spanning behavior. The sample consists of general population census data rather than organizational employees (Code 2), the analysis is conducted at the geographic neighborhood/census-tract level (Code 3), and it completely lacks the boundary spanning behavior construct and any relevant effect sizes (Code 1). Thus, it is excluded for multiple reasons [Code 1, Code 2, Code 3].. Verbatim Evidence: "We estimate the long-run effects of the 1930s Home Owners Loan Corporation (HOLC) redlining maps on census tract-level measures of socioeconomic status and economic opportunity from the Opportunity Atlas (Chetty et al. 2018). We use two identification strategies to identify the long-run effects of differential access to credit along HOLC boundaries. ... We find that the maps had large and statistically significant causal effects on a wide variety of outcomes measured at the census tract level for cohorts born in the late 1970s and early 1980s."</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="18" customHeight="1" s="10">
       <c r="A6" t="inlineStr">
@@ -705,6 +733,16 @@
           <t>BSMA0003</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>Interactions with other organizations likely influence how local governments confront complex problems. Drawing on theories of collaborative governance, we investigate the extent to which collaboration affects U.S. local governments’ prioritization of the sustainability benefits of Smart Cities Technologies (SCT). Using data from the International City/County Management Association (ICMA) 2016 Smart Cities Survey and the U.S. Census Bureau, we find that collaboration with local, regional, and private sector partners influences the extent to which local governments prioritize the sustainability benefits of SCT. Organizational capacity is also an important predictor of perceived benefits of SCT. Our findings suggest a hidden side of boundary spanning, suggesting that collaboration can enhance opportunities for sustainability technologies.</t>
@@ -730,7 +768,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P6" s="8" t="n"/>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>The study uses local government officers as key informants to evaluate organizational-level collaboration and capacity for their respective cities/counties (N=234 local governments). The survey items ask about what 'your local government' or 'your community' does, violating the individual-level analysis requirement (Code 3). Additionally, the study does not report a zero-order correlation matrix and only provides ordinal logistic regression coefficients, lacking an extractable effect size (Code 1).. Verbatim Evidence: "The data for this research is drawn from the 2016 International City/County Management Association (ICMA) Smart Cities Survey. Partnering with the Smart Cities Council, ICMA sent the survey in 2016 to 3,423 local government officers working in U.S. cities and counties... After eliminating records with missing data, our final sample includes responses from 234 local governments. Most survey responses were primarily from cities (83.3%), with the remaining responses coming from counties... A binary variable which attains a value of 1 if the community participates in collaborative efforts at county level... The participants responded to the question “What collaborative smart city efforts does your community participate in?”"</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="18" customHeight="1" s="10">
       <c r="A7" t="inlineStr">
@@ -743,6 +785,16 @@
           <t>BSMA0004</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Faced with the challenges to addressing the novelties of the changing business environments (e.g., new customer requirement, changes in customers taste and preferences, the introduction of new products or services by competitors), organizations seek to build collaboration among their employees who possess complementary knowledge. Integrating complementary knowledge enhances employees' ability to address environmental challenges and foster innovation. Despite the importance of knowledge integration for innovation, integration of such knowledge becomes difficult when employees lack a shared understanding of knowledge, and when the knowledge is newly generated. Because new knowledge is tacit in nature and highly personal to a particular individual, it is difficult to articulate, making knowledge integration (KI) an arduous task. Lack of shared understanding, the presence of new knowledge, and lack of common interests in employees creates three types of knowledge boundaries – syntactic (information processing) boundaries, semantic (interpretive) boundaries, and pragmatic (political) boundaries. The presence of knowledge boundaries makes it difficult for employees to share and access their knowledge with each other. To overcome the challenges related to the knowledge boundaries, employees use boundary-spanning objects, which are common lexicons, common meaning, and common interests, to share and access their knowledge across the boundaries. Although prior studies have emphasized the importance of knowledge integration of various knowledge sources for innovations, examinations of what enhances KI capability of employees for organizational innovation remain limited. In addition, apart from Carlile, (2004) and Franco (2013), which are both case studies, other studies that examine the role of boundary spanning objects for knowledge integration are missing. The knowledge management literature also fails to measures (the success of common lexicons, common meaning, and common interests for achieving KI capability) boundary spanning objects. Therefore, in this study, new measurement items of boundary spanning objects and novelty are developed to test the hypotheses. A survey-based design was used to collect data and measure the constructs examined in this study. Structural equation modeling (SEM) was used to test the direct relationship hypotheses. The moderation effects were tested using 1) multi-group analysis using hierarchical linear regression, and 2) relative weight of each boundary spanning object determining KI capability at the different levels of novelty. Evidence suggests that while common meaning and common interests positively influence KI capability, common lexicon does not have a statistically significant relationship with KI capability. The results also revealed that KI capability positively influences organizational innovation. Moreover, the results demonstrate that the strength of the relationship between boundary spanning objects and KI capability is different at the medium and the high level of novelty.</t>
@@ -768,7 +820,11 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="P7" s="8" t="n"/>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>The study explicitly adopts the firm as the unit of analysis and surveys managers and executives as key informants to evaluate the firm's overall knowledge integration capability and use of boundary spanning objects. The survey items use collective referents such as 'We use common designs' and ask respondents to report on the behavior of 'employees across your FIRM' rather than their own individual boundary spanning behavior. This violates the proxy guardrail, and thus the study must be excluded for analyzing data at the firm level.. Verbatim Evidence: ""The unit of analysis of this study is firm. A firm is used as the unit of analysis because the research questions seek to examine factors that determine a firm’s ability to innovate and to integrate employees’ knowledge." (p. 66) "This study also uses the key informant approach to collect data. To ensure that the respondents are key informants of a firm, screening questions are used in the survey questionnaire." (p. 67) "Given below are the statements related to the use of common lexicon (language, tools, designs, specifications, and rules) by employees across your FIRM... We use common designs for communicating information related to completing a task... We have a common understanding of expected results from completing a task." (pp. 78-79)"</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1" s="10">
       <c r="A8" t="inlineStr">
@@ -781,6 +837,16 @@
           <t>BSMA0005</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>In recent years, community–academic partnerships (CAPs) have gained traction in academia as a method for bridging the research-to-practice gap and reducing health disparities for marginalized populations. The field of social work may be well poised to enhance its ability to engage in partnerships and research around partnerships given its emphasis on conducting practice research and its historical roots in boundary spanning. In this article, the author begins by defining collaborative partnerships between academics and community stakeholders and then states specific advantages and challenges to collaborative partnerships in the field of social work. Throughout, the author explains how the historical foundations of the field (for example, acting as boundary spanners, advocating for marginalized individuals) place social workers in an ideal position to become leaders in the development, sustainment, and strengthening of CAPs. The author details the ways in which social work researchers can use the field’s unique history to enhance the development and sustainment of CAPs. The article concludes by encouraging the field to use standardized terminology, methodology, and evaluation procedures when conducting CAPs and providing strategies for social work researchers who wish
@@ -807,7 +873,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P8" s="8" t="n"/>
+      <c r="P8" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 4] This is a conceptual and historical review article, not a primary empirical study (Code 4). As a theoretical paper without quantitative data, it lacks an individual-level sample, empirical methodology, and a formal correlation matrix, meaning it provides no extractable effect sizes of interest (Code 1).. Verbatim Evidence: "In this article, the author begins by defining collaborative partnerships between academics and community stakeholders and then states specific advantages and challenges to collaborative partnerships in the field of social work. Throughout, the author explains how the historical foundations of the field (for example, acting as boundary spanners, advocating for marginalized individuals) place social workers in an ideal position to become leaders in the development, sustainment, and strengthening of CAPs. The author details the ways in which social work researchers can use the field’s unique history to enhance the development and sustainment of CAPs."</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1" s="10">
       <c r="A9" t="inlineStr">
@@ -820,6 +890,16 @@
           <t>BSMA0006</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>This article presents an empirical test of organizational identification in the context of customer–company (C-C) relationships. It investigates whether customers identify with companies and what the antecedents and consequences of such identification are. The model posits that perceived company characteristics, construed external image, and the perception of the company’s boundary-spanning agent lead to C-C identification. In turn, such identification is expected to impact both in-role behavior (i.e., product utilization) as well as extra-role behavior (i.e., citizenship). The model was tested in a consultative selling context of pharmaceutical sales reps calling on physicians. Results from the empirical test indicated that customers do indeed identify with organizations and that C-C identification positively impacts both product utilization behavior and extra-role behavior even when the effect of brand perception is accounted for. Second, the study found that the organization’s characteristics as well as the salesperson’s characteristics contributed to the development of C-C identification.</t>
@@ -845,7 +925,11 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="P9" s="8" t="n"/>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>The study examines customer-company identification and its antecedents and consequences. It surveys physicians acting in their capacity as customers of a pharmaceutical company. The study does not measure any form of boundary spanning behavior. Instead, it measures 'Perceived salesperson characteristics' (rating traits like friendly, honest, and knowledgeable) and 'Customer extra-role behaviors' (such as recommending products or providing competitive intelligence). Because it lacks any variable representing purposive interpersonal boundary spanning action, it does not provide an effect size of interest.. Verbatim Evidence: "This article presents an empirical test of organizational identification in the context of customer–company (C-C) relationships. It investigates whether customers identify with companies and what the antecedents and consequences of such identification are... A sample of 2,000 high-prescribing physicians was randomly drawn from a population of over 30,000 high-prescribing physicians in the focal drug category... Please indicate how well each of the characteristics listed describes [salesperson of target company] (5-point scale): Industry Leader, Boring, Caring, Compassionate, Cooperative, Courteous, Dynamic, Efficient, Exploitive (r), Friendly, Honest, Humorous, Innovative, Knowledgeable, Likeable, Manipulative (r), Progressive, Reliable, Responsive, Secure, Selfish (r), Sensitive, Sincere, Socially Responsible, Trustworthy."</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="18" customHeight="1" s="10">
       <c r="A10" t="inlineStr">
@@ -858,6 +942,16 @@
           <t>BSMA0007</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>The survival and growth of incumbent firms during periods of competence-destroying technological change depend on their ability to learn new technologies and introduce new products based on them. To do this successfully, incumbents must learn to absorb and assimilate new knowledge, and undertake external boundary spanning search. Although previous studies have investigated these relationships, typically they have taken a macro perspective. In order to gain a better understanding of these relationships, this study is conducted at the firm-therapeutic level in a pharmaceutical industry setting. The results of this study show that incumbent firms that leverage their prior experience, develop absorptive capacity, and undertake external boundary spanning search are successful in adapting to the new technologies.</t>
@@ -883,7 +977,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P10" s="8" t="n"/>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t>[Code 2 &amp; Code 3] The study utilizes secondary, macro-level databases (Windhover RX Deals database, IMS Lifecycle database) rather than surveying human employees. The unit of analysis is the firm-therapeutic level, and boundary spanning search is operationalized as the yearly count of strategic alliances formed by incumbent pharmaceutical firms with biotechnology firms. This violates the requirements for individual-level analysis and human employee samples.. Verbatim Evidence: "The unit of analysis is the firm-therapeutic level, i.e., the firm’s alliance activities in a therapeutic area (for example, Merck’s alliances in cardiovascular therapeutic area). The study identified 1932 alliances formed between incumbent pharmaceutical and new biotechnology firms in eighteen therapeutic areas by seventeen large pharmaceutical firms during the time period from 1991 to 2004. The boundary-spanning search activity was measured by using a yearly count of alliances formed by the incumbent firms in each therapeutic area. This data was gathered from the Windhover database."</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1" s="10">
       <c r="A11" t="inlineStr">
@@ -896,6 +994,16 @@
           <t>BSMA0008</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>In recent years, the adventure tourism sector has seen new travelers seeking self-transformation, learning, and an expanded worldview rather than risk and thrill. They have attracted attention for their contribution to the local economies. However, their motivation behind seeking such goals through adventure tourism remains unknown. Therefore, this study proposes a hypothesis explaining their transformation. An explanatory hypothesis is that adventure tourists possess the evaluation axis of cross-boundary learners who discover new selves through serendipitous encounters and events. Cross-boundary learning, a part of organizational learning, can be conceptually identified with planned happenstance theory (psychology) and effectuation theory (management) that locates self-transformation source in given non-cognitive abilities. Also, adventure tourists have an “ambivalent value” allowing them to simultaneously evaluate the exploitation of knowledge from the servicescape and the exploration of knowledge from the ethnoscape. This conceptual model thus bridges theory and practice for the development of the adventure tourism industry.</t>
@@ -921,7 +1029,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P11" s="8" t="n"/>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 2 &amp; Code 4] The study is a conceptual paper that proposes a theoretical model of adventure tourists as cross-boundary learners. It does not contain any empirical data or extractable effect sizes, and the target population is tourists rather than organizational employees. Therefore, it is excluded for being a non-primary conceptual study, lacking quantitative effect sizes, and not utilizing an organizational employee sample.. Verbatim Evidence: "This paper aims to establish an explanatory hypothesis that theoretically redefines the adventure tourist, who has become elusive due to his or her deviation from risk and thrill. [...] This study generates an explanatory hypothesis about the essential nature of contemporary adventure tourists. [...] However, these hypotheses are unobservable and are not a priori shared in the public domain. Therefore, as previously mentioned, separate empirical experiments are necessary. [...] No data was used for the research described in the article."</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1" s="10">
       <c r="A12" t="inlineStr">
@@ -934,6 +1046,16 @@
           <t>BSMA0009</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Our study investigated the effect of team knowledge on new product development (NPD). By investigating 207 NPD projects, we found that the declarative and procedural knowledge of the team and their use of IT had a positive inﬂuence on the team’s knowledge base; and that the higher the functional diversity of the project team, the greater their overall knowledge. We also found that team knowledge positively impacted new product creativity and success in the market place.</t>
@@ -959,7 +1081,11 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="P12" s="8" t="n"/>
+      <c r="P12" s="8" t="inlineStr">
+        <is>
+          <t>The study uses the new product development (NPD) team as the unit of analysis (N=207 NPD projects) and surveys product/project managers as key informants to evaluate team-level constructs. The survey items refer to 'the team' rather than the individual respondent ('I'), which violates the individual-level analysis requirement.. Verbatim Evidence: "Since our study focused on the NPD team as a unit of analysis, product/project managers were likely to assess our variables more accurately. ... We received 207 usable responses (an effective response rate of 16.5%) representing a wide range of industries in the manufacturing sector ... Information acquisition ability (modified from Moorman [22])—during this project, the team had the ability of continuously: Collecting information from customers."</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1" s="10">
       <c r="A13" t="inlineStr">
@@ -972,6 +1098,16 @@
           <t>BSMA0010</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>With the increasing popularity of organizational sensemaking in the literature, sensemaking capability of firms attracts many researchers and practitioners from different fields. Nevertheless, sensemaking capability is rarely addressed in the new product development (               NPD               ) project teams in the technology and innovation management literature. Specifically, we know little about what team sensemaking capability is, its ingredients and benefits, and how it works in               NPD               projects (e.g., its antecedents and consequences). By investigating 92               NPD               project teams, we found that (1) team sensemaking capability, which is composed of internal and external communication, information gathering, information classification, building shared mental models, and taking experimental actions, has a positive impact on the information implementation and speed‐to‐market; (2) information implementation and speed‐to‐market mediate the relationship between team sensemaking capability and new product success; and (3) team sensemaking capability mediates the relationship between team processes and information implementation and partially mediates the relationship between team processes and speed‐to‐market. We also found that team autonomy, interpersonal trust among team members, and open‐mindedness of team members positively influence the development of team sensemaking capability. Theoretical and managerial implications of the study findings are discussed.</t>
@@ -997,7 +1133,11 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="P13" s="8" t="n"/>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the team (N = 92 new product development project teams), and the variables measure team-level constructs (e.g., team sensemaking capability, team autonomy, and process effectiveness). The survey was completed by product/project managers who acted as key informants to evaluate the team's collective behavior. The survey items use team-level referents (e.g., 'Our team regularly discussed with customers'). Therefore, the study does not provide individual-level correlations for employee boundary spanning behavior and must be excluded as a macro-level (team-level) analysis.. Verbatim Evidence: "Among the 180 firms contacted, we received 92 usable returns concerning NPD projects. ... we targeted the product or project manager to complete the survey. These managers were chosen because (1) product/project managers are likely to have a 'bigger-picture view' of NPD projects than other team members; (2) project managers have a broader view of each member's behaviors than other team members... External communication: Our team regularly discussed with customers. (0.62); Our team systematically acquired external technological and market information. (0.82); Our team consulted regularly to outside experts. (0.65)"</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1" s="10">
       <c r="A14" t="inlineStr">
@@ -1010,6 +1150,16 @@
           <t>BSMA0011</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2 = Non-employee samples</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Today, many firms are striving to enhance customers’ purchase intentions by leveraging online consumer communities but a better understanding of the underlying phenomena is needed to guide their efforts most effectively. In this study we analyse how three hotel firms engage potential customers through FlyerTalk, an online consumer community of frequent travellers (FlyerTalk.com). Our results suggest that for some firms, the frequency and perceived value of their participation are two important factors that can potentially be managed toward positive purchasing intention effects.</t>
@@ -1035,7 +1185,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P14" s="8" t="n"/>
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a sample of consumers (N=139 frequent travellers from the FlyerTalk online forum) to evaluate the online posting behavior (frequency and value) of hotel representatives, as well as the consumers' own purchasing intentions. Because the data is collected from consumers rather than organizational employees, it violates the sample population guardrail and is excluded under Code 2.. Verbatim Evidence: "To test our hypotheses we collected primary data from FlyerTalk forum members via a short survey posted to a brand-independent subsection of the forum. ... Four responses with missing data were also removed leaving 139 usable responses. Summary statistics of respondent demographics are included in Table 1. ... Survey respondents were directed to different survey rating item sets customized to their preferred hotel reward program. ... The [hotel reward program] representative posts frequently on FlyerTalk ... Posts made by the [hotel reward program] representative on FlyerTalk are highly valuable to consumers ... I am more likely to stay at a property of [the hotel] because of the [hotel reward program representatives'] posts on FlyerTalk"</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1" s="10">
       <c r="A15" t="inlineStr">
@@ -1048,6 +1202,16 @@
           <t>BSMA0012</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Boundaries are a defining characteristic of organizations, and boundary roles are the link between the environment and the organization. The creation, elaboration, and functions of boundary spanning roles are examined, with attention to environmental and technological sources of variation in the structure of boundary roles. Eleven hypotheses integrate the material reviewed and are amenable to empirical test. Future research should overcome problems created when organizations are treated as “wholes” or single entities.</t>
@@ -1073,7 +1237,11 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="P15" s="8" t="n"/>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a conceptual review article that examines the functions of boundary spanning roles and proposes 11 hypotheses for future research. It does not contain any primary empirical data or report quantitative effect sizes (r), therefore it is excluded as a non-primary study.. Verbatim Evidence: "The creation, elaboration, and functions of boundary spanning roles are examined, with attention to environmental and technological sources of variation in the structure of boundary roles. Eleven hypotheses integrate the material reviewed and are amenable to empirical test. ... This review could not have been written without the foundation laid by James D. Thompson, and our debt to him should be evident to those familiar with his work. ... H1: An organization's ability to adapt to environmental contingencies depends in part on the expertise of boundary role incumbents in selecting, transmitting, and interpreting information originating in the environment."</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1" s="10">
       <c r="A16" t="inlineStr">
@@ -1086,6 +1254,16 @@
           <t>BSMA0013</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Within the wake of the COVID‐19 pandemic, we investigate work‐nonwork boundary management among workers who transitioned to remote work. Based on five waves of data and a sample of 155 remote workers, we find that the preference for segmentation was associated with greater work‐nonwork balance. We also found that having a dedicated office space within the home and fewer household members was associated with greater work‐nonwork balance. However, these variables did not moderate the relationship between segmentation preferences and work‐nonwork balance as expected. We discuss implications for future research on boundary management processes and practices.</t>
@@ -1111,7 +1289,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P16" s="8" t="n"/>
+      <c r="P16" s="8" t="inlineStr">
+        <is>
+          <t>The study examines work-nonwork (work-family) boundary management among remote workers during the COVID-19 pandemic. It focuses on individuals' preferences and strategies for segmenting work from personal life (e.g., 'I don't like to have to think about work while I'm at home'). This violates the construct validity criteria, as it measures work-life boundary management rather than purposive inter-organizational or intra-organizational boundary spanning behavior.. Verbatim Evidence: "Within the wake of the COVID-19 pandemic, we investigate work-nonwork boundary management among workers who transitioned to remote work... Specifically, guided by boundary theory, we investigate the relationship between integration-segmentation preferences and work-nonwork balance across a three-month period... Segmentation Preferences. Six items based on Kreiner’s (2006) segmentation preferences scale were used (e.g., “I don’t like to have to think about work while I’m at home”; “I prefer to keep my non-work life at home”)."</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1" s="10">
       <c r="A17" t="inlineStr">
@@ -1124,6 +1306,16 @@
           <t>BSMA0014</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Although researchers have gained considerable knowledge regarding the multi-faceted manifestation of burnout over recent years, inconsistent findings of role ambiguity as an antecedent to burnout are still prevalent. Given the complex boundary-spanning nature of sales, it is likely that global measures of role ambiguity fail to fully capture the domain and impact of role ambiguity. To help address this gap, this study provides initial evidence that facets of role ambiguity impact burnout manifestation in the sales role differently. Specifically, findings provide a foundation to help mitigate the negative impact of burnout by focusing on only certain facets of role ambiguity.</t>
@@ -1149,7 +1341,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P17" s="8" t="n"/>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on salespeople (referred to as boundary spanners) but does not measure Boundary Spanning Behavior (BSB) as a substantive construct. Instead, it measures role ambiguity (using the MULTIRAM scale), role conflict, burnout, job satisfaction, and job performance. Since there is no measurement of purposive boundary-spanning actions (e.g., information scanning, external representation, or coordination), the study lacks the target effect size of interest.. Verbatim Evidence: "the purpose of this study is to identify relationships at the facet level between role ambiguity and burnout in relation to job satisfaction and performance while controlling for role conflict (see Fig. 1). ... Role ambiguity was measured using the 45-item MULTIRAM instrument (Singh &amp; Rhoads, 1991). ... Table 1 Correlations, means, standard deviations, and reliabilities. Variables: RA Work, RA promo, RA family, RA boss, RA cust, RA other, RA cowo, Pers accom, EE, Deper, Role con, Job sat, Job perf."</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="18" customHeight="1" s="10">
       <c r="A18" t="inlineStr">
@@ -1162,6 +1358,14 @@
           <t>BSMA0015</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>999</v>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>To test some of the social and organizational psychology underpinnings of boundary spanning theory, the consultative, boundary spanning activities of 27 New York State school psychologists within their special education multidisciplinary teams were studied. More specifically, the relation between boundary spanning and task uncertainty, role specification, degree of professional training and continuing activity, size of organization, and available organizational resources was investigated. The results indicated that boundary spanning was significantly related to perceived task uncertainty. The implications of these results were discussed, and future research efforts needed to further differentiate this important construct were suggested.</t>
@@ -1187,7 +1391,11 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="P18" s="8" t="n"/>
+      <c r="P18" s="8" t="inlineStr">
+        <is>
+          <t>The study quantitatively examines the boundary spanning activities of individual school psychologists (N=27) working in multidisciplinary teams. It provides a full zero-order correlation matrix (Table 2) including internal and external boundary spanning and relevant organizational variables such as task uncertainty, environmental uncertainty, and role specification. The boundary spanning measure captures purposive consultative actions (gathering, translating, and transmitting information), meeting construct validity requirements. The unit of analysis is the individual employee, and no exclusion criteria apply.. Verbatim Evidence: "Ultimately, 27 school psychologists (50% of the 54 possible participating districts) returned their boundary spanning questionnaires. ... Boundary Spanning Activity. This variable focuses on the behavior of individuals who are involved in the process of interprofessional consultation and communication as it relates to multidisciplinary referrals and staffings. This process has two components: (a) consulting with (i.e., translating and transmitting information to) people within the organization and (b) consulting with (i.e., gathering information from and sending information to) people outside the organization. ... MDT boundary spanning activities are measured by asking how many hours and types of formal and informal consultation interactions (e.g., MDT-related meetings, phone conversations, and other communications) occur in an average week, both within and outside the school organization. ... The intercorrelation matrix, presented in Table 2, consists of 10 variables: the 3 dependent boundary spanning variables (internal, external, and total), the 5 independent BSQ variables (Perceived Environmental Uncertainty, Perceived Task Uncertainty, Perceived Role Specification, Professional Training, and Professional Activity), and the 2 independent school district characteristics..."</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1" s="10">
       <c r="A19" t="inlineStr">
@@ -1200,6 +1408,16 @@
           <t>BSMA0016</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>National sport policies’ harmonization with the World Anti-Doping Agency (WADA) has been one of the most researched topics within the sport policy domain. The literature, however, has failed to offer firsthand empirical insights from those actors who develop the policy so that harmonization occurs. The present study fills this gap by drawing on the tenets of institutional entrepreneurship to unpack the process through the experiences of the person responsible for it. The study employs a collaborative analytical autoethnography where, through memo-writings, emails, and reflective notes by the second author, it micro-theorizes the political, technical, and cultural activities that the institutional entrepreneur carried in order to harmonize Montenegro’s anti-doping policy with WADA. The study reveals that the harmonization process entails seven institutional works: boundary spanning, scanning the environment, repairing bilateral relationships, designing the new legislation, modifying structures, framing the need, and transferring responsibility. This is the first empirical study in sport management literature to examine institutional change for sport policy-making through the lenses of institutional entrepreneurship and a collaborative autoethnographic perspective.</t>
@@ -1225,7 +1443,11 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="P19" s="8" t="n"/>
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t>The study is a collaborative autoethnography examining the harmonization of national anti-doping policy through the lens of institutional entrepreneurship. It relies entirely on qualitative data, such as emails, official memos, meeting notes, and reflective narratives, rather than quantitative survey data from organizational employees. As a qualitative study, it does not provide a zero-order correlation matrix or any extractable quantitative effect sizes (r). Furthermore, the study focuses on institutional entrepreneurship and national policy harmonization rather than interpersonal boundary spanning behavior. Therefore, it must be excluded.. Verbatim Evidence: "The study employs a collaborative analytical autoethnography where, through memo-writings, emails, and reflective notes by the second author, it micro-theorizes the political, technical, and cultural activities that the institutional entrepreneur carried in order to harmonize Montenegro’s anti-doping policy with WADA. ... Qualitative in nature, autoethnography is a method that shifts the attention from the perceived reality of research participants to the researcher him/herself (as a subject) ... Furthermore, the analytical reflexivity ([b], as per Anderson’s guide; see next section) was performed through a rich set of field notes consisting of emails, official memos, meetings, and media appearances. Table 1 provides a more analytical picture of the dataset itself, demonstrating the second author’s engagement with informants beyond himself."</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1" s="10">
       <c r="A20" t="inlineStr">
@@ -1238,6 +1460,16 @@
           <t>BSMA0017</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Purpose – The purpose of this study is to examine the relationship between ethical climate and facets of job satisfaction among organizational buyers. Design/methodology/approach – This research is an empirical study. Data are collected from the industrial buyers using online panel. The INDSALES scale, the scale developed to measure job satisfaction of boundary spanners, was used to measure the job satisfaction. Partial least squares, a components-based structural equation modeling approach, was employed to conduct data analysis.</t>
@@ -1263,7 +1495,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P20" s="8" t="n"/>
+      <c r="P20" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on organizational buyers who are described as occupying boundary-spanning roles, but it does not measure boundary spanning behavior (BSB) as a construct. The variables measured are limited to ethical climate and various facets of job satisfaction (pay, policy, promotion, coworkers, supervision, work satisfaction). Because there is no quantitative measure of boundary spanning behavior itself, the study lacks the required effect size of interest.. Verbatim Evidence: "Data are collected from the industrial buyers using online panel. The INDSALES scale, the scale developed to measure job satisfaction of boundary spanners, was used to measure the job satisfaction. Ethical climate was measured using the seven-item scale proposed by Weeks et al. (2004). To measure the job satisfaction facets, the reduced version of the INDSALES scale (Churchill et al., 1974; Comer et al., 1989; Lagace et al., 1993) was adapted for use within a procurement context. Of the seven facets, six were relevant within this study[1]. Table II Assessment of the measures and construct correlations: Construct, Item loadings, CR/alpha, EC, Pay, Policy, Promotion, Coworker, Super-vision, Work satisfaction."</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1" s="10">
       <c r="A21" t="inlineStr">
@@ -1276,6 +1512,16 @@
           <t>BSMA0018</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Data from 409 members of forty-five new product teams in five high technology companies indicate the existence of four sets of boundary management activities which can be labeled Ambassador, Task Coordinator, Scout, and Guard. These activities are related to the frequency, type, and destination of communications between team members and others. This article describes these activities and examines the impact of individual and environmental variables on the frequency in which individual team members engage in them.</t>
@@ -1301,7 +1547,11 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="P21" s="8" t="n"/>
+      <c r="P21" s="8" t="inlineStr">
+        <is>
+          <t>The study's sample consists entirely of small business owners (independent entrepreneurs), who must be excluded under the population boundary guardrail (Code 2) because they operate independently rather than as embedded organizational employees. Additionally, the study relies on MANOVA and ANOVA to compare boundary spanning activities across categorical decision style groups, and does not provide a zero-order correlation matrix or extractable quantitative effect sizes (r) for the boundary spanning variables (Code 1). Therefore, the study is excluded for multiple reasons [Code 1 &amp; Code 2].. Verbatim Evidence: "Subjects in this study were 57 (29 male and 28 female) small business owners operating in a southeastern state. For this sample the term small business was used to identify owners whose firms employed less than one hundred people and had annual gross sales of less than one million dollars. ... Because BSA was defined as multidimensional in nature and was composed of three separate dimensions, the primary analytic technique used was multivariate analysis of variance (MANOVA). ... Table 4. Multivariate (MANOVA) and Univariate (ANOVA) Results of the Effect of Decision Style on Boundary Spanning Dimensions"</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1" s="10">
       <c r="A22" t="inlineStr">
@@ -1314,6 +1564,16 @@
           <t>BSMA0019</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>This article focuses on the activities teams use to manage their organizational environment beyond their teams. We used semistructured interviews with 38 new-product team managers in high-technology companies, log data from two of these teams, and questionnaires completed by members of a different set of 45 new-product teams to generate and test hypotheses about teams' external activities. Results indicate that teams engage in vertical communications aimed at molding the views of top management, horizontal communication aimed at coordinating work and obtaining feedback, and horizontal communication aimed at general scanning of the technical and market environment. Organizational teams appear to develop distinct strategies toward their environment: some specialize in particular external activities, some remain isolated from the external environment, and others engage in multiple external activities. The paper shows that the type of external communication teams engage in, not just the amount, determines performance. Over time, teams following a comprehensive strategy enter positive cycles of external activity, internal processes, and performance that enable long-term team success.</t>
@@ -1339,7 +1599,11 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="P22" s="8" t="n"/>
+      <c r="P22" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes boundary spanning activities ('ambassadorial', 'task-coordinator', 'scouting') at the team level. While data was collected from 409 individuals, their responses were aggregated to compute scores for 45 new-product development teams. The correlation matrix provided in Table 2 and subsequent regressions are based on this team-level data (N=45 teams), lacking an individual-level zero-order correlation matrix.. Verbatim Evidence: ""much of the analysis was conducted at the group level, teams were included in the final sample only if at least three-fourths of their members responded. This reduced the number of teams in the final sample to 45." (Page 8); "Factor scores were then calculated for each individual and averaged to form group scores." (Page 8); "A score was then computed for each of the 45 teams by averaging the individual scores of the members of the team" (Page 23)"</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1" s="10">
       <c r="A23" t="inlineStr">
@@ -1352,6 +1616,16 @@
           <t>BSMA0020</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>Purpose – A large number of studies indicate that coercive forms of organizational control and performance management in health care services often backfire and initiate dysfunctional consequences. The purpose of this article is to discuss new approaches to performance management in health care services when the purpose is to support innovative changes in the delivery of services.</t>
@@ -1377,7 +1651,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P23" s="8" t="n"/>
+      <c r="P23" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a conceptual review that explores and discusses new approaches to performance management in healthcare services by synthesizing existing literature, theories, and systematic reviews. It does not present a primary empirical study with quantitative data or extractable effect sizes for boundary spanning behavior.. Verbatim Evidence: "Paper type General review. Design/methodology/approach – The article represents cross-boundary work as the theoretical and empirical material used to discuss and reconsider performance management comes from several relevant research disciplines, including systematic reviews of audit and feedback interventions in health care and extant theories of human motivation and organizational control. Methodologically, the article represent cross-boundary work as the theories and empirical findings used to discuss and explore new approaches to performance management comes from several separate research disciplines, including studies of organizational control, systematic reviews of clinical audit and feedback interventions and cognitive theories of motivation."</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1" s="10">
       <c r="A24" t="inlineStr">
@@ -1390,6 +1668,16 @@
           <t>BSMA0021</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>In order to continue to be innovative in the current fast-paced and competitive environment, organizations are increasingly dependent on creative inputs developed outside their boundaries. The paper addresses the boundary spanning activities that managers undertake to a) select and mobilize creative talent, b) create shared identity, and c) combine and integrate knowledge in innovation projects involving external actors. We study boundary spanning activities in two creative projects in the LEGO group. One involves identifying and integrating deep, specialized knowledge, the other focuses on the use of external actors as a source of broad, not necessarily fully developed ideas. We find that the boundary spanning activities in these two projects differ in respect, among other things, of how the firm selects participants, formulates problems, and aligns the expectations of internal and external actors, and how knowledge is integrated across organizational boundaries. We discuss implications of our findings for managers and researchers in a business-to-business context.</t>
@@ -1415,7 +1703,11 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="P24" s="8" t="n"/>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative case study exploring boundary spanning activities in creative projects at the LEGO Group using interview data. It does not provide quantitative survey data, formal correlation matrices, or extractable zero-order effect sizes required for the meta-analysis.. Verbatim Evidence: "Information was gathered primarily through interviews. Mantere (2008) describes individual interviews as one of the best sources of information when trying to understand the motivations and character of the actions that take place in highly embedded social contexts such as organizations... The data were analyzed independently by each of the authors. We used Nvivo 9 (a software program for managing qualitative data) to categorize quotes and emerging insights."</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1" s="10">
       <c r="A25" t="inlineStr">
@@ -1426,6 +1718,16 @@
       <c r="B25" t="inlineStr">
         <is>
           <t>BSMA0022</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1456,7 +1758,11 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="P25" s="8" t="n"/>
+      <c r="P25" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study investigates the behavior of pollution control departments using qualitative interviews, archival records, and a small written survey. It is excluded for two main reasons. First, the unit of analysis is at the firm/department level (N=8 firms), which violates the requirement for individual-level employee data (Code 3). Second, the study lacks a formal zero-order Pearson correlation matrix and relies on Kendall's Tau correlations for the small firm sample, thus failing to provide extractable quantitative effect sizes required for the meta-analysis (Code 1).. Verbatim Evidence: "I chose to identify a few similar manufacturing organizations and then analyze them in detail using qualitative interviews, archival records, and several written surveys. ... Twelve rigid printed circuit firms agreed to participate in the written study and were sent questionnaires for the wet process, quality, and pollution control managers. Eight firms returned all three surveys, two returned two surveys, and two did not respond. ... Fig. 2. Paired Kendall Tau correlations between communication measures and PC initiated process innovation. ... N=8"</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="10">
       <c r="A26" t="inlineStr">
@@ -1469,6 +1775,16 @@
           <t>BSMA0023</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>Successful innovation requires firms to search beyond their organizational confines for complementary knowledge resources ahead of their competitors. While such proactive boundary-spanning search (PBS) provides relevant knowledge resources for green innovations, it can also lead to information overload that derails green innovation efforts. Therefore, there is a need to understand how and when PBS translates into green innovation. This study combines the dynamic capabilities theory with the organizational information processing theory to develop a moderated mediation model that espouses the role of green dynamic capability and analytics capability in the relationship between PBS and green innovation. The study's hypothesis is tested using firm-level survey data from 200 manufacturing firms in Ghana. Partial least squares structural equations modeling (PLS-SEM) and PROCESS were used to evaluate the research model. The results confirm a positive relationship between PBS and green dynamic capabilities, and also between green dynamic capabilities and green innovation. More importantly, PBS drives green innovation through green dynamic capability, particularly at moderate and high levels of analytics capability. The theoretical and managerial implications of the study are outlined in the text.</t>
@@ -1494,7 +1810,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P26" s="8" t="n"/>
+      <c r="P26" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates proactive boundary-spanning search at the firm level, not the individual level. The grammatical subject of the survey items is 'Our firm', indicating that the respondents are acting as macro-level key informants to evaluate organizational behavior rather than their own interpersonal boundary spanning. This violates the individual-level unit of analysis criteria.. Verbatim Evidence: ""The study's hypothesis is tested using firm-level survey data from 200 manufacturing firms in Ghana." ... "PBS was measured using five items adapted from (Wang &amp; Yang, 2023). The items are: 'Our firm has many channels to search new domain knowledge ahead of competitors,' 'Our firm can search new domain knowledge about R&amp;D, production, and marketing ahead of competitors,' 'Our firm can search new domain knowledge about technology and management ahead of competitors,' 'Our firm can search more new knowledge ahead of competitors,' and 'our firm can conduct in-depth search and obtain knowledge of emerging technologies ahead of competitors.'""</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="10">
       <c r="A27" t="inlineStr">
@@ -1507,6 +1827,16 @@
           <t>BSMA0024</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>This study analyses the presence of gender segregation in Spanish exporting ﬁrms. Both women’s access to managerial positions (vertical segregation) and women’s achievement of managerial roles that are socially associated with communal attributes (horizontal segregation) are tested. We argue that boundary-spanning (henceforth, boundary management) in export interﬁrm relationships beneﬁts from relational and communal skills and therefore could not only offer an opportunity for women to gain access to management positions but also put them at risk of falling into a rut before achieving other controlbased managerial roles. This empirical study examines the characteristics (personal and ﬁrm-level) of Spanish female managers in charge of export management through independent channels. A multivariate analysis has been performed to compare female managers with male managers both in boundary management and in the position of ﬁnance director, a control position closer to a socially stereotyped masculine role. The results show that women have slightly higher access to boundary management jobs than ﬁnance management jobs, as well as a signiﬁcantly lower promotion time than male colleagues, but they also corroborate that there is a smaller percentage of women than men in any management positions, with female managers working in younger ﬁrms with fewer resources for export activity.</t>
@@ -1532,7 +1862,11 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="P27" s="8" t="n"/>
+      <c r="P27" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure boundary spanning behavior as a quantitative construct; instead, it uses the job position of 'export manager' as a proxy for a boundary management role and compares it to finance directors to examine gender segregation. Furthermore, the paper does not provide a correlation matrix or extractable zero-order effect sizes (r) for boundary spanning behavior, relying only on mean comparisons (Mann-Whitney U tests) and logistic regressions predicting manager gender.. Verbatim Evidence: "To analyze the impact of gender stereotypes when accessing managerial positions, we first compare women's access to both finance and boundary management positions. The former is a control-based post whereas the latter is analyzed regarding a particular type of inter-organizational relationship, namely, export management in firms exporting through independent channels... We designed an online questionnaire... and submitted it to people in charge of export and finance activities... We obtained 193 valid questionnaires from export managers... and 85 from finance directors... Table 3 Logistic regression model: gender of export boundary managers."</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="10">
       <c r="A28" t="inlineStr">
@@ -1545,6 +1879,16 @@
           <t>BSMA0025</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>No abstract</t>
@@ -1570,7 +1914,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P28" s="8" t="n"/>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure Boundary Spanning Behavior (BSB), focusing instead on firm-level diversity, innovation, and internationalization. Furthermore, the analysis is conducted at the firm level (N=30 executives serving as key informants for their companies), and the paper does not report any extractable quantitative effect sizes (e.g., no correlation matrix or regression coefficients). Therefore, it is excluded for lacking the target construct/effect size and violating the individual-level analysis guardrail [Code 1 &amp; Code 3].. Verbatim Evidence: "This descriptive study was carried out with the information obtained from a sample of 30 executives from an equal number of companies... The survey evaluated (on a Likert scale with scores between 1 and 5) ten principal aspects of each variable such as: a) Diversity: Gender, Nationality, Functional Background, Educational Background and Age. b) Innovation: Product, Process, Marketing, Administration, Research and Development (R&amp;D) and Patents. c) Internationalization: Export, Joint Ventures, Foreign Trade Shows, Foreign Trade and Foreign Investment ... The analysis of the data was made from a descriptive statistic (estimation of averages and standard deviations) and a correspondence analysis to evidence the relation between variables."</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="10">
       <c r="A29" t="inlineStr">
@@ -1583,6 +1931,16 @@
           <t>BSMA0026</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>Matching survey data on PhD scientists and engineers currently working in an R&amp;D job in industry with publications and patents, we study the relation between their individual motives and the rate and nature of their inventive output. We ﬁnd that individuals with a strong taste for science, that is motivated by intellectual challenge, autonomy, and contribution to society, create more novel and impactful patents in industry. These individuals are also more involved in academic boundary spanning, proxied by scientiﬁc publications co-authored with academic scientists, and this boundary spanning partially mediates the effect of taste for science on impactful inventive output. In contrast, individuals with a strong taste for salary and career collaborate less with academic scientists, fully mediating the negative effect of taste for salary and career on impactful inventive output.</t>
@@ -1608,7 +1966,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P29" s="8" t="n"/>
+      <c r="P29" s="8" t="inlineStr">
+        <is>
+          <t>The study examines academic boundary spanning among R&amp;D scientists in industry, but it relies entirely on Poisson quasi-maximum likelihood (PQML) regressions and lacks a zero-order correlation matrix, meaning no zero-order effect sizes (r) can be extracted. Additionally, the study operationalizes academic boundary spanning as an objective count of co-publications with academic scientists, which is a measure of joint research output rather than purposive interpersonal boundary-spanning behavior.. Verbatim Evidence: "To measure involvement in academic boundary spanning, we calculate the number of publications co-authored with academic scientists (Cockburn and Henderson, 2003). We take into account all co-publications in the Web of Science published between the starting date of the current job and January 1, 2006... Given that our outcome variables are non-negative integers, we estimate the regressions using Poisson quasi-maximum likelihood (PQML). We cluster standard errors at the firm level."</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="10">
       <c r="A30" t="inlineStr">
@@ -1621,6 +1983,16 @@
           <t>BSMA0027</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>The extent to which demand and supply shocks are transmitted in the supply chain is an important topic. As many supply chains cross international borders exchange rate pass through is an important element in this context. In this paper a multivariate system that allow us to test different hypothesis with respect to the supply chain is speciﬁed. Our empirical analysis includes tests of whether there is a link between the different stages in the supply chain, whether the exchange rate pass through is complete and whether price signals are fully transmitted. Different exogeneity assumptions are testable hypothesis, and one can avoid the simultaneity problem associated with the common single equation speciﬁcations. Moreover, one can also test whether the exchange rate is determined outside the system, as well as testing for price leadership. An application is provided for the supply chain for cod between Norway and Portugal.</t>
@@ -1646,7 +2018,11 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="P30" s="8" t="n"/>
+      <c r="P30" s="8" t="inlineStr">
+        <is>
+          <t>This study analyzes macro-economic price transmission in cross-boundary supply chains for cod between Norway and Portugal. It uses national-level price and exchange rate time-series data rather than individual employee surveys. The paper violates multiple inclusion criteria: it lacks human employee samples (Code 2), analyzes macro-level market data rather than individual-level behavior (Code 3), and lacks any relevant construct or effect size for interpersonal boundary spanning behavior (Code 1). Therefore, it is excluded under Code 5 [Code 1, Code 2, Code 3].. Verbatim Evidence: "Abstract: "The extent to which demand and supply shocks are transmitted in the supply chain is an important topic. As many supply chains cross international borders exchange rate pass through is an important element in this context. In this paper a multivariate system that allow us to test different hypothesis with respect to the supply chain is specified... An application is provided for the supply chain for cod between Norway and Portugal." Data: "In our analysis we have data on prices and the exchange rate for the period January 1988 to December 1999. The Norwegian ex. vessel prices are from Norges Raafisklag, the Norwegian export price to Portugal in Norwegian kroner from the Norwegian Trade Statistics, and the Portuguese retail prices in Portuguese escudos from the Institute of National Statistics.""</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="10">
       <c r="A31" t="inlineStr">
@@ -1659,6 +2035,16 @@
           <t>BSMA0028</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>We focus on everyday role transitions involving home, work, and other places. Transitions are boundary-crossing activities, where one exits and enters roles by surmounting role boundaries. Roles can be arrayed on a continuum, spanning high segmentation to high integration. Segmentation decreases role blurring but increases the magnitude of change, rendering boundary crossing more difficult; crossing often is facilitated by rites of passage. Integration decreases the magnitude of change but increases blurring, rendering boundary creation and maintenance more difficult; this challenge often is surmounted by boundary work.</t>
@@ -1684,7 +2070,11 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="P31" s="8" t="n"/>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a theoretical and conceptual article published in the Academy of Management Review. It develops a framework and propositions regarding micro role transitions and boundary theory, but does not present primary empirical data, quantitative analysis, or an extractable correlation matrix.. Verbatim Evidence: "We focus on the transition process, developing propositions regarding the psychological (and, if relevant, physical) movement between roles. Using what we will call 'boundary theory' as a framework, we describe role transitions as a boundary-crossing activity, where one exits and enters roles by surmounting boundaries... Proposition 1: Role contrast tends to be negatively associated with role flexibility and role permeability."</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="10">
       <c r="A32" t="inlineStr">
@@ -1697,6 +2087,16 @@
           <t>BSMA0029</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Conventional wisdom suggests that market forces such as competitor aggressiveness and competitor innovativeness induce supply chain responsiveness. However, this assertion does not only lack empirical evidence but also the mechanisms that explain the supply chain responsiveness effects of market forces are under-theorized. Drawing on the contingency–capability perspective, this research develops and tests the argument that customer integration is a critical boundary-spanning capability that translates competitor aggressiveness and innovativeness into enhanced supply chain responsiveness. Empirical results based on survey data from 117 firms in Ghana reveal that both market forces are not directly related to supply chain responsiveness. Additional results, however, show that customer integration mediates the competitor aggressiveness and innovativeness-supply chain responsiveness relationships. In contributing to the limited knowledge of the determinants of responsive supply chains, this article shows that external environmental factors are essential but might be insufficient for accounting for the heterogeneity in supply chain responsiveness.</t>
@@ -1722,7 +2122,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P32" s="8" t="n"/>
+      <c r="P32" s="8" t="inlineStr">
+        <is>
+          <t>The study adopts the firm as the unit of analysis (N = 117 firms) to examine the impact of competitor actions on supply chain responsiveness through customer integration. Managers and executives were surveyed as key informants to evaluate the firm's inter-organizational relationships and supply chain integration with downstream channel members. The survey items (e.g., 'Your business processes &amp; systems are aligned with customers' needs') assess firm-level operational processes and relationships rather than individual-level interpersonal boundary-spanning behavior, violating the unit of analysis guardrail.. Verbatim Evidence: "Empirical results based on survey data from 117 firms in Ghana reveal that both market forces are not directly related to supply chain responsiveness... To identify and locate the target firms we largely relied on the databases of the Yellow Pages Ghana and the Association of Ghana Industries... In all, 170 questionnaires were hand-delivered to key informants who were willing to participate in the study... These individuals included supply chain/logistics manager (15.6%), CEO/president/vice president (30.3%), General Manager/Managing Director (19.3%), or other individuals perceived to have adequate knowledge about the company's internal and external processes... The informants were asked to indicate the extent to which their firms have integrated with key downstream channel members along with the measures and the scale used. [Customer integration items include] CI4: Your business processes &amp; systems are aligned with customers' needs."</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="10">
       <c r="A33" t="inlineStr">
@@ -1735,6 +2139,14 @@
           <t>BSMA0030</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Expatriates provide bene®ts to multinational corporations (MNCs) when they enact boundary spanning roles. They do so by relaying local information and identifying opportunities that meet internal needs of MNCs. To test hypotheses based on social capital and role theories, we surveyed 232 expatriates. The ®ndings indicated that local experience and the diversity of social networks were conducive to the boundary spanning activities of expatriates, whereas environmental uncertainty and overseas experience had little effect. By engaging in boundary spanning activities, expatriates felt less role ambiguity and gained role bene®ts, and were more eager to use the resources that were found within different communities of the host country. In addition, those expatriates who engaged in more boundary spanning activities had higher job satisfaction and more power within their own companies than those who did not.</t>
@@ -1760,7 +2172,11 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="P33" s="8" t="n"/>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
+          <t>The study examines boundary spanning behaviors (ambassador, task coordinator, and scout roles) of individual expatriates. The sample consists of individual employees (N=232) and the study provides a full zero-order correlation matrix including these boundary spanning dimensions and other variables like job satisfaction and role ambiguity. This perfectly matches the criteria for inclusion.. Verbatim Evidence: "A total of 745 expatriates were solicited through fax messages to participate in our study... 232 questionnaires (31%, out of 745) were returned. Boundary spanning behavior was measured by items that were derived from Ancona and Caldwell (1992). The 'ambassador' role of being protective and persuasive in favor of the organization... The 'task coordination' role of coordinating and negotiating with outsiders... The 'scout' role of scanning the environment was tapped by assessing the responsibility of expatriates in three tasks... Table 1 Descriptive statistics of variables in the models..."</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="10">
       <c r="A34" t="inlineStr">
@@ -1773,6 +2189,16 @@
           <t>BSMA0031</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Reducing carbon emissions and achieving net-zero goals remain critical global supply chain priorities, and the transition to a circular supply chain is pivotal in reducing carbon emissions. This study empirically examines how low-carbon operations management practices impact circular supply chain management. We collected and analysed data from 183 respondents. Results from partial least squares structural equation modelling show that net-zero capabilities have a direct positive moderating effect on green product innovation and enhance end-of-product-life management and that net-zero capability can play a major role as a boundary-spanning function in accelerating green product innovation while balancing carbon emissions in the circular supply chain. Net-zero capability refers to a firm's ability to reduce its greenhouse gas emissions and align its operations with decarbonisation efforts. For practitioners, our results highlight that firms should focus on more than just green innovation; they should strengthen their net-zero capabilities to support sustainable supply chain practices.</t>
@@ -1798,7 +2224,11 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="P34" s="8" t="n"/>
+      <c r="P34" s="8" t="inlineStr">
+        <is>
+          <t>The study uses the term 'boundary-spanning' to describe net-zero capabilities, but it violates the individual-level analysis requirement. The survey items use a 'We' referent (e.g., 'We collect complete data on carbon emissions'), indicating that the respondents (managers) acted as macro-level key informants for firm-level supply chain practices rather than reporting their own individual interpersonal boundary spanning behavior [Code 3]. Additionally, the construct measures carbon emission tracking rather than interpersonal boundary spanning actions [Code 1].. Verbatim Evidence: "Net-zero capability can play a major role as a boundary-spanning function in accelerating green product innovation while balancing carbon emissions in the circular supply chain. ... The sample consisted of various managerial roles, including 29 General Managers of Technology (15.8%), 52 Operations/Supply Chain Managers (28.4%), 47 Design/Engineering Managers (25.7%), 35 Directors of Logistics and Distributions (19.1%), and 20 Managers of Production and Purchasing (11.0%). ... Appendix 1: Net-zero capability (NZC) Please indicate your level of agreement with the following statements (1 = Strongly disagree, 7 = Strongly agree). NZC 1 ‘We collect complete data on carbon emissions from our supply chain members (suppliers and customers)’. ... NZC 4 ‘We transparently monitor the carbon emissions of our supply chain members’."</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="18" customHeight="1" s="10">
       <c r="A35" t="inlineStr">
@@ -1811,6 +2241,16 @@
           <t>BSMA0032</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>The Management by Rites (MBR) perspective studies how management creates a universal corporate culture by uniformly defining performance expectations for human systems. The MBR Model designed for this study tested that perspective.</t>
@@ -1836,7 +2276,11 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="P35" s="8" t="n"/>
+      <c r="P35" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on 'Management by Rites' and corporate culture. While it conceptually references Adams' boundary spanning model to discuss 'bounded activity' and cultural boundaries, it does not quantitatively measure individual employee boundary spanning behavior. The quantitative survey measures dimensions of corporate culture (Bureaucratic, Innovative, Supportive, Particularistic, Universalistic) using an adaptation of Wallach's Organizational Culture Index. The only correlation matrix provided (Table 8) reports the intercorrelations among these five corporate culture dimensions. Thus, the study lacks an extractable effect size for the Boundary Spanning Behavior construct.. Verbatim Evidence: "A quantitative research survey method measured the boundary management network for management-defined human systems components in corporate culture. (Abstract) ... Outlined in Table 4 is the design referred to from hereon in as the index survey or the Corporate Culture Index. It was developed from the Organizational Culture Index used by Ellen J. Wallach... (p. 338) ... TABLE 8 PEARSON'S R CORRELATION MATRIX FOR THE CORPORATE CULTURE INDEX. [Variables:] BUREAU, INNOV, SUPP, PART [and] UNIV (p. 343)"</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="18" customHeight="1" s="10">
       <c r="A36" t="inlineStr">
@@ -1849,6 +2293,16 @@
           <t>BSMA0033</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Purpose – The purpose of this paper is to examine the types of justice that affect knowledge acquisition and opportunism in strategic alliances and how these justice mechanisms function. Design/methodology/approach – Data were collected from both top-level and operating-level boundary spanners in 295 strategic alliances in China (a total of 590 boundary spanners). A structural equation model (SEM) with bias-corrected bootstrap method was used to test the hypotheses.</t>
@@ -1874,7 +2328,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P36" s="8" t="n"/>
+      <c r="P36" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study utilizes strategic alliances as the unit of analysis (N=295 firms/alliances) and evaluates firm-level outcomes (interfirm knowledge acquisition, opportunism, and alliance performance) using key informants, violating the individual-level analysis requirement (Code 3). Additionally, the independent variables measured are Organizational Citizenship Behaviors (Employee Helping Behavior and Employee Voice Behavior) performed by boundary spanners, rather than the target construct of Boundary Spanning Behavior (BSB). Therefore, the study lacks an extractable effect size of interest for BSB (Code 1).. Verbatim Evidence: "Data were collected from both top-level and operating-level boundary spanners in 295 strategic alliances in China... the final sample consisted of 295 firms with two matched informants, a response rate of 59.0% (295/500). ... Employee Helping Behavior ... (1) Help alliance partners who have been absent ... Employee Voice Behavior ... (1) I seldom develop and make recommendations concerning issues that affect this strategic alliance ... Knowledge Acquisition ... (1) Our firm has learned to jointly execute marketing, R&amp;D or production operations with this alliance partner ... Opportunism ... (1) On occasion, we lie about certain things to protect our interests"</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="18" customHeight="1" s="10">
       <c r="A37" t="inlineStr">
@@ -1887,6 +2345,16 @@
           <t>BSMA0034</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Existing models of work group effectiveness have been tested in low-technology manufacturing settings, but not in a high-technology one. Typical features of high-technology environments – substantial automation, computerized scheduling systems, complex production processes, capital-intensive production, high-cost equipment, and high product value – render them significantly different from their low-technology counterparts. The increased use of work groups and teams among high-technology manufacturers raises the question of whether existing models can be generalized to these settings. In this paper, data from 89 groups in the semiconductor manufacturing industry are used to create predictive models of group productivity, job satisfaction, and perceived performance. External variables (such as conflict with supervisors and engineers) are found to be more predictive of productivity, while internal variables (such as conflict among group members) are more predictive of satisfaction. These results highlight the importance of fostering the work group's interaction with external technical support personnel when designing and managing successful work groups in high-technology workplaces.</t>
@@ -1912,7 +2380,11 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="P37" s="8" t="n"/>
+      <c r="P37" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the predictors of production work group performance. Although individual operators were surveyed, their responses were aggregated to the group level. The unit of analysis for the correlation matrix and regressions is the work group (N=89 teams). Therefore, the study lacks individual-level correlations and must be excluded.. Verbatim Evidence: "The level of analysis in this study is the work group. The sample is drawn from eight semiconductor fabrication facilities (fabs) representing seven major firms... employee surveys were distributed to two to four operators per work group at each fab. Multiple responses were averaged together to serve as the group response. Eighty-nine work groups (72%) submitted self-report questionnaire data in addition to their production and interview data."</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="18" customHeight="1" s="10">
       <c r="A38" t="inlineStr">
@@ -1925,6 +2397,16 @@
           <t>BSMA0035</t>
         </is>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>The revolutionary advancement of technology in the past decade brought the attention of academics and management practitioners to ways of improving innovative capabilities of organizations. Advice-seeking relationships have an essential role in the knowledge production of modern-day organizations as they enable actors to acquire information, professional support and knowledge elements that they can recombine to form new knowledge. This paper conceptualizes advice-seeking behaviour as part of an inherently complex social world that can best be captured by a multiplex approach to organizational network research. It investigates how different layers of interpersonal relationships in the workplace may contribute to the appearance of advice-seeking interactions. This study examines the cases of three knowledge-intensive organizations and applies binary logistic regression to shed light on the yet invisible relational foundations of workplace collaboration. Implications for Central European audience: Central European countries attempt to improve their economic competitiveness by attracting knowledge-intensive companies as well as incentivizing innovation and digital transformation. Knowledge-intensive firms, such as business service centres or information and communication technology companies, are significant contributors to the economic output of countries such as the Czech Republic, Hungary and Poland. Recommendations derived from the results of this paper provide insights into the leadership of knowledge-intensive companies regarding creation of organizational environments that foster knowledge sharing and innovation. Measures that promote interpersonal trust, visibility of expertise and boundary-spanning behaviour are recommended.</t>
@@ -1950,7 +2432,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P38" s="8" t="n"/>
+      <c r="P38" s="8" t="inlineStr">
+        <is>
+          <t>The study adopts the dyad as the unit of analysis, investigating directed ties between pairs of employees (N = dyads). It uses binary logistic regression to predict the presence of an advice-seeking tie based on other relational dimensions (e.g., trustworthiness, informal communication). Because the data is analyzed at the dyadic/relationship level where individuals are repeated across multiple observations, it violates statistical independence and lacks an extractable zero-order correlation matrix for individual-level boundary spanning behavior.. Verbatim Evidence: "For the purpose of this study, dyads were chosen as units of the analysis. All possible (n*(n-1)) directed dyads were investigated in thenine selected dimensions. In this approach, an observation is a directed dyad ij, and variables indicate whether the actor i chose the actor j in a specific relational layer (dimension)... Binary logistic regression was used to investigate the individual explanatory power of each relational dimension (i.e., layers measured by the independent variables) on the presence of advice-seeking behaviour in these relationships."</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="18" customHeight="1" s="10">
       <c r="A39" t="inlineStr">
@@ -1963,6 +2449,16 @@
           <t>BSMA0036</t>
         </is>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2 = Non-employee samples</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>Academy of management journal</t>
@@ -1988,7 +2484,11 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="P39" s="8" t="n"/>
+      <c r="P39" s="8" t="inlineStr">
+        <is>
+          <t>The sample consists of full-time residential M.B.A. students, which violates the inclusion criteria requiring organizational employee data.. Verbatim Evidence: "The sample consisted of 304 first-year M.B.A. students at a large midwestern university. All students were enrolled in the full-time residential M.B.A. program, which divided students into four cohorts, each further partitioned into teams consisting of three to five members."</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="18" customHeight="1" s="10">
       <c r="A40" t="inlineStr">
@@ -2001,6 +2501,16 @@
           <t>BSMA0037</t>
         </is>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>Designing a supply chain network provides the basic structure for supply chain operations, where the network is a major element in a ﬁrm’s competitiveness and a signiﬁcant area of capital investment. With the boundary-spanning scope encouraged by supply chain management, the question is whether existing analyses used for network design are adequate. The general answer is yes, because the number of echelons that the analysis must span is self-limiting to a relative few. However, there remain unresolved issues in network design analysis and in the models used to support the analysis that can enhance its accuracy, appropriateness, and acceptability to practitioners. Issues discussed relate to the development of better models, the treatment of the data needed by them, and the need for comparing the various models for network design.</t>
@@ -2026,7 +2536,11 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="P40" s="8" t="n"/>
+      <c r="P40" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 2 &amp; Code 4] This is a conceptual and methodological review paper focused on mathematical modeling and unresolved issues in supply chain network design and facility location. It does not report a primary empirical study (Code 4), does not use a sample of organizational employees (Code 2), and does not measure interpersonal boundary spanning behavior, therefore lacking any extractable quantitative effect sizes (Code 1).. Verbatim Evidence: "Abstract. Designing a supply chain network provides the basic structure for supply chain operations, where the network is a major element in a firm’s competitiveness and a significant area of capital investment. ... Issues discussed relate to the development of better models, the treatment of the data needed by them, and the need for comparing the various models for network design. ... 1. Introduction: Facility location, network configuration, supply chain design, and logistics system strategy are terms that have been used to describe what has been known to researchers as the warehouse location problem."</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="18" customHeight="1" s="10">
       <c r="A41" t="inlineStr">
@@ -2039,6 +2553,16 @@
           <t>BSMA0038</t>
         </is>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>Purpose – This study aims to explore the relationship between geographic search and business model innovation and proposed a contingent framework to focus on how governmental networking and environment turbulence are interdependent moderate the relationship between geographic search and business model innovation.</t>
@@ -2064,7 +2588,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P41" s="8" t="n"/>
+      <c r="P41" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the firm (N = 287 firms), and the respondents (CEOs or senior management) serve as key informants reporting on firm-level behaviors. The survey items use 'we' and 'our company' as referents rather than measuring individual-level employee boundary spanning behavior, violating the proxy guardrail and the firm-level ban.. Verbatim Evidence: "A large-scale questionnaire survey was carried out among the firms in three high-tech parks of the Pearl River Delta, with a total of 287 firms as empirical samples. [...] The researchers contacted the CEOs or senior management teams of all firms by phone or email to confirm their willingness to participate in the study and then conducted the questionnaire survey and collection personally. [...] Geographic search [...] We are knowledgeable about all-important opportunities in the geographic regions in which we operate; We are well informed about the price and quality aspects of products in neighboring geographic regions; We closely follow the activities of companies in our industrial sector but operating outside our geographic area. [...] Business model innovation generation [...] Our company has redesigned the company profit formula. [...] Governmental networking [...] During the past three years, top managers at our company have heavily used personal ties, networks and connections"</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="18" customHeight="1" s="10">
       <c r="A42" t="inlineStr">
@@ -2077,6 +2605,16 @@
           <t>BSMA0039</t>
         </is>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>The aim of this research is to analyse how design and use are mediated in Open Source Software (OSS) design. Focusing on the Python community, our study examines a ‘‘pushed-by-users’’ design proposal through the discussions occurring in two mailing-lists: one, useroriented and the other, developer-oriented. To characterize the links between users and developers, we investigate the activities and references (knowledge sharing) performed by the contributors to these two mailing-lists. We found that the participation of users remains local to their community. However, several key participants act as boundary spanners between the user and the developer communities. This emerging role is characterized by cross-participation in parallel same-topic discussions in both mailing-lists, cohesion between crossparticipants, the occupation of a central position in the social network linking users and developers, as well as active, distinctive and adapted contributions. The user championing the proposal acts as a key boundary spanner coordinating the process and using explicit linking strategies. We argue that OSS design may be considered as a form of ‘‘role emerging design’’, i.e. design organized and pushed through emerging roles and through a balance between these roles. The OSS communities seem to provide a suitable socio-technical environment to enable such role emergence.</t>
@@ -2102,7 +2640,11 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="P42" s="8" t="n"/>
+      <c r="P42" s="8" t="inlineStr">
+        <is>
+          <t>The study utilizes a qualitative and network analysis approach (analyzing quotation links in mailing lists and conducting interviews) to identify how certain members act as boundary spanners in an open-source software community. It reports Cramer's V for categorical associations (e.g., between participant status and quoting behavior) but does not provide a zero-order correlation matrix or extractable quantitative effect sizes (r) for individual-level boundary spanning behavior and substantive outcome or antecedent variables. Therefore, it lacks the necessary statistical data for the meta-analysis.. Verbatim Evidence: "The aim of this research is thus to understand the ways in which members of OSS communities, and especially users, participate in the design process and to identify whether or not some key participants may act as boundary spanners to link the user and the developer communities. [...] The first step of our study was to identify and select some successful 'pushed-by-users' design proposals using field interviews, and to collect traces of exchanges regarding one of these proposals, in python-dev and python-list. [...] The corpus obtained is segmented into units, corresponding to comments or sub-units of comments. [...] Each unit is categorized using the coding scheme composed of two types of categories: activities and references. [...] The attraction graph (Fig. 3) represents the interactions between participants, showing who tends to quote whom in the two mailing-lists. There is an intermediary relationship (V^2 Cramer = 0.07) between the status of the participant who is quoting and the status of the participant who is being quoted."</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="18" customHeight="1" s="10">
       <c r="A43" t="inlineStr">
@@ -2115,6 +2657,16 @@
           <t>BSMA0040</t>
         </is>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>Purpose – This paper aims to find out whether superior autonomy at boundary spanning levels in service organizations results in better market orientation and performance and whether autonomy and decentralization, though conceptually different, have similar practical implications. Researchers developed a theoretical model and tested it in the post-liberalized Indian retail banking context to address these concerns.</t>
@@ -2140,7 +2692,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P43" s="8" t="n"/>
+      <c r="P43" s="8" t="inlineStr">
+        <is>
+          <t>The study adopts the bank branch as its unit of analysis, surveying branch managers as key informants to measure branch-level market orientation, autonomy, and performance. A review of the survey items in the Appendix confirms the use of macro-level referents such as 'We' or 'Our branch' (e.g., 'In our branch, we discuss with customers...', 'We collect industry information...'), rather than capturing individual-level boundary spanning behavior ('I'). This violates the individual-level analysis requirement, warranting exclusion under Code 3.. Verbatim Evidence: "Bank branches constituted the unit of analysis. Further to getting initial insights on market orientation in retail banking through interviews researchers conducted a survey among branch managers. A total of 305 branch managers were contacted of which 122 cooperated. ... Appendix. Questionnaires ... Market orientation: (1) In our branch, we discuss with customers at least once a year to find out what products or services they will need in the future. (2) We collect customer expectations and give to product development department of our bank. ... (7) We collect industry information by informal means (e.g. lunch with industry friends, talks with trade partners). ... (22) Our branch gives feedback on product development efforts to ensure that they are in line with what customers want."</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="18" customHeight="1" s="10">
       <c r="A44" t="inlineStr">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -2709,6 +2709,14 @@
           <t>BSMA0041</t>
         </is>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>999</v>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>We examine the role of cultural and language skills as resources for individuals’ boundary spanning ability in multinational corporations. Our combined qualitative and quantitative analysis shows that cultural and language skills influence the extent to which individual boundary spanners perform four functions: exchanging, linking, facilitating, and intervening. Boundary spanners with both cultural and language skills perform more functions than those with only cultural skills, and language skills are critical for performing the most demanding functions. Key boundary spanners have properties that potentially make them not only valuable organizational human capital, but also rare and difficult to imitate. Theoretical and practical implications are discussed.</t>
@@ -2734,7 +2742,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P44" s="8" t="n"/>
+      <c r="P44" s="8" t="inlineStr">
+        <is>
+          <t>The study examines boundary spanning behavior across intra-organizational boundaries (between headquarters and subsidiaries in MNCs), fulfilling the Override Gate for Intra-Organizational BSB. The unit of analysis is the individual boundary spanner (N = 118). Although the study's primary data collection was qualitative (interviews), the authors quantified the data by counting the frequency of coded boundary spanning functions (exchanging, linking, facilitating, intervening) and reported a formal correlation matrix with extractable quantitative effect sizes (Spearman's rho) for these individuals in Table 6. The BSB measures represent purposive action rather than mere communication. Therefore, the study meets all inclusion criteria and provides the required statistical data.. Verbatim Evidence: "We examine the role of cultural and language skills as resources for the boundary spanning ability of individual employees in multinational corporations (MNCs)... Data were collected in the context of a research project focusing on inter-unit knowledge and competence transfer between the parent company and the Chinese/Russian subsidiaries of four Finland-based multinationals... This process yielded a database of 1222 observations pertaining to 118 boundary spanners... The total number of observations in each coding category for each boundary spanner was counted, and the counted score was used as a measure of the strength of the evidence for his/her linguistic and/or cultural skills, or boundary spanning activity, respectively... Hypotheses 1a-2b were tested by quantitative correlation analysis (n=118 boundary spanners). For this test we used Spearman's rank correlation coefficient (Spearman's ρ, two-tailed)... [Table 6 reports Bivariate Spearman rank correlations between resources and functions]"</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="18" customHeight="1" s="10">
       <c r="A45" t="inlineStr">
@@ -2747,6 +2759,16 @@
           <t>BSMA0042</t>
         </is>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>Book chapter</t>
@@ -2772,7 +2794,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P45" s="8" t="n"/>
+      <c r="P45" s="8" t="inlineStr">
+        <is>
+          <t>The document is an encyclopedia entry titled 'Global boundary spanners' (from the Encyclopedia of International Strategic Management). It is a conceptual review rather than a primary empirical study. It contains no sample, methodology, or extractable quantitative effect sizes.. Verbatim Evidence: "28. Global boundary spanners... Global boundary spanners can be defined as individuals who are recognized by members of both their own in-group and/or relevant out-groups for their long-term commitment to engage in and facilitate significant interactions between the groups... [The document is a 3-page conceptual overview with a references section and no empirical methods or results]"</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="10">
       <c r="A46" t="inlineStr">
@@ -2785,6 +2811,14 @@
           <t>BSMA0043</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>999</v>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>A plethora of research has investigated the impact of the frontline employee on the customer, with the consensus that employees can have a tremendous impact on the customer. What remains to be discovered is the extent to which this relationship exists in the reverse. Utilizing broaden-and-build and emotional contagion theories, this study suggests that employee perceptions of a specific customer emotion (delight) have an impact on the frontline employee. Specifically, results from a structural equations model reveal that employee perceptions of customer delight lead to employee positive affect, which in turn positively influences commitment and job satisfaction as well as creates stronger external representation behaviors, internal influence behaviors, and service delivery behaviors from the employee. These findings contribute new evidence to the debate of the viability of providing customer delight and extend our knowledge beyond emotional contagion in explaining how positive customer emotions manifest in employees.</t>
@@ -2810,7 +2844,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P46" s="8" t="n"/>
+      <c r="P46" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the impact of perceived customer delight on frontline service employees. It measures customer-oriented boundary-spanning behaviors (COBSBs), specifically external representation and internal influence behaviors, adapted from Bettencourt &amp; Brown (2003). The sample consists of 431 service employees. The study provides a correlation matrix (Table 2) with zero-order correlations between the boundary-spanning dimensions (ERB, IIB) and other variables (delight, job satisfaction, employee positive affect, affective commitment). The study is at the individual level of analysis and contains extractable effect sizes, thus meeting all inclusion criteria.. Verbatim Evidence: "The customer-oriented boundary-spanning behaviors were measured using three components previously employed in service research (Bettencourt &amp; Brown, 2003). External representation behaviors were measured using a three-item scale designed to capture the extent to which an employee is a vocal advocate to outsiders of the organization's image, goods, and services. Internal influence behaviors were measured with a three-item scale intended to measure the extent to which a person takes individual initiative in communicating to the firm and co-workers about ways to improve service delivery by the organization, co-workers, and oneself... The final sample size was 431... Table 2 Means, standard deviations (SD) and correlations."</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="18" customHeight="1" s="10">
       <c r="A47" t="inlineStr">
@@ -2823,6 +2861,14 @@
           <t>BSMA0044</t>
         </is>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>999</v>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>This study examines the antecedents cf job satisfaction, commitment, and turnover intentions for 229 information systems (IS) personnel employed within several industries. The antecedents studied include boundary spanning, role ambiguity, and rcle conflict. A model of these variables was built and tested using path analysis- Rcle ambiguity was found tc be the mcst dysfunctional variable for IS personnel, acccunting fcr 10.3%. 20.2% and 22.2% Of the variance in turnover intenticns. commitment, andjob satisfaction. This information is used tc make recommendaticns to IS management. Finally, recommendaticns and directions are suggested regarding future research.</t>
@@ -2848,7 +2894,11 @@
           <t>1985</t>
         </is>
       </c>
-      <c r="P47" s="8" t="n"/>
+      <c r="P47" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on information systems (IS) personnel (N=229) and examines their boundary spanning activities, satisfying the individual-level employee requirement. Boundary spanning is defined as crossing intradepartmental and interorganizational boundaries to gather information for systems analysis and design, which aligns with the valid intra-organizational and inter-organizational BSB constructs (Screening Rule 2). The construct is measured using an adapted version of the Miles and Perrault (1976) scale, which captures purposive boundary spanning actions. Furthermore, the paper provides extractable zero-order correlations between boundary spanning and outcomes such as role conflict, job satisfaction, and organizational commitment (reported as 'Original Correlation' in Table 6). It passes all inclusion criteria.. Verbatim Evidence: "The study participants included applications programmers, programmer/analysts, analysts, and project leaders in centralized IS groups. ... data collected from a total of 229 individuals. ... Boundary spanning refers to the individual's crossing of intradepartmental and interorganizational boundaries in order to perform his/her job [2, 42]. ... The gathering of information necessary for the analysis and design of computerized systems requires IS personnel to interact with individuals outside the IS department which necessitates the crossing of departmental boundaries. Systems which cut across many different organizational functions will require IS personnel to cross many boundaries. ... To gather boundary spanning data a measure developed by Miles and Perrault [25] was adapted and used. The Miles and Perrault scale measures the boundary spanning activities of laboratory research and development personnel. ... Table 6. Reconstructed Correlations [shows Original Correlation values, e.g., BS to RC = .275, BS to COMM = .164]."</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="18" customHeight="1" s="10">
       <c r="A48" t="inlineStr">
@@ -2861,6 +2911,16 @@
           <t>BSMA0045</t>
         </is>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>This article examines the evolving use of boundary objects in cross-cultural software teams. Our field study of a Jamaican-Indian team examines the use of software specifications and project management tools as boundary objects in facilitating sharing across knowledge boundaries.We examine how and why the role and use of boundary objects may facilitate collaboration across knowledge boundaries at one time and contribute to conflict at other times. We unpack the interacting elements that both facilitate and constrain knowledge sharing, and trigger conflicts at different stages of the software team development. Specifically, we found that the use of boundary objects at transitions involving definitional control and the subsequent redistribution of power/authority may inhibit knowledge sharing. The subsequent reifying of cultural boundaries along with negative stereotyping led to relational conflict, through a process we call culturizing, as cross-cultural differences emerged as problematic for team dynamics.</t>
@@ -2886,7 +2946,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P48" s="8" t="n"/>
+      <c r="P48" s="8" t="inlineStr">
+        <is>
+          <t>The study is a purely qualitative longitudinal case study examining the use of boundary objects in cross-cultural software development teams through 42 interviews and field observations. It does not provide any extractable quantitative survey data, statistical effect sizes (r), or a formal correlation matrix required for the meta-analysis.. Verbatim Evidence: "Case studies are the preferred research strategy for a process study when an in-depth understanding of phenomena is needed (Eisenhardt, 1989). We conducted a two-year longitudinal case study of cross-cultural software development for a general insurance system across three phases... In total, 42 interviews were conducted over three phases with a wide range of participants... Detailed notes were taken of interviews rather than recording owing to the cross-cultural sensitivity that persisted between Indians at the group's IT company, GROUPIT, and Jamaican staff over the duration of the study."</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="18" customHeight="1" s="10">
       <c r="A49" t="inlineStr">
@@ -2899,6 +2963,16 @@
           <t>BSMA0046</t>
         </is>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>This research investigated how experiences in a particular boundary-spanning context (community outreach) affected members' organizational identity and identification. Multimethod panel data from 219 participants showed that intergroup comparisons with clients (emphasizing differences) and intragroup comparisons with other organization members (emphasizing similarities) changed how members construed their organization's defining qualities. Intergroup comparisons also enhanced the esteem members derived from organizational membership, which, in turn, strengthened organizational identification. Supervisors reported higher interpersonal cooperation and work effort for members whose organizational identification became stronger. The results reveal potential outcomes of boundary-spanning work as well as how organizational identification processes operate in everyday work contexts.</t>
@@ -2924,7 +2998,11 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="P49" s="8" t="n"/>
+      <c r="P49" s="8" t="inlineStr">
+        <is>
+          <t>The study examines the psychological and behavioral effects of working in a boundary-spanning context (community outreach programs), but it does not measure Boundary Spanning Behavior (BSB) as an individual-level behavioral construct. The variables measured include social comparisons (favorable client comparison), collective self-esteem, organizational identification, and internal work behaviors (assistance/affiliation cooperation, work effort, advocacy participation). There is no measure of purposive boundary-spanning actions (e.g., external information scanning, representation, or cross-boundary coordination) with extractable effect sizes.. Verbatim Evidence: "The independent variables were the extent and direction of social comparisons: 'Participants indicated on a 5-point scale... the extent to which they compared themselves with (1) agency clients and (2) other Pillsbury members.' (p. 390). Work behaviors were measured for internal cooperation and effort: 'I used McAllister’s (1995) seven-item affiliation behavior scale and three-item assistance behavior scale to measure cooperation... Supervisors assessed work effort and advocacy participation with items developed by Van Dyne, Graham, and Dienesch (1994).' (p. 391). Table 4 lists 'Intercorrelations among Pre-program and Post-program Variables', which include 'Favorable client comparison', 'Collective self-esteem', 'Organizational identification', 'Assistance cooperation', 'Affiliation cooperation', 'Work effort', 'Advocacy participation', 'Organizational tenure', 'Community outreach experience', 'Task interdependence', and 'Unit standardization' (p. 401). None of these variables measure Boundary Spanning Behavior."</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1" s="10">
       <c r="A50" t="inlineStr">
@@ -2937,6 +3015,16 @@
           <t>BSMA0047</t>
         </is>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>No abstract</t>
@@ -2962,7 +3050,13 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P50" s="8" t="n"/>
+      <c r="P50" s="8" t="inlineStr">
+        <is>
+          <t>The document is a commentary and reply to another article discussing disciplinary boundaries in alcohol public health science. It is not an empirical study, contains no primary data, and does not provide any extractable quantitative effect sizes for boundary spanning behavior.. Verbatim Evidence: "COMMENTARY
+Different Disciplines Have Different Perspectives, So What Are the Implications for the Multidisciplinary Field of Alcohol Public Health Science? A Reply to “All Boundaries Have Two Sides” by Bray and Kenkel (2024)
+IN THEIR COMMENTARY in this issue of the Journal of Studies on Alcohol and Drugs, Bray and Kenkel (2024) write..."</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1" s="10">
       <c r="A51" t="inlineStr">
@@ -2975,6 +3069,16 @@
           <t>BSMA0048</t>
         </is>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>The literature suggests that the success of innovation clusters is based on personal networks that connect members of scientific, educational, and business organizations, stimulating more formalized cross-boundary collaborations between the three sectors. But it is still unclear if such organizational collaborations actually correspond with these personal ties and which aspects of personal communication are most strongly associated with organizational collaborations. To investigate these issues, the authors applied network analysis to study an innovation cluster in Algarve, Portugal. They found that cross-boundary organizational collaborations corresponded with personal ties. Moreover, they found that collaborations appeared to correlate most strongly with emotional attachments between individuals.</t>
@@ -3000,7 +3104,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P51" s="8" t="n"/>
+      <c r="P51" s="8" t="inlineStr">
+        <is>
+          <t>The study applies a network analysis approach to examine the relationship between personal communication ties and organizational collaborations within an innovation cluster. Although 128 individuals were surveyed, their responses were aggregated to the organizational level to create networks connecting 25 organizations. The quantitative results reported are QAP (Quadratic Assignment Procedure) correlations testing the codependency between organizational collaboration links and aggregated personal tie strengths at the dyadic/organizational level, rather than zero-order correlations between individual-level constructs. Furthermore, the personal tie variables measured are communication frequency, intellectual influence, and emotional attachment, which capture mere interaction frequency and affective states rather than purposive boundary-spanning actions. Therefore, the study is excluded due to both the non-individual level of analysis ([Code 3]) and the lack of a valid BSB construct with extractable effect sizes ([Code 1]).. Verbatim Evidence: "In total, 128 respondents took part in our study. Out of them, 61 were on university faculties, 47 came from research centers, and 20 came from companies. We aggregated the survey data by mapping each unique combination of an organizational entity and a contact's name as a separate node... Next, we produced three networks connecting the 25 organizations included in the analysis... To check for correlations between organizational and personal networks in the Algarve maritime cluster, we applied the QAP correlation... to the pairs of networks. QAP is designed to test for codependencies between different types of links connecting the same nodes... Our analysis of the correlations between organizational collaboration links and the three aspects of strong personal ties found a correlation rate of 28.57% for communication frequency (p &lt; .0001; M = 2.45%), 30.43% for intellectual influence (p &lt; .0001; M = 2.88%), and 40.00% for emotional attachment (p &lt; .0001; M = 3.40%)."</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1" s="10">
       <c r="A52" t="inlineStr">
@@ -3051,6 +3159,16 @@
           <t>BSMA0050</t>
         </is>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>Post financial crisis, audit committee (AC) reforms are proposed to improve the quality of financial reporting (EC 2011; Competition Commission 2013). This paper’s empirical contribution is to investigate the extent to which ACs and audit committee chairs (ACCs) engage with chief financial officers (CFOs) and audit partners (APs) across a range of 32 financial reporting issues. It is the first large-scale survey of interactions to move beyond the micro CFO / AP dyad and to distinguish the individual ACC from the AC group. While 37% of the 5,445 reported discussions involve all three key individuals together with the full AC, 35% involve neither the AC nor the ACC and the ACC acts without the full AC in a significant minority of cases. The parties reported to be involved are similar across the three respondent groups but vary with financial reporting issue, company size and audit firm size. The paper’s theoretical contribution is to interpret the evidence using the concepts of boundary spanning and gatekeeping roles. The research reveals incomplete levels of AC and ACC engagement with financial reporting issues. Findings have implications for policymakers regarding the role, influence and effectiveness of the AC in financial reporting matters. Directions for future research are identified.</t>
@@ -3076,7 +3194,14 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P53" s="8" t="n"/>
+      <c r="P53" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a questionnaire survey to investigate the interactions among CFOs, Audit Partners (APs), and Audit Committee Chairs (ACCs) regarding financial reporting issues. It relies on frequency counts, percentages, and mean comparisons (ANOVA, Chi-square tests) to describe the incidence of discussions and the combinations of parties involved. The paper does not provide a formal zero-order correlation matrix or any extractable quantitative effect sizes (r) involving boundary spanning behavior and other constructs. Therefore, it must be excluded for lacking the necessary effect size data.. Verbatim Evidence: "The present study utilises experiential questionnaires which ask expert respondents about specific events they have encountered (Gibbins and Qu 2005). Specifically it elicits the experiences and views of the three key participant groups in audit interactions: CFOs, ACCs and APs.
+For each of the 32 financial statement issues that had been 'the subject of discussion and/or negotiation in the most recent financial year for which your financial statements have been finalised but not necessarily published', respondents were asked: 'Which parties were involved in the discussion?', followed by four tick boxes – one each for the CFO, AP, ACC and AC.
+Across all potential discussion issues, the combined sample reported 5,445 discussions. The parties involved in these discussions are shown in Table 5, which reports frequencies for the 15 combinations.
+[Table 3: Summary statistics of awareness of issues by group... Table 4: Infrequency of awareness of discussion of issues... Table 5: Parties involved in discussions]"</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="18" customHeight="1" s="10">
       <c r="A54" t="inlineStr">
@@ -3089,6 +3214,16 @@
           <t>BSMA0051</t>
         </is>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>The proactiveness - business performance relationship was examined in this study by adopting a descriptive and crosssectional research design. Structural equation modeling was applied on a purposive sample of 457 North Indian firms to assess the impact of proactiveness on business performance. Moderating effect of environmental turbulence on proactiveness – business performance relationship was also assessed. The study found proactiveness as a significant predictor of business performance. The study revealed that firms operating in a dynamic environment were likely to be benefitted more from the pursuit of proactiveness. The findings provoke managers and entrepreneurs to adopt forwardlooking and opportunity-seeking perspectives to achieve robust business performance. Managers of Indian firms can draw insights from this study and can better decide the strategic posture of their firms.</t>
@@ -3114,7 +3249,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P54" s="8" t="n"/>
+      <c r="P54" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study lacks the target effect size of interest as it measures firm-level proactiveness (a dimension of entrepreneurial orientation) rather than individual-level interpersonal boundary spanning behavior. Furthermore, the unit of analysis is the organization (N = 457 firms), and the senior executive respondents are surveyed as key informants for their firms. The survey items explicitly use 'my firm' as the referent (e.g., 'My firm actively collects and evaluates information on consumer needs and preferences'), which violates the level-of-analysis and proxy guardrails.. Verbatim Evidence: "A purposive sample of 457 North Indian organizations was taken for conducting this study. The senior - level key executives, who had decision-making power in the organization, were considered as key informants. Data were collected through a personal survey in the year 2016... Appendix Table A1. Items Selected for Measuring Proactiveness... 1 In dealing with its competitors, my firm typically initiates actions which competitors respond to... 4 My firm actively collects and evaluates information on consumer needs and preferences... 5 In general, my firm actively collects and evaluates information on technological developments."</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="18" customHeight="1" s="10">
       <c r="A55" t="inlineStr">
@@ -3127,6 +3266,14 @@
           <t>BSMA0052</t>
         </is>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>999</v>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>This study examined how leaders’ internal and external activities mediate the relationship of functional heterogeneity and interteam goal interdependence to team effectiveness (in-role performance and innovation) in interdisciplinary teams. The results of the structural equation model from a sample of 92 interdisciplinary teams indicate that leaders’ internal activities fully mediate the relationship of team functional heterogeneity and interteam goal interdependence to team in-role performance. The leaders’ external activities were found to fully mediate the relationship of interteam goal interdependence to team innovation. We discuss the implications of these findings for both theory and practice.</t>
@@ -3152,7 +3299,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P55" s="8" t="n"/>
+      <c r="P55" s="8" t="inlineStr">
+        <is>
+          <t>The study measures the boundary spanning behavior of leaders (school principals) as rated by their subordinates (team members), which qualifies as Leader BSB. Although the data is aggregated at the team level (N=92), there is exactly one leader per team, invoking the N=Leaders=N=Teams exception under Screening Rule 1. Thus, the effective unit of analysis for the boundary spanning construct is the individual leader, preserving statistical independence and preventing exclusion under Code 3.. Verbatim Evidence: "Data were collected from 92 management teams from 92 public educational organizations in Israel. [...] School administrators, usually the principal, typically serve as the leaders of these teams. [...] To assess the leader boundary activities, team members answered the Team Leader Questionnaire adapted from Druskat and Wheeler (2003). [...] The EFA and CFA analyses provided evidence that the measures of the seven activities point toward a model of seven related but distinct factors representing each leadership activity: external relating (four items, for example, “How well does the leader understand school politics,” α = .83); external scouting (six items, for example, “How often does the leader seek information and advice from peers for the team’s benefit,” α = .89); external persuading (seven items, for example, “How often does the leader act as a representative of the team with parts of the school environment” [parents, educational ministry, district], α = .92). [...] Table 1. Descriptive Statistics and Intercorrelation Matrix for Study Variables, N = 92."</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="18" customHeight="1" s="10">
       <c r="A56" t="inlineStr">
@@ -3165,6 +3316,16 @@
           <t>BSMA0053</t>
         </is>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>Membership of boundary‐spanners is controversial, as employees operate largely at the borders of the organization in close relations with customers. Nevertheless, we know little about its influence on customer satisfaction. We investigate how and when identification with the branch influences customer satisfaction. The how question is answered by showing that degree of control of one's performance mediates the impact of branch manager identification on customer satisfaction. The when question is answered by proposing two moderating variables. Locus of control regulates the extent to which identification influences performance control. Dedicated meetings between branch managers and their colleagues regulate the degree to which performance control influences customer satisfaction. Hypotheses were tested in a longitudinal design on a sample of 1,461 managers from a firm specializing in banking and financial services in Europe. Results largely confirm our hypotheses, providing a novel look on determinants of customer satisfaction from the perspective of boundary‐spanning managers.</t>
@@ -3190,7 +3351,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P56" s="8" t="n"/>
+      <c r="P56" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates organizational identification ('identification with the branch') rather than actual boundary-spanning behavior (BSB). Although the bank branch is conceptualized as a boundary-spanning unit within the organization, the variables measured (branch identification, locus of control, perceived performance control, and frequency of CS-related meetings within the branch) do not capture interpersonal boundary-spanning actions. As the study lacks a measure of boundary-spanning behavior, it provides no effect sizes of interest.. Verbatim Evidence: "We extend the effects of organization identification to the subgroup in the organization under study to include the local branch division of the bank where organization members and customers interact regularly. [...] Branch manager identification (t1). Two items were used to measure identification with the branch (Bergami and Bagozzi, 2000). The first one consisted of an eight-point visual and verbal representation of the perceived overlap between the individual’s self-identity and the identity of the branch, while the second item instructed participants to ‘indicate the degree to which your self-image overlaps with the identity of the branch as you perceive it’"</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="18" customHeight="1" s="10">
       <c r="A57" t="inlineStr">
@@ -3203,6 +3368,14 @@
           <t>BSMA0054</t>
         </is>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>999</v>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>The authors investigate three types of customer-oriented boundary-spanning behaviors (COBSBs)a frontline service employee may perform that are associated with linking a service organization to its potential or actual customers: external representation, internal influence, and service delivery. The authors propose and test a withdrawal model to explain the negative effects of role conflict and role ambiguity on COBSBs across a sample of 220 lower-level, nonprofessional service providers of a major retail bank and a sample of 90 higher-level, professional service providers from the business credit division of an international financial services corporation. The results demonstrate that (1)indirect paths through job satisfaction and organizational commitment entirely account for the negative effects of the role stressors on COBSBs, (2) the indirect negative effects of the role stressors are stronger on external representation and internal influence behaviors, and (3)role conflict also has a significant positive direct relationship with internal influence behaviors.</t>
@@ -3228,7 +3401,11 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="P57" s="8" t="n"/>
+      <c r="P57" s="8" t="inlineStr">
+        <is>
+          <t>The study examines Customer-Oriented Boundary-Spanning Behaviors (COBSBs), including external representation and internal influence, among frontline service employees. It provides a latent construct correlation matrix for two distinct individual-level employee samples (N=220 retail banking employees; N=90 business credit employees). The behaviors measured represent purposive boundary-spanning actions linking the organization to its environment, and the data is provided at the individual level, satisfying all inclusion criteria.. Verbatim Evidence: "Our first sample consisted of boundary-spanning service employees of a major, multistate retail bank. We restricted our sample to two nonmanagement service positions that primarily consisted of full-time, salaried employees. It was possible to match 220 completed employee surveys with a manager rating of COBSBs. Our second sample consisted of professional boundary-spanning service providers of the business credit division of an international financial services corporation. It was possible to match 90 employee surveys with a manager rating of COBSBs. Drawing from these literatures, we investigate three types of boundary-spanning behaviors the FSE may perform that are associated with linking the organization to its potential or actual customers (cf. Brief and Motowidlo 1986): (1) external representation, being vocal advocates to outsiders of the organization's image, products, and services (cf. Booms and Bitner 1981; Bowen and Schneider 1985); (2) internal influence, taking individual initiative in communications to the firm and coworkers to improve service delivery by the organization, coworkers, and oneself (cf. Schneider and Bowen 1984; Zeithaml et al. 1988); and (3) service delivery, serving customers in a conscientious, responsive, attentive, and courteous manner (cf. Parasuraman et al. 1988). Table 2 Latent Construct Intercorrelations and Reliability Estimates provides the correlation matrices for both samples."</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="18" customHeight="1" s="10">
       <c r="A58" t="inlineStr">
@@ -3241,6 +3418,14 @@
           <t>BSMA0055</t>
         </is>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>999</v>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>Using a sample of 281 frontline service employees of a national retail bank, we test a social exchange model of antecedents of three dimensions of customer-oriented boundary-spanning behaviors suggested by prior boundary-spanning and services marketing/management literatures: external representation, internal inﬂuence, and service delivery. In support of our hypotheses, we identify fully mediated relationships from procedural, interactional, and distributive justice to external representation and internal inﬂuence via job satisfaction and organizational commitment. Our results generally support our expectation that the indirect effects of procedural justice on external representation and internal inﬂuence are stronger than the indirect effects of distributive or interactional justice on these behaviors. Also, our results reveal no signiﬁcant indirect effects of procedural and distributive justice on service delivery behaviors. However, we ﬁnd an unexpected direct positive path from interactional justice to service delivery behaviors. We interpret this latter ﬁnding in light of the normative value of interactional justice as a source of role modeling or managerial legitimacy.</t>
@@ -3266,7 +3451,11 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="P58" s="8" t="n"/>
+      <c r="P58" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates customer-oriented boundary-spanning behaviors (COBSBs, specifically external representation and internal influence) among individual frontline service employees (N=281). The study measures interpersonal, purposive boundary-spanning actions at the individual unit of analysis, avoiding macro-level proxies or group-level aggregations. Furthermore, the paper provides a complete correlation matrix of latent constructs in Table 2, supplying extractable effect sizes. Thus, it meets all inclusion criteria for the meta-analysis.. Verbatim Evidence: ""Using a sample of 281 frontline service employees of a national retail bank, we test a social exchange model of antecedents of three dimensions of customer-oriented boundary-spanning behaviors suggested by prior boundary-spanning and services marketing/management literatures: external representation, internal influence, and service delivery." | "External representation was measured using a four-item scale designed to tap the extent to which an employee is a vocal advocate to outsiders of the organization's image, goods, and services. Internal influence was measured with a four-item scale intended to capture the extent to which a person takes individual initiative in communicating to the firm and co-workers about ways to improve service delivery by the organization, co-workers, and oneself." | "Table 2: Latent construct intercorrelations and reliability estimates... Subdiagonal entries are the latent construct intercorrelations not corrected for common method variance.""</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="18" customHeight="1" s="10">
       <c r="A59" t="inlineStr">
@@ -3279,6 +3468,16 @@
           <t>BSMA0056</t>
         </is>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>Abstract                            Business Process Management is a boundary-spanning discipline that aligns operational capabilities and technology to design and manage business processes. The               Digital Transformation               has enabled human actors, information systems, and smart products to interact with each other via multiple digital channels. The emergence of this hyper-connected world greatly leverages the prospects of business processes – but also boosts their complexity to a new level. We need to discuss how the BPM discipline can find new ways for identifying, analyzing, designing, implementing, executing, and monitoring business processes. In this research note, selected transformative trends are explored and their impact on current theories and IT artifacts in the BPM discipline is discussed to stimulate transformative thinking and prospective research in this field.</t>
@@ -3304,7 +3503,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P59" s="8" t="n"/>
+      <c r="P59" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1, Code 2, Code 4] The paper is a conceptual research note discussing the impact of technological trends on Business Process Management. It does not present a primary empirical study, lacks an individual employee sample, and contains no quantitative data or extractable effect sizes of interest.. Verbatim Evidence: "In this research note, selected transformative trends are explored and their impact on current theories and IT artifacts in the BPM discipline is discussed to stimulate transformative thinking and prospective research in this field. [...] In this research note, we focus on four technological enablers for the fact that we consider their interaction with BPM as least understood: Social Computing as a paradigm for connecting individuals digitally, Smart Devices as digitized physical resources that join processes as artificial actors in their own right [...], Big Data Analytics as a tool to automatically analyze extensive data volumes from business processes and their environments, and Real-Time Computing that enables organizations to analyze data in (near) real-time to adapt their business processes on-the-fly. [...] Given the four enablers presented in the previous section, and considering four typical phases of BPM (cf. Fig. 1), the authors conducted a workshop session, supplemented by follow-up discussions."</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="18" customHeight="1" s="10">
       <c r="A60" t="inlineStr">
@@ -3317,6 +3520,16 @@
           <t>BSMA0057</t>
         </is>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>When the ordering function is governed by administrative arrangements and sales are regulated by long-term contracts, managers may question the necessity and the tasks of the sales function within established customer relationships. The authors examine three issues related to the role of the salesperson in established industrial buyer-seller relationships: (1) appropriate measures of salesperson performance within a relationship, (2) behaviors and skills affecting salesperson performance, and (3) the effect of salesperson performance on the relationship. The results from a survey of industrial buyers suggest that the salesperson has a significant and substantial effect on relationship continuity. They also show that the salesperson contributes to perceptions of the supplier's reliability and supplier services. The key attributes of an effective salesperson are ability to resolve conflicts, ability to develop a personal relationship with customers, and ability to facilitate exchange of information between the supplier and buyer firms.</t>
@@ -3342,7 +3555,11 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="P60" s="8" t="n"/>
+      <c r="P60" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the buyer-seller relationship level rather than the independent individual level. Specifically, the data was collected from 126 purchasing managers, who each evaluated multiple supplier relationships (an average of about two per informant), resulting in a total sample of 279 relationships. Since the correlation matrix and analyses are based on these 279 relationship observations, the study includes repeated measures from the same individuals, which violates the assumption of statistical independence. Therefore, it is excluded under Code 3.. Verbatim Evidence: "The informant was the person responsible for purchases of the product category in question. In order to generalize from the data, our main premise was that relational selling behavior should apply to various categories of purchased goods. Thus, the informant was asked to identify a supplier of packaging, a supplier of component parts, and a supplier of accessories. For each of the three chosen suppliers, informants were asked to evaluate the supplier's salesperson on several behaviors in addition to characteristics of the buyer-supplier relationship. If suppliers for only one or two of the product categories could be identified, the informant was asked to evaluate those suppliers. ... This procedure produced completed questionnaires from 126 companies (a response rate of 22%). ... A total sample of 279 relationships was collected. Thus, on average each informant evaluated about two relationships. ... Given the large sample size (279 observations) and the large number of variables (30), chi-square statistics of such magnitude can be expected even if the data fit the underlying model very well."</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="18" customHeight="1" s="10">
       <c r="A61" t="inlineStr">
@@ -3353,6 +3570,16 @@
       <c r="B61" t="inlineStr">
         <is>
           <t>BSMA0058</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3385,7 +3612,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P61" s="8" t="n"/>
+      <c r="P61" s="8" t="inlineStr">
+        <is>
+          <t>The study examines how a key contact employee's human capital and social capital, along with the firm's structural capital, affect a client's likelihood of following the employee to a new firm. It does not measure boundary spanning behavior (BSB) as a construct. The variables assessed are professional skills (human capital) and relationship closeness/embeddedness (social capital), which do not capture the purposive actions (e.g., information scanning, representation, coordination) required for BSB.. Verbatim Evidence: "Human capital: 'Our contact employee in agency XYZ has a background that is highly appropriate for working with advertising.' Social capital: 'Our contact employee in agency XYZ and I have developed a close social relationship.', 'Our contact employee in agency XYZ and I are close business friends.', 'The relationship between me and our contact employee in agency XYZ gives me access to valuable information.'"</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="18" customHeight="1" s="10">
       <c r="A62" t="inlineStr">
@@ -3398,6 +3629,16 @@
           <t>BSMA0059</t>
         </is>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>B ishop P. and G ripaios P. Spatial externalities, relatedness and sector employment growth in Great Britain, Regional Studies. This paper examines the impact of externalities on employment growth in sub-regions of Great Britain by estimating ordinary least-squares (OLS) and maximum likelihood spatial models at the two-digit level for 23 sectors. Issues arising from relatedness, sector differences, competition, cross-boundary spillovers, and spatial autocorrelation are explicitly addressed. Results indicate that specialization has a generally negative impact on growth, whilst the impact of diversity is heterogeneous across sectors and strong local competition has a typically positive impact. The results question the merits of policies primarily aimed at promoting regional specialization and suggest that diversity, local competition, and sector heterogeneity are important policy issues.</t>
@@ -3423,7 +3664,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P62" s="8" t="n"/>
+      <c r="P62" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes macroeconomic employment data across 203 sub-regions in Great Britain to assess the impact of spatial externalities on sector employment growth. It lacks a primary sample of individual organizational employees and does not measure individual-level boundary spanning behavior. Instead, it relies on aggregate regional data, thus violating multiple inclusion criteria [Code 2 &amp; Code 3].. Verbatim Evidence: "Employment data for sub-regions of Great Britain at the two-digit industry level were obtained from the UK’s National On-line Manpower Information System (NOMIS) utilizing the 1992 Standard Industrial Classification (SIC) classification scheme and covering the period 1995–2002. [...] Data were collected for 203 areas at the local authority, county, and unitary authority levels. [...] The dependent variable, employment growth, is defined as the change in the log of employment in a sector in a particular area over the period 1995–2002."</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="18" customHeight="1" s="10">
       <c r="A63" t="inlineStr">
@@ -3436,6 +3681,16 @@
           <t>BSMA0060</t>
         </is>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>The temporal imagination is the understanding of the intersection of one entity’s timescape with the larger timescapes of which that entity is a part. We examine in detail what the temporal imagination is, complemented with a discussion of the related timescape idea, and why the temporal imagination is necessary to function in any timescape. We also discuss group attributes that will likely affect the development of the temporal imagination and its use and how its use in group boundary spanning efforts affect both the groups and the larger organization.</t>
@@ -3461,7 +3716,11 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="P63" s="8" t="n"/>
+      <c r="P63" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a theoretical book chapter that proposes the conceptual framework of 'temporal imagination' and its application to boundary-spanning groups. It does not conduct primary empirical research and lacks quantitative data, correlation matrices, or any extractable effect sizes.. Verbatim Evidence: "The temporal imagination is the understanding of the intersection of one entity's timescape with the larger timescapes of which that entity is a part. We examine in detail what the temporal imagination is, complemented with a discussion of the related timescape idea, and why the temporal imagination is necessary to function in any timescape. We also discuss group attributes that will likely affect the development of the temporal imagination and its use and how its use in group boundary spanning efforts affect both the groups and the larger organization. [...] In this chapter, we have proposed the concept of the temporal imagination, not as a precisely defined theoretical construct that can be instantly operationalized to begin a program of empirical research, but like its sociological progenitor, as a sensitizing concept (Blumer, 1954)."</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="18" customHeight="1" s="10">
       <c r="A64" t="inlineStr">
@@ -3474,6 +3733,16 @@
           <t>BSMA0061</t>
         </is>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>Research Summary: This Special Section of the Strategic Entrepreneurship Journal explores how business model innovation (BMI) can address grand challenges (GCs), including artificial intelligence (AI), business and global unrest, and climate change through a proposed “ABC” classification and “BMI-GC” concept. Highlighting BMI's role as a boundary-spanning, collaborative approach to innovation, we demonstrate its potential to drive sustainable solutions by rethinking value creation, delivery, and capture mechanisms. We examine how BMI may foster resilience and help firms and organizations adapt to global volatility, integrate ethical AI, and advance sustainability in business ecosystems. We offer a roadmap for future inquiry into BMI-GC, including measurement and assessment, digital transformation, and collaborative ecosystems. By embracing these research pathways, scholars can contribute to a deeper theoretical and practical understanding of BMI to address grand challenges.</t>
@@ -3499,7 +3768,14 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="P64" s="8" t="n"/>
+      <c r="P64" s="8" t="inlineStr">
+        <is>
+          <t>This paper is an editorial and literature review introducing a special section of the Strategic Entrepreneurship Journal. It presents a conceptual framework and summarizes other articles but does not contain primary empirical data or quantitative effect sizes for individual-level boundary spanning behavior.. Verbatim Evidence: "EDITORIAL
+Innovating for impact: Harnessing business model innovation to tackle grand challenges
+...
+Research Summary: This Special Section of the Strategic Entrepreneurship Journal explores how business model innovation (BMI) can address grand challenges (GCs), including artificial intelligence (AI), business and global unrest, and climate change through a proposed “ABC” classification and “BMI-GC” concept. ... In the following section, we summarize the articles in the Special Section, drawing selectively on them and from some of the articles identified in our literature review on the links between BMI and grand challenges to offer a framework for future research."</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="18" customHeight="1" s="10">
       <c r="A65" t="inlineStr">
@@ -3512,6 +3788,16 @@
           <t>BSMA0062</t>
         </is>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>Purpose – This study adopts a person-centered perspective to explore how entrepreneurs combine multiple proactive behavioral strategies across the business, personal and business-environment domains. We research whether certain combinations of proactive behavioral strategies (i.e. seeking resources, optimizing demands, seeking challenges, idea generation, environmental exploration, network crafting, self-insight and boundary management) relate to well-being and business performance. Moreover, we investigate whether entrepreneurs’ daily use of these strategies aligns with their general profiles.</t>
@@ -3537,7 +3823,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="P65" s="8" t="n"/>
+      <c r="P65" s="8" t="inlineStr">
+        <is>
+          <t>The study's sample consists of independent entrepreneurs rather than organizational employees, which violates the population boundary rule [Code 2]. Furthermore, the study measures 'boundary management' in terms of demarcating boundaries between work and personal/family life, which is a work-family boundary management construct lacking the target effect size for interpersonal boundary spanning behavior [Code 1].. Verbatim Evidence: "Data were collected among Dutch entrepreneurs owning private companies with fewer than 250 employees... Boundary management was measured with four items (Kossek et al., 2012), e.g. 'I determined whether I mixed up my work and personal activities throughout the day'."</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="18" customHeight="1" s="10">
       <c r="A66" t="inlineStr">
@@ -3550,6 +3840,16 @@
           <t>BSMA0063</t>
         </is>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>Recently, work-family scholars have empirically demonstrated the importance of congruence between employees' boundary management preferences and boundary management supplies provided by the work environment in relation to employee attitudes and behavior. However, a theoretically grounded construct that captures this congruence is lacking. The present study addresses this gap by developing the construct and measure of work-nonwork boundary management fit, based on the needs-supplies fit framework. We cross-validate the scale in three independent samples (n = 188, diverse group of employees, n = 75, employees from one hospital, and n = 81, employees from one car company) and in a fourth sample (n = 458, working parents), we demonstrated the importance of work-nonwork boundary management fit for employee well-being (i.e., stress and work-life conflict). In particular, we confirmed its unique role in predicting employee well-being, above and beyond workload and work interrupting nonwork behaviors. Hence, we argue for considering work-nonwork boundary management fit when studying how work-family policies and organizational culture affect employees in the workplace.</t>
@@ -3575,7 +3875,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P66" s="8" t="n"/>
+      <c r="P66" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on the work-nonwork interface and develops a measure for work-nonwork boundary management fit. This construct is based on how employees manage the boundaries between their work and personal/family life domains (segmentation vs. integration), which falls under Work-Family boundary management rather than inter- or intra-organizational boundary spanning.. Verbatim Evidence: "The desired amount of segmentation or integration between work and nonwork roles represents such a personal need on which fit perceptions can apply. Therefore, fulfilling one’s boundary management need by providing a “fitting” work environment (e.g., work-family policies and culture) can thus contribute to achieving a more harmonious work-nonwork interface. ... The final measure thus exists of four items including: “My need for combining work and private life is met by the opportunities offered by my organization,” “In terms of the way I want to combine work and private life, this organization fits me well,” “In terms of the way I want to separate work and private life, this job fits me well,” and “My need for separating work and private life is met by the culture and habits in my organization.”"</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="18" customHeight="1" s="10">
       <c r="A67" t="inlineStr">
@@ -3588,6 +3892,16 @@
           <t>BSMA0064</t>
         </is>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>Context is an important but largely ignored dimension of quality service encounters. This paper contributes to the hospitality service industries literature by examining how the front-of-house and backof-house boundary work (Nippert-Eng 1996, 2003) engaged by Room Attendants working within the hotel guest room space impact on the hospitality impression management performed. Qualitative data from fieldwork engaging with hotel employees located within the tourist resort of Queenstown New Zealand are used to explore the multiple fronts on which the front-of-house and back-of-house boundaries are simultaneously negotiated. The results suggest that Room Attendants negotiate the front-ofhouse and back-of-house boundary through objects – such as the guest room and articles belonging to the guest – and aspects of self – such as impression management, safety, socialising and self-responsibility for room checking. The results support the importance of considering context when seeking to understand the complexities associated with the (re)production of a reliably positive service encounter.</t>
@@ -3613,7 +3927,11 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="P67" s="8" t="n"/>
+      <c r="P67" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative investigation based on semi-structured interviews with housekeeping staff members and hotel managers in New Zealand. It does not provide any quantitative survey data, correlation matrices, or extractable effect sizes (r) required for the meta-analysis.. Verbatim Evidence: ""Qualitative data from fieldwork engaging with hotel employees located within the tourist resort of Queenstown New Zealand are used to explore the multiple fronts on which the front-of-house and back-of-house boundaries are simultaneously negotiated." "Given the exploratory nature of the research agenda, the semi-structured interview was selected as the most appropriate method for collecting data." "The 67 transcribed interviews were read initially to select out those who worked within the Housekeeping Department. Of the 67 hotel employees I interviewed, 10 were involved in housekeeping.""</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="18" customHeight="1" s="10">
       <c r="A68" t="inlineStr">
@@ -3626,6 +3944,16 @@
           <t>BSMA0065</t>
         </is>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>This research examined the relationships between structural positions and influence at the individual level of analysis. The structure of the organization was conceptualized from a social network perspective. Measures of the relative positions of employees within workflow, communication, and friendship networks were strongly related to perceptions of influence by both supervisors and non-supervisors and to promotions to the supervisory level. Measures included criticality, transaction alternatives, and centrality (access and control) in the networks and in such reference groups as the dominant coalition. A comparison of boundary-spanning and technical-core personnel indicated that contacts beyond the normal work requirements are particularly important for technical core personnel to acquire influence. Overall, the results provide support for a structural perspective on intraorganizational influence.</t>
@@ -3651,7 +3979,12 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="P68" s="8" t="n"/>
+      <c r="P68" s="8" t="inlineStr">
+        <is>
+          <t>The study examines structural influence by measuring employee positions within workflow, communication, and friendship networks. The network generator for communication asked employees to list individuals 'with whom they talked frequently about work-related topics', and 'whom they considered close friends' for friendship. The focal variables such as 'Contacts beyond the workflow' count the number of direct relationships based on these general communication and friendship ties across unit boundaries. According to the screening rules, network measures based merely on general communication frequency or talking without specifying a purposive boundary-spanning action (e.g., actively seeking knowledge, scouting information, or representing the unit) are invalid. Because the study measures structural centrality and general communication rather than purposive Boundary Spanning Behavior, it lacks an extractable effect size of interest.. Verbatim Evidence: "Networks. On the nonsupervisory questionnaire, respondents were asked to list the names of persons (1a) who provided them with inputs to their jobs and (1b) to whom they distributed the outputs from their work; (2) with whom they talked frequently about work-related topics; and (3) whom they considered close friends. These listings provided the primary basis for the three networks: (1) workflow network, (2) communication network, and (3) friendship network.
+Contacts beyond the workflow. Separate measures of contacts with others were calculated for the communication network and friendship network. This was done by counting the number of direct relationships between a focal person and persons who were not members of the focal person's immediate workgroup nor persons with whom the focal person was required to interact in performing normal work functions. This measure reflects the extent to which an employee develops relationships with persons whom that employee would not normally come into contact with during the required performance of the job."</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="18" customHeight="1" s="10">
       <c r="A69" t="inlineStr">
@@ -3664,6 +3997,14 @@
           <t>BSMA0066</t>
         </is>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>999</v>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>Research has shown that NPD project leaders should engage in boundary-spanning activities. The present study tested the impact of four boundary-spanning activities on NPD project performance and analyzed the antecedents of these activities. We hypothesized that NPD project leaders' abilities to perform these activities depend on the characteristics of their personal networks — structural holes, strength of ties, vertical and horizontal bridging ties. A Partial Least Squares test on 73 NPD projects showed that (a) “obtaining political support” and “scanning for ideas” are the boundary activities with the greatest impact on performance, (b) project leaders with strong ties in their network are more effective at these activities, (c) project leaders with structural holes in their networks are more effective in another boundary activity, “protecting the team”, although this activity does not affect NPD outcomes. These results represent an important contribution to understanding how team leaders contribute to project performance.</t>
@@ -3689,7 +4030,11 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="P69" s="8" t="n"/>
+      <c r="P69" s="8" t="inlineStr">
+        <is>
+          <t>The study examines the boundary-spanning activities of project leaders in new product development teams. The unit of analysis is the individual project leader (N=73), and the survey items explicitly use the individual referent ('During the project, to what extent did you manage to…') to assess purposive actions such as coordinating with external actors, scanning for information, and obtaining political support. This aligns perfectly with the definition of individual-level boundary spanning behavior (including Leader BSB). The paper also provides a complete zero-order correlation matrix (Appendix 3) containing the necessary effect sizes.. Verbatim Evidence: "The study was conducted on a sample of 73 project leaders in manufacturing firms (Section 3.1) and assessed the variables of NPD outcomes, boundary-spanning activities, network characteristics, and controls (Section 3.2). ... Project leaders were required to complete the questionnaire with reference to a completed NPD project. ... Boundary-spanning activities / During the project, to what extent did you manage to… / Coordinating with external actors ... Integrate stakeholders' contributions ... Scanning for information ... Scan the environment to get information on market trends ... Appendix 3. Means, standard deviations, correlations and AVE"</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1" s="10">
       <c r="A70" t="inlineStr">
@@ -3702,6 +4047,16 @@
           <t>BSMA0067</t>
         </is>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>Objective To evaluate feasibility and acceptability of a health professional resilience skills training program with neurology residents. Methods The curriculum consists of ﬁve 1-hour-long modules that included the following skills: reﬂective narrative practices, emotion regulation, communication with highly distressed individuals, boundary management, and the identiﬁcation of depression and trauma. Using a web-based survey tool, we administered the Brief Resilience Scale (BRS) and Abbreviated Maslach Burnout Inventory (aMBI) at baseline, in addition to a pre- and post-survey assessing change in beliefs and self-eﬃcacy, as well as satisfaction with the intervention. Means were compared using the Wilcoxon rank-sum and signed rank tests. Results Twenty-two residents representing each year of training completed the pre-survey; 41% were women. Subscale scores on the aMBI revealed that 50% had moderate or high emotional exhaustion, 41% had moderate depersonalization, and 37% had moderate or low personal accomplishment, though 77.3% reported high career satisfaction. Female residents had lower scores on the BRS (mean 3.26 vs 3.88, p &lt; 0.05), though scores on aMBI subscales did not diﬀer by sex. Scores did not diﬀer by year of training. Sixteen residents completed both the pre- and post-survey. Signiﬁcant increases were detected in 4 of 9 self-eﬃcacy statements. Seventy-one percent of residents were satisﬁed or extremely satisﬁed with the training. Conclusions Residents were satisﬁed with the curriculum and reported improved ability to identify and cope with work-related stress. Further study is needed to evaluate the inﬂuence of skills adoption and practice on resilience and burnout.</t>
@@ -3727,7 +4082,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P70" s="8" t="n"/>
+      <c r="P70" s="8" t="inlineStr">
+        <is>
+          <t>The study evaluates a resilience skills training program for neurology residents and measures pre-to-post changes in knowledge regarding 'boundary management' (managing professional boundaries with patients requesting nonstandard care). It does not measure structural inter-organizational or intra-organizational Boundary Spanning Behavior. Furthermore, the study only reports pre- and post-test means analyzed via Wilcoxon tests and does not provide an extractable zero-order correlation matrix or any effect sizes (r).. Verbatim Evidence: "The curriculum consists of five 1-hour-long modules that included the following skills: reflective narrative practices, emotion regulation, communication with highly distressed individuals, boundary management, and the identification of depression and trauma. [...] Boundary management: This module provided a review of why boundary management is important, encouraged residents to discuss their related skills and challenges, and instructed residents on effective techniques, including management of patients who request nonstandard care. Residents practiced these skills. [...] Statistical tests appropriate for small sample sizes were used. Wilcoxon 2-sample tests were conducted to identify sex or year of training differences in burnout and resilience at baseline. Wilcoxon signed rank tests were used to evaluate changes in level of agreement from pre to post intervention on items assessing beliefs, knowledge, and self-efficacy."</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="18" customHeight="1" s="10">
       <c r="A71" t="inlineStr">
@@ -3738,6 +4097,16 @@
       <c r="B71" t="inlineStr">
         <is>
           <t>BSMA0068</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -3798,7 +4167,11 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="P71" s="8" t="n"/>
+      <c r="P71" s="8" t="inlineStr">
+        <is>
+          <t>The study uses Q-methodology to explore perceptions of effective organizational leadership among fire officers. It does not measure boundary spanning behavior as a quantitative construct and does not provide an extractable zero-order correlation matrix or effect sizes (r) between substantive variables. The correlation matrices provided are between participants' Q-sorts (perspectives) rather than between measured constructs, meaning no effect sizes can be extracted for meta-analysis.. Verbatim Evidence: "This study explored the perceptions of fire officers on effective organizational leadership in the American fire service to discover what is shared among varied perspectives and what is distinct, and to analyze how the perspectives align with existing leadership theories and models. It employed Q methodology, which includes both qualitative and quantitative data-collection and analysis. Ten distinct perspectives emerged from the data that have varying degrees of fit with existing theories... Q methodology provides a means to access and rigorously analyze multiple, subjective viewpoints. ... It is these arrangements that are analyzed with factor analysis to compare and contrast the different, subjective interpretations of the subject matter to discover the distinct or shared viewpoints that can then be further interpreted."</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="18" customHeight="1" s="10">
       <c r="A72" t="inlineStr">
@@ -3811,6 +4184,16 @@
           <t>BSMA0069</t>
         </is>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>As Thomas Friedman so persuasively argued in his book The World is Flat, 1 a significant effect of globalization is a leveling of the playing field for many of the competitors in today’s worldwide markets. Technological innovations have revolutionized the workplace, bringing the competitive power of emerging economies’ fast-growth organizations into closer alignment with their developed-world counterparts. Paradoxically, at the same time that these developments have made doing business across borders easier, relational barriers—obstacles to productive human interactions—not only remain largely unchanged but in some cases have deepened.
@@ -3837,7 +4220,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P72" s="8" t="n"/>
+      <c r="P72" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a practitioner-oriented article published in MIT Sloan Management Review that introduces a conceptual framework for boundary-spanning leadership based on interview and survey data. It primarily reports descriptive statistics (percentages) and qualitative case examples. It does not include a formal correlation matrix or extractable quantitative effect sizes (r) necessary for meta-analysis.. Verbatim Evidence: "This article is primarily based on the authors’ book, Boundary Spanning Leadership: Six Practices for Solving Problems, Driving Innovation, and Transforming Organizations... The database for the LAD project included some 2,800 survey responses, almost 300 interviews and a wide range of secondary data... Our data showed that 86% of senior executives found it 'extremely important' to work effectively across boundaries... Yet only 7% of these executives believed they were currently 'very effective' at doing so."</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="18" customHeight="1" s="10">
       <c r="A73" t="inlineStr">
@@ -3850,6 +4237,16 @@
           <t>BSMA0070</t>
         </is>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>This dissertation examines the extent to which organizational and professional commitment, the technical environment, and the professional environment are related to boundary spanning activity. Surveys of R&amp;D professional employees, their co-workers, and their managers were used to obtain measures of commitment to their organizations and professions, perceptions of the technical and professional environment in which they worked, and the frequency with which they communicated both within and outside of the R&amp;D unit.</t>
@@ -3875,7 +4272,11 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="P73" s="8" t="n"/>
+      <c r="P73" s="8" t="inlineStr">
+        <is>
+          <t>The study measures boundary spanning activity as mere communication frequency (e.g., 'Over the past month how often have you discussed work-related issues with...'). According to Screening Rule 6, variables that merely measure communication frequency without specifying a purposive boundary-spanning action (such as seeking resources, scanning, or coordinating) lack construct validity for BSB and must be excluded. Although the study also collected managerial ratings of purposive boundary spanning behaviors (information collecting and environmental scanning), these ratings were only used to validate the self-reports and do not appear in the study's correlation matrix. Thus, there are no valid extractable effect sizes of interest.. Verbatim Evidence: "Boundary Spanning: ACTIVITY... 5-pt scale (1=low 5=high) mean of percentile rankings of intraunit &amp; extraunit communication frequency. INTRAUNIT COMMUNICATION FREQUENCY... 'How often have you discussed technical issues encountered in your current work over the past month, either face to face or by phone, with each person in your unit?'. EXTRAUNIT COMMUNICATION FREQUENCY... 6 point scale of frequency of communication Other R&amp;D units, marketing/sales, manufacturing, upper management; suppliers, vendors, customers, university researchers alumni, former co-workers, authors, professional association members. ... 2. COMPANY PERSONNEL. Over the past month how often have you discussed work-related issues with the following in personnel in your company? ... Table 3.9: Means, Standard Deviations, and Intercorrelations Between Variables"</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="18" customHeight="1" s="10">
       <c r="A74" t="inlineStr">
@@ -3888,6 +4289,16 @@
           <t>BSMA0071</t>
         </is>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>We study the relation between stability of the nonproﬁt organization’s environment and its board structure and the impact of this relation on organizational performance from the perspectives of both Agency Theory and Resource Dependence (Boundary Spanning) Theory. The impact of board characteristics on organizational performance is contextual. Speciﬁcally, we predict and show for a sample of U.S. nonproﬁts that board mechanisms related to monitoring are more likely to be effective for stable organizations, whereas board mechanisms related to boundary spanning are more effective for less stable organizations. We ﬁnd that the two theories are complementary and address different aspects of nonproﬁt performance, but the results are statistically stronger and more often consistent with resource dependence than with agency theory. Overall, this study supports Miller-Millesen’s (Nonproﬁt and Voluntary Sector Quarterly, 32: 521–547 2003) contention that, because the nonproﬁt environment is often more complex and heterogeneous than the for-proﬁt world, no one theory describes all tasks of nonproﬁt boards.</t>
@@ -3913,7 +4324,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P74" s="8" t="n"/>
+      <c r="P74" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study investigates the effect of nonprofit board composition (e.g., proportion of major donors, proportion of staff, board size) on organization-level performance (administrative expense ratio and growth in direct contributions). The unit of analysis is the nonprofit organization (N=104 organizations), violating the requirement for individual-level data (Code 3). Furthermore, the independent variables represent board structural composition rather than individual-level purposive interpersonal Boundary Spanning Behavior, meaning it lacks the relevant effect size of interest (Code 1).. Verbatim Evidence: "This study employs a sample of operating public charities to test hypotheses suggested by both Agency Theory and Resource Dependence Theory regarding the relation between board characteristics and two different measures of organizational performance. [...] We obtained governance data through a mail survey of the 473 organizations. We sent the survey to each organization and asked a staff member to fill it out. [...] Table 4 Regressions of average administrative expense ratio and growth of direct contributions on board characteristics and other variablesa [...] Number of observations (organizations) 104"</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="18" customHeight="1" s="10">
       <c r="A75" t="inlineStr">
@@ -3926,6 +4341,16 @@
           <t>BSMA0072</t>
         </is>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>Although network analysis is becoming a more viable and informative methodology for the study of interorganizational behavior, issues involving the accuracy and reliability of self-reported or ‘cognitive’ network data are still unresolved. Two networks based on information and coordination relationships in each of four major cities are examined. Reliability of responses is assessed as the percent of confirmed relationships between agency respondents and by correlating the extent of agreement in each network. In addition, two possible measurement errors are examined: systematic errors which are network-independent and idiosyncratic errors which are network-dependent. These errors are assessed through correlational analyses of the intensity of an organization's relationships with the number of its relationships that are confirmed in each network. Also systematic errors are accounted for by calculating the proportion of confirmed relationships within the different response categories used to judge the strength of relationship between ego organizations in the network. It is concluded that boundary spanning personnel of organizations can provide fairly reliable responses to network generated questions, but that errors in the data tend to be systematic in the way that prior studies of interpersonal cognitive networks report.</t>
@@ -3951,7 +4376,11 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="P75" s="8" t="n"/>
+      <c r="P75" s="8" t="inlineStr">
+        <is>
+          <t>The study violates multiple inclusion criteria [Code 1 &amp; Code 3]. First, it violates the Proxy Guardrail (Screening Rule 5) because the respondents act as key informants reporting on firm-level interorganizational relationships (e.g., 'your agency'), rather than their own individual boundary spanning behaviors. The analysis is conducted at the dyadic and organizational network levels [Code 3]. Second, the study is a methodological investigation evaluating the reliability of network self-reports by correlating adjacency matrices (ego vs. alter reciprocity). It does not measure a substantive boundary spanning behavior construct correlated with other individual-level variables, thereby lacking any extractable zero-order effect sizes of interest [Code 1].. Verbatim Evidence: "Although network analysis is becoming a more viable and informative methodology for the study of interorganizational behavior, issues involving the accuracy and reliability of self-reported or ‘cognitive’ network data are still unresolved. Reliability of responses is assessed as the percent of confirmed relationships between agency respondents and by correlating the extent of agreement in each network. Data about the formal network of services at each site were gathered from a key informant (or ‘boundary spanner’) in each organization. Boundary spanning roles (Aldrich and Herker 1977; Tushman and Scanlan 1981) are those occupied by persons who serve as liaisons with other organizations or who are deemed as particularly knowledgeable about the organization’s relationships (e.g. agency, unit, or program director). In these four sites the number of possible dyadic relationships range from 930 to 1892, and when the data are pooled across sites the total number of possible relationships is 5710. In order to assess the accuracy of the organizational respondent’s data, two relational network questions from the survey are used. The first asks respondents: “To what extent does your agency receive information for coordination, control, planning, or evaluation purposes from this agency?” A second asks: “How well coordinated are the activities of your agency with those of this other agency?” An initial and straightforward way of assessing data quality is to investigate the reciprocity of relationships by correlating the responses from organization i to j, with organization j’s responses to i."</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="18" customHeight="1" s="10">
       <c r="A76" t="inlineStr">
@@ -3964,6 +4393,16 @@
           <t>BSMA0073</t>
         </is>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>The offshoring of external audit work to so-called low-cost countries is prevalent among the Big 4 professional services firms. Despite this, our understanding of how this form of offshoring influences audit practitioners and the audit process is limited. This study examines how and why offshoring emerged as an organizational matter that changed the way audit work is organized in a Big 4 firm context. Our findings demonstrate how changes in the design of offshoring processes influence interactions between onshore and offshore auditors. We uncover how individual ‘‘boundary spanners’’ struggle to coordinate audit work across the multiple boundaries that separate onshore and offshore auditors. Furthermore, we show how the institutionalization of ‘‘boundary spanning’’ functions in organizational structures and processes can have the unintended consequence of widening the boundaries between onshore and offshore auditors. Finally, we offer evidence of the effect of offshoring on the learning process of onshore and offshore auditors.</t>
@@ -3989,7 +4428,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P76" s="8" t="n"/>
+      <c r="P76" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative case study that uses in-depth interviews, documentary analysis, and digital evidence to explore how the offshoring of audit work affects onshore auditors and the audit process in a Big 4 firm. It does not provide quantitative survey data or extractable effect sizes (e.g., zero-order correlations) for boundary spanning behavior, which are required for this meta-analysis.. Verbatim Evidence: "Given that the objective of this study is to develop our understanding of how and why offshoring emerged as an organizational matter, changing the way audit work is organized and perceived in a Big 4 firm, a qualitative research methodology was deemed most appropriate... More specifically, we used a case study approach drawing upon multiple data sources—documentary data, in-depth interviews, and digital data—to obtain detailed information about the complexities underpinning the real-life phenomenon of offshoring in audit... In the second stage of data collection, 13 semi-structured interviews were conducted with 12 (onshore) auditors within EU-TAM who were selected because of their direct experience of the offshoring process within EU-TAM."</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="18" customHeight="1" s="10">
       <c r="A77" t="inlineStr">
@@ -4002,6 +4445,16 @@
           <t>BSMA0074</t>
         </is>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>Despite the relevance of team boundary spanning in new product development (NPD), there is great deal we still do not know about these activities. For example, little is known about how these activities affect the development of team identification, an important emergent state with critical implications for new product performance. This study extends our understanding of this topic by exploring the relationship between team boundary spanning and team identification. This relationship is examined via the intervening mechanisms of team potency and team boundedness and the moderating effect of intra-team communication. Data from a time-lagged survey study of 140 NPD projects revealed that team potency and team boundedness, respectively, positively and negatively mediate the relationship between team boundary spanning and team identification. Intra-team communication was found to reduce the negative effect of team boundary spanning on team boundedness.</t>
@@ -4027,7 +4480,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="P77" s="8" t="n"/>
+      <c r="P77" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a single key-informant (NPD team leader) to evaluate the boundary spanning activities of the entire new product development (NPD) team. The unit of analysis is the team/project (N=140 NPD projects). The survey items refer to the team as a whole (e.g., 'Project leader or team members talked up the NPD project...', 'Found out whether individuals or groups inside the company supported the team's activities'). Since the data represents team-level boundary spanning rather than individual-level employee boundary spanning, it must be excluded under the Team Level Aggregation guardrail.. Verbatim Evidence: "Data from a time-lagged survey study of 140 NPD projects revealed that team potency and team boundedness, respectively, positively and negatively mediate the relationship between team boundary spanning and team identification. [...] The questionnaire was addressed to the person in the company responsible for NPD activities. These individuals were instructed to answer the questionnaire in relation to a recently completed NPD project that he or she had led and for which the NPD team was engaged in boundary spanning activities. [...] Table 2. Team boundary spanning dimensions. [...] Project leader or team members talked up the NPD project to individuals or groups in the company. [...] Second, the study used a single key-informant per organization. [...] Third, data for this study were provided by NPD team leaders."</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="18" customHeight="1" s="10">
       <c r="A78" t="inlineStr">
@@ -4040,6 +4497,16 @@
           <t>BSMA0075</t>
         </is>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>In today’s highly interconnected, uncertain, and dynamic business environment, team boundary spanning has become an important determinant of the performance of new product development (NPD) projects. Despite the positive evidence supporting the use of boundary spanning activities by NPD teams, little is still known about how boundary spanning teams become high-performance teams. The current study advances research on this subject by examining the mediating effect of team potency on the relationship between team boundary spanning and new product performance, as well as the moderating effects of team size and functional diversity on the relationship between team boundary spanning and team potency. Data from a time-lagged survey study of 140 NPD projects found that team boundary spanning can promote team potency which, in turn, results in greater product quality and new product creativity. The positive effect of team boundary spanning on team potency was found to be more pronounced for NPD teams of medium size and high levels of functional diversity.</t>
@@ -4065,7 +4532,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P78" s="8" t="n"/>
+      <c r="P78" s="8" t="inlineStr">
+        <is>
+          <t>The study adopts the new product development (NPD) team as the unit of analysis (N = 140 NPD projects). It surveys a single key informant (e.g., R&amp;D manager) per team to report on team-level boundary spanning activities, utilizing survey items with a team referent (e.g., 'Project leader or team members talked up the NPD project...'). Consequently, the reported correlations represent team-level aggregated constructs rather than individual employee behavior, which requires exclusion under Code 3 (Non-individual level).. Verbatim Evidence: "The unit of analysis was a recently launched NPD project in which the NPD team in charge had partaken in boundary spanning activities. [...] The questionnaire was addressed to the person in the company responsible for NPD activities who was instructed to answer the survey questions in relation to a new product that their company had developed [...] Thus, the study’s sample consists of 140 NPD projects, each one from a different company. [...] Table 2 Team boundary spanning dimensions [...] Project leader or team members talked up the NPD project to individuals or groups in the company. [...] Persuaded them to support the team’s activities and decisions."</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="10">
       <c r="A79" t="inlineStr">
@@ -4078,6 +4549,16 @@
           <t>BSMA0076</t>
         </is>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>Although team boundary spanning is conducive to achieving new product (NP) competitive advantage, these actions may not always deliver the expected performance. The current study makes an initial attempt to examine factors that undermine team boundary spanning positive effects on NP competitive advantage by proposing and testing a negative moderating effect of team social cohesion on the relationship between team boundary spanning and NP competitive advantage. Furthermore, the current study expects team social cohesion to have a stronger negative moderating effect on the relationship between team boundary spanning and NP competitive advantage when external task interdependence and project newness are high than when they are low. Data for this study come from 140 NPD projects developed and commercialized by Spanish manufacturing firms in high‐ and medium‐high‐technology sectors. The study’s results reveal a positive effect of team boundary spanning on NP competitive advantage. Furthermore, high levels of team social cohesion are shown to reduce the positive effect of team boundary spanning on NP competitive advantage. Finally, we found that project newness and external task interdependence accentuate the negative moderating effect of team social cohesion on the relationship between team boundary spanning and NP competitive advantage. The current study makes several contributions to the literature. First, findings from this study give us new insights into the significance of team boundary spanning to the success of NPs by revealing that boundary‐spanning activities are beneficial to achieving NP competitive advantage. Second, the study departs from existing research in that it exposes a dark side of team social cohesion for NPD teams engaged in boundary spanning activities. Last, the study expands extant research by proposing and demonstrating that project newness and external task interdependence bring about situations in which external groups present a threat to the collective identity of socially cohesive groups.</t>
@@ -4103,7 +4584,14 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P79" s="8" t="n"/>
+      <c r="P79" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the NPD team (N = 140 NPD projects). A single key informant (manager responsible for NPD activities) served as a proxy to report on the boundary-spanning behaviors of the entire team. The survey items use team-referent language (e.g., 'Project leader or team members talked up the NPD project', 'Our team had a very pleasant working atmosphere'). Because the correlations represent team-level constructs rather than individual employee boundary-spanning behavior, the study violates the Team Level Aggregation and Proxy guardrails and must be excluded.. Verbatim Evidence: "Data for this study come from 140 NPD projects developed and commercialized by Spanish manufacturing firms in high- and medium-high-technology sectors.
+This questionnaire was addressed to the person in the company responsible for NPD activities. Respondents were instructed to answer the survey questions with regard to a recently completed NPD project that they had led or managed.
+I_AMB1: Project leader or team members talked up the NPD project to individuals or groups in the company.
+Our team had a very pleasant working atmosphere."</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="18" customHeight="1" s="10">
       <c r="A80" t="inlineStr">
@@ -4116,6 +4604,16 @@
           <t>BSMA0077</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>Gender diversity pays off, particularly at senior levels in organizations. Companies with higher rates of gender diversity among senior leaders outperform their peers by a 15% margin; those with the highest percentages of female board directors enjoy as much as a two-thirds higher return on equity, sales, and invested capital. The key to occupying a high-level position in any organization is building an effective network of positive workplace relationships. Decades of research on organizational networks have shown that who you know–and who knows you–is critical to performance and career success. Full inclusion of both genders in informal organizational networks has been shown to drive productivity, innovation, and profitability. Full inclusion also supports individual well-being and deep engagement. Yet many leaders–both men and women–fail to develop gender-inclusive networks, potentially disadvantaging women since they are less likely to be connected to people in senior-level positions, given the overwhelming dominance of men in these roles. No wonder that feeling excluded from organizational networks has been identified as one of women’s top barriers to career success.</t>
@@ -4141,7 +4639,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P80" s="8" t="n"/>
+      <c r="P80" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a practitioner-oriented summary of mixed-methods research (web-based surveys and interviews) mapping the networks of individuals across organizations. Although it mentions collecting quantitative network data and analyzing it statistically, the manuscript does not report any formal correlation matrices, regression tables, or extractable quantitative effect sizes (r) required for meta-analysis. Therefore, it must be excluded for lacking an effect size of interest.. Verbatim Evidence: "Our data captured the networks of more than 16,500 individuals in 31 different companies via web-based surveys... These data were organized into matrices and analyzed statistically. To complement our quantitative findings, we also interviewed 125 individuals in these organizations. These semi-structured hour-long interviews included open-ended questions... Transcripts were analyzed to identify themes, patterns, and examples."</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="18" customHeight="1" s="10">
       <c r="A81" t="inlineStr">
@@ -4154,6 +4656,16 @@
           <t>BSMA0078</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>Abstract             The defense industry in Israel has long been considered a critical platform for the development of the high‐technology sector. This study examines the importance of knowledge combination capability work units build through social relationships to enhance their performance. Specifically, we probe how both intraunit relational capital (within a unit) and interunit relational capital (across units) enable units to build knowledge combination capabilities and how such capabilities affect their performance. Data collected from senior managers in 122 knowledge units indicate that: (1) both intra‐ and interunit relational capital are positively related to knowledge combination capability; (2) knowledge combination capability is positively associated with enhanced unit performance; (3) knowledge combination capability fully mediates the relationship between interunit relational capital and unit performance; and (4) intraunit relational capital impacts both directly and indirectly (through knowledge combination capability) on unit performance. The findings suggest that interunit relational capital entails greater variation in knowledge stocks and thus may lead to more radical innovation than intra‐relational capital that entails more similar knowledge bases and, thus, produces more incremental innovations. Copyright © 2009 Strategic Management Society.</t>
@@ -4179,7 +4691,11 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="P81" s="8" t="n"/>
+      <c r="P81" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts its analysis at the team/unit level rather than the individual employee level. The correlation matrix and statistical analyses are based on an aggregated sample of N=122 work units, using responses from unit and deputy managers as informants to evaluate the unit's collective relational capital and behavior. Because the unit of analysis is the work unit and not the individual, it lacks the individual-level zero-order correlations required for this meta-analysis.. Verbatim Evidence: "In this study, the unit was considered to be the level of analysis. Hence, all measures were specified at the unit level. Respondents were asked to evaluate the relational capital, knowledge combination capabilities, and performance of the unit. ... Overall, we received usable data from 244 respondents in 122 units, yielding a response rate of 76.7 percent. ... Table 2. Means, standard deviations, and Pearson’s correlations between research variables ... N = 122"</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="18" customHeight="1" s="10">
       <c r="A82" t="inlineStr">
@@ -4192,6 +4708,16 @@
           <t>BSMA0079</t>
         </is>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>This study examines the relationships between joint work commitments, job satisfaction, and job performance of lawyers employed by private law firms in Israel. Based on Morrow’s (1993) concept of five universal forms of commitment, their interrelationship was tested with respect to the commitment model of Randall and Cote (1991), which appeared to show in previous studies (Cohen, 1999, 2000) a better fit compared to other models. In addition, the study examined the relationship between the commitment model and work attitude and outcome, namely, job satisfaction and job performance. The results show that the commitment model of Randall and Cote was almost fully supported, except for the relationship between job involvement and continuance commitment. This relationship is better understood via career commitment. An interesting finding of this study is that job satisfaction has a mediating role in the relationship between joint work commitment and job performance. The article concludes with suggestions regarding further investigation of the interrelationships between work commitment constructs, and the relationship between joint commitment forms, job satisfaction, and job performance.</t>
@@ -4217,7 +4743,11 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="P82" s="8" t="n"/>
+      <c r="P82" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on forms of work commitment (affective, continuance, Protestant Work Ethic, career commitment, and job involvement), job satisfaction, and job performance among lawyers. None of the measured constructs represent boundary spanning behavior, which involves purposive actions to span intra- or inter-organizational boundaries.. Verbatim Evidence: "ABSTRACT. This study examines the relationships between joint work commitments, job satisfaction, and job performance of lawyers employed by private law firms in Israel. Based on Morrow’s (1993) concept of five universal forms of commitment, their interrelationship was tested with respect to the commitment model of Randall and Cote (1991)... Measures: Protestant Work Ethic. This measure was assessed by 19 items... Job Involvement. This measure is based on the 10-item scale... Affective Organizational Commitment. This measure is based on the scale developed by Allen and Meyer... Continuance Organizational Commitment... Career Commitment... Job Satisfaction... Job performance."</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="18" customHeight="1" s="10">
       <c r="A83" t="inlineStr">
@@ -4230,6 +4760,16 @@
           <t>BSMA0080</t>
         </is>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>This study analyzes the complex set of relationships among perceived organizational reputation, ﬁrm’s quality of products/services, customers’ satisfaction and multiple performance measures. A path analysis shows that reputation is inﬂuenced by customers’ satisfaction, which is a mediator in the relationship between the ﬁrm’s quality of products/services and reputation. Reputation is associated with the ﬁrm’s growth and accumulation of customers’ orders, but is not directly associated with market share, proﬁtability and ﬁnancial strength. Market share inﬂuences a ﬁrm’s profitability and is a function of the ﬁrm’s growth and accumulation of customers’ orders, but it has no inﬂuence on the ﬁrm’s ﬁnancial strength.</t>
@@ -4255,7 +4795,11 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="P83" s="8" t="n"/>
+      <c r="P83" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study is conducted at the organizational level (N = 86 industrial enterprises), with CEOs acting as macro-level key informants evaluating firm-level constructs such as perceived organizational reputation, customer satisfaction, and firm performance. It does not measure interpersonal boundary spanning behavior of individual employees. Therefore, the paper violates both the individual-level analysis requirement and lacks the target construct's effect sizes.. Verbatim Evidence: "The sample of the study was drawn from a population of 300 Kibbutz-owned industrial enterprises in Israel. ... A questionnaire to the enterprise's CEO was mailed from and returned to a university address, using a self-addressed reply envelope. ... Five measures of the performance of each firm were included in this study: growth, profitability, financial strength, market share and accumulation of customers' future orders... The participants were asked to rate their firm's performance relative to its competitors."</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="18" customHeight="1" s="10">
       <c r="A84" t="inlineStr">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -3121,6 +3121,14 @@
           <t>BSMA0049</t>
         </is>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>999</v>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>Customer engagement entails unequivocal frontline service employees’ top performances and recommendable behaviors through management appropriate leadership to ﬂourish. Under the social exchange and social identity theories, this study investigates employee customer–oriented boundary-spanning behaviors as an outcome of spiritual leadership, through the mediating eﬀect of employee spiritual survival and well-being. PROCESS macro was used to analyze data collected from 5-star hotels full-time frontline employees in Antalya, Turkey. Results indicated that the eﬀect of spiritual leadership on the three dimensions of customer-oriented boundary-spanning behaviors is fully mediated by spiritual survival and spiritual well-being. Spirituality appears to be a noteworthy but remote contributor to customer engagement via employees’ boundary-spanning behaviors. Our study contributed to the boundary-spanning and customer engagement literature by illustrating that a sense of mission and wellbeing at the workplace are adequate requirements to engage a frontline employee, whose boundaryspanning behaviors will be instrumental in fostering customer engagement. Further detailed theoretical and managerial implications are discussed.</t>
@@ -3146,7 +3154,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P52" s="8" t="n"/>
+      <c r="P52" s="8" t="inlineStr">
+        <is>
+          <t>The study measures customer-oriented boundary-spanning behaviors (COBSBs), specifically external representation, internalized influence, and service delivery, among frontline hotel employees. The sample consists of individual organizational employees (N=250) and the study provides a full zero-order correlation matrix (Table 2) between the boundary-spanning dimensions and other variables like spiritual leadership and spiritual well-being. It meets all inclusion criteria and does not violate any exclusion guardrails.. Verbatim Evidence: "The study population consisted of full-time frontline employees because first frontline staffs directly interact with, and consistently partake in their satisfaction, loyalty, and engagement... 350 questionnaires were distributed at time I and 309 were retrieved. At time II 309 questionnaires were redistributed, and 250 responses were used after deletion of unusable and incomplete questionnaires... Staffs’ COBSBs were assessed with the scale developed by Bettencourt et al. (2005) that measures service delivery with 5 items, internal influence and external representation with both 4 items... Table 2. Intercorrelations and discriminant validity criterion."</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="18" customHeight="1" s="10">
       <c r="A53" t="inlineStr">
@@ -4812,6 +4824,16 @@
           <t>BSMA0081</t>
         </is>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>Research on team leadership has primarily focused on leadership processes targeted within teams, in support of team objectives. Yet, teams are open systems that interact with other teams to achieve proximal as well as distal goals. This review clariﬁes that deﬁning ‘what’ constitutes functionally eﬀective leadership in interteam contexts requires greater precision with regard to where (within teams, across teams) and why (team goals, system goals) leadership processes are enacted, as well as greater consideration of when and among whom leadership processes arise. We begin by synthesizing ﬁndings from empirical studies published over the past 30 years that shed light on questions of what, where, why, when, and who related to interteam leadership and end by providing three overarching recommendations for how research should proceed in order to provide a more comprehensive picture of leadership in interteam contexts.</t>
@@ -4837,7 +4859,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P84" s="8" t="n"/>
+      <c r="P84" s="8" t="inlineStr">
+        <is>
+          <t>The article is a systematic literature review synthesizing findings from previous empirical studies on functional leadership in interteam contexts over the past 30 years. It does not present original primary quantitative survey data or provide extractable effect sizes required for a meta-analysis.. Verbatim Evidence: "The purpose of this review is to clarify the nature of functional leadership in interteam contexts, integrate and critically evaluate relevant findings from prior research, and identify promising areas for future inquiry... We begin by synthesizing findings from empirical studies published over the past 30 years that shed light on questions of what, where, why, when, and who related to interteam leadership... Our initial search yielded 2617 articles... This vetting process resulted in a smaller subset of 160 articles."</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="18" customHeight="1" s="10">
       <c r="A85" t="inlineStr">
@@ -4850,6 +4876,14 @@
           <t>BSMA0082</t>
         </is>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>Even though empirical studies examining leadership and effectiveness in multiteam systems (MTS) are on the rise, there is still much to learn about leading a complex “team of teams,” particularly in a field setting as opposed to a laboratory simulation. This study draws upon the multiteam systems and intergroup leadership theory literature streams to examine the role of systems thinking and leader identification as antecedents to intergroup leadership, arguing that higher levels of systems thinking and stronger leader identification with the MTS will enhance the efficacy of leader rhetoric targeted toward the development of an intergroup relational identity with boundary spanning acting as a positive moderating influence on this relationship. I further argue team functional diversity moderates the relationship between intergroup leadership and MTS effectiveness such that higher levels of intergroup leadership are needed to positively influence MTSs with higher levels of heterogeneity. Finally, team identification is evaluated for its predicted moderating effect on the relationship between intergroup leadership and MTS effectiveness such that identification with the MTS will have a positive effect on this relationship while identification with the component team will detract from it. Hypotheses were tested but not supported using a sample of 256 commanders at the squadron, group, and wing level organized in 180 MTSs within the Department of the Air Force. Supplemental analysis identified a significant positive moderating effect of systems thinking and a negative moderating effect of leader component team identification on the relationship between leader rhetoric and intergroup relational identity. Low levels of boundary spanning coupled with higher levels of intergroup relational identity resulted in lower MTS effectiveness while the opposite was true for high levels of boundary spanning and intergroup relational identity. The study concludes with a discussion of theoretical and practical implications as well as recommendations for future research.</t>
@@ -4875,7 +4909,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P85" s="8" t="n"/>
+      <c r="P85" s="8" t="inlineStr">
+        <is>
+          <t>The study examines intergroup leadership and multiteam systems (MTS) using a sample of U.S. Air Force commanders. Boundary spanning is measured at the individual employee level as a self-assessment of the commander's purposive actions across unit boundaries (e.g., 'I solicit information and resources from elsewhere...'). The study provides an extractable zero-order correlation matrix (Table 5, N=256 individuals) containing boundary spanning and other substantive variables (such as Systems Thinking and Leader Rhetoric). The research meets all inclusion criteria as it captures individual-level, intra-organizational boundary spanning behavior.. Verbatim Evidence: "Boundary Spanning. Boundary spanning was measured as a self-assessment using the 4-item empirically validated scale developed by Faraj and Yan (2009) adapted from a team focus to an individual assessment and modified for an Air Force setting. For example, the item 'To what extent does the team encourage its members to solicit information and resources from elsewhere in and/or beyond the division?' was modified to read 'To what extent do I solicit information and resources from elsewhere in and/or beyond my unit?'... 1. I solicit information and resources from elsewhere in and/or beyond my unit. 2. I try to influence important actors elsewhere in and/or beyond my unit on behalf of the unit and its mission. 3. I make use of relationships with others on behalf of my unit. 4. The work of my unit depends upon information and resources that I actively solicit, that is, information and resources beyond what comes through official channels... Table 5. Correlation Matrix for Study Population... an=256 individuals for variables 2 - 13; n=114 individuals for variable 1."</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="18" customHeight="1" s="10">
       <c r="A86" t="inlineStr">
@@ -4888,6 +4926,16 @@
           <t>BSMA0083</t>
         </is>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>This study investigates the relationship between multiple role management strategies and knowledge spillovers across roles. We focus on a particular category of boundary-spanning professionals, the scholar-practitioners—professionals who work across the boundaries of academic and practice worlds—and apply a role theory lens to study (a) the sources of interrole conflict they experience at role boundaries, (b) the strategies of multiple role management they enact, and (c) the knowledge spillovers associated to such strategies. We develop a grounded model that describes three role management strategies, which occupy different positions on a role separation–integration continuum, and generate different mechanisms of knowledge spillover. Our study sheds light on the understudied relationship between role management strategies and knowledge consequences, and the type of tensions individuals experience in this process. In addition, we discuss how the strategic management of teaching, research, and practical application roles can help bridge academic and managerial practice worlds.</t>
@@ -4913,7 +4961,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P86" s="8" t="n"/>
+      <c r="P86" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative investigation based on 16 semi-structured interviews with scholar-practitioners to develop a grounded model of multiple role management strategies. It does not provide quantitative survey data, formal correlation matrices, or extractable effect sizes (r) required for the meta-analysis.. Verbatim Evidence: "To answer these challenges, our study builds on 16 in-depth interviews with experienced scholar-practitioners to understand the strategies they use to manage their professional roles. [...] we conducted a qualitative study of experienced scholar-practitioners and developed a grounded model about the strategies that scholar-practitioners use to deal with multiple role conflicts. [...] We employed semi-structured interviews to have a deep understanding of the practices deployed by scholar-practitioners to cope with their multiple roles."</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="18" customHeight="1" s="10">
       <c r="A87" t="inlineStr">
@@ -4926,6 +4978,16 @@
           <t>BSMA0084</t>
         </is>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>Since the collapse of the price of crude oil in the mid 1980s, some participants in the sector have overhauled their approach to learning for strategic advantage. The management teams dealing with the projects discussed here demonstrated an awareness that learning can be a core rigidity as well as a core competence, and set about institutionalizing new learning. The speed of learning was an important determinant of success, leading to substantial increases in project NPVs and a rapid reinvestment in the learning capabilities themselves. Learning about `boundary management' helps to distinguish areas where internal learning could develop proprietary competitive advantage, from those areas where valuable learning might best be achieved through alliance.</t>
@@ -4951,7 +5013,11 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="P87" s="8" t="n"/>
+      <c r="P87" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative case study based on interviews with senior management in the offshore oil industry. It does not provide any quantitative survey data, correlation matrix, or extractable effect sizes (r) for individual employee boundary spanning behavior, and therefore lacks the statistical data required for this meta-analysis.. Verbatim Evidence: "This paper reports on lessons concerning strategic learning capabilities encountered in exploratory case studies in UK Continental Shelf oil field development projects... The study reported on here was based primarily on a series of interviews with senior management of three offshore oil fields in the UK Continental Shelf."</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="18" customHeight="1" s="10">
       <c r="A88" t="inlineStr">
@@ -4964,6 +5030,16 @@
           <t>BSMA0085</t>
         </is>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>Adopting a microfoundations approach to the analysis of intra-multinational enterprise (MNE) knowledge integration, we focus on mobile inventors and their boundary-spanning experience. Using inventor-patent data on US-based MNEs, we show that intra-organizational cross-border mobility and inter-organizational mobility have respectively a positive and a negative effect on knowledge integration. Cross-border mobility within the MNE enables the temporary co-location of mobile inventors in different units, facilitating the dissemination of their knowledge within the MNE. Conversely, “job-hopping” inventors may remain organizational outsiders, which hinders their ability to foster intra-MNE knowledge integration.</t>
@@ -4989,7 +5065,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P88" s="8" t="n"/>
+      <c r="P88" s="8" t="inlineStr">
+        <is>
+          <t>The study utilizes archival patent data from the USPTO to examine the effect of inventors' geographic and organizational mobility on knowledge integration, which is measured via patent citations. The unit of analysis is the inventor-patent pair (N = 170,835), and the dependent variable is intra-firm forward citations of patents. Per the screening rules, studies analyzing patent citations and archival corporate R&amp;D networks rather than individual-level interpersonal boundary spanning behavior must be excluded under Code 3.. Verbatim Evidence: "Using inventor-patent data on US-based MNEs, we show that intra-organizational cross-border mobility and inter-organizational mobility have respectively a positive and a negative effect on knowledge integration... We explore these issues using data on over 170,000 inventor-patent pairs, involving a cohort of approximately 40,000 inventors and 68,000 patents granted to 128 US-based MNEs... The existing literature has widely employed patent citations as an indicator of knowledge flows (Jaffe et al., 1993). Intra-firm forward citations (known as self-citations) are used to capture the knowledge integration within the firm boundaries... First, intra-firm cross-border mobility is computed as the number of unique countries in which an inventor has resided during the tenure at the MNE... Second, inter-organizational mobility is computed as the number of unique organizations (different from the focal MNE) for which an inventor has patented before joining the MNE"</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="18" customHeight="1" s="10">
       <c r="A89" t="inlineStr">
@@ -5002,6 +5082,16 @@
           <t>BSMA0086</t>
         </is>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>The identification and management of work dependencies is a fundamental challenge in software development organizations. This paper argues that modularization, the traditional technique intended to reduce interdependencies among components of a system, has serious limitations in the context of software development. We build on the idea of congruence, proposed in our prior work, to examine the relationship between the structure of technical and work dependencies and the impact of dependencies on software development productivity. Our empirical evaluation of the congruence framework showed that when developers’ coordination patterns are congruent with their coordination needs, the resolution time of modification requests was significantly reduced. Furthermore, our analysis highlights the importance of identifying the “right” set of technical dependencies that drive the coordination requirements among software developers. Call and data dependencies appear to have far less impact than logical dependencies.</t>
@@ -5027,7 +5117,11 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="P89" s="8" t="n"/>
+      <c r="P89" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure individual-level boundary spanning behavior, but rather socio-technical congruence (the match between task coordination requirements and actual coordination networks). Furthermore, the study violates the unit of analysis guardrail, as the unit of analysis is the software modification request (task level) rather than individual employees.. Verbatim Evidence: "The unit of analysis is the modification request which corresponds to a development work item associated with a defect or a new feature. A total of 2375 multi-team modification requests were identified... Our measure of development productivity is Resolution Time which is defined as the time, in days, it took to resolve a particular MR... congruence is defined as the proportion of coordination activities that actually occurred (represented in the CA matrix) relative to the total number of coordination activities that should have taken place (represented by the CR matrix)."</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="18" customHeight="1" s="10">
       <c r="A90" t="inlineStr">
@@ -5040,6 +5134,16 @@
           <t>BSMA0087</t>
         </is>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>Prior research on the impact of organizational memory on new product success has divergent perspectives. Such inconsistency has accrued mainly from not considering memory's multifaceted aspects, which interact with specific project characteristics. This paper tries to sort out this paradox by proposing that project innovativeness moderates the relationship among variables of organizational memory and new product success. An empirical study of 169 NPD projects of Korean manufacturing firms finds that memory sharing and the use of external information and formal procedures enhance new product success, whereas organizational memory has no effect. Project innovativeness is found to moderate memory's effect, despite some tradeoffs. As innovativeness increases, the effect of organizational memory and use of external information become stronger whereas the effect of memory sharing and use of formal procedures weaken. This suggests that firms must activate organizational memory more carefully according to project characteristics and the memory level to maximize its positive effects.</t>
@@ -5065,7 +5169,11 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="P90" s="8" t="n"/>
+      <c r="P90" s="8" t="inlineStr">
+        <is>
+          <t>The study adopts the NPD project team as the unit of analysis (N = 169 projects) and relies on individual project leaders or members acting as key informants to evaluate team-level constructs. A review of the measurement scales in Appendix A shows that the grammatical subject for the 'Use of external information' items is 'project team' (e.g., 'During the project, project team regularly discussed with customers', 'Consulted regularly outside experts'). This violates Screening Rule 4 (Team Level Aggregation) and Screening Rule 5 (Proxy Guardrail), as the constructs do not measure individual-level boundary spanning behavior.. Verbatim Evidence: "The finalized questionnaires were administered to key informants in major Korean manufacturing firms who had recent experience with participating in NPD projects as project leaders or members. In the end, 169 usable questionnaires were obtained on which we empirically test our model. The final sample consists of NPD projects... Use of external information (4 items, reliability = 0.83) During the project, project team –Regularly discussed with customers –Systematically acquired external technological and market information –Consulted regularly outside experts –Conducted systematic benchmarking"</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="18" customHeight="1" s="10">
       <c r="A91" t="inlineStr">
@@ -5078,6 +5186,16 @@
           <t>BSMA0088</t>
         </is>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>This study investigates how post-M&amp;A interdepartmental integration affects the efficiency and effectiveness of new product development (NPD).The total sample size was 251 respondents. Confirmatory factor analysis (CFA) and structural equation modeling (SEM) were used for statistical analysis. Analytical results indicate that, although collaboration interdepartmental integration positively correlates with product vision, interaction interdepartmental interaction integration does not reach a significant level. Despite the fact that some interaction is essential when developing new product competitive advantage (NPCA), such interaction does not necessarily achieve success. Further, product vision positively correlates with new product competitive advantage and NPD performance, and new product competitive advantage positively correlates with NPD performance. In addition, an examination of the mediation effect in terms of Sobel t-test reveals that product vision is a significant mediator for the influence of interdepartmental integration on new product competitive advantage, while the new product competitive advantage is also a significant mediator for the influence of interdepartmental integration on NPD performance. Moreover, this study provides a framework for managing post-M&amp;A integration and closes with a discussion of the theoretical and practical implications of the research findings.</t>
@@ -5103,7 +5221,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P91" s="8" t="n"/>
+      <c r="P91" s="8" t="inlineStr">
+        <is>
+          <t>The study collects survey data from individual employees (R&amp;D and manufacturing personnel, managers, and project leaders) but utilizes them as key informants to evaluate department-level and program-level constructs. The survey items explicitly ask respondents to evaluate the degree to which 'your department' interacted or collaborated with other departments, rather than measuring their own individual boundary spanning behavior. Because the referent is the department and the study evaluates integration at the program level, it violates the proxy guardrail and is excluded.. Verbatim Evidence: "Survey respondents were R&amp;D and manufacturing personnel, managers, and project leaders (Table 2) employed in firms manufacturing electronic and communication products and PCs... This study used program level as a basis for evaluating NPD performance, and analyzed the 251 returned questionnaires on M&amp;A. [...] 1. Interactive-based integration was measured using the five-item scale adapted from Van de Ven, Walker and Liston (1979), and Kahn (1996). Respondents were asked assess the degree to which their department interacted with other departments via meetings, committees, teleconferencing, phone conversations, phone mail, e-mail, and the exchange of standard documentation. [...] For the team members involved in post-M&amp;A interdepartmental integration, the purpose of the questions listed below is to estimate the level of understanding what degree did your department interact with other department in regards to the below activities."</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="18" customHeight="1" s="10">
       <c r="A92" t="inlineStr">
@@ -5116,6 +5238,16 @@
           <t>BSMA0089</t>
         </is>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>Digital transformation accelerates the boundary reshaping of firms’ R&amp;D cooperation and knowledge bases, bringing opportunities for breakthrough innovation following overseas mergers and acquisitions (M&amp;A). Unlike previous studies that have focused separately on digital transformation and overseas M&amp;A integration, this paper aims to explore their synergy effects on firms’ breakthrough innovation from a boundary-spanning perspective. Based on samples of Chinese manufacturing firms’ technology-sourcing overseas M&amp;A from 2012 to 2019, our empirical results show that boundary spanning in R&amp;D cooperation networks and knowledge networks mediate the synergy effects of digital transformation and appropriate overseas M&amp;A integration on firms’ breakthrough innovation. This paper not only complements recent studies that combine digital transformation and boundary-spanning theories, but also provides a deeper understanding of the relationship between boundary spanning and breakthrough innovation in the digital context. It offers important theoretical and practical insights into overseas M&amp;A and innovation in the digital era.</t>
@@ -5141,7 +5273,13 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="P92" s="8" t="n"/>
+      <c r="P92" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the firm, analyzing a sample of 146 Chinese manufacturing firms engaging in overseas M&amp;A. The construct of boundary spanning is conceptualized at the firm level, specifically measuring firm-level geographic and industrial boundary spanning within inter-firm R&amp;D cooperation networks, as well as technological boundary spanning in knowledge networks via patent data. It lacks individual-level employee boundary spanning behavior data.. Verbatim Evidence: "From the Bvd-Orbis M&amp;A database, we selected samples of Chinese manufacturing firms’ overseas M&amp;A by considering multiple criteria. [...] We ultimately selected 146 firms.
+Boundary spanning in R&amp;D cooperation networks (BSCN). We employed a snowball method to collect R&amp;D cooperation, alliance, and joint patent application information of the acquirer, the target firm, and firms that had those relationships with the merging parties three years before and after the M&amp;A.
+Boundary spanning in knowledge networks (BSKN). We collected the merging parties’ patents three years before and after M&amp;A. [...] We constructed IPC co-occurrence matrixes and visualised the acquirer’s pre- and post-M&amp;A knowledge networks."</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="18" customHeight="1" s="10">
       <c r="A93" t="inlineStr">
@@ -5154,6 +5292,16 @@
           <t>BSMA0090</t>
         </is>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>In the face of increasing global uncertainty, multinational enterprises (MNEs) have turned to downsizing to maintain profitability while emphasizing lateral collaboration to increase productivity. Here, we establish a conceptual framework and examine from a macro‐to‐micro perspective how the growing subjects of subsidiary role change, team alignment and employee engagement impact lateral collaboration. We used structural equation modelling to analyse the results of 252 surveys given to MNE subsidiaries in the Taiwanese banking industry and found that employee engagement was central to driving lateral collaboration effectiveness, indicating that the subsidiary role is critical for boundary‐spanning activities and building bridges between various teams. These activities in turn enhance subsidiary performance and lead to better people development. Our findings demonstrate that bundling employee engagement with human resource practices is a strategic way of positioning for the evolution of subsidiary management.</t>
@@ -5179,7 +5327,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P93" s="8" t="n"/>
+      <c r="P93" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure individual boundary spanning behavior (BSB). While the concept of 'boundary spanning' is mentioned in the introduction as part of the definition of lateral collaboration, the actual constructs measured are subsidiary role change, team alignment (operationalized as the presence of reporting lines and HQ coordination mechanisms), employee engagement, lateral collaboration effectiveness (operationalized as normative and affective commitment), people development, and subsidiary performance. None of the survey items measure an individual employee's purposive boundary-spanning actions (e.g., seeking information, coordinating tasks across boundaries). Therefore, the study lacks the required effect size of interest.. Verbatim Evidence: ""lateral collaboration, which is cooperation and boundary spanning achieved between groups without regard for hierarchy" (p. 407); Table 1 Definitions and questions for each variable: Team alignment (e.g., "A12 Your subsidiary encourages active collaboration between functions/departments or encourages employees to rotate between functions/department", "A21 You are requested to participate the conference call with RHQ or HQ periodically") and Lateral collaboration effectiveness (e.g., "L11 HQ has formal annual target setting for you to submit in the system with a deadline", "L21 You trust other colleagues know their works and can play their roles")."</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="18" customHeight="1" s="10">
       <c r="A94" t="inlineStr">
@@ -5192,6 +5344,16 @@
           <t>BSMA0091</t>
         </is>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>This paper investigates the impact of boundary-spanning search on innovation performance, with knowledge recombination as the underlying mechanism. It also explores the contingent eﬀect of in house training of employees by considering not invented here syndrome derived from attitude theory, and examines communication investment as a second-order moderator. We test the hypotheses based on a sample of 184 Hong Kong manufacturing ﬁrms. The results show that boundary-spanning search is positively related to innovation performance, which is negatively moderated by in house training of employees. Moreover, communication investment has a suppressing eﬀect on the moderating role of in house training of employees. This paper highlights the not invented here syndrome and its mechanism of attitude theory to examine the contingent eﬀects, providing insights for managers to balance among in house training of employees, communication investment, and boundary-spanning search to enhance innovation performance.</t>
@@ -5217,7 +5379,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P94" s="8" t="n"/>
+      <c r="P94" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the effect of business process digitisation on firm innovation performance, mediated by knowledge search (local and boundary-spanning). The sample consists of 330 firm managers who act as key informants rating firm-level behaviors. The survey items for boundary-spanning search explicitly use the firm-level referent 'In our firm, we...' (e.g., 'In our firm, we search for knowledge from research institutions, universities or colleges'). Therefore, the boundary spanning construct is measured at the firm level rather than the individual employee level, which violates the proxy guardrail and requires exclusion.. Verbatim Evidence: "we delivered 581 initial questionnaires through email and professional survey website... And the respondents were firm managers. ... boundary-spanning search was measured by five items: 'In our firm, we search for knowledge disclosed from patent gazette', 'In our firm, we search for knowledge from technology licensing', 'In our firm, we search for knowledge from research institutions, universities or colleges', 'In our firm, we search for knowledge from industry exhibitions', 'In our firm, we search for knowledge from technical publications and technical conferences'."</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="18" customHeight="1" s="10">
       <c r="A95" t="inlineStr">
@@ -5230,6 +5396,16 @@
           <t>BSMA0092</t>
         </is>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>While there is a burgeoning trend to recognize leadership as an important enabler of new venture development and growth, scant research has explored the performance mechanisms of shared leadership in the entrepreneurial context. Based on the information processing perspective, we propose a moderated mediation model to examine how shared leadership in entrepreneurial teams advance new venture performance by identifying team reflexivity as a pivotal mediator and team boundary spanning as a crucial contingency. The data set from a cross-industry sample of 94 entrepreneurial teams indicated that shared leadership exerts a positive indirect influence on new venture performance via team reflexivity; and team boundary spanning moderates such indirect influence. Finally, how our findings contribute to the entrepreneurship, leadership, team research, and managerial practice are discussed.</t>
@@ -5255,7 +5431,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P95" s="8" t="n"/>
+      <c r="P95" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on entrepreneurial teams (founders) of new ventures, which violates the employee requirement as founders operate independently rather than as embedded organizational employees (Code 2). Additionally, the focal construct is 'Team boundary spanning', measured using survey items with the grammatical subject 'We' (e.g., 'We acquire resources for the team', 'We coordinate activities with external groups'). This indicates respondents were acting as key informants for a macro-level (team) construct, and the main analyses were conducted at the aggregated team level (N=94). This violates the proxy guardrail and the individual-level analysis requirement (Code 3).. Verbatim Evidence: "we randomly identified 200 new ventures from three high-tech industrial parks in eastern China... we explained the purpose of our research to the CEOs of the targeted new ventures... Accordingly, we gathered a list of 163 entrepreneurial teams... Finally, a total of 417 questionnaires from 102 teams were received, among which 376 questionnaires from 94 teams are valid. ... Team boundary spanning was rated by a nine-item scale selected from Yan et al. (2020). These items reflect the degree to which the teams search diverse sources of external information. These items include three dimensions: ambassador activities (e.g., “We acquire resources for the team”); task coordinator activities (e.g., “We coordinate activities with external groups”); and scout activities (e.g., “We scan the environment for marketing ideas/expertise”). ... Given that our model was built at team level, we assessed the viability of individual-level data aggregation. ... Rwg values (Shared leadership = 0.98; Team reflexivity = 0.97; Team boundary spanning = 0.96; New venture performance = 0.97) were greater than the criterion of 0.70."</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="18" customHeight="1" s="10">
       <c r="A96" t="inlineStr">
@@ -5268,6 +5448,16 @@
           <t>BSMA0093</t>
         </is>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>Getting professionals who have been selected and trained to perform individually to work together is a major challenge. The objective of the article is to identify the mechanisms by which a coordinator can ensure a mediation and boundary spanning role to enable the achievement of a project. Adopting a comprehensive approach, this article is based on the case of an innovative hospital project ‘One-Day Diagnosis’ (1DD) – one day instead of several weeks – of hepatobiliary and pancreatic pathologies, for which the professionals had to change their practices. Based on the results of the study, the ﬁndings show that the mediating role of the coordinator consists in making things happen and guiding health care professionals through the innovative pathway until it becomes a routine process. The study contributes to the literature on collaboration and relational coordination by highlighting that the change of practices for collaboration is compatible with personal excellence, by outlining the active role of the boundary spanner in the change of these practices and by demonstrating that the organizational stability of projects based on disembodied procedures is a necessary illusion that requires complementary interindividual relationships and a living leadership.</t>
@@ -5293,7 +5483,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P96" s="8" t="n"/>
+      <c r="P96" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative analysis based on semi-structured interviews with 19 healthcare professionals regarding the role of a coordinator in an innovative care pathway. It does not provide any quantitative data, extractable effect sizes (r), or a correlation matrix, which are required for this meta-analysis.. Verbatim Evidence: "The study that we conducted is based on semi-structured interviews among HCPs who participate directly in the 1DD care pathway or work closely with it. We interviewed 19 HCPs between April and July 2019... We analyzed the qualitative data collected following an abductive approach and performed a two-step coding process involving an interplay between data and theories to light on understanding the observed phenomenon"</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="18" customHeight="1" s="10">
       <c r="A97" t="inlineStr">
@@ -5306,6 +5500,14 @@
           <t>BSMA0094</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>999</v>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>The current study examined the relationships among role stress, proactive personality, employee creativity, and customer-oriented boundary spanning behaviors (COBSBs) for frontline service employees (FSEs). This study collected data from 382 FSEs in international hotels in Taiwan to test the research model. The empirical results revealed that employee creativity was positively affected by proactive personality but negatively affected by role conflict and role ambiguity. FSEs’ creativity positively affects COBSBs, including external representation, internal influence, and service delivery. Internal influence also positively affects service delivery and mediates the relationship between FSEs’ creativity and service delivery.</t>
@@ -5331,7 +5533,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P97" s="8" t="n"/>
+      <c r="P97" s="8" t="inlineStr">
+        <is>
+          <t>The study collects quantitative data from 382 frontline service employees and includes a full correlation matrix. It measures customer-oriented boundary spanning behaviors (COBSBs)—specifically external representation, internal influence, and service delivery—as individual-level behaviors using self-referent items (e.g., 'I tell outsides my hotel is a great place to work'). The dataset provides extractable zero-order correlations for these valid boundary spanning constructs, satisfying all inclusion criteria.. Verbatim Evidence: "For this study, a survey was conducted of 382 FSEs working in international hotels in Taiwan in the Fall of 2019. ... For the measure of COBSB, this research used a 9-item scale from Bettencourt et al. (2005); internal influence, external representation, and service delivery were assessed with 3 items each. ... Table 2 Correlation matrix and average variance extracted. ... External Representation (ER) 'I tell outsides my hotel is a great place to work'."</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="18" customHeight="1" s="10">
       <c r="A98" t="inlineStr">
@@ -5344,6 +5550,14 @@
           <t>BSMA0095</t>
         </is>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>A number of studies have found that the performance of NPD projects greatly depends on the support they get from top management. However, research into why some projects get more support than others has been limited. The present paper takes a political approach to NPD, in which top management support is considered to be a function of a project leader’s ability to influence decision processes through personal relationships. Mobilizing the bridging perspective of social capital, we argue that project leaders need both strong ties to high-ranking others and sparseness in their networks. Vertical strong ties bring direct support and solidarity, resulting in improved access to resources and priority over other projects; sparseness provides exposure to the full range of information and interpretations in the organization, resulting in a more accurate picture of the political landscape and thus enabling the implementation of an appropriate influence strategy. A PLS analysis of a sample of 73 French project leaders involved in NPD projects provided support for our hypotheses. Hence, we contribute to a very recent stream of research showing that the structural and relational dimensions of social capital are complementary.</t>
@@ -5369,7 +5583,11 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="P98" s="8" t="n"/>
+      <c r="P98" s="8" t="inlineStr">
+        <is>
+          <t>The study examines the social capital of NPD project leaders, focusing on their intra-organizational network ties. It utilizes name generators that ask about purposive boundary-spanning actions (e.g., seeking advice and strategic information). The resulting network variables, namely vertical strong ties to top managers and network sparseness (effective size), represent valid structural boundary-spanning behaviors. The sample is composed of 73 individual project leaders, and Appendix 3 provides a full correlation matrix containing the necessary zero-order effect sizes. The study is therefore included.. Verbatim Evidence: "As a project leader, getting your job done on a daily basis often requires obtaining advice and information from others. Over the last six months, who are the key people you have regularly turned to for information and work-related advice to enhance your ability to do your day-to-day work? To address the risk of memory bias inherent to any ego-network study, we used multiple items (Appendix 2), with each extra item requiring the respondent to make an additional recall effort. Due to the focus of H2 and the nature of our dependent variable (TMS), we only considered strong ties connecting the respondent to top managers. Network sparseness. We followed Burt (1992) and Anderson (2008) and chose effective size to measure network sparseness. Appendix 3. Means and standard deviations."</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="18" customHeight="1" s="10">
       <c r="A99" t="inlineStr">
@@ -5382,6 +5600,16 @@
           <t>BSMA0096</t>
         </is>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>Though most acculturation research investigates movement across national boundaries, many other types of boundaries may exist (e.g. rural to urban migration). Rural migrant workers focus on their adaptive and exploratory consumption practices to assemble a liquid identity in China. In essence, this research examines the nature of the transitions that the vast group of Chinese (over 280 million) endures as migrant workers seek to assemble new identities through consumption activities in a liminal space. We find that family relations and government policy hinder migrants’ adjustments to urban life. Thus, we contribute to macromarketing by enriching the theories of liquid identity, boundary work, and acculturation.</t>
@@ -5407,7 +5635,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P99" s="8" t="n"/>
+      <c r="P99" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a qualitative ethnographic study using in-depth interviews with a sample of 36 migrant workers. It does not provide any quantitative data, correlation matrices, or extractable effect sizes required for a meta-analysis. Therefore, it is excluded due to a lack of an effect size of interest.. Verbatim Evidence: ""We took an ethnographic approach (Arnould and Wallendorf 1994) to understand the life domains of rural migrants in urban settings. A sample size of 36 obviously cannot generalize to 280 million migrants, but the purpose of ethnographic research is to increase the depth of understanding rather than generalization." "Long depth interviews (McCracken 1988) were conducted in the informant’s residences, workplaces, and other “hangout” locations." "All of the authors have been rigorously trained in marketing and have conducted extensive work in qualitative research.""</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="18" customHeight="1" s="10">
       <c r="A100" t="inlineStr">
@@ -5420,6 +5652,16 @@
           <t>BSMA0097</t>
         </is>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>This dissertation examined the relationships between organizational characteristics and firms' timing of entry into emerging product markets. This study is an extension of a stream of research on endogenous entry models. Research on this area essentially holds that not all firms have the same entry skills and costs. Therefore, a firm's entry timing decision is attributable to factors internal to the organization. In this dissertation, specific attention is directed toward the effects of top management team (TMT) demography, corporate governance, level of diversification, boundary spanning, past performance, capital structure, and firm size on entry timing. These organizational characteristics have been shown to be critical determinants of timing in the strategic management literature, but, remain almost unexplored in the entry timing research. Thus, through including these organizational characteristics, this study extends the current knowledge which is critical for answering the question: Why do some firms enter emerging product markets earlier/later than others?</t>
@@ -5445,7 +5687,11 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="P100" s="8" t="n"/>
+      <c r="P100" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is at the firm level (N=118 entrants). 'Boundary spanning' is operationalized as a demographic ratio (the proportion of Top Management Team members in functions like marketing and R&amp;D) rather than the interpersonal boundary spanning behavior of individual employees. Because it uses firm-level data to examine organizational entry timing rather than individual-level behavioral data, it violates the level-of-analysis guardrail and must be excluded.. Verbatim Evidence: "The hypotheses relating organizational characteristics to entry timing are tested on data on ten product categories with 118 entrants. [...] Boundary spanning was operationalized by the ratio of TMT members who are more likely to engage boundary spanning activities [to] total TMT size. [...] According to this definition, in this research, boundary spanners included the TMT members whose functions were categorized into marketing, R&amp;D, regional executive, and product division."</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="18" customHeight="1" s="10">
       <c r="A101" t="inlineStr">
@@ -5458,6 +5704,16 @@
           <t>BSMA0098</t>
         </is>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>Organisations experience increased social, political and economic pressure that is evident in the increased pressure that stakeholders place on organisations. Organisations increasingly realise that stakeholders’ values and objectives need to be incorporated into organisational strategy as well as the day-to-day management of the organisation. Organisational success and survival consequently depends on the organisation’s network of relationships, which provide the organisation with otherwise inaccessible resources and a competitive advantage.</t>
@@ -5483,7 +5739,11 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="P101" s="8" t="n"/>
+      <c r="P101" s="8" t="inlineStr">
+        <is>
+          <t>The study measures relationship outcomes (trust, commitment, relational satisfaction, and control mutuality) and goal attainment within strategic alliances. It does not measure any individual-level Boundary Spanning Behavior (BSB) construct, thus lacking an effect size of interest [Code 1]. Furthermore, the unit of analysis is the inter-organizational alliance itself (N=154 alliances), and respondents act as key informants rating their firm's relationship with a partnering organization using macro-level referents (e.g., 'my organisation'), violating the individual-level analysis requirement [Code 3].. Verbatim Evidence: "These findings were obtained through the use of an e-mail survey that obtained cross-sectional data, where 154 alliances were observed (n=154). ... The relationship outcomes (trust, commitment, relational satisfaction and control mutuality) were positively related to perceptions of goal attainment. ... Generally speaking, the partnering organisation and my organisation are both satisfied with the decision-making process. ... Both organisations within the alliance agreed on what the participating organisations can expect from one another."</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="18" customHeight="1" s="10">
       <c r="A102" t="inlineStr">
@@ -5496,6 +5756,14 @@
           <t>BSMA0099</t>
         </is>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>999</v>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>In this dissertation, I develop a conceptual model for how managers' roles as boundary spanners within their organizations affect the perceptions, attitudes, relationships, and performance of their subordinate employees. Drawing on literatures in social networks, status characteristics theory, social identity theory, and resource allocation theory, I suggest that managers' external relationships—the connections that managers make to organization members outside of their subordinate work group—have a material impact on their subordinates' perceptions of their work environment and their managers. These perceptions, I argue, serve as four specific mechanisms in an indirect effects model that connect managers' external relationship to their employees' task performance and work attitudes (eg organizational commitment) and the Leader Member Exchange (LMX) relationships between manager and subordinate. I apply the theoretical model to two salient types of managerial relationships: those with their bosses and those with their horizontal peers.</t>
@@ -5521,7 +5789,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P102" s="8" t="n"/>
+      <c r="P102" s="8" t="inlineStr">
+        <is>
+          <t>The study examines the external relationships (boundary spanning) of front-line managers with their peers and bosses. The construct is measured via advice and friendship in-degree centrality among managerial peers across the organization, which is a valid purposive network measure of intra-organizational Leader BSB. The study provides an extractable zero-order correlation matrix (Table 9, N=83 managers) containing the boundary spanning variables (Advice In-Degree, Friendship In-Degree) and manager characteristics such as Transformational Leadership, Age, and Tenure. It qualifies for inclusion under the Leader BSB and Intra-Org BSB override rules, and the N=managers analysis preserves statistical independence.. Verbatim Evidence: "In this dissertation, I explore managers' external relationships, their boundary spanning roles, and their effects of each on subordinates... I examine two salient types of managers' external relationships, those with their boss and those with their managerial peers. ... Peer networks. At Time 1, all managers completed two sociomatrices. In each case, on the computer screen, I provided the participant a list of all organization members within the hierarchical levels of interest within the organization—the front line managers and the level that included their bosses. ... To construct the advice network, for each name presented to a participant, I instructed him or her to 'please check the box if this person is someone you go to for work related or technical advice.' ... Advice in-degree is the number of a manager's peers who identify him or her as a source of work related advice. ... Table 9: Level 2/Manager Level Variables Means, Standard Deviations and Pearson Correlations ... Sample size is 83 ... Variables: 10 Transformational Leadership, 11 Advice In-Degree, 12 Friendship In-Degree."</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="18" customHeight="1" s="10">
       <c r="A103" t="inlineStr">
@@ -5534,6 +5806,16 @@
           <t>BSMA0100</t>
         </is>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>This study explores whether characteristics of the collaboration structure in software development teams affect development learning rates, with a secondary goal of testing product complexity as a moderator. We develop suitable hypotheses under the theoretical lens of cognitive load theory. The empirical study uses archival data on an ordinary least squares model to find significant associations between collaboration structure, product complexity and the learning rates exhibited by 230 development teams producing open source software. Results show two distinct subgroups of projects: The first subgroup exhibits an average 78% learning rate, and the other subgroup “unlearned”, i.e., productivity deteriorated over time instead of improved. In the learning subgroup, collaboration network density negatively impacted learning, while product complexity interacted with collaboration network centralisation and boundary spanning activity. In the unlearning subgroup, only network density impacted learning rates and no moderating effects were found. Practical implications and future opportunities for research are discussed.</t>
@@ -5559,7 +5841,11 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="P103" s="8" t="n"/>
+      <c r="P103" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study uses archival activity log data from Subversion repositories (measuring whether developers worked on the same file) to capture collaboration, rather than evaluating purposive interpersonal boundary spanning behavior. Furthermore, the unit of analysis is the open source software project (N = 230 teams), and all correlations represent project-level aggregated constructs.. Verbatim Evidence: "The unit of analysis was the OSS project. ... Two developers collaborate when they work on the same file. In the resulting network, developers are the actors and there is a link, or arc, when two developers collaborate. ... Collaboration with other teams is captured by BSA, in a second-order network where OSS projects are the actors and there is a link between two projects if two developers from each of the projects collaborate. The network data were obtained from the activity logs of each project's Subversion, a standard tool that registers each modification made by a team member to any file belonging to the project ... BSA was measured as the developer-based, inter-team degree centrality, normalised by team size ... Note: N = 230"</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="18" customHeight="1" s="10">
       <c r="A104" t="inlineStr">
@@ -5572,6 +5858,16 @@
           <t>BSMA0101</t>
         </is>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>The state of software development performance is far from being exemplar, with a success rate well below that of other industries, and understanding how to improve these projects is not only substantive but urgent. Software development is at most times a collaborative effort, yet we do not understand clearly how different collaboration structures associate with development performance metrics. This paper empirically examines the association between collaboration patterns, project productivity and product quality through a field study of working software open source new product development teams, using archival data from electronic sources related to Open Source Software projects. Collaboration structures are measured using Social Network Analysis and in terms of their network density, network centralization and the level of boundary spanning activity of team members. Productivity and quality are measured using "hard", code-based metrics. Results of regression analyses testing relevant hypotheses suggest that project managers need to strongly encourage internal collaboration, but be wary of allowing team members to participate in multiple projects. The breadth of skills within the team is a tactical asset that may increase the efficient frontier in the quality–productivity trade-off. Results also show that centralized structures associate with higher product quality and development productivity.</t>
@@ -5597,7 +5893,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P104" s="8" t="n"/>
+      <c r="P104" s="8" t="inlineStr">
+        <is>
+          <t>[Code 2 &amp; Code 3] The study analyzes boundary spanning at the team/project level rather than the individual employee level (violating Code 3). The unit of analysis is the open source software project (N=101 projects, N=807 quarterly observations), and boundary spanning activity (BSA) is measured as a team-level aggregate proxy (the proportion of team members who also work on other projects). Furthermore, the sample consists of volunteer developers from SourceForge, rather than traditional organizational employees, which violates the requirement for employee samples (Code 2).. Verbatim Evidence: "OSS has thus generated a particular innovation model, one in which the programs are developed collaboratively by dispersed teams of mostly volunteer individuals who tap into the publicly available source code and cooperate to develop the software... The unit of analysis was the NPD project. OSS project information is hosted in web-based repositories which have been used repeatedly as sources of archival data for empirical studies... The final sample was reduced to 101 projects since only that number had archived full data on all development activities. For the 101 projects, repeated measures were taken on a quarterly basis... with N = 807 data points... Thus, a plausible proxy for a team’s BSA is the number of its team members who also work on some other project, standardized by the number of team members of the focal team. To collect this metric, a script detected which team members worked on more than one project and calculated BSA for each project in the sample for each time period."</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="18" customHeight="1" s="10">
       <c r="A105" t="inlineStr">
@@ -5610,6 +5910,16 @@
           <t>BSMA0102</t>
         </is>
       </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>Technology Transfer Centres (TTCs) have been analyzed in the last few years by focusing on the relationship between a TTC, provider of knowledge-intensive services, and a ﬁrm client-receiver. Less attention has been devoted to a more complex relationship which involves in the dyadic provider-receiver tie a third relevant body, University. We provide both a theoretical and an empirical contribution by studying whether TTCs can bond the academic and industrial system and we deﬁne the activities that make-up this role such as: scanning and selection of R&amp;D opportunities, bridge building, semantic translation of domain speciﬁc knowledge, co-production of new knowledge. The boundary spanning role of TTCs is discussed drawing on different and complementary theoretical perspectives. Moreover, we test research hypotheses on the antecedents of boundary spanning activity from a knowledge-based perspective. We argue that TTC boundary spanners need to leverage on both technical skills and networking competences. Empirical investigation has been carried out with a survey of the TTC population of North East Italy. The research ﬁndings highlight the task coordination activities implied by a boundary spanning role in joint R&amp;D projects and show that the endowment of human capital at individual level and a qualiﬁed social capital at individual and organizational level are the main determinants.</t>
@@ -5635,7 +5945,11 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="P105" s="8" t="n"/>
+      <c r="P105" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the boundary spanning role of Technology Transfer Centres (TTCs) at the organizational level. The unit of analysis is the TTC (N=65), and the boundary spanning construct is operationalized as a dichotomous organizational-level variable (whether the TTC engaged in joint projects with universities). Data was collected from key informants (CEOs, directors) acting as proxies for the organization. Thus, it does not measure individual employee boundary spanning behavior and must be excluded under Code 3 (Firm/org-level analysis).. Verbatim Evidence: ""Empirical investigation has been carried out with a survey of the TTC population of North East Italy." "The second step involved a survey. A structured questionnaire was mailed to each key informant previously identified on the basis of their ability to respond to questions by virtue of her responsibility (chief executive officers, owners, technical or administrative directors of the Centre)." "The response rate was equal to 43.92% for a total of 65 respondent TTCs (39 in the Veneto, 18 in Friuli and 8 in Trentino)." "3.2.1 Boundary spanning role - The survey asked the Centres to indicate the universities they have engaged in joint projects. We coded this information into a dichotomous variable that takes the value 1 if the TTC has indicated at least one university, otherwise the variable takes the value 0.""</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="18" customHeight="1" s="10">
       <c r="A106" t="inlineStr">
@@ -5648,6 +5962,16 @@
           <t>BSMA0103</t>
         </is>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>This paper contributes to open innovation (OI) and boundary spanning literatures by providing a first understanding of industry‐based boundary spanners in university‐industry (U‐I) collaboration through case studies of Chinese multinational corporations (MNCs) and their international OI platforms. Organisational roles created by these platforms within the MNCs and their activity of bridging between organisations are examined. The analysis of 25 in‐depth interviews in two MNCs located in eight countries, along with internal documents, sheds light on U‐I collaboration practices implemented by Chinese MNCs. Two new boundary spanning roles are identified:               Dual Cultural Bridger               – as these OI platforms bridge organisational and national cultural gaps to prevent and solve problems in the collaborative process; and               International Network Enhancer               – as these OI platforms act as trust building and local knowledge listening posts for the MNC’s global network. Managerial and policy implications are provided.</t>
@@ -5673,7 +5997,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P106" s="8" t="n"/>
+      <c r="P106" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative case study based on 25 semi-structured in-depth interviews. It does not provide quantitative survey data, statistical effect sizes (r), or a formal correlation matrix, which are required for this meta-analysis.. Verbatim Evidence: "This paper contributes to open innovation (OI) and boundary spanning literatures by providing a first understanding of industry-based boundary spanners in university-industry (U-I) collaboration through case studies of Chinese multinational corporations (MNCs) and their international OI platforms. [...] The analysis of 25 in-depth interviews in two MNCs located in eight countries, along with internal documents, sheds light on U-I collaboration practices implemented by Chinese MNCs. [...] Given the research questions and the gap in the field, we adopt an exploratory case study approach (Yin, 2017). [...] For the data collection, a total of 25 interviews were carried out in two MNCs. The interviewees include 18 collaboration managers, four senior staff in the two MNCs, three external partners and experts based in Europe, Asia, North America and China. One-hour long semi-structured interviews were conducted in China and seven other countries in 2017, 2018 and 2020."</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="18" customHeight="1" s="10">
       <c r="A107" t="inlineStr">
@@ -5686,6 +6014,16 @@
           <t>BSMA0104</t>
         </is>
       </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>This dissertation examines network ties among organizations, and their impact on innovation. The analyses focus on technical exchanges between firms and their suppliers and customers, both in terms of the factors that lead firms to engage in such boundary-spanning activities, and the relationship between these boundary-spanning activities and new product development.</t>
@@ -5711,7 +6049,11 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="P107" s="8" t="n"/>
+      <c r="P107" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the firm/plant level, utilizing a survey of 973 manufacturing plants. Plant managers acted as key informants, reporting on the interorganizational ties of the plant rather than their own individual boundary spanning behaviors. The survey questions asked whether 'your plant' engaged in technical assistance or collaborative product development with its most important subcontractor or largest customer. This violates the requirement for individual-level interpersonal boundary spanning behavior.. Verbatim Evidence: "The quantitative data I analyze in this research are from a survey conducted in 1991 by Kelley and Watkins on 973 plants that perform a significant amount of metal machining in their production process, what they term the Machined Durable Goods Sector (Kelley, 1991). ... Informants for the 616 focal plants report as to whether they engaged in any of three boundary-spanning activities with their most important machining supplier. ... Table 4.1 Boundary-Spanning Close Ties to the Most Important Subcontractor ... During 1989 or 1990 did you ever: Provide technical assistance to this subcontractor? ... Receive technical assistance from this subcontractor? ... Collaborate in developing new products with this subcontractor?"</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="18" customHeight="1" s="10">
       <c r="A108" t="inlineStr">
@@ -5724,6 +6066,16 @@
           <t>BSMA0105</t>
         </is>
       </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>This cross-sectional study (conducted in April–May 2011) explored associations between partnership functioning synergy and sustainability of innovative programmes in community care. The study sample consisted of 106 professionals (of 244 individuals contacted) participating in 21 partnerships that implemented different innovative community care programmes in Rotterdam, The Netherlands. Partnership functioning was evaluated by assessing leadership, resources administration and efﬁciency. Synergy was considered the proximal outcome of partnership functioning, which, in turn, inﬂuenced the achievement of programme sustainability. On a 5-point scale of increasing sustainability, mean sustainability scores ranged from 1.9 to 4.9. The results of the regression analysis demonstrated that sustainability was positively inﬂuenced by leadership (standardised regression coefﬁcient b = 0.32; P &lt; 0.001) and non-ﬁnancial resources (b = 0.25; P = 0.008). No signiﬁcant relationship was found between administration or efﬁciency and programme sustainability. Partnership synergy acted as a mediator for partnership functioning and signiﬁcantly affected sustainability (b = 0.39; P &lt; 0.001). These ﬁndings suggest that the sustainability of innovative programmes in community care is achieved more readily when synergy is created between partners. Synergy was more likely to emerge with boundaryspanning leaders, who understood and appreciated partners’ different perspectives, and could bridge their diverse cultures and were comfortable sharing ideas, resources and power. In addition, the acknowledgement of and ability to use members’ resources were found to be valuable in engaging partners’ involvement and achieving synergy in community care partnerships.</t>
@@ -5749,7 +6101,11 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="P108" s="8" t="n"/>
+      <c r="P108" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure individual-level boundary spanning behavior. While the term 'boundary-spanning' is used conceptually to describe the type of leadership needed, the actual variable measured is general 'Leadership' (e.g., inspiring or motivating people) using the Partnership Self-Assessment Tool, lacking a quantitative BSB effect size (Code 1). Additionally, the survey items require respondents to evaluate the functioning and synergy of their partnership as a whole (e.g., 'how well the partnership uses the partners’ financial resources', 'evaluating the progress and impact of the partnership'), meaning the respondents act as key informants for a macro-level (partnership/team) construct. This violates the individual-level guardrail (Code 3).. Verbatim Evidence: "The Partnership Self-Assessment Tool: Short version (PSAT-S) was used to measure partnership synergy and dimensions of partnership functioning (Cramm et al. 2011). This instrument contains nine items that measure partnership synergy (e.g. 'By working together, how well are the partners able to identify new and creative ways to solve problems'?) and components that measure five dimensions of partnership functioning: leadership (four items; e.g. inspiring or motivating people and taking responsibility), efficiency (three items; e.g. how well the partnership uses the partners' financial resources), administration and management (four items; e.g. evaluating the progress and impact of the partnership and organising partnership activities, including meetings and projects)..."</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="18" customHeight="1" s="10">
       <c r="A109" t="inlineStr">
@@ -5762,6 +6118,16 @@
           <t>BSMA0106</t>
         </is>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>Previous research demonstrates the dysfunctional consequences of high levels of role stressors (role ambiguity and role conflict) in boundary-spanning positions. These consequences include higher levels of burnout and lower levels of satisfaction and performance. Although marketing researchers have investigated external mechanisms for coping with role stressors, research to date has not investigated the inherent capability of boundary spanners to cope with role stressors. This research examines optimism as an internal characteristic that facilitates coping with role stressors in boundary-spanning positions. The research findings reveal that optimists are able to anticipate and respond proactively to stressors, resulting in less burnout and higher levels of performance and satisfaction.</t>
@@ -5787,7 +6153,11 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="P109" s="8" t="n"/>
+      <c r="P109" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on customer service representatives in 'boundary-spanning positions' but does not measure Boundary Spanning Behavior (BSB) as a quantitative construct. The variables measured are limited to optimism, role ambiguity, role conflict, burnout, job satisfaction, and performance. Because the study only examines employees in boundary-spanning roles without actually measuring their boundary spanning actions, it lacks the target effect size of interest.. Verbatim Evidence: "This research examines optimism as an internal characteristic that facilitates coping with role stressors in boundary-spanning positions... The sample consisted of customer service representatives from a medium-sized, multifaceted service organization in the Midwestern United States. We selected a predominantly service-oriented organization, as the boundary-spanning nature of the participants’ positions increased the likelihood that role stressors (ambiguity and conflict) would be observed... Table 1 Measurement Models of Purified Scales ... Construct/Items ... Optimism (Scheier and Carver 1985) ... Role ambiguity (Rizzo, House, and Lirtzman 1970) ... Role conflict (Rizzo, House, and Lirtzman 1970) ... Burnout (Maslach &amp; Jackson 1981) ... Job satisfaction (Cammann et al. 1983) ... Performance"</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="18" customHeight="1" s="10">
       <c r="A110" t="inlineStr">
@@ -5800,6 +6170,16 @@
           <t>BSMA0107</t>
         </is>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
           <t>In this paper, we highlight the networked context of the professions. In particular, we indicate that neo-classical professionals tend to work across organizational boundaries in project teams, often to meet the needs of clients and the wider society. However, little is known about the resources that professionals draw on to meet immediate, fast paced, client demands in project network organizations (PNOs). We pinpoint how knowledge resources, human, social and organizational capital enable professionals to produce outputs at a fast pace/tempo. Temporality emerged as an unexpected but key issue in our empirical research and we explore this further here. First, we put forward how professional work organization(s) has changed by focusing on the boundaries of organizations, and how this is often temporary and project-driven. Second, we use the speciﬁc lens of knowledge resources which are drawn upon to enable networked working and ask the question: which knowledge resources enable professionals to work at a fast pace within networks? Third, appreciative of the vast literature on temporary and networked organizations in professional work, our focus is beyond a single profession or organization, and hence, we build upon the prior research on PNOs. We do this by drawing on empirical data of a humanitarian aid project networked organization (HN) that upscales across its network at high speed, often within days, to generate funds for humanitarian disasters in order to save lives.</t>
@@ -5825,7 +6205,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P110" s="8" t="n"/>
+      <c r="P110" s="8" t="inlineStr">
+        <is>
+          <t>The study is a purely qualitative case study based on 10 interviews and does not report an extractable zero-order correlation matrix or quantitative effect sizes for boundary spanning behavior.. Verbatim Evidence: "We conducted a qualitative study grounded in pragmatist philosophy and abductive inquiry that compares and iterates between theory and empirical material... The HN case study uses multiple sources of empirical material for analysis. This includes 10 interviews with HN Secretariat staff at various levels and representatives... It would also be valuable to undertake larger-scale studies that include quantitative measures and could provide a base for further comparisons."</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="18" customHeight="1" s="10">
       <c r="A111" t="inlineStr">
@@ -5838,6 +6222,16 @@
           <t>BSMA0108</t>
         </is>
       </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>This research examines the mechanisms through which entrepreneurial orientation (EO) aﬀects ﬁrm performance in an emerging market context. We argue that EO drives ﬁrms to develop the dynamic capabilities of absorptive capacity (ACAP) and boundary-spanning (BS), and that these capabilities enhance ﬁrm performance. Moreover, the eﬀectiveness of these knowledge- and network-based dynamic capabilities in mediating the EOperformance relationship is contingent on the institutional conditions ﬁrms are exposed to. We test our hypotheses using multi-sourced data on Chinese high-tech ﬁrms in business-to-business (B2B) markets. Our results show that ACAP and BS mediate the positive eﬀect of EO on ﬁrm performance, and that as the development of market-supporting institutions improves, the mediating eﬀect of ACAP becomes stronger while that of BS weakens.</t>
@@ -5863,7 +6257,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P111" s="8" t="n"/>
+      <c r="P111" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the firm level (N = 411 SMEs). The boundary-spanning construct is conceptualized as a firm-level dynamic capability and measured by surveying key informants (CTOs/CIOs) to evaluate the firm's social ties with external entities (e.g., government, business partners, research institutes). This violates the level-of-analysis guardrail, as the respondents act as macro-level proxies reporting on firm-level relationships rather than their own individual boundary-spanning behavior.. Verbatim Evidence: "We focused on SMEs in high-tech B2B markets where entrepreneurial activities are arguably more vibrant and critical to the survival and success of firms than they are to firms in consumer markets... A total of 411 firms returned the fully completed questionnaires... Specifically, general firm strategic posture (e.g. EO) and performance were evaluated by the chief executive officer, general manager, or chairperson of the firm who were invited to respond to part one of the survey, whereas information related to firm capabilities (e.g. ACAP and BS) was included in part two for which the chief technology officer or the chief information officer was the desired respondent. ... BS was reflected in managerial activities to establish and utilize social ties with other firms, government officials (Luo, 2003; Park &amp; Luo, 2001; Peng &amp; Luo, 2000), and research institutes such as universities (Gao, Xu, &amp; Yang, 2008). We followed Peng and Luo (2000) by using general questions regarding a firm's social ties with various actors in each category."</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="18" customHeight="1" s="10">
       <c r="A112" t="inlineStr">
@@ -5876,6 +6274,16 @@
           <t>BSMA0109</t>
         </is>
       </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
           <t>Effective work groups engage in external knowledge sharing—the exchange of information, know-how, and feedback with customers, organizational experts, and others outside of the group. This paper argues that the value of external knowledge sharing increases when work groups are more structurally diverse. A structurally diverse work group is one in which the members, by virtue of their different organizational affiliations, roles, or positions, can expose the group to unique sources of knowledge. It is hypothesized that if members of structurally diverse work groups engage in external knowledge sharing, their performance will improve because of this active exchange of knowledge through unique external sources. A field study of 182 work groups in a Fortune 500 telecommunications firm operationalizes structural diversity as member differences in geographic locations, functional assignments, reporting managers, and business units, as indicated by corporate database records. External knowledge sharing was measured with group member surveys and performance was assessed using senior executive ratings. Ordered logit analyses showed that external knowledge sharing was more strongly associated with performance when work groups were more structurally diverse. Implications for theory and practice around the integration of work groups and social networks are addressed.</t>
@@ -5901,7 +6309,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="P112" s="8" t="n"/>
+      <c r="P112" s="8" t="inlineStr">
+        <is>
+          <t>The study examines external knowledge sharing among work groups, but the data is aggregated to the team level. The correlation matrix reports relationships at the work group level (N = 182 work groups), not at the individual employee level, violating the individual-level analysis requirement.. Verbatim Evidence: "Data used to test the above hypotheses (see Figure 1 for a complete model) come from a sample of 182 work groups and include (1) corporate database records, (2) 20 group interviews, (3) 182 surveys of group leaders, (4) 957 surveys of group members, and (5) senior executives' ratings of group performance. ... There was at least one respondent from each work group, and responses were averaged across members and applied to the entire group. ... Table 2 Correlation Matrix with Main Study Variables (N = 182 Work Groups)"</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="18" customHeight="1" s="10">
       <c r="A113" t="inlineStr">
@@ -5914,6 +6326,16 @@
           <t>BSMA0110</t>
         </is>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>Our study responds to a call for research to integrate institutional, organizational and individual levels of analysis in examining the implications for work and employment relations of new organizational forms. We empirically examine the implementation of network forms of genetics healthcare delivery that cross organizational and professional boundaries. We highlight that less powerful professional groups may find difficulty in enacting boundary-spanning roles associated with new organizational forms. This is due, first, to inconsistency of government policy, which fragments organizations. Second, professional institutions sustain professional hierarchy and power differentials.</t>
@@ -5939,7 +6361,11 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="P113" s="8" t="n"/>
+      <c r="P113" s="8" t="inlineStr">
+        <is>
+          <t>The study employs a qualitative case study design based on 40 interviews across four cases to explore work and employment relations challenges associated with new organizational forms in healthcare. It does not provide any quantitative survey data, formal correlation matrices, or extractable zero-order effect sizes (r) required for the meta-analysis.. Verbatim Evidence: "We took a case study approach designed to engender analysis of work and employment relations challenges associated with the implementation of new organizational forms... Within this article, we present analysis of the four in-depth cases, where delivery of genetics services crossed the regional genetics centre and acute hospital boundary: 'Carcity'; 'Unicity'; 'Shipcity'; 'Bicity'... In total, we carried out 40 interviews across four cases... Rather than coding the interviews through software, such as QSR's NVivo package, so that data remained contextualized we treated the interviews holistically as narratives."</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="18" customHeight="1" s="10">
       <c r="A114" t="inlineStr">
@@ -5952,6 +6378,16 @@
           <t>BSMA0111</t>
         </is>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
           <t>Purpose – This paper aims to test the inﬂuence of external information search (EIS) on knowledge elaboration and group cognitive complexity (GCC) under the moderating effect of absorptive capacity (AC is indicated by prior knowledge base and gender diversity).</t>
@@ -5977,7 +6413,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P114" s="8" t="n"/>
+      <c r="P114" s="8" t="inlineStr">
+        <is>
+          <t>The paper conducts three studies. Study 1 uses an organizational sample, but all measures including external information search are aggregated to the team level (N=65 groups), violating the individual-level analysis requirement. Studies 2 and 3 use student samples enrolled in a bachelor course and also perform analysis at the group level (N=65 and N=37 groups respectively). Because the paper violates both the individual-level constraint (Code 3) and the organizational employee sample constraint (Code 2) across its studies, it is excluded under Code 5 [Code 2 &amp; Code 3].. Verbatim Evidence: "Study 1: 'Because groups are the level of analysis, individual scores were aggregated at the group level and the results of the aggregation statistics supported this aggregation...' Study 2: 'A sample of 268 students (104 women) participated in the study. They were enrolled in a bachelor course at a large Dutch university... organized in 65 learning groups...' Study 3: 'A total of 172 students (83 women) organized in 37 groups enrolled in a course at a Dutch university participated in the study...'"</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="18" customHeight="1" s="10">
       <c r="A115" t="inlineStr">
@@ -5990,6 +6430,16 @@
           <t>BSMA0112</t>
         </is>
       </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>Purpose – This study aims to analyze the relationship between telework and teleworkers’ characteristics and the work-nonwork conflict (WNWC) in the Brazilian context, investigating time spent in eight nonwork dimensions and the more affected dimensions.</t>
@@ -6015,7 +6465,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P115" s="8" t="n"/>
+      <c r="P115" s="8" t="inlineStr">
+        <is>
+          <t>The paper investigates 'work-nonwork boundary management' and 'work-nonwork conflict' (WNWC) in the context of telework during the COVID-19 pandemic. It focuses on the spatial and temporal boundaries between work and personal life (e.g., family, leisure, health, household management) rather than inter-organizational or intra-organizational boundary spanning behavior (BSB). Therefore, it is excluded under the Work-Family Boundary Management rule.. Verbatim Evidence: "This study aims to analyze the relationship between telework and teleworkers’ characteristics and the work-nonwork conflict (WNWC) in the Brazilian context, investigating time spent in eight nonwork dimensions and the more affected dimensions. [...] The spatial and temporal boundaries between work and nonwork were eliminated for those who could telework at home. [...] According to the boundary theory, people prefer to exercise their roles considering some point between total integration (no distinction between what belongs to work or family or when or where each role manifests itself) and total segmentation (the two dimensions as separate worlds, that occur in distinct time and space) (Nippert-Eng, 1996)."</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="18" customHeight="1" s="10">
       <c r="A116" t="inlineStr">
@@ -6028,6 +6482,16 @@
           <t>BSMA0113</t>
         </is>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
           <t>The perspectives of transaction cost economics and the resource-based view of the firm have been used extensively to understand the implications of outsourcing. However, transaction cost economics does not explain how a firm will evolve as it progressively outsources internal functions, and the resource-based view does not operationalize the unspecified competences that will be required over time. On the other hand, the lens of paradox highlights the increased expediency and complexity that outsourcing firms are expected to encounter. In this paper, paradoxes comparing operational expediency gains to increases in management, learning and strategic complexity are discussed, leading to the proposal that often unintended replacement behaviors manifest as extensive boundary spanning and new firm-level competencies are necessary to manage these paradoxes and maintain competitive advantage. In extremum tests of these propositions are provided to demonstrate that the complexity of outsourcing intangibles is informed by a lens of paradox.</t>
@@ -6053,7 +6517,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P116" s="8" t="n"/>
+      <c r="P116" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a conceptual/theoretical article that constructs theory and offers propositions regarding the behavioral consequences of outsourcing. It relies on hypothetical examples rather than primary empirical data, and does not provide any quantitative effect sizes or correlation matrices.. Verbatim Evidence: "The purpose of this article is to use the perspective of paradox to construct theory on the manner in which firms’ behaviors evolve as a result of their outsourcing decisions... Rather than argue these propositions of replacement theory anecdotally, one can test them in extremum... Consider the following hypothetical example of a firm moving from full internal integration to full disintegration... The empirical testing of these propositions is suggested for future research."</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="18" customHeight="1" s="10">
       <c r="A117" t="inlineStr">
@@ -6066,6 +6534,16 @@
           <t>BSMA0114</t>
         </is>
       </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>The aim of this research is to empirically investigate the relationships among the three vital knowledge management processes of acquisition, integration and application, and their effects on organisational innovation in the pharmaceutical manufacturing industry in Jordan; a knowledge-intensive business service (KIBS) sector. Structural equation modelling findings show an excellent fit among all these processes and innovation, with positive and significant relationships. Moreover, knowledge integration and knowledge application emerged as having strong and significant mediation effects upon the relationship between knowledge acquisition and innovation. As such, an organisation’s innovation efforts would significantly benefit from the synergistic effects of properly integrating and applying externally acquired knowledge. The findings make a valuable contribution to pharmaceutical knowledge management and innovation literature, especially in an era of open innovation. Pharmaceutical companies are advised to focus on developing proficient assimilation and application capabilities in order for acquired knowledge to have notable effects on their innovation performance.</t>
@@ -6091,7 +6569,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P117" s="8" t="n"/>
+      <c r="P117" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the impact of knowledge management processes (acquisition, integration, application) on organizational innovation. Although the survey respondents are individual employees (managers and knowledge workers), they act as key informants reporting on firm-level phenomena. This is evident from the grammatical referents in the survey items, which ask about 'The organisation', 'Our organisation', and 'My organisation' (e.g., 'The organisation accesses, collects, and acquires new ideas and information from diverse external sources'). Consequently, the knowledge acquisition construct represents a macro-level organizational activity rather than individual-level interpersonal boundary spanning behavior, violating the proxy and level-of-analysis guardrails (Code 3). Furthermore, the paper relies entirely on SEM path coefficients and does not provide a zero-order correlation matrix, failing the data extractability requirement (Code 1).. Verbatim Evidence: "The unit of analysis consisted of knowledge workers who held managerial positions in each of the participating companies... multiple respondents at different managerial levels within each pharmaceutical manufacturing company were targeted by the survey since knowledge management functions, in terms of knowledge acquisition, integration, sharing, dissemination, and application, are undertaken collectively through 'organisation-wide' efforts rather than being the sole or individual responsibility of a specific work unit or person... The same rationale applies in the case of organisational innovation... Table 1: KA1: The organisation is keen on facilitating knowledge flows between itself and the external business environment... KA3: The organisation accesses, collects, and acquires new ideas and information from diverse external sources in its business environment... KAP1: My organisation modifies its products, strategies, and behaviours in the light of its past experience"</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="18" customHeight="1" s="10">
       <c r="A118" t="inlineStr">
@@ -6104,6 +6586,16 @@
           <t>BSMA0115</t>
         </is>
       </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
           <t>The “variance hypothesis” predicts that external search breadth leads to innovation outcomes, but people have limited attention for search and cultivating breadth consumes attention. How does individuals' search breadth affect innovation outcomes? How does individuals' allocation of attention affect the efficacy of search breadth? We matched survey data with complete patent records, to examine the search behaviors of elite boundary spanners at                 IBM                 . Surprisingly, individuals who allocated attention to people inside the firm were more innovative. Individuals with high external search breadth were more innovative only when they allocated more attention to those sources. Our research identifies limits to the “variance hypothesis” and reveals two successful approaches to innovation search: “cosmopolitans” who cultivate and attend to external people and “locals” who draw upon internal people                              . © 2014 The Authors.               Strategic Management Journal               published by John Wiley &amp; Sons Ltd.</t>
@@ -6129,7 +6621,11 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="P118" s="8" t="n"/>
+      <c r="P118" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates 'external search breadth' and 'attention to external people' among elite engineers at IBM. However, the operationalization of these constructs lacks the purposive action required for valid Boundary Spanning Behavior (BSB). 'Attention to external people' is measured as the relative percentage of time spent interacting with individuals outside the organization, which explicitly violates Screening Rule 6 (excluding measures of percentage of time spent with outsiders without specifying a purposive action type). Furthermore, 'External search breadth' merely counts the number of different types of external parties the individual 'interacted with', capturing mere communication breadth without specifying a purposive boundary-spanning action such as seeking knowledge, coordinating tasks, or representing the firm. Consequently, the study lacks an extractable effect size for a valid BSB construct.. Verbatim Evidence: "External search breadth. ... we measured external search breadth as the number of different types of external parties an individual interacted with. Respondents were provided with a list of 11 different types of partners that could constitute their external network ... and were asked which ones they interacted with. ... Attention to external people. To capture the extent to which an individual allocated time with people inside versus outside the firm, we asked respondents to 'Please distribute 100 points to indicate the relative amount of time, during your typical workday, that you interact with individuals from each category listed below': (1) within your organization (e.g., individuals in your office, organizational members, etc.), (2) outside your organization (e.g., customers, suppliers, alliance partners, governmental contacts, university contacts, investors, etc.)."</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="18" customHeight="1" s="10">
       <c r="A119" t="inlineStr">
@@ -6142,6 +6638,14 @@
           <t>BSMA0116</t>
         </is>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>999</v>
+      </c>
       <c r="G119" t="inlineStr">
         <is>
           <t>THErelationships between age, aspects of tenure, locus of control, job involvement, and boundary spanning behaviour (B.S.B.) were examined using path analysis for 281 scientists and engineers. It was found that locus of control and age were significant determinants of job involvement. It was also shown that locus of control and job involvement were significant determinants of B.S.B. These findings are discussed relative to previous research on locus of control, job involvement, and B.S.B. Finally, new research designs are advocated which incorporate task characteristics, role dynamics constructs, and environmental uncertainty as determinants of B.S.B.</t>
@@ -6167,7 +6671,11 @@
           <t>1978</t>
         </is>
       </c>
-      <c r="P119" s="8" t="n"/>
+      <c r="P119" s="8" t="inlineStr">
+        <is>
+          <t>The study empirically investigates individual-level boundary spanning behavior among a sample of 281 scientists and engineers. It operationalizes BSB as obtaining information from external sources (a valid purposive action) and provides an extractable zero-order correlation matrix including BSB and other individual-level variables (age, tenure, locus of control, job involvement). Thus, it satisfies all inclusion criteria.. Verbatim Evidence: "THE relationships between age, aspects of tenure, locus of control, job involvement, and boundary spanning behaviour (B.S.B.) were examined using path analysis for 281 scientists and engineers. The study was conducted in 15 public and private research organizations located in the Western United States. Two hundred and eighty-one scientists and engineers participated in the study. Forty-five of the respondents were project leaders while the remainder were team members. Boundary Spanning Behaviour (B.S.B.) was measured with a four-item instrument developed by Keller, et al. The questions in the instrument deal with obtaining information from sources outside the organization (both written and fellow professionals). Table II presents the zero-order correlations among the study variables."</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="18" customHeight="1" s="10">
       <c r="A120" t="inlineStr">
@@ -6180,6 +6688,16 @@
           <t>BSMA0117</t>
         </is>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr">
         <is>
           <t>Customer contact personnel (CCP) are recognised as a key determinant in the attainment of customer satisfaction and service quality. While they are readily acknowledged as often representing the service in the eyes of the customer, almost no attention has been given to researching the determinants of service behaviour among CCP, from the perspective of CCP.</t>
@@ -6205,7 +6723,11 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="P120" s="8" t="n"/>
+      <c r="P120" s="8" t="inlineStr">
+        <is>
+          <t>The study surveys airline flight attendants (customer contact personnel) to investigate the antecedents of service behaviour. Although the author notes that flight attendants occupy a 'boundary spanning role', the actual variables measured in the study are Service Behaviour (coping tactics such as customer action, artful endeavours, and customer annoyance), Customer Orientation (using an abridged SOCO scale), Role Conflict, Perceived Recognition Status, Perceived Self-Status, and Uniform Perceptions. None of these constructs capture purposive Boundary Spanning Behavior (e.g., external representation, information scouting, or cross-boundary coordination). Because the study focuses entirely on service and coping behaviours and customer orientation rather than structural or active boundary spanning, it lacks a valid effect size for the meta-analysis.. Verbatim Evidence: "Table 6-11 - Pairwise Correlations (Pearson r) of Constructs to Evaluate Construct Validity: Customer Orient'n, Self-Status, Role Conflict, Recognt'n Status, Uniform Percept'ns, Service Behav'r. ... Service Behaviour is defined as: The behaviors CCP engage as a response to role conflict that entails endeavoring to fulfil demands placed upon them, or seeking to negotiate and satisfy lesser demands or avoiding demands placed upon them (Weatherly and Tansik, 1993a). ... The customer orientation scale (COS) used in this study is an abridged form of the SOCO (Saxe and Weitz, 1982) scale. ... The variables under investigation in the conceptual model as antecedents of service behaviour among CCP have been selected on the basis of ... relative status, role conflict, customer orientation and uniform perceptions."</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="18" customHeight="1" s="10">
       <c r="A121" t="inlineStr">
@@ -6218,6 +6740,16 @@
           <t>BSMA0118</t>
         </is>
       </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
           <t>This study investigated coordinated action in multiteam systems employing 233 correspondent systems, comprising 3 highly specialized 6-person teams, that were engaged in an exercise that was simultaneously “laboratory-like” and “field-like.” It enriches multiteam system theory through the combination of theoretical perspectives from the team and the large organization literatures, underscores the differential impact of large size and modular organization by specialization, and demonstrates that conventional wisdom regarding effective coordination in traditional teams and large organizations does not always transfer to multiteam systems. We empirically show that coordination enacted across team boundaries at the component team level can be detrimental to performance and that coordinated actions enacted by component team boundary spanners and system leadership positively impact system performance only when these actions are centered around the component team most critical to addressing the demands of the task environment.</t>
@@ -6243,7 +6775,11 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="P121" s="8" t="n"/>
+      <c r="P121" s="8" t="inlineStr">
+        <is>
+          <t>The study measures simulated coordination behaviors via objective indices (e.g., asset deployment frequency) within a simulator game, lacking actual job-related boundary spanning behavior effect sizes (Code 1). Furthermore, the data and correlation matrix are analyzed at the multiteam system level (N = 233 14-member systems), explicitly violating the individual-level analysis requirement (Code 3).. Verbatim Evidence: "The sample consisted of 3,262 U.S. Air Force captains with 5–9 years of experience in a broad range of professional disciplines. The participants were assigned to 233 fourteen-person teams using criteria designed to ensure that team composition was equivalent on factors including experience, job function, gender, and age... Horizontal coordinated action within the four-person point team was operationalized in terms of the frequency with which two or more members deployed their respective (and task-unique) assets (RPAs) to the same location during the same round... Table 1 Descriptive Statistics and Correlations... Note. N = 233. 14-member multiteam systems."</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="18" customHeight="1" s="10">
       <c r="A122" t="inlineStr">
@@ -6256,6 +6792,16 @@
           <t>BSMA0119</t>
         </is>
       </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
           <t>Purpose – This study aims to explore how and why employees perceive technology-mediated interruptions differently and the role of sociocultural factors in this process using sociomaterial analysis. Design/methodology/approach – Data were gathered from 34 Sri Lankan knowledge workers using a series of workshop-based activities. The concept of sociomateriality is employed to understand how sociocultural elements are entangled with technology in work-life boundary experiences.</t>
@@ -6281,7 +6827,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P122" s="8" t="n"/>
+      <c r="P122" s="8" t="inlineStr">
+        <is>
+          <t>The study employs a qualitative research methodology to explore perceptions of technology-mediated work-life boundaries using vignettes and open-ended questionnaires. It focuses on work-life boundary management, which is an invalid construct for this meta-analysis, rather than inter- or intra-organizational boundary spanning behavior. Furthermore, as a qualitative study relying on thematic analysis, it does not provide any quantitative survey data, formal correlation matrices, or extractable effect sizes (r).. Verbatim Evidence: "With the intention of exploring in detail the cultural and gender norms around the work-life boundary process, the study employs qualitative research methodology under the interpretive paradigm. In collecting data, we employed a series of activities within a workshop to collect data for the study at hand. [...] Two open-ended questionnaires (i.e. handouts) were used to collect qualitative data regarding participants’ perceptions of work-life boundaries and ICTs (Thoring et al., 2020). [...] This paper followed the inductive thematic analysis approach discussed by Braun and Clarke (2006) to analyse the textual data collected."</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="18" customHeight="1" s="10">
       <c r="A123" t="inlineStr">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -6844,6 +6844,16 @@
           <t>BSMA0120</t>
         </is>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
           <t>In this article, the authors examine antecedents and consequences of the service climate in boundary-spanning self-managing teams (SMTs) that deliver financial services. Using data from members of 61 SMTs and their customers, the authors show a differential impact of the SMT service climate on various marketing performance measures. Furthermore, they obtain support for independent group-level effects of intrateam support and team member flexibility on employee perceptions of the SMT service climate. Both effects are persistent over time and demonstrate that collective perceptions in the SMT have incremental value in the explanation of the service climate.</t>
@@ -6869,7 +6879,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="P123" s="8" t="n"/>
+      <c r="P123" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study uses the term 'boundary-spanning' to describe the structural context of the self-managing teams (i.e., frontline service teams interacting with customers) rather than measuring boundary spanning behavior as an individual-level action. Variables such as 'interteam support' capture perceived support received from other teams, not purposive boundary spanning behavior by the individual employee (Code 1). Additionally, the survey items violate the proxy guardrail by using collective referents such as 'we' and 'our team' (e.g., 'Our team is continually working...', 'Other teams act in a responsive manner...'), meaning individuals are rating team-level constructs (Code 3).. Verbatim Evidence: "Table 2: Measures and Measurement Criteria / SMT Service Climate: '1. Our team is continually working to improve the quality of service we provide to our customers.' / Interteam Support: '1. Other teams act in a responsive manner when we forward customer complaints. 2. The knowledge of other teams assists us in serving customers. 3. The quality of service delivered by other teams to our team is good.' / Intrateam Support: '1. In our team we help each other in serving the customer.'"</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="18" customHeight="1" s="10">
       <c r="A124" t="inlineStr">
@@ -6882,6 +6896,14 @@
           <t>BSMA0121</t>
         </is>
       </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>999</v>
+      </c>
       <c r="G124" t="inlineStr">
         <is>
           <t>Background: Registered nurses play a key role in hospitals, as they have an important impact on the quality of the services delivered. For nurses to perform at their best, they need organizational, leader, and coworker support. To date, few studies have explored the link between nurses_ perceived support, affective organizational commitment, and boundary-spanning behaviors. Methods: This cross-sectional research used a questionnaire survey to explore the hypothesized relationships in a sample of 273 nurses from a hospital in Belgium. Structural equation modeling was used for statistical analysis of the mediation model. Results: One hundred forty-seven (53.5%) nurses responded to the survey. Perceived support from the organization, supervisors, and coworkers positively influences nurses_ boundary-spanning behaviors. Affective organizational commitment was found to mediate the positive relationship between perceived organization support, perceived coworker support, and boundary-spanning behaviors. Perceived supervisor support and boundary-spanning behaviors showed a direct relationship not mediated by affective organizational commitment. Conclusions: Perceived support has an important influence on the boundary-spanning behavior of nurses. This study emphasizes the importance on how support exerts an influence on boundary-spanning behavior and</t>
@@ -6907,7 +6929,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P124" s="8" t="n"/>
+      <c r="P124" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates customer-oriented boundary-spanning behaviors (external representation, internal influence, service delivery) among individual registered nurses. The sample comprises valid organizational employees (N = 147-151), and the unit of analysis is the individual. The construct is measured using the Bettencourt and Brown (2003) scale, which utilizes 'I' referent items (e.g., 'I tell outsiders...'), avoiding the macro-level proxy guardrail. The paper provides a formal zero-order correlation matrix (Table 1) with extractable effect sizes, thereby fully qualifying for inclusion.. Verbatim Evidence: "The sample consisted of 147 valid responses, yielding a response rate of 53.5%... Here, we concentrate on three distinct forms of nurses’ boundary-spanning behavior: service delivery (similar to key quality service elements), external representation (as an external advocate of the company), and internal influence (as an internal champion for delivering service excellence) (Bettencourt, Brown, &amp; Mackenzie, 2005; Trybou &amp; Gemmel, 2016)... The questionnaire of Bettencourt and Brown (2003) was used to measure boundary-spanning behavior. All three outcome variables were measured with three items each. A sample question for external representation is 'I tell outsiders this is a great place to work'... A sample question for internal influence is 'I give constructive proposals for improving the services'... An example question for service delivery is 'I am courteous and respectful towards patients, no matter the circumstances'... Table 1 Cronbach's alpha and correlations"</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="18" customHeight="1" s="10">
       <c r="A125" t="inlineStr">
@@ -6920,6 +6946,16 @@
           <t>BSMA0122</t>
         </is>
       </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>Multiteam systems (i.e., teams of teams) are frequently used to deal with complex and demanding challenges that require several teams’ joint efforts. However, achieving effective horizontal coordination across component teams in these systems remains difficult. Using insights from organizational behavior research, we argue that horizontal coordination between component teams can benefit if a multiteam system is composed of generalist members who are acquainted with the multiple functions present in the overall system (i.e., high intrapersonal functional diversity [IFD]). At the same time, however, such IFD may have detrimental side effects because generalists’ broad focus may distract them from high-impact, specialized activities (i.e., aspirational behavior). Building on insights from organization theory, we propose that coordination across a multiteam system’s hierarchical layers (i.e., vertical coordinated action between a team tasked with system-wide integration and task-specialized component teams) is critical for reaping IFD’s benefits while avoiding its costs. These notions are supported in a sample of 236 14-person multiteam systems engaged in a realistic decision-making simulation. Our findings illustrate how combining insights from organizational behavior and organization theory can advance academic knowledge on multiteam systems and offer practical solutions for managing such systems.</t>
@@ -6945,7 +6981,11 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="P125" s="8" t="n"/>
+      <c r="P125" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the multiteam system level rather than the individual employee level. The sample size for the analysis is N = 236 multiteam systems, and all constructs (including horizontal coordination and vertical coordinated action) are conceptualized and measured as system-level properties. The reported correlation matrix represents system-level aggregated constructs, which violates the requirement for individual-level statistical independence.. Verbatim Evidence: "We tested our hypotheses using a sample comprised of 3,304 United States Air Force officers... As part of the course, participants were assigned to 236 fourteen-person multiteam systems... Consistent with previous research using the LDS, all constructs in this study were conceptualized as configural unit properties (Kozlowski &amp; Klein, 2000) at the multiteam system level of analysis. ... We used hierarchical linear regressions at the multiteam system level to test the interactive relationships of IFD and vertical coordinated action with the mediators... Table 1... Note: n = 236 multiteam systems."</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="18" customHeight="1" s="10">
       <c r="A126" t="inlineStr">
@@ -6958,6 +6998,14 @@
           <t>BSMA0123</t>
         </is>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>999</v>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
           <t>This manuscript investigates the role of individual team members' breadth of functional experience for their interteam coordination behavior. Integrating personal construct and social identity theories, we examine interpersonal cognitive complexity as a mediating variable and organizational identification as a moderator. We test our hypotheses across two independent field studies, comprising an international peace support training mission (Study 1) and a municipality administration (Study 2). Corroborating our predictions, interpersonal cognitive complexity appeared as a conditional mediating variable that can translate an individual's breadth of functional experience into interteam coordination. The strength and direction of this indirect relationship, however, depended on the individual's identification with the organization as a whole. Moreover, on the team level of analysis, we found members' overall interteam coordination to positively relate with team performance in Study 2. All in all, this paper advances new knowledge on the antecedents, mechanisms, contingency factors, and team-level consequences of members' boundary spanning.</t>
@@ -6983,7 +7031,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P126" s="8" t="n"/>
+      <c r="P126" s="8" t="inlineStr">
+        <is>
+          <t>The study measures individual-level interteam coordination (a form of intra-organizational boundary spanning behavior) and provides zero-order correlations with other individual-level variables such as breadth of functional experience, cognitive complexity, and organizational identification across two independent employee samples (Study 1: professionals in a coalition training exercise; Study 2: municipal office employees). The construct captures purposive boundary-spanning actions (e.g., aligning work activities, negotiating joint efforts with external teams) via an ego-network type measure, which is explicitly permitted under the Intra-Organizational BSB and Network-Based BSB override rules. Statistical independence is preserved as the unit of analysis is the individual employee, not the team or dyad.. Verbatim Evidence: "Study 1: Targeted study participants were all 172 members of the exercise’s coalition headquarters... Sixty-nine participants, distributed across 22 teams, returned complete and usable surveys... Interteam coordination. We provided respondents with a list of the teams present during the exercise and asked them to select all teams with whose members they had regularly coordinated activities... For greater clarity, we provided examples of relevant behaviors (e.g., aligning work activities, negotiating joint efforts, resolving joint problems; Ancona &amp; Caldwell, 1992)... Study 2: The second study took place in a Dutch municipality administration... 121 (distributed over 36 of the organization’s 40 teams) provided complete responses... Interteam coordination. We used a similar network-type measure as in Study 1 to quantify individuals’ interteam coordination behavior... we asked respondents to identify the specific individuals from other teams with whom they regularly coordinated when 'preparing policy advice for management or the city council, completing joint projects, participating in task groups, and/or executing day-to-day tasks'... Table 1: Means, Standard Deviations, and Correlations (Individual-level Variables, Studies 1 and 2)"</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="18" customHeight="1" s="10">
       <c r="A127" t="inlineStr">
@@ -6996,6 +7048,14 @@
           <t>BSMA0124</t>
         </is>
       </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>999</v>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
           <t>Data from 409 members of 45 new product teams in five high-technology conpanies indicate the existence of four sets of boundary management activities which can be labeled Ambassador, Task Coordinator,Scout, and Guard. These activities are related to the frequency, type, and destination of communications between team members and others. This paper describes these activities and examines the irrpact of individual and environmental variables on the frequency in vAiich individual team members engage in them.</t>
@@ -7022,7 +7082,11 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="P127" s="8" t="n"/>
+      <c r="P127" s="8" t="inlineStr">
+        <is>
+          <t>The study provides a quantitative correlation matrix (N=409) at the individual level, containing boundary spanning behavior factors (Ambassador, Task Coordinator, Scout, Guard) and individual characteristics (e.g., leadership role, years in company, number of teams) among members of new product teams. The boundary activities involve purposive cross-boundary interactions (e.g., cross-functional coordination and scanning), meeting the inclusion criteria for intra-organizational boundary spanning behavior.. Verbatim Evidence: "Data from 409 members of 45 new product teams in five high-technology companies indicate the existence of four sets of boundary management activities which can be labeled Ambassador, Task Coordinator, Scout, and Guard. ... Questionnaires were distributed to new product team members and leaders of forty-five teams in five corporations in the computer, analytic instrumentation, and photographic industries. Of the 450 questionnaires distributed, a total of 409 questionnaires were returned, yielding a response rate of approximately 89 percent. ... TABLE 2: CORRELATION MATRIX OF BOUNDARY FACTOR SCORES, TASK ENVIRONMENT VARIABLES; AND INDIVIDUAL CHARACTERISTICS N=409"</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="18" customHeight="1" s="10">
       <c r="A128" t="inlineStr">
@@ -7033,6 +7097,16 @@
       <c r="B128" t="inlineStr">
         <is>
           <t>BSMA0125</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7063,7 +7137,11 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="P128" s="8" t="n"/>
+      <c r="P128" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes research alliances at the inter-organizational level (N = 109 alliances) using top management team members (e.g., CEOs, VPs) as key informants to report on their firm's alliances, violating the individual-level analysis requirement [Code 3]. Furthermore, the independent variable closest to boundary spanning is 'Frequency of contact', which measures mere communication frequency without specifying any purposive boundary-spanning action, thus lacking construct validity [Code 1].. Verbatim Evidence: "The foci of this study are research alliances. [...] The top management team was chosen as the target based on information received during the preliminary interviews with industry executives. Therefore, a member of the top management team became the target of the interviews. In particular, the CEO, VP of Business Development, or VP of Research were targeted. [...] Each firm provided information on up to three distinct alliances. [...] Personal interviews were used to rate 97 alliances, and phone interviews were used to rate 12 alliances. [...] 2. How frequently are the senior executives from your firm and the partner in contact? 1. weekly 2. monthly 3. quarterly 4. yearly 5. never. 3. How frequently does contact between your firm and the partner firm take place at the operational level? 1. weekly 2. monthly 3. quarterly 4. yearly 5. never"</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="18" customHeight="1" s="10">
       <c r="A129" t="inlineStr">
@@ -7076,6 +7154,16 @@
           <t>BSMA0126</t>
         </is>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr">
         <is>
           <t>Leader-Member Exchange theory proposes both the salesperson and manager make contributions to their working relationship. Effective leadership is dependent upon developing a high quality relationship. This study tests the proposals of Leader-Member Exchange by examining the exchange of manager contributions (allowing the salesperson more operating freedom or latitude) and those of the salesperson. While the receipt of managerial latitude has a direct effect on the salesperson's evaluation of the working relationship, the salesperson's contributions also play a part. The manager allows more latitude to salespeople who are seen as more competent and loyal. These exchanges latitude for competency and loyalty) and the quality of the salesperson-manager relationship may be especially important when the sales task requires adaptive selling behaviors.</t>
@@ -7101,7 +7189,11 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="P129" s="8" t="n"/>
+      <c r="P129" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on Leader-Member Exchange (LMX) in the context of salesperson-manager dyads, measuring managerial latitude, salesperson loyalty, competence, LMX quality, performance, and adaptive selling behavior. None of these constructs capture interpersonal boundary spanning behavior (BSB). According to Screening Rule 6, adaptive selling (measured using the Spiro &amp; Weitz scale) is a sales tactic/flexibility measure and is distinct from structural BSB (such as information scouting or task coordination). As a result, the study lacks any relevant effect size for BSB.. Verbatim Evidence: "The salesperson responded to sixteen items assessing the degree to which they engage in adaptive selling behaviors (Spiro and Weitz 1990). This scale has been tested on both homogeneous samples... and has demonstrated internal reliability between .87 and .85... Sample Items: Each customer requires a unique approach. I am very flexible in the selling approach I use. I use a set sales approach. (Reverse score)... Table 4 Correlations... Adaptive Selling Behaviors [correlations reported with Latitude, Loyalty, Competence-skill, Competence-knowledge, Quality of Relationship, Performance]."</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="18" customHeight="1" s="10">
       <c r="A130" t="inlineStr">
@@ -7114,6 +7206,16 @@
           <t>BSMA0127</t>
         </is>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr">
         <is>
           <t>An information systems (IS) support community represents a knowledge-intensive network where IS professionals interact with end-users to resolve system use problems during the IS post-implementation stage. For IS professionals in the support function, providing support for multiple information systems to multiple business units requires knowledge about different domains (business units or technical systems). In this paper, we take a network perspective to empirically evaluate the effects of an IS worker's network position and knowledge boundary spanning on productivity. Drawing upon theories of experiential learning and knowledge boundary, we perform social network analysis and linear mixed effects modeling to analyze archival data comprising 36 IS workers and 23,450 support requests made by 4568 end-users during the first 13 months post SAP/R3 implementation in a large U.S. organization. Our findings reveal that IS workers' network centrality and boundary spanning positively influence productivity. Surprisingly, their boundary-spanning experience plays a substantially more important role than network centrality. This study makes important contributions to theory and practice in individual experiential learning in knowledge-intensive networks.</t>
@@ -7139,7 +7241,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P130" s="8" t="n"/>
+      <c r="P130" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the effect of knowledge boundary spanning on the productivity of IS workers. Although it captures intra-organizational boundary spanning across different business units, the study relies on an unbalanced panel dataset consisting of 320 person-month observations from 36 IS workers over a 13-month period. The zero-order correlation matrix provided in Table 1 is based on these 320 observations (N=320) rather than the 36 unique individuals. This data structure includes repeated measures from the same individuals over time, which violates the assumption of statistical independence required for extracting valid individual-level effect sizes. Therefore, the study must be excluded under Code 3.. Verbatim Evidence: "We combined the ticket log data and network measures with individual characteristics of IS workers, and compiled an unbalanced panel dataset of 320 observations involving 36 IS workers over 13 months for data analysis. ... Table 1 Descriptive statistics and correlations. ... N = 320; absolute value of correlation coefficient greater than 0.1 is significant at p &lt; 0.001."</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="18" customHeight="1" s="10">
       <c r="A131" t="inlineStr">
@@ -7152,6 +7258,16 @@
           <t>BSMA0128</t>
         </is>
       </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
           <t>This article develops a framework for studying cross-functional teams in organizations that focuses on three domains: organizational context, internal process, and outcome measures. The framework was developed from qualitative data from over 200 individual and group interviews, written descriptions, and team observations. We then operationally defined this model through a set of questionnaire items and validated it through quantitative analysis of data from 565 members of cross-functional teams. The resulting framework provides a base for the future study of cross-functional teams.</t>
@@ -7177,7 +7293,11 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="P131" s="8" t="n"/>
+      <c r="P131" s="8" t="inlineStr">
+        <is>
+          <t>The study measures boundary spanning (coordination and linkage) at the team level rather than the individual level. The survey items for the boundary spanning constructs use 'Our team' or 'The team' as the referent (e.g., 'Our team is good at coordinating work with other teams in the program'). According to Screening Rule 5 (Proxy Guardrail), because the respondents act as key informants for team-level behavior rather than reporting their own individual boundary spanning behavior, the study must be excluded under Code 3.. Verbatim Evidence: "Table 1 Results of Factor Analysis of the Organizational Context Domain... Coordination with other teams (alpha = .813)... Our team is good at coordinating work with other teams in the program. The team is well-informed about activities of other teams doing related work. Our team has difficulty working with other teams in the program. Our team is isolated from the rest of the program... Linkage to functions (alpha = .685)... Members of this team have enough authority to make important decisions for their home organization. Our team is able to resolve problems between the different home organizations effectively. Disputes between the different home organization represented on our team make it difficult to do our work."</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="18" customHeight="1" s="10">
       <c r="A132" t="inlineStr">
@@ -7190,6 +7310,16 @@
           <t>BSMA0129</t>
         </is>
       </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr">
         <is>
           <t>When working as a member of a team, individuals must make decisions concerning the allocation of resources (eg, effort) toward individual goals and team goals. As a result, individual and team goals, and feedback related to progress toward these goals, should be potent levers for affecting resource allocation decisions. This research develops a multilevel, multiple-goal model of individual and team regulatory processes that affect the allocation of resources across individual and team goals resulting in individual and team performance. On the basis of this model, predictions concerning the impact of individual and team performance feedback are examined empirically to evaluate the model and to understand the influence of feedback on regulatory processes and resource allocation. Two hundred thirty-seven participants were randomly formed into 79 teams of 3 that performed a simulated radar task that required teamwork. Results support the model and the predicted role of feedback in affecting the allocation of resources when individuals strive to accomplish both individual and team goals.</t>
@@ -7215,7 +7345,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="P132" s="8" t="n"/>
+      <c r="P132" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 2] The study uses a sample of undergraduate psychology students in a laboratory setting, lacking an organizational employee sample (Code 2). Additionally, the study does not measure boundary spanning behavior; rather, it examines resource allocation (individual-focused versus team-focused effort), goal setting, and strategy on a synthetic radar-tracking simulation task (Code 1).. Verbatim Evidence: "Two hundred thirty-seven undergraduate psychology students were randomly formed into 79 teams of 3. Trainees received partial course credit for their participation... The task used in this research was TEAMSim (Team Event-Based Adaptive Multilevel Simulation). TEAMSim is a PC-based simulation of a radar-tracking task (Kozlowski &amp; DeShon, 2004)."</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="18" customHeight="1" s="10">
       <c r="A133" t="inlineStr">
@@ -7228,6 +7362,16 @@
           <t>BSMA0130</t>
         </is>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
           <t>Boundary-spanning positions require occupants to interact with groups whose norms may differ from one another. It was hypothesized that individuals holding these positions would perform better if they were sensitive to social cues and able to adapt their behavior to fit the circumstances. 93 field representatives (average age 30.5 yrs) who acted as boundary spanners were given the Self-Monitoring Scale. Results show that significant relationships existed between job performance and an individual difference variable (self-monitoring) that assessed the ability of respondents to adjust their self-presentation to fit the situation; self-monitoring was most important during the period of early tenure.</t>
@@ -7253,7 +7397,11 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="P133" s="8" t="n"/>
+      <c r="P133" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure Boundary Spanning Behavior as a quantitative variable with extractable effect sizes. Instead, it examines the job performance, tenure, and self-monitoring (an individual difference/personality trait) of employees who happen to hold boundary-spanning positions (field representatives). Because BSB itself is not measured as a variable, the study lacks the required effect size of interest.. Verbatim Evidence: "Respondents were field representatives for a large franchise organization. Job duties involved servicing franchised outlets. ... To test the hypotheses, two constructs were assessed: job performance and attention to social cues. ... Attention to social cues was measured using the Self-Monitoring Scale. ... Table 1 presents means, standard deviations, and zero-order and partial correlations for all variables. ... 1. Performance 2. Tenure (months) 3. Self-monitoring"</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="18" customHeight="1" s="10">
       <c r="A134" t="inlineStr">
@@ -7266,6 +7414,16 @@
           <t>BSMA0131</t>
         </is>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr">
         <is>
           <t>Using an external perspective as a research lens, this study examined team-context interaction in five consulting teams. The data revealed three strategies toward the teams' environment: informing, parading, and probing. Informing teams remain relatively isolated from their environment; parading teams have high levels of passive observation of the environment; and probing teams actively engage outsiders. Probing teams revise their knowledge of the environment through external contact, initiate programs with outsiders, and promote their team's achievements within their organization. In this study, they were rated as the highest performers among the teams, although member satisfaction and cohesiveness suffered in the short run. Results suggested that external activities are better predictors of team performance than internal group processes for teams facing external dependence.</t>
@@ -7291,7 +7449,11 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="P134" s="8" t="n"/>
+      <c r="P134" s="8" t="inlineStr">
+        <is>
+          <t>The study is an exploratory, qualitative, and descriptive analysis of five consulting teams within a governmental organization. It utilizes a multimethod approach (interviews, observations, and small-scale surveys with N=17 responses) to build profiles of team-level strategies (informing, parading, probing). The unit of analysis is the team (N=5), and the paper only reports descriptive means for each team without providing any formal correlation matrices or extractable quantitative zero-order effect sizes (r). Therefore, it must be excluded for both lacking extractable effect sizes (Code 1) and utilizing a team-level unit of analysis (Code 3).. Verbatim Evidence: "Because this research was exploratory, I used an inductive process to study external activity in the five teams' natural environment... Using a multimethod approach, I followed teams for their first five months. Data collection focused on three sets of variables. First, I collected data on team leaders' plans right after the teams were formed through interviews... Second, I monitored team interactions with outsiders, using questionnaires, logs, interviews, and observation... Third, I assessed internal group processes and outcomes... All team members received questionnaires with envelopes to be returned directly to me. I received 17 questionnaires, a response rate of 47 percent... [Tables 2-5 present descriptive means and rankings at the team level; no correlation matrices or extractable effect sizes are provided]."</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="18" customHeight="1" s="10">
       <c r="A135" t="inlineStr">
@@ -7304,6 +7466,16 @@
           <t>BSMA0132</t>
         </is>
       </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
           <t>The market-shaping literature recognizes that consumers are actors who can shape markets. However, research into the mechanisms of consumption-driven market-shaping is only emerging. This paper shows that one way in which consumers shape markets is through boundary work, as consumers make, break, and re-make the boundaries among multiple markets. Empirically, this paper investigates how user innovation practices catalyzed the formation of four boardsport markets: surfing, kitesurfing, windsurfing, and stand-up-paddling. The findings show that consumers shape markets in three steps: (1) generating local variations of consumption practices; (2) imposing order and coherence to intermediate frames; and (3) channeling creative consumption practices into market formation. This paper contributes to the market-shaping literature by conceptualizing how consumers splinter an existing singular market into new markets. We coin the term ‘market bifurcations’ to describe how a singular, seemingly cohesive consumer practice breaks down, splintering into several local variations, which can then catalyze the formation of new markets.</t>
@@ -7329,7 +7501,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P135" s="8" t="n"/>
+      <c r="P135" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative investigation of how consumers shape markets in board sports through boundary work, relying on in-depth interviews and secondary data sources. It does not report any quantitative survey data, correlation matrices, or extractable effect sizes required for this meta-analysis.. Verbatim Evidence: "Empirically, this paper investigates how user innovation practices catalyzed the formation of four boardsport markets: surfing, kitesurfing, windsurfing, and stand-up-paddling. ... We collected 13 semi-structured in-depth interviews with respondents who were simultaneously avid boardsports consumers and commercial operators, including retailers, owner-operators, entrepreneurs, instructors, and photographers (Table 1). ... The fieldwork also included 42 pages of reflective fieldnotes jointly taken by the researchers. ... By focusing on narrative biographies of boardsports, we aimed to uncover the unfolding practices that have come to define their markets."</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="18" customHeight="1" s="10">
       <c r="A136" t="inlineStr">
@@ -7342,6 +7518,16 @@
           <t>BSMA0133</t>
         </is>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
           <t>An intriguing window on Japanese/American intercultural relations can be found in American ethnographers’ in-depth accounts of their diﬃculties with Japanese informants. Although the literature contains excellent self-analyses of this kind, this body of data has yet to be mined for general lessons regarding communication between Americans and Japanese. This paper addresses that gap by comparing several reﬂexive accounts of doing ethnography in Japan: Matthews Hamabata’s Crested Kimono, Gail Bernstein’s Haruko’s World, Liza Dalby’s Geisha, and Crafting Selves by Dorinne Kondo. Examining the barriers to Japanese/American communication through this special lens reveals a complicated picture. On the one hand, familiar factors, such as the universalism of Americans, their emphasis upon individual autonomy in social relations, and the Japanese matrix of constantly shifting in-group/outgroup relations are often the dominant inﬂuences on intercultural interactions. Yet, on the other hand, situational contexts and the value orientations and political commitments of the actors clearly do modify the expression of such factors and sometimes even reverse the expected outcomes. The present approach facilitates the representation of these complex relationships. A qualitative analysis in which an objectively framed comparison aimed at generalization rests upon the non-reiﬁed foundation of several reﬂexive ethnographies, shows promise as one strategy for transcending the stalemate between traditional group-based interpretations of culture and more recent approaches stressing individual agency and internal cultural diversity. This paper also illustrates some advantages of an anthropological approach to communication between the members of two cultures whose diﬀerences have long been a focus of interculturalist research and examines implications for models of collectivist and individualist cultures. r 2002 Elsevier Science Ltd. All rights reserved.</t>
@@ -7367,7 +7553,11 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="P136" s="8" t="n"/>
+      <c r="P136" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a qualitative comparison of four ethnographic accounts describing American ethnographers' fieldwork experiences in Japan. It does not contain quantitative data, statistical analyses, a correlation matrix, or any extractable effect sizes (r) related to individual employee boundary spanning behavior.. Verbatim Evidence: "This paper addresses that gap by comparing several reflexive accounts of doing ethnography in Japan: Matthews Hamabata’s Crested Kimono, Gail Bernstein’s Haruko’s World, Liza Dalby’s Geisha, and Crafting Selves by Dorinne Kondo... A qualitative analysis in which an objectively framed comparison aimed at generalization rests upon the non-reified foundation of several reflexive ethnographies, shows promise as one strategy for transcending the stalemate between traditional group-based interpretations of culture and more recent approaches stressing individual agency and internal cultural diversity."</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="18" customHeight="1" s="10">
       <c r="A137" t="inlineStr">
@@ -7380,6 +7570,16 @@
           <t>BSMA0134</t>
         </is>
       </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr">
         <is>
           <t>Social ties to colleagues on other work teams can spur creative ideas and workplace innovation by exposing an individual to diverse knowledge. However, for external knowledge to be recombined into innovation, the knowledge must first be recognized as potentially valuable. Going beyond traditional structural explanations, we predict that the use of diverse knowledge to generate creative ideas and solutions will depend in part on employees’ psychological attachment to the organizational groups to which they belong, i.e., their social identity, and the strength of their social ties. We test our hypotheses in an R&amp;D division of a global hightechnology firm, finding that social identity influences the creative generativity of boundary-spanning ties. Specifically, stronger team identity renders interactions with colleagues on other work teams less generative of creative ideas, while identification with an overarching, superordinate group (e.g., a division) enhances creative generativity. We also hypothesize and find that tie strength attenuates the negative effect of team identity.</t>
@@ -7405,7 +7605,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P137" s="8" t="n"/>
+      <c r="P137" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the dyadic/relationship level rather than the individual employee level. Specifically, 87 respondent researchers reported on multiple external contacts, resulting in a dataset of N=673 boundary-spanning relationships. Because each individual is included in multiple observations, the correlation matrix violates statistical independence and yields no valid individual-level effect sizes.. Verbatim Evidence: "The survey yielded 87 complete responses... Respondents provided a total of 681 external contacts, i.e., contacts on other work teams, for an average of 7.8 boundary-spanning ties per respondent. Because of missing data, the total usable sample is composed of 673 boundary-spanning relationships... As suggested above, the data have a dyadic relational structure, where each respondent researcher (ego) has multiple contacts (alters) on other work teams. In the dyadic structure, each individual researcher is included in multiple observations because he or she reported on multiple relationships. Therefore, the observations are not independent within-person."</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="18" customHeight="1" s="10">
       <c r="A138" t="inlineStr">
@@ -7418,6 +7622,16 @@
           <t>BSMA0135</t>
         </is>
       </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
           <t>The boundary spanning activity of the entrepreneur is used to examine the strategic management process in small business. In a sample of 82 owner/operators, intensive boundary spanning activity was strongly related to organizational performance, and information processing capability significantly affected the performance-boundary spanning relationship.</t>
@@ -7443,7 +7657,11 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="P138" s="8" t="n"/>
+      <c r="P138" s="8" t="inlineStr">
+        <is>
+          <t>The study violates multiple inclusion criteria [Code 1 &amp; Code 2]. First, the sample consists of independent owner/operators (entrepreneurs) who hold 51% or more ownership in small businesses, violating the employee sample requirement (Code 2). Second, the operationalization of boundary spanning merely counts the 'number of hours' and 'number of contacts' with external constituencies to calculate the percentage of time spent, without specifying any purposive boundary-spanning action, which violates the purposive action guardrail (Code 1).. Verbatim Evidence: "The focus of this study is on the strategic behavior of the owner/operator of the small business organization, the entrepreneur... Data were collected by survey instrument from the owner/operators of four different types of small business organizations. [...] The criteria were: firm be owner operated (&gt;= 51 percent ownership); firm have between 2 and 100 employees... Subjects were asked to record the number of hours and the number of contacts they had in an average week with each of nine categories of environmental constituencies. [...] The sum of the hours spent in these activities divided by the number of hours worked per week is a measure of how intensive the owner/operator's boundary spanning activity is: the percentage of work time spent in boundary spanning activity. The sum of the number of contacts is an extensive measure."</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="18" customHeight="1" s="10">
       <c r="A139" t="inlineStr">
@@ -7456,6 +7674,16 @@
           <t>BSMA0136</t>
         </is>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr">
         <is>
           <t>Improving access to support for people experiencing domestic violence and abuse requires better connections between healthcare services and specialist domestic violence and abuse (DVA) support agencies. We examined the work involved in restructuring the relationship between primary care and specialist DVA support services. This was part of a broader study of the implementation of a general practice DVA training and support programme (IRIS). We conducted an ethnography in two diﬀerent UK areas where the IRIS programme was being delivered. We investigated the work done by specialist DVA workers (Advocate Educators) in the dual role of providing training to GPs and advocacy support to patients. Drawing on concepts of boundary actors and boundary objects, we examined how interactions between clinicians and patients changed after the introduction of the IRIS programme. The referral pathway emerged as a boundary object, meeting a shared ambition of general practitioners and patients to distribute responsibility for addressing DVA. However, maintaining this as a boundary object-in-use required signiﬁcant, and often unseen, work on the part of the Advocate Educator as boundary spanner. Our study contributes to scholarship on boundary work by highlighting the role of marginal boundary actors in maintaining the use of boundary objects among disparate groups.</t>
@@ -7481,7 +7709,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P139" s="8" t="n"/>
+      <c r="P139" s="8" t="inlineStr">
+        <is>
+          <t>This study is a qualitative ethnography exploring the practices of boundary work through participant observation and semi-structured interviews. It does not provide a correlation matrix or any extractable quantitative effect sizes (r) required for the meta-analysis.. Verbatim Evidence: "We conducted an ethnography in two different UK areas where the IRIS programme was being delivered. We investigated the work done by specialist DVA workers (Advocate Educators) in the dual role of providing training to GPs and advocacy support to patients... AD collected data through participant observation and interviewing. Fieldwork was conducted over 20 months between August 2015 and March 2017 (over 100 h per field site)... 19 semi-structured interviews were conducted in each case study area with clinicians (case study one: 5, case study two: 8), services users (case study one: 8, case study two: 5), and actors involved in the commissioning and delivery of IRIS"</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="18" customHeight="1" s="10">
       <c r="A140" t="inlineStr">
@@ -7494,6 +7726,16 @@
           <t>BSMA0137</t>
         </is>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr">
         <is>
           <t>Multinational companies (MNC) are facing increasing pressure in the marketplace. It is up to MNC leaders to engage the resources available to them to ensure these firms remain competitive and avoid organizational decline. A hallmark MNC business model competitive advantage is organizational effectiveness in promoting collaboration and cooperation across organizational and environmental boundaries. Boundary crossing actors and the activities they pursue are valuable resources residing at the core of the MNC business model and hence constitute a key element of the firm’s competitive advantage. The purpose of this research is to investigate how MNC leaders can engage these resources for organizational benefit. The research question asked and answered in this study is, How can MNC leaders bolster organizational effectiveness using boundary activity resource (re) combination and control? The organizational control theory lens is used to guide this research. Using the principles of evidence-based management, a systematic review of evidence from 2002 to 2022 was conducted. The systematic review process included a systematic search for evidence including gathering input from subject matter experts and a critical assessment and quality appraisal of the evidence sources. Subsequently, the sources were subjected to an analysis and synthesis in search of emergent themes related to the research question. The research showed that organizational climate, knowledge management, and individual idiosyncrasies (combined with role idiosyncrasies) have considerable implications for leaders in the decision-making process. Although each element is important on its own, the totality of the evidence suggests it is the holistic combination of all four elements that can lead to promotion of boundary activities and hence enhancement of organizational effectiveness. Furthermore, it is an MNC leader’s responsibility to ensure an organizational climate conducive to boundary crossing activities is created and maintained for these elements to work. The recommendations resulting from the research are that MNC leaders must prioritize boundary actors and activities as core organizational value drivers, core boundary crossing competencies have to be built out, and once constructed, these competencies have to be entrenched in the organization’s compositional mechanisms and be monitored and maintained for them to remain effective.</t>
@@ -7519,7 +7761,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P140" s="8" t="n"/>
+      <c r="P140" s="8" t="inlineStr">
+        <is>
+          <t>The document is a doctoral dissertation that conducts a qualitative systematic review and realist synthesis of existing literature on boundary spanning in multinational companies. As a secondary research study (systematic review), it does not collect primary quantitative data from individual employees nor does it report an extractable zero-order correlation matrix, rendering it ineligible for the meta-analysis.. Verbatim Evidence: "Using the principles of evidence-based management, a systematic review of evidence from 2002 to 2022 was conducted. The systematic review process included a systematic search for evidence including gathering input from subject matter experts and a critical assessment and quality appraisal of the evidence sources. Subsequently, the sources were subjected to an analysis and synthesis in search of emergent themes related to the research question... A qualitative systematic review (SR) was conducted to answer the research question: How can MNC leaders bolster organizational effectiveness using boundary spanning resource (re)combination and control?"</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="18" customHeight="1" s="10">
       <c r="A141" t="inlineStr">
@@ -7530,6 +7776,16 @@
       <c r="B141" t="inlineStr">
         <is>
           <t>BSMA0138</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -7566,7 +7822,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P141" s="8" t="n"/>
+      <c r="P141" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a conceptual book chapter that proposes a framework for studying leadership in multiteam systems (MTSs) using social network analysis. It reviews existing literature, suggests sociometric prompts, and offers theoretical research questions, but it does not present any primary empirical data or a correlation matrix with extractable effect sizes.. Verbatim Evidence: "The current chapter explains how the form of MTS leadership (e.g., vertical, shared) can be captured using network analytic techniques across multiple MTS network foci... Finally, it provides example prompts that could be used to elicit leadership functions and goal foci... and it provides example research questions that stem from incorporation of network analytic techniques with the study of MTS leadership... We hope that these ideas stimulate additional thinking in this area, and ultimately, that empirical research testing of these ideas will follow."</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="18" customHeight="1" s="10">
       <c r="A142" t="inlineStr">
@@ -7579,6 +7839,16 @@
           <t>BSMA0139</t>
         </is>
       </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
           <t>Interorganizational teams are rapidly becoming more prevalent as a means to improve organizations' responsiveness. To achieve their objective, interorganizational teams must engage in extensive amounts of boundary spanning activity. This study juxtaposed three structural variables, namely team informational diversity, team boundedness, and extrateam links, in an integrated model aimed at promoting our understanding of how to increase interorganizational team boundary spanning activity and its effectiveness. The model was tested with 49 health promotion teams. Our findings indicated that three types of boundary spanning—scouting, ambassadorial, and coordinating—were positively associated with interorganizational team effectiveness. In addition, for team informational diversity, team boundedness, and extrateam links, scouting and ambassadorial activities fully mediated their relationships with team effectiveness; for team boundedness, coordinating activity also fully mediated its relationship with team effectiveness. These findings highlight the importance of incorporating structural considerations into the management of interorganizational teams.</t>
@@ -7604,7 +7874,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P142" s="8" t="n"/>
+      <c r="P142" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates boundary spanning activities at the team level, taking the interorganizational team as the unit of analysis (N = 49 health promotion teams). The provided correlation matrix reports relationships between team-level aggregated constructs (e.g., team heterogeneity, team boundary spanning activity, team effectiveness). As it lacks individual-level effect sizes, it must be excluded.. Verbatim Evidence: "The model was tested with 49 health promotion teams. ... The research population consisted of 49 health promotion teams. ... All responses in our sample fitted into the prescribed categories of boundary spanning activity: scouting, ambassadorial, coordinating, and empowering behaviours. Finally, we dummy coded every behaviour as 1 = enacted by the team or 0 = not enacted, and then summed the behaviours in each category to obtain the measures of scouting, ambassadorial, coordinating, and empowering. ... TABLE 1 Intercorrelation matrix of study variables ... N = 49."</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="18" customHeight="1" s="10">
       <c r="A143" t="inlineStr">
@@ -7617,6 +7891,16 @@
           <t>BSMA0140</t>
         </is>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
           <t>The role of gender in career mobility is a major practical and scholarly concern. Drawing on boundaryless career literature and social role theory, we examined whether gender influences employees' psychological mobility, whether this influence varies depending on the nature of career boundaries (the boundaries of job, organisation and industry) and whether it is contingent on organisational or occupational characteristics. We conducted cross‐classified multilevel analyses on 3,527 Australian employees nested within 725 organisations and 43 occupations. The results suggest that females show higher mobility preferences than males when it comes to crossing industries but not changing organisations or jobs. However, their preference for crossing career boundaries is significantly reduced when their organisation has a strong presence of female leadership. We also find that in female‐dominated occupations, females show a higher cross‐organisational mobility preference than males, while in male‐dominated occupations, females show a lower cross‐organisational mobility preference.</t>
@@ -7642,7 +7926,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P143" s="8" t="n"/>
+      <c r="P143" s="8" t="inlineStr">
+        <is>
+          <t>The study measures cross-boundary mobility preferences (i.e., psychological mobility or turnover intentions across job, organizational, and industry boundaries) rather than Boundary Spanning Behavior (which requires interpersonal, purposive actions like information exchange or coordination across boundaries). Thus, it does not contain any effect sizes of interest.. Verbatim Evidence: "For dependent variables, we created three binary variables using the individual survey in the AWRS data: cross-job mobility preference, cross-organisation mobility preference and cross-industry mobility preference. Measuring psychological mobility with a binary variable is a well-received approach in the literature... We created the mobility preference variables using individuals’ responses to this question: ‘In regard to your job, where do you want to be in 12 months’ time?’... Cross-organisation mobility preference differentiated the employees who chose options 1 or 2 from those who chose options 3 or 4. In this variable, 1 indicated a preference to change companies, and 0 indicated a preference to stay in the same company."</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="18" customHeight="1" s="10">
       <c r="A144" t="inlineStr">
@@ -7655,6 +7943,16 @@
           <t>BSMA0141</t>
         </is>
       </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr">
         <is>
           <t>Managing a complex, boundary‐spanning function to maximize its contribution to the firm can be a challenging task. This research is concerned with providing management with increased understanding of the effects of different ways of managing a function, especially a significant boundary‐spanning operation. Conducted in the context of a procurement function, through a laboratory experiment, explores the impact of performance measures, interaction with other internal organizations and access to information about external events on an individual′s decision making and “comfort level”. Results indicate that the performance measurement system determines an individual′s decision‐making performance. The broader, more effectiveness‐oriented measures also tend to make the individuals more confident and satisfied with their operating environment and decisions. The availability of interaction with other internal organizations and the access to information about external events impact on an individual′s decisions but have relatively little effect on his/her comfort level.</t>
@@ -7680,7 +7978,11 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="P144" s="8" t="n"/>
+      <c r="P144" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a sample of undergraduate students rather than actual organizational employees, which violates the sample population criteria (Code 2). Additionally, the study is a laboratory experiment analyzing decision-making performance in a computer simulation via ANOVA, lacking any zero-order correlation matrix or extractable effect sizes (r) for boundary spanning behavior (Code 1). Therefore, it is excluded for multiple reasons [Code 1 &amp; Code 2].. Verbatim Evidence: "The research was conducted using a full-factorial experimental design, resulting in 16 (4 × 2 × 2) treatments. Fifteen subjects (upper division business school undergraduates) were in each treatment... The subject is then presented, via a computer, with a sequence of 14 procurement problem situations... The decisions to the 14 problems were captured by the computer and served to set parameters for a simulation of a factory... The responses were analysed using analysis of variance with 15 observations per cell."</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="18" customHeight="1" s="10">
       <c r="A145" t="inlineStr">
@@ -7693,6 +7995,16 @@
           <t>BSMA0142</t>
         </is>
       </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr">
         <is>
           <t>A psychological contract is composed of an individual’s belief regarding the reciprocal obligations that exist between that individual and another entity with which that person is engaged. Psychological contracts are important in many business relationships, such as those between a buyer and supplier. The perceptions held by one individual may not be congruent with those of the other, in which case conflict may arise within the relationship. We introduce to the operations and supply chain literatures a comprehensive view of the theory of psychological contracts, which with few exceptions has largely been omitted from research regarding inter-firm relationships. This research investigates the processes by which individuals manage conflict in inter-firm relationships, and the extent to which decisions at both tactical and strategic levels are influenced by the experience of psychological contract violation. At the tactical level, we seek to understand how the daily operational decisions that individuals make are affected by psychological contract violation, particularly when sub-optimal decision-making is observed. At the strategic level, we consider the circumstances under which relational versus written contractual governance mechanisms are leveraged in response to conflict, and how the experience of psychological contract violation may influence these broader,firm-level decisions. Our research plan uses two different methodological approaches in investigating these issues. First, to evaluate tactical behaviors, we employ an experiment. The goal of the experiment is to determine specifically how economic decisions made by those in boundary-spanning roles deviate from optimal in response to conflict and how these behaviors are influenced by the experience of psychological contract violation. To this end, we employ a 2x2x2 factorial design in which violation timing, severity, and attribution are investigated. The experiment was accompanied by an exit survey which served to assess the experience of psychological contract violation and related issues of trust and fairness. Data from 295 subjects were included in our analysis. We observe a main effect of severity occurring during the violation, and main effects of time and attribution are evident in post-violation periods. We tie these phenomena to the psychological constructs under study. Second, in order to investigate strategic-level decisions, we propose administration of an industry survey to purchasing and sales managers. The survey will allow us to more broadly characterize types of conflict experienced in inter-firm relationships and the contractual governance mechanisms leveraged in response. Models useful for investigating these issues are developed and discussed, and a survey instrument is presented. The work presented in this dissertation is among the first to incorporate both individual-level and firm-level contracts into an investigation of tactical and strategic conflict response and resolution analysis within buyer-supplier exchange relationships.</t>
@@ -7718,7 +8030,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P145" s="8" t="n"/>
+      <c r="P145" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 2] The study violates multiple inclusion criteria. First, the only empirical data collected comes from a laboratory experiment using undergraduate students acting in hypothetical roles, lacking an organizational employee sample [Code 2]. Second, while the study mentions boundary-spanning roles, the actual variables measured in the experiment are psychological contract violation, trust, fairness, and economic decision-making (order quantity in a newsvendor problem), lacking any extractable effect size for an interpersonal Boundary Spanning Behavior construct [Code 1]. The proposed industry survey was not administered.. Verbatim Evidence: "The primary data source for these experiments was undergraduate business students from the Fisher College of Business. The specific students recruited were those taking an introductory course in operations management... In our experiment, we ask students to make decisions in accordance with their role as the buyer of floral goods for an upscale grocer... We propose the use of an industry survey to expand our evaluation of psychological contracts to a more strategic decision-making context... The effort expended so far has focused on model development and instrument design, and the resulting survey instrument represents the key contribution of the survey to our body of work thus far."</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="18" customHeight="1" s="10">
       <c r="A146" t="inlineStr">
@@ -7731,6 +8047,16 @@
           <t>BSMA0143</t>
         </is>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
           <t>ABSTRACT               This paper examines learning in interdisciplinary action teams. Research on team effectiveness has focused primarily on single‐discipline teams engaged in routine production tasks and, less often, on interdisciplinary teams engaged in discussion and management rather than action. The resulting models do not explain differences in learning in interdisciplinary action teams. Members of these teams must coordinate action in uncertain, fast‐paced situations, and the extent to which they are comfortable speaking up with observations, questions, and concerns may critically influence team outcomes. To explore what leaders of action teams do to promote speaking up and other proactive coordination behaviours – as well as how organizational context may affect these team processes and outcomes – I analysed qualitative and quantitative data from 16 operating room teams learning to use a new technology for cardiac surgery. Team leader coaching, ease of speaking up, and boundary spanning were associated with successful technology implementation. The most effective leaders helped teams learn by communicating a motivating rationale for change and by minimizing concerns about power and status differences to promote speaking up in the service of learning.</t>
@@ -7756,7 +8082,11 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="P146" s="8" t="n"/>
+      <c r="P146" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts its analysis at the team level (N = 16 operating room teams). Qualitative interview data collected from multiple informants were aggregated to create team-level variables. The reported correlation matrix represents relationships among these group-level constructs (including team boundary spanning) rather than individual-level employee boundary spanning behavior, violating the individual-level analysis requirement.. Verbatim Evidence: "The sample consisted of 16 cardiac surgery teams selected to ensure differences in geography and innovation history from the approximately 150 US hospitals that had purchased the technology. Each hospital had only one OR team learning MICS; the teams, all in well respected cardiac surgery departments, varied in size... I analysed all coded interview data related to the team learning process and the organizational context to create composite variables. ... The result is a set of numerical ratings for five team constructs (team stability, team preparation, procedure innovation, boundary spanning, and psychological safety) and four organizational constructs (history of innovation, resource constraints, management support, and information infrastructure) for each hospital."</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="18" customHeight="1" s="10">
       <c r="A147" t="inlineStr">
@@ -7769,6 +8099,16 @@
           <t>BSMA0144</t>
         </is>
       </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr">
         <is>
           <t>Purpose: Sleep deprivation among employees has become commonplace in the workforce. In the United States, the number of hours individuals sleep per night has declined by an hour and a half per night since the 1960s. As of 2005, seventy-four percent of individuals were getting less than eight hours of sleep per night on weekdays. There are negative ramifications to the organization when employees are sleep deprived such as lost productivity, increased accident rate, and increased absenteeism.</t>
@@ -7794,7 +8134,13 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P147" s="8" t="n"/>
+      <c r="P147" s="8" t="inlineStr">
+        <is>
+          <t>The study uses salespeople as boundary role personnel but does not measure boundary spanning behavior (BSB). It focuses on the effects of sleep duration on variables such as grit, happiness, perceived organizational support, perceived supervisory support, job satisfaction, organizational commitment, and turnover intentions. Furthermore, the paper does not report a zero-order correlation matrix, only mean comparisons via t-tests. Therefore, it lacks both the relevant BSB construct and extractable effect sizes.. Verbatim Evidence: "Title: 'Does Sleep Really Matter? Examining Sleep among Salespeople as Boundary Role Personnel for Key Job Factors'
+Abstract: 'The two individual factors consisted of grit and happiness while the five organizational factors consisted of perceived organizational support, perceived supervisory support, job satisfaction, organizational commitment, and turnover intentions.'
+Methodology: 'Three hundred twenty f (323) respondents successfully completed the entire survey. ... A comparison between means was used to examine if differences existed for each scale included in this study based on the two sleep categories previously created. Table 1 displays the results for each scale.'"</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="18" customHeight="1" s="10">
       <c r="A148" t="inlineStr">
@@ -7807,6 +8153,16 @@
           <t>BSMA0145</t>
         </is>
       </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr">
         <is>
           <t>Organizations are increasingly applying artificial intelligence (AI) in interorganizational systems (IOS) to mitigate demand and supply disruptions. This shift towards AI to enhance supply chain agility capabilities automates some tasks previously undertaken by boundary-spanning employees who serve as critical informational and influential links with supply chain partners. Given limited related research, we investigate the impact of AI not only on the potential displacement of boundary-spanning employee roles but also on subsequent supply chain agility. Leveraging dynamic capabilities and social network theories, we first conducted interviews with supply chain executives to develop a practitioner survey. Following a mixedmethods approach, we next applied structural equation modeling to this survey data and then probed further via follow-up interviews. The results reveal that despite displacing some employees, the use of AI in IOS enhances the remaining operational and strategic roles of the boundary-spanning employees to enrich supply chain agility. The ensuing theoretical and managerial contributions emphasize the essential role of boundaryspanning employees as part of a hybrid human-AI solution, providing insight into the need for an optimal human/AI balance in the supply chain to cope with dynamic marketplaces.</t>
@@ -7832,7 +8188,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="P148" s="8" t="n"/>
+      <c r="P148" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts a firm-level analysis where individual practitioners (supply chain professionals) act as key informants evaluating their organization's reliance on boundary-spanning employees, rather than rating their own interpersonal boundary-spanning behavior. The survey items explicitly use the macro-level referent 'We' (e.g., 'We depend on BSE to regularly exchange information or resources with partners'), which violates the proxy guardrail and the requirement for individual-level analysis.. Verbatim Evidence: "We procured an email list of practitioner members of the Council of Supply Chain Management Professionals (CSCMP). The electronic surveys were deployed via Qualtrics... We received 210 responses from the 2,235 valid emails in the list, 158 of which were deemed usable... Table 2 Survey and descriptive statistics... Reliance on strategic boundary-spanning employees (RoSBSE)... RoSBSE-1: We depend on BSE to regularly exchange information or resources with partners... RoSBSE-3: We depend on BSE to make use of their relationships with our partners on the company’s behalf... The majority of responding firms were based in North America (53.8%). Also, most firms operated in the manufacturing industry (59%)."</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="18" customHeight="1" s="10">
       <c r="A149" t="inlineStr">
@@ -7845,6 +8205,16 @@
           <t>BSMA0146</t>
         </is>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
           <t>While anecdotal and research evidence exists supporting the difﬁculties faced by foreign ﬁrms in host nation environments due to liability of foreignness, it is clear that many foreign ﬁrms have been successfully operating in the U.S. over the years. This study seeks to understand the strategies foreign ﬁrms use to cope with liabilities of foreignness in an alien environment and compete successfully with domestic ﬁrms, speciﬁcally through boundary spanning. Using a sample of 3861 ﬁrms in the U.S., we ﬁnd that foreign ﬁrms on the average underperform compared to domestic ﬁrms. We also ﬁnd these ﬁrms take a differing strategic posture to cope with the disadvantages of being a foreign ﬁrm compared to domestic rivals. Multiple mediation models indicate that once this strategic posture of foreign ﬁrms is controlled for, performance differentials do not exist between foreign and domestic ﬁrms.</t>
@@ -7870,7 +8240,13 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="P149" s="8" t="n"/>
+      <c r="P149" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the firm level (N=3861 insurance firms in the U.S.) rather than the individual employee level. The author explicitly states that the focus is on the organizational level, examining firm strategies like product variety, geographic dispersion, and group affiliation as organizational boundary spanning. It lacks any individual-level measure of interpersonal boundary spanning behavior.. Verbatim Evidence: "Using a sample of 3861 firms in the U.S., we find that foreign firms on the average underperform compared to domestic firms.
+Scholars have studied boundary spanning roles at the individual (e.g., Perrone, Zaheer, &amp; McEvily, 2003) and organizational levels (e.g., Scott, 1998). However, this study’s focus is at the organizational level and specific to the role of managing the interface between organization and environment.
+This study used two sources of data, namely the National Association of Insurance Commissioners (NAIC) database and Best’s Rating guide. [...] Product variety is operationalized using a variation of the Herfindahl Index."</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="18" customHeight="1" s="10">
       <c r="A150" t="inlineStr">
@@ -7883,6 +8259,16 @@
           <t>BSMA0147</t>
         </is>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G150" t="inlineStr">
         <is>
           <t>Currently, little is known about the internal (intrafirm) behaviors that may positively affect collaborative marketing/logistics integration, or about the benefits that may be associated with making these considerable investments. In short, what should firms be doing to promote marketing/logistics collaborative integration? What is the potential payoff? This paper addresses these questions by examining relationships between the organization's evaluation and reward system, cross-functional collaboration, effective marketing/logistics interdepartmental integration, and distribution service performance.</t>
@@ -7908,7 +8294,11 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="P150" s="8" t="n"/>
+      <c r="P150" s="8" t="inlineStr">
+        <is>
+          <t>Although the study examines intra-organizational collaboration between marketing and logistics, the survey items measure department-level interactions rather than individual-level boundary spanning behavior. The logistics managers act as macro-level key informants reporting on the activities of 'the logistics department' as a whole. According to Screening Rule 5 (Proxy Guardrail), because the grammatical subject of the survey items is the department rather than the individual employee ('I'), the study represents department-level integration and violates the individual-level analysis requirement. Therefore, the study must be excluded under Code 3.. Verbatim Evidence: "Table 2: Items, Coefficient Alphas and Mean Scores. Collaboration (alpha .93) Construct mean 2.96. During the past six months, how often did the logistics department engage in the following activities with the marketing department? (5-point scale: 1 = never; 5 = quite frequently) ... Informally working together ... Sharing ideas, information, and/or resources ... Working together as a team ... Conducting joint planning to anticipate and resolve operational problems ... Achieving goals collectively ... Developing a mutual understanding of responsibilities ... Making joint decisions about ways to improve overall cost efficiency."</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="18" customHeight="1" s="10">
       <c r="A151" t="inlineStr">
@@ -7921,6 +8311,16 @@
           <t>BSMA0148</t>
         </is>
       </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
           <t>Although cross-functional integration is important for research and development (R&amp;D), research about implications of cross-functional integration has been rather sparse. In new product development (NPD), no study to date has examined intrafirm as well as interfirm integration of key functions such as intrafirm R&amp;D–marketing–production together with interfirm integration of host R&amp;D–partner R&amp;D. Such marketing and operations interface contributes to a better understanding of how operational and marketing activities impact on competitiveness and firm performance. This study collected data from 202 electronics manufacturing firms operating in an emerging economy, mainland China and Hong Kong with international R&amp;D partnerships. The findings indicate that a high level of R&amp;D integration between firms improved NPD performance when cross-functional integration is based on existing rather than new product configurations and key technologies. Interestingly, in high distance situations, cross-functional integration in the production validation stage generated NPD success. The findings show that high environmental uncertainties lead to a high level of host and partner firms R&amp;D integration. However, product newness has no significant effects on R&amp;D integration in any of the NPD stages.</t>
@@ -7946,7 +8346,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P151" s="8" t="n"/>
+      <c r="P151" s="8" t="inlineStr">
+        <is>
+          <t>The unit of analysis is at the firm and project level (N = 202 manufacturing firms). The study surveys project leaders and engineers as key informants to evaluate inter-firm R&amp;D partnerships (between host and partner R&amp;D organizations) and intra-firm cross-functional integration (between R&amp;D, marketing, and production departments). The measures reflect organizational alliances and firm-level integration rather than individual-level employee boundary spanning behavior.. Verbatim Evidence: "This study collected data from 202 electronics manufacturing firms operating in an emerging economy, mainland China and Hong Kong with international R&amp;D partnerships. The findings indicate that a high level of R&amp;D integration between firms improved NPD performance... The target respondents for the study were project leaders, project managers, senior engineers and engineers... The final sampling frame of the study consisted of 731 firms. The study targeted two key informants for each firm to reduce the threat of common method variance... What is the approximate working hour overlap between your company and the foreign company?... How big did you feel the technology capability difference between your company and the foreign company?"</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="18" customHeight="1" s="10">
       <c r="A152" t="inlineStr">
@@ -7959,6 +8363,16 @@
           <t>BSMA0149</t>
         </is>
       </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr">
         <is>
           <t>This article aims for a deeper understanding of front-line employees (FLEs) and their boundary-spanning role in service organizations’ innovation processes from the vantage points of creativity and service innovation theory. It explores in particular FLEs’ processes of creativity by focusing on how ideas emerge and how these ideas are further managed in the organizations’ innovation processes. It draws on an in-depth empirical study of three units at a large spa and resort hotel. The article demonstrates how FLEs’ ideas are related to the assimilation and utilization of knowledge gained in the customer–supplier interface. Furthermore, it introduces the concept of ‘management by weaving’, which encompasses the middle managers’ roles in the complexity of leading diverse innovation processes in the service organization. By having the roles of facilitator, gatekeeper, and translator, middle managers hold the key position for letting FLEs play the role as innovators.</t>
@@ -7984,7 +8398,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P152" s="8" t="n"/>
+      <c r="P152" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a qualitative, single-case study methodology based on 22 interviews and observations to explore the role of front-line employees as innovators. It does not provide any extractable quantitative effect sizes (r) or a formal correlation matrix involving Boundary Spanning Behavior, thus failing the data extractability gate.. Verbatim Evidence: "Previous empirical studies on organizational creativity are to a great extent laboratory studies or quantitative field studies. This study takes a qualitative in-depth approach, and thus responds to Zhou and Shalley’s (2003) call for more qualitative research on creativity. ... An in-depth study of a large spa and resort hotel located in Sweden was performed in order to learn more about how the FLEs’ ideas emerge and are managed in the organization’s innovation processes. ... Data were collected through interviews and observations. ... A total of 22 interviews were conducted: 13 with FLEs, 7 with managers, and the remaining 2 with employees who worked primarily in the back office ... In order to analyse the role of the FLEs in the innovation processes, a ‘thematic analysis’ (Boyatzis, 1998) was used"</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="18" customHeight="1" s="10">
       <c r="A153" t="inlineStr">
@@ -7997,6 +8415,16 @@
           <t>BSMA0150</t>
         </is>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr">
         <is>
           <t>Why do so many organizations fail to respond to crises effectively, and what can be done to improve their crisis response? We aim to address these questions by developing a typology of boundaries that can help us understand and better prepare for future crises. Building on the existing literature on crisis management and boundaries, our typology seeks to address the critique of current crisis management models, such as these being too prescriptive and placing too much emphasis on assumptions that only the decisions made by the crisis management team (i.e., centralized decisions) will impact the crisis response. We address this critique by elaborating on four categories of boundaries that are relevant to manage crisis response, such as physical, mental, social, and temporal. Examples of these boundaries could include access to properties (physical), interpreting whether a crisis is happening (mental), shifting relationship dynamics (social), and the urgency of response time to a crisis (temporal). Our typology offers a lens to consider crisis management by taking into consideration the complexities and nuances that linear crisis management models have not yet adequately addressed. We argue that by identifying, defining, and understanding different configurations of boundaries, one can better manage crises toward a desired outcome.</t>
@@ -8022,7 +8450,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="P153" s="8" t="n"/>
+      <c r="P153" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a conceptual study that develops a theoretical typology of boundaries (physical, mental, social, and temporal) in crisis management. It does not provide primary quantitative empirical data or any extractable effect sizes required for the meta-analysis.. Verbatim Evidence: "We aim to address these questions by developing a typology of boundaries that can help us understand and better prepare for future crises. Building on the existing literature on crisis management and boundaries, our typology seeks to address the critique of current crisis management models... Other research avenues include refining the typology via empirical data collection, considering ways of using the understanding of boundaries to provide actionable management procedures for practitioners, and investigating whether the typology is relevant to organizations outside the realm of crisis response. Empirical testing, including manipulation of specific boundaries toward a set goal, could be instrumental to this end."</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="18" customHeight="1" s="10">
       <c r="A154" t="inlineStr">
@@ -8035,6 +8467,16 @@
           <t>BSMA0151</t>
         </is>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr">
         <is>
           <t>The literature on interorganizational relationships has explored them at the organizational level and ignored interpersonal relationships. This paper consists of a literature review analyzing, consolidating, and synthesizing studies on boundary spanners in business–to–business (B2B) interorganizational relationships, pointing out directions for future research. The review was carried out in ten steps, separated into three phases encompassing planning, collecting, and synthesizing data, and disclosing the results. The study assesses 3,156 published articles, and 45 of them addressed the theme of boundary spanners in B2B interorganizational relationships. These articles were analyzed, identifying their characteristics and the evolution of research through time. The definitions of interpersonal and interorganizational relationships were compared, observing how the literature has addressed the interdependency between these relationships. Also, the concepts and roles assigned to boundary spanners were analyzed, leading to an integrated framework of the existing literature on the theme. Finally, suggestions for future research are presented, followed by this review’s implications and limitations.</t>
@@ -8060,7 +8502,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P154" s="8" t="n"/>
+      <c r="P154" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a systematic literature review analyzing 45 articles on boundary spanners in B2B interorganizational relationships. It does not provide primary quantitative empirical data or a correlation matrix with effect sizes. Therefore, it is excluded as a non-primary study.. Verbatim Evidence: "This paper consists of a literature review analyzing, consolidating, and synthesizing studies on boundary spanners in business-to-business (B2B) interorganizational relationships, pointing out directions for future research. The review was carried out in ten steps, separated into three phases encompassing planning, collecting, and synthesizing data, and disclosing the results. The study assesses 3,156 published articles, and 45 of them addressed the theme of boundary spanners in B2B interorganizational relationships."</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="18" customHeight="1" s="10">
       <c r="A155" t="inlineStr">
@@ -8073,6 +8519,16 @@
           <t>BSMA0152</t>
         </is>
       </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr">
         <is>
           <t>Purpose – Prior studies have largely overlooked the potentially negative consequences of a buyer’s relational capital (RC) with a supplier for supply-side resilience, assuming a positive linear relationship between the constructs. Meanwhile, the focus of research has been at an organisational level without incorporating the role of boundary spanning individuals at the interface between buyer and supplier. Drawing on social capital and boundary spanning theory, the purpose of this paper is to: re-examine the relationship between RC and supply-side resilience, challenging the linear assumption; and investigate how both the strength and diversity of a boundary spanner’s ties moderate this relationship.</t>
@@ -8098,7 +8554,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P155" s="8" t="n"/>
+      <c r="P155" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study analyzes data at the firm/buyer-supplier relationship level (N=248 firms), with the respondent acting as a macro-level key informant. Survey items for the main constructs use organizational referents (e.g., 'My company', 'We'), violating the individual-level guardrail (Code 3). Furthermore, the individual-level boundary spanner variables (tie diversity and tie strength) merely measure the number of contacts across different functional categories, interaction frequency, and relationship duration. Because they do not specify purposive boundary-spanning actions (e.g., knowledge exchange, advice-seeking), they lack construct validity for BSB (Code 1).. Verbatim Evidence: "For the main data collection phase, we sought to obtain survey and archival data on manufacturing firms headquartered in China. Focussing on the fourth largest (rather than the largest) supplier mitigates social desirability bias (Li et al., 2010). A senior manager (e.g. purchasing manager or operations manager) from each firm was targeted as these managers are typically in charge of interactions with upstream suppliers and considered to be boundary spanners. The total number of completed and useful responses received was 248, i.e. a 21 per cent response rate. RC3. My company’s business relationship with this supplier is characterised by high levels of respect. SSR1. We are able to maintain high situational awareness and recognise early warning risk signals before being disrupted. For BSPTs, we followed Collins and Clark (2003) by asking respondents to identify the number of contacts in each of seven categories of actors (CEOs and Leaders, Accounting and Finance, Marketing and Sales, Procurement, Production and Operations, Research and Development, and Administration and Other) in the corresponding supplier organisation. Interaction frequency was measured as the average number of times per month that an individual in the buyer firm interacted with their identified contacts within the supplier. Relationship duration was measured using the question, 'On average, how long have you known these critical contacts?'"</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="18" customHeight="1" s="10">
       <c r="A156" t="inlineStr">
@@ -8111,6 +8571,16 @@
           <t>BSMA0153</t>
         </is>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr">
         <is>
           <t>Purpose – To better understand factors that lead to business model innovation (BMI) in organizations, this study argues that inclusive leadership is the primary source that motivates employee engagement in boundaryspanning activities, which fosters BMI by generating and integrating employee knowledge through boundaryspanning exploration.</t>
@@ -8136,7 +8606,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P156" s="8" t="n"/>
+      <c r="P156" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates boundary-spanning exploration at the organizational/macro level rather than as an individual interpersonal behavior. The methodology specifies that 'the BMI scale and boundary-spanning exploration scale items were filled out by department leaders or CEOs', indicating they served as key informants or proxies for their respective units/firms. Furthermore, boundary-spanning exploration is operationalized using the scale by Sidhu et al. (2007), which assesses firm-level organizational search (technical and market knowledge). The macro-level focus is additionally confirmed by the regression analyses, which exclusively employ firm-level control variables (firm age, firm size, industry, firm nature) rather than individual demographics. Consequently, the study violates the individual-level unit of analysis guardrail and is excluded under Code 3.. Verbatim Evidence: "We then selected 30 companies to participate in our survey, sending each 20 questionnaires. ... In addition, to eliminate common method variance, the BMI scale and boundary-spanning exploration scale items were filled out by department leaders or CEOs, and that on inclusive leadership style was filled out by department employees. ... Dependent variable. ... This study used the measurement scale developed by Zott et al. (2007), with items including “providing customers with products or services with increasing value”... Mediating variable. ... This paper measures boundary-spanning exploration of technical knowledge and market knowledge using the scale developed by Sidhu et al. (2007), which has been widely recognized by scholars. ... Control variables. To reduce the potential impact of endogenous problems in the research and enhance the robustness of the results, this paper takes enterprise size, age and industry as control variables."</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="18" customHeight="1" s="10">
       <c r="A157" t="inlineStr">
@@ -8149,6 +8623,16 @@
           <t>BSMA0154</t>
         </is>
       </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G157" t="inlineStr">
         <is>
           <t>The purpose of this article is to promote an open systems perspective on team research. The authors develop a model of team boundary activities: boundary spanning, buffering, and reinforcement. The model examines the relationship between these boundary activities and team performance, the moderating effects of organizational contextual factors, and the mediating effect of team psychological safety on the boundary work–performance relationship. These relationships were empirically tested with data collected from 64 software development teams. Boundary spanning, buffering, and boundary reinforcement were found to relate to team performance and psychological safety. Both relationships are moderated by the team’s task uncertainty and resource scarcity. The implications of the findings are offered for future research and practice.</t>
@@ -8174,7 +8658,11 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="P157" s="8" t="n"/>
+      <c r="P157" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the team (N = 64 software development teams). Individual survey responses were aggregated to the team level, and the survey items explicitly use the team as the referent (e.g., 'To what extent does the team encourage its members...'). This violates the guardrail requiring individual-level analysis and triggers the proxy/team-level exclusion.. Verbatim Evidence: "Because our model focuses on the team level, we took a number of steps before aggregating individual responses to the team level. First, to ensure that the level of measurement matches the level of theory, all survey items were worded to reference the team environment and activities. [...] On the basis of these results, individual responses were aggregated and data were analyzed at the team level. [...] To what extent does the team encourage its members to solicit information and resources from elsewhere in and/or beyond the division? [...] Model statistics: N 64"</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="18" customHeight="1" s="10">
       <c r="A158" t="inlineStr">
@@ -8187,6 +8675,16 @@
           <t>BSMA0155</t>
         </is>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G158" t="inlineStr">
         <is>
           <t>Boundary work, or task-related activities with external actors, has been shown to positively influence small group performance. However, these "external activities" may also detract from important internal group processes that help groups function. This research examines the puzzle of how groups can perform external activities without compromising their internal group dynamics. I explore how groups perform boundary work and consider the effectiveness of different methods of boundary work from a group identity perspective. Using both qualitative and quantitative methods in experimental and field-based settings, I compare and contrast boundary work that involves sending group members outside the group boundary to interact with external actors individually (i.e., an outward-bound approach), with an inward-bound approach, which entails inviting outsiders in to provide information, resources, or support to the group as a whole. Across four studies, I find that an inward-bound approach to boundary work strengthens group identity and subsequent group satisfaction and viability (Studies 1, 2 and 4), an outward-bound approach used in combination with an inward-bound approach can positively influence task performance and group satisfaction and viability (Study 4), and that an initially weak group identity leads group members to choose an inward-bound approach over an outward-bound approach when interacting with outsiders (Studies 1, 3 and 4). The main contributions of this work are 1) delineating different ways in which groups interact with outsiders, 2) considering the nature of the relationships between boundary work methods and group identity, and 3) investigating the consequences of performing these methods of boundary work using multiple criteria of group effectiveness. Findings converge to reveal that inward boundary work is an important phenomenon for organizational groups. Ultimately, this research offers a more nuanced view of the external perspective of small groups by suggesting that the ways in which groups interact with outsiders are both multidimensional and consequential.</t>
@@ -8212,7 +8710,11 @@
           <t>2030</t>
         </is>
       </c>
-      <c r="P158" s="8" t="n"/>
+      <c r="P158" s="8" t="inlineStr">
+        <is>
+          <t>The dissertation investigates group boundary work at the team level. Study 1 aggregates data to N=9 hospital senior leadership teams. Studies 2 and 3 are scenario-based experiments where boundary work is either an experimental manipulation or a categorical choice, lacking individual-level zero-order correlation data for BSB. Study 4 aggregates data to N=65 MBA student groups and reports correlations at the team level. As the analyses are conducted at the team level rather than the individual employee level, the study must be excluded.. Verbatim Evidence: "To test the hypotheses I used ordinary least squares regression with variables measured or calculated at the group level... Table 2.3. Correlations Among Study Variables. N = 9... Table 4.2. Means, Standard Deviations, and Correlations among Study Variables. Sample size ranged from 58 to 65 (groups) because of missing data."</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="18" customHeight="1" s="10">
       <c r="A159" t="inlineStr">
@@ -8225,6 +8727,16 @@
           <t>BSMA0156</t>
         </is>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G159" t="inlineStr">
         <is>
           <t>Top management teams (TMTs) interact with key external stakeholders through boundary spanning, often by holding outside directorships. Yet research suggests these activities have an equivocal relationship with firm financial performance. Although outside directorships promise informational benefits (i.e., the social network perspective), they also present challenges in the form of managerial opportunism (i.e., the agency perspective). Here, we adopt a contingency perspective to reconcile these perspectives, investigating the moderating role of cohesion, or the degree to which team members mutually support and get along with one another. We argue that boundary spanning will yield performance benefits for TMTs with high cohesion, because their increased commitment to the team will enable members to use their external relationships for the benefit of their firms. However, we also identify a boundary condition for this effect based on structural position in the TMT: that cohesion is especially relevant when proportionally more non-chief executive officer (CEO) TMT members span boundaries than CEOs span boundaries. Results from an archival study of TMTs using q-sort methodology provide support for these predictions.</t>
@@ -8250,7 +8762,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P159" s="8" t="n"/>
+      <c r="P159" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates boundary spanning at the Top Management Team (TMT) level through outside directorships. The unit of analysis is the team (N = 48 TMTs), and the boundary spanning variable represents a team-level aggregated construct (sum of outside directorship ties for each TMT member). Because the correlations and analyses are conducted at the team level rather than the individual employee level, the study must be excluded.. Verbatim Evidence: "Our sample was taken from a larger study of leadership teams of large publicly traded organizations and consisted of 48 TMTs. In line with previous research, the TMT was defined as the CEO and those senior executives who reported directly to him or her... To assess TMT boundary spanning, we adapted measures used in previous research on boundary spanning in the form of outside directorships... First, we counted and summed the number of outside ties for each TMT member in each year and averaged them over the Group Dynamic Q-sort (GDQ) time period... Table 1. Descriptive Statistics and Correlations Among Variables... Note. N = 48 teams; CEO = chief executive officer; TMT = top management team;"</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="18" customHeight="1" s="10">
       <c r="A160" t="inlineStr">
@@ -8263,6 +8779,16 @@
           <t>BSMA0157</t>
         </is>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr">
         <is>
           <t>Multiteam systems are increasingly used by organizations, but are difficult to coordinate effectively. Building from theory on representational gaps, we explain why coordination between teams in multiteam systems can be hindered by inconsistencies that exist between them regarding the definition of shared problems. We argue that frame-of-reference training, an intervention that is theorized to reduce representational gaps, can facilitate coordination and subsequent performance in multiteam systems. We studied the effects of frame-of-reference training on multiteam system coordination and performance in 249 multiteam systems comprised of specialized teams. Supporting our expectations, we found that: (a) frame-of-reference training had a positive effect on multiteam system performance by enhancing between-team coordination; (b) within-team coordination improved the relationship between frame-of-reference training and between-team coordination, ultimately improving multiteam system performance; and (c) the patterns by which within-team coordination leveraged our intervention depended on teams’ specific functions. Our findings extend representational gaps theory, highlight the interdependencies between team-level and system-level coordination, and demonstrate the utility of frame-of-reference training in a new setting.</t>
@@ -8288,7 +8814,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P160" s="8" t="n"/>
+      <c r="P160" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts its analysis at the multiteam system level (N = 249 multiteam systems, not individuals). The correlation matrix reports relationships between team/system-level aggregated constructs (e.g., between-team coordination, multiteam system performance). It lacks individual-level boundary spanning effect sizes.. Verbatim Evidence: "A total of 3,486 officers were randomly assigned to one of 249 14-person multiteam systems for the entire five-week course, such that each multiteam system was comparable with respect to members’ ability, gender, experience, age, and vocational specialty... Table 1 Descriptive Statistics and Correlations... Notes: n = 249; observations are multiteam systems of 14 members each."</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="18" customHeight="1" s="10">
       <c r="A161" t="inlineStr">
@@ -8301,6 +8831,16 @@
           <t>BSMA0158</t>
         </is>
       </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
           <t>Purpose: This study is designed to respond to repeated calls for research on sales person retentionby building upon a mature research stream to identify ways to reduce turnover in boundary spanning employees and the resultant effect it has on organizational productivity. Specifically, this research draws on the Job Demands-Resources model to explore the effect of employee perceptions of firm market orientation as a way to reduce role stressors and subsequently turnover intentions. It also looks at employee traits that may serve as a buffer to the role stress to turnover intentions link and can be part of the hiring selection process (in this case grit). In so doing, this research uses a sample of early career salespeople to examine the effects of a firm’s market orientation (MO) and selective hiring for specific traits (level of grit) on a salesperson’s intention to quit using Job Demand-Resources as a framework.</t>
@@ -8326,7 +8866,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P161" s="8" t="n"/>
+      <c r="P161" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure Boundary Spanning Behavior (BSB) as a construct. While the authors refer to the sample of salespeople as 'boundary-spanning employees', the study focuses on the effects of job demands and resources on turnover intentions. The constructs measured are perceived firm market orientation (a job-related resource), role conflict, role ambiguity, grit, job satisfaction, and turnover intentions. Since there is no variable capturing BSB, the study lacks an effect size of interest.. Verbatim Evidence: "Purpose: This study is designed to respond to repeated calls for research on sales person retentionby building upon a mature research stream to identify ways to reduce turnover in boundary spanning employees and the resultant effect it has on organizational productivity. Specifically, this research draws on the Job Demands-Resources model to explore the effect of employee perceptions of firm market orientation as a way to reduce role stressors and subsequently turnover intentions. [...] Market orientation was measured on a 14-item scale originally constructed by Narver and Slater (1995)) and adapted by Hooley et al. (2000). [...] Table 1. PLS-SEM results. Latent Variable Correlations: Grit, Job sat., MO, RA, RC, TOI."</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="18" customHeight="1" s="10">
       <c r="A162" t="inlineStr">
@@ -8339,6 +8883,16 @@
           <t>BSMA0159</t>
         </is>
       </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G162" t="inlineStr">
         <is>
           <t>What types of human and social capital identify the emergence of leaders of open innovation communities? Consistent with the norms of an engineering culture, we find that future leaders must first make strong technical contributions. Beyond technical contributions, they must then integrate their communities in order to mobilize volunteers and avoid the ever-present danger of forking and balkanization. This is enabled by two correlated but distinct social positions: social brokerage and boundary spanning between technological areas. An inherent lack of trust associated with brokerage positions can be overcome through physical interaction. Boundary spanners do not suffer this handicap and are much more likely than brokers to advance to leadership. The research separates the influence of human and social capital on promotion, and highlights previously unexamined differences between brokerage- and boundary-spanning positions. Longitudinal analyses of careers within the Internet Engineering Task Force community from 1986–2002 support the arguments.</t>
@@ -8364,7 +8918,11 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="P162" s="8" t="n"/>
+      <c r="P162" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes longitudinal data of 610 individuals observed over 5,066 trimesters. The correlation matrix (Table 2) is based on these N=5,066 person-period observations, which violates statistical independence because the same individuals are repeated across multiple observations (Code 3). Furthermore, the dependent variable of interest (individual appointment as a working group leader) is not included in the correlation matrix. The variable 'Incumbent WG chairs' is a community-level control variable rather than the individual leadership outcome. Consequently, no valid zero-order effect size (r) between boundary spanning and the outcome can be extracted (Code 1).. Verbatim Evidence: "Tables 1 and 2 describe the 610 subjects who published prior to working group chair appointment or censoring, observed over 5,066 trimesters. The dependent variable Leader is a categorical indicator that a subject appears as a working group leader at the end of the current observation period. ... [Table 2] Bivariate Correlation Matrix for Network Risk Set (N = 5,066 Observations) ... Incumbent WG chairs is a count of incumbents (those not at risk of a first leadership position) holding chair positions and is intended to gauge the extent to which the community currently fulfills its leadership needs."</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="18" customHeight="1" s="10">
       <c r="A163" t="inlineStr">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -8935,6 +8935,16 @@
           <t>BSMA0160</t>
         </is>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G163" t="inlineStr">
         <is>
           <t>In the water and energy sectors, projects geared towards new forms of cross-sectoral functioning have boomed in most European countries over the past decade, and have deeply transformed the ecology of urban services. These projects are often considered as an answer to a rising challenge affecting numerous traditional utilities: the unforeseen urban change relating to shifting (i.e. declining) demand patterns that are undermining traditional models of infrastructure management. The development of cross-sectoral strategies is considered a way both to tackle the attrition of traditional sources of revenue and to develop greener infrastructure systems by enhancing their efficiency level, often in line with low-carbon programmes implemented by national or local governments. The appeal lies in a fairly static perception of infrastructure management and technological change. Based on a detailed analysis of a traditional German local multi-utility and informed by a six-month internship within the company, the article deciphers the rationale of multi-sectoral practices, in particular the company’s transformation into a cross-utility that devised a common strategy for all its infrastructure networks and its ambiguities. Various facets of such ‘boundary work’ are analysed, focusing on organisational and financial aspects to reveal the new sites of tensions and negotiations between sectors, but also on the material component of these cross-sectoral projects through the case of one such nexus programme, a waste-toenergy programme. This programme embodies the potential contradictions between the call for reduced use of resources (i.e. the production of less waste) and the development of new urban technical systems relying primarily on those same resources.</t>
@@ -8960,7 +8970,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P163" s="8" t="n"/>
+      <c r="P163" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative, ethnographic analysis of a German municipal multi-utility transitioning into a cross-utility. It relies on participant observation (an internship) and interviews to explore cross-sectoral infrastructural practices. It does not provide any quantitative measurements of individual-level boundary spanning behavior, nor does it report any zero-order correlation matrix or extractable effect sizes.. Verbatim Evidence: "Based on a detailed analysis of a traditional German local multi-utility and informed by a six-month internship within the company, the article deciphers the rationale of multi-sectoral practices... To flesh out the reorganisation of a municipal utility and better capture the 'socio-technical geometry of powers in town' (Graham and Marvin, 2001), I decided to immerse myself directly in this technical world by being embedded within the teams of infrastructure management of a German multi-utility... The ethnographic approach conducted here endeavours to fill this gap and to complement studies on practices centred on infrastructure users... Such immersion within the utility produces results that semi-structured interviews with experts and professionals or simple data analysis (which were carried out in parallel) cannot provide"</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="18" customHeight="1" s="10">
       <c r="A164" t="inlineStr">
@@ -8973,6 +8987,16 @@
           <t>BSMA0161</t>
         </is>
       </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G164" t="inlineStr">
         <is>
           <t>This study investigated relationships between middle managers’ formal position, their strategic influence and organizational performance. Among the 259 middle managers represented in the study, managers with formal positions in boundaryspanning sub-units reported higher levels of strategic influence activity than others. At the organizational level of analysis, the study found that firm performance was associated with more uniform levels of downward strategic influence, and more varied levels of upward influence among middle management cohorts. The findings suggest that middle managers’ strategic influence arises from their ability to mediate between internal and external selection environments. In addition, positive effects on organizational performance appear to depend on: (1) whether the overall pattern of upward influence is conducive to shifts in the network centrality of individual managers; and (2) whether the pattern of downward influence is consistent with an appropriate balance between the organization’s need for control and flexibility.</t>
@@ -8998,7 +9022,11 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="P164" s="8" t="n"/>
+      <c r="P164" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study focuses on middle managers' 'strategic influence activity' (upward and downward influence) rather than Boundary Spanning Behavior (BSB). While the authors use managers' functional departments (e.g., marketing vs. finance) as a categorical structural proxy for 'boundary-spanning position', they do not measure BSB itself as a continuous behavioral construct. Upward influence captures hierarchical issue-selling (championing) and synthesizing information, which lacks a valid BSB effect size (Code 1). Furthermore, the core analyses linking these behaviors to outcomes are conducted at the organizational level (N = 15 to 25 firms), correlating firm performance with aggregated dispersion indices of managers' influence behaviors, which violates the individual-level analysis requirement (Code 3).. Verbatim Evidence: "This study investigated relationships between middle managers’ formal position, their strategic influence and organizational performance. ... To classify respondents as having positions with either boundary-spanning or nonboundary-spanning responsibilities, a two-step process was used. First, consistent with criteria specified in Thompson (1967) and elsewhere (Jemison, 1984), three functions (marketing, purchasing, and human resource management) were classified as boundary spanning and four (finance, accounting, operations, and quality control) were classified as non-boundary spanning. ... In the analysis reported here, the items listed in table I under championing and synthesizing were summed to create a scale for each manager’s overall upward influence (alpha = .79). ... Hypotheses 2 and 3 shift the unit of analysis to the organizational level and predict different effects on organizational performance. ... Specifically, the standard deviation of scale scores on the upward and downward strategic activity variables reported by managers in each organization was subtracted from a constant to produce a measure of dispersion in how managers from the same organization reported upward and downward influence activity."</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="18" customHeight="1" s="10">
       <c r="A165" t="inlineStr">
@@ -9011,6 +9039,16 @@
           <t>BSMA0162</t>
         </is>
       </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr">
         <is>
           <t>Self-assessment is increasingly prevalent in many organizations. Although managers perceive self-assessment as internally driven, the well-known link between organizational activities and the external environment suggests that outside forces play a signiﬁcant role. This investigation explores the external motivators of self-assessment through a ﬁeld study of 14 organizations. Five factors were found to link the conduct of self-assessment to the external environment: availability of an externally developed or sponsored model, presence of a boundary spanning individual, afﬁliation with professional and trade associations, pressure from powerful external entities, and potential for external reward or recognition. These ﬁndings suggest that self-assessment is driven signiﬁcantly by forces external to the organization. How these external factors combine to form the context of self-assessment may affect the outcomes of the project.</t>
@@ -9036,7 +9074,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="P165" s="8" t="n"/>
+      <c r="P165" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative exploratory field study based on interviews and observations from 14 organizations, lacking any extractable quantitative effect sizes or a correlation matrix [Code 1]. Furthermore, the unit of analysis is the organization (N=14 organizations), evaluating firm-level self-assessment adoption and external context rather than individual-level employee boundary spanning behavior [Code 3].. Verbatim Evidence: "This investigation explores the external motivators of self-assessment through a field study of 14 organizations. ... The research was carried out in 14 organizations. ... We drew from a number of research methodologies developed by social science scholars for generating theoretically useful output from qualitative data. While Glaser and Strauss’s (1967) grounded theory notion provided a useful methodological framework, we found the techniques of Strauss and Corbin (1990) and Miles and Huberman (1994) effective for operationalizing the theoretical insights from our qualitative data in a systematic fashion. ... Nine of 14 organizations employed individuals who served in a boundary spanning capacity relative to self-assessment. ... Our analysis produced five factors linking an organization’s conduct of self-assessment to its outside world."</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="18" customHeight="1" s="10">
       <c r="A166" t="inlineStr">
@@ -9049,6 +9091,16 @@
           <t>BSMA0163</t>
         </is>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G166" t="inlineStr">
         <is>
           <t>In this paper we test the hypothesis that boundary spanning is a differentiated function that is not necessarily performed by one person, as assumed in much previous research. Using longitudinal network data collected during labor negotiations, we found that some individuals on the bargaining teams ("representatives") broker ties toward their opponents, while others ("gatekeepers") broker ties from their opponents; and some broker task-oriented ties (measured by flows of advice), while others broker socioemotional ties (measured by flows of trust). Differentiation of trust and advice brokerage roles was strong throughout the negotiations, while differentiation of representative and gatekeeper roles became more distinct as the contract deadline (and increased potential for role conflict) neared. This analytic distinction suggests that role conflict must be examined differently, both conceptually and methodologically, and widens the range of options available for managing potential role conflicts.</t>
@@ -9074,7 +9126,11 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="P166" s="8" t="n"/>
+      <c r="P166" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts a longitudinal network analysis of a single case involving 14-16 negotiators. Although it provides a correlation matrix of its network variables, the study only correlates different structural measures of boundary spanning roles with each other (e.g., gatekeeper scores, representative scores, indegree, and outdegree for advice and trust networks). It does not measure or report zero-order correlations between boundary spanning behavior and any external substantive variables (such as antecedents like personality/role conflict or outcomes like job satisfaction/performance). Therefore, it lacks any effect sizes of interest for the meta-analysis.. Verbatim Evidence: "These sociometric data on flows of trust and advice constitute the primary focus of our investigation. Each flow corresponded to one of the two dimensions of interpersonal orientation. Trust provides insight into the socioemotional dimension of group interaction; advice allows for inferences about task orientation. Using this data, raw brokerage scores were calculated, following Gould and Fernandez (1989)... Table 3: Bivariate Correlations (Gatekeeper, Representative, Indegree, Outdegree for Advice and Trust totals)."</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="18" customHeight="1" s="10">
       <c r="A167" t="inlineStr">
@@ -9087,6 +9143,16 @@
           <t>BSMA0164</t>
         </is>
       </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G167" t="inlineStr">
         <is>
           <t>Background: While participatory social network analysis can help health service partnerships to solve problems, little is known about its acceptability in cross-cultural settings. We conducted two case studies of chronic illness service partnerships in 2007 and 2008 to determine whether participatory research incorporating social network analysis is acceptable for problem-solving in Australian Aboriginal health service delivery. Methods: Local research groups comprising 13–19 partnership staff, policy officers and community members were established at each of two sites to guide the research and to reflect and act on the findings. Network and work practice surveys were conducted with 42 staff, and the results were fed back to the research groups. At the end of the project, 19 informants at the two sites were interviewed, and the researchers conducted critical reflection. The effectiveness and acceptability of the participatory social network method were determined quantitatively and qualitatively. Results: Participants in both local research groups considered that the network survey had accurately described the links between workers related to the exchange of clinical and cultural information, team care relationships, involvement in service management and planning and involvement in policy development. This revealed the function of the teams and the roles of workers in each partnership. Aboriginal workers had a high number of direct links in the exchange of cultural information, illustrating their role as the cultural resource, whereas they had fewer direct links with other network members on clinical information exchange and team care. The problem of their current and future roles was discussed inside and outside the local research groups. According to the interview informants the participatory network analysis had opened the way for problem-solving by “putting issues on the table”. While there were confronting and ethically challenging aspects, these informants considered that with flexibility of data collection to account for the preferences of Aboriginal members, then the method was appropriate in cross-cultural contexts for the difficult discussions that are needed to improve partnerships. Conclusion: Critical reflection showed that the preconditions for difficult discussions are, first, that partners have the capacity to engage in such discussions, second, that partners assess whether the effort required for these discussions is balanced by the benefits they gain from the partnership, and, third, that “boundary spanning” staff can facilitate commitment to partnership goals.</t>
@@ -9112,7 +9178,11 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="P167" s="8" t="n"/>
+      <c r="P167" s="8" t="inlineStr">
+        <is>
+          <t>The study is a participatory case study evaluating the acceptability of social network analysis as a problem-solving method in health service partnerships. While it conducted network surveys (N=42) and reports mean network links and t-tests comparing groups, it does not provide an extractable zero-order correlation matrix (r) or equivalent regression statistics between individual-level boundary spanning behavior and other constructs. Thus, it lacks the quantitative effect sizes required for the meta-analysis.. Verbatim Evidence: "We conducted two case studies of chronic illness service partnerships in 2007 and 2008 to determine whether participatory research incorporating social network analysis is acceptable for problem-solving in Australian Aboriginal health service delivery... Network and work practice surveys were conducted with 42 staff, and the results were fed back to the research groups... The tables provide summary measures of the different types of links. The main finding from the data in Table 5 was a dense network of workers linked on the exchange of team care but a much less dense network of workers linked on the exchange of management and planning or policy development."</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="18" customHeight="1" s="10">
       <c r="A168" t="inlineStr">
@@ -9125,6 +9195,16 @@
           <t>BSMA0165</t>
         </is>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G168" t="inlineStr">
         <is>
           <t>This paper reports on an important subgroup of international boundary-spanners – immigrants and second or third generation migrants from the MNC’s home country living in the subsidiary host country. We take as our example the Nikkeijin (Japanese immigrants and their descendants) in Brazil. Such bicultural people are a largely unexplored source of boundary-spanning internationally competent talent for multinational enterprises. Using two different surveys, we ﬁnd that this group is recognized as a source of talent by Japanese MNCs, but that their HRM practices are not appropriate to attract and use them in their global talent management programmes.</t>
@@ -9150,7 +9230,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P168" s="8" t="n"/>
+      <c r="P168" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts two surveys to evaluate Nikkeijin as potential boundary-spanners. However, it does not provide an extractable zero-order correlation matrix (r) or regression effect sizes between a measure of individual Boundary Spanning Behavior (BSB) and other constructs. The statistical analyses are limited to descriptive statistics, t-tests comparing group means (e.g., generations, manufacturing vs. non-manufacturing), and factor analyses of survey items. Therefore, the paper lacks an extractable quantitative effect size of interest for the meta-analysis.. Verbatim Evidence: "These hypotheses are tested through two surveys: The first of these was a survey of Japanese-affiliates in Brazil, the second survey was of the Nikkeijin (Japanese Brazilians) themselves. The first survey was conducted in Brazil, in São Paulo. The survey target was 180 Japanese affiliated companies... Responses were obtained from 65 different corporations... The second survey, targeting the Nikkeijin living in Japan, was conducted in the Prefectures of Aichi... There were 157 responses... Additionally, t-tests were performed to measure the differences between the manufacturing and non-manufacturing sectors... The questions used five-point Likert scales and t-tests were applied to assess the changes of their Japanese proficiency and lifestyles... [Tables 2-6 and Appendices A-D report only means, t-values, and factor analysis results]."</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="18" customHeight="1" s="10">
       <c r="A169" t="inlineStr">
@@ -9163,6 +9247,14 @@
           <t>BSMA0166</t>
         </is>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>999</v>
+      </c>
       <c r="G169" t="inlineStr">
         <is>
           <t>Self-initiated expatriates (SIEs) who work for a subsidiary of a multinational enterprise from their country of origin and hence are familiar with both countries’ language and culture can be expected to act as boundary-spanners between the assigned expatriates sent from the parent country and host country nationals, and between the headquarters and the subsidiary. We develop a new model of boundary-spanning that encompasses both individual and organizational antecedents and validate the model using survey data from Japanese-affiliated companies in China. We find that familiarity with Chinese language and culture and the potential dual allegiance of SIEs contribute to enhancing their boundary-spanning behavior. We also find that relationships of trust among the parties concerned (social capital) and global career opportunities for such self-initiated expatriates (geocentric staffing) have positive influences on their dual allegiance. Finally, normative and systems integration of human resource management are associated with increasing levels of social capital and geocentric staffing.</t>
@@ -9188,7 +9280,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P169" s="8" t="n"/>
+      <c r="P169" s="8" t="inlineStr">
+        <is>
+          <t>The study quantitatively examines the boundary-spanning functions of individual self-initiated expatriates (SIEs) working in Japanese subsidiaries in China. It measures intra-organizational boundary spanning behavior (acting as a bridge between the local operation and the headquarters, and between assigned expatriates and local staff) at the individual level (N=91 SIEs) using supervisor ratings. The study provides a full zero-order correlation matrix in Appendix 3, satisfying the requirement for extractable effect sizes. Under the Override Rule for Intra-Organizational BSB, this is a valid BSB construct.. Verbatim Evidence: "We collected the evaluations of 91 Japanese SIEs which cover 57% of the total Japanese SIEs employed... To test the boundary-spanning functions of Japanese SIEs, we focused on the two major cross-cultural interfaces which could be influenced by individual skills and/ or human resource management: The interface between Japanese assigned expatriates and Chinese staff in the Chinese subsidiary, and that between the Japanese-affiliates in China and the headquarters in Japan. Respondents were asked about the extent to which each SIE acts as a bridge between Japanese AEs and Chinese employees as well as between the Chinese operation and the headquarters in Japan... Appendix 3: Descriptive statistics (Mean and Standard Deviation) and correlations of variables."</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="18" customHeight="1" s="10">
       <c r="A170" t="inlineStr">
@@ -9201,6 +9297,16 @@
           <t>BSMA0167</t>
         </is>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr">
         <is>
           <t>The god of this paper is to iden@ the communication tactics that tiow management teams to successtiy coordinate without becoming overloaded, and to see whether successti coordination and fidom from overload independently Muence team pefiormance. We found that how much teams comnumicatti, what they communicated abou~ and the technologies they used to communicate prdlcted coordination and overload. Team coordination but not overload prdlcted team SUWSS.</t>
@@ -9226,7 +9332,11 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="P170" s="8" t="n"/>
+      <c r="P170" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a student sample (277 students participating in a management simulation game), which violates the inclusion criteria requiring data from organizational employees (Code 2). Additionally, the study does not measure boundary spanning behavior but rather intra-team communication strategies and cognitive overload, and it lacks an extractable zero-order correlation matrix (Code 1).. Verbatim Evidence: "Participants consisted of 277 students, organized into 50 five or six member teams, who participated in the Management Game during the Spring and Fall of 1997. Of these teams, 39 consisted of full-time students and 11 consisted of part-timers... The goal of this paper is to identify the communication tactics that allow management teams to successfully coordinate without becoming overloaded, and to see whether successful coordination and freedom from overload independently influence team performance."</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="18" customHeight="1" s="10">
       <c r="A171" t="inlineStr">
@@ -9239,6 +9349,16 @@
           <t>BSMA0168</t>
         </is>
       </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G171" t="inlineStr">
         <is>
           <t>The paper explores DiMaggio and Powell's thesis that under conditions of uncertainty organizational decision makers will mimic the behavior of other organizations in their environment. We add to their discussion by positing that managers are especially likely to mimic the behavior of organizations to which they have some type of network tie via boundary-spanning personnel. Data are presented on the charitable contributions of 75 business corporations to 198 nonprofit organizations in the Minneapolis-St. Paul metropolitan area in 1980 and 1984. Using logistic regression models, we found that a firm is likely to give more money to a nonprofit that was previously funded by companies whose CEOs and/or giving officers are known personally by the firm's boundary-spanning personnel. Firms are also likely to give greater contributions to a nonprofit that is viewed more favorably by the local philanthropic elite. We also found that a nonprofit is likely to receive more money from a corporation that previously gave money to nonprofits whose directors sit on the nonprofit's board. We concluded that managers utilize the information gathered through extraorganizational, interpersonal networks to make decisions on how to relate to other organizations in their task environment and achieve organizational ends.</t>
@@ -9264,7 +9384,11 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="P171" s="8" t="n"/>
+      <c r="P171" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates mimetic processes and corporate contributions at the interorganizational and dyadic level, analyzing 14,850 dyads formed by 75 corporations and 198 nonprofits. The dependent variable is the size of corporate donations, and the unit of analysis is the firm-to-firm dyad, not individual-level employee boundary spanning behavior.. Verbatim Evidence: "Data are presented on the charitable contributions of 75 business corporations to 198 nonprofit organizations in the Minneapolis-St. Paul metropolitan area in 1980 and 1984. ... The units of analysis were the dyads formed by the 75 corporations and 198 nonprofits in the study population. ... As noted above, there are 14,850 dyads, each consisting of a corporation and a nonprofit. We postulate a logit model for the state of every dyad for each model"</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="18" customHeight="1" s="10">
       <c r="A172" t="inlineStr">
@@ -9277,6 +9401,16 @@
           <t>BSMA0169</t>
         </is>
       </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G172" t="inlineStr">
         <is>
           <t>The present study examines a set of organizational predictors of first moves. More specifically, the study employed organizational information-processing theory to derive a set of hypotheses relating organizational characteristics to the level of first- mover activity. This archival study used a pooled cross section-time series data set of domestic airlines over an 8-year period.
@@ -9303,7 +9437,11 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="P172" s="8" t="n"/>
+      <c r="P172" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the firm (domestic airlines), rather than individual employees. Boundary spanning is measured at the organizational level using the number of marketing vice-presidents as a percentage of total vice-presidents and expenditures for promotion as a percentage of sales. It does not measure the interpersonal boundary spanning behavior of individual employees.. Verbatim Evidence: "This archival study used a pooled cross section-time series data set of domestic airlines over an 8-year period. ... As noted, the unit of analysis is the level of first-mover activity within each year. This level was calculated for each airline, for each year, by summing the number of times it initiated a first move in a specific year. ... Measures of boundary spanning and specialization were obtained for each airline, for each year, from the Air Carrier Financial Statistics. ... More specifically, the amount of boundary spanning was measured by the number of marketing vice-presidents as a percent of total vice-presidents and expenditures for promotion as a percent of sales."</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="18" customHeight="1" s="10">
       <c r="A173" t="inlineStr">
@@ -9316,6 +9454,16 @@
           <t>BSMA0170</t>
         </is>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G173" t="inlineStr">
         <is>
           <t>Purpose – More enterprises adopt open innovation by breaking technological or organizational boundaries to seek internal and external knowledge when they face a fiercely competitive environment, complex market demands, and increasingly rapid technological change. In this context, a knowledge search strategy is regarded as an effective means of obtaining inside and outside resources and an important way to break the innovation bottleneck. Moreover, information technology (IT) is deemed an important asset for sourcing knowledge, whereas absorptive capacity is seen as an indispensable ability for utilizing novel knowledge. Thus, this paper aims to test the role of knowledge search in open innovation and examine the mediating effect of absorptive capacity and the moderating effect of IT capability.</t>
@@ -9341,7 +9489,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P173" s="8" t="n"/>
+      <c r="P173" s="8" t="inlineStr">
+        <is>
+          <t>The study examines firm-level knowledge search (local and boundary-spanning search) and its impact on product and process innovation. The data was collected via interviews with top managers acting as key informants for their establishments (N=1,088 firms). The survey items explicitly refer to the 'establishment' (e.g., 'in what ways has this establishment introduced new products...'), measuring macro-level organizational search channels and external relationships rather than individual-level interpersonal boundary spanning behavior. Therefore, it is excluded for being at the firm level of analysis.. Verbatim Evidence: "To test our hypotheses, we use data from the official survey on the innovative activities of the People’s Republic of China manufacturing firms conducted by the office of the World Bank. ... Following a two-stage procedure, a screening phase over the phone and a face-to-face interview with the top manager of each establishment... In the questionnaire, the item “in what ways has this establishment introduced new products or services and new or improved process?” is used for identifying knowledge search. ... LS is a binary variable 1 if the establishment developed or adapted in house, 0 otherwise. Moreover, BSS is defined as an index constructed as the sum of ways that firms introduced innovative activities."</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="18" customHeight="1" s="10">
       <c r="A174" t="inlineStr">
@@ -9354,6 +9506,16 @@
           <t>BSMA0171</t>
         </is>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr">
         <is>
           <t>With an increasing overlap between the work and non‐work domain, more research is needed to understand the factors that relate to how individuals manage their boundaries across multiple roles (i.e., work roles, family roles). Using a sample of 498 individuals, we explored the relationships between personality, O*NET job characteristic variables, and boundary management styles. Results revealed that job responsibility and work structure related to cross‐role interruptions and work identity centrality. Further, conscientiousness was related to greater perceptions of boundary control, family identity centrality, and fewer interruptions of work, while neuroticism was related to fewer interruptions of non‐work. Finally, the present findings replicated four of six defined boundary management styles put forth in prior research. Theoretical and practical implications are discussed.                                         Practitioner points                                                                        Individuals may differ in how they enact boundaries between work and non‐work as related to their individual personality.                                                           The job in which one works may relate to the manner in which boundaries between work and non‐work are managed.                                                           Organizational efforts to help employees with boundary management may be improved if job context and employee individual differences are noted and accommodated.</t>
@@ -9379,7 +9541,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P174" s="8" t="n"/>
+      <c r="P174" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on boundary management between work and non-work (family/personal life) domains, rather than inter-organizational or intra-organizational boundary spanning behavior. Studies investigating work-family or work-life boundary management lack the effect size of interest for this meta-analysis.. Verbatim Evidence: "With an increasing overlap between the work and non-work domain, more research is needed to understand the factors that relate to how individuals manage their boundaries across multiple roles (i.e., work roles, family roles). [...] Although researchers agree that individuals differ in how they manage their work and home life (Ammons, 2013; Bulger, Matthews, &amp; Hoffman, 2007; Kossek, Ruderman, Braddy, &amp; Hamm, 2012; Sturges, 2012) and there is considerable research on what drives individual preferences as to how to manage boundaries (Kreiner et al., 2009), there are few studies exploring other factors that influence individuals’ boundary management"</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="18" customHeight="1" s="10">
       <c r="A175" t="inlineStr">
@@ -9392,6 +9558,16 @@
           <t>BSMA0172</t>
         </is>
       </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr">
         <is>
           <t>The digital era is radically changing our societies and how ﬁrms do business. Innovating the business model has become a fundamental capability to survive competition, particularly for small and mediumsized enterprises (SMEs). This study investigates the digital-era role of boundary management capabilities in the processes of Business Model Innovation (BMI) in SMEs. Structural Equation Modelling is adopted to analyse data from a survey of 250 Italian experts who possess direct research and consulting experience with SMEs. Our ﬁndings reveal that digitalisation and ﬁrms’ boundaries aﬀect BMI in SMEs. Moreover, our results demonstrate how boundary management, speciﬁcally its technological and relational aspects, directly impacts BMI and mediates the relationship between boundary size and BMI. The study also oﬀers important theoretical and practical insights, calling on scholars and managers to give more attention to the boundary management of SMEs in order to support BMI.</t>
@@ -9417,7 +9593,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P175" s="8" t="n"/>
+      <c r="P175" s="8" t="inlineStr">
+        <is>
+          <t>[Code 2 &amp; Code 3] The study surveys professionals, academics, and consultants acting as key informants to evaluate firm-level variables for SMEs, specifically the SME's boundary size, firm-level boundary management capabilities, and business model innovation. It does not measure the interpersonal boundary spanning behavior of individual embedded employees. Therefore, it is excluded for using a non-employee sample (Code 2) and analyzing firm-level constructs (Code 3).. Verbatim Evidence: "We administered an online questionnaire to a sample set of Italian professionals who possess direct expertise in managing and/or consulting with SMEs about strategic decisions. ... Survey administration took place in late 2018 through the members list of the Italian Association of Business Administration and Management (AIDEA – Accademia Italiana di Economia Aziendale), which comprises 2,287 academics in business administration... Most of the AIDEA members are administrators, CEOs, advisors or consultants in both Italian and foreign companies. Only those with an active managerial or consulting role in one or more SME were included in the sample. ... Respondents were asked to indicate the extent to which the boundary area of SMEs had increased in size. The construct of boundary management capability was operationalised through three first-order constructs. To measure relational boundary management (RBM), cultural boundary management (CBM) and technological boundary management (TBM), we used a scale adapted from Caputo, Fiorentino, and Garzella (2018). To measure BMI, we used a scale adapted from previous studies..."</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="18" customHeight="1" s="10">
       <c r="A176" t="inlineStr">
@@ -9430,6 +9610,16 @@
           <t>BSMA0173</t>
         </is>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G176" t="inlineStr">
         <is>
           <t>This study investigated how a project group deals with the contradiction between distributed knowledge in boundary-spanning collaborative processes and the expectation that software systems will provide unified, codified knowledge. It employed an ethnographic, interpretive approach to examine the ways in which relevant knowledge was presented, recognized, shared or otherwise managed during a project concerned with the joint design of business process and IT systems change. Developing a group understanding of how to manage sensemaking and expertise across salient knowledge boundaries were discovered to be central to perceptions of project completion. Four stages of this development were identified. The contribution of this paper is to propose these stages as the basis for boundary-spanning group management approaches and to suggest ways of progressing the complexities of communication, consensus-building, information exchange, problem-formulation and solution-brokering that are fundamental to collaboration in IS definition. These processes are normally taken for granted, rationalized or ignored by managers of IT-related organizational change. The use of specific types of boundary-object may aid in managing such processes explicitly and ensuring rapid progress. Thus the findings have significant implications for research and practice in other forms of boundary-spanning group collaboration, such as organizational innovation and problem-solving.</t>
@@ -9455,7 +9645,11 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="P176" s="8" t="n"/>
+      <c r="P176" s="8" t="inlineStr">
+        <is>
+          <t>The paper is an ethnographic field study utilizing qualitative methods (participant observation, interviews, workshops) to investigate boundary-spanning collaborative design. It does not provide any quantitative effect sizes or a correlation matrix, thereby lacking the extractable statistical data required for the meta-analysis.. Verbatim Evidence: "It employed an ethnographic, interpretive approach to examine the ways in which relevant knowledge was presented, recognized, shared or otherwise managed during a project concerned with the joint design of business process and IT systems change... A longitudinal field study was conducted using an interpretive, ethnographic approach to data collection and analysis (Schwandt, 1998). Data collection was performed via three means: 1. Participant observation of a boundary-spanning design group. ... 2. Ad hoc interviews were conducted with group members ... 3. Group workshops were held ... The study used inductive qualitative analysis techniques"</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="18" customHeight="1" s="10">
       <c r="A177" t="inlineStr">
@@ -9468,6 +9662,14 @@
           <t>BSMA0174</t>
         </is>
       </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>999</v>
+      </c>
       <c r="G177" t="inlineStr">
         <is>
           <t>Research Summary: This paper builds theoretical arguments and shows empirical evidence of the direct benefits and indirect costs of corporate volunteering in developing countries. Spanning corporate and humanitarian sectors to work in challenging environments should activate motivational and learning benefits for participating employees. However, results from a field study of a 10-year partnership between logistics provider TNT and the United Nations World Food Program show that such boundary-spanning corporate social responsibility (CSR) can be a double-edged sword. Task interdependence with nonprofit peers while volunteering strengthens employees' partnership identification and institutional learning. However, institutional learning triggers identity strain (associated with attrition) when they return, unless firms foster a sense that they recognize CSR experiences as valuable. The findings inform the behavioral and microfoundations of the potential consequences of CSR.</t>
@@ -9493,7 +9695,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P177" s="8" t="n"/>
+      <c r="P177" s="8" t="inlineStr">
+        <is>
+          <t>The study surveys individual corporate volunteers (TNT employees) who act as boundary spanners while working with a nonprofit partner organization (WFP). The primary independent variable, 'task interdependence', is measured using behavioral items capturing the extent to which the volunteers engaged in coordination with the partner's employees (e.g., working as a team, making joint decisions, and discussing crucial project steps). This aligns with the 'Implanted Boundary Spanner' inclusion rule, as it captures purposive cross-boundary coordination behavior by individuals in a boundary-spanning role. The study provides a full zero-order correlation matrix at the individual level (N=101), yielding extractable effect sizes of interest.. Verbatim Evidence: "Reflecting the depth of such boundary-spanning, this study's primary independent variable is thus employees' task interdependence with nonprofit peers, or 'the extent to which group members rely on one another to complete their jobs' (Van de Ven, Delbecq, &amp; Koenig Jr., 1976, p. 324). I used a composite scale of three items asking respondents about the extent to which they worked as a team with WFP employees on the project, made decisions concerning the project jointly, and discussed crucial project steps together before carrying them out (α = 0.87). Table 1 Descriptive statistics [provides correlation matrix for N=101 observations]."</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="18" customHeight="1" s="10">
       <c r="A178" t="inlineStr">
@@ -9506,6 +9712,16 @@
           <t>BSMA0175</t>
         </is>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G178" t="inlineStr">
         <is>
           <t>In this study we examine the impact of market orientation of leaders on their leader-member exchange (IMX) with their followers. We review the evolution of leader-member exchange (LMX) theory over the exist five decades, and relate the strategic influence of increasing turbulence in the market environment on multiple generations of leadership styles during that period. Whereas vertical dyadic exchanges between hierarchical leaders and their followers may produce satisfactory performance of followers in equilibrium markets with predictable growth, these dyadic exchanges fail to do so in turbulent markets. Disequilibrium markets with disruptive turbulence demand introduction of discontinuous innovation from a new generation of market-oriented lateral leaders working closely with their boundary-spanning followers. We propose a number of hypotheses relating the market environment, leader-member exchange, and performance. Implications for managers and future researchers are discussed.</t>
@@ -9531,7 +9747,11 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="P178" s="8" t="n"/>
+      <c r="P178" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a conceptual review that proposes a theoretical model and hypotheses regarding the evolution of leader-member exchange (LMX) theory and market-oriented lateral leaders in turbulent markets. It does not contain an empirical study with primary data or a correlation matrix, explicitly stating that the hypotheses are tested in a separate study. Therefore, it is excluded as a non-primary study.. Verbatim Evidence: "We review the evolution of leader-member exchange (LMX) theory over the past five decades, and relate the strategic influence of increasing turbulence in the market environment on multiple generations of leadership styles during that period... We propose a number of hypotheses relating the market environment, leader-member exchange, and performance... In a separate study, these hypotheses are empirically tested."</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="18" customHeight="1" s="10">
       <c r="A179" t="inlineStr">
@@ -9544,6 +9764,16 @@
           <t>BSMA0176</t>
         </is>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr">
         <is>
           <t>We examine the extent to which executives' boundary spanning relations inside and outside their industry affect organizational strategy and performance. We posit that the informational and social influences of external ties will be reflected in the degree to which the organization's strategy conforms to or deviates from the central tendencies of its industry and that the alignment of executives' external ties with the firm's strategy will be beneficial to firm performance. Using a multiyear sample of firms in the branded foods and computer industries, we find that executives' intraindustry ties are related to strategic conformity, that extraindustry ties are associated with the adoption of deviant strategies, and that alignment of executives' external ties with the informational requirements of the firm's strategy enhances organizational performance. Our results also show that a unique or differentiated strategy is not universally advantageous and that the benefits accruing from strategic conformity are especially strong in the more uncertain computer industry.</t>
@@ -9569,7 +9799,11 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="P179" s="8" t="n"/>
+      <c r="P179" s="8" t="inlineStr">
+        <is>
+          <t>The study examines the external ties of top management teams (TMTs) using archival data, aggregating the variables to the firm or team level (N = 55 firms, 275 firm-year observations). The boundary spanning measures (e.g., trade association leadership, outside directorships) are calculated for the entire team and divided by team size. Because the correlations represent team-level aggregated constructs rather than individual-level employee behaviors, the study must be excluded.. Verbatim Evidence: "For each year (time t), we calculated the total number of external ties of all members of the top management team for each form of intra- and extraindustry linkage examined (specified below). Since the number of external ties covaries with top management team size, we divided intra- and extraindustry tie measures by team size... we examined a total of 55 firms that we examined over a baseline five-year period (fiscal years 1983-1987). With pooling (discussed below), we examined a total of 275 firm-year observations."</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="18" customHeight="1" s="10">
       <c r="A180" t="inlineStr">
@@ -9582,6 +9816,16 @@
           <t>BSMA0177</t>
         </is>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr">
         <is>
           <t>The relationship between external communication and R&amp;D team creativity has received increasing attention in the R&amp;D management literature. However, little is known about the motivational mechanism between the two. We propose a second‐stage moderation model based on social cognitive theory to explain whether, how and when R&amp;D team’s external developmental feedback motivates its creativity. Using the data gathered from 452 R&amp;D team members and 84 supervisors in a time‐lagged field study, we found external developmental feedback had a positive effect on R&amp;D team creativity via increasing team creative efficacy. Further, conditional indirect effect analyses found that a high level of cooperative goal interdependence strengthened the positive effect of team creative efficacy on R&amp;D team creativity and the mediating effect of team creative efficacy between external developmental feedback and R&amp;D team creativity.</t>
@@ -9607,7 +9851,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P180" s="8" t="n"/>
+      <c r="P180" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts its analysis at the team level rather than the individual employee level. Individual responses from team members were aggregated, and the final sample size and correlation matrix are based on N = 84 R&amp;D teams. Additionally, the boundary-spanning construct (external developmental feedback) was explicitly adapted to a team-level scale using the referent 'My team', which violates the individual-level analysis requirement.. Verbatim Evidence: "To reduce potential biases when individual responses were aggregated to the team level, we used a 60% response rate as the criterion for including teams in the analyses (Somech and Drach-Zahavy, 2013), resulting in a final sample of 84 teams... consisting of 452 team members and 84 supervisors... Zhou’s (2003) original individual-level scale was adapted into team-level scale by changing ‘I’ into ‘My team’ (Deshon et al., 2004). Sample item was ‘While giving my team feedback, external clients, experts, funding sources, or other external stakeholders focus on helping the team to learn and improve’... The tests supported the appropriateness of aggregating individual-level data to the team level... Table 1. Descriptive statistics, composition reliability values, Cronbach’s alpha coefficients, correlations, and square roots of AVE... 1n = 84"</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="18" customHeight="1" s="10">
       <c r="A181" t="inlineStr">
@@ -9620,6 +9868,16 @@
           <t>BSMA0178</t>
         </is>
       </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G181" t="inlineStr">
         <is>
           <t>This article explores the following hypothesis: There is a statistically significant relationship between a project manager’s leadership competencies and project success. Two proven questionnaires, the leadership dimensions questionnaire (LDQ) and the project success questionnaire (PSQ), were used to gather data from 52 project managers and project sponsors from a financial services company in the United Kingdom. The results from the LDQ and PSQ are presented in this article. A factor analysis of PSQ revealed three independent factors: usability, project delivery, and value of output to clients. The last factor is not related to project leadership or management, so the article concentrates on correlations between the other two factors and project leadership. Eight separate leadership dimensions were found to be statistically significantly related to performance, so the hypothesis was largely supported. Identifying such relationships provides managers with guidance on possible selection and project improvement models, whereby increased capability in leadership dimensions can lead to increased success in project management.</t>
@@ -9645,7 +9903,11 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="P181" s="8" t="n"/>
+      <c r="P181" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the relationship between a project manager's leadership competencies (measured via the Leadership Dimensions Questionnaire) and project success. It assesses dimensions such as emotional intelligence, intellectual competencies, and managerial competencies (e.g., self-awareness, influencing, managing resources), but does not measure any form of purposive Boundary Spanning Behavior (BSB) across inter-organizational or intra-organizational boundaries.. Verbatim Evidence: "This article explores the following hypothesis: There is a statistically significant relationship between a project manager’s leadership competencies and project success. Two proven questionnaires, the leadership dimensions questionnaire (LDQ) and the project success questionnaire (PSQ), were used to gather data from 52 project managers and project sponsors from a financial services company in the United Kingdom. ... Dulewicz and Higgs (2005) provided full details of the LDQ, but essentially the model proposes seven EQ dimensions, five MQ competencies, and three IQ competencies. Titles of the 15 leadership dimensions appear in Table 1."</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="18" customHeight="1" s="10">
       <c r="A182" t="inlineStr">
@@ -9658,6 +9920,16 @@
           <t>BSMA0179</t>
         </is>
       </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G182" t="inlineStr">
         <is>
           <t>Leader-member exchange (LMX) is a multidimensional construct seeking to identify the quality of the relationship between the leader and immediate subordinate. An instrument developed by Schrie-sheim, Neider, Scandura, and Tepper (1992) was utilized to determine the LMX score of 798 non-managerial employees in a casual restaurant chain. The dimensions of perceived contribution, affect, and loyalty were examined. Results demonstrate that LMX quality was high among the surveyed employees of a restaurant chain. The scores of LMX on age, gender and job tenure differed among employees while LMX scores on job status, education, and job type did not differ significantly.</t>
@@ -9683,7 +9955,11 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="P182" s="8" t="n"/>
+      <c r="P182" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses entirely on Leader-Member Exchange (LMX) quality and its subdimensions (perceived contribution, loyalty, and affect) among non-managerial restaurant employees. It does not measure any form of boundary spanning behavior (neither inter-organizational nor intra-organizational). Thus, it lacks the target construct and effect size of interest for this meta-analysis.. Verbatim Evidence: "The goal of the present study was to further examine LMX theory as related to restaurant employees and to offer suggestions as to improving the exchange relationship. Consequently, this study had three purposes... For the purposes of this study, Leader Member Exchange quality was assessed using a six-item LMX-6 scale developed by Schriesheim, Neider, Scandura, and Tepper (1992). The three components, perceived contribution, loyalty, and affect, were identified by two questionnaire items each."</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="18" customHeight="1" s="10">
       <c r="A183" t="inlineStr">
@@ -9696,6 +9972,16 @@
           <t>BSMA0180</t>
         </is>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr">
         <is>
           <t>Even though, over the last two decades, the boundaryless career concept has stimulated a wide theoretical debate, scholars have recently claimed that research on the competencies that are necessary for managing a cross-boundary career is still incomplete. Similarly, the literature on emotional and social competencies has demonstrated how they predict work performance across industries and jobs but has neglected their inﬂuence in explaining the individual’s mobility across boundaries and their impact on career success. This study aims to ﬁll these gaps by examining the effects of emotional and social competencies on boundaryless career and on objective career success. By analyzing a sample of 142 managers over a period of 8 years, we found evidence that emotional competencies positively inﬂuence the propensity of an individual to undertake physical career mobility and that career advancements are related to the possession of social competencies and depend on the adoption of boundaryless career paths. This study also provides a contribution in terms of the evaluation of the emotional and social competencies demonstrated by an individual and of the operationalization of the measurement of boundaryless career paths, considering three facets of the physical mobility construct (organizational, industrial, and geographical boundaries).</t>
@@ -9721,7 +10007,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P183" s="8" t="n"/>
+      <c r="P183" s="8" t="inlineStr">
+        <is>
+          <t>The study examines 'boundaryless career' and career success rather than Boundary Spanning Behavior (BSB). The boundaryless career construct is operationalized as physical career mobility, specifically measured by the number of firms an individual has worked for, the number of industrial sectors operated in, and the number of times they have worked abroad. This captures career transitions, turnover, and job mobility rather than the interpersonal, purposive actions characteristic of BSB (such as cross-boundary information scanning, coordination, representation, or knowledge exchange by an embedded employee). As the study lacks a valid measure of interpersonal boundary spanning behavior, it does not provide any zero-order effect sizes of interest for this meta-analysis.. Verbatim Evidence: "Boundaryless career was measured considering three types of physical mobility dimensions, namely crossing organizational, industrial, and geographical boundaries. [...] Specifically, we asked the managers of the sample to indicate: (a) organizational mobility: the number of firms they worked for; (b) industry mobility: the number of different sectors they operated in; and (c) geographical mobility: the number of times they worked abroad for at least 1 year, all with reference to the period of time from T1 to T2."</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="18" customHeight="1" s="10">
       <c r="A184" t="inlineStr">
@@ -9734,6 +10024,16 @@
           <t>BSMA0181</t>
         </is>
       </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G184" t="inlineStr">
         <is>
           <t>Aim: To identify learning from a clinical microsystems (CMS) quality improvement initiative to develop a more integrated service across a falls care pathway spanning community and hospital services. Background: Falls present a major challenge to healthcare providers internationally as populations age. A review of the falls care pathway in Sheffield, United Kingdom, identified that pathway implementation was constrained by inconsistent coordination and integration at the hospital–community interface. Approach: The initiative utilised the CMS quality improvement approach and comprised three phases. Phase 1 focussed on developing a climate for change through engaging stakeholders across the existing pathway and coaching frontline teams operating as microsystems in quality improvement. Phase 2 involved initiating change by working at the mesosystem level to identify priorities for improvement and undertake tests of change. Phase 3 engaged decision makers at the macrosystem level from across the wider pathway in achieving change identified in earlier phases of the initiative. Findings: The initiative was successful in delivering change in relation to key aspects of the pathway, engaging frontline staff and decision makers from different services within the pathway, and in building quality improvement capability within the workforce. Viewing the pathway as a series of interrelated CMS enabled stakeholders to understand the complex nature of the pathway and to target key areas for change. Particular challenges encountered arose from organisational reconfiguration and cross-boundary working. Conclusion: CMS quality improvement methodology may be a useful approach to promoting integration across a care pathway. Using a CMS approach contributed towards clinical and professional integration of some aspects of the service. Recognition of the pathway operating at meso- and macrosystem levels fostered wider stakeholder engagement with the potential of improving integration of care across a range of health and care providers involved in the pathway.</t>
@@ -9759,7 +10059,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P184" s="8" t="n"/>
+      <c r="P184" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative case study evaluating a clinical microsystems quality improvement initiative. It relies on focus groups, interviews, and observations, and does not provide quantitative survey data or extractable effect sizes (e.g., a correlation matrix) for boundary spanning behavior.. Verbatim Evidence: "An independent evaluation team comprising two academic/healthcare staff worked with the project team to capture learning. This involved undertaking focus group discussions and individual interviews with members of the team and observation of a range of meetings in each phase of the initiative. Interview/focus group transcripts and field notes of meetings were analysed by the evaluation team and the findings discussed with the project team in order to draw out the learning."</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="18" customHeight="1" s="10">
       <c r="A185" t="inlineStr">
@@ -9772,6 +10076,16 @@
           <t>BSMA0182</t>
         </is>
       </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr">
         <is>
           <t>To explain how multistakeholder groups organize democratic deliberations about complex sustainability issues, organizational scholars have focused on the key role of deliberative capacity, which encompasses the dimensions of inclusiveness, authenticity and consequentiality. However, the tensions inherent to the search of these three dimensions have been overlooked. In this paper, we argue that focusing on how spaces for deliberation are designed can help one understand how to manage such tensions. We identified the boundary work practices that shape the design of deliberative spaces and generate deliberative capacity properties in a high-level expert group (HLEG) launched by the European Commission about sustainable finance regulation. Our results show how these boundary work practices help balance deliberative tensions. We advance deliberation studies by conceptualizing deliberative boundary work, explaining how deliberative capacity is spatially generated and showing how deliberative tensions are balanced. We also contribute to boundary work theory by making explicit the deliberative nature of configuring boundary work and showing its relevancy to regulatory settings.</t>
@@ -9797,7 +10111,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P185" s="8" t="n"/>
+      <c r="P185" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative case study that uses 32 semi-structured interviews, observational data, and secondary documents to explore deliberative boundary work within a European Commission expert group. It employs the inductive 'Gioia' methodology for coding the data and does not provide any quantitative survey data, correlation matrices, or extractable zero-order effect sizes (r) required for this meta-analysis. Therefore, it is excluded.. Verbatim Evidence: "Building from 32 interviews and multiple secondary sources, we induced three types of deliberative boundary work involved in the generation of deliberative capacity: arranging – creating a bounded space for deliberation; shuffling – redistributing internal boundaries to sustain deliberation; and bridging – connecting the bounded deliberative space to other spaces... Because our second stage focused on analysing in an inductive way the boundary work involved in the HLEG-SF process as interpreted by our expert interviewees, the ‘Gioia’ approach was deemed relevant (Gioia, Corley, &amp; Hamilton, 2013). We coded our interview data using sentences and paragraphs as our coding units and labelled them with in vivo terms."</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="18" customHeight="1" s="10">
       <c r="A186" t="inlineStr">
@@ -9810,6 +10128,16 @@
           <t>BSMA0183</t>
         </is>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G186" t="inlineStr">
         <is>
           <t>Global offshoring has become a key strategy for international staffing, especially in the software industry. Global software teams engage in boundary spanning activities that may help MNEs achieve international connectivity and cope with external disruptions through their use of virtual work. However, offshoring IT professionals who bridge these boundaries in offshoring MNEs must contend with discontinuities, or perceived disruptions in expected communication flows, which impact their job satisfaction. Drawing on survey data from 193 professional consultants from an IT services offshoring MNE located primarily in Eastern Europe and working for a U.S. client, we test a model grounded in Organizational Discontinuity Theory. We find that potential discontinuities arising from the virtual work environment have no impact on the job satisfaction of offshoring IT professionals, but that those who experience team-level continuities of identification and shared vision are more satisfied with their jobs. Our findings suggest that virtual work may have become normalized such that it is not problematic in and of itself, and that fostering connectivity in boundary spanning global teams may be beneficial for MNEs. Our findings have important implications for MNEs managing disruptions created by global work arrangements as well as exogenous disruptions.</t>
@@ -9835,7 +10163,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P186" s="8" t="n"/>
+      <c r="P186" s="8" t="inlineStr">
+        <is>
+          <t>The study mentions boundary spanning as a contextual characteristic of global offshoring teams, but it does not measure Boundary Spanning Behavior (BSB) as a quantitative construct. The variables analyzed in the study are virtuality features (geographic dispersion, cultural diversity, dynamic structure, face-to-face dependence), team identification, shared vision, and job satisfaction. Therefore, it lacks an effect size of interest for BSB.. Verbatim Evidence: "Global software teams engage in boundary spanning activities that may help MNEs achieve international connectivity and cope with external disruptions through their use of virtual work. However, offshoring IT professionals who bridge these boundaries in offshoring MNEs must contend with discontinuities, or perceived disruptions in expected communication flows, which impact their job satisfaction... Table 5 Mean, standard deviation, and correlation matrix for continuous variables... Variables: 1. Team Tenure 2. Face-to-Face Dependence 3. Cultural Diversity 4. Dynamic Structure 5. Geographic Dispersion 6. Team Identification (TI) 7. Shared Vision (SV) 8. Job Satisfaction"</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="18" customHeight="1" s="10">
       <c r="A187" t="inlineStr">
@@ -9848,6 +10180,16 @@
           <t>BSMA0184</t>
         </is>
       </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G187" t="inlineStr">
         <is>
           <t>Acknowledgements: This research was funded by NSF grant #0422676 and #0726798 as well as support provided by the University of California, Irvine Center for Research on Information Technology in Organizations. The authors would like to acknowledge the helpful comments provided by Christopher Earley, Mark Griffin, John Mathieu, and Jone Pearce; assistance in data collection provided by Diaky Diaz, Christopher Reisdel and Bettina Wolf; and the generous time invested by all the film makers and film viewers who participated in the study.</t>
@@ -9873,7 +10215,11 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="P187" s="8" t="n"/>
+      <c r="P187" s="8" t="inlineStr">
+        <is>
+          <t>[Code 2 &amp; Code 3] The study violates two inclusion criteria. First, the unit of analysis is at the team level rather than the individual employee level (Code 3). Data were collected from informants and aggregated to represent 140 film-making teams, and the correlation matrix is based on N=140 teams. Second, the sample consists of independent documentary film makers who operate as independent contractors without organizational affiliation, rather than embedded organizational employees (Code 2).. Verbatim Evidence: "Our study consisted of a quantitative analysis of 140 film making teams rated by the teams and 5000 film viewers... we include teams which are not embedded in any overarching organization, that may experience even greater exposure to changing environmental conditions... The films in our sample are independent humanitarian documentary films... Where more than one film maker in a team responded to the survey, we averaged their scale scores to create a single score on each variable... hence the film making team is the unit of analysis... Each of the variables utilized in our research is a team-level construct. However, to quantify each of these measures at the team level of analysis, data was collected from individuals (film makers rated the independent variable and moderator variables; viewers provided the effectiveness ratings) and aggregated to represent the team... Table 1. Means, SD and Inter-correlations Among Variables in the Hypotheses... N=140."</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="18" customHeight="1" s="10">
       <c r="A188" t="inlineStr">
@@ -9886,6 +10232,16 @@
           <t>BSMA0185</t>
         </is>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr">
         <is>
           <t>Purpose – This paper aims to argue that the structure of the response to the World Trade Center (WTC) crisis can be characterized as an inter-organizational network and the majority of the activities can be identified as network management.</t>
@@ -9911,7 +10267,11 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="P188" s="8" t="n"/>
+      <c r="P188" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a mixed-method research strategy involving qualitative in-depth interviews and a sociometric survey to map the structural characteristics (e.g., density, centrality) of the inter-organizational response network to the World Trade Center crisis. It does not contain a quantitative correlation matrix or provide extractable zero-order effect sizes (r) involving an individual employee's boundary spanning behavior. Therefore, it lacks the required statistical data for the meta-analysis.. Verbatim Evidence: "This study uses a mixed-method research strategy, combining both quantitative and qualitative approaches. More specifically, we complement the results from in-depth interviews with results from a socio-metric survey. [...] Researchers from [Deleted for peer review process] conducted interviews with 29 first responders in 2002 and 2003. [...] At the end of each interview, interviewees were asked, “Please name 5 individuals who were instrumental in resourcing, facilitating, managing, leading, supporting, or inspiring your response efforts”. Based on the interview results, we created a one-mode network of reputation-based relationships. [...] Table II. Density, centrality and brokerage measurement results [reports Mean, SD, Variance, Centralization for Out-degree centrality, In-degree centrality, Betweenness centrality, etc.; no correlation matrix provided]."</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="18" customHeight="1" s="10">
       <c r="A189" t="inlineStr">
@@ -9924,6 +10284,14 @@
           <t>BSMA0186</t>
         </is>
       </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>999</v>
+      </c>
       <c r="G189" t="inlineStr">
         <is>
           <t>Drawing on corporate entrepreneurship (CE) and social network research, this study focuses on strategic renewal as a form of CE and examines the impact of boundary-spanning at top and middle management levels on business units’ exploratory innovation. Analyses of multi-source and multi-level data, collected from 72 top managers (TMs) and 397 middle managers (MMs) operating in 34 units of a multi-national organization, indicate that TMs’ boundary-spanning is positively related to units’ exploratory innovation, but also has a cascading effect on MMs by increasing their perceived role conflict. MMs’ role conflict is negatively related to units’ exploratory innovation and thus offsets some of the benefits gained through TMs’ boundary-spanning activities. Taking a configurational perspective on social exchanges at multiple levels, we show that role conflict is reduced by overlapping boundary-spanning ties among TMs and MMs. Surprisingly, MMs’ boundary-spanning does not relate to exploratory innovation. Our study shows that with regard to boundary-spanning, a top-down approach to CE as strategic renewal may be most effective because TMs play a key role in driving exploratory innovation. However, TMs need to be aware of the cascading social liabilities of their boundary-spanning behavior and ensure MMs develop similar networks. We advance ongoing debates in studies about CE and social networks by providing empirically validated insights into who drives strategic renewal and by uncovering the benefits and costs of social exchanges for strategic renewal. Furthermore, we uncover potential causes of mixed findings in network theory research and highlight a remedy to social liabilities.</t>
@@ -9949,7 +10317,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P189" s="8" t="n"/>
+      <c r="P189" s="8" t="inlineStr">
+        <is>
+          <t>The study measures boundary-spanning behavior of middle managers across different business units within a multi-national firm. Boundary-spanning is operationalized via a network generator that asks managers to identify units they regularly contacted for new knowledge or expertise. This satisfies both the Intra-Organizational BSB Override and the Network-Based BSB Inclusion criteria, as the ties represent purposive actions (knowledge seeking) rather than mere communication. The study provides a quantitative correlation matrix at the individual employee level (N=397 middle managers) with extractable effect sizes (e.g., between MM boundary-spanning and role conflict).. Verbatim Evidence: "To test our hypotheses, we conducted a field study in a large multi-national transport and logistics services company with approximately 163,000 employees worldwide... The primary data for this study were collected in 2010 by surveying the two population groups; the TMs and the MMs of each unit... The MMs were presented with a list of the units and were asked to tick the units that provided them with new knowledge or expertise. Responses were recorded in a 397 x 34 two-mode network matrix in which cell Xij = 1 when MMi indicated an information-seeking relationship with unit j, and Xij = 0 otherwise. Based on the egocentric network, the boundary-spanning of each MM was constructed from the number of units to which the MM in question was connected... Table 1 Means, standard deviations and correlations... n = 397 middle managers and 72 top managers in 34 business units."</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="18" customHeight="1" s="10">
       <c r="A190" t="inlineStr">
@@ -9962,6 +10334,16 @@
           <t>BSMA0187</t>
         </is>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>Compared to job-specific conditions, the interpersonal context of work has received less attention from work–family scholars. Using data from a 2007 U.S. survey of workers (N = 1,286), we examine the impact of workplace social support and interpersonal conflict on work–family conflict and exposure to boundary-spanning demands—as indexed by the frequency that workers receive work-related contact outside of normal work hours. Findings indicate that workplace social support is associated negatively with work-to-family conflict, while interpersonal conflict at work is associated with higher levels of work-to-family conflict. Results also indicate that both supportive and conflictive work contexts are associated with more frequent exposure to boundary-spanning demands. However, workers in supportive contexts are more likely to appraise these demands as beneficial for accomplishing work tasks, and are less likely to appraise them as disruptive to family roles. By contrast, workers in conflictive contexts are more likely to appraise demands as disruptive to family roles, and are less likely to appraise them as beneficial for paid work. Consequently, our findings underscore the resource and demands aspects of interpersonal work contexts and their implications for the work–family interface.</t>
@@ -9987,7 +10369,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P190" s="8" t="n"/>
+      <c r="P190" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on work-family boundary management, specifically measuring 'boundary-spanning demands' as the frequency with which individuals are contacted about work-related matters outside of normal working hours. This operationalization captures the permeability of the work-home boundary rather than an employee's purposive inter- or intra-organizational boundary spanning behavior (e.g., information scouting or representation). Therefore, it lacks the relevant construct for this meta-analysis.. Verbatim Evidence: "We use one item to assess the frequency of exposure to the following boundary-spanning demand: “How often do coworkers, supervisors, managers, customers, or clients contact you about work-related matters outside normal work hours? Include telephone, cell phone, beeper and pager calls, as well as faxes and e-mail that you have to respond to.”... Voydanoff (2007) refers to these requests as a type of boundary-spanning demand, finding them to be associated positively with work-to-family conflict."</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="18" customHeight="1" s="10">
       <c r="A191" t="inlineStr">
@@ -10000,6 +10386,16 @@
           <t>BSMA0188</t>
         </is>
       </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G191" t="inlineStr">
         <is>
           <t>This paper investigates boundary-work in management accounting in the context of globalization and hybrid professionalism. The paper demonstrates how permeable symbolic boundaries of the management accounting ﬁeld can be altered by employing expansion boundary-work. Contrasting boundary-work of IMA ofﬁcials and IMA members in Russia, we show that IMA ofﬁcials employ primarily monopolization boundary-work while IMA members employ primarily expansion boundary-work. Our ﬁndings illustrate how boundary-work is employed to exhibit organizational and occupational professionalism in the symbolic realm. The paper provides additional insight into the discursive domain of the accounting profession by linking boundary-work to globalization, two forms of professionalism, legitimacy, status and professional identity. This suggests that the professionalization process is inﬂuenced by the properties of professional boundaries.</t>
@@ -10025,7 +10421,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P191" s="8" t="n"/>
+      <c r="P191" s="8" t="inlineStr">
+        <is>
+          <t>The study is a purely qualitative investigation into boundary-work among management accountants based on 15 formal interviews and participant observations. It does not collect quantitative data or report any formal correlation matrices with extractable effect sizes (r) for a boundary spanning behavior construct. Therefore, it is excluded for lacking the required quantitative effect sizes.. Verbatim Evidence: "Formally, the empirical base of this paper consists of 15 formal interviews conducted in English and Russian with IMA members and IMA officials (see Table 1). Each interview lasted between 28 and 100 min (average 53 min). Apart from interviews, primary data sources consist of participant observations of two annual meetings with IMA members in Moscow. [...] Interview data were analyzed iteratively and coded during several stages."</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="18" customHeight="1" s="10">
       <c r="A192" t="inlineStr">
@@ -10038,6 +10438,16 @@
           <t>BSMA0189</t>
         </is>
       </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr">
         <is>
           <t>This article explores the joint production and consumption of health information and advice in the context of NHS Direct, the new telephone health information and advice service. NHS Direct is an atypical call centre environment in so far as its core staff (nurses) are highly skilled professionals. These nurses are required to collaborate closely with, and are to some extent dependent upon, non-professional lower skilled staff (call handlers) to deﬁne and prioritize their work. This introduces a number of tensions between the two groups. Nurses respond to these tensions by engaging in ‘boundary work’, the micropolitical strategies through which work identities and occupational margins are negotiated, to protect their own status. Call handlers are more subject to the pressures of work ‘speed-up’, highly aware of the risks inherent in their role, but are unable to call upon professional status, either in their resistance to managerial imperatives or in their interactions with health consumers. They are required to manage the tension between offering a safe and high quality service, characterized in their training as ‘professional’, and nurses’ boundary work, which positions them as ‘non-professional’. Here we draw on qualitative research, including call interaction data between call handler and consumer, to show how call handlers’ occupation of the contested territory between professional and non-professional status leaves them wide open to the agency of consumers, as consumers attempt to shape the service in their own interests.</t>
@@ -10063,7 +10473,11 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="P192" s="8" t="n"/>
+      <c r="P192" s="8" t="inlineStr">
+        <is>
+          <t>The study uses purely qualitative methods (participant observation, work shadowing, in-depth interviews, and conversation analysis) to examine the 'boundary work' of occupational demarcation between nurses and call handlers. It does not provide any quantitative data or extractable zero-order effect sizes (r) for boundary spanning behavior.. Verbatim Evidence: "We used a variety of qualitative methods, including participant observation (one of the researchers undertook call handler training followed by a limited number of supervised shifts ‘on the lines’); work shadowing; indepth interviews with both call centre staff and callers; and conversation analysis (CA) of recorded call interactions. The analysis presented here is based upon the participant and non-participant observations/shadowing at the call centres, interviews with nurses and call handlers and analysis of call interactions between staff and callers."</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="18" customHeight="1" s="10">
       <c r="A193" t="inlineStr">
@@ -10076,6 +10490,16 @@
           <t>BSMA0190</t>
         </is>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G193" t="inlineStr">
         <is>
           <t>Past research has studied how the selection and use of control portfolios in software projects is based on environmental and task characteristics. However, little research has examined the consequences of control mode choices on project performance. This paper reports on a study that addresses this issue in the context of outsourced software projects. In addition, we propose that boundary-spanning activities between the vendor and the client enable knowledge sharing across organizational and knowledge domain boundaries. This is expected to lead to facilitation of control through specific incentives and performance norms that are suited to client needs as well as the vendor context. Therefore, we argue that boundary spanning between the vendor and client moderates the relationship between formal controls instituted by the vendor on the development team and project performance. We also hypothesize the effect of collaboration as a clan control on project performance. We examine project performance in terms of software quality and project efficiency. The research model is empirically tested in the Indian software industry setting on a sample of 96 projects. The results suggest that formal and informal control modes have a significant impact on software project outcomes, but need to be finely tuned and directed toward appropriate objectives. In addition, boundary-spanning activities significantly improve the effectiveness of formal controls. Finally, we find that collaborative culture has provided mixed benefits by enhancing quality but reducing efficiency.</t>
@@ -10101,7 +10525,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P193" s="8" t="n"/>
+      <c r="P193" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts its analysis at the project/team level (N = 96 outsourced software projects), not the individual employee level. The respondents are project managers reporting on project characteristics. Furthermore, the boundary spanning construct is operationalized as a project-level formative construct that captures the presence of boundary spanning roles on the team, processes, and boundary objects rather than individual boundary spanning behavior. Because the unit of analysis is the project and the correlations represent project-level data, the study is excluded under Code 3.. Verbatim Evidence: "Our final sample for this study consisted of a total of 96 projects from 10 firms. ... The executives granted access to individual project managers on projects who provided the responses for each project. ... Boundary Spanning—Roles: One or more members of the project team had been formally designated to facilitate coordination with client; One or more members of the project team informally facilitated coordination with the client. ... Boundary spanning—process: Project planning meetings; Status review meetings."</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="18" customHeight="1" s="10">
       <c r="A194" t="inlineStr">
@@ -10114,6 +10542,16 @@
           <t>BSMA0191</t>
         </is>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G194" t="inlineStr">
         <is>
           <t>Recently, discussion has begun to consider serving the base of the economic pyramid for business and societal benefit. Suggestions for so doing have focused on business model innovation, improving internal capabilities, promoting stronger governance, and providing leapfrog technologies (such as ICT) to promote effective change. We consider the questions of what types of innovation are occurring when businesses and other organizations enter the base of the pyramid and what types of social, economic, and consumer benefits they bring to local communities. We base our findings on an analysis of more than 1,000 cases describing base of the pyramid activities.</t>
@@ -10139,7 +10577,11 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="P194" s="8" t="n"/>
+      <c r="P194" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study analyzes a database of 1,000 case capsules of organizations deploying information and communications technology at the base of the economic pyramid. The unit of analysis is the project or organization, not individual employees. Furthermore, the study does not measure boundary spanning behavior or provide any zero-order correlation matrices (effect sizes), relying instead on descriptive statistics and logistic regressions of categorical data derived from case abstracts.. Verbatim Evidence: "The World Resource Institute's Digital Dividend project has collected over 1,000 examples of organizations that are deploying information and communications technology at the base of the pyramid (www.digitaldividend.org). ... The original digital dividend case base consisted of over 1,000 case capsules collected over the last five years. Each case contained a short abstract plus some meta-data describing the case's location, activity type, sponsorship, sector, etc."</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="18" customHeight="1" s="10">
       <c r="A195" t="inlineStr">
@@ -10152,6 +10594,16 @@
           <t>BSMA0192</t>
         </is>
       </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G195" t="inlineStr">
         <is>
           <t>Human service organizations seeking to infuse research and other forms of evidence into their programs often need to expand their knowledge sharing systems in order to build their absorptive capacities for new information. To promote their engagement in evidence-informed practice, human service organizations can benefit from connections with intermediary organizations that assist with the dissemination and utilization of research and the use of internal knowledge brokers, called link officers. These boundaryspanning individuals work to embed external research and internal evidence in order to address current organizational priorities and service demands. This exploratory study describes the characteristics, major activities, and perceptions of link officers connected with three pioneering intermediary organizations. Quantitative and qualitative data from a survey of 137 Canadian and UK link officers provide a profile of these professionals, including how they engage practitioners to promote evidence-informed practice and the degree to which they are supported within their organizations and by intermediary organizations. The article concludes with practice and research implications for the development of the link officer role in human service organizations.</t>
@@ -10177,7 +10629,11 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="P195" s="8" t="n"/>
+      <c r="P195" s="8" t="inlineStr">
+        <is>
+          <t>The study is an exploratory descriptive analysis of Link Officers in human service organizations. It reports only descriptive statistics (means, standard deviations, and percentages) for survey responses and does not provide a formal correlation matrix, regression analysis, or any extractable quantitative effect sizes (r) between substantive variables.. Verbatim Evidence: "Descriptive statistical analyses of the survey data were conducted using the responses to the closed-ended questions. Analysis of continuous measures (e.g., years in current organizational position, FTE dedicated to the LP/LO role) and Likert-type measures involved the calculation of means and standard deviations; percentages were calculated for categorical measures."</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="18" customHeight="1" s="10">
       <c r="A196" t="inlineStr">
@@ -10190,6 +10646,16 @@
           <t>BSMA0193</t>
         </is>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr">
         <is>
           <t>The majority of team leadership studies have ignored the specific context in which that leadership takes place and the cyclical correlation of inputs and processes on ongoing performance. It is our contention that leadership is a mediator of team processes and team effectiveness on ongoing functioning of multidisciplinary teams (MDT). The members of 126 multidisciplinary teams responded to a survey on several aspects related to the functioning and leadership of their teams. The results support the hypothesis that leadership does mediate the relationship between reflexivity and effectiveness (i.e. team management performance, boundary spanning and satisfaction) within the team. Theoretically, these findings challenge those of linear models that typically analyse the impact of leadership as something that happens in isolation. Future research should describe and consider not just the team type and tasks but also investigate the roles that context and time play in team leadership.</t>
@@ -10215,7 +10681,11 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="P196" s="8" t="n"/>
+      <c r="P196" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the team level (N = 126 multidisciplinary teams) rather than the individual level. Individual survey responses were aggregated to the team level before analysis. Furthermore, the boundary spanning variable ('Team boundary spanning') measures the performance and external relations of the entire team (the CPCY) rather than individual employee behavior, acting as a team-level evaluation. This violates the individual-level boundary spanning guardrail.. Verbatim Evidence: "The members of 126 multidisciplinary teams responded to a survey on several aspects related to the functioning and leadership of their teams... The level of analysis in this study is the team. So, for statistical analyses, individual answers were aggregated at team level... Table 1. Means (M), standard deviations (SD), F-values (F), aggregate level intercorrelations (Rwg, ICC(1), ICC(2)), Cronbach alphas and correlations (N = 126 teams)... Rate the performance of CPCY with respect to the following aspects: ... Boundary Spanning (1) Relations with CNPCJR (national agency) (2) Relations with Family and Children Court (3) Relations between extended and restricted CPCY (4) Relations with children and young agencies."</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="18" customHeight="1" s="10">
       <c r="A197" t="inlineStr">
@@ -10228,6 +10698,14 @@
           <t>BSMA0194</t>
         </is>
       </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>999</v>
+      </c>
       <c r="G197" t="inlineStr">
         <is>
           <t>Firms recognize that working together through collaborative relationships offers potential benefits such as improving cooperation, information sharing, and overall performance. An additional and extremely valuable benefit of working together is the potential for creating innovative business approaches and solutions. Thus, developing external linkages has become a higher priority within many organizations. Boundary spanning employees offer one means of achieving closer cross‐firm relationships. We investigate the roles of boundary spanners by examining service providers and their relationships with customers. More specifically, we examine boundary spanning employees that are physically on‐site at customer facilities. Results provide strong support that boundary spanners perceiving higher levels of external organizational support from a client subsequently develop affective commitment to the customer. This, in turn, drives knowledge exchange and logistics innovation. A relationship between logistics innovation and performance (of service providers and of customers) was also found. Managerial implications of the research findings are discussed and suggestions presented covering future research.</t>
@@ -10253,7 +10731,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P197" s="8" t="n"/>
+      <c r="P197" s="8" t="inlineStr">
+        <is>
+          <t>This study explicitly matches the 'Implanted Boundary Spanner / Knowledge Exchange' inclusion rule (and Example 3 from the system instructions). The sample consists of boundary spanning employees (logistics implants physically on-site at customer facilities) and measures their knowledge exchange with the host firm, which represents a valid purposive boundary-spanning behavior (BSB). Because the study uses 1-to-1 matched pairs (1 LSP representative paired with 1 customer contact, resulting in N=81 dyads), statistical independence is preserved, satisfying the 1:1 Matched Dyad Safe Harbor. A zero-order correlation matrix is provided in Table 5.. Verbatim Evidence: "Specifically, we were motivated to investigate on-site employees and the relationship they develop with host organizations. The context selected for examination is employees of logistics service providers (LSPs) who work within a customer's facility. ... The single contact then distributed the letter to boundary spanners working at customer facilities. ... all 750 LSP participants were asked to forward a customer version of the letter to a key contact at their customer organizations. ... The final data for analysis included 81 dyads. ... [Table 2] Knowledge exchange... I move projects forward by exchanging ideas with members of my host firm... I exchange ideas with members of my host firm to find solutions to problems... [Table 5] Variance extracted estimates, correlations and squared correlations: logistics service provider responses"</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="18" customHeight="1" s="10">
       <c r="A198" t="inlineStr">
@@ -10266,6 +10748,16 @@
           <t>BSMA0195</t>
         </is>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr">
         <is>
           <t>Using resource dependency and institutional theories, we create and test a model examining the relationships among senior management commitment, resource allocations, and the structure of public affairs departments. Using a large sample of U.S.-based firms, we find a positive relationship between senior management commitment to the public affairs function and the level of human and monetary resources allocated to the public affairs department. Furthermore, firms structure their public affairs responsibilities into three common activity sets: communications, collaborations, and local activities. These common activities are, in turn, positively associated with senior management commitment and resources allocated to the public affairs department.</t>
@@ -10291,7 +10783,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="P198" s="8" t="n"/>
+      <c r="P198" s="8" t="inlineStr">
+        <is>
+          <t>The study surveys senior executives as macro-level key informants to measure firm-level and department-level variables, specifically the resources, structures, and activities of the corporate public affairs (PA) department. The survey items ask about the 'public affairs department' (e.g., department budgets, staff size, departmental functions) rather than the individual respondent's interpersonal boundary spanning behaviors. Consequently, the unit of analysis is the organization, violating the individual-level analysis requirement [Code 3]. Furthermore, the paper does not report a formal zero-order correlation matrix or provide any extractable effect sizes of interest [Code 1].. Verbatim Evidence: "Our sample population is composed of the senior executives in U.S.-based organizations responsible for corporate public affairs. Corporate public affairs is defined in the survey as the “management function responsible for interpreting the corporation’s non-commercial environment and managing the corporation’s responses to that environment”... The size variable is the natural logarithm of the firm’s total assets for fiscal 1998 drawn from the COMPUSTAT database... [Appendix] Please indicate the current number of full-time staff members (professional and support) within the PA function. Include all employees at the headquarters level and all those domiciled elsewhere who have solid-line reporting to headquarters PA... Please check the following functions that are currently conducted within your public affairs department."</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="18" customHeight="1" s="10">
       <c r="A199" t="inlineStr">
@@ -10342,6 +10838,16 @@
           <t>BSMA0197</t>
         </is>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>As employees’ personal lives are increasingly splintered by work demands, the boundary between work and nonwork domains is becoming ever more blurred. Grounded within a self-regulatory approach and the executive control function of inhibitory control, we operationalize and examine nonwork role re-engagement (NWRR)—the extent to which individuals can redirect attentional resources back to nonwork tasks following work-related intrusions. In phases 1 and 2, we develop and refine a psychometrically sound unidimensional measure for NWRR aligned with the self-regulatory processes of self-control and interference control underlying inhibitory control. In phase 3, we confirm the factor structure with a new sample. In phase 4 we validate the measure using the samples from phases 2 and 3 to provide evidence of criterion-related, convergent, and discriminant validity. NWRR was related to important well-being and work-related outcomes above and beyond existing self-regulatory and boundary management constructs. We offer theoretical and practical implications and an agenda to guide future research, as attentional agility becomes increasingly relevant in a home life replete with interruptions from work.</t>
@@ -10367,7 +10873,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P200" s="8" t="n"/>
+      <c r="P200" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on work-nonwork boundary management (developing a measure for nonwork role re-engagement following work-related intrusions) rather than interpersonal boundary spanning behavior across organizational or internal departmental boundaries. Therefore, it lacks an effect size of interest for this meta-analysis.. Verbatim Evidence: "Grounded within a self-regulatory approach and the executive control function of inhibitory control, we operationalize and examine nonwork role re-engagement (NWRR)—the extent to which individuals can redirect attentional resources back to nonwork tasks following work-related intrusions... For the criterion-related validity measures, work-to-life conflict (WLC) was assessed with the same measures in samples 1 and 2... To measure the flexibility of nonwork boundaries, we adapted Matthews et al.’s (2010) 5-item family flexibility-ability scale"</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="18" customHeight="1" s="10">
       <c r="A201" t="inlineStr">
@@ -10380,6 +10890,16 @@
           <t>BSMA0198</t>
         </is>
       </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G201" t="inlineStr">
         <is>
           <t>T h i s position paper distinguishes different types of activities needed in software processes and proposes enaction support for t h e m . An architecture of enaction components providing this support is sketched.</t>
@@ -10405,7 +10925,11 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="P201" s="8" t="n"/>
+      <c r="P201" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a position paper that discusses communication support and activities in software engineering environments. It does not conduct primary empirical research and does not provide quantitative data, a sample, or effect sizes for boundary spanning behavior.. Verbatim Evidence: "This position paper distinguishes different types of activities needed in software processes and proposes enaction support for them. An architecture of enaction components providing this support is sketched."</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="18" customHeight="1" s="10">
       <c r="A202" t="inlineStr">
@@ -10418,6 +10942,16 @@
           <t>BSMA0199</t>
         </is>
       </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G202" t="inlineStr">
         <is>
           <t>This article guides the development of creative insights in supply chain management. The authors begin by describing analogies’ role in advancing organization theory with a focus on image transfers between knowledge domains. While much has been said about the merits of conceptual transfers between domains, much equally remains unknown, particularly about how to deliberately develop creative insights that have the potential to challenge or enhance existing supply chain management theory. To address this issue, this research builds on prior work on analogies, creativity, and design thinking to develop a heuristic-analytic model. This model is designed to assist researchers in theorizing by analogy through a controlled dual cognitive process of divergence before convergence combined with a distant boundary-spanning knowledge search. An illustration of the model shows how creative output can provide a fresh perspective that helps render supply chains potentially more resilient.</t>
@@ -10443,7 +10977,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P202" s="8" t="n"/>
+      <c r="P202" s="8" t="inlineStr">
+        <is>
+          <t>This is a conceptual and methodological article proposing a heuristic-analytic model for developing creative supply chain theory using analogies. It does not contain primary empirical data, nor does it report any quantitative effect sizes or a correlation matrix involving individual-level boundary spanning behavior.. Verbatim Evidence: "This article guides the development of creative insights in supply chain management. The authors begin by describing analogies’ role in advancing organization theory with a focus on image transfers between knowledge domains. ... To address this issue, this research builds on prior work on analogies, creativity, and design thinking to develop a heuristic-analytic model. ... We illustrate our model by drawing on conceptually distant source phenomena pertaining to the natural sciences."</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="18" customHeight="1" s="10">
       <c r="A203" t="inlineStr">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -10800,6 +10800,16 @@
           <t>BSMA0196</t>
         </is>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G199" t="inlineStr">
         <is>
           <t>Teams must constantly balance internally focused interactions through Adaptation and externally focused processes of spanning boundaries to facilitate change. This dynamic of team Adaptation has not been studied. In empirical studies on team Boundary Management or Adaptation, attention is given to laboratory based experiments and field studies of new product development teams in high-tech industries. This research focuses on continuous quality improvement (QI) teams which are comprised of a dynamic and shifting set of members otherwise attuned to their professional daily activities not directly related to the project. The teams of interest operate in highly institutionalized and regulated service industries of healthcare. The overarching research question in this study asks what factors influence team adaptation and how do teams effectively achieve internal and external balance in their QI projects, and to what extent does this contribute to project success. To answer this question, a developmental sequential mixed methods study is conducted that utilizes qualitative analytics through grounded theory based theme development and thematic analysis as well as quantitative analytics of Qualitative Comparative Analysis (QCA) and Structural Equation Modeling. The first study is a mixed methods design utilizing a grounded theory approach for theme development followed by QCA to articulate complex causal interactions among identified factors influencing Adaptation. The sample includes 23 physicians/physician leaders/and hospital administrators who provide 39 team project examples for evaluation. The second study is a Quantitative design utilizing factor analysis to discern factors identified in study one in order to assess internal and external factor effects on Adaptation. A survey resulted in 215 responses for analysis from an expanded sample of team members in institutionally structured organizations. The third study is a Qualitative design utilizing thematic analysis to expand an understanding of the dynamic nature of Boundary Management mechanisms and team Adaptation patterns. The sample includes 13 team members providing 15 team project examples from 15 hospitals some of which are high performing teams and others are not. This research reveals that effective quality improvement project teams demonstrate Adaptation versatility by using combinations of several strategies to connect to the surrounding organization. By doing so this research contributes to the team literature as it expands descriptions of Boundary Management and Adaptation; it combines factors that have not been previously studied together and finds them to contribute to Adaptation. It also focuses on teams in situ in a context with previously limited attention. For management practice, the study provides practical explanations for team Adaptation as a process that can be mindfully guided through mechanisms of Boundary Management.</t>
@@ -10825,7 +10835,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P199" s="8" t="n"/>
+      <c r="P199" s="8" t="inlineStr">
+        <is>
+          <t>The study measures Boundary Spanning Behavior at the team-level, rather than the individual employee-level. Although the quantitative survey was administered to individual participants (N=250), the respondents were acting as key informants evaluating their team's behavior. The survey items for the boundary spanning constructs (Structural Connections and Relational Connections) use team-level referents such as 'Members have relationships with others outside the team' and 'Members collaborate with others in the organization to advance our team's efforts', rather than the individual 'I' referent. Following the proxy guardrail, studies where individuals serve as key informants to evaluate macro-level or team-level boundary spanning must be excluded.. Verbatim Evidence: "Table B1: Model Constructs and Scale Development... 3. Name of Scale: Embedded Interconnections: Structural Connections and Relational Connections... Items: a. Members have relationships with others outside the team who can help influence change (Relational); b. Members are influential with their peers outside the team (Relational); c. Members are well connected to others in the organization (Relational); d. Members effectively exchange knowledge with others in the organization (Structural); e. Members collaborate with others in the organization to advance our team’s efforts (Structural); f. Members consider the effect our work will have on others (Structural); g. Members consider how others will respond to our team’s work (Relational); h. Members invite others in the organization to engage with our work (Structural); i. Members are trusted by others in the organization (Relational)... [Page 118] First, we sought to gain an understanding of teams, but were not able to obtain team level data. Instead our survey information and results are based on the perceptions of individual participants who were asked to consider a single team in which they participate at work; thus a variety of teams are represented, but no teams as wholes are represented."</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="18" customHeight="1" s="10">
       <c r="A200" t="inlineStr">
@@ -10994,6 +11008,16 @@
           <t>BSMA0200</t>
         </is>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G203" t="inlineStr">
         <is>
           <t>The period after completing primary and adjuvant cancer treatment until recurrence or death is now recognized as a unique phase in the cancer control continuum. The term “survivorship” has been adopted to connote this phase. Survivorship is a time of transition: Issues related to diagnosis and treatment diminish in importance, and concerns related to long-term follow-up care, management of late effects, rehabilitation, and health promotion predominate. In this article, we explore the unique challenges of care and health service delivery in terms of the interface between primary care and specialist care during the survivorship period. The research literature points to problems of communication between primary and specialist providers, as well as lack of clarity about the respective roles of different members of the health-care team. Survivorship care plans are recommended as an important tool to facilitate communication and allocation of responsibility during the transition from active treatment to survivorship. Research questions that remain to be answered with respect to survivorship care plans and other aspects of survivorship care are discussed.</t>
@@ -11019,7 +11043,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P203" s="8" t="n"/>
+      <c r="P203" s="8" t="inlineStr">
+        <is>
+          <t>This article is a commentary/review discussing the challenges of care delivery and communication at the interface between primary care and oncology specialty care during cancer survivorship. It is not a primary empirical study, does not collect original quantitative survey data, and lacks any extractable zero-order effect sizes for boundary spanning behavior.. Verbatim Evidence: "In this article, we explore the unique challenges of care and health service delivery in terms of the interface between primary care and specialist care during the survivorship period. The research literature points to problems of communication between primary and specialist providers, as well as lack of clarity about the respective roles of different members of the health-care team... Research questions that remain to be answered with respect to survivorship care plans and other aspects of survivorship care are discussed."</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="18" customHeight="1" s="10">
       <c r="A204" t="inlineStr">
@@ -11032,6 +11060,16 @@
           <t>BSMA0201</t>
         </is>
       </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G204" t="inlineStr">
         <is>
           <t>In multidisciplinary teams in the oil and gas industry, we examined expertise diversity's relationship with team learning and team performance under varying levels of collective team identification. In teams with low collective identification, expertise diversity was negatively related to team learning and performance; where team identification was high, those relationships were positive. Results also supported nonlinear relationships between expertise diversity and both team learning and performance. Finally, team learning partially mediated the linear and nonlinear relationships between diversity and performance. Findings broaden understanding of the process by which and the conditions under which expertise diversity may promote team performance.</t>
@@ -11057,7 +11095,11 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="P204" s="8" t="n"/>
+      <c r="P204" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the team level (N=57 multidisciplinary teams) rather than the individual level. Team member responses are aggregated to create team-level constructs (e.g., external communication, team learning behavior). Therefore, the correlation matrix reports team-level relationships, which lacks the individual-level effect sizes required for this meta-analysis.. Verbatim Evidence: "Our final sample consisted of those 57 teams from which we had received three or more subordinate surveys and a supervisor survey, and for which archival data were available. ... Together, the above analyses supported the aggregation of informant responses from a team to create team-level variables for collective team identification, team learning, intrateam conflict, and external communication. ... Table 1 Means, Standard Deviations, and Correlations (n = 57)."</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="18" customHeight="1" s="10">
       <c r="A205" t="inlineStr">
@@ -11070,6 +11112,16 @@
           <t>BSMA0202</t>
         </is>
       </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G205" t="inlineStr">
         <is>
           <t>The definition of innovation varies from individual to individual and between individual and the team or the team and an organization. The perception of innovation and how individuals define innovation can make an organization stay competitive or go out of business. Research had shown that a traditional approach of idea generation as innovation at well intentioned organizations afforded success only 10% of the time after three years. In forming and managing project teams, which are made up of individuals or selling a service or product to a certain demography it is important and beneficial to understand their perception of innovation and if they see innovation as new, change or improvement. This study is built upon the earlier work of Zhuang (1995), Zhuang, Williamson, and Carter (1999), and McLaughlin and (2013). Prior research conducted by Caraballo and McLaughlin (2012) focused on understanding the perception of innovation as defined or understood by a homogeneous demography of Latino American professionals. This dissertation furthers the research conducted by Caraballo and McLaughlin (2012) with a focus on comprehending how a homogenous group Indian American professionals in the United States perceive or define innovation into the three categories of new, improve and change. While innovation may be understood by individuals as a multi-dimensional construct, the research tried to identify the relationship between perceptions, and gender, age and job function for the homogenous group of Indian Americans in the United States. The research followed the approach and methodology used by Caraballo and McLaughlin (2012) and the study is quantitative, exploratory and used web-based surveys to gather responses from respondents.</t>
@@ -11095,7 +11147,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P205" s="8" t="n"/>
+      <c r="P205" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on how Indian American professionals perceive and define innovation (categorized as new, improved, or change). It does not measure boundary spanning behavior (BSB) or any interpersonal cross-boundary actions, and therefore lacks the target construct and effect sizes of interest.. Verbatim Evidence: "The objective of this study from this structure was to study and explore the management question: how is innovation perceived by members of a distinct cultural and homogenous group at an individual level?... What are the perceptions of Indian professionals residing in the US toward innovation? What is the relationship between gender, generational cohort, functional association, and one’s individual (personal) perception of innovation among Indian professionals?... The dependent variables were identified as factors 1, 2, and 3, respectively, by Caraballo and McLaughlin (2012) [on perceptions of innovation: improvement/change, adoption of something that exists elsewhere, and new ideas/ something new]."</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="18" customHeight="1" s="10">
       <c r="A206" t="inlineStr">
@@ -11108,6 +11164,14 @@
           <t>BSMA0203</t>
         </is>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>999</v>
+      </c>
       <c r="G206" t="inlineStr">
         <is>
           <t>Personnel is one of the most important resources for the performance of Information Systems (IS) and Information Center (IC) organizations. The scarcity of new employees, the difficulty of training and a high turnover make personnel management in these areas a difficult problem. For IS employees, the relationships between job satisfaction, organizational commitment and intention to leave the organization have been established. Because the size of the investment and the number of organizations establishing IC organizations are growing dramatically, it has become important to understand the determinants of turnover intentions for IC as well as IS employees. Are IC employees similar to their IS counterparts? Or, is their nature basically different, as some studies have suggested? This study examines the differences between IS and IC employees in terms of demographic characteristics, participation on boundary spanning activities, role stressors, overall job satisfaction, organizational commitment and turnover intentions. The differences are found to be significant and call for special attention from IC managers to manage more properly their personnel resources. IC employees were found to participate more extensively in boundary spanning activities, experienced more role stressors (role ambiguity and role conflict), were less satisfied with their jobs and less committed to their organization. The findings also demonstrate the importance of organizational commitment as an intervening variable in models of turnover. While overall job satisfaction had both direct and indirect effects on turnover intentions among IC employees, for IS personnel it had only indirect effects through organizational commitment. The effects of role stressors and boundary spanning activities were found to be indirect via overall job satisfaction and organizational commitment for both IC and IS employees. The implications of these findings for practicing managers and for future research are discussed.</t>
@@ -11133,7 +11197,11 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="P206" s="8" t="n"/>
+      <c r="P206" s="8" t="inlineStr">
+        <is>
+          <t>The study measures intra-organizational boundary spanning behavior among individual information systems personnel (N = 464). Boundary spanning activities are defined as interacting and communicating with others outside the department (e.g., assisting other units, recommending applications to top management) using a modified version of the Miles and Perreault scale, which represents purposive cross-boundary action. It provides extractable zero-order correlations (r = -0.19) between boundary spanning activities and intention to leave the organization. Following Screening Rule 2 (Intra-Organizational BSB Inclusion), the study meets all criteria for inclusion.. Verbatim Evidence: "Sample and procedure: A questionnaire was distributed to 2548 members of the Association for Computing Machinery (ACM) in Pennsylvania, Delaware, and Southern New Jersey. ... leaving a final sample of 464 employees. ... Boundary spanning activities, defined as those by which employees interact and communicate with others outside their departments, including formal and informal written and oral communications, were measured by modifying the ten-item scale developed by Miles and Perreault [12] and used by Baroudi [2]. Each item (e.g., “assist other units in determining appropriate uses of information technology”; “recommend new applications of information technology to top management”) was scored on a five-point scale ranging from (1) not part of my job to (5) a very significant part of my job. ... Table 4: Relationships between role stressors and boundary spanning activities, and intention to leave the organization (N = 464) ... Boundary spanning activities -0.19"</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="18" customHeight="1" s="10">
       <c r="A207" t="inlineStr">
@@ -11146,6 +11214,16 @@
           <t>BSMA0204</t>
         </is>
       </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G207" t="inlineStr">
         <is>
           <t>As software development projects continue to be over budget and behind schedule, researchers continue to look for ways to improve the likelihood of project success. In this research we juxtapose two different views of what influences software development team performance during the requirements development phase. In an examination of 66 teams from 15 companies we found that team skill, managerial involvement, and little variance in team experience enable more effective team processes than do software development tools and methods. Further, we found that development teams exhibit both positive and negative boundary-spanning behaviors. Team members promote and champion their projects to the outside environment, which is considered valuable by project stakeholders. They also, however, guard themselves from their environments; keeping important information a secret from stakeholders negatively predicts performance.</t>
@@ -11171,7 +11249,11 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="P207" s="8" t="n"/>
+      <c r="P207" s="8" t="inlineStr">
+        <is>
+          <t>The study uses the team as the unit of analysis (N=66 teams) and aggregates data to the team level, which violates the requirement for individual-level boundary spanning behavior data.. Verbatim Evidence: "The model described in the previous section was tested using a cross-sectional field study of 66 teams performing requirements analysis in 15 organizations. The unit of analysis is the team, since the intent is to understand the behavior of a team as a whole rather than that of the individual team members."</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="18" customHeight="1" s="10">
       <c r="A208" t="inlineStr">
@@ -11184,6 +11266,16 @@
           <t>BSMA0205</t>
         </is>
       </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G208" t="inlineStr">
         <is>
           <t>This study examines the influence of the social network of board interlocks on strategic alliance formation. Our theoretical framework suggests how board interlock ties to other firms can increase or decrease the likelihood of alliance formation, depending on the content of relationships between CEOs (chief executive officers) and outside directors. Results suggest that CEO-board relationships characterized by independent board control reduce the likelihood of alliance formation by prompting distrust between corporate leaders, while CEO-board cooperation in strategic decision making appears to promote alliance formation by enhancing trust. The findings also show how the effects of direct interlock ties are amplified further by third-party network ties.</t>
@@ -11209,7 +11301,11 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="P208" s="8" t="n"/>
+      <c r="P208" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the firm and dyad level to predict the formation of interfirm alliances (joint ventures) based on board interlocks and CEO-board relations. The unit of analysis is the dyadic relationship between firms (N = 898 interlocked firm dyads; N = 73,510 total possible dyads). This violates the individual-level analysis requirement, as the study evaluates firm-level strategic actions rather than individual boundary spanning behavior.. Verbatim Evidence: ""The present study examines the influence of heterogeneous social processes that underlie interlock ties, and the moderating effects of indirect network ties, on the creation of strategic alliances between firms." ... "Hypothesis 1: An interlock tie between two firms will increase the likelihood of subsequent alliance formation between them." ... "Alliance formation was measured with a dichotomous variable, coded 1 if the two firms in a dyad entered into an alliance during the two-year period following the survey date (i.e., 1995-1996)." ... "Since hypothesis 1 examined the effect of interlock ties on alliance formation, the risk set for this analysis included all possible dyadic combinations between each of the focal firms in the final survey sample and all firms in the total sample frame (73,510 dyads)." ... "Table 3 ... Descriptive statistics and correlation coefficients are calculated for the sample of interlocked firms (N = 898)""</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="18" customHeight="1" s="10">
       <c r="A209" t="inlineStr">
@@ -11222,6 +11318,16 @@
           <t>BSMA0206</t>
         </is>
       </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G209" t="inlineStr">
         <is>
           <t>Leadership has been suggested to be an important factor affecting innovation. A number of studies have shown that transformational leadership positively influences organizational innovation. However, there is a lack of studies examining the contextual conditions under which this effect occurs or is augmented. Therefore, this study aimed to investigate the impact of transformational leadership on organizational innovation and to determine whether internal and external support for innovation as contextual conditions influence this effect. Organizational innovation was conceptualized as the tendency of the organization to develop new or improved products or services and its success in bringing those products or services to the market. Transformational leadership was hypothesized to have a positive influence on organizational innovation. Furthermore, this effect was proposed to be moderated by internal support for innovation, which refers to an innovation supporting climate and adequate resources allocated to innovation. Support received from external organizations for the purposes of knowledge and resource acquisition was also proposed to moderate the relationship between transformational leadership and organizational innovation. To test these hypotheses, data were collected from 163 research and development (R&amp;D) employees and managers of 43 micro‐ and small‐sized Turkish entrepreneurial software development companies. Two separate questionnaires were used to collect the data. Employees' questionnaires included measures of transformational leadership and internal support for innovation, whereas managers' questionnaires included questions about product innovations of their companies and the degree of support they received from external institutions. Organizational innovation was measured with a market‐oriented criterion developed specifically for developing countries and newly developing industries. Hierarchical regression analysis was used to test the hypothesized effects. The results of the analysis provided support for the positive influence of transformational leadership on organizational innovation. This finding is significant because this positive effect was identified in micro‐ and small‐sized companies, whereas previous research focused mainly on large companies. In addition, external support for innovation was found to significantly moderate this effect. Specifically, the relationship between transformational leadership and organizational innovation was stronger when external support was at high levels than when there was no external support. This study is the first to investigate and empirically show the importance of this contextual condition for organizational innovation. The moderating effect of internal support for innovation, however, was not significant. This study shows that transformational leadership is an important determinant of organizational innovation and encourages managers to engage in transformational leadership behaviors to promote organizational innovation. In line with this, transformational leadership, which is heavily suggested to be a subject of management training and development in developed countries, should also be incorporated into such programs in developing countries. Moreover, this study highlights the importance of external support in the organizational innovation process. The results suggest that technical and financial support received from outside the organization can be a more important contextual influence in boosting up innovation than an innovation‐supporting internal climate. Therefore, managers, particularly of micro‐ and small‐sized companies, should play external roles such as boundary spanning and should build relationships with external institutions that provide technical and financial support. The findings of this study are especially important for managers of companies that plan to or currently operate in countries with developing economies.</t>
@@ -11247,7 +11353,11 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="P209" s="8" t="n"/>
+      <c r="P209" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the effect of transformational leadership on organizational innovation, moderated by internal and external support. The 'external support' variable measures the number of innovative projects that received financial and technical assistance from external institutions (firm-level/project-level support), which is not individual-level purposive Boundary Spanning Behavior (BSB). Furthermore, the analysis is conducted entirely at the organizational level (N = 43 firms), with subordinate ratings of leadership and internal support aggregated to the firm level. Both the lack of a relevant BSB measure (Code 1) and the macro-level unit of analysis (Code 3) violate inclusion criteria.. Verbatim Evidence: "External Support for Innovation. To measure this variable, leaders were asked to indicate how many of their innovative projects received resource-based and knowledge-based support (i.e., financial and technical assistance) from external institutions in the last three years. The external institutions were organizations that support innovative projects, namely TUBITAK-TIDEB (Scientific and Technical Research Council of Turkey-Technology Monitoring and Evaluation Board) and TTGV (Technology Development Foundation of Turkey)... Aggregation of Transformational Leadership and Internal Support for Innovation Ratings. Since the dependent variable of this part of the analysis is organizational innovation, transformational leadership ratings as well as perceptions of internal support for innovation by the subordinates needed to be aggregated to organizational level. These variables were aggregated by averaging their values for each organization... Table 1. Descriptive Statistics and Correlations among the Variables... Means, standard deviations, and correlations among organizational-level variables are presented in Table 1."</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="18" customHeight="1" s="10">
       <c r="A210" t="inlineStr">
@@ -11260,6 +11370,14 @@
           <t>BSMA0207</t>
         </is>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>999</v>
+      </c>
       <c r="G210" t="inlineStr">
         <is>
           <t>Organizations have recognized that effective informal leadership is a source of competitive advantage and invest heavily in leadership development efforts. Moreover, because of historical shifts in the nature of work, this informal leadership often takes the form of inter-unit boundary spanning. Because of these two developments, discretionary boundary spanning (DBS) between units has increasingly become a critical, dynamic, bottom-up activity where individuals lacking formal authority step up and take on informal leadership responsibilities. In this study, we draw upon Simmelian Tie Theory (STT) to examine the relationship between different types of DBS and formal leaders’ perceptions of a subordinate’s informal leadership and performance. We empirically document that a small number of closed task-oriented and closed friendship-oriented DBSs are instrumental in helping individuals demonstrate informal leadership. However, we also show that DBS places constraints on informal leadership when closed ties become too numerous. This results in an inverted-U relationship between the number of closed DBS ties and perceptions of leadership where the apex (i.e., point of overembeddedness) emerges at a smaller number for friendship-oriented DBS relative to the apex for taskoriented DBSs. We discuss the theoretical implications of these results, as well as the practical implications for managers of organizations.</t>
@@ -11285,7 +11403,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P210" s="8" t="n"/>
+      <c r="P210" s="8" t="inlineStr">
+        <is>
+          <t>The study examines intra-organizational boundary spanning behavior (discretionary boundary spanning across internal teams) using a quantitative network survey of 132 employees in a large scientific project. It measures purposive boundary-spanning actions (exchanging work-related information across teams) and operationalizes them as individual-level open and closed network ties. The unit of analysis is the individual employee, and the study provides a full zero-order correlation matrix including these boundary spanning variables and informal leadership. It passes all inclusion criteria and does not trigger any exclusion guardrails.. Verbatim Evidence: "We define DBS as this type of inter-team exchange engaged in by individual team members who are not formal leaders directly charged with boundary spanning responsibilities... we collected sociometric data using a hybrid fixed roster and free recall method... With this procedure, we first presented the respondents with a list of all teams at FRIB outside their own, and then asked them to indicate whether they interacted with anyone from any of those teams... tasked respondents to characterize whether the person identified in the first stage of the procedure was (a) someone with whom they exchanged work-related information and/or (b) someone whom they considered a friend (or neither)... Table 1 Descriptive Statistics and Correlations... N = 132 (listwise)."</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="18" customHeight="1" s="10">
       <c r="A211" t="inlineStr">
@@ -11298,6 +11420,14 @@
           <t>BSMA0208</t>
         </is>
       </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>999</v>
+      </c>
       <c r="G211" t="inlineStr">
         <is>
           <t>With the emergence of "boundaryless organizations" and the increase in boundary-spanning activities, the sustainable development of organizations has been affected. Effectively promoting employees to engage in boundaryspanning activities has become of great practical significance. Besides, performance pressure has become a prevalent workplace stressor, significantly impacting employees' work behaviors. Therefore, drawing upon the cognitive-affective processing system theory and stressor-strain relationship theory, this study aims to investigate the mechanisms and boundary conditions of performance pressure on employee boundaryspanning behavior. Data collected from 336 questionnaires at two different time points is analyzed using bootstrapping and hierarchical regression to test hypotheses. The results indicate that performance pressure boosts employee boundary-spanning behavior by enhancing cognitive flexibility, while hindering this behavior by producing obsessive work passion. Moreover, achievement orientation plays a key role in moderating the impact of performance pressure on cognitive flexibility and obsessive work passion. Specifically, achievement orientation positively moderates the link between performance pressure and cognitive flexibility, while negatively moderating the relationship between performance pressure and obsessive work passion. Additionally, achievement orientation is found to moderate the indirect influence of performance pressure on employee boundaryspanning behavior through these two mediators. This study reveals that employees with high achievement orientation under performance pressure tend to develop cognitive flexibility, which motivates them to engage in more employee boundary-spanning activities. This paper also provides practical guidance for enterprises to promote employee boundary-spanning behavior. This study not only expands the research on the antecedents of employee boundary-spanning behavior but also confirms the double-edged sword effect of performance pressure on employee boundary-spanning behavior from both cognitive and affective perspectives.</t>
@@ -11323,7 +11453,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P211" s="8" t="n"/>
+      <c r="P211" s="8" t="inlineStr">
+        <is>
+          <t>The study examines employee boundary-spanning behavior at the individual level using a sample of 336 organizational employees. It measures the construct using an individual-referent version of Marrone et al.'s (2007) scale, which captures purposive boundary-spanning actions. A full zero-order correlation matrix is provided (Table 2), offering extractable effect sizes for boundary-spanning behavior.. Verbatim Evidence: "After excluding some questionnaires with short answer time and regularity of answers, 336 valid research questionnaires are finally obtained. In terms of sample characteristics, there are 162 males (48.21%) and 174 females (51.79%); in terms of age, there were 83 people under the age of 25 (24.70%)... Employee boundary-spanning behavior. It is assessed using the six-item scale developed by Marrone et al. (2007). A sample item is 'I would Persuade outsiders (e.g., faculty, clients) to support the team decisions.'... Table 2 Descriptive statistics and variable intercorrelations"</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="18" customHeight="1" s="10">
       <c r="A212" t="inlineStr">
@@ -11336,6 +11470,16 @@
           <t>BSMA0209</t>
         </is>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G212" t="inlineStr">
         <is>
           <t>Knowledge gathering can create problems as well as benefits for project teams in work environments characterized by overload, ambiguity, and politics. This paper proposes that the value of knowledge gathering in such environments is greater under conditions that enhance team processing, sensemaking, and buffering capabilities. The hypotheses were tested using independent quality ratings of 96 projects and survey data from 485 project-team members collected during a multimethod field study. The findings reveal that three capability-enhancing conditions moderated the relationship between knowledge gathering and project quality: slack time, organizational experience, and decision-making autonomy. More knowledge gathering helped teams to perform more effectively under favorable conditions but hurt performance under conditions that limited their capabilities to utilize that knowledge successfully. Implications for theory and research on knowledge and learning in organizations, team effectiveness, and organizational design are discussed.</t>
@@ -11361,7 +11505,11 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="P212" s="8" t="n"/>
+      <c r="P212" s="8" t="inlineStr">
+        <is>
+          <t>The study aggregates individual survey responses to the team level and conducts its statistical analyses with the team as the unit of analysis (N = 96 project teams). All correlation matrices and regression models report team-level aggregated constructs, meaning there are no extractable zero-order effect sizes for boundary spanning behavior at the individual employee level.. Verbatim Evidence: "The hypotheses were tested using independent quality ratings of 96 projects and survey data from 485 project-team members collected during a multimethod field study. [...] Data from the 485 members of the 96 qualifying teams were used to construct the team-level measures below; both core and noncore member responses were used because the contributions and views of each were important to project quality (Hackman 2002). [...] The responses to all eight questions were averaged across all the members of each team to create an aggregate measure of the amount of external knowledge gathered with a Cronbach's alpha of 0.85 (knowledge gathering). [...] Table 1 Descriptive Statistics and Bivariate Correlations (n = 96)"</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="18" customHeight="1" s="10">
       <c r="A213" t="inlineStr">
@@ -11374,6 +11522,16 @@
           <t>BSMA0210</t>
         </is>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G213" t="inlineStr">
         <is>
           <t>Extending the differentiation-integration view of organizational design to teams, I propose that self-managing teams engaged in knowledge-intensive work can perform more effectively by combining autonomy and external knowledge to capture the benefits of each while offsetting their risks. The complementarity between having autonomy and using external knowledge is contingent, however, on characteristics of the knowledge and the task involved. To test the hypotheses, I examined the strategic and operational effectiveness of 96 teams in a large multinational organization. Findings provide support for the theoretical model and offer implications for research on team ambidexterity and multinational management as well as team effectiveness.</t>
@@ -11399,7 +11557,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P213" s="8" t="n"/>
+      <c r="P213" s="8" t="inlineStr">
+        <is>
+          <t>The unit of analysis in this study is the team, not the individual employee. The sample consists of 96 teams in a multinational organization, and the variables for autonomy and external knowledge gathering were aggregated to the team level. The provided correlation matrix (Table 1) reports relationships between these team-level aggregated constructs (N=96). According to the screening rules, studies analyzing data at the team level must be excluded.. Verbatim Evidence: "To construct the team autonomy variable, I averaged the responses to these 20 items for each team member and then within teams... To construct the external knowledge variable, I averaged the responses to the eight survey items for each team member and then within teams (α = .85, ICC = .06, p &lt; .05, rwg = .69)... TABLE 1 Descriptive Statistics and Bivariate Correlations... a n = 96."</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="18" customHeight="1" s="10">
       <c r="A214" t="inlineStr">
@@ -11412,6 +11574,16 @@
           <t>BSMA0211</t>
         </is>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G214" t="inlineStr">
         <is>
           <t>SUMMARY             Previous research has focused on purchasing managers’ experience with role stressors and the negative effect of stress on job attitudes and performance. The potential benefits of having multiple responsibilities and a diverse role set have been overlooked. This study explored the relationship between purchasing managers’ involvement in multiple boundary spanning roles and their perceptions of positive social outcomes related to work. The relationship of these social benefits to job satisfaction was also evaluated. The relationships were analyzed using structural equation modeling. The results indicated positive relationships between each variable in the model. The implications for recruitment, supervision, and job design are discussed.</t>
@@ -11437,7 +11609,13 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="P214" s="8" t="n"/>
+      <c r="P214" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on the boundary spanning behavior of purchasing managers, which is a valid individual-level construct. However, the paper relies primarily on Structural Equation Modeling (SEM) to test its relationships and fails to provide a full square zero-order correlation matrix. While the paper includes partial rectangular cross-correlation tables (Tables III and IV) showing correlations between specific boundary spanning roles and social benefits, it does not report the intercorrelations among the BSB sub-dimensions or the zero-order correlations between BSB and key outcomes such as job satisfaction. According to the screening rules, studies that provide only partial rectangular cross-correlation tables instead of full square matrices lack the necessary data to compute composite effect sizes and must be excluded under Code 1.. Verbatim Evidence: "The data demonstrated an adequate fit with the proposed structural model. The results for this original model, showing the strengths of the relationships between each variable, are displayed in Figure 1.
+Table III: CORRELATIONS BETWEEN INDIVIDUAL BOUNDARY SPANNING ROLES AND OBTAINED SOCIAL BENEFITS
+Table IV: CORRELATIONS BETWEEN INDIVIDUAL BOUNDARY SPANNING ROLES AND DESIRED SOCIAL BENEFITS"</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="18" customHeight="1" s="10">
       <c r="A215" t="inlineStr">
@@ -11450,6 +11628,16 @@
           <t>BSMA0212</t>
         </is>
       </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G215" t="inlineStr">
         <is>
           <t>Innovation is considered the engine for firm growth. Especially innovations, through recombining seemingly unrelated knowledge streams, can have groundbreaking impact and lead to sustained competitive advantage. To generate such innovation, firms often need to go beyond their existing technological or geographical boundaries to identify and integrate novel knowledge elements. This article refers to firms’ knowledge activities of drawing upon distant knowledge (i.e., knowledge from dissimilar technological domains or distant geographical regions) to create novel technological solutions, as innovation through boundary spanning. Aiming to investigate the roles of information technology (IT) in facilitating innovation through boundary spanning, we collected data from the pharmaceutical industry over a six-year period to test the research model. The data analysis results indicate that IT supports boundary-spanning activities in firm innovation and different IT-enabled knowledge capabilities affect boundary-spanning innovation differently.</t>
@@ -11475,7 +11663,11 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="P215" s="8" t="n"/>
+      <c r="P215" s="8" t="inlineStr">
+        <is>
+          <t>This study analyzes boundary spanning at the firm level rather than individual employee behavior. It examines the effects of IT capabilities on technological and geographic boundary spanning among 31 pharmaceutical companies, operationalizing boundary spanning through firm-level patent citation data (e.g., the technological distance between a firm's patents and those cited from alliance partners). Therefore, it violates the unit of analysis guardrail and must be excluded under Code 3.. Verbatim Evidence: "We collected patent citation data for our sample companies to capture innovation through boundary spanning at the firm level. ... We capture the extent to which firms span their technological boundary by examining the distance between their own patents portfolio and the collection of patents that they cite from their alliance partners. ... We computed the technological boundary-spanning innovation as a distance measure based on the Euclidean distance between two profiles: one is comprised of the patents of the focal pharmaceutical firm, and the other is comprised of the patents that the focal firm cites from its alliance partners (Equation (1)). ... By eliminating firms that had no alliances during the time window included in this study and matching the remaining companies with IT data, we ended up with an unbalanced panel of 123 observations of 31 unique pharmaceutical companies over a six-year period from 2000 to 2005."</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="18" customHeight="1" s="10">
       <c r="A216" t="inlineStr">
@@ -11488,6 +11680,16 @@
           <t>BSMA0213</t>
         </is>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G216" t="inlineStr">
         <is>
           <t>Purpose – The current article investigates the impact of generational diversity on knowledge sharing and group performance. It, further, explores the moderating effects of intergenerational climate, boundaryspanning leadership, and respect in facilitating greater knowledge sharing and enhanced group performance. Design/methodology/approach – The authors applied partial least square structural equation modeling to test the model, using a sample of 635 employees working in the banking industry.</t>
@@ -11513,7 +11715,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P216" s="8" t="n"/>
+      <c r="P216" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study conceptualizes 'boundary-spanning leadership' as a leader's ability to bridge internal demographic and social identity boundaries (specifically, generational groups), which constitutes inclusive leadership rather than structural boundary spanning behavior (Code 1). Furthermore, the study measures generational diversity using a group-level diversity index (Blau's index based on branch composition) and evaluates branch performance, violating the individual-level analysis requirement (Code 3).. Verbatim Evidence: "Boundary-spanning leaders interact and exchange information impartially with members of all groups and are perceived as in-group prototypes by group members. This may bridge the gap between generational groups at the workplace and increase collaboration. ... Boundary-spanning leadership was measured using a three-item scale adopted from the Intergroup Rhetoric Scale by Rast (2013). ... Generational diversity. Generational diversity was measured using Blau’s (1977) index of heterogeneity (1 − ∑ρi2), where ρ was the proportion of group members in a category, and i was the number of different categories represented on a group. ... Group (branch) performance. Branch performance from employees and branch managers was measured using a four-item scale developed by Chow and Chan (2008)."</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="18" customHeight="1" s="10">
       <c r="A217" t="inlineStr">
@@ -11526,6 +11732,16 @@
           <t>BSMA0214</t>
         </is>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G217" t="inlineStr">
         <is>
           <t>This paper combines the concept of weak ties from social network research and the notion of complex knowledge to explain the role of weak ties in sharing knowledge across organization subunits in a multiunit organization. I use a network study of 120 new-product development projects undertaken by 41 divisions in a large electronics company to examine the task of developing new products in the least amount of time. Findings show that weak interunit ties help a project team search for useful knowledge in other subunits but impede the transfer of complex knowledge, which tends to require a strong tie between the two parties to a transfer. Having weak interunit ties speeds up projects when knowledge is not complex but slows them down when the knowledge to be transferred is highly complex. I discuss the implications of these findings for research on social networks and product innovation.</t>
@@ -11551,7 +11767,11 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="P217" s="8" t="n"/>
+      <c r="P217" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the effects of interunit ties on project completion time. However, the unit of analysis is the project team (N=120 new-product development projects), and the variables (such as tie weakness and knowledge complexity) are measured and analyzed at the project or divisional level, rather than measuring the boundary spanning behavior of individual employees. The correlation matrix provided (Table 1) represents project-level constructs. Therefore, it is excluded under Code 3 (Non-individual level).. Verbatim Evidence: "I use a network study of 120 new-product development projects undertaken by 41 divisions in a large electronics company to examine the task of developing new products in the least amount of time. Findings show that weak interunit ties help a project team search for useful knowledge in other subunits... I measured project completion time, the dependent variable, at the project level... Table 1: Descriptive Statistics and Correlations for Project Variables (N = 120)."</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="18" customHeight="1" s="10">
       <c r="A218" t="inlineStr">
@@ -11564,6 +11784,16 @@
           <t>BSMA0215</t>
         </is>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G218" t="inlineStr">
         <is>
           <t>This project provides an interpretation of how one cooperative support organization, the Nebraska Cooperative Council, discursively functions to help its constituent cooperatives consolidate resources in order to better intersect with organizations in a larger bureaucratic system. In analyzing qualitative data collected through in-depth interviews, surveys, and organizational documents, we found the paradox of stability and change a revealing prism through which to make sense of participants’ experiences. We work toward locating and describing how the Council, through its boundary-spanning activities, helps cooperatives manage the paradox of stability and change while protecting their core participatory ideologies. By providing networks of learning, promoting the legitimacy of cooperative forms of organizing, and protecting cooperatives’ interests, the Council is an entity helping cooperatives to reconcile their internal requirements for democracy with the external demands of the marketplace.</t>
@@ -11589,7 +11819,11 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="P218" s="8" t="n"/>
+      <c r="P218" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative analysis of discourse collected through in-depth interviews, surveys, and organizational documents regarding the boundary-spanning role of a cooperative support organization. It does not provide extractable quantitative effect sizes (r) or a correlation matrix, failing the data extractability gate for this meta-analysis.. Verbatim Evidence: "In analyzing qualitative data collected through in-depth interviews, surveys, and organizational documents, we found the paradox of stability and change a revealing prism through which to make sense of participants’ experiences. ... A thematic analysis of the discourse collected through in-depth interviews, survey questionnaires, and organizational documents was conducted using the constant comparative method (Lindlof, 1995)."</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="18" customHeight="1" s="10">
       <c r="A219" t="inlineStr">
@@ -11602,6 +11836,16 @@
           <t>BSMA0216</t>
         </is>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G219" t="inlineStr">
         <is>
           <t>Work teams must increasingly operate in complex environments characterized by multiple external actors beyond team and organizational boundaries. Although previous research demonstrates the importance of boundary spanning activities to team effectiveness, it reveals relatively little about the process of boundary spanning in these environments. In this article, we investigated the processes of boundary spanning across multiple external actors in 10 cross-organizational teams. We identified three sequences for reaching out to external actors: (a) moving inside-out from vertical actors inside the host organization to horizontal actors outside of the host organization, (b) moving outside-in from horizontal actors to vertical, and (c) staying-inside with vertical actors from the host organization. Our observations suggest that inside-out and outside-in sequences were more successful than simply pleasing the host organization. We build on our empirical findings to develop a process theory of how team boundary spanning activities across multiple external actors influence team effectiveness. Our research underscores the importance of a team’s interactions with actors in its external environment beyond those in an immediate supervisory role and provides insight into the dynamics of boundary spanning in multi-organizational contexts.</t>
@@ -11627,7 +11871,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P219" s="8" t="n"/>
+      <c r="P219" s="8" t="inlineStr">
+        <is>
+          <t>The study employs a qualitative case study and grounded theory approach based on semi-structured interviews with 46 team members from 10 cross-organizational teams. While the study proposes a process theory of team boundary spanning activities, it does not provide any extractable quantitative effect sizes (r) or a formal correlation matrix required for this meta-analysis. Therefore, it must be excluded under Code 1.. Verbatim Evidence: "To address this critical issue, we conducted a qualitative case study of externally oriented activity in 10 cross-organizational teams (COTs); that is, teams that include members external to the host organization; for example, Schopler, 1987; Zuckerman &amp; Higgins, 2002). Following other researchers who are interested in organizational processes (e.g., Anand, Gardner, &amp; Morris, 2007; Bresman, 2013; Nag &amp; Gioia, 2012), we combined a case study approach with grounded theory methodology (Langley, 1999). Specifically, we first used grounded methods to develop cases describing the sequence of early boundary spanning activity in each of 10 COTs; we then used a case study approach to compare and contrast those sequences across the 10 teams. Case studies drew on interviews with 46 team members."</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="18" customHeight="1" s="10">
       <c r="A220" t="inlineStr">
@@ -11640,6 +11888,16 @@
           <t>BSMA0217</t>
         </is>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G220" t="inlineStr">
         <is>
           <t>The paper explains the effects of internal and external team learning behaviors on the performance of marketing teams. The survey was conducted in the context of a multinational Pharmaceutical Corporation marketing its products in Turkey. Data were collected from members of marketing team which included medical sales representatives, specialized medical sales representatives and districts heads of marketing. The results indicate that both the internal team learning and the external team learning behaviors play significant roles in ensuring the success of marketing teams in continuously identifying, anticipating and satisfying the customer requirements profitably through an efficient deployment of the marketing teams’ resources.</t>
@@ -11665,7 +11923,16 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P220" s="8" t="n"/>
+      <c r="P220" s="8" t="inlineStr">
+        <is>
+          <t>The study measures 'External Team Learning' using survey items with group-level referents (e.g., 'My group', 'We', 'Group members'). Because the respondents are asked to rate their group's behavior rather than their own individual boundary-spanning behavior ('I'), the study violates the Proxy Guardrail. Even though individual responses are used (N=49), the construct represents team-level behavior, making it invalid for individual-level BSB.. Verbatim Evidence: "External Learning (α = 0.636)
+1. Group members go out and get all the relevant work information they possibly can from others –such as customers, or other parts of the organization.
+2. My group keeps others in the organization informed about what we plan and accomplish.
+3. We invite people from outside the group to present information or have discussions with us.
+4. My group frequently coordinates with other groups to meet organizational objectives.
+5. We don’t have time to communicate information about our group’s work to others who are not in the group. (reverse coded)"</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="18" customHeight="1" s="10">
       <c r="A221" t="inlineStr">
@@ -11678,6 +11945,16 @@
           <t>BSMA0218</t>
         </is>
       </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G221" t="inlineStr">
         <is>
           <t>Integration of organisational units has been extensively researched in various streams of management and organization sciences. It is very important whenever knowledge differences have to be overcome due to functional departmentalisation and the ensuing knowledge specialisation. However, extant literature does not yet appreciate the mediating role of absorptive capacity (AC) in this context. We argue that departments use integration mechanisms in order to develop and maintain such an organisational capability to absorb knowledge from other departments, so that integration can succeed to increase innovation performance. Our unique dataset of Italian manufacturing firms from various industries allows us to study this in the context of the integration of research and development (R&amp;D) and marketing and sales (M&amp;S) departments. Thereby, we provide empirical evidence on the mediating role of AC. We find evidence that R&amp;D departments build AC via formal cross-functional integration, while M&amp;S departments do so through informal integration. Moreover, we provide evidence of AC’s mediating role for the relationship between cross-functional integration mechanisms and innovation performance. Our findings also reveal significant differences between R&amp;D and M&amp;S functions in terms of effect sizes and significance levels. AC of R&amp;D departments has a significant and substantial effect on innovation performance and thus effectively acts as a mediating variable, while in case of M&amp;S departments we observe a significant direct effect between formal cross-functional integration and innovation performance without any mediation by AC.</t>
@@ -11703,7 +11980,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P221" s="8" t="n"/>
+      <c r="P221" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates cross-functional integration and absorptive capacity at the department level. The survey respondents (R&amp;D and M&amp;S professionals) act as key informants rating their department's behavior and capabilities, as evidenced by the survey item referents (e.g., 'To what extent does your department use...', 'Members of our department...'). Since the constructs represent department-level and business unit-level phenomena rather than individual employee boundary spanning behavior, the study is excluded.. Verbatim Evidence: "With the exception of the newly established construct of departmental ACs (i.e., FAC and CFAC), all variables have been measured based on previously validated items used in the management literature (see Appendix). The scales for the new concepts FAC and CFAC have been constructed on the basis of items established in the literature measuring AC at the organisational or sub-unit level... To what extent does your department use ... (1) free exchange of operating and financial information... Members of our department... (5) quickly analyse and interpret changing opportunities... Rate how your business unit is performing on the following new product development objectives relative to your firm’s stated objectives"</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="18" customHeight="1" s="10">
       <c r="A222" t="inlineStr">
@@ -11716,6 +11997,16 @@
           <t>BSMA0219</t>
         </is>
       </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G222" t="inlineStr">
         <is>
           <t>Background: Little is known about networks for positive behaviour support (PBS) in disability services. This study explores a PBS network to identify inﬂuential persons in its promotion and communication. Methods: Quantitative sociometric methods were used to identify persons who occupy positions of either boundary spanning (those that link people and groups) and/or opinion leadership (those that are sought for advice). Results: Nineteen persons were identiﬁed. Boundary spanners met all criteria for the position while opinion leaders did not. Conclusions: This is the ﬁrst published study of a PBS network in disability services and provides insights into persons involved in its systemic promotion. Boundary spanners are eﬀectively bridging the PBS network, yet persons seeking information about PBS are doing so from opinion leaders that do not display a requisite characteristic for this role. These results have implications for the wider utility of PBS within disability service systems.</t>
@@ -11741,7 +12032,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P222" s="8" t="n"/>
+      <c r="P222" s="8" t="inlineStr">
+        <is>
+          <t>The study utilizes social network analysis to identify boundary spanners and opinion leaders in the promotion of positive behaviour support (PBS) across disability services. While it uses betweenness centrality to operationalize boundary spanning, the results are purely descriptive. The paper reports the demographic and professional characteristics (frequencies and categorical data) of the identified boundary spanners but does not provide a zero-order correlation matrix or any inferential statistics (e.g., regressions) yielding an extractable effect size (r) between boundary spanning behavior and other constructs. Therefore, it lacks the quantitative data required for meta-analysis.. Verbatim Evidence: "This study used quantitative sociometric methods to identify persons in important network positions and self-reported survey data to quantify criteria associated with these positions. We acknowledge that only a small number of opinion leaders were included in the analysis. [...] Table 3 summarises the results of the network position criteria reported by the 19 persons in identified network positions, i.e., boundary spanners, opinion leaders, and combined."</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="18" customHeight="1" s="10">
       <c r="A223" t="inlineStr">
@@ -11754,6 +12049,16 @@
           <t>BSMA0220</t>
         </is>
       </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G223" t="inlineStr">
         <is>
           <t>A substantial body of research uses the concept of transactive memory systems to describe, explain, and predict the behavior and performance of teams. In a multirespondent study of 99 small to midsized technology-based firms, we extend the concept into the unique context of top management teams and discuss its implications for firm performance. Building on the multifunctional and boundary-spanning role of top managers, we develop a novel theoretical account of how the performance implications of transactive memory are shaped by the individual and conjoint influences of a top management team’s external social network ties and the rate of dynamism in the firm’s competitive environment. In so doing, we link top management team transactive memory to firm performance through transformation—more than through application—of existing scholarly understanding and through distinct operating mechanisms informed by an upper echelons perspective of the firm. Our theory and supportive findings provide new evidence on the relationship between transactive memory and firm performance. We conclude by tracing the implications of our findings for upper echelons and transactive memory research.</t>
@@ -11779,7 +12084,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P223" s="8" t="n"/>
+      <c r="P223" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts its analysis at the top management team (TMT) and firm level (N = 99 firms). The correlation matrix reports relationships between team-level aggregated constructs, specifically 'TMT average strength of external ties' and firm performance. Because the study aggregates the individual managers' network ties to the team level and provides no individual-level zero-order correlations for boundary spanning behavior, it must be excluded for lacking individual-level analysis.. Verbatim Evidence: "In a multirespondent study of 99 small to midsized technology-based firms, we extend the concept into the unique context of top management teams and discuss its implications for firm performance. ... All told, for 99 firms, we received responses from the CEO and at least another member of the top management team. ... To measure the average strength of the TMT’s external ties, we followed the methodology developed by Collins and Clark (2003) and commonly employed by upper echelons researchers. ... Aggregation is justified on two other bases instead. First, because all individuals are identified by the CEO as belonging to the TMT, their responses can reasonably be combined to gain a measure of the average strength of the TMT’s external ties (Heavey et al. 2015). Second, to gain some insight into the reliability of the average strength of ties, we relied on intraclass correlation scores (ICC1 and ICC2), which are computed to provide estimates of the reliability of the group mean (Bliese 2000). The ICC1 and ICC2 for the average strength of external ties across team members are 0.11 and 0.58, respectively, providing “prima facie evidence a group effect” for the average strength of external ties. ... Table 1 Descriptive Statistics and Correlations ... Note. N = 99."</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="18" customHeight="1" s="10">
       <c r="A224" t="inlineStr">
@@ -11792,6 +12101,16 @@
           <t>BSMA0221</t>
         </is>
       </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>Within the setting of 54 industrial corporations, the higher the variation in the membership size of the board of directors, the more rapid the rate of replacement of the president. Variations in board size are developed from a coefficient of volatility identifying yearly changes from 1947 to 1977. Further analysis of the data suggests that for relatively successful companies a significantly negative relationship exists between board size variation and rates of succession, whereas a significantly positive relationship exists for relatively unsuccessful companies. These results have implications for succession planning in the corporate presidency.</t>
@@ -11817,7 +12136,11 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="P224" s="8" t="n"/>
+      <c r="P224" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts a firm-level analysis (N = 54 petrochemical companies) to examine the relationship between board size variation and rates of succession in the corporate presidency. There are no individual-level measures of employee boundary spanning behavior, and all variables represent macro-level organizational characteristics. The unit of analysis is the firm, which violates the requirement for individual-level data.. Verbatim Evidence: "Within the setting of 54 industrial corporations, the higher the variation in the membership size of the board of directors, the more rapid the rate of replacement of the president... In light of these factors, a sample of 54 companies was identified for further study... TABLE 1: Descriptive Statistics for Variables Under Analysis (N = 54) [Variables include:] Average Succession Rate, Board Size Variation, Organizational Size, Organizational Growth, Organizational Performance, Organizational Technology."</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="18" customHeight="1" s="10">
       <c r="A225" t="inlineStr">
@@ -11830,6 +12153,16 @@
           <t>BSMA0222</t>
         </is>
       </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G225" t="inlineStr">
         <is>
           <t>Governments initiate major public sector reforms for various reasons. Although change leadership appears crucial, its role in implementing reforms in public organizations receives scant attention. Insights from public administration and change management literature help to bridge the gap between these macrolevel and microlevel perspectives. Our multilevel study of two youth care organizations addressing public sector reform explores how leadership behavior—and in interaction between top and middle managers—contributes to the concept of what we call change embeddedness among front-line employees. The use of leadership behaviors during the reform that are leader centric (shaping) appear to be associated with greater ambiguity and worse change embeddedness. However, leadership focused on engaging employees and boundary spanning with external organizations seems to support the embeddedness of the reform, especially when these behaviors are connected to a clear sense of purpose around the change.</t>
@@ -11855,7 +12188,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P225" s="8" t="n"/>
+      <c r="P225" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative case study that uses interviews and focus groups (N=3 top managers, 4 middle managers, 19 caregivers) to explore change leadership and change embeddedness in public organizations. It does not collect quantitative survey data and lacks extractable effect sizes (r) or a formal correlation matrix, thus it must be excluded for lacking quantitative effect sizes.. Verbatim Evidence: "To obtain a multilevel design, we conducted (a) interviews with the top managers of both youth care organizations (one at NHC and two at SHC), (b) interviews with two division heads per organization (four in total), and (c) four focus groups of caregivers (one group of representatives per working unit—19 caregivers in total) each reporting directly to one of the division heads... All interviews and focus groups were recorded and transcribed with the interviewees' and focus group participants' permission. Transcripts were analyzed employing an iterative approach that encompassed both a priori coding schemes (based on the literature) and emergent themes (based on a first coding by the interviewers)"</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="18" customHeight="1" s="10">
       <c r="A226" t="inlineStr">
@@ -11868,6 +12205,14 @@
           <t>BSMA0223</t>
         </is>
       </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>999</v>
+      </c>
       <c r="G226" t="inlineStr">
         <is>
           <t>Industrial research and development (R&amp;D) involves the processing and transformation of new knowledge into a commercially valuable outcome. Communication is an effective mechanism to translate, share and integrate new information into commercial products or processes. We developed a five‐factor model of team communication comprising: leadership role performance, team boundary spanning, communication safety, team reflexivity and task communication and tested the model using a one‐year longitudinal study. Analyses were conducted on team level data from 56 teams, comprising 350 employees. Independent measures of project performance were obtained from surveys of research managers as well as project customers. Three findings emerged. Different factors predicted different stakeholders' ratings of project performance. Communication safety was the strongest predictor of customer ratings of performance. Boundary spanning is most effective when performed by the project leader not the team.</t>
@@ -11893,7 +12238,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="P226" s="8" t="n"/>
+      <c r="P226" s="8" t="inlineStr">
+        <is>
+          <t>The study examines boundary spanning behavior in the context of R&amp;D teams. It measures leadership boundary spanning (the project leader's behavior) as well as team boundary spanning. Following the Leader BSB override rule and the N=Leaders=N=Teams exception, the leadership boundary spanning construct represents valid individual-level BSB (Boundary Spanning Leadership) because there is exactly one project leader per team (N=56 leaders). The study provides an extractable zero-order correlation matrix (Table 1) that includes the leader boundary spanner role, fulfilling all requirements for inclusion.. Verbatim Evidence: "Four organizations participated, providing 56 R&amp;D teams. ... At the beginning of the study there were 56 teams, comprising 294 team members and 56 leaders (providing 78% response rate). ... Teams (both leaders and team members) rated leadership role performance and team communication. ... Appendix A. Questionnaire measures; communication factor, scale and items. Leadership role performance: Boundary Spanner. Coordinating the team's task with outside stakeholders. Collaborating with others outside of the team. Scanning the environment inside and outside the organization for ideas/expertise. Negotiating resources for the team. Negotiating project goals with the customer. ... Table 1 reports the correlations between leadership roles and team communication measures at mail-out one as well as their relationship with project performance"</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="18" customHeight="1" s="10">
       <c r="A227" t="inlineStr">
@@ -11906,6 +12255,16 @@
           <t>BSMA0224</t>
         </is>
       </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G227" t="inlineStr">
         <is>
           <t>We examine how the use of mobile information and communication technologies (ICTs) among self-employed homeworkers affects their experience of work, focussing particularly on where work is carried out, how the work/non-work boundary is managed, and people’s experiences of social and professional isolation. Positively, their use enhanced people’s sense of spatio-temporal freedom by allowing them to leave the home without compromising their work availability. This also helped reduce people’s feelings of social isolation. More negatively their use enhanced people’s sense of ‘perpetual contact’, creating a sense that work was difficult to escape from. However, the extent to which mobile ICTs were used, and the extent to which their impact on people’s experiences of work were understood, were found to vary significantly, highlighting the agency that users have with regard to technology use. The findings are framed by combining Nippert-Eng’s boundary work theory, with an ‘emergent process’ perspective on socio-technical relations.</t>
@@ -11931,7 +12290,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P227" s="8" t="n"/>
+      <c r="P227" s="8" t="inlineStr">
+        <is>
+          <t>The study is purely qualitative, relying on telephone interviews with 14 self-employed homeworkers and using qualitative content analysis. It does not provide any quantitative data, correlation matrices, or extractable effect sizes (r). Furthermore, the construct examined is work-life/home-work boundary management, not inter- or intra-organizational boundary spanning behavior.. Verbatim Evidence: "Data was collected from participants via telephone interviews which typically lasted about 45 minutes, with all conversations being digitally recorded with participants’ consent. The interviews were qualitative conversations, being focussed around a standard list of open-ended questions that were asked to all interviewees. ... The analytical methodology utilized was what Berg (2006) characterizes as qualitative content analysis, with the objective being to identify patterns in the interview data. ... We examine how the use of mobile information and communication technologies (ICTs) among self-employed homeworkers affects their experience of work, focussing particularly on where work is carried out, how the work/non-work boundary is managed, and people’s experiences of social and professional isolation."</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="18" customHeight="1" s="10">
       <c r="A228" t="inlineStr">
@@ -11944,6 +12307,16 @@
           <t>BSMA0225</t>
         </is>
       </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2 = Non-employee samples</t>
+        </is>
+      </c>
       <c r="G228" t="inlineStr">
         <is>
           <t>Extant management literature suggests that boundary spanning, defined as linking an organization's internal networks with external sources of information, is crucial to an organization’s growth and sustainability in that it enables firms to build connections, share knowledge, and exchange resources. A boundary spanner is a gatekeeper with access to external partners, critical resources, and information, and therefore, plays an important role in creating opportunities for an organization. This dissertation extends the research on individual boundary spanning by examining an overlooked source–skilled digital freelancers–and identifying how and when they are likely to serve as boundary spanners with a primary focus on their boundary spanning behaviors within contracted positions and the facilitating role of human capital and strategic orientation.</t>
@@ -11969,7 +12342,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P228" s="8" t="n"/>
+      <c r="P228" s="8" t="inlineStr">
+        <is>
+          <t>The study's sample consists of skilled digital freelancers recruited from the Upwork platform. These individuals are self-employed independent contractors (gig workers) rather than embedded organizational employees. According to the screening rules, boundary spanning behavior must be examined within a population of organizational employees, and samples of self-employed individuals or non-employees must be excluded.. Verbatim Evidence: "A skilled digital freelancer is defined herein as someone who works remotely and engages in contract-based jobs for different organizations, often at the same time. ... Non-employees, such as skilled freelancers working through digital platforms, perform an increasing amount of the work within organizations (Altman et al., 2021). ... So, the final sample size was 143 (N = 143) skilled digital freelancers employed on the Upwork platform in the United States."</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="18" customHeight="1" s="10">
       <c r="A229" t="inlineStr">
@@ -11982,6 +12359,16 @@
           <t>BSMA0226</t>
         </is>
       </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G229" t="inlineStr">
         <is>
           <t>In this article we examine project-level and team-level managerial functions aimed at managing inter-team task interdependencies and investigate their effect on the performance of teams in a multi-team product development project. We hypothesize that team interface management (a team-level function) performed in the concept phase of a project, rather than the later development phase, is positively related to team performance at the project’s conclusion (i.e. product quality, product cost, development budget, development time). Furthermore, we argue that project structuring and support (a project-level function) is important in both the concept and the development phases. We test our hypotheses empirically based on a 36 months longitudinal study of a product development project in the European automotive industry comprising 39 teams. The results show that team interface management is particularly important during the concept phase of the project. Project structuring and support is most important in the development phase of the project, while hindering team performance in the concept phase. Theoretical and practical implications are discussed.</t>
@@ -12007,7 +12394,11 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="P229" s="8" t="n"/>
+      <c r="P229" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the team (N = 39 cross-functional teams), and all data were aggregated to the team level before analysis. Furthermore, the survey items for the boundary spanning construct (Team interface management) use the grammatical subject 'Our team' rather than 'I', indicating that respondents are evaluating team-level behavior rather than their own individual boundary spanning behavior. Therefore, the study lacks independent individual-level effect sizes.. Verbatim Evidence: "The project we investigated included a total of 39 cross-functional teams that were co-located in one building. ... The database for this research is made up of 452 interview responses (time 1 and time 2) from team members and team leaders, expert ratings of product quality as well as manager ratings of schedule performance, and data from company records regarding product cost and development cost (time 3). ... Given this homogeneity of within-team ratings, data were aggregated by calculating the arithmetic mean. ... All analyses were conducted at the team level with pairwise exclusion in case of missing data. ... [Appendix] Team interface management: Our team clarifies its boundaries and interdependencies with other teams within the project; Our team defines its process outputs precisely; Our team coordinates its process outputs with other teams."</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="18" customHeight="1" s="10">
       <c r="A230" t="inlineStr">
@@ -12020,6 +12411,16 @@
           <t>BSMA0227</t>
         </is>
       </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G230" t="inlineStr">
         <is>
           <t>Organizations increasingly set up multiteam projects for the development of highly complex products. While team research has emphasized the importance of team-internal processes for smaller scale projects, we know little about collaborative processes (especially between teams) in such large-scale projects. This study utilizes a multi-informant longitudinal research design on a product development project (39 teams, 36 months) in the European automotive industry investigating collaboration between and within teams. The results of the study demonstrate that interteam coordination, project commitment, and teamwork quality as rated by the team members at Time 1 (Month 12; end of concept phase) are significantly correlated to project managers’ ratings of overall team performance at Time 3 (Month 36; end of project). The process variables measured at Time 2 (Month 24; end of design phase) display generally weaker correlations with team performance at Time 3. Multiple regression analyses further detail the effects of collaborative processes within and between teams on different measures of team performance (i.e., overall performance, quality, budget, schedule). The results show that collaborative processes during the project have predictive properties in regard to later team performance and can serve as early warning indicators. Furthermore, the results of this study provide support for our hypotheses predicting positive relationships between interteam coordination, project commitment, and teamwork quality. Theoretical and practical implications of this study are discussed.</t>
@@ -12045,7 +12446,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="P230" s="8" t="n"/>
+      <c r="P230" s="8" t="inlineStr">
+        <is>
+          <t>The study collects data from individual team members but aggregates it to the team level prior to analysis. The reported correlation matrix and all subsequent analyses are conducted exclusively at the team level (N = 39 teams). This violates the inclusion criteria requiring individual-level employee data and effect sizes.. Verbatim Evidence: "Given this homogeneity of within-team ratings, data were aggregated by calculating the arithmetic mean. [...] All analyses are conducted at the team level (N = 39). [...] Table 1 Descriptive Statistics and Intercorrelations [...] N = 39 teams."</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="18" customHeight="1" s="10">
       <c r="A231" t="inlineStr">
@@ -12058,6 +12463,16 @@
           <t>BSMA0228</t>
         </is>
       </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G231" t="inlineStr">
         <is>
           <t>Purpose – Academic research on public affairs which aims to reconstruct the rationale for the involvement in public affairs, and the possible outsourcing thereof, focuses mainly on the perspective of the principal. Even though consultants are undoubtedly increasing in importance, their relevance as agents is often downplayed. This study seeks to empirically supplement the perspective of the consultant in order to identify potential inimitable functions that could explain why public affairs work is often contracted-out.</t>
@@ -12083,7 +12498,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P231" s="8" t="n"/>
+      <c r="P231" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure individual-level employee boundary spanning behavior. The sample consists of 101 public affairs agencies (consultancies), where the respondent (CEO or head of public affairs) serves as a key informant for the firm. The survey items explicitly use the macro-level referent 'We' (e.g., 'We try to build trust between societal players'), indicating the unit of analysis is the firm/agency rather than the individual (violating Screening Rule 5). Furthermore, the study investigates the perceived functions and services of public affairs agencies rather than the interpersonal boundary-spanning behaviors of organizational employees, lacking any relevant zero-order effect sizes. Therefore, it is excluded under Code 1 (No effect size of interest) and Code 3 (Non-individual level).. Verbatim Evidence: "The empirical analysis is based on data from a nationwide survey about public affairs consultants in Switzerland... The questionnaire addressed the highest-ranking person in charge of public affairs, or the CEO of the agency. 337 of 641 agencies responded to the questionnaire (53 percent); 236 agencies stated that they do not offer any public affairs services on a regular basis. Once these had been sorted out, 101 respondents formed the sample that was analyzed... Table III. Descriptive statistics: relevance of public affairs functions... We try to build trust between societal players... We see ourselves as lawyers asserting our clients' interests... Table VIII. Descriptive statistics: relevance of selection criteria for agency... We ... have a good reputation in our field of activity"</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="18" customHeight="1" s="10">
       <c r="A232" t="inlineStr">
@@ -12096,6 +12515,16 @@
           <t>BSMA0229</t>
         </is>
       </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G232" t="inlineStr">
         <is>
           <t>Scholarship in the field of health communication is broad, with interdisciplinary contributions from researchers trained in a variety of fields including communication, nursing, medicine, pharmacy, public health, and social work. In this paper, we explore the role of “health communication boundary spanners” (HCBS), individuals whose scholarly work and academic appointment reflect dual citizenship in both the communication discipline and the health professions or public health. Using a process of critical reflective inquiry, we elucidate opportunities and challenges associated with HCBS across the spectrum of health communication in order to provide guidance for individuals pursuing boundary spanning roles and those who supervise and mentor them. This dual citizen role suggests that HCBS have unique skills, identities, perspectives, and practices that contribute new ways of being and knowing that transcend traditional disciplinary boundaries. The health communication field is evolving in response to the need to address significant healthcare and policy problems. No one discipline has the ability to single-handedly fix our current healthcare systems. Narrative data from this study illustrate the importance of seeing HCBS work beyond simply being informed by disciplinary knowledge. Rather, we suggest that adapting ways of knowing and definitions of expertise is an integral part of the solution to solving persistent health problems.</t>
@@ -12121,7 +12550,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P232" s="8" t="n"/>
+      <c r="P232" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a qualitative, critical reflective inquiry approach based on the authors' own narratives of their experiences as health communication boundary spanners. It does not collect quantitative survey data from employees and lacks a formal correlation matrix or extractable effect sizes (r) of interest.. Verbatim Evidence: "Using a process of critical reflective inquiry, we elucidate opportunities and challenges associated with HCBS across the spectrum of health communication in order to provide guidance for individuals pursuing boundary spanning roles and those who supervise and mentor them. [...] We iteratively collected and analyzed data for this manuscript using the three sequential phases (Kim, 1999): descriptive, reflective, and critical summarized in Table 1. First, we used the descriptive phase to elicit narratives of actual experiences including descriptions of actions, thoughts, and feelings (Kim, 1999). [...] Each author wrote narratives of their experiences navigating a boundary spanning academic position."</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="18" customHeight="1" s="10">
       <c r="A233" t="inlineStr">
@@ -12134,6 +12567,16 @@
           <t>BSMA0230</t>
         </is>
       </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G233" t="inlineStr">
         <is>
           <t>Some audit researchers suggest that high levels of audit team structure may encumber communication within audit teams by impeding information-gathering activities. Others suggest that structure benefits communication by coordinating and controlling information flows. This study evaluated these arguments by examining the relationship between the structure of audit teams and selected communication variables (information overload, boundary spanning, satisfaction with supervision, and accuracy of information). Questionnaire data were gathered from a national sample of 109 audit teams, with three auditors responding from each team (i.e., n = 327). Information overload, satisfaction with supervision, and accuracy of information were less in audit teams with greater structure. The implication is that the level of structure adopted by teams has both positive and negative effects on communication, with structured teams providing greater control over information overload but impairing satisfaction with supervision and the accuracy of information.</t>
@@ -12159,7 +12602,11 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="P233" s="8" t="n"/>
+      <c r="P233" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the team level rather than the individual employee level. Although data was collected from 327 auditors across 109 audit teams, the researchers explicitly state that they computed a team score for each variable by aggregating individual responses. The reported correlation matrix uses the 109 audit teams as the sample size (n = 109). Therefore, the study does not provide individual-level effect sizes for boundary spanning behavior and must be excluded under the team-level aggregation guardrail.. Verbatim Evidence: "The unit of analysis for the study is the audit team. A team score for each variable was computed by summing the individual item responses provided by the three team members. For the variables under study, the proportion of total variance that is shared among teammates (Spearman-Brown formula; DeVellis 1991) is .26 for information overload, .42 for boundary spanning... TABLE 2 LISREL-Estimated Correlations of the Communication Variables With Audit Team Structure (n = 109)"</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="18" customHeight="1" s="10">
       <c r="A234" t="inlineStr">
@@ -12172,6 +12619,16 @@
           <t>BSMA0231</t>
         </is>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G234" t="inlineStr">
         <is>
           <t>In this study of 338 inpatient psychiatric departments five hypotheses concerning organizational performance and size are tested and supported. It is found that psychiatric inpatient department performance varies with hospital ownership and is inversely related to department size. It is also found that increases in department size are not marked by changes in the relative size of administrative components. With increases in size, however, private hospitals tend to employ nonprofessional or paraprofessional support staff, while public hospitals are marked by a proliferation of professional staff. Furthermore, as inpatient departments increase in size they tend to increase the number of boundary spanning and buffering structures in existence. Discussed is the extent to which size and organizational ownership affect the performance of the psychiatric department.</t>
@@ -12197,7 +12654,11 @@
           <t>1973</t>
         </is>
       </c>
-      <c r="P234" s="8" t="n"/>
+      <c r="P234" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates the correlates of performance and size across 338 inpatient psychiatric departments. The unit of analysis is the organizational department (N=338) rather than individual employees. The variables measured are macro-level structural and performance metrics (e.g., number of beds, discharge rate, staff man-hours, and the presence of outpatient services functioning as structural 'buffers') rather than individual-level, interpersonal boundary spanning behavior. Consequently, the study is excluded as a macro-level organizational analysis.. Verbatim Evidence: "In this study of 338 inpatient psychiatric departments five hypotheses concerning organizational performance and size are tested and supported. ... Department size. Size of department was measured by the number of beds devoted solely to inpatient psychiatric care. ... Input and output buffers. The existence of input buffers is determined by whether the psychiatric department had attempted to identify homogeneous elements of its task environment and restrict input accordingly. The Inventory of Psychiatric Services indicated whether a department had restrictions as to type of patient served."</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="18" customHeight="1" s="10">
       <c r="A235" t="inlineStr">
@@ -12210,6 +12671,16 @@
           <t>BSMA0232</t>
         </is>
       </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G235" t="inlineStr">
         <is>
           <t>Following the resource-advantage theory, this study advances the existing research of boundaryspanning search by examining which configuration of a new venture’s boundary-spanning search can obtain successful venture performance and how a founding team’s external relationship and the internal firm competences shape the relationship between the distant search and new venture performance. This paper is based on a questionnaire survey/analysis of a sample of 178 new ventures from China, and it offers insight to entrepreneurs with regard to the importance of building external managerial ties and developing idiosyncratic internal competences on boundary-spanning search. In addition, this study also reveals that the effectiveness of the supply-side, demand-side and spatialside boundary-spanning search on venture performance depends on investing resource at a rational level.</t>
@@ -12235,7 +12706,11 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="P235" s="8" t="n"/>
+      <c r="P235" s="8" t="inlineStr">
+        <is>
+          <t>The study measures boundary-spanning search at the firm level, using top management team members as key informants to evaluate the venture's external relationships. The survey items explicitly use macro-level referents such as 'We', 'your venture', and 'Our team'. Furthermore, the study aggregated responses using a consensus approach to assign a single rating per firm (N = 178 new ventures), confirming that the unit of analysis is the firm/team rather than individual employee boundary-spanning behavior.. Verbatim Evidence: "We used a survey methodology to gather the data for the research. This study used a sample framework of 300 firms selected randomly from the list of 650 new technology ventures located in Shenzhen... Besides, this study used the consensus approach to rate each questionnaire item from key informants. We asked two or three founding team members to deliberately assign a single rating based on consensus among those informants... We obtained 178 usable questionnaires from different firms... Supply-side search... Over the last three years, to what extent has your venture gone? 1. We are well aware of technological and technical developments within our industry... Extraindustry managerial ties... 1. Our team members put a lot of effort into communicating with knowledgeable people outside our industry"</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="18" customHeight="1" s="10">
       <c r="A236" t="inlineStr">
@@ -12248,6 +12723,16 @@
           <t>BSMA0233</t>
         </is>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G236" t="inlineStr">
         <is>
           <t>Information system development can be considered a collaboration between users and developers. The inability to leverage the localized knowledge embedded in these two stakeholders hinders software development work to achieve high performance. Exploring the ways to counter this difﬁculty is then critical. This study applies an intellectual capital perspective to address the issues around spanning the knowledge boundary between developers and users. Our ﬁndings highlighted how important effective knowledge boundary spanning is to both product and project quality. Furthermore, three dimensions of intellectual capital increased the degree to which knowledge boundary spanning was effective.</t>
@@ -12273,7 +12758,11 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="P236" s="8" t="n"/>
+      <c r="P236" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the IS development project (N=267 projects), and data is collected from single key informants (project managers, team leaders, or senior members) acting as proxies to evaluate team-level dynamics. The boundary spanning construct measures collective interactions between groups (e.g., 'Developers and users use shared terminology') rather than the purposive interpersonal boundary spanning behavior of a focal individual employee. Therefore, it violates the individual-level analysis and proxy guardrails.. Verbatim Evidence: "The potential subjects of this study were practitioners who engaged in information system development. We took a two-step approach to collecting the data. ... we delivered the survey instrument to the 750 project managers, team leaders, or senior members who were identified in the first stage. A total of 279 responses were collected ... the remaining 267 responses were used for the following analysis. ... KBS1 Developers and users use shared terminology to transfer their own knowledge to each other. KBS2 Developers and users build shared lexicon and meaning toward each other's expertise/knowledge."</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="18" customHeight="1" s="10">
       <c r="A237" t="inlineStr">
@@ -12286,6 +12775,14 @@
           <t>BSMA0234</t>
         </is>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>999</v>
+      </c>
       <c r="G237" t="inlineStr">
         <is>
           <t>There appears to be a consensus that organizational integration across functional and disciplinary specialties drives superior ﬁrm capabilities. The basic assumption is that new practices and concepts emerge from the interaction of individuals engaged in different functional departments. However, communication across functional boundaries is often difﬁcult. As such, Tushman &amp; Scanlan suggested that functional boundaries can be spanned effectively only by boundary spanners who understand the coding schemes that are attuned to the contextual information on both sides of the boundary. The study of boundary spanners has signiﬁcant performance implications to ﬁrms. Compared to its importance, theoretical development and empirical inquiries into this phenomenon are relatively scant. Thus, this study explores the factors that determine who becomes a boundary spanner and examines boundary spanners’ performance implications. A Taiwanese company provided the context for our study. Partial Least Squares (PLS) was used to test the theoretical model. The results imply that a company needs to have an appropriate mixture of boundary spanners and non-boundary spanners, because boundary spanners have higher innovative performance.</t>
@@ -12311,7 +12808,11 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="P237" s="8" t="n"/>
+      <c r="P237" s="8" t="inlineStr">
+        <is>
+          <t>The study measures boundary spanning behavior across internal organizational boundaries (inter-departmental advice-seeking network). The authors define boundary spanners as individuals who are both internal and external (inter-departmental) communication stars based on in-degree centrality from the question 'Who do you go to for help or advice on work-related matters?'. This qualifies as intra-organizational BSB under Screening Rule 2 (Intra-Org BSB Override) and network-based BSB inclusion criteria. The study provides a zero-order correlation matrix with extractable effect sizes and uses an individual-level employee sample (N=124).. Verbatim Evidence: "To assess the network relations, we follow the work of Sparrowe (2001) by asking the respondents one question: 'Who do you go to for help or advice on work-related matters?'... The in-degree centrality of an actor (individual i) was the number of individuals that ask individual i work-related matters in their answers to the above question. Consistent with Tushman &amp; Scanlan (1981b), internal communication stars were defined as those individuals in the top third of the intra-department communication and external communication stars were defined as those who are in the top third of an external communication distribution. And boundary spanners are those who are both internal and external communication stars (Tushman &amp; Scanlan, 1981b)... The sample size is 124, exceeding the recommended minimum of 40... Table 2. Correlations and discriminant validity"</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="18" customHeight="1" s="10">
       <c r="A238" t="inlineStr">
@@ -12324,6 +12825,16 @@
           <t>BSMA0235</t>
         </is>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G238" t="inlineStr">
         <is>
           <t>Purpose – The purpose of this paper is to investigate three issues: how does an innovative search (local search and boundary-spanning search) impact ﬁrm innovation performance of latecomers; how does capability reconﬁguration (capability evolution and capability substitution) mediates the relationship between innovative search and ﬁrm innovation performance; and how does the technological leapfrogging process (initial stage, following stage, synchronization stage and leading stage) moderate the relationship between capability reconﬁguration and ﬁrm innovation performance.</t>
@@ -12349,7 +12860,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P238" s="8" t="n"/>
+      <c r="P238" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts analysis at the firm level (N=290 firms) rather than the individual employee level. The respondents (middle and senior managers) serve as macro-level key informants reporting on their organization's boundary-spanning search and firm innovation performance, which violates the individual-level analysis requirement for Boundary Spanning Behavior.. Verbatim Evidence: "We sent out 750 questionnaires to part-time MBA and EMBA students at 4 universities in China who come from enterprises in different provinces and municipalities... Respondents were asked to be middle and senior managers and technical executives who understand corporate strategy and technology innovation... Eventually, we obtained valid questionnaires from 290 different companies... Boundary-spinning search includes six items: searching for knowledge from patent bulletin disclosure; searching for knowledge from technology license; searching for knowledge from external research institutions, universities or institutions of higher learning; searching for knowledge from industry exhibitions; searching for knowledge from technical publications and technical conferences and searching for knowledge from customers."</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="18" customHeight="1" s="10">
       <c r="A239" t="inlineStr">
@@ -12362,6 +12877,16 @@
           <t>BSMA0236</t>
         </is>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G239" t="inlineStr">
         <is>
           <t>This study examines personal ties between boundary-spanning personnel in interorganizational exchanges in emerging markets. Drawing on social embeddedness theory and boundary spanning theory, we propose that strong ties between boundary spanners may benefit exchange parties in their interorganizational relationships through two heightened boundary-spanning behaviors—information processing and external representation. The results from 225 manufacturer–distributor dyads in China indicate that interpersonal ties at the higher levels (between top executives) and at the lower levels (between salespersons and individual buyers) are both positively associated with relationship quality of the buyer–supplier relationship through dyadic boundary-spanning behaviors. Between two levels of interpersonal ties, ties at the lower levels exhibit a stronger association with relationship quality than do ties at the higher levels. Furthermore, the positive effects of interpersonal ties on conflict resolution and cooperation are amplified when both levels of ties are strong in the focal relationship.</t>
@@ -12387,7 +12912,11 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="P239" s="8" t="n"/>
+      <c r="P239" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the interorganizational dyad level (N=225 manufacturer-distributor dyads) rather than the individual employee level. The respondents (senior sales or purchasing managers) served as macro-level key informants to evaluate the firm's external relationships. This is confirmed by the grammatical subject of the survey items, which use 'we', 'our firm', or refer to collective entities (e.g., 'We inform each other...', 'Leaders of both sides...'). Furthermore, all constructs were operationalized by aggregating and taking the mean scores of both parties in the dyad, violating the individual-level analysis requirement.. Verbatim Evidence: "This study uses matched survey data from both the manufacturer (supplier) and the distributor (buyer) sides, in the context of the Chinese household appliances industry. Accordingly, the unit of analysis of this study is the dyad. To ensure that the respondents were capable of answering questions, we requested that contact persons be senior managers who deal directly with the other party, and who are fully responsible for the organizational relationship. All dyadic constructs are operationalized by taking mean scores of both parties’ scores in the dyads, following the aggregation approach in Yan, Simsek, and Lubatkin (2008). TM1: Leaders of both sides always invite each other to participate in various activities for socialization. C1: We inform each other in advance of changing needs. RS1: The working relationship between our firm and the supplier (buyer) is characterized by feelings of friendliness."</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="18" customHeight="1" s="10">
       <c r="A240" t="inlineStr">
@@ -12400,6 +12929,16 @@
           <t>BSMA0237</t>
         </is>
       </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G240" t="inlineStr">
         <is>
           <t>Boundary‐spanning personnel such as tax preparers, travel agents and hairdressers interface directly with customers. In their unique position, between the organization and customer, these service providers market the service to consumers while they simultaneously carry out operational functions. Both the customer and the provider bring certain expectations to the service encounter. These expectations then shape the perceptions of the service encounter. The research reported uses script methodology to compare the expectations between boundary‐spanning service providers and consumers of the same service. Draws its theoretical foundation from the expectations and scripts literatures. In Phase One, scripts of the service were elicited in order to test hypotheses based on the discovery and comparison of consumers′ and service providers′ subgoals for a typical service encounter (               H1               ). A hypothesis also tested the point at which providers and consumers enter their respective scripts of a typical service encounter (               H2               ). In Phase Two, the subgoals mentioned most frequently in Phase One were used as stimuli to elicit the specific actions which comprise the complete script. These complete scripts enabled a comparison of the elaborateness of provider and consumer scripts (               H3               ). The results of Phase One revealed that a portion of consumers′ subgoals for a service encounter are shared by providers of the service while other subgoals are unique, supporting               H1               . The point of activation of the script differed dramatically between customers and providers, supporting               H2               . The Phase Two findings provide support for the hypothesis that service providers have more elaborate scripts. Overall, the results support the notion that scripts operationalize expectations. Closes with implications for management and suggestions for future research.</t>
@@ -12425,7 +12964,19 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="P240" s="8" t="n"/>
+      <c r="P240" s="8" t="inlineStr">
+        <is>
+          <t>The study examines service expectations by comparing the cognitive scripts of consumers (undergraduates) and service providers (hairdressers) in the context of getting a haircut. It does not measure boundary spanning behavior (BSB) or any relevant organizational cross-boundary activity. Furthermore, it lacks extractable quantitative effect sizes such as zero-order correlations, relying instead on frequency counts and chi-square analyses of script elements.. Verbatim Evidence: "The purpose of this study is to address this gap by comparing the expectations of service providers and consumers of the same service. We investigate whether the same components of a service encounter are identified as important by both sets of participants.
+...
+Haircuts were selected as the context for the study for several reasons. First, having one’s hair cut in a salon is a common experience in which almost everyone participates.
+...
+The sample of consumers consisted of 48 undergraduates enrolled in marketing classes at a large university in the USA. ... The service providers were 24 hairdressers who worked in a number of shops within an eight-mile radius of the university.
+...
+Thus, two sets of scripts were obtained, one set from consumers and the other set from service providers. The unit of analysis was the script, which was composed of the subgoals of the respondent’s typical haircut.
+...
+Chi-square analysis found no significant gender differences in the frequency of mention of any of the subgoals."</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="18" customHeight="1" s="10">
       <c r="A241" t="inlineStr">
@@ -12438,6 +12989,16 @@
           <t>BSMA0238</t>
         </is>
       </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G241" t="inlineStr">
         <is>
           <t>Purpose – The purpose of this study is to explore how integration teams can build trusting relationships in component teams to enhance their leadership capability within multiteam systems to achieve common superordinate goals. The study investigates how an integration team diagnoses contextual dynamics to enhance understanding of goals in component teams and spans boundaries to create trusting relationships.</t>
@@ -12463,7 +13024,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P241" s="8" t="n"/>
+      <c r="P241" s="8" t="inlineStr">
+        <is>
+          <t>The study examines intra-organizational boundary spanning behavior among manufacturing employees. However, the paper relies entirely on Structural Equation Modeling (SEM) path coefficients and does not report a zero-order correlation matrix or any extractable bivariate effect sizes (r). Per the SEM-only Data Warning, studies lacking a correlation matrix or simple regression R^2 must be excluded.. Verbatim Evidence: "Structural equation modelling (SEM) was used for the data analysis that included all the hypothesised paths... A measurement model was developed in AMOS 24.0 for the four constructs to be tested... A structured model was constructed to formulate the standardised regression estimates (Figure 2)... Table I. Scales, items and descriptive statistics [Reports M, SD, Factor loadings, and Cronbach's alpha only]... The standardised regression weight estimates for the hypothesised paths of the structural model indicate that the structural model boundary spanning estimate was 0.86"</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="18" customHeight="1" s="10">
       <c r="A242" t="inlineStr">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -10837,7 +10837,7 @@
       </c>
       <c r="P199" s="8" t="inlineStr">
         <is>
-          <t>The study measures Boundary Spanning Behavior at the team-level, rather than the individual employee-level. Although the quantitative survey was administered to individual participants (N=250), the respondents were acting as key informants evaluating their team's behavior. The survey items for the boundary spanning constructs (Structural Connections and Relational Connections) use team-level referents such as 'Members have relationships with others outside the team' and 'Members collaborate with others in the organization to advance our team's efforts', rather than the individual 'I' referent. Following the proxy guardrail, studies where individuals serve as key informants to evaluate macro-level or team-level boundary spanning must be excluded.. Verbatim Evidence: "Table B1: Model Constructs and Scale Development... 3. Name of Scale: Embedded Interconnections: Structural Connections and Relational Connections... Items: a. Members have relationships with others outside the team who can help influence change (Relational); b. Members are influential with their peers outside the team (Relational); c. Members are well connected to others in the organization (Relational); d. Members effectively exchange knowledge with others in the organization (Structural); e. Members collaborate with others in the organization to advance our team’s efforts (Structural); f. Members consider the effect our work will have on others (Structural); g. Members consider how others will respond to our team’s work (Relational); h. Members invite others in the organization to engage with our work (Structural); i. Members are trusted by others in the organization (Relational)... [Page 118] First, we sought to gain an understanding of teams, but were not able to obtain team level data. Instead our survey information and results are based on the perceptions of individual participants who were asked to consider a single team in which they participate at work; thus a variety of teams are represented, but no teams as wholes are represented."</t>
+          <t>The study examines team boundary spanning in quality improvement project teams. Although the quantitative analysis (Study 2) surveys individual team members (N=215) and preserves statistical independence, the survey items for boundary spanning (Embedded Interconnections: Structural and Relational Connections) use a team-level referent. Specifically, the items ask respondents to evaluate the team as a whole (e.g., 'Members have relationships with others outside the team who can help influence change', 'Members collaborate with others in the organization to advance our team's efforts', 'Members invite others in the organization to engage with our work'). Under Screening Rule 5 (Proxy Guardrail), because the grammatical subject of the survey items refers to the team ('Members', 'our team's efforts') rather than the individual respondent ('I'), the respondent is acting as a macro-level key informant rating the team's boundary spanning. Therefore, the study must be excluded under Code 3 (Non-individual level).. Verbatim Evidence: "The data were analyzed in two stages – factor analysis followed by structural equation modeling... The survey consisted of two validated scales – one for Member Satisfaction and one for Team Potency. These two scales accounted for sixteen items. The remaining 23 items made up four new scales to assess Structural Connections (four items), Relational Connections (five items), Strategic Alignment (eight items), and Adaptability (six items)... Embedded Interconnections: Structural Connections and Relational Connections... Items: a. Members have relationships with others outside the team who can help influence change (Relational)... e. Members collaborate with others in the organization to advance our team’s efforts (Structural)... h. Members invite others in the organization to engage with our work (Structural)... Table B1: Model Constructs and Scale Development."</t>
         </is>
       </c>
     </row>
@@ -13041,6 +13041,16 @@
           <t>BSMA0239</t>
         </is>
       </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study</t>
+        </is>
+      </c>
       <c r="G242" t="inlineStr">
         <is>
           <t>Now more than ever, marketing is assuming a key boundary-spanning role—a role that has also redefined the composition of the marketing organization. In this paper, the marketing organization’s integrative and mutually reinforcing components of marketing activities, customer value–creating processes, networks, and stakeholders are delineated within their boundary-spanning roles as a particular emphasis (labeled MOR theory). Thematic marketing insights from a collection of 31 organization theories are used to advance knowledge on the boundary-spanning marketing organization within four areas—strategic marketing resources, marketing leadership and decision making, network alliances and collaborations, and the domestic and global marketplace.</t>
@@ -13066,7 +13076,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P242" s="8" t="n"/>
+      <c r="P242" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a theoretical review rather than a primary empirical study. It proposes a conceptual framework (MOR theory) for the boundary-spanning marketing organization by synthesizing insights from 31 organization theories. It does not provide an original empirical dataset or report quantitative effect sizes (e.g., zero-order correlations).. Verbatim Evidence: "In this paper, the marketing organization's integrative and mutually reinforcing components of marketing activities, customer value-creating processes, networks, and stakeholders are delineated within their boundary-spanning roles as a particular emphasis (labeled MOR theory). Thematic marketing insights from a collection of 31 organization theories are used to advance knowledge on the boundary-spanning marketing organization within four areas."</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="18" customHeight="1" s="10">
       <c r="A243" t="inlineStr">
@@ -13079,6 +13093,16 @@
           <t>BSMA0240</t>
         </is>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G243" t="inlineStr">
         <is>
           <t>While there is a growing interest in the role of market information processing activities (i.e., the acquisition, dissemination, and use of market information) in new product development (NPD), a number of gaps remain in our knowledge on this topic. When investigating the performance impact of market information processing, most studies have treated the three activities as independent. Our research adds to the extant knowledge by exploring not only both direct relationships between each of the market information processing activities and new product performance, but also interaction effects. We, thus, ask the question of whether there may be synergies in obtaining performance increases by jointly improving two processing activities, rather than just considering each activity independently. In addition, we investigate these effects for different levels of information quality; a topic largely neglected in the market information processing literature. Our analysis is based on empirical data from 152 Dutch NPD projects. The results indicate that market information acquisition and use are both directly associated with increased performance. We also ﬁnd signiﬁcant interaction effects for information acquisition and dissemination, and for information dissemination and use. Finally, the importance of information quality is emphasized, with lower quality information producing lower performance and wiping out the effects between various aspects of market information processing and new product performance. We provide several implications of our ﬁndings for managers and academics.</t>
@@ -13104,7 +13128,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P243" s="8" t="n"/>
+      <c r="P243" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates market information processing at the project level (N = 152 NPD projects). The survey was completed by NPD managers acting as key informants for the project team. The survey items for the information processing constructs use the 'we' referent or refer to the collective (e.g., 'We regularly met with potential customers', 'Intelligence on our competitors was generated by different departments'), indicating a team/macro-level measurement rather than individual boundary spanning behavior. Thus, the study is excluded as it violates the individual-level analysis and proxy guardrails.. Verbatim Evidence: ""We used the project level of analysis because the information used to make NPD decisions is project-specific, rather than being more generally applicable to the entire firm or a division." "Our target respondents were NPD managers. We asked these managers to report on a project in which they had been involved as project leader or as the main marketing expert." "Acquisition of Market Information: During the NPD project... We regularly met with potential customers to find out their future needs. ... Intelligence on our competitors was generated by different departments.""</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="18" customHeight="1" s="10">
       <c r="A244" t="inlineStr">
@@ -13117,6 +13145,16 @@
           <t>BSMA0241</t>
         </is>
       </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G244" t="inlineStr">
         <is>
           <t>Background: Rehabilitation services depend on competent professionals who collaborate effectively. Wellfunctioning interprofessional teams are expected to positively impact continuity of care. Key factors in continuity of care are communication and collaboration among health care professionals in a team and their patients. This study assessed the associations between team functioning and patient-reported benefits and continuity of care in somatic rehabilitation centres. Methods: This prospective cohort study uses survey data from 984 patients and from health care professionals in 15 teams in seven somatic rehabilitation centres in Western Norway. Linear mixed effect models were used to investigate associations between the interprofessional team communication and relationship scores (measured by the Relational Coordination [RC] Survey and patient-reported benefit and personal-, team- and cross-boundary continuity of care. Patient-reported continuity of care was measured using the Norwegian version of the Nijmegen Continuity Questionnaire. Results: The mean communication score for healthcare teams was 3.9 (standard deviation [SD] = 0.63, 95% confidence interval [CI] = 3.78, 4.00), and the mean relationship score was 4.1 (SD = 0.56, 95% CI = 3.97, 4.18). Communication scores in rehabilitation teams varied from 3.4–4.3 and relationship scores from 3.6–4.5. Patients treated by teams with higher relationship scores experienced better continuity between health care professionals in the team at the rehabilitation centre (b = 0.36, 95% CI = 0.05, 0.68; p = 0.024). There was a positive association between RC communication in the team the patient was treated by and patient-reported activities of daily living benefit score; all other associations between RC scores and rehabilitation benefit scores were not significant. Conclusion: Team function is associated with better patient-reported continuity of care and higher ADL-benefit scores among patients after rehabilitation. These findings indicate that interprofessional teams’ RC scores may predict rehabilitation outcomes, but further studies are needed before RC scores can be used as a quality indicator in somatic rehabilitation.</t>
@@ -13142,7 +13180,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P244" s="8" t="n"/>
+      <c r="P244" s="8" t="inlineStr">
+        <is>
+          <t>The study aggregates Relational Coordination (RC) communication and relationship scores to the team level, violating the individual-level analysis requirement (Code 3). Additionally, the study does not report a zero-order correlation matrix, only providing unstandardized regression coefficients from linear mixed-effects models, leaving no extractable effect size for the meta-analysis (Code 1).. Verbatim Evidence: "The main explanatory variables in this study were the RC communication and relationships scores, which were calculated for each team and used as continuous variables, from 1(lowest) to 5 (highest)... Given the possible intra-cluster correlation between responses from patients treated by the same team, linear mixed effect models were used to investigate associations between patient-reported rehabilitation benefit items... and NCQ-N... items (as outcome variables). The teams’ RC communication and relationship scores were used as explanatory variables. Team allocation was set as the random effect in all models."</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="18" customHeight="1" s="10">
       <c r="A245" t="inlineStr">
@@ -13155,6 +13197,16 @@
           <t>BSMA0242</t>
         </is>
       </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G245" t="inlineStr">
         <is>
           <t>Purpose The purpose of this study was to investigate how changes in patient-rated health and disability from baseline to after rehabilitation were associated with communication and relationships in rehabilitation teams and patient-rated continuity of care. Methods Linear models were used to assess the associations between relational coordination [RC] and Nijmegen Continuity Questionnaire-Norwegian version [NCQ-N] with changes in the World Health Association Disability Assessment Schedule 2.0 [WHODAS 2.0] and EuroQol EQ-VAS [EQ-VAS]. To express change in WHODAS 2.0 and EQ-VAS, the model was adjusted for WHODAS 2.0 and EQ-VAS baseline scores. Analyses for possible slopes for the various diagnosis groups were performed. Results A sample of 701 patients were included in the patient cohort, followed from before rehabilitation to 1 year after a rehabilitation stay involving treatment by 15 different interprofessional teams. The analyses revealed associations between continuity of care and changes in patient-rated health, measured with EQ-VAS (all p values &lt; 0.01). RC communication was associated with more improvement in functioning in neoplasms patient group, compared to improvement of health among included patient groups. The results revealed no associations between NCQ-N and WHODAS 2.0 global score, or between RC in the rehabilitation teams treating the patients and changes in WHODAS 2.0 global score. Conclusion The current results revealed that better personal, team and cross-boundary continuity of rehabilitation care was associated with better patient health after rehabilitation at 1-year follow-up. Measures of patient experiences with different types of continuity of care may provide a promising indicator of the quality of rehabilitation care.</t>
@@ -13180,7 +13232,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P245" s="8" t="n"/>
+      <c r="P245" s="8" t="inlineStr">
+        <is>
+          <t>The study examines the effect of team-level relational coordination (RC) among health care professionals on the health outcomes of rehabilitation patients. It must be excluded for multiple reasons: (1) The dependent variables are derived from patients, which is a non-employee sample (Code 2). (2) The independent variable (RC) is aggregated to the team level (N=15 teams) and assigned to patients, violating the individual-level analysis requirement (Code 3). (3) The study does not provide an extractable zero-order correlation matrix for the individual healthcare professionals, and the construct is intra-team relational coordination rather than purposive boundary spanning behavior (Code 1).. Verbatim Evidence: "RC subscale scores were obtained for all teams (N=15) in all rehabilitation centres by conducting a survey among health care professionals (N=124, 52% response rate). The RC subscale scores are reported as clustered mean scores for each team in this study, and scores were assigned to the patients treated by the respective teams... A sample of 701 patients were included in the patient cohort, followed from before rehabilitation to 1 year after a rehabilitation stay involving treatment by 15 different interprofessional teams."</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="18" customHeight="1" s="10">
       <c r="A246" t="inlineStr">
@@ -13193,6 +13249,16 @@
           <t>BSMA0243</t>
         </is>
       </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G246" t="inlineStr">
         <is>
           <t>Based on the four principles of self‐organization formulated by Morgan (1986), a four‐stage implementation model for empowering teams was developed. From the first to the last stage, the attention shifts from routine tasks to non‐routine tasks, from the individual to the group, and from inwards oriented to outwards directed activities. This model was used to develop five teams in an industrial glass producing firm. After two years, team progress was measured by means of a questionnaire and the results were discussed with each team. These data were used to evaluate the viability and applicability of the empowerment plan and to find relevant factors which facilitate or hinder the empowerment process. The results indicate that the step‐by‐step plan facilitates the development of empowered teams but that it should not be seen necessarily as the best or the only way of empowering working groups. Moreover, the attitude and style of management, the team cohesion and the nature of the work involved seem to interfere with team empowerment.</t>
@@ -13218,7 +13284,11 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="P246" s="8" t="n"/>
+      <c r="P246" s="8" t="inlineStr">
+        <is>
+          <t>The study is a descriptive assessment of empowerment and team development across five teams in a single firm. While it uses a questionnaire that includes a 'boundary management' dimension, it does not provide an extractable zero-order correlation matrix or any specific effect sizes (r) involving boundary spanning behavior. The only statistical effect reported is a single correlation (r=0.37) between the number of months engaged in the program and the overall empowerment score across all four stages. Therefore, the study lacks the required quantitative effect size data for the meta-analysis.. Verbatim Evidence: "To help the members of the teams to get insight into the progress of the development of their team, we constructed a self-administered questionnaire... To find an indication for the progress in the last stage we formulated 19 items, e.g., 'Team members initiate improvements' and 'The team itself deals with customer complaints'... In fact the correlation between the number of months engaged in the empowerment program and the total score over the four stages is r=0.37."</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="18" customHeight="1" s="10">
       <c r="A247" t="inlineStr">
@@ -13231,6 +13301,16 @@
           <t>BSMA0244</t>
         </is>
       </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G247" t="inlineStr">
         <is>
           <t>This three-essay project explores boundary management and work-nonwork enrichment to explain how thriving in the work domain relates to thriving in the nonwork domain. The Cross-Domain Thriving model proposed in Study 1 theorizes that when employees experience growth and energy at work, they create and deplete resources within and across roles and individual boundary management strategies, role congruency, and ease of transition moderate the degree to which thriving translates into enrichment and/or conflict across roles. Study 2 tested aspects of the cross-domain thriving model and found that neither work nor nonwork thriving was related to increased time-based conflict, but both forms of thriving predicted enrichment gains across domains. Moreover, higher levels of work-nonwork role segmentation were associated with a stronger relationship between learning in nonwork roles and affective and efficiency enrichment gains in the nonwork-to-work direction. In the work-to-nonwork direction, role congruency and cycling boundary management behavior were related to greater developmental and affective enrichment, respectively. Cycling also strengthened the positive relationship between vitality at work and work-to-nonwork capital enrichment. Study 3, a qualitative study investigating work and nonwork thriving in employees working from home during a pandemic, suggested the importance of boundary management skills as demands on learning and energy increase. Findings highlight how key employer actions and employee regulatory behavior can leverage the benefits of growth and energy in work and nonwork domains.</t>
@@ -13256,7 +13336,11 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="P247" s="8" t="n"/>
+      <c r="P247" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on work-life and work-nonwork boundary management rather than inter- or intra-organizational boundary spanning behavior. Specifically, it examines segmentation, integration, and cycling behaviors across the work-home interface, which falls under the explicit Work-Family Boundary Management exclusion and lacks the effect size of interest.. Verbatim Evidence: "I adapted Kreiner’s (2006) 4-item measure of segmentation preference to assess behaviors rather than preferences. For instance, “I don’t like work issues creeping into my home life” was changed to “I do not let work issues creep into my personal life.”... Cycling Behavior. Based on Kossek (2016), I defined cycling conceptually as “regularly fluctuating boundary management behaviors from periods of integrating work and nonwork to periods of segmenting work and nonwork”."</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="18" customHeight="1" s="10">
       <c r="A248" t="inlineStr">
@@ -13269,6 +13353,16 @@
           <t>BSMA0245</t>
         </is>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G248" t="inlineStr">
         <is>
           <t>Community-based initiatives (CBIs) are thriving in Western countries. In CBIs, citizens take a leading role in providing public services and goods. CBIs have been acclaimed for their innovativeness, problem-solving capacity, and legitimacy. However, we lack large N studies on performance of CBIs and its antecedents. This article develops and tests a model that identiﬁes relationships between performance and four antecedents by using survey data on CBIs collected in the Netherlands (N = 671). Using structural equation modelling, positive direct and indirect relationships between transformational leadership, boundary spanning leadership, organizational capacity, social capital ties, government support, and performance are found.</t>
@@ -13294,7 +13388,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P248" s="8" t="n"/>
+      <c r="P248" s="8" t="inlineStr">
+        <is>
+          <t>[Code 2 &amp; Code 3] The study uses a sample of citizen volunteers participating in community-based initiatives rather than organizational employees (Code 2). Additionally, the survey items ask respondents to report on the boundary spanning activities of 'the management (board or leading persons)' as a collective and the external contacts of 'the citizen initiative' as a whole. Thus, respondents act as macro-level key informants for the organization's boundary spanning, violating the individual level-of-analysis requirement (Code 3).. Verbatim Evidence: "We conducted a web-based survey among Dutch respondents participating in CBIs... most respondents were active volunteers (60.95%), followed by board members (25.63%), and passive or supporting volunteers (11.92%). ... Boundary spanning leadership (BSL) The management (board or leading persons) of the initiative . . . involves people from outside the organization when making decisions ... Generally speaking, how often is the citizen initiative in contact with the following parties?"</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="18" customHeight="1" s="10">
       <c r="A249" t="inlineStr">
@@ -13345,6 +13443,16 @@
           <t>BSMA0247</t>
         </is>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G250" t="inlineStr">
         <is>
           <t>This study examines the relationships between career decisions and directions and a set of independent variables including job title, demographic variables, role stressors, boundary spanning activities, perceived job characteristics, and career outcomes for 348 IS employees. Results show that the majority had already defined specific jobs they would like to hold in the near future. They were also able to define four directions for their future careers: IS technical, IS management, business, and consultant. Results show that career decisions and directions are related to some of the independent variables. IS employees in each of the four career directions could be further categorized into groups on the basis of similar characteristics. Implications of theses findings are discussed.</t>
@@ -13370,7 +13478,11 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="P250" s="8" t="n"/>
+      <c r="P250" s="8" t="inlineStr">
+        <is>
+          <t>The study measures intra-organizational boundary spanning activities (interacting and communicating with others outside the IT department). However, the paper does not report a formal correlation matrix or any zero-order correlations between boundary spanning and other continuous variables (e.g., role stressors, job satisfaction, organizational commitment, performance). The only statistical data provided are F-tests (ANOVAs) comparing group means across categorical career decision statuses and career directions. Because it does not provide the extractable quantitative effect sizes (r) required for the meta-analysis, it must be excluded.. Verbatim Evidence: "Boundary spanning activities A three-item scale was developed to assess boundary spanning activities: The degree to which employees interact and communicate with others outside their department. Each item (e.g., 'assist other units in determining appropriate uses of information technology'; 'recommend new applications of information technology to top management') was scored on a five-point scale ranging from (1) not part of my job to (5) a very significant part of my job... [The article contains no correlation matrix. Results are presented via ANOVA:] Table 4 The relationships between career decisions and the study variables... Table 5 The relationships between career directions and the study variables."</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="18" customHeight="1" s="10">
       <c r="A251" t="inlineStr">
@@ -13383,6 +13495,14 @@
           <t>BSMA0248</t>
         </is>
       </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F251" t="n">
+        <v>999</v>
+      </c>
       <c r="G251" t="inlineStr">
         <is>
           <t>This study examined the relative influence of transformational and gatekeeping leadership on team performance in a study of researchers working in industrial R&amp;D teams in Japan. Potential effects of both internal and external communication and group norms for consensus were studied as possible mediating influences on the leadership-performance relationship. Results found that, while both forms of leadership enhanced communication processes within and between groups, only gatekeeping leadership served to reduce group norms for consensus. As a result, team cultures became somewhat more accepting of expressions of divergent opinions and new ideas from various team members, an important factor in R&amp;D innovation and performance. By contrast, transformational leadership served to create team cultures in which divergence from group norms by various members was discouraged, leading to fewer innovative ideas and no performance increment. Results are discussed both in the context of the unique Japanese work environment and in the larger context of leadership processes across regions and cultures.</t>
@@ -13408,7 +13528,11 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="P251" s="8" t="n"/>
+      <c r="P251" s="8" t="inlineStr">
+        <is>
+          <t>The study measures 'gatekeeping leadership', which assesses the leader's boundary spanning behavior ('The leader coordinates the team's task efforts with outside stakeholders') as rated by subordinates. Under the Leader BSB override (Rule 1), this is a valid BSB construct. Although the data is aggregated to the team level (N=122 teams), there is exactly one leader per team (122 team leaders for 122 teams), falling under the N=Leaders=N=Teams exception. Therefore, the effective N for BSB is the N of leaders (individual-level), preserving statistical independence. The paper provides a correlation matrix with an extractable effect size (e.g., r = 0.32 for Gatekeeping leadership and Team performance).. Verbatim Evidence: "Gatekeeping leadership is a construct that has evolved from the more general construct of a gatekeeper... Gatekeepers often have communication networks with specialists outside the organizations. In this sense, they bridge organizational boundaries. ... The sample consisted of 122 R&amp;D teams from seven industrial parts manufacturers in Japan. In addition to 122 team leaders (response rate: 100%), 683 R&amp;D team members (response rate: 82.4%) and 25 managers (response rate: 100%) also participated in the study. Each team member belonged to a single team, and each team was managed by one of the 25 managers. ... Gatekeeping leadership was measured by five items adapted from Hirst and Mann (2004). An example of the items used in this scale is 'The leader coordinates the team’s task efforts with outside stakeholders'. Each team member was asked to rate his/her leader’s behaviour on a five-point scale ... Transformational leadership, gatekeeping leadership, internal communication, external communication, and norm for maintaining consensus were aggregated to mean values within each team, which was the unit of the analysis."</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="18" customHeight="1" s="10">
       <c r="A252" t="inlineStr">
@@ -13421,6 +13545,14 @@
           <t>BSMA0249</t>
         </is>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F252" t="n">
+        <v>999</v>
+      </c>
       <c r="G252" t="inlineStr">
         <is>
           <t>Due to the increasing array of sales technology, salespeople must understand how each application assists them. This study examines how business-to-business salespeople use different forms of sales technology to meet their boundary-spanning roles. Our research draws from social exchange theory and task-technology fit theory to test a model that examines how salespeople use CRM and social media technologies differentially to support competitive information collection, product information communication, and buyer information sharing. Dyadic data from industrial buyers and sellers is used to analyze the technology-behavior relationships. Our study's results reveal social media use and CRM technology both positively influence buyer-seller information exchanges; however, each technology takes a distinct route to enable the information exchange between the buyer and the seller. The results also suggest that managers need to champion the use of both technology applications to their salesforce.</t>
@@ -13446,7 +13578,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P252" s="8" t="n"/>
+      <c r="P252" s="8" t="inlineStr">
+        <is>
+          <t>The study measures 'Seller competitive information collection', capturing purposive boundary-spanning behavior (information scouting/scanning) via items such as 'When I am in the field, I try to gather and transmit reliable information' and 'I ask customers about the competition's products and strategies'. The survey was administered to individual B2B salespeople with an 'I' referent. The sample of 162 salesperson-buyer dyads relies on 1-to-1 matching, which preserves statistical independence (1:1 Matched Dyad Safe Harbor). The study reports a zero-order correlation matrix (Table 1), providing extractable effect sizes.. Verbatim Evidence: "The final data set consisted of 162 salesperson-buyer dyads. For our study, salespeople served as the respondents to the following constructs: social media utilization, customer relationship management technology utilization, and competitive information collection... Seller competitive information collection: When I am in the field, I try to gather and transmit reliable information; I always assign myself objectives to obtain information about competitors; I ask customers about the competition's products and strategies. ... Table 1 Correlations, descriptive statistics, reliability and average variance extracted... * p &lt; .05; ** p &lt; .01. Correlations are added below the diagonal."</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="18" customHeight="1" s="10">
       <c r="A253" t="inlineStr">
@@ -13459,6 +13595,16 @@
           <t>BSMA0250</t>
         </is>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G253" t="inlineStr">
         <is>
           <t>In this article the authors discuss research they conducted that examined the relationship between task difficulty and the extent of boundary-spanning activity within an organization. The authors believed that they greater degree of interunit interdependence that existed in an organization would result in a greater amount of boundary-spanning activity by that organization's members. They also believed that the greater degree of task difficulty in a given situation would also result in a greater amount of boundary-spanning activity by members. The authors hoped to examine the relationships that exist between organizational structure and the amount of intergroup activity fostered by those structures.</t>
@@ -13484,7 +13630,11 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="P253" s="8" t="n"/>
+      <c r="P253" s="8" t="inlineStr">
+        <is>
+          <t>The study uses work groups (teams) as the unit of analysis, rather than individual employees. It explicitly states that individual responses from supervisors and subordinates were pooled and averaged to compute scores for work groups. The correlation matrix provided is based on these team-level aggregated constructs (N=71 work units), which violates the individual-level analysis requirement of the meta-analysis.. Verbatim Evidence: "Following Van de Ven and colleagues (1976) and Tushman (1977, 1978), we used work groups as the units of analysis. ... Seventy-five units met the criteria for data analysis; these units included 360 potential respondents of whom 283 responded for a 79 percent response rate. ... To compute scores for work groups, supervisors' scores were added to the means of subordinates' scores, and these sums were divided by two (Van de Ven et al., 1976). ... We dropped four units whose variances exceeded the pooled variance (p &lt; .05) for two or more variables from the study. ... [Table 2] Descriptive Statistics and Zero-Order Correlations among All Variables ... aN = 71"</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="18" customHeight="1" s="10">
       <c r="A254" t="inlineStr">
@@ -13497,6 +13647,16 @@
           <t>BSMA0251</t>
         </is>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G254" t="inlineStr">
         <is>
           <t>Innovation has an intrinsic relationship with social networks because it provides a mechanism for knowledge and information to travel freely between individuals. Consequently, there is abundant research linking social networks to innovation. However, two critical gaps still exist. First, most research studies use a structural approach, and less attention is paid to the behavioral dimensions in a network. Secondly, the majority of empirical research focuses on egocentric networks or dyadic relationships between two organizations, instead of the network of organizations as a whole.</t>
@@ -13522,7 +13682,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P254" s="8" t="n"/>
+      <c r="P254" s="8" t="inlineStr">
+        <is>
+          <t>Although the study conceptualizes Network Citizenship Behavior (NCB) as an individual-level construct and surveys individual employees, the survey instrument explicitly uses the grammatical referent 'we' and 'our partner' across all items (e.g., 'We go out of our way to help our partner...'). The author notes that 'we' is used because boundary personnel represent the entire firm. According to the Proxy Trap Verification rule, survey items using 'We' or 'Our' indicate that the respondent is acting as a macro-level key informant assessing the organization's relationships. Therefore, the study violates the individual-level measurement guardrail and must be excluded.. Verbatim Evidence: "ICB, on the other hand, mostly was discussed as an individual-level construct, but at times appeared to be confused with an organizational-level construct. For example, its instrument used “we” instead of “I” in every item... The reason “we” was used instead of “I” in the construction of its items could be that boundary personnel, in a way, represent the entire firm when interacting with its suppliers or clients... Table 9: Item and Cronbach’s Alpha Scores Comparison of Original and Updated NCB Instruments... 3. We go out of our way to help our partner with business-related issues if we sense that they are in need. 4. We provide assistance to our partner if they ever have a problem in an area where we have expertise."</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="18" customHeight="1" s="10">
       <c r="A255" t="inlineStr">
@@ -13535,6 +13699,16 @@
           <t>BSMA0252</t>
         </is>
       </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G255" t="inlineStr">
         <is>
           <t>Marketing boundary spanners—especially customer service representatives—are notably susceptible to burnout. The authors define the burnout construct and develop hypotheses to examine if burnout acts as a partial mediator between role stressors and key behavioral and psychological job outcomes. Responses from 377 customer service representatives reveal that burnout levels are high relative to other burnout-prone occupations (e.g., police, nursing) and that burnout has consistent, significant, and dysfunctional effects on their behavioral and psychological outcomes. Moreover, burnout mediates the negative effects of role stressors on job outcomes, whereas the positive effects of role stressors are unmediated.</t>
@@ -13560,7 +13734,11 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="P255" s="8" t="n"/>
+      <c r="P255" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates employees in boundary-spanning positions (customer service representatives) but does not measure Boundary Spanning Behavior (BSB) as a specific interpersonal or purposive construct (e.g., information scanning, representation). The correlation matrix only contains variables for burnout dimensions (emotional exhaustion, reduced personal accomplishment, depersonalization), role stressors (role conflict, ambiguity, overload), and general job outcomes (job satisfaction, organizational commitment, turnover intentions, job performance). Because BSB itself is not measured, the study lacks an effect size of interest.. Verbatim Evidence: "Marketing boundary spanners—especially customer service representatives—are notably susceptible to burnout. ... Table 1 MEANS, STANDARD DEVIATIONS AND CORRELATIONS FOR THE CONSTRUCTS UTILIZED IN THE STUDY... Constructs: Burnout Dimensions (BURNOUT): Emotional exhaustion (EE), Reduced personal accomplishment (RPA), Depersonalization (DP). Role Stressors (RSTRESS): Role conflict (RC), Role ambiguity (RA), Role overload (RO). Psychological Outcomes (PSY-OUT): Job satisfaction (JS), Organizational commitment (OC), Turnover intentions (TI). Behavioral Outcomes (BEH-OUT): Job performance1, Job performance2. ... Boundary spanning burnout. The burnout dimensions were measured by 24 items (i.e., 8 items per dimension) drawn from the scale developed by Maslach and Jackson (1981) (see Appendix A)."</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="18" customHeight="1" s="10">
       <c r="A256" t="inlineStr">
@@ -13573,6 +13751,16 @@
           <t>BSMA0253</t>
         </is>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G256" t="inlineStr">
         <is>
           <t>No abstract</t>
@@ -13598,7 +13786,11 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="P256" s="8" t="n"/>
+      <c r="P256" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the project level (N=121 Open Source Software projects) rather than at the individual employee level. Boundary spanning activity (BSA) is measured as a team-level construct (the focal team's degree centrality in an inter-team network of projects). Furthermore, the sample consists of volunteer OSS developers who are not formal organizational employees. Therefore, the study violates both the individual-level analysis and employee sample requirements [Code 2 &amp; Code 3].. Verbatim Evidence: "The unit of analysis was the project. The population of interest was defined as the universe of OSS projects that are developed collaboratively... The final sample was reduced to 121 projects since only that number had archived a developers’ mailing list as well as active tracking systems for bugs and patches... Consequently, the measure of BSA in this dissertation is the focal team’s degree centrality in an inter-team network where the nodes are all OSS projects registered in Source Forge. This measure can be used since each project in Source Forge includes a list of developers. Once all these lists have been scanned, it is easy to detect developers who work on more than one project and then build the inter-team network in order to calculate a given project’s BSA."</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="18" customHeight="1" s="10">
       <c r="A257" t="inlineStr">
@@ -13611,6 +13803,16 @@
           <t>BSMA0254</t>
         </is>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G257" t="inlineStr">
         <is>
           <t>Because of their boundary-spanning nature, manufacturers’ representatives frequently are involved in team selling. The results from a survey of 362 manufacturers’ representatives indicates that team selling is more likely to be used by manufacturers’ representatives when the customer faces a first-time buy of a complex product, when the information needs of the customer are great, when the account requires special treatment, and when a number of people are involved in the decision to buy. In addition, team selling is more likely when the potential sale is large for the representative firm and when the product is new to the representative’s product line.</t>
@@ -13636,7 +13838,11 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="P257" s="8" t="n"/>
+      <c r="P257" s="8" t="inlineStr">
+        <is>
+          <t>The study explores the situational use of team selling by manufacturers' representatives. The authors used paired t-tests to compare the likelihood of using team selling under different conditions (e.g., high vs. low information needs, complex vs. simple products). The paper does not provide a formal correlation matrix or extractable zero-order effect sizes (r) required for the meta-analysis.. Verbatim Evidence: "Measures used to test the hypotheses each consisted of two 7-point itemized rating scales designed to assess the extent to which team selling was used in a particular buying or selling situation. For example, to measure the extent to which team selling is used when the buyer's informational needs are great, respondents indicated the likelihood of using sales teams when 'the anticipated information needs of the customer are small' and 'the anticipated information needs of the customer are great' (1 = extremely unlikely, 7 = extremely likely). T-tests were conducted on the mean differences between the respondents' ratings for each of the paired questions."</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="18" customHeight="1" s="10">
       <c r="A258" t="inlineStr">
@@ -13649,6 +13855,16 @@
           <t>BSMA0255</t>
         </is>
       </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G258" t="inlineStr">
         <is>
           <t>With congeneric mergers, which involve firms with interrelated but not identical business lines that develop diverse products and services, a major challenge for organizations is the development of a common platform that fulfills similar business functions across multiple divisions. Through a field study of a postmerger common platform development initiative, we develop a framework that highlights how environmental and organizational contexts shape the process of common platform development (CPD). Our study provides an account of how the focal organization transitioned to a platform-based approach by achieving a balance between stable and flexible aspects of the common platform through negotiations among the divisions acquired through mergers and acquisitions. These negotiations were enabled through various boundary-spanning activities and the guided successive enrichment of boundary objects used in CPD process. European Journal of Information Systems (2015) 24(2), 159–177.</t>
@@ -13674,7 +13890,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P258" s="8" t="n"/>
+      <c r="P258" s="8" t="inlineStr">
+        <is>
+          <t>The study employs a qualitative case study methodology to investigate post-merger common platform development at a single organization. Data was collected through observations, informal interviews, and secondary documentation. The study does not provide any extractable quantitative effect sizes or a formal correlation matrix, which are strictly required for this meta-analysis.. Verbatim Evidence: "We use a case study research methodology to identify various contextual elements that shape the development of a common platform in a post-merger scenario. We examine how stakeholders from different business divisions establish a common understanding of their processes to inform the development of a common platform underlying a family of similar business processes... We used various data collection strategies (Lee, 1989) to ensure continuous engagement with the research site and collect rich qualitative data as summarized in Table 1."</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="18" customHeight="1" s="10">
       <c r="A259" t="inlineStr">
@@ -13687,6 +13907,16 @@
           <t>BSMA0256</t>
         </is>
       </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G259" t="inlineStr">
         <is>
           <t>Two main targets of contemporary preferential innovation policy support, especially in Europe, are key enabling technologies (KETs) and innovation ‘missions’ focused on solving societal challenges. Both topics are associated with uniting disparate sets of capabilities, either by driving technology-based innovation into various application domains or by eliciting interdisciplinary and cross-sectoral solutions to urgent societal demands. In this study we assess to what extent pre-commercial R&amp;D collaborations span geographic and cognitive boundaries. We analyze firm-level tie formation in Dutch collaborative R&amp;D projects initiated in the period 2013–2018. Gravity models reveal that, while results for geographic proximity are mixed, some KET types are indeed related to projects in which cognitive proximity is significantly less relevant for tie formation. This contrasts with the findings for projects that retroactively received a mission label. Projects on health and care missions, and especially energy transition and sustainability missions, instead spur collaborations between cognitively proximate firms. The latter suggests that without additional policy intervention, such projects might interconnect similar rather than dissimilar knowledge bases. We conclude by discussing research and policy implications.</t>
@@ -13712,7 +13942,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P259" s="8" t="n"/>
+      <c r="P259" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates boundary spanning at the firm level by analyzing the formation of collaborative ties (dyads) between firms in R&amp;D projects, rather than measuring the interpersonal boundary spanning behavior of individual employees. The unit of analysis is the inter-firm dyad.. Verbatim Evidence: "In our empirical analysis, we investigate firm-level tie formation in collaborative R&amp;D projects in the Netherlands... The total network includes 1884 Dutch firms and 105 publicly-funded organizations. Given our focus on recombining firm capabilities, our analyses concentrate on the 1884 firms only... To construct the dependent variable, we created a set of all possible pairwise combinations of firms, each of which takes the value of one if, for a particular category, there is a collaborative tie between the given two firms, and takes the value of zero otherwise."</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="18" customHeight="1" s="10">
       <c r="A260" t="inlineStr">
@@ -13725,6 +13959,16 @@
           <t>BSMA0257</t>
         </is>
       </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G260" t="inlineStr">
         <is>
           <t>Purpose – To obtain optimal deliverables, more and more crowdsourcing platforms allow contest teams to submit tentative solutions and update scores/rankings on public leaderboards. Such feedback-seeking behavior for progress benchmarking pertains to the team representation activity of boundary spanning. The literature on virtual team performance primarily focuses on team characteristics, among which network closure is generally considered a positive factor. This study further examines how boundary spanning helps mitigate the negative impact of network closure.</t>
@@ -13750,7 +13994,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P260" s="8" t="n"/>
+      <c r="P260" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes US patents between 2001 and 2010, conceptualizing boundary spanning as a patent spanning multiple technological classes. The unit of analysis is the patent, not an individual organizational employee performing interpersonal boundary spanning behaviors. Therefore, the study violates the individual-level boundary spanning guardrail and must be excluded under Code 3.. Verbatim Evidence: ""We test our hypotheses using a comprehensive sample of patents approved in the United States between 2001 and 2010... To capture the extent to which a patent spans its primary domain (i.e., original class), we create two measures. First, we use a dichotomous variable, domain spanning (dummy), with a value of 1 if at least one subclass of the patent belongs to technology classes that are outside its original class, and 0 otherwise. ... Second, we create a continuous variable, domain spanning (ratio), measured as the number of a patent’s subclasses belonging to other classes divided by the total number of its subclasses.""</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="18" customHeight="1" s="10">
       <c r="A261" t="inlineStr">
@@ -13763,6 +14011,16 @@
           <t>BSMA0258</t>
         </is>
       </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G261" t="inlineStr">
         <is>
           <t>This study investigated the effects of small business owner decision styles on the search for external assistance information, community information, and competitor information. Results confirmed the existence of decision style differences in selection of boundary spanning activities. A conclusion is drawn that small business owners use preferred sources for gathering information related to business operations, but need to utilize additional sources to ensure a comprehensive boundary spanning role. Ways to enhance boundary spanning activities are provided</t>
@@ -13788,7 +14046,11 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="P261" s="8" t="n"/>
+      <c r="P261" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 2] The study's sample consists of independent small business owners/entrepreneurs rather than embedded organizational employees, which violates the population boundary rule (Code 2). Furthermore, the study categorizes individuals into four nominal decision style groups (ST, SF, NT, NF) and analyzes differences using MANOVA/ANOVA, without reporting a correlation matrix or extractable zero-order effect sizes (Code 1).. Verbatim Evidence: "Subjects in this study were 57 (29 male and 28 female) small business owners operating in a southeastern state. For this sample the term small business was used to identify owners whose firms employed less than one hundred people and had annual gross sales of less than one million dollars... Each subject was grouped according to primary decision style which resulted in four groups of individuals being labeled as either SF (n = 20), ST (n = 7), NF (n = 24), or NT (n = 6)... Because BSA was defined as multidimensional in nature and was composed of three separate dimensions, the primary analytic technique used was multivariate analysis of variance (MANOVA)."</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="18" customHeight="1" s="10">
       <c r="A262" t="inlineStr">
@@ -13801,6 +14063,16 @@
           <t>BSMA0259</t>
         </is>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G262" t="inlineStr">
         <is>
           <t>The influence of boundary spanning roles on strategic decision-making was explored in a field study in fifteen organizations. Results support the importance of boundary spanning roles in the strategic decision-making process and the relationship of technology to the differential strategic decision-making influence of different boundary spanning roles.</t>
@@ -13826,7 +14098,11 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="P262" s="8" t="n"/>
+      <c r="P262" s="8" t="inlineStr">
+        <is>
+          <t>The study does not provide an extractable zero-order correlation matrix or effect size (r) between boundary spanning behavior and other variables, reporting only ANOVA results and factor loadings (Code 1). Furthermore, the unit of analysis and survey referent is the department rather than the individual employee; the survey explicitly asks respondents to rate the boundary spanning activities performed by 'your department or office', acting as key informants for the subunit (Code 3). Therefore, the study is excluded for multiple reasons [Code 1 &amp; Code 3].. Verbatim Evidence: "The purpose of this section is to identify the kinds of activities performed by your department or office. Please indicate in the blank beside the activity the degree to which that activity is a part of your department's or office's activities in the service of your organization. ... The dependent variable of interest in this study is influence on strategic decisions. Every department's influence on the strategic decisions in its organization was computed by averaging all the respondents' scores for that particular department over the range of strategic decisions. ... The hypotheses were tested with a series of one way analyses of variance. The dependent variables were measures of each department's influence on strategic decisions (INFLUENCE). The independent variables were the extent to which a department engaged in one of the three boundary spanning roles (B.S.R.)."</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="18" customHeight="1" s="10">
       <c r="A263" t="inlineStr">
@@ -13839,6 +14115,14 @@
           <t>BSMA0260</t>
         </is>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F263" t="n">
+        <v>999</v>
+      </c>
       <c r="G263" t="inlineStr">
         <is>
           <t>The impact of perceived environmental demands on the roles and job satisfaction of the school psychologist in rural school systems was explored. Superintendents rated their perceptions of the community context and the psychologist’s involvement in interagency linking functions. School psychologists rated their performance of boundary-spanning functions and their job perceptions. Results indicated that certain perceived environmental pressures are related to the performance of boundaryspanning activities. Those who performed boundary-spanning functions are more satisfied with their jobs and more influential in determining their roles.</t>
@@ -13864,7 +14148,13 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="P263" s="8" t="n"/>
+      <c r="P263" s="8" t="inlineStr">
+        <is>
+          <t>The study measures individual-level boundary spanning behavior among organizational employees (rural school psychologists) using a scale adapted from Jemison (1980) assessing external interactions with community groups and agencies. It preserves statistical independence (N=18 individuals) and reports extractable quantitative effect sizes (zero-order correlations) in the text linking boundary-spanning activities to job attitudes such as role influence (r = .62), need to cooperate (r = .31), and role conflict (r = .21, .25). Additionally, the study includes a partial cross-correlation matrix (Table 3), satisfying the data extractability requirements.. Verbatim Evidence: "The questionnaire completed by school psychologists was derived from empirical studies by Jemison (1980) defining boundary-spanning roles across organizations. Thirteen boundary-spanning roles were described, and the respondents indicated the extent to which each was a part of their job.
+...
+Finally, school psychologists' perceptions of their jobs were assessed and correlated with the boundary-spanning scale scores. There were no significant differences in job satisfaction, role clarity, or influence regarding their roles between school district and regional unit psychologists (Table 5). Psychologists who engaged in more boundary-spanning activities reported having greater influence in decisions defining their role (r= .62) and higher job satisfaction. They were slightly more aware of the need to cooperate with others (r = .31) in performing their duties and saw their roles as being clear but somewhat conflicting (r= .21, .25); however, these correlations were not statistically significant."</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="18" customHeight="1" s="10">
       <c r="A264" t="inlineStr">
@@ -13877,6 +14167,16 @@
           <t>BSMA0261</t>
         </is>
       </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G264" t="inlineStr">
         <is>
           <t>Purpose – In today’s digital and post-pandemic era, construction teams can span their boundary to obtain important resources and support in computer-mediated ways. However, the benefits of computer-mediated team boundary spanning (TBS) are mostly assumed. Empirical evidence for these benefits is in lack. Thus, this study attempts to investigate the influence of computer-mediated (instant messaging in this study) TBS on construction project performance and the underlying mechanism.</t>
@@ -13902,7 +14202,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P264" s="8" t="n"/>
+      <c r="P264" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes data at the project/team level (N = 206 projects) rather than the individual employee level. The respondents act as key informants for their teams, with survey items using the referent 'My team' (e.g., 'My team often solicits information and resources from other teams...'). This violates the individual-level analysis guardrail (Code 3). Additionally, the paper relies entirely on CB-SEM path models and does not report a zero-order correlation matrix, meaning it lacks extractable effect sizes for meta-analysis (Code 1).. Verbatim Evidence: "The questionnaire was distributed to construction professionals to report the condition of the last completed project they managed. We randomly sent the link to the online survey to alumni... 206 valid questionnaires were left, thereby yielding a valid response rate of 51.5%... Table 1. Descriptive information of respondents and projects (N = 206)... Table A1: IMTBS1 My team often solicits information and resources from other teams by instant messaging... IMTBS2 My team tries to influence important actors in other teams by instant messaging... This study sheds light on team-level boundary spanning and explores its effects on system-level or project performance, thus filling the identified literature gap in the construction field."</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="18" customHeight="1" s="10">
       <c r="A265" t="inlineStr">
@@ -13915,6 +14219,14 @@
           <t>BSMA0262</t>
         </is>
       </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F265" t="n">
+        <v>999</v>
+      </c>
       <c r="G265" t="inlineStr">
         <is>
           <t>International joint ventures (IJVs) have become an important source of critical knowledge for multinational enterprises, but little is known about how knowledge can be effectively transferred to parent ﬁrms when the potential for interpartner opportunism still exists. Drawing on attachment theory, we study how boundary-spanning commitments to IJVs may help mitigate interpartner opportunism and facilitate effective knowledge transfer to parents. Speciﬁcally, we argue that knowledge transfer from IJVs to their parents is positively mediated by both boundary spanners’ organizational commitment to IJVs and parent ﬁrms’ resource commitment to IJVs. We test our arguments using survey data collected from 600 dyadic Chinese–foreign managers of 100 IJVs established in China. The results provide evidence that knowledge sharing between boundary spanners in IJVs positively affects their organizational commitment to these IJVs, which in turn positively affects knowledge transfer to parents. Similarly, knowledge sharing between such boundary spanners positively affects parent ﬁrms’ resource commitment to IJVs, which in turn positively affects knowledge transfer to parents. The mediating role of boundary spanners’ organizational commitment is stronger than that of parent ﬁrms’ resource commitment. Collectively, our ﬁndings suggest that commitment-based relational mechanisms are imperative for safeguarding effective knowledge transfer from IJVs to parent ﬁrms.</t>
@@ -13940,7 +14252,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P265" s="8" t="n"/>
+      <c r="P265" s="8" t="inlineStr">
+        <is>
+          <t>The study provides quantitative survey data from a sample of individual employees (N=346 frontline employees in the tourism industry) and reports a zero-order correlation matrix. The focal construct is boundary-spanning behavior measured at the individual level, as evidenced by the 'I' referent in the sample survey item. It captures purposive boundary-spanning action (actively seeking information and resources) and passes all inclusion criteria without triggering any exclusion filters.. Verbatim Evidence: "During the formal research process, we recruited frontline employees of 7 hotels, 5 tourist attractions, 3 travel agencies, and 3 tourism planning companies as research subjects... Ultimately, 492 questionnaires were distributed across the two phases, and a total of 346 valid questionnaires were retained, for an effective response rate of 70.3%... By reference to the scale developed by Marrone et al. (2007), a total of 5 item entries were designed. A sample item is 'I will actively seek information, customers and other resources to promote the development of my organization'... Table 2. Results of the descriptive analysis. Employee boundary-spanning behavior [correlation with] Decent work 0.508***."</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="18" customHeight="1" s="10">
       <c r="A266" t="inlineStr">
@@ -13953,6 +14269,16 @@
           <t>BSMA0263</t>
         </is>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G266" t="inlineStr">
         <is>
           <t>This paper collects 103 sample firms' 2015 to 2019 data through data envelopment analysis to measure their technical innovation performance and social network analysis to build joint-patent networks and explore knowledge-creating alliance relationships. The article highlights how tacit knowledge recombination works as a mechanism of boundary spanning. It emphasizes the significance of strategic balancing networks' position to improve technical innovation performance and competitiveness of patent-intensive (PI) firms. This research contributes to shedding additional light on the nature of the boundary-spanning mechanism and PI firms' knowledge exchanges. Specifically, it examines how balancing boundaries spanning through joint-patent networks can influence the processes of tacit knowledge transmission and recombination between knowledge-based actors.</t>
@@ -13978,7 +14304,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P266" s="8" t="n"/>
+      <c r="P266" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a team-level referent for boundary-spanning activities and analyzes data at the team level (N=71 teams measured over 11 months), violating the individual-level requirement (Code 3). Furthermore, the paper does not provide a zero-order Pearson correlation matrix, only reporting Heterotrait-Monotrait Ratio (HTMT) values and path/regression coefficients, meaning there is no extractable effect size (Code 1). Therefore, it is excluded under multiple criteria (Code 1 and Code 3).. Verbatim Evidence: "The referent-shift consensus model proposed by Chan[50]was used in designing the questionnaire, which means that variables including 'team boundary-spanning activities,' 'team job crafting,' and 'team innovation performance' was designed from the perspective of the team. A request was made for these questions to be answered from the perspective of team awareness. [...] This study examined 71 teams' balanced panel data from January to November 2022. [...] Finally, there were 41 teams in the experimental group and 30 in the control group. [...] Table 4. Analysis of Heterotrait-Monotrait Ratio discriminant validity."</t>
+        </is>
+      </c>
     </row>
     <row r="267" ht="18" customHeight="1" s="10">
       <c r="A267" t="inlineStr">
@@ -13991,6 +14321,16 @@
           <t>BSMA0264</t>
         </is>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G267" t="inlineStr">
         <is>
           <t>Setting the research background in China, this study draws on absorptive capacity, knowledge inertia and prospect theory to show the relationship between R&amp;D capability and innovation performance which comprises exploitation and exploration. We propose that stronger R&amp;D capability promotes exploitation performance but inhibits exploration performance. As exploitation represents immediate interest and exploration represents long-term interest, we introduce the notion of knowledge boundary spanning of R&amp;D network to balance short-term and long-term benefits. The empirical results show that R&amp;D capability and knowledge boundary spanning of R&amp;D network complement each other for explorative innovation while they present trade-offs for exploitative innovation. This study contributes to existing literature on R&amp;D capability–innovation performance, and it further extends our understanding by investigating the impact of knowledge boundary spanning of R&amp;D network on the R&amp;D capacity–innovation performance relationships. In addition, this study provides references on resources configuration to achieve different innovation strategies.</t>
@@ -14016,7 +14356,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P267" s="8" t="n"/>
+      <c r="P267" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study conducts its analysis at the firm level (N = 702 corporations) and operationalizes 'knowledge boundary spanning' using a firm-level demographic proxy (the number of skilled staff) rather than measuring the purposive, interpersonal boundary spanning behaviors of individual employees. It lacks both individual-level data and a valid measure of interpersonal boundary spanning behavior.. Verbatim Evidence: "To test our hypotheses, we examined corporations from the Hunan province applying for high-tech enterprises qualification in China. We collected application documents, excluded samples with incomplete data, and ultimately, obtained data of 702 corporations. The application documents consisted of R&amp;D investment, firm assets, firm sales, the number of patents, utility models, scientific and technical staff, R&amp;D staff, and others. ... Knowledge boundary spanning of R&amp;D network: We took the number of skilled staff as the proxy for knowledge boundary spanning of R&amp;D network."</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="18" customHeight="1" s="10">
       <c r="A268" t="inlineStr">
@@ -14029,6 +14373,16 @@
           <t>BSMA0265</t>
         </is>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G268" t="inlineStr">
         <is>
           <t>Open innovation is crucial for achieving high-quality and sustainable business growth. However, it remains unclear how prospective boundary-spanning search and responsive boundary-spanning search impact organizational resilience and open innovation in the VUCA (Volatility, Uncertainty, Complexity, and Ambiguity) new normal. Based on the resource-based theory and dynamic capabilities theory, this paper classifies boundaryspanning search into prospective boundary-spanning search and responsive boundary-spanning search to investigates the impact on open innovation and organizational resilience, and analyze the moderating role of big data analytics capability. The empirical study of 293 Chinese smart manufacturing firms indicates that both prospective and responsive boundary-spanning search have an inverted U-shaped impact on open innovation and organizational resilience. Organizational resilience partially mediates the relationships between prospective boundary-spanning search, responsive boundary-spanning search, and open innovation. Moreover, big data analytics capability moderates and flattens the inverted U-shaped relationships between prospective and responsive boundary-spanning search, and organizational resilience. This study explores the intrinsic mechanism of prospective and responsive boundary-spanning search on open innovation through organizational resilience. The findings enrich and expand the research on the antecedents of open innovation.</t>
@@ -14054,7 +14408,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="P268" s="8" t="n"/>
+      <c r="P268" s="8" t="inlineStr">
+        <is>
+          <t>The study analyzes boundary-spanning search at the firm level rather than individual employee behavior. Survey respondents (middle and senior managers) serve as key informants evaluating their firm's macro-level practices, as evidenced by items using the 'our firm' referent (e.g., 'our firm often identifies new opportunities'). This violates the individual-level analysis requirement and the key informant proxy guardrail.. Verbatim Evidence: "The empirical study of 293 Chinese smart manufacturing firms indicates that both prospective and responsive boundary-spanning search have an inverted U-shaped impact on open innovation and organizational resilience. [...] The survey respondents were primarily middle and senior managers from firms located in key regions such as Beijing, Shanghai, Zhengzhou, Guangdong, Chongqing, and Xi’an. [...] Prospective boundary-spanning search includes “our firm often identifies new opportunities in emerging markets before its competitors” [...] Responsive boundary-spanning search includes “our firm often follows competitors in enhancing the competitiveness of existing products in the market”..."</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="18" customHeight="1" s="10">
       <c r="A269" t="inlineStr">
@@ -14067,6 +14425,14 @@
           <t>BSMA0266</t>
         </is>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>999</v>
+      </c>
       <c r="G269" t="inlineStr">
         <is>
           <t>No abstract</t>
@@ -14092,7 +14458,13 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P269" s="8" t="n"/>
+      <c r="P269" s="8" t="inlineStr">
+        <is>
+          <t>The study examines R&amp;D teams and includes a measure of 'Leaders' Boundary-Spanning Behaviors' assessed by team members using the Ancona &amp; Caldwell (1992) scale. The subordinate ratings are aggregated to the team level (N=52 teams). Because there is exactly one leader per team, the effective sample size for the leader's boundary spanning is N=52 individual leaders. Following the Leader BSB override rule and the N=Leaders=N=Teams exception, this constitutes valid individual-level BSB. A zero-order correlation matrix is provided in Table 6, containing extractable effect sizes for the leader's boundary-spanning behaviors.. Verbatim Evidence: ""To assess the extent to which team leaders engage in boundary-spanning behaviors, I asked team members to assess team leaders’ boundary-spanning behaviors via their completion of the 21-item measure (which were anchored by 1 = “strongly disagree”, and 7 = “strongly agree”) by Ancona &amp; Caldwell (1992) and aggregated it to the team level. These 21 items represent the three dimensions of boundary-spanning behaviors, such as: (1) ambassadorial behaviors or the behaviors that involve the export of information and/or resources to outsiders (e.g., “my team leader keeps other groups in the company informed of my project team's activities,” “my team leader persuades others to support the project team's decisions”)..."
+"The cumulative number of study volunteers in this study (across the two locations) was 62 team leaders (one leader per team) and 171 team members... These final 52 teams consisted of 52 team leaders (20 from the U.S., and 32 from South Korea) and 143 team members (47 from the U.S., and 96 from South Korea)."
+"TABLE 6. MEANS, STANDARD DEVIATIONS, AND INTERCORRELATIONS FOR STUDY VARIABLES... 9 Leaders' Boundary-Spanning Behaviors""</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="18" customHeight="1" s="10">
       <c r="A270" t="inlineStr">
@@ -14105,6 +14477,14 @@
           <t>BSMA0267</t>
         </is>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>999</v>
+      </c>
       <c r="G270" t="inlineStr">
         <is>
           <t>This study examines the antecedents of job satisfaction, commitment and turnover for 229 information systems development personnel (ISDP) employed by nine companies within several industries. The antecedents studied include boundary spanning, role ambiguity and role conflict. A model of these variables is built and tested via path analysis. A secondary analysis is performed to explore the impacts of task and individual differences on the study variables. The task differences include analytic and programming tasks while the individual differences studied are age, tenure, education and years of data processing experience.</t>
@@ -14130,7 +14510,11 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="P270" s="8" t="n"/>
+      <c r="P270" s="8" t="inlineStr">
+        <is>
+          <t>The study by Baroudi (1984) examines job satisfaction, commitment, and turnover among information systems development personnel (ISDP). The sample consists of 229 ISDP across nine companies, making it a quantitative study of organizational employees. It measures boundary spanning behavior (both representational and informational) using an adapted version of the Miles and Perreault (1976) scale, capturing cross-departmental and inter-organizational interactions (e.g., 'Represent my department or work group to outsiders', 'Travel as a representative of my department or organization'). The correlations between boundary spanning and outcomes like job satisfaction, organizational commitment, and intention to quit, as well as role conflict and ambiguity, are reported in Table 5.2. Thus, the study qualifies for inclusion.. Verbatim Evidence: "This study examines the antecedents of job satisfaction, commitment and turnover for 229 information systems development personnel (ISDP) employed by nine companies within several industries. The antecedents studied include boundary spanning, role ambiguity and role conflict. A model of these variables is built and tested via path analysis... Boundary spanning refers to the extent to which the role requires the interacting or crossing of intra and inter-organizational boundaries [Adams, 1976; Tushman, 1981]... The second measure, developed by Miles and Perrault [1976], is used to investigate the boundary spanning activities of laboratory research and development personnel... The following process was employed to adapt the Miles and Perrault measure... Table 4.0 BOUNDARY SPANNING ITEMS... Table 5.2 PEARSON CORRELATIONS... BS COMM RC RA JS IQ..."</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="18" customHeight="1" s="10">
       <c r="A271" t="inlineStr">
@@ -14143,6 +14527,14 @@
           <t>BSMA0268</t>
         </is>
       </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>999</v>
+      </c>
       <c r="G271" t="inlineStr">
         <is>
           <t>The relationship between boundary-spanning role activities and conflict management styles was examined with data gathered from 189 project managers who belong to a national professional association. Five conflict management styles and six boundary role activities were measured with a survey instrument constructed from previously developed scales. The conflict management styles measured were integrating, avoiding, dominating, obliging, and compromising. The six boundary role activities measured were gathering, filtering, and transmitting information; transacting; proacting; and protecting. Hypotheses proposing specific relationships between each of the five conflict management styles and the six boundary role activities were tested with the data. Results indicated that unique combinations of boundary role activities are associated with each of the conflict management styles. Further, more cooperative conflict management styles are related to a greater number of boundary role activities that emphasize information sharing and managing relationships. Results also indicated that length of a project manager's experience moderates this relationship in that those with greater experience use more cooperative styles. A revision is suggested to the conflict management style construct.</t>
@@ -14168,7 +14560,11 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="P271" s="8" t="n"/>
+      <c r="P271" s="8" t="inlineStr">
+        <is>
+          <t>The study quantitatively measures boundary-spanning role activities (gathering, filtering, transmitting, transacting, proacting, protecting) of 189 project managers. It provides zero-order correlations (Pearson's r) between these individual-level BSB dimensions and conflict management styles (e.g., integrating, dominating, avoiding) in Table 10. The sample consists of individual employees and the BSB measures represent purposive actions spanning internal and external group boundaries. The study meets all inclusion criteria and does not violate any exclusion guardrails.. Verbatim Evidence: "Of the 776 surveys that were mailed, 197 were returned, for a response rate of 25.3%... The data from the remaining 189 usable surveys that were returned indicated that approximately 26% of the respondents were female... Table 10: Correlations: Boundary-spanning Role Activities and Conflict Management Styles [Provides Pearson correlation coefficients between Gather, Filter, Transmit, Transact, Proact, Protect and Integrate, Oblige, Dominate, Avoid, Compromise]... First, respondents are asked to determine how often they perform the given activity in their current job... The modified questionnaire stated for the first item 'Gathering information from outside your group (Examples: other teams, functions, clients, suppliers, customers, professional colleagues, public, media, etc.).'"</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="18" customHeight="1" s="10">
       <c r="A272" t="inlineStr">
@@ -14181,6 +14577,16 @@
           <t>BSMA0269</t>
         </is>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G272" t="inlineStr">
         <is>
           <t>Owing to their growing numbers and importance, both managers and researchers are increasingly concerned with the work experiences of boundary-spanning employees. Employee perceptions of organizational support *POS) may be particularly relevant to this crucial employee group. Thus reports a study of the relations between two individual-level and two organizationallevel antecedents to boundary-spanner POS. The results indicate that employee gender, amount of formal organizational recognition received, and the quality of task-related training are associated with POS. However, type of employee pay plan is not. Concludes with a discussion of these findings and their implications for effectively managing boundary-spanning employee POS.</t>
@@ -14206,7 +14612,11 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="P272" s="8" t="n"/>
+      <c r="P272" s="8" t="inlineStr">
+        <is>
+          <t>The study uses a sample of salespeople, referring to them as 'boundary-spanning employees', but it does not quantitatively measure Boundary Spanning Behavior (BSB) as a variable. The variables measured include perceived organizational support (POS), training, formal organizational recognition, gender, and pay plan type. Because there is no measurement of purposive BSB or its effect sizes, the paper lacks the effect size of interest.. Verbatim Evidence: "Data to examine the hypotheses were collected from a sample of professional boundary-spanning salespeople... Boundary-spanner perceived organizational support was measured using three items... perceptions of firm training were measured using three items... Formal organizational recognition was measured by adding together the number of promotions and pay raises each boundary-spanner had received, while gender and type of pay plan were measured by asking each respondent to mark a category that best described his or her circumstances. The Appendix contains all of the items used in this study."</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="18" customHeight="1" s="10">
       <c r="A273" t="inlineStr">
@@ -14219,6 +14629,16 @@
           <t>BSMA0270</t>
         </is>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G273" t="inlineStr">
         <is>
           <t>Purpose – The purpose of this paper is to investigate a boundary spanning, interprofessional collaboration between advanced practice nurses (APNs) and junior doctors to support junior doctors’ learning and improve patient management during the overtime shift.</t>
@@ -14244,7 +14664,15 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="P273" s="8" t="n"/>
+      <c r="P273" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure Boundary Spanning Behavior as a quantifiable individual-level behavior; instead, it uses a binary dummy variable for an intervention condition, specifically the presence of an Advanced Practice Nurse (APN) on a shift (0 = No APN, 1 = APN) [Code 1]. Furthermore, the correlation matrix is based on shift-level observations (N = 192 shifts) nested within 91 junior doctors, meaning the data involves repeated measures that violate statistical independence and are not analyzed at the individual employee level [Code 3].. Verbatim Evidence: "At the time of the study, there was only sufficient funding for an APN to work with junior doctors on half the overtime shifts. This natural experiment enabled us to compare overtime shifts with and without an APN present.
+...
+Three APNs and ninety-one junior doctors participated, resulting in a response rate of 100 and 89 percent, respectively. Data were collected from 192 overtime shifts over six months. An APN was present in 86 shifts.
+...
+Table I. Descriptive statistics for all variables, from overtime shifts (5 p.m. to 11 p.m.) completed by junior doctors and Pearson product correlations... 1 APNa [0 = No APN, 1 = APN]"</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="18" customHeight="1" s="10">
       <c r="A274" t="inlineStr">
@@ -14257,6 +14685,16 @@
           <t>BSMA0271</t>
         </is>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G274" t="inlineStr">
         <is>
           <t>National Sun Yat-sen University, Kaohsiung, Taiwan This research report compares three differing explanations of the dynamic interrelationships between internal and external innovation-related communication in a new organizational form. In the functional specialization explanation, individuals are said to focus on the mix of internal and/or external communication dictated by their formal positions. The communication stars explanation suggests that individuals maintain similar levels of communication in both networks. The cyclical model posits a more dynamic pattern that shifts back and forth between internal and external communication, depending on the consequences of their prior communication behavior. The new organizational form examined for three years was the Cancer Information Service, a geographically dispersed federal government health information program. Our results indicated that there was a lagged effect for the communication stars explanation.</t>
@@ -14282,7 +14720,11 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="P274" s="8" t="n"/>
+      <c r="P274" s="8" t="inlineStr">
+        <is>
+          <t>The study measures internal and external communication as the number of times respondents initiated or received contacts over a specified period (a frequency count). According to Screening Rule 6, mere communication frequency counts lack the purposive action inherent to BSB and are invalid. Additionally, the study only reports 'censored correlations' between these communication frequency counts across three time periods without including any other antecedents or outcomes, yielding no zero-order effect sizes of interest.. Verbatim Evidence: "Internal Communication: Respondents were asked to record the interpersonal communication contacts they initiated or received within CIS network for a three-day period... External Communication: Respondents were asked to record or estimate the number of times they initiated or received contacts with a member representing outside organizations about intervention strategies... Table 1. Means, Standard Deviations, Ranges, and Censored Correlations over Three Points in Time... These data led us to adopt a censored variable approach, normalizing the variables at the lower ranges of observed values."</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="18" customHeight="1" s="10">
       <c r="A275" t="inlineStr">
@@ -14295,6 +14737,16 @@
           <t>BSMA0272</t>
         </is>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G275" t="inlineStr">
         <is>
           <t>Firms are challenged to achieve organizational goals in an environment of increasingly decentralized information. Cross-functional project teams are employed widely as a strategy to facilitate better coordination, yet projects still fail at a rate of 31% per year. Communication is a leading cause of failure. While inter-team communication has been studied extensively, less is understood about the intra-team communication of a cross-functional project team.</t>
@@ -14320,7 +14772,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P275" s="8" t="n"/>
+      <c r="P275" s="8" t="inlineStr">
+        <is>
+          <t>The dissertation includes a quantitative study (Study 2) that measures 'cross-functional team communication frequency' among team members. However, the scale relies solely on pure communication frequency items (how often respondents communicate by email, chat, or verbally) without specifying any purposive boundary-spanning action. Per Screening Rule 6, mere communication frequency lacks construct validity for Boundary Spanning Behavior and must be excluded. The other variables measured (communication clarity, functional identity, performance) also do not represent BSB. The qualitative studies (Study 1 and 3) do not provide extractable quantitative effect sizes.. Verbatim Evidence: "Cross-functional team communication frequency. The communication frequency scale contained three items and was adapted from Kacmar, Witt, Zivnuska, and Gully’s (2003) original 8-item scale that assessed work-related communication frequency on employee performance. The definition of communication frequency in this study is measuring all communication with a cross-functional team member regardless of its purpose. The questions were preceded with the following statement: “With cross-functional team members, how frequently did you communicate…?” and the following questions were asked: (1) by email? (2) by chat? and (3) verbally? Response options ranged from 1 = “more than once a day” to 5 = “less than once a month.”"</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="18" customHeight="1" s="10">
       <c r="A276" t="inlineStr">
@@ -14333,6 +14789,16 @@
           <t>BSMA0273</t>
         </is>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G276" t="inlineStr">
         <is>
           <t>This paper describes one of the first empirical explorations into organisational knowledge creation theory as first elucidated by Nonaka and Takeuchi [1]. We extend the theory and examine it in the inter-organisational context of University-Industry (U-I) collaborative R&amp;D Projects. More specifically, the relationship between enabling conditions and knowledge conversion processes as well as the effects of these processes on the achievement of technological objectives are studied using a sample of 25 U-I collaborative R&amp;D projects into advanced technology. Quantitative and qualitative evidence supports the theory that some enabling conditions are significant for knowledge conversion processes. Furthermore, the presence of the aggregate knowledge processes is positively associated with the achievement of successful technological objectives. The theoretical and practical implications of these findings are discussed.</t>
@@ -14358,7 +14824,11 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="P276" s="8" t="n"/>
+      <c r="P276" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts analysis at the project level (N = 25 collaborative R&amp;D projects) rather than the individual employee level. Constructs such as environmental scanning and knowledge creation processes are measured as project-level characteristics, and the correlation matrix reflects project-level aggregates. This violates the individual-level analysis guardrail, precluding the extraction of individual-level effect sizes.. Verbatim Evidence: "The final research sample consisted of 25 collaborative R&amp;D projects involving the creation and development of novel intelligent systems, which consist of artificial intelligence, computer and robotic technologies... For 11 of the projects (44%), multiple informants responded. The inter-rater reliability (Cronbachs alpha) for the projects with multiple informants averaged 0.76... Table 1 Means, standard deviations and correlations... a N = 25 Projects"</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="18" customHeight="1" s="10">
       <c r="A277" t="inlineStr">
@@ -14371,6 +14841,16 @@
           <t>BSMA0274</t>
         </is>
       </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G277" t="inlineStr">
         <is>
           <t>BACKGROUND: There is a need for a better understanding of how the use of technology to complete work outside regular ofﬁce hours is related to work-life outcomes. Few studies have also investigated how individual differences in work-nonwork boundary management relate to work-life outcomes. OBJECTIVE: This study was conducted to examine how teleworking outside regular ofﬁce hours and individual boundary management relate to work-family conﬂict. METHODS: A web survey was sent to fulltime employees at the headquarters of a multinational high-tech ﬁrm in Sweden. A total of 71 answers were obtained and analyzed using regression analysis. RESULTS: The extent of teleworking after hours was unrelated to work-family conﬂict. However, as previous research has shown, having more permeable boundaries and allowing work to interrupt nonwork behavior was related to higher levels of conﬂict. CONCLUSIONS: The ﬁndings suggest that teleworking after hours is not as problematic in terms of work-family conﬂict as has been reported in previous studies. Furthermore, in order to prevent high levels of work-family conﬂict, it is seemingly beneﬁcial to avoid work interruptions during nonwork behavior.</t>
@@ -14396,7 +14876,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P277" s="8" t="n"/>
+      <c r="P277" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on work-family and work-nonwork boundary management (specifically, boundary permeability and interruption between work and personal life domains) in the context of teleworking. It does not measure purposive boundary spanning behavior across external organizational or internal functional boundaries.. Verbatim Evidence: "This study was conducted to examine how teleworking outside regular office hours and individual boundary management relate to work-family conflict. [...] Boundary management was studied as the degree of boundary permeability a person allows between work and nonwork roles. [...] Two related and highly similar theories, but with different research origins, deal with the management of boundaries [29]. These are boundary theory [28, 30] (which focuses on work and life domains), and work-family border theory [31] (which focuses more on work and family domains)."</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="18" customHeight="1" s="10">
       <c r="A278" t="inlineStr">
@@ -14409,6 +14893,16 @@
           <t>BSMA0275</t>
         </is>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G278" t="inlineStr">
         <is>
           <t>While the introduction of a new product or service carries considerable risk, incorporating customer input into the new product/service development (NPD) process increases the probability of commercial success. In their boundary spanning role, industrial (B-to-B) salespeople are well suited to serve as a conduit between customers and those inside their company who are largely responsible for the NPD process. The current study investigates the perceptions of sales managers and examines the role the sales force may play in the early stages of the NPD process. An empirical analysis is conducted to determine whether differences exist between organizations that employ key account management (KAM) systems and those that do not employ KAM systems. The findings of this study suggest that salespeople from KAM organizations are better suited to provide input into the NPD process than their non-KAM counterparts.</t>
@@ -14434,7 +14928,11 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="P278" s="8" t="n"/>
+      <c r="P278" s="8" t="inlineStr">
+        <is>
+          <t>The study does not report a zero-order correlation matrix or any extractable effect sizes (r), as it only provides mean comparisons (e.g., t-tests/ANOVAs between KAM and non-KAM systems) and chi-square statistics [Code 1]. Furthermore, the study surveys sales managers acting as key informants to evaluate the practices of their firm's entire sales force (e.g., sales force involvement in the NPD process), violating the individual-level analysis requirement [Code 3].. Verbatim Evidence: "The focus of this study was to investigate differences between organizations utilizing key account management (KAM) sales processes and organizations that do not utilize key account management processes (non-KAM) with regards to their involvement of salespeople during the early stages of the new product development process... The survey was sent to 2,650 sales managers (or sales directors) employed by firms across the United States... Usable surveys were received from 246 respondents... Sales managers (or sales directors) were first asked to evaluate the responsibilities of salespeople within the organization for acquiring new product/service information from customers."</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="18" customHeight="1" s="10">
       <c r="A279" t="inlineStr">
@@ -14447,6 +14945,16 @@
           <t>BSMA0276</t>
         </is>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G279" t="inlineStr">
         <is>
           <t>We examine how two highly successful new biotechnology firms (NBFs) source their most critical input—scientific knowledge. We find that scientists at the two NBFs enter into large numbers of collaborative research efforts with scientists at other organizations, especially universities. Formal market contracts are rarely used to govern these exchanges of scientific knowledge. Our findings suggest that the use of boundary-spanning social networks by the two NBFs increases both their learning and their flexibility in ways that would not be possible within a self-contained hierarchical organization.</t>
@@ -14472,7 +14980,11 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="P279" s="8" t="n"/>
+      <c r="P279" s="8" t="inlineStr">
+        <is>
+          <t>The study is a descriptive case study of two biotechnology firms using archival publication and patent data to examine external scientific collaborations. It does not report a correlation matrix or any extractable quantitative effect sizes (r), violating the requirement for statistical data (Code 1). Additionally, the analysis is conducted at the firm level (comparing Firm X and Firm Y) rather than the individual employee level (Code 3). Therefore, it is excluded under multiple criteria [Code 1 &amp; Code 3].. Verbatim Evidence: "We used a sample of only two firms because collecting data on social network exchanges is difficult and time-consuming. Our approach therefore represents a choice of depth over breadth... we have 10 years of data for Firm X and nine years of data for Firm Y. ... We measured exchanges of scientific knowledge in terms of scholarly publications on which scientists at the two NBFs studied were named as authors. ... At Firm X, scientists had produced 503 research publications by year 10; at Firm Y, scientists had produced 345 research publications through year 9."</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="18" customHeight="1" s="10">
       <c r="A280" t="inlineStr">
@@ -14485,6 +14997,14 @@
           <t>BSMA0277</t>
         </is>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>999</v>
+      </c>
       <c r="G280" t="inlineStr">
         <is>
           <t>Purpose – The purpose of this study is to evaluate the recognition of sexual harassment (SH); to describe the relationships among SH, employees’ burnout, customer-oriented boundary-spanning behaviors (COBSB); and to verify the moderating effect of employees’ psychological safety (PS), all within deluxe hotels in South Korea.</t>
@@ -14510,7 +15030,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P280" s="8" t="n"/>
+      <c r="P280" s="8" t="inlineStr">
+        <is>
+          <t>The study examines customer-oriented boundary-spanning behaviors (COBSB) at the individual employee level (N=334 female frontline employees in deluxe hotels). It measures purposive boundary-spanning actions (e.g., external representation, internal influence, service delivery) using a well-established scale by Bettencourt et al. (2005). The study provides a full, square quantitative correlation matrix including the COBSB construct, thus providing the required effect sizes of interest. It does not violate any level-of-analysis, proxy, or construct guardrails.. Verbatim Evidence: "A total of 334 female frontline employees working in 10 deluxe hotels, were selected as subjects for this study. ... COBSB were measured with six questions, including questions on external representation, internal influence and service delivery behaviors based on research by Bettencourt et al. (2005). ... Table II. Correlations among the latent constructs ... 7. COBSB"</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="18" customHeight="1" s="10">
       <c r="A281" t="inlineStr">
@@ -14523,6 +15047,16 @@
           <t>BSMA0278</t>
         </is>
       </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G281" t="inlineStr">
         <is>
           <t>Data from high-technology firms in Hong Kong were used to investigate whether the outcomes of problem-solving processes (solutions found, problem-solving speed, and solution quality) mediated the effects of centrifugal forces (decentralization, free flow of information, and reach) and centripetal forces (connectedness, temporal pacing, project leader expertise, and superordinate goal) on product development performance (development speed and product quality). Centrifugal and centripetal forces were indirectly related to performance through problem-solving outcomes, although some direct effects of these forces were also found. The results suggest a more complex model of product development than previously envisaged.</t>
@@ -14548,7 +15082,11 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="P281" s="8" t="n"/>
+      <c r="P281" s="8" t="inlineStr">
+        <is>
+          <t>The study examines centrifugal and centripetal forces at the project team level (N = 103 project teams). Two team members provided a single consensual rating for the team's processes, including 'reach' (external boundary spanning with customers) and 'connectedness' (internal boundary spanning across departments). The survey items use team-level referents such as 'The project team had close, personal interactions' and 'Team members put a lot of effort in interacting'. Because the unit of analysis is the team and respondents act as key informants for the team's collective behavior, the study violates the individual-level analysis guardrail and must be excluded.. Verbatim Evidence: "I asked two team members in each participating project to provide a single consensual rating for the measures of these forces. ... Reach: Team members put a lot of effort in interacting with potential customers. ... The project team members collected information about new market developments affecting customers. ... Connectedness: The project team had close, personal interactions with other members of the firm regarding the project. We had frequent consultation with other departments in the firm regarding the project."</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="18" customHeight="1" s="10">
       <c r="A282" t="inlineStr">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -13405,6 +13405,14 @@
           <t>BSMA0246</t>
         </is>
       </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>999</v>
+      </c>
       <c r="G249" t="inlineStr">
         <is>
           <t>The study examines the effects of the individual characteristics, job type, role stressors, boundary spanning activities, career outcomes, and job characteristics on the turnover propensity of 464 information systems personnel. Results show that age, organizational level, organizational tenure, job tenure, and number of years in the computer field are negatively correlated with the intention to leave the organization. Education was found to be positively correlated with turnover intentions, and while project leaders are more likely to leave the organization, IS managers are less likely. Results also show that both role stressors (role ambiguity and role conflict) and boundary spanning activities are positively correlated with turnover intentions, and that job involvement, career plateau, promotability, salary, organizational commitment, job satisfaction, satisfaction with progress, promotion, pay, status, and projects are negatively correlated while career opportunity is positively correlated with turnover intentions. Finally, all job characteristics are negatively correlated with turnover intentions. Implications of the results for practice and research are offered.</t>
@@ -13430,7 +13438,11 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="P249" s="8" t="n"/>
+      <c r="P249" s="8" t="inlineStr">
+        <is>
+          <t>The study examines boundary spanning activities of individual employees (Information Center and Information Systems personnel) across internal organizational boundaries. It provides a zero-order correlation matrix including boundary spanning activities, role stressors, job satisfaction, and organizational commitment. Following the intra-organizational BSB inclusion rule (Rule 17), this study is valid for inclusion.. Verbatim Evidence: "Boundary Spanning Activities. Boundary spanning activities, defined as communication beyond an employee's immediate department, were measured by modifying the ten-item instrument developed by Miles and Perreault (1976) and used by Baroudi (1985). ... Ninety-two IC employees and 140 IS employees (5 per company) from the 28 companies were asked to participate in the study. ... Seventy-six IC employees and 133 IS employees completed the questionnaire (82.6 and 95 percent response rates for IC and IS, respectively). The final sample consisted of 209 individuals. ... TABLE 1 Matrix of Intercorrelations among Study Variables (N = 209)"</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="18" customHeight="1" s="10">
       <c r="A250" t="inlineStr">
@@ -15097,6 +15109,16 @@
       <c r="B282" t="inlineStr">
         <is>
           <t>BSMA0279</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -15137,7 +15159,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P282" s="8" t="n"/>
+      <c r="P282" s="8" t="inlineStr">
+        <is>
+          <t>The study focuses on bidirectional boundary management behavior between the work and nonwork (personal life) domains, rather than inter- or intra-organizational boundary spanning behavior. The measured constructs are work-nonwork segmentation behavior (e.g., leaving work behind when going home) and nonwork-work segmentation behavior (e.g., leaving personal life behind when going to work). As the research strictly concerns work-family/work-life boundary management, it lacks the target effect size of interest for this meta-analysis.. Verbatim Evidence: "Our study contributes to research on the work-nonwork interface in several ways. ... Work-nonwork segmentation behavior (α=0.84) and nonwork-work segmentation behavior (α=0.82) were measured by three items each on a 7-point Likert scale (1, strongly disagree, to 7, strongly agree). ... One sample item for work-nonwork segmentation behavior is: 'I left work behind when I went home.' To measure nonwork-work segmentation behavior, we modified the items’ directionality. A sample item is: 'I left my personal life behind when I went to work.' A sample item reflecting nonwork-work integration is: 'I took care of personal matters when I was at work,' which was reversed for analyses."</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="18" customHeight="1" s="10">
       <c r="A283" t="inlineStr">
@@ -15150,6 +15176,16 @@
           <t>BSMA0280</t>
         </is>
       </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G283" t="inlineStr">
         <is>
           <t>Problems cross boundaries and so must solutions. The most important challenge for performance networks that aim to deliver better results is designing the structure that coordinates across traditional agency boundaries. Not only must this structure be clearly defined, but it also must account for the integration of a broad range of cross-government activities. Like the overarching performance network, the cross-boundary structure has the characteristics of a dynamic system, including flexibility, adaptability, growth, and the continual emergence of new forms and functions. Summer 2000 featured perfect conditions for gridlock in the sky. Flying had become an increasingly popular way to travel, and the airlines had marketed aggressively to vacationing families and business travelers. Airports were already crowded when unusual and frequent patterns of bad weather hit aviation especially hard. Delays and canceled flights became almost daily events. The public complained loudly, congressional hearings were scheduled, and the Federal Aviation Administration was about to experience unfriendly fire from an aroused media.</t>
@@ -15175,7 +15211,11 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="P283" s="8" t="n"/>
+      <c r="P283" s="8" t="inlineStr">
+        <is>
+          <t>The article is a practitioner-oriented, descriptive case study of the Federal Aviation Administration's (FAA) NextGen and Operational Evolution Plan (OEP) projects. It does not contain primary quantitative empirical data, individual-level employee samples, or correlation matrices from which effect sizes can be extracted. As it lacks quantitative effect sizes of interest, it is excluded.. Verbatim Evidence: "Structure describes how different agencies and organizations can work together and coordinate activities to achieve shared goals. The cross-boundary structure needs to coordinate solutions for a complex set of problems, so the structure itself must be clearly defined. The Next Generation Air Transportation System (NextGen) is an example of a clearly defined structure that enables multiple departments, agencies, organizations, industries, and public-private partnerships to coordinate activities at many levels of detail so our national airspace system can accommodate new technologies... NextGen is about as complex a transformation as can be imagined. In December 2003, Congress passed legislation that required the Departments of Transportation, Defense, Commerce, and Homeland Security, along with the FAA, NASA, and the White House Office of Science and Technology Policy, to develop the NextGen vision and an overarching enterprise architecture for reaching that vision."</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="18" customHeight="1" s="10">
       <c r="A284" t="inlineStr">
@@ -15188,6 +15228,16 @@
           <t>BSMA0281</t>
         </is>
       </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G284" t="inlineStr">
         <is>
           <t>This study performs an in-depth analysis of the causes and consequences of team boundary-spanning activities in the context of Chinese technology transfer, by addressing three related research questions: what are the drivers of teams’ boundary-spanning activities? How do teams conduct boundary-spanning activities? What is the impact of teams’ boundary-spanning activities? Based on the “input–moderator–output–input” model of team effectiveness theory, this study firstly explores which factors drive technology transfer teams to engage in boundary-spanning activities. Then, it examines the effects that such activities have on technology transfer performance, both directly and indirectly, through a set of mediating factors. Finally, it explores whether external environmental conditions play any moderating role in the relationship between team boundary-spanning activities and team performance. The empirical analysis is based on original primary survey data collected from a representative sample of organizations involved in the Chinese technology transfer system. The study both contributes the team effectiveness theory applied to the specific context of technology transfer and offers practical suggestions to managers of technology transfer intermediaries.</t>
@@ -15213,7 +15263,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P284" s="8" t="n"/>
+      <c r="P284" s="8" t="inlineStr">
+        <is>
+          <t>The study adopts the team as the unit of analysis (N = 402 technology transfer teams) and aggregates boundary-spanning activities at the team level to compute correlations and regressions. This violates the inclusion criteria requiring boundary-spanning behavior to be measured and analyzed at the individual employee level.. Verbatim Evidence: "The empirical analysis has been conducted on original survey data collected from 402 technology transfer teams belonging to 247 Chinese technology transfer institutions... According to the size of each technology transfer organization and the actual number of technology transfer teams, for each organization belonging to the sample we randomly selected 1–5 teams, and invited the team leader and three team members to complete the survey... After excluding incomplete or invalid questionnaires, a total of 402 sets of valid questionnaires were collected... More recently, some researchers have begun to quantify the boundary-spanning activities of team members and then aggregate them at the team level for analysis (Ancona and Caldwell 1992a; Marrone et al. 2007)."</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="18" customHeight="1" s="10">
       <c r="A285" t="inlineStr">
@@ -15226,6 +15280,16 @@
           <t>BSMA0282</t>
         </is>
       </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G285" t="inlineStr">
         <is>
           <t>One of the main reasons that firms participate in alliances is to learn know‐how and capabilities from their alliance partners. At the same time firms want to protect themselves from the opportunistic behavior of their partner to retain their own core proprietary assets. Most research has generally viewed the achievement of these objectives as mutually exclusive. In contrast, we provide empirical evidence using large‐sample survey data to show that when firms build relational capital in conjunction with an integrative approach to managing conflict, they are able to achieve both objectives simultaneously. Relational capital based on mutual trust and interaction at the individual level between alliance partners creates a basis for learning and know‐how transfer across the exchange interface. At the same time, it curbs opportunistic behavior of alliance partners, thus preventing the leakage of critical know‐how between them.</t>
@@ -15251,7 +15315,11 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="P285" s="8" t="n"/>
+      <c r="P285" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the strategic alliance between firms, not the interpersonal boundary spanning behavior of individual employees. Managers were surveyed merely as key informants to report on firm-level alliance dynamics, such as relational capital, conflict management, and learning. The grammatical referents in the survey items focus on macro-level entities (e.g., 'The alliance', 'the partners', 'Your company'), violating the individual-level behavior guardrail. Therefore, the study is excluded under Code 3.. Verbatim Evidence: "The level of analysis is an alliance between two partners... The primary recipient in each company was requested to select any one alliance that the company had been involved with and forward the questionnaire to a manager who was directly associated with that alliance... Relational capital (RC): 1. There is close, personal interaction between the partners at multiple levels... 2. The alliance is characterized by mutual respect between the partners at multiple levels... Learning (L): 1. Your company learnt or acquired some new or important information from the partner"</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="18" customHeight="1" s="10">
       <c r="A286" t="inlineStr">
@@ -15264,6 +15332,14 @@
           <t>BSMA0283</t>
         </is>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F286" t="n">
+        <v>999</v>
+      </c>
       <c r="G286" t="inlineStr">
         <is>
           <t>Purpose – Despite the increasing importance of boundary-spanning behaviors in construction projects, the research on how leader anger expressions impact employees’ boundary-spanning behaviors remains unclear. This study aims to investigate the impact of leader anger expressions on employees’ boundaryspanning behaviors in construction projects while exploring the mediating effect of work hope and the moderating effect of power distance orientation through the lens of social information processing theory. Design/methodology/approach – The empirical data were collected from a questionnaire survey of 235 employees in construction projects, and the hypotheses were tested using the PROCESS program developed by Hayes.</t>
@@ -15289,7 +15365,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="P286" s="8" t="n"/>
+      <c r="P286" s="8" t="inlineStr">
+        <is>
+          <t>The study collects quantitative survey data from individual employees (N=235) in construction projects. It measures employees' own boundary-spanning behaviors (using a scale by Marrone et al., 2007; e.g., 'I will endeavor to convince external stakeholders...') and provides a zero-order correlation matrix including boundary-spanning behavior and other variables (e.g., leader anger expressions, work hope). It passes all inclusion criteria as it analyzes purposive interpersonal boundary spanning at the individual employee level with extractable effect sizes.. Verbatim Evidence: "The empirical data were collected from a questionnaire survey of 235 employees in construction projects, and the hypotheses were tested using the PROCESS program developed by Hayes. ... Boundary-spanning behaviors. Boundary-spanning behaviors were assessed using a six-item scale developed by Marrone et al. (2007). One sample item is “I will endeavor to convince external stakeholders, such as faculty and clients, to support project decisions”. ... Table 2 shows a descriptive analysis of all variables and their bivariate correlations. The findings indicated statistically significant bivariate correlations between leader anger expressions and work hope (r = −0.19, p &lt; 0.01), and work hope and boundary-spanning behaviors (r = 0.49, p &lt; 0.01)"</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="18" customHeight="1" s="10">
       <c r="A287" t="inlineStr">
@@ -15302,6 +15382,16 @@
           <t>BSMA0284</t>
         </is>
       </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G287" t="inlineStr">
         <is>
           <t>This article proposes to examine the self-concept of members of an occupational category referred to as the “solo self-employed”—women and men who work alone and do not employ other workers. Our findings reveal that although the solo self-employed themselves do not make clear phenomenological use of the solo-self-employed category, they do speak similarly about their occupational independence, albeit without group awareness. The self-concept of the solo self-employed is mainly based on boundary work in relation to two well-known cultural-occupational categories: “employed workers” and “businesspeople.” Solo-employed workers prefer to distance themselves from these two categories and define themselves through negative comparisons between themselves and the two preceding categories. The Discussion section proposes perceiving solo selfemployment as a social category that constructs an alternative self in relation to the selves associated with popular cultural-occupational scenarios.</t>
@@ -15327,7 +15417,11 @@
           <t>2019</t>
         </is>
       </c>
-      <c r="P287" s="8" t="n"/>
+      <c r="P287" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 2] The study uses a qualitative methodology (in-depth interviews analyzed using grounded theory) and does not provide a quantitative correlation matrix or extractable effect sizes. Additionally, the sample consists exclusively of solo self-employed individuals (independent non-employees), violating the population guardrail for organizational employees.. Verbatim Evidence: "This article is based on in-depth interviews with 30 subjects—15 men and 15 women. The age range was 29 to 45, and the average age was 37. The interviews were conducted between August 2014 and December 2018. The interview sample was a purposeful sample (Berg 1998)... An analysis of the interviews was carried out in accordance with the procedure proposed by the grounded theory (Strauss and Corbin 1998)."</t>
+        </is>
+      </c>
     </row>
     <row r="288" ht="18" customHeight="1" s="10">
       <c r="A288" t="inlineStr">
@@ -15340,6 +15434,16 @@
           <t>BSMA0285</t>
         </is>
       </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G288" t="inlineStr">
         <is>
           <t>The purpose of this paper is to develop the concept of project management system from the perspective of systems science. There is a need to extend the body of knowledge for project management. In particular, the application of systems perspectives and systems theory offers a significant opportunity to advance the current state of project management knowledge. Although there have been suggestions of systems approaches for project management, rigorous systems science has not been used to support these depictions. First, we develop the background and define a perspective of project management systems. Second, assumptions and principles are drawn from systems science to provide a foundation for project management systems. Third, a model for project management systems is developed from systems sciences and management cybernetics. Our initial explorations are promising, demonstrated by a case study application review using a complex system of systems (SoS) project encompassed multiple government agencies, and we offer future directions and implications for further model refinements, applications, and research into project management systems.</t>
@@ -15365,7 +15469,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P288" s="8" t="n"/>
+      <c r="P288" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a conceptual study that develops a systems science-based model for project management systems, supplemented by a qualitative case study application review of a complex system of systems (SoS) project. It does not provide any quantitative empirical data, formal correlation matrices, or extractable statistical effect sizes (r) involving individual employees' boundary spanning behavior.. Verbatim Evidence: "The purpose of this paper is to develop the concept of project management system from the perspective of systems science. There is a need to extend the body of knowledge for project management... Third, a model for project management systems is developed from systems sciences and management cybernetics. Our initial explorations are promising, demonstrated by a case study application review using a complex system of systems (SoS) project encompassed multiple government agencies, and we offer future directions and implications for further model refinements, applications, and research into project management systems... The project output consisted of a final report that was to (1) identify and describe the system within its context and environment, (2) provide an analysis of the current system capabilities, and (3) provide a forward metasystem look towards system enhancements with potential performance improvements."</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="18" customHeight="1" s="10">
       <c r="A289" t="inlineStr">
@@ -15378,6 +15486,16 @@
           <t>BSMA0286</t>
         </is>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G289" t="inlineStr">
         <is>
           <t>Smart cities emphasize the use of advanced technology to deliver better services to and improve the well-being of their residents. Since the administrative authorities that manage cities often lack the knowledge and skills needed to transform their operations in this way, smart city initiatives usually involve a complex set of actors, from local urban authorities and their technical departments to small and large IT firms, academics, and civic organizations, as well as individual citizens. Mediating organizations are often set up to coordinate and manage such interactions. However, little is known about the roles and activities of such bodies. Using data from the Dublin smart city projects, this study draws on the concept of boundary spanning to develop a taxonomy of the work of such intermediaries. Divided into technical, political, social, and cultural domains, the study demonstrates the critical role of the work done by such bodies in enhancing collaboration among and the participation of a diverse group of citizens, IT and digital strategy departments of local authorities, universities and local/international IT companies (e.g., Google, Facebook or Airbnb), leading to a bottom-up governance style of leading smart city initiatives and projects.</t>
@@ -15403,7 +15521,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P289" s="8" t="n"/>
+      <c r="P289" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study is a qualitative case study that uses semi-structured interviews to develop a taxonomy of boundary-spanning activities, thus lacking extractable quantitative effect sizes (r) (Code 1). Furthermore, the study analyzes the role and activities of an intermediary boundary-spanning organization (Smart Dublin) in city governance, rather than focusing on the interpersonal boundary-spanning behaviors of individual employees (Code 3).. Verbatim Evidence: "A single-case design for this study offers a unique opportunity to produce concrete, context-dependent knowledge in depth and in its particular type of setting... Semi-structured interviews were identified as the primary data collection method for this study and twenty-five interviews were conducted. Alongside the interviews, secondary data, such as reports, internal documents, presentations, and websites, were also collected... As we had a significant amount of data from twenty-five transcribed interviews alongside specific knowledge of the boundary spanning domain, an empirical-to-conceptual approach was suggested following several steps for analyzing the data through established coding techniques... Understanding the roles and activities undertaken by a boundary-spanning organization to secure collaboration requires the development of a taxonomy to organize them."</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="18" customHeight="1" s="10">
       <c r="A290" t="inlineStr">
@@ -15416,6 +15538,16 @@
           <t>BSMA0287</t>
         </is>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G290" t="inlineStr">
         <is>
           <t>Purpose – The recent COVID-19 pandemic has (triggered) lots of interest in work from home (WFH) practices. Many organizations in India are changing their work practices and adopting new models of getting the work done. The purpose of the study to look at the boundary-ﬁt perspective (Ammons (2013) and two factors, namely, individual preferences (boundary control, family identity, work identity and technology stress) and environmental factors (job control, supervisor support and organizational policies). These dimensions are used and considered to create various clusters for employees working from home.</t>
@@ -15441,7 +15573,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P290" s="8" t="n"/>
+      <c r="P290" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates work-family boundary management in the context of working from home (WFH) and its effects on work-family conflict and spillover. According to the screening rules, studies focusing on work-family or work-life boundary management rather than inter- or intra-organizational boundary spanning must be excluded. Furthermore, the paper relies on K-means cluster analysis and ANOVA, and does not report a zero-order correlation matrix.. Verbatim Evidence: "The traditional work and home environment are divided by temporal, physical and psychological boundaries. Working from home has changed (blurred) the previously set boundaries like physical, psychological and temporal between work and family domain (Greer and Payne, 2014)... WFC items were adapted from Carlson et al. (2000) scale having three items each for time-based and strain-based work-family interference. Boundary management tactics items included three items each for temporal, physical, behavioral and communicative and adapted from Carlson et al. (2015) study. Family-to-work positive spillover included four items for affective, four items for behavioral and three items for value-based based on Hanson et al. (2006)."</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="18" customHeight="1" s="10">
       <c r="A291" t="inlineStr">
@@ -15454,6 +15590,16 @@
           <t>BSMA0288</t>
         </is>
       </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G291" t="inlineStr">
         <is>
           <t>This study investigates the role of gatekeepers in the transfer of information within a single R &amp; D location by comparing directly t h e performance of project groups with and without gatekeepers. The results show that gatekeepers performed a linking role only for projects performing tasks that were 'locally-oriented' while 'universallyoriented' tasks were most effectively linked to external areas by direct project member communication. Gatekeepers also appear to facilitate external communication by their locallyoriented project colleagues. A follow-up study five years later showed that almost all gatekeeping project leaders had been promoted up the managerial ladder; in contrast, one half of the non-gatekeeping project leaders had ascended the technical ladder. This implies that higher managerial levels demand strong interpersonal a s well a s technical skills.</t>
@@ -15479,7 +15625,11 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="P291" s="8" t="n"/>
+      <c r="P291" s="8" t="inlineStr">
+        <is>
+          <t>The study aggregates external communication data to the project level (N = 60 project groups) to examine its correlation with project performance, which violates the individual-level unit of analysis requirement [Code 3]. Furthermore, the individual-level analyses regarding project supervisors' career paths (Tables 3-5) only report means and percentages without providing a zero-order correlation matrix or any extractable bivariate effect sizes (r) [Code 1].. Verbatim Evidence: "For each project member, internal communications was measured by summing the number of work-related contacts reported over the 15 weeks... As discussed by Katz &amp; Tushman (1979), these individual scores were also aggregated to obtain project measures of internal and external communication. ... Gatekeepers were identified in 20 project groups while 40 projects had no gatekeepers within their memberships. ... Table 2. Correlations between project performance and external communication by project type and gatekeeper presence [reports N as projects, e.g., N=5, N=9, N=8, N=15, etc.] ... Table 3. Comparison of promotions of gatekeeping and non-gatekeeping project supervisors [reports only percentages] ... Table 4. Comparisons of mean internal and external communications of project supervisors promoted over the next 5 years [reports only means]."</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="18" customHeight="1" s="10">
       <c r="A292" t="inlineStr">
@@ -15492,6 +15642,16 @@
           <t>BSMA0289</t>
         </is>
       </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G292" t="inlineStr">
         <is>
           <t>This study examines the impacts of problem-solving and administrative communication patterns on the technical performance of 61 projects in an industrial R&amp;D laboratory. While there were no differences in the relative patterns of these two types of communication, there were systematic differences in the mechanisms by which project groups transferred administrative and problem-solving information with other areas both within and outside the organization. The overall patterns of communication were influenced by the nature of the projects' work, while the effectiveness of the various interfaces was explored via two contrasting methods: (1) direct contact by all project members and (2) contact mediated through boundary spanning individuals. The effectiveness of each of these linking mechanisms was also contingent upon the projects' tasks. This research reinforces the importance of managing communication patterns in organizations and further supports the importance of boundary spanning individuals.</t>
@@ -15517,7 +15677,11 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="P292" s="8" t="n"/>
+      <c r="P292" s="8" t="inlineStr">
+        <is>
+          <t>The study's unit of analysis is the project team (N=61 R&amp;D projects), not individual employees. Individual communication network data (from 350 professionals) was collected but aggregated to the project level. All reported correlations and regression analyses between communication patterns and technical performance are conducted at the project level (e.g., N=61 overall, or N=13, 22, 20 for specific project types). There are no extractable zero-order correlations at the individual employee level.. Verbatim Evidence: "These projects were designed around specific types of problems and represent the basic unit of analysis. At the time of this study, 61 such projects existed across the laboratory's seven divisions resulting in the employment of 350 engineering and scientific professionals... Project measures were calculated by pooling individual scores. To check on the appropriateness of pooling, a one-way ANOVA compared within project variance with between-project variance... Measures for 55 projects passed these tests and clustered into the following task categories: General Research = 13 projects; Development = 22 projects; and Technical Service = 20 projects... Table 2: Correlations Between Project Performance and Overall Communications for Different Project Types... N = 61, 13, 22, 20."</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="18" customHeight="1" s="10">
       <c r="A293" t="inlineStr">
@@ -15530,6 +15694,16 @@
           <t>BSMA0290</t>
         </is>
       </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G293" t="inlineStr">
         <is>
           <t>An investigation of the influence of boundary spanning project supervisors on the turnover and promotion of engineering professionals found that, in general, boundary spanning supervisors had little direct effect on the careers of all project subordinates. However, project supervisors who also were technical gatekeepers significantly affected the organizational careers of young engineers.</t>
@@ -15555,7 +15729,11 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="P293" s="8" t="n"/>
+      <c r="P293" s="8" t="inlineStr">
+        <is>
+          <t>The study does not provide a formal zero-order correlation matrix or extractable quantitative effect sizes (Pearson's r) between boundary spanning behavior and substantive variables. Boundary spanning is instead used as a categorical grouping variable to split the sample (engineers who reported to a 'gatekeeping supervisor' versus those who reported to a 'nongatekeeping supervisor') to compare the proportions of turnover and promotion using t-tests and hierarchical discriminant analysis. As per Screening Rule 7, studies lacking a correlation matrix that use boundary spanning to split a sample cannot yield zero-order effect sizes and must be excluded.. Verbatim Evidence: "Conceptually, gatekeepers are defined as those project members who are very high internal communicators and who also maintain very high external contacts with outside professionals. This study operationalized gatekeepers as those project members whose departmental and external professional communications were both in the top fifth of their respective distributions (Katz &amp; Tushman, 1981; Whitley &amp; Frost, 1973)... Table 1 Supervisory Influence on the Proportion of Engineers Remaining in the Organization Over a 5-Year Period... A. Prior Type of Reporting Relationship: Engineer Worked for a Supervisor Who Was: Internal Liaison (62%), Gatekeeper (82%), Gatekeeper and Internal Liaison (85%), Neither a Liaison nor a Gatekeeper (70%)... To pinpoint the influence of gatekeepers on subordinate turnover, Figure 1 plots as a function of age the cumulative retention rates of project members reporting to gatekeeping supervisors (Group A) and those members not reporting to gatekeeping supervisors (Group B)."</t>
+        </is>
+      </c>
     </row>
     <row r="294" ht="18" customHeight="1" s="10">
       <c r="A294" t="inlineStr">
@@ -15566,6 +15744,16 @@
       <c r="B294" t="inlineStr">
         <is>
           <t>BSMA0291</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -15607,7 +15795,11 @@
           <t>2009</t>
         </is>
       </c>
-      <c r="P294" s="8" t="n"/>
+      <c r="P294" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates knowledge transfer and spillovers within inter-organizational R&amp;D projects in regional innovation networks. The unit of analysis is the organization (firms, universities, and research institutes, N=492), not individual employees. Survey respondents acted as key informants for their respective organizations, and variables such as firm size and organizational network experience were analyzed. Therefore, the study lacks an individual-level measure of boundary spanning behavior.. Verbatim Evidence: "This paper, in an attempt to link up these ideas, investigates knowledge transfer processes within inter-organizational R&amp;D projects that are embedded in 23 German regional innovation networks (with almost 500 participants)... The data that was gathered by postal questionnaires in the year 2004 resulted in a rather high response rate of about 80% (approximately 500 participants). The data contained information about the performance of the firms, the extent to which information and knowledge were exchanged, network cohesion, strength of ties and much more... About 60% of the organizations were private firms. Universities amount to 10% of the total, and about 16% of the actors were public or private non-university research institutes. Most of the firms involved are SMEs with 50% having less than 20 employees and only 10% having more than 100 employees... Table 1: Regression Summary: Degree of Knowledge Absorbed from Network Partners... Independent Variables... FIRM_SIZE... Number of observations 492"</t>
+        </is>
+      </c>
     </row>
     <row r="295" ht="18" customHeight="1" s="10">
       <c r="A295" t="inlineStr">
@@ -15620,6 +15812,14 @@
           <t>BSMA0292</t>
         </is>
       </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F295" t="n">
+        <v>999</v>
+      </c>
       <c r="G295" t="inlineStr">
         <is>
           <t>Boundary -spanning activity (BSA) was studied in two departments of a large governmental research and develop ment organization. BSA was found to be higher and to have significant effects for employees when departmental goals were unclear and technology was non-routine. Under these conditions, BSA was negatively related to role ambiguity and positively related to job satisfaction. Contrary to prior re search, this study found roles with high levels of BSA to have favorable aspects for their incumbents depending upon gorl clarity and type of technology of the parent organization. Implications for the management of research and development organizations are discussed.</t>
@@ -15645,7 +15845,11 @@
           <t>1975</t>
         </is>
       </c>
-      <c r="P295" s="8" t="n"/>
+      <c r="P295" s="8" t="inlineStr">
+        <is>
+          <t>The study measures individual-level boundary-spanning activity of professional R&amp;D employees using a self-reported survey. The items capture purposive boundary spanning behaviors, such as seeking information and advice from members of other organizations and transferring that information internally. The study provides a correlation table (Table II) with extractable zero-order correlations between boundary-spanning activity and outcomes like role conflict, role ambiguity, and dimensions of job satisfaction. It does not violate any exclusion criteria.. Verbatim Evidence: "This study was conducted in two departments of a large governmental R&amp;D organization. Questionnaires were distributed to the 88 professional employees of Department A. Fifty-eight questionnaires were returned (seven of these questionnaires were not usable). The actual sample of 51 respondents (respone rate = 58%) had an average age of 40 years... Seventy-seven of the 97 professional employees in Department B returned usable questionnaires... The BSA scale utilized in the present study concerned (a) sources of work-related information, and (b) contact with people outside and inside the R&amp;D organization. ... The following four items were used to measure boundary-spanning activity. ... 3. During the last month, indicate the frequency with which you have sought information/advice from members of other organizations outside (name of organization). ... TABLE II Correlations Between Boundary-Spanning Activity and Role and Job Satisfaction Variables"</t>
+        </is>
+      </c>
     </row>
     <row r="296" ht="18" customHeight="1" s="10">
       <c r="A296" t="inlineStr">
@@ -15658,6 +15862,14 @@
           <t>BSMA0293</t>
         </is>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F296" t="n">
+        <v>999</v>
+      </c>
       <c r="G296" t="inlineStr">
         <is>
           <t>The article reports on the importance of boundary-spanning roles (BSA), which serve to link organizations confirmed by research. They are vital to the effective monitoring of the environment as well as the transfer of technology and information across boundaries. Research has shown boundary-spanning activity (BSA) to have negative effects for their incumbents, such as higher rates of marginality. Marginality is defined as one's self-orientation when presented with two or more groups with conflicting value systems. Boundary spanning activity could be positively related to levels of role conflict and ambiguity or negatively related to levels of job satisfaction. Research is conducted to test to the theory of role dynamics in BSA.</t>
@@ -15683,7 +15895,11 @@
           <t>1975</t>
         </is>
       </c>
-      <c r="P296" s="8" t="n"/>
+      <c r="P296" s="8" t="inlineStr">
+        <is>
+          <t>The study collects quantitative survey data from individual professional employees (N=51) in a government R&amp;D organization. It measures boundary-spanning activity using a 4-item scale capturing purposive actions (e.g., seeking information/advice from other organizations) and provides zero-order correlations (Tables 1 and 2) with variables such as role conflict, role ambiguity, and job satisfaction. It passes all exclusion filters, as it operates at the individual level of analysis, focuses on interpersonal boundary spanning, and provides the necessary effect sizes.. Verbatim Evidence: "The study was conducted in an applied science department of a large government research and development organization. ... The sample of 51 professional employees (a 58 percent response rate) was similar to its population in age, work experience, and education. ... To measure the level of BSA, a four item scale was constructed based on items successfully used in prior research (1, 2, 4). ... (c) During the last month, indicate the frequency with which you have sought information/advice from members of other organizations outside (name of organization). (d) During the last month, indicate the frequency with which members of organizations outside (name of organization) have sought information/advice from you. ... Tables 1 and 2 report the results of a correlational analysis."</t>
+        </is>
+      </c>
     </row>
     <row r="297" ht="18" customHeight="1" s="10">
       <c r="A297" t="inlineStr">
@@ -15696,6 +15912,16 @@
           <t>BSMA0294</t>
         </is>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G297" t="inlineStr">
         <is>
           <t>In our study of an interactive marketing organization, we examine how members of different communities perform boundary-spanning coordination work in conditions of high speed, uncertainty, and rapid change. We find that members engage in a number of cross-boundary coordination practices that make their work visible and legible to each other, and that enable ongoing revision and alignment. Drawing on the notion of a “trading zone,” we suggest that by engaging in these practices, members enact a coordination structure that affords cross-boundary coordination while facilitating adaptability, speed, and learning. We also find that these coordination practices do not eliminate jurisdictional conflicts, and often generate problematic consequences such as the privileging of speed over quality, suppression of difference, loss of comprehension, misinterpretation and ambiguity, rework, and temporal pressure. After discussing our empirical findings, we explore their implications for organizations attempting to operate in the uncertain and rapidly changing contexts of postbureaucratic work.</t>
@@ -15721,7 +15947,11 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="P297" s="8" t="n"/>
+      <c r="P297" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative field study relying on interviews, observations, and document reviews to examine boundary-spanning coordination practices in a postbureaucratic organization. It employs inductive, qualitative analysis techniques and does not provide extractable quantitative effect sizes or a correlation matrix required for the meta-analysis.. Verbatim Evidence: "Our field study focused on the everyday project-based practices of members in one of Adweb's larger offices (110 employees), and was conducted over five months in 2001. Our data collection was exploratory in nature and included interviewing, observation, and review of documents and websites. [...] We used inductive, qualitative techniques to analyze the data (Agar 1980, Eisenhardt 1989, Glaser and Strauss 1967, Strauss and Corbin 1990), informed by our focus on practices, technology use, and consequences, while remaining alert to emerging ideas."</t>
+        </is>
+      </c>
     </row>
     <row r="298" ht="18" customHeight="1" s="10">
       <c r="A298" t="inlineStr">
@@ -15734,6 +15964,16 @@
           <t>BSMA0295</t>
         </is>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>2 = Non-employee samples</t>
+        </is>
+      </c>
       <c r="G298" t="inlineStr">
         <is>
           <t>Multiple project team membership is a prevalent phenomenon in modern organizational life. However, is any leadership behavior in such a setting beneficial to individual team members’ performance? Our study suggests that working in a multiple project team setting requires particular types of leadership. In an experimental design, we manipulated charismatic and boundary-spanning leadership behaviors in single and multiple team project settings and we studied their effects on project members’ performance. When workers are part of a single team, charismatic leadership enhances their performance to a greater extent than a boundary spanning leader. When members are part of two project teams concurrently, boundary-spanning leadership behavior becomes more beneficial for individual performance compared to charismatic leadership. The main theoretical contribution lies in the insight that different organizational project forms ask for different leadership behaviors to nurture individual performance. Practically, (future) project leaders must be prepared for operating in different project settings.</t>
@@ -15759,7 +15999,11 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="P298" s="8" t="n"/>
+      <c r="P298" s="8" t="inlineStr">
+        <is>
+          <t>The study uses an experimental sample of undergraduate students participating in a course-based simulation to measure the effects of boundary spanning leadership. According to Screening Rule 4, studies relying on student samples rather than organizational employees lack population validity for this meta-analysis and must be excluded under Code 2.. Verbatim Evidence: "Participants of the study were 118 undergraduate students (age MEAN = 21.55, with 91 females, 77 % of the sample) enrolled at a Dutch university, who were randomly assigned to project teams, as part of a course. In the simulation, participants experienced project work in a virtual MTM setting and were invited to write a reflection assignment based on it. [...] We chose a student sample for two main reasons. First, the set-up of the task (see Section 3.3) and the project teams are highly aligned with project team characteristics, and hence suitable for our study."</t>
+        </is>
+      </c>
     </row>
     <row r="299" ht="18" customHeight="1" s="10">
       <c r="A299" t="inlineStr">
@@ -15772,6 +16016,16 @@
           <t>BSMA0296</t>
         </is>
       </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G299" t="inlineStr">
         <is>
           <t>Purpose – This paper aims to enrich knowledge management theory and practice by investigating how boundary spanners’ willingness to share their knowledge contributes to innovation success and by examining the contingent role of market turbulence.</t>
@@ -15797,7 +16051,17 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P299" s="8" t="n"/>
+      <c r="P299" s="8" t="inlineStr">
+        <is>
+          <t>The study measures the 'willingness to share knowledge' of marketing managers (who are conceptualized as boundary spanners), rather than their actual boundary spanning behavior. The authors explicitly state that they 'do not measure their actual sharing behaviour'. Furthermore, the survey items for the independent variable measure general knowledge sharing intentions with a 'colleague' and do not specify any cross-departmental or external boundary, lacking construct validity for Boundary Spanning Behavior. Finally, the dependent variables (NPD innovativeness and performance) are measured at the firm level, making this a cross-level study without a valid individual-level BSB effect size.. Verbatim Evidence: "In this study, we focus on boundary spanners’ willingness to share their knowledge; thus, we do not measure their actual sharing behaviour. (p. 1075)
+Willingness to share knowledge: individual’s tendency to engage in tacit knowledge sharing behaviour (Holste and Fields, 2010) (reflective)
+(1 = fully disagree, 7 = fully agree)
+If requested to do so, I would allow my colleague to spend significant time observing and collaborating with me for him/her to better understand and learn from my work (0.88)
+I would willingly share with my colleague rules of thumb, tricks of the trade and other insights into the work of my office and that of the organisation that I have learned (0.98)
+I would willingly share my new ideas with my colleague (0.87) (p. 1081)
+Cross-sectional survey data were collected from 296 top income Hungarian firms. (p. 1061)"</t>
+        </is>
+      </c>
     </row>
     <row r="300" ht="18" customHeight="1" s="10">
       <c r="A300" t="inlineStr">
@@ -15810,6 +16074,14 @@
           <t>BSMA0297</t>
         </is>
       </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F300" t="n">
+        <v>999</v>
+      </c>
       <c r="G300" t="inlineStr">
         <is>
           <t>Purpose – Our paper examines how entrepreneurial leadership (EL) impacts firm export innovativeness via digital transformation and supply chain agility. Using the dynamic capability view theory, our paper also explores the moderating impact of leaders’ boundary-spanning behavior on the connection between EL and export innovativeness.</t>
@@ -15835,7 +16107,11 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="P300" s="8" t="n"/>
+      <c r="P300" s="8" t="inlineStr">
+        <is>
+          <t>The study measures leader boundary-spanning behavior (LBSB) of middle and senior managers in export-oriented firms. The construct captures individual-level, purposive boundary-spanning actions, satisfying the 'I' referent requirement for individual behavior rather than acting as a firm-level proxy. The study provides a zero-order correlation matrix with a sample of N = 244 independent managers, allowing for the extraction of effect sizes between LBSB and variables such as entrepreneurial leadership, digital transformation, and firm export innovativeness.. Verbatim Evidence: "Participants were drawn from the alumni network of a major public university in China. These individuals, occupying middle and senior management roles, were considered well-positioned to provide informed insights into their firms’ leadership behaviors, digital practices, and export strategies. ... The final sample comprised 244 matched and usable responses. ... LBSB was gauged by adapting a 6-item scale (α = 0.88) from Marrone et al. (2007). An example item is "I reach out to individuals outside of our organization who can offer expertise or ideas about the task at hand." ... Table 3. Summary statistics and correlations of observed variables ... 2. LBSB"</t>
+        </is>
+      </c>
     </row>
     <row r="301" ht="18" customHeight="1" s="10">
       <c r="A301" t="inlineStr">
@@ -15848,6 +16124,14 @@
           <t>BSMA0298</t>
         </is>
       </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F301" t="n">
+        <v>999</v>
+      </c>
       <c r="G301" t="inlineStr">
         <is>
           <t>Given the growing importance of B2B digital platform capabilities for competitive advantage, research on its antecedents and outcomes in the business-to-business context remains scarce. To address this gap, we built on dynamic capability theory to examine how B2B organizations’ digital platform capabilities contribute to sustainable positioning. Specifically, we examined the direct and indirect associations (via organizational knowledge depth, breadth, and agility) between digital platform capabilities and sustainable positioning. Additionally, we explored the moderating role of leader boundary-spanning behaviors in the relationship between digital platform capabilities and organizational knowledge depth and breadth. Our study based on two-source survey data from top management in Chinese manufacturing firms. The findings fully support all our proposed hypotheses. Digital platform capabilities significantly enhance sustainable positioning, both directly and through improved organizational knowledge depth, breadth, and agility. Furthermore, leader boundary-spanning behaviors strengthen the impact of digital platform capabilities on both knowledge depth and breadth. These insights offer practical implications for B2B firms seeking to leverage digital platform capabilities to enhance knowledge depth, breadth, agility, and sustainable market positioning.</t>
@@ -15873,7 +16157,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="P301" s="8" t="n"/>
+      <c r="P301" s="8" t="inlineStr">
+        <is>
+          <t>The study surveys top managers (CEOs, general managers, managing directors) of Chinese manufacturing firms and measures their 'leader boundary-spanning behavior'. The items for this construct use the 'I' referent (e.g., 'I reach out to individuals outside the organization...'), demonstrating that the managers are rating their own individual-level behavior. Since N = 365 managers corresponding to 365 firms, this perfectly aligns with the CEO/Top Management Team exception where individual-level BSB is validly measured (N=firms=N=leaders). A zero-order correlation matrix is provided in Table 1, yielding extractable effect sizes. Therefore, the study meets all inclusion criteria.. Verbatim Evidence: "We collected our study's data with the support of alumni of a Chinese public sector university who hold managerial positions in various Chinese manufacturing firms. ... Through the alumni, we were able to approach the top managers of 600 organizations (CEOs, general managers, and managing directors) to invite them to participate in our study. ... After matching the data from our two sample sources and different rounds, the final dataset we retained and used for data analysis pertained to 365 firms. ... We assessed leader boundary-spanning behavior by adapting six items (α = 0.96) from Ancona and Caldwell (1992). Sample item: “I reach out to individuals outside of our organization who can offer expertise or ideas.” ... Appendix A. Scale Items ... A.6. Leader boundary-spanning behavior LBBs1: I absorb outside pressures so that organizational members can work free of interference. LBBs4: I reach out to individuals outside the organization who can provide expertise or ideas. ... Table 1 Means and correlations."</t>
+        </is>
+      </c>
     </row>
     <row r="302" ht="18" customHeight="1" s="10">
       <c r="A302" t="inlineStr">
@@ -15886,6 +16174,16 @@
           <t>BSMA0299</t>
         </is>
       </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G302" t="inlineStr">
         <is>
           <t>Organizational behavior (OB) is an area of knowledge rather than a unified theory. It consists of a growing clutch of concepts, approaches, models, and tools pertinent to the structure and functioning of organizations within their socioeconomic contexts and of the study of individuals and groups within their organizational contexts [1]. Thus, OB spans para-organizational concerns such as interorganizational networks and delivery systems. It deals with macro-organizational phenomena-organizational goals, strategies, climates, cultures, structure, management styles, and performances-and how they are shaped by one another and by such contextual factors as operating environments, societal values and institutions, technology, size, dependence, and other</t>
@@ -15911,7 +16209,11 @@
           <t>1988</t>
         </is>
       </c>
-      <c r="P302" s="8" t="n"/>
+      <c r="P302" s="8" t="inlineStr">
+        <is>
+          <t>The article is a conceptual position paper proposing a research agenda and several hypotheses regarding organizational behavior in strategic organizations for social development. It does not conduct an empirical study, lacks a sample of organizational employees, and does not report any quantitative data or correlation matrices. Consequently, it contains no extractable effect sizes of interest for the meta-analysis.. Verbatim Evidence: "OB for Social Development: A Position Paper... The thesis of this paper is that OB can best contribute to socioeconomic development of the world's poorer societies by greater concentration on their strategic organizations... Some hypotheses are offered to stimulate research on strategic organizations: H1. The greater the emphasis on intrinsic motivators, the greater will be the mission accomplishment by the strategic organization."</t>
+        </is>
+      </c>
     </row>
     <row r="303" ht="18" customHeight="1" s="10">
       <c r="A303" t="inlineStr">
@@ -15924,6 +16226,16 @@
           <t>BSMA0300</t>
         </is>
       </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G303" t="inlineStr">
         <is>
           <t>Innovation and knowledge creation are processes, which require intensive collaboration of several people. Nevertheless, the constituents of successful collaboration in innovation activities are not well-known, and the understanding of the inherently social processes by which new intangibles are created is still in its infancy. This paper examines the key facilitators of innovation in knowledge-intensive group-level collaboration based on empirical evidence. The results demonstrate that social factors are highly influential for knowledge worker teams’ ability to produce innovations. Teams whose internal processes were characterised by trust, vision, aim for excellence, participative safety and support for innovation were likely to attain high levels of innovation. Team diversity based on highly visible attributes was found to be negatively related with team innovation. Surprisingly, also external collaboration seemed to affect team innovation outcomes negatively, except for when it was aimed at general scanning for ideas and information. In addition, the differences between the more and the less innovative teams arose mainly from differences in their internal interaction processes, rather than patterns of collaboration with people outside the team.</t>
@@ -15949,7 +16261,11 @@
           <t>2011</t>
         </is>
       </c>
-      <c r="P303" s="8" t="n"/>
+      <c r="P303" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates external boundary spanning activities (ambassadorial, task-coordinator, and scouting) based on Ancona and Caldwell (1990, 1992), but the unit of analysis is the team rather than the individual employee. All quantitative data, including the correlation matrix, are aggregated to and analyzed at the team level (N = 20 knowledge worker teams). Because the correlations represent team-level aggregated constructs, the study lacks individual-level effect sizes and must be excluded under Code 3.. Verbatim Evidence: "Respondents belonged to 20 teams. The team size ranged from 3–14 members (M = 5.30, SD = 2.66). ... Team level scores for the external activities were acquired by averaging individual members’ sum-scores for each team and dividing the score by number of items. ... Table 2 Pearson correlations among team innovation outcomes and other variables ... As the sample size was small (N = 20), it was necessary to combine independent variables into composites to avoid the risk of an overfit model."</t>
+        </is>
+      </c>
     </row>
     <row r="304" ht="18" customHeight="1" s="10">
       <c r="A304" t="inlineStr">
@@ -15962,6 +16278,16 @@
           <t>BSMA0301</t>
         </is>
       </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G304" t="inlineStr">
         <is>
           <t>Purpose – The purpose of this paper is to investigate how frontline service employees’ (FSEs) perceptions of corporate social responsibility (CSR) can enhance meaningful work perceptions as well as help alleviate FSEs’ perceptions of verbal dysfunctional customer behavior.</t>
@@ -15987,7 +16313,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P304" s="8" t="n"/>
+      <c r="P304" s="8" t="inlineStr">
+        <is>
+          <t>The study surveys frontline service employees (customer service representatives) who act as boundary spanners, but it does not quantitatively measure Boundary Spanning Behavior (BSB) as a construct. Instead, it measures employees' perceptions of corporate social responsibility (CSR), perceptions of verbal dysfunctional customer behavior, perceived task significance, emotional exhaustion, and job satisfaction. Consequently, there is no extractable effect size involving purposive interpersonal boundary spanning behaviors such as external representation, information gathering, or cross-boundary coordination, necessitating exclusion for lack of an effect size of interest.. Verbatim Evidence: "The conceptual model is empirically examined through a survey of 306 FSEs of a large insurance company in South Korea and tested via structural equation modeling... A seven-item scale measuring FSEs’ CSR perceptions was adapted from Berens et al. (2005), Lichtenstein et al. (2004) and Wagner et al. (2009)... Five items of FSEs’ perceptions of verbal dysfunctional customer behavior were adapted from Wang et al. (2011), McColl-Kennedy et al. (2009) and Karatepe et al. (2009a)... The five-item perceived task significance scale was adapted from Grant (2008)... Three items were adapted from Maslach and Jackson’s (1981) burnout scale to assess FSEs’ perceptions of emotional exhaustion. Finally, in order to capture job satisfaction, three measurement items from Homburg and Stock (2004) were adopted."</t>
+        </is>
+      </c>
     </row>
     <row r="305" ht="18" customHeight="1" s="10">
       <c r="A305" t="inlineStr">
@@ -16000,6 +16330,14 @@
           <t>BSMA0302</t>
         </is>
       </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
       <c r="G305" t="inlineStr">
         <is>
           <t>Leaders' positions as external brokers in organizational networks—those acting as a bridge between individuals outside the boundaries of their team—can enhance or constrain their effectiveness. Yet, whereas extant research on network brokerage views it as a private good whose benefits accrue directly to the broker, recent research suggests brokering between external communities can serve as both a public good as well as a public liability that can spillover to team members. We integrate network leadership theory with the externalities of network brokerage perspective to examine the countervailing effects of leaders' external brokerage in an information network with peer leaders and executives on team performance. In a sample of 465 team members in 80 teams distributed across 10 sister companies within one conglomerate, we used multilevel structural equation modeling to test our hypotheses. On one hand, we found that leader external brokerage was positively associated with team performance through team members' perceptions of organizational support; on the other hand, we found that leader brokerage is detrimental to team performance by compromising leaders' commitment to their teams. Our results suggest that, while leaders are encouraged to forge connections outside their team to harvest social capital benefits, there are both public benefits and liabilities of team leaders' external networks that can impact team performance.</t>
@@ -16025,7 +16363,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P305" s="8" t="n"/>
+      <c r="P305" s="8" t="inlineStr">
+        <is>
+          <t>The study measures boundary spanning behavior of team leaders (Leader BSB) using a network generator that asks about purposive actions ('seek work-related advice and information') from peer leaders and executives within and across companies in a conglomerate. This qualifies as valid intra-organizational Leader BSB based on network ties, aligning with the inclusion overrides. The sample consists of 80 teams with exactly one leader per team, invoking the N=Leaders=N=Teams exception, preserving statistical independence. A correlation matrix providing extractable effect sizes is reported in Table 1.. Verbatim Evidence: "We collected data from a small-sized industrial conglomerate in South Korea comprising 10 sister companies... Thus, there were 44 executives, 80 teams (ranging from 2 to 10 members), and 465 members in the final sample... We used a name generation technique to derive the composition of team leaders' information networks with their peer leaders and executives (Burt, 1992). Specifically, team leaders and executives were first asked to list peer leaders and executives (within their organizational subunit and in the larger conglomerate) from whom they 'seek work-related advice and information.'... To assess leader brokerage, we computed Gould and Fernandez's (1989) total brokerage metric in UCINET 6... Table 1 Means, standard deviations, and correlations"</t>
+        </is>
+      </c>
     </row>
     <row r="306" ht="18" customHeight="1" s="10">
       <c r="A306" t="inlineStr">
@@ -16038,6 +16380,14 @@
           <t>BSMA0303</t>
         </is>
       </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F306" t="n">
+        <v>999</v>
+      </c>
       <c r="G306" t="inlineStr">
         <is>
           <t>Purpose – The research aims to examine the impacts of two different types of goal orientation, i.e. leaning goal orientation (LGO) and performance-prove goal orientation (PPGO), on employee knowledge sharing, and whether these relationships are altered by leaders’ boundary spanning behavior (BSB).</t>
@@ -16063,7 +16413,11 @@
           <t>2023</t>
         </is>
       </c>
-      <c r="P306" s="8" t="n"/>
+      <c r="P306" s="8" t="inlineStr">
+        <is>
+          <t>The study quantitatively examines Leader Boundary Spanning Behavior (Leader BSB) rated by immediate subordinates, using Ancona and Caldwell's (1992) scale. This perfectly aligns with Screening Rule 1 (Leader BSB Override), which mandates the inclusion of cross-entity dyadic data where employees rate their supervisor's boundary spanning behavior. The study provides an extractable zero-order correlation matrix at the individual employee level.. Verbatim Evidence: "We collected data from fifteen companies located in South Korea, from industries of mainly financial services, consulting and IT service. [...] In total, 177 employees and 94 leaders returned their responses (89% of response rate). [...] Leader boundary spanning behavior (BSB). Leader BSB rated by his or her immediate subordinate was measured by using the 24-item scale developed by Ancona and Caldwell (1992). A sample item includes “My leader coordinates activities with external groups” (Cronbach alpha = 0.97). [...] Table 1. Descriptive statistics and correlations of the study variables"</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="18" customHeight="1" s="10">
       <c r="A307" t="inlineStr">
@@ -16076,6 +16430,14 @@
           <t>BSMA0304</t>
         </is>
       </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F307" t="n">
+        <v>999</v>
+      </c>
       <c r="G307" t="inlineStr">
         <is>
           <t>Purpose – The purpose of this research is to examine the positive relationship between leader’s boundaryspanning behavior and employee creative behavior. Moreover, the research investigates a three-way effect by exploring leader’s boundary-spanning behavior, need for status and creative self-efficacy on employee creative behavior.</t>
@@ -16101,7 +16463,11 @@
           <t>2022</t>
         </is>
       </c>
-      <c r="P307" s="8" t="n"/>
+      <c r="P307" s="8" t="inlineStr">
+        <is>
+          <t>This study examines the effect of leader boundary-spanning behavior on employee creative behavior. The sample consists of 260 supervisor-subordinate dyads from various companies in South Korea. The focal employees rated their leader's boundary-spanning behavior, while supervisors rated the employees' creative behavior. Under Screening Rule 1 (Leader BSB &amp; Cross-Entity Inclusion), studies measuring the boundary spanning behavior of a leader/manager as rated by their subordinates must be included. The construct is validly operationalized using Marrone et al.'s (2007) structural BSB items (e.g., reaching out to individuals outside the team). A zero-order correlation matrix is provided with an extractable effect size between leader boundary-spanning behavior and employee creative behavior (r = 0.20), with individual employees as the unit of analysis (N=260).. Verbatim Evidence: "We distributed pairs of survey packages to students enrolled in an executive MBA program at a university in South Korea. We collected data from various companies mainly manufacturing, finance and IT services... We initially had distributed questionnaires to 339 independent dyads and collected 267 dyads, giving a response rate of 79%. After matching the subordinate surveys with the corresponding supervisor surveys, a total of 260 pairs were used for final analyses... employee creative behavior was rated by the employees' direct supervisor while other variables (i.e. leader's boundary-spanning behavior, need for status, creative self-efficacy and control variables) were rated by the employees... Leader boundary-spanning behavior. We assessed leader’s boundary-spanning behavior using 6 items of Marrone et al.’s (2007). A sample item is, 'My team leader reaches out to individuals outside of our team that can provide project-related expertise or ideas'... Table 1. Means, standard deviations, reliabilities, and correlations for study variables... Note(s): N = 260."</t>
+        </is>
+      </c>
     </row>
     <row r="308" ht="18" customHeight="1" s="10">
       <c r="A308" t="inlineStr">
@@ -16114,6 +16480,14 @@
           <t>BSMA0305</t>
         </is>
       </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F308" t="n">
+        <v>999</v>
+      </c>
       <c r="G308" t="inlineStr">
         <is>
           <t>Purpose – Drawing on conservation of resources (COR) theory, this research aims to advance the current understanding of leader boundary spanning by examining its effect on task performance, psychological mechanism and boundary conditions.</t>
@@ -16139,7 +16513,11 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="P308" s="8" t="n"/>
+      <c r="P308" s="8" t="inlineStr">
+        <is>
+          <t>The study examines leader boundary spanning behavior as rated by subordinates (N=155 employee-supervisor dyads), which qualifies for inclusion under the Leader BSB override rule. Furthermore, it provides a full correlation matrix with the necessary quantitative effect sizes, including zero-order correlations between leader boundary spanning, self-efficacy, and task performance.. Verbatim Evidence: "The empirical data were gathered by a paper-and-pencil survey from 155 employee-supervisor dyads working in various industries. ... The employees were asked to evaluate their immediate supervisors’ boundary spanning behavior and abusive supervision, as well as their own self-efficacy and emotional exhaustion. ... Leader boundary spanning was evaluated using the 6-item measure developed by Marrone et al. (2007). The sample item is 'My supervisor acquires resources and access (e.g. access to information) for the team' (α = 0.94). ... Table 1. Descriptive statistics and correlations among variables"</t>
+        </is>
+      </c>
     </row>
     <row r="309" ht="18" customHeight="1" s="10">
       <c r="A309" t="inlineStr">
@@ -16151,6 +16529,14 @@
         <is>
           <t>BSMA0306</t>
         </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F309" t="n">
+        <v>999</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -16181,7 +16567,11 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="P309" s="8" t="n"/>
+      <c r="P309" s="8" t="inlineStr">
+        <is>
+          <t>The study measures the boundary-spanning roles (Gatekeeper and Champion) of R&amp;D project leaders, as rated by their subordinates. Although the data is aggregated at the team level (N=87 teams), there is exactly one leader per team. Under the 'Leader BSB Override' and 'N=Leaders=N=Teams Exception', this qualifies as valid individual-level boundary spanning leadership (BSL). The paper provides a Pearson correlation matrix (Table 3) that includes the zero-order correlations between the leader's boundary-spanning roles and team performance.. Verbatim Evidence: "One hundred and three project teams were sampled from three government-sponsored and three private R&amp;D organizations... only 87 project teams, comprising 503 professionals, were finally used for further data analysis, after excluding the teams which responded to less than four questionnaires. ... Roles of leader. A multi-item scale was developed to measure the role of R&amp;D project leader based on the literature review... About half of the team members, excluding the leader (on average 2.6 per team) were randomly chosen to rate the scale of leader roles and the individual scores were aggregated at the team level. ... Table 2. The results of factor analysis on the leader's role (N = 87) ... Champion ... Acquire supports and resources ... Coalition building for support ... Gatekeeper ... Contact with information sources ... Diffuse technical/market information ... Table 3. Number, mean, standard deviation, Pearson correlation and reliability"</t>
+        </is>
+      </c>
     </row>
     <row r="310" ht="18" customHeight="1" s="10">
       <c r="A310" t="inlineStr">
@@ -16194,6 +16584,16 @@
           <t>BSMA0307</t>
         </is>
       </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G310" t="inlineStr">
         <is>
           <t>The article examines the process of innovation and knowledge sharing from a perspective that focuses on the inﬂuence that local circumstances can have. In particular, it looks at the problems of knowledge sharing between groups of professionals. It presents a comparative analysis of two studies, one involving two groups of IT professionals; the other a network of healthcare professionals. The data was collected in two sets. The ﬁrst set consisted of the results from two earlier, independent studies; the second was collected speciﬁcally for this article. We investigate the role played by boundary objects and brokers. Through an analysis of the interplay between boundary object and broker, we uncover the dynamics of the innovation process and show that the role played by the broker can be political. We identify two strategies that are used by brokers in the selection of a boundary object. The ﬁrst is directed towards achieving a balance between the actors involved and the second is directed towards controlling their activities. We conclude by suggesting that other researchers should also consider the interplay between broker and boundary object when examining cross-boundary knowledge sharing.</t>
@@ -16219,7 +16619,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P310" s="8" t="n"/>
+      <c r="P310" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative comparative analysis based on two case studies involving interviews with IT professionals and healthcare professionals. It does not provide any quantitative data, correlation matrices, or extractable effect sizes (r) required for the meta-analysis.. Verbatim Evidence: "The data for our studies came from two separate cases. The first was a group of IT professionals from different companies in a French science park who collaborated to build a Content Management System; the second was a series of innovations produced by a pluridisciplinary network of heath care professionals in a medium-sized French city. ... The analysis followed what Denzin and Lincoln (2000) describe as a moderate inductive approach. ... All of the actors involved were interviewed several times at different points in the process; the interviews lasted from 30 to 90 min."</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="18" customHeight="1" s="10">
       <c r="A311" t="inlineStr">
@@ -16232,6 +16636,16 @@
           <t>BSMA0308</t>
         </is>
       </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G311" t="inlineStr">
         <is>
           <t>Work overload is a critical but understudied stressor at work, particularly for boundary-spanning positions. Recent studies have highlighted the need for more research on the identiﬁcation of different predictors of the use of intimidation, a type of assertive impression management tactic. Relying on Lazarus's transactional theory, this study hypothesized and investigated a mediated moderation model that includes resilience, work overload, and its outcomes.</t>
@@ -16257,7 +16671,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P311" s="8" t="n"/>
+      <c r="P311" s="8" t="inlineStr">
+        <is>
+          <t>The study surveys salespeople, who hold boundary-spanning positions, but it does not measure Boundary Spanning Behavior (BSB). The measured variables are work overload, perceived resilience, intimidation (an impression management tactic directed at coworkers), and supervisor-rated sales performance. Since it lacks a quantitative measure of purposive interpersonal boundary-spanning actions, there is no effect size of interest for this meta-analysis.. Verbatim Evidence: "Work overload is a critical but understudied stressor at work, particularly for boundary-spanning positions. ... The information provided by 248 employee-supervisor dyads confirmed the proposed model. Work overload has a positive association with intimidation, and the direct effect of work overload on intimidation depends on the level of an employee's resilience. ... Work overload. We assessed work overload with the five-item scale developed by Roberts, Lapidus, &amp; Chonko, 1997. ... Intimidation. The use of intimidation was measured with a five-item scale from Bolino and Turnley (1999). Sample items include 'Be intimidating with coworkers when it will help you get your job done' and 'Deal strongly or aggressively with coworkers who interfere in your business.'"</t>
+        </is>
+      </c>
     </row>
     <row r="312" ht="18" customHeight="1" s="10">
       <c r="A312" t="inlineStr">
@@ -16270,6 +16688,16 @@
           <t>BSMA0309</t>
         </is>
       </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G312" t="inlineStr">
         <is>
           <t>The aim of the present study conducted among 1,106 Finnish employees was to identify boundary management profiles based on cross-role interruption behaviors from work to nonwork and from nonwork to work. Adopting a person-oriented approach through latent profile analysis, five profiles were identified: Work Guardians (21% of the employees), Nonwork Guardians (14%), Integrators (25%), Separators (18%) and an Intermediate Group (22%). We then examined differences between these profiles with respect to recovery experiences (psychological detachment from work, relaxation, mastery experiences, and control during off-job time) and recovery outcomes (vigor and exhaustion). Work Guardians had the poorest situation in terms of recovery experiences and outcomes. Integrators came close to Work Guardians in their responses, but they showed better relaxation and control during off-job time. Nonwork Guardians and Separators had the most beneficial recovery experiences. The Intermediate Group scored near the average in all evaluations. Altogether the findings suggest that boundary management profiles play a significant role, especially regarding recovery experiences.</t>
@@ -16295,7 +16723,11 @@
           <t>2016</t>
         </is>
       </c>
-      <c r="P312" s="8" t="n"/>
+      <c r="P312" s="8" t="inlineStr">
+        <is>
+          <t>The study investigates boundary management between work and nonwork (i.e., work-family/personal life domains), measuring how individuals allow incursions from one role to another (e.g., taking care of family needs at work or responding to work-related communications during personal time). This measures Work-Life/Work-Family boundary management, not inter-organizational or intra-organizational boundary spanning behavior. Therefore, the paper lacks the target construct and effect sizes of interest.. Verbatim Evidence: "The aim of the present study conducted among 1,106 Finnish employees was to identify boundary management profiles based on cross-role interruption behaviors from work to nonwork and from nonwork to work. ... Both nonwork interrupting work behaviors (e.g., “I take care of personal or family needs during work”) and work interrupting nonwork behaviors (e.g., “I respond to work-related communications (e.g., emails, texts, and phone calls) during my personal time away from work”) were measured with three items each, which loaded most highly on the scales developed by Kossek et al. (2012)."</t>
+        </is>
+      </c>
     </row>
     <row r="313" ht="18" customHeight="1" s="10">
       <c r="A313" t="inlineStr">
@@ -16308,6 +16740,16 @@
           <t>BSMA0310</t>
         </is>
       </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G313" t="inlineStr">
         <is>
           <t>The school safety and security planning process is important because it directs the educational organization's ability to maintain a stable safe learning environment. For this study, continuous comparison of data and theory, and a cross-case analysis generated a grounded theory. This theory stated that: When the educational leader's perception of risk was malleable and well developed, the school safety and security planning process was more comprehensive. Enhancement occurred with the establishment of a systemic approach, and through inter-organizational collaboration with community stakeholders. These stakeholders included, but were not limited to, the departments of public health, mental health, medical care, emergency management, law enforcement, fire, homeland security, and transportation</t>
@@ -16333,7 +16775,11 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="P313" s="8" t="n"/>
+      <c r="P313" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study is a qualitative/mixed-methods multiple case study that reports data using frequencies and percentages, lacking a formal correlation matrix or extractable quantitative effect sizes (r) (Code 1). Furthermore, the unit of analysis is the school or school district (N=62 sites), where educational leaders serve as key informants regarding their organization's school safety and security planning process and inter-organizational collaboration, violating the individual-level analysis requirement (Code 3).. Verbatim Evidence: "A qualitative/mixed-methods study was designed to study the phenomenon. The methodological approach was a case study, including sixty-two sites, and three pilot sites. Data collection included: document analysis, interviews, surveys, and demographic information. Data analysis entailed constant development and verification of hypotheses about relationships among categories from the collected data from each site using coding, emerging categories, data reduction, and interpretation. (Page 13) ... The sample consisted of forty-seven public school districts and eighteen non public schools. The educational leaders for this study consisted of public school district superintendents and non public school leaders of the above mentioned sample. (Page 89) ... Table 2: Overall Average Percentages for the Categories of Minimal Process, Evolving Process, and Exemplary Process for All Sites (N = 62) (Page 108)"</t>
+        </is>
+      </c>
     </row>
     <row r="314" ht="18" customHeight="1" s="10">
       <c r="A314" t="inlineStr">
@@ -16346,6 +16792,16 @@
           <t>BSMA0311</t>
         </is>
       </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G314" t="inlineStr">
         <is>
           <t>There is a vast amount of literature and research on network management strategies. However, only a limited portion of this literature examines the relationship between network management strategies and outcomes (for an exception see Meier and O’Toole 2001) Most of the research focuses on managerial activity or networking rather than on the question of which types of strategies matter the most for outcomes of complex processes in networks. This paper attempts to address the question of whether managerial strategies matter for outcomes and also explores which types of strategies have an effect on outcomes.</t>
@@ -16371,7 +16827,11 @@
           <t>2010</t>
         </is>
       </c>
-      <c r="P314" s="8" t="n"/>
+      <c r="P314" s="8" t="inlineStr">
+        <is>
+          <t>[Code 1 &amp; Code 3] The study violates two inclusion criteria. First (Code 3), the unit of analysis is the project/network rather than the individual employee. Respondents act as key informants reporting on the network management strategies employed within a specific environmental project and the project's overall outcomes, not their own interpersonal boundary spanning behavior. Second (Code 1), the paper only reports OLS regression results (beta coefficients) and does not provide a zero-order correlation matrix or extractable bivariate effect sizes (r).. Verbatim Evidence: "This article investigates the effects of network management strategies on perceived outcomes in governance networks. The research is based on a survey conducted in 2006-2007 where 337 responses to a questionnaire were received by individuals involved in environmental projects in The Netherlands... Each respondent was asked to answer the questions with a specific environmental project in mind... Table I. Measurements of outcomes... Do you think that the involved actors have contributed substantively to the management of the project?... To measure the number of strategies employed (an important variable in Hypothesis 1), the sixteen items measuring the strategies were first dichotomized6, and then the number of strategies that were actually used in the project were counted. [Note: No correlation matrix is provided in the manuscript; only OLS regression coefficients in Tables 5-8]."</t>
+        </is>
+      </c>
     </row>
     <row r="315" ht="18" customHeight="1" s="10">
       <c r="A315" t="inlineStr">
@@ -16384,6 +16844,16 @@
           <t>BSMA0312</t>
         </is>
       </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G315" t="inlineStr">
         <is>
           <t>As much as prior research has shed light on the boundary-spanning processes of global organizations and their (positive) impact on an MNC’s performance, whether, when and how past performance ultimately shapes an MNC’s boundary-spanning activities remains an open question in management research. To tackle these questions, we examine the behaviour of technology scouts in global organizations who span organizational and national boundaries to tap into novel knowledge and span internal boundaries to present this knowledge to constituents inside the MNC. Drawing on the behavioural theory of the ﬁrm, we propose that the intensity of organizational boundary spanning, the likelihood of spanning national boundaries and the way technology scouts span internal boundaries to engage with members inside the organization are sensitive to how the MNC has performed relative to its aspirations. We support our theoretical expositions with insights gained from interviewing senior industry professionals with direct experience in technology scouting in MNCs.</t>
@@ -16409,7 +16879,11 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="P315" s="8" t="n"/>
+      <c r="P315" s="8" t="inlineStr">
+        <is>
+          <t>The paper develops theoretical propositions about how performance feedback affects the boundary-spanning behaviour of technology scouts and supports its arguments using qualitative data from 15 in-depth interviews with senior industry professionals. The study does not provide quantitative data, formal correlation matrices, or extractable zero-order effect sizes (r) required for the meta-analysis.. Verbatim Evidence: "To tackle these questions, we draw upon the behavioural theory of the firm (BTF) and propose that the boundary-spanning behaviours of technology scouts are sensitive to how the MNC has performed relative to its aspirations... We support our theoretical expositions with insights gained from interviewing senior industry professionals with direct experience in technology scouting in MNCs. [...] Specifically, between 2011–15, we conducted 15 in-depth interviews with managers in European and North American MNCs (including Bayer, Johnson &amp; Johnson, Merck &amp; Co, and Novo Nordisk) on the MNCs’ sites, at technology conferences such as the Wharton Mack Institute’s Technology Conference or via phone."</t>
+        </is>
+      </c>
     </row>
     <row r="316" ht="18" customHeight="1" s="10">
       <c r="A316" t="inlineStr">
@@ -16422,6 +16896,16 @@
           <t>BSMA0313</t>
         </is>
       </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G316" t="inlineStr">
         <is>
           <t>The authors address the growing call for research into the management of supply networks serving the public sector. Building on prior action research, this empirical paper focuses on the management of supply in interorganizational, health sector networks identifying the competence requirements (skills, knowledge, traits, and behavioural indicators) associated with effective team performance. Drawing on empirical data, the authors present a competence framework that aims to capture a team’s tacit understanding of strategic supply management. Competence indicators are organized into six themes: network understanding; developing network position; relationship management; learning, knowledge and knowledge management; strategy formulation; strategy implementation. Finally, the relevance of the framework to boundary spanning personnel outside the purchasing function and to other organizations is considered.</t>
@@ -16447,7 +16931,11 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="P316" s="8" t="n"/>
+      <c r="P316" s="8" t="inlineStr">
+        <is>
+          <t>The study is qualitative, relying on semi-structured interviews with over 20 managers and purchasing personnel to develop a team competence framework. It does not provide quantitative data, a correlation matrix, or any extractable zero-order effect sizes of interest.. Verbatim Evidence: "Semi-structured interviews were conducted with over 20 managers and purchasing personnel in the focal organization, many, but not all, of whom were working in teams that were considered to be capable of strategic supply management. ... Data were analysed for all references to skills, knowledge, traits, behavioural indicators and outcomes associated with effective and ineffective performance. Over 250 items of data were identified. These were constructed into a framework describing the features of high performance, which was then critically reviewed by a small group of managers"</t>
+        </is>
+      </c>
     </row>
     <row r="317" ht="18" customHeight="1" s="10">
       <c r="A317" t="inlineStr">
@@ -16460,6 +16948,16 @@
           <t>BSMA0314</t>
         </is>
       </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>5 = Multiple reasons (specify in Notes)</t>
+        </is>
+      </c>
       <c r="G317" t="inlineStr">
         <is>
           <t>Entrepreneurial teams often struggle with simultaneous task and team challenges at an early stage of new venture creation. The way in which teams shape their teamwork is key in leveraging performance in the pre‐founding phase. Learning should help the team in establishing good teamwork and in expanding its members’ entrepreneurial capabilities. Leadership is needed to facilitate and guide this learning. Accordingly, we investigated learning and leadership as facilitators of performance in the pre‐founding phase. Specifically, we examined team reflexivity as a collective internal learning process and boundary spanning behaviour as an externally directed individual activity, operating at different levels in fostering team and individual performance. Charismatic team leadership was examined as a catalyst of learning, shaping team and individual performance ultimately. The multilevel mediation model was tested based on data from 196 members of 58 teams of a venture creation programme. Team reflexivity predicted team and individual performance. Boundary spanning behaviour was not related to performance. As hypothesised, charismatic team leadership predicted team and individual performance, both mediated by team reflexivity. This research highlights the relevance of team learning in pre‐founding teams and emphasises leadership in shaping learning and moving new ventures forward.</t>
@@ -16485,7 +16983,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P317" s="8" t="n"/>
+      <c r="P317" s="8" t="inlineStr">
+        <is>
+          <t>The study sample consists of pre-founding entrepreneurial teams (nascent founders) participating in a venture creation program with an average age of 23.8 years, which violates the requirement for an organizational employee sample [Code 2]. Additionally, although boundary spanning behavior was measured at the individual level, the only provided correlation matrix (Table 1) represents team-level aggregated constructs (N = 58 teams), with no individual-level correlations reported. This violates the individual-level analysis requirement and prevents the extraction of an individual-level zero-order correlation [Code 3].. Verbatim Evidence: "We studied teams who participated in a venture creation programme that combines education and incubation... Participants (23.5% female) were on average 23.8 years old (SD = 3.2). Their background was mainly in computer science (25.5%), engineering (19.7%), and business administration (19.4%).... TABLE 1: Descriptives and Intercorrelations of Study Variables on the Team Level... Note: N = 58 teams. Age of the team leader was available for N = 55 teams only. Gender: 0 = male, 1 = female. Correlations are given using pairwise exclusion. Individual-level variables were aggregated to the team level.... Boundary Spanning Behaviour. Following our theoretical conceptualisation, we operationalised boundary spanning behaviour on the individual level. We chose four of the twelve original items by Ancona and Caldwell (1992) to assess ambassador activities and three of the four items to assess scout activities of each individual team member, excluding the lead entrepreneur"</t>
+        </is>
+      </c>
     </row>
     <row r="318" ht="18" customHeight="1" s="10">
       <c r="A318" t="inlineStr">
@@ -16498,6 +17000,16 @@
           <t>BSMA0315</t>
         </is>
       </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G318" t="inlineStr">
         <is>
           <t>The omnichannel varies across countries due to different retail environments and retailers’ growth strategies. The Japanese big retailers’ omnichannel can be characterized by having multiple retail formats, such as department stores, general merchandise stores, convenience stores, specialty stores, Internet stores, and so on. They have grown by multiplying retail formats to appeal to different customer segments, and they have unique challenges in managing an omnichannel with many retail formats. These are (1) extremely wide variety of merchandise, (2) enormous quantity of data from transaction, inventory, logistics, and customers, (3) different organization structures and management, and (4) unique organizational capabilities in each retail format. From these challenges, we could propose further research issues as follows: (1) theoretical consideration of boundary-spanning functions among retail formats, (2) international comparative analysis reflecting the different conditions in each country, and (3) clarifying the characteristics of the omnichannel shopper in the Japanese omnichannel environment.</t>
@@ -16523,7 +17035,11 @@
           <t>2018</t>
         </is>
       </c>
-      <c r="P318" s="8" t="n"/>
+      <c r="P318" s="8" t="inlineStr">
+        <is>
+          <t>The paper is a conceptual note discussing the challenges of omnichannel management in Japanese retail corporate groups. It does not report an empirical study, lacks a sample of organizational employees, and provides no extractable quantitative effect sizes or correlation matrix.. Verbatim Evidence: "We propose several further research issues from the discussion so far... First, the Japanese omnichannel with multiple retail formats impose on retailers a question of how to overcome organizational silos, and effectively allocate resources and capabilities at the corporate group level. What is critical is boundary spanning across the retail formats to smoothly implement its omnichannel strategy. So, it is important to theoretically consider boundary spanning functions in Japanese omnichannel retailing."</t>
+        </is>
+      </c>
     </row>
     <row r="319" ht="18" customHeight="1" s="10">
       <c r="A319" t="inlineStr">
@@ -16536,6 +17052,16 @@
           <t>BSMA0316</t>
         </is>
       </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G319" t="inlineStr">
         <is>
           <t>This article makes a further contribution to opening the ‘black box’ of micropractices in ministry–agency relationships. We argue that the mechanisms that come into play in the course of institutionalizing agencification reforms – such as renegotiating mutual roles and rules in ministry–agency interactions – are only poorly covered in the existing literature. To adequately address the negotiated and contingent nature of de facto agency autonomy and political control, we develop an interpretive approach based on the concept of ‘boundary work’. The empirical focus is on ministry–agency interactions at the science–policy nexus in the contested policy field of food safety. By studying actors' stories about the institutionalization processes following the fundamental reorganization of the German food safety administration in the wake of the               BSE               crisis from a longitudinal perspective, we show how actors manage boundary conflicts via increasingly differentiated backstage coordination.</t>
@@ -16561,7 +17087,11 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="P319" s="8" t="n"/>
+      <c r="P319" s="8" t="inlineStr">
+        <is>
+          <t>The study is a qualitative narrative analysis that investigates the institutionalization of ministry-agency relationships at the science-policy nexus in German food safety policy. It relies entirely on qualitative data from semi-structured expert interviews and document analysis. As a qualitative study, it does not provide any extractable quantitative effect sizes (r) or formal correlation matrices, thus failing the Data Extractability Gate.. Verbatim Evidence: "Methodically, we draw on narrative data from semi-structured, personal expert interviews conducted with various members of the organizations involved. [...] We conducted 23 semi-structured expert interviews from June 2011 to August 2012, which lasted from 45 to 120 minutes. They were all fully and precisely transcribed with advanced rules including cross talk and long pauses."</t>
+        </is>
+      </c>
     </row>
     <row r="320" ht="18" customHeight="1" s="10">
       <c r="A320" t="inlineStr">
@@ -16574,6 +17104,14 @@
           <t>BSMA0317</t>
         </is>
       </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F320" t="n">
+        <v>999</v>
+      </c>
       <c r="G320" t="inlineStr">
         <is>
           <t>Creativity is essential for research and development efforts. Unfortunately, little is known about how the role of team leaders determines the team’s creativity. Based on a sample of 39 engineering design teams in the space industry, this study examines the effects of leader position within different ﬂows of communication on team creativity. The results indicate that the balance between holding a central or a peripheral position indeed determines the creativity of such teams. Speciﬁcally, very central and very peripheral positions of team leaders within the work-ﬂow and awareness network hamper team creativity, whereas peripheral situated team leaders within the information network propel the creativity. In addition, team leaders stimulate creativity when they stay central in the external information network. In managerial terms, the analyses implicate that stimulating engineering design team creativity requires team leaders to smartly limit their involvement in communication and mainly act as gatekeepers to external sources of information.</t>
@@ -16599,7 +17137,11 @@
           <t>2008</t>
         </is>
       </c>
-      <c r="P320" s="8" t="n"/>
+      <c r="P320" s="8" t="inlineStr">
+        <is>
+          <t>The study collects data from 39 engineering design teams in the space industry. It measures 'Leader boundary-spanning capacity' by asking team leaders how often they exchange information and knowledge with other engineering design teams within their consortia. Because there is exactly one distinct leader per team (N = 39 teams and N = 39 leaders), the leader's boundary-spanning capacity represents a valid individual-level BSB construct. Under the N=Leaders=N=Teams exception, the study is not excluded under Code 3, despite the dependent variable (creativity) being measured at the team level. A zero-order correlation (r = 0.39) between leader boundary-spanning capacity and creativity is provided. Therefore, the study is included.. Verbatim Evidence: "To explore the social structure of leadership and creativity in engineering design teams, we collected data on 39 engineering design teams with 321 team members engaged in the space industry around the globe in 17 countries. [...] In order to do so we randomly selected one team for each team leader responsible for more than one team. [...] The external communication network was addressed using the following question: On average, how often do you exchange information and knowledge with members of other engineering design teams within your instrument consortia? [...] The degree to which the team leaders are linked to other teams describes their external centrality or boundary-spanning capacity. [...] Table 2 Descriptives and correlations: main variables (n = 39). [...] 6. Leader boundary-spanning capacity [...] Correlation with 1. Creativity: 0.39**"</t>
+        </is>
+      </c>
     </row>
     <row r="321" ht="18" customHeight="1" s="10">
       <c r="A321" t="inlineStr">

--- a/BSMA_AI_Run_Validation3.xlsx
+++ b/BSMA_AI_Run_Validation3.xlsx
@@ -17154,6 +17154,16 @@
           <t>BSMA0318</t>
         </is>
       </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>1 = No effect size of interest</t>
+        </is>
+      </c>
       <c r="G321" t="inlineStr">
         <is>
           <t>This paper examines the managerial issues involved in executing technology-based projects that span international borders. The results of a bilateral comparative field study, conducted in Brazil and the United States, show that in spite of considerable social and cultural differences between two international operating environments, successful integration of multinational projects may not require fundamentally different management approaches. This, however, does require strong senior management support and efforts in developing effective organizational linkages and alliances. Managers must need to have focus on cross-boundary relationships and fine-tune their people skills to deal effectively with complex forms of negotiations, delegations, and commitments in systems which are often weak on formal command and control.</t>
@@ -17179,7 +17189,11 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="P321" s="8" t="n"/>
+      <c r="P321" s="8" t="inlineStr">
+        <is>
+          <t>The study does not measure boundary spanning behavior (BSB). Instead, it focuses on assessing the perceived importance and effectiveness of 'managerial conditioning practices' (such as project leadership, work design and delegation, management support, and communications) in multinational project environments. Additionally, the paper does not provide a correlation matrix or any extractable quantitative effect sizes (r) related to BSB.. Verbatim Evidence: "The objective was to gain insight into: 1) the effectiveness of management practices involving multinational projects and 2) possible methods for strengthening the managerial process involving multinational project integration... We have labeled these eight sets of measures, which are critical to project success, managerial conditioning practices (MCP’s). They are listed below and briefly described in Table I. MCP1 Project leadership. MCP2 Work design and delegation. MCP3 Management support. MCP4 Communications. MCP5 Work challenge. MCP6 Personal drive and motivation. MCP7 Minimum conflict, risk, and threats. MCP8 Personal appraisals and awards... The questionnaire was designed to measure the perceived: 1) importance and 2) effectiveness of each of the eight classes of MCP’s."</t>
+        </is>
+      </c>
     </row>
     <row r="322" ht="18" customHeight="1" s="10">
       <c r="A322" t="inlineStr">
@@ -17192,6 +17206,16 @@
           <t>BSMA0319</t>
         </is>
       </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>3 = Non-individual level</t>
+        </is>
+      </c>
       <c r="G322" t="inlineStr">
         <is>
           <t>Purpose – This study investigates the relationship between buyer-supplier top management team (TMT) demographic misalignment (defined as differences in TMT composition based on background, age and gender) and environmental performance (EVP).</t>
@@ -17217,7 +17241,11 @@
           <t>2020</t>
         </is>
       </c>
-      <c r="P322" s="8" t="n"/>
+      <c r="P322" s="8" t="inlineStr">
+        <is>
+          <t>The study conducts analysis at the firm/dyad level (7,493 buyer-supplier dyad-year observations) rather than the individual employee level. It examines the demographic misalignment (functional background, age, gender) between the Top Management Teams (TMTs) of buyer and supplier firms and its impact on the firm's environmental performance. Since it does not measure individual-level interpersonal boundary spanning behavior, it is excluded under the macro-level/non-individual level guardrail.. Verbatim Evidence: "The empirical setting is publicly held U.S. manufacturing firms that are present in KLD’s annual EVP ratings, the WRDS Compustat database and Bloomberg’s SPLC database. ... The analysis is performed at the level of the buyer-supplier dyad, meaning that each observation is a buyer-supplier pair. In total there are 7,493 dyad-year observations for a seven-year period, 2009 through 2015."</t>
+     